--- a/VerveStacks_ITA_grids/vt_vervestacks_ITA_v1.xlsx
+++ b/VerveStacks_ITA_grids/vt_vervestacks_ITA_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D9E62C8F-884B-4F6E-81B4-403844BF3429}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{5A7D8AF7-A579-4184-B0F0-5E7F845C348F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{963E0C0B-327F-47D9-970B-E328F40CEECC}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{52B53332-5EBC-4CDE-AB20-E695A1176B37}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="2" r:id="rId1"/>
@@ -81,30 +81,30 @@
     <t>bioenergy</t>
   </si>
   <si>
+    <t>e_w108020416-380</t>
+  </si>
+  <si>
+    <t>e_w84696559-380</t>
+  </si>
+  <si>
     <t>e_w81938081-380</t>
   </si>
   <si>
+    <t>e_w144005863-380</t>
+  </si>
+  <si>
+    <t>e_w58440884-380</t>
+  </si>
+  <si>
     <t>e_w109756016-380</t>
   </si>
   <si>
-    <t>e_w108020416-380</t>
+    <t>e_w98902899-380</t>
   </si>
   <si>
     <t>e_w34157795-380</t>
   </si>
   <si>
-    <t>e_w98902899-380</t>
-  </si>
-  <si>
-    <t>e_w58440884-380</t>
-  </si>
-  <si>
-    <t>e_w84696559-380</t>
-  </si>
-  <si>
-    <t>e_w144005863-380</t>
-  </si>
-  <si>
     <t>ep_bioenergy_G100000200236</t>
   </si>
   <si>
@@ -141,18 +141,18 @@
     <t>coal</t>
   </si>
   <si>
+    <t>e_w409439916-380</t>
+  </si>
+  <si>
+    <t>e_w418902800-380</t>
+  </si>
+  <si>
+    <t>e_w303915533-380</t>
+  </si>
+  <si>
     <t>e_w82767145-380</t>
   </si>
   <si>
-    <t>e_w303915533-380</t>
-  </si>
-  <si>
-    <t>e_w409439916-380</t>
-  </si>
-  <si>
-    <t>e_w418902800-380</t>
-  </si>
-  <si>
     <t>ep_coal_subcritical_G100000102764</t>
   </si>
   <si>
@@ -189,96 +189,96 @@
     <t>gas</t>
   </si>
   <si>
+    <t>e_w60725875-380</t>
+  </si>
+  <si>
+    <t>e_w338753171-380</t>
+  </si>
+  <si>
+    <t>e_w107438024-380</t>
+  </si>
+  <si>
+    <t>e_w411026199-380</t>
+  </si>
+  <si>
+    <t>e_w162960205-380</t>
+  </si>
+  <si>
+    <t>e_w82078641-380</t>
+  </si>
+  <si>
+    <t>e_w61157826-380</t>
+  </si>
+  <si>
+    <t>e_w1137611914-380</t>
+  </si>
+  <si>
+    <t>e_w145665799-380</t>
+  </si>
+  <si>
+    <t>e_w133601335-380</t>
+  </si>
+  <si>
+    <t>e_w103381531-380</t>
+  </si>
+  <si>
+    <t>e_w199675964-380</t>
+  </si>
+  <si>
+    <t>e_w432729521-380</t>
+  </si>
+  <si>
+    <t>e_w172302572-380</t>
+  </si>
+  <si>
+    <t>e_w99826025-380</t>
+  </si>
+  <si>
+    <t>e_w416989699-380</t>
+  </si>
+  <si>
+    <t>e_w339104227-380</t>
+  </si>
+  <si>
+    <t>e_w98900549-380</t>
+  </si>
+  <si>
     <t>e_w162828577-380</t>
   </si>
   <si>
+    <t>e_w110330925-380</t>
+  </si>
+  <si>
+    <t>e_w98421779-380</t>
+  </si>
+  <si>
+    <t>e_w116797658-380</t>
+  </si>
+  <si>
+    <t>e_w59462715-380</t>
+  </si>
+  <si>
+    <t>e_w421827453-380</t>
+  </si>
+  <si>
+    <t>e_w82084019-380</t>
+  </si>
+  <si>
+    <t>e_w110138220-380</t>
+  </si>
+  <si>
     <t>e_w100407576-380</t>
   </si>
   <si>
-    <t>e_w411026199-380</t>
-  </si>
-  <si>
-    <t>e_w416989699-380</t>
-  </si>
-  <si>
-    <t>e_w133601335-380</t>
-  </si>
-  <si>
-    <t>e_w103381531-380</t>
-  </si>
-  <si>
-    <t>e_w98900549-380</t>
-  </si>
-  <si>
-    <t>e_w110330925-380</t>
-  </si>
-  <si>
-    <t>e_w98421779-380</t>
-  </si>
-  <si>
-    <t>e_w172302572-380</t>
-  </si>
-  <si>
-    <t>e_w116797658-380</t>
-  </si>
-  <si>
     <t>e_w414663585-380</t>
   </si>
   <si>
     <t>e_w105581403-380</t>
   </si>
   <si>
-    <t>e_w339104227-380</t>
-  </si>
-  <si>
-    <t>e_w99826025-380</t>
-  </si>
-  <si>
-    <t>e_w432729521-380</t>
-  </si>
-  <si>
     <t>e_w103653592-380</t>
   </si>
   <si>
-    <t>e_w199675964-380</t>
-  </si>
-  <si>
-    <t>e_w82078641-380</t>
-  </si>
-  <si>
-    <t>e_w61157826-380</t>
-  </si>
-  <si>
-    <t>e_w1137611914-380</t>
-  </si>
-  <si>
-    <t>e_w338753171-380</t>
-  </si>
-  <si>
-    <t>e_w162960205-380</t>
-  </si>
-  <si>
-    <t>e_w60725875-380</t>
-  </si>
-  <si>
-    <t>e_w107438024-380</t>
-  </si>
-  <si>
-    <t>e_w145665799-380</t>
-  </si>
-  <si>
-    <t>e_w82084019-380</t>
-  </si>
-  <si>
-    <t>e_w59462715-380</t>
-  </si>
-  <si>
-    <t>e_w421827453-380</t>
-  </si>
-  <si>
-    <t>e_w110138220-380</t>
-  </si>
-  <si>
     <t>ep_gas_combined_cycle_G100000400339</t>
   </si>
   <si>
@@ -1044,69 +1044,69 @@
     <t>hydro</t>
   </si>
   <si>
+    <t>e_IT72-400</t>
+  </si>
+  <si>
+    <t>e_IT72-380</t>
+  </si>
+  <si>
+    <t>e_IT93-380</t>
+  </si>
+  <si>
+    <t>e_w491424937-380</t>
+  </si>
+  <si>
+    <t>e_w75602396-380</t>
+  </si>
+  <si>
+    <t>e_IT10-380</t>
+  </si>
+  <si>
+    <t>e_IT71-380</t>
+  </si>
+  <si>
+    <t>e_w61626687-380</t>
+  </si>
+  <si>
+    <t>e_w72466334-380</t>
+  </si>
+  <si>
+    <t>e_w82083756-380</t>
+  </si>
+  <si>
+    <t>e_IT71-400</t>
+  </si>
+  <si>
     <t>e_w1100665914-380</t>
   </si>
   <si>
+    <t>e_w114931087-380</t>
+  </si>
+  <si>
+    <t>e_IT21-380</t>
+  </si>
+  <si>
+    <t>e_w116517585-380</t>
+  </si>
+  <si>
+    <t>e_IT36-380</t>
+  </si>
+  <si>
+    <t>e_IT53-380</t>
+  </si>
+  <si>
+    <t>e_IT31-380</t>
+  </si>
+  <si>
+    <t>e_w104359058-380</t>
+  </si>
+  <si>
+    <t>e_w64200868-380</t>
+  </si>
+  <si>
     <t>e_IT7-380</t>
   </si>
   <si>
-    <t>e_w116517585-380</t>
-  </si>
-  <si>
-    <t>e_IT72-380</t>
-  </si>
-  <si>
-    <t>e_IT72-400</t>
-  </si>
-  <si>
-    <t>e_IT93-380</t>
-  </si>
-  <si>
-    <t>e_w491424937-380</t>
-  </si>
-  <si>
-    <t>e_w75602396-380</t>
-  </si>
-  <si>
-    <t>e_IT71-380</t>
-  </si>
-  <si>
-    <t>e_w61626687-380</t>
-  </si>
-  <si>
-    <t>e_IT10-380</t>
-  </si>
-  <si>
-    <t>e_IT31-380</t>
-  </si>
-  <si>
-    <t>e_w104359058-380</t>
-  </si>
-  <si>
-    <t>e_w64200868-380</t>
-  </si>
-  <si>
-    <t>e_w72466334-380</t>
-  </si>
-  <si>
-    <t>e_IT36-380</t>
-  </si>
-  <si>
-    <t>e_IT53-380</t>
-  </si>
-  <si>
-    <t>e_IT21-380</t>
-  </si>
-  <si>
-    <t>e_w82083756-380</t>
-  </si>
-  <si>
-    <t>e_IT71-400</t>
-  </si>
-  <si>
-    <t>e_w114931087-380</t>
-  </si>
-  <si>
     <t>ep_hydro_dam_G100000602220</t>
   </si>
   <si>
@@ -1905,12 +1905,12 @@
     <t>solar</t>
   </si>
   <si>
+    <t>elc_spv-ITA_0042</t>
+  </si>
+  <si>
     <t>elc_spv-ITA_0068</t>
   </si>
   <si>
-    <t>elc_spv-ITA_0042</t>
-  </si>
-  <si>
     <t>elc_spv-ITA_0030</t>
   </si>
   <si>
@@ -2532,12 +2532,12 @@
     <t>elc_won-ITA_0096</t>
   </si>
   <si>
+    <t>elc_won-ITA_0022</t>
+  </si>
+  <si>
     <t>elc_won-ITA_0073</t>
   </si>
   <si>
-    <t>elc_won-ITA_0022</t>
-  </si>
-  <si>
     <t>ep_windon_wind_010</t>
   </si>
   <si>
@@ -2967,28 +2967,34 @@
     <t>ele</t>
   </si>
   <si>
+    <t>Aggregated Plant - EMBER Gap - way/81938081-380_Missing Bioenergy Capacity</t>
+  </si>
+  <si>
+    <t>GW</t>
+  </si>
+  <si>
+    <t>TWh</t>
+  </si>
+  <si>
+    <t>daynite</t>
+  </si>
+  <si>
+    <t>yes</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/34157795-380_Missing Bioenergy Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/58440884-380_Missing Bioenergy Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/84696559-380_Missing Bioenergy Capacity</t>
+  </si>
+  <si>
     <t>Aggregated Plant - EMBER Gap - way/108020416-380_Missing Bioenergy Capacity</t>
   </si>
   <si>
-    <t>GW</t>
-  </si>
-  <si>
-    <t>TWh</t>
-  </si>
-  <si>
-    <t>daynite</t>
-  </si>
-  <si>
-    <t>yes</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/81938081-380_Missing Bioenergy Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/58440884-380_Missing Bioenergy Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/34157795-380_Missing Bioenergy Capacity</t>
+    <t>Aggregated Plant - EMBER Gap - way/98902899-380_Missing Bioenergy Capacity</t>
   </si>
   <si>
     <t>Aggregated Plant - EMBER Gap - way/144005863-380_Missing Bioenergy Capacity</t>
@@ -2997,12 +3003,6 @@
     <t>Aggregated Plant - EMBER Gap - way/109756016-380_Missing Bioenergy Capacity</t>
   </si>
   <si>
-    <t>Aggregated Plant - EMBER Gap - way/98902899-380_Missing Bioenergy Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/84696559-380_Missing Bioenergy Capacity</t>
-  </si>
-  <si>
     <t>Acerra power station_1</t>
   </si>
   <si>
@@ -3024,18 +3024,18 @@
     <t>Aggregated Plant</t>
   </si>
   <si>
+    <t>Aggregated Plant - EMBER Gap - way/418902800-380_Missing Coal Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/303915533-380_Missing Coal Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/409439916-380_Missing Coal Capacity</t>
+  </si>
+  <si>
     <t>Aggregated Plant - EMBER Gap - way/82767145-380_Missing Coal Capacity</t>
   </si>
   <si>
-    <t>Aggregated Plant - EMBER Gap - way/409439916-380_Missing Coal Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/418902800-380_Missing Coal Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/303915533-380_Missing Coal Capacity</t>
-  </si>
-  <si>
     <t>Fiume Santo power station_Unit 3</t>
   </si>
   <si>
@@ -3066,102 +3066,102 @@
     <t>Torrevaldaliga Nord power station_Unit 3</t>
   </si>
   <si>
+    <t>Aggregated Plant - EMBER Gap - way/145665799-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/1137611914-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/60725875-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/61157826-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/110138220-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/414663585-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/82767145-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/82078641-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/172302572-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/59462715-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/432729521-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/199675964-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/103653592-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/100407576-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/416989699-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/133601335-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/162960205-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/421827453-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/99826025-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/338753171-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/162828577-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/98900549-380_Missing Gas Capacity</t>
+  </si>
+  <si>
     <t>Aggregated Plant - EMBER Gap - way/116797658-380_Missing Gas Capacity</t>
   </si>
   <si>
+    <t>Aggregated Plant - EMBER Gap - way/339104227-380_Missing Gas Capacity</t>
+  </si>
+  <si>
     <t>Aggregated Plant - EMBER Gap - way/107438024-380_Missing Gas Capacity</t>
   </si>
   <si>
-    <t>Aggregated Plant - EMBER Gap - way/339104227-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/60725875-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/414663585-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/82078641-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/61157826-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/162828577-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/98900549-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/338753171-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/110138220-380_Missing Gas Capacity</t>
-  </si>
-  <si>
     <t>Aggregated Plant - EMBER Gap - way/103381531-380_Missing Gas Capacity</t>
   </si>
   <si>
-    <t>Aggregated Plant - EMBER Gap - way/133601335-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/162960205-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/199675964-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/432729521-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/145665799-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/1137611914-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/59462715-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/172302572-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/421827453-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/99826025-380_Missing Gas Capacity</t>
+    <t>Aggregated Plant - EMBER Gap - way/105581403-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/98421779-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/110330925-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/109756016-380_Missing Gas Capacity</t>
   </si>
   <si>
     <t>Aggregated Plant - EMBER Gap - way/82084019-380_Missing Gas Capacity</t>
   </si>
   <si>
-    <t>Aggregated Plant - EMBER Gap - way/105581403-380_Missing Gas Capacity</t>
-  </si>
-  <si>
     <t>Aggregated Plant - EMBER Gap - way/411026199-380_Missing Gas Capacity</t>
   </si>
   <si>
-    <t>Aggregated Plant - EMBER Gap - way/82767145-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/110330925-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/98421779-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/109756016-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/100407576-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/103653592-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/416989699-380_Missing Gas Capacity</t>
-  </si>
-  <si>
     <t>Altomonte power station_1</t>
   </si>
   <si>
@@ -3486,6 +3486,30 @@
     <t>Valle Secolo geothermal power plant_2</t>
   </si>
   <si>
+    <t>Aggregated Plant - IRENA Gap - way/419423704-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/491424937-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/72466334-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/82083756-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/104359058-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/75602396-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/116517585-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/96190189-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
     <t>Aggregated Plant - IRENA Gap - IT7-380_Missing Hydro Capacity</t>
   </si>
   <si>
@@ -3495,93 +3519,69 @@
     <t>Aggregated Plant - IRENA Gap - IT30-500_Missing Hydro Capacity</t>
   </si>
   <si>
+    <t>Aggregated Plant - IRENA Gap - way/61712456-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
     <t>Aggregated Plant - IRENA Gap - IT53-380_Missing Hydro Capacity</t>
   </si>
   <si>
-    <t>Aggregated Plant - IRENA Gap - way/61712456-380_Missing Hydro Capacity</t>
+    <t>Aggregated Plant - IRENA Gap - IT21-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - IT93-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/144005863-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - IT10-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/338753171-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/61626687-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/114931087-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - IT31-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - IT71-400_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - IT36-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/64200868-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/59462263-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - IT72-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/1137611914-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/109588422-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - IT72-400_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - IT71-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/108020416-380_Missing Hydro Capacity</t>
   </si>
   <si>
     <t>Aggregated Plant - IRENA Gap - way/1100665914-380_Missing Hydro Capacity</t>
   </si>
   <si>
-    <t>Aggregated Plant - IRENA Gap - way/59462263-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - IT72-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/75602396-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - IT10-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/338753171-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - IT93-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/64200868-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/109588422-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/61626687-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - IT31-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/114931087-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/419423704-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/491424937-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/104359058-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/72466334-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/82083756-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - IT71-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - IT21-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/144005863-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - IT36-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - IT71-400_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - IT72-400_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/1137611914-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/96190189-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/116517585-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/108020416-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
     <t>Baschi hydroelectric plant_</t>
   </si>
   <si>
@@ -3864,24 +3864,24 @@
     <t>Sant'Angelo hydroelectric plant_</t>
   </si>
   <si>
+    <t>Aggregated Plant - IRENA Gap - ITA_68_Missing Solar Capacity</t>
+  </si>
+  <si>
+    <t>annual</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - ITA_30_Missing Solar Capacity</t>
+  </si>
+  <si>
     <t>Aggregated Plant - IRENA Gap - ITA_42_Missing Solar Capacity</t>
   </si>
   <si>
-    <t>annual</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - ITA_30_Missing Solar Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - ITA_68_Missing Solar Capacity</t>
+    <t>Aggregated Plant - IRENA Gap - ITA_22_Missing Onshore wind energy Capacity</t>
   </si>
   <si>
     <t>Aggregated Plant - IRENA Gap - ITA_96_Missing Onshore wind energy Capacity</t>
   </si>
   <si>
-    <t>Aggregated Plant - IRENA Gap - ITA_22_Missing Onshore wind energy Capacity</t>
-  </si>
-  <si>
     <t>Aggregated Plant - IRENA Gap - ITA_73_Missing Onshore wind energy Capacity</t>
   </si>
   <si>
@@ -4974,18 +4974,18 @@
     <t>ccs retrofit of -- Sulcis power station_Unit 3</t>
   </si>
   <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/82767145-380_Missing Coal Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/303915533-380_Missing Coal Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/409439916-380_Missing Coal Capacity</t>
+  </si>
+  <si>
     <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/418902800-380_Missing Coal Capacity</t>
   </si>
   <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/82767145-380_Missing Coal Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/303915533-380_Missing Coal Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/409439916-380_Missing Coal Capacity</t>
-  </si>
-  <si>
     <t>ccs retrofit of -- Brindisi Sud power station_Unit 1</t>
   </si>
   <si>
@@ -5274,100 +5274,100 @@
     <t>ccs retrofit of -- Aggregated Plant</t>
   </si>
   <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/61157826-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/60725875-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/421827453-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/82084019-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/162960205-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/432729521-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/416989699-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/99826025-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/98900549-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/107438024-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/98421779-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/1137611914-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/110138220-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/82078641-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/199675964-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/103653592-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/103381531-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/109756016-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/411026199-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/59462715-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/145665799-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/100407576-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/116797658-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/414663585-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/133601335-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/339104227-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/172302572-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/162828577-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/82767145-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/105581403-380_Missing Gas Capacity</t>
+  </si>
+  <si>
     <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/338753171-380_Missing Gas Capacity</t>
   </si>
   <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/145665799-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/172302572-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/82767145-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/162828577-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/82078641-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/110138220-380_Missing Gas Capacity</t>
-  </si>
-  <si>
     <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/110330925-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/107438024-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/98900549-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/98421779-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/60725875-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/421827453-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/82084019-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/100407576-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/116797658-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/414663585-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/133601335-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/162960205-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/432729521-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/339104227-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/99826025-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/416989699-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/103381531-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/411026199-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/109756016-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/61157826-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/105581403-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/103653592-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/1137611914-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/199675964-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/59462715-380_Missing Gas Capacity</t>
   </si>
   <si>
     <t>ccs retrofit of -- Tavazzano power station_CCGT8, timepoint 1</t>
@@ -5771,7 +5771,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4EBEFB18-90A0-409B-A846-FB391B1A9944}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D94DD666-8343-449C-8308-35772155A542}">
   <dimension ref="B9:T455"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -5847,7 +5847,7 @@
         <v>33</v>
       </c>
       <c r="D11" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E11">
         <v>0.18317520000000001</v>
@@ -5903,7 +5903,7 @@
         <v>33</v>
       </c>
       <c r="D12" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E12">
         <v>0.18317520000000001</v>
@@ -5959,7 +5959,7 @@
         <v>33</v>
       </c>
       <c r="D13" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E13">
         <v>0.18317520000000001</v>
@@ -6015,7 +6015,7 @@
         <v>33</v>
       </c>
       <c r="D14" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E14">
         <v>0.13765950000000002</v>
@@ -6295,7 +6295,7 @@
         <v>33</v>
       </c>
       <c r="D19" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E19">
         <v>0.30649709999999997</v>
@@ -6351,7 +6351,7 @@
         <v>33</v>
       </c>
       <c r="D20" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E20">
         <v>0.30649709999999997</v>
@@ -6407,7 +6407,7 @@
         <v>33</v>
       </c>
       <c r="D21" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E21">
         <v>0.30649709999999997</v>
@@ -6463,7 +6463,7 @@
         <v>33</v>
       </c>
       <c r="D22" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="E22">
         <v>0.33007379999999992</v>
@@ -6519,7 +6519,7 @@
         <v>33</v>
       </c>
       <c r="D23" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="E23">
         <v>0.33007379999999992</v>
@@ -6575,7 +6575,7 @@
         <v>33</v>
       </c>
       <c r="D24" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="E24">
         <v>0.33007379999999992</v>
@@ -6631,7 +6631,7 @@
         <v>49</v>
       </c>
       <c r="D25" t="s">
-        <v>57</v>
+        <v>69</v>
       </c>
       <c r="E25">
         <v>0.49118125000000001</v>
@@ -6687,7 +6687,7 @@
         <v>49</v>
       </c>
       <c r="D26" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="E26">
         <v>0.52272499999999988</v>
@@ -6743,7 +6743,7 @@
         <v>49</v>
       </c>
       <c r="D27" t="s">
-        <v>51</v>
+        <v>76</v>
       </c>
       <c r="E27">
         <v>0.450625</v>
@@ -6799,7 +6799,7 @@
         <v>49</v>
       </c>
       <c r="D28" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="E28">
         <v>0.52272499999999988</v>
@@ -6855,7 +6855,7 @@
         <v>49</v>
       </c>
       <c r="D29" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="E29">
         <v>0.49118125000000001</v>
@@ -6911,7 +6911,7 @@
         <v>49</v>
       </c>
       <c r="D30" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="E30">
         <v>0.49118125000000001</v>
@@ -6967,7 +6967,7 @@
         <v>49</v>
       </c>
       <c r="D31" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="E31">
         <v>0.49118125000000001</v>
@@ -7079,7 +7079,7 @@
         <v>49</v>
       </c>
       <c r="D33" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="E33">
         <v>0.49118125000000001</v>
@@ -7247,7 +7247,7 @@
         <v>49</v>
       </c>
       <c r="D36" t="s">
-        <v>62</v>
+        <v>78</v>
       </c>
       <c r="E36">
         <v>0.49118125000000001</v>
@@ -7303,7 +7303,7 @@
         <v>49</v>
       </c>
       <c r="D37" t="s">
-        <v>62</v>
+        <v>78</v>
       </c>
       <c r="E37">
         <v>0.49118125000000001</v>
@@ -7359,7 +7359,7 @@
         <v>49</v>
       </c>
       <c r="D38" t="s">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="E38">
         <v>0.49118125000000001</v>
@@ -7415,7 +7415,7 @@
         <v>49</v>
       </c>
       <c r="D39" t="s">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="E39">
         <v>0.49118125000000001</v>
@@ -7471,7 +7471,7 @@
         <v>49</v>
       </c>
       <c r="D40" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="E40">
         <v>0.46865000000000007</v>
@@ -7527,7 +7527,7 @@
         <v>49</v>
       </c>
       <c r="D41" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="E41">
         <v>0.49118125000000001</v>
@@ -7583,7 +7583,7 @@
         <v>49</v>
       </c>
       <c r="D42" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="E42">
         <v>0.49118125000000001</v>
@@ -7639,7 +7639,7 @@
         <v>49</v>
       </c>
       <c r="D43" t="s">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="E43">
         <v>0.49118125000000001</v>
@@ -7695,7 +7695,7 @@
         <v>49</v>
       </c>
       <c r="D44" t="s">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="E44">
         <v>0.49118125000000001</v>
@@ -7751,7 +7751,7 @@
         <v>49</v>
       </c>
       <c r="D45" t="s">
-        <v>74</v>
+        <v>52</v>
       </c>
       <c r="E45">
         <v>0.49118125000000001</v>
@@ -7807,7 +7807,7 @@
         <v>49</v>
       </c>
       <c r="D46" t="s">
-        <v>74</v>
+        <v>52</v>
       </c>
       <c r="E46">
         <v>0.49118125000000001</v>
@@ -7863,7 +7863,7 @@
         <v>49</v>
       </c>
       <c r="D47" t="s">
-        <v>74</v>
+        <v>52</v>
       </c>
       <c r="E47">
         <v>0.49118125000000001</v>
@@ -7919,7 +7919,7 @@
         <v>49</v>
       </c>
       <c r="D48" t="s">
-        <v>74</v>
+        <v>52</v>
       </c>
       <c r="E48">
         <v>0.49118125000000001</v>
@@ -8143,7 +8143,7 @@
         <v>49</v>
       </c>
       <c r="D52" t="s">
-        <v>51</v>
+        <v>76</v>
       </c>
       <c r="E52">
         <v>0.54075000000000006</v>
@@ -8199,7 +8199,7 @@
         <v>49</v>
       </c>
       <c r="D53" t="s">
-        <v>51</v>
+        <v>76</v>
       </c>
       <c r="E53">
         <v>0.49118125000000001</v>
@@ -8255,7 +8255,7 @@
         <v>49</v>
       </c>
       <c r="D54" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="E54">
         <v>0.450625</v>
@@ -8311,7 +8311,7 @@
         <v>49</v>
       </c>
       <c r="D55" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="E55">
         <v>0.49118125000000001</v>
@@ -8479,7 +8479,7 @@
         <v>49</v>
       </c>
       <c r="D58" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="E58">
         <v>0.47315625000000006</v>
@@ -8535,7 +8535,7 @@
         <v>49</v>
       </c>
       <c r="D59" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="E59">
         <v>0.47315625000000006</v>
@@ -8591,7 +8591,7 @@
         <v>49</v>
       </c>
       <c r="D60" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="E60">
         <v>0.450625</v>
@@ -8647,7 +8647,7 @@
         <v>49</v>
       </c>
       <c r="D61" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="E61">
         <v>0.450625</v>
@@ -8759,7 +8759,7 @@
         <v>49</v>
       </c>
       <c r="D63" t="s">
-        <v>71</v>
+        <v>51</v>
       </c>
       <c r="E63">
         <v>0.4911812499999999</v>
@@ -8815,7 +8815,7 @@
         <v>49</v>
       </c>
       <c r="D64" t="s">
-        <v>68</v>
+        <v>55</v>
       </c>
       <c r="E64">
         <v>0.49118125000000001</v>
@@ -8871,7 +8871,7 @@
         <v>49</v>
       </c>
       <c r="D65" t="s">
-        <v>68</v>
+        <v>55</v>
       </c>
       <c r="E65">
         <v>0.49118125000000001</v>
@@ -8927,7 +8927,7 @@
         <v>49</v>
       </c>
       <c r="D66" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="E66">
         <v>0.49118125000000001</v>
@@ -9207,7 +9207,7 @@
         <v>49</v>
       </c>
       <c r="D71" t="s">
-        <v>71</v>
+        <v>51</v>
       </c>
       <c r="E71">
         <v>0.49118125000000001</v>
@@ -9263,7 +9263,7 @@
         <v>49</v>
       </c>
       <c r="D72" t="s">
-        <v>71</v>
+        <v>51</v>
       </c>
       <c r="E72">
         <v>0.49118125000000001</v>
@@ -9431,7 +9431,7 @@
         <v>49</v>
       </c>
       <c r="D75" t="s">
-        <v>61</v>
+        <v>77</v>
       </c>
       <c r="E75">
         <v>0.50470000000000004</v>
@@ -9711,7 +9711,7 @@
         <v>49</v>
       </c>
       <c r="D80" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E80">
         <v>0.49118125000000001</v>
@@ -9767,7 +9767,7 @@
         <v>49</v>
       </c>
       <c r="D81" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E81">
         <v>0.49118125000000001</v>
@@ -9823,7 +9823,7 @@
         <v>49</v>
       </c>
       <c r="D82" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E82">
         <v>0.49118125000000001</v>
@@ -9879,7 +9879,7 @@
         <v>49</v>
       </c>
       <c r="D83" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E83">
         <v>0.49118125000000001</v>
@@ -9935,7 +9935,7 @@
         <v>49</v>
       </c>
       <c r="D84" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="E84">
         <v>0.49118125000000001</v>
@@ -10103,7 +10103,7 @@
         <v>49</v>
       </c>
       <c r="D87" t="s">
-        <v>72</v>
+        <v>54</v>
       </c>
       <c r="E87">
         <v>0.49118125000000001</v>
@@ -10159,7 +10159,7 @@
         <v>49</v>
       </c>
       <c r="D88" t="s">
-        <v>72</v>
+        <v>54</v>
       </c>
       <c r="E88">
         <v>0.49118125000000001</v>
@@ -10215,7 +10215,7 @@
         <v>49</v>
       </c>
       <c r="D89" t="s">
-        <v>69</v>
+        <v>56</v>
       </c>
       <c r="E89">
         <v>0.52272499999999988</v>
@@ -10271,7 +10271,7 @@
         <v>49</v>
       </c>
       <c r="D90" t="s">
-        <v>69</v>
+        <v>56</v>
       </c>
       <c r="E90">
         <v>0.49118125000000001</v>
@@ -10327,7 +10327,7 @@
         <v>49</v>
       </c>
       <c r="D91" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E91">
         <v>0.49118125000000001</v>
@@ -10439,7 +10439,7 @@
         <v>49</v>
       </c>
       <c r="D93" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="E93">
         <v>0.49118125000000001</v>
@@ -10495,7 +10495,7 @@
         <v>49</v>
       </c>
       <c r="D94" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="E94">
         <v>0.49118125000000001</v>
@@ -10551,7 +10551,7 @@
         <v>49</v>
       </c>
       <c r="D95" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="E95">
         <v>0.49118125000000001</v>
@@ -10607,7 +10607,7 @@
         <v>49</v>
       </c>
       <c r="D96" t="s">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="E96">
         <v>0.49118125000000001</v>
@@ -10663,7 +10663,7 @@
         <v>49</v>
       </c>
       <c r="D97" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="E97">
         <v>0.49118125000000001</v>
@@ -10831,7 +10831,7 @@
         <v>49</v>
       </c>
       <c r="D100" t="s">
-        <v>73</v>
+        <v>50</v>
       </c>
       <c r="E100">
         <v>0.54075000000000006</v>
@@ -10887,7 +10887,7 @@
         <v>49</v>
       </c>
       <c r="D101" t="s">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="E101">
         <v>0.54075000000000006</v>
@@ -11055,7 +11055,7 @@
         <v>49</v>
       </c>
       <c r="D104" t="s">
-        <v>68</v>
+        <v>55</v>
       </c>
       <c r="E104">
         <v>0.49118125000000001</v>
@@ -11111,7 +11111,7 @@
         <v>49</v>
       </c>
       <c r="D105" t="s">
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="E105">
         <v>0.49118125000000001</v>
@@ -11167,7 +11167,7 @@
         <v>49</v>
       </c>
       <c r="D106" t="s">
-        <v>71</v>
+        <v>51</v>
       </c>
       <c r="E106">
         <v>0.450625</v>
@@ -11223,7 +11223,7 @@
         <v>49</v>
       </c>
       <c r="D107" t="s">
-        <v>71</v>
+        <v>51</v>
       </c>
       <c r="E107">
         <v>0.450625</v>
@@ -11279,7 +11279,7 @@
         <v>49</v>
       </c>
       <c r="D108" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="E108">
         <v>0.47315625000000006</v>
@@ -11447,7 +11447,7 @@
         <v>49</v>
       </c>
       <c r="D111" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="E111">
         <v>0.46865000000000007</v>
@@ -11559,7 +11559,7 @@
         <v>49</v>
       </c>
       <c r="D113" t="s">
-        <v>61</v>
+        <v>77</v>
       </c>
       <c r="E113">
         <v>0.49118125000000001</v>
@@ -12343,7 +12343,7 @@
         <v>49</v>
       </c>
       <c r="D127" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E127">
         <v>0.54075000000000006</v>
@@ -12399,7 +12399,7 @@
         <v>49</v>
       </c>
       <c r="D128" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E128">
         <v>0.54075000000000006</v>
@@ -12511,7 +12511,7 @@
         <v>49</v>
       </c>
       <c r="D130" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E130">
         <v>0.54075000000000006</v>
@@ -12567,7 +12567,7 @@
         <v>49</v>
       </c>
       <c r="D131" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E131">
         <v>0.54075000000000006</v>
@@ -12623,7 +12623,7 @@
         <v>49</v>
       </c>
       <c r="D132" t="s">
-        <v>15</v>
+        <v>61</v>
       </c>
       <c r="E132">
         <v>0.54075000000000006</v>
@@ -12679,7 +12679,7 @@
         <v>49</v>
       </c>
       <c r="D133" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E133">
         <v>0.54075000000000006</v>
@@ -12735,7 +12735,7 @@
         <v>49</v>
       </c>
       <c r="D134" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E134">
         <v>0.54075000000000006</v>
@@ -12903,7 +12903,7 @@
         <v>49</v>
       </c>
       <c r="D137" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E137">
         <v>0.54075000000000006</v>
@@ -12959,7 +12959,7 @@
         <v>49</v>
       </c>
       <c r="D138" t="s">
-        <v>59</v>
+        <v>19</v>
       </c>
       <c r="E138">
         <v>0.54075000000000006</v>
@@ -13015,7 +13015,7 @@
         <v>49</v>
       </c>
       <c r="D139" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E139">
         <v>0.54075000000000006</v>
@@ -13071,7 +13071,7 @@
         <v>49</v>
       </c>
       <c r="D140" t="s">
-        <v>67</v>
+        <v>37</v>
       </c>
       <c r="E140">
         <v>0.54075000000000006</v>
@@ -13743,7 +13743,7 @@
         <v>49</v>
       </c>
       <c r="D152" t="s">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="E152">
         <v>0.54075000000000006</v>
@@ -13911,7 +13911,7 @@
         <v>49</v>
       </c>
       <c r="D155" t="s">
-        <v>51</v>
+        <v>76</v>
       </c>
       <c r="E155">
         <v>0.43259999999999998</v>
@@ -14023,7 +14023,7 @@
         <v>49</v>
       </c>
       <c r="D157" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="E157">
         <v>0.48667500000000002</v>
@@ -15311,7 +15311,7 @@
         <v>49</v>
       </c>
       <c r="D180" t="s">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="E180">
         <v>0.46865000000000007</v>
@@ -15367,7 +15367,7 @@
         <v>49</v>
       </c>
       <c r="D181" t="s">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="E181">
         <v>0.46865000000000007</v>
@@ -15759,7 +15759,7 @@
         <v>49</v>
       </c>
       <c r="D188" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E188">
         <v>0.50470000000000004</v>
@@ -15815,7 +15815,7 @@
         <v>49</v>
       </c>
       <c r="D189" t="s">
-        <v>71</v>
+        <v>51</v>
       </c>
       <c r="E189">
         <v>0.48667500000000002</v>
@@ -15871,7 +15871,7 @@
         <v>49</v>
       </c>
       <c r="D190" t="s">
-        <v>71</v>
+        <v>51</v>
       </c>
       <c r="E190">
         <v>0.48667500000000002</v>
@@ -16431,7 +16431,7 @@
         <v>49</v>
       </c>
       <c r="D200" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E200">
         <v>0.50470000000000004</v>
@@ -16711,7 +16711,7 @@
         <v>49</v>
       </c>
       <c r="D205" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E205">
         <v>0.50470000000000004</v>
@@ -16879,7 +16879,7 @@
         <v>49</v>
       </c>
       <c r="D208" t="s">
-        <v>73</v>
+        <v>50</v>
       </c>
       <c r="E208">
         <v>0.46865000000000007</v>
@@ -17607,7 +17607,7 @@
         <v>49</v>
       </c>
       <c r="D221" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E221">
         <v>0.450625</v>
@@ -17775,7 +17775,7 @@
         <v>49</v>
       </c>
       <c r="D224" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E224">
         <v>0.50470000000000004</v>
@@ -17831,7 +17831,7 @@
         <v>49</v>
       </c>
       <c r="D225" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E225">
         <v>0.50470000000000004</v>
@@ -18055,7 +18055,7 @@
         <v>49</v>
       </c>
       <c r="D229" t="s">
-        <v>72</v>
+        <v>54</v>
       </c>
       <c r="E229">
         <v>0.29741250000000002</v>
@@ -18111,7 +18111,7 @@
         <v>49</v>
       </c>
       <c r="D230" t="s">
-        <v>69</v>
+        <v>56</v>
       </c>
       <c r="E230">
         <v>0.28839999999999999</v>
@@ -18167,7 +18167,7 @@
         <v>49</v>
       </c>
       <c r="D231" t="s">
-        <v>69</v>
+        <v>56</v>
       </c>
       <c r="E231">
         <v>0.28839999999999999</v>
@@ -18223,7 +18223,7 @@
         <v>49</v>
       </c>
       <c r="D232" t="s">
-        <v>61</v>
+        <v>77</v>
       </c>
       <c r="E232">
         <v>0.24784375000000003</v>
@@ -18671,7 +18671,7 @@
         <v>49</v>
       </c>
       <c r="D240" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="E240">
         <v>0.22981874999999999</v>
@@ -18727,7 +18727,7 @@
         <v>49</v>
       </c>
       <c r="D241" t="s">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="E241">
         <v>0.25235000000000002</v>
@@ -18783,7 +18783,7 @@
         <v>49</v>
       </c>
       <c r="D242" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E242">
         <v>0.23883125000000002</v>
@@ -18839,7 +18839,7 @@
         <v>49</v>
       </c>
       <c r="D243" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E243">
         <v>0.25235000000000002</v>
@@ -19119,7 +19119,7 @@
         <v>49</v>
       </c>
       <c r="D248" t="s">
-        <v>69</v>
+        <v>56</v>
       </c>
       <c r="E248">
         <v>0.27938750000000001</v>
@@ -19231,7 +19231,7 @@
         <v>49</v>
       </c>
       <c r="D250" t="s">
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="E250">
         <v>0.25235000000000002</v>
@@ -19511,7 +19511,7 @@
         <v>49</v>
       </c>
       <c r="D255" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="E255">
         <v>0.32445000000000007</v>
@@ -19623,7 +19623,7 @@
         <v>49</v>
       </c>
       <c r="D257" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E257">
         <v>0.32445000000000002</v>
@@ -19847,7 +19847,7 @@
         <v>49</v>
       </c>
       <c r="D261" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="E261">
         <v>0.27938750000000001</v>
@@ -19903,7 +19903,7 @@
         <v>49</v>
       </c>
       <c r="D262" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="E262">
         <v>0.27938750000000001</v>
@@ -19959,7 +19959,7 @@
         <v>49</v>
       </c>
       <c r="D263" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="E263">
         <v>0.27938750000000001</v>
@@ -20015,7 +20015,7 @@
         <v>49</v>
       </c>
       <c r="D264" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="E264">
         <v>0.29741250000000002</v>
@@ -20071,7 +20071,7 @@
         <v>49</v>
       </c>
       <c r="D265" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="E265">
         <v>0.29741250000000002</v>
@@ -20127,7 +20127,7 @@
         <v>49</v>
       </c>
       <c r="D266" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="E266">
         <v>0.27938750000000001</v>
@@ -20183,7 +20183,7 @@
         <v>49</v>
       </c>
       <c r="D267" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="E267">
         <v>0.27938750000000001</v>
@@ -20239,7 +20239,7 @@
         <v>49</v>
       </c>
       <c r="D268" t="s">
-        <v>51</v>
+        <v>76</v>
       </c>
       <c r="E268">
         <v>0.28839999999999999</v>
@@ -20351,7 +20351,7 @@
         <v>49</v>
       </c>
       <c r="D270" t="s">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="E270">
         <v>0.31093124999999999</v>
@@ -20407,7 +20407,7 @@
         <v>49</v>
       </c>
       <c r="D271" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="E271">
         <v>0.27938750000000001</v>
@@ -20463,7 +20463,7 @@
         <v>49</v>
       </c>
       <c r="D272" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="E272">
         <v>0.27938750000000001</v>
@@ -20799,7 +20799,7 @@
         <v>49</v>
       </c>
       <c r="D278" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E278">
         <v>0.28839999999999999</v>
@@ -20855,7 +20855,7 @@
         <v>49</v>
       </c>
       <c r="D279" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E279">
         <v>0.28839999999999999</v>
@@ -20911,7 +20911,7 @@
         <v>49</v>
       </c>
       <c r="D280" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E280">
         <v>0.28839999999999999</v>
@@ -21023,7 +21023,7 @@
         <v>465</v>
       </c>
       <c r="D282" t="s">
-        <v>57</v>
+        <v>69</v>
       </c>
       <c r="E282">
         <v>0.46865000000000007</v>
@@ -21079,7 +21079,7 @@
         <v>465</v>
       </c>
       <c r="D283" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="E283">
         <v>0.50470000000000004</v>
@@ -21135,7 +21135,7 @@
         <v>465</v>
       </c>
       <c r="D284" t="s">
-        <v>51</v>
+        <v>76</v>
       </c>
       <c r="E284">
         <v>0.43259999999999998</v>
@@ -21191,7 +21191,7 @@
         <v>465</v>
       </c>
       <c r="D285" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="E285">
         <v>0.50470000000000004</v>
@@ -21247,7 +21247,7 @@
         <v>465</v>
       </c>
       <c r="D286" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="E286">
         <v>0.46865000000000007</v>
@@ -21303,7 +21303,7 @@
         <v>465</v>
       </c>
       <c r="D287" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="E287">
         <v>0.46865000000000007</v>
@@ -21359,7 +21359,7 @@
         <v>465</v>
       </c>
       <c r="D288" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="E288">
         <v>0.46865000000000007</v>
@@ -21471,7 +21471,7 @@
         <v>465</v>
       </c>
       <c r="D290" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="E290">
         <v>0.46865000000000007</v>
@@ -21639,7 +21639,7 @@
         <v>465</v>
       </c>
       <c r="D293" t="s">
-        <v>62</v>
+        <v>78</v>
       </c>
       <c r="E293">
         <v>0.46865000000000007</v>
@@ -21695,7 +21695,7 @@
         <v>465</v>
       </c>
       <c r="D294" t="s">
-        <v>62</v>
+        <v>78</v>
       </c>
       <c r="E294">
         <v>0.46865000000000007</v>
@@ -21751,7 +21751,7 @@
         <v>465</v>
       </c>
       <c r="D295" t="s">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="E295">
         <v>0.46865000000000007</v>
@@ -21807,7 +21807,7 @@
         <v>465</v>
       </c>
       <c r="D296" t="s">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="E296">
         <v>0.46865000000000007</v>
@@ -21863,7 +21863,7 @@
         <v>465</v>
       </c>
       <c r="D297" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="E297">
         <v>0.450625</v>
@@ -21919,7 +21919,7 @@
         <v>465</v>
       </c>
       <c r="D298" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="E298">
         <v>0.46865000000000007</v>
@@ -21975,7 +21975,7 @@
         <v>465</v>
       </c>
       <c r="D299" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="E299">
         <v>0.46865000000000007</v>
@@ -22031,7 +22031,7 @@
         <v>465</v>
       </c>
       <c r="D300" t="s">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="E300">
         <v>0.46865000000000007</v>
@@ -22087,7 +22087,7 @@
         <v>465</v>
       </c>
       <c r="D301" t="s">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="E301">
         <v>0.46865000000000007</v>
@@ -22143,7 +22143,7 @@
         <v>465</v>
       </c>
       <c r="D302" t="s">
-        <v>74</v>
+        <v>52</v>
       </c>
       <c r="E302">
         <v>0.46865000000000007</v>
@@ -22199,7 +22199,7 @@
         <v>465</v>
       </c>
       <c r="D303" t="s">
-        <v>74</v>
+        <v>52</v>
       </c>
       <c r="E303">
         <v>0.46865000000000007</v>
@@ -22255,7 +22255,7 @@
         <v>465</v>
       </c>
       <c r="D304" t="s">
-        <v>74</v>
+        <v>52</v>
       </c>
       <c r="E304">
         <v>0.46865000000000007</v>
@@ -22311,7 +22311,7 @@
         <v>465</v>
       </c>
       <c r="D305" t="s">
-        <v>74</v>
+        <v>52</v>
       </c>
       <c r="E305">
         <v>0.46865000000000007</v>
@@ -22535,7 +22535,7 @@
         <v>465</v>
       </c>
       <c r="D309" t="s">
-        <v>51</v>
+        <v>76</v>
       </c>
       <c r="E309">
         <v>0.52272499999999988</v>
@@ -22591,7 +22591,7 @@
         <v>465</v>
       </c>
       <c r="D310" t="s">
-        <v>51</v>
+        <v>76</v>
       </c>
       <c r="E310">
         <v>0.46865000000000007</v>
@@ -22647,7 +22647,7 @@
         <v>465</v>
       </c>
       <c r="D311" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="E311">
         <v>0.43259999999999998</v>
@@ -22703,7 +22703,7 @@
         <v>465</v>
       </c>
       <c r="D312" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="E312">
         <v>0.46865000000000007</v>
@@ -22871,7 +22871,7 @@
         <v>465</v>
       </c>
       <c r="D315" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="E315">
         <v>0.450625</v>
@@ -22927,7 +22927,7 @@
         <v>465</v>
       </c>
       <c r="D316" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="E316">
         <v>0.450625</v>
@@ -22983,7 +22983,7 @@
         <v>465</v>
       </c>
       <c r="D317" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="E317">
         <v>0.43259999999999998</v>
@@ -23039,7 +23039,7 @@
         <v>465</v>
       </c>
       <c r="D318" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="E318">
         <v>0.43259999999999998</v>
@@ -23151,7 +23151,7 @@
         <v>465</v>
       </c>
       <c r="D320" t="s">
-        <v>71</v>
+        <v>51</v>
       </c>
       <c r="E320">
         <v>0.46865000000000007</v>
@@ -23207,7 +23207,7 @@
         <v>465</v>
       </c>
       <c r="D321" t="s">
-        <v>68</v>
+        <v>55</v>
       </c>
       <c r="E321">
         <v>0.46865000000000007</v>
@@ -23263,7 +23263,7 @@
         <v>465</v>
       </c>
       <c r="D322" t="s">
-        <v>68</v>
+        <v>55</v>
       </c>
       <c r="E322">
         <v>0.46865000000000007</v>
@@ -23319,7 +23319,7 @@
         <v>465</v>
       </c>
       <c r="D323" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="E323">
         <v>0.46865000000000007</v>
@@ -23711,7 +23711,7 @@
         <v>465</v>
       </c>
       <c r="D330" t="s">
-        <v>61</v>
+        <v>77</v>
       </c>
       <c r="E330">
         <v>0.48667500000000002</v>
@@ -23991,7 +23991,7 @@
         <v>465</v>
       </c>
       <c r="D335" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E335">
         <v>0.46865000000000007</v>
@@ -24047,7 +24047,7 @@
         <v>465</v>
       </c>
       <c r="D336" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E336">
         <v>0.46865000000000007</v>
@@ -24103,7 +24103,7 @@
         <v>465</v>
       </c>
       <c r="D337" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E337">
         <v>0.46865000000000007</v>
@@ -24159,7 +24159,7 @@
         <v>465</v>
       </c>
       <c r="D338" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E338">
         <v>0.46865000000000007</v>
@@ -24215,7 +24215,7 @@
         <v>465</v>
       </c>
       <c r="D339" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="E339">
         <v>0.46865000000000007</v>
@@ -24383,7 +24383,7 @@
         <v>465</v>
       </c>
       <c r="D342" t="s">
-        <v>72</v>
+        <v>54</v>
       </c>
       <c r="E342">
         <v>0.46865000000000007</v>
@@ -24439,7 +24439,7 @@
         <v>465</v>
       </c>
       <c r="D343" t="s">
-        <v>72</v>
+        <v>54</v>
       </c>
       <c r="E343">
         <v>0.46865000000000007</v>
@@ -24495,7 +24495,7 @@
         <v>465</v>
       </c>
       <c r="D344" t="s">
-        <v>69</v>
+        <v>56</v>
       </c>
       <c r="E344">
         <v>0.50470000000000004</v>
@@ -24551,7 +24551,7 @@
         <v>465</v>
       </c>
       <c r="D345" t="s">
-        <v>69</v>
+        <v>56</v>
       </c>
       <c r="E345">
         <v>0.46865000000000007</v>
@@ -24607,7 +24607,7 @@
         <v>465</v>
       </c>
       <c r="D346" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E346">
         <v>0.46865000000000007</v>
@@ -24719,7 +24719,7 @@
         <v>465</v>
       </c>
       <c r="D348" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="E348">
         <v>0.46865000000000007</v>
@@ -24775,7 +24775,7 @@
         <v>465</v>
       </c>
       <c r="D349" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="E349">
         <v>0.46865000000000007</v>
@@ -24831,7 +24831,7 @@
         <v>465</v>
       </c>
       <c r="D350" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="E350">
         <v>0.46865000000000007</v>
@@ -24887,7 +24887,7 @@
         <v>465</v>
       </c>
       <c r="D351" t="s">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="E351">
         <v>0.46865000000000007</v>
@@ -24943,7 +24943,7 @@
         <v>465</v>
       </c>
       <c r="D352" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="E352">
         <v>0.46865000000000007</v>
@@ -25111,7 +25111,7 @@
         <v>465</v>
       </c>
       <c r="D355" t="s">
-        <v>73</v>
+        <v>50</v>
       </c>
       <c r="E355">
         <v>0.52272499999999988</v>
@@ -25167,7 +25167,7 @@
         <v>465</v>
       </c>
       <c r="D356" t="s">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="E356">
         <v>0.52272499999999988</v>
@@ -25335,7 +25335,7 @@
         <v>465</v>
       </c>
       <c r="D359" t="s">
-        <v>68</v>
+        <v>55</v>
       </c>
       <c r="E359">
         <v>0.46865000000000007</v>
@@ -25391,7 +25391,7 @@
         <v>465</v>
       </c>
       <c r="D360" t="s">
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="E360">
         <v>0.46865000000000007</v>
@@ -25447,7 +25447,7 @@
         <v>465</v>
       </c>
       <c r="D361" t="s">
-        <v>71</v>
+        <v>51</v>
       </c>
       <c r="E361">
         <v>0.43259999999999998</v>
@@ -25503,7 +25503,7 @@
         <v>465</v>
       </c>
       <c r="D362" t="s">
-        <v>71</v>
+        <v>51</v>
       </c>
       <c r="E362">
         <v>0.43259999999999998</v>
@@ -25559,7 +25559,7 @@
         <v>465</v>
       </c>
       <c r="D363" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="E363">
         <v>0.450625</v>
@@ -25727,7 +25727,7 @@
         <v>465</v>
       </c>
       <c r="D366" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="E366">
         <v>0.450625</v>
@@ -25839,7 +25839,7 @@
         <v>465</v>
       </c>
       <c r="D368" t="s">
-        <v>61</v>
+        <v>77</v>
       </c>
       <c r="E368">
         <v>0.46865000000000007</v>
@@ -26119,7 +26119,7 @@
         <v>465</v>
       </c>
       <c r="D373" t="s">
-        <v>51</v>
+        <v>76</v>
       </c>
       <c r="E373">
         <v>0.41457500000000003</v>
@@ -26175,7 +26175,7 @@
         <v>465</v>
       </c>
       <c r="D374" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="E374">
         <v>0.46865000000000007</v>
@@ -26567,7 +26567,7 @@
         <v>465</v>
       </c>
       <c r="D381" t="s">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="E381">
         <v>0.450625</v>
@@ -26623,7 +26623,7 @@
         <v>465</v>
       </c>
       <c r="D382" t="s">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="E382">
         <v>0.450625</v>
@@ -26735,7 +26735,7 @@
         <v>465</v>
       </c>
       <c r="D384" t="s">
-        <v>71</v>
+        <v>51</v>
       </c>
       <c r="E384">
         <v>0.46865000000000007</v>
@@ -26791,7 +26791,7 @@
         <v>465</v>
       </c>
       <c r="D385" t="s">
-        <v>71</v>
+        <v>51</v>
       </c>
       <c r="E385">
         <v>0.46865000000000007</v>
@@ -27183,7 +27183,7 @@
         <v>465</v>
       </c>
       <c r="D392" t="s">
-        <v>73</v>
+        <v>50</v>
       </c>
       <c r="E392">
         <v>0.450625</v>
@@ -27575,7 +27575,7 @@
         <v>465</v>
       </c>
       <c r="D399" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E399">
         <v>0.43259999999999998</v>
@@ -27631,7 +27631,7 @@
         <v>465</v>
       </c>
       <c r="D400" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E400">
         <v>0.36951250000000002</v>
@@ -27757,7 +27757,7 @@
         <v>465</v>
       </c>
       <c r="D403" t="s">
-        <v>72</v>
+        <v>54</v>
       </c>
       <c r="E403">
         <v>0.28839999999999999</v>
@@ -27792,7 +27792,7 @@
         <v>465</v>
       </c>
       <c r="D404" t="s">
-        <v>69</v>
+        <v>56</v>
       </c>
       <c r="E404">
         <v>0.27938750000000001</v>
@@ -27827,7 +27827,7 @@
         <v>465</v>
       </c>
       <c r="D405" t="s">
-        <v>69</v>
+        <v>56</v>
       </c>
       <c r="E405">
         <v>0.27938750000000001</v>
@@ -27862,7 +27862,7 @@
         <v>465</v>
       </c>
       <c r="D406" t="s">
-        <v>61</v>
+        <v>77</v>
       </c>
       <c r="E406">
         <v>0.23883125000000002</v>
@@ -28142,7 +28142,7 @@
         <v>465</v>
       </c>
       <c r="D414" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="E414">
         <v>0.22080625000000001</v>
@@ -28177,7 +28177,7 @@
         <v>465</v>
       </c>
       <c r="D415" t="s">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="E415">
         <v>0.24333750000000001</v>
@@ -28212,7 +28212,7 @@
         <v>465</v>
       </c>
       <c r="D416" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E416">
         <v>0.22981874999999999</v>
@@ -28247,7 +28247,7 @@
         <v>465</v>
       </c>
       <c r="D417" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E417">
         <v>0.24333750000000001</v>
@@ -28422,7 +28422,7 @@
         <v>465</v>
       </c>
       <c r="D422" t="s">
-        <v>69</v>
+        <v>56</v>
       </c>
       <c r="E422">
         <v>0.27037499999999992</v>
@@ -28492,7 +28492,7 @@
         <v>465</v>
       </c>
       <c r="D424" t="s">
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="E424">
         <v>0.24333750000000001</v>
@@ -28667,7 +28667,7 @@
         <v>465</v>
       </c>
       <c r="D429" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="E429">
         <v>0.31994374999999997</v>
@@ -28737,7 +28737,7 @@
         <v>465</v>
       </c>
       <c r="D431" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E431">
         <v>0.31994374999999997</v>
@@ -28877,7 +28877,7 @@
         <v>465</v>
       </c>
       <c r="D435" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="E435">
         <v>0.27037500000000003</v>
@@ -28912,7 +28912,7 @@
         <v>465</v>
       </c>
       <c r="D436" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="E436">
         <v>0.27037500000000003</v>
@@ -28947,7 +28947,7 @@
         <v>465</v>
       </c>
       <c r="D437" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="E437">
         <v>0.27037500000000003</v>
@@ -28982,7 +28982,7 @@
         <v>465</v>
       </c>
       <c r="D438" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="E438">
         <v>0.28839999999999999</v>
@@ -29017,7 +29017,7 @@
         <v>465</v>
       </c>
       <c r="D439" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="E439">
         <v>0.28839999999999999</v>
@@ -29052,7 +29052,7 @@
         <v>465</v>
       </c>
       <c r="D440" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="E440">
         <v>0.27037500000000003</v>
@@ -29087,7 +29087,7 @@
         <v>465</v>
       </c>
       <c r="D441" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="E441">
         <v>0.27037500000000003</v>
@@ -29122,7 +29122,7 @@
         <v>465</v>
       </c>
       <c r="D442" t="s">
-        <v>51</v>
+        <v>76</v>
       </c>
       <c r="E442">
         <v>0.27938750000000001</v>
@@ -29192,7 +29192,7 @@
         <v>465</v>
       </c>
       <c r="D444" t="s">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="E444">
         <v>0.30191875000000001</v>
@@ -29227,7 +29227,7 @@
         <v>465</v>
       </c>
       <c r="D445" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="E445">
         <v>0.27037500000000003</v>
@@ -29262,7 +29262,7 @@
         <v>465</v>
       </c>
       <c r="D446" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="E446">
         <v>0.27037500000000003</v>
@@ -29472,7 +29472,7 @@
         <v>465</v>
       </c>
       <c r="D452" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E452">
         <v>0.27938750000000001</v>
@@ -29507,7 +29507,7 @@
         <v>465</v>
       </c>
       <c r="D453" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E453">
         <v>0.27938750000000001</v>
@@ -29542,7 +29542,7 @@
         <v>465</v>
       </c>
       <c r="D454" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E454">
         <v>0.27938750000000001</v>
@@ -29610,7 +29610,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6A3912DE-CC61-42FF-BED9-A8FA46374EFE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{456AA86F-7771-4A21-B626-583AA62A5A9D}">
   <dimension ref="B9:T1019"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -29692,19 +29692,19 @@
         <v>2022</v>
       </c>
       <c r="F11">
-        <v>0.49149152542372881</v>
+        <v>0.24877966101694915</v>
       </c>
       <c r="G11">
-        <v>0.36049999999999999</v>
+        <v>0.33990000000000004</v>
       </c>
       <c r="H11">
-        <v>3850.0000000000005</v>
+        <v>4427.5</v>
       </c>
       <c r="I11">
-        <v>143</v>
+        <v>157.30000000000001</v>
       </c>
       <c r="J11">
-        <v>8.4</v>
+        <v>9.240000000000002</v>
       </c>
       <c r="K11">
         <v>50</v>
@@ -29745,19 +29745,19 @@
         <v>2022</v>
       </c>
       <c r="F12">
-        <v>0.27911864406779663</v>
+        <v>1.0679322033898306</v>
       </c>
       <c r="G12">
-        <v>0.33990000000000004</v>
+        <v>0.36049999999999999</v>
       </c>
       <c r="H12">
-        <v>4427.5</v>
+        <v>3850.0000000000005</v>
       </c>
       <c r="I12">
-        <v>157.30000000000001</v>
+        <v>143</v>
       </c>
       <c r="J12">
-        <v>9.240000000000002</v>
+        <v>8.4</v>
       </c>
       <c r="K12">
         <v>50</v>
@@ -29798,19 +29798,19 @@
         <v>2022</v>
       </c>
       <c r="F13">
-        <v>0.24877966101694915</v>
+        <v>0.49149152542372881</v>
       </c>
       <c r="G13">
-        <v>0.33990000000000004</v>
+        <v>0.36049999999999999</v>
       </c>
       <c r="H13">
-        <v>4427.5</v>
+        <v>3850.0000000000005</v>
       </c>
       <c r="I13">
-        <v>157.30000000000001</v>
+        <v>143</v>
       </c>
       <c r="J13">
-        <v>9.240000000000002</v>
+        <v>8.4</v>
       </c>
       <c r="K13">
         <v>50</v>
@@ -29851,19 +29851,19 @@
         <v>2022</v>
       </c>
       <c r="F14">
-        <v>0.35800000000000004</v>
+        <v>0.22450847457627116</v>
       </c>
       <c r="G14">
-        <v>0.36050000000000004</v>
+        <v>0.33990000000000004</v>
       </c>
       <c r="H14">
-        <v>3850.0000000000009</v>
+        <v>4427.5</v>
       </c>
       <c r="I14">
-        <v>143</v>
+        <v>157.30000000000001</v>
       </c>
       <c r="J14">
-        <v>8.4</v>
+        <v>9.240000000000002</v>
       </c>
       <c r="K14">
         <v>50</v>
@@ -29904,7 +29904,7 @@
         <v>2022</v>
       </c>
       <c r="F15">
-        <v>0.39440677966101695</v>
+        <v>0.51576271186440681</v>
       </c>
       <c r="G15">
         <v>0.36049999999999999</v>
@@ -29957,19 +29957,19 @@
         <v>2022</v>
       </c>
       <c r="F16">
-        <v>0.51576271186440681</v>
+        <v>0.27911864406779663</v>
       </c>
       <c r="G16">
-        <v>0.36049999999999999</v>
+        <v>0.33990000000000004</v>
       </c>
       <c r="H16">
-        <v>3850.0000000000005</v>
+        <v>4427.5</v>
       </c>
       <c r="I16">
-        <v>143</v>
+        <v>157.30000000000001</v>
       </c>
       <c r="J16">
-        <v>8.4</v>
+        <v>9.240000000000002</v>
       </c>
       <c r="K16">
         <v>50</v>
@@ -30010,7 +30010,7 @@
         <v>2022</v>
       </c>
       <c r="F17">
-        <v>1.0679322033898306</v>
+        <v>0.39440677966101695</v>
       </c>
       <c r="G17">
         <v>0.36049999999999999</v>
@@ -30063,19 +30063,19 @@
         <v>2022</v>
       </c>
       <c r="F18">
-        <v>0.22450847457627116</v>
+        <v>0.35800000000000004</v>
       </c>
       <c r="G18">
-        <v>0.33990000000000004</v>
+        <v>0.36050000000000004</v>
       </c>
       <c r="H18">
-        <v>4427.5</v>
+        <v>3850.0000000000009</v>
       </c>
       <c r="I18">
-        <v>157.30000000000001</v>
+        <v>143</v>
       </c>
       <c r="J18">
-        <v>9.240000000000002</v>
+        <v>8.4</v>
       </c>
       <c r="K18">
         <v>50</v>
@@ -30110,7 +30110,7 @@
         <v>13</v>
       </c>
       <c r="D19" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E19">
         <v>2008</v>
@@ -30163,7 +30163,7 @@
         <v>13</v>
       </c>
       <c r="D20" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E20">
         <v>1998</v>
@@ -30216,7 +30216,7 @@
         <v>13</v>
       </c>
       <c r="D21" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E21">
         <v>2008</v>
@@ -30269,7 +30269,7 @@
         <v>13</v>
       </c>
       <c r="D22" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E22">
         <v>2001</v>
@@ -30322,7 +30322,7 @@
         <v>13</v>
       </c>
       <c r="D23" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E23">
         <v>2013</v>
@@ -30375,7 +30375,7 @@
         <v>13</v>
       </c>
       <c r="D24" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E24">
         <v>1965</v>
@@ -30428,7 +30428,7 @@
         <v>13</v>
       </c>
       <c r="D25" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E25">
         <v>2003</v>
@@ -30481,7 +30481,7 @@
         <v>13</v>
       </c>
       <c r="D26" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="E26">
         <v>2009</v>
@@ -30534,7 +30534,7 @@
         <v>13</v>
       </c>
       <c r="D27" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E27">
         <v>2018</v>
@@ -30587,7 +30587,7 @@
         <v>13</v>
       </c>
       <c r="D28" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E28">
         <v>2009</v>
@@ -30646,19 +30646,19 @@
         <v>2022</v>
       </c>
       <c r="F29">
-        <v>0.61803468208092449</v>
+        <v>0.1997687861271675</v>
       </c>
       <c r="G29">
-        <v>0.37080000000000002</v>
+        <v>0.35020000000000007</v>
       </c>
       <c r="H29">
-        <v>2200</v>
+        <v>2530</v>
       </c>
       <c r="I29">
-        <v>66</v>
+        <v>72.600000000000009</v>
       </c>
       <c r="J29">
-        <v>5.25</v>
+        <v>5.7750000000000004</v>
       </c>
       <c r="K29">
         <v>50</v>
@@ -30699,19 +30699,19 @@
         <v>2022</v>
       </c>
       <c r="F30">
-        <v>0.18416184971098257</v>
+        <v>0.61803468208092449</v>
       </c>
       <c r="G30">
-        <v>0.35020000000000001</v>
+        <v>0.37080000000000002</v>
       </c>
       <c r="H30">
-        <v>2530</v>
+        <v>2200</v>
       </c>
       <c r="I30">
-        <v>72.600000000000009</v>
+        <v>66</v>
       </c>
       <c r="J30">
-        <v>5.7750000000000004</v>
+        <v>5.25</v>
       </c>
       <c r="K30">
         <v>50</v>
@@ -30752,10 +30752,10 @@
         <v>2022</v>
       </c>
       <c r="F31">
-        <v>0.1997687861271675</v>
+        <v>0.18416184971098257</v>
       </c>
       <c r="G31">
-        <v>0.35020000000000007</v>
+        <v>0.35020000000000001</v>
       </c>
       <c r="H31">
         <v>2530</v>
@@ -30852,7 +30852,7 @@
         <v>33</v>
       </c>
       <c r="D33" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E33">
         <v>1992</v>
@@ -30905,7 +30905,7 @@
         <v>33</v>
       </c>
       <c r="D34" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E34">
         <v>1993</v>
@@ -30958,7 +30958,7 @@
         <v>33</v>
       </c>
       <c r="D35" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E35">
         <v>2005</v>
@@ -31011,7 +31011,7 @@
         <v>33</v>
       </c>
       <c r="D36" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E36">
         <v>1986</v>
@@ -31064,7 +31064,7 @@
         <v>33</v>
       </c>
       <c r="D37" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E37">
         <v>1991</v>
@@ -31117,7 +31117,7 @@
         <v>33</v>
       </c>
       <c r="D38" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E38">
         <v>1992</v>
@@ -31170,7 +31170,7 @@
         <v>33</v>
       </c>
       <c r="D39" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E39">
         <v>1993</v>
@@ -31223,7 +31223,7 @@
         <v>33</v>
       </c>
       <c r="D40" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="E40">
         <v>2009</v>
@@ -31276,7 +31276,7 @@
         <v>33</v>
       </c>
       <c r="D41" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="E41">
         <v>2010</v>
@@ -31329,7 +31329,7 @@
         <v>33</v>
       </c>
       <c r="D42" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="E42">
         <v>2010</v>
@@ -31388,7 +31388,7 @@
         <v>2022</v>
       </c>
       <c r="F43">
-        <v>0.27724868122098173</v>
+        <v>0.18546328163587858</v>
       </c>
       <c r="G43">
         <v>0.59739999999999993</v>
@@ -31441,7 +31441,7 @@
         <v>2022</v>
       </c>
       <c r="F44">
-        <v>0.35938242023115652</v>
+        <v>0.35540820705324488</v>
       </c>
       <c r="G44">
         <v>0.61799999999999999</v>
@@ -31453,7 +31453,7 @@
         <v>33</v>
       </c>
       <c r="J44">
-        <v>3.15</v>
+        <v>3.1500000000000008</v>
       </c>
       <c r="K44">
         <v>50</v>
@@ -31494,7 +31494,7 @@
         <v>2022</v>
       </c>
       <c r="F45">
-        <v>0.15976336975204969</v>
+        <v>0.28841432776844789</v>
       </c>
       <c r="G45">
         <v>0.59739999999999993</v>
@@ -31506,7 +31506,7 @@
         <v>36.300000000000004</v>
       </c>
       <c r="J45">
-        <v>3.4649999999999999</v>
+        <v>3.4650000000000003</v>
       </c>
       <c r="K45">
         <v>50</v>
@@ -31547,7 +31547,7 @@
         <v>2022</v>
       </c>
       <c r="F46">
-        <v>0.20628058875827313</v>
+        <v>0.15976336975204969</v>
       </c>
       <c r="G46">
         <v>0.59739999999999993</v>
@@ -31559,7 +31559,7 @@
         <v>36.300000000000004</v>
       </c>
       <c r="J46">
-        <v>3.4650000000000003</v>
+        <v>3.4649999999999999</v>
       </c>
       <c r="K46">
         <v>50</v>
@@ -31600,19 +31600,19 @@
         <v>2022</v>
       </c>
       <c r="F47">
-        <v>0.18092132371826522</v>
+        <v>0.39176279521880841</v>
       </c>
       <c r="G47">
-        <v>0.59739999999999993</v>
+        <v>0.61799999999999999</v>
       </c>
       <c r="H47">
-        <v>1265</v>
+        <v>1100</v>
       </c>
       <c r="I47">
-        <v>36.300000000000004</v>
+        <v>33</v>
       </c>
       <c r="J47">
-        <v>3.4649999999999999</v>
+        <v>3.1500000000000004</v>
       </c>
       <c r="K47">
         <v>50</v>
@@ -31653,7 +31653,7 @@
         <v>2022</v>
       </c>
       <c r="F48">
-        <v>0.20675370937469117</v>
+        <v>0.22104195199051649</v>
       </c>
       <c r="G48">
         <v>0.59739999999999993</v>
@@ -31706,19 +31706,19 @@
         <v>2022</v>
       </c>
       <c r="F49">
-        <v>0.23958828015410435</v>
+        <v>0.30961013138397686</v>
       </c>
       <c r="G49">
-        <v>0.59739999999999993</v>
+        <v>0.61799999999999999</v>
       </c>
       <c r="H49">
-        <v>1265</v>
+        <v>1100</v>
       </c>
       <c r="I49">
-        <v>36.300000000000004</v>
+        <v>33</v>
       </c>
       <c r="J49">
-        <v>3.4650000000000003</v>
+        <v>3.1500000000000004</v>
       </c>
       <c r="K49">
         <v>50</v>
@@ -31753,13 +31753,13 @@
         <v>49</v>
       </c>
       <c r="D50" t="s">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="E50">
         <v>2022</v>
       </c>
       <c r="F50">
-        <v>0.21574300108663427</v>
+        <v>0.16540296749975292</v>
       </c>
       <c r="G50">
         <v>0.59739999999999993</v>
@@ -31806,13 +31806,13 @@
         <v>49</v>
       </c>
       <c r="D51" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E51">
         <v>2022</v>
       </c>
       <c r="F51">
-        <v>0.15291258322631621</v>
+        <v>0.24280550034574713</v>
       </c>
       <c r="G51">
         <v>0.59739999999999993</v>
@@ -31821,10 +31821,10 @@
         <v>1265</v>
       </c>
       <c r="I51">
-        <v>36.300000000000004</v>
+        <v>36.299999999999997</v>
       </c>
       <c r="J51">
-        <v>3.4649999999999999</v>
+        <v>3.4650000000000003</v>
       </c>
       <c r="K51">
         <v>50</v>
@@ -31859,13 +31859,13 @@
         <v>49</v>
       </c>
       <c r="D52" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E52">
         <v>2022</v>
       </c>
       <c r="F52">
-        <v>0.16180725081497568</v>
+        <v>0.18092132371826522</v>
       </c>
       <c r="G52">
         <v>0.59739999999999993</v>
@@ -31912,13 +31912,13 @@
         <v>49</v>
       </c>
       <c r="D53" t="s">
-        <v>59</v>
+        <v>19</v>
       </c>
       <c r="E53">
         <v>2022</v>
       </c>
       <c r="F53">
-        <v>0.15139859725377844</v>
+        <v>0.15404807270571955</v>
       </c>
       <c r="G53">
         <v>0.59739999999999993</v>
@@ -31930,7 +31930,7 @@
         <v>36.300000000000004</v>
       </c>
       <c r="J53">
-        <v>3.4650000000000003</v>
+        <v>3.4649999999999999</v>
       </c>
       <c r="K53">
         <v>50</v>
@@ -31971,7 +31971,7 @@
         <v>2022</v>
       </c>
       <c r="F54">
-        <v>0.15726529289736232</v>
+        <v>0.20675370937469117</v>
       </c>
       <c r="G54">
         <v>0.59739999999999993</v>
@@ -32018,13 +32018,13 @@
         <v>49</v>
       </c>
       <c r="D55" t="s">
-        <v>15</v>
+        <v>61</v>
       </c>
       <c r="E55">
         <v>2022</v>
       </c>
       <c r="F55">
-        <v>0.15404807270571955</v>
+        <v>0.16748469821199241</v>
       </c>
       <c r="G55">
         <v>0.59739999999999993</v>
@@ -32036,7 +32036,7 @@
         <v>36.300000000000004</v>
       </c>
       <c r="J55">
-        <v>3.4649999999999999</v>
+        <v>3.4650000000000007</v>
       </c>
       <c r="K55">
         <v>50</v>
@@ -32071,13 +32071,13 @@
         <v>49</v>
       </c>
       <c r="D56" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E56">
         <v>2022</v>
       </c>
       <c r="F56">
-        <v>0.17713635878692077</v>
+        <v>0.15139859725377844</v>
       </c>
       <c r="G56">
         <v>0.59739999999999993</v>
@@ -32089,7 +32089,7 @@
         <v>36.300000000000004</v>
       </c>
       <c r="J56">
-        <v>3.4649999999999999</v>
+        <v>3.4650000000000003</v>
       </c>
       <c r="K56">
         <v>50</v>
@@ -32124,13 +32124,13 @@
         <v>49</v>
       </c>
       <c r="D57" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E57">
         <v>2022</v>
       </c>
       <c r="F57">
-        <v>0.21252578089499147</v>
+        <v>0.15139859725377844</v>
       </c>
       <c r="G57">
         <v>0.59739999999999993</v>
@@ -32177,13 +32177,13 @@
         <v>49</v>
       </c>
       <c r="D58" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E58">
         <v>2022</v>
       </c>
       <c r="F58">
-        <v>0.15139859725377844</v>
+        <v>0.15707604465079511</v>
       </c>
       <c r="G58">
         <v>0.59739999999999993</v>
@@ -32230,13 +32230,13 @@
         <v>49</v>
       </c>
       <c r="D59" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E59">
         <v>2022</v>
       </c>
       <c r="F59">
-        <v>0.15707604465079511</v>
+        <v>0.20628058875827313</v>
       </c>
       <c r="G59">
         <v>0.59739999999999993</v>
@@ -32283,7 +32283,7 @@
         <v>49</v>
       </c>
       <c r="D60" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E60">
         <v>2022</v>
@@ -32336,13 +32336,13 @@
         <v>49</v>
       </c>
       <c r="D61" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E61">
         <v>2022</v>
       </c>
       <c r="F61">
-        <v>0.15139859725377844</v>
+        <v>0.23958828015410435</v>
       </c>
       <c r="G61">
         <v>0.59739999999999993</v>
@@ -32389,13 +32389,13 @@
         <v>49</v>
       </c>
       <c r="D62" t="s">
-        <v>67</v>
+        <v>37</v>
       </c>
       <c r="E62">
         <v>2022</v>
       </c>
       <c r="F62">
-        <v>0.16748469821199241</v>
+        <v>0.21574300108663427</v>
       </c>
       <c r="G62">
         <v>0.59739999999999993</v>
@@ -32407,7 +32407,7 @@
         <v>36.300000000000004</v>
       </c>
       <c r="J62">
-        <v>3.4650000000000007</v>
+        <v>3.4650000000000003</v>
       </c>
       <c r="K62">
         <v>50</v>
@@ -32448,7 +32448,7 @@
         <v>2022</v>
       </c>
       <c r="F63">
-        <v>0.22104195199051649</v>
+        <v>0.27724868122098173</v>
       </c>
       <c r="G63">
         <v>0.59739999999999993</v>
@@ -32501,19 +32501,19 @@
         <v>2022</v>
       </c>
       <c r="F64">
-        <v>0.30961013138397686</v>
+        <v>0.15291258322631621</v>
       </c>
       <c r="G64">
-        <v>0.61799999999999999</v>
+        <v>0.59739999999999993</v>
       </c>
       <c r="H64">
-        <v>1100</v>
+        <v>1265</v>
       </c>
       <c r="I64">
-        <v>33</v>
+        <v>36.300000000000004</v>
       </c>
       <c r="J64">
-        <v>3.1500000000000004</v>
+        <v>3.4649999999999999</v>
       </c>
       <c r="K64">
         <v>50</v>
@@ -32554,7 +32554,7 @@
         <v>2022</v>
       </c>
       <c r="F65">
-        <v>0.16540296749975292</v>
+        <v>0.16180725081497568</v>
       </c>
       <c r="G65">
         <v>0.59739999999999993</v>
@@ -32566,7 +32566,7 @@
         <v>36.300000000000004</v>
       </c>
       <c r="J65">
-        <v>3.4650000000000003</v>
+        <v>3.4649999999999999</v>
       </c>
       <c r="K65">
         <v>50</v>
@@ -32607,19 +32607,19 @@
         <v>2022</v>
       </c>
       <c r="F66">
-        <v>0.35540820705324488</v>
+        <v>0.15726529289736232</v>
       </c>
       <c r="G66">
-        <v>0.61799999999999999</v>
+        <v>0.59739999999999993</v>
       </c>
       <c r="H66">
-        <v>1100</v>
+        <v>1265</v>
       </c>
       <c r="I66">
-        <v>33</v>
+        <v>36.300000000000004</v>
       </c>
       <c r="J66">
-        <v>3.1500000000000008</v>
+        <v>3.4650000000000003</v>
       </c>
       <c r="K66">
         <v>50</v>
@@ -32660,19 +32660,19 @@
         <v>2022</v>
       </c>
       <c r="F67">
-        <v>0.39176279521880841</v>
+        <v>0.16407822977378236</v>
       </c>
       <c r="G67">
-        <v>0.61799999999999999</v>
+        <v>0.59739999999999993</v>
       </c>
       <c r="H67">
-        <v>1100</v>
+        <v>1265</v>
       </c>
       <c r="I67">
-        <v>33</v>
+        <v>36.300000000000004</v>
       </c>
       <c r="J67">
-        <v>3.1500000000000004</v>
+        <v>3.4650000000000003</v>
       </c>
       <c r="K67">
         <v>50</v>
@@ -32713,7 +32713,7 @@
         <v>2022</v>
       </c>
       <c r="F68">
-        <v>0.18546328163587858</v>
+        <v>0.15253408673318178</v>
       </c>
       <c r="G68">
         <v>0.59739999999999993</v>
@@ -32766,7 +32766,7 @@
         <v>2022</v>
       </c>
       <c r="F69">
-        <v>0.28841432776844789</v>
+        <v>0.22804413711350377</v>
       </c>
       <c r="G69">
         <v>0.59739999999999993</v>
@@ -32819,7 +32819,7 @@
         <v>2022</v>
       </c>
       <c r="F70">
-        <v>0.24280550034574713</v>
+        <v>0.21952796601797872</v>
       </c>
       <c r="G70">
         <v>0.59739999999999993</v>
@@ -32828,7 +32828,7 @@
         <v>1265</v>
       </c>
       <c r="I70">
-        <v>36.299999999999997</v>
+        <v>36.300000000000004</v>
       </c>
       <c r="J70">
         <v>3.4650000000000003</v>
@@ -32872,19 +32872,19 @@
         <v>2022</v>
       </c>
       <c r="F71">
-        <v>0.22804413711350377</v>
+        <v>0.35938242023115652</v>
       </c>
       <c r="G71">
-        <v>0.59739999999999993</v>
+        <v>0.61799999999999999</v>
       </c>
       <c r="H71">
-        <v>1265</v>
+        <v>1100</v>
       </c>
       <c r="I71">
-        <v>36.300000000000004</v>
+        <v>33</v>
       </c>
       <c r="J71">
-        <v>3.4650000000000003</v>
+        <v>3.15</v>
       </c>
       <c r="K71">
         <v>50</v>
@@ -32925,7 +32925,7 @@
         <v>2022</v>
       </c>
       <c r="F72">
-        <v>0.16407822977378236</v>
+        <v>0.17713635878692077</v>
       </c>
       <c r="G72">
         <v>0.59739999999999993</v>
@@ -32937,7 +32937,7 @@
         <v>36.300000000000004</v>
       </c>
       <c r="J72">
-        <v>3.4650000000000003</v>
+        <v>3.4649999999999999</v>
       </c>
       <c r="K72">
         <v>50</v>
@@ -32978,7 +32978,7 @@
         <v>2022</v>
       </c>
       <c r="F73">
-        <v>0.15253408673318178</v>
+        <v>0.21252578089499147</v>
       </c>
       <c r="G73">
         <v>0.59739999999999993</v>
@@ -33031,7 +33031,7 @@
         <v>2022</v>
       </c>
       <c r="F74">
-        <v>0.21952796601797872</v>
+        <v>0.15139859725377844</v>
       </c>
       <c r="G74">
         <v>0.59739999999999993</v>
@@ -33078,7 +33078,7 @@
         <v>49</v>
       </c>
       <c r="D75" t="s">
-        <v>57</v>
+        <v>69</v>
       </c>
       <c r="E75">
         <v>2006</v>
@@ -33131,7 +33131,7 @@
         <v>49</v>
       </c>
       <c r="D76" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="E76">
         <v>2012</v>
@@ -33184,7 +33184,7 @@
         <v>49</v>
       </c>
       <c r="D77" t="s">
-        <v>51</v>
+        <v>76</v>
       </c>
       <c r="E77">
         <v>1993</v>
@@ -33237,7 +33237,7 @@
         <v>49</v>
       </c>
       <c r="D78" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="E78">
         <v>2011</v>
@@ -33290,7 +33290,7 @@
         <v>49</v>
       </c>
       <c r="D79" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="E79">
         <v>2005</v>
@@ -33343,7 +33343,7 @@
         <v>49</v>
       </c>
       <c r="D80" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="E80">
         <v>2006</v>
@@ -33396,7 +33396,7 @@
         <v>49</v>
       </c>
       <c r="D81" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="E81">
         <v>2006</v>
@@ -33502,7 +33502,7 @@
         <v>49</v>
       </c>
       <c r="D83" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="E83">
         <v>2003</v>
@@ -33661,7 +33661,7 @@
         <v>49</v>
       </c>
       <c r="D86" t="s">
-        <v>62</v>
+        <v>78</v>
       </c>
       <c r="E86">
         <v>2004</v>
@@ -33714,7 +33714,7 @@
         <v>49</v>
       </c>
       <c r="D87" t="s">
-        <v>62</v>
+        <v>78</v>
       </c>
       <c r="E87">
         <v>2005</v>
@@ -33767,7 +33767,7 @@
         <v>49</v>
       </c>
       <c r="D88" t="s">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="E88">
         <v>2005</v>
@@ -33820,7 +33820,7 @@
         <v>49</v>
       </c>
       <c r="D89" t="s">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="E89">
         <v>2005</v>
@@ -33873,7 +33873,7 @@
         <v>49</v>
       </c>
       <c r="D90" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="E90">
         <v>2004</v>
@@ -33926,7 +33926,7 @@
         <v>49</v>
       </c>
       <c r="D91" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="E91">
         <v>2004</v>
@@ -33979,7 +33979,7 @@
         <v>49</v>
       </c>
       <c r="D92" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="E92">
         <v>2004</v>
@@ -34032,7 +34032,7 @@
         <v>49</v>
       </c>
       <c r="D93" t="s">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="E93">
         <v>2008</v>
@@ -34085,7 +34085,7 @@
         <v>49</v>
       </c>
       <c r="D94" t="s">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="E94">
         <v>2008</v>
@@ -34138,7 +34138,7 @@
         <v>49</v>
       </c>
       <c r="D95" t="s">
-        <v>74</v>
+        <v>52</v>
       </c>
       <c r="E95">
         <v>2002</v>
@@ -34191,7 +34191,7 @@
         <v>49</v>
       </c>
       <c r="D96" t="s">
-        <v>74</v>
+        <v>52</v>
       </c>
       <c r="E96">
         <v>2002</v>
@@ -34244,7 +34244,7 @@
         <v>49</v>
       </c>
       <c r="D97" t="s">
-        <v>74</v>
+        <v>52</v>
       </c>
       <c r="E97">
         <v>2003</v>
@@ -34297,7 +34297,7 @@
         <v>49</v>
       </c>
       <c r="D98" t="s">
-        <v>74</v>
+        <v>52</v>
       </c>
       <c r="E98">
         <v>2003</v>
@@ -34509,7 +34509,7 @@
         <v>49</v>
       </c>
       <c r="D102" t="s">
-        <v>51</v>
+        <v>76</v>
       </c>
       <c r="E102">
         <v>2023</v>
@@ -34562,7 +34562,7 @@
         <v>49</v>
       </c>
       <c r="D103" t="s">
-        <v>51</v>
+        <v>76</v>
       </c>
       <c r="E103">
         <v>2001</v>
@@ -34615,7 +34615,7 @@
         <v>49</v>
       </c>
       <c r="D104" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="E104">
         <v>1999</v>
@@ -34668,7 +34668,7 @@
         <v>49</v>
       </c>
       <c r="D105" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="E105">
         <v>2010</v>
@@ -34827,7 +34827,7 @@
         <v>49</v>
       </c>
       <c r="D108" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="E108">
         <v>1997</v>
@@ -34880,7 +34880,7 @@
         <v>49</v>
       </c>
       <c r="D109" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="E109">
         <v>1997</v>
@@ -34933,7 +34933,7 @@
         <v>49</v>
       </c>
       <c r="D110" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="E110">
         <v>1998</v>
@@ -34986,7 +34986,7 @@
         <v>49</v>
       </c>
       <c r="D111" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="E111">
         <v>1999</v>
@@ -35092,7 +35092,7 @@
         <v>49</v>
       </c>
       <c r="D113" t="s">
-        <v>71</v>
+        <v>51</v>
       </c>
       <c r="E113">
         <v>2010</v>
@@ -35145,7 +35145,7 @@
         <v>49</v>
       </c>
       <c r="D114" t="s">
-        <v>68</v>
+        <v>55</v>
       </c>
       <c r="E114">
         <v>2003</v>
@@ -35198,7 +35198,7 @@
         <v>49</v>
       </c>
       <c r="D115" t="s">
-        <v>68</v>
+        <v>55</v>
       </c>
       <c r="E115">
         <v>2003</v>
@@ -35251,7 +35251,7 @@
         <v>49</v>
       </c>
       <c r="D116" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="E116">
         <v>2006</v>
@@ -35516,7 +35516,7 @@
         <v>49</v>
       </c>
       <c r="D121" t="s">
-        <v>71</v>
+        <v>51</v>
       </c>
       <c r="E121">
         <v>2010</v>
@@ -35569,7 +35569,7 @@
         <v>49</v>
       </c>
       <c r="D122" t="s">
-        <v>71</v>
+        <v>51</v>
       </c>
       <c r="E122">
         <v>2010</v>
@@ -35728,7 +35728,7 @@
         <v>49</v>
       </c>
       <c r="D125" t="s">
-        <v>61</v>
+        <v>77</v>
       </c>
       <c r="E125">
         <v>2018</v>
@@ -35993,7 +35993,7 @@
         <v>49</v>
       </c>
       <c r="D130" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E130">
         <v>2010</v>
@@ -36046,7 +36046,7 @@
         <v>49</v>
       </c>
       <c r="D131" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E131">
         <v>2010</v>
@@ -36099,7 +36099,7 @@
         <v>49</v>
       </c>
       <c r="D132" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E132">
         <v>2004</v>
@@ -36152,7 +36152,7 @@
         <v>49</v>
       </c>
       <c r="D133" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E133">
         <v>2004</v>
@@ -36205,7 +36205,7 @@
         <v>49</v>
       </c>
       <c r="D134" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="E134">
         <v>2008</v>
@@ -36364,7 +36364,7 @@
         <v>49</v>
       </c>
       <c r="D137" t="s">
-        <v>72</v>
+        <v>54</v>
       </c>
       <c r="E137">
         <v>2005</v>
@@ -36417,7 +36417,7 @@
         <v>49</v>
       </c>
       <c r="D138" t="s">
-        <v>72</v>
+        <v>54</v>
       </c>
       <c r="E138">
         <v>2005</v>
@@ -36470,7 +36470,7 @@
         <v>49</v>
       </c>
       <c r="D139" t="s">
-        <v>69</v>
+        <v>56</v>
       </c>
       <c r="E139">
         <v>2015</v>
@@ -36523,7 +36523,7 @@
         <v>49</v>
       </c>
       <c r="D140" t="s">
-        <v>69</v>
+        <v>56</v>
       </c>
       <c r="E140">
         <v>2004</v>
@@ -36576,7 +36576,7 @@
         <v>49</v>
       </c>
       <c r="D141" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E141">
         <v>2006</v>
@@ -36682,7 +36682,7 @@
         <v>49</v>
       </c>
       <c r="D143" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="E143">
         <v>2004</v>
@@ -36735,7 +36735,7 @@
         <v>49</v>
       </c>
       <c r="D144" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="E144">
         <v>2005</v>
@@ -36788,7 +36788,7 @@
         <v>49</v>
       </c>
       <c r="D145" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="E145">
         <v>2006</v>
@@ -36841,7 +36841,7 @@
         <v>49</v>
       </c>
       <c r="D146" t="s">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="E146">
         <v>2008</v>
@@ -36894,7 +36894,7 @@
         <v>49</v>
       </c>
       <c r="D147" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="E147">
         <v>2007</v>
@@ -37053,7 +37053,7 @@
         <v>49</v>
       </c>
       <c r="D150" t="s">
-        <v>73</v>
+        <v>50</v>
       </c>
       <c r="E150">
         <v>2026</v>
@@ -37106,7 +37106,7 @@
         <v>49</v>
       </c>
       <c r="D151" t="s">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="E151">
         <v>2022</v>
@@ -37265,7 +37265,7 @@
         <v>49</v>
       </c>
       <c r="D154" t="s">
-        <v>68</v>
+        <v>55</v>
       </c>
       <c r="E154">
         <v>2003</v>
@@ -37318,7 +37318,7 @@
         <v>49</v>
       </c>
       <c r="D155" t="s">
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="E155">
         <v>2008</v>
@@ -37371,7 +37371,7 @@
         <v>49</v>
       </c>
       <c r="D156" t="s">
-        <v>71</v>
+        <v>51</v>
       </c>
       <c r="E156">
         <v>1999</v>
@@ -37424,7 +37424,7 @@
         <v>49</v>
       </c>
       <c r="D157" t="s">
-        <v>71</v>
+        <v>51</v>
       </c>
       <c r="E157">
         <v>1999</v>
@@ -37477,7 +37477,7 @@
         <v>49</v>
       </c>
       <c r="D158" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="E158">
         <v>1997</v>
@@ -37636,7 +37636,7 @@
         <v>49</v>
       </c>
       <c r="D161" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="E161">
         <v>2006</v>
@@ -37742,7 +37742,7 @@
         <v>49</v>
       </c>
       <c r="D163" t="s">
-        <v>61</v>
+        <v>77</v>
       </c>
       <c r="E163">
         <v>2007</v>
@@ -38272,7 +38272,7 @@
         <v>49</v>
       </c>
       <c r="D173" t="s">
-        <v>51</v>
+        <v>76</v>
       </c>
       <c r="E173">
         <v>1992</v>
@@ -38378,7 +38378,7 @@
         <v>49</v>
       </c>
       <c r="D175" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="E175">
         <v>2015</v>
@@ -39597,7 +39597,7 @@
         <v>49</v>
       </c>
       <c r="D198" t="s">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="E198">
         <v>2004</v>
@@ -39650,7 +39650,7 @@
         <v>49</v>
       </c>
       <c r="D199" t="s">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="E199">
         <v>2008</v>
@@ -40021,7 +40021,7 @@
         <v>49</v>
       </c>
       <c r="D206" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E206">
         <v>2022</v>
@@ -40074,7 +40074,7 @@
         <v>49</v>
       </c>
       <c r="D207" t="s">
-        <v>71</v>
+        <v>51</v>
       </c>
       <c r="E207">
         <v>2005</v>
@@ -40127,7 +40127,7 @@
         <v>49</v>
       </c>
       <c r="D208" t="s">
-        <v>71</v>
+        <v>51</v>
       </c>
       <c r="E208">
         <v>2015</v>
@@ -40657,7 +40657,7 @@
         <v>49</v>
       </c>
       <c r="D218" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E218">
         <v>2022</v>
@@ -40922,7 +40922,7 @@
         <v>49</v>
       </c>
       <c r="D223" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E223">
         <v>2022</v>
@@ -41081,7 +41081,7 @@
         <v>49</v>
       </c>
       <c r="D226" t="s">
-        <v>73</v>
+        <v>50</v>
       </c>
       <c r="E226">
         <v>2009</v>
@@ -41770,7 +41770,7 @@
         <v>49</v>
       </c>
       <c r="D239" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E239">
         <v>1994</v>
@@ -41929,7 +41929,7 @@
         <v>49</v>
       </c>
       <c r="D242" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E242">
         <v>1990</v>
@@ -41982,7 +41982,7 @@
         <v>49</v>
       </c>
       <c r="D243" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E243">
         <v>2022</v>
@@ -42194,7 +42194,7 @@
         <v>49</v>
       </c>
       <c r="D247" t="s">
-        <v>72</v>
+        <v>54</v>
       </c>
       <c r="E247">
         <v>2024</v>
@@ -42247,7 +42247,7 @@
         <v>49</v>
       </c>
       <c r="D248" t="s">
-        <v>69</v>
+        <v>56</v>
       </c>
       <c r="E248">
         <v>2023</v>
@@ -42300,7 +42300,7 @@
         <v>49</v>
       </c>
       <c r="D249" t="s">
-        <v>69</v>
+        <v>56</v>
       </c>
       <c r="E249">
         <v>2023</v>
@@ -42353,7 +42353,7 @@
         <v>49</v>
       </c>
       <c r="D250" t="s">
-        <v>61</v>
+        <v>77</v>
       </c>
       <c r="E250">
         <v>1997</v>
@@ -42777,7 +42777,7 @@
         <v>49</v>
       </c>
       <c r="D258" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="E258">
         <v>1999</v>
@@ -42830,7 +42830,7 @@
         <v>49</v>
       </c>
       <c r="D259" t="s">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="E259">
         <v>2008</v>
@@ -42883,7 +42883,7 @@
         <v>49</v>
       </c>
       <c r="D260" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E260">
         <v>1992</v>
@@ -42936,7 +42936,7 @@
         <v>49</v>
       </c>
       <c r="D261" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E261">
         <v>2005</v>
@@ -43201,7 +43201,7 @@
         <v>49</v>
       </c>
       <c r="D266" t="s">
-        <v>69</v>
+        <v>56</v>
       </c>
       <c r="E266">
         <v>2015</v>
@@ -43307,7 +43307,7 @@
         <v>49</v>
       </c>
       <c r="D268" t="s">
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="E268">
         <v>2004</v>
@@ -43572,7 +43572,7 @@
         <v>49</v>
       </c>
       <c r="D273" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="E273">
         <v>2024</v>
@@ -43678,7 +43678,7 @@
         <v>49</v>
       </c>
       <c r="D275" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E275">
         <v>2023</v>
@@ -43890,7 +43890,7 @@
         <v>49</v>
       </c>
       <c r="D279" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="E279">
         <v>1975</v>
@@ -43943,7 +43943,7 @@
         <v>49</v>
       </c>
       <c r="D280" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="E280">
         <v>1975</v>
@@ -43996,7 +43996,7 @@
         <v>49</v>
       </c>
       <c r="D281" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="E281">
         <v>1975</v>
@@ -44049,7 +44049,7 @@
         <v>49</v>
       </c>
       <c r="D282" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="E282">
         <v>1976</v>
@@ -44102,7 +44102,7 @@
         <v>49</v>
       </c>
       <c r="D283" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="E283">
         <v>1975</v>
@@ -44155,7 +44155,7 @@
         <v>49</v>
       </c>
       <c r="D284" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="E284">
         <v>1971</v>
@@ -44208,7 +44208,7 @@
         <v>49</v>
       </c>
       <c r="D285" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="E285">
         <v>1976</v>
@@ -44261,7 +44261,7 @@
         <v>49</v>
       </c>
       <c r="D286" t="s">
-        <v>51</v>
+        <v>76</v>
       </c>
       <c r="E286">
         <v>1985</v>
@@ -44367,7 +44367,7 @@
         <v>49</v>
       </c>
       <c r="D288" t="s">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="E288">
         <v>2015</v>
@@ -44420,7 +44420,7 @@
         <v>49</v>
       </c>
       <c r="D289" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="E289">
         <v>1967</v>
@@ -44473,7 +44473,7 @@
         <v>49</v>
       </c>
       <c r="D290" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="E290">
         <v>1971</v>
@@ -44791,7 +44791,7 @@
         <v>49</v>
       </c>
       <c r="D296" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E296">
         <v>1978</v>
@@ -44844,7 +44844,7 @@
         <v>49</v>
       </c>
       <c r="D297" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E297">
         <v>1981</v>
@@ -44897,7 +44897,7 @@
         <v>49</v>
       </c>
       <c r="D298" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E298">
         <v>1987</v>
@@ -45321,7 +45321,7 @@
         <v>319</v>
       </c>
       <c r="D306" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="E306">
         <v>1991</v>
@@ -45374,7 +45374,7 @@
         <v>319</v>
       </c>
       <c r="D307" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="E307">
         <v>1991</v>
@@ -46434,25 +46434,25 @@
         <v>334</v>
       </c>
       <c r="D327" t="s">
-        <v>335</v>
+        <v>147</v>
       </c>
       <c r="E327">
         <v>2022</v>
       </c>
       <c r="F327">
-        <v>0.19299421182171778</v>
+        <v>4.5464982592616207E-2</v>
       </c>
       <c r="G327">
         <v>1</v>
       </c>
       <c r="H327">
-        <v>3162.5000000000005</v>
+        <v>3712.5000000000005</v>
       </c>
       <c r="I327">
-        <v>60.500000000000014</v>
+        <v>71.5</v>
       </c>
       <c r="J327">
-        <v>2.3100000000000005</v>
+        <v>2.52</v>
       </c>
       <c r="K327">
         <v>100</v>
@@ -46487,13 +46487,13 @@
         <v>334</v>
       </c>
       <c r="D328" t="s">
-        <v>147</v>
+        <v>335</v>
       </c>
       <c r="E328">
         <v>2022</v>
       </c>
       <c r="F328">
-        <v>4.5464982592616207E-2</v>
+        <v>4.4073197411209589E-2</v>
       </c>
       <c r="G328">
         <v>1</v>
@@ -46546,19 +46546,19 @@
         <v>2022</v>
       </c>
       <c r="F329">
-        <v>0.54140443556717466</v>
+        <v>0.10067246145507874</v>
       </c>
       <c r="G329">
         <v>1</v>
       </c>
       <c r="H329">
-        <v>2750</v>
+        <v>3162.5000000000005</v>
       </c>
       <c r="I329">
-        <v>55.000000000000007</v>
+        <v>60.500000000000014</v>
       </c>
       <c r="J329">
-        <v>2.1</v>
+        <v>2.3100000000000005</v>
       </c>
       <c r="K329">
         <v>100</v>
@@ -46593,13 +46593,13 @@
         <v>334</v>
       </c>
       <c r="D330" t="s">
-        <v>317</v>
+        <v>337</v>
       </c>
       <c r="E330">
         <v>2022</v>
       </c>
       <c r="F330">
-        <v>0.13082780705222213</v>
+        <v>6.9589259070330922E-2</v>
       </c>
       <c r="G330">
         <v>1</v>
@@ -46608,7 +46608,7 @@
         <v>3162.5000000000005</v>
       </c>
       <c r="I330">
-        <v>60.500000000000014</v>
+        <v>60.500000000000007</v>
       </c>
       <c r="J330">
         <v>2.3100000000000005</v>
@@ -46646,25 +46646,25 @@
         <v>334</v>
       </c>
       <c r="D331" t="s">
-        <v>337</v>
+        <v>170</v>
       </c>
       <c r="E331">
         <v>2022</v>
       </c>
       <c r="F331">
-        <v>4.1753555442198553E-2</v>
+        <v>0.50939337639482241</v>
       </c>
       <c r="G331">
         <v>1</v>
       </c>
       <c r="H331">
-        <v>3712.5000000000005</v>
+        <v>2750</v>
       </c>
       <c r="I331">
-        <v>71.5</v>
+        <v>55.000000000000007</v>
       </c>
       <c r="J331">
-        <v>2.52</v>
+        <v>2.1</v>
       </c>
       <c r="K331">
         <v>100</v>
@@ -46705,7 +46705,7 @@
         <v>2022</v>
       </c>
       <c r="F332">
-        <v>0.10067246145507874</v>
+        <v>0.10670353057450742</v>
       </c>
       <c r="G332">
         <v>1</v>
@@ -46758,7 +46758,7 @@
         <v>2022</v>
       </c>
       <c r="F333">
-        <v>4.4073197411209589E-2</v>
+        <v>4.3145340623605172E-2</v>
       </c>
       <c r="G333">
         <v>1</v>
@@ -46811,7 +46811,7 @@
         <v>2022</v>
       </c>
       <c r="F334">
-        <v>6.9589259070330922E-2</v>
+        <v>0.20320063648536632</v>
       </c>
       <c r="G334">
         <v>1</v>
@@ -46820,7 +46820,7 @@
         <v>3162.5000000000005</v>
       </c>
       <c r="I334">
-        <v>60.500000000000007</v>
+        <v>60.500000000000014</v>
       </c>
       <c r="J334">
         <v>2.3100000000000005</v>
@@ -46858,25 +46858,25 @@
         <v>334</v>
       </c>
       <c r="D335" t="s">
-        <v>170</v>
+        <v>341</v>
       </c>
       <c r="E335">
         <v>2022</v>
       </c>
       <c r="F335">
-        <v>0.50939337639482241</v>
+        <v>5.8918906012880183E-2</v>
       </c>
       <c r="G335">
         <v>1</v>
       </c>
       <c r="H335">
-        <v>2750</v>
+        <v>3162.5000000000005</v>
       </c>
       <c r="I335">
-        <v>55.000000000000007</v>
+        <v>60.500000000000021</v>
       </c>
       <c r="J335">
-        <v>2.1</v>
+        <v>2.3100000000000005</v>
       </c>
       <c r="K335">
         <v>100</v>
@@ -46911,13 +46911,13 @@
         <v>334</v>
       </c>
       <c r="D336" t="s">
-        <v>341</v>
+        <v>14</v>
       </c>
       <c r="E336">
         <v>2022</v>
       </c>
       <c r="F336">
-        <v>0.10670353057450742</v>
+        <v>8.7682466428616976E-2</v>
       </c>
       <c r="G336">
         <v>1</v>
@@ -46926,7 +46926,7 @@
         <v>3162.5000000000005</v>
       </c>
       <c r="I336">
-        <v>60.500000000000014</v>
+        <v>60.500000000000007</v>
       </c>
       <c r="J336">
         <v>2.3100000000000005</v>
@@ -46970,19 +46970,19 @@
         <v>2022</v>
       </c>
       <c r="F337">
-        <v>4.3145340623605172E-2</v>
+        <v>5.1032123318242681E-2</v>
       </c>
       <c r="G337">
         <v>1</v>
       </c>
       <c r="H337">
-        <v>3712.5000000000005</v>
+        <v>3162.5000000000005</v>
       </c>
       <c r="I337">
-        <v>71.5</v>
+        <v>60.500000000000021</v>
       </c>
       <c r="J337">
-        <v>2.52</v>
+        <v>2.3100000000000005</v>
       </c>
       <c r="K337">
         <v>100</v>
@@ -47017,25 +47017,25 @@
         <v>334</v>
       </c>
       <c r="D338" t="s">
-        <v>343</v>
+        <v>193</v>
       </c>
       <c r="E338">
         <v>2022</v>
       </c>
       <c r="F338">
-        <v>5.8918906012880183E-2</v>
+        <v>0.61052976624370348</v>
       </c>
       <c r="G338">
         <v>1</v>
       </c>
       <c r="H338">
-        <v>3162.5000000000005</v>
+        <v>2750</v>
       </c>
       <c r="I338">
-        <v>60.500000000000021</v>
+        <v>55.000000000000007</v>
       </c>
       <c r="J338">
-        <v>2.3100000000000005</v>
+        <v>2.1</v>
       </c>
       <c r="K338">
         <v>100</v>
@@ -47070,13 +47070,13 @@
         <v>334</v>
       </c>
       <c r="D339" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E339">
         <v>2022</v>
       </c>
       <c r="F339">
-        <v>8.7682466428616976E-2</v>
+        <v>0.11134281451252948</v>
       </c>
       <c r="G339">
         <v>1</v>
@@ -47085,7 +47085,7 @@
         <v>3162.5000000000005</v>
       </c>
       <c r="I339">
-        <v>60.500000000000007</v>
+        <v>60.500000000000014</v>
       </c>
       <c r="J339">
         <v>2.3100000000000005</v>
@@ -47123,13 +47123,13 @@
         <v>334</v>
       </c>
       <c r="D340" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E340">
         <v>2022</v>
       </c>
       <c r="F340">
-        <v>5.1032123318242681E-2</v>
+        <v>0.1577356538927501</v>
       </c>
       <c r="G340">
         <v>1</v>
@@ -47138,7 +47138,7 @@
         <v>3162.5000000000005</v>
       </c>
       <c r="I340">
-        <v>60.500000000000021</v>
+        <v>60.500000000000014</v>
       </c>
       <c r="J340">
         <v>2.3100000000000005</v>
@@ -47176,13 +47176,13 @@
         <v>334</v>
       </c>
       <c r="D341" t="s">
-        <v>345</v>
+        <v>91</v>
       </c>
       <c r="E341">
         <v>2022</v>
       </c>
       <c r="F341">
-        <v>0.20320063648536632</v>
+        <v>0.29181095970158766</v>
       </c>
       <c r="G341">
         <v>1</v>
@@ -47229,25 +47229,25 @@
         <v>334</v>
       </c>
       <c r="D342" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="E342">
         <v>2022</v>
       </c>
       <c r="F342">
-        <v>4.4073197411209589E-2</v>
+        <v>0.35629700644009438</v>
       </c>
       <c r="G342">
         <v>1</v>
       </c>
       <c r="H342">
-        <v>3712.5000000000005</v>
+        <v>2750</v>
       </c>
       <c r="I342">
-        <v>71.5</v>
+        <v>55</v>
       </c>
       <c r="J342">
-        <v>2.52</v>
+        <v>2.1</v>
       </c>
       <c r="K342">
         <v>100</v>
@@ -47282,25 +47282,25 @@
         <v>334</v>
       </c>
       <c r="D343" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="E343">
         <v>2022</v>
       </c>
       <c r="F343">
-        <v>0.57944656385895543</v>
+        <v>6.0310691194286808E-2</v>
       </c>
       <c r="G343">
         <v>1</v>
       </c>
       <c r="H343">
-        <v>2750</v>
+        <v>3162.5000000000005</v>
       </c>
       <c r="I343">
-        <v>55.000000000000007</v>
+        <v>60.500000000000014</v>
       </c>
       <c r="J343">
-        <v>2.1</v>
+        <v>2.3100000000000005</v>
       </c>
       <c r="K343">
         <v>100</v>
@@ -47335,25 +47335,25 @@
         <v>334</v>
       </c>
       <c r="D344" t="s">
-        <v>348</v>
+        <v>57</v>
       </c>
       <c r="E344">
         <v>2022</v>
       </c>
       <c r="F344">
-        <v>1.0883760118599757</v>
+        <v>5.4743550468660328E-2</v>
       </c>
       <c r="G344">
         <v>1</v>
       </c>
       <c r="H344">
-        <v>2750</v>
+        <v>3162.5000000000005</v>
       </c>
       <c r="I344">
-        <v>55.000000000000007</v>
+        <v>60.500000000000014</v>
       </c>
       <c r="J344">
-        <v>2.1</v>
+        <v>2.3100000000000005</v>
       </c>
       <c r="K344">
         <v>100</v>
@@ -47388,25 +47388,25 @@
         <v>334</v>
       </c>
       <c r="D345" t="s">
-        <v>193</v>
+        <v>254</v>
       </c>
       <c r="E345">
         <v>2022</v>
       </c>
       <c r="F345">
-        <v>0.61052976624370348</v>
+        <v>0.22871669814448767</v>
       </c>
       <c r="G345">
         <v>1</v>
       </c>
       <c r="H345">
-        <v>2750</v>
+        <v>3162.5000000000005</v>
       </c>
       <c r="I345">
-        <v>55.000000000000007</v>
+        <v>60.500000000000014</v>
       </c>
       <c r="J345">
-        <v>2.1</v>
+        <v>2.3100000000000005</v>
       </c>
       <c r="K345">
         <v>100</v>
@@ -47441,13 +47441,13 @@
         <v>334</v>
       </c>
       <c r="D346" t="s">
-        <v>21</v>
+        <v>207</v>
       </c>
       <c r="E346">
         <v>2022</v>
       </c>
       <c r="F346">
-        <v>0.11134281451252948</v>
+        <v>7.8403898552572848E-2</v>
       </c>
       <c r="G346">
         <v>1</v>
@@ -47494,13 +47494,13 @@
         <v>334</v>
       </c>
       <c r="D347" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="E347">
         <v>2022</v>
       </c>
       <c r="F347">
-        <v>0.1577356538927501</v>
+        <v>0.19299421182171778</v>
       </c>
       <c r="G347">
         <v>1</v>
@@ -47547,13 +47547,13 @@
         <v>334</v>
       </c>
       <c r="D348" t="s">
-        <v>91</v>
+        <v>51</v>
       </c>
       <c r="E348">
         <v>2022</v>
       </c>
       <c r="F348">
-        <v>0.29181095970158766</v>
+        <v>0.23196419690110309</v>
       </c>
       <c r="G348">
         <v>1</v>
@@ -47600,13 +47600,13 @@
         <v>334</v>
       </c>
       <c r="D349" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="E349">
         <v>2022</v>
       </c>
       <c r="F349">
-        <v>0.15541601192373908</v>
+        <v>0.13036387865841995</v>
       </c>
       <c r="G349">
         <v>1</v>
@@ -47653,25 +47653,25 @@
         <v>334</v>
       </c>
       <c r="D350" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="E350">
         <v>2022</v>
       </c>
       <c r="F350">
-        <v>6.3558189950902247E-2</v>
+        <v>0.56367299846968055</v>
       </c>
       <c r="G350">
         <v>1</v>
       </c>
       <c r="H350">
-        <v>3162.5000000000005</v>
+        <v>2750</v>
       </c>
       <c r="I350">
-        <v>60.500000000000014</v>
+        <v>55.000000000000007</v>
       </c>
       <c r="J350">
-        <v>2.3100000000000005</v>
+        <v>2.1</v>
       </c>
       <c r="K350">
         <v>100</v>
@@ -47706,25 +47706,25 @@
         <v>334</v>
       </c>
       <c r="D351" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="E351">
         <v>2022</v>
       </c>
       <c r="F351">
-        <v>0.56367299846968055</v>
+        <v>4.1753555442198553E-2</v>
       </c>
       <c r="G351">
         <v>1</v>
       </c>
       <c r="H351">
-        <v>2750</v>
+        <v>3712.5000000000005</v>
       </c>
       <c r="I351">
-        <v>55.000000000000007</v>
+        <v>71.5</v>
       </c>
       <c r="J351">
-        <v>2.1</v>
+        <v>2.52</v>
       </c>
       <c r="K351">
         <v>100</v>
@@ -47759,25 +47759,25 @@
         <v>334</v>
       </c>
       <c r="D352" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="E352">
         <v>2022</v>
       </c>
       <c r="F352">
-        <v>0.35629700644009438</v>
+        <v>0.15541601192373908</v>
       </c>
       <c r="G352">
         <v>1</v>
       </c>
       <c r="H352">
-        <v>2750</v>
+        <v>3162.5000000000005</v>
       </c>
       <c r="I352">
-        <v>55</v>
+        <v>60.500000000000014</v>
       </c>
       <c r="J352">
-        <v>2.1</v>
+        <v>2.3100000000000005</v>
       </c>
       <c r="K352">
         <v>100</v>
@@ -47812,13 +47812,13 @@
         <v>334</v>
       </c>
       <c r="D353" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="E353">
         <v>2022</v>
       </c>
       <c r="F353">
-        <v>6.0310691194286808E-2</v>
+        <v>6.3558189950902247E-2</v>
       </c>
       <c r="G353">
         <v>1</v>
@@ -47865,25 +47865,25 @@
         <v>334</v>
       </c>
       <c r="D354" t="s">
-        <v>70</v>
+        <v>352</v>
       </c>
       <c r="E354">
         <v>2022</v>
       </c>
       <c r="F354">
-        <v>5.4743550468660328E-2</v>
+        <v>4.4073197411209589E-2</v>
       </c>
       <c r="G354">
         <v>1</v>
       </c>
       <c r="H354">
-        <v>3162.5000000000005</v>
+        <v>3712.5000000000005</v>
       </c>
       <c r="I354">
-        <v>60.500000000000014</v>
+        <v>71.5</v>
       </c>
       <c r="J354">
-        <v>2.3100000000000005</v>
+        <v>2.52</v>
       </c>
       <c r="K354">
         <v>100</v>
@@ -47918,25 +47918,25 @@
         <v>334</v>
       </c>
       <c r="D355" t="s">
-        <v>254</v>
+        <v>353</v>
       </c>
       <c r="E355">
         <v>2022</v>
       </c>
       <c r="F355">
-        <v>0.22871669814448767</v>
+        <v>0.57944656385895543</v>
       </c>
       <c r="G355">
         <v>1</v>
       </c>
       <c r="H355">
-        <v>3162.5000000000005</v>
+        <v>2750</v>
       </c>
       <c r="I355">
-        <v>60.500000000000014</v>
+        <v>55.000000000000007</v>
       </c>
       <c r="J355">
-        <v>2.3100000000000005</v>
+        <v>2.1</v>
       </c>
       <c r="K355">
         <v>100</v>
@@ -47971,25 +47971,25 @@
         <v>334</v>
       </c>
       <c r="D356" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="E356">
         <v>2022</v>
       </c>
       <c r="F356">
-        <v>0.13036387865841995</v>
+        <v>1.0883760118599757</v>
       </c>
       <c r="G356">
         <v>1</v>
       </c>
       <c r="H356">
-        <v>3162.5000000000005</v>
+        <v>2750</v>
       </c>
       <c r="I356">
-        <v>60.500000000000014</v>
+        <v>55.000000000000007</v>
       </c>
       <c r="J356">
-        <v>2.3100000000000005</v>
+        <v>2.1</v>
       </c>
       <c r="K356">
         <v>100</v>
@@ -48024,25 +48024,25 @@
         <v>334</v>
       </c>
       <c r="D357" t="s">
-        <v>207</v>
+        <v>355</v>
       </c>
       <c r="E357">
         <v>2022</v>
       </c>
       <c r="F357">
-        <v>7.8403898552572848E-2</v>
+        <v>0.54140443556717466</v>
       </c>
       <c r="G357">
         <v>1</v>
       </c>
       <c r="H357">
-        <v>3162.5000000000005</v>
+        <v>2750</v>
       </c>
       <c r="I357">
-        <v>60.500000000000014</v>
+        <v>55.000000000000007</v>
       </c>
       <c r="J357">
-        <v>2.3100000000000005</v>
+        <v>2.1</v>
       </c>
       <c r="K357">
         <v>100</v>
@@ -48077,13 +48077,13 @@
         <v>334</v>
       </c>
       <c r="D358" t="s">
-        <v>71</v>
+        <v>317</v>
       </c>
       <c r="E358">
         <v>2022</v>
       </c>
       <c r="F358">
-        <v>0.23196419690110309</v>
+        <v>0.13082780705222213</v>
       </c>
       <c r="G358">
         <v>1</v>
@@ -48183,7 +48183,7 @@
         <v>334</v>
       </c>
       <c r="D360" t="s">
-        <v>346</v>
+        <v>352</v>
       </c>
       <c r="E360">
         <v>1959</v>
@@ -48289,7 +48289,7 @@
         <v>334</v>
       </c>
       <c r="D362" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E362">
         <v>1973</v>
@@ -48395,7 +48395,7 @@
         <v>334</v>
       </c>
       <c r="D364" t="s">
-        <v>348</v>
+        <v>354</v>
       </c>
       <c r="E364">
         <v>1963</v>
@@ -48448,7 +48448,7 @@
         <v>334</v>
       </c>
       <c r="D365" t="s">
-        <v>335</v>
+        <v>346</v>
       </c>
       <c r="E365">
         <v>2015</v>
@@ -48501,7 +48501,7 @@
         <v>334</v>
       </c>
       <c r="D366" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="E366">
         <v>1931</v>
@@ -48554,7 +48554,7 @@
         <v>334</v>
       </c>
       <c r="D367" t="s">
-        <v>336</v>
+        <v>355</v>
       </c>
       <c r="E367">
         <v>1949</v>
@@ -48607,7 +48607,7 @@
         <v>334</v>
       </c>
       <c r="D368" t="s">
-        <v>353</v>
+        <v>344</v>
       </c>
       <c r="E368">
         <v>1951</v>
@@ -48713,7 +48713,7 @@
         <v>334</v>
       </c>
       <c r="D370" t="s">
-        <v>354</v>
+        <v>345</v>
       </c>
       <c r="E370">
         <v>1958</v>
@@ -48766,7 +48766,7 @@
         <v>334</v>
       </c>
       <c r="D371" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="E371">
         <v>1967</v>
@@ -48819,7 +48819,7 @@
         <v>334</v>
       </c>
       <c r="D372" t="s">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="E372">
         <v>1968</v>
@@ -48872,7 +48872,7 @@
         <v>334</v>
       </c>
       <c r="D373" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="E373">
         <v>1929</v>
@@ -48925,7 +48925,7 @@
         <v>334</v>
       </c>
       <c r="D374" t="s">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="E374">
         <v>1949</v>
@@ -49031,7 +49031,7 @@
         <v>334</v>
       </c>
       <c r="D376" t="s">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="E376">
         <v>1952</v>
@@ -49084,7 +49084,7 @@
         <v>334</v>
       </c>
       <c r="D377" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="E377">
         <v>1913</v>
@@ -49137,7 +49137,7 @@
         <v>334</v>
       </c>
       <c r="D378" t="s">
-        <v>353</v>
+        <v>344</v>
       </c>
       <c r="E378">
         <v>1924</v>
@@ -49243,7 +49243,7 @@
         <v>334</v>
       </c>
       <c r="D380" t="s">
-        <v>353</v>
+        <v>344</v>
       </c>
       <c r="E380">
         <v>1971</v>
@@ -49349,7 +49349,7 @@
         <v>334</v>
       </c>
       <c r="D382" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="E382">
         <v>1927</v>
@@ -49402,7 +49402,7 @@
         <v>334</v>
       </c>
       <c r="D383" t="s">
-        <v>348</v>
+        <v>354</v>
       </c>
       <c r="E383">
         <v>1928</v>
@@ -49508,7 +49508,7 @@
         <v>334</v>
       </c>
       <c r="D385" t="s">
-        <v>348</v>
+        <v>354</v>
       </c>
       <c r="E385">
         <v>1938</v>
@@ -49561,7 +49561,7 @@
         <v>334</v>
       </c>
       <c r="D386" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="E386">
         <v>1920</v>
@@ -49614,7 +49614,7 @@
         <v>334</v>
       </c>
       <c r="D387" t="s">
-        <v>348</v>
+        <v>354</v>
       </c>
       <c r="E387">
         <v>1947</v>
@@ -49667,7 +49667,7 @@
         <v>334</v>
       </c>
       <c r="D388" t="s">
-        <v>349</v>
+        <v>343</v>
       </c>
       <c r="E388">
         <v>1950</v>
@@ -49720,7 +49720,7 @@
         <v>334</v>
       </c>
       <c r="D389" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E389">
         <v>1954</v>
@@ -49826,7 +49826,7 @@
         <v>334</v>
       </c>
       <c r="D391" t="s">
-        <v>353</v>
+        <v>344</v>
       </c>
       <c r="E391">
         <v>1971</v>
@@ -49879,7 +49879,7 @@
         <v>334</v>
       </c>
       <c r="D392" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="E392">
         <v>1959</v>
@@ -49985,7 +49985,7 @@
         <v>334</v>
       </c>
       <c r="D394" t="s">
-        <v>348</v>
+        <v>354</v>
       </c>
       <c r="E394">
         <v>1955</v>
@@ -50038,7 +50038,7 @@
         <v>334</v>
       </c>
       <c r="D395" t="s">
-        <v>348</v>
+        <v>354</v>
       </c>
       <c r="E395">
         <v>1959</v>
@@ -50091,7 +50091,7 @@
         <v>334</v>
       </c>
       <c r="D396" t="s">
-        <v>348</v>
+        <v>354</v>
       </c>
       <c r="E396">
         <v>1954</v>
@@ -50303,7 +50303,7 @@
         <v>334</v>
       </c>
       <c r="D400" t="s">
-        <v>57</v>
+        <v>69</v>
       </c>
       <c r="E400">
         <v>2022</v>
@@ -50515,7 +50515,7 @@
         <v>334</v>
       </c>
       <c r="D404" t="s">
-        <v>69</v>
+        <v>56</v>
       </c>
       <c r="E404">
         <v>2022</v>
@@ -50621,7 +50621,7 @@
         <v>409</v>
       </c>
       <c r="D406" t="s">
-        <v>71</v>
+        <v>51</v>
       </c>
       <c r="E406">
         <v>1989</v>
@@ -50674,7 +50674,7 @@
         <v>409</v>
       </c>
       <c r="D407" t="s">
-        <v>355</v>
+        <v>347</v>
       </c>
       <c r="E407">
         <v>1975</v>
@@ -50780,7 +50780,7 @@
         <v>409</v>
       </c>
       <c r="D409" t="s">
-        <v>348</v>
+        <v>354</v>
       </c>
       <c r="E409">
         <v>2015</v>
@@ -50833,7 +50833,7 @@
         <v>409</v>
       </c>
       <c r="D410" t="s">
-        <v>347</v>
+        <v>353</v>
       </c>
       <c r="E410">
         <v>2015</v>
@@ -50886,7 +50886,7 @@
         <v>409</v>
       </c>
       <c r="D411" t="s">
-        <v>347</v>
+        <v>353</v>
       </c>
       <c r="E411">
         <v>1982</v>
@@ -50939,7 +50939,7 @@
         <v>409</v>
       </c>
       <c r="D412" t="s">
-        <v>353</v>
+        <v>344</v>
       </c>
       <c r="E412">
         <v>2015</v>
@@ -51045,7 +51045,7 @@
         <v>409</v>
       </c>
       <c r="D414" t="s">
-        <v>69</v>
+        <v>56</v>
       </c>
       <c r="E414">
         <v>1961</v>
@@ -51098,7 +51098,7 @@
         <v>409</v>
       </c>
       <c r="D415" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="E415">
         <v>2005</v>
@@ -51310,7 +51310,7 @@
         <v>409</v>
       </c>
       <c r="D419" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="E419">
         <v>1971</v>
@@ -51363,7 +51363,7 @@
         <v>409</v>
       </c>
       <c r="D420" t="s">
-        <v>349</v>
+        <v>343</v>
       </c>
       <c r="E420">
         <v>1973</v>
@@ -51522,7 +51522,7 @@
         <v>409</v>
       </c>
       <c r="D423" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="E423">
         <v>1978</v>
@@ -51575,7 +51575,7 @@
         <v>409</v>
       </c>
       <c r="D424" t="s">
-        <v>336</v>
+        <v>355</v>
       </c>
       <c r="E424">
         <v>1923</v>
@@ -51628,7 +51628,7 @@
         <v>334</v>
       </c>
       <c r="D425" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="E425">
         <v>1959</v>
@@ -51734,7 +51734,7 @@
         <v>334</v>
       </c>
       <c r="D427" t="s">
-        <v>348</v>
+        <v>354</v>
       </c>
       <c r="E427">
         <v>1949</v>
@@ -51893,7 +51893,7 @@
         <v>334</v>
       </c>
       <c r="D430" t="s">
-        <v>348</v>
+        <v>354</v>
       </c>
       <c r="E430">
         <v>1960</v>
@@ -51946,7 +51946,7 @@
         <v>334</v>
       </c>
       <c r="D431" t="s">
-        <v>337</v>
+        <v>349</v>
       </c>
       <c r="E431">
         <v>1962</v>
@@ -51999,7 +51999,7 @@
         <v>334</v>
       </c>
       <c r="D432" t="s">
-        <v>336</v>
+        <v>355</v>
       </c>
       <c r="E432">
         <v>2015</v>
@@ -52052,7 +52052,7 @@
         <v>334</v>
       </c>
       <c r="D433" t="s">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="E433">
         <v>1927</v>
@@ -52105,7 +52105,7 @@
         <v>334</v>
       </c>
       <c r="D434" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="E434">
         <v>1954</v>
@@ -52211,7 +52211,7 @@
         <v>334</v>
       </c>
       <c r="D436" t="s">
-        <v>336</v>
+        <v>355</v>
       </c>
       <c r="E436">
         <v>1956</v>
@@ -52264,7 +52264,7 @@
         <v>334</v>
       </c>
       <c r="D437" t="s">
-        <v>353</v>
+        <v>344</v>
       </c>
       <c r="E437">
         <v>1956</v>
@@ -52370,7 +52370,7 @@
         <v>334</v>
       </c>
       <c r="D439" t="s">
-        <v>336</v>
+        <v>355</v>
       </c>
       <c r="E439">
         <v>1960</v>
@@ -52476,7 +52476,7 @@
         <v>334</v>
       </c>
       <c r="D441" t="s">
-        <v>335</v>
+        <v>346</v>
       </c>
       <c r="E441">
         <v>2015</v>
@@ -52582,7 +52582,7 @@
         <v>334</v>
       </c>
       <c r="D443" t="s">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="E443">
         <v>2015</v>
@@ -52635,7 +52635,7 @@
         <v>334</v>
       </c>
       <c r="D444" t="s">
-        <v>347</v>
+        <v>353</v>
       </c>
       <c r="E444">
         <v>2015</v>
@@ -52741,7 +52741,7 @@
         <v>334</v>
       </c>
       <c r="D446" t="s">
-        <v>57</v>
+        <v>69</v>
       </c>
       <c r="E446">
         <v>1955</v>
@@ -52794,7 +52794,7 @@
         <v>334</v>
       </c>
       <c r="D447" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E447">
         <v>2015</v>
@@ -52900,7 +52900,7 @@
         <v>334</v>
       </c>
       <c r="D449" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="E449">
         <v>1932</v>
@@ -53059,7 +53059,7 @@
         <v>334</v>
       </c>
       <c r="D452" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="E452">
         <v>1924</v>
@@ -53165,7 +53165,7 @@
         <v>334</v>
       </c>
       <c r="D454" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="E454">
         <v>2002</v>
@@ -53271,7 +53271,7 @@
         <v>334</v>
       </c>
       <c r="D456" t="s">
-        <v>348</v>
+        <v>354</v>
       </c>
       <c r="E456">
         <v>1948</v>
@@ -53324,7 +53324,7 @@
         <v>334</v>
       </c>
       <c r="D457" t="s">
-        <v>335</v>
+        <v>346</v>
       </c>
       <c r="E457">
         <v>2015</v>
@@ -53377,7 +53377,7 @@
         <v>334</v>
       </c>
       <c r="D458" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="E458">
         <v>1914</v>
@@ -53483,7 +53483,7 @@
         <v>334</v>
       </c>
       <c r="D460" t="s">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="E460">
         <v>1958</v>
@@ -53536,7 +53536,7 @@
         <v>465</v>
       </c>
       <c r="D461" t="s">
-        <v>57</v>
+        <v>69</v>
       </c>
       <c r="E461">
         <v>2006</v>
@@ -53589,7 +53589,7 @@
         <v>465</v>
       </c>
       <c r="D462" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="E462">
         <v>2012</v>
@@ -53642,7 +53642,7 @@
         <v>465</v>
       </c>
       <c r="D463" t="s">
-        <v>51</v>
+        <v>76</v>
       </c>
       <c r="E463">
         <v>1993</v>
@@ -53695,7 +53695,7 @@
         <v>465</v>
       </c>
       <c r="D464" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="E464">
         <v>2011</v>
@@ -53748,7 +53748,7 @@
         <v>465</v>
       </c>
       <c r="D465" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="E465">
         <v>2005</v>
@@ -53801,7 +53801,7 @@
         <v>465</v>
       </c>
       <c r="D466" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="E466">
         <v>2006</v>
@@ -53854,7 +53854,7 @@
         <v>465</v>
       </c>
       <c r="D467" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="E467">
         <v>2006</v>
@@ -53960,7 +53960,7 @@
         <v>465</v>
       </c>
       <c r="D469" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="E469">
         <v>2003</v>
@@ -54119,7 +54119,7 @@
         <v>465</v>
       </c>
       <c r="D472" t="s">
-        <v>62</v>
+        <v>78</v>
       </c>
       <c r="E472">
         <v>2004</v>
@@ -54172,7 +54172,7 @@
         <v>465</v>
       </c>
       <c r="D473" t="s">
-        <v>62</v>
+        <v>78</v>
       </c>
       <c r="E473">
         <v>2005</v>
@@ -54225,7 +54225,7 @@
         <v>465</v>
       </c>
       <c r="D474" t="s">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="E474">
         <v>2005</v>
@@ -54278,7 +54278,7 @@
         <v>465</v>
       </c>
       <c r="D475" t="s">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="E475">
         <v>2005</v>
@@ -54331,7 +54331,7 @@
         <v>465</v>
       </c>
       <c r="D476" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="E476">
         <v>2004</v>
@@ -54384,7 +54384,7 @@
         <v>465</v>
       </c>
       <c r="D477" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="E477">
         <v>2004</v>
@@ -54437,7 +54437,7 @@
         <v>465</v>
       </c>
       <c r="D478" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="E478">
         <v>2004</v>
@@ -54490,7 +54490,7 @@
         <v>465</v>
       </c>
       <c r="D479" t="s">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="E479">
         <v>2008</v>
@@ -54543,7 +54543,7 @@
         <v>465</v>
       </c>
       <c r="D480" t="s">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="E480">
         <v>2008</v>
@@ -54596,7 +54596,7 @@
         <v>465</v>
       </c>
       <c r="D481" t="s">
-        <v>74</v>
+        <v>52</v>
       </c>
       <c r="E481">
         <v>2002</v>
@@ -54649,7 +54649,7 @@
         <v>465</v>
       </c>
       <c r="D482" t="s">
-        <v>74</v>
+        <v>52</v>
       </c>
       <c r="E482">
         <v>2002</v>
@@ -54702,7 +54702,7 @@
         <v>465</v>
       </c>
       <c r="D483" t="s">
-        <v>74</v>
+        <v>52</v>
       </c>
       <c r="E483">
         <v>2003</v>
@@ -54755,7 +54755,7 @@
         <v>465</v>
       </c>
       <c r="D484" t="s">
-        <v>74</v>
+        <v>52</v>
       </c>
       <c r="E484">
         <v>2003</v>
@@ -54967,7 +54967,7 @@
         <v>465</v>
       </c>
       <c r="D488" t="s">
-        <v>51</v>
+        <v>76</v>
       </c>
       <c r="E488">
         <v>2023</v>
@@ -55020,7 +55020,7 @@
         <v>465</v>
       </c>
       <c r="D489" t="s">
-        <v>51</v>
+        <v>76</v>
       </c>
       <c r="E489">
         <v>2001</v>
@@ -55073,7 +55073,7 @@
         <v>465</v>
       </c>
       <c r="D490" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="E490">
         <v>1999</v>
@@ -55126,7 +55126,7 @@
         <v>465</v>
       </c>
       <c r="D491" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="E491">
         <v>2010</v>
@@ -55285,7 +55285,7 @@
         <v>465</v>
       </c>
       <c r="D494" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="E494">
         <v>1997</v>
@@ -55338,7 +55338,7 @@
         <v>465</v>
       </c>
       <c r="D495" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="E495">
         <v>1997</v>
@@ -55391,7 +55391,7 @@
         <v>465</v>
       </c>
       <c r="D496" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="E496">
         <v>1998</v>
@@ -55444,7 +55444,7 @@
         <v>465</v>
       </c>
       <c r="D497" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="E497">
         <v>1999</v>
@@ -55550,7 +55550,7 @@
         <v>465</v>
       </c>
       <c r="D499" t="s">
-        <v>71</v>
+        <v>51</v>
       </c>
       <c r="E499">
         <v>2010</v>
@@ -55603,7 +55603,7 @@
         <v>465</v>
       </c>
       <c r="D500" t="s">
-        <v>68</v>
+        <v>55</v>
       </c>
       <c r="E500">
         <v>2003</v>
@@ -55656,7 +55656,7 @@
         <v>465</v>
       </c>
       <c r="D501" t="s">
-        <v>68</v>
+        <v>55</v>
       </c>
       <c r="E501">
         <v>2003</v>
@@ -55709,7 +55709,7 @@
         <v>465</v>
       </c>
       <c r="D502" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="E502">
         <v>2006</v>
@@ -56080,7 +56080,7 @@
         <v>465</v>
       </c>
       <c r="D509" t="s">
-        <v>61</v>
+        <v>77</v>
       </c>
       <c r="E509">
         <v>2018</v>
@@ -56345,7 +56345,7 @@
         <v>465</v>
       </c>
       <c r="D514" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E514">
         <v>2010</v>
@@ -56398,7 +56398,7 @@
         <v>465</v>
       </c>
       <c r="D515" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E515">
         <v>2010</v>
@@ -56451,7 +56451,7 @@
         <v>465</v>
       </c>
       <c r="D516" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E516">
         <v>2004</v>
@@ -56504,7 +56504,7 @@
         <v>465</v>
       </c>
       <c r="D517" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E517">
         <v>2004</v>
@@ -56557,7 +56557,7 @@
         <v>465</v>
       </c>
       <c r="D518" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="E518">
         <v>2008</v>
@@ -56716,7 +56716,7 @@
         <v>465</v>
       </c>
       <c r="D521" t="s">
-        <v>72</v>
+        <v>54</v>
       </c>
       <c r="E521">
         <v>2005</v>
@@ -56769,7 +56769,7 @@
         <v>465</v>
       </c>
       <c r="D522" t="s">
-        <v>72</v>
+        <v>54</v>
       </c>
       <c r="E522">
         <v>2005</v>
@@ -56822,7 +56822,7 @@
         <v>465</v>
       </c>
       <c r="D523" t="s">
-        <v>69</v>
+        <v>56</v>
       </c>
       <c r="E523">
         <v>2015</v>
@@ -56875,7 +56875,7 @@
         <v>465</v>
       </c>
       <c r="D524" t="s">
-        <v>69</v>
+        <v>56</v>
       </c>
       <c r="E524">
         <v>2004</v>
@@ -56928,7 +56928,7 @@
         <v>465</v>
       </c>
       <c r="D525" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E525">
         <v>2006</v>
@@ -57034,7 +57034,7 @@
         <v>465</v>
       </c>
       <c r="D527" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="E527">
         <v>2004</v>
@@ -57087,7 +57087,7 @@
         <v>465</v>
       </c>
       <c r="D528" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="E528">
         <v>2005</v>
@@ -57140,7 +57140,7 @@
         <v>465</v>
       </c>
       <c r="D529" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="E529">
         <v>2006</v>
@@ -57193,7 +57193,7 @@
         <v>465</v>
       </c>
       <c r="D530" t="s">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="E530">
         <v>2008</v>
@@ -57246,7 +57246,7 @@
         <v>465</v>
       </c>
       <c r="D531" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="E531">
         <v>2007</v>
@@ -57405,7 +57405,7 @@
         <v>465</v>
       </c>
       <c r="D534" t="s">
-        <v>73</v>
+        <v>50</v>
       </c>
       <c r="E534">
         <v>2026</v>
@@ -57458,7 +57458,7 @@
         <v>465</v>
       </c>
       <c r="D535" t="s">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="E535">
         <v>2022</v>
@@ -57617,7 +57617,7 @@
         <v>465</v>
       </c>
       <c r="D538" t="s">
-        <v>68</v>
+        <v>55</v>
       </c>
       <c r="E538">
         <v>2003</v>
@@ -57670,7 +57670,7 @@
         <v>465</v>
       </c>
       <c r="D539" t="s">
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="E539">
         <v>2008</v>
@@ -57723,7 +57723,7 @@
         <v>465</v>
       </c>
       <c r="D540" t="s">
-        <v>71</v>
+        <v>51</v>
       </c>
       <c r="E540">
         <v>1999</v>
@@ -57776,7 +57776,7 @@
         <v>465</v>
       </c>
       <c r="D541" t="s">
-        <v>71</v>
+        <v>51</v>
       </c>
       <c r="E541">
         <v>1999</v>
@@ -57829,7 +57829,7 @@
         <v>465</v>
       </c>
       <c r="D542" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="E542">
         <v>1997</v>
@@ -57988,7 +57988,7 @@
         <v>465</v>
       </c>
       <c r="D545" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="E545">
         <v>2006</v>
@@ -58094,7 +58094,7 @@
         <v>465</v>
       </c>
       <c r="D547" t="s">
-        <v>61</v>
+        <v>77</v>
       </c>
       <c r="E547">
         <v>2007</v>
@@ -58359,7 +58359,7 @@
         <v>465</v>
       </c>
       <c r="D552" t="s">
-        <v>51</v>
+        <v>76</v>
       </c>
       <c r="E552">
         <v>1992</v>
@@ -58412,7 +58412,7 @@
         <v>465</v>
       </c>
       <c r="D553" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="E553">
         <v>2015</v>
@@ -58783,7 +58783,7 @@
         <v>465</v>
       </c>
       <c r="D560" t="s">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="E560">
         <v>2004</v>
@@ -58836,7 +58836,7 @@
         <v>465</v>
       </c>
       <c r="D561" t="s">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="E561">
         <v>2008</v>
@@ -58942,7 +58942,7 @@
         <v>465</v>
       </c>
       <c r="D563" t="s">
-        <v>71</v>
+        <v>51</v>
       </c>
       <c r="E563">
         <v>2005</v>
@@ -58995,7 +58995,7 @@
         <v>465</v>
       </c>
       <c r="D564" t="s">
-        <v>71</v>
+        <v>51</v>
       </c>
       <c r="E564">
         <v>2015</v>
@@ -59366,7 +59366,7 @@
         <v>465</v>
       </c>
       <c r="D571" t="s">
-        <v>73</v>
+        <v>50</v>
       </c>
       <c r="E571">
         <v>2009</v>
@@ -59737,7 +59737,7 @@
         <v>465</v>
       </c>
       <c r="D578" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E578">
         <v>1994</v>
@@ -59790,7 +59790,7 @@
         <v>465</v>
       </c>
       <c r="D579" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E579">
         <v>1990</v>
@@ -59949,7 +59949,7 @@
         <v>465</v>
       </c>
       <c r="D582" t="s">
-        <v>72</v>
+        <v>54</v>
       </c>
       <c r="E582">
         <v>2024</v>
@@ -60002,7 +60002,7 @@
         <v>465</v>
       </c>
       <c r="D583" t="s">
-        <v>69</v>
+        <v>56</v>
       </c>
       <c r="E583">
         <v>2023</v>
@@ -60055,7 +60055,7 @@
         <v>465</v>
       </c>
       <c r="D584" t="s">
-        <v>69</v>
+        <v>56</v>
       </c>
       <c r="E584">
         <v>2023</v>
@@ -60108,7 +60108,7 @@
         <v>465</v>
       </c>
       <c r="D585" t="s">
-        <v>61</v>
+        <v>77</v>
       </c>
       <c r="E585">
         <v>1997</v>
@@ -60532,7 +60532,7 @@
         <v>465</v>
       </c>
       <c r="D593" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="E593">
         <v>1999</v>
@@ -60585,7 +60585,7 @@
         <v>465</v>
       </c>
       <c r="D594" t="s">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="E594">
         <v>2008</v>
@@ -60638,7 +60638,7 @@
         <v>465</v>
       </c>
       <c r="D595" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E595">
         <v>1992</v>
@@ -60691,7 +60691,7 @@
         <v>465</v>
       </c>
       <c r="D596" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E596">
         <v>2005</v>
@@ -60956,7 +60956,7 @@
         <v>465</v>
       </c>
       <c r="D601" t="s">
-        <v>69</v>
+        <v>56</v>
       </c>
       <c r="E601">
         <v>2015</v>
@@ -61062,7 +61062,7 @@
         <v>465</v>
       </c>
       <c r="D603" t="s">
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="E603">
         <v>2004</v>
@@ -61327,7 +61327,7 @@
         <v>465</v>
       </c>
       <c r="D608" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="E608">
         <v>2024</v>
@@ -61433,7 +61433,7 @@
         <v>465</v>
       </c>
       <c r="D610" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E610">
         <v>2023</v>
@@ -61645,7 +61645,7 @@
         <v>465</v>
       </c>
       <c r="D614" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="E614">
         <v>1975</v>
@@ -61698,7 +61698,7 @@
         <v>465</v>
       </c>
       <c r="D615" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="E615">
         <v>1975</v>
@@ -61751,7 +61751,7 @@
         <v>465</v>
       </c>
       <c r="D616" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="E616">
         <v>1975</v>
@@ -61804,7 +61804,7 @@
         <v>465</v>
       </c>
       <c r="D617" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="E617">
         <v>1976</v>
@@ -61857,7 +61857,7 @@
         <v>465</v>
       </c>
       <c r="D618" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="E618">
         <v>1975</v>
@@ -61910,7 +61910,7 @@
         <v>465</v>
       </c>
       <c r="D619" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="E619">
         <v>1971</v>
@@ -61963,7 +61963,7 @@
         <v>465</v>
       </c>
       <c r="D620" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="E620">
         <v>1976</v>
@@ -62016,7 +62016,7 @@
         <v>465</v>
       </c>
       <c r="D621" t="s">
-        <v>51</v>
+        <v>76</v>
       </c>
       <c r="E621">
         <v>1985</v>
@@ -62122,7 +62122,7 @@
         <v>465</v>
       </c>
       <c r="D623" t="s">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="E623">
         <v>2015</v>
@@ -62175,7 +62175,7 @@
         <v>465</v>
       </c>
       <c r="D624" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="E624">
         <v>1967</v>
@@ -62228,7 +62228,7 @@
         <v>465</v>
       </c>
       <c r="D625" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="E625">
         <v>1971</v>
@@ -62546,7 +62546,7 @@
         <v>465</v>
       </c>
       <c r="D631" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E631">
         <v>1978</v>
@@ -62599,7 +62599,7 @@
         <v>465</v>
       </c>
       <c r="D632" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E632">
         <v>1981</v>
@@ -62652,7 +62652,7 @@
         <v>465</v>
       </c>
       <c r="D633" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E633">
         <v>1987</v>
@@ -62764,7 +62764,7 @@
         <v>2022</v>
       </c>
       <c r="F635">
-        <v>6.6457416582336482</v>
+        <v>6.6039408899415779</v>
       </c>
       <c r="G635">
         <v>1</v>
@@ -62820,7 +62820,7 @@
         <v>2022</v>
       </c>
       <c r="F636">
-        <v>6.6039408899415779</v>
+        <v>6.6457416582336482</v>
       </c>
       <c r="G636">
         <v>1</v>
@@ -64718,7 +64718,7 @@
         <v>621</v>
       </c>
       <c r="D670" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="E670">
         <v>2015</v>
@@ -70622,7 +70622,7 @@
         <v>2022</v>
       </c>
       <c r="F796">
-        <v>0.69928302455480262</v>
+        <v>0.6793056475905862</v>
       </c>
       <c r="G796">
         <v>0.33123000000000002</v>
@@ -70645,7 +70645,7 @@
         <v>2022</v>
       </c>
       <c r="F797">
-        <v>0.6793056475905862</v>
+        <v>0.69928302455480262</v>
       </c>
       <c r="G797">
         <v>0.33123000000000002</v>
@@ -70892,7 +70892,7 @@
         <v>829</v>
       </c>
       <c r="D808" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="E808">
         <v>2018</v>

--- a/VerveStacks_ITA_grids/vt_vervestacks_ITA_v1.xlsx
+++ b/VerveStacks_ITA_grids/vt_vervestacks_ITA_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D69ED8CF-5FDA-4781-BF49-66022604291E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B4A9251F-B647-4980-B891-C7EE2AD8AC5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{76AE0CD9-8994-4B25-8BA2-7CF347AE7E57}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{2746CD58-AB47-4095-96F1-7E4D81CAAD97}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="2" r:id="rId1"/>
@@ -81,30 +81,30 @@
     <t>bioenergy</t>
   </si>
   <si>
+    <t>e_w108020416-380</t>
+  </si>
+  <si>
+    <t>e_w81938081-380</t>
+  </si>
+  <si>
+    <t>e_w98902899-380</t>
+  </si>
+  <si>
+    <t>e_w58440884-380</t>
+  </si>
+  <si>
+    <t>e_w109756016-380</t>
+  </si>
+  <si>
+    <t>e_w34157795-380</t>
+  </si>
+  <si>
+    <t>e_w144005863-380</t>
+  </si>
+  <si>
     <t>e_w84696559-380</t>
   </si>
   <si>
-    <t>e_w144005863-380</t>
-  </si>
-  <si>
-    <t>e_w109756016-380</t>
-  </si>
-  <si>
-    <t>e_w98902899-380</t>
-  </si>
-  <si>
-    <t>e_w34157795-380</t>
-  </si>
-  <si>
-    <t>e_w81938081-380</t>
-  </si>
-  <si>
-    <t>e_w58440884-380</t>
-  </si>
-  <si>
-    <t>e_w108020416-380</t>
-  </si>
-  <si>
     <t>ep_bioenergy_G100000200236</t>
   </si>
   <si>
@@ -141,18 +141,18 @@
     <t>coal</t>
   </si>
   <si>
+    <t>e_w82767145-380</t>
+  </si>
+  <si>
+    <t>e_w409439916-380</t>
+  </si>
+  <si>
     <t>e_w303915533-380</t>
   </si>
   <si>
-    <t>e_w409439916-380</t>
-  </si>
-  <si>
     <t>e_w418902800-380</t>
   </si>
   <si>
-    <t>e_w82767145-380</t>
-  </si>
-  <si>
     <t>ep_coal_subcritical_G100000102764</t>
   </si>
   <si>
@@ -189,120 +189,120 @@
     <t>gas</t>
   </si>
   <si>
+    <t>e_w411026199-380</t>
+  </si>
+  <si>
+    <t>e_w99826025-380</t>
+  </si>
+  <si>
+    <t>e_w103653592-380</t>
+  </si>
+  <si>
+    <t>e_w109993642-380</t>
+  </si>
+  <si>
+    <t>e_w162960205-380</t>
+  </si>
+  <si>
+    <t>e_w338753171-380</t>
+  </si>
+  <si>
+    <t>e_w158739183-380</t>
+  </si>
+  <si>
+    <t>e_w103974940-380</t>
+  </si>
+  <si>
+    <t>e_w82084019-380</t>
+  </si>
+  <si>
+    <t>e_w432729521-380</t>
+  </si>
+  <si>
+    <t>e_w172302572-380</t>
+  </si>
+  <si>
+    <t>e_w199675964-380</t>
+  </si>
+  <si>
+    <t>e_w414663585-380</t>
+  </si>
+  <si>
+    <t>e_w1137611914-380</t>
+  </si>
+  <si>
+    <t>e_w255011550-380</t>
+  </si>
+  <si>
+    <t>e_w105581403-380</t>
+  </si>
+  <si>
+    <t>e_w181125039-380</t>
+  </si>
+  <si>
+    <t>e_w133601335-380</t>
+  </si>
+  <si>
+    <t>e_w103381531-380</t>
+  </si>
+  <si>
+    <t>e_w339104227-380</t>
+  </si>
+  <si>
+    <t>e_w98421779-380</t>
+  </si>
+  <si>
+    <t>e_w419423704-380</t>
+  </si>
+  <si>
+    <t>e_w116797658-380</t>
+  </si>
+  <si>
+    <t>e_w61157826-380</t>
+  </si>
+  <si>
+    <t>e_w98900549-380</t>
+  </si>
+  <si>
+    <t>e_w162828577-380</t>
+  </si>
+  <si>
+    <t>e_w132450233-380</t>
+  </si>
+  <si>
+    <t>e_w110330925-380</t>
+  </si>
+  <si>
+    <t>e_w105757794-380</t>
+  </si>
+  <si>
+    <t>e_w82078641-380</t>
+  </si>
+  <si>
+    <t>e_w100407576-380</t>
+  </si>
+  <si>
     <t>e_w149997403-380</t>
   </si>
   <si>
+    <t>e_w421827453-380</t>
+  </si>
+  <si>
     <t>e_w59462715-380</t>
   </si>
   <si>
-    <t>e_w162960205-380</t>
-  </si>
-  <si>
-    <t>e_w338753171-380</t>
-  </si>
-  <si>
-    <t>e_w103381531-380</t>
+    <t>e_w145665799-380</t>
+  </si>
+  <si>
+    <t>e_w107438024-380</t>
   </si>
   <si>
     <t>e_w60725875-380</t>
   </si>
   <si>
-    <t>e_w145665799-380</t>
-  </si>
-  <si>
-    <t>e_w98421779-380</t>
-  </si>
-  <si>
-    <t>e_w419423704-380</t>
-  </si>
-  <si>
-    <t>e_w116797658-380</t>
-  </si>
-  <si>
-    <t>e_w339104227-380</t>
-  </si>
-  <si>
-    <t>e_w99826025-380</t>
-  </si>
-  <si>
     <t>e_w416989699-380</t>
   </si>
   <si>
-    <t>e_w133601335-380</t>
-  </si>
-  <si>
-    <t>e_w411026199-380</t>
-  </si>
-  <si>
-    <t>e_w107438024-380</t>
-  </si>
-  <si>
-    <t>e_w158739183-380</t>
-  </si>
-  <si>
-    <t>e_w103974940-380</t>
-  </si>
-  <si>
-    <t>e_w414663585-380</t>
-  </si>
-  <si>
-    <t>e_w255011550-380</t>
-  </si>
-  <si>
-    <t>e_w105581403-380</t>
-  </si>
-  <si>
-    <t>e_w82078641-380</t>
-  </si>
-  <si>
-    <t>e_w61157826-380</t>
-  </si>
-  <si>
-    <t>e_w181125039-380</t>
-  </si>
-  <si>
-    <t>e_w1137611914-380</t>
-  </si>
-  <si>
-    <t>e_w82084019-380</t>
-  </si>
-  <si>
-    <t>e_w432729521-380</t>
-  </si>
-  <si>
-    <t>e_w172302572-380</t>
-  </si>
-  <si>
-    <t>e_w98900549-380</t>
-  </si>
-  <si>
-    <t>e_w199675964-380</t>
-  </si>
-  <si>
-    <t>e_w103653592-380</t>
-  </si>
-  <si>
-    <t>e_w109993642-380</t>
-  </si>
-  <si>
-    <t>e_w105757794-380</t>
-  </si>
-  <si>
-    <t>e_w110330925-380</t>
-  </si>
-  <si>
-    <t>e_w132450233-380</t>
-  </si>
-  <si>
-    <t>e_w100407576-380</t>
-  </si>
-  <si>
-    <t>e_w162828577-380</t>
-  </si>
-  <si>
-    <t>e_w421827453-380</t>
-  </si>
-  <si>
     <t>ep_gas_combined_cycle_G100000400339</t>
   </si>
   <si>
@@ -966,9 +966,45 @@
     <t>hydro</t>
   </si>
   <si>
+    <t>e_IT7-380</t>
+  </si>
+  <si>
+    <t>e_w491424937-380</t>
+  </si>
+  <si>
+    <t>e_w75602396-380</t>
+  </si>
+  <si>
+    <t>e_IT72-380</t>
+  </si>
+  <si>
+    <t>e_IT71-380</t>
+  </si>
+  <si>
+    <t>e_w61626687-380</t>
+  </si>
+  <si>
+    <t>e_IT10-380</t>
+  </si>
+  <si>
+    <t>e_w64200868-380</t>
+  </si>
+  <si>
+    <t>e_IT72-400</t>
+  </si>
+  <si>
+    <t>e_IT93-380</t>
+  </si>
+  <si>
     <t>e_w82083756-380</t>
   </si>
   <si>
+    <t>e_w72466334-380</t>
+  </si>
+  <si>
+    <t>e_IT36-380</t>
+  </si>
+  <si>
     <t>e_w116517585-380</t>
   </si>
   <si>
@@ -978,57 +1014,21 @@
     <t>e_w104359058-380</t>
   </si>
   <si>
-    <t>e_w64200868-380</t>
-  </si>
-  <si>
-    <t>e_IT93-380</t>
-  </si>
-  <si>
-    <t>e_IT36-380</t>
-  </si>
-  <si>
-    <t>e_w72466334-380</t>
+    <t>e_w1100665914-380</t>
   </si>
   <si>
     <t>e_IT53-380</t>
   </si>
   <si>
-    <t>e_w75602396-380</t>
-  </si>
-  <si>
     <t>e_IT31-380</t>
   </si>
   <si>
-    <t>e_IT7-380</t>
-  </si>
-  <si>
-    <t>e_IT71-380</t>
-  </si>
-  <si>
-    <t>e_w491424937-380</t>
-  </si>
-  <si>
-    <t>e_IT72-400</t>
-  </si>
-  <si>
-    <t>e_IT10-380</t>
-  </si>
-  <si>
     <t>e_IT71-400</t>
   </si>
   <si>
-    <t>e_w61626687-380</t>
-  </si>
-  <si>
-    <t>e_IT72-380</t>
-  </si>
-  <si>
     <t>e_IT21-380</t>
   </si>
   <si>
-    <t>e_w1100665914-380</t>
-  </si>
-  <si>
     <t>ep_hydro_dam_G100000602220</t>
   </si>
   <si>
@@ -1407,15 +1407,15 @@
     <t>solar</t>
   </si>
   <si>
+    <t>elc_spv-ITA_0042</t>
+  </si>
+  <si>
+    <t>elc_spv-ITA_0030</t>
+  </si>
+  <si>
     <t>elc_spv-ITA_0068</t>
   </si>
   <si>
-    <t>elc_spv-ITA_0030</t>
-  </si>
-  <si>
-    <t>elc_spv-ITA_0042</t>
-  </si>
-  <si>
     <t>ep_solar_pv_001</t>
   </si>
   <si>
@@ -2031,15 +2031,15 @@
     <t>windon</t>
   </si>
   <si>
+    <t>elc_won-ITA_0022</t>
+  </si>
+  <si>
     <t>elc_won-ITA_0096</t>
   </si>
   <si>
     <t>elc_won-ITA_0073</t>
   </si>
   <si>
-    <t>elc_won-ITA_0022</t>
-  </si>
-  <si>
     <t>ep_windon_wind_010</t>
   </si>
   <si>
@@ -2469,42 +2469,42 @@
     <t>ele</t>
   </si>
   <si>
+    <t>Aggregated Plant - EMBER Gap - way/108020416-380_Missing Bioenergy Capacity</t>
+  </si>
+  <si>
+    <t>GW</t>
+  </si>
+  <si>
+    <t>TWh</t>
+  </si>
+  <si>
+    <t>daynite</t>
+  </si>
+  <si>
+    <t>yes</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/81938081-380_Missing Bioenergy Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/84696559-380_Missing Bioenergy Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/144005863-380_Missing Bioenergy Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/98902899-380_Missing Bioenergy Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/109756016-380_Missing Bioenergy Capacity</t>
+  </si>
+  <si>
     <t>Aggregated Plant - EMBER Gap - way/58440884-380_Missing Bioenergy Capacity</t>
   </si>
   <si>
-    <t>GW</t>
-  </si>
-  <si>
-    <t>TWh</t>
-  </si>
-  <si>
-    <t>daynite</t>
-  </si>
-  <si>
-    <t>yes</t>
-  </si>
-  <si>
     <t>Aggregated Plant - EMBER Gap - way/34157795-380_Missing Bioenergy Capacity</t>
   </si>
   <si>
-    <t>Aggregated Plant - EMBER Gap - way/84696559-380_Missing Bioenergy Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/81938081-380_Missing Bioenergy Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/108020416-380_Missing Bioenergy Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/144005863-380_Missing Bioenergy Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/109756016-380_Missing Bioenergy Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/98902899-380_Missing Bioenergy Capacity</t>
-  </si>
-  <si>
     <t>Acerra power station_1</t>
   </si>
   <si>
@@ -2526,15 +2526,15 @@
     <t>Aggregated Plant</t>
   </si>
   <si>
+    <t>Aggregated Plant - EMBER Gap - way/418902800-380_Missing Coal Capacity</t>
+  </si>
+  <si>
     <t>Aggregated Plant - EMBER Gap - way/409439916-380_Missing Coal Capacity</t>
   </si>
   <si>
     <t>Aggregated Plant - EMBER Gap - way/82767145-380_Missing Coal Capacity</t>
   </si>
   <si>
-    <t>Aggregated Plant - EMBER Gap - way/418902800-380_Missing Coal Capacity</t>
-  </si>
-  <si>
     <t>Aggregated Plant - EMBER Gap - way/303915533-380_Missing Coal Capacity</t>
   </si>
   <si>
@@ -2568,126 +2568,126 @@
     <t>Torrevaldaliga Nord power station_Unit 3</t>
   </si>
   <si>
+    <t>Aggregated Plant - EMBER Gap - way/181125039-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/199675964-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/432729521-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/411026199-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/110330925-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/98421779-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/105581403-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/109756016-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/82084019-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/59462715-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/105757794-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/255011550-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/172302572-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/162960205-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/149997403-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/133601335-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/416989699-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/103653592-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/100407576-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/61157826-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/419423704-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/414663585-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/1137611914-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/145665799-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/158739183-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/338753171-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/60725875-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/162828577-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/98900549-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/109993642-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/82767145-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/103381531-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/107438024-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/116797658-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/339104227-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/82078641-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/103974940-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/99826025-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/421827453-380_Missing Gas Capacity</t>
+  </si>
+  <si>
     <t>Aggregated Plant - EMBER Gap - way/132450233-380_Missing Gas Capacity</t>
   </si>
   <si>
-    <t>Aggregated Plant - EMBER Gap - way/82078641-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/103974940-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/338753171-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/162828577-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/98900549-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/59462715-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/105757794-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/172302572-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/255011550-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/107438024-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/60725875-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/109756016-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/110330925-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/82084019-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/105581403-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/411026199-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/98421779-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/181125039-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/199675964-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/432729521-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/414663585-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/133601335-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/149997403-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/61157826-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/162960205-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/419423704-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/421827453-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/99826025-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/1137611914-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/158739183-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/145665799-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/100407576-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/103653592-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/339104227-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/116797658-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/109993642-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/82767145-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/103381531-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/416989699-380_Missing Gas Capacity</t>
-  </si>
-  <si>
     <t>Altomonte power station_1</t>
   </si>
   <si>
@@ -3000,102 +3000,102 @@
     <t>Valle Secolo geothermal power plant_2</t>
   </si>
   <si>
+    <t>Aggregated Plant - IRENA Gap - IT71-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/108020416-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/144005863-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - IT21-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - IT31-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/114931087-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/61626687-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - IT53-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - IT30-500_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - IT7-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/339703159-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/61712456-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/419423704-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/491424937-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/104359058-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/82083756-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/72466334-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/64200868-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
     <t>Aggregated Plant - IRENA Gap - way/75602396-380_Missing Hydro Capacity</t>
   </si>
   <si>
-    <t>Aggregated Plant - IRENA Gap - IT7-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/339703159-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - IT30-500_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/61712456-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - IT71-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - IT53-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/108020416-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - IT31-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/114931087-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/61626687-380_Missing Hydro Capacity</t>
+    <t>Aggregated Plant - IRENA Gap - way/109588422-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/1137611914-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - IT72-400_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/1100665914-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/59462263-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - IT72-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - IT93-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/338753171-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - IT10-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - IT71-400_Missing Hydro Capacity</t>
   </si>
   <si>
     <t>Aggregated Plant - IRENA Gap - IT36-380_Missing Hydro Capacity</t>
   </si>
   <si>
-    <t>Aggregated Plant - IRENA Gap - IT71-400_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/72466334-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/82083756-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/419423704-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - IT93-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - IT10-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/338753171-380_Missing Hydro Capacity</t>
+    <t>Aggregated Plant - IRENA Gap - way/96190189-380_Missing Hydro Capacity</t>
   </si>
   <si>
     <t>Aggregated Plant - IRENA Gap - way/116517585-380_Missing Hydro Capacity</t>
   </si>
   <si>
-    <t>Aggregated Plant - IRENA Gap - way/96190189-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/64200868-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/144005863-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - IT21-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/1100665914-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - IT72-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/59462263-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/109588422-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - IT72-400_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/1137611914-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/491424937-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/104359058-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
     <t>Baschi hydroelectric plant_</t>
   </si>
   <si>
@@ -3396,21 +3396,21 @@
     <t>annual</t>
   </si>
   <si>
+    <t>Aggregated Plant - IRENA Gap - ITA_30_Missing Solar Capacity</t>
+  </si>
+  <si>
     <t>Aggregated Plant - IRENA Gap - ITA_42_Missing Solar Capacity</t>
   </si>
   <si>
-    <t>Aggregated Plant - IRENA Gap - ITA_30_Missing Solar Capacity</t>
+    <t>Aggregated Plant - IRENA Gap - ITA_73_Missing Onshore wind energy Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - ITA_22_Missing Onshore wind energy Capacity</t>
   </si>
   <si>
     <t>Aggregated Plant - IRENA Gap - ITA_96_Missing Onshore wind energy Capacity</t>
   </si>
   <si>
-    <t>Aggregated Plant - IRENA Gap - ITA_22_Missing Onshore wind energy Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - ITA_73_Missing Onshore wind energy Capacity</t>
-  </si>
-  <si>
     <t>AF</t>
   </si>
   <si>
@@ -4002,18 +4002,18 @@
     <t>ccs retrofit of -- Sulcis power station_Unit 3</t>
   </si>
   <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/82767145-380_Missing Coal Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/418902800-380_Missing Coal Capacity</t>
+  </si>
+  <si>
     <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/303915533-380_Missing Coal Capacity</t>
   </si>
   <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/82767145-380_Missing Coal Capacity</t>
-  </si>
-  <si>
     <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/409439916-380_Missing Coal Capacity</t>
   </si>
   <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/418902800-380_Missing Coal Capacity</t>
-  </si>
-  <si>
     <t>ccs retrofit of -- Brindisi Sud power station_Unit 1</t>
   </si>
   <si>
@@ -4302,124 +4302,124 @@
     <t>ccs retrofit of -- Aggregated Plant</t>
   </si>
   <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/82084019-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/98421779-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/98900549-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/107438024-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/414663585-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/82767145-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/162828577-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/172302572-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/116797658-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/181125039-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/105581403-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/255011550-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/162960205-380_Missing Gas Capacity</t>
+  </si>
+  <si>
     <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/149997403-380_Missing Gas Capacity</t>
   </si>
   <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/162960205-380_Missing Gas Capacity</t>
-  </si>
-  <si>
     <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/419423704-380_Missing Gas Capacity</t>
   </si>
   <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/145665799-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/59462715-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/109993642-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/199675964-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/103653592-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/1137611914-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/82078641-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/411026199-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/109756016-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/100407576-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/60725875-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/421827453-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/103974940-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/110330925-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/338753171-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/61157826-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/105757794-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/416989699-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/99826025-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/133601335-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/158739183-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/339104227-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/132450233-380_Missing Gas Capacity</t>
+  </si>
+  <si>
     <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/432729521-380_Missing Gas Capacity</t>
   </si>
   <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/59462715-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/109993642-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/414663585-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/82767145-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/172302572-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/162828577-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/116797658-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/61157826-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/133601335-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/158739183-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/339104227-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/98421779-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/98900549-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/107438024-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/103974940-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/145665799-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/60725875-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/82084019-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/421827453-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/105757794-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/99826025-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/132450233-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/100407576-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/109756016-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/411026199-380_Missing Gas Capacity</t>
-  </si>
-  <si>
     <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/103381531-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/255011550-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/105581403-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/181125039-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/338753171-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/110330925-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/82078641-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/199675964-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/1137611914-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/103653592-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/416989699-380_Missing Gas Capacity</t>
   </si>
   <si>
     <t>ccs retrofit of -- Tavazzano power station_CCGT8, timepoint 1</t>
@@ -4823,7 +4823,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{60EA3804-B50F-4C92-86E6-4AB9FF2E547F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A6A27A1D-9C76-44F1-A09D-C45F372B37F0}">
   <dimension ref="B9:T278"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -5011,7 +5011,7 @@
         <v>33</v>
       </c>
       <c r="D13" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E13">
         <v>0.18317520000000001</v>
@@ -5067,7 +5067,7 @@
         <v>33</v>
       </c>
       <c r="D14" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E14">
         <v>0.13765950000000002</v>
@@ -5347,7 +5347,7 @@
         <v>33</v>
       </c>
       <c r="D19" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E19">
         <v>0.30649709999999997</v>
@@ -5403,7 +5403,7 @@
         <v>33</v>
       </c>
       <c r="D20" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E20">
         <v>0.30649709999999997</v>
@@ -5459,7 +5459,7 @@
         <v>33</v>
       </c>
       <c r="D21" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E21">
         <v>0.30649709999999997</v>
@@ -5515,7 +5515,7 @@
         <v>33</v>
       </c>
       <c r="D22" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E22">
         <v>0.33007379999999992</v>
@@ -5571,7 +5571,7 @@
         <v>33</v>
       </c>
       <c r="D23" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E23">
         <v>0.33007379999999992</v>
@@ -5627,7 +5627,7 @@
         <v>33</v>
       </c>
       <c r="D24" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E24">
         <v>0.33007379999999992</v>
@@ -5683,7 +5683,7 @@
         <v>49</v>
       </c>
       <c r="D25" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="E25">
         <v>0.49118125000000001</v>
@@ -5739,7 +5739,7 @@
         <v>49</v>
       </c>
       <c r="D26" t="s">
-        <v>77</v>
+        <v>60</v>
       </c>
       <c r="E26">
         <v>0.52272499999999988</v>
@@ -5795,7 +5795,7 @@
         <v>49</v>
       </c>
       <c r="D27" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="E27">
         <v>0.450625</v>
@@ -5851,7 +5851,7 @@
         <v>49</v>
       </c>
       <c r="D28" t="s">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="E28">
         <v>0.52272499999999988</v>
@@ -5907,7 +5907,7 @@
         <v>49</v>
       </c>
       <c r="D29" t="s">
-        <v>56</v>
+        <v>84</v>
       </c>
       <c r="E29">
         <v>0.49118125000000001</v>
@@ -5963,7 +5963,7 @@
         <v>49</v>
       </c>
       <c r="D30" t="s">
-        <v>56</v>
+        <v>84</v>
       </c>
       <c r="E30">
         <v>0.49118125000000001</v>
@@ -6019,7 +6019,7 @@
         <v>49</v>
       </c>
       <c r="D31" t="s">
-        <v>56</v>
+        <v>84</v>
       </c>
       <c r="E31">
         <v>0.49118125000000001</v>
@@ -6131,7 +6131,7 @@
         <v>49</v>
       </c>
       <c r="D33" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="E33">
         <v>0.49118125000000001</v>
@@ -6299,7 +6299,7 @@
         <v>49</v>
       </c>
       <c r="D36" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="E36">
         <v>0.49118125000000001</v>
@@ -6355,7 +6355,7 @@
         <v>49</v>
       </c>
       <c r="D37" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="E37">
         <v>0.49118125000000001</v>
@@ -6411,7 +6411,7 @@
         <v>49</v>
       </c>
       <c r="D38" t="s">
-        <v>59</v>
+        <v>72</v>
       </c>
       <c r="E38">
         <v>0.49118125000000001</v>
@@ -6467,7 +6467,7 @@
         <v>49</v>
       </c>
       <c r="D39" t="s">
-        <v>59</v>
+        <v>72</v>
       </c>
       <c r="E39">
         <v>0.49118125000000001</v>
@@ -6523,7 +6523,7 @@
         <v>49</v>
       </c>
       <c r="D40" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="E40">
         <v>0.46865000000000007</v>
@@ -6579,7 +6579,7 @@
         <v>49</v>
       </c>
       <c r="D41" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="E41">
         <v>0.49118125000000001</v>
@@ -6635,7 +6635,7 @@
         <v>49</v>
       </c>
       <c r="D42" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="E42">
         <v>0.49118125000000001</v>
@@ -6691,7 +6691,7 @@
         <v>49</v>
       </c>
       <c r="D43" t="s">
-        <v>74</v>
+        <v>63</v>
       </c>
       <c r="E43">
         <v>0.49118125000000001</v>
@@ -6747,7 +6747,7 @@
         <v>49</v>
       </c>
       <c r="D44" t="s">
-        <v>74</v>
+        <v>63</v>
       </c>
       <c r="E44">
         <v>0.49118125000000001</v>
@@ -6803,7 +6803,7 @@
         <v>49</v>
       </c>
       <c r="D45" t="s">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="E45">
         <v>0.49118125000000001</v>
@@ -6859,7 +6859,7 @@
         <v>49</v>
       </c>
       <c r="D46" t="s">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="E46">
         <v>0.49118125000000001</v>
@@ -6915,7 +6915,7 @@
         <v>49</v>
       </c>
       <c r="D47" t="s">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="E47">
         <v>0.49118125000000001</v>
@@ -6971,7 +6971,7 @@
         <v>49</v>
       </c>
       <c r="D48" t="s">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="E48">
         <v>0.49118125000000001</v>
@@ -7027,7 +7027,7 @@
         <v>49</v>
       </c>
       <c r="D49" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="E49">
         <v>0.47315625000000006</v>
@@ -7083,7 +7083,7 @@
         <v>49</v>
       </c>
       <c r="D50" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="E50">
         <v>0.47315625000000006</v>
@@ -7139,7 +7139,7 @@
         <v>49</v>
       </c>
       <c r="D51" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="E51">
         <v>0.49118125000000001</v>
@@ -7195,7 +7195,7 @@
         <v>49</v>
       </c>
       <c r="D52" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="E52">
         <v>0.54075000000000006</v>
@@ -7251,7 +7251,7 @@
         <v>49</v>
       </c>
       <c r="D53" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="E53">
         <v>0.49118125000000001</v>
@@ -7363,7 +7363,7 @@
         <v>49</v>
       </c>
       <c r="D55" t="s">
-        <v>76</v>
+        <v>59</v>
       </c>
       <c r="E55">
         <v>0.49118125000000001</v>
@@ -7419,7 +7419,7 @@
         <v>49</v>
       </c>
       <c r="D56" t="s">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="E56">
         <v>0.49118125000000001</v>
@@ -7475,7 +7475,7 @@
         <v>49</v>
       </c>
       <c r="D57" t="s">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="E57">
         <v>0.49118125000000001</v>
@@ -7531,7 +7531,7 @@
         <v>49</v>
       </c>
       <c r="D58" t="s">
-        <v>62</v>
+        <v>87</v>
       </c>
       <c r="E58">
         <v>0.47315625000000006</v>
@@ -7587,7 +7587,7 @@
         <v>49</v>
       </c>
       <c r="D59" t="s">
-        <v>62</v>
+        <v>87</v>
       </c>
       <c r="E59">
         <v>0.47315625000000006</v>
@@ -7643,7 +7643,7 @@
         <v>49</v>
       </c>
       <c r="D60" t="s">
-        <v>62</v>
+        <v>87</v>
       </c>
       <c r="E60">
         <v>0.450625</v>
@@ -7699,7 +7699,7 @@
         <v>49</v>
       </c>
       <c r="D61" t="s">
-        <v>62</v>
+        <v>87</v>
       </c>
       <c r="E61">
         <v>0.450625</v>
@@ -7811,7 +7811,7 @@
         <v>49</v>
       </c>
       <c r="D63" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E63">
         <v>0.4911812499999999</v>
@@ -7867,7 +7867,7 @@
         <v>49</v>
       </c>
       <c r="D64" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="E64">
         <v>0.49118125000000001</v>
@@ -7923,7 +7923,7 @@
         <v>49</v>
       </c>
       <c r="D65" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="E65">
         <v>0.49118125000000001</v>
@@ -7979,7 +7979,7 @@
         <v>49</v>
       </c>
       <c r="D66" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="E66">
         <v>0.49118125000000001</v>
@@ -8147,7 +8147,7 @@
         <v>49</v>
       </c>
       <c r="D69" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="E69">
         <v>0.49118125000000001</v>
@@ -8203,7 +8203,7 @@
         <v>49</v>
       </c>
       <c r="D70" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="E70">
         <v>0.49118125000000001</v>
@@ -8259,7 +8259,7 @@
         <v>49</v>
       </c>
       <c r="D71" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E71">
         <v>0.49118125000000001</v>
@@ -8315,7 +8315,7 @@
         <v>49</v>
       </c>
       <c r="D72" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E72">
         <v>0.49118125000000001</v>
@@ -8371,7 +8371,7 @@
         <v>49</v>
       </c>
       <c r="D73" t="s">
-        <v>81</v>
+        <v>53</v>
       </c>
       <c r="E73">
         <v>0.49118125000000001</v>
@@ -8427,7 +8427,7 @@
         <v>49</v>
       </c>
       <c r="D74" t="s">
-        <v>81</v>
+        <v>53</v>
       </c>
       <c r="E74">
         <v>0.49118125000000001</v>
@@ -8483,7 +8483,7 @@
         <v>49</v>
       </c>
       <c r="D75" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="E75">
         <v>0.50470000000000004</v>
@@ -8539,7 +8539,7 @@
         <v>49</v>
       </c>
       <c r="D76" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="E76">
         <v>0.49118125000000001</v>
@@ -8595,7 +8595,7 @@
         <v>49</v>
       </c>
       <c r="D77" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="E77">
         <v>0.49118125000000001</v>
@@ -8763,7 +8763,7 @@
         <v>49</v>
       </c>
       <c r="D80" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E80">
         <v>0.49118125000000001</v>
@@ -8819,7 +8819,7 @@
         <v>49</v>
       </c>
       <c r="D81" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E81">
         <v>0.49118125000000001</v>
@@ -8875,7 +8875,7 @@
         <v>49</v>
       </c>
       <c r="D82" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="E82">
         <v>0.49118125000000001</v>
@@ -8931,7 +8931,7 @@
         <v>49</v>
       </c>
       <c r="D83" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="E83">
         <v>0.49118125000000001</v>
@@ -8987,7 +8987,7 @@
         <v>49</v>
       </c>
       <c r="D84" t="s">
-        <v>79</v>
+        <v>61</v>
       </c>
       <c r="E84">
         <v>0.49118125000000001</v>
@@ -9043,7 +9043,7 @@
         <v>49</v>
       </c>
       <c r="D85" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="E85">
         <v>0.49118125000000001</v>
@@ -9099,7 +9099,7 @@
         <v>49</v>
       </c>
       <c r="D86" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="E86">
         <v>0.49118125000000001</v>
@@ -9155,7 +9155,7 @@
         <v>49</v>
       </c>
       <c r="D87" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E87">
         <v>0.49118125000000001</v>
@@ -9211,7 +9211,7 @@
         <v>49</v>
       </c>
       <c r="D88" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E88">
         <v>0.49118125000000001</v>
@@ -9267,7 +9267,7 @@
         <v>49</v>
       </c>
       <c r="D89" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E89">
         <v>0.52272499999999988</v>
@@ -9323,7 +9323,7 @@
         <v>49</v>
       </c>
       <c r="D90" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E90">
         <v>0.49118125000000001</v>
@@ -9379,7 +9379,7 @@
         <v>49</v>
       </c>
       <c r="D91" t="s">
-        <v>64</v>
+        <v>50</v>
       </c>
       <c r="E91">
         <v>0.49118125000000001</v>
@@ -9435,7 +9435,7 @@
         <v>49</v>
       </c>
       <c r="D92" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="E92">
         <v>0.52272499999999988</v>
@@ -9491,7 +9491,7 @@
         <v>49</v>
       </c>
       <c r="D93" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E93">
         <v>0.49118125000000001</v>
@@ -9547,7 +9547,7 @@
         <v>49</v>
       </c>
       <c r="D94" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E94">
         <v>0.49118125000000001</v>
@@ -9603,7 +9603,7 @@
         <v>49</v>
       </c>
       <c r="D95" t="s">
-        <v>51</v>
+        <v>83</v>
       </c>
       <c r="E95">
         <v>0.49118125000000001</v>
@@ -9659,7 +9659,7 @@
         <v>49</v>
       </c>
       <c r="D96" t="s">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="E96">
         <v>0.49118125000000001</v>
@@ -9715,7 +9715,7 @@
         <v>49</v>
       </c>
       <c r="D97" t="s">
-        <v>80</v>
+        <v>52</v>
       </c>
       <c r="E97">
         <v>0.49118125000000001</v>
@@ -9827,7 +9827,7 @@
         <v>49</v>
       </c>
       <c r="D99" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="E99">
         <v>0.54075000000000006</v>
@@ -9883,7 +9883,7 @@
         <v>49</v>
       </c>
       <c r="D100" t="s">
-        <v>55</v>
+        <v>86</v>
       </c>
       <c r="E100">
         <v>0.54075000000000006</v>
@@ -9939,7 +9939,7 @@
         <v>49</v>
       </c>
       <c r="D101" t="s">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="E101">
         <v>0.54075000000000006</v>
@@ -9995,7 +9995,7 @@
         <v>49</v>
       </c>
       <c r="D102" t="s">
-        <v>50</v>
+        <v>81</v>
       </c>
       <c r="E102">
         <v>0.49118125000000001</v>
@@ -10051,7 +10051,7 @@
         <v>49</v>
       </c>
       <c r="D103" t="s">
-        <v>50</v>
+        <v>81</v>
       </c>
       <c r="E103">
         <v>0.49118125000000001</v>
@@ -10107,7 +10107,7 @@
         <v>49</v>
       </c>
       <c r="D104" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="E104">
         <v>0.49118125000000001</v>
@@ -10163,7 +10163,7 @@
         <v>49</v>
       </c>
       <c r="D105" t="s">
-        <v>57</v>
+        <v>70</v>
       </c>
       <c r="E105">
         <v>0.49118125000000001</v>
@@ -10219,7 +10219,7 @@
         <v>49</v>
       </c>
       <c r="D106" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E106">
         <v>0.450625</v>
@@ -10275,7 +10275,7 @@
         <v>49</v>
       </c>
       <c r="D107" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E107">
         <v>0.450625</v>
@@ -10331,7 +10331,7 @@
         <v>49</v>
       </c>
       <c r="D108" t="s">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="E108">
         <v>0.47315625000000006</v>
@@ -10443,7 +10443,7 @@
         <v>49</v>
       </c>
       <c r="D110" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="E110">
         <v>0.49118125000000001</v>
@@ -10499,7 +10499,7 @@
         <v>49</v>
       </c>
       <c r="D111" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="E111">
         <v>0.46865000000000007</v>
@@ -10611,7 +10611,7 @@
         <v>49</v>
       </c>
       <c r="D113" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="E113">
         <v>0.49118125000000001</v>
@@ -11115,7 +11115,7 @@
         <v>49</v>
       </c>
       <c r="D122" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E122">
         <v>0.54075000000000006</v>
@@ -11171,7 +11171,7 @@
         <v>49</v>
       </c>
       <c r="D123" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E123">
         <v>0.54075000000000006</v>
@@ -11227,7 +11227,7 @@
         <v>49</v>
       </c>
       <c r="D124" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E124">
         <v>0.54075000000000006</v>
@@ -11283,7 +11283,7 @@
         <v>49</v>
       </c>
       <c r="D125" t="s">
-        <v>75</v>
+        <v>34</v>
       </c>
       <c r="E125">
         <v>0.54075000000000006</v>
@@ -11563,7 +11563,7 @@
         <v>49</v>
       </c>
       <c r="D130" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E130">
         <v>0.54075000000000006</v>
@@ -11619,7 +11619,7 @@
         <v>49</v>
       </c>
       <c r="D131" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E131">
         <v>0.54075000000000006</v>
@@ -11675,7 +11675,7 @@
         <v>49</v>
       </c>
       <c r="D132" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E132">
         <v>0.54075000000000006</v>
@@ -11731,7 +11731,7 @@
         <v>49</v>
       </c>
       <c r="D133" t="s">
-        <v>58</v>
+        <v>18</v>
       </c>
       <c r="E133">
         <v>0.54075000000000006</v>
@@ -12459,7 +12459,7 @@
         <v>49</v>
       </c>
       <c r="D146" t="s">
-        <v>37</v>
+        <v>78</v>
       </c>
       <c r="E146">
         <v>0.54075000000000006</v>
@@ -12627,7 +12627,7 @@
         <v>49</v>
       </c>
       <c r="D149" t="s">
-        <v>16</v>
+        <v>54</v>
       </c>
       <c r="E149">
         <v>0.54075000000000006</v>
@@ -12683,7 +12683,7 @@
         <v>49</v>
       </c>
       <c r="D150" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E150">
         <v>0.54075000000000006</v>
@@ -13467,7 +13467,7 @@
         <v>49</v>
       </c>
       <c r="D164" t="s">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="E164">
         <v>0.48667500000000002</v>
@@ -14307,7 +14307,7 @@
         <v>49</v>
       </c>
       <c r="D179" t="s">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="E179">
         <v>0.46865000000000007</v>
@@ -14363,7 +14363,7 @@
         <v>49</v>
       </c>
       <c r="D180" t="s">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="E180">
         <v>0.46865000000000007</v>
@@ -14587,7 +14587,7 @@
         <v>49</v>
       </c>
       <c r="D184" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E184">
         <v>0.48667500000000002</v>
@@ -14643,7 +14643,7 @@
         <v>49</v>
       </c>
       <c r="D185" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E185">
         <v>0.48667500000000002</v>
@@ -15371,7 +15371,7 @@
         <v>49</v>
       </c>
       <c r="D198" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E198">
         <v>0.50470000000000004</v>
@@ -15595,7 +15595,7 @@
         <v>49</v>
       </c>
       <c r="D202" t="s">
-        <v>55</v>
+        <v>86</v>
       </c>
       <c r="E202">
         <v>0.46865000000000007</v>
@@ -16323,7 +16323,7 @@
         <v>49</v>
       </c>
       <c r="D215" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="E215">
         <v>0.450625</v>
@@ -16491,7 +16491,7 @@
         <v>49</v>
       </c>
       <c r="D218" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E218">
         <v>0.50470000000000004</v>
@@ -16547,7 +16547,7 @@
         <v>49</v>
       </c>
       <c r="D219" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E219">
         <v>0.50470000000000004</v>
@@ -16715,7 +16715,7 @@
         <v>49</v>
       </c>
       <c r="D222" t="s">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="E222">
         <v>0.450625</v>
@@ -16771,7 +16771,7 @@
         <v>49</v>
       </c>
       <c r="D223" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E223">
         <v>0.29741250000000002</v>
@@ -16827,7 +16827,7 @@
         <v>49</v>
       </c>
       <c r="D224" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E224">
         <v>0.28839999999999999</v>
@@ -16883,7 +16883,7 @@
         <v>49</v>
       </c>
       <c r="D225" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E225">
         <v>0.28839999999999999</v>
@@ -16939,7 +16939,7 @@
         <v>49</v>
       </c>
       <c r="D226" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="E226">
         <v>0.24784375000000003</v>
@@ -17443,7 +17443,7 @@
         <v>49</v>
       </c>
       <c r="D235" t="s">
-        <v>74</v>
+        <v>63</v>
       </c>
       <c r="E235">
         <v>0.25235000000000002</v>
@@ -17723,7 +17723,7 @@
         <v>49</v>
       </c>
       <c r="D240" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E240">
         <v>0.27938750000000001</v>
@@ -17835,7 +17835,7 @@
         <v>49</v>
       </c>
       <c r="D242" t="s">
-        <v>57</v>
+        <v>70</v>
       </c>
       <c r="E242">
         <v>0.25235000000000002</v>
@@ -18031,7 +18031,7 @@
         <v>49</v>
       </c>
       <c r="D247" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="E247">
         <v>0.32445000000000007</v>
@@ -18101,7 +18101,7 @@
         <v>49</v>
       </c>
       <c r="D249" t="s">
-        <v>64</v>
+        <v>50</v>
       </c>
       <c r="E249">
         <v>0.32445000000000002</v>
@@ -18241,7 +18241,7 @@
         <v>49</v>
       </c>
       <c r="D253" t="s">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="E253">
         <v>0.27938750000000001</v>
@@ -18276,7 +18276,7 @@
         <v>49</v>
       </c>
       <c r="D254" t="s">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="E254">
         <v>0.27938750000000001</v>
@@ -18311,7 +18311,7 @@
         <v>49</v>
       </c>
       <c r="D255" t="s">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="E255">
         <v>0.27938750000000001</v>
@@ -18346,7 +18346,7 @@
         <v>49</v>
       </c>
       <c r="D256" t="s">
-        <v>59</v>
+        <v>72</v>
       </c>
       <c r="E256">
         <v>0.31093124999999999</v>
@@ -18381,7 +18381,7 @@
         <v>49</v>
       </c>
       <c r="D257" t="s">
-        <v>56</v>
+        <v>84</v>
       </c>
       <c r="E257">
         <v>0.27938750000000001</v>
@@ -18416,7 +18416,7 @@
         <v>49</v>
       </c>
       <c r="D258" t="s">
-        <v>56</v>
+        <v>84</v>
       </c>
       <c r="E258">
         <v>0.27938750000000001</v>
@@ -18451,7 +18451,7 @@
         <v>49</v>
       </c>
       <c r="D259" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="E259">
         <v>0.26136249999999994</v>
@@ -18486,7 +18486,7 @@
         <v>49</v>
       </c>
       <c r="D260" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E260">
         <v>0.28839999999999999</v>
@@ -18521,7 +18521,7 @@
         <v>49</v>
       </c>
       <c r="D261" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E261">
         <v>0.28839999999999999</v>
@@ -18556,7 +18556,7 @@
         <v>49</v>
       </c>
       <c r="D262" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E262">
         <v>0.28839999999999999</v>
@@ -18626,7 +18626,7 @@
         <v>439</v>
       </c>
       <c r="D264" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="E264">
         <v>0.41457500000000003</v>
@@ -18731,7 +18731,7 @@
         <v>439</v>
       </c>
       <c r="D267" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E267">
         <v>0.22981874999999999</v>
@@ -18941,7 +18941,7 @@
         <v>439</v>
       </c>
       <c r="D273" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="E273">
         <v>0.27938750000000001</v>
@@ -19149,7 +19149,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6006FBBA-11E2-4AE7-86C8-10F3A7DAEAC5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B44CA91-07A2-4CE2-819D-A0286D6F19AA}">
   <dimension ref="B9:T842"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -19231,19 +19231,19 @@
         <v>2022</v>
       </c>
       <c r="F11">
-        <v>1.0679322033898306</v>
+        <v>0.24877966101694915</v>
       </c>
       <c r="G11">
-        <v>0.36049999999999999</v>
+        <v>0.33990000000000004</v>
       </c>
       <c r="H11">
-        <v>3850.0000000000005</v>
+        <v>4427.5</v>
       </c>
       <c r="I11">
-        <v>143</v>
+        <v>157.30000000000001</v>
       </c>
       <c r="J11">
-        <v>8.4</v>
+        <v>9.240000000000002</v>
       </c>
       <c r="K11">
         <v>50</v>
@@ -19284,19 +19284,19 @@
         <v>2022</v>
       </c>
       <c r="F12">
-        <v>0.22450847457627116</v>
+        <v>0.49149152542372881</v>
       </c>
       <c r="G12">
-        <v>0.33990000000000004</v>
+        <v>0.36049999999999999</v>
       </c>
       <c r="H12">
-        <v>4427.5</v>
+        <v>3850.0000000000005</v>
       </c>
       <c r="I12">
-        <v>157.30000000000001</v>
+        <v>143</v>
       </c>
       <c r="J12">
-        <v>9.240000000000002</v>
+        <v>8.4</v>
       </c>
       <c r="K12">
         <v>50</v>
@@ -19337,19 +19337,19 @@
         <v>2022</v>
       </c>
       <c r="F13">
-        <v>0.27911864406779663</v>
+        <v>0.39440677966101695</v>
       </c>
       <c r="G13">
-        <v>0.33990000000000004</v>
+        <v>0.36049999999999999</v>
       </c>
       <c r="H13">
-        <v>4427.5</v>
+        <v>3850.0000000000005</v>
       </c>
       <c r="I13">
-        <v>157.30000000000001</v>
+        <v>143</v>
       </c>
       <c r="J13">
-        <v>9.240000000000002</v>
+        <v>8.4</v>
       </c>
       <c r="K13">
         <v>50</v>
@@ -19390,7 +19390,7 @@
         <v>2022</v>
       </c>
       <c r="F14">
-        <v>0.39440677966101695</v>
+        <v>0.51576271186440681</v>
       </c>
       <c r="G14">
         <v>0.36049999999999999</v>
@@ -19443,19 +19443,19 @@
         <v>2022</v>
       </c>
       <c r="F15">
-        <v>0.35800000000000004</v>
+        <v>0.27911864406779663</v>
       </c>
       <c r="G15">
-        <v>0.36050000000000004</v>
+        <v>0.33990000000000004</v>
       </c>
       <c r="H15">
-        <v>3850.0000000000009</v>
+        <v>4427.5</v>
       </c>
       <c r="I15">
-        <v>143</v>
+        <v>157.30000000000001</v>
       </c>
       <c r="J15">
-        <v>8.4</v>
+        <v>9.240000000000002</v>
       </c>
       <c r="K15">
         <v>50</v>
@@ -19496,13 +19496,13 @@
         <v>2022</v>
       </c>
       <c r="F16">
-        <v>0.49149152542372881</v>
+        <v>0.35800000000000004</v>
       </c>
       <c r="G16">
-        <v>0.36049999999999999</v>
+        <v>0.36050000000000004</v>
       </c>
       <c r="H16">
-        <v>3850.0000000000005</v>
+        <v>3850.0000000000009</v>
       </c>
       <c r="I16">
         <v>143</v>
@@ -19549,19 +19549,19 @@
         <v>2022</v>
       </c>
       <c r="F17">
-        <v>0.51576271186440681</v>
+        <v>0.22450847457627116</v>
       </c>
       <c r="G17">
-        <v>0.36049999999999999</v>
+        <v>0.33990000000000004</v>
       </c>
       <c r="H17">
-        <v>3850.0000000000005</v>
+        <v>4427.5</v>
       </c>
       <c r="I17">
-        <v>143</v>
+        <v>157.30000000000001</v>
       </c>
       <c r="J17">
-        <v>8.4</v>
+        <v>9.240000000000002</v>
       </c>
       <c r="K17">
         <v>50</v>
@@ -19602,19 +19602,19 @@
         <v>2022</v>
       </c>
       <c r="F18">
-        <v>0.24877966101694915</v>
+        <v>1.0679322033898306</v>
       </c>
       <c r="G18">
-        <v>0.33990000000000004</v>
+        <v>0.36049999999999999</v>
       </c>
       <c r="H18">
-        <v>4427.5</v>
+        <v>3850.0000000000005</v>
       </c>
       <c r="I18">
-        <v>157.30000000000001</v>
+        <v>143</v>
       </c>
       <c r="J18">
-        <v>9.240000000000002</v>
+        <v>8.4</v>
       </c>
       <c r="K18">
         <v>50</v>
@@ -19649,7 +19649,7 @@
         <v>13</v>
       </c>
       <c r="D19" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="E19">
         <v>2008</v>
@@ -19702,7 +19702,7 @@
         <v>13</v>
       </c>
       <c r="D20" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E20">
         <v>1998</v>
@@ -19755,7 +19755,7 @@
         <v>13</v>
       </c>
       <c r="D21" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="E21">
         <v>2008</v>
@@ -19808,7 +19808,7 @@
         <v>13</v>
       </c>
       <c r="D22" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E22">
         <v>2001</v>
@@ -19861,7 +19861,7 @@
         <v>13</v>
       </c>
       <c r="D23" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E23">
         <v>2013</v>
@@ -19914,7 +19914,7 @@
         <v>13</v>
       </c>
       <c r="D24" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="E24">
         <v>1965</v>
@@ -19967,7 +19967,7 @@
         <v>13</v>
       </c>
       <c r="D25" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E25">
         <v>2003</v>
@@ -20020,7 +20020,7 @@
         <v>13</v>
       </c>
       <c r="D26" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E26">
         <v>2009</v>
@@ -20073,7 +20073,7 @@
         <v>13</v>
       </c>
       <c r="D27" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="E27">
         <v>2018</v>
@@ -20126,7 +20126,7 @@
         <v>13</v>
       </c>
       <c r="D28" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="E28">
         <v>2009</v>
@@ -20185,19 +20185,19 @@
         <v>2022</v>
       </c>
       <c r="F29">
-        <v>0.18416184971098257</v>
+        <v>0.61803468208092449</v>
       </c>
       <c r="G29">
-        <v>0.35020000000000001</v>
+        <v>0.37080000000000002</v>
       </c>
       <c r="H29">
-        <v>2530</v>
+        <v>2200</v>
       </c>
       <c r="I29">
-        <v>72.600000000000009</v>
+        <v>66</v>
       </c>
       <c r="J29">
-        <v>5.7750000000000004</v>
+        <v>5.25</v>
       </c>
       <c r="K29">
         <v>50</v>
@@ -20291,19 +20291,19 @@
         <v>2022</v>
       </c>
       <c r="F31">
-        <v>0.61803468208092449</v>
+        <v>0.18416184971098257</v>
       </c>
       <c r="G31">
-        <v>0.37080000000000002</v>
+        <v>0.35020000000000001</v>
       </c>
       <c r="H31">
-        <v>2200</v>
+        <v>2530</v>
       </c>
       <c r="I31">
-        <v>66</v>
+        <v>72.600000000000009</v>
       </c>
       <c r="J31">
-        <v>5.25</v>
+        <v>5.7750000000000004</v>
       </c>
       <c r="K31">
         <v>50</v>
@@ -20497,7 +20497,7 @@
         <v>33</v>
       </c>
       <c r="D35" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E35">
         <v>2005</v>
@@ -20550,7 +20550,7 @@
         <v>33</v>
       </c>
       <c r="D36" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E36">
         <v>1986</v>
@@ -20603,7 +20603,7 @@
         <v>33</v>
       </c>
       <c r="D37" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E37">
         <v>1991</v>
@@ -20656,7 +20656,7 @@
         <v>33</v>
       </c>
       <c r="D38" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E38">
         <v>1992</v>
@@ -20709,7 +20709,7 @@
         <v>33</v>
       </c>
       <c r="D39" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E39">
         <v>1993</v>
@@ -20762,7 +20762,7 @@
         <v>33</v>
       </c>
       <c r="D40" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E40">
         <v>2009</v>
@@ -20815,7 +20815,7 @@
         <v>33</v>
       </c>
       <c r="D41" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E41">
         <v>2010</v>
@@ -20868,7 +20868,7 @@
         <v>33</v>
       </c>
       <c r="D42" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E42">
         <v>2010</v>
@@ -20927,7 +20927,7 @@
         <v>2022</v>
       </c>
       <c r="F43">
-        <v>0.18824049497996109</v>
+        <v>0.20557907614758497</v>
       </c>
       <c r="G43">
         <v>0.59739999999999993</v>
@@ -20980,7 +20980,7 @@
         <v>2022</v>
       </c>
       <c r="F44">
-        <v>0.21113131843159935</v>
+        <v>0.20212110068999706</v>
       </c>
       <c r="G44">
         <v>0.59739999999999993</v>
@@ -21033,19 +21033,19 @@
         <v>2022</v>
       </c>
       <c r="F45">
-        <v>0.49339465314217229</v>
+        <v>0.19481551873734657</v>
       </c>
       <c r="G45">
-        <v>0.61799999999999999</v>
+        <v>0.59739999999999993</v>
       </c>
       <c r="H45">
-        <v>1100</v>
+        <v>1265</v>
       </c>
       <c r="I45">
-        <v>33</v>
+        <v>36.300000000000004</v>
       </c>
       <c r="J45">
-        <v>3.1500000000000004</v>
+        <v>3.4650000000000003</v>
       </c>
       <c r="K45">
         <v>50</v>
@@ -21086,19 +21086,19 @@
         <v>2022</v>
       </c>
       <c r="F46">
-        <v>0.45732943023592104</v>
+        <v>0.18702289798785268</v>
       </c>
       <c r="G46">
-        <v>0.61799999999999999</v>
+        <v>0.59739999999999993</v>
       </c>
       <c r="H46">
-        <v>1100</v>
+        <v>1265</v>
       </c>
       <c r="I46">
-        <v>33</v>
+        <v>36.300000000000004</v>
       </c>
       <c r="J46">
-        <v>3.1500000000000004</v>
+        <v>3.4650000000000003</v>
       </c>
       <c r="K46">
         <v>50</v>
@@ -21133,25 +21133,25 @@
         <v>49</v>
       </c>
       <c r="D47" t="s">
-        <v>16</v>
+        <v>54</v>
       </c>
       <c r="E47">
         <v>2022</v>
       </c>
       <c r="F47">
-        <v>0.19822479031525012</v>
+        <v>0.49339465314217229</v>
       </c>
       <c r="G47">
-        <v>0.59739999999999993</v>
+        <v>0.61799999999999999</v>
       </c>
       <c r="H47">
-        <v>1265</v>
+        <v>1100</v>
       </c>
       <c r="I47">
-        <v>36.300000000000004</v>
+        <v>33</v>
       </c>
       <c r="J47">
-        <v>3.4650000000000003</v>
+        <v>3.1500000000000004</v>
       </c>
       <c r="K47">
         <v>50</v>
@@ -21186,25 +21186,25 @@
         <v>49</v>
       </c>
       <c r="D48" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E48">
         <v>2022</v>
       </c>
       <c r="F48">
-        <v>0.26604494277568891</v>
+        <v>0.45732943023592104</v>
       </c>
       <c r="G48">
-        <v>0.59739999999999993</v>
+        <v>0.61799999999999999</v>
       </c>
       <c r="H48">
-        <v>1265</v>
+        <v>1100</v>
       </c>
       <c r="I48">
-        <v>36.300000000000004</v>
+        <v>33</v>
       </c>
       <c r="J48">
-        <v>3.4650000000000003</v>
+        <v>3.1500000000000004</v>
       </c>
       <c r="K48">
         <v>50</v>
@@ -21239,13 +21239,13 @@
         <v>49</v>
       </c>
       <c r="D49" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E49">
         <v>2022</v>
       </c>
       <c r="F49">
-        <v>0.23864901045324952</v>
+        <v>0.17484692806676855</v>
       </c>
       <c r="G49">
         <v>0.59739999999999993</v>
@@ -21292,25 +21292,25 @@
         <v>49</v>
       </c>
       <c r="D50" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E50">
         <v>2022</v>
       </c>
       <c r="F50">
-        <v>0.31243538817501959</v>
+        <v>0.18872753377680451</v>
       </c>
       <c r="G50">
-        <v>0.61799999999999999</v>
+        <v>0.59739999999999993</v>
       </c>
       <c r="H50">
-        <v>1100</v>
+        <v>1265</v>
       </c>
       <c r="I50">
-        <v>33</v>
+        <v>36.300000000000004</v>
       </c>
       <c r="J50">
-        <v>3.1500000000000004</v>
+        <v>3.4650000000000007</v>
       </c>
       <c r="K50">
         <v>50</v>
@@ -21345,13 +21345,13 @@
         <v>49</v>
       </c>
       <c r="D51" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E51">
         <v>2022</v>
       </c>
       <c r="F51">
-        <v>0.20820908565053911</v>
+        <v>0.29344087509812827</v>
       </c>
       <c r="G51">
         <v>0.59739999999999993</v>
@@ -21363,7 +21363,7 @@
         <v>36.300000000000004</v>
       </c>
       <c r="J51">
-        <v>3.4650000000000007</v>
+        <v>3.4650000000000003</v>
       </c>
       <c r="K51">
         <v>50</v>
@@ -21398,13 +21398,13 @@
         <v>49</v>
       </c>
       <c r="D52" t="s">
-        <v>58</v>
+        <v>18</v>
       </c>
       <c r="E52">
         <v>2022</v>
       </c>
       <c r="F52">
-        <v>0.18629233979258764</v>
+        <v>0.19822479031525012</v>
       </c>
       <c r="G52">
         <v>0.59739999999999993</v>
@@ -21457,7 +21457,7 @@
         <v>2022</v>
       </c>
       <c r="F53">
-        <v>0.20236462008841874</v>
+        <v>0.19481551873734657</v>
       </c>
       <c r="G53">
         <v>0.59739999999999993</v>
@@ -21563,7 +21563,7 @@
         <v>2022</v>
       </c>
       <c r="F55">
-        <v>0.20212110068999706</v>
+        <v>0.21551466760318963</v>
       </c>
       <c r="G55">
         <v>0.59739999999999993</v>
@@ -21616,7 +21616,7 @@
         <v>2022</v>
       </c>
       <c r="F56">
-        <v>0.26543614427963469</v>
+        <v>0.22793415692269547</v>
       </c>
       <c r="G56">
         <v>0.59739999999999993</v>
@@ -21669,7 +21669,7 @@
         <v>2022</v>
       </c>
       <c r="F57">
-        <v>0.23280454489112914</v>
+        <v>0.21283595422055113</v>
       </c>
       <c r="G57">
         <v>0.59739999999999993</v>
@@ -21681,7 +21681,7 @@
         <v>36.300000000000004</v>
       </c>
       <c r="J57">
-        <v>3.4650000000000007</v>
+        <v>3.4650000000000003</v>
       </c>
       <c r="K57">
         <v>50</v>
@@ -21722,7 +21722,7 @@
         <v>2022</v>
       </c>
       <c r="F58">
-        <v>0.20557907614758497</v>
+        <v>0.1548783373961905</v>
       </c>
       <c r="G58">
         <v>0.59739999999999993</v>
@@ -21734,7 +21734,7 @@
         <v>36.300000000000004</v>
       </c>
       <c r="J58">
-        <v>3.4650000000000003</v>
+        <v>3.4649999999999999</v>
       </c>
       <c r="K58">
         <v>50</v>
@@ -21775,19 +21775,19 @@
         <v>2022</v>
       </c>
       <c r="F59">
-        <v>0.37112356319464518</v>
+        <v>0.27347228442755023</v>
       </c>
       <c r="G59">
-        <v>0.61799999999999999</v>
+        <v>0.59739999999999993</v>
       </c>
       <c r="H59">
-        <v>1100</v>
+        <v>1265</v>
       </c>
       <c r="I59">
-        <v>33</v>
+        <v>36.300000000000004</v>
       </c>
       <c r="J59">
-        <v>3.1500000000000004</v>
+        <v>3.4650000000000003</v>
       </c>
       <c r="K59">
         <v>50</v>
@@ -21828,7 +21828,7 @@
         <v>2022</v>
       </c>
       <c r="F60">
-        <v>0.17484692806676855</v>
+        <v>0.18556178159732259</v>
       </c>
       <c r="G60">
         <v>0.59739999999999993</v>
@@ -21881,7 +21881,7 @@
         <v>2022</v>
       </c>
       <c r="F61">
-        <v>0.18872753377680451</v>
+        <v>0.23280454489112914</v>
       </c>
       <c r="G61">
         <v>0.59739999999999993</v>
@@ -21934,7 +21934,7 @@
         <v>2022</v>
       </c>
       <c r="F62">
-        <v>0.22793415692269547</v>
+        <v>0.26604494277568891</v>
       </c>
       <c r="G62">
         <v>0.59739999999999993</v>
@@ -21987,7 +21987,7 @@
         <v>2022</v>
       </c>
       <c r="F63">
-        <v>0.1548783373961905</v>
+        <v>0.19481551873734657</v>
       </c>
       <c r="G63">
         <v>0.59739999999999993</v>
@@ -21999,7 +21999,7 @@
         <v>36.300000000000004</v>
       </c>
       <c r="J63">
-        <v>3.4649999999999999</v>
+        <v>3.4650000000000003</v>
       </c>
       <c r="K63">
         <v>50</v>
@@ -22040,7 +22040,7 @@
         <v>2022</v>
       </c>
       <c r="F64">
-        <v>0.27347228442755023</v>
+        <v>0.20820908565053911</v>
       </c>
       <c r="G64">
         <v>0.59739999999999993</v>
@@ -22052,7 +22052,7 @@
         <v>36.300000000000004</v>
       </c>
       <c r="J64">
-        <v>3.4650000000000003</v>
+        <v>3.4650000000000007</v>
       </c>
       <c r="K64">
         <v>50</v>
@@ -22093,7 +22093,7 @@
         <v>2022</v>
       </c>
       <c r="F65">
-        <v>0.28443065735652601</v>
+        <v>0.18629233979258764</v>
       </c>
       <c r="G65">
         <v>0.59739999999999993</v>
@@ -22146,19 +22146,19 @@
         <v>2022</v>
       </c>
       <c r="F66">
-        <v>0.39839773581787374</v>
+        <v>0.20236462008841874</v>
       </c>
       <c r="G66">
-        <v>0.61799999999999999</v>
+        <v>0.59739999999999993</v>
       </c>
       <c r="H66">
-        <v>1100</v>
+        <v>1265</v>
       </c>
       <c r="I66">
-        <v>33</v>
+        <v>36.300000000000004</v>
       </c>
       <c r="J66">
-        <v>3.1500000000000004</v>
+        <v>3.4650000000000003</v>
       </c>
       <c r="K66">
         <v>50</v>
@@ -22199,19 +22199,19 @@
         <v>2022</v>
       </c>
       <c r="F67">
-        <v>0.18556178159732259</v>
+        <v>0.39839773581787374</v>
       </c>
       <c r="G67">
-        <v>0.59739999999999993</v>
+        <v>0.61799999999999999</v>
       </c>
       <c r="H67">
-        <v>1265</v>
+        <v>1100</v>
       </c>
       <c r="I67">
-        <v>36.300000000000004</v>
+        <v>33</v>
       </c>
       <c r="J67">
-        <v>3.4650000000000003</v>
+        <v>3.1500000000000004</v>
       </c>
       <c r="K67">
         <v>50</v>
@@ -22252,19 +22252,19 @@
         <v>2022</v>
       </c>
       <c r="F68">
-        <v>0.21283595422055113</v>
+        <v>0.30829555840185086</v>
       </c>
       <c r="G68">
-        <v>0.59739999999999993</v>
+        <v>0.61799999999999999</v>
       </c>
       <c r="H68">
-        <v>1265</v>
+        <v>1100</v>
       </c>
       <c r="I68">
-        <v>36.300000000000004</v>
+        <v>33</v>
       </c>
       <c r="J68">
-        <v>3.4650000000000003</v>
+        <v>3.1500000000000004</v>
       </c>
       <c r="K68">
         <v>50</v>
@@ -22299,13 +22299,13 @@
         <v>49</v>
       </c>
       <c r="D69" t="s">
-        <v>75</v>
+        <v>34</v>
       </c>
       <c r="E69">
         <v>2022</v>
       </c>
       <c r="F69">
-        <v>0.29344087509812827</v>
+        <v>0.27761211420071885</v>
       </c>
       <c r="G69">
         <v>0.59739999999999993</v>
@@ -22352,25 +22352,25 @@
         <v>49</v>
       </c>
       <c r="D70" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E70">
         <v>2022</v>
       </c>
       <c r="F70">
-        <v>0.19481551873734657</v>
+        <v>0.3567559186877659</v>
       </c>
       <c r="G70">
-        <v>0.59739999999999993</v>
+        <v>0.61799999999999999</v>
       </c>
       <c r="H70">
-        <v>1265</v>
+        <v>1100</v>
       </c>
       <c r="I70">
-        <v>36.300000000000004</v>
+        <v>33</v>
       </c>
       <c r="J70">
-        <v>3.4650000000000003</v>
+        <v>3.1500000000000004</v>
       </c>
       <c r="K70">
         <v>50</v>
@@ -22405,13 +22405,13 @@
         <v>49</v>
       </c>
       <c r="D71" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E71">
         <v>2022</v>
       </c>
       <c r="F71">
-        <v>0.19481551873734657</v>
+        <v>0.18507474280047922</v>
       </c>
       <c r="G71">
         <v>0.59739999999999993</v>
@@ -22423,7 +22423,7 @@
         <v>36.300000000000004</v>
       </c>
       <c r="J71">
-        <v>3.4650000000000003</v>
+        <v>3.4649999999999999</v>
       </c>
       <c r="K71">
         <v>50</v>
@@ -22458,25 +22458,25 @@
         <v>49</v>
       </c>
       <c r="D72" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E72">
         <v>2022</v>
       </c>
       <c r="F72">
-        <v>0.30829555840185086</v>
+        <v>0.19676367392472002</v>
       </c>
       <c r="G72">
-        <v>0.61799999999999999</v>
+        <v>0.59739999999999993</v>
       </c>
       <c r="H72">
-        <v>1100</v>
+        <v>1265</v>
       </c>
       <c r="I72">
-        <v>33</v>
+        <v>36.300000000000004</v>
       </c>
       <c r="J72">
-        <v>3.1500000000000004</v>
+        <v>3.4650000000000003</v>
       </c>
       <c r="K72">
         <v>50</v>
@@ -22511,13 +22511,13 @@
         <v>49</v>
       </c>
       <c r="D73" t="s">
-        <v>37</v>
+        <v>78</v>
       </c>
       <c r="E73">
         <v>2022</v>
       </c>
       <c r="F73">
-        <v>0.27761211420071885</v>
+        <v>0.16608022972358796</v>
       </c>
       <c r="G73">
         <v>0.59739999999999993</v>
@@ -22570,7 +22570,7 @@
         <v>2022</v>
       </c>
       <c r="F74">
-        <v>0.21551466760318963</v>
+        <v>0.28443065735652601</v>
       </c>
       <c r="G74">
         <v>0.59739999999999993</v>
@@ -22623,19 +22623,19 @@
         <v>2022</v>
       </c>
       <c r="F75">
-        <v>0.19481551873734657</v>
+        <v>0.43468212618270452</v>
       </c>
       <c r="G75">
-        <v>0.59739999999999993</v>
+        <v>0.61799999999999988</v>
       </c>
       <c r="H75">
-        <v>1265</v>
+        <v>1100</v>
       </c>
       <c r="I75">
-        <v>36.300000000000004</v>
+        <v>33</v>
       </c>
       <c r="J75">
-        <v>3.4650000000000003</v>
+        <v>3.1500000000000004</v>
       </c>
       <c r="K75">
         <v>50</v>
@@ -22676,7 +22676,7 @@
         <v>2022</v>
       </c>
       <c r="F76">
-        <v>0.18702289798785268</v>
+        <v>0.18824049497996109</v>
       </c>
       <c r="G76">
         <v>0.59739999999999993</v>
@@ -22729,7 +22729,7 @@
         <v>2022</v>
       </c>
       <c r="F77">
-        <v>0.16608022972358796</v>
+        <v>0.19627663512787666</v>
       </c>
       <c r="G77">
         <v>0.59739999999999993</v>
@@ -22741,7 +22741,7 @@
         <v>36.300000000000004</v>
       </c>
       <c r="J77">
-        <v>3.4650000000000003</v>
+        <v>3.4649999999999999</v>
       </c>
       <c r="K77">
         <v>50</v>
@@ -22782,7 +22782,7 @@
         <v>2022</v>
       </c>
       <c r="F78">
-        <v>0.19676367392472002</v>
+        <v>0.21113131843159935</v>
       </c>
       <c r="G78">
         <v>0.59739999999999993</v>
@@ -22835,19 +22835,19 @@
         <v>2022</v>
       </c>
       <c r="F79">
-        <v>0.18507474280047922</v>
+        <v>0.31243538817501959</v>
       </c>
       <c r="G79">
-        <v>0.59739999999999993</v>
+        <v>0.61799999999999999</v>
       </c>
       <c r="H79">
-        <v>1265</v>
+        <v>1100</v>
       </c>
       <c r="I79">
-        <v>36.300000000000004</v>
+        <v>33</v>
       </c>
       <c r="J79">
-        <v>3.4649999999999999</v>
+        <v>3.1500000000000004</v>
       </c>
       <c r="K79">
         <v>50</v>
@@ -22888,10 +22888,10 @@
         <v>2022</v>
       </c>
       <c r="F80">
-        <v>0.43468212618270452</v>
+        <v>0.37112356319464518</v>
       </c>
       <c r="G80">
-        <v>0.61799999999999988</v>
+        <v>0.61799999999999999</v>
       </c>
       <c r="H80">
         <v>1100</v>
@@ -22941,19 +22941,19 @@
         <v>2022</v>
       </c>
       <c r="F81">
-        <v>0.3567559186877659</v>
+        <v>0.23864901045324952</v>
       </c>
       <c r="G81">
-        <v>0.61799999999999999</v>
+        <v>0.59739999999999993</v>
       </c>
       <c r="H81">
-        <v>1100</v>
+        <v>1265</v>
       </c>
       <c r="I81">
-        <v>33</v>
+        <v>36.300000000000004</v>
       </c>
       <c r="J81">
-        <v>3.1500000000000004</v>
+        <v>3.4650000000000003</v>
       </c>
       <c r="K81">
         <v>50</v>
@@ -22994,7 +22994,7 @@
         <v>2022</v>
       </c>
       <c r="F82">
-        <v>0.19627663512787666</v>
+        <v>0.26543614427963469</v>
       </c>
       <c r="G82">
         <v>0.59739999999999993</v>
@@ -23006,7 +23006,7 @@
         <v>36.300000000000004</v>
       </c>
       <c r="J82">
-        <v>3.4649999999999999</v>
+        <v>3.4650000000000003</v>
       </c>
       <c r="K82">
         <v>50</v>
@@ -23041,7 +23041,7 @@
         <v>49</v>
       </c>
       <c r="D83" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="E83">
         <v>2006</v>
@@ -23094,7 +23094,7 @@
         <v>49</v>
       </c>
       <c r="D84" t="s">
-        <v>77</v>
+        <v>60</v>
       </c>
       <c r="E84">
         <v>2012</v>
@@ -23147,7 +23147,7 @@
         <v>49</v>
       </c>
       <c r="D85" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="E85">
         <v>1993</v>
@@ -23200,7 +23200,7 @@
         <v>49</v>
       </c>
       <c r="D86" t="s">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="E86">
         <v>2011</v>
@@ -23253,7 +23253,7 @@
         <v>49</v>
       </c>
       <c r="D87" t="s">
-        <v>56</v>
+        <v>84</v>
       </c>
       <c r="E87">
         <v>2005</v>
@@ -23306,7 +23306,7 @@
         <v>49</v>
       </c>
       <c r="D88" t="s">
-        <v>56</v>
+        <v>84</v>
       </c>
       <c r="E88">
         <v>2006</v>
@@ -23359,7 +23359,7 @@
         <v>49</v>
       </c>
       <c r="D89" t="s">
-        <v>56</v>
+        <v>84</v>
       </c>
       <c r="E89">
         <v>2006</v>
@@ -23465,7 +23465,7 @@
         <v>49</v>
       </c>
       <c r="D91" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="E91">
         <v>2003</v>
@@ -23624,7 +23624,7 @@
         <v>49</v>
       </c>
       <c r="D94" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="E94">
         <v>2004</v>
@@ -23677,7 +23677,7 @@
         <v>49</v>
       </c>
       <c r="D95" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="E95">
         <v>2005</v>
@@ -23730,7 +23730,7 @@
         <v>49</v>
       </c>
       <c r="D96" t="s">
-        <v>59</v>
+        <v>72</v>
       </c>
       <c r="E96">
         <v>2005</v>
@@ -23783,7 +23783,7 @@
         <v>49</v>
       </c>
       <c r="D97" t="s">
-        <v>59</v>
+        <v>72</v>
       </c>
       <c r="E97">
         <v>2005</v>
@@ -23836,7 +23836,7 @@
         <v>49</v>
       </c>
       <c r="D98" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="E98">
         <v>2004</v>
@@ -23889,7 +23889,7 @@
         <v>49</v>
       </c>
       <c r="D99" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="E99">
         <v>2004</v>
@@ -23942,7 +23942,7 @@
         <v>49</v>
       </c>
       <c r="D100" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="E100">
         <v>2004</v>
@@ -23995,7 +23995,7 @@
         <v>49</v>
       </c>
       <c r="D101" t="s">
-        <v>74</v>
+        <v>63</v>
       </c>
       <c r="E101">
         <v>2008</v>
@@ -24048,7 +24048,7 @@
         <v>49</v>
       </c>
       <c r="D102" t="s">
-        <v>74</v>
+        <v>63</v>
       </c>
       <c r="E102">
         <v>2008</v>
@@ -24101,7 +24101,7 @@
         <v>49</v>
       </c>
       <c r="D103" t="s">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="E103">
         <v>2002</v>
@@ -24154,7 +24154,7 @@
         <v>49</v>
       </c>
       <c r="D104" t="s">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="E104">
         <v>2002</v>
@@ -24207,7 +24207,7 @@
         <v>49</v>
       </c>
       <c r="D105" t="s">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="E105">
         <v>2003</v>
@@ -24260,7 +24260,7 @@
         <v>49</v>
       </c>
       <c r="D106" t="s">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="E106">
         <v>2003</v>
@@ -24313,7 +24313,7 @@
         <v>49</v>
       </c>
       <c r="D107" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="E107">
         <v>2000</v>
@@ -24366,7 +24366,7 @@
         <v>49</v>
       </c>
       <c r="D108" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="E108">
         <v>2000</v>
@@ -24419,7 +24419,7 @@
         <v>49</v>
       </c>
       <c r="D109" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="E109">
         <v>2007</v>
@@ -24472,7 +24472,7 @@
         <v>49</v>
       </c>
       <c r="D110" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="E110">
         <v>2023</v>
@@ -24525,7 +24525,7 @@
         <v>49</v>
       </c>
       <c r="D111" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="E111">
         <v>2001</v>
@@ -24631,7 +24631,7 @@
         <v>49</v>
       </c>
       <c r="D113" t="s">
-        <v>76</v>
+        <v>59</v>
       </c>
       <c r="E113">
         <v>2010</v>
@@ -24684,7 +24684,7 @@
         <v>49</v>
       </c>
       <c r="D114" t="s">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="E114">
         <v>2005</v>
@@ -24737,7 +24737,7 @@
         <v>49</v>
       </c>
       <c r="D115" t="s">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="E115">
         <v>2009</v>
@@ -24790,7 +24790,7 @@
         <v>49</v>
       </c>
       <c r="D116" t="s">
-        <v>62</v>
+        <v>87</v>
       </c>
       <c r="E116">
         <v>1997</v>
@@ -24843,7 +24843,7 @@
         <v>49</v>
       </c>
       <c r="D117" t="s">
-        <v>62</v>
+        <v>87</v>
       </c>
       <c r="E117">
         <v>1997</v>
@@ -24896,7 +24896,7 @@
         <v>49</v>
       </c>
       <c r="D118" t="s">
-        <v>62</v>
+        <v>87</v>
       </c>
       <c r="E118">
         <v>1998</v>
@@ -24949,7 +24949,7 @@
         <v>49</v>
       </c>
       <c r="D119" t="s">
-        <v>62</v>
+        <v>87</v>
       </c>
       <c r="E119">
         <v>1999</v>
@@ -25055,7 +25055,7 @@
         <v>49</v>
       </c>
       <c r="D121" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E121">
         <v>2010</v>
@@ -25108,7 +25108,7 @@
         <v>49</v>
       </c>
       <c r="D122" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="E122">
         <v>2003</v>
@@ -25161,7 +25161,7 @@
         <v>49</v>
       </c>
       <c r="D123" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="E123">
         <v>2003</v>
@@ -25214,7 +25214,7 @@
         <v>49</v>
       </c>
       <c r="D124" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="E124">
         <v>2006</v>
@@ -25373,7 +25373,7 @@
         <v>49</v>
       </c>
       <c r="D127" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="E127">
         <v>2002</v>
@@ -25426,7 +25426,7 @@
         <v>49</v>
       </c>
       <c r="D128" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="E128">
         <v>2002</v>
@@ -25479,7 +25479,7 @@
         <v>49</v>
       </c>
       <c r="D129" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E129">
         <v>2010</v>
@@ -25532,7 +25532,7 @@
         <v>49</v>
       </c>
       <c r="D130" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E130">
         <v>2010</v>
@@ -25585,7 +25585,7 @@
         <v>49</v>
       </c>
       <c r="D131" t="s">
-        <v>81</v>
+        <v>53</v>
       </c>
       <c r="E131">
         <v>2008</v>
@@ -25638,7 +25638,7 @@
         <v>49</v>
       </c>
       <c r="D132" t="s">
-        <v>81</v>
+        <v>53</v>
       </c>
       <c r="E132">
         <v>2008</v>
@@ -25691,7 +25691,7 @@
         <v>49</v>
       </c>
       <c r="D133" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="E133">
         <v>2018</v>
@@ -25744,7 +25744,7 @@
         <v>49</v>
       </c>
       <c r="D134" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="E134">
         <v>2006</v>
@@ -25797,7 +25797,7 @@
         <v>49</v>
       </c>
       <c r="D135" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="E135">
         <v>2007</v>
@@ -25956,7 +25956,7 @@
         <v>49</v>
       </c>
       <c r="D138" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E138">
         <v>2010</v>
@@ -26009,7 +26009,7 @@
         <v>49</v>
       </c>
       <c r="D139" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E139">
         <v>2010</v>
@@ -26062,7 +26062,7 @@
         <v>49</v>
       </c>
       <c r="D140" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="E140">
         <v>2004</v>
@@ -26115,7 +26115,7 @@
         <v>49</v>
       </c>
       <c r="D141" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="E141">
         <v>2004</v>
@@ -26168,7 +26168,7 @@
         <v>49</v>
       </c>
       <c r="D142" t="s">
-        <v>79</v>
+        <v>61</v>
       </c>
       <c r="E142">
         <v>2008</v>
@@ -26221,7 +26221,7 @@
         <v>49</v>
       </c>
       <c r="D143" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="E143">
         <v>2007</v>
@@ -26274,7 +26274,7 @@
         <v>49</v>
       </c>
       <c r="D144" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="E144">
         <v>2007</v>
@@ -26327,7 +26327,7 @@
         <v>49</v>
       </c>
       <c r="D145" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E145">
         <v>2005</v>
@@ -26380,7 +26380,7 @@
         <v>49</v>
       </c>
       <c r="D146" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E146">
         <v>2005</v>
@@ -26433,7 +26433,7 @@
         <v>49</v>
       </c>
       <c r="D147" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E147">
         <v>2015</v>
@@ -26486,7 +26486,7 @@
         <v>49</v>
       </c>
       <c r="D148" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E148">
         <v>2004</v>
@@ -26539,7 +26539,7 @@
         <v>49</v>
       </c>
       <c r="D149" t="s">
-        <v>64</v>
+        <v>50</v>
       </c>
       <c r="E149">
         <v>2006</v>
@@ -26592,7 +26592,7 @@
         <v>49</v>
       </c>
       <c r="D150" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="E150">
         <v>2011</v>
@@ -26645,7 +26645,7 @@
         <v>49</v>
       </c>
       <c r="D151" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E151">
         <v>2004</v>
@@ -26698,7 +26698,7 @@
         <v>49</v>
       </c>
       <c r="D152" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E152">
         <v>2005</v>
@@ -26751,7 +26751,7 @@
         <v>49</v>
       </c>
       <c r="D153" t="s">
-        <v>51</v>
+        <v>83</v>
       </c>
       <c r="E153">
         <v>2006</v>
@@ -26804,7 +26804,7 @@
         <v>49</v>
       </c>
       <c r="D154" t="s">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="E154">
         <v>2008</v>
@@ -26857,7 +26857,7 @@
         <v>49</v>
       </c>
       <c r="D155" t="s">
-        <v>80</v>
+        <v>52</v>
       </c>
       <c r="E155">
         <v>2007</v>
@@ -26963,7 +26963,7 @@
         <v>49</v>
       </c>
       <c r="D157" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="E157">
         <v>2023</v>
@@ -27016,7 +27016,7 @@
         <v>49</v>
       </c>
       <c r="D158" t="s">
-        <v>55</v>
+        <v>86</v>
       </c>
       <c r="E158">
         <v>2026</v>
@@ -27069,7 +27069,7 @@
         <v>49</v>
       </c>
       <c r="D159" t="s">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="E159">
         <v>2022</v>
@@ -27122,7 +27122,7 @@
         <v>49</v>
       </c>
       <c r="D160" t="s">
-        <v>50</v>
+        <v>81</v>
       </c>
       <c r="E160">
         <v>2003</v>
@@ -27175,7 +27175,7 @@
         <v>49</v>
       </c>
       <c r="D161" t="s">
-        <v>50</v>
+        <v>81</v>
       </c>
       <c r="E161">
         <v>2003</v>
@@ -27228,7 +27228,7 @@
         <v>49</v>
       </c>
       <c r="D162" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="E162">
         <v>2003</v>
@@ -27281,7 +27281,7 @@
         <v>49</v>
       </c>
       <c r="D163" t="s">
-        <v>57</v>
+        <v>70</v>
       </c>
       <c r="E163">
         <v>2008</v>
@@ -27334,7 +27334,7 @@
         <v>49</v>
       </c>
       <c r="D164" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E164">
         <v>1999</v>
@@ -27387,7 +27387,7 @@
         <v>49</v>
       </c>
       <c r="D165" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E165">
         <v>1999</v>
@@ -27440,7 +27440,7 @@
         <v>49</v>
       </c>
       <c r="D166" t="s">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="E166">
         <v>1997</v>
@@ -27546,7 +27546,7 @@
         <v>49</v>
       </c>
       <c r="D168" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="E168">
         <v>2001</v>
@@ -27599,7 +27599,7 @@
         <v>49</v>
       </c>
       <c r="D169" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="E169">
         <v>2006</v>
@@ -27705,7 +27705,7 @@
         <v>49</v>
       </c>
       <c r="D171" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="E171">
         <v>2007</v>
@@ -28288,7 +28288,7 @@
         <v>49</v>
       </c>
       <c r="D182" t="s">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="E182">
         <v>2015</v>
@@ -29083,7 +29083,7 @@
         <v>49</v>
       </c>
       <c r="D197" t="s">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="E197">
         <v>2004</v>
@@ -29136,7 +29136,7 @@
         <v>49</v>
       </c>
       <c r="D198" t="s">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="E198">
         <v>2008</v>
@@ -29348,7 +29348,7 @@
         <v>49</v>
       </c>
       <c r="D202" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E202">
         <v>2005</v>
@@ -29401,7 +29401,7 @@
         <v>49</v>
       </c>
       <c r="D203" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E203">
         <v>2015</v>
@@ -30090,7 +30090,7 @@
         <v>49</v>
       </c>
       <c r="D216" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E216">
         <v>2022</v>
@@ -30302,7 +30302,7 @@
         <v>49</v>
       </c>
       <c r="D220" t="s">
-        <v>55</v>
+        <v>86</v>
       </c>
       <c r="E220">
         <v>2009</v>
@@ -30991,7 +30991,7 @@
         <v>49</v>
       </c>
       <c r="D233" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="E233">
         <v>1994</v>
@@ -31150,7 +31150,7 @@
         <v>49</v>
       </c>
       <c r="D236" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E236">
         <v>1990</v>
@@ -31203,7 +31203,7 @@
         <v>49</v>
       </c>
       <c r="D237" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E237">
         <v>2022</v>
@@ -31362,7 +31362,7 @@
         <v>49</v>
       </c>
       <c r="D240" t="s">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="E240">
         <v>2006</v>
@@ -31415,7 +31415,7 @@
         <v>49</v>
       </c>
       <c r="D241" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E241">
         <v>2024</v>
@@ -31468,7 +31468,7 @@
         <v>49</v>
       </c>
       <c r="D242" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E242">
         <v>2023</v>
@@ -31521,7 +31521,7 @@
         <v>49</v>
       </c>
       <c r="D243" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E243">
         <v>2023</v>
@@ -31574,7 +31574,7 @@
         <v>49</v>
       </c>
       <c r="D244" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="E244">
         <v>1997</v>
@@ -32051,7 +32051,7 @@
         <v>49</v>
       </c>
       <c r="D253" t="s">
-        <v>74</v>
+        <v>63</v>
       </c>
       <c r="E253">
         <v>2008</v>
@@ -32316,7 +32316,7 @@
         <v>49</v>
       </c>
       <c r="D258" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E258">
         <v>2015</v>
@@ -32422,7 +32422,7 @@
         <v>49</v>
       </c>
       <c r="D260" t="s">
-        <v>57</v>
+        <v>70</v>
       </c>
       <c r="E260">
         <v>2004</v>
@@ -32687,7 +32687,7 @@
         <v>49</v>
       </c>
       <c r="D265" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="E265">
         <v>2024</v>
@@ -32793,7 +32793,7 @@
         <v>49</v>
       </c>
       <c r="D267" t="s">
-        <v>64</v>
+        <v>50</v>
       </c>
       <c r="E267">
         <v>2023</v>
@@ -33005,7 +33005,7 @@
         <v>49</v>
       </c>
       <c r="D271" t="s">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="E271">
         <v>1975</v>
@@ -33058,7 +33058,7 @@
         <v>49</v>
       </c>
       <c r="D272" t="s">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="E272">
         <v>1975</v>
@@ -33111,7 +33111,7 @@
         <v>49</v>
       </c>
       <c r="D273" t="s">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="E273">
         <v>1975</v>
@@ -33164,7 +33164,7 @@
         <v>49</v>
       </c>
       <c r="D274" t="s">
-        <v>59</v>
+        <v>72</v>
       </c>
       <c r="E274">
         <v>2015</v>
@@ -33217,7 +33217,7 @@
         <v>49</v>
       </c>
       <c r="D275" t="s">
-        <v>56</v>
+        <v>84</v>
       </c>
       <c r="E275">
         <v>1967</v>
@@ -33270,7 +33270,7 @@
         <v>49</v>
       </c>
       <c r="D276" t="s">
-        <v>56</v>
+        <v>84</v>
       </c>
       <c r="E276">
         <v>1971</v>
@@ -33323,7 +33323,7 @@
         <v>49</v>
       </c>
       <c r="D277" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="E277">
         <v>1970</v>
@@ -33376,7 +33376,7 @@
         <v>49</v>
       </c>
       <c r="D278" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E278">
         <v>1978</v>
@@ -33429,7 +33429,7 @@
         <v>49</v>
       </c>
       <c r="D279" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E279">
         <v>1981</v>
@@ -33482,7 +33482,7 @@
         <v>49</v>
       </c>
       <c r="D280" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E280">
         <v>1987</v>
@@ -33906,7 +33906,7 @@
         <v>293</v>
       </c>
       <c r="D288" t="s">
-        <v>62</v>
+        <v>87</v>
       </c>
       <c r="E288">
         <v>1991</v>
@@ -33959,7 +33959,7 @@
         <v>293</v>
       </c>
       <c r="D289" t="s">
-        <v>62</v>
+        <v>87</v>
       </c>
       <c r="E289">
         <v>1991</v>
@@ -35019,25 +35019,25 @@
         <v>308</v>
       </c>
       <c r="D309" t="s">
-        <v>151</v>
+        <v>99</v>
       </c>
       <c r="E309">
         <v>2022</v>
       </c>
       <c r="F309">
-        <v>4.5464982592616207E-2</v>
+        <v>0.29181095970158766</v>
       </c>
       <c r="G309">
         <v>1</v>
       </c>
       <c r="H309">
-        <v>3712.5000000000005</v>
+        <v>3162.5000000000005</v>
       </c>
       <c r="I309">
-        <v>71.5</v>
+        <v>60.500000000000014</v>
       </c>
       <c r="J309">
-        <v>2.52</v>
+        <v>2.3100000000000005</v>
       </c>
       <c r="K309">
         <v>100</v>
@@ -35078,7 +35078,7 @@
         <v>2022</v>
       </c>
       <c r="F310">
-        <v>0.35629700644009438</v>
+        <v>0.54140443556717466</v>
       </c>
       <c r="G310">
         <v>1</v>
@@ -35087,7 +35087,7 @@
         <v>2750</v>
       </c>
       <c r="I310">
-        <v>55</v>
+        <v>55.000000000000007</v>
       </c>
       <c r="J310">
         <v>2.1</v>
@@ -35125,13 +35125,13 @@
         <v>308</v>
       </c>
       <c r="D311" t="s">
-        <v>53</v>
+        <v>310</v>
       </c>
       <c r="E311">
         <v>2022</v>
       </c>
       <c r="F311">
-        <v>0.23196419690110309</v>
+        <v>0.10670353057450742</v>
       </c>
       <c r="G311">
         <v>1</v>
@@ -35178,13 +35178,13 @@
         <v>308</v>
       </c>
       <c r="D312" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="E312">
         <v>2022</v>
       </c>
       <c r="F312">
-        <v>4.1753555442198553E-2</v>
+        <v>4.3145340623605172E-2</v>
       </c>
       <c r="G312">
         <v>1</v>
@@ -35231,13 +35231,13 @@
         <v>308</v>
       </c>
       <c r="D313" t="s">
-        <v>311</v>
+        <v>20</v>
       </c>
       <c r="E313">
         <v>2022</v>
       </c>
       <c r="F313">
-        <v>0.13036387865841995</v>
+        <v>0.11134281451252948</v>
       </c>
       <c r="G313">
         <v>1</v>
@@ -35284,25 +35284,25 @@
         <v>308</v>
       </c>
       <c r="D314" t="s">
-        <v>193</v>
+        <v>312</v>
       </c>
       <c r="E314">
         <v>2022</v>
       </c>
       <c r="F314">
-        <v>0.61052976624370348</v>
+        <v>0.10067246145507874</v>
       </c>
       <c r="G314">
         <v>1</v>
       </c>
       <c r="H314">
-        <v>2750</v>
+        <v>3162.5000000000005</v>
       </c>
       <c r="I314">
-        <v>55.000000000000007</v>
+        <v>60.500000000000014</v>
       </c>
       <c r="J314">
-        <v>2.1</v>
+        <v>2.3100000000000005</v>
       </c>
       <c r="K314">
         <v>100</v>
@@ -35337,13 +35337,13 @@
         <v>308</v>
       </c>
       <c r="D315" t="s">
-        <v>291</v>
+        <v>313</v>
       </c>
       <c r="E315">
         <v>2022</v>
       </c>
       <c r="F315">
-        <v>0.13082780705222213</v>
+        <v>5.8918906012880183E-2</v>
       </c>
       <c r="G315">
         <v>1</v>
@@ -35352,7 +35352,7 @@
         <v>3162.5000000000005</v>
       </c>
       <c r="I315">
-        <v>60.500000000000014</v>
+        <v>60.500000000000021</v>
       </c>
       <c r="J315">
         <v>2.3100000000000005</v>
@@ -35390,25 +35390,25 @@
         <v>308</v>
       </c>
       <c r="D316" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="E316">
         <v>2022</v>
       </c>
       <c r="F316">
-        <v>0.57944656385895543</v>
+        <v>5.1032123318242681E-2</v>
       </c>
       <c r="G316">
         <v>1</v>
       </c>
       <c r="H316">
-        <v>2750</v>
+        <v>3162.5000000000005</v>
       </c>
       <c r="I316">
-        <v>55.000000000000007</v>
+        <v>60.500000000000021</v>
       </c>
       <c r="J316">
-        <v>2.1</v>
+        <v>2.3100000000000005</v>
       </c>
       <c r="K316">
         <v>100</v>
@@ -35443,25 +35443,25 @@
         <v>308</v>
       </c>
       <c r="D317" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="E317">
         <v>2022</v>
       </c>
       <c r="F317">
-        <v>1.0883760118599757</v>
+        <v>0.20320063648536632</v>
       </c>
       <c r="G317">
         <v>1</v>
       </c>
       <c r="H317">
-        <v>2750</v>
+        <v>3162.5000000000005</v>
       </c>
       <c r="I317">
-        <v>55.000000000000007</v>
+        <v>60.500000000000014</v>
       </c>
       <c r="J317">
-        <v>2.1</v>
+        <v>2.3100000000000005</v>
       </c>
       <c r="K317">
         <v>100</v>
@@ -35496,25 +35496,25 @@
         <v>308</v>
       </c>
       <c r="D318" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="E318">
         <v>2022</v>
       </c>
       <c r="F318">
-        <v>6.9589259070330922E-2</v>
+        <v>1.0883760118599757</v>
       </c>
       <c r="G318">
         <v>1</v>
       </c>
       <c r="H318">
-        <v>3162.5000000000005</v>
+        <v>2750</v>
       </c>
       <c r="I318">
-        <v>60.500000000000007</v>
+        <v>55.000000000000007</v>
       </c>
       <c r="J318">
-        <v>2.3100000000000005</v>
+        <v>2.1</v>
       </c>
       <c r="K318">
         <v>100</v>
@@ -35549,25 +35549,25 @@
         <v>308</v>
       </c>
       <c r="D319" t="s">
-        <v>315</v>
+        <v>151</v>
       </c>
       <c r="E319">
         <v>2022</v>
       </c>
       <c r="F319">
-        <v>0.15541601192373908</v>
+        <v>4.5464982592616207E-2</v>
       </c>
       <c r="G319">
         <v>1</v>
       </c>
       <c r="H319">
-        <v>3162.5000000000005</v>
+        <v>3712.5000000000005</v>
       </c>
       <c r="I319">
-        <v>60.500000000000014</v>
+        <v>71.5</v>
       </c>
       <c r="J319">
-        <v>2.3100000000000005</v>
+        <v>2.52</v>
       </c>
       <c r="K319">
         <v>100</v>
@@ -35602,25 +35602,25 @@
         <v>308</v>
       </c>
       <c r="D320" t="s">
-        <v>15</v>
+        <v>317</v>
       </c>
       <c r="E320">
         <v>2022</v>
       </c>
       <c r="F320">
-        <v>0.11134281451252948</v>
+        <v>4.4073197411209589E-2</v>
       </c>
       <c r="G320">
         <v>1</v>
       </c>
       <c r="H320">
-        <v>3162.5000000000005</v>
+        <v>3712.5000000000005</v>
       </c>
       <c r="I320">
-        <v>60.500000000000014</v>
+        <v>71.5</v>
       </c>
       <c r="J320">
-        <v>2.3100000000000005</v>
+        <v>2.52</v>
       </c>
       <c r="K320">
         <v>100</v>
@@ -35655,13 +35655,13 @@
         <v>308</v>
       </c>
       <c r="D321" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="E321">
         <v>2022</v>
       </c>
       <c r="F321">
-        <v>0.1577356538927501</v>
+        <v>6.9589259070330922E-2</v>
       </c>
       <c r="G321">
         <v>1</v>
@@ -35670,7 +35670,7 @@
         <v>3162.5000000000005</v>
       </c>
       <c r="I321">
-        <v>60.500000000000014</v>
+        <v>60.500000000000007</v>
       </c>
       <c r="J321">
         <v>2.3100000000000005</v>
@@ -35708,25 +35708,25 @@
         <v>308</v>
       </c>
       <c r="D322" t="s">
-        <v>99</v>
+        <v>71</v>
       </c>
       <c r="E322">
         <v>2022</v>
       </c>
       <c r="F322">
-        <v>0.29181095970158766</v>
+        <v>0.50939337639482241</v>
       </c>
       <c r="G322">
         <v>1</v>
       </c>
       <c r="H322">
-        <v>3162.5000000000005</v>
+        <v>2750</v>
       </c>
       <c r="I322">
-        <v>60.500000000000014</v>
+        <v>55.000000000000007</v>
       </c>
       <c r="J322">
-        <v>2.3100000000000005</v>
+        <v>2.1</v>
       </c>
       <c r="K322">
         <v>100</v>
@@ -35761,13 +35761,13 @@
         <v>308</v>
       </c>
       <c r="D323" t="s">
-        <v>317</v>
+        <v>291</v>
       </c>
       <c r="E323">
         <v>2022</v>
       </c>
       <c r="F323">
-        <v>6.3558189950902247E-2</v>
+        <v>0.13082780705222213</v>
       </c>
       <c r="G323">
         <v>1</v>
@@ -35814,25 +35814,25 @@
         <v>308</v>
       </c>
       <c r="D324" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="E324">
         <v>2022</v>
       </c>
       <c r="F324">
-        <v>4.3145340623605172E-2</v>
+        <v>0.35629700644009438</v>
       </c>
       <c r="G324">
         <v>1</v>
       </c>
       <c r="H324">
-        <v>3712.5000000000005</v>
+        <v>2750</v>
       </c>
       <c r="I324">
-        <v>71.5</v>
+        <v>55</v>
       </c>
       <c r="J324">
-        <v>2.52</v>
+        <v>2.1</v>
       </c>
       <c r="K324">
         <v>100</v>
@@ -35867,25 +35867,25 @@
         <v>308</v>
       </c>
       <c r="D325" t="s">
-        <v>319</v>
+        <v>14</v>
       </c>
       <c r="E325">
         <v>2022</v>
       </c>
       <c r="F325">
-        <v>4.4073197411209589E-2</v>
+        <v>8.7682466428616976E-2</v>
       </c>
       <c r="G325">
         <v>1</v>
       </c>
       <c r="H325">
-        <v>3712.5000000000005</v>
+        <v>3162.5000000000005</v>
       </c>
       <c r="I325">
-        <v>71.5</v>
+        <v>60.500000000000007</v>
       </c>
       <c r="J325">
-        <v>2.52</v>
+        <v>2.3100000000000005</v>
       </c>
       <c r="K325">
         <v>100</v>
@@ -35926,19 +35926,19 @@
         <v>2022</v>
       </c>
       <c r="F326">
-        <v>0.54140443556717466</v>
+        <v>0.1577356538927501</v>
       </c>
       <c r="G326">
         <v>1</v>
       </c>
       <c r="H326">
-        <v>2750</v>
+        <v>3162.5000000000005</v>
       </c>
       <c r="I326">
-        <v>55.000000000000007</v>
+        <v>60.500000000000014</v>
       </c>
       <c r="J326">
-        <v>2.1</v>
+        <v>2.3100000000000005</v>
       </c>
       <c r="K326">
         <v>100</v>
@@ -35979,7 +35979,7 @@
         <v>2022</v>
       </c>
       <c r="F327">
-        <v>5.8918906012880183E-2</v>
+        <v>0.15541601192373908</v>
       </c>
       <c r="G327">
         <v>1</v>
@@ -35988,7 +35988,7 @@
         <v>3162.5000000000005</v>
       </c>
       <c r="I327">
-        <v>60.500000000000021</v>
+        <v>60.500000000000014</v>
       </c>
       <c r="J327">
         <v>2.3100000000000005</v>
@@ -36032,19 +36032,19 @@
         <v>2022</v>
       </c>
       <c r="F328">
-        <v>0.10670353057450742</v>
+        <v>4.1753555442198553E-2</v>
       </c>
       <c r="G328">
         <v>1</v>
       </c>
       <c r="H328">
-        <v>3162.5000000000005</v>
+        <v>3712.5000000000005</v>
       </c>
       <c r="I328">
-        <v>60.500000000000014</v>
+        <v>71.5</v>
       </c>
       <c r="J328">
-        <v>2.3100000000000005</v>
+        <v>2.52</v>
       </c>
       <c r="K328">
         <v>100</v>
@@ -36079,25 +36079,25 @@
         <v>308</v>
       </c>
       <c r="D329" t="s">
-        <v>58</v>
+        <v>323</v>
       </c>
       <c r="E329">
         <v>2022</v>
       </c>
       <c r="F329">
-        <v>0.50939337639482241</v>
+        <v>0.13036387865841995</v>
       </c>
       <c r="G329">
         <v>1</v>
       </c>
       <c r="H329">
-        <v>2750</v>
+        <v>3162.5000000000005</v>
       </c>
       <c r="I329">
-        <v>55.000000000000007</v>
+        <v>60.500000000000014</v>
       </c>
       <c r="J329">
-        <v>2.1</v>
+        <v>2.3100000000000005</v>
       </c>
       <c r="K329">
         <v>100</v>
@@ -36132,25 +36132,25 @@
         <v>308</v>
       </c>
       <c r="D330" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="E330">
         <v>2022</v>
       </c>
       <c r="F330">
-        <v>4.4073197411209589E-2</v>
+        <v>0.57944656385895543</v>
       </c>
       <c r="G330">
         <v>1</v>
       </c>
       <c r="H330">
-        <v>3712.5000000000005</v>
+        <v>2750</v>
       </c>
       <c r="I330">
-        <v>71.5</v>
+        <v>55.000000000000007</v>
       </c>
       <c r="J330">
-        <v>2.52</v>
+        <v>2.1</v>
       </c>
       <c r="K330">
         <v>100</v>
@@ -36185,13 +36185,13 @@
         <v>308</v>
       </c>
       <c r="D331" t="s">
-        <v>324</v>
+        <v>55</v>
       </c>
       <c r="E331">
         <v>2022</v>
       </c>
       <c r="F331">
-        <v>0.20320063648536632</v>
+        <v>0.23196419690110309</v>
       </c>
       <c r="G331">
         <v>1</v>
@@ -36238,13 +36238,13 @@
         <v>308</v>
       </c>
       <c r="D332" t="s">
-        <v>325</v>
+        <v>204</v>
       </c>
       <c r="E332">
         <v>2022</v>
       </c>
       <c r="F332">
-        <v>6.0310691194286808E-2</v>
+        <v>7.8403898552572848E-2</v>
       </c>
       <c r="G332">
         <v>1</v>
@@ -36291,13 +36291,13 @@
         <v>308</v>
       </c>
       <c r="D333" t="s">
-        <v>74</v>
+        <v>325</v>
       </c>
       <c r="E333">
         <v>2022</v>
       </c>
       <c r="F333">
-        <v>5.4743550468660328E-2</v>
+        <v>0.19299421182171778</v>
       </c>
       <c r="G333">
         <v>1</v>
@@ -36344,13 +36344,13 @@
         <v>308</v>
       </c>
       <c r="D334" t="s">
-        <v>21</v>
+        <v>326</v>
       </c>
       <c r="E334">
         <v>2022</v>
       </c>
       <c r="F334">
-        <v>8.7682466428616976E-2</v>
+        <v>6.3558189950902247E-2</v>
       </c>
       <c r="G334">
         <v>1</v>
@@ -36359,7 +36359,7 @@
         <v>3162.5000000000005</v>
       </c>
       <c r="I334">
-        <v>60.500000000000007</v>
+        <v>60.500000000000014</v>
       </c>
       <c r="J334">
         <v>2.3100000000000005</v>
@@ -36397,25 +36397,25 @@
         <v>308</v>
       </c>
       <c r="D335" t="s">
-        <v>326</v>
+        <v>193</v>
       </c>
       <c r="E335">
         <v>2022</v>
       </c>
       <c r="F335">
-        <v>5.1032123318242681E-2</v>
+        <v>0.61052976624370348</v>
       </c>
       <c r="G335">
         <v>1</v>
       </c>
       <c r="H335">
-        <v>3162.5000000000005</v>
+        <v>2750</v>
       </c>
       <c r="I335">
-        <v>60.500000000000021</v>
+        <v>55.000000000000007</v>
       </c>
       <c r="J335">
-        <v>2.3100000000000005</v>
+        <v>2.1</v>
       </c>
       <c r="K335">
         <v>100</v>
@@ -36456,19 +36456,19 @@
         <v>2022</v>
       </c>
       <c r="F336">
-        <v>0.10067246145507874</v>
+        <v>4.4073197411209589E-2</v>
       </c>
       <c r="G336">
         <v>1</v>
       </c>
       <c r="H336">
-        <v>3162.5000000000005</v>
+        <v>3712.5000000000005</v>
       </c>
       <c r="I336">
-        <v>60.500000000000014</v>
+        <v>71.5</v>
       </c>
       <c r="J336">
-        <v>2.3100000000000005</v>
+        <v>2.52</v>
       </c>
       <c r="K336">
         <v>100</v>
@@ -36509,19 +36509,19 @@
         <v>2022</v>
       </c>
       <c r="F337">
-        <v>0.56367299846968055</v>
+        <v>6.0310691194286808E-2</v>
       </c>
       <c r="G337">
         <v>1</v>
       </c>
       <c r="H337">
-        <v>2750</v>
+        <v>3162.5000000000005</v>
       </c>
       <c r="I337">
-        <v>55.000000000000007</v>
+        <v>60.500000000000014</v>
       </c>
       <c r="J337">
-        <v>2.1</v>
+        <v>2.3100000000000005</v>
       </c>
       <c r="K337">
         <v>100</v>
@@ -36556,13 +36556,13 @@
         <v>308</v>
       </c>
       <c r="D338" t="s">
-        <v>329</v>
+        <v>239</v>
       </c>
       <c r="E338">
         <v>2022</v>
       </c>
       <c r="F338">
-        <v>0.19299421182171778</v>
+        <v>0.22871669814448767</v>
       </c>
       <c r="G338">
         <v>1</v>
@@ -36609,13 +36609,13 @@
         <v>308</v>
       </c>
       <c r="D339" t="s">
-        <v>204</v>
+        <v>63</v>
       </c>
       <c r="E339">
         <v>2022</v>
       </c>
       <c r="F339">
-        <v>7.8403898552572848E-2</v>
+        <v>5.4743550468660328E-2</v>
       </c>
       <c r="G339">
         <v>1</v>
@@ -36662,25 +36662,25 @@
         <v>308</v>
       </c>
       <c r="D340" t="s">
-        <v>239</v>
+        <v>329</v>
       </c>
       <c r="E340">
         <v>2022</v>
       </c>
       <c r="F340">
-        <v>0.22871669814448767</v>
+        <v>0.56367299846968055</v>
       </c>
       <c r="G340">
         <v>1</v>
       </c>
       <c r="H340">
-        <v>3162.5000000000005</v>
+        <v>2750</v>
       </c>
       <c r="I340">
-        <v>60.500000000000014</v>
+        <v>55.000000000000007</v>
       </c>
       <c r="J340">
-        <v>2.3100000000000005</v>
+        <v>2.1</v>
       </c>
       <c r="K340">
         <v>100</v>
@@ -36768,7 +36768,7 @@
         <v>308</v>
       </c>
       <c r="D342" t="s">
-        <v>319</v>
+        <v>327</v>
       </c>
       <c r="E342">
         <v>1959</v>
@@ -36874,7 +36874,7 @@
         <v>308</v>
       </c>
       <c r="D344" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="E344">
         <v>1973</v>
@@ -36980,7 +36980,7 @@
         <v>308</v>
       </c>
       <c r="D346" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="E346">
         <v>1963</v>
@@ -37033,7 +37033,7 @@
         <v>308</v>
       </c>
       <c r="D347" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="E347">
         <v>2015</v>
@@ -37086,7 +37086,7 @@
         <v>308</v>
       </c>
       <c r="D348" t="s">
-        <v>327</v>
+        <v>312</v>
       </c>
       <c r="E348">
         <v>1931</v>
@@ -37139,7 +37139,7 @@
         <v>308</v>
       </c>
       <c r="D349" t="s">
-        <v>320</v>
+        <v>309</v>
       </c>
       <c r="E349">
         <v>1949</v>
@@ -37192,7 +37192,7 @@
         <v>308</v>
       </c>
       <c r="D350" t="s">
-        <v>309</v>
+        <v>319</v>
       </c>
       <c r="E350">
         <v>1951</v>
@@ -37298,7 +37298,7 @@
         <v>308</v>
       </c>
       <c r="D352" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="E352">
         <v>1958</v>
@@ -37351,7 +37351,7 @@
         <v>308</v>
       </c>
       <c r="D353" t="s">
-        <v>322</v>
+        <v>310</v>
       </c>
       <c r="E353">
         <v>1967</v>
@@ -37404,7 +37404,7 @@
         <v>308</v>
       </c>
       <c r="D354" t="s">
-        <v>324</v>
+        <v>315</v>
       </c>
       <c r="E354">
         <v>1968</v>
@@ -37457,7 +37457,7 @@
         <v>308</v>
       </c>
       <c r="D355" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="E355">
         <v>1929</v>
@@ -37510,7 +37510,7 @@
         <v>308</v>
       </c>
       <c r="D356" t="s">
-        <v>324</v>
+        <v>315</v>
       </c>
       <c r="E356">
         <v>1949</v>
@@ -37616,7 +37616,7 @@
         <v>308</v>
       </c>
       <c r="D358" t="s">
-        <v>74</v>
+        <v>63</v>
       </c>
       <c r="E358">
         <v>1952</v>
@@ -37669,7 +37669,7 @@
         <v>308</v>
       </c>
       <c r="D359" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="E359">
         <v>1913</v>
@@ -37722,7 +37722,7 @@
         <v>308</v>
       </c>
       <c r="D360" t="s">
-        <v>309</v>
+        <v>319</v>
       </c>
       <c r="E360">
         <v>1924</v>
@@ -37828,7 +37828,7 @@
         <v>308</v>
       </c>
       <c r="D362" t="s">
-        <v>309</v>
+        <v>319</v>
       </c>
       <c r="E362">
         <v>1971</v>
@@ -37934,7 +37934,7 @@
         <v>308</v>
       </c>
       <c r="D364" t="s">
-        <v>318</v>
+        <v>311</v>
       </c>
       <c r="E364">
         <v>1927</v>
@@ -37987,7 +37987,7 @@
         <v>308</v>
       </c>
       <c r="D365" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="E365">
         <v>1928</v>
@@ -38093,7 +38093,7 @@
         <v>308</v>
       </c>
       <c r="D367" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="E367">
         <v>1938</v>
@@ -38146,7 +38146,7 @@
         <v>308</v>
       </c>
       <c r="D368" t="s">
-        <v>323</v>
+        <v>317</v>
       </c>
       <c r="E368">
         <v>1920</v>
@@ -38199,7 +38199,7 @@
         <v>308</v>
       </c>
       <c r="D369" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="E369">
         <v>1947</v>
@@ -38252,7 +38252,7 @@
         <v>308</v>
       </c>
       <c r="D370" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="E370">
         <v>1950</v>
@@ -38305,7 +38305,7 @@
         <v>308</v>
       </c>
       <c r="D371" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="E371">
         <v>1954</v>
@@ -38411,7 +38411,7 @@
         <v>308</v>
       </c>
       <c r="D373" t="s">
-        <v>309</v>
+        <v>319</v>
       </c>
       <c r="E373">
         <v>1971</v>
@@ -38464,7 +38464,7 @@
         <v>308</v>
       </c>
       <c r="D374" t="s">
-        <v>327</v>
+        <v>312</v>
       </c>
       <c r="E374">
         <v>1959</v>
@@ -38570,7 +38570,7 @@
         <v>308</v>
       </c>
       <c r="D376" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="E376">
         <v>1955</v>
@@ -38623,7 +38623,7 @@
         <v>308</v>
       </c>
       <c r="D377" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="E377">
         <v>1959</v>
@@ -38676,7 +38676,7 @@
         <v>308</v>
       </c>
       <c r="D378" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="E378">
         <v>1954</v>
@@ -38888,7 +38888,7 @@
         <v>308</v>
       </c>
       <c r="D382" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="E382">
         <v>2022</v>
@@ -39100,7 +39100,7 @@
         <v>308</v>
       </c>
       <c r="D386" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E386">
         <v>2022</v>
@@ -39206,7 +39206,7 @@
         <v>383</v>
       </c>
       <c r="D388" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E388">
         <v>1989</v>
@@ -39259,7 +39259,7 @@
         <v>383</v>
       </c>
       <c r="D389" t="s">
-        <v>311</v>
+        <v>323</v>
       </c>
       <c r="E389">
         <v>1975</v>
@@ -39312,7 +39312,7 @@
         <v>383</v>
       </c>
       <c r="D390" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="E390">
         <v>1966</v>
@@ -39365,7 +39365,7 @@
         <v>383</v>
       </c>
       <c r="D391" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="E391">
         <v>2015</v>
@@ -39418,7 +39418,7 @@
         <v>383</v>
       </c>
       <c r="D392" t="s">
-        <v>312</v>
+        <v>324</v>
       </c>
       <c r="E392">
         <v>2015</v>
@@ -39471,7 +39471,7 @@
         <v>383</v>
       </c>
       <c r="D393" t="s">
-        <v>312</v>
+        <v>324</v>
       </c>
       <c r="E393">
         <v>1982</v>
@@ -39524,7 +39524,7 @@
         <v>383</v>
       </c>
       <c r="D394" t="s">
-        <v>309</v>
+        <v>319</v>
       </c>
       <c r="E394">
         <v>2015</v>
@@ -39577,7 +39577,7 @@
         <v>383</v>
       </c>
       <c r="D395" t="s">
-        <v>317</v>
+        <v>326</v>
       </c>
       <c r="E395">
         <v>2015</v>
@@ -39630,7 +39630,7 @@
         <v>383</v>
       </c>
       <c r="D396" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E396">
         <v>1961</v>
@@ -39683,7 +39683,7 @@
         <v>383</v>
       </c>
       <c r="D397" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="E397">
         <v>2005</v>
@@ -39736,7 +39736,7 @@
         <v>383</v>
       </c>
       <c r="D398" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="E398">
         <v>1991</v>
@@ -39895,7 +39895,7 @@
         <v>383</v>
       </c>
       <c r="D401" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="E401">
         <v>1971</v>
@@ -39948,7 +39948,7 @@
         <v>383</v>
       </c>
       <c r="D402" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="E402">
         <v>1973</v>
@@ -40107,7 +40107,7 @@
         <v>383</v>
       </c>
       <c r="D405" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E405">
         <v>1978</v>
@@ -40160,7 +40160,7 @@
         <v>383</v>
       </c>
       <c r="D406" t="s">
-        <v>320</v>
+        <v>309</v>
       </c>
       <c r="E406">
         <v>1923</v>
@@ -40213,7 +40213,7 @@
         <v>308</v>
       </c>
       <c r="D407" t="s">
-        <v>321</v>
+        <v>313</v>
       </c>
       <c r="E407">
         <v>1959</v>
@@ -40319,7 +40319,7 @@
         <v>308</v>
       </c>
       <c r="D409" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="E409">
         <v>1949</v>
@@ -40372,7 +40372,7 @@
         <v>308</v>
       </c>
       <c r="D410" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="E410">
         <v>1953</v>
@@ -40478,7 +40478,7 @@
         <v>308</v>
       </c>
       <c r="D412" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="E412">
         <v>1960</v>
@@ -40531,7 +40531,7 @@
         <v>308</v>
       </c>
       <c r="D413" t="s">
-        <v>310</v>
+        <v>322</v>
       </c>
       <c r="E413">
         <v>1962</v>
@@ -40584,7 +40584,7 @@
         <v>308</v>
       </c>
       <c r="D414" t="s">
-        <v>320</v>
+        <v>309</v>
       </c>
       <c r="E414">
         <v>2015</v>
@@ -40637,7 +40637,7 @@
         <v>308</v>
       </c>
       <c r="D415" t="s">
-        <v>324</v>
+        <v>315</v>
       </c>
       <c r="E415">
         <v>1927</v>
@@ -40690,7 +40690,7 @@
         <v>308</v>
       </c>
       <c r="D416" t="s">
-        <v>326</v>
+        <v>314</v>
       </c>
       <c r="E416">
         <v>1954</v>
@@ -40796,7 +40796,7 @@
         <v>308</v>
       </c>
       <c r="D418" t="s">
-        <v>320</v>
+        <v>309</v>
       </c>
       <c r="E418">
         <v>1956</v>
@@ -40849,7 +40849,7 @@
         <v>308</v>
       </c>
       <c r="D419" t="s">
-        <v>309</v>
+        <v>319</v>
       </c>
       <c r="E419">
         <v>1956</v>
@@ -40955,7 +40955,7 @@
         <v>308</v>
       </c>
       <c r="D421" t="s">
-        <v>320</v>
+        <v>309</v>
       </c>
       <c r="E421">
         <v>1960</v>
@@ -41061,7 +41061,7 @@
         <v>308</v>
       </c>
       <c r="D423" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="E423">
         <v>2015</v>
@@ -41167,7 +41167,7 @@
         <v>308</v>
       </c>
       <c r="D425" t="s">
-        <v>324</v>
+        <v>315</v>
       </c>
       <c r="E425">
         <v>2015</v>
@@ -41220,7 +41220,7 @@
         <v>308</v>
       </c>
       <c r="D426" t="s">
-        <v>312</v>
+        <v>324</v>
       </c>
       <c r="E426">
         <v>2015</v>
@@ -41326,7 +41326,7 @@
         <v>308</v>
       </c>
       <c r="D428" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="E428">
         <v>1955</v>
@@ -41379,7 +41379,7 @@
         <v>308</v>
       </c>
       <c r="D429" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="E429">
         <v>2015</v>
@@ -41485,7 +41485,7 @@
         <v>308</v>
       </c>
       <c r="D431" t="s">
-        <v>318</v>
+        <v>311</v>
       </c>
       <c r="E431">
         <v>1932</v>
@@ -41644,7 +41644,7 @@
         <v>308</v>
       </c>
       <c r="D434" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="E434">
         <v>1924</v>
@@ -41750,7 +41750,7 @@
         <v>308</v>
       </c>
       <c r="D436" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="E436">
         <v>2002</v>
@@ -41856,7 +41856,7 @@
         <v>308</v>
       </c>
       <c r="D438" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="E438">
         <v>1948</v>
@@ -41909,7 +41909,7 @@
         <v>308</v>
       </c>
       <c r="D439" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="E439">
         <v>2015</v>
@@ -41962,7 +41962,7 @@
         <v>308</v>
       </c>
       <c r="D440" t="s">
-        <v>323</v>
+        <v>317</v>
       </c>
       <c r="E440">
         <v>1914</v>
@@ -42068,7 +42068,7 @@
         <v>308</v>
       </c>
       <c r="D442" t="s">
-        <v>74</v>
+        <v>63</v>
       </c>
       <c r="E442">
         <v>1958</v>
@@ -42121,7 +42121,7 @@
         <v>439</v>
       </c>
       <c r="D443" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="E443">
         <v>1992</v>
@@ -42280,7 +42280,7 @@
         <v>439</v>
       </c>
       <c r="D446" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E446">
         <v>1992</v>
@@ -42598,7 +42598,7 @@
         <v>439</v>
       </c>
       <c r="D452" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="E452">
         <v>1985</v>
@@ -42922,7 +42922,7 @@
         <v>2022</v>
       </c>
       <c r="F458">
-        <v>6.6457416582336482</v>
+        <v>6.6039408899415779</v>
       </c>
       <c r="G458">
         <v>1</v>
@@ -43034,7 +43034,7 @@
         <v>2022</v>
       </c>
       <c r="F460">
-        <v>6.6039408899415779</v>
+        <v>6.6457416582336482</v>
       </c>
       <c r="G460">
         <v>1</v>
@@ -44876,7 +44876,7 @@
         <v>455</v>
       </c>
       <c r="D493" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="E493">
         <v>2015</v>
@@ -51156,7 +51156,7 @@
         <v>2022</v>
       </c>
       <c r="F618">
-        <v>0.67351932785461166</v>
+        <v>0.6793056475905862</v>
       </c>
       <c r="G618">
         <v>0.33123000000000002</v>
@@ -51179,7 +51179,7 @@
         <v>2022</v>
       </c>
       <c r="F619">
-        <v>0.69928302455480262</v>
+        <v>0.67351932785461166</v>
       </c>
       <c r="G619">
         <v>0.33123000000000002</v>
@@ -51202,7 +51202,7 @@
         <v>2022</v>
       </c>
       <c r="F620">
-        <v>0.6793056475905862</v>
+        <v>0.69928302455480262</v>
       </c>
       <c r="G620">
         <v>0.33123000000000002</v>
@@ -51449,7 +51449,7 @@
         <v>663</v>
       </c>
       <c r="D631" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="E631">
         <v>2018</v>

--- a/VerveStacks_ITA_grids/vt_vervestacks_ITA_v1.xlsx
+++ b/VerveStacks_ITA_grids/vt_vervestacks_ITA_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B4A9251F-B647-4980-B891-C7EE2AD8AC5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D3F0C473-25ED-43FB-AB82-EBAC97E4941B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{2746CD58-AB47-4095-96F1-7E4D81CAAD97}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{1DDFC537-3BF2-47FF-8258-3FBB00AFD16C}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="2" r:id="rId1"/>
@@ -81,30 +81,30 @@
     <t>bioenergy</t>
   </si>
   <si>
+    <t>e_w58440884-380</t>
+  </si>
+  <si>
+    <t>e_w84696559-380</t>
+  </si>
+  <si>
+    <t>e_w109756016-380</t>
+  </si>
+  <si>
+    <t>e_w81938081-380</t>
+  </si>
+  <si>
+    <t>e_w98902899-380</t>
+  </si>
+  <si>
+    <t>e_w34157795-380</t>
+  </si>
+  <si>
     <t>e_w108020416-380</t>
   </si>
   <si>
-    <t>e_w81938081-380</t>
-  </si>
-  <si>
-    <t>e_w98902899-380</t>
-  </si>
-  <si>
-    <t>e_w58440884-380</t>
-  </si>
-  <si>
-    <t>e_w109756016-380</t>
-  </si>
-  <si>
-    <t>e_w34157795-380</t>
-  </si>
-  <si>
     <t>e_w144005863-380</t>
   </si>
   <si>
-    <t>e_w84696559-380</t>
-  </si>
-  <si>
     <t>ep_bioenergy_G100000200236</t>
   </si>
   <si>
@@ -141,15 +141,15 @@
     <t>coal</t>
   </si>
   <si>
+    <t>e_w303915533-380</t>
+  </si>
+  <si>
+    <t>e_w409439916-380</t>
+  </si>
+  <si>
     <t>e_w82767145-380</t>
   </si>
   <si>
-    <t>e_w409439916-380</t>
-  </si>
-  <si>
-    <t>e_w303915533-380</t>
-  </si>
-  <si>
     <t>e_w418902800-380</t>
   </si>
   <si>
@@ -189,10 +189,103 @@
     <t>gas</t>
   </si>
   <si>
+    <t>e_w105757794-380</t>
+  </si>
+  <si>
+    <t>e_w132450233-380</t>
+  </si>
+  <si>
+    <t>e_w162828577-380</t>
+  </si>
+  <si>
+    <t>e_w98900549-380</t>
+  </si>
+  <si>
+    <t>e_w162960205-380</t>
+  </si>
+  <si>
+    <t>e_w199675964-380</t>
+  </si>
+  <si>
+    <t>e_w158739183-380</t>
+  </si>
+  <si>
+    <t>e_w103974940-380</t>
+  </si>
+  <si>
+    <t>e_w181125039-380</t>
+  </si>
+  <si>
+    <t>e_w133601335-380</t>
+  </si>
+  <si>
+    <t>e_w103381531-380</t>
+  </si>
+  <si>
+    <t>e_w82078641-380</t>
+  </si>
+  <si>
+    <t>e_w61157826-380</t>
+  </si>
+  <si>
+    <t>e_w338753171-380</t>
+  </si>
+  <si>
+    <t>e_w1137611914-380</t>
+  </si>
+  <si>
+    <t>e_w339104227-380</t>
+  </si>
+  <si>
+    <t>e_w414663585-380</t>
+  </si>
+  <si>
+    <t>e_w255011550-380</t>
+  </si>
+  <si>
+    <t>e_w105581403-380</t>
+  </si>
+  <si>
+    <t>e_w60725875-380</t>
+  </si>
+  <si>
+    <t>e_w145665799-380</t>
+  </si>
+  <si>
+    <t>e_w432729521-380</t>
+  </si>
+  <si>
+    <t>e_w172302572-380</t>
+  </si>
+  <si>
+    <t>e_w100407576-380</t>
+  </si>
+  <si>
+    <t>e_w98421779-380</t>
+  </si>
+  <si>
+    <t>e_w419423704-380</t>
+  </si>
+  <si>
+    <t>e_w116797658-380</t>
+  </si>
+  <si>
+    <t>e_w99826025-380</t>
+  </si>
+  <si>
+    <t>e_w416989699-380</t>
+  </si>
+  <si>
     <t>e_w411026199-380</t>
   </si>
   <si>
-    <t>e_w99826025-380</t>
+    <t>e_w149997403-380</t>
+  </si>
+  <si>
+    <t>e_w421827453-380</t>
+  </si>
+  <si>
+    <t>e_w59462715-380</t>
   </si>
   <si>
     <t>e_w103653592-380</t>
@@ -201,108 +294,15 @@
     <t>e_w109993642-380</t>
   </si>
   <si>
-    <t>e_w162960205-380</t>
-  </si>
-  <si>
-    <t>e_w338753171-380</t>
-  </si>
-  <si>
-    <t>e_w158739183-380</t>
-  </si>
-  <si>
-    <t>e_w103974940-380</t>
-  </si>
-  <si>
     <t>e_w82084019-380</t>
   </si>
   <si>
-    <t>e_w432729521-380</t>
-  </si>
-  <si>
-    <t>e_w172302572-380</t>
-  </si>
-  <si>
-    <t>e_w199675964-380</t>
-  </si>
-  <si>
-    <t>e_w414663585-380</t>
-  </si>
-  <si>
-    <t>e_w1137611914-380</t>
-  </si>
-  <si>
-    <t>e_w255011550-380</t>
-  </si>
-  <si>
-    <t>e_w105581403-380</t>
-  </si>
-  <si>
-    <t>e_w181125039-380</t>
-  </si>
-  <si>
-    <t>e_w133601335-380</t>
-  </si>
-  <si>
-    <t>e_w103381531-380</t>
-  </si>
-  <si>
-    <t>e_w339104227-380</t>
-  </si>
-  <si>
-    <t>e_w98421779-380</t>
-  </si>
-  <si>
-    <t>e_w419423704-380</t>
-  </si>
-  <si>
-    <t>e_w116797658-380</t>
-  </si>
-  <si>
-    <t>e_w61157826-380</t>
-  </si>
-  <si>
-    <t>e_w98900549-380</t>
-  </si>
-  <si>
-    <t>e_w162828577-380</t>
-  </si>
-  <si>
-    <t>e_w132450233-380</t>
+    <t>e_w107438024-380</t>
   </si>
   <si>
     <t>e_w110330925-380</t>
   </si>
   <si>
-    <t>e_w105757794-380</t>
-  </si>
-  <si>
-    <t>e_w82078641-380</t>
-  </si>
-  <si>
-    <t>e_w100407576-380</t>
-  </si>
-  <si>
-    <t>e_w149997403-380</t>
-  </si>
-  <si>
-    <t>e_w421827453-380</t>
-  </si>
-  <si>
-    <t>e_w59462715-380</t>
-  </si>
-  <si>
-    <t>e_w145665799-380</t>
-  </si>
-  <si>
-    <t>e_w107438024-380</t>
-  </si>
-  <si>
-    <t>e_w60725875-380</t>
-  </si>
-  <si>
-    <t>e_w416989699-380</t>
-  </si>
-  <si>
     <t>ep_gas_combined_cycle_G100000400339</t>
   </si>
   <si>
@@ -966,69 +966,69 @@
     <t>hydro</t>
   </si>
   <si>
+    <t>e_IT71-400</t>
+  </si>
+  <si>
+    <t>e_IT72-380</t>
+  </si>
+  <si>
+    <t>e_IT72-400</t>
+  </si>
+  <si>
+    <t>e_IT36-380</t>
+  </si>
+  <si>
+    <t>e_w116517585-380</t>
+  </si>
+  <si>
+    <t>e_w82083756-380</t>
+  </si>
+  <si>
+    <t>e_IT53-380</t>
+  </si>
+  <si>
+    <t>e_w1100665914-380</t>
+  </si>
+  <si>
+    <t>e_w64200868-380</t>
+  </si>
+  <si>
+    <t>e_w72466334-380</t>
+  </si>
+  <si>
+    <t>e_w61626687-380</t>
+  </si>
+  <si>
+    <t>e_w114931087-380</t>
+  </si>
+  <si>
+    <t>e_w104359058-380</t>
+  </si>
+  <si>
+    <t>e_IT31-380</t>
+  </si>
+  <si>
+    <t>e_IT93-380</t>
+  </si>
+  <si>
+    <t>e_w491424937-380</t>
+  </si>
+  <si>
+    <t>e_IT71-380</t>
+  </si>
+  <si>
+    <t>e_IT21-380</t>
+  </si>
+  <si>
     <t>e_IT7-380</t>
   </si>
   <si>
-    <t>e_w491424937-380</t>
+    <t>e_IT10-380</t>
   </si>
   <si>
     <t>e_w75602396-380</t>
   </si>
   <si>
-    <t>e_IT72-380</t>
-  </si>
-  <si>
-    <t>e_IT71-380</t>
-  </si>
-  <si>
-    <t>e_w61626687-380</t>
-  </si>
-  <si>
-    <t>e_IT10-380</t>
-  </si>
-  <si>
-    <t>e_w64200868-380</t>
-  </si>
-  <si>
-    <t>e_IT72-400</t>
-  </si>
-  <si>
-    <t>e_IT93-380</t>
-  </si>
-  <si>
-    <t>e_w82083756-380</t>
-  </si>
-  <si>
-    <t>e_w72466334-380</t>
-  </si>
-  <si>
-    <t>e_IT36-380</t>
-  </si>
-  <si>
-    <t>e_w116517585-380</t>
-  </si>
-  <si>
-    <t>e_w114931087-380</t>
-  </si>
-  <si>
-    <t>e_w104359058-380</t>
-  </si>
-  <si>
-    <t>e_w1100665914-380</t>
-  </si>
-  <si>
-    <t>e_IT53-380</t>
-  </si>
-  <si>
-    <t>e_IT31-380</t>
-  </si>
-  <si>
-    <t>e_IT71-400</t>
-  </si>
-  <si>
-    <t>e_IT21-380</t>
-  </si>
-  <si>
     <t>ep_hydro_dam_G100000602220</t>
   </si>
   <si>
@@ -1407,15 +1407,15 @@
     <t>solar</t>
   </si>
   <si>
+    <t>elc_spv-ITA_0068</t>
+  </si>
+  <si>
+    <t>elc_spv-ITA_0030</t>
+  </si>
+  <si>
     <t>elc_spv-ITA_0042</t>
   </si>
   <si>
-    <t>elc_spv-ITA_0030</t>
-  </si>
-  <si>
-    <t>elc_spv-ITA_0068</t>
-  </si>
-  <si>
     <t>ep_solar_pv_001</t>
   </si>
   <si>
@@ -2031,15 +2031,15 @@
     <t>windon</t>
   </si>
   <si>
+    <t>elc_won-ITA_0073</t>
+  </si>
+  <si>
     <t>elc_won-ITA_0022</t>
   </si>
   <si>
     <t>elc_won-ITA_0096</t>
   </si>
   <si>
-    <t>elc_won-ITA_0073</t>
-  </si>
-  <si>
     <t>ep_windon_wind_010</t>
   </si>
   <si>
@@ -2469,42 +2469,42 @@
     <t>ele</t>
   </si>
   <si>
+    <t>Aggregated Plant - EMBER Gap - way/81938081-380_Missing Bioenergy Capacity</t>
+  </si>
+  <si>
+    <t>GW</t>
+  </si>
+  <si>
+    <t>TWh</t>
+  </si>
+  <si>
+    <t>daynite</t>
+  </si>
+  <si>
+    <t>yes</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/34157795-380_Missing Bioenergy Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/58440884-380_Missing Bioenergy Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/84696559-380_Missing Bioenergy Capacity</t>
+  </si>
+  <si>
     <t>Aggregated Plant - EMBER Gap - way/108020416-380_Missing Bioenergy Capacity</t>
   </si>
   <si>
-    <t>GW</t>
-  </si>
-  <si>
-    <t>TWh</t>
-  </si>
-  <si>
-    <t>daynite</t>
-  </si>
-  <si>
-    <t>yes</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/81938081-380_Missing Bioenergy Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/84696559-380_Missing Bioenergy Capacity</t>
-  </si>
-  <si>
     <t>Aggregated Plant - EMBER Gap - way/144005863-380_Missing Bioenergy Capacity</t>
   </si>
   <si>
+    <t>Aggregated Plant - EMBER Gap - way/109756016-380_Missing Bioenergy Capacity</t>
+  </si>
+  <si>
     <t>Aggregated Plant - EMBER Gap - way/98902899-380_Missing Bioenergy Capacity</t>
   </si>
   <si>
-    <t>Aggregated Plant - EMBER Gap - way/109756016-380_Missing Bioenergy Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/58440884-380_Missing Bioenergy Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/34157795-380_Missing Bioenergy Capacity</t>
-  </si>
-  <si>
     <t>Acerra power station_1</t>
   </si>
   <si>
@@ -2526,15 +2526,15 @@
     <t>Aggregated Plant</t>
   </si>
   <si>
+    <t>Aggregated Plant - EMBER Gap - way/82767145-380_Missing Coal Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/409439916-380_Missing Coal Capacity</t>
+  </si>
+  <si>
     <t>Aggregated Plant - EMBER Gap - way/418902800-380_Missing Coal Capacity</t>
   </si>
   <si>
-    <t>Aggregated Plant - EMBER Gap - way/409439916-380_Missing Coal Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/82767145-380_Missing Coal Capacity</t>
-  </si>
-  <si>
     <t>Aggregated Plant - EMBER Gap - way/303915533-380_Missing Coal Capacity</t>
   </si>
   <si>
@@ -2568,126 +2568,126 @@
     <t>Torrevaldaliga Nord power station_Unit 3</t>
   </si>
   <si>
+    <t>Aggregated Plant - EMBER Gap - way/432729521-380_Missing Gas Capacity</t>
+  </si>
+  <si>
     <t>Aggregated Plant - EMBER Gap - way/181125039-380_Missing Gas Capacity</t>
   </si>
   <si>
     <t>Aggregated Plant - EMBER Gap - way/199675964-380_Missing Gas Capacity</t>
   </si>
   <si>
-    <t>Aggregated Plant - EMBER Gap - way/432729521-380_Missing Gas Capacity</t>
+    <t>Aggregated Plant - EMBER Gap - way/107438024-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/116797658-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/339104227-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/82078641-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/103974940-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/162828577-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/98900549-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/338753171-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/60725875-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/133601335-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/149997403-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/162960205-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/419423704-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/414663585-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/61157826-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/255011550-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/132450233-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/172302572-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/59462715-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/105757794-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/100407576-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/103653592-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/416989699-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/82767145-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/109993642-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/103381531-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/145665799-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/1137611914-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/158739183-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/109756016-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/110330925-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/82084019-380_Missing Gas Capacity</t>
   </si>
   <si>
     <t>Aggregated Plant - EMBER Gap - way/411026199-380_Missing Gas Capacity</t>
   </si>
   <si>
-    <t>Aggregated Plant - EMBER Gap - way/110330925-380_Missing Gas Capacity</t>
-  </si>
-  <si>
     <t>Aggregated Plant - EMBER Gap - way/98421779-380_Missing Gas Capacity</t>
   </si>
   <si>
     <t>Aggregated Plant - EMBER Gap - way/105581403-380_Missing Gas Capacity</t>
   </si>
   <si>
-    <t>Aggregated Plant - EMBER Gap - way/109756016-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/82084019-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/59462715-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/105757794-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/255011550-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/172302572-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/162960205-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/149997403-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/133601335-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/416989699-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/103653592-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/100407576-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/61157826-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/419423704-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/414663585-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/1137611914-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/145665799-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/158739183-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/338753171-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/60725875-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/162828577-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/98900549-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/109993642-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/82767145-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/103381531-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/107438024-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/116797658-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/339104227-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/82078641-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/103974940-380_Missing Gas Capacity</t>
+    <t>Aggregated Plant - EMBER Gap - way/421827453-380_Missing Gas Capacity</t>
   </si>
   <si>
     <t>Aggregated Plant - EMBER Gap - way/99826025-380_Missing Gas Capacity</t>
   </si>
   <si>
-    <t>Aggregated Plant - EMBER Gap - way/421827453-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/132450233-380_Missing Gas Capacity</t>
-  </si>
-  <si>
     <t>Altomonte power station_1</t>
   </si>
   <si>
@@ -3000,102 +3000,102 @@
     <t>Valle Secolo geothermal power plant_2</t>
   </si>
   <si>
+    <t>Aggregated Plant - IRENA Gap - IT72-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/59462263-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/1100665914-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - IT93-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - IT10-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/338753171-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/64200868-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - IT31-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/61626687-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/114931087-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/75602396-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - IT30-500_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - IT53-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/61712456-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/144005863-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - IT21-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/116517585-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/96190189-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - IT72-400_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/1137611914-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/109588422-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - IT7-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/339703159-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/419423704-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/491424937-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/82083756-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/104359058-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/72466334-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
     <t>Aggregated Plant - IRENA Gap - IT71-380_Missing Hydro Capacity</t>
   </si>
   <si>
     <t>Aggregated Plant - IRENA Gap - way/108020416-380_Missing Hydro Capacity</t>
   </si>
   <si>
-    <t>Aggregated Plant - IRENA Gap - way/144005863-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - IT21-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - IT31-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/114931087-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/61626687-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - IT53-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - IT30-500_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - IT7-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/339703159-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/61712456-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/419423704-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/491424937-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/104359058-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/82083756-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/72466334-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/64200868-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/75602396-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/109588422-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/1137611914-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - IT72-400_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/1100665914-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/59462263-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - IT72-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - IT93-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/338753171-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - IT10-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
     <t>Aggregated Plant - IRENA Gap - IT71-400_Missing Hydro Capacity</t>
   </si>
   <si>
     <t>Aggregated Plant - IRENA Gap - IT36-380_Missing Hydro Capacity</t>
   </si>
   <si>
-    <t>Aggregated Plant - IRENA Gap - way/96190189-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/116517585-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
     <t>Baschi hydroelectric plant_</t>
   </si>
   <si>
@@ -3390,16 +3390,19 @@
     <t>San Filippo del Mela power station_1</t>
   </si>
   <si>
+    <t>Aggregated Plant - IRENA Gap - ITA_42_Missing Solar Capacity</t>
+  </si>
+  <si>
+    <t>annual</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - ITA_30_Missing Solar Capacity</t>
+  </si>
+  <si>
     <t>Aggregated Plant - IRENA Gap - ITA_68_Missing Solar Capacity</t>
   </si>
   <si>
-    <t>annual</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - ITA_30_Missing Solar Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - ITA_42_Missing Solar Capacity</t>
+    <t>Aggregated Plant - IRENA Gap - ITA_96_Missing Onshore wind energy Capacity</t>
   </si>
   <si>
     <t>Aggregated Plant - IRENA Gap - ITA_73_Missing Onshore wind energy Capacity</t>
@@ -3408,9 +3411,6 @@
     <t>Aggregated Plant - IRENA Gap - ITA_22_Missing Onshore wind energy Capacity</t>
   </si>
   <si>
-    <t>Aggregated Plant - IRENA Gap - ITA_96_Missing Onshore wind energy Capacity</t>
-  </si>
-  <si>
     <t>AF</t>
   </si>
   <si>
@@ -4002,18 +4002,18 @@
     <t>ccs retrofit of -- Sulcis power station_Unit 3</t>
   </si>
   <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/409439916-380_Missing Coal Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/303915533-380_Missing Coal Capacity</t>
+  </si>
+  <si>
     <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/82767145-380_Missing Coal Capacity</t>
   </si>
   <si>
     <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/418902800-380_Missing Coal Capacity</t>
   </si>
   <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/303915533-380_Missing Coal Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/409439916-380_Missing Coal Capacity</t>
-  </si>
-  <si>
     <t>ccs retrofit of -- Brindisi Sud power station_Unit 1</t>
   </si>
   <si>
@@ -4302,124 +4302,124 @@
     <t>ccs retrofit of -- Aggregated Plant</t>
   </si>
   <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/149997403-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/162960205-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/419423704-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/432729521-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/132450233-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/100407576-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/59462715-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/109993642-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/199675964-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/82078641-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/103653592-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/145665799-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/107438024-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/98900549-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/338753171-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/110330925-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/105757794-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/61157826-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/181125039-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/255011550-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/105581403-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/133601335-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/158739183-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/339104227-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/103974940-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/116797658-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/416989699-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/99826025-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/98421779-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/1137611914-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/60725875-380_Missing Gas Capacity</t>
+  </si>
+  <si>
     <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/82084019-380_Missing Gas Capacity</t>
   </si>
   <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/98421779-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/98900549-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/107438024-380_Missing Gas Capacity</t>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/82767145-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/172302572-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/162828577-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/103381531-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/109756016-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/411026199-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/421827453-380_Missing Gas Capacity</t>
   </si>
   <si>
     <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/414663585-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/82767145-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/162828577-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/172302572-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/116797658-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/181125039-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/105581403-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/255011550-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/162960205-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/149997403-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/419423704-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/145665799-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/59462715-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/109993642-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/199675964-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/103653592-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/1137611914-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/82078641-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/411026199-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/109756016-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/100407576-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/60725875-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/421827453-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/103974940-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/110330925-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/338753171-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/61157826-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/105757794-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/416989699-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/99826025-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/133601335-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/158739183-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/339104227-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/132450233-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/432729521-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/103381531-380_Missing Gas Capacity</t>
   </si>
   <si>
     <t>ccs retrofit of -- Tavazzano power station_CCGT8, timepoint 1</t>
@@ -4823,7 +4823,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A6A27A1D-9C76-44F1-A09D-C45F372B37F0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79EAB795-ED9D-409C-A1D9-4B12B28916EB}">
   <dimension ref="B9:T278"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -5011,7 +5011,7 @@
         <v>33</v>
       </c>
       <c r="D13" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E13">
         <v>0.18317520000000001</v>
@@ -5067,7 +5067,7 @@
         <v>33</v>
       </c>
       <c r="D14" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E14">
         <v>0.13765950000000002</v>
@@ -5515,7 +5515,7 @@
         <v>33</v>
       </c>
       <c r="D22" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E22">
         <v>0.33007379999999992</v>
@@ -5571,7 +5571,7 @@
         <v>33</v>
       </c>
       <c r="D23" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E23">
         <v>0.33007379999999992</v>
@@ -5627,7 +5627,7 @@
         <v>33</v>
       </c>
       <c r="D24" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E24">
         <v>0.33007379999999992</v>
@@ -5683,7 +5683,7 @@
         <v>49</v>
       </c>
       <c r="D25" t="s">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="E25">
         <v>0.49118125000000001</v>
@@ -5739,7 +5739,7 @@
         <v>49</v>
       </c>
       <c r="D26" t="s">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="E26">
         <v>0.52272499999999988</v>
@@ -5795,7 +5795,7 @@
         <v>49</v>
       </c>
       <c r="D27" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="E27">
         <v>0.450625</v>
@@ -5851,7 +5851,7 @@
         <v>49</v>
       </c>
       <c r="D28" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="E28">
         <v>0.52272499999999988</v>
@@ -5907,7 +5907,7 @@
         <v>49</v>
       </c>
       <c r="D29" t="s">
-        <v>84</v>
+        <v>70</v>
       </c>
       <c r="E29">
         <v>0.49118125000000001</v>
@@ -5963,7 +5963,7 @@
         <v>49</v>
       </c>
       <c r="D30" t="s">
-        <v>84</v>
+        <v>70</v>
       </c>
       <c r="E30">
         <v>0.49118125000000001</v>
@@ -6019,7 +6019,7 @@
         <v>49</v>
       </c>
       <c r="D31" t="s">
-        <v>84</v>
+        <v>70</v>
       </c>
       <c r="E31">
         <v>0.49118125000000001</v>
@@ -6131,7 +6131,7 @@
         <v>49</v>
       </c>
       <c r="D33" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="E33">
         <v>0.49118125000000001</v>
@@ -6299,7 +6299,7 @@
         <v>49</v>
       </c>
       <c r="D36" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="E36">
         <v>0.49118125000000001</v>
@@ -6355,7 +6355,7 @@
         <v>49</v>
       </c>
       <c r="D37" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="E37">
         <v>0.49118125000000001</v>
@@ -6411,7 +6411,7 @@
         <v>49</v>
       </c>
       <c r="D38" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="E38">
         <v>0.49118125000000001</v>
@@ -6467,7 +6467,7 @@
         <v>49</v>
       </c>
       <c r="D39" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="E39">
         <v>0.49118125000000001</v>
@@ -6523,7 +6523,7 @@
         <v>49</v>
       </c>
       <c r="D40" t="s">
-        <v>74</v>
+        <v>53</v>
       </c>
       <c r="E40">
         <v>0.46865000000000007</v>
@@ -6579,7 +6579,7 @@
         <v>49</v>
       </c>
       <c r="D41" t="s">
-        <v>74</v>
+        <v>53</v>
       </c>
       <c r="E41">
         <v>0.49118125000000001</v>
@@ -6635,7 +6635,7 @@
         <v>49</v>
       </c>
       <c r="D42" t="s">
-        <v>74</v>
+        <v>53</v>
       </c>
       <c r="E42">
         <v>0.49118125000000001</v>
@@ -6691,7 +6691,7 @@
         <v>49</v>
       </c>
       <c r="D43" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E43">
         <v>0.49118125000000001</v>
@@ -6747,7 +6747,7 @@
         <v>49</v>
       </c>
       <c r="D44" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E44">
         <v>0.49118125000000001</v>
@@ -6803,7 +6803,7 @@
         <v>49</v>
       </c>
       <c r="D45" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E45">
         <v>0.49118125000000001</v>
@@ -6859,7 +6859,7 @@
         <v>49</v>
       </c>
       <c r="D46" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E46">
         <v>0.49118125000000001</v>
@@ -6915,7 +6915,7 @@
         <v>49</v>
       </c>
       <c r="D47" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E47">
         <v>0.49118125000000001</v>
@@ -6971,7 +6971,7 @@
         <v>49</v>
       </c>
       <c r="D48" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E48">
         <v>0.49118125000000001</v>
@@ -7027,7 +7027,7 @@
         <v>49</v>
       </c>
       <c r="D49" t="s">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="E49">
         <v>0.47315625000000006</v>
@@ -7083,7 +7083,7 @@
         <v>49</v>
       </c>
       <c r="D50" t="s">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="E50">
         <v>0.47315625000000006</v>
@@ -7195,7 +7195,7 @@
         <v>49</v>
       </c>
       <c r="D52" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="E52">
         <v>0.54075000000000006</v>
@@ -7251,7 +7251,7 @@
         <v>49</v>
       </c>
       <c r="D53" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="E53">
         <v>0.49118125000000001</v>
@@ -7363,7 +7363,7 @@
         <v>49</v>
       </c>
       <c r="D55" t="s">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="E55">
         <v>0.49118125000000001</v>
@@ -7419,7 +7419,7 @@
         <v>49</v>
       </c>
       <c r="D56" t="s">
-        <v>51</v>
+        <v>77</v>
       </c>
       <c r="E56">
         <v>0.49118125000000001</v>
@@ -7475,7 +7475,7 @@
         <v>49</v>
       </c>
       <c r="D57" t="s">
-        <v>51</v>
+        <v>77</v>
       </c>
       <c r="E57">
         <v>0.49118125000000001</v>
@@ -7531,7 +7531,7 @@
         <v>49</v>
       </c>
       <c r="D58" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="E58">
         <v>0.47315625000000006</v>
@@ -7587,7 +7587,7 @@
         <v>49</v>
       </c>
       <c r="D59" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="E59">
         <v>0.47315625000000006</v>
@@ -7643,7 +7643,7 @@
         <v>49</v>
       </c>
       <c r="D60" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="E60">
         <v>0.450625</v>
@@ -7699,7 +7699,7 @@
         <v>49</v>
       </c>
       <c r="D61" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="E61">
         <v>0.450625</v>
@@ -7811,7 +7811,7 @@
         <v>49</v>
       </c>
       <c r="D63" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="E63">
         <v>0.4911812499999999</v>
@@ -7867,7 +7867,7 @@
         <v>49</v>
       </c>
       <c r="D64" t="s">
-        <v>79</v>
+        <v>61</v>
       </c>
       <c r="E64">
         <v>0.49118125000000001</v>
@@ -7923,7 +7923,7 @@
         <v>49</v>
       </c>
       <c r="D65" t="s">
-        <v>79</v>
+        <v>61</v>
       </c>
       <c r="E65">
         <v>0.49118125000000001</v>
@@ -7979,7 +7979,7 @@
         <v>49</v>
       </c>
       <c r="D66" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E66">
         <v>0.49118125000000001</v>
@@ -8259,7 +8259,7 @@
         <v>49</v>
       </c>
       <c r="D71" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="E71">
         <v>0.49118125000000001</v>
@@ -8315,7 +8315,7 @@
         <v>49</v>
       </c>
       <c r="D72" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="E72">
         <v>0.49118125000000001</v>
@@ -8371,7 +8371,7 @@
         <v>49</v>
       </c>
       <c r="D73" t="s">
-        <v>53</v>
+        <v>84</v>
       </c>
       <c r="E73">
         <v>0.49118125000000001</v>
@@ -8427,7 +8427,7 @@
         <v>49</v>
       </c>
       <c r="D74" t="s">
-        <v>53</v>
+        <v>84</v>
       </c>
       <c r="E74">
         <v>0.49118125000000001</v>
@@ -8483,7 +8483,7 @@
         <v>49</v>
       </c>
       <c r="D75" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="E75">
         <v>0.50470000000000004</v>
@@ -8539,7 +8539,7 @@
         <v>49</v>
       </c>
       <c r="D76" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="E76">
         <v>0.49118125000000001</v>
@@ -8595,7 +8595,7 @@
         <v>49</v>
       </c>
       <c r="D77" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="E77">
         <v>0.49118125000000001</v>
@@ -8763,7 +8763,7 @@
         <v>49</v>
       </c>
       <c r="D80" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E80">
         <v>0.49118125000000001</v>
@@ -8819,7 +8819,7 @@
         <v>49</v>
       </c>
       <c r="D81" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E81">
         <v>0.49118125000000001</v>
@@ -8875,7 +8875,7 @@
         <v>49</v>
       </c>
       <c r="D82" t="s">
-        <v>58</v>
+        <v>85</v>
       </c>
       <c r="E82">
         <v>0.49118125000000001</v>
@@ -8931,7 +8931,7 @@
         <v>49</v>
       </c>
       <c r="D83" t="s">
-        <v>58</v>
+        <v>85</v>
       </c>
       <c r="E83">
         <v>0.49118125000000001</v>
@@ -8987,7 +8987,7 @@
         <v>49</v>
       </c>
       <c r="D84" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="E84">
         <v>0.49118125000000001</v>
@@ -9043,7 +9043,7 @@
         <v>49</v>
       </c>
       <c r="D85" t="s">
-        <v>76</v>
+        <v>51</v>
       </c>
       <c r="E85">
         <v>0.49118125000000001</v>
@@ -9099,7 +9099,7 @@
         <v>49</v>
       </c>
       <c r="D86" t="s">
-        <v>76</v>
+        <v>51</v>
       </c>
       <c r="E86">
         <v>0.49118125000000001</v>
@@ -9267,7 +9267,7 @@
         <v>49</v>
       </c>
       <c r="D89" t="s">
-        <v>73</v>
+        <v>62</v>
       </c>
       <c r="E89">
         <v>0.52272499999999988</v>
@@ -9323,7 +9323,7 @@
         <v>49</v>
       </c>
       <c r="D90" t="s">
-        <v>73</v>
+        <v>62</v>
       </c>
       <c r="E90">
         <v>0.49118125000000001</v>
@@ -9379,7 +9379,7 @@
         <v>49</v>
       </c>
       <c r="D91" t="s">
-        <v>50</v>
+        <v>79</v>
       </c>
       <c r="E91">
         <v>0.49118125000000001</v>
@@ -9491,7 +9491,7 @@
         <v>49</v>
       </c>
       <c r="D93" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E93">
         <v>0.49118125000000001</v>
@@ -9547,7 +9547,7 @@
         <v>49</v>
       </c>
       <c r="D94" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E94">
         <v>0.49118125000000001</v>
@@ -9603,7 +9603,7 @@
         <v>49</v>
       </c>
       <c r="D95" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E95">
         <v>0.49118125000000001</v>
@@ -9659,7 +9659,7 @@
         <v>49</v>
       </c>
       <c r="D96" t="s">
-        <v>75</v>
+        <v>52</v>
       </c>
       <c r="E96">
         <v>0.49118125000000001</v>
@@ -9715,7 +9715,7 @@
         <v>49</v>
       </c>
       <c r="D97" t="s">
-        <v>52</v>
+        <v>83</v>
       </c>
       <c r="E97">
         <v>0.49118125000000001</v>
@@ -9827,7 +9827,7 @@
         <v>49</v>
       </c>
       <c r="D99" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="E99">
         <v>0.54075000000000006</v>
@@ -9883,7 +9883,7 @@
         <v>49</v>
       </c>
       <c r="D100" t="s">
-        <v>86</v>
+        <v>69</v>
       </c>
       <c r="E100">
         <v>0.54075000000000006</v>
@@ -9939,7 +9939,7 @@
         <v>49</v>
       </c>
       <c r="D101" t="s">
-        <v>75</v>
+        <v>52</v>
       </c>
       <c r="E101">
         <v>0.54075000000000006</v>
@@ -9995,7 +9995,7 @@
         <v>49</v>
       </c>
       <c r="D102" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E102">
         <v>0.49118125000000001</v>
@@ -10051,7 +10051,7 @@
         <v>49</v>
       </c>
       <c r="D103" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E103">
         <v>0.49118125000000001</v>
@@ -10107,7 +10107,7 @@
         <v>49</v>
       </c>
       <c r="D104" t="s">
-        <v>79</v>
+        <v>61</v>
       </c>
       <c r="E104">
         <v>0.49118125000000001</v>
@@ -10163,7 +10163,7 @@
         <v>49</v>
       </c>
       <c r="D105" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="E105">
         <v>0.49118125000000001</v>
@@ -10219,7 +10219,7 @@
         <v>49</v>
       </c>
       <c r="D106" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="E106">
         <v>0.450625</v>
@@ -10275,7 +10275,7 @@
         <v>49</v>
       </c>
       <c r="D107" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="E107">
         <v>0.450625</v>
@@ -10331,7 +10331,7 @@
         <v>49</v>
       </c>
       <c r="D108" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="E108">
         <v>0.47315625000000006</v>
@@ -10443,7 +10443,7 @@
         <v>49</v>
       </c>
       <c r="D110" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="E110">
         <v>0.49118125000000001</v>
@@ -10499,7 +10499,7 @@
         <v>49</v>
       </c>
       <c r="D111" t="s">
-        <v>74</v>
+        <v>53</v>
       </c>
       <c r="E111">
         <v>0.46865000000000007</v>
@@ -10611,7 +10611,7 @@
         <v>49</v>
       </c>
       <c r="D113" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="E113">
         <v>0.49118125000000001</v>
@@ -11115,7 +11115,7 @@
         <v>49</v>
       </c>
       <c r="D122" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E122">
         <v>0.54075000000000006</v>
@@ -11171,7 +11171,7 @@
         <v>49</v>
       </c>
       <c r="D123" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E123">
         <v>0.54075000000000006</v>
@@ -11227,7 +11227,7 @@
         <v>49</v>
       </c>
       <c r="D124" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E124">
         <v>0.54075000000000006</v>
@@ -11283,7 +11283,7 @@
         <v>49</v>
       </c>
       <c r="D125" t="s">
-        <v>34</v>
+        <v>75</v>
       </c>
       <c r="E125">
         <v>0.54075000000000006</v>
@@ -11563,7 +11563,7 @@
         <v>49</v>
       </c>
       <c r="D130" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E130">
         <v>0.54075000000000006</v>
@@ -11619,7 +11619,7 @@
         <v>49</v>
       </c>
       <c r="D131" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E131">
         <v>0.54075000000000006</v>
@@ -11675,7 +11675,7 @@
         <v>49</v>
       </c>
       <c r="D132" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E132">
         <v>0.54075000000000006</v>
@@ -11731,7 +11731,7 @@
         <v>49</v>
       </c>
       <c r="D133" t="s">
-        <v>18</v>
+        <v>58</v>
       </c>
       <c r="E133">
         <v>0.54075000000000006</v>
@@ -11843,7 +11843,7 @@
         <v>49</v>
       </c>
       <c r="D135" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E135">
         <v>0.54075000000000006</v>
@@ -12403,7 +12403,7 @@
         <v>49</v>
       </c>
       <c r="D145" t="s">
-        <v>85</v>
+        <v>16</v>
       </c>
       <c r="E145">
         <v>0.54075000000000006</v>
@@ -12459,7 +12459,7 @@
         <v>49</v>
       </c>
       <c r="D146" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E146">
         <v>0.54075000000000006</v>
@@ -12571,7 +12571,7 @@
         <v>49</v>
       </c>
       <c r="D148" t="s">
-        <v>53</v>
+        <v>36</v>
       </c>
       <c r="E148">
         <v>0.54075000000000006</v>
@@ -12627,7 +12627,7 @@
         <v>49</v>
       </c>
       <c r="D149" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E149">
         <v>0.54075000000000006</v>
@@ -12683,7 +12683,7 @@
         <v>49</v>
       </c>
       <c r="D150" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E150">
         <v>0.54075000000000006</v>
@@ -12907,7 +12907,7 @@
         <v>49</v>
       </c>
       <c r="D154" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E154">
         <v>0.54075000000000006</v>
@@ -12963,7 +12963,7 @@
         <v>49</v>
       </c>
       <c r="D155" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E155">
         <v>0.54075000000000006</v>
@@ -13075,7 +13075,7 @@
         <v>49</v>
       </c>
       <c r="D157" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E157">
         <v>0.54075000000000006</v>
@@ -13131,7 +13131,7 @@
         <v>49</v>
       </c>
       <c r="D158" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E158">
         <v>0.54075000000000006</v>
@@ -13187,7 +13187,7 @@
         <v>49</v>
       </c>
       <c r="D159" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E159">
         <v>0.54075000000000006</v>
@@ -13467,7 +13467,7 @@
         <v>49</v>
       </c>
       <c r="D164" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="E164">
         <v>0.48667500000000002</v>
@@ -14307,7 +14307,7 @@
         <v>49</v>
       </c>
       <c r="D179" t="s">
-        <v>75</v>
+        <v>52</v>
       </c>
       <c r="E179">
         <v>0.46865000000000007</v>
@@ -14363,7 +14363,7 @@
         <v>49</v>
       </c>
       <c r="D180" t="s">
-        <v>75</v>
+        <v>52</v>
       </c>
       <c r="E180">
         <v>0.46865000000000007</v>
@@ -14587,7 +14587,7 @@
         <v>49</v>
       </c>
       <c r="D184" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="E184">
         <v>0.48667500000000002</v>
@@ -14643,7 +14643,7 @@
         <v>49</v>
       </c>
       <c r="D185" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="E185">
         <v>0.48667500000000002</v>
@@ -15371,7 +15371,7 @@
         <v>49</v>
       </c>
       <c r="D198" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E198">
         <v>0.50470000000000004</v>
@@ -15595,7 +15595,7 @@
         <v>49</v>
       </c>
       <c r="D202" t="s">
-        <v>86</v>
+        <v>69</v>
       </c>
       <c r="E202">
         <v>0.46865000000000007</v>
@@ -16323,7 +16323,7 @@
         <v>49</v>
       </c>
       <c r="D215" t="s">
-        <v>58</v>
+        <v>85</v>
       </c>
       <c r="E215">
         <v>0.450625</v>
@@ -16491,7 +16491,7 @@
         <v>49</v>
       </c>
       <c r="D218" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E218">
         <v>0.50470000000000004</v>
@@ -16547,7 +16547,7 @@
         <v>49</v>
       </c>
       <c r="D219" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E219">
         <v>0.50470000000000004</v>
@@ -16715,7 +16715,7 @@
         <v>49</v>
       </c>
       <c r="D222" t="s">
-        <v>51</v>
+        <v>77</v>
       </c>
       <c r="E222">
         <v>0.450625</v>
@@ -16827,7 +16827,7 @@
         <v>49</v>
       </c>
       <c r="D224" t="s">
-        <v>73</v>
+        <v>62</v>
       </c>
       <c r="E224">
         <v>0.28839999999999999</v>
@@ -16883,7 +16883,7 @@
         <v>49</v>
       </c>
       <c r="D225" t="s">
-        <v>73</v>
+        <v>62</v>
       </c>
       <c r="E225">
         <v>0.28839999999999999</v>
@@ -16939,7 +16939,7 @@
         <v>49</v>
       </c>
       <c r="D226" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="E226">
         <v>0.24784375000000003</v>
@@ -17443,7 +17443,7 @@
         <v>49</v>
       </c>
       <c r="D235" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E235">
         <v>0.25235000000000002</v>
@@ -17723,7 +17723,7 @@
         <v>49</v>
       </c>
       <c r="D240" t="s">
-        <v>73</v>
+        <v>62</v>
       </c>
       <c r="E240">
         <v>0.27938750000000001</v>
@@ -17835,7 +17835,7 @@
         <v>49</v>
       </c>
       <c r="D242" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="E242">
         <v>0.25235000000000002</v>
@@ -18031,7 +18031,7 @@
         <v>49</v>
       </c>
       <c r="D247" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="E247">
         <v>0.32445000000000007</v>
@@ -18101,7 +18101,7 @@
         <v>49</v>
       </c>
       <c r="D249" t="s">
-        <v>50</v>
+        <v>79</v>
       </c>
       <c r="E249">
         <v>0.32445000000000002</v>
@@ -18241,7 +18241,7 @@
         <v>49</v>
       </c>
       <c r="D253" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="E253">
         <v>0.27938750000000001</v>
@@ -18276,7 +18276,7 @@
         <v>49</v>
       </c>
       <c r="D254" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="E254">
         <v>0.27938750000000001</v>
@@ -18311,7 +18311,7 @@
         <v>49</v>
       </c>
       <c r="D255" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="E255">
         <v>0.27938750000000001</v>
@@ -18346,7 +18346,7 @@
         <v>49</v>
       </c>
       <c r="D256" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="E256">
         <v>0.31093124999999999</v>
@@ -18381,7 +18381,7 @@
         <v>49</v>
       </c>
       <c r="D257" t="s">
-        <v>84</v>
+        <v>70</v>
       </c>
       <c r="E257">
         <v>0.27938750000000001</v>
@@ -18416,7 +18416,7 @@
         <v>49</v>
       </c>
       <c r="D258" t="s">
-        <v>84</v>
+        <v>70</v>
       </c>
       <c r="E258">
         <v>0.27938750000000001</v>
@@ -18451,7 +18451,7 @@
         <v>49</v>
       </c>
       <c r="D259" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="E259">
         <v>0.26136249999999994</v>
@@ -18486,7 +18486,7 @@
         <v>49</v>
       </c>
       <c r="D260" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E260">
         <v>0.28839999999999999</v>
@@ -18521,7 +18521,7 @@
         <v>49</v>
       </c>
       <c r="D261" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E261">
         <v>0.28839999999999999</v>
@@ -18556,7 +18556,7 @@
         <v>49</v>
       </c>
       <c r="D262" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E262">
         <v>0.28839999999999999</v>
@@ -18626,7 +18626,7 @@
         <v>439</v>
       </c>
       <c r="D264" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="E264">
         <v>0.41457500000000003</v>
@@ -18731,7 +18731,7 @@
         <v>439</v>
       </c>
       <c r="D267" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E267">
         <v>0.22981874999999999</v>
@@ -18941,7 +18941,7 @@
         <v>439</v>
       </c>
       <c r="D273" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="E273">
         <v>0.27938750000000001</v>
@@ -19149,7 +19149,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B44CA91-07A2-4CE2-819D-A0286D6F19AA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4AB5D649-5C86-4AA2-9E28-49C5EB87801E}">
   <dimension ref="B9:T842"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -19231,19 +19231,19 @@
         <v>2022</v>
       </c>
       <c r="F11">
-        <v>0.24877966101694915</v>
+        <v>0.51576271186440681</v>
       </c>
       <c r="G11">
-        <v>0.33990000000000004</v>
+        <v>0.36049999999999999</v>
       </c>
       <c r="H11">
-        <v>4427.5</v>
+        <v>3850.0000000000005</v>
       </c>
       <c r="I11">
-        <v>157.30000000000001</v>
+        <v>143</v>
       </c>
       <c r="J11">
-        <v>9.240000000000002</v>
+        <v>8.4</v>
       </c>
       <c r="K11">
         <v>50</v>
@@ -19284,7 +19284,7 @@
         <v>2022</v>
       </c>
       <c r="F12">
-        <v>0.49149152542372881</v>
+        <v>1.0679322033898306</v>
       </c>
       <c r="G12">
         <v>0.36049999999999999</v>
@@ -19337,19 +19337,19 @@
         <v>2022</v>
       </c>
       <c r="F13">
-        <v>0.39440677966101695</v>
+        <v>0.27911864406779663</v>
       </c>
       <c r="G13">
-        <v>0.36049999999999999</v>
+        <v>0.33990000000000004</v>
       </c>
       <c r="H13">
-        <v>3850.0000000000005</v>
+        <v>4427.5</v>
       </c>
       <c r="I13">
-        <v>143</v>
+        <v>157.30000000000001</v>
       </c>
       <c r="J13">
-        <v>8.4</v>
+        <v>9.240000000000002</v>
       </c>
       <c r="K13">
         <v>50</v>
@@ -19390,7 +19390,7 @@
         <v>2022</v>
       </c>
       <c r="F14">
-        <v>0.51576271186440681</v>
+        <v>0.49149152542372881</v>
       </c>
       <c r="G14">
         <v>0.36049999999999999</v>
@@ -19443,19 +19443,19 @@
         <v>2022</v>
       </c>
       <c r="F15">
-        <v>0.27911864406779663</v>
+        <v>0.39440677966101695</v>
       </c>
       <c r="G15">
-        <v>0.33990000000000004</v>
+        <v>0.36049999999999999</v>
       </c>
       <c r="H15">
-        <v>4427.5</v>
+        <v>3850.0000000000005</v>
       </c>
       <c r="I15">
-        <v>157.30000000000001</v>
+        <v>143</v>
       </c>
       <c r="J15">
-        <v>9.240000000000002</v>
+        <v>8.4</v>
       </c>
       <c r="K15">
         <v>50</v>
@@ -19549,7 +19549,7 @@
         <v>2022</v>
       </c>
       <c r="F17">
-        <v>0.22450847457627116</v>
+        <v>0.24877966101694915</v>
       </c>
       <c r="G17">
         <v>0.33990000000000004</v>
@@ -19602,19 +19602,19 @@
         <v>2022</v>
       </c>
       <c r="F18">
-        <v>1.0679322033898306</v>
+        <v>0.22450847457627116</v>
       </c>
       <c r="G18">
-        <v>0.36049999999999999</v>
+        <v>0.33990000000000004</v>
       </c>
       <c r="H18">
-        <v>3850.0000000000005</v>
+        <v>4427.5</v>
       </c>
       <c r="I18">
-        <v>143</v>
+        <v>157.30000000000001</v>
       </c>
       <c r="J18">
-        <v>8.4</v>
+        <v>9.240000000000002</v>
       </c>
       <c r="K18">
         <v>50</v>
@@ -19649,7 +19649,7 @@
         <v>13</v>
       </c>
       <c r="D19" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="E19">
         <v>2008</v>
@@ -19702,7 +19702,7 @@
         <v>13</v>
       </c>
       <c r="D20" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E20">
         <v>1998</v>
@@ -19755,7 +19755,7 @@
         <v>13</v>
       </c>
       <c r="D21" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E21">
         <v>2008</v>
@@ -19861,7 +19861,7 @@
         <v>13</v>
       </c>
       <c r="D23" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E23">
         <v>2013</v>
@@ -19914,7 +19914,7 @@
         <v>13</v>
       </c>
       <c r="D24" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="E24">
         <v>1965</v>
@@ -19967,7 +19967,7 @@
         <v>13</v>
       </c>
       <c r="D25" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E25">
         <v>2003</v>
@@ -20020,7 +20020,7 @@
         <v>13</v>
       </c>
       <c r="D26" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E26">
         <v>2009</v>
@@ -20073,7 +20073,7 @@
         <v>13</v>
       </c>
       <c r="D27" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E27">
         <v>2018</v>
@@ -20126,7 +20126,7 @@
         <v>13</v>
       </c>
       <c r="D28" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="E28">
         <v>2009</v>
@@ -20185,19 +20185,19 @@
         <v>2022</v>
       </c>
       <c r="F29">
-        <v>0.61803468208092449</v>
+        <v>0.18416184971098257</v>
       </c>
       <c r="G29">
-        <v>0.37080000000000002</v>
+        <v>0.35020000000000001</v>
       </c>
       <c r="H29">
-        <v>2200</v>
+        <v>2530</v>
       </c>
       <c r="I29">
-        <v>66</v>
+        <v>72.600000000000009</v>
       </c>
       <c r="J29">
-        <v>5.25</v>
+        <v>5.7750000000000004</v>
       </c>
       <c r="K29">
         <v>50</v>
@@ -20291,19 +20291,19 @@
         <v>2022</v>
       </c>
       <c r="F31">
-        <v>0.18416184971098257</v>
+        <v>0.61803468208092449</v>
       </c>
       <c r="G31">
-        <v>0.35020000000000001</v>
+        <v>0.37080000000000002</v>
       </c>
       <c r="H31">
-        <v>2530</v>
+        <v>2200</v>
       </c>
       <c r="I31">
-        <v>72.600000000000009</v>
+        <v>66</v>
       </c>
       <c r="J31">
-        <v>5.7750000000000004</v>
+        <v>5.25</v>
       </c>
       <c r="K31">
         <v>50</v>
@@ -20497,7 +20497,7 @@
         <v>33</v>
       </c>
       <c r="D35" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E35">
         <v>2005</v>
@@ -20550,7 +20550,7 @@
         <v>33</v>
       </c>
       <c r="D36" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E36">
         <v>1986</v>
@@ -20762,7 +20762,7 @@
         <v>33</v>
       </c>
       <c r="D40" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E40">
         <v>2009</v>
@@ -20815,7 +20815,7 @@
         <v>33</v>
       </c>
       <c r="D41" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E41">
         <v>2010</v>
@@ -20868,7 +20868,7 @@
         <v>33</v>
       </c>
       <c r="D42" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E42">
         <v>2010</v>
@@ -20927,7 +20927,7 @@
         <v>2022</v>
       </c>
       <c r="F43">
-        <v>0.20557907614758497</v>
+        <v>0.16608022972358796</v>
       </c>
       <c r="G43">
         <v>0.59739999999999993</v>
@@ -20980,7 +20980,7 @@
         <v>2022</v>
       </c>
       <c r="F44">
-        <v>0.20212110068999706</v>
+        <v>0.18507474280047922</v>
       </c>
       <c r="G44">
         <v>0.59739999999999993</v>
@@ -20992,7 +20992,7 @@
         <v>36.300000000000004</v>
       </c>
       <c r="J44">
-        <v>3.4650000000000003</v>
+        <v>3.4649999999999999</v>
       </c>
       <c r="K44">
         <v>50</v>
@@ -21033,19 +21033,19 @@
         <v>2022</v>
       </c>
       <c r="F45">
-        <v>0.19481551873734657</v>
+        <v>0.3567559186877659</v>
       </c>
       <c r="G45">
-        <v>0.59739999999999993</v>
+        <v>0.61799999999999999</v>
       </c>
       <c r="H45">
-        <v>1265</v>
+        <v>1100</v>
       </c>
       <c r="I45">
-        <v>36.300000000000004</v>
+        <v>33</v>
       </c>
       <c r="J45">
-        <v>3.4650000000000003</v>
+        <v>3.1500000000000004</v>
       </c>
       <c r="K45">
         <v>50</v>
@@ -21080,13 +21080,13 @@
         <v>49</v>
       </c>
       <c r="D46" t="s">
-        <v>53</v>
+        <v>36</v>
       </c>
       <c r="E46">
         <v>2022</v>
       </c>
       <c r="F46">
-        <v>0.18702289798785268</v>
+        <v>0.27761211420071885</v>
       </c>
       <c r="G46">
         <v>0.59739999999999993</v>
@@ -21133,13 +21133,13 @@
         <v>49</v>
       </c>
       <c r="D47" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E47">
         <v>2022</v>
       </c>
       <c r="F47">
-        <v>0.49339465314217229</v>
+        <v>0.30829555840185086</v>
       </c>
       <c r="G47">
         <v>0.61799999999999999</v>
@@ -21186,13 +21186,13 @@
         <v>49</v>
       </c>
       <c r="D48" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E48">
         <v>2022</v>
       </c>
       <c r="F48">
-        <v>0.45732943023592104</v>
+        <v>0.49339465314217229</v>
       </c>
       <c r="G48">
         <v>0.61799999999999999</v>
@@ -21239,13 +21239,13 @@
         <v>49</v>
       </c>
       <c r="D49" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E49">
         <v>2022</v>
       </c>
       <c r="F49">
-        <v>0.17484692806676855</v>
+        <v>0.21551466760318963</v>
       </c>
       <c r="G49">
         <v>0.59739999999999993</v>
@@ -21292,13 +21292,13 @@
         <v>49</v>
       </c>
       <c r="D50" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E50">
         <v>2022</v>
       </c>
       <c r="F50">
-        <v>0.18872753377680451</v>
+        <v>0.17484692806676855</v>
       </c>
       <c r="G50">
         <v>0.59739999999999993</v>
@@ -21310,7 +21310,7 @@
         <v>36.300000000000004</v>
       </c>
       <c r="J50">
-        <v>3.4650000000000007</v>
+        <v>3.4650000000000003</v>
       </c>
       <c r="K50">
         <v>50</v>
@@ -21345,13 +21345,13 @@
         <v>49</v>
       </c>
       <c r="D51" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E51">
         <v>2022</v>
       </c>
       <c r="F51">
-        <v>0.29344087509812827</v>
+        <v>0.18872753377680451</v>
       </c>
       <c r="G51">
         <v>0.59739999999999993</v>
@@ -21363,7 +21363,7 @@
         <v>36.300000000000004</v>
       </c>
       <c r="J51">
-        <v>3.4650000000000003</v>
+        <v>3.4650000000000007</v>
       </c>
       <c r="K51">
         <v>50</v>
@@ -21398,13 +21398,13 @@
         <v>49</v>
       </c>
       <c r="D52" t="s">
-        <v>18</v>
+        <v>58</v>
       </c>
       <c r="E52">
         <v>2022</v>
       </c>
       <c r="F52">
-        <v>0.19822479031525012</v>
+        <v>0.18556178159732259</v>
       </c>
       <c r="G52">
         <v>0.59739999999999993</v>
@@ -21457,7 +21457,7 @@
         <v>2022</v>
       </c>
       <c r="F53">
-        <v>0.19481551873734657</v>
+        <v>0.23280454489112914</v>
       </c>
       <c r="G53">
         <v>0.59739999999999993</v>
@@ -21469,7 +21469,7 @@
         <v>36.300000000000004</v>
       </c>
       <c r="J53">
-        <v>3.4650000000000003</v>
+        <v>3.4650000000000007</v>
       </c>
       <c r="K53">
         <v>50</v>
@@ -21510,7 +21510,7 @@
         <v>2022</v>
       </c>
       <c r="F54">
-        <v>0.19481551873734657</v>
+        <v>0.26604494277568891</v>
       </c>
       <c r="G54">
         <v>0.59739999999999993</v>
@@ -21563,7 +21563,7 @@
         <v>2022</v>
       </c>
       <c r="F55">
-        <v>0.21551466760318963</v>
+        <v>0.28443065735652601</v>
       </c>
       <c r="G55">
         <v>0.59739999999999993</v>
@@ -21616,19 +21616,19 @@
         <v>2022</v>
       </c>
       <c r="F56">
-        <v>0.22793415692269547</v>
+        <v>0.39839773581787374</v>
       </c>
       <c r="G56">
-        <v>0.59739999999999993</v>
+        <v>0.61799999999999999</v>
       </c>
       <c r="H56">
-        <v>1265</v>
+        <v>1100</v>
       </c>
       <c r="I56">
-        <v>36.300000000000004</v>
+        <v>33</v>
       </c>
       <c r="J56">
-        <v>3.4650000000000003</v>
+        <v>3.1500000000000004</v>
       </c>
       <c r="K56">
         <v>50</v>
@@ -21669,19 +21669,19 @@
         <v>2022</v>
       </c>
       <c r="F57">
-        <v>0.21283595422055113</v>
+        <v>0.45732943023592104</v>
       </c>
       <c r="G57">
-        <v>0.59739999999999993</v>
+        <v>0.61799999999999999</v>
       </c>
       <c r="H57">
-        <v>1265</v>
+        <v>1100</v>
       </c>
       <c r="I57">
-        <v>36.300000000000004</v>
+        <v>33</v>
       </c>
       <c r="J57">
-        <v>3.4650000000000003</v>
+        <v>3.1500000000000004</v>
       </c>
       <c r="K57">
         <v>50</v>
@@ -21722,7 +21722,7 @@
         <v>2022</v>
       </c>
       <c r="F58">
-        <v>0.1548783373961905</v>
+        <v>0.21283595422055113</v>
       </c>
       <c r="G58">
         <v>0.59739999999999993</v>
@@ -21734,7 +21734,7 @@
         <v>36.300000000000004</v>
       </c>
       <c r="J58">
-        <v>3.4649999999999999</v>
+        <v>3.4650000000000003</v>
       </c>
       <c r="K58">
         <v>50</v>
@@ -21775,7 +21775,7 @@
         <v>2022</v>
       </c>
       <c r="F59">
-        <v>0.27347228442755023</v>
+        <v>0.19481551873734657</v>
       </c>
       <c r="G59">
         <v>0.59739999999999993</v>
@@ -21828,7 +21828,7 @@
         <v>2022</v>
       </c>
       <c r="F60">
-        <v>0.18556178159732259</v>
+        <v>0.22793415692269547</v>
       </c>
       <c r="G60">
         <v>0.59739999999999993</v>
@@ -21881,7 +21881,7 @@
         <v>2022</v>
       </c>
       <c r="F61">
-        <v>0.23280454489112914</v>
+        <v>0.1548783373961905</v>
       </c>
       <c r="G61">
         <v>0.59739999999999993</v>
@@ -21893,7 +21893,7 @@
         <v>36.300000000000004</v>
       </c>
       <c r="J61">
-        <v>3.4650000000000007</v>
+        <v>3.4649999999999999</v>
       </c>
       <c r="K61">
         <v>50</v>
@@ -21934,7 +21934,7 @@
         <v>2022</v>
       </c>
       <c r="F62">
-        <v>0.26604494277568891</v>
+        <v>0.27347228442755023</v>
       </c>
       <c r="G62">
         <v>0.59739999999999993</v>
@@ -21987,7 +21987,7 @@
         <v>2022</v>
       </c>
       <c r="F63">
-        <v>0.19481551873734657</v>
+        <v>0.23864901045324952</v>
       </c>
       <c r="G63">
         <v>0.59739999999999993</v>
@@ -22040,19 +22040,19 @@
         <v>2022</v>
       </c>
       <c r="F64">
-        <v>0.20820908565053911</v>
+        <v>0.31243538817501959</v>
       </c>
       <c r="G64">
-        <v>0.59739999999999993</v>
+        <v>0.61799999999999999</v>
       </c>
       <c r="H64">
-        <v>1265</v>
+        <v>1100</v>
       </c>
       <c r="I64">
-        <v>36.300000000000004</v>
+        <v>33</v>
       </c>
       <c r="J64">
-        <v>3.4650000000000007</v>
+        <v>3.1500000000000004</v>
       </c>
       <c r="K64">
         <v>50</v>
@@ -22093,7 +22093,7 @@
         <v>2022</v>
       </c>
       <c r="F65">
-        <v>0.18629233979258764</v>
+        <v>0.19481551873734657</v>
       </c>
       <c r="G65">
         <v>0.59739999999999993</v>
@@ -22146,7 +22146,7 @@
         <v>2022</v>
       </c>
       <c r="F66">
-        <v>0.20236462008841874</v>
+        <v>0.19481551873734657</v>
       </c>
       <c r="G66">
         <v>0.59739999999999993</v>
@@ -22199,10 +22199,10 @@
         <v>2022</v>
       </c>
       <c r="F67">
-        <v>0.39839773581787374</v>
+        <v>0.43468212618270452</v>
       </c>
       <c r="G67">
-        <v>0.61799999999999999</v>
+        <v>0.61799999999999988</v>
       </c>
       <c r="H67">
         <v>1100</v>
@@ -22252,19 +22252,19 @@
         <v>2022</v>
       </c>
       <c r="F68">
-        <v>0.30829555840185086</v>
+        <v>0.20820908565053911</v>
       </c>
       <c r="G68">
-        <v>0.61799999999999999</v>
+        <v>0.59739999999999993</v>
       </c>
       <c r="H68">
-        <v>1100</v>
+        <v>1265</v>
       </c>
       <c r="I68">
-        <v>33</v>
+        <v>36.300000000000004</v>
       </c>
       <c r="J68">
-        <v>3.1500000000000004</v>
+        <v>3.4650000000000007</v>
       </c>
       <c r="K68">
         <v>50</v>
@@ -22299,13 +22299,13 @@
         <v>49</v>
       </c>
       <c r="D69" t="s">
-        <v>34</v>
+        <v>75</v>
       </c>
       <c r="E69">
         <v>2022</v>
       </c>
       <c r="F69">
-        <v>0.27761211420071885</v>
+        <v>0.18629233979258764</v>
       </c>
       <c r="G69">
         <v>0.59739999999999993</v>
@@ -22352,25 +22352,25 @@
         <v>49</v>
       </c>
       <c r="D70" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E70">
         <v>2022</v>
       </c>
       <c r="F70">
-        <v>0.3567559186877659</v>
+        <v>0.20236462008841874</v>
       </c>
       <c r="G70">
-        <v>0.61799999999999999</v>
+        <v>0.59739999999999993</v>
       </c>
       <c r="H70">
-        <v>1100</v>
+        <v>1265</v>
       </c>
       <c r="I70">
-        <v>33</v>
+        <v>36.300000000000004</v>
       </c>
       <c r="J70">
-        <v>3.1500000000000004</v>
+        <v>3.4650000000000003</v>
       </c>
       <c r="K70">
         <v>50</v>
@@ -22405,13 +22405,13 @@
         <v>49</v>
       </c>
       <c r="D71" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E71">
         <v>2022</v>
       </c>
       <c r="F71">
-        <v>0.18507474280047922</v>
+        <v>0.20212110068999706</v>
       </c>
       <c r="G71">
         <v>0.59739999999999993</v>
@@ -22423,7 +22423,7 @@
         <v>36.300000000000004</v>
       </c>
       <c r="J71">
-        <v>3.4649999999999999</v>
+        <v>3.4650000000000003</v>
       </c>
       <c r="K71">
         <v>50</v>
@@ -22458,13 +22458,13 @@
         <v>49</v>
       </c>
       <c r="D72" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E72">
         <v>2022</v>
       </c>
       <c r="F72">
-        <v>0.19676367392472002</v>
+        <v>0.26543614427963469</v>
       </c>
       <c r="G72">
         <v>0.59739999999999993</v>
@@ -22511,13 +22511,13 @@
         <v>49</v>
       </c>
       <c r="D73" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E73">
         <v>2022</v>
       </c>
       <c r="F73">
-        <v>0.16608022972358796</v>
+        <v>0.20557907614758497</v>
       </c>
       <c r="G73">
         <v>0.59739999999999993</v>
@@ -22564,13 +22564,13 @@
         <v>49</v>
       </c>
       <c r="D74" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E74">
         <v>2022</v>
       </c>
       <c r="F74">
-        <v>0.28443065735652601</v>
+        <v>0.18824049497996109</v>
       </c>
       <c r="G74">
         <v>0.59739999999999993</v>
@@ -22617,25 +22617,25 @@
         <v>49</v>
       </c>
       <c r="D75" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E75">
         <v>2022</v>
       </c>
       <c r="F75">
-        <v>0.43468212618270452</v>
+        <v>0.19627663512787666</v>
       </c>
       <c r="G75">
-        <v>0.61799999999999988</v>
+        <v>0.59739999999999993</v>
       </c>
       <c r="H75">
-        <v>1100</v>
+        <v>1265</v>
       </c>
       <c r="I75">
-        <v>33</v>
+        <v>36.300000000000004</v>
       </c>
       <c r="J75">
-        <v>3.1500000000000004</v>
+        <v>3.4649999999999999</v>
       </c>
       <c r="K75">
         <v>50</v>
@@ -22670,13 +22670,13 @@
         <v>49</v>
       </c>
       <c r="D76" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E76">
         <v>2022</v>
       </c>
       <c r="F76">
-        <v>0.18824049497996109</v>
+        <v>0.21113131843159935</v>
       </c>
       <c r="G76">
         <v>0.59739999999999993</v>
@@ -22723,13 +22723,13 @@
         <v>49</v>
       </c>
       <c r="D77" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E77">
         <v>2022</v>
       </c>
       <c r="F77">
-        <v>0.19627663512787666</v>
+        <v>0.19481551873734657</v>
       </c>
       <c r="G77">
         <v>0.59739999999999993</v>
@@ -22741,7 +22741,7 @@
         <v>36.300000000000004</v>
       </c>
       <c r="J77">
-        <v>3.4649999999999999</v>
+        <v>3.4650000000000003</v>
       </c>
       <c r="K77">
         <v>50</v>
@@ -22776,13 +22776,13 @@
         <v>49</v>
       </c>
       <c r="D78" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E78">
         <v>2022</v>
       </c>
       <c r="F78">
-        <v>0.21113131843159935</v>
+        <v>0.18702289798785268</v>
       </c>
       <c r="G78">
         <v>0.59739999999999993</v>
@@ -22829,25 +22829,25 @@
         <v>49</v>
       </c>
       <c r="D79" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E79">
         <v>2022</v>
       </c>
       <c r="F79">
-        <v>0.31243538817501959</v>
+        <v>0.29344087509812827</v>
       </c>
       <c r="G79">
-        <v>0.61799999999999999</v>
+        <v>0.59739999999999993</v>
       </c>
       <c r="H79">
-        <v>1100</v>
+        <v>1265</v>
       </c>
       <c r="I79">
-        <v>33</v>
+        <v>36.300000000000004</v>
       </c>
       <c r="J79">
-        <v>3.1500000000000004</v>
+        <v>3.4650000000000003</v>
       </c>
       <c r="K79">
         <v>50</v>
@@ -22882,25 +22882,25 @@
         <v>49</v>
       </c>
       <c r="D80" t="s">
-        <v>85</v>
+        <v>16</v>
       </c>
       <c r="E80">
         <v>2022</v>
       </c>
       <c r="F80">
-        <v>0.37112356319464518</v>
+        <v>0.19822479031525012</v>
       </c>
       <c r="G80">
-        <v>0.61799999999999999</v>
+        <v>0.59739999999999993</v>
       </c>
       <c r="H80">
-        <v>1100</v>
+        <v>1265</v>
       </c>
       <c r="I80">
-        <v>33</v>
+        <v>36.300000000000004</v>
       </c>
       <c r="J80">
-        <v>3.1500000000000004</v>
+        <v>3.4650000000000003</v>
       </c>
       <c r="K80">
         <v>50</v>
@@ -22941,19 +22941,19 @@
         <v>2022</v>
       </c>
       <c r="F81">
-        <v>0.23864901045324952</v>
+        <v>0.37112356319464518</v>
       </c>
       <c r="G81">
-        <v>0.59739999999999993</v>
+        <v>0.61799999999999999</v>
       </c>
       <c r="H81">
-        <v>1265</v>
+        <v>1100</v>
       </c>
       <c r="I81">
-        <v>36.300000000000004</v>
+        <v>33</v>
       </c>
       <c r="J81">
-        <v>3.4650000000000003</v>
+        <v>3.1500000000000004</v>
       </c>
       <c r="K81">
         <v>50</v>
@@ -22994,7 +22994,7 @@
         <v>2022</v>
       </c>
       <c r="F82">
-        <v>0.26543614427963469</v>
+        <v>0.19676367392472002</v>
       </c>
       <c r="G82">
         <v>0.59739999999999993</v>
@@ -23041,7 +23041,7 @@
         <v>49</v>
       </c>
       <c r="D83" t="s">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="E83">
         <v>2006</v>
@@ -23094,7 +23094,7 @@
         <v>49</v>
       </c>
       <c r="D84" t="s">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="E84">
         <v>2012</v>
@@ -23147,7 +23147,7 @@
         <v>49</v>
       </c>
       <c r="D85" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="E85">
         <v>1993</v>
@@ -23200,7 +23200,7 @@
         <v>49</v>
       </c>
       <c r="D86" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="E86">
         <v>2011</v>
@@ -23253,7 +23253,7 @@
         <v>49</v>
       </c>
       <c r="D87" t="s">
-        <v>84</v>
+        <v>70</v>
       </c>
       <c r="E87">
         <v>2005</v>
@@ -23306,7 +23306,7 @@
         <v>49</v>
       </c>
       <c r="D88" t="s">
-        <v>84</v>
+        <v>70</v>
       </c>
       <c r="E88">
         <v>2006</v>
@@ -23359,7 +23359,7 @@
         <v>49</v>
       </c>
       <c r="D89" t="s">
-        <v>84</v>
+        <v>70</v>
       </c>
       <c r="E89">
         <v>2006</v>
@@ -23465,7 +23465,7 @@
         <v>49</v>
       </c>
       <c r="D91" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="E91">
         <v>2003</v>
@@ -23624,7 +23624,7 @@
         <v>49</v>
       </c>
       <c r="D94" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="E94">
         <v>2004</v>
@@ -23677,7 +23677,7 @@
         <v>49</v>
       </c>
       <c r="D95" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="E95">
         <v>2005</v>
@@ -23730,7 +23730,7 @@
         <v>49</v>
       </c>
       <c r="D96" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="E96">
         <v>2005</v>
@@ -23783,7 +23783,7 @@
         <v>49</v>
       </c>
       <c r="D97" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="E97">
         <v>2005</v>
@@ -23836,7 +23836,7 @@
         <v>49</v>
       </c>
       <c r="D98" t="s">
-        <v>74</v>
+        <v>53</v>
       </c>
       <c r="E98">
         <v>2004</v>
@@ -23889,7 +23889,7 @@
         <v>49</v>
       </c>
       <c r="D99" t="s">
-        <v>74</v>
+        <v>53</v>
       </c>
       <c r="E99">
         <v>2004</v>
@@ -23942,7 +23942,7 @@
         <v>49</v>
       </c>
       <c r="D100" t="s">
-        <v>74</v>
+        <v>53</v>
       </c>
       <c r="E100">
         <v>2004</v>
@@ -23995,7 +23995,7 @@
         <v>49</v>
       </c>
       <c r="D101" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E101">
         <v>2008</v>
@@ -24048,7 +24048,7 @@
         <v>49</v>
       </c>
       <c r="D102" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E102">
         <v>2008</v>
@@ -24101,7 +24101,7 @@
         <v>49</v>
       </c>
       <c r="D103" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E103">
         <v>2002</v>
@@ -24154,7 +24154,7 @@
         <v>49</v>
       </c>
       <c r="D104" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E104">
         <v>2002</v>
@@ -24207,7 +24207,7 @@
         <v>49</v>
       </c>
       <c r="D105" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E105">
         <v>2003</v>
@@ -24260,7 +24260,7 @@
         <v>49</v>
       </c>
       <c r="D106" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E106">
         <v>2003</v>
@@ -24313,7 +24313,7 @@
         <v>49</v>
       </c>
       <c r="D107" t="s">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="E107">
         <v>2000</v>
@@ -24366,7 +24366,7 @@
         <v>49</v>
       </c>
       <c r="D108" t="s">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="E108">
         <v>2000</v>
@@ -24472,7 +24472,7 @@
         <v>49</v>
       </c>
       <c r="D110" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="E110">
         <v>2023</v>
@@ -24525,7 +24525,7 @@
         <v>49</v>
       </c>
       <c r="D111" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="E111">
         <v>2001</v>
@@ -24631,7 +24631,7 @@
         <v>49</v>
       </c>
       <c r="D113" t="s">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="E113">
         <v>2010</v>
@@ -24684,7 +24684,7 @@
         <v>49</v>
       </c>
       <c r="D114" t="s">
-        <v>51</v>
+        <v>77</v>
       </c>
       <c r="E114">
         <v>2005</v>
@@ -24737,7 +24737,7 @@
         <v>49</v>
       </c>
       <c r="D115" t="s">
-        <v>51</v>
+        <v>77</v>
       </c>
       <c r="E115">
         <v>2009</v>
@@ -24790,7 +24790,7 @@
         <v>49</v>
       </c>
       <c r="D116" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="E116">
         <v>1997</v>
@@ -24843,7 +24843,7 @@
         <v>49</v>
       </c>
       <c r="D117" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="E117">
         <v>1997</v>
@@ -24896,7 +24896,7 @@
         <v>49</v>
       </c>
       <c r="D118" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="E118">
         <v>1998</v>
@@ -24949,7 +24949,7 @@
         <v>49</v>
       </c>
       <c r="D119" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="E119">
         <v>1999</v>
@@ -25055,7 +25055,7 @@
         <v>49</v>
       </c>
       <c r="D121" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="E121">
         <v>2010</v>
@@ -25108,7 +25108,7 @@
         <v>49</v>
       </c>
       <c r="D122" t="s">
-        <v>79</v>
+        <v>61</v>
       </c>
       <c r="E122">
         <v>2003</v>
@@ -25161,7 +25161,7 @@
         <v>49</v>
       </c>
       <c r="D123" t="s">
-        <v>79</v>
+        <v>61</v>
       </c>
       <c r="E123">
         <v>2003</v>
@@ -25214,7 +25214,7 @@
         <v>49</v>
       </c>
       <c r="D124" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E124">
         <v>2006</v>
@@ -25479,7 +25479,7 @@
         <v>49</v>
       </c>
       <c r="D129" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="E129">
         <v>2010</v>
@@ -25532,7 +25532,7 @@
         <v>49</v>
       </c>
       <c r="D130" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="E130">
         <v>2010</v>
@@ -25585,7 +25585,7 @@
         <v>49</v>
       </c>
       <c r="D131" t="s">
-        <v>53</v>
+        <v>84</v>
       </c>
       <c r="E131">
         <v>2008</v>
@@ -25638,7 +25638,7 @@
         <v>49</v>
       </c>
       <c r="D132" t="s">
-        <v>53</v>
+        <v>84</v>
       </c>
       <c r="E132">
         <v>2008</v>
@@ -25691,7 +25691,7 @@
         <v>49</v>
       </c>
       <c r="D133" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="E133">
         <v>2018</v>
@@ -25744,7 +25744,7 @@
         <v>49</v>
       </c>
       <c r="D134" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="E134">
         <v>2006</v>
@@ -25797,7 +25797,7 @@
         <v>49</v>
       </c>
       <c r="D135" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="E135">
         <v>2007</v>
@@ -25956,7 +25956,7 @@
         <v>49</v>
       </c>
       <c r="D138" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E138">
         <v>2010</v>
@@ -26009,7 +26009,7 @@
         <v>49</v>
       </c>
       <c r="D139" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E139">
         <v>2010</v>
@@ -26062,7 +26062,7 @@
         <v>49</v>
       </c>
       <c r="D140" t="s">
-        <v>58</v>
+        <v>85</v>
       </c>
       <c r="E140">
         <v>2004</v>
@@ -26115,7 +26115,7 @@
         <v>49</v>
       </c>
       <c r="D141" t="s">
-        <v>58</v>
+        <v>85</v>
       </c>
       <c r="E141">
         <v>2004</v>
@@ -26168,7 +26168,7 @@
         <v>49</v>
       </c>
       <c r="D142" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="E142">
         <v>2008</v>
@@ -26221,7 +26221,7 @@
         <v>49</v>
       </c>
       <c r="D143" t="s">
-        <v>76</v>
+        <v>51</v>
       </c>
       <c r="E143">
         <v>2007</v>
@@ -26274,7 +26274,7 @@
         <v>49</v>
       </c>
       <c r="D144" t="s">
-        <v>76</v>
+        <v>51</v>
       </c>
       <c r="E144">
         <v>2007</v>
@@ -26433,7 +26433,7 @@
         <v>49</v>
       </c>
       <c r="D147" t="s">
-        <v>73</v>
+        <v>62</v>
       </c>
       <c r="E147">
         <v>2015</v>
@@ -26486,7 +26486,7 @@
         <v>49</v>
       </c>
       <c r="D148" t="s">
-        <v>73</v>
+        <v>62</v>
       </c>
       <c r="E148">
         <v>2004</v>
@@ -26539,7 +26539,7 @@
         <v>49</v>
       </c>
       <c r="D149" t="s">
-        <v>50</v>
+        <v>79</v>
       </c>
       <c r="E149">
         <v>2006</v>
@@ -26645,7 +26645,7 @@
         <v>49</v>
       </c>
       <c r="D151" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E151">
         <v>2004</v>
@@ -26698,7 +26698,7 @@
         <v>49</v>
       </c>
       <c r="D152" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E152">
         <v>2005</v>
@@ -26751,7 +26751,7 @@
         <v>49</v>
       </c>
       <c r="D153" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E153">
         <v>2006</v>
@@ -26804,7 +26804,7 @@
         <v>49</v>
       </c>
       <c r="D154" t="s">
-        <v>75</v>
+        <v>52</v>
       </c>
       <c r="E154">
         <v>2008</v>
@@ -26857,7 +26857,7 @@
         <v>49</v>
       </c>
       <c r="D155" t="s">
-        <v>52</v>
+        <v>83</v>
       </c>
       <c r="E155">
         <v>2007</v>
@@ -26963,7 +26963,7 @@
         <v>49</v>
       </c>
       <c r="D157" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="E157">
         <v>2023</v>
@@ -27016,7 +27016,7 @@
         <v>49</v>
       </c>
       <c r="D158" t="s">
-        <v>86</v>
+        <v>69</v>
       </c>
       <c r="E158">
         <v>2026</v>
@@ -27069,7 +27069,7 @@
         <v>49</v>
       </c>
       <c r="D159" t="s">
-        <v>75</v>
+        <v>52</v>
       </c>
       <c r="E159">
         <v>2022</v>
@@ -27122,7 +27122,7 @@
         <v>49</v>
       </c>
       <c r="D160" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E160">
         <v>2003</v>
@@ -27175,7 +27175,7 @@
         <v>49</v>
       </c>
       <c r="D161" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E161">
         <v>2003</v>
@@ -27228,7 +27228,7 @@
         <v>49</v>
       </c>
       <c r="D162" t="s">
-        <v>79</v>
+        <v>61</v>
       </c>
       <c r="E162">
         <v>2003</v>
@@ -27281,7 +27281,7 @@
         <v>49</v>
       </c>
       <c r="D163" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="E163">
         <v>2008</v>
@@ -27334,7 +27334,7 @@
         <v>49</v>
       </c>
       <c r="D164" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="E164">
         <v>1999</v>
@@ -27387,7 +27387,7 @@
         <v>49</v>
       </c>
       <c r="D165" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="E165">
         <v>1999</v>
@@ -27440,7 +27440,7 @@
         <v>49</v>
       </c>
       <c r="D166" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="E166">
         <v>1997</v>
@@ -27546,7 +27546,7 @@
         <v>49</v>
       </c>
       <c r="D168" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="E168">
         <v>2001</v>
@@ -27599,7 +27599,7 @@
         <v>49</v>
       </c>
       <c r="D169" t="s">
-        <v>74</v>
+        <v>53</v>
       </c>
       <c r="E169">
         <v>2006</v>
@@ -27705,7 +27705,7 @@
         <v>49</v>
       </c>
       <c r="D171" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="E171">
         <v>2007</v>
@@ -28288,7 +28288,7 @@
         <v>49</v>
       </c>
       <c r="D182" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="E182">
         <v>2015</v>
@@ -29083,7 +29083,7 @@
         <v>49</v>
       </c>
       <c r="D197" t="s">
-        <v>75</v>
+        <v>52</v>
       </c>
       <c r="E197">
         <v>2004</v>
@@ -29136,7 +29136,7 @@
         <v>49</v>
       </c>
       <c r="D198" t="s">
-        <v>75</v>
+        <v>52</v>
       </c>
       <c r="E198">
         <v>2008</v>
@@ -29348,7 +29348,7 @@
         <v>49</v>
       </c>
       <c r="D202" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="E202">
         <v>2005</v>
@@ -29401,7 +29401,7 @@
         <v>49</v>
       </c>
       <c r="D203" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="E203">
         <v>2015</v>
@@ -30090,7 +30090,7 @@
         <v>49</v>
       </c>
       <c r="D216" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E216">
         <v>2022</v>
@@ -30302,7 +30302,7 @@
         <v>49</v>
       </c>
       <c r="D220" t="s">
-        <v>86</v>
+        <v>69</v>
       </c>
       <c r="E220">
         <v>2009</v>
@@ -30991,7 +30991,7 @@
         <v>49</v>
       </c>
       <c r="D233" t="s">
-        <v>58</v>
+        <v>85</v>
       </c>
       <c r="E233">
         <v>1994</v>
@@ -31150,7 +31150,7 @@
         <v>49</v>
       </c>
       <c r="D236" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E236">
         <v>1990</v>
@@ -31203,7 +31203,7 @@
         <v>49</v>
       </c>
       <c r="D237" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E237">
         <v>2022</v>
@@ -31362,7 +31362,7 @@
         <v>49</v>
       </c>
       <c r="D240" t="s">
-        <v>51</v>
+        <v>77</v>
       </c>
       <c r="E240">
         <v>2006</v>
@@ -31468,7 +31468,7 @@
         <v>49</v>
       </c>
       <c r="D242" t="s">
-        <v>73</v>
+        <v>62</v>
       </c>
       <c r="E242">
         <v>2023</v>
@@ -31521,7 +31521,7 @@
         <v>49</v>
       </c>
       <c r="D243" t="s">
-        <v>73</v>
+        <v>62</v>
       </c>
       <c r="E243">
         <v>2023</v>
@@ -31574,7 +31574,7 @@
         <v>49</v>
       </c>
       <c r="D244" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="E244">
         <v>1997</v>
@@ -32051,7 +32051,7 @@
         <v>49</v>
       </c>
       <c r="D253" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E253">
         <v>2008</v>
@@ -32316,7 +32316,7 @@
         <v>49</v>
       </c>
       <c r="D258" t="s">
-        <v>73</v>
+        <v>62</v>
       </c>
       <c r="E258">
         <v>2015</v>
@@ -32422,7 +32422,7 @@
         <v>49</v>
       </c>
       <c r="D260" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="E260">
         <v>2004</v>
@@ -32687,7 +32687,7 @@
         <v>49</v>
       </c>
       <c r="D265" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="E265">
         <v>2024</v>
@@ -32793,7 +32793,7 @@
         <v>49</v>
       </c>
       <c r="D267" t="s">
-        <v>50</v>
+        <v>79</v>
       </c>
       <c r="E267">
         <v>2023</v>
@@ -33005,7 +33005,7 @@
         <v>49</v>
       </c>
       <c r="D271" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="E271">
         <v>1975</v>
@@ -33058,7 +33058,7 @@
         <v>49</v>
       </c>
       <c r="D272" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="E272">
         <v>1975</v>
@@ -33111,7 +33111,7 @@
         <v>49</v>
       </c>
       <c r="D273" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="E273">
         <v>1975</v>
@@ -33164,7 +33164,7 @@
         <v>49</v>
       </c>
       <c r="D274" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="E274">
         <v>2015</v>
@@ -33217,7 +33217,7 @@
         <v>49</v>
       </c>
       <c r="D275" t="s">
-        <v>84</v>
+        <v>70</v>
       </c>
       <c r="E275">
         <v>1967</v>
@@ -33270,7 +33270,7 @@
         <v>49</v>
       </c>
       <c r="D276" t="s">
-        <v>84</v>
+        <v>70</v>
       </c>
       <c r="E276">
         <v>1971</v>
@@ -33323,7 +33323,7 @@
         <v>49</v>
       </c>
       <c r="D277" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="E277">
         <v>1970</v>
@@ -33376,7 +33376,7 @@
         <v>49</v>
       </c>
       <c r="D278" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E278">
         <v>1978</v>
@@ -33429,7 +33429,7 @@
         <v>49</v>
       </c>
       <c r="D279" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E279">
         <v>1981</v>
@@ -33482,7 +33482,7 @@
         <v>49</v>
       </c>
       <c r="D280" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E280">
         <v>1987</v>
@@ -33906,7 +33906,7 @@
         <v>293</v>
       </c>
       <c r="D288" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="E288">
         <v>1991</v>
@@ -33959,7 +33959,7 @@
         <v>293</v>
       </c>
       <c r="D289" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="E289">
         <v>1991</v>
@@ -35019,25 +35019,25 @@
         <v>308</v>
       </c>
       <c r="D309" t="s">
-        <v>99</v>
+        <v>193</v>
       </c>
       <c r="E309">
         <v>2022</v>
       </c>
       <c r="F309">
-        <v>0.29181095970158766</v>
+        <v>0.61052976624370348</v>
       </c>
       <c r="G309">
         <v>1</v>
       </c>
       <c r="H309">
-        <v>3162.5000000000005</v>
+        <v>2750</v>
       </c>
       <c r="I309">
-        <v>60.500000000000014</v>
+        <v>55.000000000000007</v>
       </c>
       <c r="J309">
-        <v>2.3100000000000005</v>
+        <v>2.1</v>
       </c>
       <c r="K309">
         <v>100</v>
@@ -35078,19 +35078,19 @@
         <v>2022</v>
       </c>
       <c r="F310">
-        <v>0.54140443556717466</v>
+        <v>6.0310691194286808E-2</v>
       </c>
       <c r="G310">
         <v>1</v>
       </c>
       <c r="H310">
-        <v>2750</v>
+        <v>3162.5000000000005</v>
       </c>
       <c r="I310">
-        <v>55.000000000000007</v>
+        <v>60.500000000000014</v>
       </c>
       <c r="J310">
-        <v>2.1</v>
+        <v>2.3100000000000005</v>
       </c>
       <c r="K310">
         <v>100</v>
@@ -35131,7 +35131,7 @@
         <v>2022</v>
       </c>
       <c r="F311">
-        <v>0.10670353057450742</v>
+        <v>0.10067246145507874</v>
       </c>
       <c r="G311">
         <v>1</v>
@@ -35184,7 +35184,7 @@
         <v>2022</v>
       </c>
       <c r="F312">
-        <v>4.3145340623605172E-2</v>
+        <v>4.4073197411209589E-2</v>
       </c>
       <c r="G312">
         <v>1</v>
@@ -35237,7 +35237,7 @@
         <v>2022</v>
       </c>
       <c r="F313">
-        <v>0.11134281451252948</v>
+        <v>8.7682466428616976E-2</v>
       </c>
       <c r="G313">
         <v>1</v>
@@ -35246,7 +35246,7 @@
         <v>3162.5000000000005</v>
       </c>
       <c r="I313">
-        <v>60.500000000000014</v>
+        <v>60.500000000000007</v>
       </c>
       <c r="J313">
         <v>2.3100000000000005</v>
@@ -35290,7 +35290,7 @@
         <v>2022</v>
       </c>
       <c r="F314">
-        <v>0.10067246145507874</v>
+        <v>0.15541601192373908</v>
       </c>
       <c r="G314">
         <v>1</v>
@@ -35337,13 +35337,13 @@
         <v>308</v>
       </c>
       <c r="D315" t="s">
-        <v>313</v>
+        <v>21</v>
       </c>
       <c r="E315">
         <v>2022</v>
       </c>
       <c r="F315">
-        <v>5.8918906012880183E-2</v>
+        <v>0.11134281451252948</v>
       </c>
       <c r="G315">
         <v>1</v>
@@ -35352,7 +35352,7 @@
         <v>3162.5000000000005</v>
       </c>
       <c r="I315">
-        <v>60.500000000000021</v>
+        <v>60.500000000000014</v>
       </c>
       <c r="J315">
         <v>2.3100000000000005</v>
@@ -35390,13 +35390,13 @@
         <v>308</v>
       </c>
       <c r="D316" t="s">
-        <v>314</v>
+        <v>99</v>
       </c>
       <c r="E316">
         <v>2022</v>
       </c>
       <c r="F316">
-        <v>5.1032123318242681E-2</v>
+        <v>0.29181095970158766</v>
       </c>
       <c r="G316">
         <v>1</v>
@@ -35405,7 +35405,7 @@
         <v>3162.5000000000005</v>
       </c>
       <c r="I316">
-        <v>60.500000000000021</v>
+        <v>60.500000000000014</v>
       </c>
       <c r="J316">
         <v>2.3100000000000005</v>
@@ -35443,25 +35443,25 @@
         <v>308</v>
       </c>
       <c r="D317" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="E317">
         <v>2022</v>
       </c>
       <c r="F317">
-        <v>0.20320063648536632</v>
+        <v>4.1753555442198553E-2</v>
       </c>
       <c r="G317">
         <v>1</v>
       </c>
       <c r="H317">
-        <v>3162.5000000000005</v>
+        <v>3712.5000000000005</v>
       </c>
       <c r="I317">
-        <v>60.500000000000014</v>
+        <v>71.5</v>
       </c>
       <c r="J317">
-        <v>2.3100000000000005</v>
+        <v>2.52</v>
       </c>
       <c r="K317">
         <v>100</v>
@@ -35496,13 +35496,13 @@
         <v>308</v>
       </c>
       <c r="D318" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="E318">
         <v>2022</v>
       </c>
       <c r="F318">
-        <v>1.0883760118599757</v>
+        <v>0.35629700644009438</v>
       </c>
       <c r="G318">
         <v>1</v>
@@ -35511,7 +35511,7 @@
         <v>2750</v>
       </c>
       <c r="I318">
-        <v>55.000000000000007</v>
+        <v>55</v>
       </c>
       <c r="J318">
         <v>2.1</v>
@@ -35549,25 +35549,25 @@
         <v>308</v>
       </c>
       <c r="D319" t="s">
-        <v>151</v>
+        <v>64</v>
       </c>
       <c r="E319">
         <v>2022</v>
       </c>
       <c r="F319">
-        <v>4.5464982592616207E-2</v>
+        <v>5.4743550468660328E-2</v>
       </c>
       <c r="G319">
         <v>1</v>
       </c>
       <c r="H319">
-        <v>3712.5000000000005</v>
+        <v>3162.5000000000005</v>
       </c>
       <c r="I319">
-        <v>71.5</v>
+        <v>60.500000000000014</v>
       </c>
       <c r="J319">
-        <v>2.52</v>
+        <v>2.3100000000000005</v>
       </c>
       <c r="K319">
         <v>100</v>
@@ -35602,25 +35602,25 @@
         <v>308</v>
       </c>
       <c r="D320" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="E320">
         <v>2022</v>
       </c>
       <c r="F320">
-        <v>4.4073197411209589E-2</v>
+        <v>6.3558189950902247E-2</v>
       </c>
       <c r="G320">
         <v>1</v>
       </c>
       <c r="H320">
-        <v>3712.5000000000005</v>
+        <v>3162.5000000000005</v>
       </c>
       <c r="I320">
-        <v>71.5</v>
+        <v>60.500000000000014</v>
       </c>
       <c r="J320">
-        <v>2.52</v>
+        <v>2.3100000000000005</v>
       </c>
       <c r="K320">
         <v>100</v>
@@ -35655,13 +35655,13 @@
         <v>308</v>
       </c>
       <c r="D321" t="s">
-        <v>318</v>
+        <v>204</v>
       </c>
       <c r="E321">
         <v>2022</v>
       </c>
       <c r="F321">
-        <v>6.9589259070330922E-2</v>
+        <v>7.8403898552572848E-2</v>
       </c>
       <c r="G321">
         <v>1</v>
@@ -35670,7 +35670,7 @@
         <v>3162.5000000000005</v>
       </c>
       <c r="I321">
-        <v>60.500000000000007</v>
+        <v>60.500000000000014</v>
       </c>
       <c r="J321">
         <v>2.3100000000000005</v>
@@ -35708,25 +35708,25 @@
         <v>308</v>
       </c>
       <c r="D322" t="s">
-        <v>71</v>
+        <v>316</v>
       </c>
       <c r="E322">
         <v>2022</v>
       </c>
       <c r="F322">
-        <v>0.50939337639482241</v>
+        <v>0.19299421182171778</v>
       </c>
       <c r="G322">
         <v>1</v>
       </c>
       <c r="H322">
-        <v>2750</v>
+        <v>3162.5000000000005</v>
       </c>
       <c r="I322">
-        <v>55.000000000000007</v>
+        <v>60.500000000000014</v>
       </c>
       <c r="J322">
-        <v>2.1</v>
+        <v>2.3100000000000005</v>
       </c>
       <c r="K322">
         <v>100</v>
@@ -35761,13 +35761,13 @@
         <v>308</v>
       </c>
       <c r="D323" t="s">
-        <v>291</v>
+        <v>239</v>
       </c>
       <c r="E323">
         <v>2022</v>
       </c>
       <c r="F323">
-        <v>0.13082780705222213</v>
+        <v>0.22871669814448767</v>
       </c>
       <c r="G323">
         <v>1</v>
@@ -35814,13 +35814,13 @@
         <v>308</v>
       </c>
       <c r="D324" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="E324">
         <v>2022</v>
       </c>
       <c r="F324">
-        <v>0.35629700644009438</v>
+        <v>1.0883760118599757</v>
       </c>
       <c r="G324">
         <v>1</v>
@@ -35829,7 +35829,7 @@
         <v>2750</v>
       </c>
       <c r="I324">
-        <v>55</v>
+        <v>55.000000000000007</v>
       </c>
       <c r="J324">
         <v>2.1</v>
@@ -35867,13 +35867,13 @@
         <v>308</v>
       </c>
       <c r="D325" t="s">
-        <v>14</v>
+        <v>318</v>
       </c>
       <c r="E325">
         <v>2022</v>
       </c>
       <c r="F325">
-        <v>8.7682466428616976E-2</v>
+        <v>0.1577356538927501</v>
       </c>
       <c r="G325">
         <v>1</v>
@@ -35882,7 +35882,7 @@
         <v>3162.5000000000005</v>
       </c>
       <c r="I325">
-        <v>60.500000000000007</v>
+        <v>60.500000000000014</v>
       </c>
       <c r="J325">
         <v>2.3100000000000005</v>
@@ -35920,13 +35920,13 @@
         <v>308</v>
       </c>
       <c r="D326" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="E326">
         <v>2022</v>
       </c>
       <c r="F326">
-        <v>0.1577356538927501</v>
+        <v>5.1032123318242681E-2</v>
       </c>
       <c r="G326">
         <v>1</v>
@@ -35935,7 +35935,7 @@
         <v>3162.5000000000005</v>
       </c>
       <c r="I326">
-        <v>60.500000000000014</v>
+        <v>60.500000000000021</v>
       </c>
       <c r="J326">
         <v>2.3100000000000005</v>
@@ -35973,13 +35973,13 @@
         <v>308</v>
       </c>
       <c r="D327" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="E327">
         <v>2022</v>
       </c>
       <c r="F327">
-        <v>0.15541601192373908</v>
+        <v>0.13036387865841995</v>
       </c>
       <c r="G327">
         <v>1</v>
@@ -36026,25 +36026,25 @@
         <v>308</v>
       </c>
       <c r="D328" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="E328">
         <v>2022</v>
       </c>
       <c r="F328">
-        <v>4.1753555442198553E-2</v>
+        <v>0.57944656385895543</v>
       </c>
       <c r="G328">
         <v>1</v>
       </c>
       <c r="H328">
-        <v>3712.5000000000005</v>
+        <v>2750</v>
       </c>
       <c r="I328">
-        <v>71.5</v>
+        <v>55.000000000000007</v>
       </c>
       <c r="J328">
-        <v>2.52</v>
+        <v>2.1</v>
       </c>
       <c r="K328">
         <v>100</v>
@@ -36079,25 +36079,25 @@
         <v>308</v>
       </c>
       <c r="D329" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="E329">
         <v>2022</v>
       </c>
       <c r="F329">
-        <v>0.13036387865841995</v>
+        <v>4.4073197411209589E-2</v>
       </c>
       <c r="G329">
         <v>1</v>
       </c>
       <c r="H329">
-        <v>3162.5000000000005</v>
+        <v>3712.5000000000005</v>
       </c>
       <c r="I329">
-        <v>60.500000000000014</v>
+        <v>71.5</v>
       </c>
       <c r="J329">
-        <v>2.3100000000000005</v>
+        <v>2.52</v>
       </c>
       <c r="K329">
         <v>100</v>
@@ -36132,25 +36132,25 @@
         <v>308</v>
       </c>
       <c r="D330" t="s">
-        <v>324</v>
+        <v>291</v>
       </c>
       <c r="E330">
         <v>2022</v>
       </c>
       <c r="F330">
-        <v>0.57944656385895543</v>
+        <v>0.13082780705222213</v>
       </c>
       <c r="G330">
         <v>1</v>
       </c>
       <c r="H330">
-        <v>2750</v>
+        <v>3162.5000000000005</v>
       </c>
       <c r="I330">
-        <v>55.000000000000007</v>
+        <v>60.500000000000014</v>
       </c>
       <c r="J330">
-        <v>2.1</v>
+        <v>2.3100000000000005</v>
       </c>
       <c r="K330">
         <v>100</v>
@@ -36185,13 +36185,13 @@
         <v>308</v>
       </c>
       <c r="D331" t="s">
-        <v>55</v>
+        <v>323</v>
       </c>
       <c r="E331">
         <v>2022</v>
       </c>
       <c r="F331">
-        <v>0.23196419690110309</v>
+        <v>6.9589259070330922E-2</v>
       </c>
       <c r="G331">
         <v>1</v>
@@ -36200,7 +36200,7 @@
         <v>3162.5000000000005</v>
       </c>
       <c r="I331">
-        <v>60.500000000000014</v>
+        <v>60.500000000000007</v>
       </c>
       <c r="J331">
         <v>2.3100000000000005</v>
@@ -36238,25 +36238,25 @@
         <v>308</v>
       </c>
       <c r="D332" t="s">
-        <v>204</v>
+        <v>75</v>
       </c>
       <c r="E332">
         <v>2022</v>
       </c>
       <c r="F332">
-        <v>7.8403898552572848E-2</v>
+        <v>0.50939337639482241</v>
       </c>
       <c r="G332">
         <v>1</v>
       </c>
       <c r="H332">
-        <v>3162.5000000000005</v>
+        <v>2750</v>
       </c>
       <c r="I332">
-        <v>60.500000000000014</v>
+        <v>55.000000000000007</v>
       </c>
       <c r="J332">
-        <v>2.3100000000000005</v>
+        <v>2.1</v>
       </c>
       <c r="K332">
         <v>100</v>
@@ -36291,13 +36291,13 @@
         <v>308</v>
       </c>
       <c r="D333" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="E333">
         <v>2022</v>
       </c>
       <c r="F333">
-        <v>0.19299421182171778</v>
+        <v>0.10670353057450742</v>
       </c>
       <c r="G333">
         <v>1</v>
@@ -36344,13 +36344,13 @@
         <v>308</v>
       </c>
       <c r="D334" t="s">
-        <v>326</v>
+        <v>63</v>
       </c>
       <c r="E334">
         <v>2022</v>
       </c>
       <c r="F334">
-        <v>6.3558189950902247E-2</v>
+        <v>0.23196419690110309</v>
       </c>
       <c r="G334">
         <v>1</v>
@@ -36397,25 +36397,25 @@
         <v>308</v>
       </c>
       <c r="D335" t="s">
-        <v>193</v>
+        <v>325</v>
       </c>
       <c r="E335">
         <v>2022</v>
       </c>
       <c r="F335">
-        <v>0.61052976624370348</v>
+        <v>5.8918906012880183E-2</v>
       </c>
       <c r="G335">
         <v>1</v>
       </c>
       <c r="H335">
-        <v>2750</v>
+        <v>3162.5000000000005</v>
       </c>
       <c r="I335">
-        <v>55.000000000000007</v>
+        <v>60.500000000000021</v>
       </c>
       <c r="J335">
-        <v>2.1</v>
+        <v>2.3100000000000005</v>
       </c>
       <c r="K335">
         <v>100</v>
@@ -36450,13 +36450,13 @@
         <v>308</v>
       </c>
       <c r="D336" t="s">
-        <v>327</v>
+        <v>151</v>
       </c>
       <c r="E336">
         <v>2022</v>
       </c>
       <c r="F336">
-        <v>4.4073197411209589E-2</v>
+        <v>4.5464982592616207E-2</v>
       </c>
       <c r="G336">
         <v>1</v>
@@ -36503,25 +36503,25 @@
         <v>308</v>
       </c>
       <c r="D337" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="E337">
         <v>2022</v>
       </c>
       <c r="F337">
-        <v>6.0310691194286808E-2</v>
+        <v>0.56367299846968055</v>
       </c>
       <c r="G337">
         <v>1</v>
       </c>
       <c r="H337">
-        <v>3162.5000000000005</v>
+        <v>2750</v>
       </c>
       <c r="I337">
-        <v>60.500000000000014</v>
+        <v>55.000000000000007</v>
       </c>
       <c r="J337">
-        <v>2.3100000000000005</v>
+        <v>2.1</v>
       </c>
       <c r="K337">
         <v>100</v>
@@ -36556,25 +36556,25 @@
         <v>308</v>
       </c>
       <c r="D338" t="s">
-        <v>239</v>
+        <v>327</v>
       </c>
       <c r="E338">
         <v>2022</v>
       </c>
       <c r="F338">
-        <v>0.22871669814448767</v>
+        <v>0.54140443556717466</v>
       </c>
       <c r="G338">
         <v>1</v>
       </c>
       <c r="H338">
-        <v>3162.5000000000005</v>
+        <v>2750</v>
       </c>
       <c r="I338">
-        <v>60.500000000000014</v>
+        <v>55.000000000000007</v>
       </c>
       <c r="J338">
-        <v>2.3100000000000005</v>
+        <v>2.1</v>
       </c>
       <c r="K338">
         <v>100</v>
@@ -36609,13 +36609,13 @@
         <v>308</v>
       </c>
       <c r="D339" t="s">
-        <v>63</v>
+        <v>328</v>
       </c>
       <c r="E339">
         <v>2022</v>
       </c>
       <c r="F339">
-        <v>5.4743550468660328E-2</v>
+        <v>0.20320063648536632</v>
       </c>
       <c r="G339">
         <v>1</v>
@@ -36668,19 +36668,19 @@
         <v>2022</v>
       </c>
       <c r="F340">
-        <v>0.56367299846968055</v>
+        <v>4.3145340623605172E-2</v>
       </c>
       <c r="G340">
         <v>1</v>
       </c>
       <c r="H340">
-        <v>2750</v>
+        <v>3712.5000000000005</v>
       </c>
       <c r="I340">
-        <v>55.000000000000007</v>
+        <v>71.5</v>
       </c>
       <c r="J340">
-        <v>2.1</v>
+        <v>2.52</v>
       </c>
       <c r="K340">
         <v>100</v>
@@ -36768,7 +36768,7 @@
         <v>308</v>
       </c>
       <c r="D342" t="s">
-        <v>327</v>
+        <v>322</v>
       </c>
       <c r="E342">
         <v>1959</v>
@@ -36874,7 +36874,7 @@
         <v>308</v>
       </c>
       <c r="D344" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="E344">
         <v>1973</v>
@@ -36980,7 +36980,7 @@
         <v>308</v>
       </c>
       <c r="D346" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="E346">
         <v>1963</v>
@@ -37033,7 +37033,7 @@
         <v>308</v>
       </c>
       <c r="D347" t="s">
-        <v>325</v>
+        <v>316</v>
       </c>
       <c r="E347">
         <v>2015</v>
@@ -37086,7 +37086,7 @@
         <v>308</v>
       </c>
       <c r="D348" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="E348">
         <v>1931</v>
@@ -37139,7 +37139,7 @@
         <v>308</v>
       </c>
       <c r="D349" t="s">
-        <v>309</v>
+        <v>327</v>
       </c>
       <c r="E349">
         <v>1949</v>
@@ -37192,7 +37192,7 @@
         <v>308</v>
       </c>
       <c r="D350" t="s">
-        <v>319</v>
+        <v>314</v>
       </c>
       <c r="E350">
         <v>1951</v>
@@ -37298,7 +37298,7 @@
         <v>308</v>
       </c>
       <c r="D352" t="s">
-        <v>328</v>
+        <v>309</v>
       </c>
       <c r="E352">
         <v>1958</v>
@@ -37351,7 +37351,7 @@
         <v>308</v>
       </c>
       <c r="D353" t="s">
-        <v>310</v>
+        <v>324</v>
       </c>
       <c r="E353">
         <v>1967</v>
@@ -37404,7 +37404,7 @@
         <v>308</v>
       </c>
       <c r="D354" t="s">
-        <v>315</v>
+        <v>328</v>
       </c>
       <c r="E354">
         <v>1968</v>
@@ -37457,7 +37457,7 @@
         <v>308</v>
       </c>
       <c r="D355" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="E355">
         <v>1929</v>
@@ -37510,7 +37510,7 @@
         <v>308</v>
       </c>
       <c r="D356" t="s">
-        <v>315</v>
+        <v>328</v>
       </c>
       <c r="E356">
         <v>1949</v>
@@ -37616,7 +37616,7 @@
         <v>308</v>
       </c>
       <c r="D358" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E358">
         <v>1952</v>
@@ -37669,7 +37669,7 @@
         <v>308</v>
       </c>
       <c r="D359" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="E359">
         <v>1913</v>
@@ -37722,7 +37722,7 @@
         <v>308</v>
       </c>
       <c r="D360" t="s">
-        <v>319</v>
+        <v>314</v>
       </c>
       <c r="E360">
         <v>1924</v>
@@ -37828,7 +37828,7 @@
         <v>308</v>
       </c>
       <c r="D362" t="s">
-        <v>319</v>
+        <v>314</v>
       </c>
       <c r="E362">
         <v>1971</v>
@@ -37934,7 +37934,7 @@
         <v>308</v>
       </c>
       <c r="D364" t="s">
-        <v>311</v>
+        <v>329</v>
       </c>
       <c r="E364">
         <v>1927</v>
@@ -37987,7 +37987,7 @@
         <v>308</v>
       </c>
       <c r="D365" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="E365">
         <v>1928</v>
@@ -38093,7 +38093,7 @@
         <v>308</v>
       </c>
       <c r="D367" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="E367">
         <v>1938</v>
@@ -38146,7 +38146,7 @@
         <v>308</v>
       </c>
       <c r="D368" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="E368">
         <v>1920</v>
@@ -38199,7 +38199,7 @@
         <v>308</v>
       </c>
       <c r="D369" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="E369">
         <v>1947</v>
@@ -38252,7 +38252,7 @@
         <v>308</v>
       </c>
       <c r="D370" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="E370">
         <v>1950</v>
@@ -38305,7 +38305,7 @@
         <v>308</v>
       </c>
       <c r="D371" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="E371">
         <v>1954</v>
@@ -38411,7 +38411,7 @@
         <v>308</v>
       </c>
       <c r="D373" t="s">
-        <v>319</v>
+        <v>314</v>
       </c>
       <c r="E373">
         <v>1971</v>
@@ -38464,7 +38464,7 @@
         <v>308</v>
       </c>
       <c r="D374" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="E374">
         <v>1959</v>
@@ -38570,7 +38570,7 @@
         <v>308</v>
       </c>
       <c r="D376" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="E376">
         <v>1955</v>
@@ -38623,7 +38623,7 @@
         <v>308</v>
       </c>
       <c r="D377" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="E377">
         <v>1959</v>
@@ -38676,7 +38676,7 @@
         <v>308</v>
       </c>
       <c r="D378" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="E378">
         <v>1954</v>
@@ -38888,7 +38888,7 @@
         <v>308</v>
       </c>
       <c r="D382" t="s">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="E382">
         <v>2022</v>
@@ -39100,7 +39100,7 @@
         <v>308</v>
       </c>
       <c r="D386" t="s">
-        <v>73</v>
+        <v>62</v>
       </c>
       <c r="E386">
         <v>2022</v>
@@ -39206,7 +39206,7 @@
         <v>383</v>
       </c>
       <c r="D388" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="E388">
         <v>1989</v>
@@ -39259,7 +39259,7 @@
         <v>383</v>
       </c>
       <c r="D389" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="E389">
         <v>1975</v>
@@ -39312,7 +39312,7 @@
         <v>383</v>
       </c>
       <c r="D390" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="E390">
         <v>1966</v>
@@ -39365,7 +39365,7 @@
         <v>383</v>
       </c>
       <c r="D391" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="E391">
         <v>2015</v>
@@ -39418,7 +39418,7 @@
         <v>383</v>
       </c>
       <c r="D392" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="E392">
         <v>2015</v>
@@ -39471,7 +39471,7 @@
         <v>383</v>
       </c>
       <c r="D393" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="E393">
         <v>1982</v>
@@ -39524,7 +39524,7 @@
         <v>383</v>
       </c>
       <c r="D394" t="s">
-        <v>319</v>
+        <v>314</v>
       </c>
       <c r="E394">
         <v>2015</v>
@@ -39577,7 +39577,7 @@
         <v>383</v>
       </c>
       <c r="D395" t="s">
-        <v>326</v>
+        <v>315</v>
       </c>
       <c r="E395">
         <v>2015</v>
@@ -39630,7 +39630,7 @@
         <v>383</v>
       </c>
       <c r="D396" t="s">
-        <v>73</v>
+        <v>62</v>
       </c>
       <c r="E396">
         <v>1961</v>
@@ -39683,7 +39683,7 @@
         <v>383</v>
       </c>
       <c r="D397" t="s">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="E397">
         <v>2005</v>
@@ -39736,7 +39736,7 @@
         <v>383</v>
       </c>
       <c r="D398" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="E398">
         <v>1991</v>
@@ -39895,7 +39895,7 @@
         <v>383</v>
       </c>
       <c r="D401" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="E401">
         <v>1971</v>
@@ -39948,7 +39948,7 @@
         <v>383</v>
       </c>
       <c r="D402" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="E402">
         <v>1973</v>
@@ -40107,7 +40107,7 @@
         <v>383</v>
       </c>
       <c r="D405" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E405">
         <v>1978</v>
@@ -40160,7 +40160,7 @@
         <v>383</v>
       </c>
       <c r="D406" t="s">
-        <v>309</v>
+        <v>327</v>
       </c>
       <c r="E406">
         <v>1923</v>
@@ -40213,7 +40213,7 @@
         <v>308</v>
       </c>
       <c r="D407" t="s">
-        <v>313</v>
+        <v>325</v>
       </c>
       <c r="E407">
         <v>1959</v>
@@ -40319,7 +40319,7 @@
         <v>308</v>
       </c>
       <c r="D409" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="E409">
         <v>1949</v>
@@ -40372,7 +40372,7 @@
         <v>308</v>
       </c>
       <c r="D410" t="s">
-        <v>321</v>
+        <v>312</v>
       </c>
       <c r="E410">
         <v>1953</v>
@@ -40478,7 +40478,7 @@
         <v>308</v>
       </c>
       <c r="D412" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="E412">
         <v>1960</v>
@@ -40531,7 +40531,7 @@
         <v>308</v>
       </c>
       <c r="D413" t="s">
-        <v>322</v>
+        <v>313</v>
       </c>
       <c r="E413">
         <v>1962</v>
@@ -40584,7 +40584,7 @@
         <v>308</v>
       </c>
       <c r="D414" t="s">
-        <v>309</v>
+        <v>327</v>
       </c>
       <c r="E414">
         <v>2015</v>
@@ -40637,7 +40637,7 @@
         <v>308</v>
       </c>
       <c r="D415" t="s">
-        <v>315</v>
+        <v>328</v>
       </c>
       <c r="E415">
         <v>1927</v>
@@ -40690,7 +40690,7 @@
         <v>308</v>
       </c>
       <c r="D416" t="s">
-        <v>314</v>
+        <v>319</v>
       </c>
       <c r="E416">
         <v>1954</v>
@@ -40796,7 +40796,7 @@
         <v>308</v>
       </c>
       <c r="D418" t="s">
-        <v>309</v>
+        <v>327</v>
       </c>
       <c r="E418">
         <v>1956</v>
@@ -40849,7 +40849,7 @@
         <v>308</v>
       </c>
       <c r="D419" t="s">
-        <v>319</v>
+        <v>314</v>
       </c>
       <c r="E419">
         <v>1956</v>
@@ -40955,7 +40955,7 @@
         <v>308</v>
       </c>
       <c r="D421" t="s">
-        <v>309</v>
+        <v>327</v>
       </c>
       <c r="E421">
         <v>1960</v>
@@ -41061,7 +41061,7 @@
         <v>308</v>
       </c>
       <c r="D423" t="s">
-        <v>325</v>
+        <v>316</v>
       </c>
       <c r="E423">
         <v>2015</v>
@@ -41167,7 +41167,7 @@
         <v>308</v>
       </c>
       <c r="D425" t="s">
-        <v>315</v>
+        <v>328</v>
       </c>
       <c r="E425">
         <v>2015</v>
@@ -41220,7 +41220,7 @@
         <v>308</v>
       </c>
       <c r="D426" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="E426">
         <v>2015</v>
@@ -41326,7 +41326,7 @@
         <v>308</v>
       </c>
       <c r="D428" t="s">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="E428">
         <v>1955</v>
@@ -41379,7 +41379,7 @@
         <v>308</v>
       </c>
       <c r="D429" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="E429">
         <v>2015</v>
@@ -41485,7 +41485,7 @@
         <v>308</v>
       </c>
       <c r="D431" t="s">
-        <v>311</v>
+        <v>329</v>
       </c>
       <c r="E431">
         <v>1932</v>
@@ -41644,7 +41644,7 @@
         <v>308</v>
       </c>
       <c r="D434" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="E434">
         <v>1924</v>
@@ -41750,7 +41750,7 @@
         <v>308</v>
       </c>
       <c r="D436" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="E436">
         <v>2002</v>
@@ -41856,7 +41856,7 @@
         <v>308</v>
       </c>
       <c r="D438" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="E438">
         <v>1948</v>
@@ -41909,7 +41909,7 @@
         <v>308</v>
       </c>
       <c r="D439" t="s">
-        <v>325</v>
+        <v>316</v>
       </c>
       <c r="E439">
         <v>2015</v>
@@ -41962,7 +41962,7 @@
         <v>308</v>
       </c>
       <c r="D440" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="E440">
         <v>1914</v>
@@ -42068,7 +42068,7 @@
         <v>308</v>
       </c>
       <c r="D442" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E442">
         <v>1958</v>
@@ -42121,7 +42121,7 @@
         <v>439</v>
       </c>
       <c r="D443" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="E443">
         <v>1992</v>
@@ -42280,7 +42280,7 @@
         <v>439</v>
       </c>
       <c r="D446" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E446">
         <v>1992</v>
@@ -42598,7 +42598,7 @@
         <v>439</v>
       </c>
       <c r="D452" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="E452">
         <v>1985</v>
@@ -42922,7 +42922,7 @@
         <v>2022</v>
       </c>
       <c r="F458">
-        <v>6.6039408899415779</v>
+        <v>6.6457416582336482</v>
       </c>
       <c r="G458">
         <v>1</v>
@@ -42940,7 +42940,7 @@
         <v>33</v>
       </c>
       <c r="L458">
-        <v>0.20730554769553741</v>
+        <v>0.20730554769553747</v>
       </c>
       <c r="N458" t="s">
         <v>809</v>
@@ -42996,7 +42996,7 @@
         <v>33</v>
       </c>
       <c r="L459">
-        <v>0.20730554769553741</v>
+        <v>0.20730554769553747</v>
       </c>
       <c r="N459" t="s">
         <v>809</v>
@@ -43034,7 +43034,7 @@
         <v>2022</v>
       </c>
       <c r="F460">
-        <v>6.6457416582336482</v>
+        <v>6.6039408899415779</v>
       </c>
       <c r="G460">
         <v>1</v>
@@ -43052,7 +43052,7 @@
         <v>33</v>
       </c>
       <c r="L460">
-        <v>0.20730554769553741</v>
+        <v>0.20730554769553747</v>
       </c>
       <c r="N460" t="s">
         <v>809</v>
@@ -44876,7 +44876,7 @@
         <v>455</v>
       </c>
       <c r="D493" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="E493">
         <v>2015</v>
@@ -51156,7 +51156,7 @@
         <v>2022</v>
       </c>
       <c r="F618">
-        <v>0.6793056475905862</v>
+        <v>0.69928302455480262</v>
       </c>
       <c r="G618">
         <v>0.33123000000000002</v>
@@ -51179,7 +51179,7 @@
         <v>2022</v>
       </c>
       <c r="F619">
-        <v>0.67351932785461166</v>
+        <v>0.6793056475905862</v>
       </c>
       <c r="G619">
         <v>0.33123000000000002</v>
@@ -51202,7 +51202,7 @@
         <v>2022</v>
       </c>
       <c r="F620">
-        <v>0.69928302455480262</v>
+        <v>0.67351932785461166</v>
       </c>
       <c r="G620">
         <v>0.33123000000000002</v>
@@ -51449,7 +51449,7 @@
         <v>663</v>
       </c>
       <c r="D631" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="E631">
         <v>2018</v>

--- a/VerveStacks_ITA_grids/vt_vervestacks_ITA_v1.xlsx
+++ b/VerveStacks_ITA_grids/vt_vervestacks_ITA_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D3F0C473-25ED-43FB-AB82-EBAC97E4941B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{42129CE0-ACF3-4BA9-8079-71ABF5135AE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{1DDFC537-3BF2-47FF-8258-3FBB00AFD16C}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{759BFB8F-310B-4985-8F67-E13AE06D1BDA}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="2" r:id="rId1"/>
@@ -81,30 +81,30 @@
     <t>bioenergy</t>
   </si>
   <si>
+    <t>e_w144005863-380</t>
+  </si>
+  <si>
     <t>e_w58440884-380</t>
   </si>
   <si>
+    <t>e_w81938081-380</t>
+  </si>
+  <si>
+    <t>e_w34157795-380</t>
+  </si>
+  <si>
+    <t>e_w108020416-380</t>
+  </si>
+  <si>
+    <t>e_w109756016-380</t>
+  </si>
+  <si>
+    <t>e_w98902899-380</t>
+  </si>
+  <si>
     <t>e_w84696559-380</t>
   </si>
   <si>
-    <t>e_w109756016-380</t>
-  </si>
-  <si>
-    <t>e_w81938081-380</t>
-  </si>
-  <si>
-    <t>e_w98902899-380</t>
-  </si>
-  <si>
-    <t>e_w34157795-380</t>
-  </si>
-  <si>
-    <t>e_w108020416-380</t>
-  </si>
-  <si>
-    <t>e_w144005863-380</t>
-  </si>
-  <si>
     <t>ep_bioenergy_G100000200236</t>
   </si>
   <si>
@@ -141,18 +141,18 @@
     <t>coal</t>
   </si>
   <si>
+    <t>e_w418902800-380</t>
+  </si>
+  <si>
     <t>e_w303915533-380</t>
   </si>
   <si>
+    <t>e_w82767145-380</t>
+  </si>
+  <si>
     <t>e_w409439916-380</t>
   </si>
   <si>
-    <t>e_w82767145-380</t>
-  </si>
-  <si>
-    <t>e_w418902800-380</t>
-  </si>
-  <si>
     <t>ep_coal_subcritical_G100000102764</t>
   </si>
   <si>
@@ -189,120 +189,120 @@
     <t>gas</t>
   </si>
   <si>
+    <t>e_w110330925-380</t>
+  </si>
+  <si>
+    <t>e_w162828577-380</t>
+  </si>
+  <si>
+    <t>e_w98900549-380</t>
+  </si>
+  <si>
+    <t>e_w100407576-380</t>
+  </si>
+  <si>
+    <t>e_w149997403-380</t>
+  </si>
+  <si>
+    <t>e_w339104227-380</t>
+  </si>
+  <si>
+    <t>e_w181125039-380</t>
+  </si>
+  <si>
+    <t>e_w133601335-380</t>
+  </si>
+  <si>
+    <t>e_w103381531-380</t>
+  </si>
+  <si>
+    <t>e_w82084019-380</t>
+  </si>
+  <si>
+    <t>e_w432729521-380</t>
+  </si>
+  <si>
+    <t>e_w172302572-380</t>
+  </si>
+  <si>
+    <t>e_w99826025-380</t>
+  </si>
+  <si>
+    <t>e_w421827453-380</t>
+  </si>
+  <si>
+    <t>e_w416989699-380</t>
+  </si>
+  <si>
+    <t>e_w411026199-380</t>
+  </si>
+  <si>
+    <t>e_w107438024-380</t>
+  </si>
+  <si>
+    <t>e_w199675964-380</t>
+  </si>
+  <si>
+    <t>e_w60725875-380</t>
+  </si>
+  <si>
+    <t>e_w145665799-380</t>
+  </si>
+  <si>
+    <t>e_w338753171-380</t>
+  </si>
+  <si>
+    <t>e_w162960205-380</t>
+  </si>
+  <si>
+    <t>e_w158739183-380</t>
+  </si>
+  <si>
+    <t>e_w59462715-380</t>
+  </si>
+  <si>
+    <t>e_w103974940-380</t>
+  </si>
+  <si>
+    <t>e_w98421779-380</t>
+  </si>
+  <si>
+    <t>e_w419423704-380</t>
+  </si>
+  <si>
+    <t>e_w116797658-380</t>
+  </si>
+  <si>
+    <t>e_w82078641-380</t>
+  </si>
+  <si>
+    <t>e_w61157826-380</t>
+  </si>
+  <si>
+    <t>e_w105581403-380</t>
+  </si>
+  <si>
+    <t>e_w255011550-380</t>
+  </si>
+  <si>
+    <t>e_w414663585-380</t>
+  </si>
+  <si>
+    <t>e_w103653592-380</t>
+  </si>
+  <si>
+    <t>e_w109993642-380</t>
+  </si>
+  <si>
     <t>e_w105757794-380</t>
   </si>
   <si>
+    <t>e_w1137611914-380</t>
+  </si>
+  <si>
     <t>e_w132450233-380</t>
   </si>
   <si>
-    <t>e_w162828577-380</t>
-  </si>
-  <si>
-    <t>e_w98900549-380</t>
-  </si>
-  <si>
-    <t>e_w162960205-380</t>
-  </si>
-  <si>
-    <t>e_w199675964-380</t>
-  </si>
-  <si>
-    <t>e_w158739183-380</t>
-  </si>
-  <si>
-    <t>e_w103974940-380</t>
-  </si>
-  <si>
-    <t>e_w181125039-380</t>
-  </si>
-  <si>
-    <t>e_w133601335-380</t>
-  </si>
-  <si>
-    <t>e_w103381531-380</t>
-  </si>
-  <si>
-    <t>e_w82078641-380</t>
-  </si>
-  <si>
-    <t>e_w61157826-380</t>
-  </si>
-  <si>
-    <t>e_w338753171-380</t>
-  </si>
-  <si>
-    <t>e_w1137611914-380</t>
-  </si>
-  <si>
-    <t>e_w339104227-380</t>
-  </si>
-  <si>
-    <t>e_w414663585-380</t>
-  </si>
-  <si>
-    <t>e_w255011550-380</t>
-  </si>
-  <si>
-    <t>e_w105581403-380</t>
-  </si>
-  <si>
-    <t>e_w60725875-380</t>
-  </si>
-  <si>
-    <t>e_w145665799-380</t>
-  </si>
-  <si>
-    <t>e_w432729521-380</t>
-  </si>
-  <si>
-    <t>e_w172302572-380</t>
-  </si>
-  <si>
-    <t>e_w100407576-380</t>
-  </si>
-  <si>
-    <t>e_w98421779-380</t>
-  </si>
-  <si>
-    <t>e_w419423704-380</t>
-  </si>
-  <si>
-    <t>e_w116797658-380</t>
-  </si>
-  <si>
-    <t>e_w99826025-380</t>
-  </si>
-  <si>
-    <t>e_w416989699-380</t>
-  </si>
-  <si>
-    <t>e_w411026199-380</t>
-  </si>
-  <si>
-    <t>e_w149997403-380</t>
-  </si>
-  <si>
-    <t>e_w421827453-380</t>
-  </si>
-  <si>
-    <t>e_w59462715-380</t>
-  </si>
-  <si>
-    <t>e_w103653592-380</t>
-  </si>
-  <si>
-    <t>e_w109993642-380</t>
-  </si>
-  <si>
-    <t>e_w82084019-380</t>
-  </si>
-  <si>
-    <t>e_w107438024-380</t>
-  </si>
-  <si>
-    <t>e_w110330925-380</t>
-  </si>
-  <si>
     <t>ep_gas_combined_cycle_G100000400339</t>
   </si>
   <si>
@@ -966,69 +966,69 @@
     <t>hydro</t>
   </si>
   <si>
+    <t>e_w491424937-380</t>
+  </si>
+  <si>
+    <t>e_w61626687-380</t>
+  </si>
+  <si>
+    <t>e_w72466334-380</t>
+  </si>
+  <si>
+    <t>e_w114931087-380</t>
+  </si>
+  <si>
+    <t>e_IT10-380</t>
+  </si>
+  <si>
+    <t>e_IT7-380</t>
+  </si>
+  <si>
+    <t>e_w75602396-380</t>
+  </si>
+  <si>
+    <t>e_w1100665914-380</t>
+  </si>
+  <si>
+    <t>e_w82083756-380</t>
+  </si>
+  <si>
+    <t>e_IT71-380</t>
+  </si>
+  <si>
+    <t>e_IT31-380</t>
+  </si>
+  <si>
+    <t>e_IT21-380</t>
+  </si>
+  <si>
+    <t>e_w116517585-380</t>
+  </si>
+  <si>
+    <t>e_IT72-380</t>
+  </si>
+  <si>
+    <t>e_IT72-400</t>
+  </si>
+  <si>
+    <t>e_IT93-380</t>
+  </si>
+  <si>
     <t>e_IT71-400</t>
   </si>
   <si>
-    <t>e_IT72-380</t>
-  </si>
-  <si>
-    <t>e_IT72-400</t>
+    <t>e_IT53-380</t>
+  </si>
+  <si>
+    <t>e_w104359058-380</t>
   </si>
   <si>
     <t>e_IT36-380</t>
   </si>
   <si>
-    <t>e_w116517585-380</t>
-  </si>
-  <si>
-    <t>e_w82083756-380</t>
-  </si>
-  <si>
-    <t>e_IT53-380</t>
-  </si>
-  <si>
-    <t>e_w1100665914-380</t>
-  </si>
-  <si>
     <t>e_w64200868-380</t>
   </si>
   <si>
-    <t>e_w72466334-380</t>
-  </si>
-  <si>
-    <t>e_w61626687-380</t>
-  </si>
-  <si>
-    <t>e_w114931087-380</t>
-  </si>
-  <si>
-    <t>e_w104359058-380</t>
-  </si>
-  <si>
-    <t>e_IT31-380</t>
-  </si>
-  <si>
-    <t>e_IT93-380</t>
-  </si>
-  <si>
-    <t>e_w491424937-380</t>
-  </si>
-  <si>
-    <t>e_IT71-380</t>
-  </si>
-  <si>
-    <t>e_IT21-380</t>
-  </si>
-  <si>
-    <t>e_IT7-380</t>
-  </si>
-  <si>
-    <t>e_IT10-380</t>
-  </si>
-  <si>
-    <t>e_w75602396-380</t>
-  </si>
-  <si>
     <t>ep_hydro_dam_G100000602220</t>
   </si>
   <si>
@@ -2031,12 +2031,12 @@
     <t>windon</t>
   </si>
   <si>
+    <t>elc_won-ITA_0022</t>
+  </si>
+  <si>
     <t>elc_won-ITA_0073</t>
   </si>
   <si>
-    <t>elc_won-ITA_0022</t>
-  </si>
-  <si>
     <t>elc_won-ITA_0096</t>
   </si>
   <si>
@@ -2469,19 +2469,34 @@
     <t>ele</t>
   </si>
   <si>
+    <t>Aggregated Plant - EMBER Gap - way/108020416-380_Missing Bioenergy Capacity</t>
+  </si>
+  <si>
+    <t>GW</t>
+  </si>
+  <si>
+    <t>TWh</t>
+  </si>
+  <si>
+    <t>daynite</t>
+  </si>
+  <si>
+    <t>yes</t>
+  </si>
+  <si>
     <t>Aggregated Plant - EMBER Gap - way/81938081-380_Missing Bioenergy Capacity</t>
   </si>
   <si>
-    <t>GW</t>
-  </si>
-  <si>
-    <t>TWh</t>
-  </si>
-  <si>
-    <t>daynite</t>
-  </si>
-  <si>
-    <t>yes</t>
+    <t>Aggregated Plant - EMBER Gap - way/84696559-380_Missing Bioenergy Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/144005863-380_Missing Bioenergy Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/109756016-380_Missing Bioenergy Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/98902899-380_Missing Bioenergy Capacity</t>
   </si>
   <si>
     <t>Aggregated Plant - EMBER Gap - way/34157795-380_Missing Bioenergy Capacity</t>
@@ -2490,21 +2505,6 @@
     <t>Aggregated Plant - EMBER Gap - way/58440884-380_Missing Bioenergy Capacity</t>
   </si>
   <si>
-    <t>Aggregated Plant - EMBER Gap - way/84696559-380_Missing Bioenergy Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/108020416-380_Missing Bioenergy Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/144005863-380_Missing Bioenergy Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/109756016-380_Missing Bioenergy Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/98902899-380_Missing Bioenergy Capacity</t>
-  </si>
-  <si>
     <t>Acerra power station_1</t>
   </si>
   <si>
@@ -2526,15 +2526,15 @@
     <t>Aggregated Plant</t>
   </si>
   <si>
+    <t>Aggregated Plant - EMBER Gap - way/418902800-380_Missing Coal Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/409439916-380_Missing Coal Capacity</t>
+  </si>
+  <si>
     <t>Aggregated Plant - EMBER Gap - way/82767145-380_Missing Coal Capacity</t>
   </si>
   <si>
-    <t>Aggregated Plant - EMBER Gap - way/409439916-380_Missing Coal Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/418902800-380_Missing Coal Capacity</t>
-  </si>
-  <si>
     <t>Aggregated Plant - EMBER Gap - way/303915533-380_Missing Coal Capacity</t>
   </si>
   <si>
@@ -2568,126 +2568,126 @@
     <t>Torrevaldaliga Nord power station_Unit 3</t>
   </si>
   <si>
+    <t>Aggregated Plant - EMBER Gap - way/103381531-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/149997403-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/162960205-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/133601335-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/199675964-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/181125039-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/82078641-380_Missing Gas Capacity</t>
+  </si>
+  <si>
     <t>Aggregated Plant - EMBER Gap - way/432729521-380_Missing Gas Capacity</t>
   </si>
   <si>
-    <t>Aggregated Plant - EMBER Gap - way/181125039-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/199675964-380_Missing Gas Capacity</t>
+    <t>Aggregated Plant - EMBER Gap - way/103974940-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/162828577-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/98900549-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/338753171-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/1137611914-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/158739183-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/145665799-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/110330925-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/105581403-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/109756016-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/98421779-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/411026199-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/82084019-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/116797658-380_Missing Gas Capacity</t>
   </si>
   <si>
     <t>Aggregated Plant - EMBER Gap - way/107438024-380_Missing Gas Capacity</t>
   </si>
   <si>
-    <t>Aggregated Plant - EMBER Gap - way/116797658-380_Missing Gas Capacity</t>
-  </si>
-  <si>
     <t>Aggregated Plant - EMBER Gap - way/339104227-380_Missing Gas Capacity</t>
   </si>
   <si>
-    <t>Aggregated Plant - EMBER Gap - way/82078641-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/103974940-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/162828577-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/98900549-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/338753171-380_Missing Gas Capacity</t>
+    <t>Aggregated Plant - EMBER Gap - way/419423704-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/61157826-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/414663585-380_Missing Gas Capacity</t>
   </si>
   <si>
     <t>Aggregated Plant - EMBER Gap - way/60725875-380_Missing Gas Capacity</t>
   </si>
   <si>
-    <t>Aggregated Plant - EMBER Gap - way/133601335-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/149997403-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/162960205-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/419423704-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/414663585-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/61157826-380_Missing Gas Capacity</t>
+    <t>Aggregated Plant - EMBER Gap - way/109993642-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/82767145-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/99826025-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/421827453-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/100407576-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/59462715-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/105757794-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/132450233-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/416989699-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/103653592-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/172302572-380_Missing Gas Capacity</t>
   </si>
   <si>
     <t>Aggregated Plant - EMBER Gap - way/255011550-380_Missing Gas Capacity</t>
   </si>
   <si>
-    <t>Aggregated Plant - EMBER Gap - way/132450233-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/172302572-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/59462715-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/105757794-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/100407576-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/103653592-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/416989699-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/82767145-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/109993642-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/103381531-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/145665799-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/1137611914-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/158739183-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/109756016-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/110330925-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/82084019-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/411026199-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/98421779-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/105581403-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/421827453-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/99826025-380_Missing Gas Capacity</t>
-  </si>
-  <si>
     <t>Altomonte power station_1</t>
   </si>
   <si>
@@ -3000,6 +3000,57 @@
     <t>Valle Secolo geothermal power plant_2</t>
   </si>
   <si>
+    <t>Aggregated Plant - IRENA Gap - way/109588422-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/82083756-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/419423704-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/491424937-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - IT72-400_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/1137611914-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/61626687-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - IT31-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/114931087-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - IT93-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - IT10-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/338753171-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/64200868-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/104359058-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/72466334-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - IT71-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/108020416-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
     <t>Aggregated Plant - IRENA Gap - IT72-380_Missing Hydro Capacity</t>
   </si>
   <si>
@@ -3009,37 +3060,28 @@
     <t>Aggregated Plant - IRENA Gap - way/1100665914-380_Missing Hydro Capacity</t>
   </si>
   <si>
-    <t>Aggregated Plant - IRENA Gap - IT93-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - IT10-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/338753171-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/64200868-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - IT31-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/61626687-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/114931087-380_Missing Hydro Capacity</t>
+    <t>Aggregated Plant - IRENA Gap - way/61712456-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - IT30-500_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - IT53-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - IT7-380_Missing Hydro Capacity</t>
   </si>
   <si>
     <t>Aggregated Plant - IRENA Gap - way/75602396-380_Missing Hydro Capacity</t>
   </si>
   <si>
-    <t>Aggregated Plant - IRENA Gap - IT30-500_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - IT53-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/61712456-380_Missing Hydro Capacity</t>
+    <t>Aggregated Plant - IRENA Gap - way/339703159-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - IT36-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - IT71-400_Missing Hydro Capacity</t>
   </si>
   <si>
     <t>Aggregated Plant - IRENA Gap - way/144005863-380_Missing Hydro Capacity</t>
@@ -3048,54 +3090,12 @@
     <t>Aggregated Plant - IRENA Gap - IT21-380_Missing Hydro Capacity</t>
   </si>
   <si>
+    <t>Aggregated Plant - IRENA Gap - way/96190189-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
     <t>Aggregated Plant - IRENA Gap - way/116517585-380_Missing Hydro Capacity</t>
   </si>
   <si>
-    <t>Aggregated Plant - IRENA Gap - way/96190189-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - IT72-400_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/1137611914-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/109588422-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - IT7-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/339703159-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/419423704-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/491424937-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/82083756-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/104359058-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/72466334-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - IT71-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/108020416-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - IT71-400_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - IT36-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
     <t>Baschi hydroelectric plant_</t>
   </si>
   <si>
@@ -3390,27 +3390,27 @@
     <t>San Filippo del Mela power station_1</t>
   </si>
   <si>
+    <t>Aggregated Plant - IRENA Gap - ITA_30_Missing Solar Capacity</t>
+  </si>
+  <si>
+    <t>annual</t>
+  </si>
+  <si>
     <t>Aggregated Plant - IRENA Gap - ITA_42_Missing Solar Capacity</t>
   </si>
   <si>
-    <t>annual</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - ITA_30_Missing Solar Capacity</t>
-  </si>
-  <si>
     <t>Aggregated Plant - IRENA Gap - ITA_68_Missing Solar Capacity</t>
   </si>
   <si>
     <t>Aggregated Plant - IRENA Gap - ITA_96_Missing Onshore wind energy Capacity</t>
   </si>
   <si>
+    <t>Aggregated Plant - IRENA Gap - ITA_22_Missing Onshore wind energy Capacity</t>
+  </si>
+  <si>
     <t>Aggregated Plant - IRENA Gap - ITA_73_Missing Onshore wind energy Capacity</t>
   </si>
   <si>
-    <t>Aggregated Plant - IRENA Gap - ITA_22_Missing Onshore wind energy Capacity</t>
-  </si>
-  <si>
     <t>AF</t>
   </si>
   <si>
@@ -4002,18 +4002,18 @@
     <t>ccs retrofit of -- Sulcis power station_Unit 3</t>
   </si>
   <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/418902800-380_Missing Coal Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/303915533-380_Missing Coal Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/82767145-380_Missing Coal Capacity</t>
+  </si>
+  <si>
     <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/409439916-380_Missing Coal Capacity</t>
   </si>
   <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/303915533-380_Missing Coal Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/82767145-380_Missing Coal Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/418902800-380_Missing Coal Capacity</t>
-  </si>
-  <si>
     <t>ccs retrofit of -- Brindisi Sud power station_Unit 1</t>
   </si>
   <si>
@@ -4302,124 +4302,124 @@
     <t>ccs retrofit of -- Aggregated Plant</t>
   </si>
   <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/181125039-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/105581403-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/255011550-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/60725875-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/172302572-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/82767145-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/162828577-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/116797658-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/414663585-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/162960205-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/432729521-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/419423704-380_Missing Gas Capacity</t>
+  </si>
+  <si>
     <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/149997403-380_Missing Gas Capacity</t>
   </si>
   <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/162960205-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/419423704-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/432729521-380_Missing Gas Capacity</t>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/103381531-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/109756016-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/411026199-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/100407576-380_Missing Gas Capacity</t>
   </si>
   <si>
     <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/132450233-380_Missing Gas Capacity</t>
   </si>
   <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/100407576-380_Missing Gas Capacity</t>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/145665799-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/199675964-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/82078641-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/1137611914-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/103653592-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/98900549-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/98421779-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/107438024-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/82084019-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/421827453-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/133601335-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/158739183-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/99826025-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/416989699-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/105757794-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/338753171-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/110330925-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/109993642-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/61157826-380_Missing Gas Capacity</t>
   </si>
   <si>
     <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/59462715-380_Missing Gas Capacity</t>
   </si>
   <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/109993642-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/199675964-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/82078641-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/103653592-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/145665799-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/107438024-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/98900549-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/338753171-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/110330925-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/105757794-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/61157826-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/181125039-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/255011550-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/105581403-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/133601335-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/158739183-380_Missing Gas Capacity</t>
-  </si>
-  <si>
     <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/339104227-380_Missing Gas Capacity</t>
   </si>
   <si>
     <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/103974940-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/116797658-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/416989699-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/99826025-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/98421779-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/1137611914-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/60725875-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/82084019-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/82767145-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/172302572-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/162828577-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/103381531-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/109756016-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/411026199-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/421827453-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/414663585-380_Missing Gas Capacity</t>
   </si>
   <si>
     <t>ccs retrofit of -- Tavazzano power station_CCGT8, timepoint 1</t>
@@ -4823,7 +4823,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79EAB795-ED9D-409C-A1D9-4B12B28916EB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{66881B80-BC81-41E3-880C-18CC1EFDB6F0}">
   <dimension ref="B9:T278"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -4899,7 +4899,7 @@
         <v>33</v>
       </c>
       <c r="D11" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E11">
         <v>0.18317520000000001</v>
@@ -4955,7 +4955,7 @@
         <v>33</v>
       </c>
       <c r="D12" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E12">
         <v>0.18317520000000001</v>
@@ -5011,7 +5011,7 @@
         <v>33</v>
       </c>
       <c r="D13" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E13">
         <v>0.18317520000000001</v>
@@ -5067,7 +5067,7 @@
         <v>33</v>
       </c>
       <c r="D14" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E14">
         <v>0.13765950000000002</v>
@@ -5347,7 +5347,7 @@
         <v>33</v>
       </c>
       <c r="D19" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E19">
         <v>0.30649709999999997</v>
@@ -5403,7 +5403,7 @@
         <v>33</v>
       </c>
       <c r="D20" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E20">
         <v>0.30649709999999997</v>
@@ -5459,7 +5459,7 @@
         <v>33</v>
       </c>
       <c r="D21" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E21">
         <v>0.30649709999999997</v>
@@ -5683,7 +5683,7 @@
         <v>49</v>
       </c>
       <c r="D25" t="s">
-        <v>87</v>
+        <v>50</v>
       </c>
       <c r="E25">
         <v>0.49118125000000001</v>
@@ -5739,7 +5739,7 @@
         <v>49</v>
       </c>
       <c r="D26" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="E26">
         <v>0.52272499999999988</v>
@@ -5795,7 +5795,7 @@
         <v>49</v>
       </c>
       <c r="D27" t="s">
-        <v>73</v>
+        <v>53</v>
       </c>
       <c r="E27">
         <v>0.450625</v>
@@ -5851,7 +5851,7 @@
         <v>49</v>
       </c>
       <c r="D28" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="E28">
         <v>0.52272499999999988</v>
@@ -5907,7 +5907,7 @@
         <v>49</v>
       </c>
       <c r="D29" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E29">
         <v>0.49118125000000001</v>
@@ -5963,7 +5963,7 @@
         <v>49</v>
       </c>
       <c r="D30" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E30">
         <v>0.49118125000000001</v>
@@ -6019,7 +6019,7 @@
         <v>49</v>
       </c>
       <c r="D31" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E31">
         <v>0.49118125000000001</v>
@@ -6131,7 +6131,7 @@
         <v>49</v>
       </c>
       <c r="D33" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E33">
         <v>0.49118125000000001</v>
@@ -6299,7 +6299,7 @@
         <v>49</v>
       </c>
       <c r="D36" t="s">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="E36">
         <v>0.49118125000000001</v>
@@ -6355,7 +6355,7 @@
         <v>49</v>
       </c>
       <c r="D37" t="s">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="E37">
         <v>0.49118125000000001</v>
@@ -6411,7 +6411,7 @@
         <v>49</v>
       </c>
       <c r="D38" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E38">
         <v>0.49118125000000001</v>
@@ -6467,7 +6467,7 @@
         <v>49</v>
       </c>
       <c r="D39" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E39">
         <v>0.49118125000000001</v>
@@ -6523,7 +6523,7 @@
         <v>49</v>
       </c>
       <c r="D40" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E40">
         <v>0.46865000000000007</v>
@@ -6579,7 +6579,7 @@
         <v>49</v>
       </c>
       <c r="D41" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E41">
         <v>0.49118125000000001</v>
@@ -6635,7 +6635,7 @@
         <v>49</v>
       </c>
       <c r="D42" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E42">
         <v>0.49118125000000001</v>
@@ -6691,7 +6691,7 @@
         <v>49</v>
       </c>
       <c r="D43" t="s">
-        <v>64</v>
+        <v>86</v>
       </c>
       <c r="E43">
         <v>0.49118125000000001</v>
@@ -6747,7 +6747,7 @@
         <v>49</v>
       </c>
       <c r="D44" t="s">
-        <v>64</v>
+        <v>86</v>
       </c>
       <c r="E44">
         <v>0.49118125000000001</v>
@@ -6803,7 +6803,7 @@
         <v>49</v>
       </c>
       <c r="D45" t="s">
-        <v>86</v>
+        <v>66</v>
       </c>
       <c r="E45">
         <v>0.49118125000000001</v>
@@ -6859,7 +6859,7 @@
         <v>49</v>
       </c>
       <c r="D46" t="s">
-        <v>86</v>
+        <v>66</v>
       </c>
       <c r="E46">
         <v>0.49118125000000001</v>
@@ -6915,7 +6915,7 @@
         <v>49</v>
       </c>
       <c r="D47" t="s">
-        <v>86</v>
+        <v>66</v>
       </c>
       <c r="E47">
         <v>0.49118125000000001</v>
@@ -6971,7 +6971,7 @@
         <v>49</v>
       </c>
       <c r="D48" t="s">
-        <v>86</v>
+        <v>66</v>
       </c>
       <c r="E48">
         <v>0.49118125000000001</v>
@@ -7027,7 +7027,7 @@
         <v>49</v>
       </c>
       <c r="D49" t="s">
-        <v>50</v>
+        <v>85</v>
       </c>
       <c r="E49">
         <v>0.47315625000000006</v>
@@ -7083,7 +7083,7 @@
         <v>49</v>
       </c>
       <c r="D50" t="s">
-        <v>50</v>
+        <v>85</v>
       </c>
       <c r="E50">
         <v>0.47315625000000006</v>
@@ -7139,7 +7139,7 @@
         <v>49</v>
       </c>
       <c r="D51" t="s">
-        <v>57</v>
+        <v>74</v>
       </c>
       <c r="E51">
         <v>0.49118125000000001</v>
@@ -7195,7 +7195,7 @@
         <v>49</v>
       </c>
       <c r="D52" t="s">
-        <v>73</v>
+        <v>53</v>
       </c>
       <c r="E52">
         <v>0.54075000000000006</v>
@@ -7251,7 +7251,7 @@
         <v>49</v>
       </c>
       <c r="D53" t="s">
-        <v>73</v>
+        <v>53</v>
       </c>
       <c r="E53">
         <v>0.49118125000000001</v>
@@ -7363,7 +7363,7 @@
         <v>49</v>
       </c>
       <c r="D55" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="E55">
         <v>0.49118125000000001</v>
@@ -7419,7 +7419,7 @@
         <v>49</v>
       </c>
       <c r="D56" t="s">
-        <v>77</v>
+        <v>62</v>
       </c>
       <c r="E56">
         <v>0.49118125000000001</v>
@@ -7475,7 +7475,7 @@
         <v>49</v>
       </c>
       <c r="D57" t="s">
-        <v>77</v>
+        <v>62</v>
       </c>
       <c r="E57">
         <v>0.49118125000000001</v>
@@ -7531,7 +7531,7 @@
         <v>49</v>
       </c>
       <c r="D58" t="s">
-        <v>78</v>
+        <v>64</v>
       </c>
       <c r="E58">
         <v>0.47315625000000006</v>
@@ -7587,7 +7587,7 @@
         <v>49</v>
       </c>
       <c r="D59" t="s">
-        <v>78</v>
+        <v>64</v>
       </c>
       <c r="E59">
         <v>0.47315625000000006</v>
@@ -7643,7 +7643,7 @@
         <v>49</v>
       </c>
       <c r="D60" t="s">
-        <v>78</v>
+        <v>64</v>
       </c>
       <c r="E60">
         <v>0.450625</v>
@@ -7699,7 +7699,7 @@
         <v>49</v>
       </c>
       <c r="D61" t="s">
-        <v>78</v>
+        <v>64</v>
       </c>
       <c r="E61">
         <v>0.450625</v>
@@ -7811,7 +7811,7 @@
         <v>49</v>
       </c>
       <c r="D63" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="E63">
         <v>0.4911812499999999</v>
@@ -7867,7 +7867,7 @@
         <v>49</v>
       </c>
       <c r="D64" t="s">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="E64">
         <v>0.49118125000000001</v>
@@ -7923,7 +7923,7 @@
         <v>49</v>
       </c>
       <c r="D65" t="s">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="E65">
         <v>0.49118125000000001</v>
@@ -7979,7 +7979,7 @@
         <v>49</v>
       </c>
       <c r="D66" t="s">
-        <v>81</v>
+        <v>63</v>
       </c>
       <c r="E66">
         <v>0.49118125000000001</v>
@@ -8147,7 +8147,7 @@
         <v>49</v>
       </c>
       <c r="D69" t="s">
-        <v>56</v>
+        <v>72</v>
       </c>
       <c r="E69">
         <v>0.49118125000000001</v>
@@ -8203,7 +8203,7 @@
         <v>49</v>
       </c>
       <c r="D70" t="s">
-        <v>56</v>
+        <v>72</v>
       </c>
       <c r="E70">
         <v>0.49118125000000001</v>
@@ -8259,7 +8259,7 @@
         <v>49</v>
       </c>
       <c r="D71" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="E71">
         <v>0.49118125000000001</v>
@@ -8315,7 +8315,7 @@
         <v>49</v>
       </c>
       <c r="D72" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="E72">
         <v>0.49118125000000001</v>
@@ -8483,7 +8483,7 @@
         <v>49</v>
       </c>
       <c r="D75" t="s">
-        <v>66</v>
+        <v>82</v>
       </c>
       <c r="E75">
         <v>0.50470000000000004</v>
@@ -8539,7 +8539,7 @@
         <v>49</v>
       </c>
       <c r="D76" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E76">
         <v>0.49118125000000001</v>
@@ -8595,7 +8595,7 @@
         <v>49</v>
       </c>
       <c r="D77" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E77">
         <v>0.49118125000000001</v>
@@ -8763,7 +8763,7 @@
         <v>49</v>
       </c>
       <c r="D80" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E80">
         <v>0.49118125000000001</v>
@@ -8819,7 +8819,7 @@
         <v>49</v>
       </c>
       <c r="D81" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E81">
         <v>0.49118125000000001</v>
@@ -8875,7 +8875,7 @@
         <v>49</v>
       </c>
       <c r="D82" t="s">
-        <v>85</v>
+        <v>59</v>
       </c>
       <c r="E82">
         <v>0.49118125000000001</v>
@@ -8931,7 +8931,7 @@
         <v>49</v>
       </c>
       <c r="D83" t="s">
-        <v>85</v>
+        <v>59</v>
       </c>
       <c r="E83">
         <v>0.49118125000000001</v>
@@ -8987,7 +8987,7 @@
         <v>49</v>
       </c>
       <c r="D84" t="s">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="E84">
         <v>0.49118125000000001</v>
@@ -9043,7 +9043,7 @@
         <v>49</v>
       </c>
       <c r="D85" t="s">
-        <v>51</v>
+        <v>87</v>
       </c>
       <c r="E85">
         <v>0.49118125000000001</v>
@@ -9099,7 +9099,7 @@
         <v>49</v>
       </c>
       <c r="D86" t="s">
-        <v>51</v>
+        <v>87</v>
       </c>
       <c r="E86">
         <v>0.49118125000000001</v>
@@ -9155,7 +9155,7 @@
         <v>49</v>
       </c>
       <c r="D87" t="s">
-        <v>54</v>
+        <v>71</v>
       </c>
       <c r="E87">
         <v>0.49118125000000001</v>
@@ -9211,7 +9211,7 @@
         <v>49</v>
       </c>
       <c r="D88" t="s">
-        <v>54</v>
+        <v>71</v>
       </c>
       <c r="E88">
         <v>0.49118125000000001</v>
@@ -9267,7 +9267,7 @@
         <v>49</v>
       </c>
       <c r="D89" t="s">
-        <v>62</v>
+        <v>79</v>
       </c>
       <c r="E89">
         <v>0.52272499999999988</v>
@@ -9323,7 +9323,7 @@
         <v>49</v>
       </c>
       <c r="D90" t="s">
-        <v>62</v>
+        <v>79</v>
       </c>
       <c r="E90">
         <v>0.49118125000000001</v>
@@ -9379,7 +9379,7 @@
         <v>49</v>
       </c>
       <c r="D91" t="s">
-        <v>79</v>
+        <v>65</v>
       </c>
       <c r="E91">
         <v>0.49118125000000001</v>
@@ -9435,7 +9435,7 @@
         <v>49</v>
       </c>
       <c r="D92" t="s">
-        <v>57</v>
+        <v>74</v>
       </c>
       <c r="E92">
         <v>0.52272499999999988</v>
@@ -9603,7 +9603,7 @@
         <v>49</v>
       </c>
       <c r="D95" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="E95">
         <v>0.49118125000000001</v>
@@ -9659,7 +9659,7 @@
         <v>49</v>
       </c>
       <c r="D96" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E96">
         <v>0.49118125000000001</v>
@@ -9827,7 +9827,7 @@
         <v>49</v>
       </c>
       <c r="D99" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E99">
         <v>0.54075000000000006</v>
@@ -9883,7 +9883,7 @@
         <v>49</v>
       </c>
       <c r="D100" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E100">
         <v>0.54075000000000006</v>
@@ -9939,7 +9939,7 @@
         <v>49</v>
       </c>
       <c r="D101" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E101">
         <v>0.54075000000000006</v>
@@ -9995,7 +9995,7 @@
         <v>49</v>
       </c>
       <c r="D102" t="s">
-        <v>80</v>
+        <v>54</v>
       </c>
       <c r="E102">
         <v>0.49118125000000001</v>
@@ -10051,7 +10051,7 @@
         <v>49</v>
       </c>
       <c r="D103" t="s">
-        <v>80</v>
+        <v>54</v>
       </c>
       <c r="E103">
         <v>0.49118125000000001</v>
@@ -10107,7 +10107,7 @@
         <v>49</v>
       </c>
       <c r="D104" t="s">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="E104">
         <v>0.49118125000000001</v>
@@ -10163,7 +10163,7 @@
         <v>49</v>
       </c>
       <c r="D105" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E105">
         <v>0.49118125000000001</v>
@@ -10219,7 +10219,7 @@
         <v>49</v>
       </c>
       <c r="D106" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="E106">
         <v>0.450625</v>
@@ -10275,7 +10275,7 @@
         <v>49</v>
       </c>
       <c r="D107" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="E107">
         <v>0.450625</v>
@@ -10331,7 +10331,7 @@
         <v>49</v>
       </c>
       <c r="D108" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E108">
         <v>0.47315625000000006</v>
@@ -10443,7 +10443,7 @@
         <v>49</v>
       </c>
       <c r="D110" t="s">
-        <v>67</v>
+        <v>81</v>
       </c>
       <c r="E110">
         <v>0.49118125000000001</v>
@@ -10499,7 +10499,7 @@
         <v>49</v>
       </c>
       <c r="D111" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E111">
         <v>0.46865000000000007</v>
@@ -10611,7 +10611,7 @@
         <v>49</v>
       </c>
       <c r="D113" t="s">
-        <v>66</v>
+        <v>82</v>
       </c>
       <c r="E113">
         <v>0.49118125000000001</v>
@@ -12403,7 +12403,7 @@
         <v>49</v>
       </c>
       <c r="D145" t="s">
-        <v>16</v>
+        <v>85</v>
       </c>
       <c r="E145">
         <v>0.54075000000000006</v>
@@ -12515,7 +12515,7 @@
         <v>49</v>
       </c>
       <c r="D147" t="s">
-        <v>52</v>
+        <v>36</v>
       </c>
       <c r="E147">
         <v>0.54075000000000006</v>
@@ -12571,7 +12571,7 @@
         <v>49</v>
       </c>
       <c r="D148" t="s">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="E148">
         <v>0.54075000000000006</v>
@@ -13187,7 +13187,7 @@
         <v>49</v>
       </c>
       <c r="D159" t="s">
-        <v>85</v>
+        <v>19</v>
       </c>
       <c r="E159">
         <v>0.54075000000000006</v>
@@ -13467,7 +13467,7 @@
         <v>49</v>
       </c>
       <c r="D164" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E164">
         <v>0.48667500000000002</v>
@@ -14307,7 +14307,7 @@
         <v>49</v>
       </c>
       <c r="D179" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E179">
         <v>0.46865000000000007</v>
@@ -14363,7 +14363,7 @@
         <v>49</v>
       </c>
       <c r="D180" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E180">
         <v>0.46865000000000007</v>
@@ -14587,7 +14587,7 @@
         <v>49</v>
       </c>
       <c r="D184" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="E184">
         <v>0.48667500000000002</v>
@@ -14643,7 +14643,7 @@
         <v>49</v>
       </c>
       <c r="D185" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="E185">
         <v>0.48667500000000002</v>
@@ -15371,7 +15371,7 @@
         <v>49</v>
       </c>
       <c r="D198" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E198">
         <v>0.50470000000000004</v>
@@ -15595,7 +15595,7 @@
         <v>49</v>
       </c>
       <c r="D202" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E202">
         <v>0.46865000000000007</v>
@@ -16323,7 +16323,7 @@
         <v>49</v>
       </c>
       <c r="D215" t="s">
-        <v>85</v>
+        <v>59</v>
       </c>
       <c r="E215">
         <v>0.450625</v>
@@ -16491,7 +16491,7 @@
         <v>49</v>
       </c>
       <c r="D218" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E218">
         <v>0.50470000000000004</v>
@@ -16547,7 +16547,7 @@
         <v>49</v>
       </c>
       <c r="D219" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E219">
         <v>0.50470000000000004</v>
@@ -16715,7 +16715,7 @@
         <v>49</v>
       </c>
       <c r="D222" t="s">
-        <v>77</v>
+        <v>62</v>
       </c>
       <c r="E222">
         <v>0.450625</v>
@@ -16771,7 +16771,7 @@
         <v>49</v>
       </c>
       <c r="D223" t="s">
-        <v>54</v>
+        <v>71</v>
       </c>
       <c r="E223">
         <v>0.29741250000000002</v>
@@ -16827,7 +16827,7 @@
         <v>49</v>
       </c>
       <c r="D224" t="s">
-        <v>62</v>
+        <v>79</v>
       </c>
       <c r="E224">
         <v>0.28839999999999999</v>
@@ -16883,7 +16883,7 @@
         <v>49</v>
       </c>
       <c r="D225" t="s">
-        <v>62</v>
+        <v>79</v>
       </c>
       <c r="E225">
         <v>0.28839999999999999</v>
@@ -16939,7 +16939,7 @@
         <v>49</v>
       </c>
       <c r="D226" t="s">
-        <v>66</v>
+        <v>82</v>
       </c>
       <c r="E226">
         <v>0.24784375000000003</v>
@@ -17443,7 +17443,7 @@
         <v>49</v>
       </c>
       <c r="D235" t="s">
-        <v>64</v>
+        <v>86</v>
       </c>
       <c r="E235">
         <v>0.25235000000000002</v>
@@ -17723,7 +17723,7 @@
         <v>49</v>
       </c>
       <c r="D240" t="s">
-        <v>62</v>
+        <v>79</v>
       </c>
       <c r="E240">
         <v>0.27938750000000001</v>
@@ -17835,7 +17835,7 @@
         <v>49</v>
       </c>
       <c r="D242" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E242">
         <v>0.25235000000000002</v>
@@ -18031,7 +18031,7 @@
         <v>49</v>
       </c>
       <c r="D247" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E247">
         <v>0.32445000000000007</v>
@@ -18101,7 +18101,7 @@
         <v>49</v>
       </c>
       <c r="D249" t="s">
-        <v>79</v>
+        <v>65</v>
       </c>
       <c r="E249">
         <v>0.32445000000000002</v>
@@ -18241,7 +18241,7 @@
         <v>49</v>
       </c>
       <c r="D253" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E253">
         <v>0.27938750000000001</v>
@@ -18276,7 +18276,7 @@
         <v>49</v>
       </c>
       <c r="D254" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E254">
         <v>0.27938750000000001</v>
@@ -18311,7 +18311,7 @@
         <v>49</v>
       </c>
       <c r="D255" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E255">
         <v>0.27938750000000001</v>
@@ -18346,7 +18346,7 @@
         <v>49</v>
       </c>
       <c r="D256" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E256">
         <v>0.31093124999999999</v>
@@ -18381,7 +18381,7 @@
         <v>49</v>
       </c>
       <c r="D257" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E257">
         <v>0.27938750000000001</v>
@@ -18416,7 +18416,7 @@
         <v>49</v>
       </c>
       <c r="D258" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E258">
         <v>0.27938750000000001</v>
@@ -18451,7 +18451,7 @@
         <v>49</v>
       </c>
       <c r="D259" t="s">
-        <v>67</v>
+        <v>81</v>
       </c>
       <c r="E259">
         <v>0.26136249999999994</v>
@@ -18486,7 +18486,7 @@
         <v>49</v>
       </c>
       <c r="D260" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E260">
         <v>0.28839999999999999</v>
@@ -18521,7 +18521,7 @@
         <v>49</v>
       </c>
       <c r="D261" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E261">
         <v>0.28839999999999999</v>
@@ -18556,7 +18556,7 @@
         <v>49</v>
       </c>
       <c r="D262" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E262">
         <v>0.28839999999999999</v>
@@ -18626,7 +18626,7 @@
         <v>439</v>
       </c>
       <c r="D264" t="s">
-        <v>73</v>
+        <v>53</v>
       </c>
       <c r="E264">
         <v>0.41457500000000003</v>
@@ -18731,7 +18731,7 @@
         <v>439</v>
       </c>
       <c r="D267" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E267">
         <v>0.22981874999999999</v>
@@ -18766,7 +18766,7 @@
         <v>439</v>
       </c>
       <c r="D268" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E268">
         <v>0.24333750000000001</v>
@@ -18941,7 +18941,7 @@
         <v>439</v>
       </c>
       <c r="D273" t="s">
-        <v>73</v>
+        <v>53</v>
       </c>
       <c r="E273">
         <v>0.27938750000000001</v>
@@ -19149,7 +19149,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4AB5D649-5C86-4AA2-9E28-49C5EB87801E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3FC67D3B-D05A-40E9-9CA1-8ABE0866A3F6}">
   <dimension ref="B9:T842"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -19231,19 +19231,19 @@
         <v>2022</v>
       </c>
       <c r="F11">
-        <v>0.51576271186440681</v>
+        <v>0.22450847457627116</v>
       </c>
       <c r="G11">
-        <v>0.36049999999999999</v>
+        <v>0.33990000000000004</v>
       </c>
       <c r="H11">
-        <v>3850.0000000000005</v>
+        <v>4427.5</v>
       </c>
       <c r="I11">
-        <v>143</v>
+        <v>157.30000000000001</v>
       </c>
       <c r="J11">
-        <v>8.4</v>
+        <v>9.240000000000002</v>
       </c>
       <c r="K11">
         <v>50</v>
@@ -19284,7 +19284,7 @@
         <v>2022</v>
       </c>
       <c r="F12">
-        <v>1.0679322033898306</v>
+        <v>0.51576271186440681</v>
       </c>
       <c r="G12">
         <v>0.36049999999999999</v>
@@ -19337,19 +19337,19 @@
         <v>2022</v>
       </c>
       <c r="F13">
-        <v>0.27911864406779663</v>
+        <v>0.49149152542372881</v>
       </c>
       <c r="G13">
-        <v>0.33990000000000004</v>
+        <v>0.36049999999999999</v>
       </c>
       <c r="H13">
-        <v>4427.5</v>
+        <v>3850.0000000000005</v>
       </c>
       <c r="I13">
-        <v>157.30000000000001</v>
+        <v>143</v>
       </c>
       <c r="J13">
-        <v>9.240000000000002</v>
+        <v>8.4</v>
       </c>
       <c r="K13">
         <v>50</v>
@@ -19390,13 +19390,13 @@
         <v>2022</v>
       </c>
       <c r="F14">
-        <v>0.49149152542372881</v>
+        <v>0.35800000000000004</v>
       </c>
       <c r="G14">
-        <v>0.36049999999999999</v>
+        <v>0.36050000000000004</v>
       </c>
       <c r="H14">
-        <v>3850.0000000000005</v>
+        <v>3850.0000000000009</v>
       </c>
       <c r="I14">
         <v>143</v>
@@ -19443,19 +19443,19 @@
         <v>2022</v>
       </c>
       <c r="F15">
-        <v>0.39440677966101695</v>
+        <v>0.24877966101694915</v>
       </c>
       <c r="G15">
-        <v>0.36049999999999999</v>
+        <v>0.33990000000000004</v>
       </c>
       <c r="H15">
-        <v>3850.0000000000005</v>
+        <v>4427.5</v>
       </c>
       <c r="I15">
-        <v>143</v>
+        <v>157.30000000000001</v>
       </c>
       <c r="J15">
-        <v>8.4</v>
+        <v>9.240000000000002</v>
       </c>
       <c r="K15">
         <v>50</v>
@@ -19496,19 +19496,19 @@
         <v>2022</v>
       </c>
       <c r="F16">
-        <v>0.35800000000000004</v>
+        <v>0.27911864406779663</v>
       </c>
       <c r="G16">
-        <v>0.36050000000000004</v>
+        <v>0.33990000000000004</v>
       </c>
       <c r="H16">
-        <v>3850.0000000000009</v>
+        <v>4427.5</v>
       </c>
       <c r="I16">
-        <v>143</v>
+        <v>157.30000000000001</v>
       </c>
       <c r="J16">
-        <v>8.4</v>
+        <v>9.240000000000002</v>
       </c>
       <c r="K16">
         <v>50</v>
@@ -19549,19 +19549,19 @@
         <v>2022</v>
       </c>
       <c r="F17">
-        <v>0.24877966101694915</v>
+        <v>0.39440677966101695</v>
       </c>
       <c r="G17">
-        <v>0.33990000000000004</v>
+        <v>0.36049999999999999</v>
       </c>
       <c r="H17">
-        <v>4427.5</v>
+        <v>3850.0000000000005</v>
       </c>
       <c r="I17">
-        <v>157.30000000000001</v>
+        <v>143</v>
       </c>
       <c r="J17">
-        <v>9.240000000000002</v>
+        <v>8.4</v>
       </c>
       <c r="K17">
         <v>50</v>
@@ -19602,19 +19602,19 @@
         <v>2022</v>
       </c>
       <c r="F18">
-        <v>0.22450847457627116</v>
+        <v>1.0679322033898306</v>
       </c>
       <c r="G18">
-        <v>0.33990000000000004</v>
+        <v>0.36049999999999999</v>
       </c>
       <c r="H18">
-        <v>4427.5</v>
+        <v>3850.0000000000005</v>
       </c>
       <c r="I18">
-        <v>157.30000000000001</v>
+        <v>143</v>
       </c>
       <c r="J18">
-        <v>9.240000000000002</v>
+        <v>8.4</v>
       </c>
       <c r="K18">
         <v>50</v>
@@ -19649,7 +19649,7 @@
         <v>13</v>
       </c>
       <c r="D19" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="E19">
         <v>2008</v>
@@ -19702,7 +19702,7 @@
         <v>13</v>
       </c>
       <c r="D20" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E20">
         <v>1998</v>
@@ -19755,7 +19755,7 @@
         <v>13</v>
       </c>
       <c r="D21" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E21">
         <v>2008</v>
@@ -19808,7 +19808,7 @@
         <v>13</v>
       </c>
       <c r="D22" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E22">
         <v>2001</v>
@@ -19861,7 +19861,7 @@
         <v>13</v>
       </c>
       <c r="D23" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E23">
         <v>2013</v>
@@ -19914,7 +19914,7 @@
         <v>13</v>
       </c>
       <c r="D24" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E24">
         <v>1965</v>
@@ -19967,7 +19967,7 @@
         <v>13</v>
       </c>
       <c r="D25" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E25">
         <v>2003</v>
@@ -20020,7 +20020,7 @@
         <v>13</v>
       </c>
       <c r="D26" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="E26">
         <v>2009</v>
@@ -20073,7 +20073,7 @@
         <v>13</v>
       </c>
       <c r="D27" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E27">
         <v>2018</v>
@@ -20126,7 +20126,7 @@
         <v>13</v>
       </c>
       <c r="D28" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="E28">
         <v>2009</v>
@@ -20185,19 +20185,19 @@
         <v>2022</v>
       </c>
       <c r="F29">
-        <v>0.18416184971098257</v>
+        <v>0.61803468208092449</v>
       </c>
       <c r="G29">
-        <v>0.35020000000000001</v>
+        <v>0.37080000000000002</v>
       </c>
       <c r="H29">
-        <v>2530</v>
+        <v>2200</v>
       </c>
       <c r="I29">
-        <v>72.600000000000009</v>
+        <v>66</v>
       </c>
       <c r="J29">
-        <v>5.7750000000000004</v>
+        <v>5.25</v>
       </c>
       <c r="K29">
         <v>50</v>
@@ -20238,10 +20238,10 @@
         <v>2022</v>
       </c>
       <c r="F30">
-        <v>0.1997687861271675</v>
+        <v>0.18416184971098257</v>
       </c>
       <c r="G30">
-        <v>0.35020000000000007</v>
+        <v>0.35020000000000001</v>
       </c>
       <c r="H30">
         <v>2530</v>
@@ -20344,19 +20344,19 @@
         <v>2022</v>
       </c>
       <c r="F32">
-        <v>0.61803468208092449</v>
+        <v>0.1997687861271675</v>
       </c>
       <c r="G32">
-        <v>0.37080000000000002</v>
+        <v>0.35020000000000007</v>
       </c>
       <c r="H32">
-        <v>2200</v>
+        <v>2530</v>
       </c>
       <c r="I32">
-        <v>66</v>
+        <v>72.600000000000009</v>
       </c>
       <c r="J32">
-        <v>5.25</v>
+        <v>5.7750000000000004</v>
       </c>
       <c r="K32">
         <v>50</v>
@@ -20391,7 +20391,7 @@
         <v>33</v>
       </c>
       <c r="D33" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E33">
         <v>1992</v>
@@ -20444,7 +20444,7 @@
         <v>33</v>
       </c>
       <c r="D34" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E34">
         <v>1993</v>
@@ -20497,7 +20497,7 @@
         <v>33</v>
       </c>
       <c r="D35" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E35">
         <v>2005</v>
@@ -20550,7 +20550,7 @@
         <v>33</v>
       </c>
       <c r="D36" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E36">
         <v>1986</v>
@@ -20603,7 +20603,7 @@
         <v>33</v>
       </c>
       <c r="D37" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E37">
         <v>1991</v>
@@ -20656,7 +20656,7 @@
         <v>33</v>
       </c>
       <c r="D38" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E38">
         <v>1992</v>
@@ -20709,7 +20709,7 @@
         <v>33</v>
       </c>
       <c r="D39" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E39">
         <v>1993</v>
@@ -20927,7 +20927,7 @@
         <v>2022</v>
       </c>
       <c r="F43">
-        <v>0.16608022972358796</v>
+        <v>0.19676367392472002</v>
       </c>
       <c r="G43">
         <v>0.59739999999999993</v>
@@ -20980,19 +20980,19 @@
         <v>2022</v>
       </c>
       <c r="F44">
-        <v>0.18507474280047922</v>
+        <v>0.3567559186877659</v>
       </c>
       <c r="G44">
-        <v>0.59739999999999993</v>
+        <v>0.61799999999999999</v>
       </c>
       <c r="H44">
-        <v>1265</v>
+        <v>1100</v>
       </c>
       <c r="I44">
-        <v>36.300000000000004</v>
+        <v>33</v>
       </c>
       <c r="J44">
-        <v>3.4649999999999999</v>
+        <v>3.1500000000000004</v>
       </c>
       <c r="K44">
         <v>50</v>
@@ -21027,25 +21027,25 @@
         <v>49</v>
       </c>
       <c r="D45" t="s">
-        <v>52</v>
+        <v>36</v>
       </c>
       <c r="E45">
         <v>2022</v>
       </c>
       <c r="F45">
-        <v>0.3567559186877659</v>
+        <v>0.27761211420071885</v>
       </c>
       <c r="G45">
-        <v>0.61799999999999999</v>
+        <v>0.59739999999999993</v>
       </c>
       <c r="H45">
-        <v>1100</v>
+        <v>1265</v>
       </c>
       <c r="I45">
-        <v>33</v>
+        <v>36.300000000000004</v>
       </c>
       <c r="J45">
-        <v>3.1500000000000004</v>
+        <v>3.4650000000000003</v>
       </c>
       <c r="K45">
         <v>50</v>
@@ -21080,25 +21080,25 @@
         <v>49</v>
       </c>
       <c r="D46" t="s">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="E46">
         <v>2022</v>
       </c>
       <c r="F46">
-        <v>0.27761211420071885</v>
+        <v>0.30829555840185086</v>
       </c>
       <c r="G46">
-        <v>0.59739999999999993</v>
+        <v>0.61799999999999999</v>
       </c>
       <c r="H46">
-        <v>1265</v>
+        <v>1100</v>
       </c>
       <c r="I46">
-        <v>36.300000000000004</v>
+        <v>33</v>
       </c>
       <c r="J46">
-        <v>3.4650000000000003</v>
+        <v>3.1500000000000004</v>
       </c>
       <c r="K46">
         <v>50</v>
@@ -21139,10 +21139,10 @@
         <v>2022</v>
       </c>
       <c r="F47">
-        <v>0.30829555840185086</v>
+        <v>0.43468212618270452</v>
       </c>
       <c r="G47">
-        <v>0.61799999999999999</v>
+        <v>0.61799999999999988</v>
       </c>
       <c r="H47">
         <v>1100</v>
@@ -21192,19 +21192,19 @@
         <v>2022</v>
       </c>
       <c r="F48">
-        <v>0.49339465314217229</v>
+        <v>0.18824049497996109</v>
       </c>
       <c r="G48">
-        <v>0.61799999999999999</v>
+        <v>0.59739999999999993</v>
       </c>
       <c r="H48">
-        <v>1100</v>
+        <v>1265</v>
       </c>
       <c r="I48">
-        <v>33</v>
+        <v>36.300000000000004</v>
       </c>
       <c r="J48">
-        <v>3.1500000000000004</v>
+        <v>3.4650000000000003</v>
       </c>
       <c r="K48">
         <v>50</v>
@@ -21245,7 +21245,7 @@
         <v>2022</v>
       </c>
       <c r="F49">
-        <v>0.21551466760318963</v>
+        <v>0.19481551873734657</v>
       </c>
       <c r="G49">
         <v>0.59739999999999993</v>
@@ -21298,7 +21298,7 @@
         <v>2022</v>
       </c>
       <c r="F50">
-        <v>0.17484692806676855</v>
+        <v>0.18556178159732259</v>
       </c>
       <c r="G50">
         <v>0.59739999999999993</v>
@@ -21351,7 +21351,7 @@
         <v>2022</v>
       </c>
       <c r="F51">
-        <v>0.18872753377680451</v>
+        <v>0.23280454489112914</v>
       </c>
       <c r="G51">
         <v>0.59739999999999993</v>
@@ -21404,7 +21404,7 @@
         <v>2022</v>
       </c>
       <c r="F52">
-        <v>0.18556178159732259</v>
+        <v>0.26604494277568891</v>
       </c>
       <c r="G52">
         <v>0.59739999999999993</v>
@@ -21457,7 +21457,7 @@
         <v>2022</v>
       </c>
       <c r="F53">
-        <v>0.23280454489112914</v>
+        <v>0.29344087509812827</v>
       </c>
       <c r="G53">
         <v>0.59739999999999993</v>
@@ -21469,7 +21469,7 @@
         <v>36.300000000000004</v>
       </c>
       <c r="J53">
-        <v>3.4650000000000007</v>
+        <v>3.4650000000000003</v>
       </c>
       <c r="K53">
         <v>50</v>
@@ -21510,7 +21510,7 @@
         <v>2022</v>
       </c>
       <c r="F54">
-        <v>0.26604494277568891</v>
+        <v>0.19481551873734657</v>
       </c>
       <c r="G54">
         <v>0.59739999999999993</v>
@@ -21563,7 +21563,7 @@
         <v>2022</v>
       </c>
       <c r="F55">
-        <v>0.28443065735652601</v>
+        <v>0.19481551873734657</v>
       </c>
       <c r="G55">
         <v>0.59739999999999993</v>
@@ -21616,19 +21616,19 @@
         <v>2022</v>
       </c>
       <c r="F56">
-        <v>0.39839773581787374</v>
+        <v>0.20212110068999706</v>
       </c>
       <c r="G56">
-        <v>0.61799999999999999</v>
+        <v>0.59739999999999993</v>
       </c>
       <c r="H56">
-        <v>1100</v>
+        <v>1265</v>
       </c>
       <c r="I56">
-        <v>33</v>
+        <v>36.300000000000004</v>
       </c>
       <c r="J56">
-        <v>3.1500000000000004</v>
+        <v>3.4650000000000003</v>
       </c>
       <c r="K56">
         <v>50</v>
@@ -21669,19 +21669,19 @@
         <v>2022</v>
       </c>
       <c r="F57">
-        <v>0.45732943023592104</v>
+        <v>0.19627663512787666</v>
       </c>
       <c r="G57">
-        <v>0.61799999999999999</v>
+        <v>0.59739999999999993</v>
       </c>
       <c r="H57">
-        <v>1100</v>
+        <v>1265</v>
       </c>
       <c r="I57">
-        <v>33</v>
+        <v>36.300000000000004</v>
       </c>
       <c r="J57">
-        <v>3.1500000000000004</v>
+        <v>3.4649999999999999</v>
       </c>
       <c r="K57">
         <v>50</v>
@@ -21722,7 +21722,7 @@
         <v>2022</v>
       </c>
       <c r="F58">
-        <v>0.21283595422055113</v>
+        <v>0.26543614427963469</v>
       </c>
       <c r="G58">
         <v>0.59739999999999993</v>
@@ -21775,7 +21775,7 @@
         <v>2022</v>
       </c>
       <c r="F59">
-        <v>0.19481551873734657</v>
+        <v>0.20557907614758497</v>
       </c>
       <c r="G59">
         <v>0.59739999999999993</v>
@@ -21828,19 +21828,19 @@
         <v>2022</v>
       </c>
       <c r="F60">
-        <v>0.22793415692269547</v>
+        <v>0.37112356319464518</v>
       </c>
       <c r="G60">
-        <v>0.59739999999999993</v>
+        <v>0.61799999999999999</v>
       </c>
       <c r="H60">
-        <v>1265</v>
+        <v>1100</v>
       </c>
       <c r="I60">
-        <v>36.300000000000004</v>
+        <v>33</v>
       </c>
       <c r="J60">
-        <v>3.4650000000000003</v>
+        <v>3.1500000000000004</v>
       </c>
       <c r="K60">
         <v>50</v>
@@ -21881,7 +21881,7 @@
         <v>2022</v>
       </c>
       <c r="F61">
-        <v>0.1548783373961905</v>
+        <v>0.21551466760318963</v>
       </c>
       <c r="G61">
         <v>0.59739999999999993</v>
@@ -21893,7 +21893,7 @@
         <v>36.300000000000004</v>
       </c>
       <c r="J61">
-        <v>3.4649999999999999</v>
+        <v>3.4650000000000003</v>
       </c>
       <c r="K61">
         <v>50</v>
@@ -21934,7 +21934,7 @@
         <v>2022</v>
       </c>
       <c r="F62">
-        <v>0.27347228442755023</v>
+        <v>0.23864901045324952</v>
       </c>
       <c r="G62">
         <v>0.59739999999999993</v>
@@ -21987,19 +21987,19 @@
         <v>2022</v>
       </c>
       <c r="F63">
-        <v>0.23864901045324952</v>
+        <v>0.31243538817501959</v>
       </c>
       <c r="G63">
-        <v>0.59739999999999993</v>
+        <v>0.61799999999999999</v>
       </c>
       <c r="H63">
-        <v>1265</v>
+        <v>1100</v>
       </c>
       <c r="I63">
-        <v>36.300000000000004</v>
+        <v>33</v>
       </c>
       <c r="J63">
-        <v>3.4650000000000003</v>
+        <v>3.1500000000000004</v>
       </c>
       <c r="K63">
         <v>50</v>
@@ -22040,7 +22040,7 @@
         <v>2022</v>
       </c>
       <c r="F64">
-        <v>0.31243538817501959</v>
+        <v>0.45732943023592104</v>
       </c>
       <c r="G64">
         <v>0.61799999999999999</v>
@@ -22093,19 +22093,19 @@
         <v>2022</v>
       </c>
       <c r="F65">
-        <v>0.19481551873734657</v>
+        <v>0.49339465314217229</v>
       </c>
       <c r="G65">
-        <v>0.59739999999999993</v>
+        <v>0.61799999999999999</v>
       </c>
       <c r="H65">
-        <v>1265</v>
+        <v>1100</v>
       </c>
       <c r="I65">
-        <v>36.300000000000004</v>
+        <v>33</v>
       </c>
       <c r="J65">
-        <v>3.4650000000000003</v>
+        <v>3.1500000000000004</v>
       </c>
       <c r="K65">
         <v>50</v>
@@ -22146,7 +22146,7 @@
         <v>2022</v>
       </c>
       <c r="F66">
-        <v>0.19481551873734657</v>
+        <v>0.17484692806676855</v>
       </c>
       <c r="G66">
         <v>0.59739999999999993</v>
@@ -22199,19 +22199,19 @@
         <v>2022</v>
       </c>
       <c r="F67">
-        <v>0.43468212618270452</v>
+        <v>0.21113131843159935</v>
       </c>
       <c r="G67">
-        <v>0.61799999999999988</v>
+        <v>0.59739999999999993</v>
       </c>
       <c r="H67">
-        <v>1100</v>
+        <v>1265</v>
       </c>
       <c r="I67">
-        <v>33</v>
+        <v>36.300000000000004</v>
       </c>
       <c r="J67">
-        <v>3.1500000000000004</v>
+        <v>3.4650000000000003</v>
       </c>
       <c r="K67">
         <v>50</v>
@@ -22252,7 +22252,7 @@
         <v>2022</v>
       </c>
       <c r="F68">
-        <v>0.20820908565053911</v>
+        <v>0.18872753377680451</v>
       </c>
       <c r="G68">
         <v>0.59739999999999993</v>
@@ -22305,7 +22305,7 @@
         <v>2022</v>
       </c>
       <c r="F69">
-        <v>0.18629233979258764</v>
+        <v>0.20820908565053911</v>
       </c>
       <c r="G69">
         <v>0.59739999999999993</v>
@@ -22317,7 +22317,7 @@
         <v>36.300000000000004</v>
       </c>
       <c r="J69">
-        <v>3.4650000000000003</v>
+        <v>3.4650000000000007</v>
       </c>
       <c r="K69">
         <v>50</v>
@@ -22358,7 +22358,7 @@
         <v>2022</v>
       </c>
       <c r="F70">
-        <v>0.20236462008841874</v>
+        <v>0.18629233979258764</v>
       </c>
       <c r="G70">
         <v>0.59739999999999993</v>
@@ -22411,7 +22411,7 @@
         <v>2022</v>
       </c>
       <c r="F71">
-        <v>0.20212110068999706</v>
+        <v>0.20236462008841874</v>
       </c>
       <c r="G71">
         <v>0.59739999999999993</v>
@@ -22464,7 +22464,7 @@
         <v>2022</v>
       </c>
       <c r="F72">
-        <v>0.26543614427963469</v>
+        <v>0.28443065735652601</v>
       </c>
       <c r="G72">
         <v>0.59739999999999993</v>
@@ -22517,19 +22517,19 @@
         <v>2022</v>
       </c>
       <c r="F73">
-        <v>0.20557907614758497</v>
+        <v>0.39839773581787374</v>
       </c>
       <c r="G73">
-        <v>0.59739999999999993</v>
+        <v>0.61799999999999999</v>
       </c>
       <c r="H73">
-        <v>1265</v>
+        <v>1100</v>
       </c>
       <c r="I73">
-        <v>36.300000000000004</v>
+        <v>33</v>
       </c>
       <c r="J73">
-        <v>3.4650000000000003</v>
+        <v>3.1500000000000004</v>
       </c>
       <c r="K73">
         <v>50</v>
@@ -22570,7 +22570,7 @@
         <v>2022</v>
       </c>
       <c r="F74">
-        <v>0.18824049497996109</v>
+        <v>0.27347228442755023</v>
       </c>
       <c r="G74">
         <v>0.59739999999999993</v>
@@ -22623,7 +22623,7 @@
         <v>2022</v>
       </c>
       <c r="F75">
-        <v>0.19627663512787666</v>
+        <v>0.1548783373961905</v>
       </c>
       <c r="G75">
         <v>0.59739999999999993</v>
@@ -22676,7 +22676,7 @@
         <v>2022</v>
       </c>
       <c r="F76">
-        <v>0.21113131843159935</v>
+        <v>0.22793415692269547</v>
       </c>
       <c r="G76">
         <v>0.59739999999999993</v>
@@ -22829,13 +22829,13 @@
         <v>49</v>
       </c>
       <c r="D79" t="s">
-        <v>85</v>
+        <v>19</v>
       </c>
       <c r="E79">
         <v>2022</v>
       </c>
       <c r="F79">
-        <v>0.29344087509812827</v>
+        <v>0.19822479031525012</v>
       </c>
       <c r="G79">
         <v>0.59739999999999993</v>
@@ -22882,13 +22882,13 @@
         <v>49</v>
       </c>
       <c r="D80" t="s">
-        <v>16</v>
+        <v>85</v>
       </c>
       <c r="E80">
         <v>2022</v>
       </c>
       <c r="F80">
-        <v>0.19822479031525012</v>
+        <v>0.16608022972358796</v>
       </c>
       <c r="G80">
         <v>0.59739999999999993</v>
@@ -22941,19 +22941,19 @@
         <v>2022</v>
       </c>
       <c r="F81">
-        <v>0.37112356319464518</v>
+        <v>0.21283595422055113</v>
       </c>
       <c r="G81">
-        <v>0.61799999999999999</v>
+        <v>0.59739999999999993</v>
       </c>
       <c r="H81">
-        <v>1100</v>
+        <v>1265</v>
       </c>
       <c r="I81">
-        <v>33</v>
+        <v>36.300000000000004</v>
       </c>
       <c r="J81">
-        <v>3.1500000000000004</v>
+        <v>3.4650000000000003</v>
       </c>
       <c r="K81">
         <v>50</v>
@@ -22994,7 +22994,7 @@
         <v>2022</v>
       </c>
       <c r="F82">
-        <v>0.19676367392472002</v>
+        <v>0.18507474280047922</v>
       </c>
       <c r="G82">
         <v>0.59739999999999993</v>
@@ -23006,7 +23006,7 @@
         <v>36.300000000000004</v>
       </c>
       <c r="J82">
-        <v>3.4650000000000003</v>
+        <v>3.4649999999999999</v>
       </c>
       <c r="K82">
         <v>50</v>
@@ -23041,7 +23041,7 @@
         <v>49</v>
       </c>
       <c r="D83" t="s">
-        <v>87</v>
+        <v>50</v>
       </c>
       <c r="E83">
         <v>2006</v>
@@ -23094,7 +23094,7 @@
         <v>49</v>
       </c>
       <c r="D84" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="E84">
         <v>2012</v>
@@ -23147,7 +23147,7 @@
         <v>49</v>
       </c>
       <c r="D85" t="s">
-        <v>73</v>
+        <v>53</v>
       </c>
       <c r="E85">
         <v>1993</v>
@@ -23200,7 +23200,7 @@
         <v>49</v>
       </c>
       <c r="D86" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="E86">
         <v>2011</v>
@@ -23253,7 +23253,7 @@
         <v>49</v>
       </c>
       <c r="D87" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E87">
         <v>2005</v>
@@ -23306,7 +23306,7 @@
         <v>49</v>
       </c>
       <c r="D88" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E88">
         <v>2006</v>
@@ -23359,7 +23359,7 @@
         <v>49</v>
       </c>
       <c r="D89" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E89">
         <v>2006</v>
@@ -23465,7 +23465,7 @@
         <v>49</v>
       </c>
       <c r="D91" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E91">
         <v>2003</v>
@@ -23624,7 +23624,7 @@
         <v>49</v>
       </c>
       <c r="D94" t="s">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="E94">
         <v>2004</v>
@@ -23677,7 +23677,7 @@
         <v>49</v>
       </c>
       <c r="D95" t="s">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="E95">
         <v>2005</v>
@@ -23730,7 +23730,7 @@
         <v>49</v>
       </c>
       <c r="D96" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E96">
         <v>2005</v>
@@ -23783,7 +23783,7 @@
         <v>49</v>
       </c>
       <c r="D97" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E97">
         <v>2005</v>
@@ -23836,7 +23836,7 @@
         <v>49</v>
       </c>
       <c r="D98" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E98">
         <v>2004</v>
@@ -23889,7 +23889,7 @@
         <v>49</v>
       </c>
       <c r="D99" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E99">
         <v>2004</v>
@@ -23942,7 +23942,7 @@
         <v>49</v>
       </c>
       <c r="D100" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E100">
         <v>2004</v>
@@ -23995,7 +23995,7 @@
         <v>49</v>
       </c>
       <c r="D101" t="s">
-        <v>64</v>
+        <v>86</v>
       </c>
       <c r="E101">
         <v>2008</v>
@@ -24048,7 +24048,7 @@
         <v>49</v>
       </c>
       <c r="D102" t="s">
-        <v>64</v>
+        <v>86</v>
       </c>
       <c r="E102">
         <v>2008</v>
@@ -24101,7 +24101,7 @@
         <v>49</v>
       </c>
       <c r="D103" t="s">
-        <v>86</v>
+        <v>66</v>
       </c>
       <c r="E103">
         <v>2002</v>
@@ -24154,7 +24154,7 @@
         <v>49</v>
       </c>
       <c r="D104" t="s">
-        <v>86</v>
+        <v>66</v>
       </c>
       <c r="E104">
         <v>2002</v>
@@ -24207,7 +24207,7 @@
         <v>49</v>
       </c>
       <c r="D105" t="s">
-        <v>86</v>
+        <v>66</v>
       </c>
       <c r="E105">
         <v>2003</v>
@@ -24260,7 +24260,7 @@
         <v>49</v>
       </c>
       <c r="D106" t="s">
-        <v>86</v>
+        <v>66</v>
       </c>
       <c r="E106">
         <v>2003</v>
@@ -24313,7 +24313,7 @@
         <v>49</v>
       </c>
       <c r="D107" t="s">
-        <v>50</v>
+        <v>85</v>
       </c>
       <c r="E107">
         <v>2000</v>
@@ -24366,7 +24366,7 @@
         <v>49</v>
       </c>
       <c r="D108" t="s">
-        <v>50</v>
+        <v>85</v>
       </c>
       <c r="E108">
         <v>2000</v>
@@ -24419,7 +24419,7 @@
         <v>49</v>
       </c>
       <c r="D109" t="s">
-        <v>57</v>
+        <v>74</v>
       </c>
       <c r="E109">
         <v>2007</v>
@@ -24472,7 +24472,7 @@
         <v>49</v>
       </c>
       <c r="D110" t="s">
-        <v>73</v>
+        <v>53</v>
       </c>
       <c r="E110">
         <v>2023</v>
@@ -24525,7 +24525,7 @@
         <v>49</v>
       </c>
       <c r="D111" t="s">
-        <v>73</v>
+        <v>53</v>
       </c>
       <c r="E111">
         <v>2001</v>
@@ -24631,7 +24631,7 @@
         <v>49</v>
       </c>
       <c r="D113" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="E113">
         <v>2010</v>
@@ -24684,7 +24684,7 @@
         <v>49</v>
       </c>
       <c r="D114" t="s">
-        <v>77</v>
+        <v>62</v>
       </c>
       <c r="E114">
         <v>2005</v>
@@ -24737,7 +24737,7 @@
         <v>49</v>
       </c>
       <c r="D115" t="s">
-        <v>77</v>
+        <v>62</v>
       </c>
       <c r="E115">
         <v>2009</v>
@@ -24790,7 +24790,7 @@
         <v>49</v>
       </c>
       <c r="D116" t="s">
-        <v>78</v>
+        <v>64</v>
       </c>
       <c r="E116">
         <v>1997</v>
@@ -24843,7 +24843,7 @@
         <v>49</v>
       </c>
       <c r="D117" t="s">
-        <v>78</v>
+        <v>64</v>
       </c>
       <c r="E117">
         <v>1997</v>
@@ -24896,7 +24896,7 @@
         <v>49</v>
       </c>
       <c r="D118" t="s">
-        <v>78</v>
+        <v>64</v>
       </c>
       <c r="E118">
         <v>1998</v>
@@ -24949,7 +24949,7 @@
         <v>49</v>
       </c>
       <c r="D119" t="s">
-        <v>78</v>
+        <v>64</v>
       </c>
       <c r="E119">
         <v>1999</v>
@@ -25055,7 +25055,7 @@
         <v>49</v>
       </c>
       <c r="D121" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="E121">
         <v>2010</v>
@@ -25108,7 +25108,7 @@
         <v>49</v>
       </c>
       <c r="D122" t="s">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="E122">
         <v>2003</v>
@@ -25161,7 +25161,7 @@
         <v>49</v>
       </c>
       <c r="D123" t="s">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="E123">
         <v>2003</v>
@@ -25214,7 +25214,7 @@
         <v>49</v>
       </c>
       <c r="D124" t="s">
-        <v>81</v>
+        <v>63</v>
       </c>
       <c r="E124">
         <v>2006</v>
@@ -25373,7 +25373,7 @@
         <v>49</v>
       </c>
       <c r="D127" t="s">
-        <v>56</v>
+        <v>72</v>
       </c>
       <c r="E127">
         <v>2002</v>
@@ -25426,7 +25426,7 @@
         <v>49</v>
       </c>
       <c r="D128" t="s">
-        <v>56</v>
+        <v>72</v>
       </c>
       <c r="E128">
         <v>2002</v>
@@ -25479,7 +25479,7 @@
         <v>49</v>
       </c>
       <c r="D129" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="E129">
         <v>2010</v>
@@ -25532,7 +25532,7 @@
         <v>49</v>
       </c>
       <c r="D130" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="E130">
         <v>2010</v>
@@ -25691,7 +25691,7 @@
         <v>49</v>
       </c>
       <c r="D133" t="s">
-        <v>66</v>
+        <v>82</v>
       </c>
       <c r="E133">
         <v>2018</v>
@@ -25744,7 +25744,7 @@
         <v>49</v>
       </c>
       <c r="D134" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E134">
         <v>2006</v>
@@ -25797,7 +25797,7 @@
         <v>49</v>
       </c>
       <c r="D135" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E135">
         <v>2007</v>
@@ -25956,7 +25956,7 @@
         <v>49</v>
       </c>
       <c r="D138" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E138">
         <v>2010</v>
@@ -26009,7 +26009,7 @@
         <v>49</v>
       </c>
       <c r="D139" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E139">
         <v>2010</v>
@@ -26062,7 +26062,7 @@
         <v>49</v>
       </c>
       <c r="D140" t="s">
-        <v>85</v>
+        <v>59</v>
       </c>
       <c r="E140">
         <v>2004</v>
@@ -26115,7 +26115,7 @@
         <v>49</v>
       </c>
       <c r="D141" t="s">
-        <v>85</v>
+        <v>59</v>
       </c>
       <c r="E141">
         <v>2004</v>
@@ -26168,7 +26168,7 @@
         <v>49</v>
       </c>
       <c r="D142" t="s">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="E142">
         <v>2008</v>
@@ -26221,7 +26221,7 @@
         <v>49</v>
       </c>
       <c r="D143" t="s">
-        <v>51</v>
+        <v>87</v>
       </c>
       <c r="E143">
         <v>2007</v>
@@ -26274,7 +26274,7 @@
         <v>49</v>
       </c>
       <c r="D144" t="s">
-        <v>51</v>
+        <v>87</v>
       </c>
       <c r="E144">
         <v>2007</v>
@@ -26327,7 +26327,7 @@
         <v>49</v>
       </c>
       <c r="D145" t="s">
-        <v>54</v>
+        <v>71</v>
       </c>
       <c r="E145">
         <v>2005</v>
@@ -26380,7 +26380,7 @@
         <v>49</v>
       </c>
       <c r="D146" t="s">
-        <v>54</v>
+        <v>71</v>
       </c>
       <c r="E146">
         <v>2005</v>
@@ -26433,7 +26433,7 @@
         <v>49</v>
       </c>
       <c r="D147" t="s">
-        <v>62</v>
+        <v>79</v>
       </c>
       <c r="E147">
         <v>2015</v>
@@ -26486,7 +26486,7 @@
         <v>49</v>
       </c>
       <c r="D148" t="s">
-        <v>62</v>
+        <v>79</v>
       </c>
       <c r="E148">
         <v>2004</v>
@@ -26539,7 +26539,7 @@
         <v>49</v>
       </c>
       <c r="D149" t="s">
-        <v>79</v>
+        <v>65</v>
       </c>
       <c r="E149">
         <v>2006</v>
@@ -26592,7 +26592,7 @@
         <v>49</v>
       </c>
       <c r="D150" t="s">
-        <v>57</v>
+        <v>74</v>
       </c>
       <c r="E150">
         <v>2011</v>
@@ -26751,7 +26751,7 @@
         <v>49</v>
       </c>
       <c r="D153" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="E153">
         <v>2006</v>
@@ -26804,7 +26804,7 @@
         <v>49</v>
       </c>
       <c r="D154" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E154">
         <v>2008</v>
@@ -26963,7 +26963,7 @@
         <v>49</v>
       </c>
       <c r="D157" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E157">
         <v>2023</v>
@@ -27016,7 +27016,7 @@
         <v>49</v>
       </c>
       <c r="D158" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E158">
         <v>2026</v>
@@ -27069,7 +27069,7 @@
         <v>49</v>
       </c>
       <c r="D159" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E159">
         <v>2022</v>
@@ -27122,7 +27122,7 @@
         <v>49</v>
       </c>
       <c r="D160" t="s">
-        <v>80</v>
+        <v>54</v>
       </c>
       <c r="E160">
         <v>2003</v>
@@ -27175,7 +27175,7 @@
         <v>49</v>
       </c>
       <c r="D161" t="s">
-        <v>80</v>
+        <v>54</v>
       </c>
       <c r="E161">
         <v>2003</v>
@@ -27228,7 +27228,7 @@
         <v>49</v>
       </c>
       <c r="D162" t="s">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="E162">
         <v>2003</v>
@@ -27281,7 +27281,7 @@
         <v>49</v>
       </c>
       <c r="D163" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E163">
         <v>2008</v>
@@ -27334,7 +27334,7 @@
         <v>49</v>
       </c>
       <c r="D164" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="E164">
         <v>1999</v>
@@ -27387,7 +27387,7 @@
         <v>49</v>
       </c>
       <c r="D165" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="E165">
         <v>1999</v>
@@ -27440,7 +27440,7 @@
         <v>49</v>
       </c>
       <c r="D166" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E166">
         <v>1997</v>
@@ -27546,7 +27546,7 @@
         <v>49</v>
       </c>
       <c r="D168" t="s">
-        <v>67</v>
+        <v>81</v>
       </c>
       <c r="E168">
         <v>2001</v>
@@ -27599,7 +27599,7 @@
         <v>49</v>
       </c>
       <c r="D169" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E169">
         <v>2006</v>
@@ -27705,7 +27705,7 @@
         <v>49</v>
       </c>
       <c r="D171" t="s">
-        <v>66</v>
+        <v>82</v>
       </c>
       <c r="E171">
         <v>2007</v>
@@ -28288,7 +28288,7 @@
         <v>49</v>
       </c>
       <c r="D182" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E182">
         <v>2015</v>
@@ -29083,7 +29083,7 @@
         <v>49</v>
       </c>
       <c r="D197" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E197">
         <v>2004</v>
@@ -29136,7 +29136,7 @@
         <v>49</v>
       </c>
       <c r="D198" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E198">
         <v>2008</v>
@@ -29348,7 +29348,7 @@
         <v>49</v>
       </c>
       <c r="D202" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="E202">
         <v>2005</v>
@@ -29401,7 +29401,7 @@
         <v>49</v>
       </c>
       <c r="D203" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="E203">
         <v>2015</v>
@@ -30090,7 +30090,7 @@
         <v>49</v>
       </c>
       <c r="D216" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E216">
         <v>2022</v>
@@ -30302,7 +30302,7 @@
         <v>49</v>
       </c>
       <c r="D220" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E220">
         <v>2009</v>
@@ -30991,7 +30991,7 @@
         <v>49</v>
       </c>
       <c r="D233" t="s">
-        <v>85</v>
+        <v>59</v>
       </c>
       <c r="E233">
         <v>1994</v>
@@ -31150,7 +31150,7 @@
         <v>49</v>
       </c>
       <c r="D236" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E236">
         <v>1990</v>
@@ -31203,7 +31203,7 @@
         <v>49</v>
       </c>
       <c r="D237" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E237">
         <v>2022</v>
@@ -31362,7 +31362,7 @@
         <v>49</v>
       </c>
       <c r="D240" t="s">
-        <v>77</v>
+        <v>62</v>
       </c>
       <c r="E240">
         <v>2006</v>
@@ -31415,7 +31415,7 @@
         <v>49</v>
       </c>
       <c r="D241" t="s">
-        <v>54</v>
+        <v>71</v>
       </c>
       <c r="E241">
         <v>2024</v>
@@ -31468,7 +31468,7 @@
         <v>49</v>
       </c>
       <c r="D242" t="s">
-        <v>62</v>
+        <v>79</v>
       </c>
       <c r="E242">
         <v>2023</v>
@@ -31521,7 +31521,7 @@
         <v>49</v>
       </c>
       <c r="D243" t="s">
-        <v>62</v>
+        <v>79</v>
       </c>
       <c r="E243">
         <v>2023</v>
@@ -31574,7 +31574,7 @@
         <v>49</v>
       </c>
       <c r="D244" t="s">
-        <v>66</v>
+        <v>82</v>
       </c>
       <c r="E244">
         <v>1997</v>
@@ -32051,7 +32051,7 @@
         <v>49</v>
       </c>
       <c r="D253" t="s">
-        <v>64</v>
+        <v>86</v>
       </c>
       <c r="E253">
         <v>2008</v>
@@ -32316,7 +32316,7 @@
         <v>49</v>
       </c>
       <c r="D258" t="s">
-        <v>62</v>
+        <v>79</v>
       </c>
       <c r="E258">
         <v>2015</v>
@@ -32422,7 +32422,7 @@
         <v>49</v>
       </c>
       <c r="D260" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E260">
         <v>2004</v>
@@ -32687,7 +32687,7 @@
         <v>49</v>
       </c>
       <c r="D265" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E265">
         <v>2024</v>
@@ -32793,7 +32793,7 @@
         <v>49</v>
       </c>
       <c r="D267" t="s">
-        <v>79</v>
+        <v>65</v>
       </c>
       <c r="E267">
         <v>2023</v>
@@ -33005,7 +33005,7 @@
         <v>49</v>
       </c>
       <c r="D271" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E271">
         <v>1975</v>
@@ -33058,7 +33058,7 @@
         <v>49</v>
       </c>
       <c r="D272" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E272">
         <v>1975</v>
@@ -33111,7 +33111,7 @@
         <v>49</v>
       </c>
       <c r="D273" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E273">
         <v>1975</v>
@@ -33164,7 +33164,7 @@
         <v>49</v>
       </c>
       <c r="D274" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E274">
         <v>2015</v>
@@ -33217,7 +33217,7 @@
         <v>49</v>
       </c>
       <c r="D275" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E275">
         <v>1967</v>
@@ -33270,7 +33270,7 @@
         <v>49</v>
       </c>
       <c r="D276" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E276">
         <v>1971</v>
@@ -33323,7 +33323,7 @@
         <v>49</v>
       </c>
       <c r="D277" t="s">
-        <v>67</v>
+        <v>81</v>
       </c>
       <c r="E277">
         <v>1970</v>
@@ -33376,7 +33376,7 @@
         <v>49</v>
       </c>
       <c r="D278" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E278">
         <v>1978</v>
@@ -33429,7 +33429,7 @@
         <v>49</v>
       </c>
       <c r="D279" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E279">
         <v>1981</v>
@@ -33482,7 +33482,7 @@
         <v>49</v>
       </c>
       <c r="D280" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E280">
         <v>1987</v>
@@ -33906,7 +33906,7 @@
         <v>293</v>
       </c>
       <c r="D288" t="s">
-        <v>78</v>
+        <v>64</v>
       </c>
       <c r="E288">
         <v>1991</v>
@@ -33959,7 +33959,7 @@
         <v>293</v>
       </c>
       <c r="D289" t="s">
-        <v>78</v>
+        <v>64</v>
       </c>
       <c r="E289">
         <v>1991</v>
@@ -35019,25 +35019,25 @@
         <v>308</v>
       </c>
       <c r="D309" t="s">
-        <v>193</v>
+        <v>14</v>
       </c>
       <c r="E309">
         <v>2022</v>
       </c>
       <c r="F309">
-        <v>0.61052976624370348</v>
+        <v>0.11134281451252948</v>
       </c>
       <c r="G309">
         <v>1</v>
       </c>
       <c r="H309">
-        <v>2750</v>
+        <v>3162.5000000000005</v>
       </c>
       <c r="I309">
-        <v>55.000000000000007</v>
+        <v>60.500000000000014</v>
       </c>
       <c r="J309">
-        <v>2.1</v>
+        <v>2.3100000000000005</v>
       </c>
       <c r="K309">
         <v>100</v>
@@ -35078,7 +35078,7 @@
         <v>2022</v>
       </c>
       <c r="F310">
-        <v>6.0310691194286808E-2</v>
+        <v>0.10670353057450742</v>
       </c>
       <c r="G310">
         <v>1</v>
@@ -35125,13 +35125,13 @@
         <v>308</v>
       </c>
       <c r="D311" t="s">
-        <v>310</v>
+        <v>18</v>
       </c>
       <c r="E311">
         <v>2022</v>
       </c>
       <c r="F311">
-        <v>0.10067246145507874</v>
+        <v>8.7682466428616976E-2</v>
       </c>
       <c r="G311">
         <v>1</v>
@@ -35140,7 +35140,7 @@
         <v>3162.5000000000005</v>
       </c>
       <c r="I311">
-        <v>60.500000000000014</v>
+        <v>60.500000000000007</v>
       </c>
       <c r="J311">
         <v>2.3100000000000005</v>
@@ -35178,25 +35178,25 @@
         <v>308</v>
       </c>
       <c r="D312" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="E312">
         <v>2022</v>
       </c>
       <c r="F312">
-        <v>4.4073197411209589E-2</v>
+        <v>5.1032123318242681E-2</v>
       </c>
       <c r="G312">
         <v>1</v>
       </c>
       <c r="H312">
-        <v>3712.5000000000005</v>
+        <v>3162.5000000000005</v>
       </c>
       <c r="I312">
-        <v>71.5</v>
+        <v>60.500000000000021</v>
       </c>
       <c r="J312">
-        <v>2.52</v>
+        <v>2.3100000000000005</v>
       </c>
       <c r="K312">
         <v>100</v>
@@ -35231,13 +35231,13 @@
         <v>308</v>
       </c>
       <c r="D313" t="s">
-        <v>20</v>
+        <v>239</v>
       </c>
       <c r="E313">
         <v>2022</v>
       </c>
       <c r="F313">
-        <v>8.7682466428616976E-2</v>
+        <v>0.22871669814448767</v>
       </c>
       <c r="G313">
         <v>1</v>
@@ -35246,7 +35246,7 @@
         <v>3162.5000000000005</v>
       </c>
       <c r="I313">
-        <v>60.500000000000007</v>
+        <v>60.500000000000014</v>
       </c>
       <c r="J313">
         <v>2.3100000000000005</v>
@@ -35284,13 +35284,13 @@
         <v>308</v>
       </c>
       <c r="D314" t="s">
-        <v>312</v>
+        <v>204</v>
       </c>
       <c r="E314">
         <v>2022</v>
       </c>
       <c r="F314">
-        <v>0.15541601192373908</v>
+        <v>7.8403898552572848E-2</v>
       </c>
       <c r="G314">
         <v>1</v>
@@ -35337,13 +35337,13 @@
         <v>308</v>
       </c>
       <c r="D315" t="s">
-        <v>21</v>
+        <v>311</v>
       </c>
       <c r="E315">
         <v>2022</v>
       </c>
       <c r="F315">
-        <v>0.11134281451252948</v>
+        <v>0.1577356538927501</v>
       </c>
       <c r="G315">
         <v>1</v>
@@ -35390,13 +35390,13 @@
         <v>308</v>
       </c>
       <c r="D316" t="s">
-        <v>99</v>
+        <v>312</v>
       </c>
       <c r="E316">
         <v>2022</v>
       </c>
       <c r="F316">
-        <v>0.29181095970158766</v>
+        <v>0.13036387865841995</v>
       </c>
       <c r="G316">
         <v>1</v>
@@ -35449,19 +35449,19 @@
         <v>2022</v>
       </c>
       <c r="F317">
-        <v>4.1753555442198553E-2</v>
+        <v>0.20320063648536632</v>
       </c>
       <c r="G317">
         <v>1</v>
       </c>
       <c r="H317">
-        <v>3712.5000000000005</v>
+        <v>3162.5000000000005</v>
       </c>
       <c r="I317">
-        <v>71.5</v>
+        <v>60.500000000000014</v>
       </c>
       <c r="J317">
-        <v>2.52</v>
+        <v>2.3100000000000005</v>
       </c>
       <c r="K317">
         <v>100</v>
@@ -35502,7 +35502,7 @@
         <v>2022</v>
       </c>
       <c r="F318">
-        <v>0.35629700644009438</v>
+        <v>0.54140443556717466</v>
       </c>
       <c r="G318">
         <v>1</v>
@@ -35511,7 +35511,7 @@
         <v>2750</v>
       </c>
       <c r="I318">
-        <v>55</v>
+        <v>55.000000000000007</v>
       </c>
       <c r="J318">
         <v>2.1</v>
@@ -35549,25 +35549,25 @@
         <v>308</v>
       </c>
       <c r="D319" t="s">
-        <v>64</v>
+        <v>315</v>
       </c>
       <c r="E319">
         <v>2022</v>
       </c>
       <c r="F319">
-        <v>5.4743550468660328E-2</v>
+        <v>4.3145340623605172E-2</v>
       </c>
       <c r="G319">
         <v>1</v>
       </c>
       <c r="H319">
-        <v>3162.5000000000005</v>
+        <v>3712.5000000000005</v>
       </c>
       <c r="I319">
-        <v>60.500000000000014</v>
+        <v>71.5</v>
       </c>
       <c r="J319">
-        <v>2.3100000000000005</v>
+        <v>2.52</v>
       </c>
       <c r="K319">
         <v>100</v>
@@ -35602,13 +35602,13 @@
         <v>308</v>
       </c>
       <c r="D320" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="E320">
         <v>2022</v>
       </c>
       <c r="F320">
-        <v>6.3558189950902247E-2</v>
+        <v>0.19299421182171778</v>
       </c>
       <c r="G320">
         <v>1</v>
@@ -35655,25 +35655,25 @@
         <v>308</v>
       </c>
       <c r="D321" t="s">
-        <v>204</v>
+        <v>317</v>
       </c>
       <c r="E321">
         <v>2022</v>
       </c>
       <c r="F321">
-        <v>7.8403898552572848E-2</v>
+        <v>0.35629700644009438</v>
       </c>
       <c r="G321">
         <v>1</v>
       </c>
       <c r="H321">
-        <v>3162.5000000000005</v>
+        <v>2750</v>
       </c>
       <c r="I321">
-        <v>60.500000000000014</v>
+        <v>55</v>
       </c>
       <c r="J321">
-        <v>2.3100000000000005</v>
+        <v>2.1</v>
       </c>
       <c r="K321">
         <v>100</v>
@@ -35708,13 +35708,13 @@
         <v>308</v>
       </c>
       <c r="D322" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="E322">
         <v>2022</v>
       </c>
       <c r="F322">
-        <v>0.19299421182171778</v>
+        <v>5.8918906012880183E-2</v>
       </c>
       <c r="G322">
         <v>1</v>
@@ -35723,7 +35723,7 @@
         <v>3162.5000000000005</v>
       </c>
       <c r="I322">
-        <v>60.500000000000014</v>
+        <v>60.500000000000021</v>
       </c>
       <c r="J322">
         <v>2.3100000000000005</v>
@@ -35761,25 +35761,25 @@
         <v>308</v>
       </c>
       <c r="D323" t="s">
-        <v>239</v>
+        <v>319</v>
       </c>
       <c r="E323">
         <v>2022</v>
       </c>
       <c r="F323">
-        <v>0.22871669814448767</v>
+        <v>4.4073197411209589E-2</v>
       </c>
       <c r="G323">
         <v>1</v>
       </c>
       <c r="H323">
-        <v>3162.5000000000005</v>
+        <v>3712.5000000000005</v>
       </c>
       <c r="I323">
-        <v>60.500000000000014</v>
+        <v>71.5</v>
       </c>
       <c r="J323">
-        <v>2.3100000000000005</v>
+        <v>2.52</v>
       </c>
       <c r="K323">
         <v>100</v>
@@ -35814,13 +35814,13 @@
         <v>308</v>
       </c>
       <c r="D324" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="E324">
         <v>2022</v>
       </c>
       <c r="F324">
-        <v>1.0883760118599757</v>
+        <v>0.56367299846968055</v>
       </c>
       <c r="G324">
         <v>1</v>
@@ -35867,13 +35867,13 @@
         <v>308</v>
       </c>
       <c r="D325" t="s">
-        <v>318</v>
+        <v>99</v>
       </c>
       <c r="E325">
         <v>2022</v>
       </c>
       <c r="F325">
-        <v>0.1577356538927501</v>
+        <v>0.29181095970158766</v>
       </c>
       <c r="G325">
         <v>1</v>
@@ -35920,25 +35920,25 @@
         <v>308</v>
       </c>
       <c r="D326" t="s">
-        <v>319</v>
+        <v>193</v>
       </c>
       <c r="E326">
         <v>2022</v>
       </c>
       <c r="F326">
-        <v>5.1032123318242681E-2</v>
+        <v>0.61052976624370348</v>
       </c>
       <c r="G326">
         <v>1</v>
       </c>
       <c r="H326">
-        <v>3162.5000000000005</v>
+        <v>2750</v>
       </c>
       <c r="I326">
-        <v>60.500000000000021</v>
+        <v>55.000000000000007</v>
       </c>
       <c r="J326">
-        <v>2.3100000000000005</v>
+        <v>2.1</v>
       </c>
       <c r="K326">
         <v>100</v>
@@ -35973,13 +35973,13 @@
         <v>308</v>
       </c>
       <c r="D327" t="s">
-        <v>320</v>
+        <v>70</v>
       </c>
       <c r="E327">
         <v>2022</v>
       </c>
       <c r="F327">
-        <v>0.13036387865841995</v>
+        <v>0.23196419690110309</v>
       </c>
       <c r="G327">
         <v>1</v>
@@ -36026,25 +36026,25 @@
         <v>308</v>
       </c>
       <c r="D328" t="s">
-        <v>321</v>
+        <v>291</v>
       </c>
       <c r="E328">
         <v>2022</v>
       </c>
       <c r="F328">
-        <v>0.57944656385895543</v>
+        <v>0.13082780705222213</v>
       </c>
       <c r="G328">
         <v>1</v>
       </c>
       <c r="H328">
-        <v>2750</v>
+        <v>3162.5000000000005</v>
       </c>
       <c r="I328">
-        <v>55.000000000000007</v>
+        <v>60.500000000000014</v>
       </c>
       <c r="J328">
-        <v>2.1</v>
+        <v>2.3100000000000005</v>
       </c>
       <c r="K328">
         <v>100</v>
@@ -36079,13 +36079,13 @@
         <v>308</v>
       </c>
       <c r="D329" t="s">
-        <v>322</v>
+        <v>151</v>
       </c>
       <c r="E329">
         <v>2022</v>
       </c>
       <c r="F329">
-        <v>4.4073197411209589E-2</v>
+        <v>4.5464982592616207E-2</v>
       </c>
       <c r="G329">
         <v>1</v>
@@ -36132,25 +36132,25 @@
         <v>308</v>
       </c>
       <c r="D330" t="s">
-        <v>291</v>
+        <v>321</v>
       </c>
       <c r="E330">
         <v>2022</v>
       </c>
       <c r="F330">
-        <v>0.13082780705222213</v>
+        <v>4.1753555442198553E-2</v>
       </c>
       <c r="G330">
         <v>1</v>
       </c>
       <c r="H330">
-        <v>3162.5000000000005</v>
+        <v>3712.5000000000005</v>
       </c>
       <c r="I330">
-        <v>60.500000000000014</v>
+        <v>71.5</v>
       </c>
       <c r="J330">
-        <v>2.3100000000000005</v>
+        <v>2.52</v>
       </c>
       <c r="K330">
         <v>100</v>
@@ -36185,13 +36185,13 @@
         <v>308</v>
       </c>
       <c r="D331" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="E331">
         <v>2022</v>
       </c>
       <c r="F331">
-        <v>6.9589259070330922E-2</v>
+        <v>0.10067246145507874</v>
       </c>
       <c r="G331">
         <v>1</v>
@@ -36200,7 +36200,7 @@
         <v>3162.5000000000005</v>
       </c>
       <c r="I331">
-        <v>60.500000000000007</v>
+        <v>60.500000000000014</v>
       </c>
       <c r="J331">
         <v>2.3100000000000005</v>
@@ -36238,25 +36238,25 @@
         <v>308</v>
       </c>
       <c r="D332" t="s">
-        <v>75</v>
+        <v>323</v>
       </c>
       <c r="E332">
         <v>2022</v>
       </c>
       <c r="F332">
-        <v>0.50939337639482241</v>
+        <v>4.4073197411209589E-2</v>
       </c>
       <c r="G332">
         <v>1</v>
       </c>
       <c r="H332">
-        <v>2750</v>
+        <v>3712.5000000000005</v>
       </c>
       <c r="I332">
-        <v>55.000000000000007</v>
+        <v>71.5</v>
       </c>
       <c r="J332">
-        <v>2.1</v>
+        <v>2.52</v>
       </c>
       <c r="K332">
         <v>100</v>
@@ -36297,7 +36297,7 @@
         <v>2022</v>
       </c>
       <c r="F333">
-        <v>0.10670353057450742</v>
+        <v>6.9589259070330922E-2</v>
       </c>
       <c r="G333">
         <v>1</v>
@@ -36306,7 +36306,7 @@
         <v>3162.5000000000005</v>
       </c>
       <c r="I333">
-        <v>60.500000000000014</v>
+        <v>60.500000000000007</v>
       </c>
       <c r="J333">
         <v>2.3100000000000005</v>
@@ -36344,13 +36344,13 @@
         <v>308</v>
       </c>
       <c r="D334" t="s">
-        <v>63</v>
+        <v>325</v>
       </c>
       <c r="E334">
         <v>2022</v>
       </c>
       <c r="F334">
-        <v>0.23196419690110309</v>
+        <v>6.0310691194286808E-2</v>
       </c>
       <c r="G334">
         <v>1</v>
@@ -36397,13 +36397,13 @@
         <v>308</v>
       </c>
       <c r="D335" t="s">
-        <v>325</v>
+        <v>86</v>
       </c>
       <c r="E335">
         <v>2022</v>
       </c>
       <c r="F335">
-        <v>5.8918906012880183E-2</v>
+        <v>5.4743550468660328E-2</v>
       </c>
       <c r="G335">
         <v>1</v>
@@ -36412,7 +36412,7 @@
         <v>3162.5000000000005</v>
       </c>
       <c r="I335">
-        <v>60.500000000000021</v>
+        <v>60.500000000000014</v>
       </c>
       <c r="J335">
         <v>2.3100000000000005</v>
@@ -36450,25 +36450,25 @@
         <v>308</v>
       </c>
       <c r="D336" t="s">
-        <v>151</v>
+        <v>326</v>
       </c>
       <c r="E336">
         <v>2022</v>
       </c>
       <c r="F336">
-        <v>4.5464982592616207E-2</v>
+        <v>6.3558189950902247E-2</v>
       </c>
       <c r="G336">
         <v>1</v>
       </c>
       <c r="H336">
-        <v>3712.5000000000005</v>
+        <v>3162.5000000000005</v>
       </c>
       <c r="I336">
-        <v>71.5</v>
+        <v>60.500000000000014</v>
       </c>
       <c r="J336">
-        <v>2.52</v>
+        <v>2.3100000000000005</v>
       </c>
       <c r="K336">
         <v>100</v>
@@ -36503,13 +36503,13 @@
         <v>308</v>
       </c>
       <c r="D337" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="E337">
         <v>2022</v>
       </c>
       <c r="F337">
-        <v>0.56367299846968055</v>
+        <v>0.57944656385895543</v>
       </c>
       <c r="G337">
         <v>1</v>
@@ -36556,25 +36556,25 @@
         <v>308</v>
       </c>
       <c r="D338" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="E338">
         <v>2022</v>
       </c>
       <c r="F338">
-        <v>0.54140443556717466</v>
+        <v>0.15541601192373908</v>
       </c>
       <c r="G338">
         <v>1</v>
       </c>
       <c r="H338">
-        <v>2750</v>
+        <v>3162.5000000000005</v>
       </c>
       <c r="I338">
-        <v>55.000000000000007</v>
+        <v>60.500000000000014</v>
       </c>
       <c r="J338">
-        <v>2.1</v>
+        <v>2.3100000000000005</v>
       </c>
       <c r="K338">
         <v>100</v>
@@ -36609,25 +36609,25 @@
         <v>308</v>
       </c>
       <c r="D339" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="E339">
         <v>2022</v>
       </c>
       <c r="F339">
-        <v>0.20320063648536632</v>
+        <v>1.0883760118599757</v>
       </c>
       <c r="G339">
         <v>1</v>
       </c>
       <c r="H339">
-        <v>3162.5000000000005</v>
+        <v>2750</v>
       </c>
       <c r="I339">
-        <v>60.500000000000014</v>
+        <v>55.000000000000007</v>
       </c>
       <c r="J339">
-        <v>2.3100000000000005</v>
+        <v>2.1</v>
       </c>
       <c r="K339">
         <v>100</v>
@@ -36662,25 +36662,25 @@
         <v>308</v>
       </c>
       <c r="D340" t="s">
-        <v>329</v>
+        <v>76</v>
       </c>
       <c r="E340">
         <v>2022</v>
       </c>
       <c r="F340">
-        <v>4.3145340623605172E-2</v>
+        <v>0.50939337639482241</v>
       </c>
       <c r="G340">
         <v>1</v>
       </c>
       <c r="H340">
-        <v>3712.5000000000005</v>
+        <v>2750</v>
       </c>
       <c r="I340">
-        <v>71.5</v>
+        <v>55.000000000000007</v>
       </c>
       <c r="J340">
-        <v>2.52</v>
+        <v>2.1</v>
       </c>
       <c r="K340">
         <v>100</v>
@@ -36768,7 +36768,7 @@
         <v>308</v>
       </c>
       <c r="D342" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="E342">
         <v>1959</v>
@@ -36874,7 +36874,7 @@
         <v>308</v>
       </c>
       <c r="D344" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E344">
         <v>1973</v>
@@ -36980,7 +36980,7 @@
         <v>308</v>
       </c>
       <c r="D346" t="s">
-        <v>317</v>
+        <v>329</v>
       </c>
       <c r="E346">
         <v>1963</v>
@@ -37086,7 +37086,7 @@
         <v>308</v>
       </c>
       <c r="D348" t="s">
-        <v>310</v>
+        <v>322</v>
       </c>
       <c r="E348">
         <v>1931</v>
@@ -37139,7 +37139,7 @@
         <v>308</v>
       </c>
       <c r="D349" t="s">
-        <v>327</v>
+        <v>314</v>
       </c>
       <c r="E349">
         <v>1949</v>
@@ -37192,7 +37192,7 @@
         <v>308</v>
       </c>
       <c r="D350" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="E350">
         <v>1951</v>
@@ -37298,7 +37298,7 @@
         <v>308</v>
       </c>
       <c r="D352" t="s">
-        <v>309</v>
+        <v>325</v>
       </c>
       <c r="E352">
         <v>1958</v>
@@ -37351,7 +37351,7 @@
         <v>308</v>
       </c>
       <c r="D353" t="s">
-        <v>324</v>
+        <v>309</v>
       </c>
       <c r="E353">
         <v>1967</v>
@@ -37404,7 +37404,7 @@
         <v>308</v>
       </c>
       <c r="D354" t="s">
-        <v>328</v>
+        <v>313</v>
       </c>
       <c r="E354">
         <v>1968</v>
@@ -37457,7 +37457,7 @@
         <v>308</v>
       </c>
       <c r="D355" t="s">
-        <v>326</v>
+        <v>320</v>
       </c>
       <c r="E355">
         <v>1929</v>
@@ -37510,7 +37510,7 @@
         <v>308</v>
       </c>
       <c r="D356" t="s">
-        <v>328</v>
+        <v>313</v>
       </c>
       <c r="E356">
         <v>1949</v>
@@ -37616,7 +37616,7 @@
         <v>308</v>
       </c>
       <c r="D358" t="s">
-        <v>64</v>
+        <v>86</v>
       </c>
       <c r="E358">
         <v>1952</v>
@@ -37669,7 +37669,7 @@
         <v>308</v>
       </c>
       <c r="D359" t="s">
-        <v>326</v>
+        <v>320</v>
       </c>
       <c r="E359">
         <v>1913</v>
@@ -37722,7 +37722,7 @@
         <v>308</v>
       </c>
       <c r="D360" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="E360">
         <v>1924</v>
@@ -37828,7 +37828,7 @@
         <v>308</v>
       </c>
       <c r="D362" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="E362">
         <v>1971</v>
@@ -37934,7 +37934,7 @@
         <v>308</v>
       </c>
       <c r="D364" t="s">
-        <v>329</v>
+        <v>315</v>
       </c>
       <c r="E364">
         <v>1927</v>
@@ -37987,7 +37987,7 @@
         <v>308</v>
       </c>
       <c r="D365" t="s">
-        <v>317</v>
+        <v>329</v>
       </c>
       <c r="E365">
         <v>1928</v>
@@ -38093,7 +38093,7 @@
         <v>308</v>
       </c>
       <c r="D367" t="s">
-        <v>317</v>
+        <v>329</v>
       </c>
       <c r="E367">
         <v>1938</v>
@@ -38146,7 +38146,7 @@
         <v>308</v>
       </c>
       <c r="D368" t="s">
-        <v>311</v>
+        <v>323</v>
       </c>
       <c r="E368">
         <v>1920</v>
@@ -38199,7 +38199,7 @@
         <v>308</v>
       </c>
       <c r="D369" t="s">
-        <v>317</v>
+        <v>329</v>
       </c>
       <c r="E369">
         <v>1947</v>
@@ -38252,7 +38252,7 @@
         <v>308</v>
       </c>
       <c r="D370" t="s">
-        <v>318</v>
+        <v>311</v>
       </c>
       <c r="E370">
         <v>1950</v>
@@ -38305,7 +38305,7 @@
         <v>308</v>
       </c>
       <c r="D371" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E371">
         <v>1954</v>
@@ -38411,7 +38411,7 @@
         <v>308</v>
       </c>
       <c r="D373" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="E373">
         <v>1971</v>
@@ -38464,7 +38464,7 @@
         <v>308</v>
       </c>
       <c r="D374" t="s">
-        <v>310</v>
+        <v>322</v>
       </c>
       <c r="E374">
         <v>1959</v>
@@ -38570,7 +38570,7 @@
         <v>308</v>
       </c>
       <c r="D376" t="s">
-        <v>317</v>
+        <v>329</v>
       </c>
       <c r="E376">
         <v>1955</v>
@@ -38623,7 +38623,7 @@
         <v>308</v>
       </c>
       <c r="D377" t="s">
-        <v>317</v>
+        <v>329</v>
       </c>
       <c r="E377">
         <v>1959</v>
@@ -38676,7 +38676,7 @@
         <v>308</v>
       </c>
       <c r="D378" t="s">
-        <v>317</v>
+        <v>329</v>
       </c>
       <c r="E378">
         <v>1954</v>
@@ -38888,7 +38888,7 @@
         <v>308</v>
       </c>
       <c r="D382" t="s">
-        <v>87</v>
+        <v>50</v>
       </c>
       <c r="E382">
         <v>2022</v>
@@ -39100,7 +39100,7 @@
         <v>308</v>
       </c>
       <c r="D386" t="s">
-        <v>62</v>
+        <v>79</v>
       </c>
       <c r="E386">
         <v>2022</v>
@@ -39206,7 +39206,7 @@
         <v>383</v>
       </c>
       <c r="D388" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="E388">
         <v>1989</v>
@@ -39259,7 +39259,7 @@
         <v>383</v>
       </c>
       <c r="D389" t="s">
-        <v>320</v>
+        <v>312</v>
       </c>
       <c r="E389">
         <v>1975</v>
@@ -39312,7 +39312,7 @@
         <v>383</v>
       </c>
       <c r="D390" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E390">
         <v>1966</v>
@@ -39365,7 +39365,7 @@
         <v>383</v>
       </c>
       <c r="D391" t="s">
-        <v>317</v>
+        <v>329</v>
       </c>
       <c r="E391">
         <v>2015</v>
@@ -39418,7 +39418,7 @@
         <v>383</v>
       </c>
       <c r="D392" t="s">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="E392">
         <v>2015</v>
@@ -39471,7 +39471,7 @@
         <v>383</v>
       </c>
       <c r="D393" t="s">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="E393">
         <v>1982</v>
@@ -39524,7 +39524,7 @@
         <v>383</v>
       </c>
       <c r="D394" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="E394">
         <v>2015</v>
@@ -39577,7 +39577,7 @@
         <v>383</v>
       </c>
       <c r="D395" t="s">
-        <v>315</v>
+        <v>326</v>
       </c>
       <c r="E395">
         <v>2015</v>
@@ -39630,7 +39630,7 @@
         <v>383</v>
       </c>
       <c r="D396" t="s">
-        <v>62</v>
+        <v>79</v>
       </c>
       <c r="E396">
         <v>1961</v>
@@ -39683,7 +39683,7 @@
         <v>383</v>
       </c>
       <c r="D397" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="E397">
         <v>2005</v>
@@ -39736,7 +39736,7 @@
         <v>383</v>
       </c>
       <c r="D398" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E398">
         <v>1991</v>
@@ -39895,7 +39895,7 @@
         <v>383</v>
       </c>
       <c r="D401" t="s">
-        <v>326</v>
+        <v>320</v>
       </c>
       <c r="E401">
         <v>1971</v>
@@ -39948,7 +39948,7 @@
         <v>383</v>
       </c>
       <c r="D402" t="s">
-        <v>318</v>
+        <v>311</v>
       </c>
       <c r="E402">
         <v>1973</v>
@@ -40107,7 +40107,7 @@
         <v>383</v>
       </c>
       <c r="D405" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="E405">
         <v>1978</v>
@@ -40160,7 +40160,7 @@
         <v>383</v>
       </c>
       <c r="D406" t="s">
-        <v>327</v>
+        <v>314</v>
       </c>
       <c r="E406">
         <v>1923</v>
@@ -40213,7 +40213,7 @@
         <v>308</v>
       </c>
       <c r="D407" t="s">
-        <v>325</v>
+        <v>318</v>
       </c>
       <c r="E407">
         <v>1959</v>
@@ -40319,7 +40319,7 @@
         <v>308</v>
       </c>
       <c r="D409" t="s">
-        <v>317</v>
+        <v>329</v>
       </c>
       <c r="E409">
         <v>1949</v>
@@ -40372,7 +40372,7 @@
         <v>308</v>
       </c>
       <c r="D410" t="s">
-        <v>312</v>
+        <v>328</v>
       </c>
       <c r="E410">
         <v>1953</v>
@@ -40478,7 +40478,7 @@
         <v>308</v>
       </c>
       <c r="D412" t="s">
-        <v>317</v>
+        <v>329</v>
       </c>
       <c r="E412">
         <v>1960</v>
@@ -40531,7 +40531,7 @@
         <v>308</v>
       </c>
       <c r="D413" t="s">
-        <v>313</v>
+        <v>321</v>
       </c>
       <c r="E413">
         <v>1962</v>
@@ -40584,7 +40584,7 @@
         <v>308</v>
       </c>
       <c r="D414" t="s">
-        <v>327</v>
+        <v>314</v>
       </c>
       <c r="E414">
         <v>2015</v>
@@ -40637,7 +40637,7 @@
         <v>308</v>
       </c>
       <c r="D415" t="s">
-        <v>328</v>
+        <v>313</v>
       </c>
       <c r="E415">
         <v>1927</v>
@@ -40690,7 +40690,7 @@
         <v>308</v>
       </c>
       <c r="D416" t="s">
-        <v>319</v>
+        <v>310</v>
       </c>
       <c r="E416">
         <v>1954</v>
@@ -40796,7 +40796,7 @@
         <v>308</v>
       </c>
       <c r="D418" t="s">
-        <v>327</v>
+        <v>314</v>
       </c>
       <c r="E418">
         <v>1956</v>
@@ -40849,7 +40849,7 @@
         <v>308</v>
       </c>
       <c r="D419" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="E419">
         <v>1956</v>
@@ -40955,7 +40955,7 @@
         <v>308</v>
       </c>
       <c r="D421" t="s">
-        <v>327</v>
+        <v>314</v>
       </c>
       <c r="E421">
         <v>1960</v>
@@ -41167,7 +41167,7 @@
         <v>308</v>
       </c>
       <c r="D425" t="s">
-        <v>328</v>
+        <v>313</v>
       </c>
       <c r="E425">
         <v>2015</v>
@@ -41220,7 +41220,7 @@
         <v>308</v>
       </c>
       <c r="D426" t="s">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="E426">
         <v>2015</v>
@@ -41326,7 +41326,7 @@
         <v>308</v>
       </c>
       <c r="D428" t="s">
-        <v>87</v>
+        <v>50</v>
       </c>
       <c r="E428">
         <v>1955</v>
@@ -41379,7 +41379,7 @@
         <v>308</v>
       </c>
       <c r="D429" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E429">
         <v>2015</v>
@@ -41485,7 +41485,7 @@
         <v>308</v>
       </c>
       <c r="D431" t="s">
-        <v>329</v>
+        <v>315</v>
       </c>
       <c r="E431">
         <v>1932</v>
@@ -41644,7 +41644,7 @@
         <v>308</v>
       </c>
       <c r="D434" t="s">
-        <v>326</v>
+        <v>320</v>
       </c>
       <c r="E434">
         <v>1924</v>
@@ -41750,7 +41750,7 @@
         <v>308</v>
       </c>
       <c r="D436" t="s">
-        <v>326</v>
+        <v>320</v>
       </c>
       <c r="E436">
         <v>2002</v>
@@ -41856,7 +41856,7 @@
         <v>308</v>
       </c>
       <c r="D438" t="s">
-        <v>317</v>
+        <v>329</v>
       </c>
       <c r="E438">
         <v>1948</v>
@@ -41962,7 +41962,7 @@
         <v>308</v>
       </c>
       <c r="D440" t="s">
-        <v>311</v>
+        <v>323</v>
       </c>
       <c r="E440">
         <v>1914</v>
@@ -42068,7 +42068,7 @@
         <v>308</v>
       </c>
       <c r="D442" t="s">
-        <v>64</v>
+        <v>86</v>
       </c>
       <c r="E442">
         <v>1958</v>
@@ -42121,7 +42121,7 @@
         <v>439</v>
       </c>
       <c r="D443" t="s">
-        <v>73</v>
+        <v>53</v>
       </c>
       <c r="E443">
         <v>1992</v>
@@ -42280,7 +42280,7 @@
         <v>439</v>
       </c>
       <c r="D446" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E446">
         <v>1992</v>
@@ -42333,7 +42333,7 @@
         <v>439</v>
       </c>
       <c r="D447" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E447">
         <v>2005</v>
@@ -42598,7 +42598,7 @@
         <v>439</v>
       </c>
       <c r="D452" t="s">
-        <v>73</v>
+        <v>53</v>
       </c>
       <c r="E452">
         <v>1985</v>
@@ -42940,7 +42940,7 @@
         <v>33</v>
       </c>
       <c r="L458">
-        <v>0.20730554769553747</v>
+        <v>0.20730554769553741</v>
       </c>
       <c r="N458" t="s">
         <v>809</v>
@@ -42996,7 +42996,7 @@
         <v>33</v>
       </c>
       <c r="L459">
-        <v>0.20730554769553747</v>
+        <v>0.20730554769553741</v>
       </c>
       <c r="N459" t="s">
         <v>809</v>
@@ -43052,7 +43052,7 @@
         <v>33</v>
       </c>
       <c r="L460">
-        <v>0.20730554769553747</v>
+        <v>0.20730554769553741</v>
       </c>
       <c r="N460" t="s">
         <v>809</v>
@@ -51156,7 +51156,7 @@
         <v>2022</v>
       </c>
       <c r="F618">
-        <v>0.69928302455480262</v>
+        <v>0.6793056475905862</v>
       </c>
       <c r="G618">
         <v>0.33123000000000002</v>
@@ -51179,7 +51179,7 @@
         <v>2022</v>
       </c>
       <c r="F619">
-        <v>0.6793056475905862</v>
+        <v>0.69928302455480262</v>
       </c>
       <c r="G619">
         <v>0.33123000000000002</v>
@@ -51449,7 +51449,7 @@
         <v>663</v>
       </c>
       <c r="D631" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="E631">
         <v>2018</v>

--- a/VerveStacks_ITA_grids/vt_vervestacks_ITA_v1.xlsx
+++ b/VerveStacks_ITA_grids/vt_vervestacks_ITA_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{42129CE0-ACF3-4BA9-8079-71ABF5135AE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{17CC1CF1-C667-4724-8500-E92D040965CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{759BFB8F-310B-4985-8F67-E13AE06D1BDA}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{DAB421F1-2271-42C0-99F4-CCC3CB460F73}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="2" r:id="rId1"/>
@@ -84,27 +84,27 @@
     <t>e_w144005863-380</t>
   </si>
   <si>
+    <t>e_w81938081-380</t>
+  </si>
+  <si>
+    <t>e_w108020416-380</t>
+  </si>
+  <si>
+    <t>e_w109756016-380</t>
+  </si>
+  <si>
+    <t>e_w34157795-380</t>
+  </si>
+  <si>
+    <t>e_w84696559-380</t>
+  </si>
+  <si>
+    <t>e_w98902899-380</t>
+  </si>
+  <si>
     <t>e_w58440884-380</t>
   </si>
   <si>
-    <t>e_w81938081-380</t>
-  </si>
-  <si>
-    <t>e_w34157795-380</t>
-  </si>
-  <si>
-    <t>e_w108020416-380</t>
-  </si>
-  <si>
-    <t>e_w109756016-380</t>
-  </si>
-  <si>
-    <t>e_w98902899-380</t>
-  </si>
-  <si>
-    <t>e_w84696559-380</t>
-  </si>
-  <si>
     <t>ep_bioenergy_G100000200236</t>
   </si>
   <si>
@@ -141,18 +141,18 @@
     <t>coal</t>
   </si>
   <si>
+    <t>e_w409439916-380</t>
+  </si>
+  <si>
     <t>e_w418902800-380</t>
   </si>
   <si>
+    <t>e_w82767145-380</t>
+  </si>
+  <si>
     <t>e_w303915533-380</t>
   </si>
   <si>
-    <t>e_w82767145-380</t>
-  </si>
-  <si>
-    <t>e_w409439916-380</t>
-  </si>
-  <si>
     <t>ep_coal_subcritical_G100000102764</t>
   </si>
   <si>
@@ -198,108 +198,108 @@
     <t>e_w98900549-380</t>
   </si>
   <si>
+    <t>e_w172302572-380</t>
+  </si>
+  <si>
+    <t>e_w432729521-380</t>
+  </si>
+  <si>
+    <t>e_w109993642-380</t>
+  </si>
+  <si>
+    <t>e_w103653592-380</t>
+  </si>
+  <si>
+    <t>e_w199675964-380</t>
+  </si>
+  <si>
+    <t>e_w181125039-380</t>
+  </si>
+  <si>
+    <t>e_w133601335-380</t>
+  </si>
+  <si>
+    <t>e_w103381531-380</t>
+  </si>
+  <si>
+    <t>e_w59462715-380</t>
+  </si>
+  <si>
+    <t>e_w421827453-380</t>
+  </si>
+  <si>
+    <t>e_w1137611914-380</t>
+  </si>
+  <si>
+    <t>e_w149997403-380</t>
+  </si>
+  <si>
     <t>e_w100407576-380</t>
   </si>
   <si>
-    <t>e_w149997403-380</t>
+    <t>e_w60725875-380</t>
+  </si>
+  <si>
+    <t>e_w145665799-380</t>
+  </si>
+  <si>
+    <t>e_w158739183-380</t>
+  </si>
+  <si>
+    <t>e_w103974940-380</t>
+  </si>
+  <si>
+    <t>e_w82084019-380</t>
+  </si>
+  <si>
+    <t>e_w338753171-380</t>
+  </si>
+  <si>
+    <t>e_w162960205-380</t>
+  </si>
+  <si>
+    <t>e_w61157826-380</t>
+  </si>
+  <si>
+    <t>e_w98421779-380</t>
+  </si>
+  <si>
+    <t>e_w419423704-380</t>
+  </si>
+  <si>
+    <t>e_w116797658-380</t>
+  </si>
+  <si>
+    <t>e_w414663585-380</t>
+  </si>
+  <si>
+    <t>e_w255011550-380</t>
+  </si>
+  <si>
+    <t>e_w105581403-380</t>
+  </si>
+  <si>
+    <t>e_w82078641-380</t>
   </si>
   <si>
     <t>e_w339104227-380</t>
   </si>
   <si>
-    <t>e_w181125039-380</t>
-  </si>
-  <si>
-    <t>e_w133601335-380</t>
-  </si>
-  <si>
-    <t>e_w103381531-380</t>
-  </si>
-  <si>
-    <t>e_w82084019-380</t>
-  </si>
-  <si>
-    <t>e_w432729521-380</t>
-  </si>
-  <si>
-    <t>e_w172302572-380</t>
+    <t>e_w107438024-380</t>
+  </si>
+  <si>
+    <t>e_w411026199-380</t>
+  </si>
+  <si>
+    <t>e_w416989699-380</t>
+  </si>
+  <si>
+    <t>e_w105757794-380</t>
   </si>
   <si>
     <t>e_w99826025-380</t>
   </si>
   <si>
-    <t>e_w421827453-380</t>
-  </si>
-  <si>
-    <t>e_w416989699-380</t>
-  </si>
-  <si>
-    <t>e_w411026199-380</t>
-  </si>
-  <si>
-    <t>e_w107438024-380</t>
-  </si>
-  <si>
-    <t>e_w199675964-380</t>
-  </si>
-  <si>
-    <t>e_w60725875-380</t>
-  </si>
-  <si>
-    <t>e_w145665799-380</t>
-  </si>
-  <si>
-    <t>e_w338753171-380</t>
-  </si>
-  <si>
-    <t>e_w162960205-380</t>
-  </si>
-  <si>
-    <t>e_w158739183-380</t>
-  </si>
-  <si>
-    <t>e_w59462715-380</t>
-  </si>
-  <si>
-    <t>e_w103974940-380</t>
-  </si>
-  <si>
-    <t>e_w98421779-380</t>
-  </si>
-  <si>
-    <t>e_w419423704-380</t>
-  </si>
-  <si>
-    <t>e_w116797658-380</t>
-  </si>
-  <si>
-    <t>e_w82078641-380</t>
-  </si>
-  <si>
-    <t>e_w61157826-380</t>
-  </si>
-  <si>
-    <t>e_w105581403-380</t>
-  </si>
-  <si>
-    <t>e_w255011550-380</t>
-  </si>
-  <si>
-    <t>e_w414663585-380</t>
-  </si>
-  <si>
-    <t>e_w103653592-380</t>
-  </si>
-  <si>
-    <t>e_w109993642-380</t>
-  </si>
-  <si>
-    <t>e_w105757794-380</t>
-  </si>
-  <si>
-    <t>e_w1137611914-380</t>
-  </si>
-  <si>
     <t>e_w132450233-380</t>
   </si>
   <si>
@@ -966,69 +966,69 @@
     <t>hydro</t>
   </si>
   <si>
+    <t>e_IT53-380</t>
+  </si>
+  <si>
     <t>e_w491424937-380</t>
   </si>
   <si>
+    <t>e_w116517585-380</t>
+  </si>
+  <si>
+    <t>e_w82083756-380</t>
+  </si>
+  <si>
+    <t>e_w114931087-380</t>
+  </si>
+  <si>
+    <t>e_w1100665914-380</t>
+  </si>
+  <si>
+    <t>e_IT71-400</t>
+  </si>
+  <si>
+    <t>e_w75602396-380</t>
+  </si>
+  <si>
+    <t>e_IT71-380</t>
+  </si>
+  <si>
     <t>e_w61626687-380</t>
   </si>
   <si>
+    <t>e_IT7-380</t>
+  </si>
+  <si>
+    <t>e_IT36-380</t>
+  </si>
+  <si>
     <t>e_w72466334-380</t>
   </si>
   <si>
-    <t>e_w114931087-380</t>
+    <t>e_w64200868-380</t>
+  </si>
+  <si>
+    <t>e_IT72-380</t>
+  </si>
+  <si>
+    <t>e_IT72-400</t>
+  </si>
+  <si>
+    <t>e_IT93-380</t>
   </si>
   <si>
     <t>e_IT10-380</t>
   </si>
   <si>
-    <t>e_IT7-380</t>
-  </si>
-  <si>
-    <t>e_w75602396-380</t>
-  </si>
-  <si>
-    <t>e_w1100665914-380</t>
-  </si>
-  <si>
-    <t>e_w82083756-380</t>
-  </si>
-  <si>
-    <t>e_IT71-380</t>
+    <t>e_IT21-380</t>
+  </si>
+  <si>
+    <t>e_w104359058-380</t>
   </si>
   <si>
     <t>e_IT31-380</t>
   </si>
   <si>
-    <t>e_IT21-380</t>
-  </si>
-  <si>
-    <t>e_w116517585-380</t>
-  </si>
-  <si>
-    <t>e_IT72-380</t>
-  </si>
-  <si>
-    <t>e_IT72-400</t>
-  </si>
-  <si>
-    <t>e_IT93-380</t>
-  </si>
-  <si>
-    <t>e_IT71-400</t>
-  </si>
-  <si>
-    <t>e_IT53-380</t>
-  </si>
-  <si>
-    <t>e_w104359058-380</t>
-  </si>
-  <si>
-    <t>e_IT36-380</t>
-  </si>
-  <si>
-    <t>e_w64200868-380</t>
-  </si>
-  <si>
     <t>ep_hydro_dam_G100000602220</t>
   </si>
   <si>
@@ -1407,15 +1407,15 @@
     <t>solar</t>
   </si>
   <si>
+    <t>elc_spv-ITA_0030</t>
+  </si>
+  <si>
+    <t>elc_spv-ITA_0042</t>
+  </si>
+  <si>
     <t>elc_spv-ITA_0068</t>
   </si>
   <si>
-    <t>elc_spv-ITA_0030</t>
-  </si>
-  <si>
-    <t>elc_spv-ITA_0042</t>
-  </si>
-  <si>
     <t>ep_solar_pv_001</t>
   </si>
   <si>
@@ -2484,27 +2484,27 @@
     <t>yes</t>
   </si>
   <si>
+    <t>Aggregated Plant - EMBER Gap - way/84696559-380_Missing Bioenergy Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/144005863-380_Missing Bioenergy Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/98902899-380_Missing Bioenergy Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/109756016-380_Missing Bioenergy Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/34157795-380_Missing Bioenergy Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/58440884-380_Missing Bioenergy Capacity</t>
+  </si>
+  <si>
     <t>Aggregated Plant - EMBER Gap - way/81938081-380_Missing Bioenergy Capacity</t>
   </si>
   <si>
-    <t>Aggregated Plant - EMBER Gap - way/84696559-380_Missing Bioenergy Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/144005863-380_Missing Bioenergy Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/109756016-380_Missing Bioenergy Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/98902899-380_Missing Bioenergy Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/34157795-380_Missing Bioenergy Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/58440884-380_Missing Bioenergy Capacity</t>
-  </si>
-  <si>
     <t>Acerra power station_1</t>
   </si>
   <si>
@@ -2526,18 +2526,18 @@
     <t>Aggregated Plant</t>
   </si>
   <si>
+    <t>Aggregated Plant - EMBER Gap - way/409439916-380_Missing Coal Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/303915533-380_Missing Coal Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/82767145-380_Missing Coal Capacity</t>
+  </si>
+  <si>
     <t>Aggregated Plant - EMBER Gap - way/418902800-380_Missing Coal Capacity</t>
   </si>
   <si>
-    <t>Aggregated Plant - EMBER Gap - way/409439916-380_Missing Coal Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/82767145-380_Missing Coal Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/303915533-380_Missing Coal Capacity</t>
-  </si>
-  <si>
     <t>Fiume Santo power station_Unit 3</t>
   </si>
   <si>
@@ -2568,16 +2568,76 @@
     <t>Torrevaldaliga Nord power station_Unit 3</t>
   </si>
   <si>
+    <t>Aggregated Plant - EMBER Gap - way/416989699-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/100407576-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/103653592-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/82767145-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/109993642-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/162828577-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/98900549-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/338753171-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/99826025-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/421827453-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/1137611914-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/158739183-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/145665799-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/132450233-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/116797658-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/107438024-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/339104227-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/162960205-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/149997403-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/133601335-380_Missing Gas Capacity</t>
+  </si>
+  <si>
     <t>Aggregated Plant - EMBER Gap - way/103381531-380_Missing Gas Capacity</t>
   </si>
   <si>
-    <t>Aggregated Plant - EMBER Gap - way/149997403-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/162960205-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/133601335-380_Missing Gas Capacity</t>
+    <t>Aggregated Plant - EMBER Gap - way/103974940-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/82078641-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/432729521-380_Missing Gas Capacity</t>
   </si>
   <si>
     <t>Aggregated Plant - EMBER Gap - way/199675964-380_Missing Gas Capacity</t>
@@ -2586,108 +2646,48 @@
     <t>Aggregated Plant - EMBER Gap - way/181125039-380_Missing Gas Capacity</t>
   </si>
   <si>
-    <t>Aggregated Plant - EMBER Gap - way/82078641-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/432729521-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/103974940-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/162828577-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/98900549-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/338753171-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/1137611914-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/158739183-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/145665799-380_Missing Gas Capacity</t>
+    <t>Aggregated Plant - EMBER Gap - way/105757794-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/172302572-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/255011550-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/59462715-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/411026199-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/82084019-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/98421779-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/105581403-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/60725875-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/109756016-380_Missing Gas Capacity</t>
   </si>
   <si>
     <t>Aggregated Plant - EMBER Gap - way/110330925-380_Missing Gas Capacity</t>
   </si>
   <si>
-    <t>Aggregated Plant - EMBER Gap - way/105581403-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/109756016-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/98421779-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/411026199-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/82084019-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/116797658-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/107438024-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/339104227-380_Missing Gas Capacity</t>
+    <t>Aggregated Plant - EMBER Gap - way/61157826-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/414663585-380_Missing Gas Capacity</t>
   </si>
   <si>
     <t>Aggregated Plant - EMBER Gap - way/419423704-380_Missing Gas Capacity</t>
   </si>
   <si>
-    <t>Aggregated Plant - EMBER Gap - way/61157826-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/414663585-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/60725875-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/109993642-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/82767145-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/99826025-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/421827453-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/100407576-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/59462715-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/105757794-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/132450233-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/416989699-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/103653592-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/172302572-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/255011550-380_Missing Gas Capacity</t>
-  </si>
-  <si>
     <t>Altomonte power station_1</t>
   </si>
   <si>
@@ -3000,33 +3000,78 @@
     <t>Valle Secolo geothermal power plant_2</t>
   </si>
   <si>
+    <t>Aggregated Plant - IRENA Gap - IT53-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/61712456-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - IT7-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/339703159-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - IT30-500_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/64200868-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - IT71-400_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - IT36-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/419423704-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/491424937-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/104359058-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/72466334-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/82083756-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/1100665914-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - IT72-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/59462263-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/96190189-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/116517585-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/61626687-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - IT31-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/114931087-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/1137611914-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
     <t>Aggregated Plant - IRENA Gap - way/109588422-380_Missing Hydro Capacity</t>
   </si>
   <si>
-    <t>Aggregated Plant - IRENA Gap - way/82083756-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/419423704-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/491424937-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
     <t>Aggregated Plant - IRENA Gap - IT72-400_Missing Hydro Capacity</t>
   </si>
   <si>
-    <t>Aggregated Plant - IRENA Gap - way/1137611914-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/61626687-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - IT31-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/114931087-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
     <t>Aggregated Plant - IRENA Gap - IT93-380_Missing Hydro Capacity</t>
   </si>
   <si>
@@ -3036,13 +3081,10 @@
     <t>Aggregated Plant - IRENA Gap - way/338753171-380_Missing Hydro Capacity</t>
   </si>
   <si>
-    <t>Aggregated Plant - IRENA Gap - way/64200868-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/104359058-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/72466334-380_Missing Hydro Capacity</t>
+    <t>Aggregated Plant - IRENA Gap - IT21-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/144005863-380_Missing Hydro Capacity</t>
   </si>
   <si>
     <t>Aggregated Plant - IRENA Gap - IT71-380_Missing Hydro Capacity</t>
@@ -3051,51 +3093,9 @@
     <t>Aggregated Plant - IRENA Gap - way/108020416-380_Missing Hydro Capacity</t>
   </si>
   <si>
-    <t>Aggregated Plant - IRENA Gap - IT72-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/59462263-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/1100665914-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/61712456-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - IT30-500_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - IT53-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - IT7-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
     <t>Aggregated Plant - IRENA Gap - way/75602396-380_Missing Hydro Capacity</t>
   </si>
   <si>
-    <t>Aggregated Plant - IRENA Gap - way/339703159-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - IT36-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - IT71-400_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/144005863-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - IT21-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/96190189-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/116517585-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
     <t>Baschi hydroelectric plant_</t>
   </si>
   <si>
@@ -3402,15 +3402,15 @@
     <t>Aggregated Plant - IRENA Gap - ITA_68_Missing Solar Capacity</t>
   </si>
   <si>
+    <t>Aggregated Plant - IRENA Gap - ITA_73_Missing Onshore wind energy Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - ITA_22_Missing Onshore wind energy Capacity</t>
+  </si>
+  <si>
     <t>Aggregated Plant - IRENA Gap - ITA_96_Missing Onshore wind energy Capacity</t>
   </si>
   <si>
-    <t>Aggregated Plant - IRENA Gap - ITA_22_Missing Onshore wind energy Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - ITA_73_Missing Onshore wind energy Capacity</t>
-  </si>
-  <si>
     <t>AF</t>
   </si>
   <si>
@@ -4005,15 +4005,15 @@
     <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/418902800-380_Missing Coal Capacity</t>
   </si>
   <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/409439916-380_Missing Coal Capacity</t>
+  </si>
+  <si>
     <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/303915533-380_Missing Coal Capacity</t>
   </si>
   <si>
     <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/82767145-380_Missing Coal Capacity</t>
   </si>
   <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/409439916-380_Missing Coal Capacity</t>
-  </si>
-  <si>
     <t>ccs retrofit of -- Brindisi Sud power station_Unit 1</t>
   </si>
   <si>
@@ -4302,124 +4302,124 @@
     <t>ccs retrofit of -- Aggregated Plant</t>
   </si>
   <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/116797658-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/61157826-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/105757794-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/99826025-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/416989699-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/100407576-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/132450233-380_Missing Gas Capacity</t>
+  </si>
+  <si>
     <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/181125039-380_Missing Gas Capacity</t>
   </si>
   <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/255011550-380_Missing Gas Capacity</t>
+  </si>
+  <si>
     <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/105581403-380_Missing Gas Capacity</t>
   </si>
   <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/255011550-380_Missing Gas Capacity</t>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/158739183-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/339104227-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/133601335-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/145665799-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/59462715-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/172302572-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/414663585-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/421827453-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/82084019-380_Missing Gas Capacity</t>
   </si>
   <si>
     <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/60725875-380_Missing Gas Capacity</t>
   </si>
   <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/172302572-380_Missing Gas Capacity</t>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/109993642-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/103974940-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/162828577-380_Missing Gas Capacity</t>
   </si>
   <si>
     <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/82767145-380_Missing Gas Capacity</t>
   </si>
   <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/162828577-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/116797658-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/414663585-380_Missing Gas Capacity</t>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/149997403-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/432729521-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/419423704-380_Missing Gas Capacity</t>
   </si>
   <si>
     <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/162960205-380_Missing Gas Capacity</t>
   </si>
   <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/432729521-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/419423704-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/149997403-380_Missing Gas Capacity</t>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/103653592-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/1137611914-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/82078641-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/199675964-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/98900549-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/107438024-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/98421779-380_Missing Gas Capacity</t>
   </si>
   <si>
     <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/103381531-380_Missing Gas Capacity</t>
   </si>
   <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/411026199-380_Missing Gas Capacity</t>
+  </si>
+  <si>
     <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/109756016-380_Missing Gas Capacity</t>
   </si>
   <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/411026199-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/100407576-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/132450233-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/145665799-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/199675964-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/82078641-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/1137611914-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/103653592-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/98900549-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/98421779-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/107438024-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/82084019-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/421827453-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/133601335-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/158739183-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/99826025-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/416989699-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/105757794-380_Missing Gas Capacity</t>
-  </si>
-  <si>
     <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/338753171-380_Missing Gas Capacity</t>
   </si>
   <si>
     <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/110330925-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/109993642-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/61157826-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/59462715-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/339104227-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/103974940-380_Missing Gas Capacity</t>
   </si>
   <si>
     <t>ccs retrofit of -- Tavazzano power station_CCGT8, timepoint 1</t>
@@ -4823,7 +4823,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{66881B80-BC81-41E3-880C-18CC1EFDB6F0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{50A3CAD2-9147-48DF-8460-A3EF8D381C04}">
   <dimension ref="B9:T278"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -4899,7 +4899,7 @@
         <v>33</v>
       </c>
       <c r="D11" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E11">
         <v>0.18317520000000001</v>
@@ -4955,7 +4955,7 @@
         <v>33</v>
       </c>
       <c r="D12" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E12">
         <v>0.18317520000000001</v>
@@ -5011,7 +5011,7 @@
         <v>33</v>
       </c>
       <c r="D13" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E13">
         <v>0.18317520000000001</v>
@@ -5067,7 +5067,7 @@
         <v>33</v>
       </c>
       <c r="D14" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E14">
         <v>0.13765950000000002</v>
@@ -5347,7 +5347,7 @@
         <v>33</v>
       </c>
       <c r="D19" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E19">
         <v>0.30649709999999997</v>
@@ -5403,7 +5403,7 @@
         <v>33</v>
       </c>
       <c r="D20" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E20">
         <v>0.30649709999999997</v>
@@ -5459,7 +5459,7 @@
         <v>33</v>
       </c>
       <c r="D21" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E21">
         <v>0.30649709999999997</v>
@@ -5739,7 +5739,7 @@
         <v>49</v>
       </c>
       <c r="D26" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="E26">
         <v>0.52272499999999988</v>
@@ -5795,7 +5795,7 @@
         <v>49</v>
       </c>
       <c r="D27" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="E27">
         <v>0.450625</v>
@@ -5851,7 +5851,7 @@
         <v>49</v>
       </c>
       <c r="D28" t="s">
-        <v>55</v>
+        <v>81</v>
       </c>
       <c r="E28">
         <v>0.52272499999999988</v>
@@ -5907,7 +5907,7 @@
         <v>49</v>
       </c>
       <c r="D29" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="E29">
         <v>0.49118125000000001</v>
@@ -5963,7 +5963,7 @@
         <v>49</v>
       </c>
       <c r="D30" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="E30">
         <v>0.49118125000000001</v>
@@ -6019,7 +6019,7 @@
         <v>49</v>
       </c>
       <c r="D31" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="E31">
         <v>0.49118125000000001</v>
@@ -6131,7 +6131,7 @@
         <v>49</v>
       </c>
       <c r="D33" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E33">
         <v>0.49118125000000001</v>
@@ -6299,7 +6299,7 @@
         <v>49</v>
       </c>
       <c r="D36" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E36">
         <v>0.49118125000000001</v>
@@ -6355,7 +6355,7 @@
         <v>49</v>
       </c>
       <c r="D37" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E37">
         <v>0.49118125000000001</v>
@@ -6411,7 +6411,7 @@
         <v>49</v>
       </c>
       <c r="D38" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E38">
         <v>0.49118125000000001</v>
@@ -6467,7 +6467,7 @@
         <v>49</v>
       </c>
       <c r="D39" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E39">
         <v>0.49118125000000001</v>
@@ -6691,7 +6691,7 @@
         <v>49</v>
       </c>
       <c r="D43" t="s">
-        <v>86</v>
+        <v>63</v>
       </c>
       <c r="E43">
         <v>0.49118125000000001</v>
@@ -6747,7 +6747,7 @@
         <v>49</v>
       </c>
       <c r="D44" t="s">
-        <v>86</v>
+        <v>63</v>
       </c>
       <c r="E44">
         <v>0.49118125000000001</v>
@@ -6803,7 +6803,7 @@
         <v>49</v>
       </c>
       <c r="D45" t="s">
-        <v>66</v>
+        <v>82</v>
       </c>
       <c r="E45">
         <v>0.49118125000000001</v>
@@ -6859,7 +6859,7 @@
         <v>49</v>
       </c>
       <c r="D46" t="s">
-        <v>66</v>
+        <v>82</v>
       </c>
       <c r="E46">
         <v>0.49118125000000001</v>
@@ -6915,7 +6915,7 @@
         <v>49</v>
       </c>
       <c r="D47" t="s">
-        <v>66</v>
+        <v>82</v>
       </c>
       <c r="E47">
         <v>0.49118125000000001</v>
@@ -6971,7 +6971,7 @@
         <v>49</v>
       </c>
       <c r="D48" t="s">
-        <v>66</v>
+        <v>82</v>
       </c>
       <c r="E48">
         <v>0.49118125000000001</v>
@@ -7139,7 +7139,7 @@
         <v>49</v>
       </c>
       <c r="D51" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="E51">
         <v>0.49118125000000001</v>
@@ -7195,7 +7195,7 @@
         <v>49</v>
       </c>
       <c r="D52" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="E52">
         <v>0.54075000000000006</v>
@@ -7251,7 +7251,7 @@
         <v>49</v>
       </c>
       <c r="D53" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="E53">
         <v>0.49118125000000001</v>
@@ -7363,7 +7363,7 @@
         <v>49</v>
       </c>
       <c r="D55" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="E55">
         <v>0.49118125000000001</v>
@@ -7419,7 +7419,7 @@
         <v>49</v>
       </c>
       <c r="D56" t="s">
-        <v>62</v>
+        <v>86</v>
       </c>
       <c r="E56">
         <v>0.49118125000000001</v>
@@ -7475,7 +7475,7 @@
         <v>49</v>
       </c>
       <c r="D57" t="s">
-        <v>62</v>
+        <v>86</v>
       </c>
       <c r="E57">
         <v>0.49118125000000001</v>
@@ -7531,7 +7531,7 @@
         <v>49</v>
       </c>
       <c r="D58" t="s">
-        <v>64</v>
+        <v>84</v>
       </c>
       <c r="E58">
         <v>0.47315625000000006</v>
@@ -7587,7 +7587,7 @@
         <v>49</v>
       </c>
       <c r="D59" t="s">
-        <v>64</v>
+        <v>84</v>
       </c>
       <c r="E59">
         <v>0.47315625000000006</v>
@@ -7643,7 +7643,7 @@
         <v>49</v>
       </c>
       <c r="D60" t="s">
-        <v>64</v>
+        <v>84</v>
       </c>
       <c r="E60">
         <v>0.450625</v>
@@ -7699,7 +7699,7 @@
         <v>49</v>
       </c>
       <c r="D61" t="s">
-        <v>64</v>
+        <v>84</v>
       </c>
       <c r="E61">
         <v>0.450625</v>
@@ -7811,7 +7811,7 @@
         <v>49</v>
       </c>
       <c r="D63" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E63">
         <v>0.4911812499999999</v>
@@ -7867,7 +7867,7 @@
         <v>49</v>
       </c>
       <c r="D64" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E64">
         <v>0.49118125000000001</v>
@@ -7923,7 +7923,7 @@
         <v>49</v>
       </c>
       <c r="D65" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E65">
         <v>0.49118125000000001</v>
@@ -7979,7 +7979,7 @@
         <v>49</v>
       </c>
       <c r="D66" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E66">
         <v>0.49118125000000001</v>
@@ -8147,7 +8147,7 @@
         <v>49</v>
       </c>
       <c r="D69" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="E69">
         <v>0.49118125000000001</v>
@@ -8203,7 +8203,7 @@
         <v>49</v>
       </c>
       <c r="D70" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="E70">
         <v>0.49118125000000001</v>
@@ -8259,7 +8259,7 @@
         <v>49</v>
       </c>
       <c r="D71" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E71">
         <v>0.49118125000000001</v>
@@ -8315,7 +8315,7 @@
         <v>49</v>
       </c>
       <c r="D72" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E72">
         <v>0.49118125000000001</v>
@@ -8371,7 +8371,7 @@
         <v>49</v>
       </c>
       <c r="D73" t="s">
-        <v>84</v>
+        <v>55</v>
       </c>
       <c r="E73">
         <v>0.49118125000000001</v>
@@ -8427,7 +8427,7 @@
         <v>49</v>
       </c>
       <c r="D74" t="s">
-        <v>84</v>
+        <v>55</v>
       </c>
       <c r="E74">
         <v>0.49118125000000001</v>
@@ -8483,7 +8483,7 @@
         <v>49</v>
       </c>
       <c r="D75" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="E75">
         <v>0.50470000000000004</v>
@@ -8539,7 +8539,7 @@
         <v>49</v>
       </c>
       <c r="D76" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E76">
         <v>0.49118125000000001</v>
@@ -8595,7 +8595,7 @@
         <v>49</v>
       </c>
       <c r="D77" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E77">
         <v>0.49118125000000001</v>
@@ -8763,7 +8763,7 @@
         <v>49</v>
       </c>
       <c r="D80" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E80">
         <v>0.49118125000000001</v>
@@ -8819,7 +8819,7 @@
         <v>49</v>
       </c>
       <c r="D81" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E81">
         <v>0.49118125000000001</v>
@@ -8875,7 +8875,7 @@
         <v>49</v>
       </c>
       <c r="D82" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
       <c r="E82">
         <v>0.49118125000000001</v>
@@ -8931,7 +8931,7 @@
         <v>49</v>
       </c>
       <c r="D83" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
       <c r="E83">
         <v>0.49118125000000001</v>
@@ -8987,7 +8987,7 @@
         <v>49</v>
       </c>
       <c r="D84" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="E84">
         <v>0.49118125000000001</v>
@@ -9155,7 +9155,7 @@
         <v>49</v>
       </c>
       <c r="D87" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E87">
         <v>0.49118125000000001</v>
@@ -9211,7 +9211,7 @@
         <v>49</v>
       </c>
       <c r="D88" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E88">
         <v>0.49118125000000001</v>
@@ -9267,7 +9267,7 @@
         <v>49</v>
       </c>
       <c r="D89" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="E89">
         <v>0.52272499999999988</v>
@@ -9323,7 +9323,7 @@
         <v>49</v>
       </c>
       <c r="D90" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="E90">
         <v>0.49118125000000001</v>
@@ -9379,7 +9379,7 @@
         <v>49</v>
       </c>
       <c r="D91" t="s">
-        <v>65</v>
+        <v>83</v>
       </c>
       <c r="E91">
         <v>0.49118125000000001</v>
@@ -9435,7 +9435,7 @@
         <v>49</v>
       </c>
       <c r="D92" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="E92">
         <v>0.52272499999999988</v>
@@ -9603,7 +9603,7 @@
         <v>49</v>
       </c>
       <c r="D95" t="s">
-        <v>73</v>
+        <v>61</v>
       </c>
       <c r="E95">
         <v>0.49118125000000001</v>
@@ -9715,7 +9715,7 @@
         <v>49</v>
       </c>
       <c r="D97" t="s">
-        <v>83</v>
+        <v>56</v>
       </c>
       <c r="E97">
         <v>0.49118125000000001</v>
@@ -9827,7 +9827,7 @@
         <v>49</v>
       </c>
       <c r="D99" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E99">
         <v>0.54075000000000006</v>
@@ -9883,7 +9883,7 @@
         <v>49</v>
       </c>
       <c r="D100" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E100">
         <v>0.54075000000000006</v>
@@ -9995,7 +9995,7 @@
         <v>49</v>
       </c>
       <c r="D102" t="s">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="E102">
         <v>0.49118125000000001</v>
@@ -10051,7 +10051,7 @@
         <v>49</v>
       </c>
       <c r="D103" t="s">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="E103">
         <v>0.49118125000000001</v>
@@ -10107,7 +10107,7 @@
         <v>49</v>
       </c>
       <c r="D104" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E104">
         <v>0.49118125000000001</v>
@@ -10163,7 +10163,7 @@
         <v>49</v>
       </c>
       <c r="D105" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E105">
         <v>0.49118125000000001</v>
@@ -10219,7 +10219,7 @@
         <v>49</v>
       </c>
       <c r="D106" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E106">
         <v>0.450625</v>
@@ -10275,7 +10275,7 @@
         <v>49</v>
       </c>
       <c r="D107" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E107">
         <v>0.450625</v>
@@ -10331,7 +10331,7 @@
         <v>49</v>
       </c>
       <c r="D108" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E108">
         <v>0.47315625000000006</v>
@@ -10443,7 +10443,7 @@
         <v>49</v>
       </c>
       <c r="D110" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="E110">
         <v>0.49118125000000001</v>
@@ -10611,7 +10611,7 @@
         <v>49</v>
       </c>
       <c r="D113" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="E113">
         <v>0.49118125000000001</v>
@@ -12963,7 +12963,7 @@
         <v>49</v>
       </c>
       <c r="D155" t="s">
-        <v>82</v>
+        <v>17</v>
       </c>
       <c r="E155">
         <v>0.54075000000000006</v>
@@ -13075,7 +13075,7 @@
         <v>49</v>
       </c>
       <c r="D157" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E157">
         <v>0.54075000000000006</v>
@@ -13131,7 +13131,7 @@
         <v>49</v>
       </c>
       <c r="D158" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E158">
         <v>0.54075000000000006</v>
@@ -13187,7 +13187,7 @@
         <v>49</v>
       </c>
       <c r="D159" t="s">
-        <v>19</v>
+        <v>84</v>
       </c>
       <c r="E159">
         <v>0.54075000000000006</v>
@@ -13467,7 +13467,7 @@
         <v>49</v>
       </c>
       <c r="D164" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E164">
         <v>0.48667500000000002</v>
@@ -14587,7 +14587,7 @@
         <v>49</v>
       </c>
       <c r="D184" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E184">
         <v>0.48667500000000002</v>
@@ -14643,7 +14643,7 @@
         <v>49</v>
       </c>
       <c r="D185" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E185">
         <v>0.48667500000000002</v>
@@ -15371,7 +15371,7 @@
         <v>49</v>
       </c>
       <c r="D198" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="E198">
         <v>0.50470000000000004</v>
@@ -15595,7 +15595,7 @@
         <v>49</v>
       </c>
       <c r="D202" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E202">
         <v>0.46865000000000007</v>
@@ -16323,7 +16323,7 @@
         <v>49</v>
       </c>
       <c r="D215" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
       <c r="E215">
         <v>0.450625</v>
@@ -16715,7 +16715,7 @@
         <v>49</v>
       </c>
       <c r="D222" t="s">
-        <v>62</v>
+        <v>86</v>
       </c>
       <c r="E222">
         <v>0.450625</v>
@@ -16771,7 +16771,7 @@
         <v>49</v>
       </c>
       <c r="D223" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E223">
         <v>0.29741250000000002</v>
@@ -16827,7 +16827,7 @@
         <v>49</v>
       </c>
       <c r="D224" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="E224">
         <v>0.28839999999999999</v>
@@ -16883,7 +16883,7 @@
         <v>49</v>
       </c>
       <c r="D225" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="E225">
         <v>0.28839999999999999</v>
@@ -16939,7 +16939,7 @@
         <v>49</v>
       </c>
       <c r="D226" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="E226">
         <v>0.24784375000000003</v>
@@ -17443,7 +17443,7 @@
         <v>49</v>
       </c>
       <c r="D235" t="s">
-        <v>86</v>
+        <v>63</v>
       </c>
       <c r="E235">
         <v>0.25235000000000002</v>
@@ -17723,7 +17723,7 @@
         <v>49</v>
       </c>
       <c r="D240" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="E240">
         <v>0.27938750000000001</v>
@@ -17835,7 +17835,7 @@
         <v>49</v>
       </c>
       <c r="D242" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E242">
         <v>0.25235000000000002</v>
@@ -18031,7 +18031,7 @@
         <v>49</v>
       </c>
       <c r="D247" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E247">
         <v>0.32445000000000007</v>
@@ -18101,7 +18101,7 @@
         <v>49</v>
       </c>
       <c r="D249" t="s">
-        <v>65</v>
+        <v>83</v>
       </c>
       <c r="E249">
         <v>0.32445000000000002</v>
@@ -18241,7 +18241,7 @@
         <v>49</v>
       </c>
       <c r="D253" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E253">
         <v>0.27938750000000001</v>
@@ -18276,7 +18276,7 @@
         <v>49</v>
       </c>
       <c r="D254" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E254">
         <v>0.27938750000000001</v>
@@ -18311,7 +18311,7 @@
         <v>49</v>
       </c>
       <c r="D255" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E255">
         <v>0.27938750000000001</v>
@@ -18346,7 +18346,7 @@
         <v>49</v>
       </c>
       <c r="D256" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E256">
         <v>0.31093124999999999</v>
@@ -18381,7 +18381,7 @@
         <v>49</v>
       </c>
       <c r="D257" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="E257">
         <v>0.27938750000000001</v>
@@ -18416,7 +18416,7 @@
         <v>49</v>
       </c>
       <c r="D258" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="E258">
         <v>0.27938750000000001</v>
@@ -18451,7 +18451,7 @@
         <v>49</v>
       </c>
       <c r="D259" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="E259">
         <v>0.26136249999999994</v>
@@ -18486,7 +18486,7 @@
         <v>49</v>
       </c>
       <c r="D260" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="E260">
         <v>0.28839999999999999</v>
@@ -18521,7 +18521,7 @@
         <v>49</v>
       </c>
       <c r="D261" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="E261">
         <v>0.28839999999999999</v>
@@ -18556,7 +18556,7 @@
         <v>49</v>
       </c>
       <c r="D262" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="E262">
         <v>0.28839999999999999</v>
@@ -18626,7 +18626,7 @@
         <v>439</v>
       </c>
       <c r="D264" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="E264">
         <v>0.41457500000000003</v>
@@ -18731,7 +18731,7 @@
         <v>439</v>
       </c>
       <c r="D267" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E267">
         <v>0.22981874999999999</v>
@@ -18766,7 +18766,7 @@
         <v>439</v>
       </c>
       <c r="D268" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E268">
         <v>0.24333750000000001</v>
@@ -18941,7 +18941,7 @@
         <v>439</v>
       </c>
       <c r="D273" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="E273">
         <v>0.27938750000000001</v>
@@ -19149,7 +19149,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3FC67D3B-D05A-40E9-9CA1-8ABE0866A3F6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9FC99B37-5ED5-4C89-BC3F-D11FD46CA681}">
   <dimension ref="B9:T842"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -19284,7 +19284,7 @@
         <v>2022</v>
       </c>
       <c r="F12">
-        <v>0.51576271186440681</v>
+        <v>0.49149152542372881</v>
       </c>
       <c r="G12">
         <v>0.36049999999999999</v>
@@ -19337,19 +19337,19 @@
         <v>2022</v>
       </c>
       <c r="F13">
-        <v>0.49149152542372881</v>
+        <v>0.24877966101694915</v>
       </c>
       <c r="G13">
-        <v>0.36049999999999999</v>
+        <v>0.33990000000000004</v>
       </c>
       <c r="H13">
-        <v>3850.0000000000005</v>
+        <v>4427.5</v>
       </c>
       <c r="I13">
-        <v>143</v>
+        <v>157.30000000000001</v>
       </c>
       <c r="J13">
-        <v>8.4</v>
+        <v>9.240000000000002</v>
       </c>
       <c r="K13">
         <v>50</v>
@@ -19390,19 +19390,19 @@
         <v>2022</v>
       </c>
       <c r="F14">
-        <v>0.35800000000000004</v>
+        <v>0.27911864406779663</v>
       </c>
       <c r="G14">
-        <v>0.36050000000000004</v>
+        <v>0.33990000000000004</v>
       </c>
       <c r="H14">
-        <v>3850.0000000000009</v>
+        <v>4427.5</v>
       </c>
       <c r="I14">
-        <v>143</v>
+        <v>157.30000000000001</v>
       </c>
       <c r="J14">
-        <v>8.4</v>
+        <v>9.240000000000002</v>
       </c>
       <c r="K14">
         <v>50</v>
@@ -19443,19 +19443,19 @@
         <v>2022</v>
       </c>
       <c r="F15">
-        <v>0.24877966101694915</v>
+        <v>0.35800000000000004</v>
       </c>
       <c r="G15">
-        <v>0.33990000000000004</v>
+        <v>0.36050000000000004</v>
       </c>
       <c r="H15">
-        <v>4427.5</v>
+        <v>3850.0000000000009</v>
       </c>
       <c r="I15">
-        <v>157.30000000000001</v>
+        <v>143</v>
       </c>
       <c r="J15">
-        <v>9.240000000000002</v>
+        <v>8.4</v>
       </c>
       <c r="K15">
         <v>50</v>
@@ -19496,19 +19496,19 @@
         <v>2022</v>
       </c>
       <c r="F16">
-        <v>0.27911864406779663</v>
+        <v>1.0679322033898306</v>
       </c>
       <c r="G16">
-        <v>0.33990000000000004</v>
+        <v>0.36049999999999999</v>
       </c>
       <c r="H16">
-        <v>4427.5</v>
+        <v>3850.0000000000005</v>
       </c>
       <c r="I16">
-        <v>157.30000000000001</v>
+        <v>143</v>
       </c>
       <c r="J16">
-        <v>9.240000000000002</v>
+        <v>8.4</v>
       </c>
       <c r="K16">
         <v>50</v>
@@ -19602,7 +19602,7 @@
         <v>2022</v>
       </c>
       <c r="F18">
-        <v>1.0679322033898306</v>
+        <v>0.51576271186440681</v>
       </c>
       <c r="G18">
         <v>0.36049999999999999</v>
@@ -19649,7 +19649,7 @@
         <v>13</v>
       </c>
       <c r="D19" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E19">
         <v>2008</v>
@@ -19702,7 +19702,7 @@
         <v>13</v>
       </c>
       <c r="D20" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="E20">
         <v>1998</v>
@@ -19755,7 +19755,7 @@
         <v>13</v>
       </c>
       <c r="D21" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E21">
         <v>2008</v>
@@ -19808,7 +19808,7 @@
         <v>13</v>
       </c>
       <c r="D22" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E22">
         <v>2001</v>
@@ -19914,7 +19914,7 @@
         <v>13</v>
       </c>
       <c r="D24" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E24">
         <v>1965</v>
@@ -19967,7 +19967,7 @@
         <v>13</v>
       </c>
       <c r="D25" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E25">
         <v>2003</v>
@@ -20073,7 +20073,7 @@
         <v>13</v>
       </c>
       <c r="D27" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E27">
         <v>2018</v>
@@ -20126,7 +20126,7 @@
         <v>13</v>
       </c>
       <c r="D28" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E28">
         <v>2009</v>
@@ -20185,19 +20185,19 @@
         <v>2022</v>
       </c>
       <c r="F29">
-        <v>0.61803468208092449</v>
+        <v>0.1997687861271675</v>
       </c>
       <c r="G29">
-        <v>0.37080000000000002</v>
+        <v>0.35020000000000007</v>
       </c>
       <c r="H29">
-        <v>2200</v>
+        <v>2530</v>
       </c>
       <c r="I29">
-        <v>66</v>
+        <v>72.600000000000009</v>
       </c>
       <c r="J29">
-        <v>5.25</v>
+        <v>5.7750000000000004</v>
       </c>
       <c r="K29">
         <v>50</v>
@@ -20238,19 +20238,19 @@
         <v>2022</v>
       </c>
       <c r="F30">
-        <v>0.18416184971098257</v>
+        <v>0.61803468208092449</v>
       </c>
       <c r="G30">
-        <v>0.35020000000000001</v>
+        <v>0.37080000000000002</v>
       </c>
       <c r="H30">
-        <v>2530</v>
+        <v>2200</v>
       </c>
       <c r="I30">
-        <v>72.600000000000009</v>
+        <v>66</v>
       </c>
       <c r="J30">
-        <v>5.7750000000000004</v>
+        <v>5.25</v>
       </c>
       <c r="K30">
         <v>50</v>
@@ -20344,10 +20344,10 @@
         <v>2022</v>
       </c>
       <c r="F32">
-        <v>0.1997687861271675</v>
+        <v>0.18416184971098257</v>
       </c>
       <c r="G32">
-        <v>0.35020000000000007</v>
+        <v>0.35020000000000001</v>
       </c>
       <c r="H32">
         <v>2530</v>
@@ -20391,7 +20391,7 @@
         <v>33</v>
       </c>
       <c r="D33" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E33">
         <v>1992</v>
@@ -20444,7 +20444,7 @@
         <v>33</v>
       </c>
       <c r="D34" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E34">
         <v>1993</v>
@@ -20497,7 +20497,7 @@
         <v>33</v>
       </c>
       <c r="D35" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E35">
         <v>2005</v>
@@ -20550,7 +20550,7 @@
         <v>33</v>
       </c>
       <c r="D36" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E36">
         <v>1986</v>
@@ -20603,7 +20603,7 @@
         <v>33</v>
       </c>
       <c r="D37" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E37">
         <v>1991</v>
@@ -20656,7 +20656,7 @@
         <v>33</v>
       </c>
       <c r="D38" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E38">
         <v>1992</v>
@@ -20709,7 +20709,7 @@
         <v>33</v>
       </c>
       <c r="D39" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E39">
         <v>1993</v>
@@ -21139,19 +21139,19 @@
         <v>2022</v>
       </c>
       <c r="F47">
-        <v>0.43468212618270452</v>
+        <v>0.19481551873734657</v>
       </c>
       <c r="G47">
-        <v>0.61799999999999988</v>
+        <v>0.59739999999999993</v>
       </c>
       <c r="H47">
-        <v>1100</v>
+        <v>1265</v>
       </c>
       <c r="I47">
-        <v>33</v>
+        <v>36.300000000000004</v>
       </c>
       <c r="J47">
-        <v>3.1500000000000004</v>
+        <v>3.4650000000000003</v>
       </c>
       <c r="K47">
         <v>50</v>
@@ -21192,7 +21192,7 @@
         <v>2022</v>
       </c>
       <c r="F48">
-        <v>0.18824049497996109</v>
+        <v>0.19481551873734657</v>
       </c>
       <c r="G48">
         <v>0.59739999999999993</v>
@@ -21245,7 +21245,7 @@
         <v>2022</v>
       </c>
       <c r="F49">
-        <v>0.19481551873734657</v>
+        <v>0.18702289798785268</v>
       </c>
       <c r="G49">
         <v>0.59739999999999993</v>
@@ -21298,7 +21298,7 @@
         <v>2022</v>
       </c>
       <c r="F50">
-        <v>0.18556178159732259</v>
+        <v>0.19481551873734657</v>
       </c>
       <c r="G50">
         <v>0.59739999999999993</v>
@@ -21351,7 +21351,7 @@
         <v>2022</v>
       </c>
       <c r="F51">
-        <v>0.23280454489112914</v>
+        <v>0.21551466760318963</v>
       </c>
       <c r="G51">
         <v>0.59739999999999993</v>
@@ -21363,7 +21363,7 @@
         <v>36.300000000000004</v>
       </c>
       <c r="J51">
-        <v>3.4650000000000007</v>
+        <v>3.4650000000000003</v>
       </c>
       <c r="K51">
         <v>50</v>
@@ -21404,7 +21404,7 @@
         <v>2022</v>
       </c>
       <c r="F52">
-        <v>0.26604494277568891</v>
+        <v>0.18556178159732259</v>
       </c>
       <c r="G52">
         <v>0.59739999999999993</v>
@@ -21457,7 +21457,7 @@
         <v>2022</v>
       </c>
       <c r="F53">
-        <v>0.29344087509812827</v>
+        <v>0.23280454489112914</v>
       </c>
       <c r="G53">
         <v>0.59739999999999993</v>
@@ -21469,7 +21469,7 @@
         <v>36.300000000000004</v>
       </c>
       <c r="J53">
-        <v>3.4650000000000003</v>
+        <v>3.4650000000000007</v>
       </c>
       <c r="K53">
         <v>50</v>
@@ -21510,7 +21510,7 @@
         <v>2022</v>
       </c>
       <c r="F54">
-        <v>0.19481551873734657</v>
+        <v>0.26604494277568891</v>
       </c>
       <c r="G54">
         <v>0.59739999999999993</v>
@@ -21563,7 +21563,7 @@
         <v>2022</v>
       </c>
       <c r="F55">
-        <v>0.19481551873734657</v>
+        <v>0.21113131843159935</v>
       </c>
       <c r="G55">
         <v>0.59739999999999993</v>
@@ -21616,7 +21616,7 @@
         <v>2022</v>
       </c>
       <c r="F56">
-        <v>0.20212110068999706</v>
+        <v>0.19627663512787666</v>
       </c>
       <c r="G56">
         <v>0.59739999999999993</v>
@@ -21628,7 +21628,7 @@
         <v>36.300000000000004</v>
       </c>
       <c r="J56">
-        <v>3.4650000000000003</v>
+        <v>3.4649999999999999</v>
       </c>
       <c r="K56">
         <v>50</v>
@@ -21669,7 +21669,7 @@
         <v>2022</v>
       </c>
       <c r="F57">
-        <v>0.19627663512787666</v>
+        <v>0.21283595422055113</v>
       </c>
       <c r="G57">
         <v>0.59739999999999993</v>
@@ -21681,7 +21681,7 @@
         <v>36.300000000000004</v>
       </c>
       <c r="J57">
-        <v>3.4649999999999999</v>
+        <v>3.4650000000000003</v>
       </c>
       <c r="K57">
         <v>50</v>
@@ -21722,7 +21722,7 @@
         <v>2022</v>
       </c>
       <c r="F58">
-        <v>0.26543614427963469</v>
+        <v>0.18824049497996109</v>
       </c>
       <c r="G58">
         <v>0.59739999999999993</v>
@@ -21775,19 +21775,19 @@
         <v>2022</v>
       </c>
       <c r="F59">
-        <v>0.20557907614758497</v>
+        <v>0.43468212618270452</v>
       </c>
       <c r="G59">
-        <v>0.59739999999999993</v>
+        <v>0.61799999999999988</v>
       </c>
       <c r="H59">
-        <v>1265</v>
+        <v>1100</v>
       </c>
       <c r="I59">
-        <v>36.300000000000004</v>
+        <v>33</v>
       </c>
       <c r="J59">
-        <v>3.4650000000000003</v>
+        <v>3.1500000000000004</v>
       </c>
       <c r="K59">
         <v>50</v>
@@ -21828,19 +21828,19 @@
         <v>2022</v>
       </c>
       <c r="F60">
-        <v>0.37112356319464518</v>
+        <v>0.23864901045324952</v>
       </c>
       <c r="G60">
-        <v>0.61799999999999999</v>
+        <v>0.59739999999999993</v>
       </c>
       <c r="H60">
-        <v>1100</v>
+        <v>1265</v>
       </c>
       <c r="I60">
-        <v>33</v>
+        <v>36.300000000000004</v>
       </c>
       <c r="J60">
-        <v>3.1500000000000004</v>
+        <v>3.4650000000000003</v>
       </c>
       <c r="K60">
         <v>50</v>
@@ -21881,19 +21881,19 @@
         <v>2022</v>
       </c>
       <c r="F61">
-        <v>0.21551466760318963</v>
+        <v>0.31243538817501959</v>
       </c>
       <c r="G61">
-        <v>0.59739999999999993</v>
+        <v>0.61799999999999999</v>
       </c>
       <c r="H61">
-        <v>1265</v>
+        <v>1100</v>
       </c>
       <c r="I61">
-        <v>36.300000000000004</v>
+        <v>33</v>
       </c>
       <c r="J61">
-        <v>3.4650000000000003</v>
+        <v>3.1500000000000004</v>
       </c>
       <c r="K61">
         <v>50</v>
@@ -21934,7 +21934,7 @@
         <v>2022</v>
       </c>
       <c r="F62">
-        <v>0.23864901045324952</v>
+        <v>0.17484692806676855</v>
       </c>
       <c r="G62">
         <v>0.59739999999999993</v>
@@ -21987,19 +21987,19 @@
         <v>2022</v>
       </c>
       <c r="F63">
-        <v>0.31243538817501959</v>
+        <v>0.18872753377680451</v>
       </c>
       <c r="G63">
-        <v>0.61799999999999999</v>
+        <v>0.59739999999999993</v>
       </c>
       <c r="H63">
-        <v>1100</v>
+        <v>1265</v>
       </c>
       <c r="I63">
-        <v>33</v>
+        <v>36.300000000000004</v>
       </c>
       <c r="J63">
-        <v>3.1500000000000004</v>
+        <v>3.4650000000000007</v>
       </c>
       <c r="K63">
         <v>50</v>
@@ -22040,19 +22040,19 @@
         <v>2022</v>
       </c>
       <c r="F64">
-        <v>0.45732943023592104</v>
+        <v>0.29344087509812827</v>
       </c>
       <c r="G64">
-        <v>0.61799999999999999</v>
+        <v>0.59739999999999993</v>
       </c>
       <c r="H64">
-        <v>1100</v>
+        <v>1265</v>
       </c>
       <c r="I64">
-        <v>33</v>
+        <v>36.300000000000004</v>
       </c>
       <c r="J64">
-        <v>3.1500000000000004</v>
+        <v>3.4650000000000003</v>
       </c>
       <c r="K64">
         <v>50</v>
@@ -22093,7 +22093,7 @@
         <v>2022</v>
       </c>
       <c r="F65">
-        <v>0.49339465314217229</v>
+        <v>0.45732943023592104</v>
       </c>
       <c r="G65">
         <v>0.61799999999999999</v>
@@ -22146,19 +22146,19 @@
         <v>2022</v>
       </c>
       <c r="F66">
-        <v>0.17484692806676855</v>
+        <v>0.49339465314217229</v>
       </c>
       <c r="G66">
-        <v>0.59739999999999993</v>
+        <v>0.61799999999999999</v>
       </c>
       <c r="H66">
-        <v>1265</v>
+        <v>1100</v>
       </c>
       <c r="I66">
-        <v>36.300000000000004</v>
+        <v>33</v>
       </c>
       <c r="J66">
-        <v>3.4650000000000003</v>
+        <v>3.1500000000000004</v>
       </c>
       <c r="K66">
         <v>50</v>
@@ -22199,19 +22199,19 @@
         <v>2022</v>
       </c>
       <c r="F67">
-        <v>0.21113131843159935</v>
+        <v>0.39839773581787374</v>
       </c>
       <c r="G67">
-        <v>0.59739999999999993</v>
+        <v>0.61799999999999999</v>
       </c>
       <c r="H67">
-        <v>1265</v>
+        <v>1100</v>
       </c>
       <c r="I67">
-        <v>36.300000000000004</v>
+        <v>33</v>
       </c>
       <c r="J67">
-        <v>3.4650000000000003</v>
+        <v>3.1500000000000004</v>
       </c>
       <c r="K67">
         <v>50</v>
@@ -22252,7 +22252,7 @@
         <v>2022</v>
       </c>
       <c r="F68">
-        <v>0.18872753377680451</v>
+        <v>0.20820908565053911</v>
       </c>
       <c r="G68">
         <v>0.59739999999999993</v>
@@ -22305,7 +22305,7 @@
         <v>2022</v>
       </c>
       <c r="F69">
-        <v>0.20820908565053911</v>
+        <v>0.18629233979258764</v>
       </c>
       <c r="G69">
         <v>0.59739999999999993</v>
@@ -22317,7 +22317,7 @@
         <v>36.300000000000004</v>
       </c>
       <c r="J69">
-        <v>3.4650000000000007</v>
+        <v>3.4650000000000003</v>
       </c>
       <c r="K69">
         <v>50</v>
@@ -22358,7 +22358,7 @@
         <v>2022</v>
       </c>
       <c r="F70">
-        <v>0.18629233979258764</v>
+        <v>0.20236462008841874</v>
       </c>
       <c r="G70">
         <v>0.59739999999999993</v>
@@ -22411,7 +22411,7 @@
         <v>2022</v>
       </c>
       <c r="F71">
-        <v>0.20236462008841874</v>
+        <v>0.22793415692269547</v>
       </c>
       <c r="G71">
         <v>0.59739999999999993</v>
@@ -22464,7 +22464,7 @@
         <v>2022</v>
       </c>
       <c r="F72">
-        <v>0.28443065735652601</v>
+        <v>0.1548783373961905</v>
       </c>
       <c r="G72">
         <v>0.59739999999999993</v>
@@ -22476,7 +22476,7 @@
         <v>36.300000000000004</v>
       </c>
       <c r="J72">
-        <v>3.4650000000000003</v>
+        <v>3.4649999999999999</v>
       </c>
       <c r="K72">
         <v>50</v>
@@ -22517,19 +22517,19 @@
         <v>2022</v>
       </c>
       <c r="F73">
-        <v>0.39839773581787374</v>
+        <v>0.27347228442755023</v>
       </c>
       <c r="G73">
-        <v>0.61799999999999999</v>
+        <v>0.59739999999999993</v>
       </c>
       <c r="H73">
-        <v>1100</v>
+        <v>1265</v>
       </c>
       <c r="I73">
-        <v>33</v>
+        <v>36.300000000000004</v>
       </c>
       <c r="J73">
-        <v>3.1500000000000004</v>
+        <v>3.4650000000000003</v>
       </c>
       <c r="K73">
         <v>50</v>
@@ -22570,7 +22570,7 @@
         <v>2022</v>
       </c>
       <c r="F74">
-        <v>0.27347228442755023</v>
+        <v>0.28443065735652601</v>
       </c>
       <c r="G74">
         <v>0.59739999999999993</v>
@@ -22623,7 +22623,7 @@
         <v>2022</v>
       </c>
       <c r="F75">
-        <v>0.1548783373961905</v>
+        <v>0.19481551873734657</v>
       </c>
       <c r="G75">
         <v>0.59739999999999993</v>
@@ -22635,7 +22635,7 @@
         <v>36.300000000000004</v>
       </c>
       <c r="J75">
-        <v>3.4649999999999999</v>
+        <v>3.4650000000000003</v>
       </c>
       <c r="K75">
         <v>50</v>
@@ -22670,13 +22670,13 @@
         <v>49</v>
       </c>
       <c r="D76" t="s">
-        <v>82</v>
+        <v>17</v>
       </c>
       <c r="E76">
         <v>2022</v>
       </c>
       <c r="F76">
-        <v>0.22793415692269547</v>
+        <v>0.19822479031525012</v>
       </c>
       <c r="G76">
         <v>0.59739999999999993</v>
@@ -22723,25 +22723,25 @@
         <v>49</v>
       </c>
       <c r="D77" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E77">
         <v>2022</v>
       </c>
       <c r="F77">
-        <v>0.19481551873734657</v>
+        <v>0.37112356319464518</v>
       </c>
       <c r="G77">
-        <v>0.59739999999999993</v>
+        <v>0.61799999999999999</v>
       </c>
       <c r="H77">
-        <v>1265</v>
+        <v>1100</v>
       </c>
       <c r="I77">
-        <v>36.300000000000004</v>
+        <v>33</v>
       </c>
       <c r="J77">
-        <v>3.4650000000000003</v>
+        <v>3.1500000000000004</v>
       </c>
       <c r="K77">
         <v>50</v>
@@ -22776,13 +22776,13 @@
         <v>49</v>
       </c>
       <c r="D78" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E78">
         <v>2022</v>
       </c>
       <c r="F78">
-        <v>0.18702289798785268</v>
+        <v>0.20557907614758497</v>
       </c>
       <c r="G78">
         <v>0.59739999999999993</v>
@@ -22829,13 +22829,13 @@
         <v>49</v>
       </c>
       <c r="D79" t="s">
-        <v>19</v>
+        <v>84</v>
       </c>
       <c r="E79">
         <v>2022</v>
       </c>
       <c r="F79">
-        <v>0.19822479031525012</v>
+        <v>0.26543614427963469</v>
       </c>
       <c r="G79">
         <v>0.59739999999999993</v>
@@ -22941,7 +22941,7 @@
         <v>2022</v>
       </c>
       <c r="F81">
-        <v>0.21283595422055113</v>
+        <v>0.20212110068999706</v>
       </c>
       <c r="G81">
         <v>0.59739999999999993</v>
@@ -23094,7 +23094,7 @@
         <v>49</v>
       </c>
       <c r="D84" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="E84">
         <v>2012</v>
@@ -23147,7 +23147,7 @@
         <v>49</v>
       </c>
       <c r="D85" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="E85">
         <v>1993</v>
@@ -23200,7 +23200,7 @@
         <v>49</v>
       </c>
       <c r="D86" t="s">
-        <v>55</v>
+        <v>81</v>
       </c>
       <c r="E86">
         <v>2011</v>
@@ -23253,7 +23253,7 @@
         <v>49</v>
       </c>
       <c r="D87" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="E87">
         <v>2005</v>
@@ -23306,7 +23306,7 @@
         <v>49</v>
       </c>
       <c r="D88" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="E88">
         <v>2006</v>
@@ -23359,7 +23359,7 @@
         <v>49</v>
       </c>
       <c r="D89" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="E89">
         <v>2006</v>
@@ -23465,7 +23465,7 @@
         <v>49</v>
       </c>
       <c r="D91" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E91">
         <v>2003</v>
@@ -23624,7 +23624,7 @@
         <v>49</v>
       </c>
       <c r="D94" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E94">
         <v>2004</v>
@@ -23677,7 +23677,7 @@
         <v>49</v>
       </c>
       <c r="D95" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E95">
         <v>2005</v>
@@ -23730,7 +23730,7 @@
         <v>49</v>
       </c>
       <c r="D96" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E96">
         <v>2005</v>
@@ -23783,7 +23783,7 @@
         <v>49</v>
       </c>
       <c r="D97" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E97">
         <v>2005</v>
@@ -23995,7 +23995,7 @@
         <v>49</v>
       </c>
       <c r="D101" t="s">
-        <v>86</v>
+        <v>63</v>
       </c>
       <c r="E101">
         <v>2008</v>
@@ -24048,7 +24048,7 @@
         <v>49</v>
       </c>
       <c r="D102" t="s">
-        <v>86</v>
+        <v>63</v>
       </c>
       <c r="E102">
         <v>2008</v>
@@ -24101,7 +24101,7 @@
         <v>49</v>
       </c>
       <c r="D103" t="s">
-        <v>66</v>
+        <v>82</v>
       </c>
       <c r="E103">
         <v>2002</v>
@@ -24154,7 +24154,7 @@
         <v>49</v>
       </c>
       <c r="D104" t="s">
-        <v>66</v>
+        <v>82</v>
       </c>
       <c r="E104">
         <v>2002</v>
@@ -24207,7 +24207,7 @@
         <v>49</v>
       </c>
       <c r="D105" t="s">
-        <v>66</v>
+        <v>82</v>
       </c>
       <c r="E105">
         <v>2003</v>
@@ -24260,7 +24260,7 @@
         <v>49</v>
       </c>
       <c r="D106" t="s">
-        <v>66</v>
+        <v>82</v>
       </c>
       <c r="E106">
         <v>2003</v>
@@ -24419,7 +24419,7 @@
         <v>49</v>
       </c>
       <c r="D109" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="E109">
         <v>2007</v>
@@ -24472,7 +24472,7 @@
         <v>49</v>
       </c>
       <c r="D110" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="E110">
         <v>2023</v>
@@ -24525,7 +24525,7 @@
         <v>49</v>
       </c>
       <c r="D111" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="E111">
         <v>2001</v>
@@ -24631,7 +24631,7 @@
         <v>49</v>
       </c>
       <c r="D113" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="E113">
         <v>2010</v>
@@ -24684,7 +24684,7 @@
         <v>49</v>
       </c>
       <c r="D114" t="s">
-        <v>62</v>
+        <v>86</v>
       </c>
       <c r="E114">
         <v>2005</v>
@@ -24737,7 +24737,7 @@
         <v>49</v>
       </c>
       <c r="D115" t="s">
-        <v>62</v>
+        <v>86</v>
       </c>
       <c r="E115">
         <v>2009</v>
@@ -24790,7 +24790,7 @@
         <v>49</v>
       </c>
       <c r="D116" t="s">
-        <v>64</v>
+        <v>84</v>
       </c>
       <c r="E116">
         <v>1997</v>
@@ -24843,7 +24843,7 @@
         <v>49</v>
       </c>
       <c r="D117" t="s">
-        <v>64</v>
+        <v>84</v>
       </c>
       <c r="E117">
         <v>1997</v>
@@ -24896,7 +24896,7 @@
         <v>49</v>
       </c>
       <c r="D118" t="s">
-        <v>64</v>
+        <v>84</v>
       </c>
       <c r="E118">
         <v>1998</v>
@@ -24949,7 +24949,7 @@
         <v>49</v>
       </c>
       <c r="D119" t="s">
-        <v>64</v>
+        <v>84</v>
       </c>
       <c r="E119">
         <v>1999</v>
@@ -25055,7 +25055,7 @@
         <v>49</v>
       </c>
       <c r="D121" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E121">
         <v>2010</v>
@@ -25108,7 +25108,7 @@
         <v>49</v>
       </c>
       <c r="D122" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E122">
         <v>2003</v>
@@ -25161,7 +25161,7 @@
         <v>49</v>
       </c>
       <c r="D123" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E123">
         <v>2003</v>
@@ -25214,7 +25214,7 @@
         <v>49</v>
       </c>
       <c r="D124" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E124">
         <v>2006</v>
@@ -25373,7 +25373,7 @@
         <v>49</v>
       </c>
       <c r="D127" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="E127">
         <v>2002</v>
@@ -25426,7 +25426,7 @@
         <v>49</v>
       </c>
       <c r="D128" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="E128">
         <v>2002</v>
@@ -25479,7 +25479,7 @@
         <v>49</v>
       </c>
       <c r="D129" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E129">
         <v>2010</v>
@@ -25532,7 +25532,7 @@
         <v>49</v>
       </c>
       <c r="D130" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E130">
         <v>2010</v>
@@ -25585,7 +25585,7 @@
         <v>49</v>
       </c>
       <c r="D131" t="s">
-        <v>84</v>
+        <v>55</v>
       </c>
       <c r="E131">
         <v>2008</v>
@@ -25638,7 +25638,7 @@
         <v>49</v>
       </c>
       <c r="D132" t="s">
-        <v>84</v>
+        <v>55</v>
       </c>
       <c r="E132">
         <v>2008</v>
@@ -25691,7 +25691,7 @@
         <v>49</v>
       </c>
       <c r="D133" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="E133">
         <v>2018</v>
@@ -25744,7 +25744,7 @@
         <v>49</v>
       </c>
       <c r="D134" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E134">
         <v>2006</v>
@@ -25797,7 +25797,7 @@
         <v>49</v>
       </c>
       <c r="D135" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E135">
         <v>2007</v>
@@ -25956,7 +25956,7 @@
         <v>49</v>
       </c>
       <c r="D138" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E138">
         <v>2010</v>
@@ -26009,7 +26009,7 @@
         <v>49</v>
       </c>
       <c r="D139" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E139">
         <v>2010</v>
@@ -26062,7 +26062,7 @@
         <v>49</v>
       </c>
       <c r="D140" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
       <c r="E140">
         <v>2004</v>
@@ -26115,7 +26115,7 @@
         <v>49</v>
       </c>
       <c r="D141" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
       <c r="E141">
         <v>2004</v>
@@ -26168,7 +26168,7 @@
         <v>49</v>
       </c>
       <c r="D142" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="E142">
         <v>2008</v>
@@ -26327,7 +26327,7 @@
         <v>49</v>
       </c>
       <c r="D145" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E145">
         <v>2005</v>
@@ -26380,7 +26380,7 @@
         <v>49</v>
       </c>
       <c r="D146" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E146">
         <v>2005</v>
@@ -26433,7 +26433,7 @@
         <v>49</v>
       </c>
       <c r="D147" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="E147">
         <v>2015</v>
@@ -26486,7 +26486,7 @@
         <v>49</v>
       </c>
       <c r="D148" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="E148">
         <v>2004</v>
@@ -26539,7 +26539,7 @@
         <v>49</v>
       </c>
       <c r="D149" t="s">
-        <v>65</v>
+        <v>83</v>
       </c>
       <c r="E149">
         <v>2006</v>
@@ -26592,7 +26592,7 @@
         <v>49</v>
       </c>
       <c r="D150" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="E150">
         <v>2011</v>
@@ -26751,7 +26751,7 @@
         <v>49</v>
       </c>
       <c r="D153" t="s">
-        <v>73</v>
+        <v>61</v>
       </c>
       <c r="E153">
         <v>2006</v>
@@ -26857,7 +26857,7 @@
         <v>49</v>
       </c>
       <c r="D155" t="s">
-        <v>83</v>
+        <v>56</v>
       </c>
       <c r="E155">
         <v>2007</v>
@@ -26963,7 +26963,7 @@
         <v>49</v>
       </c>
       <c r="D157" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E157">
         <v>2023</v>
@@ -27016,7 +27016,7 @@
         <v>49</v>
       </c>
       <c r="D158" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E158">
         <v>2026</v>
@@ -27122,7 +27122,7 @@
         <v>49</v>
       </c>
       <c r="D160" t="s">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="E160">
         <v>2003</v>
@@ -27175,7 +27175,7 @@
         <v>49</v>
       </c>
       <c r="D161" t="s">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="E161">
         <v>2003</v>
@@ -27228,7 +27228,7 @@
         <v>49</v>
       </c>
       <c r="D162" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E162">
         <v>2003</v>
@@ -27281,7 +27281,7 @@
         <v>49</v>
       </c>
       <c r="D163" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E163">
         <v>2008</v>
@@ -27334,7 +27334,7 @@
         <v>49</v>
       </c>
       <c r="D164" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E164">
         <v>1999</v>
@@ -27387,7 +27387,7 @@
         <v>49</v>
       </c>
       <c r="D165" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E165">
         <v>1999</v>
@@ -27440,7 +27440,7 @@
         <v>49</v>
       </c>
       <c r="D166" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E166">
         <v>1997</v>
@@ -27546,7 +27546,7 @@
         <v>49</v>
       </c>
       <c r="D168" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="E168">
         <v>2001</v>
@@ -27705,7 +27705,7 @@
         <v>49</v>
       </c>
       <c r="D171" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="E171">
         <v>2007</v>
@@ -28288,7 +28288,7 @@
         <v>49</v>
       </c>
       <c r="D182" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E182">
         <v>2015</v>
@@ -29348,7 +29348,7 @@
         <v>49</v>
       </c>
       <c r="D202" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E202">
         <v>2005</v>
@@ -29401,7 +29401,7 @@
         <v>49</v>
       </c>
       <c r="D203" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E203">
         <v>2015</v>
@@ -30090,7 +30090,7 @@
         <v>49</v>
       </c>
       <c r="D216" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="E216">
         <v>2022</v>
@@ -30302,7 +30302,7 @@
         <v>49</v>
       </c>
       <c r="D220" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E220">
         <v>2009</v>
@@ -30991,7 +30991,7 @@
         <v>49</v>
       </c>
       <c r="D233" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
       <c r="E233">
         <v>1994</v>
@@ -31362,7 +31362,7 @@
         <v>49</v>
       </c>
       <c r="D240" t="s">
-        <v>62</v>
+        <v>86</v>
       </c>
       <c r="E240">
         <v>2006</v>
@@ -31415,7 +31415,7 @@
         <v>49</v>
       </c>
       <c r="D241" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E241">
         <v>2024</v>
@@ -31468,7 +31468,7 @@
         <v>49</v>
       </c>
       <c r="D242" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="E242">
         <v>2023</v>
@@ -31521,7 +31521,7 @@
         <v>49</v>
       </c>
       <c r="D243" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="E243">
         <v>2023</v>
@@ -31574,7 +31574,7 @@
         <v>49</v>
       </c>
       <c r="D244" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="E244">
         <v>1997</v>
@@ -32051,7 +32051,7 @@
         <v>49</v>
       </c>
       <c r="D253" t="s">
-        <v>86</v>
+        <v>63</v>
       </c>
       <c r="E253">
         <v>2008</v>
@@ -32316,7 +32316,7 @@
         <v>49</v>
       </c>
       <c r="D258" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="E258">
         <v>2015</v>
@@ -32422,7 +32422,7 @@
         <v>49</v>
       </c>
       <c r="D260" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E260">
         <v>2004</v>
@@ -32687,7 +32687,7 @@
         <v>49</v>
       </c>
       <c r="D265" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E265">
         <v>2024</v>
@@ -32793,7 +32793,7 @@
         <v>49</v>
       </c>
       <c r="D267" t="s">
-        <v>65</v>
+        <v>83</v>
       </c>
       <c r="E267">
         <v>2023</v>
@@ -33005,7 +33005,7 @@
         <v>49</v>
       </c>
       <c r="D271" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E271">
         <v>1975</v>
@@ -33058,7 +33058,7 @@
         <v>49</v>
       </c>
       <c r="D272" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E272">
         <v>1975</v>
@@ -33111,7 +33111,7 @@
         <v>49</v>
       </c>
       <c r="D273" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E273">
         <v>1975</v>
@@ -33164,7 +33164,7 @@
         <v>49</v>
       </c>
       <c r="D274" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E274">
         <v>2015</v>
@@ -33217,7 +33217,7 @@
         <v>49</v>
       </c>
       <c r="D275" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="E275">
         <v>1967</v>
@@ -33270,7 +33270,7 @@
         <v>49</v>
       </c>
       <c r="D276" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="E276">
         <v>1971</v>
@@ -33323,7 +33323,7 @@
         <v>49</v>
       </c>
       <c r="D277" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="E277">
         <v>1970</v>
@@ -33376,7 +33376,7 @@
         <v>49</v>
       </c>
       <c r="D278" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="E278">
         <v>1978</v>
@@ -33429,7 +33429,7 @@
         <v>49</v>
       </c>
       <c r="D279" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="E279">
         <v>1981</v>
@@ -33482,7 +33482,7 @@
         <v>49</v>
       </c>
       <c r="D280" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="E280">
         <v>1987</v>
@@ -33906,7 +33906,7 @@
         <v>293</v>
       </c>
       <c r="D288" t="s">
-        <v>64</v>
+        <v>84</v>
       </c>
       <c r="E288">
         <v>1991</v>
@@ -33959,7 +33959,7 @@
         <v>293</v>
       </c>
       <c r="D289" t="s">
-        <v>64</v>
+        <v>84</v>
       </c>
       <c r="E289">
         <v>1991</v>
@@ -35019,13 +35019,13 @@
         <v>308</v>
       </c>
       <c r="D309" t="s">
-        <v>14</v>
+        <v>309</v>
       </c>
       <c r="E309">
         <v>2022</v>
       </c>
       <c r="F309">
-        <v>0.11134281451252948</v>
+        <v>6.3558189950902247E-2</v>
       </c>
       <c r="G309">
         <v>1</v>
@@ -35072,7 +35072,7 @@
         <v>308</v>
       </c>
       <c r="D310" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="E310">
         <v>2022</v>
@@ -35125,25 +35125,25 @@
         <v>308</v>
       </c>
       <c r="D311" t="s">
-        <v>18</v>
+        <v>311</v>
       </c>
       <c r="E311">
         <v>2022</v>
       </c>
       <c r="F311">
-        <v>8.7682466428616976E-2</v>
+        <v>4.1753555442198553E-2</v>
       </c>
       <c r="G311">
         <v>1</v>
       </c>
       <c r="H311">
-        <v>3162.5000000000005</v>
+        <v>3712.5000000000005</v>
       </c>
       <c r="I311">
-        <v>60.500000000000007</v>
+        <v>71.5</v>
       </c>
       <c r="J311">
-        <v>2.3100000000000005</v>
+        <v>2.52</v>
       </c>
       <c r="K311">
         <v>100</v>
@@ -35178,25 +35178,25 @@
         <v>308</v>
       </c>
       <c r="D312" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="E312">
         <v>2022</v>
       </c>
       <c r="F312">
-        <v>5.1032123318242681E-2</v>
+        <v>0.35629700644009438</v>
       </c>
       <c r="G312">
         <v>1</v>
       </c>
       <c r="H312">
-        <v>3162.5000000000005</v>
+        <v>2750</v>
       </c>
       <c r="I312">
-        <v>60.500000000000021</v>
+        <v>55</v>
       </c>
       <c r="J312">
-        <v>2.3100000000000005</v>
+        <v>2.1</v>
       </c>
       <c r="K312">
         <v>100</v>
@@ -35231,13 +35231,13 @@
         <v>308</v>
       </c>
       <c r="D313" t="s">
-        <v>239</v>
+        <v>313</v>
       </c>
       <c r="E313">
         <v>2022</v>
       </c>
       <c r="F313">
-        <v>0.22871669814448767</v>
+        <v>0.13036387865841995</v>
       </c>
       <c r="G313">
         <v>1</v>
@@ -35284,13 +35284,13 @@
         <v>308</v>
       </c>
       <c r="D314" t="s">
-        <v>204</v>
+        <v>314</v>
       </c>
       <c r="E314">
         <v>2022</v>
       </c>
       <c r="F314">
-        <v>7.8403898552572848E-2</v>
+        <v>0.19299421182171778</v>
       </c>
       <c r="G314">
         <v>1</v>
@@ -35337,13 +35337,13 @@
         <v>308</v>
       </c>
       <c r="D315" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="E315">
         <v>2022</v>
       </c>
       <c r="F315">
-        <v>0.1577356538927501</v>
+        <v>6.0310691194286808E-2</v>
       </c>
       <c r="G315">
         <v>1</v>
@@ -35390,13 +35390,13 @@
         <v>308</v>
       </c>
       <c r="D316" t="s">
-        <v>312</v>
+        <v>239</v>
       </c>
       <c r="E316">
         <v>2022</v>
       </c>
       <c r="F316">
-        <v>0.13036387865841995</v>
+        <v>0.22871669814448767</v>
       </c>
       <c r="G316">
         <v>1</v>
@@ -35443,13 +35443,13 @@
         <v>308</v>
       </c>
       <c r="D317" t="s">
-        <v>313</v>
+        <v>204</v>
       </c>
       <c r="E317">
         <v>2022</v>
       </c>
       <c r="F317">
-        <v>0.20320063648536632</v>
+        <v>7.8403898552572848E-2</v>
       </c>
       <c r="G317">
         <v>1</v>
@@ -35496,13 +35496,13 @@
         <v>308</v>
       </c>
       <c r="D318" t="s">
-        <v>314</v>
+        <v>193</v>
       </c>
       <c r="E318">
         <v>2022</v>
       </c>
       <c r="F318">
-        <v>0.54140443556717466</v>
+        <v>0.61052976624370348</v>
       </c>
       <c r="G318">
         <v>1</v>
@@ -35549,7 +35549,7 @@
         <v>308</v>
       </c>
       <c r="D319" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="E319">
         <v>2022</v>
@@ -35602,13 +35602,13 @@
         <v>308</v>
       </c>
       <c r="D320" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="E320">
         <v>2022</v>
       </c>
       <c r="F320">
-        <v>0.19299421182171778</v>
+        <v>5.8918906012880183E-2</v>
       </c>
       <c r="G320">
         <v>1</v>
@@ -35617,7 +35617,7 @@
         <v>3162.5000000000005</v>
       </c>
       <c r="I320">
-        <v>60.500000000000014</v>
+        <v>60.500000000000021</v>
       </c>
       <c r="J320">
         <v>2.3100000000000005</v>
@@ -35655,25 +35655,25 @@
         <v>308</v>
       </c>
       <c r="D321" t="s">
-        <v>317</v>
+        <v>16</v>
       </c>
       <c r="E321">
         <v>2022</v>
       </c>
       <c r="F321">
-        <v>0.35629700644009438</v>
+        <v>8.7682466428616976E-2</v>
       </c>
       <c r="G321">
         <v>1</v>
       </c>
       <c r="H321">
-        <v>2750</v>
+        <v>3162.5000000000005</v>
       </c>
       <c r="I321">
-        <v>55</v>
+        <v>60.500000000000007</v>
       </c>
       <c r="J321">
-        <v>2.1</v>
+        <v>2.3100000000000005</v>
       </c>
       <c r="K321">
         <v>100</v>
@@ -35714,7 +35714,7 @@
         <v>2022</v>
       </c>
       <c r="F322">
-        <v>5.8918906012880183E-2</v>
+        <v>5.1032123318242681E-2</v>
       </c>
       <c r="G322">
         <v>1</v>
@@ -35767,19 +35767,19 @@
         <v>2022</v>
       </c>
       <c r="F323">
-        <v>4.4073197411209589E-2</v>
+        <v>0.54140443556717466</v>
       </c>
       <c r="G323">
         <v>1</v>
       </c>
       <c r="H323">
-        <v>3712.5000000000005</v>
+        <v>2750</v>
       </c>
       <c r="I323">
-        <v>71.5</v>
+        <v>55.000000000000007</v>
       </c>
       <c r="J323">
-        <v>2.52</v>
+        <v>2.1</v>
       </c>
       <c r="K323">
         <v>100</v>
@@ -35814,25 +35814,25 @@
         <v>308</v>
       </c>
       <c r="D324" t="s">
-        <v>320</v>
+        <v>99</v>
       </c>
       <c r="E324">
         <v>2022</v>
       </c>
       <c r="F324">
-        <v>0.56367299846968055</v>
+        <v>0.29181095970158766</v>
       </c>
       <c r="G324">
         <v>1</v>
       </c>
       <c r="H324">
-        <v>2750</v>
+        <v>3162.5000000000005</v>
       </c>
       <c r="I324">
-        <v>55.000000000000007</v>
+        <v>60.500000000000014</v>
       </c>
       <c r="J324">
-        <v>2.1</v>
+        <v>2.3100000000000005</v>
       </c>
       <c r="K324">
         <v>100</v>
@@ -35867,13 +35867,13 @@
         <v>308</v>
       </c>
       <c r="D325" t="s">
-        <v>99</v>
+        <v>63</v>
       </c>
       <c r="E325">
         <v>2022</v>
       </c>
       <c r="F325">
-        <v>0.29181095970158766</v>
+        <v>5.4743550468660328E-2</v>
       </c>
       <c r="G325">
         <v>1</v>
@@ -35920,25 +35920,25 @@
         <v>308</v>
       </c>
       <c r="D326" t="s">
-        <v>193</v>
+        <v>320</v>
       </c>
       <c r="E326">
         <v>2022</v>
       </c>
       <c r="F326">
-        <v>0.61052976624370348</v>
+        <v>0.15541601192373908</v>
       </c>
       <c r="G326">
         <v>1</v>
       </c>
       <c r="H326">
-        <v>2750</v>
+        <v>3162.5000000000005</v>
       </c>
       <c r="I326">
-        <v>55.000000000000007</v>
+        <v>60.500000000000014</v>
       </c>
       <c r="J326">
-        <v>2.1</v>
+        <v>2.3100000000000005</v>
       </c>
       <c r="K326">
         <v>100</v>
@@ -35973,7 +35973,7 @@
         <v>308</v>
       </c>
       <c r="D327" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E327">
         <v>2022</v>
@@ -36026,13 +36026,13 @@
         <v>308</v>
       </c>
       <c r="D328" t="s">
-        <v>291</v>
+        <v>321</v>
       </c>
       <c r="E328">
         <v>2022</v>
       </c>
       <c r="F328">
-        <v>0.13082780705222213</v>
+        <v>0.1577356538927501</v>
       </c>
       <c r="G328">
         <v>1</v>
@@ -36079,25 +36079,25 @@
         <v>308</v>
       </c>
       <c r="D329" t="s">
-        <v>151</v>
+        <v>14</v>
       </c>
       <c r="E329">
         <v>2022</v>
       </c>
       <c r="F329">
-        <v>4.5464982592616207E-2</v>
+        <v>0.11134281451252948</v>
       </c>
       <c r="G329">
         <v>1</v>
       </c>
       <c r="H329">
-        <v>3712.5000000000005</v>
+        <v>3162.5000000000005</v>
       </c>
       <c r="I329">
-        <v>71.5</v>
+        <v>60.500000000000014</v>
       </c>
       <c r="J329">
-        <v>2.52</v>
+        <v>2.3100000000000005</v>
       </c>
       <c r="K329">
         <v>100</v>
@@ -36132,25 +36132,25 @@
         <v>308</v>
       </c>
       <c r="D330" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="E330">
         <v>2022</v>
       </c>
       <c r="F330">
-        <v>4.1753555442198553E-2</v>
+        <v>1.0883760118599757</v>
       </c>
       <c r="G330">
         <v>1</v>
       </c>
       <c r="H330">
-        <v>3712.5000000000005</v>
+        <v>2750</v>
       </c>
       <c r="I330">
-        <v>71.5</v>
+        <v>55.000000000000007</v>
       </c>
       <c r="J330">
-        <v>2.52</v>
+        <v>2.1</v>
       </c>
       <c r="K330">
         <v>100</v>
@@ -36185,7 +36185,7 @@
         <v>308</v>
       </c>
       <c r="D331" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="E331">
         <v>2022</v>
@@ -36238,7 +36238,7 @@
         <v>308</v>
       </c>
       <c r="D332" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="E332">
         <v>2022</v>
@@ -36291,7 +36291,7 @@
         <v>308</v>
       </c>
       <c r="D333" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="E333">
         <v>2022</v>
@@ -36344,13 +36344,13 @@
         <v>308</v>
       </c>
       <c r="D334" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="E334">
         <v>2022</v>
       </c>
       <c r="F334">
-        <v>6.0310691194286808E-2</v>
+        <v>0.20320063648536632</v>
       </c>
       <c r="G334">
         <v>1</v>
@@ -36397,25 +36397,25 @@
         <v>308</v>
       </c>
       <c r="D335" t="s">
-        <v>86</v>
+        <v>327</v>
       </c>
       <c r="E335">
         <v>2022</v>
       </c>
       <c r="F335">
-        <v>5.4743550468660328E-2</v>
+        <v>0.56367299846968055</v>
       </c>
       <c r="G335">
         <v>1</v>
       </c>
       <c r="H335">
-        <v>3162.5000000000005</v>
+        <v>2750</v>
       </c>
       <c r="I335">
-        <v>60.500000000000014</v>
+        <v>55.000000000000007</v>
       </c>
       <c r="J335">
-        <v>2.3100000000000005</v>
+        <v>2.1</v>
       </c>
       <c r="K335">
         <v>100</v>
@@ -36450,25 +36450,25 @@
         <v>308</v>
       </c>
       <c r="D336" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="E336">
         <v>2022</v>
       </c>
       <c r="F336">
-        <v>6.3558189950902247E-2</v>
+        <v>0.57944656385895543</v>
       </c>
       <c r="G336">
         <v>1</v>
       </c>
       <c r="H336">
-        <v>3162.5000000000005</v>
+        <v>2750</v>
       </c>
       <c r="I336">
-        <v>60.500000000000014</v>
+        <v>55.000000000000007</v>
       </c>
       <c r="J336">
-        <v>2.3100000000000005</v>
+        <v>2.1</v>
       </c>
       <c r="K336">
         <v>100</v>
@@ -36503,25 +36503,25 @@
         <v>308</v>
       </c>
       <c r="D337" t="s">
-        <v>327</v>
+        <v>151</v>
       </c>
       <c r="E337">
         <v>2022</v>
       </c>
       <c r="F337">
-        <v>0.57944656385895543</v>
+        <v>4.5464982592616207E-2</v>
       </c>
       <c r="G337">
         <v>1</v>
       </c>
       <c r="H337">
-        <v>2750</v>
+        <v>3712.5000000000005</v>
       </c>
       <c r="I337">
-        <v>55.000000000000007</v>
+        <v>71.5</v>
       </c>
       <c r="J337">
-        <v>2.1</v>
+        <v>2.52</v>
       </c>
       <c r="K337">
         <v>100</v>
@@ -36556,25 +36556,25 @@
         <v>308</v>
       </c>
       <c r="D338" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="E338">
         <v>2022</v>
       </c>
       <c r="F338">
-        <v>0.15541601192373908</v>
+        <v>4.4073197411209589E-2</v>
       </c>
       <c r="G338">
         <v>1</v>
       </c>
       <c r="H338">
-        <v>3162.5000000000005</v>
+        <v>3712.5000000000005</v>
       </c>
       <c r="I338">
-        <v>60.500000000000014</v>
+        <v>71.5</v>
       </c>
       <c r="J338">
-        <v>2.3100000000000005</v>
+        <v>2.52</v>
       </c>
       <c r="K338">
         <v>100</v>
@@ -36609,25 +36609,25 @@
         <v>308</v>
       </c>
       <c r="D339" t="s">
-        <v>329</v>
+        <v>291</v>
       </c>
       <c r="E339">
         <v>2022</v>
       </c>
       <c r="F339">
-        <v>1.0883760118599757</v>
+        <v>0.13082780705222213</v>
       </c>
       <c r="G339">
         <v>1</v>
       </c>
       <c r="H339">
-        <v>2750</v>
+        <v>3162.5000000000005</v>
       </c>
       <c r="I339">
-        <v>55.000000000000007</v>
+        <v>60.500000000000014</v>
       </c>
       <c r="J339">
-        <v>2.1</v>
+        <v>2.3100000000000005</v>
       </c>
       <c r="K339">
         <v>100</v>
@@ -36662,7 +36662,7 @@
         <v>308</v>
       </c>
       <c r="D340" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E340">
         <v>2022</v>
@@ -36768,7 +36768,7 @@
         <v>308</v>
       </c>
       <c r="D342" t="s">
-        <v>319</v>
+        <v>329</v>
       </c>
       <c r="E342">
         <v>1959</v>
@@ -36874,7 +36874,7 @@
         <v>308</v>
       </c>
       <c r="D344" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E344">
         <v>1973</v>
@@ -36980,7 +36980,7 @@
         <v>308</v>
       </c>
       <c r="D346" t="s">
-        <v>329</v>
+        <v>322</v>
       </c>
       <c r="E346">
         <v>1963</v>
@@ -37033,7 +37033,7 @@
         <v>308</v>
       </c>
       <c r="D347" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="E347">
         <v>2015</v>
@@ -37086,7 +37086,7 @@
         <v>308</v>
       </c>
       <c r="D348" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="E348">
         <v>1931</v>
@@ -37139,7 +37139,7 @@
         <v>308</v>
       </c>
       <c r="D349" t="s">
-        <v>314</v>
+        <v>319</v>
       </c>
       <c r="E349">
         <v>1949</v>
@@ -37192,7 +37192,7 @@
         <v>308</v>
       </c>
       <c r="D350" t="s">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="E350">
         <v>1951</v>
@@ -37298,7 +37298,7 @@
         <v>308</v>
       </c>
       <c r="D352" t="s">
-        <v>325</v>
+        <v>315</v>
       </c>
       <c r="E352">
         <v>1958</v>
@@ -37351,7 +37351,7 @@
         <v>308</v>
       </c>
       <c r="D353" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="E353">
         <v>1967</v>
@@ -37404,7 +37404,7 @@
         <v>308</v>
       </c>
       <c r="D354" t="s">
-        <v>313</v>
+        <v>326</v>
       </c>
       <c r="E354">
         <v>1968</v>
@@ -37457,7 +37457,7 @@
         <v>308</v>
       </c>
       <c r="D355" t="s">
-        <v>320</v>
+        <v>327</v>
       </c>
       <c r="E355">
         <v>1929</v>
@@ -37510,7 +37510,7 @@
         <v>308</v>
       </c>
       <c r="D356" t="s">
-        <v>313</v>
+        <v>326</v>
       </c>
       <c r="E356">
         <v>1949</v>
@@ -37616,7 +37616,7 @@
         <v>308</v>
       </c>
       <c r="D358" t="s">
-        <v>86</v>
+        <v>63</v>
       </c>
       <c r="E358">
         <v>1952</v>
@@ -37669,7 +37669,7 @@
         <v>308</v>
       </c>
       <c r="D359" t="s">
-        <v>320</v>
+        <v>327</v>
       </c>
       <c r="E359">
         <v>1913</v>
@@ -37722,7 +37722,7 @@
         <v>308</v>
       </c>
       <c r="D360" t="s">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="E360">
         <v>1924</v>
@@ -37828,7 +37828,7 @@
         <v>308</v>
       </c>
       <c r="D362" t="s">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="E362">
         <v>1971</v>
@@ -37934,7 +37934,7 @@
         <v>308</v>
       </c>
       <c r="D364" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="E364">
         <v>1927</v>
@@ -37987,7 +37987,7 @@
         <v>308</v>
       </c>
       <c r="D365" t="s">
-        <v>329</v>
+        <v>322</v>
       </c>
       <c r="E365">
         <v>1928</v>
@@ -38093,7 +38093,7 @@
         <v>308</v>
       </c>
       <c r="D367" t="s">
-        <v>329</v>
+        <v>322</v>
       </c>
       <c r="E367">
         <v>1938</v>
@@ -38146,7 +38146,7 @@
         <v>308</v>
       </c>
       <c r="D368" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="E368">
         <v>1920</v>
@@ -38199,7 +38199,7 @@
         <v>308</v>
       </c>
       <c r="D369" t="s">
-        <v>329</v>
+        <v>322</v>
       </c>
       <c r="E369">
         <v>1947</v>
@@ -38252,7 +38252,7 @@
         <v>308</v>
       </c>
       <c r="D370" t="s">
-        <v>311</v>
+        <v>321</v>
       </c>
       <c r="E370">
         <v>1950</v>
@@ -38305,7 +38305,7 @@
         <v>308</v>
       </c>
       <c r="D371" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E371">
         <v>1954</v>
@@ -38411,7 +38411,7 @@
         <v>308</v>
       </c>
       <c r="D373" t="s">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="E373">
         <v>1971</v>
@@ -38464,7 +38464,7 @@
         <v>308</v>
       </c>
       <c r="D374" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="E374">
         <v>1959</v>
@@ -38570,7 +38570,7 @@
         <v>308</v>
       </c>
       <c r="D376" t="s">
-        <v>329</v>
+        <v>322</v>
       </c>
       <c r="E376">
         <v>1955</v>
@@ -38623,7 +38623,7 @@
         <v>308</v>
       </c>
       <c r="D377" t="s">
-        <v>329</v>
+        <v>322</v>
       </c>
       <c r="E377">
         <v>1959</v>
@@ -38676,7 +38676,7 @@
         <v>308</v>
       </c>
       <c r="D378" t="s">
-        <v>329</v>
+        <v>322</v>
       </c>
       <c r="E378">
         <v>1954</v>
@@ -39100,7 +39100,7 @@
         <v>308</v>
       </c>
       <c r="D386" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="E386">
         <v>2022</v>
@@ -39206,7 +39206,7 @@
         <v>383</v>
       </c>
       <c r="D388" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E388">
         <v>1989</v>
@@ -39259,7 +39259,7 @@
         <v>383</v>
       </c>
       <c r="D389" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="E389">
         <v>1975</v>
@@ -39312,7 +39312,7 @@
         <v>383</v>
       </c>
       <c r="D390" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E390">
         <v>1966</v>
@@ -39365,7 +39365,7 @@
         <v>383</v>
       </c>
       <c r="D391" t="s">
-        <v>329</v>
+        <v>322</v>
       </c>
       <c r="E391">
         <v>2015</v>
@@ -39418,7 +39418,7 @@
         <v>383</v>
       </c>
       <c r="D392" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="E392">
         <v>2015</v>
@@ -39471,7 +39471,7 @@
         <v>383</v>
       </c>
       <c r="D393" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="E393">
         <v>1982</v>
@@ -39524,7 +39524,7 @@
         <v>383</v>
       </c>
       <c r="D394" t="s">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="E394">
         <v>2015</v>
@@ -39577,7 +39577,7 @@
         <v>383</v>
       </c>
       <c r="D395" t="s">
-        <v>326</v>
+        <v>309</v>
       </c>
       <c r="E395">
         <v>2015</v>
@@ -39630,7 +39630,7 @@
         <v>383</v>
       </c>
       <c r="D396" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="E396">
         <v>1961</v>
@@ -39683,7 +39683,7 @@
         <v>383</v>
       </c>
       <c r="D397" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="E397">
         <v>2005</v>
@@ -39736,7 +39736,7 @@
         <v>383</v>
       </c>
       <c r="D398" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E398">
         <v>1991</v>
@@ -39895,7 +39895,7 @@
         <v>383</v>
       </c>
       <c r="D401" t="s">
-        <v>320</v>
+        <v>327</v>
       </c>
       <c r="E401">
         <v>1971</v>
@@ -39948,7 +39948,7 @@
         <v>383</v>
       </c>
       <c r="D402" t="s">
-        <v>311</v>
+        <v>321</v>
       </c>
       <c r="E402">
         <v>1973</v>
@@ -40160,7 +40160,7 @@
         <v>383</v>
       </c>
       <c r="D406" t="s">
-        <v>314</v>
+        <v>319</v>
       </c>
       <c r="E406">
         <v>1923</v>
@@ -40213,7 +40213,7 @@
         <v>308</v>
       </c>
       <c r="D407" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="E407">
         <v>1959</v>
@@ -40319,7 +40319,7 @@
         <v>308</v>
       </c>
       <c r="D409" t="s">
-        <v>329</v>
+        <v>322</v>
       </c>
       <c r="E409">
         <v>1949</v>
@@ -40372,7 +40372,7 @@
         <v>308</v>
       </c>
       <c r="D410" t="s">
-        <v>328</v>
+        <v>320</v>
       </c>
       <c r="E410">
         <v>1953</v>
@@ -40478,7 +40478,7 @@
         <v>308</v>
       </c>
       <c r="D412" t="s">
-        <v>329</v>
+        <v>322</v>
       </c>
       <c r="E412">
         <v>1960</v>
@@ -40531,7 +40531,7 @@
         <v>308</v>
       </c>
       <c r="D413" t="s">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="E413">
         <v>1962</v>
@@ -40584,7 +40584,7 @@
         <v>308</v>
       </c>
       <c r="D414" t="s">
-        <v>314</v>
+        <v>319</v>
       </c>
       <c r="E414">
         <v>2015</v>
@@ -40637,7 +40637,7 @@
         <v>308</v>
       </c>
       <c r="D415" t="s">
-        <v>313</v>
+        <v>326</v>
       </c>
       <c r="E415">
         <v>1927</v>
@@ -40690,7 +40690,7 @@
         <v>308</v>
       </c>
       <c r="D416" t="s">
-        <v>310</v>
+        <v>318</v>
       </c>
       <c r="E416">
         <v>1954</v>
@@ -40796,7 +40796,7 @@
         <v>308</v>
       </c>
       <c r="D418" t="s">
-        <v>314</v>
+        <v>319</v>
       </c>
       <c r="E418">
         <v>1956</v>
@@ -40849,7 +40849,7 @@
         <v>308</v>
       </c>
       <c r="D419" t="s">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="E419">
         <v>1956</v>
@@ -40955,7 +40955,7 @@
         <v>308</v>
       </c>
       <c r="D421" t="s">
-        <v>314</v>
+        <v>319</v>
       </c>
       <c r="E421">
         <v>1960</v>
@@ -41061,7 +41061,7 @@
         <v>308</v>
       </c>
       <c r="D423" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="E423">
         <v>2015</v>
@@ -41167,7 +41167,7 @@
         <v>308</v>
       </c>
       <c r="D425" t="s">
-        <v>313</v>
+        <v>326</v>
       </c>
       <c r="E425">
         <v>2015</v>
@@ -41220,7 +41220,7 @@
         <v>308</v>
       </c>
       <c r="D426" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="E426">
         <v>2015</v>
@@ -41379,7 +41379,7 @@
         <v>308</v>
       </c>
       <c r="D429" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E429">
         <v>2015</v>
@@ -41485,7 +41485,7 @@
         <v>308</v>
       </c>
       <c r="D431" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="E431">
         <v>1932</v>
@@ -41644,7 +41644,7 @@
         <v>308</v>
       </c>
       <c r="D434" t="s">
-        <v>320</v>
+        <v>327</v>
       </c>
       <c r="E434">
         <v>1924</v>
@@ -41750,7 +41750,7 @@
         <v>308</v>
       </c>
       <c r="D436" t="s">
-        <v>320</v>
+        <v>327</v>
       </c>
       <c r="E436">
         <v>2002</v>
@@ -41856,7 +41856,7 @@
         <v>308</v>
       </c>
       <c r="D438" t="s">
-        <v>329</v>
+        <v>322</v>
       </c>
       <c r="E438">
         <v>1948</v>
@@ -41909,7 +41909,7 @@
         <v>308</v>
       </c>
       <c r="D439" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="E439">
         <v>2015</v>
@@ -41962,7 +41962,7 @@
         <v>308</v>
       </c>
       <c r="D440" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="E440">
         <v>1914</v>
@@ -42068,7 +42068,7 @@
         <v>308</v>
       </c>
       <c r="D442" t="s">
-        <v>86</v>
+        <v>63</v>
       </c>
       <c r="E442">
         <v>1958</v>
@@ -42121,7 +42121,7 @@
         <v>439</v>
       </c>
       <c r="D443" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="E443">
         <v>1992</v>
@@ -42280,7 +42280,7 @@
         <v>439</v>
       </c>
       <c r="D446" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E446">
         <v>1992</v>
@@ -42333,7 +42333,7 @@
         <v>439</v>
       </c>
       <c r="D447" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E447">
         <v>2005</v>
@@ -42598,7 +42598,7 @@
         <v>439</v>
       </c>
       <c r="D452" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="E452">
         <v>1985</v>
@@ -42922,7 +42922,7 @@
         <v>2022</v>
       </c>
       <c r="F458">
-        <v>6.6457416582336482</v>
+        <v>6.6307854518247753</v>
       </c>
       <c r="G458">
         <v>1</v>
@@ -42978,7 +42978,7 @@
         <v>2022</v>
       </c>
       <c r="F459">
-        <v>6.6307854518247753</v>
+        <v>6.6039408899415779</v>
       </c>
       <c r="G459">
         <v>1</v>
@@ -43034,7 +43034,7 @@
         <v>2022</v>
       </c>
       <c r="F460">
-        <v>6.6039408899415779</v>
+        <v>6.6457416582336482</v>
       </c>
       <c r="G460">
         <v>1</v>
@@ -43812,7 +43812,7 @@
         <v>455</v>
       </c>
       <c r="D474" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="E474">
         <v>2015</v>
@@ -44876,7 +44876,7 @@
         <v>455</v>
       </c>
       <c r="D493" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="E493">
         <v>2015</v>

--- a/VerveStacks_ITA_grids/vt_vervestacks_ITA_v1.xlsx
+++ b/VerveStacks_ITA_grids/vt_vervestacks_ITA_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{17CC1CF1-C667-4724-8500-E92D040965CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C6FFF0AF-5FA4-47CE-AA42-BCC0B4A30B40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{DAB421F1-2271-42C0-99F4-CCC3CB460F73}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{945238FB-BE21-4170-9238-36C66C9696A9}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="2" r:id="rId1"/>
@@ -81,30 +81,30 @@
     <t>bioenergy</t>
   </si>
   <si>
+    <t>e_w84696559-380</t>
+  </si>
+  <si>
     <t>e_w144005863-380</t>
   </si>
   <si>
+    <t>e_w34157795-380</t>
+  </si>
+  <si>
+    <t>e_w98902899-380</t>
+  </si>
+  <si>
     <t>e_w81938081-380</t>
   </si>
   <si>
+    <t>e_w58440884-380</t>
+  </si>
+  <si>
     <t>e_w108020416-380</t>
   </si>
   <si>
     <t>e_w109756016-380</t>
   </si>
   <si>
-    <t>e_w34157795-380</t>
-  </si>
-  <si>
-    <t>e_w84696559-380</t>
-  </si>
-  <si>
-    <t>e_w98902899-380</t>
-  </si>
-  <si>
-    <t>e_w58440884-380</t>
-  </si>
-  <si>
     <t>ep_bioenergy_G100000200236</t>
   </si>
   <si>
@@ -147,12 +147,12 @@
     <t>e_w418902800-380</t>
   </si>
   <si>
+    <t>e_w303915533-380</t>
+  </si>
+  <si>
     <t>e_w82767145-380</t>
   </si>
   <si>
-    <t>e_w303915533-380</t>
-  </si>
-  <si>
     <t>ep_coal_subcritical_G100000102764</t>
   </si>
   <si>
@@ -189,120 +189,120 @@
     <t>gas</t>
   </si>
   <si>
+    <t>e_w149997403-380</t>
+  </si>
+  <si>
+    <t>e_w59462715-380</t>
+  </si>
+  <si>
+    <t>e_w82084019-380</t>
+  </si>
+  <si>
+    <t>e_w107438024-380</t>
+  </si>
+  <si>
+    <t>e_w411026199-380</t>
+  </si>
+  <si>
+    <t>e_w416989699-380</t>
+  </si>
+  <si>
+    <t>e_w432729521-380</t>
+  </si>
+  <si>
+    <t>e_w172302572-380</t>
+  </si>
+  <si>
+    <t>e_w199675964-380</t>
+  </si>
+  <si>
+    <t>e_w109993642-380</t>
+  </si>
+  <si>
+    <t>e_w103653592-380</t>
+  </si>
+  <si>
+    <t>e_w82078641-380</t>
+  </si>
+  <si>
+    <t>e_w61157826-380</t>
+  </si>
+  <si>
+    <t>e_w99826025-380</t>
+  </si>
+  <si>
+    <t>e_w1137611914-380</t>
+  </si>
+  <si>
+    <t>e_w60725875-380</t>
+  </si>
+  <si>
+    <t>e_w145665799-380</t>
+  </si>
+  <si>
+    <t>e_w339104227-380</t>
+  </si>
+  <si>
+    <t>e_w98421779-380</t>
+  </si>
+  <si>
+    <t>e_w419423704-380</t>
+  </si>
+  <si>
+    <t>e_w116797658-380</t>
+  </si>
+  <si>
+    <t>e_w414663585-380</t>
+  </si>
+  <si>
+    <t>e_w255011550-380</t>
+  </si>
+  <si>
+    <t>e_w162960205-380</t>
+  </si>
+  <si>
+    <t>e_w105581403-380</t>
+  </si>
+  <si>
+    <t>e_w158739183-380</t>
+  </si>
+  <si>
+    <t>e_w103974940-380</t>
+  </si>
+  <si>
+    <t>e_w98900549-380</t>
+  </si>
+  <si>
+    <t>e_w162828577-380</t>
+  </si>
+  <si>
+    <t>e_w338753171-380</t>
+  </si>
+  <si>
+    <t>e_w103381531-380</t>
+  </si>
+  <si>
+    <t>e_w133601335-380</t>
+  </si>
+  <si>
+    <t>e_w181125039-380</t>
+  </si>
+  <si>
+    <t>e_w105757794-380</t>
+  </si>
+  <si>
     <t>e_w110330925-380</t>
   </si>
   <si>
-    <t>e_w162828577-380</t>
-  </si>
-  <si>
-    <t>e_w98900549-380</t>
-  </si>
-  <si>
-    <t>e_w172302572-380</t>
-  </si>
-  <si>
-    <t>e_w432729521-380</t>
-  </si>
-  <si>
-    <t>e_w109993642-380</t>
-  </si>
-  <si>
-    <t>e_w103653592-380</t>
-  </si>
-  <si>
-    <t>e_w199675964-380</t>
-  </si>
-  <si>
-    <t>e_w181125039-380</t>
-  </si>
-  <si>
-    <t>e_w133601335-380</t>
-  </si>
-  <si>
-    <t>e_w103381531-380</t>
-  </si>
-  <si>
-    <t>e_w59462715-380</t>
+    <t>e_w100407576-380</t>
+  </si>
+  <si>
+    <t>e_w132450233-380</t>
   </si>
   <si>
     <t>e_w421827453-380</t>
   </si>
   <si>
-    <t>e_w1137611914-380</t>
-  </si>
-  <si>
-    <t>e_w149997403-380</t>
-  </si>
-  <si>
-    <t>e_w100407576-380</t>
-  </si>
-  <si>
-    <t>e_w60725875-380</t>
-  </si>
-  <si>
-    <t>e_w145665799-380</t>
-  </si>
-  <si>
-    <t>e_w158739183-380</t>
-  </si>
-  <si>
-    <t>e_w103974940-380</t>
-  </si>
-  <si>
-    <t>e_w82084019-380</t>
-  </si>
-  <si>
-    <t>e_w338753171-380</t>
-  </si>
-  <si>
-    <t>e_w162960205-380</t>
-  </si>
-  <si>
-    <t>e_w61157826-380</t>
-  </si>
-  <si>
-    <t>e_w98421779-380</t>
-  </si>
-  <si>
-    <t>e_w419423704-380</t>
-  </si>
-  <si>
-    <t>e_w116797658-380</t>
-  </si>
-  <si>
-    <t>e_w414663585-380</t>
-  </si>
-  <si>
-    <t>e_w255011550-380</t>
-  </si>
-  <si>
-    <t>e_w105581403-380</t>
-  </si>
-  <si>
-    <t>e_w82078641-380</t>
-  </si>
-  <si>
-    <t>e_w339104227-380</t>
-  </si>
-  <si>
-    <t>e_w107438024-380</t>
-  </si>
-  <si>
-    <t>e_w411026199-380</t>
-  </si>
-  <si>
-    <t>e_w416989699-380</t>
-  </si>
-  <si>
-    <t>e_w105757794-380</t>
-  </si>
-  <si>
-    <t>e_w99826025-380</t>
-  </si>
-  <si>
-    <t>e_w132450233-380</t>
-  </si>
-  <si>
     <t>ep_gas_combined_cycle_G100000400339</t>
   </si>
   <si>
@@ -966,69 +966,69 @@
     <t>hydro</t>
   </si>
   <si>
+    <t>e_w61626687-380</t>
+  </si>
+  <si>
+    <t>e_w1100665914-380</t>
+  </si>
+  <si>
+    <t>e_IT71-380</t>
+  </si>
+  <si>
+    <t>e_w82083756-380</t>
+  </si>
+  <si>
+    <t>e_IT7-380</t>
+  </si>
+  <si>
+    <t>e_w114931087-380</t>
+  </si>
+  <si>
+    <t>e_w491424937-380</t>
+  </si>
+  <si>
+    <t>e_IT71-400</t>
+  </si>
+  <si>
+    <t>e_w75602396-380</t>
+  </si>
+  <si>
+    <t>e_w64200868-380</t>
+  </si>
+  <si>
+    <t>e_w116517585-380</t>
+  </si>
+  <si>
+    <t>e_w104359058-380</t>
+  </si>
+  <si>
+    <t>e_IT31-380</t>
+  </si>
+  <si>
+    <t>e_IT21-380</t>
+  </si>
+  <si>
+    <t>e_IT72-380</t>
+  </si>
+  <si>
+    <t>e_IT72-400</t>
+  </si>
+  <si>
+    <t>e_IT36-380</t>
+  </si>
+  <si>
     <t>e_IT53-380</t>
   </si>
   <si>
-    <t>e_w491424937-380</t>
-  </si>
-  <si>
-    <t>e_w116517585-380</t>
-  </si>
-  <si>
-    <t>e_w82083756-380</t>
-  </si>
-  <si>
-    <t>e_w114931087-380</t>
-  </si>
-  <si>
-    <t>e_w1100665914-380</t>
-  </si>
-  <si>
-    <t>e_IT71-400</t>
-  </si>
-  <si>
-    <t>e_w75602396-380</t>
-  </si>
-  <si>
-    <t>e_IT71-380</t>
-  </si>
-  <si>
-    <t>e_w61626687-380</t>
-  </si>
-  <si>
-    <t>e_IT7-380</t>
-  </si>
-  <si>
-    <t>e_IT36-380</t>
-  </si>
-  <si>
     <t>e_w72466334-380</t>
   </si>
   <si>
-    <t>e_w64200868-380</t>
-  </si>
-  <si>
-    <t>e_IT72-380</t>
-  </si>
-  <si>
-    <t>e_IT72-400</t>
+    <t>e_IT10-380</t>
   </si>
   <si>
     <t>e_IT93-380</t>
   </si>
   <si>
-    <t>e_IT10-380</t>
-  </si>
-  <si>
-    <t>e_IT21-380</t>
-  </si>
-  <si>
-    <t>e_w104359058-380</t>
-  </si>
-  <si>
-    <t>e_IT31-380</t>
-  </si>
-  <si>
     <t>ep_hydro_dam_G100000602220</t>
   </si>
   <si>
@@ -1407,15 +1407,15 @@
     <t>solar</t>
   </si>
   <si>
+    <t>elc_spv-ITA_0068</t>
+  </si>
+  <si>
     <t>elc_spv-ITA_0030</t>
   </si>
   <si>
     <t>elc_spv-ITA_0042</t>
   </si>
   <si>
-    <t>elc_spv-ITA_0068</t>
-  </si>
-  <si>
     <t>ep_solar_pv_001</t>
   </si>
   <si>
@@ -2031,15 +2031,15 @@
     <t>windon</t>
   </si>
   <si>
+    <t>elc_won-ITA_0073</t>
+  </si>
+  <si>
+    <t>elc_won-ITA_0096</t>
+  </si>
+  <si>
     <t>elc_won-ITA_0022</t>
   </si>
   <si>
-    <t>elc_won-ITA_0073</t>
-  </si>
-  <si>
-    <t>elc_won-ITA_0096</t>
-  </si>
-  <si>
     <t>ep_windon_wind_010</t>
   </si>
   <si>
@@ -2469,42 +2469,42 @@
     <t>ele</t>
   </si>
   <si>
+    <t>Aggregated Plant - EMBER Gap - way/109756016-380_Missing Bioenergy Capacity</t>
+  </si>
+  <si>
+    <t>GW</t>
+  </si>
+  <si>
+    <t>TWh</t>
+  </si>
+  <si>
+    <t>daynite</t>
+  </si>
+  <si>
+    <t>yes</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/144005863-380_Missing Bioenergy Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/98902899-380_Missing Bioenergy Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/81938081-380_Missing Bioenergy Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/84696559-380_Missing Bioenergy Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/34157795-380_Missing Bioenergy Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/58440884-380_Missing Bioenergy Capacity</t>
+  </si>
+  <si>
     <t>Aggregated Plant - EMBER Gap - way/108020416-380_Missing Bioenergy Capacity</t>
   </si>
   <si>
-    <t>GW</t>
-  </si>
-  <si>
-    <t>TWh</t>
-  </si>
-  <si>
-    <t>daynite</t>
-  </si>
-  <si>
-    <t>yes</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/84696559-380_Missing Bioenergy Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/144005863-380_Missing Bioenergy Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/98902899-380_Missing Bioenergy Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/109756016-380_Missing Bioenergy Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/34157795-380_Missing Bioenergy Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/58440884-380_Missing Bioenergy Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/81938081-380_Missing Bioenergy Capacity</t>
-  </si>
-  <si>
     <t>Acerra power station_1</t>
   </si>
   <si>
@@ -2529,15 +2529,15 @@
     <t>Aggregated Plant - EMBER Gap - way/409439916-380_Missing Coal Capacity</t>
   </si>
   <si>
+    <t>Aggregated Plant - EMBER Gap - way/418902800-380_Missing Coal Capacity</t>
+  </si>
+  <si>
     <t>Aggregated Plant - EMBER Gap - way/303915533-380_Missing Coal Capacity</t>
   </si>
   <si>
     <t>Aggregated Plant - EMBER Gap - way/82767145-380_Missing Coal Capacity</t>
   </si>
   <si>
-    <t>Aggregated Plant - EMBER Gap - way/418902800-380_Missing Coal Capacity</t>
-  </si>
-  <si>
     <t>Fiume Santo power station_Unit 3</t>
   </si>
   <si>
@@ -2568,126 +2568,126 @@
     <t>Torrevaldaliga Nord power station_Unit 3</t>
   </si>
   <si>
+    <t>Aggregated Plant - EMBER Gap - way/338753171-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/162828577-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/98900549-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/149997403-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/162960205-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/133601335-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/82084019-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/411026199-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/110330925-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/105581403-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/98421779-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/109756016-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/421827453-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/99826025-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/107438024-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/116797658-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/339104227-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/60725875-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/82078641-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/103974940-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/109993642-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/82767145-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/158739183-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/145665799-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/1137611914-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/132450233-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/59462715-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/105757794-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/255011550-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/172302572-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/414663585-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/419423704-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/61157826-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/181125039-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/103381531-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/199675964-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/432729521-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/100407576-380_Missing Gas Capacity</t>
+  </si>
+  <si>
     <t>Aggregated Plant - EMBER Gap - way/416989699-380_Missing Gas Capacity</t>
   </si>
   <si>
-    <t>Aggregated Plant - EMBER Gap - way/100407576-380_Missing Gas Capacity</t>
-  </si>
-  <si>
     <t>Aggregated Plant - EMBER Gap - way/103653592-380_Missing Gas Capacity</t>
   </si>
   <si>
-    <t>Aggregated Plant - EMBER Gap - way/82767145-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/109993642-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/162828577-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/98900549-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/338753171-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/99826025-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/421827453-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/1137611914-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/158739183-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/145665799-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/132450233-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/116797658-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/107438024-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/339104227-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/162960205-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/149997403-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/133601335-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/103381531-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/103974940-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/82078641-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/432729521-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/199675964-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/181125039-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/105757794-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/172302572-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/255011550-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/59462715-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/411026199-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/82084019-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/98421779-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/105581403-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/60725875-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/109756016-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/110330925-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/61157826-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/414663585-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/419423704-380_Missing Gas Capacity</t>
-  </si>
-  <si>
     <t>Altomonte power station_1</t>
   </si>
   <si>
@@ -3000,102 +3000,102 @@
     <t>Valle Secolo geothermal power plant_2</t>
   </si>
   <si>
+    <t>Aggregated Plant - IRENA Gap - way/64200868-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/114931087-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - IT31-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/61626687-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - IT71-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/108020416-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - IT71-400_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - IT36-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/1100665914-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - IT72-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/59462263-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - IT10-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - IT93-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/338753171-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/75602396-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/419423704-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/491424937-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/72466334-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/104359058-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/82083756-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/116517585-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/96190189-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - IT21-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/144005863-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/1137611914-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/109588422-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - IT72-400_Missing Hydro Capacity</t>
+  </si>
+  <si>
     <t>Aggregated Plant - IRENA Gap - IT53-380_Missing Hydro Capacity</t>
   </si>
   <si>
+    <t>Aggregated Plant - IRENA Gap - IT7-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/339703159-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
     <t>Aggregated Plant - IRENA Gap - way/61712456-380_Missing Hydro Capacity</t>
   </si>
   <si>
-    <t>Aggregated Plant - IRENA Gap - IT7-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/339703159-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
     <t>Aggregated Plant - IRENA Gap - IT30-500_Missing Hydro Capacity</t>
   </si>
   <si>
-    <t>Aggregated Plant - IRENA Gap - way/64200868-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - IT71-400_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - IT36-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/419423704-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/491424937-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/104359058-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/72466334-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/82083756-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/1100665914-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - IT72-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/59462263-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/96190189-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/116517585-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/61626687-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - IT31-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/114931087-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/1137611914-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/109588422-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - IT72-400_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - IT93-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - IT10-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/338753171-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - IT21-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/144005863-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - IT71-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/108020416-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/75602396-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
     <t>Baschi hydroelectric plant_</t>
   </si>
   <si>
@@ -3402,15 +3402,15 @@
     <t>Aggregated Plant - IRENA Gap - ITA_68_Missing Solar Capacity</t>
   </si>
   <si>
+    <t>Aggregated Plant - IRENA Gap - ITA_96_Missing Onshore wind energy Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - ITA_22_Missing Onshore wind energy Capacity</t>
+  </si>
+  <si>
     <t>Aggregated Plant - IRENA Gap - ITA_73_Missing Onshore wind energy Capacity</t>
   </si>
   <si>
-    <t>Aggregated Plant - IRENA Gap - ITA_22_Missing Onshore wind energy Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - ITA_96_Missing Onshore wind energy Capacity</t>
-  </si>
-  <si>
     <t>AF</t>
   </si>
   <si>
@@ -4002,18 +4002,18 @@
     <t>ccs retrofit of -- Sulcis power station_Unit 3</t>
   </si>
   <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/409439916-380_Missing Coal Capacity</t>
+  </si>
+  <si>
     <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/418902800-380_Missing Coal Capacity</t>
   </si>
   <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/409439916-380_Missing Coal Capacity</t>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/82767145-380_Missing Coal Capacity</t>
   </si>
   <si>
     <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/303915533-380_Missing Coal Capacity</t>
   </si>
   <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/82767145-380_Missing Coal Capacity</t>
-  </si>
-  <si>
     <t>ccs retrofit of -- Brindisi Sud power station_Unit 1</t>
   </si>
   <si>
@@ -4302,124 +4302,124 @@
     <t>ccs retrofit of -- Aggregated Plant</t>
   </si>
   <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/109993642-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/59462715-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/411026199-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/109756016-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/103381531-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/103974940-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/133601335-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/339104227-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/158739183-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/145665799-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/338753171-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/110330925-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/105581403-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/255011550-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/181125039-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/132450233-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/100407576-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/99826025-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/105757794-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/416989699-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/162960205-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/419423704-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/432729521-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/149997403-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/82078641-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/1137611914-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/199675964-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/103653592-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/107438024-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/98421779-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/82767145-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/98900549-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/82084019-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/421827453-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/172302572-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/60725875-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/162828577-380_Missing Gas Capacity</t>
+  </si>
+  <si>
     <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/116797658-380_Missing Gas Capacity</t>
   </si>
   <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/414663585-380_Missing Gas Capacity</t>
+  </si>
+  <si>
     <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/61157826-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/105757794-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/99826025-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/416989699-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/100407576-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/132450233-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/181125039-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/255011550-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/105581403-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/158739183-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/339104227-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/133601335-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/145665799-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/59462715-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/172302572-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/414663585-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/421827453-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/82084019-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/60725875-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/109993642-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/103974940-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/162828577-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/82767145-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/149997403-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/432729521-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/419423704-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/162960205-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/103653592-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/1137611914-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/82078641-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/199675964-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/98900549-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/107438024-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/98421779-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/103381531-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/411026199-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/109756016-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/338753171-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/110330925-380_Missing Gas Capacity</t>
   </si>
   <si>
     <t>ccs retrofit of -- Tavazzano power station_CCGT8, timepoint 1</t>
@@ -4823,7 +4823,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{50A3CAD2-9147-48DF-8460-A3EF8D381C04}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54BAE8D9-5115-45D9-AB7C-D5B117159D4E}">
   <dimension ref="B9:T278"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -5011,7 +5011,7 @@
         <v>33</v>
       </c>
       <c r="D13" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E13">
         <v>0.18317520000000001</v>
@@ -5067,7 +5067,7 @@
         <v>33</v>
       </c>
       <c r="D14" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E14">
         <v>0.13765950000000002</v>
@@ -5515,7 +5515,7 @@
         <v>33</v>
       </c>
       <c r="D22" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E22">
         <v>0.33007379999999992</v>
@@ -5571,7 +5571,7 @@
         <v>33</v>
       </c>
       <c r="D23" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E23">
         <v>0.33007379999999992</v>
@@ -5627,7 +5627,7 @@
         <v>33</v>
       </c>
       <c r="D24" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E24">
         <v>0.33007379999999992</v>
@@ -5683,7 +5683,7 @@
         <v>49</v>
       </c>
       <c r="D25" t="s">
-        <v>50</v>
+        <v>84</v>
       </c>
       <c r="E25">
         <v>0.49118125000000001</v>
@@ -5739,7 +5739,7 @@
         <v>49</v>
       </c>
       <c r="D26" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="E26">
         <v>0.52272499999999988</v>
@@ -5795,7 +5795,7 @@
         <v>49</v>
       </c>
       <c r="D27" t="s">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="E27">
         <v>0.450625</v>
@@ -5851,7 +5851,7 @@
         <v>49</v>
       </c>
       <c r="D28" t="s">
-        <v>81</v>
+        <v>67</v>
       </c>
       <c r="E28">
         <v>0.52272499999999988</v>
@@ -5907,7 +5907,7 @@
         <v>49</v>
       </c>
       <c r="D29" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E29">
         <v>0.49118125000000001</v>
@@ -5963,7 +5963,7 @@
         <v>49</v>
       </c>
       <c r="D30" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E30">
         <v>0.49118125000000001</v>
@@ -6019,7 +6019,7 @@
         <v>49</v>
       </c>
       <c r="D31" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E31">
         <v>0.49118125000000001</v>
@@ -6131,7 +6131,7 @@
         <v>49</v>
       </c>
       <c r="D33" t="s">
-        <v>59</v>
+        <v>81</v>
       </c>
       <c r="E33">
         <v>0.49118125000000001</v>
@@ -6299,7 +6299,7 @@
         <v>49</v>
       </c>
       <c r="D36" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="E36">
         <v>0.49118125000000001</v>
@@ -6355,7 +6355,7 @@
         <v>49</v>
       </c>
       <c r="D37" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="E37">
         <v>0.49118125000000001</v>
@@ -6411,7 +6411,7 @@
         <v>49</v>
       </c>
       <c r="D38" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="E38">
         <v>0.49118125000000001</v>
@@ -6467,7 +6467,7 @@
         <v>49</v>
       </c>
       <c r="D39" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="E39">
         <v>0.49118125000000001</v>
@@ -6523,7 +6523,7 @@
         <v>49</v>
       </c>
       <c r="D40" t="s">
-        <v>52</v>
+        <v>77</v>
       </c>
       <c r="E40">
         <v>0.46865000000000007</v>
@@ -6579,7 +6579,7 @@
         <v>49</v>
       </c>
       <c r="D41" t="s">
-        <v>52</v>
+        <v>77</v>
       </c>
       <c r="E41">
         <v>0.49118125000000001</v>
@@ -6635,7 +6635,7 @@
         <v>49</v>
       </c>
       <c r="D42" t="s">
-        <v>52</v>
+        <v>77</v>
       </c>
       <c r="E42">
         <v>0.49118125000000001</v>
@@ -6691,7 +6691,7 @@
         <v>49</v>
       </c>
       <c r="D43" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E43">
         <v>0.49118125000000001</v>
@@ -6747,7 +6747,7 @@
         <v>49</v>
       </c>
       <c r="D44" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E44">
         <v>0.49118125000000001</v>
@@ -6803,7 +6803,7 @@
         <v>49</v>
       </c>
       <c r="D45" t="s">
-        <v>82</v>
+        <v>53</v>
       </c>
       <c r="E45">
         <v>0.49118125000000001</v>
@@ -6859,7 +6859,7 @@
         <v>49</v>
       </c>
       <c r="D46" t="s">
-        <v>82</v>
+        <v>53</v>
       </c>
       <c r="E46">
         <v>0.49118125000000001</v>
@@ -6915,7 +6915,7 @@
         <v>49</v>
       </c>
       <c r="D47" t="s">
-        <v>82</v>
+        <v>53</v>
       </c>
       <c r="E47">
         <v>0.49118125000000001</v>
@@ -6971,7 +6971,7 @@
         <v>49</v>
       </c>
       <c r="D48" t="s">
-        <v>82</v>
+        <v>53</v>
       </c>
       <c r="E48">
         <v>0.49118125000000001</v>
@@ -7027,7 +7027,7 @@
         <v>49</v>
       </c>
       <c r="D49" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E49">
         <v>0.47315625000000006</v>
@@ -7083,7 +7083,7 @@
         <v>49</v>
       </c>
       <c r="D50" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E50">
         <v>0.47315625000000006</v>
@@ -7139,7 +7139,7 @@
         <v>49</v>
       </c>
       <c r="D51" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="E51">
         <v>0.49118125000000001</v>
@@ -7195,7 +7195,7 @@
         <v>49</v>
       </c>
       <c r="D52" t="s">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="E52">
         <v>0.54075000000000006</v>
@@ -7251,7 +7251,7 @@
         <v>49</v>
       </c>
       <c r="D53" t="s">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="E53">
         <v>0.49118125000000001</v>
@@ -7363,7 +7363,7 @@
         <v>49</v>
       </c>
       <c r="D55" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="E55">
         <v>0.49118125000000001</v>
@@ -7419,7 +7419,7 @@
         <v>49</v>
       </c>
       <c r="D56" t="s">
-        <v>86</v>
+        <v>63</v>
       </c>
       <c r="E56">
         <v>0.49118125000000001</v>
@@ -7475,7 +7475,7 @@
         <v>49</v>
       </c>
       <c r="D57" t="s">
-        <v>86</v>
+        <v>63</v>
       </c>
       <c r="E57">
         <v>0.49118125000000001</v>
@@ -7531,7 +7531,7 @@
         <v>49</v>
       </c>
       <c r="D58" t="s">
-        <v>84</v>
+        <v>55</v>
       </c>
       <c r="E58">
         <v>0.47315625000000006</v>
@@ -7587,7 +7587,7 @@
         <v>49</v>
       </c>
       <c r="D59" t="s">
-        <v>84</v>
+        <v>55</v>
       </c>
       <c r="E59">
         <v>0.47315625000000006</v>
@@ -7643,7 +7643,7 @@
         <v>49</v>
       </c>
       <c r="D60" t="s">
-        <v>84</v>
+        <v>55</v>
       </c>
       <c r="E60">
         <v>0.450625</v>
@@ -7699,7 +7699,7 @@
         <v>49</v>
       </c>
       <c r="D61" t="s">
-        <v>84</v>
+        <v>55</v>
       </c>
       <c r="E61">
         <v>0.450625</v>
@@ -7811,7 +7811,7 @@
         <v>49</v>
       </c>
       <c r="D63" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="E63">
         <v>0.4911812499999999</v>
@@ -7867,7 +7867,7 @@
         <v>49</v>
       </c>
       <c r="D64" t="s">
-        <v>80</v>
+        <v>61</v>
       </c>
       <c r="E64">
         <v>0.49118125000000001</v>
@@ -7923,7 +7923,7 @@
         <v>49</v>
       </c>
       <c r="D65" t="s">
-        <v>80</v>
+        <v>61</v>
       </c>
       <c r="E65">
         <v>0.49118125000000001</v>
@@ -7979,7 +7979,7 @@
         <v>49</v>
       </c>
       <c r="D66" t="s">
-        <v>62</v>
+        <v>87</v>
       </c>
       <c r="E66">
         <v>0.49118125000000001</v>
@@ -8147,7 +8147,7 @@
         <v>49</v>
       </c>
       <c r="D69" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="E69">
         <v>0.49118125000000001</v>
@@ -8203,7 +8203,7 @@
         <v>49</v>
       </c>
       <c r="D70" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="E70">
         <v>0.49118125000000001</v>
@@ -8259,7 +8259,7 @@
         <v>49</v>
       </c>
       <c r="D71" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="E71">
         <v>0.49118125000000001</v>
@@ -8315,7 +8315,7 @@
         <v>49</v>
       </c>
       <c r="D72" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="E72">
         <v>0.49118125000000001</v>
@@ -8371,7 +8371,7 @@
         <v>49</v>
       </c>
       <c r="D73" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="E73">
         <v>0.49118125000000001</v>
@@ -8427,7 +8427,7 @@
         <v>49</v>
       </c>
       <c r="D74" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="E74">
         <v>0.49118125000000001</v>
@@ -8483,7 +8483,7 @@
         <v>49</v>
       </c>
       <c r="D75" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="E75">
         <v>0.50470000000000004</v>
@@ -8539,7 +8539,7 @@
         <v>49</v>
       </c>
       <c r="D76" t="s">
-        <v>58</v>
+        <v>82</v>
       </c>
       <c r="E76">
         <v>0.49118125000000001</v>
@@ -8595,7 +8595,7 @@
         <v>49</v>
       </c>
       <c r="D77" t="s">
-        <v>58</v>
+        <v>82</v>
       </c>
       <c r="E77">
         <v>0.49118125000000001</v>
@@ -8763,7 +8763,7 @@
         <v>49</v>
       </c>
       <c r="D80" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E80">
         <v>0.49118125000000001</v>
@@ -8819,7 +8819,7 @@
         <v>49</v>
       </c>
       <c r="D81" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E81">
         <v>0.49118125000000001</v>
@@ -8875,7 +8875,7 @@
         <v>49</v>
       </c>
       <c r="D82" t="s">
-        <v>70</v>
+        <v>52</v>
       </c>
       <c r="E82">
         <v>0.49118125000000001</v>
@@ -8931,7 +8931,7 @@
         <v>49</v>
       </c>
       <c r="D83" t="s">
-        <v>70</v>
+        <v>52</v>
       </c>
       <c r="E83">
         <v>0.49118125000000001</v>
@@ -8987,7 +8987,7 @@
         <v>49</v>
       </c>
       <c r="D84" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E84">
         <v>0.49118125000000001</v>
@@ -9043,7 +9043,7 @@
         <v>49</v>
       </c>
       <c r="D85" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E85">
         <v>0.49118125000000001</v>
@@ -9099,7 +9099,7 @@
         <v>49</v>
       </c>
       <c r="D86" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E86">
         <v>0.49118125000000001</v>
@@ -9155,7 +9155,7 @@
         <v>49</v>
       </c>
       <c r="D87" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E87">
         <v>0.49118125000000001</v>
@@ -9211,7 +9211,7 @@
         <v>49</v>
       </c>
       <c r="D88" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E88">
         <v>0.49118125000000001</v>
@@ -9267,7 +9267,7 @@
         <v>49</v>
       </c>
       <c r="D89" t="s">
-        <v>73</v>
+        <v>62</v>
       </c>
       <c r="E89">
         <v>0.52272499999999988</v>
@@ -9323,7 +9323,7 @@
         <v>49</v>
       </c>
       <c r="D90" t="s">
-        <v>73</v>
+        <v>62</v>
       </c>
       <c r="E90">
         <v>0.49118125000000001</v>
@@ -9379,7 +9379,7 @@
         <v>49</v>
       </c>
       <c r="D91" t="s">
-        <v>83</v>
+        <v>54</v>
       </c>
       <c r="E91">
         <v>0.49118125000000001</v>
@@ -9435,7 +9435,7 @@
         <v>49</v>
       </c>
       <c r="D92" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="E92">
         <v>0.52272499999999988</v>
@@ -9491,7 +9491,7 @@
         <v>49</v>
       </c>
       <c r="D93" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E93">
         <v>0.49118125000000001</v>
@@ -9547,7 +9547,7 @@
         <v>49</v>
       </c>
       <c r="D94" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E94">
         <v>0.49118125000000001</v>
@@ -9603,7 +9603,7 @@
         <v>49</v>
       </c>
       <c r="D95" t="s">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="E95">
         <v>0.49118125000000001</v>
@@ -9659,7 +9659,7 @@
         <v>49</v>
       </c>
       <c r="D96" t="s">
-        <v>51</v>
+        <v>78</v>
       </c>
       <c r="E96">
         <v>0.49118125000000001</v>
@@ -9715,7 +9715,7 @@
         <v>49</v>
       </c>
       <c r="D97" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="E97">
         <v>0.49118125000000001</v>
@@ -9827,7 +9827,7 @@
         <v>49</v>
       </c>
       <c r="D99" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="E99">
         <v>0.54075000000000006</v>
@@ -9883,7 +9883,7 @@
         <v>49</v>
       </c>
       <c r="D100" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E100">
         <v>0.54075000000000006</v>
@@ -9939,7 +9939,7 @@
         <v>49</v>
       </c>
       <c r="D101" t="s">
-        <v>51</v>
+        <v>78</v>
       </c>
       <c r="E101">
         <v>0.54075000000000006</v>
@@ -9995,7 +9995,7 @@
         <v>49</v>
       </c>
       <c r="D102" t="s">
-        <v>64</v>
+        <v>50</v>
       </c>
       <c r="E102">
         <v>0.49118125000000001</v>
@@ -10051,7 +10051,7 @@
         <v>49</v>
       </c>
       <c r="D103" t="s">
-        <v>64</v>
+        <v>50</v>
       </c>
       <c r="E103">
         <v>0.49118125000000001</v>
@@ -10107,7 +10107,7 @@
         <v>49</v>
       </c>
       <c r="D104" t="s">
-        <v>80</v>
+        <v>61</v>
       </c>
       <c r="E104">
         <v>0.49118125000000001</v>
@@ -10163,7 +10163,7 @@
         <v>49</v>
       </c>
       <c r="D105" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="E105">
         <v>0.49118125000000001</v>
@@ -10219,7 +10219,7 @@
         <v>49</v>
       </c>
       <c r="D106" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="E106">
         <v>0.450625</v>
@@ -10275,7 +10275,7 @@
         <v>49</v>
       </c>
       <c r="D107" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="E107">
         <v>0.450625</v>
@@ -10331,7 +10331,7 @@
         <v>49</v>
       </c>
       <c r="D108" t="s">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="E108">
         <v>0.47315625000000006</v>
@@ -10443,7 +10443,7 @@
         <v>49</v>
       </c>
       <c r="D110" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="E110">
         <v>0.49118125000000001</v>
@@ -10499,7 +10499,7 @@
         <v>49</v>
       </c>
       <c r="D111" t="s">
-        <v>52</v>
+        <v>77</v>
       </c>
       <c r="E111">
         <v>0.46865000000000007</v>
@@ -10611,7 +10611,7 @@
         <v>49</v>
       </c>
       <c r="D113" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="E113">
         <v>0.49118125000000001</v>
@@ -11115,7 +11115,7 @@
         <v>49</v>
       </c>
       <c r="D122" t="s">
-        <v>78</v>
+        <v>37</v>
       </c>
       <c r="E122">
         <v>0.54075000000000006</v>
@@ -11563,7 +11563,7 @@
         <v>49</v>
       </c>
       <c r="D130" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E130">
         <v>0.54075000000000006</v>
@@ -11619,7 +11619,7 @@
         <v>49</v>
       </c>
       <c r="D131" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E131">
         <v>0.54075000000000006</v>
@@ -11675,7 +11675,7 @@
         <v>49</v>
       </c>
       <c r="D132" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E132">
         <v>0.54075000000000006</v>
@@ -11731,7 +11731,7 @@
         <v>49</v>
       </c>
       <c r="D133" t="s">
-        <v>58</v>
+        <v>21</v>
       </c>
       <c r="E133">
         <v>0.54075000000000006</v>
@@ -11843,7 +11843,7 @@
         <v>49</v>
       </c>
       <c r="D135" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E135">
         <v>0.54075000000000006</v>
@@ -12459,7 +12459,7 @@
         <v>49</v>
       </c>
       <c r="D146" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E146">
         <v>0.54075000000000006</v>
@@ -12515,7 +12515,7 @@
         <v>49</v>
       </c>
       <c r="D147" t="s">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="E147">
         <v>0.54075000000000006</v>
@@ -12571,7 +12571,7 @@
         <v>49</v>
       </c>
       <c r="D148" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E148">
         <v>0.54075000000000006</v>
@@ -12627,7 +12627,7 @@
         <v>49</v>
       </c>
       <c r="D149" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E149">
         <v>0.54075000000000006</v>
@@ -12683,7 +12683,7 @@
         <v>49</v>
       </c>
       <c r="D150" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E150">
         <v>0.54075000000000006</v>
@@ -12907,7 +12907,7 @@
         <v>49</v>
       </c>
       <c r="D154" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E154">
         <v>0.54075000000000006</v>
@@ -12963,7 +12963,7 @@
         <v>49</v>
       </c>
       <c r="D155" t="s">
-        <v>17</v>
+        <v>81</v>
       </c>
       <c r="E155">
         <v>0.54075000000000006</v>
@@ -13467,7 +13467,7 @@
         <v>49</v>
       </c>
       <c r="D164" t="s">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="E164">
         <v>0.48667500000000002</v>
@@ -14307,7 +14307,7 @@
         <v>49</v>
       </c>
       <c r="D179" t="s">
-        <v>51</v>
+        <v>78</v>
       </c>
       <c r="E179">
         <v>0.46865000000000007</v>
@@ -14363,7 +14363,7 @@
         <v>49</v>
       </c>
       <c r="D180" t="s">
-        <v>51</v>
+        <v>78</v>
       </c>
       <c r="E180">
         <v>0.46865000000000007</v>
@@ -14587,7 +14587,7 @@
         <v>49</v>
       </c>
       <c r="D184" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="E184">
         <v>0.48667500000000002</v>
@@ -14643,7 +14643,7 @@
         <v>49</v>
       </c>
       <c r="D185" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="E185">
         <v>0.48667500000000002</v>
@@ -15371,7 +15371,7 @@
         <v>49</v>
       </c>
       <c r="D198" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E198">
         <v>0.50470000000000004</v>
@@ -15595,7 +15595,7 @@
         <v>49</v>
       </c>
       <c r="D202" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E202">
         <v>0.46865000000000007</v>
@@ -16323,7 +16323,7 @@
         <v>49</v>
       </c>
       <c r="D215" t="s">
-        <v>70</v>
+        <v>52</v>
       </c>
       <c r="E215">
         <v>0.450625</v>
@@ -16491,7 +16491,7 @@
         <v>49</v>
       </c>
       <c r="D218" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E218">
         <v>0.50470000000000004</v>
@@ -16547,7 +16547,7 @@
         <v>49</v>
       </c>
       <c r="D219" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E219">
         <v>0.50470000000000004</v>
@@ -16715,7 +16715,7 @@
         <v>49</v>
       </c>
       <c r="D222" t="s">
-        <v>86</v>
+        <v>63</v>
       </c>
       <c r="E222">
         <v>0.450625</v>
@@ -16771,7 +16771,7 @@
         <v>49</v>
       </c>
       <c r="D223" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E223">
         <v>0.29741250000000002</v>
@@ -16827,7 +16827,7 @@
         <v>49</v>
       </c>
       <c r="D224" t="s">
-        <v>73</v>
+        <v>62</v>
       </c>
       <c r="E224">
         <v>0.28839999999999999</v>
@@ -16883,7 +16883,7 @@
         <v>49</v>
       </c>
       <c r="D225" t="s">
-        <v>73</v>
+        <v>62</v>
       </c>
       <c r="E225">
         <v>0.28839999999999999</v>
@@ -16939,7 +16939,7 @@
         <v>49</v>
       </c>
       <c r="D226" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="E226">
         <v>0.24784375000000003</v>
@@ -17443,7 +17443,7 @@
         <v>49</v>
       </c>
       <c r="D235" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E235">
         <v>0.25235000000000002</v>
@@ -17723,7 +17723,7 @@
         <v>49</v>
       </c>
       <c r="D240" t="s">
-        <v>73</v>
+        <v>62</v>
       </c>
       <c r="E240">
         <v>0.27938750000000001</v>
@@ -17835,7 +17835,7 @@
         <v>49</v>
       </c>
       <c r="D242" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="E242">
         <v>0.25235000000000002</v>
@@ -18031,7 +18031,7 @@
         <v>49</v>
       </c>
       <c r="D247" t="s">
-        <v>59</v>
+        <v>81</v>
       </c>
       <c r="E247">
         <v>0.32445000000000007</v>
@@ -18101,7 +18101,7 @@
         <v>49</v>
       </c>
       <c r="D249" t="s">
-        <v>83</v>
+        <v>54</v>
       </c>
       <c r="E249">
         <v>0.32445000000000002</v>
@@ -18241,7 +18241,7 @@
         <v>49</v>
       </c>
       <c r="D253" t="s">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="E253">
         <v>0.27938750000000001</v>
@@ -18276,7 +18276,7 @@
         <v>49</v>
       </c>
       <c r="D254" t="s">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="E254">
         <v>0.27938750000000001</v>
@@ -18311,7 +18311,7 @@
         <v>49</v>
       </c>
       <c r="D255" t="s">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="E255">
         <v>0.27938750000000001</v>
@@ -18346,7 +18346,7 @@
         <v>49</v>
       </c>
       <c r="D256" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="E256">
         <v>0.31093124999999999</v>
@@ -18381,7 +18381,7 @@
         <v>49</v>
       </c>
       <c r="D257" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E257">
         <v>0.27938750000000001</v>
@@ -18416,7 +18416,7 @@
         <v>49</v>
       </c>
       <c r="D258" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E258">
         <v>0.27938750000000001</v>
@@ -18451,7 +18451,7 @@
         <v>49</v>
       </c>
       <c r="D259" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="E259">
         <v>0.26136249999999994</v>
@@ -18486,7 +18486,7 @@
         <v>49</v>
       </c>
       <c r="D260" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E260">
         <v>0.28839999999999999</v>
@@ -18521,7 +18521,7 @@
         <v>49</v>
       </c>
       <c r="D261" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E261">
         <v>0.28839999999999999</v>
@@ -18556,7 +18556,7 @@
         <v>49</v>
       </c>
       <c r="D262" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E262">
         <v>0.28839999999999999</v>
@@ -18626,7 +18626,7 @@
         <v>439</v>
       </c>
       <c r="D264" t="s">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="E264">
         <v>0.41457500000000003</v>
@@ -18731,7 +18731,7 @@
         <v>439</v>
       </c>
       <c r="D267" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E267">
         <v>0.22981874999999999</v>
@@ -18941,7 +18941,7 @@
         <v>439</v>
       </c>
       <c r="D273" t="s">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="E273">
         <v>0.27938750000000001</v>
@@ -19149,7 +19149,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9FC99B37-5ED5-4C89-BC3F-D11FD46CA681}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8278635E-A0A5-4394-BD1F-13B024BBC90D}">
   <dimension ref="B9:T842"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -19231,19 +19231,19 @@
         <v>2022</v>
       </c>
       <c r="F11">
-        <v>0.22450847457627116</v>
+        <v>1.0679322033898306</v>
       </c>
       <c r="G11">
-        <v>0.33990000000000004</v>
+        <v>0.36049999999999999</v>
       </c>
       <c r="H11">
-        <v>4427.5</v>
+        <v>3850.0000000000005</v>
       </c>
       <c r="I11">
-        <v>157.30000000000001</v>
+        <v>143</v>
       </c>
       <c r="J11">
-        <v>9.240000000000002</v>
+        <v>8.4</v>
       </c>
       <c r="K11">
         <v>50</v>
@@ -19284,19 +19284,19 @@
         <v>2022</v>
       </c>
       <c r="F12">
-        <v>0.49149152542372881</v>
+        <v>0.22450847457627116</v>
       </c>
       <c r="G12">
-        <v>0.36049999999999999</v>
+        <v>0.33990000000000004</v>
       </c>
       <c r="H12">
-        <v>3850.0000000000005</v>
+        <v>4427.5</v>
       </c>
       <c r="I12">
-        <v>143</v>
+        <v>157.30000000000001</v>
       </c>
       <c r="J12">
-        <v>8.4</v>
+        <v>9.240000000000002</v>
       </c>
       <c r="K12">
         <v>50</v>
@@ -19337,19 +19337,19 @@
         <v>2022</v>
       </c>
       <c r="F13">
-        <v>0.24877966101694915</v>
+        <v>0.35800000000000004</v>
       </c>
       <c r="G13">
-        <v>0.33990000000000004</v>
+        <v>0.36050000000000004</v>
       </c>
       <c r="H13">
-        <v>4427.5</v>
+        <v>3850.0000000000009</v>
       </c>
       <c r="I13">
-        <v>157.30000000000001</v>
+        <v>143</v>
       </c>
       <c r="J13">
-        <v>9.240000000000002</v>
+        <v>8.4</v>
       </c>
       <c r="K13">
         <v>50</v>
@@ -19390,19 +19390,19 @@
         <v>2022</v>
       </c>
       <c r="F14">
-        <v>0.27911864406779663</v>
+        <v>0.39440677966101695</v>
       </c>
       <c r="G14">
-        <v>0.33990000000000004</v>
+        <v>0.36049999999999999</v>
       </c>
       <c r="H14">
-        <v>4427.5</v>
+        <v>3850.0000000000005</v>
       </c>
       <c r="I14">
-        <v>157.30000000000001</v>
+        <v>143</v>
       </c>
       <c r="J14">
-        <v>9.240000000000002</v>
+        <v>8.4</v>
       </c>
       <c r="K14">
         <v>50</v>
@@ -19443,13 +19443,13 @@
         <v>2022</v>
       </c>
       <c r="F15">
-        <v>0.35800000000000004</v>
+        <v>0.49149152542372881</v>
       </c>
       <c r="G15">
-        <v>0.36050000000000004</v>
+        <v>0.36049999999999999</v>
       </c>
       <c r="H15">
-        <v>3850.0000000000009</v>
+        <v>3850.0000000000005</v>
       </c>
       <c r="I15">
         <v>143</v>
@@ -19496,7 +19496,7 @@
         <v>2022</v>
       </c>
       <c r="F16">
-        <v>1.0679322033898306</v>
+        <v>0.51576271186440681</v>
       </c>
       <c r="G16">
         <v>0.36049999999999999</v>
@@ -19549,19 +19549,19 @@
         <v>2022</v>
       </c>
       <c r="F17">
-        <v>0.39440677966101695</v>
+        <v>0.24877966101694915</v>
       </c>
       <c r="G17">
-        <v>0.36049999999999999</v>
+        <v>0.33990000000000004</v>
       </c>
       <c r="H17">
-        <v>3850.0000000000005</v>
+        <v>4427.5</v>
       </c>
       <c r="I17">
-        <v>143</v>
+        <v>157.30000000000001</v>
       </c>
       <c r="J17">
-        <v>8.4</v>
+        <v>9.240000000000002</v>
       </c>
       <c r="K17">
         <v>50</v>
@@ -19602,19 +19602,19 @@
         <v>2022</v>
       </c>
       <c r="F18">
-        <v>0.51576271186440681</v>
+        <v>0.27911864406779663</v>
       </c>
       <c r="G18">
-        <v>0.36049999999999999</v>
+        <v>0.33990000000000004</v>
       </c>
       <c r="H18">
-        <v>3850.0000000000005</v>
+        <v>4427.5</v>
       </c>
       <c r="I18">
-        <v>143</v>
+        <v>157.30000000000001</v>
       </c>
       <c r="J18">
-        <v>8.4</v>
+        <v>9.240000000000002</v>
       </c>
       <c r="K18">
         <v>50</v>
@@ -19649,7 +19649,7 @@
         <v>13</v>
       </c>
       <c r="D19" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="E19">
         <v>2008</v>
@@ -19702,7 +19702,7 @@
         <v>13</v>
       </c>
       <c r="D20" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E20">
         <v>1998</v>
@@ -19755,7 +19755,7 @@
         <v>13</v>
       </c>
       <c r="D21" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E21">
         <v>2008</v>
@@ -19808,7 +19808,7 @@
         <v>13</v>
       </c>
       <c r="D22" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E22">
         <v>2001</v>
@@ -19861,7 +19861,7 @@
         <v>13</v>
       </c>
       <c r="D23" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E23">
         <v>2013</v>
@@ -19914,7 +19914,7 @@
         <v>13</v>
       </c>
       <c r="D24" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E24">
         <v>1965</v>
@@ -19967,7 +19967,7 @@
         <v>13</v>
       </c>
       <c r="D25" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E25">
         <v>2003</v>
@@ -20020,7 +20020,7 @@
         <v>13</v>
       </c>
       <c r="D26" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E26">
         <v>2009</v>
@@ -20073,7 +20073,7 @@
         <v>13</v>
       </c>
       <c r="D27" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E27">
         <v>2018</v>
@@ -20126,7 +20126,7 @@
         <v>13</v>
       </c>
       <c r="D28" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="E28">
         <v>2009</v>
@@ -20291,19 +20291,19 @@
         <v>2022</v>
       </c>
       <c r="F31">
-        <v>0.61803468208092449</v>
+        <v>0.18416184971098257</v>
       </c>
       <c r="G31">
-        <v>0.37080000000000002</v>
+        <v>0.35020000000000001</v>
       </c>
       <c r="H31">
-        <v>2200</v>
+        <v>2530</v>
       </c>
       <c r="I31">
-        <v>66</v>
+        <v>72.600000000000009</v>
       </c>
       <c r="J31">
-        <v>5.25</v>
+        <v>5.7750000000000004</v>
       </c>
       <c r="K31">
         <v>50</v>
@@ -20344,19 +20344,19 @@
         <v>2022</v>
       </c>
       <c r="F32">
-        <v>0.18416184971098257</v>
+        <v>0.61803468208092449</v>
       </c>
       <c r="G32">
-        <v>0.35020000000000001</v>
+        <v>0.37080000000000002</v>
       </c>
       <c r="H32">
-        <v>2530</v>
+        <v>2200</v>
       </c>
       <c r="I32">
-        <v>72.600000000000009</v>
+        <v>66</v>
       </c>
       <c r="J32">
-        <v>5.7750000000000004</v>
+        <v>5.25</v>
       </c>
       <c r="K32">
         <v>50</v>
@@ -20497,7 +20497,7 @@
         <v>33</v>
       </c>
       <c r="D35" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E35">
         <v>2005</v>
@@ -20550,7 +20550,7 @@
         <v>33</v>
       </c>
       <c r="D36" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E36">
         <v>1986</v>
@@ -20762,7 +20762,7 @@
         <v>33</v>
       </c>
       <c r="D40" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E40">
         <v>2009</v>
@@ -20815,7 +20815,7 @@
         <v>33</v>
       </c>
       <c r="D41" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E41">
         <v>2010</v>
@@ -20868,7 +20868,7 @@
         <v>33</v>
       </c>
       <c r="D42" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E42">
         <v>2010</v>
@@ -20927,7 +20927,7 @@
         <v>2022</v>
       </c>
       <c r="F43">
-        <v>0.19676367392472002</v>
+        <v>0.18824049497996109</v>
       </c>
       <c r="G43">
         <v>0.59739999999999993</v>
@@ -20980,19 +20980,19 @@
         <v>2022</v>
       </c>
       <c r="F44">
-        <v>0.3567559186877659</v>
+        <v>0.21113131843159935</v>
       </c>
       <c r="G44">
-        <v>0.61799999999999999</v>
+        <v>0.59739999999999993</v>
       </c>
       <c r="H44">
-        <v>1100</v>
+        <v>1265</v>
       </c>
       <c r="I44">
-        <v>33</v>
+        <v>36.300000000000004</v>
       </c>
       <c r="J44">
-        <v>3.1500000000000004</v>
+        <v>3.4650000000000003</v>
       </c>
       <c r="K44">
         <v>50</v>
@@ -21027,13 +21027,13 @@
         <v>49</v>
       </c>
       <c r="D45" t="s">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="E45">
         <v>2022</v>
       </c>
       <c r="F45">
-        <v>0.27761211420071885</v>
+        <v>0.29344087509812827</v>
       </c>
       <c r="G45">
         <v>0.59739999999999993</v>
@@ -21080,13 +21080,13 @@
         <v>49</v>
       </c>
       <c r="D46" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E46">
         <v>2022</v>
       </c>
       <c r="F46">
-        <v>0.30829555840185086</v>
+        <v>0.37112356319464518</v>
       </c>
       <c r="G46">
         <v>0.61799999999999999</v>
@@ -21133,13 +21133,13 @@
         <v>49</v>
       </c>
       <c r="D47" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E47">
         <v>2022</v>
       </c>
       <c r="F47">
-        <v>0.19481551873734657</v>
+        <v>0.20557907614758497</v>
       </c>
       <c r="G47">
         <v>0.59739999999999993</v>
@@ -21186,13 +21186,13 @@
         <v>49</v>
       </c>
       <c r="D48" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E48">
         <v>2022</v>
       </c>
       <c r="F48">
-        <v>0.19481551873734657</v>
+        <v>0.26543614427963469</v>
       </c>
       <c r="G48">
         <v>0.59739999999999993</v>
@@ -21239,13 +21239,13 @@
         <v>49</v>
       </c>
       <c r="D49" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E49">
         <v>2022</v>
       </c>
       <c r="F49">
-        <v>0.18702289798785268</v>
+        <v>0.19481551873734657</v>
       </c>
       <c r="G49">
         <v>0.59739999999999993</v>
@@ -21292,7 +21292,7 @@
         <v>49</v>
       </c>
       <c r="D50" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E50">
         <v>2022</v>
@@ -21345,7 +21345,7 @@
         <v>49</v>
       </c>
       <c r="D51" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E51">
         <v>2022</v>
@@ -21398,13 +21398,13 @@
         <v>49</v>
       </c>
       <c r="D52" t="s">
-        <v>58</v>
+        <v>21</v>
       </c>
       <c r="E52">
         <v>2022</v>
       </c>
       <c r="F52">
-        <v>0.18556178159732259</v>
+        <v>0.19822479031525012</v>
       </c>
       <c r="G52">
         <v>0.59739999999999993</v>
@@ -21457,7 +21457,7 @@
         <v>2022</v>
       </c>
       <c r="F53">
-        <v>0.23280454489112914</v>
+        <v>0.18702289798785268</v>
       </c>
       <c r="G53">
         <v>0.59739999999999993</v>
@@ -21469,7 +21469,7 @@
         <v>36.300000000000004</v>
       </c>
       <c r="J53">
-        <v>3.4650000000000007</v>
+        <v>3.4650000000000003</v>
       </c>
       <c r="K53">
         <v>50</v>
@@ -21510,7 +21510,7 @@
         <v>2022</v>
       </c>
       <c r="F54">
-        <v>0.26604494277568891</v>
+        <v>0.19481551873734657</v>
       </c>
       <c r="G54">
         <v>0.59739999999999993</v>
@@ -21563,7 +21563,7 @@
         <v>2022</v>
       </c>
       <c r="F55">
-        <v>0.21113131843159935</v>
+        <v>0.28443065735652601</v>
       </c>
       <c r="G55">
         <v>0.59739999999999993</v>
@@ -21616,19 +21616,19 @@
         <v>2022</v>
       </c>
       <c r="F56">
-        <v>0.19627663512787666</v>
+        <v>0.39839773581787374</v>
       </c>
       <c r="G56">
-        <v>0.59739999999999993</v>
+        <v>0.61799999999999999</v>
       </c>
       <c r="H56">
-        <v>1265</v>
+        <v>1100</v>
       </c>
       <c r="I56">
-        <v>36.300000000000004</v>
+        <v>33</v>
       </c>
       <c r="J56">
-        <v>3.4649999999999999</v>
+        <v>3.1500000000000004</v>
       </c>
       <c r="K56">
         <v>50</v>
@@ -21669,7 +21669,7 @@
         <v>2022</v>
       </c>
       <c r="F57">
-        <v>0.21283595422055113</v>
+        <v>0.20212110068999706</v>
       </c>
       <c r="G57">
         <v>0.59739999999999993</v>
@@ -21722,7 +21722,7 @@
         <v>2022</v>
       </c>
       <c r="F58">
-        <v>0.18824049497996109</v>
+        <v>0.21283595422055113</v>
       </c>
       <c r="G58">
         <v>0.59739999999999993</v>
@@ -21775,19 +21775,19 @@
         <v>2022</v>
       </c>
       <c r="F59">
-        <v>0.43468212618270452</v>
+        <v>0.23864901045324952</v>
       </c>
       <c r="G59">
-        <v>0.61799999999999988</v>
+        <v>0.59739999999999993</v>
       </c>
       <c r="H59">
-        <v>1100</v>
+        <v>1265</v>
       </c>
       <c r="I59">
-        <v>33</v>
+        <v>36.300000000000004</v>
       </c>
       <c r="J59">
-        <v>3.1500000000000004</v>
+        <v>3.4650000000000003</v>
       </c>
       <c r="K59">
         <v>50</v>
@@ -21828,19 +21828,19 @@
         <v>2022</v>
       </c>
       <c r="F60">
-        <v>0.23864901045324952</v>
+        <v>0.31243538817501959</v>
       </c>
       <c r="G60">
-        <v>0.59739999999999993</v>
+        <v>0.61799999999999999</v>
       </c>
       <c r="H60">
-        <v>1265</v>
+        <v>1100</v>
       </c>
       <c r="I60">
-        <v>36.300000000000004</v>
+        <v>33</v>
       </c>
       <c r="J60">
-        <v>3.4650000000000003</v>
+        <v>3.1500000000000004</v>
       </c>
       <c r="K60">
         <v>50</v>
@@ -21881,19 +21881,19 @@
         <v>2022</v>
       </c>
       <c r="F61">
-        <v>0.31243538817501959</v>
+        <v>0.19481551873734657</v>
       </c>
       <c r="G61">
-        <v>0.61799999999999999</v>
+        <v>0.59739999999999993</v>
       </c>
       <c r="H61">
-        <v>1100</v>
+        <v>1265</v>
       </c>
       <c r="I61">
-        <v>33</v>
+        <v>36.300000000000004</v>
       </c>
       <c r="J61">
-        <v>3.1500000000000004</v>
+        <v>3.4650000000000003</v>
       </c>
       <c r="K61">
         <v>50</v>
@@ -21934,7 +21934,7 @@
         <v>2022</v>
       </c>
       <c r="F62">
-        <v>0.17484692806676855</v>
+        <v>0.20820908565053911</v>
       </c>
       <c r="G62">
         <v>0.59739999999999993</v>
@@ -21946,7 +21946,7 @@
         <v>36.300000000000004</v>
       </c>
       <c r="J62">
-        <v>3.4650000000000003</v>
+        <v>3.4650000000000007</v>
       </c>
       <c r="K62">
         <v>50</v>
@@ -21987,7 +21987,7 @@
         <v>2022</v>
       </c>
       <c r="F63">
-        <v>0.18872753377680451</v>
+        <v>0.18629233979258764</v>
       </c>
       <c r="G63">
         <v>0.59739999999999993</v>
@@ -21999,7 +21999,7 @@
         <v>36.300000000000004</v>
       </c>
       <c r="J63">
-        <v>3.4650000000000007</v>
+        <v>3.4650000000000003</v>
       </c>
       <c r="K63">
         <v>50</v>
@@ -22040,7 +22040,7 @@
         <v>2022</v>
       </c>
       <c r="F64">
-        <v>0.29344087509812827</v>
+        <v>0.20236462008841874</v>
       </c>
       <c r="G64">
         <v>0.59739999999999993</v>
@@ -22093,19 +22093,19 @@
         <v>2022</v>
       </c>
       <c r="F65">
-        <v>0.45732943023592104</v>
+        <v>0.22793415692269547</v>
       </c>
       <c r="G65">
-        <v>0.61799999999999999</v>
+        <v>0.59739999999999993</v>
       </c>
       <c r="H65">
-        <v>1100</v>
+        <v>1265</v>
       </c>
       <c r="I65">
-        <v>33</v>
+        <v>36.300000000000004</v>
       </c>
       <c r="J65">
-        <v>3.1500000000000004</v>
+        <v>3.4650000000000003</v>
       </c>
       <c r="K65">
         <v>50</v>
@@ -22146,19 +22146,19 @@
         <v>2022</v>
       </c>
       <c r="F66">
-        <v>0.49339465314217229</v>
+        <v>0.1548783373961905</v>
       </c>
       <c r="G66">
-        <v>0.61799999999999999</v>
+        <v>0.59739999999999993</v>
       </c>
       <c r="H66">
-        <v>1100</v>
+        <v>1265</v>
       </c>
       <c r="I66">
-        <v>33</v>
+        <v>36.300000000000004</v>
       </c>
       <c r="J66">
-        <v>3.1500000000000004</v>
+        <v>3.4649999999999999</v>
       </c>
       <c r="K66">
         <v>50</v>
@@ -22199,7 +22199,7 @@
         <v>2022</v>
       </c>
       <c r="F67">
-        <v>0.39839773581787374</v>
+        <v>0.49339465314217229</v>
       </c>
       <c r="G67">
         <v>0.61799999999999999</v>
@@ -22252,7 +22252,7 @@
         <v>2022</v>
       </c>
       <c r="F68">
-        <v>0.20820908565053911</v>
+        <v>0.27347228442755023</v>
       </c>
       <c r="G68">
         <v>0.59739999999999993</v>
@@ -22264,7 +22264,7 @@
         <v>36.300000000000004</v>
       </c>
       <c r="J68">
-        <v>3.4650000000000007</v>
+        <v>3.4650000000000003</v>
       </c>
       <c r="K68">
         <v>50</v>
@@ -22305,7 +22305,7 @@
         <v>2022</v>
       </c>
       <c r="F69">
-        <v>0.18629233979258764</v>
+        <v>0.17484692806676855</v>
       </c>
       <c r="G69">
         <v>0.59739999999999993</v>
@@ -22358,7 +22358,7 @@
         <v>2022</v>
       </c>
       <c r="F70">
-        <v>0.20236462008841874</v>
+        <v>0.18872753377680451</v>
       </c>
       <c r="G70">
         <v>0.59739999999999993</v>
@@ -22370,7 +22370,7 @@
         <v>36.300000000000004</v>
       </c>
       <c r="J70">
-        <v>3.4650000000000003</v>
+        <v>3.4650000000000007</v>
       </c>
       <c r="K70">
         <v>50</v>
@@ -22411,19 +22411,19 @@
         <v>2022</v>
       </c>
       <c r="F71">
-        <v>0.22793415692269547</v>
+        <v>0.30829555840185086</v>
       </c>
       <c r="G71">
-        <v>0.59739999999999993</v>
+        <v>0.61799999999999999</v>
       </c>
       <c r="H71">
-        <v>1265</v>
+        <v>1100</v>
       </c>
       <c r="I71">
-        <v>36.300000000000004</v>
+        <v>33</v>
       </c>
       <c r="J71">
-        <v>3.4650000000000003</v>
+        <v>3.1500000000000004</v>
       </c>
       <c r="K71">
         <v>50</v>
@@ -22458,13 +22458,13 @@
         <v>49</v>
       </c>
       <c r="D72" t="s">
-        <v>78</v>
+        <v>37</v>
       </c>
       <c r="E72">
         <v>2022</v>
       </c>
       <c r="F72">
-        <v>0.1548783373961905</v>
+        <v>0.27761211420071885</v>
       </c>
       <c r="G72">
         <v>0.59739999999999993</v>
@@ -22476,7 +22476,7 @@
         <v>36.300000000000004</v>
       </c>
       <c r="J72">
-        <v>3.4649999999999999</v>
+        <v>3.4650000000000003</v>
       </c>
       <c r="K72">
         <v>50</v>
@@ -22511,25 +22511,25 @@
         <v>49</v>
       </c>
       <c r="D73" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E73">
         <v>2022</v>
       </c>
       <c r="F73">
-        <v>0.27347228442755023</v>
+        <v>0.3567559186877659</v>
       </c>
       <c r="G73">
-        <v>0.59739999999999993</v>
+        <v>0.61799999999999999</v>
       </c>
       <c r="H73">
-        <v>1265</v>
+        <v>1100</v>
       </c>
       <c r="I73">
-        <v>36.300000000000004</v>
+        <v>33</v>
       </c>
       <c r="J73">
-        <v>3.4650000000000003</v>
+        <v>3.1500000000000004</v>
       </c>
       <c r="K73">
         <v>50</v>
@@ -22564,25 +22564,25 @@
         <v>49</v>
       </c>
       <c r="D74" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E74">
         <v>2022</v>
       </c>
       <c r="F74">
-        <v>0.28443065735652601</v>
+        <v>0.45732943023592104</v>
       </c>
       <c r="G74">
-        <v>0.59739999999999993</v>
+        <v>0.61799999999999999</v>
       </c>
       <c r="H74">
-        <v>1265</v>
+        <v>1100</v>
       </c>
       <c r="I74">
-        <v>36.300000000000004</v>
+        <v>33</v>
       </c>
       <c r="J74">
-        <v>3.4650000000000003</v>
+        <v>3.1500000000000004</v>
       </c>
       <c r="K74">
         <v>50</v>
@@ -22617,13 +22617,13 @@
         <v>49</v>
       </c>
       <c r="D75" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E75">
         <v>2022</v>
       </c>
       <c r="F75">
-        <v>0.19481551873734657</v>
+        <v>0.26604494277568891</v>
       </c>
       <c r="G75">
         <v>0.59739999999999993</v>
@@ -22670,13 +22670,13 @@
         <v>49</v>
       </c>
       <c r="D76" t="s">
-        <v>17</v>
+        <v>81</v>
       </c>
       <c r="E76">
         <v>2022</v>
       </c>
       <c r="F76">
-        <v>0.19822479031525012</v>
+        <v>0.23280454489112914</v>
       </c>
       <c r="G76">
         <v>0.59739999999999993</v>
@@ -22688,7 +22688,7 @@
         <v>36.300000000000004</v>
       </c>
       <c r="J76">
-        <v>3.4650000000000003</v>
+        <v>3.4650000000000007</v>
       </c>
       <c r="K76">
         <v>50</v>
@@ -22729,19 +22729,19 @@
         <v>2022</v>
       </c>
       <c r="F77">
-        <v>0.37112356319464518</v>
+        <v>0.18556178159732259</v>
       </c>
       <c r="G77">
-        <v>0.61799999999999999</v>
+        <v>0.59739999999999993</v>
       </c>
       <c r="H77">
-        <v>1100</v>
+        <v>1265</v>
       </c>
       <c r="I77">
-        <v>33</v>
+        <v>36.300000000000004</v>
       </c>
       <c r="J77">
-        <v>3.1500000000000004</v>
+        <v>3.4650000000000003</v>
       </c>
       <c r="K77">
         <v>50</v>
@@ -22782,7 +22782,7 @@
         <v>2022</v>
       </c>
       <c r="F78">
-        <v>0.20557907614758497</v>
+        <v>0.16608022972358796</v>
       </c>
       <c r="G78">
         <v>0.59739999999999993</v>
@@ -22835,7 +22835,7 @@
         <v>2022</v>
       </c>
       <c r="F79">
-        <v>0.26543614427963469</v>
+        <v>0.19676367392472002</v>
       </c>
       <c r="G79">
         <v>0.59739999999999993</v>
@@ -22888,19 +22888,19 @@
         <v>2022</v>
       </c>
       <c r="F80">
-        <v>0.16608022972358796</v>
+        <v>0.43468212618270452</v>
       </c>
       <c r="G80">
-        <v>0.59739999999999993</v>
+        <v>0.61799999999999988</v>
       </c>
       <c r="H80">
-        <v>1265</v>
+        <v>1100</v>
       </c>
       <c r="I80">
-        <v>36.300000000000004</v>
+        <v>33</v>
       </c>
       <c r="J80">
-        <v>3.4650000000000003</v>
+        <v>3.1500000000000004</v>
       </c>
       <c r="K80">
         <v>50</v>
@@ -22941,7 +22941,7 @@
         <v>2022</v>
       </c>
       <c r="F81">
-        <v>0.20212110068999706</v>
+        <v>0.18507474280047922</v>
       </c>
       <c r="G81">
         <v>0.59739999999999993</v>
@@ -22953,7 +22953,7 @@
         <v>36.300000000000004</v>
       </c>
       <c r="J81">
-        <v>3.4650000000000003</v>
+        <v>3.4649999999999999</v>
       </c>
       <c r="K81">
         <v>50</v>
@@ -22994,7 +22994,7 @@
         <v>2022</v>
       </c>
       <c r="F82">
-        <v>0.18507474280047922</v>
+        <v>0.19627663512787666</v>
       </c>
       <c r="G82">
         <v>0.59739999999999993</v>
@@ -23041,7 +23041,7 @@
         <v>49</v>
       </c>
       <c r="D83" t="s">
-        <v>50</v>
+        <v>84</v>
       </c>
       <c r="E83">
         <v>2006</v>
@@ -23094,7 +23094,7 @@
         <v>49</v>
       </c>
       <c r="D84" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="E84">
         <v>2012</v>
@@ -23147,7 +23147,7 @@
         <v>49</v>
       </c>
       <c r="D85" t="s">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="E85">
         <v>1993</v>
@@ -23200,7 +23200,7 @@
         <v>49</v>
       </c>
       <c r="D86" t="s">
-        <v>81</v>
+        <v>67</v>
       </c>
       <c r="E86">
         <v>2011</v>
@@ -23253,7 +23253,7 @@
         <v>49</v>
       </c>
       <c r="D87" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E87">
         <v>2005</v>
@@ -23306,7 +23306,7 @@
         <v>49</v>
       </c>
       <c r="D88" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E88">
         <v>2006</v>
@@ -23359,7 +23359,7 @@
         <v>49</v>
       </c>
       <c r="D89" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E89">
         <v>2006</v>
@@ -23465,7 +23465,7 @@
         <v>49</v>
       </c>
       <c r="D91" t="s">
-        <v>59</v>
+        <v>81</v>
       </c>
       <c r="E91">
         <v>2003</v>
@@ -23624,7 +23624,7 @@
         <v>49</v>
       </c>
       <c r="D94" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="E94">
         <v>2004</v>
@@ -23677,7 +23677,7 @@
         <v>49</v>
       </c>
       <c r="D95" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="E95">
         <v>2005</v>
@@ -23730,7 +23730,7 @@
         <v>49</v>
       </c>
       <c r="D96" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="E96">
         <v>2005</v>
@@ -23783,7 +23783,7 @@
         <v>49</v>
       </c>
       <c r="D97" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="E97">
         <v>2005</v>
@@ -23836,7 +23836,7 @@
         <v>49</v>
       </c>
       <c r="D98" t="s">
-        <v>52</v>
+        <v>77</v>
       </c>
       <c r="E98">
         <v>2004</v>
@@ -23889,7 +23889,7 @@
         <v>49</v>
       </c>
       <c r="D99" t="s">
-        <v>52</v>
+        <v>77</v>
       </c>
       <c r="E99">
         <v>2004</v>
@@ -23942,7 +23942,7 @@
         <v>49</v>
       </c>
       <c r="D100" t="s">
-        <v>52</v>
+        <v>77</v>
       </c>
       <c r="E100">
         <v>2004</v>
@@ -23995,7 +23995,7 @@
         <v>49</v>
       </c>
       <c r="D101" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E101">
         <v>2008</v>
@@ -24048,7 +24048,7 @@
         <v>49</v>
       </c>
       <c r="D102" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E102">
         <v>2008</v>
@@ -24101,7 +24101,7 @@
         <v>49</v>
       </c>
       <c r="D103" t="s">
-        <v>82</v>
+        <v>53</v>
       </c>
       <c r="E103">
         <v>2002</v>
@@ -24154,7 +24154,7 @@
         <v>49</v>
       </c>
       <c r="D104" t="s">
-        <v>82</v>
+        <v>53</v>
       </c>
       <c r="E104">
         <v>2002</v>
@@ -24207,7 +24207,7 @@
         <v>49</v>
       </c>
       <c r="D105" t="s">
-        <v>82</v>
+        <v>53</v>
       </c>
       <c r="E105">
         <v>2003</v>
@@ -24260,7 +24260,7 @@
         <v>49</v>
       </c>
       <c r="D106" t="s">
-        <v>82</v>
+        <v>53</v>
       </c>
       <c r="E106">
         <v>2003</v>
@@ -24313,7 +24313,7 @@
         <v>49</v>
       </c>
       <c r="D107" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E107">
         <v>2000</v>
@@ -24366,7 +24366,7 @@
         <v>49</v>
       </c>
       <c r="D108" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E108">
         <v>2000</v>
@@ -24419,7 +24419,7 @@
         <v>49</v>
       </c>
       <c r="D109" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="E109">
         <v>2007</v>
@@ -24472,7 +24472,7 @@
         <v>49</v>
       </c>
       <c r="D110" t="s">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="E110">
         <v>2023</v>
@@ -24525,7 +24525,7 @@
         <v>49</v>
       </c>
       <c r="D111" t="s">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="E111">
         <v>2001</v>
@@ -24631,7 +24631,7 @@
         <v>49</v>
       </c>
       <c r="D113" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="E113">
         <v>2010</v>
@@ -24684,7 +24684,7 @@
         <v>49</v>
       </c>
       <c r="D114" t="s">
-        <v>86</v>
+        <v>63</v>
       </c>
       <c r="E114">
         <v>2005</v>
@@ -24737,7 +24737,7 @@
         <v>49</v>
       </c>
       <c r="D115" t="s">
-        <v>86</v>
+        <v>63</v>
       </c>
       <c r="E115">
         <v>2009</v>
@@ -24790,7 +24790,7 @@
         <v>49</v>
       </c>
       <c r="D116" t="s">
-        <v>84</v>
+        <v>55</v>
       </c>
       <c r="E116">
         <v>1997</v>
@@ -24843,7 +24843,7 @@
         <v>49</v>
       </c>
       <c r="D117" t="s">
-        <v>84</v>
+        <v>55</v>
       </c>
       <c r="E117">
         <v>1997</v>
@@ -24896,7 +24896,7 @@
         <v>49</v>
       </c>
       <c r="D118" t="s">
-        <v>84</v>
+        <v>55</v>
       </c>
       <c r="E118">
         <v>1998</v>
@@ -24949,7 +24949,7 @@
         <v>49</v>
       </c>
       <c r="D119" t="s">
-        <v>84</v>
+        <v>55</v>
       </c>
       <c r="E119">
         <v>1999</v>
@@ -25055,7 +25055,7 @@
         <v>49</v>
       </c>
       <c r="D121" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="E121">
         <v>2010</v>
@@ -25108,7 +25108,7 @@
         <v>49</v>
       </c>
       <c r="D122" t="s">
-        <v>80</v>
+        <v>61</v>
       </c>
       <c r="E122">
         <v>2003</v>
@@ -25161,7 +25161,7 @@
         <v>49</v>
       </c>
       <c r="D123" t="s">
-        <v>80</v>
+        <v>61</v>
       </c>
       <c r="E123">
         <v>2003</v>
@@ -25214,7 +25214,7 @@
         <v>49</v>
       </c>
       <c r="D124" t="s">
-        <v>62</v>
+        <v>87</v>
       </c>
       <c r="E124">
         <v>2006</v>
@@ -25373,7 +25373,7 @@
         <v>49</v>
       </c>
       <c r="D127" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="E127">
         <v>2002</v>
@@ -25426,7 +25426,7 @@
         <v>49</v>
       </c>
       <c r="D128" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="E128">
         <v>2002</v>
@@ -25479,7 +25479,7 @@
         <v>49</v>
       </c>
       <c r="D129" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="E129">
         <v>2010</v>
@@ -25532,7 +25532,7 @@
         <v>49</v>
       </c>
       <c r="D130" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="E130">
         <v>2010</v>
@@ -25585,7 +25585,7 @@
         <v>49</v>
       </c>
       <c r="D131" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="E131">
         <v>2008</v>
@@ -25638,7 +25638,7 @@
         <v>49</v>
       </c>
       <c r="D132" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="E132">
         <v>2008</v>
@@ -25691,7 +25691,7 @@
         <v>49</v>
       </c>
       <c r="D133" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="E133">
         <v>2018</v>
@@ -25744,7 +25744,7 @@
         <v>49</v>
       </c>
       <c r="D134" t="s">
-        <v>58</v>
+        <v>82</v>
       </c>
       <c r="E134">
         <v>2006</v>
@@ -25797,7 +25797,7 @@
         <v>49</v>
       </c>
       <c r="D135" t="s">
-        <v>58</v>
+        <v>82</v>
       </c>
       <c r="E135">
         <v>2007</v>
@@ -25956,7 +25956,7 @@
         <v>49</v>
       </c>
       <c r="D138" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E138">
         <v>2010</v>
@@ -26009,7 +26009,7 @@
         <v>49</v>
       </c>
       <c r="D139" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E139">
         <v>2010</v>
@@ -26062,7 +26062,7 @@
         <v>49</v>
       </c>
       <c r="D140" t="s">
-        <v>70</v>
+        <v>52</v>
       </c>
       <c r="E140">
         <v>2004</v>
@@ -26115,7 +26115,7 @@
         <v>49</v>
       </c>
       <c r="D141" t="s">
-        <v>70</v>
+        <v>52</v>
       </c>
       <c r="E141">
         <v>2004</v>
@@ -26168,7 +26168,7 @@
         <v>49</v>
       </c>
       <c r="D142" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E142">
         <v>2008</v>
@@ -26221,7 +26221,7 @@
         <v>49</v>
       </c>
       <c r="D143" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E143">
         <v>2007</v>
@@ -26274,7 +26274,7 @@
         <v>49</v>
       </c>
       <c r="D144" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E144">
         <v>2007</v>
@@ -26327,7 +26327,7 @@
         <v>49</v>
       </c>
       <c r="D145" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E145">
         <v>2005</v>
@@ -26380,7 +26380,7 @@
         <v>49</v>
       </c>
       <c r="D146" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E146">
         <v>2005</v>
@@ -26433,7 +26433,7 @@
         <v>49</v>
       </c>
       <c r="D147" t="s">
-        <v>73</v>
+        <v>62</v>
       </c>
       <c r="E147">
         <v>2015</v>
@@ -26486,7 +26486,7 @@
         <v>49</v>
       </c>
       <c r="D148" t="s">
-        <v>73</v>
+        <v>62</v>
       </c>
       <c r="E148">
         <v>2004</v>
@@ -26539,7 +26539,7 @@
         <v>49</v>
       </c>
       <c r="D149" t="s">
-        <v>83</v>
+        <v>54</v>
       </c>
       <c r="E149">
         <v>2006</v>
@@ -26592,7 +26592,7 @@
         <v>49</v>
       </c>
       <c r="D150" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="E150">
         <v>2011</v>
@@ -26645,7 +26645,7 @@
         <v>49</v>
       </c>
       <c r="D151" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E151">
         <v>2004</v>
@@ -26698,7 +26698,7 @@
         <v>49</v>
       </c>
       <c r="D152" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E152">
         <v>2005</v>
@@ -26751,7 +26751,7 @@
         <v>49</v>
       </c>
       <c r="D153" t="s">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="E153">
         <v>2006</v>
@@ -26804,7 +26804,7 @@
         <v>49</v>
       </c>
       <c r="D154" t="s">
-        <v>51</v>
+        <v>78</v>
       </c>
       <c r="E154">
         <v>2008</v>
@@ -26857,7 +26857,7 @@
         <v>49</v>
       </c>
       <c r="D155" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="E155">
         <v>2007</v>
@@ -26963,7 +26963,7 @@
         <v>49</v>
       </c>
       <c r="D157" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="E157">
         <v>2023</v>
@@ -27016,7 +27016,7 @@
         <v>49</v>
       </c>
       <c r="D158" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E158">
         <v>2026</v>
@@ -27069,7 +27069,7 @@
         <v>49</v>
       </c>
       <c r="D159" t="s">
-        <v>51</v>
+        <v>78</v>
       </c>
       <c r="E159">
         <v>2022</v>
@@ -27122,7 +27122,7 @@
         <v>49</v>
       </c>
       <c r="D160" t="s">
-        <v>64</v>
+        <v>50</v>
       </c>
       <c r="E160">
         <v>2003</v>
@@ -27175,7 +27175,7 @@
         <v>49</v>
       </c>
       <c r="D161" t="s">
-        <v>64</v>
+        <v>50</v>
       </c>
       <c r="E161">
         <v>2003</v>
@@ -27228,7 +27228,7 @@
         <v>49</v>
       </c>
       <c r="D162" t="s">
-        <v>80</v>
+        <v>61</v>
       </c>
       <c r="E162">
         <v>2003</v>
@@ -27281,7 +27281,7 @@
         <v>49</v>
       </c>
       <c r="D163" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="E163">
         <v>2008</v>
@@ -27334,7 +27334,7 @@
         <v>49</v>
       </c>
       <c r="D164" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="E164">
         <v>1999</v>
@@ -27387,7 +27387,7 @@
         <v>49</v>
       </c>
       <c r="D165" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="E165">
         <v>1999</v>
@@ -27440,7 +27440,7 @@
         <v>49</v>
       </c>
       <c r="D166" t="s">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="E166">
         <v>1997</v>
@@ -27546,7 +27546,7 @@
         <v>49</v>
       </c>
       <c r="D168" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="E168">
         <v>2001</v>
@@ -27599,7 +27599,7 @@
         <v>49</v>
       </c>
       <c r="D169" t="s">
-        <v>52</v>
+        <v>77</v>
       </c>
       <c r="E169">
         <v>2006</v>
@@ -27705,7 +27705,7 @@
         <v>49</v>
       </c>
       <c r="D171" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="E171">
         <v>2007</v>
@@ -28288,7 +28288,7 @@
         <v>49</v>
       </c>
       <c r="D182" t="s">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="E182">
         <v>2015</v>
@@ -29083,7 +29083,7 @@
         <v>49</v>
       </c>
       <c r="D197" t="s">
-        <v>51</v>
+        <v>78</v>
       </c>
       <c r="E197">
         <v>2004</v>
@@ -29136,7 +29136,7 @@
         <v>49</v>
       </c>
       <c r="D198" t="s">
-        <v>51</v>
+        <v>78</v>
       </c>
       <c r="E198">
         <v>2008</v>
@@ -29348,7 +29348,7 @@
         <v>49</v>
       </c>
       <c r="D202" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="E202">
         <v>2005</v>
@@ -29401,7 +29401,7 @@
         <v>49</v>
       </c>
       <c r="D203" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="E203">
         <v>2015</v>
@@ -30090,7 +30090,7 @@
         <v>49</v>
       </c>
       <c r="D216" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E216">
         <v>2022</v>
@@ -30302,7 +30302,7 @@
         <v>49</v>
       </c>
       <c r="D220" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E220">
         <v>2009</v>
@@ -30991,7 +30991,7 @@
         <v>49</v>
       </c>
       <c r="D233" t="s">
-        <v>70</v>
+        <v>52</v>
       </c>
       <c r="E233">
         <v>1994</v>
@@ -31150,7 +31150,7 @@
         <v>49</v>
       </c>
       <c r="D236" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E236">
         <v>1990</v>
@@ -31203,7 +31203,7 @@
         <v>49</v>
       </c>
       <c r="D237" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E237">
         <v>2022</v>
@@ -31362,7 +31362,7 @@
         <v>49</v>
       </c>
       <c r="D240" t="s">
-        <v>86</v>
+        <v>63</v>
       </c>
       <c r="E240">
         <v>2006</v>
@@ -31415,7 +31415,7 @@
         <v>49</v>
       </c>
       <c r="D241" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E241">
         <v>2024</v>
@@ -31468,7 +31468,7 @@
         <v>49</v>
       </c>
       <c r="D242" t="s">
-        <v>73</v>
+        <v>62</v>
       </c>
       <c r="E242">
         <v>2023</v>
@@ -31521,7 +31521,7 @@
         <v>49</v>
       </c>
       <c r="D243" t="s">
-        <v>73</v>
+        <v>62</v>
       </c>
       <c r="E243">
         <v>2023</v>
@@ -31574,7 +31574,7 @@
         <v>49</v>
       </c>
       <c r="D244" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="E244">
         <v>1997</v>
@@ -32051,7 +32051,7 @@
         <v>49</v>
       </c>
       <c r="D253" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E253">
         <v>2008</v>
@@ -32316,7 +32316,7 @@
         <v>49</v>
       </c>
       <c r="D258" t="s">
-        <v>73</v>
+        <v>62</v>
       </c>
       <c r="E258">
         <v>2015</v>
@@ -32422,7 +32422,7 @@
         <v>49</v>
       </c>
       <c r="D260" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="E260">
         <v>2004</v>
@@ -32687,7 +32687,7 @@
         <v>49</v>
       </c>
       <c r="D265" t="s">
-        <v>59</v>
+        <v>81</v>
       </c>
       <c r="E265">
         <v>2024</v>
@@ -32793,7 +32793,7 @@
         <v>49</v>
       </c>
       <c r="D267" t="s">
-        <v>83</v>
+        <v>54</v>
       </c>
       <c r="E267">
         <v>2023</v>
@@ -33005,7 +33005,7 @@
         <v>49</v>
       </c>
       <c r="D271" t="s">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="E271">
         <v>1975</v>
@@ -33058,7 +33058,7 @@
         <v>49</v>
       </c>
       <c r="D272" t="s">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="E272">
         <v>1975</v>
@@ -33111,7 +33111,7 @@
         <v>49</v>
       </c>
       <c r="D273" t="s">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="E273">
         <v>1975</v>
@@ -33164,7 +33164,7 @@
         <v>49</v>
       </c>
       <c r="D274" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="E274">
         <v>2015</v>
@@ -33217,7 +33217,7 @@
         <v>49</v>
       </c>
       <c r="D275" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E275">
         <v>1967</v>
@@ -33270,7 +33270,7 @@
         <v>49</v>
       </c>
       <c r="D276" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E276">
         <v>1971</v>
@@ -33323,7 +33323,7 @@
         <v>49</v>
       </c>
       <c r="D277" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="E277">
         <v>1970</v>
@@ -33376,7 +33376,7 @@
         <v>49</v>
       </c>
       <c r="D278" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E278">
         <v>1978</v>
@@ -33429,7 +33429,7 @@
         <v>49</v>
       </c>
       <c r="D279" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E279">
         <v>1981</v>
@@ -33482,7 +33482,7 @@
         <v>49</v>
       </c>
       <c r="D280" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E280">
         <v>1987</v>
@@ -33906,7 +33906,7 @@
         <v>293</v>
       </c>
       <c r="D288" t="s">
-        <v>84</v>
+        <v>55</v>
       </c>
       <c r="E288">
         <v>1991</v>
@@ -33959,7 +33959,7 @@
         <v>293</v>
       </c>
       <c r="D289" t="s">
-        <v>84</v>
+        <v>55</v>
       </c>
       <c r="E289">
         <v>1991</v>
@@ -35025,7 +35025,7 @@
         <v>2022</v>
       </c>
       <c r="F309">
-        <v>6.3558189950902247E-2</v>
+        <v>5.1032123318242681E-2</v>
       </c>
       <c r="G309">
         <v>1</v>
@@ -35034,7 +35034,7 @@
         <v>3162.5000000000005</v>
       </c>
       <c r="I309">
-        <v>60.500000000000014</v>
+        <v>60.500000000000021</v>
       </c>
       <c r="J309">
         <v>2.3100000000000005</v>
@@ -35072,25 +35072,25 @@
         <v>308</v>
       </c>
       <c r="D310" t="s">
-        <v>310</v>
+        <v>69</v>
       </c>
       <c r="E310">
         <v>2022</v>
       </c>
       <c r="F310">
-        <v>0.10670353057450742</v>
+        <v>0.50939337639482241</v>
       </c>
       <c r="G310">
         <v>1</v>
       </c>
       <c r="H310">
-        <v>3162.5000000000005</v>
+        <v>2750</v>
       </c>
       <c r="I310">
-        <v>60.500000000000014</v>
+        <v>55.000000000000007</v>
       </c>
       <c r="J310">
-        <v>2.3100000000000005</v>
+        <v>2.1</v>
       </c>
       <c r="K310">
         <v>100</v>
@@ -35125,25 +35125,25 @@
         <v>308</v>
       </c>
       <c r="D311" t="s">
-        <v>311</v>
+        <v>204</v>
       </c>
       <c r="E311">
         <v>2022</v>
       </c>
       <c r="F311">
-        <v>4.1753555442198553E-2</v>
+        <v>7.8403898552572848E-2</v>
       </c>
       <c r="G311">
         <v>1</v>
       </c>
       <c r="H311">
-        <v>3712.5000000000005</v>
+        <v>3162.5000000000005</v>
       </c>
       <c r="I311">
-        <v>71.5</v>
+        <v>60.500000000000014</v>
       </c>
       <c r="J311">
-        <v>2.52</v>
+        <v>2.3100000000000005</v>
       </c>
       <c r="K311">
         <v>100</v>
@@ -35178,25 +35178,25 @@
         <v>308</v>
       </c>
       <c r="D312" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="E312">
         <v>2022</v>
       </c>
       <c r="F312">
-        <v>0.35629700644009438</v>
+        <v>0.19299421182171778</v>
       </c>
       <c r="G312">
         <v>1</v>
       </c>
       <c r="H312">
-        <v>2750</v>
+        <v>3162.5000000000005</v>
       </c>
       <c r="I312">
-        <v>55</v>
+        <v>60.500000000000014</v>
       </c>
       <c r="J312">
-        <v>2.1</v>
+        <v>2.3100000000000005</v>
       </c>
       <c r="K312">
         <v>100</v>
@@ -35231,13 +35231,13 @@
         <v>308</v>
       </c>
       <c r="D313" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="E313">
         <v>2022</v>
       </c>
       <c r="F313">
-        <v>0.13036387865841995</v>
+        <v>5.8918906012880183E-2</v>
       </c>
       <c r="G313">
         <v>1</v>
@@ -35246,7 +35246,7 @@
         <v>3162.5000000000005</v>
       </c>
       <c r="I313">
-        <v>60.500000000000014</v>
+        <v>60.500000000000021</v>
       </c>
       <c r="J313">
         <v>2.3100000000000005</v>
@@ -35284,25 +35284,25 @@
         <v>308</v>
       </c>
       <c r="D314" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="E314">
         <v>2022</v>
       </c>
       <c r="F314">
-        <v>0.19299421182171778</v>
+        <v>0.35629700644009438</v>
       </c>
       <c r="G314">
         <v>1</v>
       </c>
       <c r="H314">
-        <v>3162.5000000000005</v>
+        <v>2750</v>
       </c>
       <c r="I314">
-        <v>60.500000000000014</v>
+        <v>55</v>
       </c>
       <c r="J314">
-        <v>2.3100000000000005</v>
+        <v>2.1</v>
       </c>
       <c r="K314">
         <v>100</v>
@@ -35337,25 +35337,25 @@
         <v>308</v>
       </c>
       <c r="D315" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="E315">
         <v>2022</v>
       </c>
       <c r="F315">
-        <v>6.0310691194286808E-2</v>
+        <v>0.54140443556717466</v>
       </c>
       <c r="G315">
         <v>1</v>
       </c>
       <c r="H315">
-        <v>3162.5000000000005</v>
+        <v>2750</v>
       </c>
       <c r="I315">
-        <v>60.500000000000014</v>
+        <v>55.000000000000007</v>
       </c>
       <c r="J315">
-        <v>2.3100000000000005</v>
+        <v>2.1</v>
       </c>
       <c r="K315">
         <v>100</v>
@@ -35390,13 +35390,13 @@
         <v>308</v>
       </c>
       <c r="D316" t="s">
-        <v>239</v>
+        <v>291</v>
       </c>
       <c r="E316">
         <v>2022</v>
       </c>
       <c r="F316">
-        <v>0.22871669814448767</v>
+        <v>0.13082780705222213</v>
       </c>
       <c r="G316">
         <v>1</v>
@@ -35443,13 +35443,13 @@
         <v>308</v>
       </c>
       <c r="D317" t="s">
-        <v>204</v>
+        <v>79</v>
       </c>
       <c r="E317">
         <v>2022</v>
       </c>
       <c r="F317">
-        <v>7.8403898552572848E-2</v>
+        <v>0.23196419690110309</v>
       </c>
       <c r="G317">
         <v>1</v>
@@ -35496,25 +35496,25 @@
         <v>308</v>
       </c>
       <c r="D318" t="s">
-        <v>193</v>
+        <v>314</v>
       </c>
       <c r="E318">
         <v>2022</v>
       </c>
       <c r="F318">
-        <v>0.61052976624370348</v>
+        <v>0.13036387865841995</v>
       </c>
       <c r="G318">
         <v>1</v>
       </c>
       <c r="H318">
-        <v>2750</v>
+        <v>3162.5000000000005</v>
       </c>
       <c r="I318">
-        <v>55.000000000000007</v>
+        <v>60.500000000000014</v>
       </c>
       <c r="J318">
-        <v>2.1</v>
+        <v>2.3100000000000005</v>
       </c>
       <c r="K318">
         <v>100</v>
@@ -35549,25 +35549,25 @@
         <v>308</v>
       </c>
       <c r="D319" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="E319">
         <v>2022</v>
       </c>
       <c r="F319">
-        <v>4.3145340623605172E-2</v>
+        <v>0.10670353057450742</v>
       </c>
       <c r="G319">
         <v>1</v>
       </c>
       <c r="H319">
-        <v>3712.5000000000005</v>
+        <v>3162.5000000000005</v>
       </c>
       <c r="I319">
-        <v>71.5</v>
+        <v>60.500000000000014</v>
       </c>
       <c r="J319">
-        <v>2.52</v>
+        <v>2.3100000000000005</v>
       </c>
       <c r="K319">
         <v>100</v>
@@ -35602,13 +35602,13 @@
         <v>308</v>
       </c>
       <c r="D320" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="E320">
         <v>2022</v>
       </c>
       <c r="F320">
-        <v>5.8918906012880183E-2</v>
+        <v>6.0310691194286808E-2</v>
       </c>
       <c r="G320">
         <v>1</v>
@@ -35617,7 +35617,7 @@
         <v>3162.5000000000005</v>
       </c>
       <c r="I320">
-        <v>60.500000000000021</v>
+        <v>60.500000000000014</v>
       </c>
       <c r="J320">
         <v>2.3100000000000005</v>
@@ -35655,13 +35655,13 @@
         <v>308</v>
       </c>
       <c r="D321" t="s">
-        <v>16</v>
+        <v>64</v>
       </c>
       <c r="E321">
         <v>2022</v>
       </c>
       <c r="F321">
-        <v>8.7682466428616976E-2</v>
+        <v>5.4743550468660328E-2</v>
       </c>
       <c r="G321">
         <v>1</v>
@@ -35670,7 +35670,7 @@
         <v>3162.5000000000005</v>
       </c>
       <c r="I321">
-        <v>60.500000000000007</v>
+        <v>60.500000000000014</v>
       </c>
       <c r="J321">
         <v>2.3100000000000005</v>
@@ -35708,13 +35708,13 @@
         <v>308</v>
       </c>
       <c r="D322" t="s">
-        <v>318</v>
+        <v>239</v>
       </c>
       <c r="E322">
         <v>2022</v>
       </c>
       <c r="F322">
-        <v>5.1032123318242681E-2</v>
+        <v>0.22871669814448767</v>
       </c>
       <c r="G322">
         <v>1</v>
@@ -35723,7 +35723,7 @@
         <v>3162.5000000000005</v>
       </c>
       <c r="I322">
-        <v>60.500000000000021</v>
+        <v>60.500000000000014</v>
       </c>
       <c r="J322">
         <v>2.3100000000000005</v>
@@ -35761,25 +35761,25 @@
         <v>308</v>
       </c>
       <c r="D323" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="E323">
         <v>2022</v>
       </c>
       <c r="F323">
-        <v>0.54140443556717466</v>
+        <v>4.3145340623605172E-2</v>
       </c>
       <c r="G323">
         <v>1</v>
       </c>
       <c r="H323">
-        <v>2750</v>
+        <v>3712.5000000000005</v>
       </c>
       <c r="I323">
-        <v>55.000000000000007</v>
+        <v>71.5</v>
       </c>
       <c r="J323">
-        <v>2.1</v>
+        <v>2.52</v>
       </c>
       <c r="K323">
         <v>100</v>
@@ -35814,25 +35814,25 @@
         <v>308</v>
       </c>
       <c r="D324" t="s">
-        <v>99</v>
+        <v>318</v>
       </c>
       <c r="E324">
         <v>2022</v>
       </c>
       <c r="F324">
-        <v>0.29181095970158766</v>
+        <v>1.0883760118599757</v>
       </c>
       <c r="G324">
         <v>1</v>
       </c>
       <c r="H324">
-        <v>3162.5000000000005</v>
+        <v>2750</v>
       </c>
       <c r="I324">
-        <v>60.500000000000014</v>
+        <v>55.000000000000007</v>
       </c>
       <c r="J324">
-        <v>2.3100000000000005</v>
+        <v>2.1</v>
       </c>
       <c r="K324">
         <v>100</v>
@@ -35867,25 +35867,25 @@
         <v>308</v>
       </c>
       <c r="D325" t="s">
-        <v>63</v>
+        <v>151</v>
       </c>
       <c r="E325">
         <v>2022</v>
       </c>
       <c r="F325">
-        <v>5.4743550468660328E-2</v>
+        <v>4.5464982592616207E-2</v>
       </c>
       <c r="G325">
         <v>1</v>
       </c>
       <c r="H325">
-        <v>3162.5000000000005</v>
+        <v>3712.5000000000005</v>
       </c>
       <c r="I325">
-        <v>60.500000000000014</v>
+        <v>71.5</v>
       </c>
       <c r="J325">
-        <v>2.3100000000000005</v>
+        <v>2.52</v>
       </c>
       <c r="K325">
         <v>100</v>
@@ -35920,13 +35920,13 @@
         <v>308</v>
       </c>
       <c r="D326" t="s">
-        <v>320</v>
+        <v>20</v>
       </c>
       <c r="E326">
         <v>2022</v>
       </c>
       <c r="F326">
-        <v>0.15541601192373908</v>
+        <v>8.7682466428616976E-2</v>
       </c>
       <c r="G326">
         <v>1</v>
@@ -35935,7 +35935,7 @@
         <v>3162.5000000000005</v>
       </c>
       <c r="I326">
-        <v>60.500000000000014</v>
+        <v>60.500000000000007</v>
       </c>
       <c r="J326">
         <v>2.3100000000000005</v>
@@ -35973,25 +35973,25 @@
         <v>308</v>
       </c>
       <c r="D327" t="s">
-        <v>71</v>
+        <v>319</v>
       </c>
       <c r="E327">
         <v>2022</v>
       </c>
       <c r="F327">
-        <v>0.23196419690110309</v>
+        <v>4.1753555442198553E-2</v>
       </c>
       <c r="G327">
         <v>1</v>
       </c>
       <c r="H327">
-        <v>3162.5000000000005</v>
+        <v>3712.5000000000005</v>
       </c>
       <c r="I327">
-        <v>60.500000000000014</v>
+        <v>71.5</v>
       </c>
       <c r="J327">
-        <v>2.3100000000000005</v>
+        <v>2.52</v>
       </c>
       <c r="K327">
         <v>100</v>
@@ -36026,25 +36026,25 @@
         <v>308</v>
       </c>
       <c r="D328" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="E328">
         <v>2022</v>
       </c>
       <c r="F328">
-        <v>0.1577356538927501</v>
+        <v>0.57944656385895543</v>
       </c>
       <c r="G328">
         <v>1</v>
       </c>
       <c r="H328">
-        <v>3162.5000000000005</v>
+        <v>2750</v>
       </c>
       <c r="I328">
-        <v>60.500000000000014</v>
+        <v>55.000000000000007</v>
       </c>
       <c r="J328">
-        <v>2.3100000000000005</v>
+        <v>2.1</v>
       </c>
       <c r="K328">
         <v>100</v>
@@ -36079,25 +36079,25 @@
         <v>308</v>
       </c>
       <c r="D329" t="s">
-        <v>14</v>
+        <v>321</v>
       </c>
       <c r="E329">
         <v>2022</v>
       </c>
       <c r="F329">
-        <v>0.11134281451252948</v>
+        <v>4.4073197411209589E-2</v>
       </c>
       <c r="G329">
         <v>1</v>
       </c>
       <c r="H329">
-        <v>3162.5000000000005</v>
+        <v>3712.5000000000005</v>
       </c>
       <c r="I329">
-        <v>60.500000000000014</v>
+        <v>71.5</v>
       </c>
       <c r="J329">
-        <v>2.3100000000000005</v>
+        <v>2.52</v>
       </c>
       <c r="K329">
         <v>100</v>
@@ -36132,25 +36132,25 @@
         <v>308</v>
       </c>
       <c r="D330" t="s">
-        <v>322</v>
+        <v>99</v>
       </c>
       <c r="E330">
         <v>2022</v>
       </c>
       <c r="F330">
-        <v>1.0883760118599757</v>
+        <v>0.29181095970158766</v>
       </c>
       <c r="G330">
         <v>1</v>
       </c>
       <c r="H330">
-        <v>2750</v>
+        <v>3162.5000000000005</v>
       </c>
       <c r="I330">
-        <v>55.000000000000007</v>
+        <v>60.500000000000014</v>
       </c>
       <c r="J330">
-        <v>2.1</v>
+        <v>2.3100000000000005</v>
       </c>
       <c r="K330">
         <v>100</v>
@@ -36185,25 +36185,25 @@
         <v>308</v>
       </c>
       <c r="D331" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="E331">
         <v>2022</v>
       </c>
       <c r="F331">
-        <v>0.10067246145507874</v>
+        <v>0.56367299846968055</v>
       </c>
       <c r="G331">
         <v>1</v>
       </c>
       <c r="H331">
-        <v>3162.5000000000005</v>
+        <v>2750</v>
       </c>
       <c r="I331">
-        <v>60.500000000000014</v>
+        <v>55.000000000000007</v>
       </c>
       <c r="J331">
-        <v>2.3100000000000005</v>
+        <v>2.1</v>
       </c>
       <c r="K331">
         <v>100</v>
@@ -36238,25 +36238,25 @@
         <v>308</v>
       </c>
       <c r="D332" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="E332">
         <v>2022</v>
       </c>
       <c r="F332">
-        <v>4.4073197411209589E-2</v>
+        <v>0.10067246145507874</v>
       </c>
       <c r="G332">
         <v>1</v>
       </c>
       <c r="H332">
-        <v>3712.5000000000005</v>
+        <v>3162.5000000000005</v>
       </c>
       <c r="I332">
-        <v>71.5</v>
+        <v>60.500000000000014</v>
       </c>
       <c r="J332">
-        <v>2.52</v>
+        <v>2.3100000000000005</v>
       </c>
       <c r="K332">
         <v>100</v>
@@ -36291,25 +36291,25 @@
         <v>308</v>
       </c>
       <c r="D333" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="E333">
         <v>2022</v>
       </c>
       <c r="F333">
-        <v>6.9589259070330922E-2</v>
+        <v>4.4073197411209589E-2</v>
       </c>
       <c r="G333">
         <v>1</v>
       </c>
       <c r="H333">
-        <v>3162.5000000000005</v>
+        <v>3712.5000000000005</v>
       </c>
       <c r="I333">
-        <v>60.500000000000007</v>
+        <v>71.5</v>
       </c>
       <c r="J333">
-        <v>2.3100000000000005</v>
+        <v>2.52</v>
       </c>
       <c r="K333">
         <v>100</v>
@@ -36344,13 +36344,13 @@
         <v>308</v>
       </c>
       <c r="D334" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="E334">
         <v>2022</v>
       </c>
       <c r="F334">
-        <v>0.20320063648536632</v>
+        <v>0.15541601192373908</v>
       </c>
       <c r="G334">
         <v>1</v>
@@ -36397,25 +36397,25 @@
         <v>308</v>
       </c>
       <c r="D335" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="E335">
         <v>2022</v>
       </c>
       <c r="F335">
-        <v>0.56367299846968055</v>
+        <v>6.3558189950902247E-2</v>
       </c>
       <c r="G335">
         <v>1</v>
       </c>
       <c r="H335">
-        <v>2750</v>
+        <v>3162.5000000000005</v>
       </c>
       <c r="I335">
-        <v>55.000000000000007</v>
+        <v>60.500000000000014</v>
       </c>
       <c r="J335">
-        <v>2.1</v>
+        <v>2.3100000000000005</v>
       </c>
       <c r="K335">
         <v>100</v>
@@ -36450,25 +36450,25 @@
         <v>308</v>
       </c>
       <c r="D336" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="E336">
         <v>2022</v>
       </c>
       <c r="F336">
-        <v>0.57944656385895543</v>
+        <v>0.1577356538927501</v>
       </c>
       <c r="G336">
         <v>1</v>
       </c>
       <c r="H336">
-        <v>2750</v>
+        <v>3162.5000000000005</v>
       </c>
       <c r="I336">
-        <v>55.000000000000007</v>
+        <v>60.500000000000014</v>
       </c>
       <c r="J336">
-        <v>2.1</v>
+        <v>2.3100000000000005</v>
       </c>
       <c r="K336">
         <v>100</v>
@@ -36503,25 +36503,25 @@
         <v>308</v>
       </c>
       <c r="D337" t="s">
-        <v>151</v>
+        <v>328</v>
       </c>
       <c r="E337">
         <v>2022</v>
       </c>
       <c r="F337">
-        <v>4.5464982592616207E-2</v>
+        <v>0.20320063648536632</v>
       </c>
       <c r="G337">
         <v>1</v>
       </c>
       <c r="H337">
-        <v>3712.5000000000005</v>
+        <v>3162.5000000000005</v>
       </c>
       <c r="I337">
-        <v>71.5</v>
+        <v>60.500000000000014</v>
       </c>
       <c r="J337">
-        <v>2.52</v>
+        <v>2.3100000000000005</v>
       </c>
       <c r="K337">
         <v>100</v>
@@ -36556,25 +36556,25 @@
         <v>308</v>
       </c>
       <c r="D338" t="s">
-        <v>329</v>
+        <v>15</v>
       </c>
       <c r="E338">
         <v>2022</v>
       </c>
       <c r="F338">
-        <v>4.4073197411209589E-2</v>
+        <v>0.11134281451252948</v>
       </c>
       <c r="G338">
         <v>1</v>
       </c>
       <c r="H338">
-        <v>3712.5000000000005</v>
+        <v>3162.5000000000005</v>
       </c>
       <c r="I338">
-        <v>71.5</v>
+        <v>60.500000000000014</v>
       </c>
       <c r="J338">
-        <v>2.52</v>
+        <v>2.3100000000000005</v>
       </c>
       <c r="K338">
         <v>100</v>
@@ -36609,25 +36609,25 @@
         <v>308</v>
       </c>
       <c r="D339" t="s">
-        <v>291</v>
+        <v>193</v>
       </c>
       <c r="E339">
         <v>2022</v>
       </c>
       <c r="F339">
-        <v>0.13082780705222213</v>
+        <v>0.61052976624370348</v>
       </c>
       <c r="G339">
         <v>1</v>
       </c>
       <c r="H339">
-        <v>3162.5000000000005</v>
+        <v>2750</v>
       </c>
       <c r="I339">
-        <v>60.500000000000014</v>
+        <v>55.000000000000007</v>
       </c>
       <c r="J339">
-        <v>2.3100000000000005</v>
+        <v>2.1</v>
       </c>
       <c r="K339">
         <v>100</v>
@@ -36662,25 +36662,25 @@
         <v>308</v>
       </c>
       <c r="D340" t="s">
-        <v>75</v>
+        <v>329</v>
       </c>
       <c r="E340">
         <v>2022</v>
       </c>
       <c r="F340">
-        <v>0.50939337639482241</v>
+        <v>6.9589259070330922E-2</v>
       </c>
       <c r="G340">
         <v>1</v>
       </c>
       <c r="H340">
-        <v>2750</v>
+        <v>3162.5000000000005</v>
       </c>
       <c r="I340">
-        <v>55.000000000000007</v>
+        <v>60.500000000000007</v>
       </c>
       <c r="J340">
-        <v>2.1</v>
+        <v>2.3100000000000005</v>
       </c>
       <c r="K340">
         <v>100</v>
@@ -36768,7 +36768,7 @@
         <v>308</v>
       </c>
       <c r="D342" t="s">
-        <v>329</v>
+        <v>321</v>
       </c>
       <c r="E342">
         <v>1959</v>
@@ -36874,7 +36874,7 @@
         <v>308</v>
       </c>
       <c r="D344" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E344">
         <v>1973</v>
@@ -36980,7 +36980,7 @@
         <v>308</v>
       </c>
       <c r="D346" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="E346">
         <v>1963</v>
@@ -37033,7 +37033,7 @@
         <v>308</v>
       </c>
       <c r="D347" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="E347">
         <v>2015</v>
@@ -37139,7 +37139,7 @@
         <v>308</v>
       </c>
       <c r="D349" t="s">
-        <v>319</v>
+        <v>313</v>
       </c>
       <c r="E349">
         <v>1949</v>
@@ -37298,7 +37298,7 @@
         <v>308</v>
       </c>
       <c r="D352" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="E352">
         <v>1958</v>
@@ -37351,7 +37351,7 @@
         <v>308</v>
       </c>
       <c r="D353" t="s">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="E353">
         <v>1967</v>
@@ -37404,7 +37404,7 @@
         <v>308</v>
       </c>
       <c r="D354" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="E354">
         <v>1968</v>
@@ -37457,7 +37457,7 @@
         <v>308</v>
       </c>
       <c r="D355" t="s">
-        <v>327</v>
+        <v>322</v>
       </c>
       <c r="E355">
         <v>1929</v>
@@ -37510,7 +37510,7 @@
         <v>308</v>
       </c>
       <c r="D356" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="E356">
         <v>1949</v>
@@ -37616,7 +37616,7 @@
         <v>308</v>
       </c>
       <c r="D358" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E358">
         <v>1952</v>
@@ -37669,7 +37669,7 @@
         <v>308</v>
       </c>
       <c r="D359" t="s">
-        <v>327</v>
+        <v>322</v>
       </c>
       <c r="E359">
         <v>1913</v>
@@ -37934,7 +37934,7 @@
         <v>308</v>
       </c>
       <c r="D364" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="E364">
         <v>1927</v>
@@ -37987,7 +37987,7 @@
         <v>308</v>
       </c>
       <c r="D365" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="E365">
         <v>1928</v>
@@ -38093,7 +38093,7 @@
         <v>308</v>
       </c>
       <c r="D367" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="E367">
         <v>1938</v>
@@ -38199,7 +38199,7 @@
         <v>308</v>
       </c>
       <c r="D369" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="E369">
         <v>1947</v>
@@ -38252,7 +38252,7 @@
         <v>308</v>
       </c>
       <c r="D370" t="s">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="E370">
         <v>1950</v>
@@ -38305,7 +38305,7 @@
         <v>308</v>
       </c>
       <c r="D371" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E371">
         <v>1954</v>
@@ -38570,7 +38570,7 @@
         <v>308</v>
       </c>
       <c r="D376" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="E376">
         <v>1955</v>
@@ -38623,7 +38623,7 @@
         <v>308</v>
       </c>
       <c r="D377" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="E377">
         <v>1959</v>
@@ -38676,7 +38676,7 @@
         <v>308</v>
       </c>
       <c r="D378" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="E378">
         <v>1954</v>
@@ -38888,7 +38888,7 @@
         <v>308</v>
       </c>
       <c r="D382" t="s">
-        <v>50</v>
+        <v>84</v>
       </c>
       <c r="E382">
         <v>2022</v>
@@ -39100,7 +39100,7 @@
         <v>308</v>
       </c>
       <c r="D386" t="s">
-        <v>73</v>
+        <v>62</v>
       </c>
       <c r="E386">
         <v>2022</v>
@@ -39206,7 +39206,7 @@
         <v>383</v>
       </c>
       <c r="D388" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="E388">
         <v>1989</v>
@@ -39259,7 +39259,7 @@
         <v>383</v>
       </c>
       <c r="D389" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="E389">
         <v>1975</v>
@@ -39312,7 +39312,7 @@
         <v>383</v>
       </c>
       <c r="D390" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="E390">
         <v>1966</v>
@@ -39365,7 +39365,7 @@
         <v>383</v>
       </c>
       <c r="D391" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="E391">
         <v>2015</v>
@@ -39418,7 +39418,7 @@
         <v>383</v>
       </c>
       <c r="D392" t="s">
-        <v>328</v>
+        <v>320</v>
       </c>
       <c r="E392">
         <v>2015</v>
@@ -39471,7 +39471,7 @@
         <v>383</v>
       </c>
       <c r="D393" t="s">
-        <v>328</v>
+        <v>320</v>
       </c>
       <c r="E393">
         <v>1982</v>
@@ -39577,7 +39577,7 @@
         <v>383</v>
       </c>
       <c r="D395" t="s">
-        <v>309</v>
+        <v>326</v>
       </c>
       <c r="E395">
         <v>2015</v>
@@ -39630,7 +39630,7 @@
         <v>383</v>
       </c>
       <c r="D396" t="s">
-        <v>73</v>
+        <v>62</v>
       </c>
       <c r="E396">
         <v>1961</v>
@@ -39683,7 +39683,7 @@
         <v>383</v>
       </c>
       <c r="D397" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="E397">
         <v>2005</v>
@@ -39736,7 +39736,7 @@
         <v>383</v>
       </c>
       <c r="D398" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="E398">
         <v>1991</v>
@@ -39895,7 +39895,7 @@
         <v>383</v>
       </c>
       <c r="D401" t="s">
-        <v>327</v>
+        <v>322</v>
       </c>
       <c r="E401">
         <v>1971</v>
@@ -39948,7 +39948,7 @@
         <v>383</v>
       </c>
       <c r="D402" t="s">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="E402">
         <v>1973</v>
@@ -40107,7 +40107,7 @@
         <v>383</v>
       </c>
       <c r="D405" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E405">
         <v>1978</v>
@@ -40160,7 +40160,7 @@
         <v>383</v>
       </c>
       <c r="D406" t="s">
-        <v>319</v>
+        <v>313</v>
       </c>
       <c r="E406">
         <v>1923</v>
@@ -40213,7 +40213,7 @@
         <v>308</v>
       </c>
       <c r="D407" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="E407">
         <v>1959</v>
@@ -40319,7 +40319,7 @@
         <v>308</v>
       </c>
       <c r="D409" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="E409">
         <v>1949</v>
@@ -40372,7 +40372,7 @@
         <v>308</v>
       </c>
       <c r="D410" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="E410">
         <v>1953</v>
@@ -40478,7 +40478,7 @@
         <v>308</v>
       </c>
       <c r="D412" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="E412">
         <v>1960</v>
@@ -40531,7 +40531,7 @@
         <v>308</v>
       </c>
       <c r="D413" t="s">
-        <v>311</v>
+        <v>319</v>
       </c>
       <c r="E413">
         <v>1962</v>
@@ -40584,7 +40584,7 @@
         <v>308</v>
       </c>
       <c r="D414" t="s">
-        <v>319</v>
+        <v>313</v>
       </c>
       <c r="E414">
         <v>2015</v>
@@ -40637,7 +40637,7 @@
         <v>308</v>
       </c>
       <c r="D415" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="E415">
         <v>1927</v>
@@ -40690,7 +40690,7 @@
         <v>308</v>
       </c>
       <c r="D416" t="s">
-        <v>318</v>
+        <v>309</v>
       </c>
       <c r="E416">
         <v>1954</v>
@@ -40796,7 +40796,7 @@
         <v>308</v>
       </c>
       <c r="D418" t="s">
-        <v>319</v>
+        <v>313</v>
       </c>
       <c r="E418">
         <v>1956</v>
@@ -40955,7 +40955,7 @@
         <v>308</v>
       </c>
       <c r="D421" t="s">
-        <v>319</v>
+        <v>313</v>
       </c>
       <c r="E421">
         <v>1960</v>
@@ -41061,7 +41061,7 @@
         <v>308</v>
       </c>
       <c r="D423" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="E423">
         <v>2015</v>
@@ -41167,7 +41167,7 @@
         <v>308</v>
       </c>
       <c r="D425" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="E425">
         <v>2015</v>
@@ -41220,7 +41220,7 @@
         <v>308</v>
       </c>
       <c r="D426" t="s">
-        <v>328</v>
+        <v>320</v>
       </c>
       <c r="E426">
         <v>2015</v>
@@ -41326,7 +41326,7 @@
         <v>308</v>
       </c>
       <c r="D428" t="s">
-        <v>50</v>
+        <v>84</v>
       </c>
       <c r="E428">
         <v>1955</v>
@@ -41379,7 +41379,7 @@
         <v>308</v>
       </c>
       <c r="D429" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E429">
         <v>2015</v>
@@ -41485,7 +41485,7 @@
         <v>308</v>
       </c>
       <c r="D431" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="E431">
         <v>1932</v>
@@ -41644,7 +41644,7 @@
         <v>308</v>
       </c>
       <c r="D434" t="s">
-        <v>327</v>
+        <v>322</v>
       </c>
       <c r="E434">
         <v>1924</v>
@@ -41750,7 +41750,7 @@
         <v>308</v>
       </c>
       <c r="D436" t="s">
-        <v>327</v>
+        <v>322</v>
       </c>
       <c r="E436">
         <v>2002</v>
@@ -41856,7 +41856,7 @@
         <v>308</v>
       </c>
       <c r="D438" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="E438">
         <v>1948</v>
@@ -41909,7 +41909,7 @@
         <v>308</v>
       </c>
       <c r="D439" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="E439">
         <v>2015</v>
@@ -42068,7 +42068,7 @@
         <v>308</v>
       </c>
       <c r="D442" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E442">
         <v>1958</v>
@@ -42121,7 +42121,7 @@
         <v>439</v>
       </c>
       <c r="D443" t="s">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="E443">
         <v>1992</v>
@@ -42280,7 +42280,7 @@
         <v>439</v>
       </c>
       <c r="D446" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E446">
         <v>1992</v>
@@ -42598,7 +42598,7 @@
         <v>439</v>
       </c>
       <c r="D452" t="s">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="E452">
         <v>1985</v>
@@ -42922,7 +42922,7 @@
         <v>2022</v>
       </c>
       <c r="F458">
-        <v>6.6307854518247753</v>
+        <v>6.6457416582336482</v>
       </c>
       <c r="G458">
         <v>1</v>
@@ -42978,7 +42978,7 @@
         <v>2022</v>
       </c>
       <c r="F459">
-        <v>6.6039408899415779</v>
+        <v>6.6307854518247753</v>
       </c>
       <c r="G459">
         <v>1</v>
@@ -43034,7 +43034,7 @@
         <v>2022</v>
       </c>
       <c r="F460">
-        <v>6.6457416582336482</v>
+        <v>6.6039408899415779</v>
       </c>
       <c r="G460">
         <v>1</v>
@@ -43812,7 +43812,7 @@
         <v>455</v>
       </c>
       <c r="D474" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="E474">
         <v>2015</v>
@@ -44876,7 +44876,7 @@
         <v>455</v>
       </c>
       <c r="D493" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="E493">
         <v>2015</v>
@@ -51156,7 +51156,7 @@
         <v>2022</v>
       </c>
       <c r="F618">
-        <v>0.6793056475905862</v>
+        <v>0.69928302455480262</v>
       </c>
       <c r="G618">
         <v>0.33123000000000002</v>
@@ -51179,7 +51179,7 @@
         <v>2022</v>
       </c>
       <c r="F619">
-        <v>0.69928302455480262</v>
+        <v>0.67351932785461166</v>
       </c>
       <c r="G619">
         <v>0.33123000000000002</v>
@@ -51202,7 +51202,7 @@
         <v>2022</v>
       </c>
       <c r="F620">
-        <v>0.67351932785461166</v>
+        <v>0.6793056475905862</v>
       </c>
       <c r="G620">
         <v>0.33123000000000002</v>
@@ -51449,7 +51449,7 @@
         <v>663</v>
       </c>
       <c r="D631" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="E631">
         <v>2018</v>

--- a/VerveStacks_ITA_grids/vt_vervestacks_ITA_v1.xlsx
+++ b/VerveStacks_ITA_grids/vt_vervestacks_ITA_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C6FFF0AF-5FA4-47CE-AA42-BCC0B4A30B40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D74BFAC3-12B0-4D05-8B3E-5ADAFC0163EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{945238FB-BE21-4170-9238-36C66C9696A9}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{41AE1675-1BC9-4E47-915A-9F40DC1E702C}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="2" r:id="rId1"/>
@@ -81,30 +81,30 @@
     <t>bioenergy</t>
   </si>
   <si>
+    <t>e_w98902899-380</t>
+  </si>
+  <si>
+    <t>e_w58440884-380</t>
+  </si>
+  <si>
     <t>e_w84696559-380</t>
   </si>
   <si>
+    <t>e_w34157795-380</t>
+  </si>
+  <si>
+    <t>e_w81938081-380</t>
+  </si>
+  <si>
+    <t>e_w109756016-380</t>
+  </si>
+  <si>
     <t>e_w144005863-380</t>
   </si>
   <si>
-    <t>e_w34157795-380</t>
-  </si>
-  <si>
-    <t>e_w98902899-380</t>
-  </si>
-  <si>
-    <t>e_w81938081-380</t>
-  </si>
-  <si>
-    <t>e_w58440884-380</t>
-  </si>
-  <si>
     <t>e_w108020416-380</t>
   </si>
   <si>
-    <t>e_w109756016-380</t>
-  </si>
-  <si>
     <t>ep_bioenergy_G100000200236</t>
   </si>
   <si>
@@ -141,18 +141,18 @@
     <t>coal</t>
   </si>
   <si>
+    <t>e_w82767145-380</t>
+  </si>
+  <si>
+    <t>e_w303915533-380</t>
+  </si>
+  <si>
+    <t>e_w418902800-380</t>
+  </si>
+  <si>
     <t>e_w409439916-380</t>
   </si>
   <si>
-    <t>e_w418902800-380</t>
-  </si>
-  <si>
-    <t>e_w303915533-380</t>
-  </si>
-  <si>
-    <t>e_w82767145-380</t>
-  </si>
-  <si>
     <t>ep_coal_subcritical_G100000102764</t>
   </si>
   <si>
@@ -189,120 +189,120 @@
     <t>gas</t>
   </si>
   <si>
+    <t>e_w411026199-380</t>
+  </si>
+  <si>
+    <t>e_w99826025-380</t>
+  </si>
+  <si>
+    <t>e_w103653592-380</t>
+  </si>
+  <si>
+    <t>e_w109993642-380</t>
+  </si>
+  <si>
+    <t>e_w105581403-380</t>
+  </si>
+  <si>
+    <t>e_w255011550-380</t>
+  </si>
+  <si>
+    <t>e_w199675964-380</t>
+  </si>
+  <si>
+    <t>e_w82084019-380</t>
+  </si>
+  <si>
+    <t>e_w98421779-380</t>
+  </si>
+  <si>
+    <t>e_w419423704-380</t>
+  </si>
+  <si>
+    <t>e_w116797658-380</t>
+  </si>
+  <si>
+    <t>e_w158739183-380</t>
+  </si>
+  <si>
+    <t>e_w103974940-380</t>
+  </si>
+  <si>
+    <t>e_w432729521-380</t>
+  </si>
+  <si>
+    <t>e_w414663585-380</t>
+  </si>
+  <si>
+    <t>e_w172302572-380</t>
+  </si>
+  <si>
+    <t>e_w181125039-380</t>
+  </si>
+  <si>
+    <t>e_w133601335-380</t>
+  </si>
+  <si>
+    <t>e_w103381531-380</t>
+  </si>
+  <si>
+    <t>e_w339104227-380</t>
+  </si>
+  <si>
+    <t>e_w59462715-380</t>
+  </si>
+  <si>
+    <t>e_w421827453-380</t>
+  </si>
+  <si>
     <t>e_w149997403-380</t>
   </si>
   <si>
-    <t>e_w59462715-380</t>
-  </si>
-  <si>
-    <t>e_w82084019-380</t>
+    <t>e_w100407576-380</t>
+  </si>
+  <si>
+    <t>e_w1137611914-380</t>
+  </si>
+  <si>
+    <t>e_w98900549-380</t>
+  </si>
+  <si>
+    <t>e_w162828577-380</t>
+  </si>
+  <si>
+    <t>e_w132450233-380</t>
+  </si>
+  <si>
+    <t>e_w110330925-380</t>
+  </si>
+  <si>
+    <t>e_w61157826-380</t>
+  </si>
+  <si>
+    <t>e_w82078641-380</t>
+  </si>
+  <si>
+    <t>e_w162960205-380</t>
+  </si>
+  <si>
+    <t>e_w338753171-380</t>
+  </si>
+  <si>
+    <t>e_w145665799-380</t>
+  </si>
+  <si>
+    <t>e_w60725875-380</t>
   </si>
   <si>
     <t>e_w107438024-380</t>
   </si>
   <si>
-    <t>e_w411026199-380</t>
+    <t>e_w105757794-380</t>
   </si>
   <si>
     <t>e_w416989699-380</t>
   </si>
   <si>
-    <t>e_w432729521-380</t>
-  </si>
-  <si>
-    <t>e_w172302572-380</t>
-  </si>
-  <si>
-    <t>e_w199675964-380</t>
-  </si>
-  <si>
-    <t>e_w109993642-380</t>
-  </si>
-  <si>
-    <t>e_w103653592-380</t>
-  </si>
-  <si>
-    <t>e_w82078641-380</t>
-  </si>
-  <si>
-    <t>e_w61157826-380</t>
-  </si>
-  <si>
-    <t>e_w99826025-380</t>
-  </si>
-  <si>
-    <t>e_w1137611914-380</t>
-  </si>
-  <si>
-    <t>e_w60725875-380</t>
-  </si>
-  <si>
-    <t>e_w145665799-380</t>
-  </si>
-  <si>
-    <t>e_w339104227-380</t>
-  </si>
-  <si>
-    <t>e_w98421779-380</t>
-  </si>
-  <si>
-    <t>e_w419423704-380</t>
-  </si>
-  <si>
-    <t>e_w116797658-380</t>
-  </si>
-  <si>
-    <t>e_w414663585-380</t>
-  </si>
-  <si>
-    <t>e_w255011550-380</t>
-  </si>
-  <si>
-    <t>e_w162960205-380</t>
-  </si>
-  <si>
-    <t>e_w105581403-380</t>
-  </si>
-  <si>
-    <t>e_w158739183-380</t>
-  </si>
-  <si>
-    <t>e_w103974940-380</t>
-  </si>
-  <si>
-    <t>e_w98900549-380</t>
-  </si>
-  <si>
-    <t>e_w162828577-380</t>
-  </si>
-  <si>
-    <t>e_w338753171-380</t>
-  </si>
-  <si>
-    <t>e_w103381531-380</t>
-  </si>
-  <si>
-    <t>e_w133601335-380</t>
-  </si>
-  <si>
-    <t>e_w181125039-380</t>
-  </si>
-  <si>
-    <t>e_w105757794-380</t>
-  </si>
-  <si>
-    <t>e_w110330925-380</t>
-  </si>
-  <si>
-    <t>e_w100407576-380</t>
-  </si>
-  <si>
-    <t>e_w132450233-380</t>
-  </si>
-  <si>
-    <t>e_w421827453-380</t>
-  </si>
-  <si>
     <t>ep_gas_combined_cycle_G100000400339</t>
   </si>
   <si>
@@ -966,69 +966,69 @@
     <t>hydro</t>
   </si>
   <si>
+    <t>e_w114931087-380</t>
+  </si>
+  <si>
+    <t>e_IT72-400</t>
+  </si>
+  <si>
+    <t>e_IT93-380</t>
+  </si>
+  <si>
+    <t>e_IT71-380</t>
+  </si>
+  <si>
+    <t>e_IT71-400</t>
+  </si>
+  <si>
+    <t>e_IT10-380</t>
+  </si>
+  <si>
+    <t>e_w116517585-380</t>
+  </si>
+  <si>
+    <t>e_IT21-380</t>
+  </si>
+  <si>
     <t>e_w61626687-380</t>
   </si>
   <si>
+    <t>e_IT72-380</t>
+  </si>
+  <si>
+    <t>e_IT7-380</t>
+  </si>
+  <si>
+    <t>e_w64200868-380</t>
+  </si>
+  <si>
+    <t>e_w72466334-380</t>
+  </si>
+  <si>
+    <t>e_IT36-380</t>
+  </si>
+  <si>
+    <t>e_w104359058-380</t>
+  </si>
+  <si>
+    <t>e_IT31-380</t>
+  </si>
+  <si>
     <t>e_w1100665914-380</t>
   </si>
   <si>
-    <t>e_IT71-380</t>
+    <t>e_w491424937-380</t>
+  </si>
+  <si>
+    <t>e_w75602396-380</t>
+  </si>
+  <si>
+    <t>e_IT53-380</t>
   </si>
   <si>
     <t>e_w82083756-380</t>
   </si>
   <si>
-    <t>e_IT7-380</t>
-  </si>
-  <si>
-    <t>e_w114931087-380</t>
-  </si>
-  <si>
-    <t>e_w491424937-380</t>
-  </si>
-  <si>
-    <t>e_IT71-400</t>
-  </si>
-  <si>
-    <t>e_w75602396-380</t>
-  </si>
-  <si>
-    <t>e_w64200868-380</t>
-  </si>
-  <si>
-    <t>e_w116517585-380</t>
-  </si>
-  <si>
-    <t>e_w104359058-380</t>
-  </si>
-  <si>
-    <t>e_IT31-380</t>
-  </si>
-  <si>
-    <t>e_IT21-380</t>
-  </si>
-  <si>
-    <t>e_IT72-380</t>
-  </si>
-  <si>
-    <t>e_IT72-400</t>
-  </si>
-  <si>
-    <t>e_IT36-380</t>
-  </si>
-  <si>
-    <t>e_IT53-380</t>
-  </si>
-  <si>
-    <t>e_w72466334-380</t>
-  </si>
-  <si>
-    <t>e_IT10-380</t>
-  </si>
-  <si>
-    <t>e_IT93-380</t>
-  </si>
-  <si>
     <t>ep_hydro_dam_G100000602220</t>
   </si>
   <si>
@@ -1407,15 +1407,15 @@
     <t>solar</t>
   </si>
   <si>
+    <t>elc_spv-ITA_0042</t>
+  </si>
+  <si>
     <t>elc_spv-ITA_0068</t>
   </si>
   <si>
     <t>elc_spv-ITA_0030</t>
   </si>
   <si>
-    <t>elc_spv-ITA_0042</t>
-  </si>
-  <si>
     <t>ep_solar_pv_001</t>
   </si>
   <si>
@@ -2031,15 +2031,15 @@
     <t>windon</t>
   </si>
   <si>
+    <t>elc_won-ITA_0022</t>
+  </si>
+  <si>
+    <t>elc_won-ITA_0096</t>
+  </si>
+  <si>
     <t>elc_won-ITA_0073</t>
   </si>
   <si>
-    <t>elc_won-ITA_0096</t>
-  </si>
-  <si>
-    <t>elc_won-ITA_0022</t>
-  </si>
-  <si>
     <t>ep_windon_wind_010</t>
   </si>
   <si>
@@ -2469,42 +2469,42 @@
     <t>ele</t>
   </si>
   <si>
+    <t>Aggregated Plant - EMBER Gap - way/58440884-380_Missing Bioenergy Capacity</t>
+  </si>
+  <si>
+    <t>GW</t>
+  </si>
+  <si>
+    <t>TWh</t>
+  </si>
+  <si>
+    <t>daynite</t>
+  </si>
+  <si>
+    <t>yes</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/34157795-380_Missing Bioenergy Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/108020416-380_Missing Bioenergy Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/84696559-380_Missing Bioenergy Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/81938081-380_Missing Bioenergy Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/98902899-380_Missing Bioenergy Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/144005863-380_Missing Bioenergy Capacity</t>
+  </si>
+  <si>
     <t>Aggregated Plant - EMBER Gap - way/109756016-380_Missing Bioenergy Capacity</t>
   </si>
   <si>
-    <t>GW</t>
-  </si>
-  <si>
-    <t>TWh</t>
-  </si>
-  <si>
-    <t>daynite</t>
-  </si>
-  <si>
-    <t>yes</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/144005863-380_Missing Bioenergy Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/98902899-380_Missing Bioenergy Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/81938081-380_Missing Bioenergy Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/84696559-380_Missing Bioenergy Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/34157795-380_Missing Bioenergy Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/58440884-380_Missing Bioenergy Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/108020416-380_Missing Bioenergy Capacity</t>
-  </si>
-  <si>
     <t>Acerra power station_1</t>
   </si>
   <si>
@@ -2532,12 +2532,12 @@
     <t>Aggregated Plant - EMBER Gap - way/418902800-380_Missing Coal Capacity</t>
   </si>
   <si>
+    <t>Aggregated Plant - EMBER Gap - way/82767145-380_Missing Coal Capacity</t>
+  </si>
+  <si>
     <t>Aggregated Plant - EMBER Gap - way/303915533-380_Missing Coal Capacity</t>
   </si>
   <si>
-    <t>Aggregated Plant - EMBER Gap - way/82767145-380_Missing Coal Capacity</t>
-  </si>
-  <si>
     <t>Fiume Santo power station_Unit 3</t>
   </si>
   <si>
@@ -2568,6 +2568,54 @@
     <t>Torrevaldaliga Nord power station_Unit 3</t>
   </si>
   <si>
+    <t>Aggregated Plant - EMBER Gap - way/132450233-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/82078641-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/103974940-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/103381531-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/411026199-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/105581403-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/110330925-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/109756016-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/98421779-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/82084019-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/416989699-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/103653592-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/100407576-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/181125039-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/432729521-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/199675964-380_Missing Gas Capacity</t>
+  </si>
+  <si>
     <t>Aggregated Plant - EMBER Gap - way/338753171-380_Missing Gas Capacity</t>
   </si>
   <si>
@@ -2577,117 +2625,69 @@
     <t>Aggregated Plant - EMBER Gap - way/98900549-380_Missing Gas Capacity</t>
   </si>
   <si>
+    <t>Aggregated Plant - EMBER Gap - way/255011550-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/105757794-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/59462715-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/172302572-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/133601335-380_Missing Gas Capacity</t>
+  </si>
+  <si>
     <t>Aggregated Plant - EMBER Gap - way/149997403-380_Missing Gas Capacity</t>
   </si>
   <si>
     <t>Aggregated Plant - EMBER Gap - way/162960205-380_Missing Gas Capacity</t>
   </si>
   <si>
-    <t>Aggregated Plant - EMBER Gap - way/133601335-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/82084019-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/411026199-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/110330925-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/105581403-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/98421779-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/109756016-380_Missing Gas Capacity</t>
+    <t>Aggregated Plant - EMBER Gap - way/109993642-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/419423704-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/61157826-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/414663585-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/82767145-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/107438024-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/339104227-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/116797658-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/1137611914-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/60725875-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/158739183-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/145665799-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/99826025-380_Missing Gas Capacity</t>
   </si>
   <si>
     <t>Aggregated Plant - EMBER Gap - way/421827453-380_Missing Gas Capacity</t>
   </si>
   <si>
-    <t>Aggregated Plant - EMBER Gap - way/99826025-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/107438024-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/116797658-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/339104227-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/60725875-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/82078641-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/103974940-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/109993642-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/82767145-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/158739183-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/145665799-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/1137611914-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/132450233-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/59462715-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/105757794-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/255011550-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/172302572-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/414663585-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/419423704-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/61157826-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/181125039-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/103381531-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/199675964-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/432729521-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/100407576-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/416989699-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/103653592-380_Missing Gas Capacity</t>
-  </si>
-  <si>
     <t>Altomonte power station_1</t>
   </si>
   <si>
@@ -3000,22 +3000,94 @@
     <t>Valle Secolo geothermal power plant_2</t>
   </si>
   <si>
+    <t>Aggregated Plant - IRENA Gap - way/96190189-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/116517585-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - IT93-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/338753171-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - IT10-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - IT53-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - IT30-500_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/61712456-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - IT71-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - IT7-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/339703159-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - IT72-400_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/109588422-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/1137611914-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/108020416-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
     <t>Aggregated Plant - IRENA Gap - way/64200868-380_Missing Hydro Capacity</t>
   </si>
   <si>
+    <t>Aggregated Plant - IRENA Gap - way/144005863-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - IT21-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/61626687-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
     <t>Aggregated Plant - IRENA Gap - way/114931087-380_Missing Hydro Capacity</t>
   </si>
   <si>
     <t>Aggregated Plant - IRENA Gap - IT31-380_Missing Hydro Capacity</t>
   </si>
   <si>
-    <t>Aggregated Plant - IRENA Gap - way/61626687-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - IT71-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/108020416-380_Missing Hydro Capacity</t>
+    <t>Aggregated Plant - IRENA Gap - way/59462263-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/1100665914-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - IT72-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/104359058-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/82083756-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/491424937-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/419423704-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/72466334-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/75602396-380_Missing Hydro Capacity</t>
   </si>
   <si>
     <t>Aggregated Plant - IRENA Gap - IT71-400_Missing Hydro Capacity</t>
@@ -3024,78 +3096,6 @@
     <t>Aggregated Plant - IRENA Gap - IT36-380_Missing Hydro Capacity</t>
   </si>
   <si>
-    <t>Aggregated Plant - IRENA Gap - way/1100665914-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - IT72-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/59462263-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - IT10-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - IT93-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/338753171-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/75602396-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/419423704-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/491424937-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/72466334-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/104359058-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/82083756-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/116517585-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/96190189-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - IT21-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/144005863-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/1137611914-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/109588422-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - IT72-400_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - IT53-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - IT7-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/339703159-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/61712456-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - IT30-500_Missing Hydro Capacity</t>
-  </si>
-  <si>
     <t>Baschi hydroelectric plant_</t>
   </si>
   <si>
@@ -3396,21 +3396,21 @@
     <t>annual</t>
   </si>
   <si>
+    <t>Aggregated Plant - IRENA Gap - ITA_68_Missing Solar Capacity</t>
+  </si>
+  <si>
     <t>Aggregated Plant - IRENA Gap - ITA_42_Missing Solar Capacity</t>
   </si>
   <si>
-    <t>Aggregated Plant - IRENA Gap - ITA_68_Missing Solar Capacity</t>
-  </si>
-  <si>
     <t>Aggregated Plant - IRENA Gap - ITA_96_Missing Onshore wind energy Capacity</t>
   </si>
   <si>
+    <t>Aggregated Plant - IRENA Gap - ITA_73_Missing Onshore wind energy Capacity</t>
+  </si>
+  <si>
     <t>Aggregated Plant - IRENA Gap - ITA_22_Missing Onshore wind energy Capacity</t>
   </si>
   <si>
-    <t>Aggregated Plant - IRENA Gap - ITA_73_Missing Onshore wind energy Capacity</t>
-  </si>
-  <si>
     <t>AF</t>
   </si>
   <si>
@@ -4002,6 +4002,9 @@
     <t>ccs retrofit of -- Sulcis power station_Unit 3</t>
   </si>
   <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/303915533-380_Missing Coal Capacity</t>
+  </si>
+  <si>
     <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/409439916-380_Missing Coal Capacity</t>
   </si>
   <si>
@@ -4011,9 +4014,6 @@
     <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/82767145-380_Missing Coal Capacity</t>
   </si>
   <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/303915533-380_Missing Coal Capacity</t>
-  </si>
-  <si>
     <t>ccs retrofit of -- Brindisi Sud power station_Unit 1</t>
   </si>
   <si>
@@ -4302,10 +4302,58 @@
     <t>ccs retrofit of -- Aggregated Plant</t>
   </si>
   <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/132450233-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/149997403-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/162960205-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/162828577-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/172302572-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/82767145-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/61157826-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/103974940-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/59462715-380_Missing Gas Capacity</t>
+  </si>
+  <si>
     <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/109993642-380_Missing Gas Capacity</t>
   </si>
   <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/59462715-380_Missing Gas Capacity</t>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/414663585-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/145665799-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/82084019-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/60725875-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/421827453-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/110330925-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/338753171-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/103381531-380_Missing Gas Capacity</t>
   </si>
   <si>
     <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/411026199-380_Missing Gas Capacity</t>
@@ -4314,112 +4362,64 @@
     <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/109756016-380_Missing Gas Capacity</t>
   </si>
   <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/103381531-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/103974940-380_Missing Gas Capacity</t>
-  </si>
-  <si>
     <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/133601335-380_Missing Gas Capacity</t>
   </si>
   <si>
     <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/339104227-380_Missing Gas Capacity</t>
   </si>
   <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/116797658-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/419423704-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/100407576-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/82078641-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/416989699-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/105757794-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/99826025-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/105581403-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/181125039-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/255011550-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/103653592-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/199675964-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/1137611914-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/432729521-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/98421779-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/98900549-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/107438024-380_Missing Gas Capacity</t>
+  </si>
+  <si>
     <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/158739183-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/145665799-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/338753171-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/110330925-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/105581403-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/255011550-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/181125039-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/132450233-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/100407576-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/99826025-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/105757794-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/416989699-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/162960205-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/419423704-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/432729521-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/149997403-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/82078641-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/1137611914-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/199675964-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/103653592-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/107438024-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/98421779-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/82767145-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/98900549-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/82084019-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/421827453-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/172302572-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/60725875-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/162828577-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/116797658-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/414663585-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/61157826-380_Missing Gas Capacity</t>
   </si>
   <si>
     <t>ccs retrofit of -- Tavazzano power station_CCGT8, timepoint 1</t>
@@ -4823,7 +4823,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54BAE8D9-5115-45D9-AB7C-D5B117159D4E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6DC652D2-71A7-45BF-93A5-CE6DCE854CD1}">
   <dimension ref="B9:T278"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -4899,7 +4899,7 @@
         <v>33</v>
       </c>
       <c r="D11" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="E11">
         <v>0.18317520000000001</v>
@@ -4955,7 +4955,7 @@
         <v>33</v>
       </c>
       <c r="D12" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="E12">
         <v>0.18317520000000001</v>
@@ -5011,7 +5011,7 @@
         <v>33</v>
       </c>
       <c r="D13" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E13">
         <v>0.18317520000000001</v>
@@ -5067,7 +5067,7 @@
         <v>33</v>
       </c>
       <c r="D14" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E14">
         <v>0.13765950000000002</v>
@@ -5347,7 +5347,7 @@
         <v>33</v>
       </c>
       <c r="D19" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E19">
         <v>0.30649709999999997</v>
@@ -5403,7 +5403,7 @@
         <v>33</v>
       </c>
       <c r="D20" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E20">
         <v>0.30649709999999997</v>
@@ -5459,7 +5459,7 @@
         <v>33</v>
       </c>
       <c r="D21" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E21">
         <v>0.30649709999999997</v>
@@ -5515,7 +5515,7 @@
         <v>33</v>
       </c>
       <c r="D22" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E22">
         <v>0.33007379999999992</v>
@@ -5571,7 +5571,7 @@
         <v>33</v>
       </c>
       <c r="D23" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E23">
         <v>0.33007379999999992</v>
@@ -5627,7 +5627,7 @@
         <v>33</v>
       </c>
       <c r="D24" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E24">
         <v>0.33007379999999992</v>
@@ -5683,7 +5683,7 @@
         <v>49</v>
       </c>
       <c r="D25" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="E25">
         <v>0.49118125000000001</v>
@@ -5739,7 +5739,7 @@
         <v>49</v>
       </c>
       <c r="D26" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="E26">
         <v>0.52272499999999988</v>
@@ -5795,7 +5795,7 @@
         <v>49</v>
       </c>
       <c r="D27" t="s">
-        <v>85</v>
+        <v>73</v>
       </c>
       <c r="E27">
         <v>0.450625</v>
@@ -5851,7 +5851,7 @@
         <v>49</v>
       </c>
       <c r="D28" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="E28">
         <v>0.52272499999999988</v>
@@ -5907,7 +5907,7 @@
         <v>49</v>
       </c>
       <c r="D29" t="s">
-        <v>66</v>
+        <v>83</v>
       </c>
       <c r="E29">
         <v>0.49118125000000001</v>
@@ -5963,7 +5963,7 @@
         <v>49</v>
       </c>
       <c r="D30" t="s">
-        <v>66</v>
+        <v>83</v>
       </c>
       <c r="E30">
         <v>0.49118125000000001</v>
@@ -6019,7 +6019,7 @@
         <v>49</v>
       </c>
       <c r="D31" t="s">
-        <v>66</v>
+        <v>83</v>
       </c>
       <c r="E31">
         <v>0.49118125000000001</v>
@@ -6131,7 +6131,7 @@
         <v>49</v>
       </c>
       <c r="D33" t="s">
-        <v>81</v>
+        <v>67</v>
       </c>
       <c r="E33">
         <v>0.49118125000000001</v>
@@ -6299,7 +6299,7 @@
         <v>49</v>
       </c>
       <c r="D36" t="s">
-        <v>74</v>
+        <v>54</v>
       </c>
       <c r="E36">
         <v>0.49118125000000001</v>
@@ -6355,7 +6355,7 @@
         <v>49</v>
       </c>
       <c r="D37" t="s">
-        <v>74</v>
+        <v>54</v>
       </c>
       <c r="E37">
         <v>0.49118125000000001</v>
@@ -6411,7 +6411,7 @@
         <v>49</v>
       </c>
       <c r="D38" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="E38">
         <v>0.49118125000000001</v>
@@ -6467,7 +6467,7 @@
         <v>49</v>
       </c>
       <c r="D39" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="E39">
         <v>0.49118125000000001</v>
@@ -6523,7 +6523,7 @@
         <v>49</v>
       </c>
       <c r="D40" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E40">
         <v>0.46865000000000007</v>
@@ -6579,7 +6579,7 @@
         <v>49</v>
       </c>
       <c r="D41" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E41">
         <v>0.49118125000000001</v>
@@ -6635,7 +6635,7 @@
         <v>49</v>
       </c>
       <c r="D42" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E42">
         <v>0.49118125000000001</v>
@@ -6691,7 +6691,7 @@
         <v>49</v>
       </c>
       <c r="D43" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="E43">
         <v>0.49118125000000001</v>
@@ -6747,7 +6747,7 @@
         <v>49</v>
       </c>
       <c r="D44" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="E44">
         <v>0.49118125000000001</v>
@@ -6803,7 +6803,7 @@
         <v>49</v>
       </c>
       <c r="D45" t="s">
-        <v>53</v>
+        <v>85</v>
       </c>
       <c r="E45">
         <v>0.49118125000000001</v>
@@ -6859,7 +6859,7 @@
         <v>49</v>
       </c>
       <c r="D46" t="s">
-        <v>53</v>
+        <v>85</v>
       </c>
       <c r="E46">
         <v>0.49118125000000001</v>
@@ -6915,7 +6915,7 @@
         <v>49</v>
       </c>
       <c r="D47" t="s">
-        <v>53</v>
+        <v>85</v>
       </c>
       <c r="E47">
         <v>0.49118125000000001</v>
@@ -6971,7 +6971,7 @@
         <v>49</v>
       </c>
       <c r="D48" t="s">
-        <v>53</v>
+        <v>85</v>
       </c>
       <c r="E48">
         <v>0.49118125000000001</v>
@@ -7027,7 +7027,7 @@
         <v>49</v>
       </c>
       <c r="D49" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="E49">
         <v>0.47315625000000006</v>
@@ -7083,7 +7083,7 @@
         <v>49</v>
       </c>
       <c r="D50" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="E50">
         <v>0.47315625000000006</v>
@@ -7139,7 +7139,7 @@
         <v>49</v>
       </c>
       <c r="D51" t="s">
-        <v>76</v>
+        <v>62</v>
       </c>
       <c r="E51">
         <v>0.49118125000000001</v>
@@ -7195,7 +7195,7 @@
         <v>49</v>
       </c>
       <c r="D52" t="s">
-        <v>85</v>
+        <v>73</v>
       </c>
       <c r="E52">
         <v>0.54075000000000006</v>
@@ -7251,7 +7251,7 @@
         <v>49</v>
       </c>
       <c r="D53" t="s">
-        <v>85</v>
+        <v>73</v>
       </c>
       <c r="E53">
         <v>0.49118125000000001</v>
@@ -7363,7 +7363,7 @@
         <v>49</v>
       </c>
       <c r="D55" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="E55">
         <v>0.49118125000000001</v>
@@ -7419,7 +7419,7 @@
         <v>49</v>
       </c>
       <c r="D56" t="s">
-        <v>63</v>
+        <v>51</v>
       </c>
       <c r="E56">
         <v>0.49118125000000001</v>
@@ -7475,7 +7475,7 @@
         <v>49</v>
       </c>
       <c r="D57" t="s">
-        <v>63</v>
+        <v>51</v>
       </c>
       <c r="E57">
         <v>0.49118125000000001</v>
@@ -7531,7 +7531,7 @@
         <v>49</v>
       </c>
       <c r="D58" t="s">
-        <v>55</v>
+        <v>87</v>
       </c>
       <c r="E58">
         <v>0.47315625000000006</v>
@@ -7587,7 +7587,7 @@
         <v>49</v>
       </c>
       <c r="D59" t="s">
-        <v>55</v>
+        <v>87</v>
       </c>
       <c r="E59">
         <v>0.47315625000000006</v>
@@ -7643,7 +7643,7 @@
         <v>49</v>
       </c>
       <c r="D60" t="s">
-        <v>55</v>
+        <v>87</v>
       </c>
       <c r="E60">
         <v>0.450625</v>
@@ -7699,7 +7699,7 @@
         <v>49</v>
       </c>
       <c r="D61" t="s">
-        <v>55</v>
+        <v>87</v>
       </c>
       <c r="E61">
         <v>0.450625</v>
@@ -7811,7 +7811,7 @@
         <v>49</v>
       </c>
       <c r="D63" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="E63">
         <v>0.4911812499999999</v>
@@ -7867,7 +7867,7 @@
         <v>49</v>
       </c>
       <c r="D64" t="s">
-        <v>61</v>
+        <v>80</v>
       </c>
       <c r="E64">
         <v>0.49118125000000001</v>
@@ -7923,7 +7923,7 @@
         <v>49</v>
       </c>
       <c r="D65" t="s">
-        <v>61</v>
+        <v>80</v>
       </c>
       <c r="E65">
         <v>0.49118125000000001</v>
@@ -7979,7 +7979,7 @@
         <v>49</v>
       </c>
       <c r="D66" t="s">
-        <v>87</v>
+        <v>71</v>
       </c>
       <c r="E66">
         <v>0.49118125000000001</v>
@@ -8147,7 +8147,7 @@
         <v>49</v>
       </c>
       <c r="D69" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="E69">
         <v>0.49118125000000001</v>
@@ -8203,7 +8203,7 @@
         <v>49</v>
       </c>
       <c r="D70" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="E70">
         <v>0.49118125000000001</v>
@@ -8259,7 +8259,7 @@
         <v>49</v>
       </c>
       <c r="D71" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="E71">
         <v>0.49118125000000001</v>
@@ -8315,7 +8315,7 @@
         <v>49</v>
       </c>
       <c r="D72" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="E72">
         <v>0.49118125000000001</v>
@@ -8371,7 +8371,7 @@
         <v>49</v>
       </c>
       <c r="D73" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="E73">
         <v>0.49118125000000001</v>
@@ -8427,7 +8427,7 @@
         <v>49</v>
       </c>
       <c r="D74" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="E74">
         <v>0.49118125000000001</v>
@@ -8483,7 +8483,7 @@
         <v>49</v>
       </c>
       <c r="D75" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="E75">
         <v>0.50470000000000004</v>
@@ -8539,7 +8539,7 @@
         <v>49</v>
       </c>
       <c r="D76" t="s">
-        <v>82</v>
+        <v>66</v>
       </c>
       <c r="E76">
         <v>0.49118125000000001</v>
@@ -8595,7 +8595,7 @@
         <v>49</v>
       </c>
       <c r="D77" t="s">
-        <v>82</v>
+        <v>66</v>
       </c>
       <c r="E77">
         <v>0.49118125000000001</v>
@@ -8763,7 +8763,7 @@
         <v>49</v>
       </c>
       <c r="D80" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E80">
         <v>0.49118125000000001</v>
@@ -8819,7 +8819,7 @@
         <v>49</v>
       </c>
       <c r="D81" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E81">
         <v>0.49118125000000001</v>
@@ -8875,7 +8875,7 @@
         <v>49</v>
       </c>
       <c r="D82" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="E82">
         <v>0.49118125000000001</v>
@@ -8931,7 +8931,7 @@
         <v>49</v>
       </c>
       <c r="D83" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="E83">
         <v>0.49118125000000001</v>
@@ -8987,7 +8987,7 @@
         <v>49</v>
       </c>
       <c r="D84" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E84">
         <v>0.49118125000000001</v>
@@ -9043,7 +9043,7 @@
         <v>49</v>
       </c>
       <c r="D85" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="E85">
         <v>0.49118125000000001</v>
@@ -9099,7 +9099,7 @@
         <v>49</v>
       </c>
       <c r="D86" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="E86">
         <v>0.49118125000000001</v>
@@ -9155,7 +9155,7 @@
         <v>49</v>
       </c>
       <c r="D87" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="E87">
         <v>0.49118125000000001</v>
@@ -9211,7 +9211,7 @@
         <v>49</v>
       </c>
       <c r="D88" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="E88">
         <v>0.49118125000000001</v>
@@ -9267,7 +9267,7 @@
         <v>49</v>
       </c>
       <c r="D89" t="s">
-        <v>62</v>
+        <v>79</v>
       </c>
       <c r="E89">
         <v>0.52272499999999988</v>
@@ -9323,7 +9323,7 @@
         <v>49</v>
       </c>
       <c r="D90" t="s">
-        <v>62</v>
+        <v>79</v>
       </c>
       <c r="E90">
         <v>0.49118125000000001</v>
@@ -9379,7 +9379,7 @@
         <v>49</v>
       </c>
       <c r="D91" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="E91">
         <v>0.49118125000000001</v>
@@ -9435,7 +9435,7 @@
         <v>49</v>
       </c>
       <c r="D92" t="s">
-        <v>76</v>
+        <v>62</v>
       </c>
       <c r="E92">
         <v>0.52272499999999988</v>
@@ -9491,7 +9491,7 @@
         <v>49</v>
       </c>
       <c r="D93" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E93">
         <v>0.49118125000000001</v>
@@ -9547,7 +9547,7 @@
         <v>49</v>
       </c>
       <c r="D94" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E94">
         <v>0.49118125000000001</v>
@@ -9603,7 +9603,7 @@
         <v>49</v>
       </c>
       <c r="D95" t="s">
-        <v>51</v>
+        <v>70</v>
       </c>
       <c r="E95">
         <v>0.49118125000000001</v>
@@ -9659,7 +9659,7 @@
         <v>49</v>
       </c>
       <c r="D96" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E96">
         <v>0.49118125000000001</v>
@@ -9715,7 +9715,7 @@
         <v>49</v>
       </c>
       <c r="D97" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="E97">
         <v>0.49118125000000001</v>
@@ -9827,7 +9827,7 @@
         <v>49</v>
       </c>
       <c r="D99" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="E99">
         <v>0.54075000000000006</v>
@@ -9883,7 +9883,7 @@
         <v>49</v>
       </c>
       <c r="D100" t="s">
-        <v>65</v>
+        <v>84</v>
       </c>
       <c r="E100">
         <v>0.54075000000000006</v>
@@ -9939,7 +9939,7 @@
         <v>49</v>
       </c>
       <c r="D101" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E101">
         <v>0.54075000000000006</v>
@@ -9995,7 +9995,7 @@
         <v>49</v>
       </c>
       <c r="D102" t="s">
-        <v>50</v>
+        <v>72</v>
       </c>
       <c r="E102">
         <v>0.49118125000000001</v>
@@ -10051,7 +10051,7 @@
         <v>49</v>
       </c>
       <c r="D103" t="s">
-        <v>50</v>
+        <v>72</v>
       </c>
       <c r="E103">
         <v>0.49118125000000001</v>
@@ -10107,7 +10107,7 @@
         <v>49</v>
       </c>
       <c r="D104" t="s">
-        <v>61</v>
+        <v>80</v>
       </c>
       <c r="E104">
         <v>0.49118125000000001</v>
@@ -10163,7 +10163,7 @@
         <v>49</v>
       </c>
       <c r="D105" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="E105">
         <v>0.49118125000000001</v>
@@ -10219,7 +10219,7 @@
         <v>49</v>
       </c>
       <c r="D106" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="E106">
         <v>0.450625</v>
@@ -10275,7 +10275,7 @@
         <v>49</v>
       </c>
       <c r="D107" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="E107">
         <v>0.450625</v>
@@ -10331,7 +10331,7 @@
         <v>49</v>
       </c>
       <c r="D108" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="E108">
         <v>0.47315625000000006</v>
@@ -10443,7 +10443,7 @@
         <v>49</v>
       </c>
       <c r="D110" t="s">
-        <v>72</v>
+        <v>55</v>
       </c>
       <c r="E110">
         <v>0.49118125000000001</v>
@@ -10499,7 +10499,7 @@
         <v>49</v>
       </c>
       <c r="D111" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E111">
         <v>0.46865000000000007</v>
@@ -10611,7 +10611,7 @@
         <v>49</v>
       </c>
       <c r="D113" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="E113">
         <v>0.49118125000000001</v>
@@ -11059,7 +11059,7 @@
         <v>49</v>
       </c>
       <c r="D121" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E121">
         <v>0.54075000000000006</v>
@@ -11115,7 +11115,7 @@
         <v>49</v>
       </c>
       <c r="D122" t="s">
-        <v>37</v>
+        <v>77</v>
       </c>
       <c r="E122">
         <v>0.54075000000000006</v>
@@ -11171,7 +11171,7 @@
         <v>49</v>
       </c>
       <c r="D123" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E123">
         <v>0.54075000000000006</v>
@@ -11227,7 +11227,7 @@
         <v>49</v>
       </c>
       <c r="D124" t="s">
-        <v>76</v>
+        <v>34</v>
       </c>
       <c r="E124">
         <v>0.54075000000000006</v>
@@ -11507,7 +11507,7 @@
         <v>49</v>
       </c>
       <c r="D129" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E129">
         <v>0.54075000000000006</v>
@@ -11731,7 +11731,7 @@
         <v>49</v>
       </c>
       <c r="D133" t="s">
-        <v>21</v>
+        <v>59</v>
       </c>
       <c r="E133">
         <v>0.54075000000000006</v>
@@ -11787,7 +11787,7 @@
         <v>49</v>
       </c>
       <c r="D134" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E134">
         <v>0.54075000000000006</v>
@@ -11899,7 +11899,7 @@
         <v>49</v>
       </c>
       <c r="D136" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E136">
         <v>0.54075000000000006</v>
@@ -11955,7 +11955,7 @@
         <v>49</v>
       </c>
       <c r="D137" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E137">
         <v>0.54075000000000006</v>
@@ -12011,7 +12011,7 @@
         <v>49</v>
       </c>
       <c r="D138" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E138">
         <v>0.54075000000000006</v>
@@ -12067,7 +12067,7 @@
         <v>49</v>
       </c>
       <c r="D139" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E139">
         <v>0.54075000000000006</v>
@@ -12123,7 +12123,7 @@
         <v>49</v>
       </c>
       <c r="D140" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E140">
         <v>0.54075000000000006</v>
@@ -12179,7 +12179,7 @@
         <v>49</v>
       </c>
       <c r="D141" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E141">
         <v>0.54075000000000006</v>
@@ -12235,7 +12235,7 @@
         <v>49</v>
       </c>
       <c r="D142" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E142">
         <v>0.54075000000000006</v>
@@ -12291,7 +12291,7 @@
         <v>49</v>
       </c>
       <c r="D143" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E143">
         <v>0.54075000000000006</v>
@@ -12347,7 +12347,7 @@
         <v>49</v>
       </c>
       <c r="D144" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E144">
         <v>0.54075000000000006</v>
@@ -12739,7 +12739,7 @@
         <v>49</v>
       </c>
       <c r="D151" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E151">
         <v>0.54075000000000006</v>
@@ -12795,7 +12795,7 @@
         <v>49</v>
       </c>
       <c r="D152" t="s">
-        <v>74</v>
+        <v>19</v>
       </c>
       <c r="E152">
         <v>0.54075000000000006</v>
@@ -12851,7 +12851,7 @@
         <v>49</v>
       </c>
       <c r="D153" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E153">
         <v>0.54075000000000006</v>
@@ -13019,7 +13019,7 @@
         <v>49</v>
       </c>
       <c r="D156" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E156">
         <v>0.54075000000000006</v>
@@ -13467,7 +13467,7 @@
         <v>49</v>
       </c>
       <c r="D164" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="E164">
         <v>0.48667500000000002</v>
@@ -14307,7 +14307,7 @@
         <v>49</v>
       </c>
       <c r="D179" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E179">
         <v>0.46865000000000007</v>
@@ -14363,7 +14363,7 @@
         <v>49</v>
       </c>
       <c r="D180" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E180">
         <v>0.46865000000000007</v>
@@ -14587,7 +14587,7 @@
         <v>49</v>
       </c>
       <c r="D184" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="E184">
         <v>0.48667500000000002</v>
@@ -14643,7 +14643,7 @@
         <v>49</v>
       </c>
       <c r="D185" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="E185">
         <v>0.48667500000000002</v>
@@ -15371,7 +15371,7 @@
         <v>49</v>
       </c>
       <c r="D198" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="E198">
         <v>0.50470000000000004</v>
@@ -15595,7 +15595,7 @@
         <v>49</v>
       </c>
       <c r="D202" t="s">
-        <v>65</v>
+        <v>84</v>
       </c>
       <c r="E202">
         <v>0.46865000000000007</v>
@@ -16323,7 +16323,7 @@
         <v>49</v>
       </c>
       <c r="D215" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="E215">
         <v>0.450625</v>
@@ -16491,7 +16491,7 @@
         <v>49</v>
       </c>
       <c r="D218" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E218">
         <v>0.50470000000000004</v>
@@ -16547,7 +16547,7 @@
         <v>49</v>
       </c>
       <c r="D219" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E219">
         <v>0.50470000000000004</v>
@@ -16715,7 +16715,7 @@
         <v>49</v>
       </c>
       <c r="D222" t="s">
-        <v>63</v>
+        <v>51</v>
       </c>
       <c r="E222">
         <v>0.450625</v>
@@ -16771,7 +16771,7 @@
         <v>49</v>
       </c>
       <c r="D223" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="E223">
         <v>0.29741250000000002</v>
@@ -16827,7 +16827,7 @@
         <v>49</v>
       </c>
       <c r="D224" t="s">
-        <v>62</v>
+        <v>79</v>
       </c>
       <c r="E224">
         <v>0.28839999999999999</v>
@@ -16883,7 +16883,7 @@
         <v>49</v>
       </c>
       <c r="D225" t="s">
-        <v>62</v>
+        <v>79</v>
       </c>
       <c r="E225">
         <v>0.28839999999999999</v>
@@ -16939,7 +16939,7 @@
         <v>49</v>
       </c>
       <c r="D226" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="E226">
         <v>0.24784375000000003</v>
@@ -17443,7 +17443,7 @@
         <v>49</v>
       </c>
       <c r="D235" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="E235">
         <v>0.25235000000000002</v>
@@ -17723,7 +17723,7 @@
         <v>49</v>
       </c>
       <c r="D240" t="s">
-        <v>62</v>
+        <v>79</v>
       </c>
       <c r="E240">
         <v>0.27938750000000001</v>
@@ -17835,7 +17835,7 @@
         <v>49</v>
       </c>
       <c r="D242" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="E242">
         <v>0.25235000000000002</v>
@@ -18031,7 +18031,7 @@
         <v>49</v>
       </c>
       <c r="D247" t="s">
-        <v>81</v>
+        <v>67</v>
       </c>
       <c r="E247">
         <v>0.32445000000000007</v>
@@ -18101,7 +18101,7 @@
         <v>49</v>
       </c>
       <c r="D249" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="E249">
         <v>0.32445000000000002</v>
@@ -18241,7 +18241,7 @@
         <v>49</v>
       </c>
       <c r="D253" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="E253">
         <v>0.27938750000000001</v>
@@ -18276,7 +18276,7 @@
         <v>49</v>
       </c>
       <c r="D254" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="E254">
         <v>0.27938750000000001</v>
@@ -18311,7 +18311,7 @@
         <v>49</v>
       </c>
       <c r="D255" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="E255">
         <v>0.27938750000000001</v>
@@ -18346,7 +18346,7 @@
         <v>49</v>
       </c>
       <c r="D256" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="E256">
         <v>0.31093124999999999</v>
@@ -18381,7 +18381,7 @@
         <v>49</v>
       </c>
       <c r="D257" t="s">
-        <v>66</v>
+        <v>83</v>
       </c>
       <c r="E257">
         <v>0.27938750000000001</v>
@@ -18416,7 +18416,7 @@
         <v>49</v>
       </c>
       <c r="D258" t="s">
-        <v>66</v>
+        <v>83</v>
       </c>
       <c r="E258">
         <v>0.27938750000000001</v>
@@ -18451,7 +18451,7 @@
         <v>49</v>
       </c>
       <c r="D259" t="s">
-        <v>72</v>
+        <v>55</v>
       </c>
       <c r="E259">
         <v>0.26136249999999994</v>
@@ -18486,7 +18486,7 @@
         <v>49</v>
       </c>
       <c r="D260" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="E260">
         <v>0.28839999999999999</v>
@@ -18521,7 +18521,7 @@
         <v>49</v>
       </c>
       <c r="D261" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="E261">
         <v>0.28839999999999999</v>
@@ -18556,7 +18556,7 @@
         <v>49</v>
       </c>
       <c r="D262" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="E262">
         <v>0.28839999999999999</v>
@@ -18626,7 +18626,7 @@
         <v>439</v>
       </c>
       <c r="D264" t="s">
-        <v>85</v>
+        <v>73</v>
       </c>
       <c r="E264">
         <v>0.41457500000000003</v>
@@ -18731,7 +18731,7 @@
         <v>439</v>
       </c>
       <c r="D267" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E267">
         <v>0.22981874999999999</v>
@@ -18766,7 +18766,7 @@
         <v>439</v>
       </c>
       <c r="D268" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="E268">
         <v>0.24333750000000001</v>
@@ -18941,7 +18941,7 @@
         <v>439</v>
       </c>
       <c r="D273" t="s">
-        <v>85</v>
+        <v>73</v>
       </c>
       <c r="E273">
         <v>0.27938750000000001</v>
@@ -19149,7 +19149,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8278635E-A0A5-4394-BD1F-13B024BBC90D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2ACDE4EF-75AA-4582-AACC-29C11C0F2FA8}">
   <dimension ref="B9:T842"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -19231,7 +19231,7 @@
         <v>2022</v>
       </c>
       <c r="F11">
-        <v>1.0679322033898306</v>
+        <v>0.39440677966101695</v>
       </c>
       <c r="G11">
         <v>0.36049999999999999</v>
@@ -19284,19 +19284,19 @@
         <v>2022</v>
       </c>
       <c r="F12">
-        <v>0.22450847457627116</v>
+        <v>0.51576271186440681</v>
       </c>
       <c r="G12">
-        <v>0.33990000000000004</v>
+        <v>0.36049999999999999</v>
       </c>
       <c r="H12">
-        <v>4427.5</v>
+        <v>3850.0000000000005</v>
       </c>
       <c r="I12">
-        <v>157.30000000000001</v>
+        <v>143</v>
       </c>
       <c r="J12">
-        <v>9.240000000000002</v>
+        <v>8.4</v>
       </c>
       <c r="K12">
         <v>50</v>
@@ -19337,13 +19337,13 @@
         <v>2022</v>
       </c>
       <c r="F13">
-        <v>0.35800000000000004</v>
+        <v>1.0679322033898306</v>
       </c>
       <c r="G13">
-        <v>0.36050000000000004</v>
+        <v>0.36049999999999999</v>
       </c>
       <c r="H13">
-        <v>3850.0000000000009</v>
+        <v>3850.0000000000005</v>
       </c>
       <c r="I13">
         <v>143</v>
@@ -19390,13 +19390,13 @@
         <v>2022</v>
       </c>
       <c r="F14">
-        <v>0.39440677966101695</v>
+        <v>0.35800000000000004</v>
       </c>
       <c r="G14">
-        <v>0.36049999999999999</v>
+        <v>0.36050000000000004</v>
       </c>
       <c r="H14">
-        <v>3850.0000000000005</v>
+        <v>3850.0000000000009</v>
       </c>
       <c r="I14">
         <v>143</v>
@@ -19496,19 +19496,19 @@
         <v>2022</v>
       </c>
       <c r="F16">
-        <v>0.51576271186440681</v>
+        <v>0.27911864406779663</v>
       </c>
       <c r="G16">
-        <v>0.36049999999999999</v>
+        <v>0.33990000000000004</v>
       </c>
       <c r="H16">
-        <v>3850.0000000000005</v>
+        <v>4427.5</v>
       </c>
       <c r="I16">
-        <v>143</v>
+        <v>157.30000000000001</v>
       </c>
       <c r="J16">
-        <v>8.4</v>
+        <v>9.240000000000002</v>
       </c>
       <c r="K16">
         <v>50</v>
@@ -19549,7 +19549,7 @@
         <v>2022</v>
       </c>
       <c r="F17">
-        <v>0.24877966101694915</v>
+        <v>0.22450847457627116</v>
       </c>
       <c r="G17">
         <v>0.33990000000000004</v>
@@ -19602,7 +19602,7 @@
         <v>2022</v>
       </c>
       <c r="F18">
-        <v>0.27911864406779663</v>
+        <v>0.24877966101694915</v>
       </c>
       <c r="G18">
         <v>0.33990000000000004</v>
@@ -19649,7 +19649,7 @@
         <v>13</v>
       </c>
       <c r="D19" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E19">
         <v>2008</v>
@@ -19702,7 +19702,7 @@
         <v>13</v>
       </c>
       <c r="D20" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="E20">
         <v>1998</v>
@@ -19808,7 +19808,7 @@
         <v>13</v>
       </c>
       <c r="D22" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E22">
         <v>2001</v>
@@ -19861,7 +19861,7 @@
         <v>13</v>
       </c>
       <c r="D23" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E23">
         <v>2013</v>
@@ -19914,7 +19914,7 @@
         <v>13</v>
       </c>
       <c r="D24" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E24">
         <v>1965</v>
@@ -19967,7 +19967,7 @@
         <v>13</v>
       </c>
       <c r="D25" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E25">
         <v>2003</v>
@@ -20020,7 +20020,7 @@
         <v>13</v>
       </c>
       <c r="D26" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E26">
         <v>2009</v>
@@ -20126,7 +20126,7 @@
         <v>13</v>
       </c>
       <c r="D28" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E28">
         <v>2009</v>
@@ -20185,19 +20185,19 @@
         <v>2022</v>
       </c>
       <c r="F29">
-        <v>0.1997687861271675</v>
+        <v>0.61803468208092449</v>
       </c>
       <c r="G29">
-        <v>0.35020000000000007</v>
+        <v>0.37080000000000002</v>
       </c>
       <c r="H29">
-        <v>2530</v>
+        <v>2200</v>
       </c>
       <c r="I29">
-        <v>72.600000000000009</v>
+        <v>66</v>
       </c>
       <c r="J29">
-        <v>5.7750000000000004</v>
+        <v>5.25</v>
       </c>
       <c r="K29">
         <v>50</v>
@@ -20238,19 +20238,19 @@
         <v>2022</v>
       </c>
       <c r="F30">
-        <v>0.61803468208092449</v>
+        <v>0.18416184971098257</v>
       </c>
       <c r="G30">
-        <v>0.37080000000000002</v>
+        <v>0.35020000000000001</v>
       </c>
       <c r="H30">
-        <v>2200</v>
+        <v>2530</v>
       </c>
       <c r="I30">
-        <v>66</v>
+        <v>72.600000000000009</v>
       </c>
       <c r="J30">
-        <v>5.25</v>
+        <v>5.7750000000000004</v>
       </c>
       <c r="K30">
         <v>50</v>
@@ -20291,19 +20291,19 @@
         <v>2022</v>
       </c>
       <c r="F31">
-        <v>0.18416184971098257</v>
+        <v>0.61803468208092449</v>
       </c>
       <c r="G31">
-        <v>0.35020000000000001</v>
+        <v>0.37080000000000002</v>
       </c>
       <c r="H31">
-        <v>2530</v>
+        <v>2200</v>
       </c>
       <c r="I31">
-        <v>72.600000000000009</v>
+        <v>66</v>
       </c>
       <c r="J31">
-        <v>5.7750000000000004</v>
+        <v>5.25</v>
       </c>
       <c r="K31">
         <v>50</v>
@@ -20344,19 +20344,19 @@
         <v>2022</v>
       </c>
       <c r="F32">
-        <v>0.61803468208092449</v>
+        <v>0.1997687861271675</v>
       </c>
       <c r="G32">
-        <v>0.37080000000000002</v>
+        <v>0.35020000000000007</v>
       </c>
       <c r="H32">
-        <v>2200</v>
+        <v>2530</v>
       </c>
       <c r="I32">
-        <v>66</v>
+        <v>72.600000000000009</v>
       </c>
       <c r="J32">
-        <v>5.25</v>
+        <v>5.7750000000000004</v>
       </c>
       <c r="K32">
         <v>50</v>
@@ -20391,7 +20391,7 @@
         <v>33</v>
       </c>
       <c r="D33" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="E33">
         <v>1992</v>
@@ -20444,7 +20444,7 @@
         <v>33</v>
       </c>
       <c r="D34" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="E34">
         <v>1993</v>
@@ -20497,7 +20497,7 @@
         <v>33</v>
       </c>
       <c r="D35" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E35">
         <v>2005</v>
@@ -20550,7 +20550,7 @@
         <v>33</v>
       </c>
       <c r="D36" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E36">
         <v>1986</v>
@@ -20603,7 +20603,7 @@
         <v>33</v>
       </c>
       <c r="D37" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E37">
         <v>1991</v>
@@ -20656,7 +20656,7 @@
         <v>33</v>
       </c>
       <c r="D38" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E38">
         <v>1992</v>
@@ -20709,7 +20709,7 @@
         <v>33</v>
       </c>
       <c r="D39" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E39">
         <v>1993</v>
@@ -20762,7 +20762,7 @@
         <v>33</v>
       </c>
       <c r="D40" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E40">
         <v>2009</v>
@@ -20815,7 +20815,7 @@
         <v>33</v>
       </c>
       <c r="D41" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E41">
         <v>2010</v>
@@ -20868,7 +20868,7 @@
         <v>33</v>
       </c>
       <c r="D42" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E42">
         <v>2010</v>
@@ -20927,7 +20927,7 @@
         <v>2022</v>
       </c>
       <c r="F43">
-        <v>0.18824049497996109</v>
+        <v>0.20557907614758497</v>
       </c>
       <c r="G43">
         <v>0.59739999999999993</v>
@@ -20980,7 +20980,7 @@
         <v>2022</v>
       </c>
       <c r="F44">
-        <v>0.21113131843159935</v>
+        <v>0.20212110068999706</v>
       </c>
       <c r="G44">
         <v>0.59739999999999993</v>
@@ -21033,7 +21033,7 @@
         <v>2022</v>
       </c>
       <c r="F45">
-        <v>0.29344087509812827</v>
+        <v>0.19481551873734657</v>
       </c>
       <c r="G45">
         <v>0.59739999999999993</v>
@@ -21086,19 +21086,19 @@
         <v>2022</v>
       </c>
       <c r="F46">
-        <v>0.37112356319464518</v>
+        <v>0.18702289798785268</v>
       </c>
       <c r="G46">
-        <v>0.61799999999999999</v>
+        <v>0.59739999999999993</v>
       </c>
       <c r="H46">
-        <v>1100</v>
+        <v>1265</v>
       </c>
       <c r="I46">
-        <v>33</v>
+        <v>36.300000000000004</v>
       </c>
       <c r="J46">
-        <v>3.1500000000000004</v>
+        <v>3.4650000000000003</v>
       </c>
       <c r="K46">
         <v>50</v>
@@ -21139,7 +21139,7 @@
         <v>2022</v>
       </c>
       <c r="F47">
-        <v>0.20557907614758497</v>
+        <v>0.27347228442755023</v>
       </c>
       <c r="G47">
         <v>0.59739999999999993</v>
@@ -21192,7 +21192,7 @@
         <v>2022</v>
       </c>
       <c r="F48">
-        <v>0.26543614427963469</v>
+        <v>0.1548783373961905</v>
       </c>
       <c r="G48">
         <v>0.59739999999999993</v>
@@ -21204,7 +21204,7 @@
         <v>36.300000000000004</v>
       </c>
       <c r="J48">
-        <v>3.4650000000000003</v>
+        <v>3.4649999999999999</v>
       </c>
       <c r="K48">
         <v>50</v>
@@ -21245,7 +21245,7 @@
         <v>2022</v>
       </c>
       <c r="F49">
-        <v>0.19481551873734657</v>
+        <v>0.21551466760318963</v>
       </c>
       <c r="G49">
         <v>0.59739999999999993</v>
@@ -21298,7 +21298,7 @@
         <v>2022</v>
       </c>
       <c r="F50">
-        <v>0.19481551873734657</v>
+        <v>0.29344087509812827</v>
       </c>
       <c r="G50">
         <v>0.59739999999999993</v>
@@ -21351,7 +21351,7 @@
         <v>2022</v>
       </c>
       <c r="F51">
-        <v>0.21551466760318963</v>
+        <v>0.20820908565053911</v>
       </c>
       <c r="G51">
         <v>0.59739999999999993</v>
@@ -21363,7 +21363,7 @@
         <v>36.300000000000004</v>
       </c>
       <c r="J51">
-        <v>3.4650000000000003</v>
+        <v>3.4650000000000007</v>
       </c>
       <c r="K51">
         <v>50</v>
@@ -21398,13 +21398,13 @@
         <v>49</v>
       </c>
       <c r="D52" t="s">
-        <v>21</v>
+        <v>59</v>
       </c>
       <c r="E52">
         <v>2022</v>
       </c>
       <c r="F52">
-        <v>0.19822479031525012</v>
+        <v>0.18629233979258764</v>
       </c>
       <c r="G52">
         <v>0.59739999999999993</v>
@@ -21451,13 +21451,13 @@
         <v>49</v>
       </c>
       <c r="D53" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E53">
         <v>2022</v>
       </c>
       <c r="F53">
-        <v>0.18702289798785268</v>
+        <v>0.20236462008841874</v>
       </c>
       <c r="G53">
         <v>0.59739999999999993</v>
@@ -21504,13 +21504,13 @@
         <v>49</v>
       </c>
       <c r="D54" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E54">
         <v>2022</v>
       </c>
       <c r="F54">
-        <v>0.19481551873734657</v>
+        <v>0.17484692806676855</v>
       </c>
       <c r="G54">
         <v>0.59739999999999993</v>
@@ -21557,13 +21557,13 @@
         <v>49</v>
       </c>
       <c r="D55" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E55">
         <v>2022</v>
       </c>
       <c r="F55">
-        <v>0.28443065735652601</v>
+        <v>0.18872753377680451</v>
       </c>
       <c r="G55">
         <v>0.59739999999999993</v>
@@ -21575,7 +21575,7 @@
         <v>36.300000000000004</v>
       </c>
       <c r="J55">
-        <v>3.4650000000000003</v>
+        <v>3.4650000000000007</v>
       </c>
       <c r="K55">
         <v>50</v>
@@ -21610,25 +21610,25 @@
         <v>49</v>
       </c>
       <c r="D56" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E56">
         <v>2022</v>
       </c>
       <c r="F56">
-        <v>0.39839773581787374</v>
+        <v>0.19481551873734657</v>
       </c>
       <c r="G56">
-        <v>0.61799999999999999</v>
+        <v>0.59739999999999993</v>
       </c>
       <c r="H56">
-        <v>1100</v>
+        <v>1265</v>
       </c>
       <c r="I56">
-        <v>33</v>
+        <v>36.300000000000004</v>
       </c>
       <c r="J56">
-        <v>3.1500000000000004</v>
+        <v>3.4650000000000003</v>
       </c>
       <c r="K56">
         <v>50</v>
@@ -21663,13 +21663,13 @@
         <v>49</v>
       </c>
       <c r="D57" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E57">
         <v>2022</v>
       </c>
       <c r="F57">
-        <v>0.20212110068999706</v>
+        <v>0.22793415692269547</v>
       </c>
       <c r="G57">
         <v>0.59739999999999993</v>
@@ -21716,13 +21716,13 @@
         <v>49</v>
       </c>
       <c r="D58" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E58">
         <v>2022</v>
       </c>
       <c r="F58">
-        <v>0.21283595422055113</v>
+        <v>0.19481551873734657</v>
       </c>
       <c r="G58">
         <v>0.59739999999999993</v>
@@ -21769,13 +21769,13 @@
         <v>49</v>
       </c>
       <c r="D59" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E59">
         <v>2022</v>
       </c>
       <c r="F59">
-        <v>0.23864901045324952</v>
+        <v>0.18556178159732259</v>
       </c>
       <c r="G59">
         <v>0.59739999999999993</v>
@@ -21822,25 +21822,25 @@
         <v>49</v>
       </c>
       <c r="D60" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E60">
         <v>2022</v>
       </c>
       <c r="F60">
-        <v>0.31243538817501959</v>
+        <v>0.23280454489112914</v>
       </c>
       <c r="G60">
-        <v>0.61799999999999999</v>
+        <v>0.59739999999999993</v>
       </c>
       <c r="H60">
-        <v>1100</v>
+        <v>1265</v>
       </c>
       <c r="I60">
-        <v>33</v>
+        <v>36.300000000000004</v>
       </c>
       <c r="J60">
-        <v>3.1500000000000004</v>
+        <v>3.4650000000000007</v>
       </c>
       <c r="K60">
         <v>50</v>
@@ -21875,13 +21875,13 @@
         <v>49</v>
       </c>
       <c r="D61" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E61">
         <v>2022</v>
       </c>
       <c r="F61">
-        <v>0.19481551873734657</v>
+        <v>0.26604494277568891</v>
       </c>
       <c r="G61">
         <v>0.59739999999999993</v>
@@ -21928,13 +21928,13 @@
         <v>49</v>
       </c>
       <c r="D62" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E62">
         <v>2022</v>
       </c>
       <c r="F62">
-        <v>0.20820908565053911</v>
+        <v>0.19481551873734657</v>
       </c>
       <c r="G62">
         <v>0.59739999999999993</v>
@@ -21946,7 +21946,7 @@
         <v>36.300000000000004</v>
       </c>
       <c r="J62">
-        <v>3.4650000000000007</v>
+        <v>3.4650000000000003</v>
       </c>
       <c r="K62">
         <v>50</v>
@@ -21981,13 +21981,13 @@
         <v>49</v>
       </c>
       <c r="D63" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E63">
         <v>2022</v>
       </c>
       <c r="F63">
-        <v>0.18629233979258764</v>
+        <v>0.21113131843159935</v>
       </c>
       <c r="G63">
         <v>0.59739999999999993</v>
@@ -22034,13 +22034,13 @@
         <v>49</v>
       </c>
       <c r="D64" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E64">
         <v>2022</v>
       </c>
       <c r="F64">
-        <v>0.20236462008841874</v>
+        <v>0.19627663512787666</v>
       </c>
       <c r="G64">
         <v>0.59739999999999993</v>
@@ -22052,7 +22052,7 @@
         <v>36.300000000000004</v>
       </c>
       <c r="J64">
-        <v>3.4650000000000003</v>
+        <v>3.4649999999999999</v>
       </c>
       <c r="K64">
         <v>50</v>
@@ -22087,13 +22087,13 @@
         <v>49</v>
       </c>
       <c r="D65" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E65">
         <v>2022</v>
       </c>
       <c r="F65">
-        <v>0.22793415692269547</v>
+        <v>0.18824049497996109</v>
       </c>
       <c r="G65">
         <v>0.59739999999999993</v>
@@ -22140,25 +22140,25 @@
         <v>49</v>
       </c>
       <c r="D66" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E66">
         <v>2022</v>
       </c>
       <c r="F66">
-        <v>0.1548783373961905</v>
+        <v>0.43468212618270452</v>
       </c>
       <c r="G66">
-        <v>0.59739999999999993</v>
+        <v>0.61799999999999988</v>
       </c>
       <c r="H66">
-        <v>1265</v>
+        <v>1100</v>
       </c>
       <c r="I66">
-        <v>36.300000000000004</v>
+        <v>33</v>
       </c>
       <c r="J66">
-        <v>3.4649999999999999</v>
+        <v>3.1500000000000004</v>
       </c>
       <c r="K66">
         <v>50</v>
@@ -22193,25 +22193,25 @@
         <v>49</v>
       </c>
       <c r="D67" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E67">
         <v>2022</v>
       </c>
       <c r="F67">
-        <v>0.49339465314217229</v>
+        <v>0.21283595422055113</v>
       </c>
       <c r="G67">
-        <v>0.61799999999999999</v>
+        <v>0.59739999999999993</v>
       </c>
       <c r="H67">
-        <v>1100</v>
+        <v>1265</v>
       </c>
       <c r="I67">
-        <v>33</v>
+        <v>36.300000000000004</v>
       </c>
       <c r="J67">
-        <v>3.1500000000000004</v>
+        <v>3.4650000000000003</v>
       </c>
       <c r="K67">
         <v>50</v>
@@ -22246,13 +22246,13 @@
         <v>49</v>
       </c>
       <c r="D68" t="s">
-        <v>74</v>
+        <v>19</v>
       </c>
       <c r="E68">
         <v>2022</v>
       </c>
       <c r="F68">
-        <v>0.27347228442755023</v>
+        <v>0.19822479031525012</v>
       </c>
       <c r="G68">
         <v>0.59739999999999993</v>
@@ -22305,19 +22305,19 @@
         <v>2022</v>
       </c>
       <c r="F69">
-        <v>0.17484692806676855</v>
+        <v>0.30829555840185086</v>
       </c>
       <c r="G69">
-        <v>0.59739999999999993</v>
+        <v>0.61799999999999999</v>
       </c>
       <c r="H69">
-        <v>1265</v>
+        <v>1100</v>
       </c>
       <c r="I69">
-        <v>36.300000000000004</v>
+        <v>33</v>
       </c>
       <c r="J69">
-        <v>3.4650000000000003</v>
+        <v>3.1500000000000004</v>
       </c>
       <c r="K69">
         <v>50</v>
@@ -22352,13 +22352,13 @@
         <v>49</v>
       </c>
       <c r="D70" t="s">
-        <v>76</v>
+        <v>34</v>
       </c>
       <c r="E70">
         <v>2022</v>
       </c>
       <c r="F70">
-        <v>0.18872753377680451</v>
+        <v>0.27761211420071885</v>
       </c>
       <c r="G70">
         <v>0.59739999999999993</v>
@@ -22370,7 +22370,7 @@
         <v>36.300000000000004</v>
       </c>
       <c r="J70">
-        <v>3.4650000000000007</v>
+        <v>3.4650000000000003</v>
       </c>
       <c r="K70">
         <v>50</v>
@@ -22405,13 +22405,13 @@
         <v>49</v>
       </c>
       <c r="D71" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E71">
         <v>2022</v>
       </c>
       <c r="F71">
-        <v>0.30829555840185086</v>
+        <v>0.3567559186877659</v>
       </c>
       <c r="G71">
         <v>0.61799999999999999</v>
@@ -22458,13 +22458,13 @@
         <v>49</v>
       </c>
       <c r="D72" t="s">
-        <v>37</v>
+        <v>77</v>
       </c>
       <c r="E72">
         <v>2022</v>
       </c>
       <c r="F72">
-        <v>0.27761211420071885</v>
+        <v>0.18507474280047922</v>
       </c>
       <c r="G72">
         <v>0.59739999999999993</v>
@@ -22476,7 +22476,7 @@
         <v>36.300000000000004</v>
       </c>
       <c r="J72">
-        <v>3.4650000000000003</v>
+        <v>3.4649999999999999</v>
       </c>
       <c r="K72">
         <v>50</v>
@@ -22517,19 +22517,19 @@
         <v>2022</v>
       </c>
       <c r="F73">
-        <v>0.3567559186877659</v>
+        <v>0.19676367392472002</v>
       </c>
       <c r="G73">
-        <v>0.61799999999999999</v>
+        <v>0.59739999999999993</v>
       </c>
       <c r="H73">
-        <v>1100</v>
+        <v>1265</v>
       </c>
       <c r="I73">
-        <v>33</v>
+        <v>36.300000000000004</v>
       </c>
       <c r="J73">
-        <v>3.1500000000000004</v>
+        <v>3.4650000000000003</v>
       </c>
       <c r="K73">
         <v>50</v>
@@ -22570,7 +22570,7 @@
         <v>2022</v>
       </c>
       <c r="F74">
-        <v>0.45732943023592104</v>
+        <v>0.39839773581787374</v>
       </c>
       <c r="G74">
         <v>0.61799999999999999</v>
@@ -22623,7 +22623,7 @@
         <v>2022</v>
       </c>
       <c r="F75">
-        <v>0.26604494277568891</v>
+        <v>0.28443065735652601</v>
       </c>
       <c r="G75">
         <v>0.59739999999999993</v>
@@ -22676,19 +22676,19 @@
         <v>2022</v>
       </c>
       <c r="F76">
-        <v>0.23280454489112914</v>
+        <v>0.49339465314217229</v>
       </c>
       <c r="G76">
-        <v>0.59739999999999993</v>
+        <v>0.61799999999999999</v>
       </c>
       <c r="H76">
-        <v>1265</v>
+        <v>1100</v>
       </c>
       <c r="I76">
-        <v>36.300000000000004</v>
+        <v>33</v>
       </c>
       <c r="J76">
-        <v>3.4650000000000007</v>
+        <v>3.1500000000000004</v>
       </c>
       <c r="K76">
         <v>50</v>
@@ -22729,19 +22729,19 @@
         <v>2022</v>
       </c>
       <c r="F77">
-        <v>0.18556178159732259</v>
+        <v>0.45732943023592104</v>
       </c>
       <c r="G77">
-        <v>0.59739999999999993</v>
+        <v>0.61799999999999999</v>
       </c>
       <c r="H77">
-        <v>1265</v>
+        <v>1100</v>
       </c>
       <c r="I77">
-        <v>36.300000000000004</v>
+        <v>33</v>
       </c>
       <c r="J77">
-        <v>3.4650000000000003</v>
+        <v>3.1500000000000004</v>
       </c>
       <c r="K77">
         <v>50</v>
@@ -22782,19 +22782,19 @@
         <v>2022</v>
       </c>
       <c r="F78">
-        <v>0.16608022972358796</v>
+        <v>0.31243538817501959</v>
       </c>
       <c r="G78">
-        <v>0.59739999999999993</v>
+        <v>0.61799999999999999</v>
       </c>
       <c r="H78">
-        <v>1265</v>
+        <v>1100</v>
       </c>
       <c r="I78">
-        <v>36.300000000000004</v>
+        <v>33</v>
       </c>
       <c r="J78">
-        <v>3.4650000000000003</v>
+        <v>3.1500000000000004</v>
       </c>
       <c r="K78">
         <v>50</v>
@@ -22835,7 +22835,7 @@
         <v>2022</v>
       </c>
       <c r="F79">
-        <v>0.19676367392472002</v>
+        <v>0.23864901045324952</v>
       </c>
       <c r="G79">
         <v>0.59739999999999993</v>
@@ -22888,10 +22888,10 @@
         <v>2022</v>
       </c>
       <c r="F80">
-        <v>0.43468212618270452</v>
+        <v>0.37112356319464518</v>
       </c>
       <c r="G80">
-        <v>0.61799999999999988</v>
+        <v>0.61799999999999999</v>
       </c>
       <c r="H80">
         <v>1100</v>
@@ -22941,7 +22941,7 @@
         <v>2022</v>
       </c>
       <c r="F81">
-        <v>0.18507474280047922</v>
+        <v>0.16608022972358796</v>
       </c>
       <c r="G81">
         <v>0.59739999999999993</v>
@@ -22953,7 +22953,7 @@
         <v>36.300000000000004</v>
       </c>
       <c r="J81">
-        <v>3.4649999999999999</v>
+        <v>3.4650000000000003</v>
       </c>
       <c r="K81">
         <v>50</v>
@@ -22994,7 +22994,7 @@
         <v>2022</v>
       </c>
       <c r="F82">
-        <v>0.19627663512787666</v>
+        <v>0.26543614427963469</v>
       </c>
       <c r="G82">
         <v>0.59739999999999993</v>
@@ -23006,7 +23006,7 @@
         <v>36.300000000000004</v>
       </c>
       <c r="J82">
-        <v>3.4649999999999999</v>
+        <v>3.4650000000000003</v>
       </c>
       <c r="K82">
         <v>50</v>
@@ -23041,7 +23041,7 @@
         <v>49</v>
       </c>
       <c r="D83" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="E83">
         <v>2006</v>
@@ -23094,7 +23094,7 @@
         <v>49</v>
       </c>
       <c r="D84" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="E84">
         <v>2012</v>
@@ -23147,7 +23147,7 @@
         <v>49</v>
       </c>
       <c r="D85" t="s">
-        <v>85</v>
+        <v>73</v>
       </c>
       <c r="E85">
         <v>1993</v>
@@ -23200,7 +23200,7 @@
         <v>49</v>
       </c>
       <c r="D86" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="E86">
         <v>2011</v>
@@ -23253,7 +23253,7 @@
         <v>49</v>
       </c>
       <c r="D87" t="s">
-        <v>66</v>
+        <v>83</v>
       </c>
       <c r="E87">
         <v>2005</v>
@@ -23306,7 +23306,7 @@
         <v>49</v>
       </c>
       <c r="D88" t="s">
-        <v>66</v>
+        <v>83</v>
       </c>
       <c r="E88">
         <v>2006</v>
@@ -23359,7 +23359,7 @@
         <v>49</v>
       </c>
       <c r="D89" t="s">
-        <v>66</v>
+        <v>83</v>
       </c>
       <c r="E89">
         <v>2006</v>
@@ -23465,7 +23465,7 @@
         <v>49</v>
       </c>
       <c r="D91" t="s">
-        <v>81</v>
+        <v>67</v>
       </c>
       <c r="E91">
         <v>2003</v>
@@ -23624,7 +23624,7 @@
         <v>49</v>
       </c>
       <c r="D94" t="s">
-        <v>74</v>
+        <v>54</v>
       </c>
       <c r="E94">
         <v>2004</v>
@@ -23677,7 +23677,7 @@
         <v>49</v>
       </c>
       <c r="D95" t="s">
-        <v>74</v>
+        <v>54</v>
       </c>
       <c r="E95">
         <v>2005</v>
@@ -23730,7 +23730,7 @@
         <v>49</v>
       </c>
       <c r="D96" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="E96">
         <v>2005</v>
@@ -23783,7 +23783,7 @@
         <v>49</v>
       </c>
       <c r="D97" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="E97">
         <v>2005</v>
@@ -23836,7 +23836,7 @@
         <v>49</v>
       </c>
       <c r="D98" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E98">
         <v>2004</v>
@@ -23889,7 +23889,7 @@
         <v>49</v>
       </c>
       <c r="D99" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E99">
         <v>2004</v>
@@ -23942,7 +23942,7 @@
         <v>49</v>
       </c>
       <c r="D100" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E100">
         <v>2004</v>
@@ -23995,7 +23995,7 @@
         <v>49</v>
       </c>
       <c r="D101" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="E101">
         <v>2008</v>
@@ -24048,7 +24048,7 @@
         <v>49</v>
       </c>
       <c r="D102" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="E102">
         <v>2008</v>
@@ -24101,7 +24101,7 @@
         <v>49</v>
       </c>
       <c r="D103" t="s">
-        <v>53</v>
+        <v>85</v>
       </c>
       <c r="E103">
         <v>2002</v>
@@ -24154,7 +24154,7 @@
         <v>49</v>
       </c>
       <c r="D104" t="s">
-        <v>53</v>
+        <v>85</v>
       </c>
       <c r="E104">
         <v>2002</v>
@@ -24207,7 +24207,7 @@
         <v>49</v>
       </c>
       <c r="D105" t="s">
-        <v>53</v>
+        <v>85</v>
       </c>
       <c r="E105">
         <v>2003</v>
@@ -24260,7 +24260,7 @@
         <v>49</v>
       </c>
       <c r="D106" t="s">
-        <v>53</v>
+        <v>85</v>
       </c>
       <c r="E106">
         <v>2003</v>
@@ -24313,7 +24313,7 @@
         <v>49</v>
       </c>
       <c r="D107" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="E107">
         <v>2000</v>
@@ -24366,7 +24366,7 @@
         <v>49</v>
       </c>
       <c r="D108" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="E108">
         <v>2000</v>
@@ -24419,7 +24419,7 @@
         <v>49</v>
       </c>
       <c r="D109" t="s">
-        <v>76</v>
+        <v>62</v>
       </c>
       <c r="E109">
         <v>2007</v>
@@ -24472,7 +24472,7 @@
         <v>49</v>
       </c>
       <c r="D110" t="s">
-        <v>85</v>
+        <v>73</v>
       </c>
       <c r="E110">
         <v>2023</v>
@@ -24525,7 +24525,7 @@
         <v>49</v>
       </c>
       <c r="D111" t="s">
-        <v>85</v>
+        <v>73</v>
       </c>
       <c r="E111">
         <v>2001</v>
@@ -24631,7 +24631,7 @@
         <v>49</v>
       </c>
       <c r="D113" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="E113">
         <v>2010</v>
@@ -24684,7 +24684,7 @@
         <v>49</v>
       </c>
       <c r="D114" t="s">
-        <v>63</v>
+        <v>51</v>
       </c>
       <c r="E114">
         <v>2005</v>
@@ -24737,7 +24737,7 @@
         <v>49</v>
       </c>
       <c r="D115" t="s">
-        <v>63</v>
+        <v>51</v>
       </c>
       <c r="E115">
         <v>2009</v>
@@ -24790,7 +24790,7 @@
         <v>49</v>
       </c>
       <c r="D116" t="s">
-        <v>55</v>
+        <v>87</v>
       </c>
       <c r="E116">
         <v>1997</v>
@@ -24843,7 +24843,7 @@
         <v>49</v>
       </c>
       <c r="D117" t="s">
-        <v>55</v>
+        <v>87</v>
       </c>
       <c r="E117">
         <v>1997</v>
@@ -24896,7 +24896,7 @@
         <v>49</v>
       </c>
       <c r="D118" t="s">
-        <v>55</v>
+        <v>87</v>
       </c>
       <c r="E118">
         <v>1998</v>
@@ -24949,7 +24949,7 @@
         <v>49</v>
       </c>
       <c r="D119" t="s">
-        <v>55</v>
+        <v>87</v>
       </c>
       <c r="E119">
         <v>1999</v>
@@ -25055,7 +25055,7 @@
         <v>49</v>
       </c>
       <c r="D121" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="E121">
         <v>2010</v>
@@ -25108,7 +25108,7 @@
         <v>49</v>
       </c>
       <c r="D122" t="s">
-        <v>61</v>
+        <v>80</v>
       </c>
       <c r="E122">
         <v>2003</v>
@@ -25161,7 +25161,7 @@
         <v>49</v>
       </c>
       <c r="D123" t="s">
-        <v>61</v>
+        <v>80</v>
       </c>
       <c r="E123">
         <v>2003</v>
@@ -25214,7 +25214,7 @@
         <v>49</v>
       </c>
       <c r="D124" t="s">
-        <v>87</v>
+        <v>71</v>
       </c>
       <c r="E124">
         <v>2006</v>
@@ -25373,7 +25373,7 @@
         <v>49</v>
       </c>
       <c r="D127" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="E127">
         <v>2002</v>
@@ -25426,7 +25426,7 @@
         <v>49</v>
       </c>
       <c r="D128" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="E128">
         <v>2002</v>
@@ -25479,7 +25479,7 @@
         <v>49</v>
       </c>
       <c r="D129" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="E129">
         <v>2010</v>
@@ -25532,7 +25532,7 @@
         <v>49</v>
       </c>
       <c r="D130" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="E130">
         <v>2010</v>
@@ -25585,7 +25585,7 @@
         <v>49</v>
       </c>
       <c r="D131" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="E131">
         <v>2008</v>
@@ -25638,7 +25638,7 @@
         <v>49</v>
       </c>
       <c r="D132" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="E132">
         <v>2008</v>
@@ -25691,7 +25691,7 @@
         <v>49</v>
       </c>
       <c r="D133" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="E133">
         <v>2018</v>
@@ -25744,7 +25744,7 @@
         <v>49</v>
       </c>
       <c r="D134" t="s">
-        <v>82</v>
+        <v>66</v>
       </c>
       <c r="E134">
         <v>2006</v>
@@ -25797,7 +25797,7 @@
         <v>49</v>
       </c>
       <c r="D135" t="s">
-        <v>82</v>
+        <v>66</v>
       </c>
       <c r="E135">
         <v>2007</v>
@@ -25956,7 +25956,7 @@
         <v>49</v>
       </c>
       <c r="D138" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E138">
         <v>2010</v>
@@ -26009,7 +26009,7 @@
         <v>49</v>
       </c>
       <c r="D139" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E139">
         <v>2010</v>
@@ -26062,7 +26062,7 @@
         <v>49</v>
       </c>
       <c r="D140" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="E140">
         <v>2004</v>
@@ -26115,7 +26115,7 @@
         <v>49</v>
       </c>
       <c r="D141" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="E141">
         <v>2004</v>
@@ -26168,7 +26168,7 @@
         <v>49</v>
       </c>
       <c r="D142" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E142">
         <v>2008</v>
@@ -26221,7 +26221,7 @@
         <v>49</v>
       </c>
       <c r="D143" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="E143">
         <v>2007</v>
@@ -26274,7 +26274,7 @@
         <v>49</v>
       </c>
       <c r="D144" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="E144">
         <v>2007</v>
@@ -26327,7 +26327,7 @@
         <v>49</v>
       </c>
       <c r="D145" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="E145">
         <v>2005</v>
@@ -26380,7 +26380,7 @@
         <v>49</v>
       </c>
       <c r="D146" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="E146">
         <v>2005</v>
@@ -26433,7 +26433,7 @@
         <v>49</v>
       </c>
       <c r="D147" t="s">
-        <v>62</v>
+        <v>79</v>
       </c>
       <c r="E147">
         <v>2015</v>
@@ -26486,7 +26486,7 @@
         <v>49</v>
       </c>
       <c r="D148" t="s">
-        <v>62</v>
+        <v>79</v>
       </c>
       <c r="E148">
         <v>2004</v>
@@ -26539,7 +26539,7 @@
         <v>49</v>
       </c>
       <c r="D149" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="E149">
         <v>2006</v>
@@ -26592,7 +26592,7 @@
         <v>49</v>
       </c>
       <c r="D150" t="s">
-        <v>76</v>
+        <v>62</v>
       </c>
       <c r="E150">
         <v>2011</v>
@@ -26645,7 +26645,7 @@
         <v>49</v>
       </c>
       <c r="D151" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E151">
         <v>2004</v>
@@ -26698,7 +26698,7 @@
         <v>49</v>
       </c>
       <c r="D152" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E152">
         <v>2005</v>
@@ -26751,7 +26751,7 @@
         <v>49</v>
       </c>
       <c r="D153" t="s">
-        <v>51</v>
+        <v>70</v>
       </c>
       <c r="E153">
         <v>2006</v>
@@ -26804,7 +26804,7 @@
         <v>49</v>
       </c>
       <c r="D154" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E154">
         <v>2008</v>
@@ -26857,7 +26857,7 @@
         <v>49</v>
       </c>
       <c r="D155" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="E155">
         <v>2007</v>
@@ -26963,7 +26963,7 @@
         <v>49</v>
       </c>
       <c r="D157" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="E157">
         <v>2023</v>
@@ -27016,7 +27016,7 @@
         <v>49</v>
       </c>
       <c r="D158" t="s">
-        <v>65</v>
+        <v>84</v>
       </c>
       <c r="E158">
         <v>2026</v>
@@ -27069,7 +27069,7 @@
         <v>49</v>
       </c>
       <c r="D159" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E159">
         <v>2022</v>
@@ -27122,7 +27122,7 @@
         <v>49</v>
       </c>
       <c r="D160" t="s">
-        <v>50</v>
+        <v>72</v>
       </c>
       <c r="E160">
         <v>2003</v>
@@ -27175,7 +27175,7 @@
         <v>49</v>
       </c>
       <c r="D161" t="s">
-        <v>50</v>
+        <v>72</v>
       </c>
       <c r="E161">
         <v>2003</v>
@@ -27228,7 +27228,7 @@
         <v>49</v>
       </c>
       <c r="D162" t="s">
-        <v>61</v>
+        <v>80</v>
       </c>
       <c r="E162">
         <v>2003</v>
@@ -27281,7 +27281,7 @@
         <v>49</v>
       </c>
       <c r="D163" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="E163">
         <v>2008</v>
@@ -27334,7 +27334,7 @@
         <v>49</v>
       </c>
       <c r="D164" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="E164">
         <v>1999</v>
@@ -27387,7 +27387,7 @@
         <v>49</v>
       </c>
       <c r="D165" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="E165">
         <v>1999</v>
@@ -27440,7 +27440,7 @@
         <v>49</v>
       </c>
       <c r="D166" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="E166">
         <v>1997</v>
@@ -27546,7 +27546,7 @@
         <v>49</v>
       </c>
       <c r="D168" t="s">
-        <v>72</v>
+        <v>55</v>
       </c>
       <c r="E168">
         <v>2001</v>
@@ -27599,7 +27599,7 @@
         <v>49</v>
       </c>
       <c r="D169" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E169">
         <v>2006</v>
@@ -27705,7 +27705,7 @@
         <v>49</v>
       </c>
       <c r="D171" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="E171">
         <v>2007</v>
@@ -28288,7 +28288,7 @@
         <v>49</v>
       </c>
       <c r="D182" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="E182">
         <v>2015</v>
@@ -29083,7 +29083,7 @@
         <v>49</v>
       </c>
       <c r="D197" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E197">
         <v>2004</v>
@@ -29136,7 +29136,7 @@
         <v>49</v>
       </c>
       <c r="D198" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E198">
         <v>2008</v>
@@ -29348,7 +29348,7 @@
         <v>49</v>
       </c>
       <c r="D202" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="E202">
         <v>2005</v>
@@ -29401,7 +29401,7 @@
         <v>49</v>
       </c>
       <c r="D203" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="E203">
         <v>2015</v>
@@ -30090,7 +30090,7 @@
         <v>49</v>
       </c>
       <c r="D216" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="E216">
         <v>2022</v>
@@ -30302,7 +30302,7 @@
         <v>49</v>
       </c>
       <c r="D220" t="s">
-        <v>65</v>
+        <v>84</v>
       </c>
       <c r="E220">
         <v>2009</v>
@@ -30991,7 +30991,7 @@
         <v>49</v>
       </c>
       <c r="D233" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="E233">
         <v>1994</v>
@@ -31150,7 +31150,7 @@
         <v>49</v>
       </c>
       <c r="D236" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E236">
         <v>1990</v>
@@ -31203,7 +31203,7 @@
         <v>49</v>
       </c>
       <c r="D237" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E237">
         <v>2022</v>
@@ -31362,7 +31362,7 @@
         <v>49</v>
       </c>
       <c r="D240" t="s">
-        <v>63</v>
+        <v>51</v>
       </c>
       <c r="E240">
         <v>2006</v>
@@ -31415,7 +31415,7 @@
         <v>49</v>
       </c>
       <c r="D241" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="E241">
         <v>2024</v>
@@ -31468,7 +31468,7 @@
         <v>49</v>
       </c>
       <c r="D242" t="s">
-        <v>62</v>
+        <v>79</v>
       </c>
       <c r="E242">
         <v>2023</v>
@@ -31521,7 +31521,7 @@
         <v>49</v>
       </c>
       <c r="D243" t="s">
-        <v>62</v>
+        <v>79</v>
       </c>
       <c r="E243">
         <v>2023</v>
@@ -31574,7 +31574,7 @@
         <v>49</v>
       </c>
       <c r="D244" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="E244">
         <v>1997</v>
@@ -32051,7 +32051,7 @@
         <v>49</v>
       </c>
       <c r="D253" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="E253">
         <v>2008</v>
@@ -32316,7 +32316,7 @@
         <v>49</v>
       </c>
       <c r="D258" t="s">
-        <v>62</v>
+        <v>79</v>
       </c>
       <c r="E258">
         <v>2015</v>
@@ -32422,7 +32422,7 @@
         <v>49</v>
       </c>
       <c r="D260" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="E260">
         <v>2004</v>
@@ -32687,7 +32687,7 @@
         <v>49</v>
       </c>
       <c r="D265" t="s">
-        <v>81</v>
+        <v>67</v>
       </c>
       <c r="E265">
         <v>2024</v>
@@ -32793,7 +32793,7 @@
         <v>49</v>
       </c>
       <c r="D267" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="E267">
         <v>2023</v>
@@ -33005,7 +33005,7 @@
         <v>49</v>
       </c>
       <c r="D271" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="E271">
         <v>1975</v>
@@ -33058,7 +33058,7 @@
         <v>49</v>
       </c>
       <c r="D272" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="E272">
         <v>1975</v>
@@ -33111,7 +33111,7 @@
         <v>49</v>
       </c>
       <c r="D273" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="E273">
         <v>1975</v>
@@ -33164,7 +33164,7 @@
         <v>49</v>
       </c>
       <c r="D274" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="E274">
         <v>2015</v>
@@ -33217,7 +33217,7 @@
         <v>49</v>
       </c>
       <c r="D275" t="s">
-        <v>66</v>
+        <v>83</v>
       </c>
       <c r="E275">
         <v>1967</v>
@@ -33270,7 +33270,7 @@
         <v>49</v>
       </c>
       <c r="D276" t="s">
-        <v>66</v>
+        <v>83</v>
       </c>
       <c r="E276">
         <v>1971</v>
@@ -33323,7 +33323,7 @@
         <v>49</v>
       </c>
       <c r="D277" t="s">
-        <v>72</v>
+        <v>55</v>
       </c>
       <c r="E277">
         <v>1970</v>
@@ -33376,7 +33376,7 @@
         <v>49</v>
       </c>
       <c r="D278" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="E278">
         <v>1978</v>
@@ -33429,7 +33429,7 @@
         <v>49</v>
       </c>
       <c r="D279" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="E279">
         <v>1981</v>
@@ -33482,7 +33482,7 @@
         <v>49</v>
       </c>
       <c r="D280" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="E280">
         <v>1987</v>
@@ -33906,7 +33906,7 @@
         <v>293</v>
       </c>
       <c r="D288" t="s">
-        <v>55</v>
+        <v>87</v>
       </c>
       <c r="E288">
         <v>1991</v>
@@ -33959,7 +33959,7 @@
         <v>293</v>
       </c>
       <c r="D289" t="s">
-        <v>55</v>
+        <v>87</v>
       </c>
       <c r="E289">
         <v>1991</v>
@@ -35019,13 +35019,13 @@
         <v>308</v>
       </c>
       <c r="D309" t="s">
-        <v>309</v>
+        <v>99</v>
       </c>
       <c r="E309">
         <v>2022</v>
       </c>
       <c r="F309">
-        <v>5.1032123318242681E-2</v>
+        <v>0.29181095970158766</v>
       </c>
       <c r="G309">
         <v>1</v>
@@ -35034,7 +35034,7 @@
         <v>3162.5000000000005</v>
       </c>
       <c r="I309">
-        <v>60.500000000000021</v>
+        <v>60.500000000000014</v>
       </c>
       <c r="J309">
         <v>2.3100000000000005</v>
@@ -35072,25 +35072,25 @@
         <v>308</v>
       </c>
       <c r="D310" t="s">
-        <v>69</v>
+        <v>309</v>
       </c>
       <c r="E310">
         <v>2022</v>
       </c>
       <c r="F310">
-        <v>0.50939337639482241</v>
+        <v>0.13036387865841995</v>
       </c>
       <c r="G310">
         <v>1</v>
       </c>
       <c r="H310">
-        <v>2750</v>
+        <v>3162.5000000000005</v>
       </c>
       <c r="I310">
-        <v>55.000000000000007</v>
+        <v>60.500000000000014</v>
       </c>
       <c r="J310">
-        <v>2.1</v>
+        <v>2.3100000000000005</v>
       </c>
       <c r="K310">
         <v>100</v>
@@ -35125,25 +35125,25 @@
         <v>308</v>
       </c>
       <c r="D311" t="s">
-        <v>204</v>
+        <v>310</v>
       </c>
       <c r="E311">
         <v>2022</v>
       </c>
       <c r="F311">
-        <v>7.8403898552572848E-2</v>
+        <v>4.4073197411209589E-2</v>
       </c>
       <c r="G311">
         <v>1</v>
       </c>
       <c r="H311">
-        <v>3162.5000000000005</v>
+        <v>3712.5000000000005</v>
       </c>
       <c r="I311">
-        <v>60.500000000000014</v>
+        <v>71.5</v>
       </c>
       <c r="J311">
-        <v>2.3100000000000005</v>
+        <v>2.52</v>
       </c>
       <c r="K311">
         <v>100</v>
@@ -35178,13 +35178,13 @@
         <v>308</v>
       </c>
       <c r="D312" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="E312">
         <v>2022</v>
       </c>
       <c r="F312">
-        <v>0.19299421182171778</v>
+        <v>6.9589259070330922E-2</v>
       </c>
       <c r="G312">
         <v>1</v>
@@ -35193,7 +35193,7 @@
         <v>3162.5000000000005</v>
       </c>
       <c r="I312">
-        <v>60.500000000000014</v>
+        <v>60.500000000000007</v>
       </c>
       <c r="J312">
         <v>2.3100000000000005</v>
@@ -35231,13 +35231,13 @@
         <v>308</v>
       </c>
       <c r="D313" t="s">
-        <v>311</v>
+        <v>20</v>
       </c>
       <c r="E313">
         <v>2022</v>
       </c>
       <c r="F313">
-        <v>5.8918906012880183E-2</v>
+        <v>0.11134281451252948</v>
       </c>
       <c r="G313">
         <v>1</v>
@@ -35246,7 +35246,7 @@
         <v>3162.5000000000005</v>
       </c>
       <c r="I313">
-        <v>60.500000000000021</v>
+        <v>60.500000000000014</v>
       </c>
       <c r="J313">
         <v>2.3100000000000005</v>
@@ -35290,19 +35290,19 @@
         <v>2022</v>
       </c>
       <c r="F314">
-        <v>0.35629700644009438</v>
+        <v>5.8918906012880183E-2</v>
       </c>
       <c r="G314">
         <v>1</v>
       </c>
       <c r="H314">
-        <v>2750</v>
+        <v>3162.5000000000005</v>
       </c>
       <c r="I314">
-        <v>55</v>
+        <v>60.500000000000021</v>
       </c>
       <c r="J314">
-        <v>2.1</v>
+        <v>2.3100000000000005</v>
       </c>
       <c r="K314">
         <v>100</v>
@@ -35343,19 +35343,19 @@
         <v>2022</v>
       </c>
       <c r="F315">
-        <v>0.54140443556717466</v>
+        <v>6.0310691194286808E-2</v>
       </c>
       <c r="G315">
         <v>1</v>
       </c>
       <c r="H315">
-        <v>2750</v>
+        <v>3162.5000000000005</v>
       </c>
       <c r="I315">
-        <v>55.000000000000007</v>
+        <v>60.500000000000014</v>
       </c>
       <c r="J315">
-        <v>2.1</v>
+        <v>2.3100000000000005</v>
       </c>
       <c r="K315">
         <v>100</v>
@@ -35390,13 +35390,13 @@
         <v>308</v>
       </c>
       <c r="D316" t="s">
-        <v>291</v>
+        <v>239</v>
       </c>
       <c r="E316">
         <v>2022</v>
       </c>
       <c r="F316">
-        <v>0.13082780705222213</v>
+        <v>0.22871669814448767</v>
       </c>
       <c r="G316">
         <v>1</v>
@@ -35443,13 +35443,13 @@
         <v>308</v>
       </c>
       <c r="D317" t="s">
-        <v>79</v>
+        <v>314</v>
       </c>
       <c r="E317">
         <v>2022</v>
       </c>
       <c r="F317">
-        <v>0.23196419690110309</v>
+        <v>0.20320063648536632</v>
       </c>
       <c r="G317">
         <v>1</v>
@@ -35496,25 +35496,25 @@
         <v>308</v>
       </c>
       <c r="D318" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="E318">
         <v>2022</v>
       </c>
       <c r="F318">
-        <v>0.13036387865841995</v>
+        <v>4.1753555442198553E-2</v>
       </c>
       <c r="G318">
         <v>1</v>
       </c>
       <c r="H318">
-        <v>3162.5000000000005</v>
+        <v>3712.5000000000005</v>
       </c>
       <c r="I318">
-        <v>60.500000000000014</v>
+        <v>71.5</v>
       </c>
       <c r="J318">
-        <v>2.3100000000000005</v>
+        <v>2.52</v>
       </c>
       <c r="K318">
         <v>100</v>
@@ -35549,25 +35549,25 @@
         <v>308</v>
       </c>
       <c r="D319" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="E319">
         <v>2022</v>
       </c>
       <c r="F319">
-        <v>0.10670353057450742</v>
+        <v>0.56367299846968055</v>
       </c>
       <c r="G319">
         <v>1</v>
       </c>
       <c r="H319">
-        <v>3162.5000000000005</v>
+        <v>2750</v>
       </c>
       <c r="I319">
-        <v>60.500000000000014</v>
+        <v>55.000000000000007</v>
       </c>
       <c r="J319">
-        <v>2.3100000000000005</v>
+        <v>2.1</v>
       </c>
       <c r="K319">
         <v>100</v>
@@ -35602,13 +35602,13 @@
         <v>308</v>
       </c>
       <c r="D320" t="s">
-        <v>316</v>
+        <v>21</v>
       </c>
       <c r="E320">
         <v>2022</v>
       </c>
       <c r="F320">
-        <v>6.0310691194286808E-2</v>
+        <v>8.7682466428616976E-2</v>
       </c>
       <c r="G320">
         <v>1</v>
@@ -35617,7 +35617,7 @@
         <v>3162.5000000000005</v>
       </c>
       <c r="I320">
-        <v>60.500000000000014</v>
+        <v>60.500000000000007</v>
       </c>
       <c r="J320">
         <v>2.3100000000000005</v>
@@ -35655,13 +35655,13 @@
         <v>308</v>
       </c>
       <c r="D321" t="s">
-        <v>64</v>
+        <v>317</v>
       </c>
       <c r="E321">
         <v>2022</v>
       </c>
       <c r="F321">
-        <v>5.4743550468660328E-2</v>
+        <v>5.1032123318242681E-2</v>
       </c>
       <c r="G321">
         <v>1</v>
@@ -35670,7 +35670,7 @@
         <v>3162.5000000000005</v>
       </c>
       <c r="I321">
-        <v>60.500000000000014</v>
+        <v>60.500000000000021</v>
       </c>
       <c r="J321">
         <v>2.3100000000000005</v>
@@ -35708,13 +35708,13 @@
         <v>308</v>
       </c>
       <c r="D322" t="s">
-        <v>239</v>
+        <v>318</v>
       </c>
       <c r="E322">
         <v>2022</v>
       </c>
       <c r="F322">
-        <v>0.22871669814448767</v>
+        <v>0.10067246145507874</v>
       </c>
       <c r="G322">
         <v>1</v>
@@ -35761,25 +35761,25 @@
         <v>308</v>
       </c>
       <c r="D323" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="E323">
         <v>2022</v>
       </c>
       <c r="F323">
-        <v>4.3145340623605172E-2</v>
+        <v>0.54140443556717466</v>
       </c>
       <c r="G323">
         <v>1</v>
       </c>
       <c r="H323">
-        <v>3712.5000000000005</v>
+        <v>2750</v>
       </c>
       <c r="I323">
-        <v>71.5</v>
+        <v>55.000000000000007</v>
       </c>
       <c r="J323">
-        <v>2.52</v>
+        <v>2.1</v>
       </c>
       <c r="K323">
         <v>100</v>
@@ -35814,7 +35814,7 @@
         <v>308</v>
       </c>
       <c r="D324" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="E324">
         <v>2022</v>
@@ -35867,25 +35867,25 @@
         <v>308</v>
       </c>
       <c r="D325" t="s">
-        <v>151</v>
+        <v>74</v>
       </c>
       <c r="E325">
         <v>2022</v>
       </c>
       <c r="F325">
-        <v>4.5464982592616207E-2</v>
+        <v>5.4743550468660328E-2</v>
       </c>
       <c r="G325">
         <v>1</v>
       </c>
       <c r="H325">
-        <v>3712.5000000000005</v>
+        <v>3162.5000000000005</v>
       </c>
       <c r="I325">
-        <v>71.5</v>
+        <v>60.500000000000014</v>
       </c>
       <c r="J325">
-        <v>2.52</v>
+        <v>2.3100000000000005</v>
       </c>
       <c r="K325">
         <v>100</v>
@@ -35920,13 +35920,13 @@
         <v>308</v>
       </c>
       <c r="D326" t="s">
-        <v>20</v>
+        <v>321</v>
       </c>
       <c r="E326">
         <v>2022</v>
       </c>
       <c r="F326">
-        <v>8.7682466428616976E-2</v>
+        <v>0.1577356538927501</v>
       </c>
       <c r="G326">
         <v>1</v>
@@ -35935,7 +35935,7 @@
         <v>3162.5000000000005</v>
       </c>
       <c r="I326">
-        <v>60.500000000000007</v>
+        <v>60.500000000000014</v>
       </c>
       <c r="J326">
         <v>2.3100000000000005</v>
@@ -35973,25 +35973,25 @@
         <v>308</v>
       </c>
       <c r="D327" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="E327">
         <v>2022</v>
       </c>
       <c r="F327">
-        <v>4.1753555442198553E-2</v>
+        <v>0.15541601192373908</v>
       </c>
       <c r="G327">
         <v>1</v>
       </c>
       <c r="H327">
-        <v>3712.5000000000005</v>
+        <v>3162.5000000000005</v>
       </c>
       <c r="I327">
-        <v>71.5</v>
+        <v>60.500000000000014</v>
       </c>
       <c r="J327">
-        <v>2.52</v>
+        <v>2.3100000000000005</v>
       </c>
       <c r="K327">
         <v>100</v>
@@ -36026,7 +36026,7 @@
         <v>308</v>
       </c>
       <c r="D328" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="E328">
         <v>2022</v>
@@ -36079,7 +36079,7 @@
         <v>308</v>
       </c>
       <c r="D329" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="E329">
         <v>2022</v>
@@ -36132,13 +36132,13 @@
         <v>308</v>
       </c>
       <c r="D330" t="s">
-        <v>99</v>
+        <v>325</v>
       </c>
       <c r="E330">
         <v>2022</v>
       </c>
       <c r="F330">
-        <v>0.29181095970158766</v>
+        <v>0.19299421182171778</v>
       </c>
       <c r="G330">
         <v>1</v>
@@ -36185,13 +36185,13 @@
         <v>308</v>
       </c>
       <c r="D331" t="s">
-        <v>322</v>
+        <v>59</v>
       </c>
       <c r="E331">
         <v>2022</v>
       </c>
       <c r="F331">
-        <v>0.56367299846968055</v>
+        <v>0.50939337639482241</v>
       </c>
       <c r="G331">
         <v>1</v>
@@ -36238,13 +36238,13 @@
         <v>308</v>
       </c>
       <c r="D332" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="E332">
         <v>2022</v>
       </c>
       <c r="F332">
-        <v>0.10067246145507874</v>
+        <v>0.10670353057450742</v>
       </c>
       <c r="G332">
         <v>1</v>
@@ -36291,13 +36291,13 @@
         <v>308</v>
       </c>
       <c r="D333" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="E333">
         <v>2022</v>
       </c>
       <c r="F333">
-        <v>4.4073197411209589E-2</v>
+        <v>4.3145340623605172E-2</v>
       </c>
       <c r="G333">
         <v>1</v>
@@ -36344,13 +36344,13 @@
         <v>308</v>
       </c>
       <c r="D334" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="E334">
         <v>2022</v>
       </c>
       <c r="F334">
-        <v>0.15541601192373908</v>
+        <v>6.3558189950902247E-2</v>
       </c>
       <c r="G334">
         <v>1</v>
@@ -36397,25 +36397,25 @@
         <v>308</v>
       </c>
       <c r="D335" t="s">
-        <v>326</v>
+        <v>193</v>
       </c>
       <c r="E335">
         <v>2022</v>
       </c>
       <c r="F335">
-        <v>6.3558189950902247E-2</v>
+        <v>0.61052976624370348</v>
       </c>
       <c r="G335">
         <v>1</v>
       </c>
       <c r="H335">
-        <v>3162.5000000000005</v>
+        <v>2750</v>
       </c>
       <c r="I335">
-        <v>60.500000000000014</v>
+        <v>55.000000000000007</v>
       </c>
       <c r="J335">
-        <v>2.3100000000000005</v>
+        <v>2.1</v>
       </c>
       <c r="K335">
         <v>100</v>
@@ -36450,13 +36450,13 @@
         <v>308</v>
       </c>
       <c r="D336" t="s">
-        <v>327</v>
+        <v>204</v>
       </c>
       <c r="E336">
         <v>2022</v>
       </c>
       <c r="F336">
-        <v>0.1577356538927501</v>
+        <v>7.8403898552572848E-2</v>
       </c>
       <c r="G336">
         <v>1</v>
@@ -36503,25 +36503,25 @@
         <v>308</v>
       </c>
       <c r="D337" t="s">
-        <v>328</v>
+        <v>151</v>
       </c>
       <c r="E337">
         <v>2022</v>
       </c>
       <c r="F337">
-        <v>0.20320063648536632</v>
+        <v>4.5464982592616207E-2</v>
       </c>
       <c r="G337">
         <v>1</v>
       </c>
       <c r="H337">
-        <v>3162.5000000000005</v>
+        <v>3712.5000000000005</v>
       </c>
       <c r="I337">
-        <v>60.500000000000014</v>
+        <v>71.5</v>
       </c>
       <c r="J337">
-        <v>2.3100000000000005</v>
+        <v>2.52</v>
       </c>
       <c r="K337">
         <v>100</v>
@@ -36556,25 +36556,25 @@
         <v>308</v>
       </c>
       <c r="D338" t="s">
-        <v>15</v>
+        <v>329</v>
       </c>
       <c r="E338">
         <v>2022</v>
       </c>
       <c r="F338">
-        <v>0.11134281451252948</v>
+        <v>0.35629700644009438</v>
       </c>
       <c r="G338">
         <v>1</v>
       </c>
       <c r="H338">
-        <v>3162.5000000000005</v>
+        <v>2750</v>
       </c>
       <c r="I338">
-        <v>60.500000000000014</v>
+        <v>55</v>
       </c>
       <c r="J338">
-        <v>2.3100000000000005</v>
+        <v>2.1</v>
       </c>
       <c r="K338">
         <v>100</v>
@@ -36609,25 +36609,25 @@
         <v>308</v>
       </c>
       <c r="D339" t="s">
-        <v>193</v>
+        <v>291</v>
       </c>
       <c r="E339">
         <v>2022</v>
       </c>
       <c r="F339">
-        <v>0.61052976624370348</v>
+        <v>0.13082780705222213</v>
       </c>
       <c r="G339">
         <v>1</v>
       </c>
       <c r="H339">
-        <v>2750</v>
+        <v>3162.5000000000005</v>
       </c>
       <c r="I339">
-        <v>55.000000000000007</v>
+        <v>60.500000000000014</v>
       </c>
       <c r="J339">
-        <v>2.1</v>
+        <v>2.3100000000000005</v>
       </c>
       <c r="K339">
         <v>100</v>
@@ -36662,13 +36662,13 @@
         <v>308</v>
       </c>
       <c r="D340" t="s">
-        <v>329</v>
+        <v>82</v>
       </c>
       <c r="E340">
         <v>2022</v>
       </c>
       <c r="F340">
-        <v>6.9589259070330922E-2</v>
+        <v>0.23196419690110309</v>
       </c>
       <c r="G340">
         <v>1</v>
@@ -36677,7 +36677,7 @@
         <v>3162.5000000000005</v>
       </c>
       <c r="I340">
-        <v>60.500000000000007</v>
+        <v>60.500000000000014</v>
       </c>
       <c r="J340">
         <v>2.3100000000000005</v>
@@ -36768,7 +36768,7 @@
         <v>308</v>
       </c>
       <c r="D342" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="E342">
         <v>1959</v>
@@ -36874,7 +36874,7 @@
         <v>308</v>
       </c>
       <c r="D344" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E344">
         <v>1973</v>
@@ -36980,7 +36980,7 @@
         <v>308</v>
       </c>
       <c r="D346" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="E346">
         <v>1963</v>
@@ -37033,7 +37033,7 @@
         <v>308</v>
       </c>
       <c r="D347" t="s">
-        <v>310</v>
+        <v>325</v>
       </c>
       <c r="E347">
         <v>2015</v>
@@ -37086,7 +37086,7 @@
         <v>308</v>
       </c>
       <c r="D348" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="E348">
         <v>1931</v>
@@ -37139,7 +37139,7 @@
         <v>308</v>
       </c>
       <c r="D349" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="E349">
         <v>1949</v>
@@ -37192,7 +37192,7 @@
         <v>308</v>
       </c>
       <c r="D350" t="s">
-        <v>312</v>
+        <v>329</v>
       </c>
       <c r="E350">
         <v>1951</v>
@@ -37298,7 +37298,7 @@
         <v>308</v>
       </c>
       <c r="D352" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="E352">
         <v>1958</v>
@@ -37351,7 +37351,7 @@
         <v>308</v>
       </c>
       <c r="D353" t="s">
-        <v>315</v>
+        <v>326</v>
       </c>
       <c r="E353">
         <v>1967</v>
@@ -37404,7 +37404,7 @@
         <v>308</v>
       </c>
       <c r="D354" t="s">
-        <v>328</v>
+        <v>314</v>
       </c>
       <c r="E354">
         <v>1968</v>
@@ -37457,7 +37457,7 @@
         <v>308</v>
       </c>
       <c r="D355" t="s">
-        <v>322</v>
+        <v>316</v>
       </c>
       <c r="E355">
         <v>1929</v>
@@ -37510,7 +37510,7 @@
         <v>308</v>
       </c>
       <c r="D356" t="s">
-        <v>328</v>
+        <v>314</v>
       </c>
       <c r="E356">
         <v>1949</v>
@@ -37616,7 +37616,7 @@
         <v>308</v>
       </c>
       <c r="D358" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="E358">
         <v>1952</v>
@@ -37669,7 +37669,7 @@
         <v>308</v>
       </c>
       <c r="D359" t="s">
-        <v>322</v>
+        <v>316</v>
       </c>
       <c r="E359">
         <v>1913</v>
@@ -37722,7 +37722,7 @@
         <v>308</v>
       </c>
       <c r="D360" t="s">
-        <v>312</v>
+        <v>329</v>
       </c>
       <c r="E360">
         <v>1924</v>
@@ -37828,7 +37828,7 @@
         <v>308</v>
       </c>
       <c r="D362" t="s">
-        <v>312</v>
+        <v>329</v>
       </c>
       <c r="E362">
         <v>1971</v>
@@ -37934,7 +37934,7 @@
         <v>308</v>
       </c>
       <c r="D364" t="s">
-        <v>317</v>
+        <v>327</v>
       </c>
       <c r="E364">
         <v>1927</v>
@@ -37987,7 +37987,7 @@
         <v>308</v>
       </c>
       <c r="D365" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="E365">
         <v>1928</v>
@@ -38093,7 +38093,7 @@
         <v>308</v>
       </c>
       <c r="D367" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="E367">
         <v>1938</v>
@@ -38146,7 +38146,7 @@
         <v>308</v>
       </c>
       <c r="D368" t="s">
-        <v>324</v>
+        <v>310</v>
       </c>
       <c r="E368">
         <v>1920</v>
@@ -38199,7 +38199,7 @@
         <v>308</v>
       </c>
       <c r="D369" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="E369">
         <v>1947</v>
@@ -38252,7 +38252,7 @@
         <v>308</v>
       </c>
       <c r="D370" t="s">
-        <v>327</v>
+        <v>321</v>
       </c>
       <c r="E370">
         <v>1950</v>
@@ -38305,7 +38305,7 @@
         <v>308</v>
       </c>
       <c r="D371" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E371">
         <v>1954</v>
@@ -38411,7 +38411,7 @@
         <v>308</v>
       </c>
       <c r="D373" t="s">
-        <v>312</v>
+        <v>329</v>
       </c>
       <c r="E373">
         <v>1971</v>
@@ -38464,7 +38464,7 @@
         <v>308</v>
       </c>
       <c r="D374" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="E374">
         <v>1959</v>
@@ -38570,7 +38570,7 @@
         <v>308</v>
       </c>
       <c r="D376" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="E376">
         <v>1955</v>
@@ -38623,7 +38623,7 @@
         <v>308</v>
       </c>
       <c r="D377" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="E377">
         <v>1959</v>
@@ -38676,7 +38676,7 @@
         <v>308</v>
       </c>
       <c r="D378" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="E378">
         <v>1954</v>
@@ -38888,7 +38888,7 @@
         <v>308</v>
       </c>
       <c r="D382" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="E382">
         <v>2022</v>
@@ -39100,7 +39100,7 @@
         <v>308</v>
       </c>
       <c r="D386" t="s">
-        <v>62</v>
+        <v>79</v>
       </c>
       <c r="E386">
         <v>2022</v>
@@ -39206,7 +39206,7 @@
         <v>383</v>
       </c>
       <c r="D388" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="E388">
         <v>1989</v>
@@ -39259,7 +39259,7 @@
         <v>383</v>
       </c>
       <c r="D389" t="s">
-        <v>314</v>
+        <v>309</v>
       </c>
       <c r="E389">
         <v>1975</v>
@@ -39312,7 +39312,7 @@
         <v>383</v>
       </c>
       <c r="D390" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="E390">
         <v>1966</v>
@@ -39365,7 +39365,7 @@
         <v>383</v>
       </c>
       <c r="D391" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="E391">
         <v>2015</v>
@@ -39418,7 +39418,7 @@
         <v>383</v>
       </c>
       <c r="D392" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="E392">
         <v>2015</v>
@@ -39471,7 +39471,7 @@
         <v>383</v>
       </c>
       <c r="D393" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="E393">
         <v>1982</v>
@@ -39524,7 +39524,7 @@
         <v>383</v>
       </c>
       <c r="D394" t="s">
-        <v>312</v>
+        <v>329</v>
       </c>
       <c r="E394">
         <v>2015</v>
@@ -39577,7 +39577,7 @@
         <v>383</v>
       </c>
       <c r="D395" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="E395">
         <v>2015</v>
@@ -39630,7 +39630,7 @@
         <v>383</v>
       </c>
       <c r="D396" t="s">
-        <v>62</v>
+        <v>79</v>
       </c>
       <c r="E396">
         <v>1961</v>
@@ -39683,7 +39683,7 @@
         <v>383</v>
       </c>
       <c r="D397" t="s">
-        <v>329</v>
+        <v>311</v>
       </c>
       <c r="E397">
         <v>2005</v>
@@ -39736,7 +39736,7 @@
         <v>383</v>
       </c>
       <c r="D398" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="E398">
         <v>1991</v>
@@ -39895,7 +39895,7 @@
         <v>383</v>
       </c>
       <c r="D401" t="s">
-        <v>322</v>
+        <v>316</v>
       </c>
       <c r="E401">
         <v>1971</v>
@@ -39948,7 +39948,7 @@
         <v>383</v>
       </c>
       <c r="D402" t="s">
-        <v>327</v>
+        <v>321</v>
       </c>
       <c r="E402">
         <v>1973</v>
@@ -40107,7 +40107,7 @@
         <v>383</v>
       </c>
       <c r="D405" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E405">
         <v>1978</v>
@@ -40160,7 +40160,7 @@
         <v>383</v>
       </c>
       <c r="D406" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="E406">
         <v>1923</v>
@@ -40213,7 +40213,7 @@
         <v>308</v>
       </c>
       <c r="D407" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="E407">
         <v>1959</v>
@@ -40319,7 +40319,7 @@
         <v>308</v>
       </c>
       <c r="D409" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="E409">
         <v>1949</v>
@@ -40372,7 +40372,7 @@
         <v>308</v>
       </c>
       <c r="D410" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="E410">
         <v>1953</v>
@@ -40478,7 +40478,7 @@
         <v>308</v>
       </c>
       <c r="D412" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="E412">
         <v>1960</v>
@@ -40531,7 +40531,7 @@
         <v>308</v>
       </c>
       <c r="D413" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="E413">
         <v>1962</v>
@@ -40584,7 +40584,7 @@
         <v>308</v>
       </c>
       <c r="D414" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="E414">
         <v>2015</v>
@@ -40637,7 +40637,7 @@
         <v>308</v>
       </c>
       <c r="D415" t="s">
-        <v>328</v>
+        <v>314</v>
       </c>
       <c r="E415">
         <v>1927</v>
@@ -40690,7 +40690,7 @@
         <v>308</v>
       </c>
       <c r="D416" t="s">
-        <v>309</v>
+        <v>317</v>
       </c>
       <c r="E416">
         <v>1954</v>
@@ -40796,7 +40796,7 @@
         <v>308</v>
       </c>
       <c r="D418" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="E418">
         <v>1956</v>
@@ -40849,7 +40849,7 @@
         <v>308</v>
       </c>
       <c r="D419" t="s">
-        <v>312</v>
+        <v>329</v>
       </c>
       <c r="E419">
         <v>1956</v>
@@ -40955,7 +40955,7 @@
         <v>308</v>
       </c>
       <c r="D421" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="E421">
         <v>1960</v>
@@ -41061,7 +41061,7 @@
         <v>308</v>
       </c>
       <c r="D423" t="s">
-        <v>310</v>
+        <v>325</v>
       </c>
       <c r="E423">
         <v>2015</v>
@@ -41167,7 +41167,7 @@
         <v>308</v>
       </c>
       <c r="D425" t="s">
-        <v>328</v>
+        <v>314</v>
       </c>
       <c r="E425">
         <v>2015</v>
@@ -41220,7 +41220,7 @@
         <v>308</v>
       </c>
       <c r="D426" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="E426">
         <v>2015</v>
@@ -41326,7 +41326,7 @@
         <v>308</v>
       </c>
       <c r="D428" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="E428">
         <v>1955</v>
@@ -41379,7 +41379,7 @@
         <v>308</v>
       </c>
       <c r="D429" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E429">
         <v>2015</v>
@@ -41485,7 +41485,7 @@
         <v>308</v>
       </c>
       <c r="D431" t="s">
-        <v>317</v>
+        <v>327</v>
       </c>
       <c r="E431">
         <v>1932</v>
@@ -41644,7 +41644,7 @@
         <v>308</v>
       </c>
       <c r="D434" t="s">
-        <v>322</v>
+        <v>316</v>
       </c>
       <c r="E434">
         <v>1924</v>
@@ -41750,7 +41750,7 @@
         <v>308</v>
       </c>
       <c r="D436" t="s">
-        <v>322</v>
+        <v>316</v>
       </c>
       <c r="E436">
         <v>2002</v>
@@ -41856,7 +41856,7 @@
         <v>308</v>
       </c>
       <c r="D438" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="E438">
         <v>1948</v>
@@ -41909,7 +41909,7 @@
         <v>308</v>
       </c>
       <c r="D439" t="s">
-        <v>310</v>
+        <v>325</v>
       </c>
       <c r="E439">
         <v>2015</v>
@@ -41962,7 +41962,7 @@
         <v>308</v>
       </c>
       <c r="D440" t="s">
-        <v>324</v>
+        <v>310</v>
       </c>
       <c r="E440">
         <v>1914</v>
@@ -42068,7 +42068,7 @@
         <v>308</v>
       </c>
       <c r="D442" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="E442">
         <v>1958</v>
@@ -42121,7 +42121,7 @@
         <v>439</v>
       </c>
       <c r="D443" t="s">
-        <v>85</v>
+        <v>73</v>
       </c>
       <c r="E443">
         <v>1992</v>
@@ -42280,7 +42280,7 @@
         <v>439</v>
       </c>
       <c r="D446" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E446">
         <v>1992</v>
@@ -42333,7 +42333,7 @@
         <v>439</v>
       </c>
       <c r="D447" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="E447">
         <v>2005</v>
@@ -42598,7 +42598,7 @@
         <v>439</v>
       </c>
       <c r="D452" t="s">
-        <v>85</v>
+        <v>73</v>
       </c>
       <c r="E452">
         <v>1985</v>
@@ -42922,7 +42922,7 @@
         <v>2022</v>
       </c>
       <c r="F458">
-        <v>6.6457416582336482</v>
+        <v>6.6039408899415779</v>
       </c>
       <c r="G458">
         <v>1</v>
@@ -42978,7 +42978,7 @@
         <v>2022</v>
       </c>
       <c r="F459">
-        <v>6.6307854518247753</v>
+        <v>6.6457416582336482</v>
       </c>
       <c r="G459">
         <v>1</v>
@@ -43034,7 +43034,7 @@
         <v>2022</v>
       </c>
       <c r="F460">
-        <v>6.6039408899415779</v>
+        <v>6.6307854518247753</v>
       </c>
       <c r="G460">
         <v>1</v>
@@ -43812,7 +43812,7 @@
         <v>455</v>
       </c>
       <c r="D474" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="E474">
         <v>2015</v>
@@ -44876,7 +44876,7 @@
         <v>455</v>
       </c>
       <c r="D493" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="E493">
         <v>2015</v>
@@ -51156,7 +51156,7 @@
         <v>2022</v>
       </c>
       <c r="F618">
-        <v>0.69928302455480262</v>
+        <v>0.6793056475905862</v>
       </c>
       <c r="G618">
         <v>0.33123000000000002</v>
@@ -51202,7 +51202,7 @@
         <v>2022</v>
       </c>
       <c r="F620">
-        <v>0.6793056475905862</v>
+        <v>0.69928302455480262</v>
       </c>
       <c r="G620">
         <v>0.33123000000000002</v>
@@ -51449,7 +51449,7 @@
         <v>663</v>
       </c>
       <c r="D631" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="E631">
         <v>2018</v>

--- a/VerveStacks_ITA_grids/vt_vervestacks_ITA_v1.xlsx
+++ b/VerveStacks_ITA_grids/vt_vervestacks_ITA_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D74BFAC3-12B0-4D05-8B3E-5ADAFC0163EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{DF4314EB-413D-4B24-8AE2-5731D5AA75D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{41AE1675-1BC9-4E47-915A-9F40DC1E702C}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{F15EF9EB-C453-40F3-95EF-6CE3AF814F0D}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="2" r:id="rId1"/>
@@ -81,30 +81,30 @@
     <t>bioenergy</t>
   </si>
   <si>
+    <t>e_w144005863-380</t>
+  </si>
+  <si>
+    <t>e_w84696559-380</t>
+  </si>
+  <si>
+    <t>e_w34157795-380</t>
+  </si>
+  <si>
     <t>e_w98902899-380</t>
   </si>
   <si>
+    <t>e_w81938081-380</t>
+  </si>
+  <si>
+    <t>e_w108020416-380</t>
+  </si>
+  <si>
     <t>e_w58440884-380</t>
   </si>
   <si>
-    <t>e_w84696559-380</t>
-  </si>
-  <si>
-    <t>e_w34157795-380</t>
-  </si>
-  <si>
-    <t>e_w81938081-380</t>
-  </si>
-  <si>
     <t>e_w109756016-380</t>
   </si>
   <si>
-    <t>e_w144005863-380</t>
-  </si>
-  <si>
-    <t>e_w108020416-380</t>
-  </si>
-  <si>
     <t>ep_bioenergy_G100000200236</t>
   </si>
   <si>
@@ -141,18 +141,18 @@
     <t>coal</t>
   </si>
   <si>
+    <t>e_w303915533-380</t>
+  </si>
+  <si>
+    <t>e_w409439916-380</t>
+  </si>
+  <si>
+    <t>e_w418902800-380</t>
+  </si>
+  <si>
     <t>e_w82767145-380</t>
   </si>
   <si>
-    <t>e_w303915533-380</t>
-  </si>
-  <si>
-    <t>e_w418902800-380</t>
-  </si>
-  <si>
-    <t>e_w409439916-380</t>
-  </si>
-  <si>
     <t>ep_coal_subcritical_G100000102764</t>
   </si>
   <si>
@@ -189,120 +189,120 @@
     <t>gas</t>
   </si>
   <si>
+    <t>e_w110330925-380</t>
+  </si>
+  <si>
+    <t>e_w162828577-380</t>
+  </si>
+  <si>
+    <t>e_w98900549-380</t>
+  </si>
+  <si>
+    <t>e_w103381531-380</t>
+  </si>
+  <si>
+    <t>e_w133601335-380</t>
+  </si>
+  <si>
+    <t>e_w199675964-380</t>
+  </si>
+  <si>
+    <t>e_w338753171-380</t>
+  </si>
+  <si>
+    <t>e_w162960205-380</t>
+  </si>
+  <si>
+    <t>e_w98421779-380</t>
+  </si>
+  <si>
+    <t>e_w419423704-380</t>
+  </si>
+  <si>
+    <t>e_w116797658-380</t>
+  </si>
+  <si>
+    <t>e_w414663585-380</t>
+  </si>
+  <si>
+    <t>e_w255011550-380</t>
+  </si>
+  <si>
+    <t>e_w181125039-380</t>
+  </si>
+  <si>
+    <t>e_w105581403-380</t>
+  </si>
+  <si>
+    <t>e_w432729521-380</t>
+  </si>
+  <si>
+    <t>e_w172302572-380</t>
+  </si>
+  <si>
+    <t>e_w339104227-380</t>
+  </si>
+  <si>
+    <t>e_w158739183-380</t>
+  </si>
+  <si>
+    <t>e_w103974940-380</t>
+  </si>
+  <si>
+    <t>e_w59462715-380</t>
+  </si>
+  <si>
+    <t>e_w421827453-380</t>
+  </si>
+  <si>
+    <t>e_w149997403-380</t>
+  </si>
+  <si>
+    <t>e_w107438024-380</t>
+  </si>
+  <si>
+    <t>e_w100407576-380</t>
+  </si>
+  <si>
+    <t>e_w82078641-380</t>
+  </si>
+  <si>
+    <t>e_w61157826-380</t>
+  </si>
+  <si>
+    <t>e_w1137611914-380</t>
+  </si>
+  <si>
+    <t>e_w109993642-380</t>
+  </si>
+  <si>
     <t>e_w411026199-380</t>
   </si>
   <si>
+    <t>e_w416989699-380</t>
+  </si>
+  <si>
     <t>e_w99826025-380</t>
   </si>
   <si>
+    <t>e_w82084019-380</t>
+  </si>
+  <si>
+    <t>e_w145665799-380</t>
+  </si>
+  <si>
+    <t>e_w60725875-380</t>
+  </si>
+  <si>
+    <t>e_w105757794-380</t>
+  </si>
+  <si>
     <t>e_w103653592-380</t>
   </si>
   <si>
-    <t>e_w109993642-380</t>
-  </si>
-  <si>
-    <t>e_w105581403-380</t>
-  </si>
-  <si>
-    <t>e_w255011550-380</t>
-  </si>
-  <si>
-    <t>e_w199675964-380</t>
-  </si>
-  <si>
-    <t>e_w82084019-380</t>
-  </si>
-  <si>
-    <t>e_w98421779-380</t>
-  </si>
-  <si>
-    <t>e_w419423704-380</t>
-  </si>
-  <si>
-    <t>e_w116797658-380</t>
-  </si>
-  <si>
-    <t>e_w158739183-380</t>
-  </si>
-  <si>
-    <t>e_w103974940-380</t>
-  </si>
-  <si>
-    <t>e_w432729521-380</t>
-  </si>
-  <si>
-    <t>e_w414663585-380</t>
-  </si>
-  <si>
-    <t>e_w172302572-380</t>
-  </si>
-  <si>
-    <t>e_w181125039-380</t>
-  </si>
-  <si>
-    <t>e_w133601335-380</t>
-  </si>
-  <si>
-    <t>e_w103381531-380</t>
-  </si>
-  <si>
-    <t>e_w339104227-380</t>
-  </si>
-  <si>
-    <t>e_w59462715-380</t>
-  </si>
-  <si>
-    <t>e_w421827453-380</t>
-  </si>
-  <si>
-    <t>e_w149997403-380</t>
-  </si>
-  <si>
-    <t>e_w100407576-380</t>
-  </si>
-  <si>
-    <t>e_w1137611914-380</t>
-  </si>
-  <si>
-    <t>e_w98900549-380</t>
-  </si>
-  <si>
-    <t>e_w162828577-380</t>
-  </si>
-  <si>
     <t>e_w132450233-380</t>
   </si>
   <si>
-    <t>e_w110330925-380</t>
-  </si>
-  <si>
-    <t>e_w61157826-380</t>
-  </si>
-  <si>
-    <t>e_w82078641-380</t>
-  </si>
-  <si>
-    <t>e_w162960205-380</t>
-  </si>
-  <si>
-    <t>e_w338753171-380</t>
-  </si>
-  <si>
-    <t>e_w145665799-380</t>
-  </si>
-  <si>
-    <t>e_w60725875-380</t>
-  </si>
-  <si>
-    <t>e_w107438024-380</t>
-  </si>
-  <si>
-    <t>e_w105757794-380</t>
-  </si>
-  <si>
-    <t>e_w416989699-380</t>
-  </si>
-  <si>
     <t>ep_gas_combined_cycle_G100000400339</t>
   </si>
   <si>
@@ -966,66 +966,66 @@
     <t>hydro</t>
   </si>
   <si>
+    <t>e_IT53-380</t>
+  </si>
+  <si>
+    <t>e_IT21-380</t>
+  </si>
+  <si>
+    <t>e_w72466334-380</t>
+  </si>
+  <si>
+    <t>e_w116517585-380</t>
+  </si>
+  <si>
+    <t>e_IT72-400</t>
+  </si>
+  <si>
+    <t>e_IT93-380</t>
+  </si>
+  <si>
+    <t>e_w61626687-380</t>
+  </si>
+  <si>
+    <t>e_IT71-400</t>
+  </si>
+  <si>
+    <t>e_w491424937-380</t>
+  </si>
+  <si>
+    <t>e_w75602396-380</t>
+  </si>
+  <si>
+    <t>e_w64200868-380</t>
+  </si>
+  <si>
+    <t>e_IT72-380</t>
+  </si>
+  <si>
+    <t>e_IT36-380</t>
+  </si>
+  <si>
+    <t>e_w104359058-380</t>
+  </si>
+  <si>
+    <t>e_IT31-380</t>
+  </si>
+  <si>
+    <t>e_IT10-380</t>
+  </si>
+  <si>
     <t>e_w114931087-380</t>
   </si>
   <si>
-    <t>e_IT72-400</t>
-  </si>
-  <si>
-    <t>e_IT93-380</t>
+    <t>e_IT7-380</t>
   </si>
   <si>
     <t>e_IT71-380</t>
   </si>
   <si>
-    <t>e_IT71-400</t>
-  </si>
-  <si>
-    <t>e_IT10-380</t>
-  </si>
-  <si>
-    <t>e_w116517585-380</t>
-  </si>
-  <si>
-    <t>e_IT21-380</t>
-  </si>
-  <si>
-    <t>e_w61626687-380</t>
-  </si>
-  <si>
-    <t>e_IT72-380</t>
-  </si>
-  <si>
-    <t>e_IT7-380</t>
-  </si>
-  <si>
-    <t>e_w64200868-380</t>
-  </si>
-  <si>
-    <t>e_w72466334-380</t>
-  </si>
-  <si>
-    <t>e_IT36-380</t>
-  </si>
-  <si>
-    <t>e_w104359058-380</t>
-  </si>
-  <si>
-    <t>e_IT31-380</t>
-  </si>
-  <si>
     <t>e_w1100665914-380</t>
   </si>
   <si>
-    <t>e_w491424937-380</t>
-  </si>
-  <si>
-    <t>e_w75602396-380</t>
-  </si>
-  <si>
-    <t>e_IT53-380</t>
-  </si>
-  <si>
     <t>e_w82083756-380</t>
   </si>
   <si>
@@ -2031,15 +2031,15 @@
     <t>windon</t>
   </si>
   <si>
+    <t>elc_won-ITA_0096</t>
+  </si>
+  <si>
+    <t>elc_won-ITA_0073</t>
+  </si>
+  <si>
     <t>elc_won-ITA_0022</t>
   </si>
   <si>
-    <t>elc_won-ITA_0096</t>
-  </si>
-  <si>
-    <t>elc_won-ITA_0073</t>
-  </si>
-  <si>
     <t>ep_windon_wind_010</t>
   </si>
   <si>
@@ -2469,42 +2469,42 @@
     <t>ele</t>
   </si>
   <si>
+    <t>Aggregated Plant - EMBER Gap - way/108020416-380_Missing Bioenergy Capacity</t>
+  </si>
+  <si>
+    <t>GW</t>
+  </si>
+  <si>
+    <t>TWh</t>
+  </si>
+  <si>
+    <t>daynite</t>
+  </si>
+  <si>
+    <t>yes</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/144005863-380_Missing Bioenergy Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/109756016-380_Missing Bioenergy Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/98902899-380_Missing Bioenergy Capacity</t>
+  </si>
+  <si>
     <t>Aggregated Plant - EMBER Gap - way/58440884-380_Missing Bioenergy Capacity</t>
   </si>
   <si>
-    <t>GW</t>
-  </si>
-  <si>
-    <t>TWh</t>
-  </si>
-  <si>
-    <t>daynite</t>
-  </si>
-  <si>
-    <t>yes</t>
-  </si>
-  <si>
     <t>Aggregated Plant - EMBER Gap - way/34157795-380_Missing Bioenergy Capacity</t>
   </si>
   <si>
-    <t>Aggregated Plant - EMBER Gap - way/108020416-380_Missing Bioenergy Capacity</t>
+    <t>Aggregated Plant - EMBER Gap - way/81938081-380_Missing Bioenergy Capacity</t>
   </si>
   <si>
     <t>Aggregated Plant - EMBER Gap - way/84696559-380_Missing Bioenergy Capacity</t>
   </si>
   <si>
-    <t>Aggregated Plant - EMBER Gap - way/81938081-380_Missing Bioenergy Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/98902899-380_Missing Bioenergy Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/144005863-380_Missing Bioenergy Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/109756016-380_Missing Bioenergy Capacity</t>
-  </si>
-  <si>
     <t>Acerra power station_1</t>
   </si>
   <si>
@@ -2526,18 +2526,18 @@
     <t>Aggregated Plant</t>
   </si>
   <si>
+    <t>Aggregated Plant - EMBER Gap - way/418902800-380_Missing Coal Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/303915533-380_Missing Coal Capacity</t>
+  </si>
+  <si>
     <t>Aggregated Plant - EMBER Gap - way/409439916-380_Missing Coal Capacity</t>
   </si>
   <si>
-    <t>Aggregated Plant - EMBER Gap - way/418902800-380_Missing Coal Capacity</t>
-  </si>
-  <si>
     <t>Aggregated Plant - EMBER Gap - way/82767145-380_Missing Coal Capacity</t>
   </si>
   <si>
-    <t>Aggregated Plant - EMBER Gap - way/303915533-380_Missing Coal Capacity</t>
-  </si>
-  <si>
     <t>Fiume Santo power station_Unit 3</t>
   </si>
   <si>
@@ -2568,126 +2568,126 @@
     <t>Torrevaldaliga Nord power station_Unit 3</t>
   </si>
   <si>
+    <t>Aggregated Plant - EMBER Gap - way/145665799-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/1137611914-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/158739183-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/61157826-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/414663585-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/419423704-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/416989699-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/103653592-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/100407576-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/133601335-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/149997403-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/162960205-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/99826025-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/421827453-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/338753171-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/103381531-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/98900549-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/162828577-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/181125039-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/432729521-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/199675964-380_Missing Gas Capacity</t>
+  </si>
+  <si>
     <t>Aggregated Plant - EMBER Gap - way/132450233-380_Missing Gas Capacity</t>
   </si>
   <si>
+    <t>Aggregated Plant - EMBER Gap - way/105757794-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/59462715-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/172302572-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/255011550-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/107438024-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/339104227-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/116797658-380_Missing Gas Capacity</t>
+  </si>
+  <si>
     <t>Aggregated Plant - EMBER Gap - way/82078641-380_Missing Gas Capacity</t>
   </si>
   <si>
     <t>Aggregated Plant - EMBER Gap - way/103974940-380_Missing Gas Capacity</t>
   </si>
   <si>
-    <t>Aggregated Plant - EMBER Gap - way/103381531-380_Missing Gas Capacity</t>
+    <t>Aggregated Plant - EMBER Gap - way/82084019-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/98421779-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/105581403-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/109756016-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/60725875-380_Missing Gas Capacity</t>
   </si>
   <si>
     <t>Aggregated Plant - EMBER Gap - way/411026199-380_Missing Gas Capacity</t>
   </si>
   <si>
-    <t>Aggregated Plant - EMBER Gap - way/105581403-380_Missing Gas Capacity</t>
-  </si>
-  <si>
     <t>Aggregated Plant - EMBER Gap - way/110330925-380_Missing Gas Capacity</t>
   </si>
   <si>
-    <t>Aggregated Plant - EMBER Gap - way/109756016-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/98421779-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/82084019-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/416989699-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/103653592-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/100407576-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/181125039-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/432729521-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/199675964-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/338753171-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/162828577-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/98900549-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/255011550-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/105757794-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/59462715-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/172302572-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/133601335-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/149997403-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/162960205-380_Missing Gas Capacity</t>
+    <t>Aggregated Plant - EMBER Gap - way/82767145-380_Missing Gas Capacity</t>
   </si>
   <si>
     <t>Aggregated Plant - EMBER Gap - way/109993642-380_Missing Gas Capacity</t>
   </si>
   <si>
-    <t>Aggregated Plant - EMBER Gap - way/419423704-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/61157826-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/414663585-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/82767145-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/107438024-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/339104227-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/116797658-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/1137611914-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/60725875-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/158739183-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/145665799-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/99826025-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/421827453-380_Missing Gas Capacity</t>
-  </si>
-  <si>
     <t>Altomonte power station_1</t>
   </si>
   <si>
@@ -3000,102 +3000,102 @@
     <t>Valle Secolo geothermal power plant_2</t>
   </si>
   <si>
+    <t>Aggregated Plant - IRENA Gap - way/491424937-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/72466334-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/82083756-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/104359058-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/419423704-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - IT7-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/339703159-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - IT53-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - IT30-500_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/61712456-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/61626687-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - IT31-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/114931087-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - IT71-400_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - IT36-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/109588422-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/1137611914-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - IT72-400_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/64200868-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/116517585-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
     <t>Aggregated Plant - IRENA Gap - way/96190189-380_Missing Hydro Capacity</t>
   </si>
   <si>
-    <t>Aggregated Plant - IRENA Gap - way/116517585-380_Missing Hydro Capacity</t>
+    <t>Aggregated Plant - IRENA Gap - way/144005863-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - IT21-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - IT72-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/1100665914-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/59462263-380_Missing Hydro Capacity</t>
   </si>
   <si>
     <t>Aggregated Plant - IRENA Gap - IT93-380_Missing Hydro Capacity</t>
   </si>
   <si>
+    <t>Aggregated Plant - IRENA Gap - IT10-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
     <t>Aggregated Plant - IRENA Gap - way/338753171-380_Missing Hydro Capacity</t>
   </si>
   <si>
-    <t>Aggregated Plant - IRENA Gap - IT10-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - IT53-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - IT30-500_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/61712456-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
     <t>Aggregated Plant - IRENA Gap - IT71-380_Missing Hydro Capacity</t>
   </si>
   <si>
-    <t>Aggregated Plant - IRENA Gap - IT7-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/339703159-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - IT72-400_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/109588422-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/1137611914-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
     <t>Aggregated Plant - IRENA Gap - way/108020416-380_Missing Hydro Capacity</t>
   </si>
   <si>
-    <t>Aggregated Plant - IRENA Gap - way/64200868-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/144005863-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - IT21-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/61626687-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/114931087-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - IT31-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/59462263-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/1100665914-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - IT72-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/104359058-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/82083756-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/491424937-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/419423704-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/72466334-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
     <t>Aggregated Plant - IRENA Gap - way/75602396-380_Missing Hydro Capacity</t>
   </si>
   <si>
-    <t>Aggregated Plant - IRENA Gap - IT71-400_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - IT36-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
     <t>Baschi hydroelectric plant_</t>
   </si>
   <si>
@@ -3402,15 +3402,15 @@
     <t>Aggregated Plant - IRENA Gap - ITA_42_Missing Solar Capacity</t>
   </si>
   <si>
+    <t>Aggregated Plant - IRENA Gap - ITA_22_Missing Onshore wind energy Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - ITA_73_Missing Onshore wind energy Capacity</t>
+  </si>
+  <si>
     <t>Aggregated Plant - IRENA Gap - ITA_96_Missing Onshore wind energy Capacity</t>
   </si>
   <si>
-    <t>Aggregated Plant - IRENA Gap - ITA_73_Missing Onshore wind energy Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - ITA_22_Missing Onshore wind energy Capacity</t>
-  </si>
-  <si>
     <t>AF</t>
   </si>
   <si>
@@ -4002,18 +4002,18 @@
     <t>ccs retrofit of -- Sulcis power station_Unit 3</t>
   </si>
   <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/418902800-380_Missing Coal Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/82767145-380_Missing Coal Capacity</t>
+  </si>
+  <si>
     <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/303915533-380_Missing Coal Capacity</t>
   </si>
   <si>
     <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/409439916-380_Missing Coal Capacity</t>
   </si>
   <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/418902800-380_Missing Coal Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/82767145-380_Missing Coal Capacity</t>
-  </si>
-  <si>
     <t>ccs retrofit of -- Brindisi Sud power station_Unit 1</t>
   </si>
   <si>
@@ -4302,124 +4302,124 @@
     <t>ccs retrofit of -- Aggregated Plant</t>
   </si>
   <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/98900549-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/145665799-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/181125039-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/105757794-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/99826025-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/416989699-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/103381531-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/109756016-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/411026199-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/100407576-380_Missing Gas Capacity</t>
+  </si>
+  <si>
     <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/132450233-380_Missing Gas Capacity</t>
   </si>
   <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/255011550-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/103974940-380_Missing Gas Capacity</t>
+  </si>
+  <si>
     <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/149997403-380_Missing Gas Capacity</t>
   </si>
   <si>
     <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/162960205-380_Missing Gas Capacity</t>
   </si>
   <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/432729521-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/419423704-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/107438024-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/98421779-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/414663585-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/158739183-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/133601335-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/339104227-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/116797658-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/61157826-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/421827453-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/82084019-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/60725875-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/338753171-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/110330925-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/172302572-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/82767145-380_Missing Gas Capacity</t>
+  </si>
+  <si>
     <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/162828577-380_Missing Gas Capacity</t>
   </si>
   <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/172302572-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/82767145-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/61157826-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/103974940-380_Missing Gas Capacity</t>
-  </si>
-  <si>
     <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/59462715-380_Missing Gas Capacity</t>
   </si>
   <si>
     <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/109993642-380_Missing Gas Capacity</t>
   </si>
   <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/414663585-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/145665799-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/82084019-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/60725875-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/421827453-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/110330925-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/338753171-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/103381531-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/411026199-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/109756016-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/133601335-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/339104227-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/116797658-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/419423704-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/100407576-380_Missing Gas Capacity</t>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/1137611914-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/103653592-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/199675964-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/105581403-380_Missing Gas Capacity</t>
   </si>
   <si>
     <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/82078641-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/416989699-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/105757794-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/99826025-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/105581403-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/181125039-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/255011550-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/103653592-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/199675964-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/1137611914-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/432729521-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/98421779-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/98900549-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/107438024-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/158739183-380_Missing Gas Capacity</t>
   </si>
   <si>
     <t>ccs retrofit of -- Tavazzano power station_CCGT8, timepoint 1</t>
@@ -4823,7 +4823,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6DC652D2-71A7-45BF-93A5-CE6DCE854CD1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{14190EE1-BB23-4B15-8E99-05AE39C9759E}">
   <dimension ref="B9:T278"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -4899,7 +4899,7 @@
         <v>33</v>
       </c>
       <c r="D11" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E11">
         <v>0.18317520000000001</v>
@@ -4955,7 +4955,7 @@
         <v>33</v>
       </c>
       <c r="D12" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E12">
         <v>0.18317520000000001</v>
@@ -5011,7 +5011,7 @@
         <v>33</v>
       </c>
       <c r="D13" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E13">
         <v>0.18317520000000001</v>
@@ -5067,7 +5067,7 @@
         <v>33</v>
       </c>
       <c r="D14" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E14">
         <v>0.13765950000000002</v>
@@ -5515,7 +5515,7 @@
         <v>33</v>
       </c>
       <c r="D22" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="E22">
         <v>0.33007379999999992</v>
@@ -5571,7 +5571,7 @@
         <v>33</v>
       </c>
       <c r="D23" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="E23">
         <v>0.33007379999999992</v>
@@ -5627,7 +5627,7 @@
         <v>33</v>
       </c>
       <c r="D24" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="E24">
         <v>0.33007379999999992</v>
@@ -5683,7 +5683,7 @@
         <v>49</v>
       </c>
       <c r="D25" t="s">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="E25">
         <v>0.49118125000000001</v>
@@ -5739,7 +5739,7 @@
         <v>49</v>
       </c>
       <c r="D26" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E26">
         <v>0.52272499999999988</v>
@@ -5795,7 +5795,7 @@
         <v>49</v>
       </c>
       <c r="D27" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E27">
         <v>0.450625</v>
@@ -5851,7 +5851,7 @@
         <v>49</v>
       </c>
       <c r="D28" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="E28">
         <v>0.52272499999999988</v>
@@ -6131,7 +6131,7 @@
         <v>49</v>
       </c>
       <c r="D33" t="s">
-        <v>67</v>
+        <v>54</v>
       </c>
       <c r="E33">
         <v>0.49118125000000001</v>
@@ -6299,7 +6299,7 @@
         <v>49</v>
       </c>
       <c r="D36" t="s">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="E36">
         <v>0.49118125000000001</v>
@@ -6355,7 +6355,7 @@
         <v>49</v>
       </c>
       <c r="D37" t="s">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="E37">
         <v>0.49118125000000001</v>
@@ -6523,7 +6523,7 @@
         <v>49</v>
       </c>
       <c r="D40" t="s">
-        <v>75</v>
+        <v>52</v>
       </c>
       <c r="E40">
         <v>0.46865000000000007</v>
@@ -6579,7 +6579,7 @@
         <v>49</v>
       </c>
       <c r="D41" t="s">
-        <v>75</v>
+        <v>52</v>
       </c>
       <c r="E41">
         <v>0.49118125000000001</v>
@@ -6635,7 +6635,7 @@
         <v>49</v>
       </c>
       <c r="D42" t="s">
-        <v>75</v>
+        <v>52</v>
       </c>
       <c r="E42">
         <v>0.49118125000000001</v>
@@ -6691,7 +6691,7 @@
         <v>49</v>
       </c>
       <c r="D43" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="E43">
         <v>0.49118125000000001</v>
@@ -6747,7 +6747,7 @@
         <v>49</v>
       </c>
       <c r="D44" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="E44">
         <v>0.49118125000000001</v>
@@ -6803,7 +6803,7 @@
         <v>49</v>
       </c>
       <c r="D45" t="s">
-        <v>85</v>
+        <v>73</v>
       </c>
       <c r="E45">
         <v>0.49118125000000001</v>
@@ -6859,7 +6859,7 @@
         <v>49</v>
       </c>
       <c r="D46" t="s">
-        <v>85</v>
+        <v>73</v>
       </c>
       <c r="E46">
         <v>0.49118125000000001</v>
@@ -6915,7 +6915,7 @@
         <v>49</v>
       </c>
       <c r="D47" t="s">
-        <v>85</v>
+        <v>73</v>
       </c>
       <c r="E47">
         <v>0.49118125000000001</v>
@@ -6971,7 +6971,7 @@
         <v>49</v>
       </c>
       <c r="D48" t="s">
-        <v>85</v>
+        <v>73</v>
       </c>
       <c r="E48">
         <v>0.49118125000000001</v>
@@ -7027,7 +7027,7 @@
         <v>49</v>
       </c>
       <c r="D49" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E49">
         <v>0.47315625000000006</v>
@@ -7083,7 +7083,7 @@
         <v>49</v>
       </c>
       <c r="D50" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E50">
         <v>0.47315625000000006</v>
@@ -7139,7 +7139,7 @@
         <v>49</v>
       </c>
       <c r="D51" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="E51">
         <v>0.49118125000000001</v>
@@ -7195,7 +7195,7 @@
         <v>49</v>
       </c>
       <c r="D52" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E52">
         <v>0.54075000000000006</v>
@@ -7251,7 +7251,7 @@
         <v>49</v>
       </c>
       <c r="D53" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E53">
         <v>0.49118125000000001</v>
@@ -7363,7 +7363,7 @@
         <v>49</v>
       </c>
       <c r="D55" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E55">
         <v>0.49118125000000001</v>
@@ -7419,7 +7419,7 @@
         <v>49</v>
       </c>
       <c r="D56" t="s">
-        <v>51</v>
+        <v>81</v>
       </c>
       <c r="E56">
         <v>0.49118125000000001</v>
@@ -7475,7 +7475,7 @@
         <v>49</v>
       </c>
       <c r="D57" t="s">
-        <v>51</v>
+        <v>81</v>
       </c>
       <c r="E57">
         <v>0.49118125000000001</v>
@@ -7531,7 +7531,7 @@
         <v>49</v>
       </c>
       <c r="D58" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="E58">
         <v>0.47315625000000006</v>
@@ -7587,7 +7587,7 @@
         <v>49</v>
       </c>
       <c r="D59" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="E59">
         <v>0.47315625000000006</v>
@@ -7643,7 +7643,7 @@
         <v>49</v>
       </c>
       <c r="D60" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="E60">
         <v>0.450625</v>
@@ -7699,7 +7699,7 @@
         <v>49</v>
       </c>
       <c r="D61" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="E61">
         <v>0.450625</v>
@@ -7811,7 +7811,7 @@
         <v>49</v>
       </c>
       <c r="D63" t="s">
-        <v>82</v>
+        <v>56</v>
       </c>
       <c r="E63">
         <v>0.4911812499999999</v>
@@ -7867,7 +7867,7 @@
         <v>49</v>
       </c>
       <c r="D64" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="E64">
         <v>0.49118125000000001</v>
@@ -7923,7 +7923,7 @@
         <v>49</v>
       </c>
       <c r="D65" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="E65">
         <v>0.49118125000000001</v>
@@ -8147,7 +8147,7 @@
         <v>49</v>
       </c>
       <c r="D69" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="E69">
         <v>0.49118125000000001</v>
@@ -8203,7 +8203,7 @@
         <v>49</v>
       </c>
       <c r="D70" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="E70">
         <v>0.49118125000000001</v>
@@ -8259,7 +8259,7 @@
         <v>49</v>
       </c>
       <c r="D71" t="s">
-        <v>82</v>
+        <v>56</v>
       </c>
       <c r="E71">
         <v>0.49118125000000001</v>
@@ -8315,7 +8315,7 @@
         <v>49</v>
       </c>
       <c r="D72" t="s">
-        <v>82</v>
+        <v>56</v>
       </c>
       <c r="E72">
         <v>0.49118125000000001</v>
@@ -8371,7 +8371,7 @@
         <v>49</v>
       </c>
       <c r="D73" t="s">
-        <v>53</v>
+        <v>78</v>
       </c>
       <c r="E73">
         <v>0.49118125000000001</v>
@@ -8427,7 +8427,7 @@
         <v>49</v>
       </c>
       <c r="D74" t="s">
-        <v>53</v>
+        <v>78</v>
       </c>
       <c r="E74">
         <v>0.49118125000000001</v>
@@ -8483,7 +8483,7 @@
         <v>49</v>
       </c>
       <c r="D75" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="E75">
         <v>0.50470000000000004</v>
@@ -8539,7 +8539,7 @@
         <v>49</v>
       </c>
       <c r="D76" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="E76">
         <v>0.49118125000000001</v>
@@ -8595,7 +8595,7 @@
         <v>49</v>
       </c>
       <c r="D77" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="E77">
         <v>0.49118125000000001</v>
@@ -8763,7 +8763,7 @@
         <v>49</v>
       </c>
       <c r="D80" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E80">
         <v>0.49118125000000001</v>
@@ -8819,7 +8819,7 @@
         <v>49</v>
       </c>
       <c r="D81" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E81">
         <v>0.49118125000000001</v>
@@ -8875,7 +8875,7 @@
         <v>49</v>
       </c>
       <c r="D82" t="s">
-        <v>57</v>
+        <v>82</v>
       </c>
       <c r="E82">
         <v>0.49118125000000001</v>
@@ -8931,7 +8931,7 @@
         <v>49</v>
       </c>
       <c r="D83" t="s">
-        <v>57</v>
+        <v>82</v>
       </c>
       <c r="E83">
         <v>0.49118125000000001</v>
@@ -8987,7 +8987,7 @@
         <v>49</v>
       </c>
       <c r="D84" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E84">
         <v>0.49118125000000001</v>
@@ -9043,7 +9043,7 @@
         <v>49</v>
       </c>
       <c r="D85" t="s">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="E85">
         <v>0.49118125000000001</v>
@@ -9099,7 +9099,7 @@
         <v>49</v>
       </c>
       <c r="D86" t="s">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="E86">
         <v>0.49118125000000001</v>
@@ -9155,7 +9155,7 @@
         <v>49</v>
       </c>
       <c r="D87" t="s">
-        <v>81</v>
+        <v>57</v>
       </c>
       <c r="E87">
         <v>0.49118125000000001</v>
@@ -9211,7 +9211,7 @@
         <v>49</v>
       </c>
       <c r="D88" t="s">
-        <v>81</v>
+        <v>57</v>
       </c>
       <c r="E88">
         <v>0.49118125000000001</v>
@@ -9267,7 +9267,7 @@
         <v>49</v>
       </c>
       <c r="D89" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="E89">
         <v>0.52272499999999988</v>
@@ -9323,7 +9323,7 @@
         <v>49</v>
       </c>
       <c r="D90" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="E90">
         <v>0.49118125000000001</v>
@@ -9379,7 +9379,7 @@
         <v>49</v>
       </c>
       <c r="D91" t="s">
-        <v>50</v>
+        <v>79</v>
       </c>
       <c r="E91">
         <v>0.49118125000000001</v>
@@ -9435,7 +9435,7 @@
         <v>49</v>
       </c>
       <c r="D92" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="E92">
         <v>0.52272499999999988</v>
@@ -9491,7 +9491,7 @@
         <v>49</v>
       </c>
       <c r="D93" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="E93">
         <v>0.49118125000000001</v>
@@ -9547,7 +9547,7 @@
         <v>49</v>
       </c>
       <c r="D94" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="E94">
         <v>0.49118125000000001</v>
@@ -9659,7 +9659,7 @@
         <v>49</v>
       </c>
       <c r="D96" t="s">
-        <v>76</v>
+        <v>51</v>
       </c>
       <c r="E96">
         <v>0.49118125000000001</v>
@@ -9715,7 +9715,7 @@
         <v>49</v>
       </c>
       <c r="D97" t="s">
-        <v>52</v>
+        <v>86</v>
       </c>
       <c r="E97">
         <v>0.49118125000000001</v>
@@ -9939,7 +9939,7 @@
         <v>49</v>
       </c>
       <c r="D101" t="s">
-        <v>76</v>
+        <v>51</v>
       </c>
       <c r="E101">
         <v>0.54075000000000006</v>
@@ -10107,7 +10107,7 @@
         <v>49</v>
       </c>
       <c r="D104" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="E104">
         <v>0.49118125000000001</v>
@@ -10219,7 +10219,7 @@
         <v>49</v>
       </c>
       <c r="D106" t="s">
-        <v>82</v>
+        <v>56</v>
       </c>
       <c r="E106">
         <v>0.450625</v>
@@ -10275,7 +10275,7 @@
         <v>49</v>
       </c>
       <c r="D107" t="s">
-        <v>82</v>
+        <v>56</v>
       </c>
       <c r="E107">
         <v>0.450625</v>
@@ -10331,7 +10331,7 @@
         <v>49</v>
       </c>
       <c r="D108" t="s">
-        <v>68</v>
+        <v>53</v>
       </c>
       <c r="E108">
         <v>0.47315625000000006</v>
@@ -10443,7 +10443,7 @@
         <v>49</v>
       </c>
       <c r="D110" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="E110">
         <v>0.49118125000000001</v>
@@ -10499,7 +10499,7 @@
         <v>49</v>
       </c>
       <c r="D111" t="s">
-        <v>75</v>
+        <v>52</v>
       </c>
       <c r="E111">
         <v>0.46865000000000007</v>
@@ -10611,7 +10611,7 @@
         <v>49</v>
       </c>
       <c r="D113" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="E113">
         <v>0.49118125000000001</v>
@@ -11059,7 +11059,7 @@
         <v>49</v>
       </c>
       <c r="D121" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E121">
         <v>0.54075000000000006</v>
@@ -11227,7 +11227,7 @@
         <v>49</v>
       </c>
       <c r="D124" t="s">
-        <v>34</v>
+        <v>75</v>
       </c>
       <c r="E124">
         <v>0.54075000000000006</v>
@@ -11283,7 +11283,7 @@
         <v>49</v>
       </c>
       <c r="D125" t="s">
-        <v>75</v>
+        <v>21</v>
       </c>
       <c r="E125">
         <v>0.54075000000000006</v>
@@ -11507,7 +11507,7 @@
         <v>49</v>
       </c>
       <c r="D129" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E129">
         <v>0.54075000000000006</v>
@@ -11563,7 +11563,7 @@
         <v>49</v>
       </c>
       <c r="D130" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E130">
         <v>0.54075000000000006</v>
@@ -11619,7 +11619,7 @@
         <v>49</v>
       </c>
       <c r="D131" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E131">
         <v>0.54075000000000006</v>
@@ -11675,7 +11675,7 @@
         <v>49</v>
       </c>
       <c r="D132" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E132">
         <v>0.54075000000000006</v>
@@ -11731,7 +11731,7 @@
         <v>49</v>
       </c>
       <c r="D133" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E133">
         <v>0.54075000000000006</v>
@@ -11787,7 +11787,7 @@
         <v>49</v>
       </c>
       <c r="D134" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E134">
         <v>0.54075000000000006</v>
@@ -11899,7 +11899,7 @@
         <v>49</v>
       </c>
       <c r="D136" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E136">
         <v>0.54075000000000006</v>
@@ -11955,7 +11955,7 @@
         <v>49</v>
       </c>
       <c r="D137" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E137">
         <v>0.54075000000000006</v>
@@ -12011,7 +12011,7 @@
         <v>49</v>
       </c>
       <c r="D138" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E138">
         <v>0.54075000000000006</v>
@@ -12067,7 +12067,7 @@
         <v>49</v>
       </c>
       <c r="D139" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E139">
         <v>0.54075000000000006</v>
@@ -12123,7 +12123,7 @@
         <v>49</v>
       </c>
       <c r="D140" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E140">
         <v>0.54075000000000006</v>
@@ -12179,7 +12179,7 @@
         <v>49</v>
       </c>
       <c r="D141" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E141">
         <v>0.54075000000000006</v>
@@ -12235,7 +12235,7 @@
         <v>49</v>
       </c>
       <c r="D142" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E142">
         <v>0.54075000000000006</v>
@@ -12291,7 +12291,7 @@
         <v>49</v>
       </c>
       <c r="D143" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E143">
         <v>0.54075000000000006</v>
@@ -12347,7 +12347,7 @@
         <v>49</v>
       </c>
       <c r="D144" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E144">
         <v>0.54075000000000006</v>
@@ -12515,7 +12515,7 @@
         <v>49</v>
       </c>
       <c r="D147" t="s">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="E147">
         <v>0.54075000000000006</v>
@@ -12571,7 +12571,7 @@
         <v>49</v>
       </c>
       <c r="D148" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E148">
         <v>0.54075000000000006</v>
@@ -12627,7 +12627,7 @@
         <v>49</v>
       </c>
       <c r="D149" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E149">
         <v>0.54075000000000006</v>
@@ -12683,7 +12683,7 @@
         <v>49</v>
       </c>
       <c r="D150" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E150">
         <v>0.54075000000000006</v>
@@ -12739,7 +12739,7 @@
         <v>49</v>
       </c>
       <c r="D151" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E151">
         <v>0.54075000000000006</v>
@@ -12795,7 +12795,7 @@
         <v>49</v>
       </c>
       <c r="D152" t="s">
-        <v>19</v>
+        <v>74</v>
       </c>
       <c r="E152">
         <v>0.54075000000000006</v>
@@ -12851,7 +12851,7 @@
         <v>49</v>
       </c>
       <c r="D153" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E153">
         <v>0.54075000000000006</v>
@@ -13019,7 +13019,7 @@
         <v>49</v>
       </c>
       <c r="D156" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E156">
         <v>0.54075000000000006</v>
@@ -13467,7 +13467,7 @@
         <v>49</v>
       </c>
       <c r="D164" t="s">
-        <v>68</v>
+        <v>53</v>
       </c>
       <c r="E164">
         <v>0.48667500000000002</v>
@@ -14307,7 +14307,7 @@
         <v>49</v>
       </c>
       <c r="D179" t="s">
-        <v>76</v>
+        <v>51</v>
       </c>
       <c r="E179">
         <v>0.46865000000000007</v>
@@ -14363,7 +14363,7 @@
         <v>49</v>
       </c>
       <c r="D180" t="s">
-        <v>76</v>
+        <v>51</v>
       </c>
       <c r="E180">
         <v>0.46865000000000007</v>
@@ -14587,7 +14587,7 @@
         <v>49</v>
       </c>
       <c r="D184" t="s">
-        <v>82</v>
+        <v>56</v>
       </c>
       <c r="E184">
         <v>0.48667500000000002</v>
@@ -14643,7 +14643,7 @@
         <v>49</v>
       </c>
       <c r="D185" t="s">
-        <v>82</v>
+        <v>56</v>
       </c>
       <c r="E185">
         <v>0.48667500000000002</v>
@@ -15371,7 +15371,7 @@
         <v>49</v>
       </c>
       <c r="D198" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E198">
         <v>0.50470000000000004</v>
@@ -16323,7 +16323,7 @@
         <v>49</v>
       </c>
       <c r="D215" t="s">
-        <v>57</v>
+        <v>82</v>
       </c>
       <c r="E215">
         <v>0.450625</v>
@@ -16491,7 +16491,7 @@
         <v>49</v>
       </c>
       <c r="D218" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E218">
         <v>0.50470000000000004</v>
@@ -16547,7 +16547,7 @@
         <v>49</v>
       </c>
       <c r="D219" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E219">
         <v>0.50470000000000004</v>
@@ -16715,7 +16715,7 @@
         <v>49</v>
       </c>
       <c r="D222" t="s">
-        <v>51</v>
+        <v>81</v>
       </c>
       <c r="E222">
         <v>0.450625</v>
@@ -16771,7 +16771,7 @@
         <v>49</v>
       </c>
       <c r="D223" t="s">
-        <v>81</v>
+        <v>57</v>
       </c>
       <c r="E223">
         <v>0.29741250000000002</v>
@@ -16827,7 +16827,7 @@
         <v>49</v>
       </c>
       <c r="D224" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="E224">
         <v>0.28839999999999999</v>
@@ -16883,7 +16883,7 @@
         <v>49</v>
       </c>
       <c r="D225" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="E225">
         <v>0.28839999999999999</v>
@@ -16939,7 +16939,7 @@
         <v>49</v>
       </c>
       <c r="D226" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="E226">
         <v>0.24784375000000003</v>
@@ -17443,7 +17443,7 @@
         <v>49</v>
       </c>
       <c r="D235" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="E235">
         <v>0.25235000000000002</v>
@@ -17723,7 +17723,7 @@
         <v>49</v>
       </c>
       <c r="D240" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="E240">
         <v>0.27938750000000001</v>
@@ -18031,7 +18031,7 @@
         <v>49</v>
       </c>
       <c r="D247" t="s">
-        <v>67</v>
+        <v>54</v>
       </c>
       <c r="E247">
         <v>0.32445000000000007</v>
@@ -18101,7 +18101,7 @@
         <v>49</v>
       </c>
       <c r="D249" t="s">
-        <v>50</v>
+        <v>79</v>
       </c>
       <c r="E249">
         <v>0.32445000000000002</v>
@@ -18241,7 +18241,7 @@
         <v>49</v>
       </c>
       <c r="D253" t="s">
-        <v>68</v>
+        <v>53</v>
       </c>
       <c r="E253">
         <v>0.27938750000000001</v>
@@ -18276,7 +18276,7 @@
         <v>49</v>
       </c>
       <c r="D254" t="s">
-        <v>68</v>
+        <v>53</v>
       </c>
       <c r="E254">
         <v>0.27938750000000001</v>
@@ -18311,7 +18311,7 @@
         <v>49</v>
       </c>
       <c r="D255" t="s">
-        <v>68</v>
+        <v>53</v>
       </c>
       <c r="E255">
         <v>0.27938750000000001</v>
@@ -18451,7 +18451,7 @@
         <v>49</v>
       </c>
       <c r="D259" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="E259">
         <v>0.26136249999999994</v>
@@ -18486,7 +18486,7 @@
         <v>49</v>
       </c>
       <c r="D260" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E260">
         <v>0.28839999999999999</v>
@@ -18521,7 +18521,7 @@
         <v>49</v>
       </c>
       <c r="D261" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E261">
         <v>0.28839999999999999</v>
@@ -18556,7 +18556,7 @@
         <v>49</v>
       </c>
       <c r="D262" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E262">
         <v>0.28839999999999999</v>
@@ -18626,7 +18626,7 @@
         <v>439</v>
       </c>
       <c r="D264" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E264">
         <v>0.41457500000000003</v>
@@ -18731,7 +18731,7 @@
         <v>439</v>
       </c>
       <c r="D267" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E267">
         <v>0.22981874999999999</v>
@@ -18766,7 +18766,7 @@
         <v>439</v>
       </c>
       <c r="D268" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E268">
         <v>0.24333750000000001</v>
@@ -18941,7 +18941,7 @@
         <v>439</v>
       </c>
       <c r="D273" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E273">
         <v>0.27938750000000001</v>
@@ -19149,7 +19149,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2ACDE4EF-75AA-4582-AACC-29C11C0F2FA8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0D9870CC-17A2-4C55-BCFE-5422EEA2AA86}">
   <dimension ref="B9:T842"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -19231,19 +19231,19 @@
         <v>2022</v>
       </c>
       <c r="F11">
-        <v>0.39440677966101695</v>
+        <v>0.22450847457627116</v>
       </c>
       <c r="G11">
-        <v>0.36049999999999999</v>
+        <v>0.33990000000000004</v>
       </c>
       <c r="H11">
-        <v>3850.0000000000005</v>
+        <v>4427.5</v>
       </c>
       <c r="I11">
-        <v>143</v>
+        <v>157.30000000000001</v>
       </c>
       <c r="J11">
-        <v>8.4</v>
+        <v>9.240000000000002</v>
       </c>
       <c r="K11">
         <v>50</v>
@@ -19284,7 +19284,7 @@
         <v>2022</v>
       </c>
       <c r="F12">
-        <v>0.51576271186440681</v>
+        <v>1.0679322033898306</v>
       </c>
       <c r="G12">
         <v>0.36049999999999999</v>
@@ -19337,13 +19337,13 @@
         <v>2022</v>
       </c>
       <c r="F13">
-        <v>1.0679322033898306</v>
+        <v>0.35800000000000004</v>
       </c>
       <c r="G13">
-        <v>0.36049999999999999</v>
+        <v>0.36050000000000004</v>
       </c>
       <c r="H13">
-        <v>3850.0000000000005</v>
+        <v>3850.0000000000009</v>
       </c>
       <c r="I13">
         <v>143</v>
@@ -19390,13 +19390,13 @@
         <v>2022</v>
       </c>
       <c r="F14">
-        <v>0.35800000000000004</v>
+        <v>0.39440677966101695</v>
       </c>
       <c r="G14">
-        <v>0.36050000000000004</v>
+        <v>0.36049999999999999</v>
       </c>
       <c r="H14">
-        <v>3850.0000000000009</v>
+        <v>3850.0000000000005</v>
       </c>
       <c r="I14">
         <v>143</v>
@@ -19496,7 +19496,7 @@
         <v>2022</v>
       </c>
       <c r="F16">
-        <v>0.27911864406779663</v>
+        <v>0.24877966101694915</v>
       </c>
       <c r="G16">
         <v>0.33990000000000004</v>
@@ -19549,19 +19549,19 @@
         <v>2022</v>
       </c>
       <c r="F17">
-        <v>0.22450847457627116</v>
+        <v>0.51576271186440681</v>
       </c>
       <c r="G17">
-        <v>0.33990000000000004</v>
+        <v>0.36049999999999999</v>
       </c>
       <c r="H17">
-        <v>4427.5</v>
+        <v>3850.0000000000005</v>
       </c>
       <c r="I17">
-        <v>157.30000000000001</v>
+        <v>143</v>
       </c>
       <c r="J17">
-        <v>9.240000000000002</v>
+        <v>8.4</v>
       </c>
       <c r="K17">
         <v>50</v>
@@ -19602,7 +19602,7 @@
         <v>2022</v>
       </c>
       <c r="F18">
-        <v>0.24877966101694915</v>
+        <v>0.27911864406779663</v>
       </c>
       <c r="G18">
         <v>0.33990000000000004</v>
@@ -19649,7 +19649,7 @@
         <v>13</v>
       </c>
       <c r="D19" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E19">
         <v>2008</v>
@@ -19702,7 +19702,7 @@
         <v>13</v>
       </c>
       <c r="D20" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E20">
         <v>1998</v>
@@ -19808,7 +19808,7 @@
         <v>13</v>
       </c>
       <c r="D22" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E22">
         <v>2001</v>
@@ -19861,7 +19861,7 @@
         <v>13</v>
       </c>
       <c r="D23" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E23">
         <v>2013</v>
@@ -19914,7 +19914,7 @@
         <v>13</v>
       </c>
       <c r="D24" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E24">
         <v>1965</v>
@@ -19967,7 +19967,7 @@
         <v>13</v>
       </c>
       <c r="D25" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E25">
         <v>2003</v>
@@ -20020,7 +20020,7 @@
         <v>13</v>
       </c>
       <c r="D26" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="E26">
         <v>2009</v>
@@ -20126,7 +20126,7 @@
         <v>13</v>
       </c>
       <c r="D28" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E28">
         <v>2009</v>
@@ -20185,19 +20185,19 @@
         <v>2022</v>
       </c>
       <c r="F29">
-        <v>0.61803468208092449</v>
+        <v>0.18416184971098257</v>
       </c>
       <c r="G29">
-        <v>0.37080000000000002</v>
+        <v>0.35020000000000001</v>
       </c>
       <c r="H29">
-        <v>2200</v>
+        <v>2530</v>
       </c>
       <c r="I29">
-        <v>66</v>
+        <v>72.600000000000009</v>
       </c>
       <c r="J29">
-        <v>5.25</v>
+        <v>5.7750000000000004</v>
       </c>
       <c r="K29">
         <v>50</v>
@@ -20238,10 +20238,10 @@
         <v>2022</v>
       </c>
       <c r="F30">
-        <v>0.18416184971098257</v>
+        <v>0.1997687861271675</v>
       </c>
       <c r="G30">
-        <v>0.35020000000000001</v>
+        <v>0.35020000000000007</v>
       </c>
       <c r="H30">
         <v>2530</v>
@@ -20344,19 +20344,19 @@
         <v>2022</v>
       </c>
       <c r="F32">
-        <v>0.1997687861271675</v>
+        <v>0.61803468208092449</v>
       </c>
       <c r="G32">
-        <v>0.35020000000000007</v>
+        <v>0.37080000000000002</v>
       </c>
       <c r="H32">
-        <v>2530</v>
+        <v>2200</v>
       </c>
       <c r="I32">
-        <v>72.600000000000009</v>
+        <v>66</v>
       </c>
       <c r="J32">
-        <v>5.7750000000000004</v>
+        <v>5.25</v>
       </c>
       <c r="K32">
         <v>50</v>
@@ -20391,7 +20391,7 @@
         <v>33</v>
       </c>
       <c r="D33" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E33">
         <v>1992</v>
@@ -20444,7 +20444,7 @@
         <v>33</v>
       </c>
       <c r="D34" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E34">
         <v>1993</v>
@@ -20497,7 +20497,7 @@
         <v>33</v>
       </c>
       <c r="D35" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E35">
         <v>2005</v>
@@ -20550,7 +20550,7 @@
         <v>33</v>
       </c>
       <c r="D36" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E36">
         <v>1986</v>
@@ -20762,7 +20762,7 @@
         <v>33</v>
       </c>
       <c r="D40" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="E40">
         <v>2009</v>
@@ -20815,7 +20815,7 @@
         <v>33</v>
       </c>
       <c r="D41" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="E41">
         <v>2010</v>
@@ -20868,7 +20868,7 @@
         <v>33</v>
       </c>
       <c r="D42" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="E42">
         <v>2010</v>
@@ -20927,7 +20927,7 @@
         <v>2022</v>
       </c>
       <c r="F43">
-        <v>0.20557907614758497</v>
+        <v>0.19676367392472002</v>
       </c>
       <c r="G43">
         <v>0.59739999999999993</v>
@@ -20980,19 +20980,19 @@
         <v>2022</v>
       </c>
       <c r="F44">
-        <v>0.20212110068999706</v>
+        <v>0.3567559186877659</v>
       </c>
       <c r="G44">
-        <v>0.59739999999999993</v>
+        <v>0.61799999999999999</v>
       </c>
       <c r="H44">
-        <v>1265</v>
+        <v>1100</v>
       </c>
       <c r="I44">
-        <v>36.300000000000004</v>
+        <v>33</v>
       </c>
       <c r="J44">
-        <v>3.4650000000000003</v>
+        <v>3.1500000000000004</v>
       </c>
       <c r="K44">
         <v>50</v>
@@ -21027,13 +21027,13 @@
         <v>49</v>
       </c>
       <c r="D45" t="s">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="E45">
         <v>2022</v>
       </c>
       <c r="F45">
-        <v>0.19481551873734657</v>
+        <v>0.27761211420071885</v>
       </c>
       <c r="G45">
         <v>0.59739999999999993</v>
@@ -21080,25 +21080,25 @@
         <v>49</v>
       </c>
       <c r="D46" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E46">
         <v>2022</v>
       </c>
       <c r="F46">
-        <v>0.18702289798785268</v>
+        <v>0.30829555840185086</v>
       </c>
       <c r="G46">
-        <v>0.59739999999999993</v>
+        <v>0.61799999999999999</v>
       </c>
       <c r="H46">
-        <v>1265</v>
+        <v>1100</v>
       </c>
       <c r="I46">
-        <v>36.300000000000004</v>
+        <v>33</v>
       </c>
       <c r="J46">
-        <v>3.4650000000000003</v>
+        <v>3.1500000000000004</v>
       </c>
       <c r="K46">
         <v>50</v>
@@ -21133,13 +21133,13 @@
         <v>49</v>
       </c>
       <c r="D47" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E47">
         <v>2022</v>
       </c>
       <c r="F47">
-        <v>0.27347228442755023</v>
+        <v>0.26604494277568891</v>
       </c>
       <c r="G47">
         <v>0.59739999999999993</v>
@@ -21186,13 +21186,13 @@
         <v>49</v>
       </c>
       <c r="D48" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E48">
         <v>2022</v>
       </c>
       <c r="F48">
-        <v>0.1548783373961905</v>
+        <v>0.23280454489112914</v>
       </c>
       <c r="G48">
         <v>0.59739999999999993</v>
@@ -21204,7 +21204,7 @@
         <v>36.300000000000004</v>
       </c>
       <c r="J48">
-        <v>3.4649999999999999</v>
+        <v>3.4650000000000007</v>
       </c>
       <c r="K48">
         <v>50</v>
@@ -21239,7 +21239,7 @@
         <v>49</v>
       </c>
       <c r="D49" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E49">
         <v>2022</v>
@@ -21292,25 +21292,25 @@
         <v>49</v>
       </c>
       <c r="D50" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E50">
         <v>2022</v>
       </c>
       <c r="F50">
-        <v>0.29344087509812827</v>
+        <v>0.45732943023592104</v>
       </c>
       <c r="G50">
-        <v>0.59739999999999993</v>
+        <v>0.61799999999999999</v>
       </c>
       <c r="H50">
-        <v>1265</v>
+        <v>1100</v>
       </c>
       <c r="I50">
-        <v>36.300000000000004</v>
+        <v>33</v>
       </c>
       <c r="J50">
-        <v>3.4650000000000003</v>
+        <v>3.1500000000000004</v>
       </c>
       <c r="K50">
         <v>50</v>
@@ -21345,25 +21345,25 @@
         <v>49</v>
       </c>
       <c r="D51" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E51">
         <v>2022</v>
       </c>
       <c r="F51">
-        <v>0.20820908565053911</v>
+        <v>0.49339465314217229</v>
       </c>
       <c r="G51">
-        <v>0.59739999999999993</v>
+        <v>0.61799999999999999</v>
       </c>
       <c r="H51">
-        <v>1265</v>
+        <v>1100</v>
       </c>
       <c r="I51">
-        <v>36.300000000000004</v>
+        <v>33</v>
       </c>
       <c r="J51">
-        <v>3.4650000000000007</v>
+        <v>3.1500000000000004</v>
       </c>
       <c r="K51">
         <v>50</v>
@@ -21398,13 +21398,13 @@
         <v>49</v>
       </c>
       <c r="D52" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E52">
         <v>2022</v>
       </c>
       <c r="F52">
-        <v>0.18629233979258764</v>
+        <v>0.20820908565053911</v>
       </c>
       <c r="G52">
         <v>0.59739999999999993</v>
@@ -21416,7 +21416,7 @@
         <v>36.300000000000004</v>
       </c>
       <c r="J52">
-        <v>3.4650000000000003</v>
+        <v>3.4650000000000007</v>
       </c>
       <c r="K52">
         <v>50</v>
@@ -21451,13 +21451,13 @@
         <v>49</v>
       </c>
       <c r="D53" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E53">
         <v>2022</v>
       </c>
       <c r="F53">
-        <v>0.20236462008841874</v>
+        <v>0.18629233979258764</v>
       </c>
       <c r="G53">
         <v>0.59739999999999993</v>
@@ -21504,13 +21504,13 @@
         <v>49</v>
       </c>
       <c r="D54" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E54">
         <v>2022</v>
       </c>
       <c r="F54">
-        <v>0.17484692806676855</v>
+        <v>0.20236462008841874</v>
       </c>
       <c r="G54">
         <v>0.59739999999999993</v>
@@ -21557,13 +21557,13 @@
         <v>49</v>
       </c>
       <c r="D55" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E55">
         <v>2022</v>
       </c>
       <c r="F55">
-        <v>0.18872753377680451</v>
+        <v>0.22793415692269547</v>
       </c>
       <c r="G55">
         <v>0.59739999999999993</v>
@@ -21575,7 +21575,7 @@
         <v>36.300000000000004</v>
       </c>
       <c r="J55">
-        <v>3.4650000000000007</v>
+        <v>3.4650000000000003</v>
       </c>
       <c r="K55">
         <v>50</v>
@@ -21610,13 +21610,13 @@
         <v>49</v>
       </c>
       <c r="D56" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E56">
         <v>2022</v>
       </c>
       <c r="F56">
-        <v>0.19481551873734657</v>
+        <v>0.1548783373961905</v>
       </c>
       <c r="G56">
         <v>0.59739999999999993</v>
@@ -21628,7 +21628,7 @@
         <v>36.300000000000004</v>
       </c>
       <c r="J56">
-        <v>3.4650000000000003</v>
+        <v>3.4649999999999999</v>
       </c>
       <c r="K56">
         <v>50</v>
@@ -21663,13 +21663,13 @@
         <v>49</v>
       </c>
       <c r="D57" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E57">
         <v>2022</v>
       </c>
       <c r="F57">
-        <v>0.22793415692269547</v>
+        <v>0.18556178159732259</v>
       </c>
       <c r="G57">
         <v>0.59739999999999993</v>
@@ -21716,13 +21716,13 @@
         <v>49</v>
       </c>
       <c r="D58" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E58">
         <v>2022</v>
       </c>
       <c r="F58">
-        <v>0.19481551873734657</v>
+        <v>0.27347228442755023</v>
       </c>
       <c r="G58">
         <v>0.59739999999999993</v>
@@ -21769,13 +21769,13 @@
         <v>49</v>
       </c>
       <c r="D59" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E59">
         <v>2022</v>
       </c>
       <c r="F59">
-        <v>0.18556178159732259</v>
+        <v>0.19481551873734657</v>
       </c>
       <c r="G59">
         <v>0.59739999999999993</v>
@@ -21822,13 +21822,13 @@
         <v>49</v>
       </c>
       <c r="D60" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E60">
         <v>2022</v>
       </c>
       <c r="F60">
-        <v>0.23280454489112914</v>
+        <v>0.19481551873734657</v>
       </c>
       <c r="G60">
         <v>0.59739999999999993</v>
@@ -21840,7 +21840,7 @@
         <v>36.300000000000004</v>
       </c>
       <c r="J60">
-        <v>3.4650000000000007</v>
+        <v>3.4650000000000003</v>
       </c>
       <c r="K60">
         <v>50</v>
@@ -21875,13 +21875,13 @@
         <v>49</v>
       </c>
       <c r="D61" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E61">
         <v>2022</v>
       </c>
       <c r="F61">
-        <v>0.26604494277568891</v>
+        <v>0.19481551873734657</v>
       </c>
       <c r="G61">
         <v>0.59739999999999993</v>
@@ -21928,13 +21928,13 @@
         <v>49</v>
       </c>
       <c r="D62" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E62">
         <v>2022</v>
       </c>
       <c r="F62">
-        <v>0.19481551873734657</v>
+        <v>0.17484692806676855</v>
       </c>
       <c r="G62">
         <v>0.59739999999999993</v>
@@ -21981,13 +21981,13 @@
         <v>49</v>
       </c>
       <c r="D63" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E63">
         <v>2022</v>
       </c>
       <c r="F63">
-        <v>0.21113131843159935</v>
+        <v>0.18872753377680451</v>
       </c>
       <c r="G63">
         <v>0.59739999999999993</v>
@@ -21999,7 +21999,7 @@
         <v>36.300000000000004</v>
       </c>
       <c r="J63">
-        <v>3.4650000000000003</v>
+        <v>3.4650000000000007</v>
       </c>
       <c r="K63">
         <v>50</v>
@@ -22034,13 +22034,13 @@
         <v>49</v>
       </c>
       <c r="D64" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E64">
         <v>2022</v>
       </c>
       <c r="F64">
-        <v>0.19627663512787666</v>
+        <v>0.21113131843159935</v>
       </c>
       <c r="G64">
         <v>0.59739999999999993</v>
@@ -22052,7 +22052,7 @@
         <v>36.300000000000004</v>
       </c>
       <c r="J64">
-        <v>3.4649999999999999</v>
+        <v>3.4650000000000003</v>
       </c>
       <c r="K64">
         <v>50</v>
@@ -22087,13 +22087,13 @@
         <v>49</v>
       </c>
       <c r="D65" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E65">
         <v>2022</v>
       </c>
       <c r="F65">
-        <v>0.18824049497996109</v>
+        <v>0.19627663512787666</v>
       </c>
       <c r="G65">
         <v>0.59739999999999993</v>
@@ -22105,7 +22105,7 @@
         <v>36.300000000000004</v>
       </c>
       <c r="J65">
-        <v>3.4650000000000003</v>
+        <v>3.4649999999999999</v>
       </c>
       <c r="K65">
         <v>50</v>
@@ -22140,25 +22140,25 @@
         <v>49</v>
       </c>
       <c r="D66" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E66">
         <v>2022</v>
       </c>
       <c r="F66">
-        <v>0.43468212618270452</v>
+        <v>0.18824049497996109</v>
       </c>
       <c r="G66">
-        <v>0.61799999999999988</v>
+        <v>0.59739999999999993</v>
       </c>
       <c r="H66">
-        <v>1100</v>
+        <v>1265</v>
       </c>
       <c r="I66">
-        <v>33</v>
+        <v>36.300000000000004</v>
       </c>
       <c r="J66">
-        <v>3.1500000000000004</v>
+        <v>3.4650000000000003</v>
       </c>
       <c r="K66">
         <v>50</v>
@@ -22193,25 +22193,25 @@
         <v>49</v>
       </c>
       <c r="D67" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E67">
         <v>2022</v>
       </c>
       <c r="F67">
-        <v>0.21283595422055113</v>
+        <v>0.37112356319464518</v>
       </c>
       <c r="G67">
-        <v>0.59739999999999993</v>
+        <v>0.61799999999999999</v>
       </c>
       <c r="H67">
-        <v>1265</v>
+        <v>1100</v>
       </c>
       <c r="I67">
-        <v>36.300000000000004</v>
+        <v>33</v>
       </c>
       <c r="J67">
-        <v>3.4650000000000003</v>
+        <v>3.1500000000000004</v>
       </c>
       <c r="K67">
         <v>50</v>
@@ -22246,25 +22246,25 @@
         <v>49</v>
       </c>
       <c r="D68" t="s">
-        <v>19</v>
+        <v>74</v>
       </c>
       <c r="E68">
         <v>2022</v>
       </c>
       <c r="F68">
-        <v>0.19822479031525012</v>
+        <v>0.43468212618270452</v>
       </c>
       <c r="G68">
-        <v>0.59739999999999993</v>
+        <v>0.61799999999999988</v>
       </c>
       <c r="H68">
-        <v>1265</v>
+        <v>1100</v>
       </c>
       <c r="I68">
-        <v>36.300000000000004</v>
+        <v>33</v>
       </c>
       <c r="J68">
-        <v>3.4650000000000003</v>
+        <v>3.1500000000000004</v>
       </c>
       <c r="K68">
         <v>50</v>
@@ -22299,25 +22299,25 @@
         <v>49</v>
       </c>
       <c r="D69" t="s">
-        <v>75</v>
+        <v>21</v>
       </c>
       <c r="E69">
         <v>2022</v>
       </c>
       <c r="F69">
-        <v>0.30829555840185086</v>
+        <v>0.19822479031525012</v>
       </c>
       <c r="G69">
-        <v>0.61799999999999999</v>
+        <v>0.59739999999999993</v>
       </c>
       <c r="H69">
-        <v>1100</v>
+        <v>1265</v>
       </c>
       <c r="I69">
-        <v>33</v>
+        <v>36.300000000000004</v>
       </c>
       <c r="J69">
-        <v>3.1500000000000004</v>
+        <v>3.4650000000000003</v>
       </c>
       <c r="K69">
         <v>50</v>
@@ -22352,13 +22352,13 @@
         <v>49</v>
       </c>
       <c r="D70" t="s">
-        <v>34</v>
+        <v>75</v>
       </c>
       <c r="E70">
         <v>2022</v>
       </c>
       <c r="F70">
-        <v>0.27761211420071885</v>
+        <v>0.28443065735652601</v>
       </c>
       <c r="G70">
         <v>0.59739999999999993</v>
@@ -22411,7 +22411,7 @@
         <v>2022</v>
       </c>
       <c r="F71">
-        <v>0.3567559186877659</v>
+        <v>0.39839773581787374</v>
       </c>
       <c r="G71">
         <v>0.61799999999999999</v>
@@ -22464,7 +22464,7 @@
         <v>2022</v>
       </c>
       <c r="F72">
-        <v>0.18507474280047922</v>
+        <v>0.21283595422055113</v>
       </c>
       <c r="G72">
         <v>0.59739999999999993</v>
@@ -22476,7 +22476,7 @@
         <v>36.300000000000004</v>
       </c>
       <c r="J72">
-        <v>3.4649999999999999</v>
+        <v>3.4650000000000003</v>
       </c>
       <c r="K72">
         <v>50</v>
@@ -22517,7 +22517,7 @@
         <v>2022</v>
       </c>
       <c r="F73">
-        <v>0.19676367392472002</v>
+        <v>0.18702289798785268</v>
       </c>
       <c r="G73">
         <v>0.59739999999999993</v>
@@ -22570,19 +22570,19 @@
         <v>2022</v>
       </c>
       <c r="F74">
-        <v>0.39839773581787374</v>
+        <v>0.20557907614758497</v>
       </c>
       <c r="G74">
-        <v>0.61799999999999999</v>
+        <v>0.59739999999999993</v>
       </c>
       <c r="H74">
-        <v>1100</v>
+        <v>1265</v>
       </c>
       <c r="I74">
-        <v>33</v>
+        <v>36.300000000000004</v>
       </c>
       <c r="J74">
-        <v>3.1500000000000004</v>
+        <v>3.4650000000000003</v>
       </c>
       <c r="K74">
         <v>50</v>
@@ -22623,7 +22623,7 @@
         <v>2022</v>
       </c>
       <c r="F75">
-        <v>0.28443065735652601</v>
+        <v>0.26543614427963469</v>
       </c>
       <c r="G75">
         <v>0.59739999999999993</v>
@@ -22676,19 +22676,19 @@
         <v>2022</v>
       </c>
       <c r="F76">
-        <v>0.49339465314217229</v>
+        <v>0.20212110068999706</v>
       </c>
       <c r="G76">
-        <v>0.61799999999999999</v>
+        <v>0.59739999999999993</v>
       </c>
       <c r="H76">
-        <v>1100</v>
+        <v>1265</v>
       </c>
       <c r="I76">
-        <v>33</v>
+        <v>36.300000000000004</v>
       </c>
       <c r="J76">
-        <v>3.1500000000000004</v>
+        <v>3.4650000000000003</v>
       </c>
       <c r="K76">
         <v>50</v>
@@ -22729,19 +22729,19 @@
         <v>2022</v>
       </c>
       <c r="F77">
-        <v>0.45732943023592104</v>
+        <v>0.29344087509812827</v>
       </c>
       <c r="G77">
-        <v>0.61799999999999999</v>
+        <v>0.59739999999999993</v>
       </c>
       <c r="H77">
-        <v>1100</v>
+        <v>1265</v>
       </c>
       <c r="I77">
-        <v>33</v>
+        <v>36.300000000000004</v>
       </c>
       <c r="J77">
-        <v>3.1500000000000004</v>
+        <v>3.4650000000000003</v>
       </c>
       <c r="K77">
         <v>50</v>
@@ -22888,19 +22888,19 @@
         <v>2022</v>
       </c>
       <c r="F80">
-        <v>0.37112356319464518</v>
+        <v>0.16608022972358796</v>
       </c>
       <c r="G80">
-        <v>0.61799999999999999</v>
+        <v>0.59739999999999993</v>
       </c>
       <c r="H80">
-        <v>1100</v>
+        <v>1265</v>
       </c>
       <c r="I80">
-        <v>33</v>
+        <v>36.300000000000004</v>
       </c>
       <c r="J80">
-        <v>3.1500000000000004</v>
+        <v>3.4650000000000003</v>
       </c>
       <c r="K80">
         <v>50</v>
@@ -22941,7 +22941,7 @@
         <v>2022</v>
       </c>
       <c r="F81">
-        <v>0.16608022972358796</v>
+        <v>0.19481551873734657</v>
       </c>
       <c r="G81">
         <v>0.59739999999999993</v>
@@ -22994,7 +22994,7 @@
         <v>2022</v>
       </c>
       <c r="F82">
-        <v>0.26543614427963469</v>
+        <v>0.18507474280047922</v>
       </c>
       <c r="G82">
         <v>0.59739999999999993</v>
@@ -23006,7 +23006,7 @@
         <v>36.300000000000004</v>
       </c>
       <c r="J82">
-        <v>3.4650000000000003</v>
+        <v>3.4649999999999999</v>
       </c>
       <c r="K82">
         <v>50</v>
@@ -23041,7 +23041,7 @@
         <v>49</v>
       </c>
       <c r="D83" t="s">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="E83">
         <v>2006</v>
@@ -23094,7 +23094,7 @@
         <v>49</v>
       </c>
       <c r="D84" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E84">
         <v>2012</v>
@@ -23147,7 +23147,7 @@
         <v>49</v>
       </c>
       <c r="D85" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E85">
         <v>1993</v>
@@ -23200,7 +23200,7 @@
         <v>49</v>
       </c>
       <c r="D86" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="E86">
         <v>2011</v>
@@ -23465,7 +23465,7 @@
         <v>49</v>
       </c>
       <c r="D91" t="s">
-        <v>67</v>
+        <v>54</v>
       </c>
       <c r="E91">
         <v>2003</v>
@@ -23624,7 +23624,7 @@
         <v>49</v>
       </c>
       <c r="D94" t="s">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="E94">
         <v>2004</v>
@@ -23677,7 +23677,7 @@
         <v>49</v>
       </c>
       <c r="D95" t="s">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="E95">
         <v>2005</v>
@@ -23836,7 +23836,7 @@
         <v>49</v>
       </c>
       <c r="D98" t="s">
-        <v>75</v>
+        <v>52</v>
       </c>
       <c r="E98">
         <v>2004</v>
@@ -23889,7 +23889,7 @@
         <v>49</v>
       </c>
       <c r="D99" t="s">
-        <v>75</v>
+        <v>52</v>
       </c>
       <c r="E99">
         <v>2004</v>
@@ -23942,7 +23942,7 @@
         <v>49</v>
       </c>
       <c r="D100" t="s">
-        <v>75</v>
+        <v>52</v>
       </c>
       <c r="E100">
         <v>2004</v>
@@ -23995,7 +23995,7 @@
         <v>49</v>
       </c>
       <c r="D101" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="E101">
         <v>2008</v>
@@ -24048,7 +24048,7 @@
         <v>49</v>
       </c>
       <c r="D102" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="E102">
         <v>2008</v>
@@ -24101,7 +24101,7 @@
         <v>49</v>
       </c>
       <c r="D103" t="s">
-        <v>85</v>
+        <v>73</v>
       </c>
       <c r="E103">
         <v>2002</v>
@@ -24154,7 +24154,7 @@
         <v>49</v>
       </c>
       <c r="D104" t="s">
-        <v>85</v>
+        <v>73</v>
       </c>
       <c r="E104">
         <v>2002</v>
@@ -24207,7 +24207,7 @@
         <v>49</v>
       </c>
       <c r="D105" t="s">
-        <v>85</v>
+        <v>73</v>
       </c>
       <c r="E105">
         <v>2003</v>
@@ -24260,7 +24260,7 @@
         <v>49</v>
       </c>
       <c r="D106" t="s">
-        <v>85</v>
+        <v>73</v>
       </c>
       <c r="E106">
         <v>2003</v>
@@ -24313,7 +24313,7 @@
         <v>49</v>
       </c>
       <c r="D107" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E107">
         <v>2000</v>
@@ -24366,7 +24366,7 @@
         <v>49</v>
       </c>
       <c r="D108" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E108">
         <v>2000</v>
@@ -24419,7 +24419,7 @@
         <v>49</v>
       </c>
       <c r="D109" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="E109">
         <v>2007</v>
@@ -24472,7 +24472,7 @@
         <v>49</v>
       </c>
       <c r="D110" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E110">
         <v>2023</v>
@@ -24525,7 +24525,7 @@
         <v>49</v>
       </c>
       <c r="D111" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E111">
         <v>2001</v>
@@ -24631,7 +24631,7 @@
         <v>49</v>
       </c>
       <c r="D113" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E113">
         <v>2010</v>
@@ -24684,7 +24684,7 @@
         <v>49</v>
       </c>
       <c r="D114" t="s">
-        <v>51</v>
+        <v>81</v>
       </c>
       <c r="E114">
         <v>2005</v>
@@ -24737,7 +24737,7 @@
         <v>49</v>
       </c>
       <c r="D115" t="s">
-        <v>51</v>
+        <v>81</v>
       </c>
       <c r="E115">
         <v>2009</v>
@@ -24790,7 +24790,7 @@
         <v>49</v>
       </c>
       <c r="D116" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="E116">
         <v>1997</v>
@@ -24843,7 +24843,7 @@
         <v>49</v>
       </c>
       <c r="D117" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="E117">
         <v>1997</v>
@@ -24896,7 +24896,7 @@
         <v>49</v>
       </c>
       <c r="D118" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="E118">
         <v>1998</v>
@@ -24949,7 +24949,7 @@
         <v>49</v>
       </c>
       <c r="D119" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="E119">
         <v>1999</v>
@@ -25055,7 +25055,7 @@
         <v>49</v>
       </c>
       <c r="D121" t="s">
-        <v>82</v>
+        <v>56</v>
       </c>
       <c r="E121">
         <v>2010</v>
@@ -25108,7 +25108,7 @@
         <v>49</v>
       </c>
       <c r="D122" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="E122">
         <v>2003</v>
@@ -25161,7 +25161,7 @@
         <v>49</v>
       </c>
       <c r="D123" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="E123">
         <v>2003</v>
@@ -25373,7 +25373,7 @@
         <v>49</v>
       </c>
       <c r="D127" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="E127">
         <v>2002</v>
@@ -25426,7 +25426,7 @@
         <v>49</v>
       </c>
       <c r="D128" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="E128">
         <v>2002</v>
@@ -25479,7 +25479,7 @@
         <v>49</v>
       </c>
       <c r="D129" t="s">
-        <v>82</v>
+        <v>56</v>
       </c>
       <c r="E129">
         <v>2010</v>
@@ -25532,7 +25532,7 @@
         <v>49</v>
       </c>
       <c r="D130" t="s">
-        <v>82</v>
+        <v>56</v>
       </c>
       <c r="E130">
         <v>2010</v>
@@ -25585,7 +25585,7 @@
         <v>49</v>
       </c>
       <c r="D131" t="s">
-        <v>53</v>
+        <v>78</v>
       </c>
       <c r="E131">
         <v>2008</v>
@@ -25638,7 +25638,7 @@
         <v>49</v>
       </c>
       <c r="D132" t="s">
-        <v>53</v>
+        <v>78</v>
       </c>
       <c r="E132">
         <v>2008</v>
@@ -25691,7 +25691,7 @@
         <v>49</v>
       </c>
       <c r="D133" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="E133">
         <v>2018</v>
@@ -25744,7 +25744,7 @@
         <v>49</v>
       </c>
       <c r="D134" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="E134">
         <v>2006</v>
@@ -25797,7 +25797,7 @@
         <v>49</v>
       </c>
       <c r="D135" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="E135">
         <v>2007</v>
@@ -25956,7 +25956,7 @@
         <v>49</v>
       </c>
       <c r="D138" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E138">
         <v>2010</v>
@@ -26009,7 +26009,7 @@
         <v>49</v>
       </c>
       <c r="D139" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E139">
         <v>2010</v>
@@ -26062,7 +26062,7 @@
         <v>49</v>
       </c>
       <c r="D140" t="s">
-        <v>57</v>
+        <v>82</v>
       </c>
       <c r="E140">
         <v>2004</v>
@@ -26115,7 +26115,7 @@
         <v>49</v>
       </c>
       <c r="D141" t="s">
-        <v>57</v>
+        <v>82</v>
       </c>
       <c r="E141">
         <v>2004</v>
@@ -26168,7 +26168,7 @@
         <v>49</v>
       </c>
       <c r="D142" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E142">
         <v>2008</v>
@@ -26221,7 +26221,7 @@
         <v>49</v>
       </c>
       <c r="D143" t="s">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="E143">
         <v>2007</v>
@@ -26274,7 +26274,7 @@
         <v>49</v>
       </c>
       <c r="D144" t="s">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="E144">
         <v>2007</v>
@@ -26327,7 +26327,7 @@
         <v>49</v>
       </c>
       <c r="D145" t="s">
-        <v>81</v>
+        <v>57</v>
       </c>
       <c r="E145">
         <v>2005</v>
@@ -26380,7 +26380,7 @@
         <v>49</v>
       </c>
       <c r="D146" t="s">
-        <v>81</v>
+        <v>57</v>
       </c>
       <c r="E146">
         <v>2005</v>
@@ -26433,7 +26433,7 @@
         <v>49</v>
       </c>
       <c r="D147" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="E147">
         <v>2015</v>
@@ -26486,7 +26486,7 @@
         <v>49</v>
       </c>
       <c r="D148" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="E148">
         <v>2004</v>
@@ -26539,7 +26539,7 @@
         <v>49</v>
       </c>
       <c r="D149" t="s">
-        <v>50</v>
+        <v>79</v>
       </c>
       <c r="E149">
         <v>2006</v>
@@ -26592,7 +26592,7 @@
         <v>49</v>
       </c>
       <c r="D150" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="E150">
         <v>2011</v>
@@ -26645,7 +26645,7 @@
         <v>49</v>
       </c>
       <c r="D151" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="E151">
         <v>2004</v>
@@ -26698,7 +26698,7 @@
         <v>49</v>
       </c>
       <c r="D152" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="E152">
         <v>2005</v>
@@ -26804,7 +26804,7 @@
         <v>49</v>
       </c>
       <c r="D154" t="s">
-        <v>76</v>
+        <v>51</v>
       </c>
       <c r="E154">
         <v>2008</v>
@@ -26857,7 +26857,7 @@
         <v>49</v>
       </c>
       <c r="D155" t="s">
-        <v>52</v>
+        <v>86</v>
       </c>
       <c r="E155">
         <v>2007</v>
@@ -27069,7 +27069,7 @@
         <v>49</v>
       </c>
       <c r="D159" t="s">
-        <v>76</v>
+        <v>51</v>
       </c>
       <c r="E159">
         <v>2022</v>
@@ -27228,7 +27228,7 @@
         <v>49</v>
       </c>
       <c r="D162" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="E162">
         <v>2003</v>
@@ -27334,7 +27334,7 @@
         <v>49</v>
       </c>
       <c r="D164" t="s">
-        <v>82</v>
+        <v>56</v>
       </c>
       <c r="E164">
         <v>1999</v>
@@ -27387,7 +27387,7 @@
         <v>49</v>
       </c>
       <c r="D165" t="s">
-        <v>82</v>
+        <v>56</v>
       </c>
       <c r="E165">
         <v>1999</v>
@@ -27440,7 +27440,7 @@
         <v>49</v>
       </c>
       <c r="D166" t="s">
-        <v>68</v>
+        <v>53</v>
       </c>
       <c r="E166">
         <v>1997</v>
@@ -27546,7 +27546,7 @@
         <v>49</v>
       </c>
       <c r="D168" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="E168">
         <v>2001</v>
@@ -27599,7 +27599,7 @@
         <v>49</v>
       </c>
       <c r="D169" t="s">
-        <v>75</v>
+        <v>52</v>
       </c>
       <c r="E169">
         <v>2006</v>
@@ -27705,7 +27705,7 @@
         <v>49</v>
       </c>
       <c r="D171" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="E171">
         <v>2007</v>
@@ -28288,7 +28288,7 @@
         <v>49</v>
       </c>
       <c r="D182" t="s">
-        <v>68</v>
+        <v>53</v>
       </c>
       <c r="E182">
         <v>2015</v>
@@ -29083,7 +29083,7 @@
         <v>49</v>
       </c>
       <c r="D197" t="s">
-        <v>76</v>
+        <v>51</v>
       </c>
       <c r="E197">
         <v>2004</v>
@@ -29136,7 +29136,7 @@
         <v>49</v>
       </c>
       <c r="D198" t="s">
-        <v>76</v>
+        <v>51</v>
       </c>
       <c r="E198">
         <v>2008</v>
@@ -29348,7 +29348,7 @@
         <v>49</v>
       </c>
       <c r="D202" t="s">
-        <v>82</v>
+        <v>56</v>
       </c>
       <c r="E202">
         <v>2005</v>
@@ -29401,7 +29401,7 @@
         <v>49</v>
       </c>
       <c r="D203" t="s">
-        <v>82</v>
+        <v>56</v>
       </c>
       <c r="E203">
         <v>2015</v>
@@ -30090,7 +30090,7 @@
         <v>49</v>
       </c>
       <c r="D216" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E216">
         <v>2022</v>
@@ -30991,7 +30991,7 @@
         <v>49</v>
       </c>
       <c r="D233" t="s">
-        <v>57</v>
+        <v>82</v>
       </c>
       <c r="E233">
         <v>1994</v>
@@ -31150,7 +31150,7 @@
         <v>49</v>
       </c>
       <c r="D236" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E236">
         <v>1990</v>
@@ -31203,7 +31203,7 @@
         <v>49</v>
       </c>
       <c r="D237" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E237">
         <v>2022</v>
@@ -31362,7 +31362,7 @@
         <v>49</v>
       </c>
       <c r="D240" t="s">
-        <v>51</v>
+        <v>81</v>
       </c>
       <c r="E240">
         <v>2006</v>
@@ -31415,7 +31415,7 @@
         <v>49</v>
       </c>
       <c r="D241" t="s">
-        <v>81</v>
+        <v>57</v>
       </c>
       <c r="E241">
         <v>2024</v>
@@ -31468,7 +31468,7 @@
         <v>49</v>
       </c>
       <c r="D242" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="E242">
         <v>2023</v>
@@ -31521,7 +31521,7 @@
         <v>49</v>
       </c>
       <c r="D243" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="E243">
         <v>2023</v>
@@ -31574,7 +31574,7 @@
         <v>49</v>
       </c>
       <c r="D244" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="E244">
         <v>1997</v>
@@ -32051,7 +32051,7 @@
         <v>49</v>
       </c>
       <c r="D253" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="E253">
         <v>2008</v>
@@ -32316,7 +32316,7 @@
         <v>49</v>
       </c>
       <c r="D258" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="E258">
         <v>2015</v>
@@ -32687,7 +32687,7 @@
         <v>49</v>
       </c>
       <c r="D265" t="s">
-        <v>67</v>
+        <v>54</v>
       </c>
       <c r="E265">
         <v>2024</v>
@@ -32793,7 +32793,7 @@
         <v>49</v>
       </c>
       <c r="D267" t="s">
-        <v>50</v>
+        <v>79</v>
       </c>
       <c r="E267">
         <v>2023</v>
@@ -33005,7 +33005,7 @@
         <v>49</v>
       </c>
       <c r="D271" t="s">
-        <v>68</v>
+        <v>53</v>
       </c>
       <c r="E271">
         <v>1975</v>
@@ -33058,7 +33058,7 @@
         <v>49</v>
       </c>
       <c r="D272" t="s">
-        <v>68</v>
+        <v>53</v>
       </c>
       <c r="E272">
         <v>1975</v>
@@ -33111,7 +33111,7 @@
         <v>49</v>
       </c>
       <c r="D273" t="s">
-        <v>68</v>
+        <v>53</v>
       </c>
       <c r="E273">
         <v>1975</v>
@@ -33323,7 +33323,7 @@
         <v>49</v>
       </c>
       <c r="D277" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="E277">
         <v>1970</v>
@@ -33376,7 +33376,7 @@
         <v>49</v>
       </c>
       <c r="D278" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E278">
         <v>1978</v>
@@ -33429,7 +33429,7 @@
         <v>49</v>
       </c>
       <c r="D279" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E279">
         <v>1981</v>
@@ -33482,7 +33482,7 @@
         <v>49</v>
       </c>
       <c r="D280" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E280">
         <v>1987</v>
@@ -33906,7 +33906,7 @@
         <v>293</v>
       </c>
       <c r="D288" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="E288">
         <v>1991</v>
@@ -33959,7 +33959,7 @@
         <v>293</v>
       </c>
       <c r="D289" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="E289">
         <v>1991</v>
@@ -35019,13 +35019,13 @@
         <v>308</v>
       </c>
       <c r="D309" t="s">
-        <v>99</v>
+        <v>309</v>
       </c>
       <c r="E309">
         <v>2022</v>
       </c>
       <c r="F309">
-        <v>0.29181095970158766</v>
+        <v>6.3558189950902247E-2</v>
       </c>
       <c r="G309">
         <v>1</v>
@@ -35072,25 +35072,25 @@
         <v>308</v>
       </c>
       <c r="D310" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="E310">
         <v>2022</v>
       </c>
       <c r="F310">
-        <v>0.13036387865841995</v>
+        <v>0.56367299846968055</v>
       </c>
       <c r="G310">
         <v>1</v>
       </c>
       <c r="H310">
-        <v>3162.5000000000005</v>
+        <v>2750</v>
       </c>
       <c r="I310">
-        <v>60.500000000000014</v>
+        <v>55.000000000000007</v>
       </c>
       <c r="J310">
-        <v>2.3100000000000005</v>
+        <v>2.1</v>
       </c>
       <c r="K310">
         <v>100</v>
@@ -35125,25 +35125,25 @@
         <v>308</v>
       </c>
       <c r="D311" t="s">
-        <v>310</v>
+        <v>14</v>
       </c>
       <c r="E311">
         <v>2022</v>
       </c>
       <c r="F311">
-        <v>4.4073197411209589E-2</v>
+        <v>0.11134281451252948</v>
       </c>
       <c r="G311">
         <v>1</v>
       </c>
       <c r="H311">
-        <v>3712.5000000000005</v>
+        <v>3162.5000000000005</v>
       </c>
       <c r="I311">
-        <v>71.5</v>
+        <v>60.500000000000014</v>
       </c>
       <c r="J311">
-        <v>2.52</v>
+        <v>2.3100000000000005</v>
       </c>
       <c r="K311">
         <v>100</v>
@@ -35184,7 +35184,7 @@
         <v>2022</v>
       </c>
       <c r="F312">
-        <v>6.9589259070330922E-2</v>
+        <v>0.1577356538927501</v>
       </c>
       <c r="G312">
         <v>1</v>
@@ -35193,7 +35193,7 @@
         <v>3162.5000000000005</v>
       </c>
       <c r="I312">
-        <v>60.500000000000007</v>
+        <v>60.500000000000014</v>
       </c>
       <c r="J312">
         <v>2.3100000000000005</v>
@@ -35231,13 +35231,13 @@
         <v>308</v>
       </c>
       <c r="D313" t="s">
-        <v>20</v>
+        <v>291</v>
       </c>
       <c r="E313">
         <v>2022</v>
       </c>
       <c r="F313">
-        <v>0.11134281451252948</v>
+        <v>0.13082780705222213</v>
       </c>
       <c r="G313">
         <v>1</v>
@@ -35284,25 +35284,25 @@
         <v>308</v>
       </c>
       <c r="D314" t="s">
-        <v>312</v>
+        <v>59</v>
       </c>
       <c r="E314">
         <v>2022</v>
       </c>
       <c r="F314">
-        <v>5.8918906012880183E-2</v>
+        <v>0.50939337639482241</v>
       </c>
       <c r="G314">
         <v>1</v>
       </c>
       <c r="H314">
-        <v>3162.5000000000005</v>
+        <v>2750</v>
       </c>
       <c r="I314">
-        <v>60.500000000000021</v>
+        <v>55.000000000000007</v>
       </c>
       <c r="J314">
-        <v>2.3100000000000005</v>
+        <v>2.1</v>
       </c>
       <c r="K314">
         <v>100</v>
@@ -35337,25 +35337,25 @@
         <v>308</v>
       </c>
       <c r="D315" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E315">
         <v>2022</v>
       </c>
       <c r="F315">
-        <v>6.0310691194286808E-2</v>
+        <v>4.1753555442198553E-2</v>
       </c>
       <c r="G315">
         <v>1</v>
       </c>
       <c r="H315">
-        <v>3162.5000000000005</v>
+        <v>3712.5000000000005</v>
       </c>
       <c r="I315">
-        <v>60.500000000000014</v>
+        <v>71.5</v>
       </c>
       <c r="J315">
-        <v>2.3100000000000005</v>
+        <v>2.52</v>
       </c>
       <c r="K315">
         <v>100</v>
@@ -35390,25 +35390,25 @@
         <v>308</v>
       </c>
       <c r="D316" t="s">
-        <v>239</v>
+        <v>313</v>
       </c>
       <c r="E316">
         <v>2022</v>
       </c>
       <c r="F316">
-        <v>0.22871669814448767</v>
+        <v>4.4073197411209589E-2</v>
       </c>
       <c r="G316">
         <v>1</v>
       </c>
       <c r="H316">
-        <v>3162.5000000000005</v>
+        <v>3712.5000000000005</v>
       </c>
       <c r="I316">
-        <v>60.500000000000014</v>
+        <v>71.5</v>
       </c>
       <c r="J316">
-        <v>2.3100000000000005</v>
+        <v>2.52</v>
       </c>
       <c r="K316">
         <v>100</v>
@@ -35449,7 +35449,7 @@
         <v>2022</v>
       </c>
       <c r="F317">
-        <v>0.20320063648536632</v>
+        <v>6.9589259070330922E-2</v>
       </c>
       <c r="G317">
         <v>1</v>
@@ -35458,7 +35458,7 @@
         <v>3162.5000000000005</v>
       </c>
       <c r="I317">
-        <v>60.500000000000014</v>
+        <v>60.500000000000007</v>
       </c>
       <c r="J317">
         <v>2.3100000000000005</v>
@@ -35502,19 +35502,19 @@
         <v>2022</v>
       </c>
       <c r="F318">
-        <v>4.1753555442198553E-2</v>
+        <v>5.1032123318242681E-2</v>
       </c>
       <c r="G318">
         <v>1</v>
       </c>
       <c r="H318">
-        <v>3712.5000000000005</v>
+        <v>3162.5000000000005</v>
       </c>
       <c r="I318">
-        <v>71.5</v>
+        <v>60.500000000000021</v>
       </c>
       <c r="J318">
-        <v>2.52</v>
+        <v>2.3100000000000005</v>
       </c>
       <c r="K318">
         <v>100</v>
@@ -35555,19 +35555,19 @@
         <v>2022</v>
       </c>
       <c r="F319">
-        <v>0.56367299846968055</v>
+        <v>6.0310691194286808E-2</v>
       </c>
       <c r="G319">
         <v>1</v>
       </c>
       <c r="H319">
-        <v>2750</v>
+        <v>3162.5000000000005</v>
       </c>
       <c r="I319">
-        <v>55.000000000000007</v>
+        <v>60.500000000000014</v>
       </c>
       <c r="J319">
-        <v>2.1</v>
+        <v>2.3100000000000005</v>
       </c>
       <c r="K319">
         <v>100</v>
@@ -35602,13 +35602,13 @@
         <v>308</v>
       </c>
       <c r="D320" t="s">
-        <v>21</v>
+        <v>317</v>
       </c>
       <c r="E320">
         <v>2022</v>
       </c>
       <c r="F320">
-        <v>8.7682466428616976E-2</v>
+        <v>0.10670353057450742</v>
       </c>
       <c r="G320">
         <v>1</v>
@@ -35617,7 +35617,7 @@
         <v>3162.5000000000005</v>
       </c>
       <c r="I320">
-        <v>60.500000000000007</v>
+        <v>60.500000000000014</v>
       </c>
       <c r="J320">
         <v>2.3100000000000005</v>
@@ -35655,25 +35655,25 @@
         <v>308</v>
       </c>
       <c r="D321" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="E321">
         <v>2022</v>
       </c>
       <c r="F321">
-        <v>5.1032123318242681E-2</v>
+        <v>4.3145340623605172E-2</v>
       </c>
       <c r="G321">
         <v>1</v>
       </c>
       <c r="H321">
-        <v>3162.5000000000005</v>
+        <v>3712.5000000000005</v>
       </c>
       <c r="I321">
-        <v>60.500000000000021</v>
+        <v>71.5</v>
       </c>
       <c r="J321">
-        <v>2.3100000000000005</v>
+        <v>2.52</v>
       </c>
       <c r="K321">
         <v>100</v>
@@ -35708,25 +35708,25 @@
         <v>308</v>
       </c>
       <c r="D322" t="s">
-        <v>318</v>
+        <v>193</v>
       </c>
       <c r="E322">
         <v>2022</v>
       </c>
       <c r="F322">
-        <v>0.10067246145507874</v>
+        <v>0.61052976624370348</v>
       </c>
       <c r="G322">
         <v>1</v>
       </c>
       <c r="H322">
-        <v>3162.5000000000005</v>
+        <v>2750</v>
       </c>
       <c r="I322">
-        <v>60.500000000000014</v>
+        <v>55.000000000000007</v>
       </c>
       <c r="J322">
-        <v>2.3100000000000005</v>
+        <v>2.1</v>
       </c>
       <c r="K322">
         <v>100</v>
@@ -35761,25 +35761,25 @@
         <v>308</v>
       </c>
       <c r="D323" t="s">
-        <v>319</v>
+        <v>77</v>
       </c>
       <c r="E323">
         <v>2022</v>
       </c>
       <c r="F323">
-        <v>0.54140443556717466</v>
+        <v>5.4743550468660328E-2</v>
       </c>
       <c r="G323">
         <v>1</v>
       </c>
       <c r="H323">
-        <v>2750</v>
+        <v>3162.5000000000005</v>
       </c>
       <c r="I323">
-        <v>55.000000000000007</v>
+        <v>60.500000000000014</v>
       </c>
       <c r="J323">
-        <v>2.1</v>
+        <v>2.3100000000000005</v>
       </c>
       <c r="K323">
         <v>100</v>
@@ -35814,7 +35814,7 @@
         <v>308</v>
       </c>
       <c r="D324" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="E324">
         <v>2022</v>
@@ -35867,13 +35867,13 @@
         <v>308</v>
       </c>
       <c r="D325" t="s">
-        <v>74</v>
+        <v>320</v>
       </c>
       <c r="E325">
         <v>2022</v>
       </c>
       <c r="F325">
-        <v>5.4743550468660328E-2</v>
+        <v>0.10067246145507874</v>
       </c>
       <c r="G325">
         <v>1</v>
@@ -35926,7 +35926,7 @@
         <v>2022</v>
       </c>
       <c r="F326">
-        <v>0.1577356538927501</v>
+        <v>0.15541601192373908</v>
       </c>
       <c r="G326">
         <v>1</v>
@@ -35973,13 +35973,13 @@
         <v>308</v>
       </c>
       <c r="D327" t="s">
-        <v>322</v>
+        <v>56</v>
       </c>
       <c r="E327">
         <v>2022</v>
       </c>
       <c r="F327">
-        <v>0.15541601192373908</v>
+        <v>0.23196419690110309</v>
       </c>
       <c r="G327">
         <v>1</v>
@@ -36026,7 +36026,7 @@
         <v>308</v>
       </c>
       <c r="D328" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="E328">
         <v>2022</v>
@@ -36079,7 +36079,7 @@
         <v>308</v>
       </c>
       <c r="D329" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="E329">
         <v>2022</v>
@@ -36132,13 +36132,13 @@
         <v>308</v>
       </c>
       <c r="D330" t="s">
-        <v>325</v>
+        <v>19</v>
       </c>
       <c r="E330">
         <v>2022</v>
       </c>
       <c r="F330">
-        <v>0.19299421182171778</v>
+        <v>8.7682466428616976E-2</v>
       </c>
       <c r="G330">
         <v>1</v>
@@ -36147,7 +36147,7 @@
         <v>3162.5000000000005</v>
       </c>
       <c r="I330">
-        <v>60.500000000000014</v>
+        <v>60.500000000000007</v>
       </c>
       <c r="J330">
         <v>2.3100000000000005</v>
@@ -36185,25 +36185,25 @@
         <v>308</v>
       </c>
       <c r="D331" t="s">
-        <v>59</v>
+        <v>99</v>
       </c>
       <c r="E331">
         <v>2022</v>
       </c>
       <c r="F331">
-        <v>0.50939337639482241</v>
+        <v>0.29181095970158766</v>
       </c>
       <c r="G331">
         <v>1</v>
       </c>
       <c r="H331">
-        <v>2750</v>
+        <v>3162.5000000000005</v>
       </c>
       <c r="I331">
-        <v>55.000000000000007</v>
+        <v>60.500000000000014</v>
       </c>
       <c r="J331">
-        <v>2.1</v>
+        <v>2.3100000000000005</v>
       </c>
       <c r="K331">
         <v>100</v>
@@ -36238,13 +36238,13 @@
         <v>308</v>
       </c>
       <c r="D332" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="E332">
         <v>2022</v>
       </c>
       <c r="F332">
-        <v>0.10670353057450742</v>
+        <v>0.20320063648536632</v>
       </c>
       <c r="G332">
         <v>1</v>
@@ -36291,25 +36291,25 @@
         <v>308</v>
       </c>
       <c r="D333" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="E333">
         <v>2022</v>
       </c>
       <c r="F333">
-        <v>4.3145340623605172E-2</v>
+        <v>0.13036387865841995</v>
       </c>
       <c r="G333">
         <v>1</v>
       </c>
       <c r="H333">
-        <v>3712.5000000000005</v>
+        <v>3162.5000000000005</v>
       </c>
       <c r="I333">
-        <v>71.5</v>
+        <v>60.500000000000014</v>
       </c>
       <c r="J333">
-        <v>2.52</v>
+        <v>2.3100000000000005</v>
       </c>
       <c r="K333">
         <v>100</v>
@@ -36344,25 +36344,25 @@
         <v>308</v>
       </c>
       <c r="D334" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="E334">
         <v>2022</v>
       </c>
       <c r="F334">
-        <v>6.3558189950902247E-2</v>
+        <v>0.54140443556717466</v>
       </c>
       <c r="G334">
         <v>1</v>
       </c>
       <c r="H334">
-        <v>3162.5000000000005</v>
+        <v>2750</v>
       </c>
       <c r="I334">
-        <v>60.500000000000014</v>
+        <v>55.000000000000007</v>
       </c>
       <c r="J334">
-        <v>2.3100000000000005</v>
+        <v>2.1</v>
       </c>
       <c r="K334">
         <v>100</v>
@@ -36397,25 +36397,25 @@
         <v>308</v>
       </c>
       <c r="D335" t="s">
-        <v>193</v>
+        <v>151</v>
       </c>
       <c r="E335">
         <v>2022</v>
       </c>
       <c r="F335">
-        <v>0.61052976624370348</v>
+        <v>4.5464982592616207E-2</v>
       </c>
       <c r="G335">
         <v>1</v>
       </c>
       <c r="H335">
-        <v>2750</v>
+        <v>3712.5000000000005</v>
       </c>
       <c r="I335">
-        <v>55.000000000000007</v>
+        <v>71.5</v>
       </c>
       <c r="J335">
-        <v>2.1</v>
+        <v>2.52</v>
       </c>
       <c r="K335">
         <v>100</v>
@@ -36450,13 +36450,13 @@
         <v>308</v>
       </c>
       <c r="D336" t="s">
-        <v>204</v>
+        <v>327</v>
       </c>
       <c r="E336">
         <v>2022</v>
       </c>
       <c r="F336">
-        <v>7.8403898552572848E-2</v>
+        <v>5.8918906012880183E-2</v>
       </c>
       <c r="G336">
         <v>1</v>
@@ -36465,7 +36465,7 @@
         <v>3162.5000000000005</v>
       </c>
       <c r="I336">
-        <v>60.500000000000014</v>
+        <v>60.500000000000021</v>
       </c>
       <c r="J336">
         <v>2.3100000000000005</v>
@@ -36503,25 +36503,25 @@
         <v>308</v>
       </c>
       <c r="D337" t="s">
-        <v>151</v>
+        <v>239</v>
       </c>
       <c r="E337">
         <v>2022</v>
       </c>
       <c r="F337">
-        <v>4.5464982592616207E-2</v>
+        <v>0.22871669814448767</v>
       </c>
       <c r="G337">
         <v>1</v>
       </c>
       <c r="H337">
-        <v>3712.5000000000005</v>
+        <v>3162.5000000000005</v>
       </c>
       <c r="I337">
-        <v>71.5</v>
+        <v>60.500000000000014</v>
       </c>
       <c r="J337">
-        <v>2.52</v>
+        <v>2.3100000000000005</v>
       </c>
       <c r="K337">
         <v>100</v>
@@ -36556,25 +36556,25 @@
         <v>308</v>
       </c>
       <c r="D338" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="E338">
         <v>2022</v>
       </c>
       <c r="F338">
-        <v>0.35629700644009438</v>
+        <v>0.19299421182171778</v>
       </c>
       <c r="G338">
         <v>1</v>
       </c>
       <c r="H338">
-        <v>2750</v>
+        <v>3162.5000000000005</v>
       </c>
       <c r="I338">
-        <v>55</v>
+        <v>60.500000000000014</v>
       </c>
       <c r="J338">
-        <v>2.1</v>
+        <v>2.3100000000000005</v>
       </c>
       <c r="K338">
         <v>100</v>
@@ -36609,13 +36609,13 @@
         <v>308</v>
       </c>
       <c r="D339" t="s">
-        <v>291</v>
+        <v>204</v>
       </c>
       <c r="E339">
         <v>2022</v>
       </c>
       <c r="F339">
-        <v>0.13082780705222213</v>
+        <v>7.8403898552572848E-2</v>
       </c>
       <c r="G339">
         <v>1</v>
@@ -36662,25 +36662,25 @@
         <v>308</v>
       </c>
       <c r="D340" t="s">
-        <v>82</v>
+        <v>329</v>
       </c>
       <c r="E340">
         <v>2022</v>
       </c>
       <c r="F340">
-        <v>0.23196419690110309</v>
+        <v>0.35629700644009438</v>
       </c>
       <c r="G340">
         <v>1</v>
       </c>
       <c r="H340">
-        <v>3162.5000000000005</v>
+        <v>2750</v>
       </c>
       <c r="I340">
-        <v>60.500000000000014</v>
+        <v>55</v>
       </c>
       <c r="J340">
-        <v>2.3100000000000005</v>
+        <v>2.1</v>
       </c>
       <c r="K340">
         <v>100</v>
@@ -36768,7 +36768,7 @@
         <v>308</v>
       </c>
       <c r="D342" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="E342">
         <v>1959</v>
@@ -36874,7 +36874,7 @@
         <v>308</v>
       </c>
       <c r="D344" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E344">
         <v>1973</v>
@@ -36980,7 +36980,7 @@
         <v>308</v>
       </c>
       <c r="D346" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="E346">
         <v>1963</v>
@@ -37033,7 +37033,7 @@
         <v>308</v>
       </c>
       <c r="D347" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="E347">
         <v>2015</v>
@@ -37086,7 +37086,7 @@
         <v>308</v>
       </c>
       <c r="D348" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="E348">
         <v>1931</v>
@@ -37139,7 +37139,7 @@
         <v>308</v>
       </c>
       <c r="D349" t="s">
-        <v>319</v>
+        <v>326</v>
       </c>
       <c r="E349">
         <v>1949</v>
@@ -37298,7 +37298,7 @@
         <v>308</v>
       </c>
       <c r="D352" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="E352">
         <v>1958</v>
@@ -37351,7 +37351,7 @@
         <v>308</v>
       </c>
       <c r="D353" t="s">
-        <v>326</v>
+        <v>317</v>
       </c>
       <c r="E353">
         <v>1967</v>
@@ -37404,7 +37404,7 @@
         <v>308</v>
       </c>
       <c r="D354" t="s">
-        <v>314</v>
+        <v>324</v>
       </c>
       <c r="E354">
         <v>1968</v>
@@ -37457,7 +37457,7 @@
         <v>308</v>
       </c>
       <c r="D355" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="E355">
         <v>1929</v>
@@ -37510,7 +37510,7 @@
         <v>308</v>
       </c>
       <c r="D356" t="s">
-        <v>314</v>
+        <v>324</v>
       </c>
       <c r="E356">
         <v>1949</v>
@@ -37616,7 +37616,7 @@
         <v>308</v>
       </c>
       <c r="D358" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="E358">
         <v>1952</v>
@@ -37669,7 +37669,7 @@
         <v>308</v>
       </c>
       <c r="D359" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="E359">
         <v>1913</v>
@@ -37934,7 +37934,7 @@
         <v>308</v>
       </c>
       <c r="D364" t="s">
-        <v>327</v>
+        <v>318</v>
       </c>
       <c r="E364">
         <v>1927</v>
@@ -37987,7 +37987,7 @@
         <v>308</v>
       </c>
       <c r="D365" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="E365">
         <v>1928</v>
@@ -38093,7 +38093,7 @@
         <v>308</v>
       </c>
       <c r="D367" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="E367">
         <v>1938</v>
@@ -38146,7 +38146,7 @@
         <v>308</v>
       </c>
       <c r="D368" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="E368">
         <v>1920</v>
@@ -38199,7 +38199,7 @@
         <v>308</v>
       </c>
       <c r="D369" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="E369">
         <v>1947</v>
@@ -38252,7 +38252,7 @@
         <v>308</v>
       </c>
       <c r="D370" t="s">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="E370">
         <v>1950</v>
@@ -38305,7 +38305,7 @@
         <v>308</v>
       </c>
       <c r="D371" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E371">
         <v>1954</v>
@@ -38464,7 +38464,7 @@
         <v>308</v>
       </c>
       <c r="D374" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="E374">
         <v>1959</v>
@@ -38570,7 +38570,7 @@
         <v>308</v>
       </c>
       <c r="D376" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="E376">
         <v>1955</v>
@@ -38623,7 +38623,7 @@
         <v>308</v>
       </c>
       <c r="D377" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="E377">
         <v>1959</v>
@@ -38676,7 +38676,7 @@
         <v>308</v>
       </c>
       <c r="D378" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="E378">
         <v>1954</v>
@@ -38888,7 +38888,7 @@
         <v>308</v>
       </c>
       <c r="D382" t="s">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="E382">
         <v>2022</v>
@@ -39100,7 +39100,7 @@
         <v>308</v>
       </c>
       <c r="D386" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="E386">
         <v>2022</v>
@@ -39206,7 +39206,7 @@
         <v>383</v>
       </c>
       <c r="D388" t="s">
-        <v>82</v>
+        <v>56</v>
       </c>
       <c r="E388">
         <v>1989</v>
@@ -39259,7 +39259,7 @@
         <v>383</v>
       </c>
       <c r="D389" t="s">
-        <v>309</v>
+        <v>325</v>
       </c>
       <c r="E389">
         <v>1975</v>
@@ -39365,7 +39365,7 @@
         <v>383</v>
       </c>
       <c r="D391" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="E391">
         <v>2015</v>
@@ -39418,7 +39418,7 @@
         <v>383</v>
       </c>
       <c r="D392" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="E392">
         <v>2015</v>
@@ -39471,7 +39471,7 @@
         <v>383</v>
       </c>
       <c r="D393" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="E393">
         <v>1982</v>
@@ -39577,7 +39577,7 @@
         <v>383</v>
       </c>
       <c r="D395" t="s">
-        <v>328</v>
+        <v>309</v>
       </c>
       <c r="E395">
         <v>2015</v>
@@ -39630,7 +39630,7 @@
         <v>383</v>
       </c>
       <c r="D396" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="E396">
         <v>1961</v>
@@ -39683,7 +39683,7 @@
         <v>383</v>
       </c>
       <c r="D397" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="E397">
         <v>2005</v>
@@ -39895,7 +39895,7 @@
         <v>383</v>
       </c>
       <c r="D401" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="E401">
         <v>1971</v>
@@ -39948,7 +39948,7 @@
         <v>383</v>
       </c>
       <c r="D402" t="s">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="E402">
         <v>1973</v>
@@ -40107,7 +40107,7 @@
         <v>383</v>
       </c>
       <c r="D405" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="E405">
         <v>1978</v>
@@ -40160,7 +40160,7 @@
         <v>383</v>
       </c>
       <c r="D406" t="s">
-        <v>319</v>
+        <v>326</v>
       </c>
       <c r="E406">
         <v>1923</v>
@@ -40213,7 +40213,7 @@
         <v>308</v>
       </c>
       <c r="D407" t="s">
-        <v>312</v>
+        <v>327</v>
       </c>
       <c r="E407">
         <v>1959</v>
@@ -40319,7 +40319,7 @@
         <v>308</v>
       </c>
       <c r="D409" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="E409">
         <v>1949</v>
@@ -40372,7 +40372,7 @@
         <v>308</v>
       </c>
       <c r="D410" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="E410">
         <v>1953</v>
@@ -40478,7 +40478,7 @@
         <v>308</v>
       </c>
       <c r="D412" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="E412">
         <v>1960</v>
@@ -40531,7 +40531,7 @@
         <v>308</v>
       </c>
       <c r="D413" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="E413">
         <v>1962</v>
@@ -40584,7 +40584,7 @@
         <v>308</v>
       </c>
       <c r="D414" t="s">
-        <v>319</v>
+        <v>326</v>
       </c>
       <c r="E414">
         <v>2015</v>
@@ -40637,7 +40637,7 @@
         <v>308</v>
       </c>
       <c r="D415" t="s">
-        <v>314</v>
+        <v>324</v>
       </c>
       <c r="E415">
         <v>1927</v>
@@ -40690,7 +40690,7 @@
         <v>308</v>
       </c>
       <c r="D416" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="E416">
         <v>1954</v>
@@ -40796,7 +40796,7 @@
         <v>308</v>
       </c>
       <c r="D418" t="s">
-        <v>319</v>
+        <v>326</v>
       </c>
       <c r="E418">
         <v>1956</v>
@@ -40955,7 +40955,7 @@
         <v>308</v>
       </c>
       <c r="D421" t="s">
-        <v>319</v>
+        <v>326</v>
       </c>
       <c r="E421">
         <v>1960</v>
@@ -41061,7 +41061,7 @@
         <v>308</v>
       </c>
       <c r="D423" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="E423">
         <v>2015</v>
@@ -41167,7 +41167,7 @@
         <v>308</v>
       </c>
       <c r="D425" t="s">
-        <v>314</v>
+        <v>324</v>
       </c>
       <c r="E425">
         <v>2015</v>
@@ -41220,7 +41220,7 @@
         <v>308</v>
       </c>
       <c r="D426" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="E426">
         <v>2015</v>
@@ -41326,7 +41326,7 @@
         <v>308</v>
       </c>
       <c r="D428" t="s">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="E428">
         <v>1955</v>
@@ -41379,7 +41379,7 @@
         <v>308</v>
       </c>
       <c r="D429" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E429">
         <v>2015</v>
@@ -41485,7 +41485,7 @@
         <v>308</v>
       </c>
       <c r="D431" t="s">
-        <v>327</v>
+        <v>318</v>
       </c>
       <c r="E431">
         <v>1932</v>
@@ -41644,7 +41644,7 @@
         <v>308</v>
       </c>
       <c r="D434" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="E434">
         <v>1924</v>
@@ -41750,7 +41750,7 @@
         <v>308</v>
       </c>
       <c r="D436" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="E436">
         <v>2002</v>
@@ -41856,7 +41856,7 @@
         <v>308</v>
       </c>
       <c r="D438" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="E438">
         <v>1948</v>
@@ -41909,7 +41909,7 @@
         <v>308</v>
       </c>
       <c r="D439" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="E439">
         <v>2015</v>
@@ -41962,7 +41962,7 @@
         <v>308</v>
       </c>
       <c r="D440" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="E440">
         <v>1914</v>
@@ -42068,7 +42068,7 @@
         <v>308</v>
       </c>
       <c r="D442" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="E442">
         <v>1958</v>
@@ -42121,7 +42121,7 @@
         <v>439</v>
       </c>
       <c r="D443" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E443">
         <v>1992</v>
@@ -42280,7 +42280,7 @@
         <v>439</v>
       </c>
       <c r="D446" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E446">
         <v>1992</v>
@@ -42333,7 +42333,7 @@
         <v>439</v>
       </c>
       <c r="D447" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E447">
         <v>2005</v>
@@ -42598,7 +42598,7 @@
         <v>439</v>
       </c>
       <c r="D452" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E452">
         <v>1985</v>
@@ -51156,7 +51156,7 @@
         <v>2022</v>
       </c>
       <c r="F618">
-        <v>0.6793056475905862</v>
+        <v>0.67351932785461166</v>
       </c>
       <c r="G618">
         <v>0.33123000000000002</v>
@@ -51179,7 +51179,7 @@
         <v>2022</v>
       </c>
       <c r="F619">
-        <v>0.67351932785461166</v>
+        <v>0.69928302455480262</v>
       </c>
       <c r="G619">
         <v>0.33123000000000002</v>
@@ -51202,7 +51202,7 @@
         <v>2022</v>
       </c>
       <c r="F620">
-        <v>0.69928302455480262</v>
+        <v>0.6793056475905862</v>
       </c>
       <c r="G620">
         <v>0.33123000000000002</v>
@@ -51449,7 +51449,7 @@
         <v>663</v>
       </c>
       <c r="D631" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="E631">
         <v>2018</v>

--- a/VerveStacks_ITA_grids/vt_vervestacks_ITA_v1.xlsx
+++ b/VerveStacks_ITA_grids/vt_vervestacks_ITA_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DA16249E-531C-4A7D-B0B6-A1B6C96F2AF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1F336694-BEA4-4018-9362-46A6BC28C1CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{E6FD9D55-E65B-4BD8-B5A4-3EE2B1E3FE6F}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{2A1D06F7-6D45-4AC7-AB8F-D886BFA01A27}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="2" r:id="rId1"/>
@@ -81,30 +81,30 @@
     <t>bioenergy</t>
   </si>
   <si>
+    <t>e_w144005863-380</t>
+  </si>
+  <si>
+    <t>e_w34157795-380</t>
+  </si>
+  <si>
     <t>e_w109756016-380</t>
   </si>
   <si>
     <t>e_w98902899-380</t>
   </si>
   <si>
+    <t>e_w58440884-380</t>
+  </si>
+  <si>
+    <t>e_w81938081-380</t>
+  </si>
+  <si>
+    <t>e_w84696559-380</t>
+  </si>
+  <si>
     <t>e_w108020416-380</t>
   </si>
   <si>
-    <t>e_w58440884-380</t>
-  </si>
-  <si>
-    <t>e_w81938081-380</t>
-  </si>
-  <si>
-    <t>e_w34157795-380</t>
-  </si>
-  <si>
-    <t>e_w84696559-380</t>
-  </si>
-  <si>
-    <t>e_w144005863-380</t>
-  </si>
-  <si>
     <t>ep_bioenergy_G100000200236</t>
   </si>
   <si>
@@ -141,18 +141,18 @@
     <t>coal</t>
   </si>
   <si>
+    <t>e_w409439916-380</t>
+  </si>
+  <si>
+    <t>e_w418902800-380</t>
+  </si>
+  <si>
+    <t>e_w303915533-380</t>
+  </si>
+  <si>
     <t>e_w82767145-380</t>
   </si>
   <si>
-    <t>e_w303915533-380</t>
-  </si>
-  <si>
-    <t>e_w418902800-380</t>
-  </si>
-  <si>
-    <t>e_w409439916-380</t>
-  </si>
-  <si>
     <t>ep_coal_subcritical_G100000102764</t>
   </si>
   <si>
@@ -189,120 +189,120 @@
     <t>gas</t>
   </si>
   <si>
+    <t>e_w110330925-380</t>
+  </si>
+  <si>
+    <t>e_w162828577-380</t>
+  </si>
+  <si>
+    <t>e_w98900549-380</t>
+  </si>
+  <si>
+    <t>e_w162960205-380</t>
+  </si>
+  <si>
+    <t>e_w338753171-380</t>
+  </si>
+  <si>
+    <t>e_w432729521-380</t>
+  </si>
+  <si>
+    <t>e_w172302572-380</t>
+  </si>
+  <si>
+    <t>e_w99826025-380</t>
+  </si>
+  <si>
+    <t>e_w416989699-380</t>
+  </si>
+  <si>
+    <t>e_w411026199-380</t>
+  </si>
+  <si>
+    <t>e_w107438024-380</t>
+  </si>
+  <si>
+    <t>e_w339104227-380</t>
+  </si>
+  <si>
+    <t>e_w98421779-380</t>
+  </si>
+  <si>
+    <t>e_w103381531-380</t>
+  </si>
+  <si>
+    <t>e_w419423704-380</t>
+  </si>
+  <si>
+    <t>e_w116797658-380</t>
+  </si>
+  <si>
+    <t>e_w109993642-380</t>
+  </si>
+  <si>
+    <t>e_w103653592-380</t>
+  </si>
+  <si>
+    <t>e_w414663585-380</t>
+  </si>
+  <si>
+    <t>e_w255011550-380</t>
+  </si>
+  <si>
+    <t>e_w105581403-380</t>
+  </si>
+  <si>
+    <t>e_w60725875-380</t>
+  </si>
+  <si>
+    <t>e_w133601335-380</t>
+  </si>
+  <si>
+    <t>e_w145665799-380</t>
+  </si>
+  <si>
+    <t>e_w82084019-380</t>
+  </si>
+  <si>
+    <t>e_w199675964-380</t>
+  </si>
+  <si>
+    <t>e_w158739183-380</t>
+  </si>
+  <si>
+    <t>e_w103974940-380</t>
+  </si>
+  <si>
+    <t>e_w59462715-380</t>
+  </si>
+  <si>
+    <t>e_w181125039-380</t>
+  </si>
+  <si>
+    <t>e_w1137611914-380</t>
+  </si>
+  <si>
+    <t>e_w61157826-380</t>
+  </si>
+  <si>
+    <t>e_w82078641-380</t>
+  </si>
+  <si>
+    <t>e_w100407576-380</t>
+  </si>
+  <si>
+    <t>e_w149997403-380</t>
+  </si>
+  <si>
     <t>e_w105757794-380</t>
   </si>
   <si>
+    <t>e_w421827453-380</t>
+  </si>
+  <si>
     <t>e_w132450233-380</t>
   </si>
   <si>
-    <t>e_w162828577-380</t>
-  </si>
-  <si>
-    <t>e_w98900549-380</t>
-  </si>
-  <si>
-    <t>e_w100407576-380</t>
-  </si>
-  <si>
-    <t>e_w60725875-380</t>
-  </si>
-  <si>
-    <t>e_w145665799-380</t>
-  </si>
-  <si>
-    <t>e_w158739183-380</t>
-  </si>
-  <si>
-    <t>e_w103974940-380</t>
-  </si>
-  <si>
-    <t>e_w98421779-380</t>
-  </si>
-  <si>
-    <t>e_w419423704-380</t>
-  </si>
-  <si>
-    <t>e_w116797658-380</t>
-  </si>
-  <si>
-    <t>e_w339104227-380</t>
-  </si>
-  <si>
-    <t>e_w149997403-380</t>
-  </si>
-  <si>
-    <t>e_w432729521-380</t>
-  </si>
-  <si>
-    <t>e_w172302572-380</t>
-  </si>
-  <si>
-    <t>e_w181125039-380</t>
-  </si>
-  <si>
-    <t>e_w133601335-380</t>
-  </si>
-  <si>
-    <t>e_w103381531-380</t>
-  </si>
-  <si>
-    <t>e_w199675964-380</t>
-  </si>
-  <si>
-    <t>e_w338753171-380</t>
-  </si>
-  <si>
-    <t>e_w162960205-380</t>
-  </si>
-  <si>
-    <t>e_w421827453-380</t>
-  </si>
-  <si>
-    <t>e_w109993642-380</t>
-  </si>
-  <si>
-    <t>e_w103653592-380</t>
-  </si>
-  <si>
-    <t>e_w99826025-380</t>
-  </si>
-  <si>
-    <t>e_w416989699-380</t>
-  </si>
-  <si>
-    <t>e_w411026199-380</t>
-  </si>
-  <si>
-    <t>e_w107438024-380</t>
-  </si>
-  <si>
-    <t>e_w59462715-380</t>
-  </si>
-  <si>
-    <t>e_w105581403-380</t>
-  </si>
-  <si>
-    <t>e_w255011550-380</t>
-  </si>
-  <si>
-    <t>e_w414663585-380</t>
-  </si>
-  <si>
-    <t>e_w1137611914-380</t>
-  </si>
-  <si>
-    <t>e_w61157826-380</t>
-  </si>
-  <si>
-    <t>e_w82084019-380</t>
-  </si>
-  <si>
-    <t>e_w82078641-380</t>
-  </si>
-  <si>
-    <t>e_w110330925-380</t>
-  </si>
-  <si>
     <t>ep_gas_combined_cycle_G100000400339</t>
   </si>
   <si>
@@ -966,69 +966,69 @@
     <t>hydro</t>
   </si>
   <si>
+    <t>e_IT72-400</t>
+  </si>
+  <si>
+    <t>e_IT93-380</t>
+  </si>
+  <si>
+    <t>e_w61626687-380</t>
+  </si>
+  <si>
+    <t>e_w104359058-380</t>
+  </si>
+  <si>
+    <t>e_w82083756-380</t>
+  </si>
+  <si>
+    <t>e_IT31-380</t>
+  </si>
+  <si>
+    <t>e_w1100665914-380</t>
+  </si>
+  <si>
+    <t>e_w64200868-380</t>
+  </si>
+  <si>
+    <t>e_w116517585-380</t>
+  </si>
+  <si>
+    <t>e_IT72-380</t>
+  </si>
+  <si>
+    <t>e_IT53-380</t>
+  </si>
+  <si>
     <t>e_IT10-380</t>
   </si>
   <si>
-    <t>e_w61626687-380</t>
-  </si>
-  <si>
-    <t>e_IT31-380</t>
+    <t>e_IT7-380</t>
+  </si>
+  <si>
+    <t>e_IT36-380</t>
+  </si>
+  <si>
+    <t>e_IT21-380</t>
+  </si>
+  <si>
+    <t>e_w491424937-380</t>
+  </si>
+  <si>
+    <t>e_w75602396-380</t>
+  </si>
+  <si>
+    <t>e_IT71-380</t>
+  </si>
+  <si>
+    <t>e_w114931087-380</t>
   </si>
   <si>
     <t>e_w72466334-380</t>
   </si>
   <si>
-    <t>e_IT36-380</t>
-  </si>
-  <si>
-    <t>e_IT93-380</t>
-  </si>
-  <si>
-    <t>e_w114931087-380</t>
-  </si>
-  <si>
-    <t>e_IT71-380</t>
-  </si>
-  <si>
-    <t>e_IT21-380</t>
-  </si>
-  <si>
-    <t>e_w75602396-380</t>
-  </si>
-  <si>
-    <t>e_IT53-380</t>
-  </si>
-  <si>
-    <t>e_w116517585-380</t>
-  </si>
-  <si>
-    <t>e_w491424937-380</t>
-  </si>
-  <si>
-    <t>e_IT72-400</t>
-  </si>
-  <si>
-    <t>e_w104359058-380</t>
-  </si>
-  <si>
-    <t>e_w64200868-380</t>
-  </si>
-  <si>
-    <t>e_IT7-380</t>
-  </si>
-  <si>
     <t>e_IT71-400</t>
   </si>
   <si>
-    <t>e_IT72-380</t>
-  </si>
-  <si>
-    <t>e_w82083756-380</t>
-  </si>
-  <si>
-    <t>e_w1100665914-380</t>
-  </si>
-  <si>
     <t>ep_hydro_dam_G100000602220</t>
   </si>
   <si>
@@ -1407,15 +1407,15 @@
     <t>solar</t>
   </si>
   <si>
+    <t>elc_spv-ITA_0042</t>
+  </si>
+  <si>
+    <t>elc_spv-ITA_0030</t>
+  </si>
+  <si>
     <t>elc_spv-ITA_0068</t>
   </si>
   <si>
-    <t>elc_spv-ITA_0030</t>
-  </si>
-  <si>
-    <t>elc_spv-ITA_0042</t>
-  </si>
-  <si>
     <t>ep_solar_pv_001</t>
   </si>
   <si>
@@ -2031,15 +2031,15 @@
     <t>windon</t>
   </si>
   <si>
+    <t>elc_won-ITA_0096</t>
+  </si>
+  <si>
+    <t>elc_won-ITA_0022</t>
+  </si>
+  <si>
     <t>elc_won-ITA_0073</t>
   </si>
   <si>
-    <t>elc_won-ITA_0022</t>
-  </si>
-  <si>
-    <t>elc_won-ITA_0096</t>
-  </si>
-  <si>
     <t>ep_windon_wind_010</t>
   </si>
   <si>
@@ -2469,42 +2469,42 @@
     <t>ele</t>
   </si>
   <si>
+    <t>Aggregated Plant - EMBER Gap - way/144005863-380_Missing Bioenergy Capacity</t>
+  </si>
+  <si>
+    <t>GW</t>
+  </si>
+  <si>
+    <t>TWh</t>
+  </si>
+  <si>
+    <t>daynite</t>
+  </si>
+  <si>
+    <t>yes</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/109756016-380_Missing Bioenergy Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/98902899-380_Missing Bioenergy Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/108020416-380_Missing Bioenergy Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/34157795-380_Missing Bioenergy Capacity</t>
+  </si>
+  <si>
     <t>Aggregated Plant - EMBER Gap - way/58440884-380_Missing Bioenergy Capacity</t>
   </si>
   <si>
-    <t>GW</t>
-  </si>
-  <si>
-    <t>TWh</t>
-  </si>
-  <si>
-    <t>daynite</t>
-  </si>
-  <si>
-    <t>yes</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/34157795-380_Missing Bioenergy Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/109756016-380_Missing Bioenergy Capacity</t>
-  </si>
-  <si>
     <t>Aggregated Plant - EMBER Gap - way/81938081-380_Missing Bioenergy Capacity</t>
   </si>
   <si>
-    <t>Aggregated Plant - EMBER Gap - way/98902899-380_Missing Bioenergy Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/144005863-380_Missing Bioenergy Capacity</t>
-  </si>
-  <si>
     <t>Aggregated Plant - EMBER Gap - way/84696559-380_Missing Bioenergy Capacity</t>
   </si>
   <si>
-    <t>Aggregated Plant - EMBER Gap - way/108020416-380_Missing Bioenergy Capacity</t>
-  </si>
-  <si>
     <t>Acerra power station_1</t>
   </si>
   <si>
@@ -2526,15 +2526,15 @@
     <t>Aggregated Plant</t>
   </si>
   <si>
+    <t>Aggregated Plant - EMBER Gap - way/303915533-380_Missing Coal Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/409439916-380_Missing Coal Capacity</t>
+  </si>
+  <si>
     <t>Aggregated Plant - EMBER Gap - way/82767145-380_Missing Coal Capacity</t>
   </si>
   <si>
-    <t>Aggregated Plant - EMBER Gap - way/409439916-380_Missing Coal Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/303915533-380_Missing Coal Capacity</t>
-  </si>
-  <si>
     <t>Aggregated Plant - EMBER Gap - way/418902800-380_Missing Coal Capacity</t>
   </si>
   <si>
@@ -2580,52 +2580,94 @@
     <t>Aggregated Plant - EMBER Gap - way/172302572-380_Missing Gas Capacity</t>
   </si>
   <si>
+    <t>Aggregated Plant - EMBER Gap - way/61157826-380_Missing Gas Capacity</t>
+  </si>
+  <si>
     <t>Aggregated Plant - EMBER Gap - way/414663585-380_Missing Gas Capacity</t>
   </si>
   <si>
+    <t>Aggregated Plant - EMBER Gap - way/419423704-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/421827453-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/99826025-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/100407576-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/103653592-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/416989699-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/110330925-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/82084019-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/105581403-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/109756016-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/98421779-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/411026199-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/98900549-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/132450233-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/162828577-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/338753171-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/60725875-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/103974940-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/82078641-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/107438024-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/339104227-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/116797658-380_Missing Gas Capacity</t>
+  </si>
+  <si>
     <t>Aggregated Plant - EMBER Gap - way/181125039-380_Missing Gas Capacity</t>
   </si>
   <si>
-    <t>Aggregated Plant - EMBER Gap - way/338753171-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/98900549-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/162828577-380_Missing Gas Capacity</t>
-  </si>
-  <si>
     <t>Aggregated Plant - EMBER Gap - way/199675964-380_Missing Gas Capacity</t>
   </si>
   <si>
-    <t>Aggregated Plant - EMBER Gap - way/419423704-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/61157826-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/100407576-380_Missing Gas Capacity</t>
-  </si>
-  <si>
     <t>Aggregated Plant - EMBER Gap - way/432729521-380_Missing Gas Capacity</t>
   </si>
   <si>
-    <t>Aggregated Plant - EMBER Gap - way/103653592-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/416989699-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/116797658-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/339104227-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/107438024-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/132450233-380_Missing Gas Capacity</t>
+    <t>Aggregated Plant - EMBER Gap - way/82767145-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/109993642-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/103381531-380_Missing Gas Capacity</t>
   </si>
   <si>
     <t>Aggregated Plant - EMBER Gap - way/1137611914-380_Missing Gas Capacity</t>
@@ -2637,57 +2679,15 @@
     <t>Aggregated Plant - EMBER Gap - way/145665799-380_Missing Gas Capacity</t>
   </si>
   <si>
-    <t>Aggregated Plant - EMBER Gap - way/98421779-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/109756016-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/411026199-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/105581403-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/110330925-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/82084019-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/60725875-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/99826025-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/421827453-380_Missing Gas Capacity</t>
+    <t>Aggregated Plant - EMBER Gap - way/162960205-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/133601335-380_Missing Gas Capacity</t>
   </si>
   <si>
     <t>Aggregated Plant - EMBER Gap - way/149997403-380_Missing Gas Capacity</t>
   </si>
   <si>
-    <t>Aggregated Plant - EMBER Gap - way/162960205-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/133601335-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/82767145-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/109993642-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/103974940-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/82078641-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/103381531-380_Missing Gas Capacity</t>
-  </si>
-  <si>
     <t>Altomonte power station_1</t>
   </si>
   <si>
@@ -3006,54 +3006,87 @@
     <t>Aggregated Plant - IRENA Gap - IT21-380_Missing Hydro Capacity</t>
   </si>
   <si>
+    <t>Aggregated Plant - IRENA Gap - IT36-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - IT71-400_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - IT7-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/339703159-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/61712456-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - IT30-500_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - IT53-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - IT71-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/108020416-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/96190189-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/116517585-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/64200868-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/59462263-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
     <t>Aggregated Plant - IRENA Gap - IT72-380_Missing Hydro Capacity</t>
   </si>
   <si>
+    <t>Aggregated Plant - IRENA Gap - way/1100665914-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - IT93-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - IT10-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/338753171-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/75602396-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/1137611914-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/109588422-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - IT72-400_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/104359058-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/419423704-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/491424937-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
     <t>Aggregated Plant - IRENA Gap - way/72466334-380_Missing Hydro Capacity</t>
   </si>
   <si>
-    <t>Aggregated Plant - IRENA Gap - way/64200868-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/59462263-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/1100665914-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/116517585-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/96190189-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/491424937-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/419423704-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
     <t>Aggregated Plant - IRENA Gap - way/82083756-380_Missing Hydro Capacity</t>
   </si>
   <si>
-    <t>Aggregated Plant - IRENA Gap - way/104359058-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - IT71-400_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - IT36-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - IT71-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/108020416-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/75602396-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
     <t>Aggregated Plant - IRENA Gap - IT31-380_Missing Hydro Capacity</t>
   </si>
   <si>
@@ -3063,39 +3096,6 @@
     <t>Aggregated Plant - IRENA Gap - way/61626687-380_Missing Hydro Capacity</t>
   </si>
   <si>
-    <t>Aggregated Plant - IRENA Gap - way/1137611914-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - IT93-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - IT10-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/338753171-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/61712456-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - IT30-500_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - IT7-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/339703159-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - IT53-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/109588422-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - IT72-400_Missing Hydro Capacity</t>
-  </si>
-  <si>
     <t>Baschi hydroelectric plant_</t>
   </si>
   <si>
@@ -3402,15 +3402,15 @@
     <t>Aggregated Plant - IRENA Gap - ITA_42_Missing Solar Capacity</t>
   </si>
   <si>
+    <t>Aggregated Plant - IRENA Gap - ITA_73_Missing Onshore wind energy Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - ITA_96_Missing Onshore wind energy Capacity</t>
+  </si>
+  <si>
     <t>Aggregated Plant - IRENA Gap - ITA_22_Missing Onshore wind energy Capacity</t>
   </si>
   <si>
-    <t>Aggregated Plant - IRENA Gap - ITA_73_Missing Onshore wind energy Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - ITA_96_Missing Onshore wind energy Capacity</t>
-  </si>
-  <si>
     <t>AF</t>
   </si>
   <si>
@@ -4002,18 +4002,18 @@
     <t>ccs retrofit of -- Sulcis power station_Unit 3</t>
   </si>
   <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/82767145-380_Missing Coal Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/303915533-380_Missing Coal Capacity</t>
+  </si>
+  <si>
     <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/418902800-380_Missing Coal Capacity</t>
   </si>
   <si>
     <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/409439916-380_Missing Coal Capacity</t>
   </si>
   <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/303915533-380_Missing Coal Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/82767145-380_Missing Coal Capacity</t>
-  </si>
-  <si>
     <t>ccs retrofit of -- Brindisi Sud power station_Unit 1</t>
   </si>
   <si>
@@ -4302,124 +4302,124 @@
     <t>ccs retrofit of -- Aggregated Plant</t>
   </si>
   <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/339104227-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/158739183-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/133601335-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/255011550-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/105581403-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/181125039-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/61157826-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/82767145-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/162828577-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/145665799-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/172302572-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/105757794-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/99826025-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/416989699-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/103974940-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/109756016-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/411026199-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/103381531-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/98421779-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/116797658-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/414663585-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/107438024-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/109993642-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/82084019-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/60725875-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/59462715-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/103653592-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/82078641-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/199675964-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/1137611914-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/432729521-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/419423704-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/162960205-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/149997403-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/98900549-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/110330925-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/338753171-380_Missing Gas Capacity</t>
+  </si>
+  <si>
     <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/100407576-380_Missing Gas Capacity</t>
   </si>
   <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/145665799-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/432729521-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/149997403-380_Missing Gas Capacity</t>
-  </si>
-  <si>
     <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/132450233-380_Missing Gas Capacity</t>
   </si>
   <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/105757794-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/98900549-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/107438024-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/98421779-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/414663585-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/416989699-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/99826025-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/338753171-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/110330925-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/199675964-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/103653592-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/1137611914-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/82078641-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/109756016-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/411026199-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/103381531-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/59462715-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/109993642-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/116797658-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/162960205-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/61157826-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/103974940-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/82084019-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/60725875-380_Missing Gas Capacity</t>
-  </si>
-  <si>
     <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/421827453-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/419423704-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/162828577-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/82767145-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/172302572-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/255011550-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/181125039-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/105581403-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/339104227-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/158739183-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/133601335-380_Missing Gas Capacity</t>
   </si>
   <si>
     <t>ccs retrofit of -- Tavazzano power station_CCGT8, timepoint 1</t>
@@ -4823,7 +4823,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EFC6F6B0-4E0C-490F-B845-2E14F7D4737A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ACD3945A-C2BB-4CC0-97DF-EF47AC177268}">
   <dimension ref="B9:T278"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -4899,7 +4899,7 @@
         <v>33</v>
       </c>
       <c r="D11" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E11">
         <v>0.12764790000000001</v>
@@ -4955,7 +4955,7 @@
         <v>33</v>
       </c>
       <c r="D12" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E12">
         <v>0.12764790000000001</v>
@@ -5011,7 +5011,7 @@
         <v>33</v>
       </c>
       <c r="D13" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E13">
         <v>0.12764790000000001</v>
@@ -5067,7 +5067,7 @@
         <v>33</v>
       </c>
       <c r="D14" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E14">
         <v>8.7830160000000032E-2</v>
@@ -5347,7 +5347,7 @@
         <v>33</v>
       </c>
       <c r="D19" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E19">
         <v>0.260522535</v>
@@ -5403,7 +5403,7 @@
         <v>33</v>
       </c>
       <c r="D20" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E20">
         <v>0.260522535</v>
@@ -5459,7 +5459,7 @@
         <v>33</v>
       </c>
       <c r="D21" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E21">
         <v>0.260522535</v>
@@ -5515,7 +5515,7 @@
         <v>33</v>
       </c>
       <c r="D22" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="E22">
         <v>0.28056272999999998</v>
@@ -5571,7 +5571,7 @@
         <v>33</v>
       </c>
       <c r="D23" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="E23">
         <v>0.28056272999999998</v>
@@ -5627,7 +5627,7 @@
         <v>33</v>
       </c>
       <c r="D24" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="E24">
         <v>0.28056272999999998</v>
@@ -5683,7 +5683,7 @@
         <v>49</v>
       </c>
       <c r="D25" t="s">
-        <v>87</v>
+        <v>50</v>
       </c>
       <c r="E25">
         <v>0.41750406250000005</v>
@@ -5739,7 +5739,7 @@
         <v>49</v>
       </c>
       <c r="D26" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="E26">
         <v>0.44431624999999997</v>
@@ -5795,7 +5795,7 @@
         <v>49</v>
       </c>
       <c r="D27" t="s">
-        <v>54</v>
+        <v>83</v>
       </c>
       <c r="E27">
         <v>0.38303124999999993</v>
@@ -5851,7 +5851,7 @@
         <v>49</v>
       </c>
       <c r="D28" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E28">
         <v>0.44431624999999997</v>
@@ -5907,7 +5907,7 @@
         <v>49</v>
       </c>
       <c r="D29" t="s">
-        <v>56</v>
+        <v>73</v>
       </c>
       <c r="E29">
         <v>0.41750406249999999</v>
@@ -5963,7 +5963,7 @@
         <v>49</v>
       </c>
       <c r="D30" t="s">
-        <v>56</v>
+        <v>73</v>
       </c>
       <c r="E30">
         <v>0.41750406249999999</v>
@@ -6019,7 +6019,7 @@
         <v>49</v>
       </c>
       <c r="D31" t="s">
-        <v>56</v>
+        <v>73</v>
       </c>
       <c r="E31">
         <v>0.41750406249999999</v>
@@ -6131,7 +6131,7 @@
         <v>49</v>
       </c>
       <c r="D33" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="E33">
         <v>0.41750406249999999</v>
@@ -6299,7 +6299,7 @@
         <v>49</v>
       </c>
       <c r="D36" t="s">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="E36">
         <v>0.41750406249999999</v>
@@ -6355,7 +6355,7 @@
         <v>49</v>
       </c>
       <c r="D37" t="s">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="E37">
         <v>0.41750406249999999</v>
@@ -6411,7 +6411,7 @@
         <v>49</v>
       </c>
       <c r="D38" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="E38">
         <v>0.41750406249999999</v>
@@ -6467,7 +6467,7 @@
         <v>49</v>
       </c>
       <c r="D39" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="E39">
         <v>0.41750406249999999</v>
@@ -6523,7 +6523,7 @@
         <v>49</v>
       </c>
       <c r="D40" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E40">
         <v>0.3983525</v>
@@ -6579,7 +6579,7 @@
         <v>49</v>
       </c>
       <c r="D41" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E41">
         <v>0.41750406249999999</v>
@@ -6635,7 +6635,7 @@
         <v>49</v>
       </c>
       <c r="D42" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E42">
         <v>0.41750406249999999</v>
@@ -6691,7 +6691,7 @@
         <v>49</v>
       </c>
       <c r="D43" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="E43">
         <v>0.41750406249999999</v>
@@ -6747,7 +6747,7 @@
         <v>49</v>
       </c>
       <c r="D44" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="E44">
         <v>0.41750406249999999</v>
@@ -6803,7 +6803,7 @@
         <v>49</v>
       </c>
       <c r="D45" t="s">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="E45">
         <v>0.41750406249999999</v>
@@ -6859,7 +6859,7 @@
         <v>49</v>
       </c>
       <c r="D46" t="s">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="E46">
         <v>0.41750406249999999</v>
@@ -6915,7 +6915,7 @@
         <v>49</v>
       </c>
       <c r="D47" t="s">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="E47">
         <v>0.41750406249999999</v>
@@ -6971,7 +6971,7 @@
         <v>49</v>
       </c>
       <c r="D48" t="s">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="E48">
         <v>0.41750406249999999</v>
@@ -7027,7 +7027,7 @@
         <v>49</v>
       </c>
       <c r="D49" t="s">
-        <v>50</v>
+        <v>85</v>
       </c>
       <c r="E49">
         <v>0.40218281250000004</v>
@@ -7083,7 +7083,7 @@
         <v>49</v>
       </c>
       <c r="D50" t="s">
-        <v>50</v>
+        <v>85</v>
       </c>
       <c r="E50">
         <v>0.40218281250000004</v>
@@ -7139,7 +7139,7 @@
         <v>49</v>
       </c>
       <c r="D51" t="s">
-        <v>58</v>
+        <v>77</v>
       </c>
       <c r="E51">
         <v>0.41750406249999999</v>
@@ -7195,7 +7195,7 @@
         <v>49</v>
       </c>
       <c r="D52" t="s">
-        <v>54</v>
+        <v>83</v>
       </c>
       <c r="E52">
         <v>0.45963749999999998</v>
@@ -7251,7 +7251,7 @@
         <v>49</v>
       </c>
       <c r="D53" t="s">
-        <v>54</v>
+        <v>83</v>
       </c>
       <c r="E53">
         <v>0.41750406249999999</v>
@@ -7363,7 +7363,7 @@
         <v>49</v>
       </c>
       <c r="D55" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="E55">
         <v>0.41750406249999999</v>
@@ -7419,7 +7419,7 @@
         <v>49</v>
       </c>
       <c r="D56" t="s">
-        <v>75</v>
+        <v>57</v>
       </c>
       <c r="E56">
         <v>0.41750406249999999</v>
@@ -7475,7 +7475,7 @@
         <v>49</v>
       </c>
       <c r="D57" t="s">
-        <v>75</v>
+        <v>57</v>
       </c>
       <c r="E57">
         <v>0.41750406249999999</v>
@@ -7531,7 +7531,7 @@
         <v>49</v>
       </c>
       <c r="D58" t="s">
-        <v>76</v>
+        <v>58</v>
       </c>
       <c r="E58">
         <v>0.40218281249999999</v>
@@ -7587,7 +7587,7 @@
         <v>49</v>
       </c>
       <c r="D59" t="s">
-        <v>76</v>
+        <v>58</v>
       </c>
       <c r="E59">
         <v>0.40218281249999999</v>
@@ -7643,7 +7643,7 @@
         <v>49</v>
       </c>
       <c r="D60" t="s">
-        <v>76</v>
+        <v>58</v>
       </c>
       <c r="E60">
         <v>0.38303124999999993</v>
@@ -7699,7 +7699,7 @@
         <v>49</v>
       </c>
       <c r="D61" t="s">
-        <v>76</v>
+        <v>58</v>
       </c>
       <c r="E61">
         <v>0.38303124999999993</v>
@@ -7811,7 +7811,7 @@
         <v>49</v>
       </c>
       <c r="D63" t="s">
-        <v>70</v>
+        <v>54</v>
       </c>
       <c r="E63">
         <v>0.41750406249999999</v>
@@ -7867,7 +7867,7 @@
         <v>49</v>
       </c>
       <c r="D64" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="E64">
         <v>0.41750406249999999</v>
@@ -7923,7 +7923,7 @@
         <v>49</v>
       </c>
       <c r="D65" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="E65">
         <v>0.41750406249999999</v>
@@ -7979,7 +7979,7 @@
         <v>49</v>
       </c>
       <c r="D66" t="s">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="E66">
         <v>0.41750406249999999</v>
@@ -8147,7 +8147,7 @@
         <v>49</v>
       </c>
       <c r="D69" t="s">
-        <v>57</v>
+        <v>76</v>
       </c>
       <c r="E69">
         <v>0.41750406249999999</v>
@@ -8203,7 +8203,7 @@
         <v>49</v>
       </c>
       <c r="D70" t="s">
-        <v>57</v>
+        <v>76</v>
       </c>
       <c r="E70">
         <v>0.41750406249999999</v>
@@ -8259,7 +8259,7 @@
         <v>49</v>
       </c>
       <c r="D71" t="s">
-        <v>70</v>
+        <v>54</v>
       </c>
       <c r="E71">
         <v>0.41750406249999999</v>
@@ -8315,7 +8315,7 @@
         <v>49</v>
       </c>
       <c r="D72" t="s">
-        <v>70</v>
+        <v>54</v>
       </c>
       <c r="E72">
         <v>0.41750406249999999</v>
@@ -8371,7 +8371,7 @@
         <v>49</v>
       </c>
       <c r="D73" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="E73">
         <v>0.41750406249999999</v>
@@ -8427,7 +8427,7 @@
         <v>49</v>
       </c>
       <c r="D74" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="E74">
         <v>0.41750406249999999</v>
@@ -8483,7 +8483,7 @@
         <v>49</v>
       </c>
       <c r="D75" t="s">
-        <v>82</v>
+        <v>68</v>
       </c>
       <c r="E75">
         <v>0.42899500000000002</v>
@@ -8539,7 +8539,7 @@
         <v>49</v>
       </c>
       <c r="D76" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="E76">
         <v>0.41750406249999999</v>
@@ -8595,7 +8595,7 @@
         <v>49</v>
       </c>
       <c r="D77" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="E77">
         <v>0.41750406249999999</v>
@@ -8763,7 +8763,7 @@
         <v>49</v>
       </c>
       <c r="D80" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E80">
         <v>0.41750406249999999</v>
@@ -8819,7 +8819,7 @@
         <v>49</v>
       </c>
       <c r="D81" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E81">
         <v>0.41750406249999999</v>
@@ -8875,7 +8875,7 @@
         <v>49</v>
       </c>
       <c r="D82" t="s">
-        <v>85</v>
+        <v>74</v>
       </c>
       <c r="E82">
         <v>0.41750406249999999</v>
@@ -8931,7 +8931,7 @@
         <v>49</v>
       </c>
       <c r="D83" t="s">
-        <v>85</v>
+        <v>74</v>
       </c>
       <c r="E83">
         <v>0.41750406249999999</v>
@@ -8987,7 +8987,7 @@
         <v>49</v>
       </c>
       <c r="D84" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="E84">
         <v>0.41750406249999999</v>
@@ -9043,7 +9043,7 @@
         <v>49</v>
       </c>
       <c r="D85" t="s">
-        <v>51</v>
+        <v>87</v>
       </c>
       <c r="E85">
         <v>0.41750406249999999</v>
@@ -9099,7 +9099,7 @@
         <v>49</v>
       </c>
       <c r="D86" t="s">
-        <v>51</v>
+        <v>87</v>
       </c>
       <c r="E86">
         <v>0.41750406249999999</v>
@@ -9155,7 +9155,7 @@
         <v>49</v>
       </c>
       <c r="D87" t="s">
-        <v>71</v>
+        <v>53</v>
       </c>
       <c r="E87">
         <v>0.41750406249999999</v>
@@ -9211,7 +9211,7 @@
         <v>49</v>
       </c>
       <c r="D88" t="s">
-        <v>71</v>
+        <v>53</v>
       </c>
       <c r="E88">
         <v>0.41750406249999999</v>
@@ -9267,7 +9267,7 @@
         <v>49</v>
       </c>
       <c r="D89" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="E89">
         <v>0.44431624999999997</v>
@@ -9323,7 +9323,7 @@
         <v>49</v>
       </c>
       <c r="D90" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="E90">
         <v>0.41750406249999999</v>
@@ -9379,7 +9379,7 @@
         <v>49</v>
       </c>
       <c r="D91" t="s">
-        <v>77</v>
+        <v>59</v>
       </c>
       <c r="E91">
         <v>0.41750406249999999</v>
@@ -9435,7 +9435,7 @@
         <v>49</v>
       </c>
       <c r="D92" t="s">
-        <v>58</v>
+        <v>77</v>
       </c>
       <c r="E92">
         <v>0.44431624999999997</v>
@@ -9491,7 +9491,7 @@
         <v>49</v>
       </c>
       <c r="D93" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="E93">
         <v>0.41750406249999999</v>
@@ -9547,7 +9547,7 @@
         <v>49</v>
       </c>
       <c r="D94" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="E94">
         <v>0.41750406249999999</v>
@@ -9603,7 +9603,7 @@
         <v>49</v>
       </c>
       <c r="D95" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E95">
         <v>0.41750406249999999</v>
@@ -9659,7 +9659,7 @@
         <v>49</v>
       </c>
       <c r="D96" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E96">
         <v>0.41750406249999999</v>
@@ -9715,7 +9715,7 @@
         <v>49</v>
       </c>
       <c r="D97" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="E97">
         <v>0.41750406249999999</v>
@@ -9827,7 +9827,7 @@
         <v>49</v>
       </c>
       <c r="D99" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="E99">
         <v>0.45963749999999998</v>
@@ -9883,7 +9883,7 @@
         <v>49</v>
       </c>
       <c r="D100" t="s">
-        <v>55</v>
+        <v>71</v>
       </c>
       <c r="E100">
         <v>0.45963749999999998</v>
@@ -9939,7 +9939,7 @@
         <v>49</v>
       </c>
       <c r="D101" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E101">
         <v>0.45963749999999998</v>
@@ -9995,7 +9995,7 @@
         <v>49</v>
       </c>
       <c r="D102" t="s">
-        <v>63</v>
+        <v>84</v>
       </c>
       <c r="E102">
         <v>0.41750406249999999</v>
@@ -10051,7 +10051,7 @@
         <v>49</v>
       </c>
       <c r="D103" t="s">
-        <v>63</v>
+        <v>84</v>
       </c>
       <c r="E103">
         <v>0.41750406249999999</v>
@@ -10107,7 +10107,7 @@
         <v>49</v>
       </c>
       <c r="D104" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="E104">
         <v>0.41750406249999999</v>
@@ -10163,7 +10163,7 @@
         <v>49</v>
       </c>
       <c r="D105" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="E105">
         <v>0.41750406249999999</v>
@@ -10219,7 +10219,7 @@
         <v>49</v>
       </c>
       <c r="D106" t="s">
-        <v>70</v>
+        <v>54</v>
       </c>
       <c r="E106">
         <v>0.38303124999999993</v>
@@ -10275,7 +10275,7 @@
         <v>49</v>
       </c>
       <c r="D107" t="s">
-        <v>70</v>
+        <v>54</v>
       </c>
       <c r="E107">
         <v>0.38303124999999993</v>
@@ -10331,7 +10331,7 @@
         <v>49</v>
       </c>
       <c r="D108" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="E108">
         <v>0.4021828125000001</v>
@@ -10443,7 +10443,7 @@
         <v>49</v>
       </c>
       <c r="D110" t="s">
-        <v>81</v>
+        <v>69</v>
       </c>
       <c r="E110">
         <v>0.41750406249999999</v>
@@ -10499,7 +10499,7 @@
         <v>49</v>
       </c>
       <c r="D111" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E111">
         <v>0.3983525</v>
@@ -10611,7 +10611,7 @@
         <v>49</v>
       </c>
       <c r="D113" t="s">
-        <v>82</v>
+        <v>68</v>
       </c>
       <c r="E113">
         <v>0.41750406249999999</v>
@@ -11955,7 +11955,7 @@
         <v>49</v>
       </c>
       <c r="D137" t="s">
-        <v>14</v>
+        <v>64</v>
       </c>
       <c r="E137">
         <v>0.45963749999999998</v>
@@ -12011,7 +12011,7 @@
         <v>49</v>
       </c>
       <c r="D138" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E138">
         <v>0.45963749999999998</v>
@@ -12067,7 +12067,7 @@
         <v>49</v>
       </c>
       <c r="D139" t="s">
-        <v>65</v>
+        <v>16</v>
       </c>
       <c r="E139">
         <v>0.45963749999999998</v>
@@ -12515,7 +12515,7 @@
         <v>49</v>
       </c>
       <c r="D147" t="s">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="E147">
         <v>0.45963749999999998</v>
@@ -12571,7 +12571,7 @@
         <v>49</v>
       </c>
       <c r="D148" t="s">
-        <v>34</v>
+        <v>52</v>
       </c>
       <c r="E148">
         <v>0.45963749999999998</v>
@@ -13467,7 +13467,7 @@
         <v>49</v>
       </c>
       <c r="D164" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="E164">
         <v>0.41367375000000001</v>
@@ -14307,7 +14307,7 @@
         <v>49</v>
       </c>
       <c r="D179" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E179">
         <v>0.39835250000000011</v>
@@ -14363,7 +14363,7 @@
         <v>49</v>
       </c>
       <c r="D180" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E180">
         <v>0.39835250000000011</v>
@@ -14587,7 +14587,7 @@
         <v>49</v>
       </c>
       <c r="D184" t="s">
-        <v>70</v>
+        <v>54</v>
       </c>
       <c r="E184">
         <v>0.41367375000000001</v>
@@ -14643,7 +14643,7 @@
         <v>49</v>
       </c>
       <c r="D185" t="s">
-        <v>70</v>
+        <v>54</v>
       </c>
       <c r="E185">
         <v>0.41367375000000001</v>
@@ -15371,7 +15371,7 @@
         <v>49</v>
       </c>
       <c r="D198" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E198">
         <v>0.42899500000000002</v>
@@ -15595,7 +15595,7 @@
         <v>49</v>
       </c>
       <c r="D202" t="s">
-        <v>55</v>
+        <v>71</v>
       </c>
       <c r="E202">
         <v>0.3983525</v>
@@ -16323,7 +16323,7 @@
         <v>49</v>
       </c>
       <c r="D215" t="s">
-        <v>85</v>
+        <v>74</v>
       </c>
       <c r="E215">
         <v>0.38303124999999993</v>
@@ -16491,7 +16491,7 @@
         <v>49</v>
       </c>
       <c r="D218" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E218">
         <v>0.42899499999999996</v>
@@ -16547,7 +16547,7 @@
         <v>49</v>
       </c>
       <c r="D219" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E219">
         <v>0.42899499999999996</v>
@@ -16715,7 +16715,7 @@
         <v>49</v>
       </c>
       <c r="D222" t="s">
-        <v>75</v>
+        <v>57</v>
       </c>
       <c r="E222">
         <v>0.38303124999999993</v>
@@ -16771,7 +16771,7 @@
         <v>49</v>
       </c>
       <c r="D223" t="s">
-        <v>71</v>
+        <v>53</v>
       </c>
       <c r="E223">
         <v>0.25280062500000006</v>
@@ -16827,7 +16827,7 @@
         <v>49</v>
       </c>
       <c r="D224" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="E224">
         <v>0.24514000000000002</v>
@@ -16883,7 +16883,7 @@
         <v>49</v>
       </c>
       <c r="D225" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="E225">
         <v>0.24514000000000002</v>
@@ -16939,7 +16939,7 @@
         <v>49</v>
       </c>
       <c r="D226" t="s">
-        <v>82</v>
+        <v>68</v>
       </c>
       <c r="E226">
         <v>0.21066718750000002</v>
@@ -17443,7 +17443,7 @@
         <v>49</v>
       </c>
       <c r="D235" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="E235">
         <v>0.21449750000000001</v>
@@ -17723,7 +17723,7 @@
         <v>49</v>
       </c>
       <c r="D240" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="E240">
         <v>0.23747937499999999</v>
@@ -17835,7 +17835,7 @@
         <v>49</v>
       </c>
       <c r="D242" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="E242">
         <v>0.21449750000000001</v>
@@ -18031,7 +18031,7 @@
         <v>49</v>
       </c>
       <c r="D247" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="E247">
         <v>0.27578249999999999</v>
@@ -18101,7 +18101,7 @@
         <v>49</v>
       </c>
       <c r="D249" t="s">
-        <v>77</v>
+        <v>59</v>
       </c>
       <c r="E249">
         <v>0.27578249999999999</v>
@@ -18241,7 +18241,7 @@
         <v>49</v>
       </c>
       <c r="D253" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="E253">
         <v>0.23747937499999999</v>
@@ -18276,7 +18276,7 @@
         <v>49</v>
       </c>
       <c r="D254" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="E254">
         <v>0.23747937499999999</v>
@@ -18311,7 +18311,7 @@
         <v>49</v>
       </c>
       <c r="D255" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="E255">
         <v>0.23747937499999999</v>
@@ -18346,7 +18346,7 @@
         <v>49</v>
       </c>
       <c r="D256" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="E256">
         <v>0.26429156249999997</v>
@@ -18381,7 +18381,7 @@
         <v>49</v>
       </c>
       <c r="D257" t="s">
-        <v>56</v>
+        <v>73</v>
       </c>
       <c r="E257">
         <v>0.23747937499999999</v>
@@ -18416,7 +18416,7 @@
         <v>49</v>
       </c>
       <c r="D258" t="s">
-        <v>56</v>
+        <v>73</v>
       </c>
       <c r="E258">
         <v>0.23747937499999999</v>
@@ -18451,7 +18451,7 @@
         <v>49</v>
       </c>
       <c r="D259" t="s">
-        <v>81</v>
+        <v>69</v>
       </c>
       <c r="E259">
         <v>0.22215812499999998</v>
@@ -18486,7 +18486,7 @@
         <v>49</v>
       </c>
       <c r="D260" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E260">
         <v>0.24514000000000002</v>
@@ -18521,7 +18521,7 @@
         <v>49</v>
       </c>
       <c r="D261" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E261">
         <v>0.24514000000000002</v>
@@ -18556,7 +18556,7 @@
         <v>49</v>
       </c>
       <c r="D262" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E262">
         <v>0.24514000000000002</v>
@@ -18626,7 +18626,7 @@
         <v>439</v>
       </c>
       <c r="D264" t="s">
-        <v>54</v>
+        <v>83</v>
       </c>
       <c r="E264">
         <v>0.35238875000000003</v>
@@ -18731,7 +18731,7 @@
         <v>439</v>
       </c>
       <c r="D267" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E267">
         <v>0.19534593749999996</v>
@@ -18766,7 +18766,7 @@
         <v>439</v>
       </c>
       <c r="D268" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E268">
         <v>0.206836875</v>
@@ -18941,7 +18941,7 @@
         <v>439</v>
       </c>
       <c r="D273" t="s">
-        <v>54</v>
+        <v>83</v>
       </c>
       <c r="E273">
         <v>0.23747937499999999</v>
@@ -19149,7 +19149,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5682C18E-FDA8-4BED-BCE8-21E33940EB32}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8274CAE5-81D4-4E1C-9B5E-E29ABC72335C}">
   <dimension ref="B9:T842"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -19231,7 +19231,7 @@
         <v>2022</v>
       </c>
       <c r="F11">
-        <v>0.27911864406779663</v>
+        <v>0.22450847457627116</v>
       </c>
       <c r="G11">
         <v>0.28891500000000003</v>
@@ -19284,13 +19284,13 @@
         <v>2022</v>
       </c>
       <c r="F12">
-        <v>0.39440677966101695</v>
+        <v>0.35800000000000004</v>
       </c>
       <c r="G12">
         <v>0.306425</v>
       </c>
       <c r="H12">
-        <v>3850.0000000000005</v>
+        <v>3850.0000000000009</v>
       </c>
       <c r="I12">
         <v>143</v>
@@ -19337,7 +19337,7 @@
         <v>2022</v>
       </c>
       <c r="F13">
-        <v>0.24877966101694915</v>
+        <v>0.27911864406779663</v>
       </c>
       <c r="G13">
         <v>0.28891500000000003</v>
@@ -19390,7 +19390,7 @@
         <v>2022</v>
       </c>
       <c r="F14">
-        <v>0.51576271186440681</v>
+        <v>0.39440677966101695</v>
       </c>
       <c r="G14">
         <v>0.306425</v>
@@ -19443,7 +19443,7 @@
         <v>2022</v>
       </c>
       <c r="F15">
-        <v>0.49149152542372881</v>
+        <v>0.51576271186440681</v>
       </c>
       <c r="G15">
         <v>0.306425</v>
@@ -19496,13 +19496,13 @@
         <v>2022</v>
       </c>
       <c r="F16">
-        <v>0.35800000000000004</v>
+        <v>0.49149152542372881</v>
       </c>
       <c r="G16">
         <v>0.306425</v>
       </c>
       <c r="H16">
-        <v>3850.0000000000009</v>
+        <v>3850.0000000000005</v>
       </c>
       <c r="I16">
         <v>143</v>
@@ -19602,7 +19602,7 @@
         <v>2022</v>
       </c>
       <c r="F18">
-        <v>0.22450847457627116</v>
+        <v>0.24877966101694915</v>
       </c>
       <c r="G18">
         <v>0.28891500000000003</v>
@@ -19702,7 +19702,7 @@
         <v>13</v>
       </c>
       <c r="D20" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E20">
         <v>1998</v>
@@ -19755,7 +19755,7 @@
         <v>13</v>
       </c>
       <c r="D21" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E21">
         <v>2008</v>
@@ -19808,7 +19808,7 @@
         <v>13</v>
       </c>
       <c r="D22" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="E22">
         <v>2001</v>
@@ -19861,7 +19861,7 @@
         <v>13</v>
       </c>
       <c r="D23" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E23">
         <v>2013</v>
@@ -19914,7 +19914,7 @@
         <v>13</v>
       </c>
       <c r="D24" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="E24">
         <v>1965</v>
@@ -19967,7 +19967,7 @@
         <v>13</v>
       </c>
       <c r="D25" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E25">
         <v>2003</v>
@@ -20020,7 +20020,7 @@
         <v>13</v>
       </c>
       <c r="D26" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="E26">
         <v>2009</v>
@@ -20073,7 +20073,7 @@
         <v>13</v>
       </c>
       <c r="D27" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E27">
         <v>2018</v>
@@ -20185,19 +20185,19 @@
         <v>2022</v>
       </c>
       <c r="F29">
-        <v>0.61803468208092449</v>
+        <v>0.1997687861271675</v>
       </c>
       <c r="G29">
-        <v>0.31518000000000002</v>
+        <v>0.29766999999999999</v>
       </c>
       <c r="H29">
-        <v>2200</v>
+        <v>2530</v>
       </c>
       <c r="I29">
-        <v>66</v>
+        <v>72.600000000000009</v>
       </c>
       <c r="J29">
-        <v>5.25</v>
+        <v>5.7750000000000004</v>
       </c>
       <c r="K29">
         <v>50</v>
@@ -20238,19 +20238,19 @@
         <v>2022</v>
       </c>
       <c r="F30">
-        <v>0.18416184971098257</v>
+        <v>0.61803468208092449</v>
       </c>
       <c r="G30">
-        <v>0.29766999999999999</v>
+        <v>0.31518000000000002</v>
       </c>
       <c r="H30">
-        <v>2530</v>
+        <v>2200</v>
       </c>
       <c r="I30">
-        <v>72.600000000000009</v>
+        <v>66</v>
       </c>
       <c r="J30">
-        <v>5.7750000000000004</v>
+        <v>5.25</v>
       </c>
       <c r="K30">
         <v>50</v>
@@ -20291,19 +20291,19 @@
         <v>2022</v>
       </c>
       <c r="F31">
-        <v>0.61803468208092449</v>
+        <v>0.18416184971098257</v>
       </c>
       <c r="G31">
-        <v>0.31518000000000002</v>
+        <v>0.29766999999999999</v>
       </c>
       <c r="H31">
-        <v>2200</v>
+        <v>2530</v>
       </c>
       <c r="I31">
-        <v>66</v>
+        <v>72.600000000000009</v>
       </c>
       <c r="J31">
-        <v>5.25</v>
+        <v>5.7750000000000004</v>
       </c>
       <c r="K31">
         <v>50</v>
@@ -20344,19 +20344,19 @@
         <v>2022</v>
       </c>
       <c r="F32">
-        <v>0.1997687861271675</v>
+        <v>0.61803468208092449</v>
       </c>
       <c r="G32">
-        <v>0.29766999999999999</v>
+        <v>0.31518000000000002</v>
       </c>
       <c r="H32">
-        <v>2530</v>
+        <v>2200</v>
       </c>
       <c r="I32">
-        <v>72.600000000000009</v>
+        <v>66</v>
       </c>
       <c r="J32">
-        <v>5.7750000000000004</v>
+        <v>5.25</v>
       </c>
       <c r="K32">
         <v>50</v>
@@ -20391,7 +20391,7 @@
         <v>33</v>
       </c>
       <c r="D33" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E33">
         <v>1992</v>
@@ -20444,7 +20444,7 @@
         <v>33</v>
       </c>
       <c r="D34" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E34">
         <v>1993</v>
@@ -20497,7 +20497,7 @@
         <v>33</v>
       </c>
       <c r="D35" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E35">
         <v>2005</v>
@@ -20550,7 +20550,7 @@
         <v>33</v>
       </c>
       <c r="D36" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E36">
         <v>1986</v>
@@ -20603,7 +20603,7 @@
         <v>33</v>
       </c>
       <c r="D37" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E37">
         <v>1991</v>
@@ -20656,7 +20656,7 @@
         <v>33</v>
       </c>
       <c r="D38" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E38">
         <v>1992</v>
@@ -20709,7 +20709,7 @@
         <v>33</v>
       </c>
       <c r="D39" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E39">
         <v>1993</v>
@@ -20762,7 +20762,7 @@
         <v>33</v>
       </c>
       <c r="D40" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="E40">
         <v>2009</v>
@@ -20815,7 +20815,7 @@
         <v>33</v>
       </c>
       <c r="D41" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="E41">
         <v>2010</v>
@@ -20868,7 +20868,7 @@
         <v>33</v>
       </c>
       <c r="D42" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="E42">
         <v>2010</v>
@@ -20927,7 +20927,7 @@
         <v>2022</v>
       </c>
       <c r="F43">
-        <v>0.16608022972358796</v>
+        <v>0.19676367392472002</v>
       </c>
       <c r="G43">
         <v>0.50778999999999996</v>
@@ -20980,19 +20980,19 @@
         <v>2022</v>
       </c>
       <c r="F44">
-        <v>0.18507474280047922</v>
+        <v>0.3567559186877659</v>
       </c>
       <c r="G44">
-        <v>0.50778999999999996</v>
+        <v>0.52529999999999999</v>
       </c>
       <c r="H44">
-        <v>1265</v>
+        <v>1100</v>
       </c>
       <c r="I44">
-        <v>36.300000000000004</v>
+        <v>33</v>
       </c>
       <c r="J44">
-        <v>3.4649999999999999</v>
+        <v>3.1500000000000004</v>
       </c>
       <c r="K44">
         <v>50</v>
@@ -21027,25 +21027,25 @@
         <v>49</v>
       </c>
       <c r="D45" t="s">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="E45">
         <v>2022</v>
       </c>
       <c r="F45">
-        <v>0.3567559186877659</v>
+        <v>0.27761211420071885</v>
       </c>
       <c r="G45">
-        <v>0.52529999999999999</v>
+        <v>0.50778999999999996</v>
       </c>
       <c r="H45">
-        <v>1100</v>
+        <v>1265</v>
       </c>
       <c r="I45">
-        <v>33</v>
+        <v>36.300000000000004</v>
       </c>
       <c r="J45">
-        <v>3.1500000000000004</v>
+        <v>3.4650000000000003</v>
       </c>
       <c r="K45">
         <v>50</v>
@@ -21080,25 +21080,25 @@
         <v>49</v>
       </c>
       <c r="D46" t="s">
-        <v>34</v>
+        <v>52</v>
       </c>
       <c r="E46">
         <v>2022</v>
       </c>
       <c r="F46">
-        <v>0.27761211420071885</v>
+        <v>0.30829555840185086</v>
       </c>
       <c r="G46">
-        <v>0.50778999999999996</v>
+        <v>0.52529999999999999</v>
       </c>
       <c r="H46">
-        <v>1265</v>
+        <v>1100</v>
       </c>
       <c r="I46">
-        <v>36.300000000000004</v>
+        <v>33</v>
       </c>
       <c r="J46">
-        <v>3.4650000000000003</v>
+        <v>3.1500000000000004</v>
       </c>
       <c r="K46">
         <v>50</v>
@@ -21139,7 +21139,7 @@
         <v>2022</v>
       </c>
       <c r="F47">
-        <v>0.30829555840185086</v>
+        <v>0.49339465314217229</v>
       </c>
       <c r="G47">
         <v>0.52529999999999999</v>
@@ -21192,7 +21192,7 @@
         <v>2022</v>
       </c>
       <c r="F48">
-        <v>0.43468212618270452</v>
+        <v>0.45732943023592104</v>
       </c>
       <c r="G48">
         <v>0.52529999999999999</v>
@@ -21245,7 +21245,7 @@
         <v>2022</v>
       </c>
       <c r="F49">
-        <v>0.23864901045324952</v>
+        <v>0.19481551873734657</v>
       </c>
       <c r="G49">
         <v>0.50778999999999996</v>
@@ -21298,19 +21298,19 @@
         <v>2022</v>
       </c>
       <c r="F50">
-        <v>0.31243538817501959</v>
+        <v>0.19481551873734657</v>
       </c>
       <c r="G50">
-        <v>0.52529999999999999</v>
+        <v>0.50778999999999996</v>
       </c>
       <c r="H50">
-        <v>1100</v>
+        <v>1265</v>
       </c>
       <c r="I50">
-        <v>33</v>
+        <v>36.300000000000004</v>
       </c>
       <c r="J50">
-        <v>3.1500000000000004</v>
+        <v>3.4650000000000003</v>
       </c>
       <c r="K50">
         <v>50</v>
@@ -21351,7 +21351,7 @@
         <v>2022</v>
       </c>
       <c r="F51">
-        <v>0.17484692806676855</v>
+        <v>0.20212110068999706</v>
       </c>
       <c r="G51">
         <v>0.50778999999999996</v>
@@ -21404,7 +21404,7 @@
         <v>2022</v>
       </c>
       <c r="F52">
-        <v>0.18872753377680451</v>
+        <v>0.26543614427963469</v>
       </c>
       <c r="G52">
         <v>0.50778999999999996</v>
@@ -21416,7 +21416,7 @@
         <v>36.300000000000004</v>
       </c>
       <c r="J52">
-        <v>3.4650000000000007</v>
+        <v>3.4650000000000003</v>
       </c>
       <c r="K52">
         <v>50</v>
@@ -21457,7 +21457,7 @@
         <v>2022</v>
       </c>
       <c r="F53">
-        <v>0.20820908565053911</v>
+        <v>0.20557907614758497</v>
       </c>
       <c r="G53">
         <v>0.50778999999999996</v>
@@ -21469,7 +21469,7 @@
         <v>36.300000000000004</v>
       </c>
       <c r="J53">
-        <v>3.4650000000000007</v>
+        <v>3.4650000000000003</v>
       </c>
       <c r="K53">
         <v>50</v>
@@ -21510,19 +21510,19 @@
         <v>2022</v>
       </c>
       <c r="F54">
-        <v>0.18629233979258764</v>
+        <v>0.37112356319464518</v>
       </c>
       <c r="G54">
-        <v>0.50778999999999996</v>
+        <v>0.52529999999999999</v>
       </c>
       <c r="H54">
-        <v>1265</v>
+        <v>1100</v>
       </c>
       <c r="I54">
-        <v>36.300000000000004</v>
+        <v>33</v>
       </c>
       <c r="J54">
-        <v>3.4650000000000003</v>
+        <v>3.1500000000000004</v>
       </c>
       <c r="K54">
         <v>50</v>
@@ -21563,7 +21563,7 @@
         <v>2022</v>
       </c>
       <c r="F55">
-        <v>0.20236462008841874</v>
+        <v>0.19481551873734657</v>
       </c>
       <c r="G55">
         <v>0.50778999999999996</v>
@@ -21616,7 +21616,7 @@
         <v>2022</v>
       </c>
       <c r="F56">
-        <v>0.19481551873734657</v>
+        <v>0.20820908565053911</v>
       </c>
       <c r="G56">
         <v>0.50778999999999996</v>
@@ -21628,7 +21628,7 @@
         <v>36.300000000000004</v>
       </c>
       <c r="J56">
-        <v>3.4650000000000003</v>
+        <v>3.4650000000000007</v>
       </c>
       <c r="K56">
         <v>50</v>
@@ -21669,7 +21669,7 @@
         <v>2022</v>
       </c>
       <c r="F57">
-        <v>0.18824049497996109</v>
+        <v>0.26604494277568891</v>
       </c>
       <c r="G57">
         <v>0.50778999999999996</v>
@@ -21716,13 +21716,13 @@
         <v>49</v>
       </c>
       <c r="D58" t="s">
-        <v>14</v>
+        <v>64</v>
       </c>
       <c r="E58">
         <v>2022</v>
       </c>
       <c r="F58">
-        <v>0.19822479031525012</v>
+        <v>0.18629233979258764</v>
       </c>
       <c r="G58">
         <v>0.50778999999999996</v>
@@ -21769,13 +21769,13 @@
         <v>49</v>
       </c>
       <c r="D59" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E59">
         <v>2022</v>
       </c>
       <c r="F59">
-        <v>0.19481551873734657</v>
+        <v>0.20236462008841874</v>
       </c>
       <c r="G59">
         <v>0.50778999999999996</v>
@@ -21822,13 +21822,13 @@
         <v>49</v>
       </c>
       <c r="D60" t="s">
-        <v>65</v>
+        <v>16</v>
       </c>
       <c r="E60">
         <v>2022</v>
       </c>
       <c r="F60">
-        <v>0.19481551873734657</v>
+        <v>0.19822479031525012</v>
       </c>
       <c r="G60">
         <v>0.50778999999999996</v>
@@ -21881,7 +21881,7 @@
         <v>2022</v>
       </c>
       <c r="F61">
-        <v>0.18556178159732259</v>
+        <v>0.18702289798785268</v>
       </c>
       <c r="G61">
         <v>0.50778999999999996</v>
@@ -21934,7 +21934,7 @@
         <v>2022</v>
       </c>
       <c r="F62">
-        <v>0.23280454489112914</v>
+        <v>0.19481551873734657</v>
       </c>
       <c r="G62">
         <v>0.50778999999999996</v>
@@ -21946,7 +21946,7 @@
         <v>36.300000000000004</v>
       </c>
       <c r="J62">
-        <v>3.4650000000000007</v>
+        <v>3.4650000000000003</v>
       </c>
       <c r="K62">
         <v>50</v>
@@ -21987,7 +21987,7 @@
         <v>2022</v>
       </c>
       <c r="F63">
-        <v>0.26604494277568891</v>
+        <v>0.22793415692269547</v>
       </c>
       <c r="G63">
         <v>0.50778999999999996</v>
@@ -22040,7 +22040,7 @@
         <v>2022</v>
       </c>
       <c r="F64">
-        <v>0.21551466760318963</v>
+        <v>0.1548783373961905</v>
       </c>
       <c r="G64">
         <v>0.50778999999999996</v>
@@ -22052,7 +22052,7 @@
         <v>36.300000000000004</v>
       </c>
       <c r="J64">
-        <v>3.4650000000000003</v>
+        <v>3.4649999999999999</v>
       </c>
       <c r="K64">
         <v>50</v>
@@ -22093,19 +22093,19 @@
         <v>2022</v>
       </c>
       <c r="F65">
-        <v>0.45732943023592104</v>
+        <v>0.27347228442755023</v>
       </c>
       <c r="G65">
-        <v>0.52529999999999999</v>
+        <v>0.50778999999999996</v>
       </c>
       <c r="H65">
-        <v>1100</v>
+        <v>1265</v>
       </c>
       <c r="I65">
-        <v>33</v>
+        <v>36.300000000000004</v>
       </c>
       <c r="J65">
-        <v>3.1500000000000004</v>
+        <v>3.4650000000000003</v>
       </c>
       <c r="K65">
         <v>50</v>
@@ -22146,19 +22146,19 @@
         <v>2022</v>
       </c>
       <c r="F66">
-        <v>0.49339465314217229</v>
+        <v>0.23864901045324952</v>
       </c>
       <c r="G66">
-        <v>0.52529999999999999</v>
+        <v>0.50778999999999996</v>
       </c>
       <c r="H66">
-        <v>1100</v>
+        <v>1265</v>
       </c>
       <c r="I66">
-        <v>33</v>
+        <v>36.300000000000004</v>
       </c>
       <c r="J66">
-        <v>3.1500000000000004</v>
+        <v>3.4650000000000003</v>
       </c>
       <c r="K66">
         <v>50</v>
@@ -22199,7 +22199,7 @@
         <v>2022</v>
       </c>
       <c r="F67">
-        <v>0.19627663512787666</v>
+        <v>0.23280454489112914</v>
       </c>
       <c r="G67">
         <v>0.50778999999999996</v>
@@ -22211,7 +22211,7 @@
         <v>36.300000000000004</v>
       </c>
       <c r="J67">
-        <v>3.4649999999999999</v>
+        <v>3.4650000000000007</v>
       </c>
       <c r="K67">
         <v>50</v>
@@ -22252,19 +22252,19 @@
         <v>2022</v>
       </c>
       <c r="F68">
-        <v>0.18702289798785268</v>
+        <v>0.31243538817501959</v>
       </c>
       <c r="G68">
-        <v>0.50778999999999996</v>
+        <v>0.52529999999999999</v>
       </c>
       <c r="H68">
-        <v>1265</v>
+        <v>1100</v>
       </c>
       <c r="I68">
-        <v>36.300000000000004</v>
+        <v>33</v>
       </c>
       <c r="J68">
-        <v>3.4650000000000003</v>
+        <v>3.1500000000000004</v>
       </c>
       <c r="K68">
         <v>50</v>
@@ -22305,7 +22305,7 @@
         <v>2022</v>
       </c>
       <c r="F69">
-        <v>0.19481551873734657</v>
+        <v>0.29344087509812827</v>
       </c>
       <c r="G69">
         <v>0.50778999999999996</v>
@@ -22358,7 +22358,7 @@
         <v>2022</v>
       </c>
       <c r="F70">
-        <v>0.20212110068999706</v>
+        <v>0.21551466760318963</v>
       </c>
       <c r="G70">
         <v>0.50778999999999996</v>
@@ -22411,7 +22411,7 @@
         <v>2022</v>
       </c>
       <c r="F71">
-        <v>0.26543614427963469</v>
+        <v>0.17484692806676855</v>
       </c>
       <c r="G71">
         <v>0.50778999999999996</v>
@@ -22464,7 +22464,7 @@
         <v>2022</v>
       </c>
       <c r="F72">
-        <v>0.20557907614758497</v>
+        <v>0.18872753377680451</v>
       </c>
       <c r="G72">
         <v>0.50778999999999996</v>
@@ -22476,7 +22476,7 @@
         <v>36.300000000000004</v>
       </c>
       <c r="J72">
-        <v>3.4650000000000003</v>
+        <v>3.4650000000000007</v>
       </c>
       <c r="K72">
         <v>50</v>
@@ -22517,19 +22517,19 @@
         <v>2022</v>
       </c>
       <c r="F73">
-        <v>0.37112356319464518</v>
+        <v>0.21113131843159935</v>
       </c>
       <c r="G73">
-        <v>0.52529999999999999</v>
+        <v>0.50778999999999996</v>
       </c>
       <c r="H73">
-        <v>1100</v>
+        <v>1265</v>
       </c>
       <c r="I73">
-        <v>33</v>
+        <v>36.300000000000004</v>
       </c>
       <c r="J73">
-        <v>3.1500000000000004</v>
+        <v>3.4650000000000003</v>
       </c>
       <c r="K73">
         <v>50</v>
@@ -22570,7 +22570,7 @@
         <v>2022</v>
       </c>
       <c r="F74">
-        <v>0.21113131843159935</v>
+        <v>0.18556178159732259</v>
       </c>
       <c r="G74">
         <v>0.50778999999999996</v>
@@ -22623,7 +22623,7 @@
         <v>2022</v>
       </c>
       <c r="F75">
-        <v>0.27347228442755023</v>
+        <v>0.21283595422055113</v>
       </c>
       <c r="G75">
         <v>0.50778999999999996</v>
@@ -22676,19 +22676,19 @@
         <v>2022</v>
       </c>
       <c r="F76">
-        <v>0.1548783373961905</v>
+        <v>0.39839773581787374</v>
       </c>
       <c r="G76">
-        <v>0.50778999999999996</v>
+        <v>0.52529999999999999</v>
       </c>
       <c r="H76">
-        <v>1265</v>
+        <v>1100</v>
       </c>
       <c r="I76">
-        <v>36.300000000000004</v>
+        <v>33</v>
       </c>
       <c r="J76">
-        <v>3.4649999999999999</v>
+        <v>3.1500000000000004</v>
       </c>
       <c r="K76">
         <v>50</v>
@@ -22729,7 +22729,7 @@
         <v>2022</v>
       </c>
       <c r="F77">
-        <v>0.22793415692269547</v>
+        <v>0.28443065735652601</v>
       </c>
       <c r="G77">
         <v>0.50778999999999996</v>
@@ -22782,19 +22782,19 @@
         <v>2022</v>
       </c>
       <c r="F78">
-        <v>0.21283595422055113</v>
+        <v>0.43468212618270452</v>
       </c>
       <c r="G78">
-        <v>0.50778999999999996</v>
+        <v>0.52529999999999999</v>
       </c>
       <c r="H78">
-        <v>1265</v>
+        <v>1100</v>
       </c>
       <c r="I78">
-        <v>36.300000000000004</v>
+        <v>33</v>
       </c>
       <c r="J78">
-        <v>3.4650000000000003</v>
+        <v>3.1500000000000004</v>
       </c>
       <c r="K78">
         <v>50</v>
@@ -22835,19 +22835,19 @@
         <v>2022</v>
       </c>
       <c r="F79">
-        <v>0.39839773581787374</v>
+        <v>0.18824049497996109</v>
       </c>
       <c r="G79">
-        <v>0.52529999999999999</v>
+        <v>0.50778999999999996</v>
       </c>
       <c r="H79">
-        <v>1100</v>
+        <v>1265</v>
       </c>
       <c r="I79">
-        <v>33</v>
+        <v>36.300000000000004</v>
       </c>
       <c r="J79">
-        <v>3.1500000000000004</v>
+        <v>3.4650000000000003</v>
       </c>
       <c r="K79">
         <v>50</v>
@@ -22888,7 +22888,7 @@
         <v>2022</v>
       </c>
       <c r="F80">
-        <v>0.29344087509812827</v>
+        <v>0.16608022972358796</v>
       </c>
       <c r="G80">
         <v>0.50778999999999996</v>
@@ -22941,7 +22941,7 @@
         <v>2022</v>
       </c>
       <c r="F81">
-        <v>0.28443065735652601</v>
+        <v>0.19627663512787666</v>
       </c>
       <c r="G81">
         <v>0.50778999999999996</v>
@@ -22953,7 +22953,7 @@
         <v>36.300000000000004</v>
       </c>
       <c r="J81">
-        <v>3.4650000000000003</v>
+        <v>3.4649999999999999</v>
       </c>
       <c r="K81">
         <v>50</v>
@@ -22994,7 +22994,7 @@
         <v>2022</v>
       </c>
       <c r="F82">
-        <v>0.19676367392472002</v>
+        <v>0.18507474280047922</v>
       </c>
       <c r="G82">
         <v>0.50778999999999996</v>
@@ -23006,7 +23006,7 @@
         <v>36.300000000000004</v>
       </c>
       <c r="J82">
-        <v>3.4650000000000003</v>
+        <v>3.4649999999999999</v>
       </c>
       <c r="K82">
         <v>50</v>
@@ -23041,7 +23041,7 @@
         <v>49</v>
       </c>
       <c r="D83" t="s">
-        <v>87</v>
+        <v>50</v>
       </c>
       <c r="E83">
         <v>2006</v>
@@ -23094,7 +23094,7 @@
         <v>49</v>
       </c>
       <c r="D84" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="E84">
         <v>2012</v>
@@ -23147,7 +23147,7 @@
         <v>49</v>
       </c>
       <c r="D85" t="s">
-        <v>54</v>
+        <v>83</v>
       </c>
       <c r="E85">
         <v>1993</v>
@@ -23200,7 +23200,7 @@
         <v>49</v>
       </c>
       <c r="D86" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E86">
         <v>2011</v>
@@ -23253,7 +23253,7 @@
         <v>49</v>
       </c>
       <c r="D87" t="s">
-        <v>56</v>
+        <v>73</v>
       </c>
       <c r="E87">
         <v>2005</v>
@@ -23306,7 +23306,7 @@
         <v>49</v>
       </c>
       <c r="D88" t="s">
-        <v>56</v>
+        <v>73</v>
       </c>
       <c r="E88">
         <v>2006</v>
@@ -23359,7 +23359,7 @@
         <v>49</v>
       </c>
       <c r="D89" t="s">
-        <v>56</v>
+        <v>73</v>
       </c>
       <c r="E89">
         <v>2006</v>
@@ -23465,7 +23465,7 @@
         <v>49</v>
       </c>
       <c r="D91" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="E91">
         <v>2003</v>
@@ -23624,7 +23624,7 @@
         <v>49</v>
       </c>
       <c r="D94" t="s">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="E94">
         <v>2004</v>
@@ -23677,7 +23677,7 @@
         <v>49</v>
       </c>
       <c r="D95" t="s">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="E95">
         <v>2005</v>
@@ -23730,7 +23730,7 @@
         <v>49</v>
       </c>
       <c r="D96" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="E96">
         <v>2005</v>
@@ -23783,7 +23783,7 @@
         <v>49</v>
       </c>
       <c r="D97" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="E97">
         <v>2005</v>
@@ -23836,7 +23836,7 @@
         <v>49</v>
       </c>
       <c r="D98" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E98">
         <v>2004</v>
@@ -23889,7 +23889,7 @@
         <v>49</v>
       </c>
       <c r="D99" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E99">
         <v>2004</v>
@@ -23942,7 +23942,7 @@
         <v>49</v>
       </c>
       <c r="D100" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E100">
         <v>2004</v>
@@ -23995,7 +23995,7 @@
         <v>49</v>
       </c>
       <c r="D101" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="E101">
         <v>2008</v>
@@ -24048,7 +24048,7 @@
         <v>49</v>
       </c>
       <c r="D102" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="E102">
         <v>2008</v>
@@ -24101,7 +24101,7 @@
         <v>49</v>
       </c>
       <c r="D103" t="s">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="E103">
         <v>2002</v>
@@ -24154,7 +24154,7 @@
         <v>49</v>
       </c>
       <c r="D104" t="s">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="E104">
         <v>2002</v>
@@ -24207,7 +24207,7 @@
         <v>49</v>
       </c>
       <c r="D105" t="s">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="E105">
         <v>2003</v>
@@ -24260,7 +24260,7 @@
         <v>49</v>
       </c>
       <c r="D106" t="s">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="E106">
         <v>2003</v>
@@ -24313,7 +24313,7 @@
         <v>49</v>
       </c>
       <c r="D107" t="s">
-        <v>50</v>
+        <v>85</v>
       </c>
       <c r="E107">
         <v>2000</v>
@@ -24366,7 +24366,7 @@
         <v>49</v>
       </c>
       <c r="D108" t="s">
-        <v>50</v>
+        <v>85</v>
       </c>
       <c r="E108">
         <v>2000</v>
@@ -24419,7 +24419,7 @@
         <v>49</v>
       </c>
       <c r="D109" t="s">
-        <v>58</v>
+        <v>77</v>
       </c>
       <c r="E109">
         <v>2007</v>
@@ -24472,7 +24472,7 @@
         <v>49</v>
       </c>
       <c r="D110" t="s">
-        <v>54</v>
+        <v>83</v>
       </c>
       <c r="E110">
         <v>2023</v>
@@ -24525,7 +24525,7 @@
         <v>49</v>
       </c>
       <c r="D111" t="s">
-        <v>54</v>
+        <v>83</v>
       </c>
       <c r="E111">
         <v>2001</v>
@@ -24631,7 +24631,7 @@
         <v>49</v>
       </c>
       <c r="D113" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="E113">
         <v>2010</v>
@@ -24684,7 +24684,7 @@
         <v>49</v>
       </c>
       <c r="D114" t="s">
-        <v>75</v>
+        <v>57</v>
       </c>
       <c r="E114">
         <v>2005</v>
@@ -24737,7 +24737,7 @@
         <v>49</v>
       </c>
       <c r="D115" t="s">
-        <v>75</v>
+        <v>57</v>
       </c>
       <c r="E115">
         <v>2009</v>
@@ -24790,7 +24790,7 @@
         <v>49</v>
       </c>
       <c r="D116" t="s">
-        <v>76</v>
+        <v>58</v>
       </c>
       <c r="E116">
         <v>1997</v>
@@ -24843,7 +24843,7 @@
         <v>49</v>
       </c>
       <c r="D117" t="s">
-        <v>76</v>
+        <v>58</v>
       </c>
       <c r="E117">
         <v>1997</v>
@@ -24896,7 +24896,7 @@
         <v>49</v>
       </c>
       <c r="D118" t="s">
-        <v>76</v>
+        <v>58</v>
       </c>
       <c r="E118">
         <v>1998</v>
@@ -24949,7 +24949,7 @@
         <v>49</v>
       </c>
       <c r="D119" t="s">
-        <v>76</v>
+        <v>58</v>
       </c>
       <c r="E119">
         <v>1999</v>
@@ -25055,7 +25055,7 @@
         <v>49</v>
       </c>
       <c r="D121" t="s">
-        <v>70</v>
+        <v>54</v>
       </c>
       <c r="E121">
         <v>2010</v>
@@ -25108,7 +25108,7 @@
         <v>49</v>
       </c>
       <c r="D122" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="E122">
         <v>2003</v>
@@ -25161,7 +25161,7 @@
         <v>49</v>
       </c>
       <c r="D123" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="E123">
         <v>2003</v>
@@ -25214,7 +25214,7 @@
         <v>49</v>
       </c>
       <c r="D124" t="s">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="E124">
         <v>2006</v>
@@ -25373,7 +25373,7 @@
         <v>49</v>
       </c>
       <c r="D127" t="s">
-        <v>57</v>
+        <v>76</v>
       </c>
       <c r="E127">
         <v>2002</v>
@@ -25426,7 +25426,7 @@
         <v>49</v>
       </c>
       <c r="D128" t="s">
-        <v>57</v>
+        <v>76</v>
       </c>
       <c r="E128">
         <v>2002</v>
@@ -25479,7 +25479,7 @@
         <v>49</v>
       </c>
       <c r="D129" t="s">
-        <v>70</v>
+        <v>54</v>
       </c>
       <c r="E129">
         <v>2010</v>
@@ -25532,7 +25532,7 @@
         <v>49</v>
       </c>
       <c r="D130" t="s">
-        <v>70</v>
+        <v>54</v>
       </c>
       <c r="E130">
         <v>2010</v>
@@ -25585,7 +25585,7 @@
         <v>49</v>
       </c>
       <c r="D131" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="E131">
         <v>2008</v>
@@ -25638,7 +25638,7 @@
         <v>49</v>
       </c>
       <c r="D132" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="E132">
         <v>2008</v>
@@ -25691,7 +25691,7 @@
         <v>49</v>
       </c>
       <c r="D133" t="s">
-        <v>82</v>
+        <v>68</v>
       </c>
       <c r="E133">
         <v>2018</v>
@@ -25744,7 +25744,7 @@
         <v>49</v>
       </c>
       <c r="D134" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="E134">
         <v>2006</v>
@@ -25797,7 +25797,7 @@
         <v>49</v>
       </c>
       <c r="D135" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="E135">
         <v>2007</v>
@@ -25956,7 +25956,7 @@
         <v>49</v>
       </c>
       <c r="D138" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E138">
         <v>2010</v>
@@ -26009,7 +26009,7 @@
         <v>49</v>
       </c>
       <c r="D139" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E139">
         <v>2010</v>
@@ -26062,7 +26062,7 @@
         <v>49</v>
       </c>
       <c r="D140" t="s">
-        <v>85</v>
+        <v>74</v>
       </c>
       <c r="E140">
         <v>2004</v>
@@ -26115,7 +26115,7 @@
         <v>49</v>
       </c>
       <c r="D141" t="s">
-        <v>85</v>
+        <v>74</v>
       </c>
       <c r="E141">
         <v>2004</v>
@@ -26168,7 +26168,7 @@
         <v>49</v>
       </c>
       <c r="D142" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="E142">
         <v>2008</v>
@@ -26221,7 +26221,7 @@
         <v>49</v>
       </c>
       <c r="D143" t="s">
-        <v>51</v>
+        <v>87</v>
       </c>
       <c r="E143">
         <v>2007</v>
@@ -26274,7 +26274,7 @@
         <v>49</v>
       </c>
       <c r="D144" t="s">
-        <v>51</v>
+        <v>87</v>
       </c>
       <c r="E144">
         <v>2007</v>
@@ -26327,7 +26327,7 @@
         <v>49</v>
       </c>
       <c r="D145" t="s">
-        <v>71</v>
+        <v>53</v>
       </c>
       <c r="E145">
         <v>2005</v>
@@ -26380,7 +26380,7 @@
         <v>49</v>
       </c>
       <c r="D146" t="s">
-        <v>71</v>
+        <v>53</v>
       </c>
       <c r="E146">
         <v>2005</v>
@@ -26433,7 +26433,7 @@
         <v>49</v>
       </c>
       <c r="D147" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="E147">
         <v>2015</v>
@@ -26486,7 +26486,7 @@
         <v>49</v>
       </c>
       <c r="D148" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="E148">
         <v>2004</v>
@@ -26539,7 +26539,7 @@
         <v>49</v>
       </c>
       <c r="D149" t="s">
-        <v>77</v>
+        <v>59</v>
       </c>
       <c r="E149">
         <v>2006</v>
@@ -26592,7 +26592,7 @@
         <v>49</v>
       </c>
       <c r="D150" t="s">
-        <v>58</v>
+        <v>77</v>
       </c>
       <c r="E150">
         <v>2011</v>
@@ -26645,7 +26645,7 @@
         <v>49</v>
       </c>
       <c r="D151" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="E151">
         <v>2004</v>
@@ -26698,7 +26698,7 @@
         <v>49</v>
       </c>
       <c r="D152" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="E152">
         <v>2005</v>
@@ -26751,7 +26751,7 @@
         <v>49</v>
       </c>
       <c r="D153" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E153">
         <v>2006</v>
@@ -26804,7 +26804,7 @@
         <v>49</v>
       </c>
       <c r="D154" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E154">
         <v>2008</v>
@@ -26857,7 +26857,7 @@
         <v>49</v>
       </c>
       <c r="D155" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="E155">
         <v>2007</v>
@@ -26963,7 +26963,7 @@
         <v>49</v>
       </c>
       <c r="D157" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="E157">
         <v>2023</v>
@@ -27016,7 +27016,7 @@
         <v>49</v>
       </c>
       <c r="D158" t="s">
-        <v>55</v>
+        <v>71</v>
       </c>
       <c r="E158">
         <v>2026</v>
@@ -27069,7 +27069,7 @@
         <v>49</v>
       </c>
       <c r="D159" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E159">
         <v>2022</v>
@@ -27122,7 +27122,7 @@
         <v>49</v>
       </c>
       <c r="D160" t="s">
-        <v>63</v>
+        <v>84</v>
       </c>
       <c r="E160">
         <v>2003</v>
@@ -27175,7 +27175,7 @@
         <v>49</v>
       </c>
       <c r="D161" t="s">
-        <v>63</v>
+        <v>84</v>
       </c>
       <c r="E161">
         <v>2003</v>
@@ -27228,7 +27228,7 @@
         <v>49</v>
       </c>
       <c r="D162" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="E162">
         <v>2003</v>
@@ -27281,7 +27281,7 @@
         <v>49</v>
       </c>
       <c r="D163" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="E163">
         <v>2008</v>
@@ -27334,7 +27334,7 @@
         <v>49</v>
       </c>
       <c r="D164" t="s">
-        <v>70</v>
+        <v>54</v>
       </c>
       <c r="E164">
         <v>1999</v>
@@ -27387,7 +27387,7 @@
         <v>49</v>
       </c>
       <c r="D165" t="s">
-        <v>70</v>
+        <v>54</v>
       </c>
       <c r="E165">
         <v>1999</v>
@@ -27440,7 +27440,7 @@
         <v>49</v>
       </c>
       <c r="D166" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="E166">
         <v>1997</v>
@@ -27546,7 +27546,7 @@
         <v>49</v>
       </c>
       <c r="D168" t="s">
-        <v>81</v>
+        <v>69</v>
       </c>
       <c r="E168">
         <v>2001</v>
@@ -27599,7 +27599,7 @@
         <v>49</v>
       </c>
       <c r="D169" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E169">
         <v>2006</v>
@@ -27705,7 +27705,7 @@
         <v>49</v>
       </c>
       <c r="D171" t="s">
-        <v>82</v>
+        <v>68</v>
       </c>
       <c r="E171">
         <v>2007</v>
@@ -28288,7 +28288,7 @@
         <v>49</v>
       </c>
       <c r="D182" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="E182">
         <v>2015</v>
@@ -29083,7 +29083,7 @@
         <v>49</v>
       </c>
       <c r="D197" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E197">
         <v>2004</v>
@@ -29136,7 +29136,7 @@
         <v>49</v>
       </c>
       <c r="D198" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E198">
         <v>2008</v>
@@ -29348,7 +29348,7 @@
         <v>49</v>
       </c>
       <c r="D202" t="s">
-        <v>70</v>
+        <v>54</v>
       </c>
       <c r="E202">
         <v>2005</v>
@@ -29401,7 +29401,7 @@
         <v>49</v>
       </c>
       <c r="D203" t="s">
-        <v>70</v>
+        <v>54</v>
       </c>
       <c r="E203">
         <v>2015</v>
@@ -30090,7 +30090,7 @@
         <v>49</v>
       </c>
       <c r="D216" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E216">
         <v>2022</v>
@@ -30302,7 +30302,7 @@
         <v>49</v>
       </c>
       <c r="D220" t="s">
-        <v>55</v>
+        <v>71</v>
       </c>
       <c r="E220">
         <v>2009</v>
@@ -30991,7 +30991,7 @@
         <v>49</v>
       </c>
       <c r="D233" t="s">
-        <v>85</v>
+        <v>74</v>
       </c>
       <c r="E233">
         <v>1994</v>
@@ -31150,7 +31150,7 @@
         <v>49</v>
       </c>
       <c r="D236" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E236">
         <v>1990</v>
@@ -31203,7 +31203,7 @@
         <v>49</v>
       </c>
       <c r="D237" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E237">
         <v>2022</v>
@@ -31362,7 +31362,7 @@
         <v>49</v>
       </c>
       <c r="D240" t="s">
-        <v>75</v>
+        <v>57</v>
       </c>
       <c r="E240">
         <v>2006</v>
@@ -31415,7 +31415,7 @@
         <v>49</v>
       </c>
       <c r="D241" t="s">
-        <v>71</v>
+        <v>53</v>
       </c>
       <c r="E241">
         <v>2024</v>
@@ -31468,7 +31468,7 @@
         <v>49</v>
       </c>
       <c r="D242" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="E242">
         <v>2023</v>
@@ -31521,7 +31521,7 @@
         <v>49</v>
       </c>
       <c r="D243" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="E243">
         <v>2023</v>
@@ -31574,7 +31574,7 @@
         <v>49</v>
       </c>
       <c r="D244" t="s">
-        <v>82</v>
+        <v>68</v>
       </c>
       <c r="E244">
         <v>1997</v>
@@ -32051,7 +32051,7 @@
         <v>49</v>
       </c>
       <c r="D253" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="E253">
         <v>2008</v>
@@ -32316,7 +32316,7 @@
         <v>49</v>
       </c>
       <c r="D258" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="E258">
         <v>2015</v>
@@ -32422,7 +32422,7 @@
         <v>49</v>
       </c>
       <c r="D260" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="E260">
         <v>2004</v>
@@ -32687,7 +32687,7 @@
         <v>49</v>
       </c>
       <c r="D265" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="E265">
         <v>2024</v>
@@ -32793,7 +32793,7 @@
         <v>49</v>
       </c>
       <c r="D267" t="s">
-        <v>77</v>
+        <v>59</v>
       </c>
       <c r="E267">
         <v>2023</v>
@@ -33005,7 +33005,7 @@
         <v>49</v>
       </c>
       <c r="D271" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="E271">
         <v>1975</v>
@@ -33058,7 +33058,7 @@
         <v>49</v>
       </c>
       <c r="D272" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="E272">
         <v>1975</v>
@@ -33111,7 +33111,7 @@
         <v>49</v>
       </c>
       <c r="D273" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="E273">
         <v>1975</v>
@@ -33164,7 +33164,7 @@
         <v>49</v>
       </c>
       <c r="D274" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="E274">
         <v>2015</v>
@@ -33217,7 +33217,7 @@
         <v>49</v>
       </c>
       <c r="D275" t="s">
-        <v>56</v>
+        <v>73</v>
       </c>
       <c r="E275">
         <v>1967</v>
@@ -33270,7 +33270,7 @@
         <v>49</v>
       </c>
       <c r="D276" t="s">
-        <v>56</v>
+        <v>73</v>
       </c>
       <c r="E276">
         <v>1971</v>
@@ -33323,7 +33323,7 @@
         <v>49</v>
       </c>
       <c r="D277" t="s">
-        <v>81</v>
+        <v>69</v>
       </c>
       <c r="E277">
         <v>1970</v>
@@ -33376,7 +33376,7 @@
         <v>49</v>
       </c>
       <c r="D278" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E278">
         <v>1978</v>
@@ -33429,7 +33429,7 @@
         <v>49</v>
       </c>
       <c r="D279" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E279">
         <v>1981</v>
@@ -33482,7 +33482,7 @@
         <v>49</v>
       </c>
       <c r="D280" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E280">
         <v>1987</v>
@@ -33906,7 +33906,7 @@
         <v>293</v>
       </c>
       <c r="D288" t="s">
-        <v>76</v>
+        <v>58</v>
       </c>
       <c r="E288">
         <v>1991</v>
@@ -33959,7 +33959,7 @@
         <v>293</v>
       </c>
       <c r="D289" t="s">
-        <v>76</v>
+        <v>58</v>
       </c>
       <c r="E289">
         <v>1991</v>
@@ -35019,25 +35019,25 @@
         <v>308</v>
       </c>
       <c r="D309" t="s">
-        <v>309</v>
+        <v>151</v>
       </c>
       <c r="E309">
         <v>2022</v>
       </c>
       <c r="F309">
-        <v>0.20320063648536632</v>
+        <v>4.5464982592616207E-2</v>
       </c>
       <c r="G309">
         <v>1</v>
       </c>
       <c r="H309">
-        <v>3162.5000000000005</v>
+        <v>3712.5000000000005</v>
       </c>
       <c r="I309">
-        <v>60.500000000000014</v>
+        <v>71.5</v>
       </c>
       <c r="J309">
-        <v>2.3100000000000005</v>
+        <v>2.52</v>
       </c>
       <c r="K309">
         <v>100</v>
@@ -35072,13 +35072,13 @@
         <v>308</v>
       </c>
       <c r="D310" t="s">
-        <v>291</v>
+        <v>80</v>
       </c>
       <c r="E310">
         <v>2022</v>
       </c>
       <c r="F310">
-        <v>0.13082780705222213</v>
+        <v>5.4743550468660328E-2</v>
       </c>
       <c r="G310">
         <v>1</v>
@@ -35125,25 +35125,25 @@
         <v>308</v>
       </c>
       <c r="D311" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="E311">
         <v>2022</v>
       </c>
       <c r="F311">
-        <v>5.1032123318242681E-2</v>
+        <v>4.4073197411209589E-2</v>
       </c>
       <c r="G311">
         <v>1</v>
       </c>
       <c r="H311">
-        <v>3162.5000000000005</v>
+        <v>3712.5000000000005</v>
       </c>
       <c r="I311">
-        <v>60.500000000000021</v>
+        <v>71.5</v>
       </c>
       <c r="J311">
-        <v>2.3100000000000005</v>
+        <v>2.52</v>
       </c>
       <c r="K311">
         <v>100</v>
@@ -35178,25 +35178,25 @@
         <v>308</v>
       </c>
       <c r="D312" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="E312">
         <v>2022</v>
       </c>
       <c r="F312">
-        <v>4.4073197411209589E-2</v>
+        <v>6.9589259070330922E-2</v>
       </c>
       <c r="G312">
         <v>1</v>
       </c>
       <c r="H312">
-        <v>3712.5000000000005</v>
+        <v>3162.5000000000005</v>
       </c>
       <c r="I312">
-        <v>71.5</v>
+        <v>60.500000000000007</v>
       </c>
       <c r="J312">
-        <v>2.52</v>
+        <v>2.3100000000000005</v>
       </c>
       <c r="K312">
         <v>100</v>
@@ -35231,13 +35231,13 @@
         <v>308</v>
       </c>
       <c r="D313" t="s">
-        <v>83</v>
+        <v>311</v>
       </c>
       <c r="E313">
         <v>2022</v>
       </c>
       <c r="F313">
-        <v>5.4743550468660328E-2</v>
+        <v>5.1032123318242681E-2</v>
       </c>
       <c r="G313">
         <v>1</v>
@@ -35246,7 +35246,7 @@
         <v>3162.5000000000005</v>
       </c>
       <c r="I313">
-        <v>60.500000000000014</v>
+        <v>60.500000000000021</v>
       </c>
       <c r="J313">
         <v>2.3100000000000005</v>
@@ -35290,19 +35290,19 @@
         <v>2022</v>
       </c>
       <c r="F314">
-        <v>0.1577356538927501</v>
+        <v>0.57944656385895543</v>
       </c>
       <c r="G314">
         <v>1</v>
       </c>
       <c r="H314">
-        <v>3162.5000000000005</v>
+        <v>2750</v>
       </c>
       <c r="I314">
-        <v>60.500000000000014</v>
+        <v>55.000000000000007</v>
       </c>
       <c r="J314">
-        <v>2.3100000000000005</v>
+        <v>2.1</v>
       </c>
       <c r="K314">
         <v>100</v>
@@ -35337,13 +35337,13 @@
         <v>308</v>
       </c>
       <c r="D315" t="s">
-        <v>313</v>
+        <v>291</v>
       </c>
       <c r="E315">
         <v>2022</v>
       </c>
       <c r="F315">
-        <v>0.15541601192373908</v>
+        <v>0.13082780705222213</v>
       </c>
       <c r="G315">
         <v>1</v>
@@ -35390,13 +35390,13 @@
         <v>308</v>
       </c>
       <c r="D316" t="s">
-        <v>193</v>
+        <v>313</v>
       </c>
       <c r="E316">
         <v>2022</v>
       </c>
       <c r="F316">
-        <v>0.61052976624370348</v>
+        <v>0.35629700644009438</v>
       </c>
       <c r="G316">
         <v>1</v>
@@ -35405,7 +35405,7 @@
         <v>2750</v>
       </c>
       <c r="I316">
-        <v>55.000000000000007</v>
+        <v>55</v>
       </c>
       <c r="J316">
         <v>2.1</v>
@@ -35443,25 +35443,25 @@
         <v>308</v>
       </c>
       <c r="D317" t="s">
-        <v>21</v>
+        <v>314</v>
       </c>
       <c r="E317">
         <v>2022</v>
       </c>
       <c r="F317">
-        <v>0.11134281451252948</v>
+        <v>4.4073197411209589E-2</v>
       </c>
       <c r="G317">
         <v>1</v>
       </c>
       <c r="H317">
-        <v>3162.5000000000005</v>
+        <v>3712.5000000000005</v>
       </c>
       <c r="I317">
-        <v>60.500000000000014</v>
+        <v>71.5</v>
       </c>
       <c r="J317">
-        <v>2.3100000000000005</v>
+        <v>2.52</v>
       </c>
       <c r="K317">
         <v>100</v>
@@ -35496,13 +35496,13 @@
         <v>308</v>
       </c>
       <c r="D318" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="E318">
         <v>2022</v>
       </c>
       <c r="F318">
-        <v>6.9589259070330922E-2</v>
+        <v>0.19299421182171778</v>
       </c>
       <c r="G318">
         <v>1</v>
@@ -35511,7 +35511,7 @@
         <v>3162.5000000000005</v>
       </c>
       <c r="I318">
-        <v>60.500000000000007</v>
+        <v>60.500000000000014</v>
       </c>
       <c r="J318">
         <v>2.3100000000000005</v>
@@ -35549,13 +35549,13 @@
         <v>308</v>
       </c>
       <c r="D319" t="s">
-        <v>315</v>
+        <v>239</v>
       </c>
       <c r="E319">
         <v>2022</v>
       </c>
       <c r="F319">
-        <v>0.13036387865841995</v>
+        <v>0.22871669814448767</v>
       </c>
       <c r="G319">
         <v>1</v>
@@ -35602,25 +35602,25 @@
         <v>308</v>
       </c>
       <c r="D320" t="s">
-        <v>99</v>
+        <v>316</v>
       </c>
       <c r="E320">
         <v>2022</v>
       </c>
       <c r="F320">
-        <v>0.29181095970158766</v>
+        <v>1.0883760118599757</v>
       </c>
       <c r="G320">
         <v>1</v>
       </c>
       <c r="H320">
-        <v>3162.5000000000005</v>
+        <v>2750</v>
       </c>
       <c r="I320">
-        <v>60.500000000000014</v>
+        <v>55.000000000000007</v>
       </c>
       <c r="J320">
-        <v>2.3100000000000005</v>
+        <v>2.1</v>
       </c>
       <c r="K320">
         <v>100</v>
@@ -35655,25 +35655,25 @@
         <v>308</v>
       </c>
       <c r="D321" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="E321">
         <v>2022</v>
       </c>
       <c r="F321">
-        <v>5.8918906012880183E-2</v>
+        <v>4.1753555442198553E-2</v>
       </c>
       <c r="G321">
         <v>1</v>
       </c>
       <c r="H321">
-        <v>3162.5000000000005</v>
+        <v>3712.5000000000005</v>
       </c>
       <c r="I321">
-        <v>60.500000000000021</v>
+        <v>71.5</v>
       </c>
       <c r="J321">
-        <v>2.3100000000000005</v>
+        <v>2.52</v>
       </c>
       <c r="K321">
         <v>100</v>
@@ -35708,13 +35708,13 @@
         <v>308</v>
       </c>
       <c r="D322" t="s">
-        <v>16</v>
+        <v>318</v>
       </c>
       <c r="E322">
         <v>2022</v>
       </c>
       <c r="F322">
-        <v>8.7682466428616976E-2</v>
+        <v>0.10067246145507874</v>
       </c>
       <c r="G322">
         <v>1</v>
@@ -35723,7 +35723,7 @@
         <v>3162.5000000000005</v>
       </c>
       <c r="I322">
-        <v>60.500000000000007</v>
+        <v>60.500000000000014</v>
       </c>
       <c r="J322">
         <v>2.3100000000000005</v>
@@ -35761,13 +35761,13 @@
         <v>308</v>
       </c>
       <c r="D323" t="s">
-        <v>317</v>
+        <v>193</v>
       </c>
       <c r="E323">
         <v>2022</v>
       </c>
       <c r="F323">
-        <v>0.56367299846968055</v>
+        <v>0.61052976624370348</v>
       </c>
       <c r="G323">
         <v>1</v>
@@ -35814,25 +35814,25 @@
         <v>308</v>
       </c>
       <c r="D324" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="E324">
         <v>2022</v>
       </c>
       <c r="F324">
-        <v>4.3145340623605172E-2</v>
+        <v>6.3558189950902247E-2</v>
       </c>
       <c r="G324">
         <v>1</v>
       </c>
       <c r="H324">
-        <v>3712.5000000000005</v>
+        <v>3162.5000000000005</v>
       </c>
       <c r="I324">
-        <v>71.5</v>
+        <v>60.500000000000014</v>
       </c>
       <c r="J324">
-        <v>2.52</v>
+        <v>2.3100000000000005</v>
       </c>
       <c r="K324">
         <v>100</v>
@@ -35867,13 +35867,13 @@
         <v>308</v>
       </c>
       <c r="D325" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="E325">
         <v>2022</v>
       </c>
       <c r="F325">
-        <v>6.3558189950902247E-2</v>
+        <v>0.20320063648536632</v>
       </c>
       <c r="G325">
         <v>1</v>
@@ -35920,25 +35920,25 @@
         <v>308</v>
       </c>
       <c r="D326" t="s">
-        <v>239</v>
+        <v>321</v>
       </c>
       <c r="E326">
         <v>2022</v>
       </c>
       <c r="F326">
-        <v>0.22871669814448767</v>
+        <v>0.54140443556717466</v>
       </c>
       <c r="G326">
         <v>1</v>
       </c>
       <c r="H326">
-        <v>3162.5000000000005</v>
+        <v>2750</v>
       </c>
       <c r="I326">
-        <v>60.500000000000014</v>
+        <v>55.000000000000007</v>
       </c>
       <c r="J326">
-        <v>2.3100000000000005</v>
+        <v>2.1</v>
       </c>
       <c r="K326">
         <v>100</v>
@@ -35973,25 +35973,25 @@
         <v>308</v>
       </c>
       <c r="D327" t="s">
-        <v>320</v>
+        <v>54</v>
       </c>
       <c r="E327">
         <v>2022</v>
       </c>
       <c r="F327">
-        <v>4.1753555442198553E-2</v>
+        <v>0.23196419690110309</v>
       </c>
       <c r="G327">
         <v>1</v>
       </c>
       <c r="H327">
-        <v>3712.5000000000005</v>
+        <v>3162.5000000000005</v>
       </c>
       <c r="I327">
-        <v>71.5</v>
+        <v>60.500000000000014</v>
       </c>
       <c r="J327">
-        <v>2.52</v>
+        <v>2.3100000000000005</v>
       </c>
       <c r="K327">
         <v>100</v>
@@ -36026,13 +36026,13 @@
         <v>308</v>
       </c>
       <c r="D328" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="E328">
         <v>2022</v>
       </c>
       <c r="F328">
-        <v>0.10670353057450742</v>
+        <v>0.15541601192373908</v>
       </c>
       <c r="G328">
         <v>1</v>
@@ -36079,13 +36079,13 @@
         <v>308</v>
       </c>
       <c r="D329" t="s">
-        <v>60</v>
+        <v>323</v>
       </c>
       <c r="E329">
         <v>2022</v>
       </c>
       <c r="F329">
-        <v>0.50939337639482241</v>
+        <v>0.56367299846968055</v>
       </c>
       <c r="G329">
         <v>1</v>
@@ -36132,25 +36132,25 @@
         <v>308</v>
       </c>
       <c r="D330" t="s">
-        <v>322</v>
+        <v>204</v>
       </c>
       <c r="E330">
         <v>2022</v>
       </c>
       <c r="F330">
-        <v>4.4073197411209589E-2</v>
+        <v>7.8403898552572848E-2</v>
       </c>
       <c r="G330">
         <v>1</v>
       </c>
       <c r="H330">
-        <v>3712.5000000000005</v>
+        <v>3162.5000000000005</v>
       </c>
       <c r="I330">
-        <v>71.5</v>
+        <v>60.500000000000014</v>
       </c>
       <c r="J330">
-        <v>2.52</v>
+        <v>2.3100000000000005</v>
       </c>
       <c r="K330">
         <v>100</v>
@@ -36185,13 +36185,13 @@
         <v>308</v>
       </c>
       <c r="D331" t="s">
-        <v>323</v>
+        <v>64</v>
       </c>
       <c r="E331">
         <v>2022</v>
       </c>
       <c r="F331">
-        <v>0.57944656385895543</v>
+        <v>0.50939337639482241</v>
       </c>
       <c r="G331">
         <v>1</v>
@@ -36244,19 +36244,19 @@
         <v>2022</v>
       </c>
       <c r="F332">
-        <v>1.0883760118599757</v>
+        <v>0.10670353057450742</v>
       </c>
       <c r="G332">
         <v>1</v>
       </c>
       <c r="H332">
-        <v>2750</v>
+        <v>3162.5000000000005</v>
       </c>
       <c r="I332">
-        <v>55.000000000000007</v>
+        <v>60.500000000000014</v>
       </c>
       <c r="J332">
-        <v>2.1</v>
+        <v>2.3100000000000005</v>
       </c>
       <c r="K332">
         <v>100</v>
@@ -36297,19 +36297,19 @@
         <v>2022</v>
       </c>
       <c r="F333">
-        <v>0.54140443556717466</v>
+        <v>4.3145340623605172E-2</v>
       </c>
       <c r="G333">
         <v>1</v>
       </c>
       <c r="H333">
-        <v>2750</v>
+        <v>3712.5000000000005</v>
       </c>
       <c r="I333">
-        <v>55.000000000000007</v>
+        <v>71.5</v>
       </c>
       <c r="J333">
-        <v>2.1</v>
+        <v>2.52</v>
       </c>
       <c r="K333">
         <v>100</v>
@@ -36344,13 +36344,13 @@
         <v>308</v>
       </c>
       <c r="D334" t="s">
-        <v>70</v>
+        <v>326</v>
       </c>
       <c r="E334">
         <v>2022</v>
       </c>
       <c r="F334">
-        <v>0.23196419690110309</v>
+        <v>5.8918906012880183E-2</v>
       </c>
       <c r="G334">
         <v>1</v>
@@ -36359,7 +36359,7 @@
         <v>3162.5000000000005</v>
       </c>
       <c r="I334">
-        <v>60.500000000000014</v>
+        <v>60.500000000000021</v>
       </c>
       <c r="J334">
         <v>2.3100000000000005</v>
@@ -36397,13 +36397,13 @@
         <v>308</v>
       </c>
       <c r="D335" t="s">
-        <v>326</v>
+        <v>21</v>
       </c>
       <c r="E335">
         <v>2022</v>
       </c>
       <c r="F335">
-        <v>6.0310691194286808E-2</v>
+        <v>8.7682466428616976E-2</v>
       </c>
       <c r="G335">
         <v>1</v>
@@ -36412,7 +36412,7 @@
         <v>3162.5000000000005</v>
       </c>
       <c r="I335">
-        <v>60.500000000000014</v>
+        <v>60.500000000000007</v>
       </c>
       <c r="J335">
         <v>2.3100000000000005</v>
@@ -36456,7 +36456,7 @@
         <v>2022</v>
       </c>
       <c r="F336">
-        <v>0.10067246145507874</v>
+        <v>0.13036387865841995</v>
       </c>
       <c r="G336">
         <v>1</v>
@@ -36503,13 +36503,13 @@
         <v>308</v>
       </c>
       <c r="D337" t="s">
-        <v>204</v>
+        <v>14</v>
       </c>
       <c r="E337">
         <v>2022</v>
       </c>
       <c r="F337">
-        <v>7.8403898552572848E-2</v>
+        <v>0.11134281451252948</v>
       </c>
       <c r="G337">
         <v>1</v>
@@ -36556,25 +36556,25 @@
         <v>308</v>
       </c>
       <c r="D338" t="s">
-        <v>328</v>
+        <v>99</v>
       </c>
       <c r="E338">
         <v>2022</v>
       </c>
       <c r="F338">
-        <v>0.35629700644009438</v>
+        <v>0.29181095970158766</v>
       </c>
       <c r="G338">
         <v>1</v>
       </c>
       <c r="H338">
-        <v>2750</v>
+        <v>3162.5000000000005</v>
       </c>
       <c r="I338">
-        <v>55</v>
+        <v>60.500000000000014</v>
       </c>
       <c r="J338">
-        <v>2.1</v>
+        <v>2.3100000000000005</v>
       </c>
       <c r="K338">
         <v>100</v>
@@ -36609,13 +36609,13 @@
         <v>308</v>
       </c>
       <c r="D339" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="E339">
         <v>2022</v>
       </c>
       <c r="F339">
-        <v>0.19299421182171778</v>
+        <v>0.1577356538927501</v>
       </c>
       <c r="G339">
         <v>1</v>
@@ -36662,25 +36662,25 @@
         <v>308</v>
       </c>
       <c r="D340" t="s">
-        <v>151</v>
+        <v>329</v>
       </c>
       <c r="E340">
         <v>2022</v>
       </c>
       <c r="F340">
-        <v>4.5464982592616207E-2</v>
+        <v>6.0310691194286808E-2</v>
       </c>
       <c r="G340">
         <v>1</v>
       </c>
       <c r="H340">
-        <v>3712.5000000000005</v>
+        <v>3162.5000000000005</v>
       </c>
       <c r="I340">
-        <v>71.5</v>
+        <v>60.500000000000014</v>
       </c>
       <c r="J340">
-        <v>2.52</v>
+        <v>2.3100000000000005</v>
       </c>
       <c r="K340">
         <v>100</v>
@@ -36768,7 +36768,7 @@
         <v>308</v>
       </c>
       <c r="D342" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="E342">
         <v>1959</v>
@@ -36874,7 +36874,7 @@
         <v>308</v>
       </c>
       <c r="D344" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="E344">
         <v>1973</v>
@@ -36980,7 +36980,7 @@
         <v>308</v>
       </c>
       <c r="D346" t="s">
-        <v>324</v>
+        <v>316</v>
       </c>
       <c r="E346">
         <v>1963</v>
@@ -37033,7 +37033,7 @@
         <v>308</v>
       </c>
       <c r="D347" t="s">
-        <v>329</v>
+        <v>315</v>
       </c>
       <c r="E347">
         <v>2015</v>
@@ -37086,7 +37086,7 @@
         <v>308</v>
       </c>
       <c r="D348" t="s">
-        <v>327</v>
+        <v>318</v>
       </c>
       <c r="E348">
         <v>1931</v>
@@ -37139,7 +37139,7 @@
         <v>308</v>
       </c>
       <c r="D349" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="E349">
         <v>1949</v>
@@ -37192,7 +37192,7 @@
         <v>308</v>
       </c>
       <c r="D350" t="s">
-        <v>328</v>
+        <v>313</v>
       </c>
       <c r="E350">
         <v>1951</v>
@@ -37298,7 +37298,7 @@
         <v>308</v>
       </c>
       <c r="D352" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="E352">
         <v>1958</v>
@@ -37351,7 +37351,7 @@
         <v>308</v>
       </c>
       <c r="D353" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="E353">
         <v>1967</v>
@@ -37404,7 +37404,7 @@
         <v>308</v>
       </c>
       <c r="D354" t="s">
-        <v>309</v>
+        <v>320</v>
       </c>
       <c r="E354">
         <v>1968</v>
@@ -37457,7 +37457,7 @@
         <v>308</v>
       </c>
       <c r="D355" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="E355">
         <v>1929</v>
@@ -37510,7 +37510,7 @@
         <v>308</v>
       </c>
       <c r="D356" t="s">
-        <v>309</v>
+        <v>320</v>
       </c>
       <c r="E356">
         <v>1949</v>
@@ -37616,7 +37616,7 @@
         <v>308</v>
       </c>
       <c r="D358" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="E358">
         <v>1952</v>
@@ -37669,7 +37669,7 @@
         <v>308</v>
       </c>
       <c r="D359" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="E359">
         <v>1913</v>
@@ -37722,7 +37722,7 @@
         <v>308</v>
       </c>
       <c r="D360" t="s">
-        <v>328</v>
+        <v>313</v>
       </c>
       <c r="E360">
         <v>1924</v>
@@ -37828,7 +37828,7 @@
         <v>308</v>
       </c>
       <c r="D362" t="s">
-        <v>328</v>
+        <v>313</v>
       </c>
       <c r="E362">
         <v>1971</v>
@@ -37934,7 +37934,7 @@
         <v>308</v>
       </c>
       <c r="D364" t="s">
-        <v>318</v>
+        <v>325</v>
       </c>
       <c r="E364">
         <v>1927</v>
@@ -37987,7 +37987,7 @@
         <v>308</v>
       </c>
       <c r="D365" t="s">
-        <v>324</v>
+        <v>316</v>
       </c>
       <c r="E365">
         <v>1928</v>
@@ -38093,7 +38093,7 @@
         <v>308</v>
       </c>
       <c r="D367" t="s">
-        <v>324</v>
+        <v>316</v>
       </c>
       <c r="E367">
         <v>1938</v>
@@ -38146,7 +38146,7 @@
         <v>308</v>
       </c>
       <c r="D368" t="s">
-        <v>322</v>
+        <v>309</v>
       </c>
       <c r="E368">
         <v>1920</v>
@@ -38199,7 +38199,7 @@
         <v>308</v>
       </c>
       <c r="D369" t="s">
-        <v>324</v>
+        <v>316</v>
       </c>
       <c r="E369">
         <v>1947</v>
@@ -38252,7 +38252,7 @@
         <v>308</v>
       </c>
       <c r="D370" t="s">
-        <v>312</v>
+        <v>328</v>
       </c>
       <c r="E370">
         <v>1950</v>
@@ -38305,7 +38305,7 @@
         <v>308</v>
       </c>
       <c r="D371" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="E371">
         <v>1954</v>
@@ -38411,7 +38411,7 @@
         <v>308</v>
       </c>
       <c r="D373" t="s">
-        <v>328</v>
+        <v>313</v>
       </c>
       <c r="E373">
         <v>1971</v>
@@ -38464,7 +38464,7 @@
         <v>308</v>
       </c>
       <c r="D374" t="s">
-        <v>327</v>
+        <v>318</v>
       </c>
       <c r="E374">
         <v>1959</v>
@@ -38570,7 +38570,7 @@
         <v>308</v>
       </c>
       <c r="D376" t="s">
-        <v>324</v>
+        <v>316</v>
       </c>
       <c r="E376">
         <v>1955</v>
@@ -38623,7 +38623,7 @@
         <v>308</v>
       </c>
       <c r="D377" t="s">
-        <v>324</v>
+        <v>316</v>
       </c>
       <c r="E377">
         <v>1959</v>
@@ -38676,7 +38676,7 @@
         <v>308</v>
       </c>
       <c r="D378" t="s">
-        <v>324</v>
+        <v>316</v>
       </c>
       <c r="E378">
         <v>1954</v>
@@ -38888,7 +38888,7 @@
         <v>308</v>
       </c>
       <c r="D382" t="s">
-        <v>87</v>
+        <v>50</v>
       </c>
       <c r="E382">
         <v>2022</v>
@@ -39100,7 +39100,7 @@
         <v>308</v>
       </c>
       <c r="D386" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="E386">
         <v>2022</v>
@@ -39206,7 +39206,7 @@
         <v>383</v>
       </c>
       <c r="D388" t="s">
-        <v>70</v>
+        <v>54</v>
       </c>
       <c r="E388">
         <v>1989</v>
@@ -39259,7 +39259,7 @@
         <v>383</v>
       </c>
       <c r="D389" t="s">
-        <v>315</v>
+        <v>327</v>
       </c>
       <c r="E389">
         <v>1975</v>
@@ -39312,7 +39312,7 @@
         <v>383</v>
       </c>
       <c r="D390" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="E390">
         <v>1966</v>
@@ -39365,7 +39365,7 @@
         <v>383</v>
       </c>
       <c r="D391" t="s">
-        <v>324</v>
+        <v>316</v>
       </c>
       <c r="E391">
         <v>2015</v>
@@ -39418,7 +39418,7 @@
         <v>383</v>
       </c>
       <c r="D392" t="s">
-        <v>323</v>
+        <v>312</v>
       </c>
       <c r="E392">
         <v>2015</v>
@@ -39471,7 +39471,7 @@
         <v>383</v>
       </c>
       <c r="D393" t="s">
-        <v>323</v>
+        <v>312</v>
       </c>
       <c r="E393">
         <v>1982</v>
@@ -39524,7 +39524,7 @@
         <v>383</v>
       </c>
       <c r="D394" t="s">
-        <v>328</v>
+        <v>313</v>
       </c>
       <c r="E394">
         <v>2015</v>
@@ -39630,7 +39630,7 @@
         <v>383</v>
       </c>
       <c r="D396" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="E396">
         <v>1961</v>
@@ -39683,7 +39683,7 @@
         <v>383</v>
       </c>
       <c r="D397" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="E397">
         <v>2005</v>
@@ -39736,7 +39736,7 @@
         <v>383</v>
       </c>
       <c r="D398" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="E398">
         <v>1991</v>
@@ -39895,7 +39895,7 @@
         <v>383</v>
       </c>
       <c r="D401" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="E401">
         <v>1971</v>
@@ -39948,7 +39948,7 @@
         <v>383</v>
       </c>
       <c r="D402" t="s">
-        <v>312</v>
+        <v>328</v>
       </c>
       <c r="E402">
         <v>1973</v>
@@ -40107,7 +40107,7 @@
         <v>383</v>
       </c>
       <c r="D405" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="E405">
         <v>1978</v>
@@ -40160,7 +40160,7 @@
         <v>383</v>
       </c>
       <c r="D406" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="E406">
         <v>1923</v>
@@ -40213,7 +40213,7 @@
         <v>308</v>
       </c>
       <c r="D407" t="s">
-        <v>316</v>
+        <v>326</v>
       </c>
       <c r="E407">
         <v>1959</v>
@@ -40319,7 +40319,7 @@
         <v>308</v>
       </c>
       <c r="D409" t="s">
-        <v>324</v>
+        <v>316</v>
       </c>
       <c r="E409">
         <v>1949</v>
@@ -40372,7 +40372,7 @@
         <v>308</v>
       </c>
       <c r="D410" t="s">
-        <v>313</v>
+        <v>322</v>
       </c>
       <c r="E410">
         <v>1953</v>
@@ -40478,7 +40478,7 @@
         <v>308</v>
       </c>
       <c r="D412" t="s">
-        <v>324</v>
+        <v>316</v>
       </c>
       <c r="E412">
         <v>1960</v>
@@ -40531,7 +40531,7 @@
         <v>308</v>
       </c>
       <c r="D413" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="E413">
         <v>1962</v>
@@ -40584,7 +40584,7 @@
         <v>308</v>
       </c>
       <c r="D414" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="E414">
         <v>2015</v>
@@ -40637,7 +40637,7 @@
         <v>308</v>
       </c>
       <c r="D415" t="s">
-        <v>309</v>
+        <v>320</v>
       </c>
       <c r="E415">
         <v>1927</v>
@@ -40690,7 +40690,7 @@
         <v>308</v>
       </c>
       <c r="D416" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="E416">
         <v>1954</v>
@@ -40796,7 +40796,7 @@
         <v>308</v>
       </c>
       <c r="D418" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="E418">
         <v>1956</v>
@@ -40849,7 +40849,7 @@
         <v>308</v>
       </c>
       <c r="D419" t="s">
-        <v>328</v>
+        <v>313</v>
       </c>
       <c r="E419">
         <v>1956</v>
@@ -40955,7 +40955,7 @@
         <v>308</v>
       </c>
       <c r="D421" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="E421">
         <v>1960</v>
@@ -41061,7 +41061,7 @@
         <v>308</v>
       </c>
       <c r="D423" t="s">
-        <v>329</v>
+        <v>315</v>
       </c>
       <c r="E423">
         <v>2015</v>
@@ -41167,7 +41167,7 @@
         <v>308</v>
       </c>
       <c r="D425" t="s">
-        <v>309</v>
+        <v>320</v>
       </c>
       <c r="E425">
         <v>2015</v>
@@ -41220,7 +41220,7 @@
         <v>308</v>
       </c>
       <c r="D426" t="s">
-        <v>323</v>
+        <v>312</v>
       </c>
       <c r="E426">
         <v>2015</v>
@@ -41326,7 +41326,7 @@
         <v>308</v>
       </c>
       <c r="D428" t="s">
-        <v>87</v>
+        <v>50</v>
       </c>
       <c r="E428">
         <v>1955</v>
@@ -41379,7 +41379,7 @@
         <v>308</v>
       </c>
       <c r="D429" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="E429">
         <v>2015</v>
@@ -41485,7 +41485,7 @@
         <v>308</v>
       </c>
       <c r="D431" t="s">
-        <v>318</v>
+        <v>325</v>
       </c>
       <c r="E431">
         <v>1932</v>
@@ -41644,7 +41644,7 @@
         <v>308</v>
       </c>
       <c r="D434" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="E434">
         <v>1924</v>
@@ -41750,7 +41750,7 @@
         <v>308</v>
       </c>
       <c r="D436" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="E436">
         <v>2002</v>
@@ -41856,7 +41856,7 @@
         <v>308</v>
       </c>
       <c r="D438" t="s">
-        <v>324</v>
+        <v>316</v>
       </c>
       <c r="E438">
         <v>1948</v>
@@ -41909,7 +41909,7 @@
         <v>308</v>
       </c>
       <c r="D439" t="s">
-        <v>329</v>
+        <v>315</v>
       </c>
       <c r="E439">
         <v>2015</v>
@@ -41962,7 +41962,7 @@
         <v>308</v>
       </c>
       <c r="D440" t="s">
-        <v>322</v>
+        <v>309</v>
       </c>
       <c r="E440">
         <v>1914</v>
@@ -42068,7 +42068,7 @@
         <v>308</v>
       </c>
       <c r="D442" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="E442">
         <v>1958</v>
@@ -42121,7 +42121,7 @@
         <v>439</v>
       </c>
       <c r="D443" t="s">
-        <v>54</v>
+        <v>83</v>
       </c>
       <c r="E443">
         <v>1992</v>
@@ -42280,7 +42280,7 @@
         <v>439</v>
       </c>
       <c r="D446" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E446">
         <v>1992</v>
@@ -42333,7 +42333,7 @@
         <v>439</v>
       </c>
       <c r="D447" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E447">
         <v>2005</v>
@@ -42598,7 +42598,7 @@
         <v>439</v>
       </c>
       <c r="D452" t="s">
-        <v>54</v>
+        <v>83</v>
       </c>
       <c r="E452">
         <v>1985</v>
@@ -42922,7 +42922,7 @@
         <v>2022</v>
       </c>
       <c r="F458">
-        <v>6.6457416582336482</v>
+        <v>6.6039408899415779</v>
       </c>
       <c r="G458">
         <v>1</v>
@@ -43034,7 +43034,7 @@
         <v>2022</v>
       </c>
       <c r="F460">
-        <v>6.6039408899415779</v>
+        <v>6.6457416582336482</v>
       </c>
       <c r="G460">
         <v>1</v>
@@ -44876,7 +44876,7 @@
         <v>455</v>
       </c>
       <c r="D493" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="E493">
         <v>2015</v>
@@ -51156,7 +51156,7 @@
         <v>2022</v>
       </c>
       <c r="F618">
-        <v>0.69928302455480262</v>
+        <v>0.67351932785461166</v>
       </c>
       <c r="G618">
         <v>0.33123000000000002</v>
@@ -51202,7 +51202,7 @@
         <v>2022</v>
       </c>
       <c r="F620">
-        <v>0.67351932785461166</v>
+        <v>0.69928302455480262</v>
       </c>
       <c r="G620">
         <v>0.33123000000000002</v>

--- a/VerveStacks_ITA_grids/vt_vervestacks_ITA_v1.xlsx
+++ b/VerveStacks_ITA_grids/vt_vervestacks_ITA_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A123C998-59B0-4A9D-80A0-37FA9C01564E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{61CC0EA6-F78B-49D9-9FAF-B2EA0424AF33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{060A1D40-C8CB-4472-993D-2962FE451115}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{B802FF8B-77F1-4651-A8F1-26C528872C0D}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="2" r:id="rId1"/>
@@ -81,30 +81,30 @@
     <t>bioenergy</t>
   </si>
   <si>
+    <t>e_w34157795-380</t>
+  </si>
+  <si>
+    <t>e_w144005863-380</t>
+  </si>
+  <si>
+    <t>e_w98902899-380</t>
+  </si>
+  <si>
+    <t>e_w81938081-380</t>
+  </si>
+  <si>
+    <t>e_w84696559-380</t>
+  </si>
+  <si>
+    <t>e_w58440884-380</t>
+  </si>
+  <si>
+    <t>e_w109756016-380</t>
+  </si>
+  <si>
     <t>e_w108020416-380</t>
   </si>
   <si>
-    <t>e_w98902899-380</t>
-  </si>
-  <si>
-    <t>e_w84696559-380</t>
-  </si>
-  <si>
-    <t>e_w81938081-380</t>
-  </si>
-  <si>
-    <t>e_w144005863-380</t>
-  </si>
-  <si>
-    <t>e_w34157795-380</t>
-  </si>
-  <si>
-    <t>e_w109756016-380</t>
-  </si>
-  <si>
-    <t>e_w58440884-380</t>
-  </si>
-  <si>
     <t>ep_bioenergy_G100000200236</t>
   </si>
   <si>
@@ -141,12 +141,12 @@
     <t>coal</t>
   </si>
   <si>
+    <t>e_w409439916-380</t>
+  </si>
+  <si>
     <t>e_w418902800-380</t>
   </si>
   <si>
-    <t>e_w409439916-380</t>
-  </si>
-  <si>
     <t>e_w303915533-380</t>
   </si>
   <si>
@@ -189,120 +189,120 @@
     <t>gas</t>
   </si>
   <si>
+    <t>e_w133601335-380</t>
+  </si>
+  <si>
+    <t>e_w105581403-380</t>
+  </si>
+  <si>
+    <t>e_w255011550-380</t>
+  </si>
+  <si>
+    <t>e_w414663585-380</t>
+  </si>
+  <si>
+    <t>e_w107438024-380</t>
+  </si>
+  <si>
+    <t>e_w411026199-380</t>
+  </si>
+  <si>
+    <t>e_w158739183-380</t>
+  </si>
+  <si>
+    <t>e_w103974940-380</t>
+  </si>
+  <si>
+    <t>e_w60725875-380</t>
+  </si>
+  <si>
+    <t>e_w145665799-380</t>
+  </si>
+  <si>
+    <t>e_w339104227-380</t>
+  </si>
+  <si>
+    <t>e_w82078641-380</t>
+  </si>
+  <si>
+    <t>e_w61157826-380</t>
+  </si>
+  <si>
+    <t>e_w1137611914-380</t>
+  </si>
+  <si>
+    <t>e_w416989699-380</t>
+  </si>
+  <si>
+    <t>e_w432729521-380</t>
+  </si>
+  <si>
+    <t>e_w172302572-380</t>
+  </si>
+  <si>
+    <t>e_w59462715-380</t>
+  </si>
+  <si>
+    <t>e_w421827453-380</t>
+  </si>
+  <si>
     <t>e_w149997403-380</t>
   </si>
   <si>
-    <t>e_w59462715-380</t>
+    <t>e_w100407576-380</t>
+  </si>
+  <si>
+    <t>e_w109993642-380</t>
+  </si>
+  <si>
+    <t>e_w103653592-380</t>
+  </si>
+  <si>
+    <t>e_w99826025-380</t>
+  </si>
+  <si>
+    <t>e_w82084019-380</t>
+  </si>
+  <si>
+    <t>e_w98900549-380</t>
+  </si>
+  <si>
+    <t>e_w162828577-380</t>
+  </si>
+  <si>
+    <t>e_w132450233-380</t>
+  </si>
+  <si>
+    <t>e_w110330925-380</t>
+  </si>
+  <si>
+    <t>e_w116797658-380</t>
+  </si>
+  <si>
+    <t>e_w419423704-380</t>
+  </si>
+  <si>
+    <t>e_w98421779-380</t>
+  </si>
+  <si>
+    <t>e_w162960205-380</t>
+  </si>
+  <si>
+    <t>e_w338753171-380</t>
+  </si>
+  <si>
+    <t>e_w199675964-380</t>
   </si>
   <si>
     <t>e_w103381531-380</t>
   </si>
   <si>
-    <t>e_w133601335-380</t>
+    <t>e_w105757794-380</t>
   </si>
   <si>
     <t>e_w181125039-380</t>
   </si>
   <si>
-    <t>e_w116797658-380</t>
-  </si>
-  <si>
-    <t>e_w339104227-380</t>
-  </si>
-  <si>
-    <t>e_w60725875-380</t>
-  </si>
-  <si>
-    <t>e_w145665799-380</t>
-  </si>
-  <si>
-    <t>e_w338753171-380</t>
-  </si>
-  <si>
-    <t>e_w162960205-380</t>
-  </si>
-  <si>
-    <t>e_w432729521-380</t>
-  </si>
-  <si>
-    <t>e_w172302572-380</t>
-  </si>
-  <si>
-    <t>e_w98900549-380</t>
-  </si>
-  <si>
-    <t>e_w419423704-380</t>
-  </si>
-  <si>
-    <t>e_w162828577-380</t>
-  </si>
-  <si>
-    <t>e_w132450233-380</t>
-  </si>
-  <si>
-    <t>e_w110330925-380</t>
-  </si>
-  <si>
-    <t>e_w105757794-380</t>
-  </si>
-  <si>
-    <t>e_w158739183-380</t>
-  </si>
-  <si>
-    <t>e_w103974940-380</t>
-  </si>
-  <si>
-    <t>e_w199675964-380</t>
-  </si>
-  <si>
-    <t>e_w82078641-380</t>
-  </si>
-  <si>
-    <t>e_w98421779-380</t>
-  </si>
-  <si>
-    <t>e_w61157826-380</t>
-  </si>
-  <si>
-    <t>e_w1137611914-380</t>
-  </si>
-  <si>
-    <t>e_w99826025-380</t>
-  </si>
-  <si>
-    <t>e_w416989699-380</t>
-  </si>
-  <si>
-    <t>e_w411026199-380</t>
-  </si>
-  <si>
-    <t>e_w107438024-380</t>
-  </si>
-  <si>
-    <t>e_w103653592-380</t>
-  </si>
-  <si>
-    <t>e_w109993642-380</t>
-  </si>
-  <si>
-    <t>e_w105581403-380</t>
-  </si>
-  <si>
-    <t>e_w255011550-380</t>
-  </si>
-  <si>
-    <t>e_w414663585-380</t>
-  </si>
-  <si>
-    <t>e_w100407576-380</t>
-  </si>
-  <si>
-    <t>e_w82084019-380</t>
-  </si>
-  <si>
-    <t>e_w421827453-380</t>
-  </si>
-  <si>
     <t>ep_gas_combined_cycle_G100000400339</t>
   </si>
   <si>
@@ -966,69 +966,69 @@
     <t>hydro</t>
   </si>
   <si>
+    <t>e_w104359058-380</t>
+  </si>
+  <si>
+    <t>e_w64200868-380</t>
+  </si>
+  <si>
+    <t>e_IT71-400</t>
+  </si>
+  <si>
+    <t>e_IT71-380</t>
+  </si>
+  <si>
+    <t>e_IT36-380</t>
+  </si>
+  <si>
+    <t>e_w1100665914-380</t>
+  </si>
+  <si>
+    <t>e_IT93-380</t>
+  </si>
+  <si>
+    <t>e_w61626687-380</t>
+  </si>
+  <si>
+    <t>e_IT31-380</t>
+  </si>
+  <si>
+    <t>e_w72466334-380</t>
+  </si>
+  <si>
+    <t>e_w82083756-380</t>
+  </si>
+  <si>
+    <t>e_IT53-380</t>
+  </si>
+  <si>
+    <t>e_IT7-380</t>
+  </si>
+  <si>
+    <t>e_w75602396-380</t>
+  </si>
+  <si>
+    <t>e_w491424937-380</t>
+  </si>
+  <si>
+    <t>e_IT72-400</t>
+  </si>
+  <si>
+    <t>e_w116517585-380</t>
+  </si>
+  <si>
     <t>e_w114931087-380</t>
   </si>
   <si>
-    <t>e_w64200868-380</t>
-  </si>
-  <si>
-    <t>e_IT36-380</t>
-  </si>
-  <si>
-    <t>e_IT53-380</t>
-  </si>
-  <si>
-    <t>e_IT71-400</t>
-  </si>
-  <si>
-    <t>e_w72466334-380</t>
-  </si>
-  <si>
-    <t>e_IT93-380</t>
-  </si>
-  <si>
-    <t>e_w82083756-380</t>
-  </si>
-  <si>
-    <t>e_w116517585-380</t>
+    <t>e_IT72-380</t>
   </si>
   <si>
     <t>e_IT21-380</t>
   </si>
   <si>
-    <t>e_IT7-380</t>
-  </si>
-  <si>
-    <t>e_w1100665914-380</t>
-  </si>
-  <si>
-    <t>e_w75602396-380</t>
-  </si>
-  <si>
-    <t>e_w491424937-380</t>
-  </si>
-  <si>
-    <t>e_IT72-400</t>
-  </si>
-  <si>
     <t>e_IT10-380</t>
   </si>
   <si>
-    <t>e_IT31-380</t>
-  </si>
-  <si>
-    <t>e_w104359058-380</t>
-  </si>
-  <si>
-    <t>e_IT71-380</t>
-  </si>
-  <si>
-    <t>e_IT72-380</t>
-  </si>
-  <si>
-    <t>e_w61626687-380</t>
-  </si>
-  <si>
     <t>ep_hydro_dam_G100000602220</t>
   </si>
   <si>
@@ -1680,21 +1680,24 @@
     <t>ele</t>
   </si>
   <si>
+    <t>Aggregated Plant - EMBER Gap - way/81938081-380_Missing Bioenergy Capacity</t>
+  </si>
+  <si>
+    <t>GW</t>
+  </si>
+  <si>
+    <t>TWh</t>
+  </si>
+  <si>
+    <t>daynite</t>
+  </si>
+  <si>
+    <t>yes</t>
+  </si>
+  <si>
     <t>Aggregated Plant - EMBER Gap - way/98902899-380_Missing Bioenergy Capacity</t>
   </si>
   <si>
-    <t>GW</t>
-  </si>
-  <si>
-    <t>TWh</t>
-  </si>
-  <si>
-    <t>daynite</t>
-  </si>
-  <si>
-    <t>yes</t>
-  </si>
-  <si>
     <t>Aggregated Plant - EMBER Gap - way/144005863-380_Missing Bioenergy Capacity</t>
   </si>
   <si>
@@ -1707,15 +1710,12 @@
     <t>Aggregated Plant - EMBER Gap - way/84696559-380_Missing Bioenergy Capacity</t>
   </si>
   <si>
-    <t>Aggregated Plant - EMBER Gap - way/81938081-380_Missing Bioenergy Capacity</t>
+    <t>Aggregated Plant - EMBER Gap - way/58440884-380_Missing Bioenergy Capacity</t>
   </si>
   <si>
     <t>Aggregated Plant - EMBER Gap - way/34157795-380_Missing Bioenergy Capacity</t>
   </si>
   <si>
-    <t>Aggregated Plant - EMBER Gap - way/58440884-380_Missing Bioenergy Capacity</t>
-  </si>
-  <si>
     <t>Acerra power station_1</t>
   </si>
   <si>
@@ -1737,18 +1737,18 @@
     <t>Aggregated Plant</t>
   </si>
   <si>
+    <t>Aggregated Plant - EMBER Gap - way/82767145-380_Missing Coal Capacity</t>
+  </si>
+  <si>
     <t>Aggregated Plant - EMBER Gap - way/303915533-380_Missing Coal Capacity</t>
   </si>
   <si>
+    <t>Aggregated Plant - EMBER Gap - way/409439916-380_Missing Coal Capacity</t>
+  </si>
+  <si>
     <t>Aggregated Plant - EMBER Gap - way/418902800-380_Missing Coal Capacity</t>
   </si>
   <si>
-    <t>Aggregated Plant - EMBER Gap - way/82767145-380_Missing Coal Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/409439916-380_Missing Coal Capacity</t>
-  </si>
-  <si>
     <t>Fiume Santo power station_Unit 3</t>
   </si>
   <si>
@@ -1779,126 +1779,126 @@
     <t>Torrevaldaliga Nord power station_Unit 3</t>
   </si>
   <si>
+    <t>Aggregated Plant - EMBER Gap - way/414663585-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/419423704-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/61157826-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/98421779-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/110330925-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/82084019-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/109756016-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/411026199-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/105581403-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/107438024-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/116797658-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/339104227-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/103381531-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/1137611914-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/145665799-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/158739183-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/60725875-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/421827453-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/99826025-380_Missing Gas Capacity</t>
+  </si>
+  <si>
     <t>Aggregated Plant - EMBER Gap - way/181125039-380_Missing Gas Capacity</t>
   </si>
   <si>
+    <t>Aggregated Plant - EMBER Gap - way/199675964-380_Missing Gas Capacity</t>
+  </si>
+  <si>
     <t>Aggregated Plant - EMBER Gap - way/432729521-380_Missing Gas Capacity</t>
   </si>
   <si>
-    <t>Aggregated Plant - EMBER Gap - way/99826025-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/421827453-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/199675964-380_Missing Gas Capacity</t>
+    <t>Aggregated Plant - EMBER Gap - way/103653592-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/109993642-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/416989699-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/100407576-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/82767145-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/59462715-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/172302572-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/105757794-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/255011550-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/338753171-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/162828577-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/98900549-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/82078641-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/103974940-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/133601335-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/162960205-380_Missing Gas Capacity</t>
   </si>
   <si>
     <t>Aggregated Plant - EMBER Gap - way/149997403-380_Missing Gas Capacity</t>
   </si>
   <si>
-    <t>Aggregated Plant - EMBER Gap - way/133601335-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/162960205-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/105757794-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/172302572-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/255011550-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/59462715-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/339104227-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/107438024-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/116797658-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/60725875-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/109993642-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/82767145-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/103974940-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/416989699-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/103653592-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/82078641-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/100407576-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/61157826-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/414663585-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/419423704-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/103381531-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/105581403-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/82084019-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/411026199-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/110330925-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/109756016-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/98421779-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/145665799-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/158739183-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/1137611914-380_Missing Gas Capacity</t>
-  </si>
-  <si>
     <t>Aggregated Plant - EMBER Gap - way/132450233-380_Missing Gas Capacity</t>
   </si>
   <si>
-    <t>Aggregated Plant - EMBER Gap - way/162828577-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/98900549-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/338753171-380_Missing Gas Capacity</t>
-  </si>
-  <si>
     <t>Altomonte power station_1</t>
   </si>
   <si>
@@ -2211,102 +2211,102 @@
     <t>Valle Secolo geothermal power plant_2</t>
   </si>
   <si>
+    <t>Aggregated Plant - IRENA Gap - IT71-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/108020416-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/59462263-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/1100665914-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - IT72-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/1137611914-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/109588422-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - IT72-400_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/419423704-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/72466334-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/104359058-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/491424937-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/82083756-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - IT36-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/75602396-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
     <t>Aggregated Plant - IRENA Gap - IT71-400_Missing Hydro Capacity</t>
   </si>
   <si>
-    <t>Aggregated Plant - IRENA Gap - IT36-380_Missing Hydro Capacity</t>
+    <t>Aggregated Plant - IRENA Gap - way/339703159-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/61712456-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - IT53-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - IT30-500_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - IT7-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/144005863-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - IT21-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/64200868-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/338753171-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - IT10-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - IT93-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/61626687-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - IT31-380_Missing Hydro Capacity</t>
   </si>
   <si>
     <t>Aggregated Plant - IRENA Gap - way/114931087-380_Missing Hydro Capacity</t>
   </si>
   <si>
-    <t>Aggregated Plant - IRENA Gap - IT31-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/61626687-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/144005863-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - IT21-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/339703159-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - IT30-500_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/61712456-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - IT53-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - IT7-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - IT72-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/1100665914-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/59462263-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/75602396-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - IT10-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/338753171-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - IT72-400_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/1137611914-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/109588422-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - IT71-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/108020416-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/419423704-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/491424937-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/82083756-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/104359058-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/72466334-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/64200868-380_Missing Hydro Capacity</t>
+    <t>Aggregated Plant - IRENA Gap - way/116517585-380_Missing Hydro Capacity</t>
   </si>
   <si>
     <t>Aggregated Plant - IRENA Gap - way/96190189-380_Missing Hydro Capacity</t>
   </si>
   <si>
-    <t>Aggregated Plant - IRENA Gap - way/116517585-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - IT93-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
     <t>Baschi hydroelectric plant_</t>
   </si>
   <si>
@@ -2601,27 +2601,27 @@
     <t>San Filippo del Mela power station_1</t>
   </si>
   <si>
+    <t>Aggregated Plant - IRENA Gap - ITA_42_Missing Solar Capacity</t>
+  </si>
+  <si>
+    <t>annual</t>
+  </si>
+  <si>
     <t>Aggregated Plant - IRENA Gap - ITA_68_Missing Solar Capacity</t>
   </si>
   <si>
-    <t>annual</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - ITA_42_Missing Solar Capacity</t>
-  </si>
-  <si>
     <t>Aggregated Plant - IRENA Gap - ITA_30_Missing Solar Capacity</t>
   </si>
   <si>
+    <t>Aggregated Plant - IRENA Gap - ITA_22_Missing Onshore wind energy Capacity</t>
+  </si>
+  <si>
     <t>Aggregated Plant - IRENA Gap - ITA_73_Missing Onshore wind energy Capacity</t>
   </si>
   <si>
     <t>Aggregated Plant - IRENA Gap - ITA_96_Missing Onshore wind energy Capacity</t>
   </si>
   <si>
-    <t>Aggregated Plant - IRENA Gap - ITA_22_Missing Onshore wind energy Capacity</t>
-  </si>
-  <si>
     <t>AF</t>
   </si>
   <si>
@@ -3213,18 +3213,18 @@
     <t>ccs retrofit of -- Sulcis power station_Unit 3</t>
   </si>
   <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/418902800-380_Missing Coal Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/82767145-380_Missing Coal Capacity</t>
+  </si>
+  <si>
     <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/409439916-380_Missing Coal Capacity</t>
   </si>
   <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/82767145-380_Missing Coal Capacity</t>
-  </si>
-  <si>
     <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/303915533-380_Missing Coal Capacity</t>
   </si>
   <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/418902800-380_Missing Coal Capacity</t>
-  </si>
-  <si>
     <t>ccs retrofit of -- Brindisi Sud power station_Unit 1</t>
   </si>
   <si>
@@ -3513,16 +3513,61 @@
     <t>ccs retrofit of -- Aggregated Plant</t>
   </si>
   <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/145665799-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/82084019-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/110330925-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/338753171-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/414663585-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/116797658-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/61157826-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/109756016-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/411026199-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/82767145-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/172302572-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/99826025-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/416989699-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/162828577-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/105757794-380_Missing Gas Capacity</t>
+  </si>
+  <si>
     <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/103381531-380_Missing Gas Capacity</t>
   </si>
   <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/82767145-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/162828577-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/172302572-380_Missing Gas Capacity</t>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/109993642-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/59462715-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/105581403-380_Missing Gas Capacity</t>
   </si>
   <si>
     <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/181125039-380_Missing Gas Capacity</t>
@@ -3531,106 +3576,61 @@
     <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/255011550-380_Missing Gas Capacity</t>
   </si>
   <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/105581403-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/110330925-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/338753171-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/99826025-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/105757794-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/145665799-380_Missing Gas Capacity</t>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/98421779-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/107438024-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/60725875-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/1137611914-380_Missing Gas Capacity</t>
   </si>
   <si>
     <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/199675964-380_Missing Gas Capacity</t>
   </si>
   <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/103653592-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/82078641-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/103974940-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/339104227-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/158739183-380_Missing Gas Capacity</t>
+  </si>
+  <si>
     <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/133601335-380_Missing Gas Capacity</t>
   </si>
   <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/158739183-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/61157826-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/339104227-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/1137611914-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/107438024-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/411026199-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/109756016-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/59462715-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/109993642-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/98421779-380_Missing Gas Capacity</t>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/100407576-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/132450233-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/432729521-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/162960205-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/149997403-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/421827453-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/419423704-380_Missing Gas Capacity</t>
   </si>
   <si>
     <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/98900549-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/82078641-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/103653592-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/149997403-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/162960205-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/419423704-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/432729521-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/421827453-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/60725875-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/82084019-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/100407576-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/132450233-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/416989699-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/116797658-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/414663585-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/103974940-380_Missing Gas Capacity</t>
   </si>
   <si>
     <t>ccs retrofit of -- Tavazzano power station_CCGT8, timepoint 1</t>
@@ -4034,7 +4034,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{26EE8CF2-63F3-4667-907F-E42BBA703FF3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D0D3EA3A-814F-4FD4-A2FC-ACA8492B52CF}">
   <dimension ref="B9:T278"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -4110,7 +4110,7 @@
         <v>33</v>
       </c>
       <c r="D11" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E11">
         <v>0.12764790000000001</v>
@@ -4166,7 +4166,7 @@
         <v>33</v>
       </c>
       <c r="D12" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E12">
         <v>0.12764790000000001</v>
@@ -4558,7 +4558,7 @@
         <v>33</v>
       </c>
       <c r="D19" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E19">
         <v>0.260522535</v>
@@ -4614,7 +4614,7 @@
         <v>33</v>
       </c>
       <c r="D20" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E20">
         <v>0.260522535</v>
@@ -4670,7 +4670,7 @@
         <v>33</v>
       </c>
       <c r="D21" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E21">
         <v>0.260522535</v>
@@ -4894,7 +4894,7 @@
         <v>49</v>
       </c>
       <c r="D25" t="s">
-        <v>67</v>
+        <v>78</v>
       </c>
       <c r="E25">
         <v>0.41750406250000005</v>
@@ -4950,7 +4950,7 @@
         <v>49</v>
       </c>
       <c r="D26" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="E26">
         <v>0.44431624999999997</v>
@@ -5006,7 +5006,7 @@
         <v>49</v>
       </c>
       <c r="D27" t="s">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="E27">
         <v>0.38303124999999993</v>
@@ -5062,7 +5062,7 @@
         <v>49</v>
       </c>
       <c r="D28" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="E28">
         <v>0.44431624999999997</v>
@@ -5118,7 +5118,7 @@
         <v>49</v>
       </c>
       <c r="D29" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E29">
         <v>0.41750406249999999</v>
@@ -5174,7 +5174,7 @@
         <v>49</v>
       </c>
       <c r="D30" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E30">
         <v>0.41750406249999999</v>
@@ -5230,7 +5230,7 @@
         <v>49</v>
       </c>
       <c r="D31" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E31">
         <v>0.41750406249999999</v>
@@ -5342,7 +5342,7 @@
         <v>49</v>
       </c>
       <c r="D33" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="E33">
         <v>0.41750406249999999</v>
@@ -5510,7 +5510,7 @@
         <v>49</v>
       </c>
       <c r="D36" t="s">
-        <v>82</v>
+        <v>51</v>
       </c>
       <c r="E36">
         <v>0.41750406249999999</v>
@@ -5566,7 +5566,7 @@
         <v>49</v>
       </c>
       <c r="D37" t="s">
-        <v>82</v>
+        <v>51</v>
       </c>
       <c r="E37">
         <v>0.41750406249999999</v>
@@ -5622,7 +5622,7 @@
         <v>49</v>
       </c>
       <c r="D38" t="s">
-        <v>55</v>
+        <v>79</v>
       </c>
       <c r="E38">
         <v>0.41750406249999999</v>
@@ -5678,7 +5678,7 @@
         <v>49</v>
       </c>
       <c r="D39" t="s">
-        <v>55</v>
+        <v>79</v>
       </c>
       <c r="E39">
         <v>0.41750406249999999</v>
@@ -5734,7 +5734,7 @@
         <v>49</v>
       </c>
       <c r="D40" t="s">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="E40">
         <v>0.3983525</v>
@@ -5790,7 +5790,7 @@
         <v>49</v>
       </c>
       <c r="D41" t="s">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="E41">
         <v>0.41750406249999999</v>
@@ -5846,7 +5846,7 @@
         <v>49</v>
       </c>
       <c r="D42" t="s">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="E42">
         <v>0.41750406249999999</v>
@@ -5902,7 +5902,7 @@
         <v>49</v>
       </c>
       <c r="D43" t="s">
-        <v>75</v>
+        <v>63</v>
       </c>
       <c r="E43">
         <v>0.41750406249999999</v>
@@ -5958,7 +5958,7 @@
         <v>49</v>
       </c>
       <c r="D44" t="s">
-        <v>75</v>
+        <v>63</v>
       </c>
       <c r="E44">
         <v>0.41750406249999999</v>
@@ -6014,7 +6014,7 @@
         <v>49</v>
       </c>
       <c r="D45" t="s">
-        <v>79</v>
+        <v>54</v>
       </c>
       <c r="E45">
         <v>0.41750406249999999</v>
@@ -6070,7 +6070,7 @@
         <v>49</v>
       </c>
       <c r="D46" t="s">
-        <v>79</v>
+        <v>54</v>
       </c>
       <c r="E46">
         <v>0.41750406249999999</v>
@@ -6126,7 +6126,7 @@
         <v>49</v>
       </c>
       <c r="D47" t="s">
-        <v>79</v>
+        <v>54</v>
       </c>
       <c r="E47">
         <v>0.41750406249999999</v>
@@ -6182,7 +6182,7 @@
         <v>49</v>
       </c>
       <c r="D48" t="s">
-        <v>79</v>
+        <v>54</v>
       </c>
       <c r="E48">
         <v>0.41750406249999999</v>
@@ -6238,7 +6238,7 @@
         <v>49</v>
       </c>
       <c r="D49" t="s">
-        <v>68</v>
+        <v>86</v>
       </c>
       <c r="E49">
         <v>0.40218281250000004</v>
@@ -6294,7 +6294,7 @@
         <v>49</v>
       </c>
       <c r="D50" t="s">
-        <v>68</v>
+        <v>86</v>
       </c>
       <c r="E50">
         <v>0.40218281250000004</v>
@@ -6350,7 +6350,7 @@
         <v>49</v>
       </c>
       <c r="D51" t="s">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="E51">
         <v>0.41750406249999999</v>
@@ -6406,7 +6406,7 @@
         <v>49</v>
       </c>
       <c r="D52" t="s">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="E52">
         <v>0.45963749999999998</v>
@@ -6462,7 +6462,7 @@
         <v>49</v>
       </c>
       <c r="D53" t="s">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="E53">
         <v>0.41750406249999999</v>
@@ -6574,7 +6574,7 @@
         <v>49</v>
       </c>
       <c r="D55" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="E55">
         <v>0.41750406249999999</v>
@@ -6630,7 +6630,7 @@
         <v>49</v>
       </c>
       <c r="D56" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="E56">
         <v>0.41750406249999999</v>
@@ -6686,7 +6686,7 @@
         <v>49</v>
       </c>
       <c r="D57" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="E57">
         <v>0.41750406249999999</v>
@@ -6742,7 +6742,7 @@
         <v>49</v>
       </c>
       <c r="D58" t="s">
-        <v>77</v>
+        <v>64</v>
       </c>
       <c r="E58">
         <v>0.40218281249999999</v>
@@ -6798,7 +6798,7 @@
         <v>49</v>
       </c>
       <c r="D59" t="s">
-        <v>77</v>
+        <v>64</v>
       </c>
       <c r="E59">
         <v>0.40218281249999999</v>
@@ -6854,7 +6854,7 @@
         <v>49</v>
       </c>
       <c r="D60" t="s">
-        <v>77</v>
+        <v>64</v>
       </c>
       <c r="E60">
         <v>0.38303124999999993</v>
@@ -6910,7 +6910,7 @@
         <v>49</v>
       </c>
       <c r="D61" t="s">
-        <v>77</v>
+        <v>64</v>
       </c>
       <c r="E61">
         <v>0.38303124999999993</v>
@@ -7022,7 +7022,7 @@
         <v>49</v>
       </c>
       <c r="D63" t="s">
-        <v>59</v>
+        <v>83</v>
       </c>
       <c r="E63">
         <v>0.41750406249999999</v>
@@ -7078,7 +7078,7 @@
         <v>49</v>
       </c>
       <c r="D64" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="E64">
         <v>0.41750406249999999</v>
@@ -7134,7 +7134,7 @@
         <v>49</v>
       </c>
       <c r="D65" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="E65">
         <v>0.41750406249999999</v>
@@ -7190,7 +7190,7 @@
         <v>49</v>
       </c>
       <c r="D66" t="s">
-        <v>87</v>
+        <v>68</v>
       </c>
       <c r="E66">
         <v>0.41750406249999999</v>
@@ -7358,7 +7358,7 @@
         <v>49</v>
       </c>
       <c r="D69" t="s">
-        <v>69</v>
+        <v>56</v>
       </c>
       <c r="E69">
         <v>0.41750406249999999</v>
@@ -7414,7 +7414,7 @@
         <v>49</v>
       </c>
       <c r="D70" t="s">
-        <v>69</v>
+        <v>56</v>
       </c>
       <c r="E70">
         <v>0.41750406249999999</v>
@@ -7470,7 +7470,7 @@
         <v>49</v>
       </c>
       <c r="D71" t="s">
-        <v>59</v>
+        <v>83</v>
       </c>
       <c r="E71">
         <v>0.41750406249999999</v>
@@ -7526,7 +7526,7 @@
         <v>49</v>
       </c>
       <c r="D72" t="s">
-        <v>59</v>
+        <v>83</v>
       </c>
       <c r="E72">
         <v>0.41750406249999999</v>
@@ -7582,7 +7582,7 @@
         <v>49</v>
       </c>
       <c r="D73" t="s">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="E73">
         <v>0.41750406249999999</v>
@@ -7638,7 +7638,7 @@
         <v>49</v>
       </c>
       <c r="D74" t="s">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="E74">
         <v>0.41750406249999999</v>
@@ -7694,7 +7694,7 @@
         <v>49</v>
       </c>
       <c r="D75" t="s">
-        <v>84</v>
+        <v>53</v>
       </c>
       <c r="E75">
         <v>0.42899500000000002</v>
@@ -7750,7 +7750,7 @@
         <v>49</v>
       </c>
       <c r="D76" t="s">
-        <v>54</v>
+        <v>87</v>
       </c>
       <c r="E76">
         <v>0.41750406249999999</v>
@@ -7806,7 +7806,7 @@
         <v>49</v>
       </c>
       <c r="D77" t="s">
-        <v>54</v>
+        <v>87</v>
       </c>
       <c r="E77">
         <v>0.41750406249999999</v>
@@ -8086,7 +8086,7 @@
         <v>49</v>
       </c>
       <c r="D82" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
       <c r="E82">
         <v>0.41750406249999999</v>
@@ -8142,7 +8142,7 @@
         <v>49</v>
       </c>
       <c r="D83" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
       <c r="E83">
         <v>0.41750406249999999</v>
@@ -8198,7 +8198,7 @@
         <v>49</v>
       </c>
       <c r="D84" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="E84">
         <v>0.41750406249999999</v>
@@ -8254,7 +8254,7 @@
         <v>49</v>
       </c>
       <c r="D85" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="E85">
         <v>0.41750406249999999</v>
@@ -8310,7 +8310,7 @@
         <v>49</v>
       </c>
       <c r="D86" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="E86">
         <v>0.41750406249999999</v>
@@ -8366,7 +8366,7 @@
         <v>49</v>
       </c>
       <c r="D87" t="s">
-        <v>60</v>
+        <v>82</v>
       </c>
       <c r="E87">
         <v>0.41750406249999999</v>
@@ -8422,7 +8422,7 @@
         <v>49</v>
       </c>
       <c r="D88" t="s">
-        <v>60</v>
+        <v>82</v>
       </c>
       <c r="E88">
         <v>0.41750406249999999</v>
@@ -8478,7 +8478,7 @@
         <v>49</v>
       </c>
       <c r="D89" t="s">
-        <v>74</v>
+        <v>62</v>
       </c>
       <c r="E89">
         <v>0.44431624999999997</v>
@@ -8534,7 +8534,7 @@
         <v>49</v>
       </c>
       <c r="D90" t="s">
-        <v>74</v>
+        <v>62</v>
       </c>
       <c r="E90">
         <v>0.41750406249999999</v>
@@ -8590,7 +8590,7 @@
         <v>49</v>
       </c>
       <c r="D91" t="s">
-        <v>78</v>
+        <v>55</v>
       </c>
       <c r="E91">
         <v>0.41750406249999999</v>
@@ -8646,7 +8646,7 @@
         <v>49</v>
       </c>
       <c r="D92" t="s">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="E92">
         <v>0.44431624999999997</v>
@@ -8814,7 +8814,7 @@
         <v>49</v>
       </c>
       <c r="D95" t="s">
-        <v>51</v>
+        <v>67</v>
       </c>
       <c r="E95">
         <v>0.41750406249999999</v>
@@ -8870,7 +8870,7 @@
         <v>49</v>
       </c>
       <c r="D96" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="E96">
         <v>0.41750406249999999</v>
@@ -8926,7 +8926,7 @@
         <v>49</v>
       </c>
       <c r="D97" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="E97">
         <v>0.41750406249999999</v>
@@ -9038,7 +9038,7 @@
         <v>49</v>
       </c>
       <c r="D99" t="s">
-        <v>64</v>
+        <v>80</v>
       </c>
       <c r="E99">
         <v>0.45963749999999998</v>
@@ -9094,7 +9094,7 @@
         <v>49</v>
       </c>
       <c r="D100" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E100">
         <v>0.45963749999999998</v>
@@ -9150,7 +9150,7 @@
         <v>49</v>
       </c>
       <c r="D101" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="E101">
         <v>0.45963749999999998</v>
@@ -9206,7 +9206,7 @@
         <v>49</v>
       </c>
       <c r="D102" t="s">
-        <v>50</v>
+        <v>69</v>
       </c>
       <c r="E102">
         <v>0.41750406249999999</v>
@@ -9262,7 +9262,7 @@
         <v>49</v>
       </c>
       <c r="D103" t="s">
-        <v>50</v>
+        <v>69</v>
       </c>
       <c r="E103">
         <v>0.41750406249999999</v>
@@ -9318,7 +9318,7 @@
         <v>49</v>
       </c>
       <c r="D104" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="E104">
         <v>0.41750406249999999</v>
@@ -9374,7 +9374,7 @@
         <v>49</v>
       </c>
       <c r="D105" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="E105">
         <v>0.41750406249999999</v>
@@ -9430,7 +9430,7 @@
         <v>49</v>
       </c>
       <c r="D106" t="s">
-        <v>59</v>
+        <v>83</v>
       </c>
       <c r="E106">
         <v>0.38303124999999993</v>
@@ -9486,7 +9486,7 @@
         <v>49</v>
       </c>
       <c r="D107" t="s">
-        <v>59</v>
+        <v>83</v>
       </c>
       <c r="E107">
         <v>0.38303124999999993</v>
@@ -9542,7 +9542,7 @@
         <v>49</v>
       </c>
       <c r="D108" t="s">
-        <v>52</v>
+        <v>85</v>
       </c>
       <c r="E108">
         <v>0.4021828125000001</v>
@@ -9654,7 +9654,7 @@
         <v>49</v>
       </c>
       <c r="D110" t="s">
-        <v>83</v>
+        <v>52</v>
       </c>
       <c r="E110">
         <v>0.41750406249999999</v>
@@ -9710,7 +9710,7 @@
         <v>49</v>
       </c>
       <c r="D111" t="s">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="E111">
         <v>0.3983525</v>
@@ -9822,7 +9822,7 @@
         <v>49</v>
       </c>
       <c r="D113" t="s">
-        <v>84</v>
+        <v>53</v>
       </c>
       <c r="E113">
         <v>0.41750406249999999</v>
@@ -10326,7 +10326,7 @@
         <v>49</v>
       </c>
       <c r="D122" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E122">
         <v>0.45963749999999998</v>
@@ -10382,7 +10382,7 @@
         <v>49</v>
       </c>
       <c r="D123" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E123">
         <v>0.45963749999999998</v>
@@ -10438,7 +10438,7 @@
         <v>49</v>
       </c>
       <c r="D124" t="s">
-        <v>76</v>
+        <v>37</v>
       </c>
       <c r="E124">
         <v>0.45963749999999998</v>
@@ -10718,7 +10718,7 @@
         <v>49</v>
       </c>
       <c r="D129" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E129">
         <v>0.45963749999999998</v>
@@ -11054,7 +11054,7 @@
         <v>49</v>
       </c>
       <c r="D135" t="s">
-        <v>20</v>
+        <v>79</v>
       </c>
       <c r="E135">
         <v>0.45963749999999998</v>
@@ -11166,7 +11166,7 @@
         <v>49</v>
       </c>
       <c r="D137" t="s">
-        <v>37</v>
+        <v>65</v>
       </c>
       <c r="E137">
         <v>0.45963749999999998</v>
@@ -11222,7 +11222,7 @@
         <v>49</v>
       </c>
       <c r="D138" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E138">
         <v>0.45963749999999998</v>
@@ -11278,7 +11278,7 @@
         <v>49</v>
       </c>
       <c r="D139" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E139">
         <v>0.45963749999999998</v>
@@ -11334,7 +11334,7 @@
         <v>49</v>
       </c>
       <c r="D140" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E140">
         <v>0.45963749999999998</v>
@@ -11390,7 +11390,7 @@
         <v>49</v>
       </c>
       <c r="D141" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E141">
         <v>0.45963749999999998</v>
@@ -11446,7 +11446,7 @@
         <v>49</v>
       </c>
       <c r="D142" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E142">
         <v>0.45963749999999998</v>
@@ -11502,7 +11502,7 @@
         <v>49</v>
       </c>
       <c r="D143" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E143">
         <v>0.45963749999999998</v>
@@ -11558,7 +11558,7 @@
         <v>49</v>
       </c>
       <c r="D144" t="s">
-        <v>72</v>
+        <v>20</v>
       </c>
       <c r="E144">
         <v>0.45963749999999998</v>
@@ -11670,7 +11670,7 @@
         <v>49</v>
       </c>
       <c r="D146" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E146">
         <v>0.45963749999999998</v>
@@ -12678,7 +12678,7 @@
         <v>49</v>
       </c>
       <c r="D164" t="s">
-        <v>52</v>
+        <v>85</v>
       </c>
       <c r="E164">
         <v>0.41367375000000001</v>
@@ -13518,7 +13518,7 @@
         <v>49</v>
       </c>
       <c r="D179" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="E179">
         <v>0.39835250000000011</v>
@@ -13574,7 +13574,7 @@
         <v>49</v>
       </c>
       <c r="D180" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="E180">
         <v>0.39835250000000011</v>
@@ -13798,7 +13798,7 @@
         <v>49</v>
       </c>
       <c r="D184" t="s">
-        <v>59</v>
+        <v>83</v>
       </c>
       <c r="E184">
         <v>0.41367375000000001</v>
@@ -13854,7 +13854,7 @@
         <v>49</v>
       </c>
       <c r="D185" t="s">
-        <v>59</v>
+        <v>83</v>
       </c>
       <c r="E185">
         <v>0.41367375000000001</v>
@@ -14582,7 +14582,7 @@
         <v>49</v>
       </c>
       <c r="D198" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E198">
         <v>0.42899500000000002</v>
@@ -14806,7 +14806,7 @@
         <v>49</v>
       </c>
       <c r="D202" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E202">
         <v>0.3983525</v>
@@ -15534,7 +15534,7 @@
         <v>49</v>
       </c>
       <c r="D215" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
       <c r="E215">
         <v>0.38303124999999993</v>
@@ -15702,7 +15702,7 @@
         <v>49</v>
       </c>
       <c r="D218" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E218">
         <v>0.42899499999999996</v>
@@ -15758,7 +15758,7 @@
         <v>49</v>
       </c>
       <c r="D219" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E219">
         <v>0.42899499999999996</v>
@@ -15926,7 +15926,7 @@
         <v>49</v>
       </c>
       <c r="D222" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="E222">
         <v>0.38303124999999993</v>
@@ -15982,7 +15982,7 @@
         <v>49</v>
       </c>
       <c r="D223" t="s">
-        <v>60</v>
+        <v>82</v>
       </c>
       <c r="E223">
         <v>0.25280062500000006</v>
@@ -16038,7 +16038,7 @@
         <v>49</v>
       </c>
       <c r="D224" t="s">
-        <v>74</v>
+        <v>62</v>
       </c>
       <c r="E224">
         <v>0.24514000000000002</v>
@@ -16094,7 +16094,7 @@
         <v>49</v>
       </c>
       <c r="D225" t="s">
-        <v>74</v>
+        <v>62</v>
       </c>
       <c r="E225">
         <v>0.24514000000000002</v>
@@ -16150,7 +16150,7 @@
         <v>49</v>
       </c>
       <c r="D226" t="s">
-        <v>84</v>
+        <v>53</v>
       </c>
       <c r="E226">
         <v>0.21066718750000002</v>
@@ -16654,7 +16654,7 @@
         <v>49</v>
       </c>
       <c r="D235" t="s">
-        <v>75</v>
+        <v>63</v>
       </c>
       <c r="E235">
         <v>0.21449750000000001</v>
@@ -16934,7 +16934,7 @@
         <v>49</v>
       </c>
       <c r="D240" t="s">
-        <v>74</v>
+        <v>62</v>
       </c>
       <c r="E240">
         <v>0.23747937499999999</v>
@@ -17046,7 +17046,7 @@
         <v>49</v>
       </c>
       <c r="D242" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="E242">
         <v>0.21449750000000001</v>
@@ -17242,7 +17242,7 @@
         <v>49</v>
       </c>
       <c r="D247" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="E247">
         <v>0.27578249999999999</v>
@@ -17312,7 +17312,7 @@
         <v>49</v>
       </c>
       <c r="D249" t="s">
-        <v>78</v>
+        <v>55</v>
       </c>
       <c r="E249">
         <v>0.27578249999999999</v>
@@ -17452,7 +17452,7 @@
         <v>49</v>
       </c>
       <c r="D253" t="s">
-        <v>52</v>
+        <v>85</v>
       </c>
       <c r="E253">
         <v>0.23747937499999999</v>
@@ -17487,7 +17487,7 @@
         <v>49</v>
       </c>
       <c r="D254" t="s">
-        <v>52</v>
+        <v>85</v>
       </c>
       <c r="E254">
         <v>0.23747937499999999</v>
@@ -17522,7 +17522,7 @@
         <v>49</v>
       </c>
       <c r="D255" t="s">
-        <v>52</v>
+        <v>85</v>
       </c>
       <c r="E255">
         <v>0.23747937499999999</v>
@@ -17557,7 +17557,7 @@
         <v>49</v>
       </c>
       <c r="D256" t="s">
-        <v>55</v>
+        <v>79</v>
       </c>
       <c r="E256">
         <v>0.26429156249999997</v>
@@ -17592,7 +17592,7 @@
         <v>49</v>
       </c>
       <c r="D257" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E257">
         <v>0.23747937499999999</v>
@@ -17627,7 +17627,7 @@
         <v>49</v>
       </c>
       <c r="D258" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E258">
         <v>0.23747937499999999</v>
@@ -17662,7 +17662,7 @@
         <v>49</v>
       </c>
       <c r="D259" t="s">
-        <v>83</v>
+        <v>52</v>
       </c>
       <c r="E259">
         <v>0.22215812499999998</v>
@@ -17697,7 +17697,7 @@
         <v>49</v>
       </c>
       <c r="D260" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E260">
         <v>0.24514000000000002</v>
@@ -17732,7 +17732,7 @@
         <v>49</v>
       </c>
       <c r="D261" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E261">
         <v>0.24514000000000002</v>
@@ -17767,7 +17767,7 @@
         <v>49</v>
       </c>
       <c r="D262" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E262">
         <v>0.24514000000000002</v>
@@ -17837,7 +17837,7 @@
         <v>439</v>
       </c>
       <c r="D264" t="s">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="E264">
         <v>0.35238875000000003</v>
@@ -17977,7 +17977,7 @@
         <v>439</v>
       </c>
       <c r="D268" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E268">
         <v>0.206836875</v>
@@ -18152,7 +18152,7 @@
         <v>439</v>
       </c>
       <c r="D273" t="s">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="E273">
         <v>0.23747937499999999</v>
@@ -18360,7 +18360,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8FA493AF-DDEA-4475-9CEF-74606729E3F4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CAC2B88A-405C-446E-81B2-C0420EDDE10C}">
   <dimension ref="B9:T641"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -18442,19 +18442,19 @@
         <v>2022</v>
       </c>
       <c r="F11">
-        <v>0.24877966101694915</v>
+        <v>0.35800000000000004</v>
       </c>
       <c r="G11">
-        <v>0.28891500000000003</v>
+        <v>0.306425</v>
       </c>
       <c r="H11">
-        <v>4427.5</v>
+        <v>3850.0000000000009</v>
       </c>
       <c r="I11">
-        <v>157.30000000000001</v>
+        <v>143</v>
       </c>
       <c r="J11">
-        <v>9.240000000000002</v>
+        <v>8.4</v>
       </c>
       <c r="K11">
         <v>50</v>
@@ -18495,19 +18495,19 @@
         <v>2022</v>
       </c>
       <c r="F12">
-        <v>0.39440677966101695</v>
+        <v>0.22450847457627116</v>
       </c>
       <c r="G12">
-        <v>0.306425</v>
+        <v>0.28891500000000003</v>
       </c>
       <c r="H12">
-        <v>3850.0000000000005</v>
+        <v>4427.5</v>
       </c>
       <c r="I12">
-        <v>143</v>
+        <v>157.30000000000001</v>
       </c>
       <c r="J12">
-        <v>8.4</v>
+        <v>9.240000000000002</v>
       </c>
       <c r="K12">
         <v>50</v>
@@ -18548,7 +18548,7 @@
         <v>2022</v>
       </c>
       <c r="F13">
-        <v>1.0679322033898306</v>
+        <v>0.39440677966101695</v>
       </c>
       <c r="G13">
         <v>0.306425</v>
@@ -18654,19 +18654,19 @@
         <v>2022</v>
       </c>
       <c r="F15">
-        <v>0.22450847457627116</v>
+        <v>1.0679322033898306</v>
       </c>
       <c r="G15">
-        <v>0.28891500000000003</v>
+        <v>0.306425</v>
       </c>
       <c r="H15">
-        <v>4427.5</v>
+        <v>3850.0000000000005</v>
       </c>
       <c r="I15">
-        <v>157.30000000000001</v>
+        <v>143</v>
       </c>
       <c r="J15">
-        <v>9.240000000000002</v>
+        <v>8.4</v>
       </c>
       <c r="K15">
         <v>50</v>
@@ -18707,13 +18707,13 @@
         <v>2022</v>
       </c>
       <c r="F16">
-        <v>0.35800000000000004</v>
+        <v>0.51576271186440681</v>
       </c>
       <c r="G16">
         <v>0.306425</v>
       </c>
       <c r="H16">
-        <v>3850.0000000000009</v>
+        <v>3850.0000000000005</v>
       </c>
       <c r="I16">
         <v>143</v>
@@ -18813,19 +18813,19 @@
         <v>2022</v>
       </c>
       <c r="F18">
-        <v>0.51576271186440681</v>
+        <v>0.24877966101694915</v>
       </c>
       <c r="G18">
-        <v>0.306425</v>
+        <v>0.28891500000000003</v>
       </c>
       <c r="H18">
-        <v>3850.0000000000005</v>
+        <v>4427.5</v>
       </c>
       <c r="I18">
-        <v>143</v>
+        <v>157.30000000000001</v>
       </c>
       <c r="J18">
-        <v>8.4</v>
+        <v>9.240000000000002</v>
       </c>
       <c r="K18">
         <v>50</v>
@@ -18860,7 +18860,7 @@
         <v>13</v>
       </c>
       <c r="D19" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E19">
         <v>2008</v>
@@ -18913,7 +18913,7 @@
         <v>13</v>
       </c>
       <c r="D20" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E20">
         <v>1998</v>
@@ -19019,7 +19019,7 @@
         <v>13</v>
       </c>
       <c r="D22" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="E22">
         <v>2001</v>
@@ -19072,7 +19072,7 @@
         <v>13</v>
       </c>
       <c r="D23" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E23">
         <v>2013</v>
@@ -19125,7 +19125,7 @@
         <v>13</v>
       </c>
       <c r="D24" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="E24">
         <v>1965</v>
@@ -19231,7 +19231,7 @@
         <v>13</v>
       </c>
       <c r="D26" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E26">
         <v>2009</v>
@@ -19337,7 +19337,7 @@
         <v>13</v>
       </c>
       <c r="D28" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E28">
         <v>2009</v>
@@ -19396,19 +19396,19 @@
         <v>2022</v>
       </c>
       <c r="F29">
-        <v>0.61803468208092449</v>
+        <v>0.1997687861271675</v>
       </c>
       <c r="G29">
-        <v>0.31518000000000002</v>
+        <v>0.29766999999999999</v>
       </c>
       <c r="H29">
-        <v>2200</v>
+        <v>2530</v>
       </c>
       <c r="I29">
-        <v>66</v>
+        <v>72.600000000000009</v>
       </c>
       <c r="J29">
-        <v>5.25</v>
+        <v>5.7750000000000004</v>
       </c>
       <c r="K29">
         <v>50</v>
@@ -19449,19 +19449,19 @@
         <v>2022</v>
       </c>
       <c r="F30">
-        <v>0.1997687861271675</v>
+        <v>0.61803468208092449</v>
       </c>
       <c r="G30">
-        <v>0.29766999999999999</v>
+        <v>0.31518000000000002</v>
       </c>
       <c r="H30">
-        <v>2530</v>
+        <v>2200</v>
       </c>
       <c r="I30">
-        <v>72.600000000000009</v>
+        <v>66</v>
       </c>
       <c r="J30">
-        <v>5.7750000000000004</v>
+        <v>5.25</v>
       </c>
       <c r="K30">
         <v>50</v>
@@ -19602,7 +19602,7 @@
         <v>33</v>
       </c>
       <c r="D33" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E33">
         <v>1992</v>
@@ -19655,7 +19655,7 @@
         <v>33</v>
       </c>
       <c r="D34" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E34">
         <v>1993</v>
@@ -19814,7 +19814,7 @@
         <v>33</v>
       </c>
       <c r="D37" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E37">
         <v>1991</v>
@@ -19867,7 +19867,7 @@
         <v>33</v>
       </c>
       <c r="D38" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E38">
         <v>1992</v>
@@ -19920,7 +19920,7 @@
         <v>33</v>
       </c>
       <c r="D39" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E39">
         <v>1993</v>
@@ -20138,7 +20138,7 @@
         <v>2022</v>
       </c>
       <c r="F43">
-        <v>0.18824049497996109</v>
+        <v>0.23280454489112914</v>
       </c>
       <c r="G43">
         <v>0.50778999999999996</v>
@@ -20150,7 +20150,7 @@
         <v>36.300000000000004</v>
       </c>
       <c r="J43">
-        <v>3.4650000000000003</v>
+        <v>3.4650000000000007</v>
       </c>
       <c r="K43">
         <v>50</v>
@@ -20191,7 +20191,7 @@
         <v>2022</v>
       </c>
       <c r="F44">
-        <v>0.21113131843159935</v>
+        <v>0.27347228442755023</v>
       </c>
       <c r="G44">
         <v>0.50778999999999996</v>
@@ -20244,7 +20244,7 @@
         <v>2022</v>
       </c>
       <c r="F45">
-        <v>0.26604494277568891</v>
+        <v>0.1548783373961905</v>
       </c>
       <c r="G45">
         <v>0.50778999999999996</v>
@@ -20256,7 +20256,7 @@
         <v>36.300000000000004</v>
       </c>
       <c r="J45">
-        <v>3.4650000000000003</v>
+        <v>3.4649999999999999</v>
       </c>
       <c r="K45">
         <v>50</v>
@@ -20297,7 +20297,7 @@
         <v>2022</v>
       </c>
       <c r="F46">
-        <v>0.23280454489112914</v>
+        <v>0.22793415692269547</v>
       </c>
       <c r="G46">
         <v>0.50778999999999996</v>
@@ -20309,7 +20309,7 @@
         <v>36.300000000000004</v>
       </c>
       <c r="J46">
-        <v>3.4650000000000007</v>
+        <v>3.4650000000000003</v>
       </c>
       <c r="K46">
         <v>50</v>
@@ -20350,19 +20350,19 @@
         <v>2022</v>
       </c>
       <c r="F47">
-        <v>0.18556178159732259</v>
+        <v>0.37112356319464518</v>
       </c>
       <c r="G47">
-        <v>0.50778999999999996</v>
+        <v>0.52529999999999999</v>
       </c>
       <c r="H47">
-        <v>1265</v>
+        <v>1100</v>
       </c>
       <c r="I47">
-        <v>36.300000000000004</v>
+        <v>33</v>
       </c>
       <c r="J47">
-        <v>3.4650000000000003</v>
+        <v>3.1500000000000004</v>
       </c>
       <c r="K47">
         <v>50</v>
@@ -20403,7 +20403,7 @@
         <v>2022</v>
       </c>
       <c r="F48">
-        <v>0.20236462008841874</v>
+        <v>0.20557907614758497</v>
       </c>
       <c r="G48">
         <v>0.50778999999999996</v>
@@ -20456,7 +20456,7 @@
         <v>2022</v>
       </c>
       <c r="F49">
-        <v>0.19481551873734657</v>
+        <v>0.17484692806676855</v>
       </c>
       <c r="G49">
         <v>0.50778999999999996</v>
@@ -20509,7 +20509,7 @@
         <v>2022</v>
       </c>
       <c r="F50">
-        <v>0.23864901045324952</v>
+        <v>0.18872753377680451</v>
       </c>
       <c r="G50">
         <v>0.50778999999999996</v>
@@ -20521,7 +20521,7 @@
         <v>36.300000000000004</v>
       </c>
       <c r="J50">
-        <v>3.4650000000000003</v>
+        <v>3.4650000000000007</v>
       </c>
       <c r="K50">
         <v>50</v>
@@ -20562,19 +20562,19 @@
         <v>2022</v>
       </c>
       <c r="F51">
-        <v>0.31243538817501959</v>
+        <v>0.23864901045324952</v>
       </c>
       <c r="G51">
-        <v>0.52529999999999999</v>
+        <v>0.50778999999999996</v>
       </c>
       <c r="H51">
-        <v>1100</v>
+        <v>1265</v>
       </c>
       <c r="I51">
-        <v>33</v>
+        <v>36.300000000000004</v>
       </c>
       <c r="J51">
-        <v>3.1500000000000004</v>
+        <v>3.4650000000000003</v>
       </c>
       <c r="K51">
         <v>50</v>
@@ -20615,7 +20615,7 @@
         <v>2022</v>
       </c>
       <c r="F52">
-        <v>0.45732943023592104</v>
+        <v>0.31243538817501959</v>
       </c>
       <c r="G52">
         <v>0.52529999999999999</v>
@@ -20668,19 +20668,19 @@
         <v>2022</v>
       </c>
       <c r="F53">
-        <v>0.49339465314217229</v>
+        <v>0.19481551873734657</v>
       </c>
       <c r="G53">
-        <v>0.52529999999999999</v>
+        <v>0.50778999999999996</v>
       </c>
       <c r="H53">
-        <v>1100</v>
+        <v>1265</v>
       </c>
       <c r="I53">
-        <v>33</v>
+        <v>36.300000000000004</v>
       </c>
       <c r="J53">
-        <v>3.1500000000000004</v>
+        <v>3.4650000000000003</v>
       </c>
       <c r="K53">
         <v>50</v>
@@ -20721,7 +20721,7 @@
         <v>2022</v>
       </c>
       <c r="F54">
-        <v>0.19481551873734657</v>
+        <v>0.28443065735652601</v>
       </c>
       <c r="G54">
         <v>0.50778999999999996</v>
@@ -20774,19 +20774,19 @@
         <v>2022</v>
       </c>
       <c r="F55">
-        <v>0.19481551873734657</v>
+        <v>0.39839773581787374</v>
       </c>
       <c r="G55">
-        <v>0.50778999999999996</v>
+        <v>0.52529999999999999</v>
       </c>
       <c r="H55">
-        <v>1265</v>
+        <v>1100</v>
       </c>
       <c r="I55">
-        <v>36.300000000000004</v>
+        <v>33</v>
       </c>
       <c r="J55">
-        <v>3.4650000000000003</v>
+        <v>3.1500000000000004</v>
       </c>
       <c r="K55">
         <v>50</v>
@@ -20827,19 +20827,19 @@
         <v>2022</v>
       </c>
       <c r="F56">
-        <v>0.30829555840185086</v>
+        <v>0.21283595422055113</v>
       </c>
       <c r="G56">
-        <v>0.52529999999999999</v>
+        <v>0.50778999999999996</v>
       </c>
       <c r="H56">
-        <v>1100</v>
+        <v>1265</v>
       </c>
       <c r="I56">
-        <v>33</v>
+        <v>36.300000000000004</v>
       </c>
       <c r="J56">
-        <v>3.1500000000000004</v>
+        <v>3.4650000000000003</v>
       </c>
       <c r="K56">
         <v>50</v>
@@ -20880,7 +20880,7 @@
         <v>2022</v>
       </c>
       <c r="F57">
-        <v>0.18629233979258764</v>
+        <v>0.26543614427963469</v>
       </c>
       <c r="G57">
         <v>0.50778999999999996</v>
@@ -20927,13 +20927,13 @@
         <v>49</v>
       </c>
       <c r="D58" t="s">
-        <v>37</v>
+        <v>65</v>
       </c>
       <c r="E58">
         <v>2022</v>
       </c>
       <c r="F58">
-        <v>0.27761211420071885</v>
+        <v>0.19481551873734657</v>
       </c>
       <c r="G58">
         <v>0.50778999999999996</v>
@@ -20980,25 +20980,25 @@
         <v>49</v>
       </c>
       <c r="D59" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E59">
         <v>2022</v>
       </c>
       <c r="F59">
-        <v>0.3567559186877659</v>
+        <v>0.19481551873734657</v>
       </c>
       <c r="G59">
-        <v>0.52529999999999999</v>
+        <v>0.50778999999999996</v>
       </c>
       <c r="H59">
-        <v>1100</v>
+        <v>1265</v>
       </c>
       <c r="I59">
-        <v>33</v>
+        <v>36.300000000000004</v>
       </c>
       <c r="J59">
-        <v>3.1500000000000004</v>
+        <v>3.4650000000000003</v>
       </c>
       <c r="K59">
         <v>50</v>
@@ -21033,13 +21033,13 @@
         <v>49</v>
       </c>
       <c r="D60" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E60">
         <v>2022</v>
       </c>
       <c r="F60">
-        <v>0.18507474280047922</v>
+        <v>0.21113131843159935</v>
       </c>
       <c r="G60">
         <v>0.50778999999999996</v>
@@ -21051,7 +21051,7 @@
         <v>36.300000000000004</v>
       </c>
       <c r="J60">
-        <v>3.4649999999999999</v>
+        <v>3.4650000000000003</v>
       </c>
       <c r="K60">
         <v>50</v>
@@ -21086,13 +21086,13 @@
         <v>49</v>
       </c>
       <c r="D61" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E61">
         <v>2022</v>
       </c>
       <c r="F61">
-        <v>0.19676367392472002</v>
+        <v>0.19627663512787666</v>
       </c>
       <c r="G61">
         <v>0.50778999999999996</v>
@@ -21104,7 +21104,7 @@
         <v>36.300000000000004</v>
       </c>
       <c r="J61">
-        <v>3.4650000000000003</v>
+        <v>3.4649999999999999</v>
       </c>
       <c r="K61">
         <v>50</v>
@@ -21139,13 +21139,13 @@
         <v>49</v>
       </c>
       <c r="D62" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E62">
         <v>2022</v>
       </c>
       <c r="F62">
-        <v>0.16608022972358796</v>
+        <v>0.18824049497996109</v>
       </c>
       <c r="G62">
         <v>0.50778999999999996</v>
@@ -21192,25 +21192,25 @@
         <v>49</v>
       </c>
       <c r="D63" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E63">
         <v>2022</v>
       </c>
       <c r="F63">
-        <v>0.17484692806676855</v>
+        <v>0.43468212618270452</v>
       </c>
       <c r="G63">
-        <v>0.50778999999999996</v>
+        <v>0.52529999999999999</v>
       </c>
       <c r="H63">
-        <v>1265</v>
+        <v>1100</v>
       </c>
       <c r="I63">
-        <v>36.300000000000004</v>
+        <v>33</v>
       </c>
       <c r="J63">
-        <v>3.4650000000000003</v>
+        <v>3.1500000000000004</v>
       </c>
       <c r="K63">
         <v>50</v>
@@ -21245,13 +21245,13 @@
         <v>49</v>
       </c>
       <c r="D64" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E64">
         <v>2022</v>
       </c>
       <c r="F64">
-        <v>0.18872753377680451</v>
+        <v>0.18702289798785268</v>
       </c>
       <c r="G64">
         <v>0.50778999999999996</v>
@@ -21263,7 +21263,7 @@
         <v>36.300000000000004</v>
       </c>
       <c r="J64">
-        <v>3.4650000000000007</v>
+        <v>3.4650000000000003</v>
       </c>
       <c r="K64">
         <v>50</v>
@@ -21298,13 +21298,13 @@
         <v>49</v>
       </c>
       <c r="D65" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E65">
         <v>2022</v>
       </c>
       <c r="F65">
-        <v>0.21551466760318963</v>
+        <v>0.19481551873734657</v>
       </c>
       <c r="G65">
         <v>0.50778999999999996</v>
@@ -21351,13 +21351,13 @@
         <v>49</v>
       </c>
       <c r="D66" t="s">
-        <v>72</v>
+        <v>20</v>
       </c>
       <c r="E66">
         <v>2022</v>
       </c>
       <c r="F66">
-        <v>0.28443065735652601</v>
+        <v>0.19822479031525012</v>
       </c>
       <c r="G66">
         <v>0.50778999999999996</v>
@@ -21410,7 +21410,7 @@
         <v>2022</v>
       </c>
       <c r="F67">
-        <v>0.20820908565053911</v>
+        <v>0.20212110068999706</v>
       </c>
       <c r="G67">
         <v>0.50778999999999996</v>
@@ -21422,7 +21422,7 @@
         <v>36.300000000000004</v>
       </c>
       <c r="J67">
-        <v>3.4650000000000007</v>
+        <v>3.4650000000000003</v>
       </c>
       <c r="K67">
         <v>50</v>
@@ -21463,19 +21463,19 @@
         <v>2022</v>
       </c>
       <c r="F68">
-        <v>0.39839773581787374</v>
+        <v>0.29344087509812827</v>
       </c>
       <c r="G68">
-        <v>0.52529999999999999</v>
+        <v>0.50778999999999996</v>
       </c>
       <c r="H68">
-        <v>1100</v>
+        <v>1265</v>
       </c>
       <c r="I68">
-        <v>33</v>
+        <v>36.300000000000004</v>
       </c>
       <c r="J68">
-        <v>3.1500000000000004</v>
+        <v>3.4650000000000003</v>
       </c>
       <c r="K68">
         <v>50</v>
@@ -21516,19 +21516,19 @@
         <v>2022</v>
       </c>
       <c r="F69">
-        <v>0.21283595422055113</v>
+        <v>0.30829555840185086</v>
       </c>
       <c r="G69">
-        <v>0.50778999999999996</v>
+        <v>0.52529999999999999</v>
       </c>
       <c r="H69">
-        <v>1265</v>
+        <v>1100</v>
       </c>
       <c r="I69">
-        <v>36.300000000000004</v>
+        <v>33</v>
       </c>
       <c r="J69">
-        <v>3.4650000000000003</v>
+        <v>3.1500000000000004</v>
       </c>
       <c r="K69">
         <v>50</v>
@@ -21563,13 +21563,13 @@
         <v>49</v>
       </c>
       <c r="D70" t="s">
-        <v>76</v>
+        <v>37</v>
       </c>
       <c r="E70">
         <v>2022</v>
       </c>
       <c r="F70">
-        <v>0.20212110068999706</v>
+        <v>0.27761211420071885</v>
       </c>
       <c r="G70">
         <v>0.50778999999999996</v>
@@ -21616,25 +21616,25 @@
         <v>49</v>
       </c>
       <c r="D71" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E71">
         <v>2022</v>
       </c>
       <c r="F71">
-        <v>0.26543614427963469</v>
+        <v>0.3567559186877659</v>
       </c>
       <c r="G71">
-        <v>0.50778999999999996</v>
+        <v>0.52529999999999999</v>
       </c>
       <c r="H71">
-        <v>1265</v>
+        <v>1100</v>
       </c>
       <c r="I71">
-        <v>36.300000000000004</v>
+        <v>33</v>
       </c>
       <c r="J71">
-        <v>3.4650000000000003</v>
+        <v>3.1500000000000004</v>
       </c>
       <c r="K71">
         <v>50</v>
@@ -21669,13 +21669,13 @@
         <v>49</v>
       </c>
       <c r="D72" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E72">
         <v>2022</v>
       </c>
       <c r="F72">
-        <v>0.20557907614758497</v>
+        <v>0.18507474280047922</v>
       </c>
       <c r="G72">
         <v>0.50778999999999996</v>
@@ -21687,7 +21687,7 @@
         <v>36.300000000000004</v>
       </c>
       <c r="J72">
-        <v>3.4650000000000003</v>
+        <v>3.4649999999999999</v>
       </c>
       <c r="K72">
         <v>50</v>
@@ -21722,25 +21722,25 @@
         <v>49</v>
       </c>
       <c r="D73" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E73">
         <v>2022</v>
       </c>
       <c r="F73">
-        <v>0.37112356319464518</v>
+        <v>0.19676367392472002</v>
       </c>
       <c r="G73">
-        <v>0.52529999999999999</v>
+        <v>0.50778999999999996</v>
       </c>
       <c r="H73">
-        <v>1100</v>
+        <v>1265</v>
       </c>
       <c r="I73">
-        <v>33</v>
+        <v>36.300000000000004</v>
       </c>
       <c r="J73">
-        <v>3.1500000000000004</v>
+        <v>3.4650000000000003</v>
       </c>
       <c r="K73">
         <v>50</v>
@@ -21775,13 +21775,13 @@
         <v>49</v>
       </c>
       <c r="D74" t="s">
-        <v>20</v>
+        <v>79</v>
       </c>
       <c r="E74">
         <v>2022</v>
       </c>
       <c r="F74">
-        <v>0.19822479031525012</v>
+        <v>0.20236462008841874</v>
       </c>
       <c r="G74">
         <v>0.50778999999999996</v>
@@ -21834,7 +21834,7 @@
         <v>2022</v>
       </c>
       <c r="F75">
-        <v>0.19481551873734657</v>
+        <v>0.18629233979258764</v>
       </c>
       <c r="G75">
         <v>0.50778999999999996</v>
@@ -21887,7 +21887,7 @@
         <v>2022</v>
       </c>
       <c r="F76">
-        <v>0.18702289798785268</v>
+        <v>0.20820908565053911</v>
       </c>
       <c r="G76">
         <v>0.50778999999999996</v>
@@ -21899,7 +21899,7 @@
         <v>36.300000000000004</v>
       </c>
       <c r="J76">
-        <v>3.4650000000000003</v>
+        <v>3.4650000000000007</v>
       </c>
       <c r="K76">
         <v>50</v>
@@ -21940,19 +21940,19 @@
         <v>2022</v>
       </c>
       <c r="F77">
-        <v>0.27347228442755023</v>
+        <v>0.49339465314217229</v>
       </c>
       <c r="G77">
-        <v>0.50778999999999996</v>
+        <v>0.52529999999999999</v>
       </c>
       <c r="H77">
-        <v>1265</v>
+        <v>1100</v>
       </c>
       <c r="I77">
-        <v>36.300000000000004</v>
+        <v>33</v>
       </c>
       <c r="J77">
-        <v>3.4650000000000003</v>
+        <v>3.1500000000000004</v>
       </c>
       <c r="K77">
         <v>50</v>
@@ -21993,19 +21993,19 @@
         <v>2022</v>
       </c>
       <c r="F78">
-        <v>0.1548783373961905</v>
+        <v>0.45732943023592104</v>
       </c>
       <c r="G78">
-        <v>0.50778999999999996</v>
+        <v>0.52529999999999999</v>
       </c>
       <c r="H78">
-        <v>1265</v>
+        <v>1100</v>
       </c>
       <c r="I78">
-        <v>36.300000000000004</v>
+        <v>33</v>
       </c>
       <c r="J78">
-        <v>3.4649999999999999</v>
+        <v>3.1500000000000004</v>
       </c>
       <c r="K78">
         <v>50</v>
@@ -22046,7 +22046,7 @@
         <v>2022</v>
       </c>
       <c r="F79">
-        <v>0.22793415692269547</v>
+        <v>0.21551466760318963</v>
       </c>
       <c r="G79">
         <v>0.50778999999999996</v>
@@ -22099,19 +22099,19 @@
         <v>2022</v>
       </c>
       <c r="F80">
-        <v>0.43468212618270452</v>
+        <v>0.26604494277568891</v>
       </c>
       <c r="G80">
-        <v>0.52529999999999999</v>
+        <v>0.50778999999999996</v>
       </c>
       <c r="H80">
-        <v>1100</v>
+        <v>1265</v>
       </c>
       <c r="I80">
-        <v>33</v>
+        <v>36.300000000000004</v>
       </c>
       <c r="J80">
-        <v>3.1500000000000004</v>
+        <v>3.4650000000000003</v>
       </c>
       <c r="K80">
         <v>50</v>
@@ -22152,7 +22152,7 @@
         <v>2022</v>
       </c>
       <c r="F81">
-        <v>0.29344087509812827</v>
+        <v>0.16608022972358796</v>
       </c>
       <c r="G81">
         <v>0.50778999999999996</v>
@@ -22205,7 +22205,7 @@
         <v>2022</v>
       </c>
       <c r="F82">
-        <v>0.19627663512787666</v>
+        <v>0.18556178159732259</v>
       </c>
       <c r="G82">
         <v>0.50778999999999996</v>
@@ -22217,7 +22217,7 @@
         <v>36.300000000000004</v>
       </c>
       <c r="J82">
-        <v>3.4649999999999999</v>
+        <v>3.4650000000000003</v>
       </c>
       <c r="K82">
         <v>50</v>
@@ -22252,7 +22252,7 @@
         <v>49</v>
       </c>
       <c r="D83" t="s">
-        <v>67</v>
+        <v>78</v>
       </c>
       <c r="E83">
         <v>2006</v>
@@ -22305,7 +22305,7 @@
         <v>49</v>
       </c>
       <c r="D84" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="E84">
         <v>2012</v>
@@ -22358,7 +22358,7 @@
         <v>49</v>
       </c>
       <c r="D85" t="s">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="E85">
         <v>1993</v>
@@ -22411,7 +22411,7 @@
         <v>49</v>
       </c>
       <c r="D86" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="E86">
         <v>2011</v>
@@ -22464,7 +22464,7 @@
         <v>49</v>
       </c>
       <c r="D87" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E87">
         <v>2005</v>
@@ -22517,7 +22517,7 @@
         <v>49</v>
       </c>
       <c r="D88" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E88">
         <v>2006</v>
@@ -22570,7 +22570,7 @@
         <v>49</v>
       </c>
       <c r="D89" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E89">
         <v>2006</v>
@@ -22676,7 +22676,7 @@
         <v>49</v>
       </c>
       <c r="D91" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="E91">
         <v>2003</v>
@@ -22835,7 +22835,7 @@
         <v>49</v>
       </c>
       <c r="D94" t="s">
-        <v>82</v>
+        <v>51</v>
       </c>
       <c r="E94">
         <v>2004</v>
@@ -22888,7 +22888,7 @@
         <v>49</v>
       </c>
       <c r="D95" t="s">
-        <v>82</v>
+        <v>51</v>
       </c>
       <c r="E95">
         <v>2005</v>
@@ -22941,7 +22941,7 @@
         <v>49</v>
       </c>
       <c r="D96" t="s">
-        <v>55</v>
+        <v>79</v>
       </c>
       <c r="E96">
         <v>2005</v>
@@ -22994,7 +22994,7 @@
         <v>49</v>
       </c>
       <c r="D97" t="s">
-        <v>55</v>
+        <v>79</v>
       </c>
       <c r="E97">
         <v>2005</v>
@@ -23047,7 +23047,7 @@
         <v>49</v>
       </c>
       <c r="D98" t="s">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="E98">
         <v>2004</v>
@@ -23100,7 +23100,7 @@
         <v>49</v>
       </c>
       <c r="D99" t="s">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="E99">
         <v>2004</v>
@@ -23153,7 +23153,7 @@
         <v>49</v>
       </c>
       <c r="D100" t="s">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="E100">
         <v>2004</v>
@@ -23206,7 +23206,7 @@
         <v>49</v>
       </c>
       <c r="D101" t="s">
-        <v>75</v>
+        <v>63</v>
       </c>
       <c r="E101">
         <v>2008</v>
@@ -23259,7 +23259,7 @@
         <v>49</v>
       </c>
       <c r="D102" t="s">
-        <v>75</v>
+        <v>63</v>
       </c>
       <c r="E102">
         <v>2008</v>
@@ -23312,7 +23312,7 @@
         <v>49</v>
       </c>
       <c r="D103" t="s">
-        <v>79</v>
+        <v>54</v>
       </c>
       <c r="E103">
         <v>2002</v>
@@ -23365,7 +23365,7 @@
         <v>49</v>
       </c>
       <c r="D104" t="s">
-        <v>79</v>
+        <v>54</v>
       </c>
       <c r="E104">
         <v>2002</v>
@@ -23418,7 +23418,7 @@
         <v>49</v>
       </c>
       <c r="D105" t="s">
-        <v>79</v>
+        <v>54</v>
       </c>
       <c r="E105">
         <v>2003</v>
@@ -23471,7 +23471,7 @@
         <v>49</v>
       </c>
       <c r="D106" t="s">
-        <v>79</v>
+        <v>54</v>
       </c>
       <c r="E106">
         <v>2003</v>
@@ -23524,7 +23524,7 @@
         <v>49</v>
       </c>
       <c r="D107" t="s">
-        <v>68</v>
+        <v>86</v>
       </c>
       <c r="E107">
         <v>2000</v>
@@ -23577,7 +23577,7 @@
         <v>49</v>
       </c>
       <c r="D108" t="s">
-        <v>68</v>
+        <v>86</v>
       </c>
       <c r="E108">
         <v>2000</v>
@@ -23630,7 +23630,7 @@
         <v>49</v>
       </c>
       <c r="D109" t="s">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="E109">
         <v>2007</v>
@@ -23683,7 +23683,7 @@
         <v>49</v>
       </c>
       <c r="D110" t="s">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="E110">
         <v>2023</v>
@@ -23736,7 +23736,7 @@
         <v>49</v>
       </c>
       <c r="D111" t="s">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="E111">
         <v>2001</v>
@@ -23842,7 +23842,7 @@
         <v>49</v>
       </c>
       <c r="D113" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="E113">
         <v>2010</v>
@@ -23895,7 +23895,7 @@
         <v>49</v>
       </c>
       <c r="D114" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="E114">
         <v>2005</v>
@@ -23948,7 +23948,7 @@
         <v>49</v>
       </c>
       <c r="D115" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="E115">
         <v>2009</v>
@@ -24001,7 +24001,7 @@
         <v>49</v>
       </c>
       <c r="D116" t="s">
-        <v>77</v>
+        <v>64</v>
       </c>
       <c r="E116">
         <v>1997</v>
@@ -24054,7 +24054,7 @@
         <v>49</v>
       </c>
       <c r="D117" t="s">
-        <v>77</v>
+        <v>64</v>
       </c>
       <c r="E117">
         <v>1997</v>
@@ -24107,7 +24107,7 @@
         <v>49</v>
       </c>
       <c r="D118" t="s">
-        <v>77</v>
+        <v>64</v>
       </c>
       <c r="E118">
         <v>1998</v>
@@ -24160,7 +24160,7 @@
         <v>49</v>
       </c>
       <c r="D119" t="s">
-        <v>77</v>
+        <v>64</v>
       </c>
       <c r="E119">
         <v>1999</v>
@@ -24266,7 +24266,7 @@
         <v>49</v>
       </c>
       <c r="D121" t="s">
-        <v>59</v>
+        <v>83</v>
       </c>
       <c r="E121">
         <v>2010</v>
@@ -24319,7 +24319,7 @@
         <v>49</v>
       </c>
       <c r="D122" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="E122">
         <v>2003</v>
@@ -24372,7 +24372,7 @@
         <v>49</v>
       </c>
       <c r="D123" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="E123">
         <v>2003</v>
@@ -24425,7 +24425,7 @@
         <v>49</v>
       </c>
       <c r="D124" t="s">
-        <v>87</v>
+        <v>68</v>
       </c>
       <c r="E124">
         <v>2006</v>
@@ -24584,7 +24584,7 @@
         <v>49</v>
       </c>
       <c r="D127" t="s">
-        <v>69</v>
+        <v>56</v>
       </c>
       <c r="E127">
         <v>2002</v>
@@ -24637,7 +24637,7 @@
         <v>49</v>
       </c>
       <c r="D128" t="s">
-        <v>69</v>
+        <v>56</v>
       </c>
       <c r="E128">
         <v>2002</v>
@@ -24690,7 +24690,7 @@
         <v>49</v>
       </c>
       <c r="D129" t="s">
-        <v>59</v>
+        <v>83</v>
       </c>
       <c r="E129">
         <v>2010</v>
@@ -24743,7 +24743,7 @@
         <v>49</v>
       </c>
       <c r="D130" t="s">
-        <v>59</v>
+        <v>83</v>
       </c>
       <c r="E130">
         <v>2010</v>
@@ -24796,7 +24796,7 @@
         <v>49</v>
       </c>
       <c r="D131" t="s">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="E131">
         <v>2008</v>
@@ -24849,7 +24849,7 @@
         <v>49</v>
       </c>
       <c r="D132" t="s">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="E132">
         <v>2008</v>
@@ -24902,7 +24902,7 @@
         <v>49</v>
       </c>
       <c r="D133" t="s">
-        <v>84</v>
+        <v>53</v>
       </c>
       <c r="E133">
         <v>2018</v>
@@ -24955,7 +24955,7 @@
         <v>49</v>
       </c>
       <c r="D134" t="s">
-        <v>54</v>
+        <v>87</v>
       </c>
       <c r="E134">
         <v>2006</v>
@@ -25008,7 +25008,7 @@
         <v>49</v>
       </c>
       <c r="D135" t="s">
-        <v>54</v>
+        <v>87</v>
       </c>
       <c r="E135">
         <v>2007</v>
@@ -25273,7 +25273,7 @@
         <v>49</v>
       </c>
       <c r="D140" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
       <c r="E140">
         <v>2004</v>
@@ -25326,7 +25326,7 @@
         <v>49</v>
       </c>
       <c r="D141" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
       <c r="E141">
         <v>2004</v>
@@ -25379,7 +25379,7 @@
         <v>49</v>
       </c>
       <c r="D142" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="E142">
         <v>2008</v>
@@ -25432,7 +25432,7 @@
         <v>49</v>
       </c>
       <c r="D143" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="E143">
         <v>2007</v>
@@ -25485,7 +25485,7 @@
         <v>49</v>
       </c>
       <c r="D144" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="E144">
         <v>2007</v>
@@ -25538,7 +25538,7 @@
         <v>49</v>
       </c>
       <c r="D145" t="s">
-        <v>60</v>
+        <v>82</v>
       </c>
       <c r="E145">
         <v>2005</v>
@@ -25591,7 +25591,7 @@
         <v>49</v>
       </c>
       <c r="D146" t="s">
-        <v>60</v>
+        <v>82</v>
       </c>
       <c r="E146">
         <v>2005</v>
@@ -25644,7 +25644,7 @@
         <v>49</v>
       </c>
       <c r="D147" t="s">
-        <v>74</v>
+        <v>62</v>
       </c>
       <c r="E147">
         <v>2015</v>
@@ -25697,7 +25697,7 @@
         <v>49</v>
       </c>
       <c r="D148" t="s">
-        <v>74</v>
+        <v>62</v>
       </c>
       <c r="E148">
         <v>2004</v>
@@ -25750,7 +25750,7 @@
         <v>49</v>
       </c>
       <c r="D149" t="s">
-        <v>78</v>
+        <v>55</v>
       </c>
       <c r="E149">
         <v>2006</v>
@@ -25803,7 +25803,7 @@
         <v>49</v>
       </c>
       <c r="D150" t="s">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="E150">
         <v>2011</v>
@@ -25962,7 +25962,7 @@
         <v>49</v>
       </c>
       <c r="D153" t="s">
-        <v>51</v>
+        <v>67</v>
       </c>
       <c r="E153">
         <v>2006</v>
@@ -26015,7 +26015,7 @@
         <v>49</v>
       </c>
       <c r="D154" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="E154">
         <v>2008</v>
@@ -26068,7 +26068,7 @@
         <v>49</v>
       </c>
       <c r="D155" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="E155">
         <v>2007</v>
@@ -26174,7 +26174,7 @@
         <v>49</v>
       </c>
       <c r="D157" t="s">
-        <v>64</v>
+        <v>80</v>
       </c>
       <c r="E157">
         <v>2023</v>
@@ -26227,7 +26227,7 @@
         <v>49</v>
       </c>
       <c r="D158" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E158">
         <v>2026</v>
@@ -26280,7 +26280,7 @@
         <v>49</v>
       </c>
       <c r="D159" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="E159">
         <v>2022</v>
@@ -26333,7 +26333,7 @@
         <v>49</v>
       </c>
       <c r="D160" t="s">
-        <v>50</v>
+        <v>69</v>
       </c>
       <c r="E160">
         <v>2003</v>
@@ -26386,7 +26386,7 @@
         <v>49</v>
       </c>
       <c r="D161" t="s">
-        <v>50</v>
+        <v>69</v>
       </c>
       <c r="E161">
         <v>2003</v>
@@ -26439,7 +26439,7 @@
         <v>49</v>
       </c>
       <c r="D162" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="E162">
         <v>2003</v>
@@ -26492,7 +26492,7 @@
         <v>49</v>
       </c>
       <c r="D163" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="E163">
         <v>2008</v>
@@ -26545,7 +26545,7 @@
         <v>49</v>
       </c>
       <c r="D164" t="s">
-        <v>59</v>
+        <v>83</v>
       </c>
       <c r="E164">
         <v>1999</v>
@@ -26598,7 +26598,7 @@
         <v>49</v>
       </c>
       <c r="D165" t="s">
-        <v>59</v>
+        <v>83</v>
       </c>
       <c r="E165">
         <v>1999</v>
@@ -26651,7 +26651,7 @@
         <v>49</v>
       </c>
       <c r="D166" t="s">
-        <v>52</v>
+        <v>85</v>
       </c>
       <c r="E166">
         <v>1997</v>
@@ -26757,7 +26757,7 @@
         <v>49</v>
       </c>
       <c r="D168" t="s">
-        <v>83</v>
+        <v>52</v>
       </c>
       <c r="E168">
         <v>2001</v>
@@ -26810,7 +26810,7 @@
         <v>49</v>
       </c>
       <c r="D169" t="s">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="E169">
         <v>2006</v>
@@ -26916,7 +26916,7 @@
         <v>49</v>
       </c>
       <c r="D171" t="s">
-        <v>84</v>
+        <v>53</v>
       </c>
       <c r="E171">
         <v>2007</v>
@@ -27499,7 +27499,7 @@
         <v>49</v>
       </c>
       <c r="D182" t="s">
-        <v>52</v>
+        <v>85</v>
       </c>
       <c r="E182">
         <v>2015</v>
@@ -28294,7 +28294,7 @@
         <v>49</v>
       </c>
       <c r="D197" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="E197">
         <v>2004</v>
@@ -28347,7 +28347,7 @@
         <v>49</v>
       </c>
       <c r="D198" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="E198">
         <v>2008</v>
@@ -28559,7 +28559,7 @@
         <v>49</v>
       </c>
       <c r="D202" t="s">
-        <v>59</v>
+        <v>83</v>
       </c>
       <c r="E202">
         <v>2005</v>
@@ -28612,7 +28612,7 @@
         <v>49</v>
       </c>
       <c r="D203" t="s">
-        <v>59</v>
+        <v>83</v>
       </c>
       <c r="E203">
         <v>2015</v>
@@ -29301,7 +29301,7 @@
         <v>49</v>
       </c>
       <c r="D216" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E216">
         <v>2022</v>
@@ -29513,7 +29513,7 @@
         <v>49</v>
       </c>
       <c r="D220" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E220">
         <v>2009</v>
@@ -30202,7 +30202,7 @@
         <v>49</v>
       </c>
       <c r="D233" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
       <c r="E233">
         <v>1994</v>
@@ -30361,7 +30361,7 @@
         <v>49</v>
       </c>
       <c r="D236" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E236">
         <v>1990</v>
@@ -30414,7 +30414,7 @@
         <v>49</v>
       </c>
       <c r="D237" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E237">
         <v>2022</v>
@@ -30573,7 +30573,7 @@
         <v>49</v>
       </c>
       <c r="D240" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="E240">
         <v>2006</v>
@@ -30626,7 +30626,7 @@
         <v>49</v>
       </c>
       <c r="D241" t="s">
-        <v>60</v>
+        <v>82</v>
       </c>
       <c r="E241">
         <v>2024</v>
@@ -30679,7 +30679,7 @@
         <v>49</v>
       </c>
       <c r="D242" t="s">
-        <v>74</v>
+        <v>62</v>
       </c>
       <c r="E242">
         <v>2023</v>
@@ -30732,7 +30732,7 @@
         <v>49</v>
       </c>
       <c r="D243" t="s">
-        <v>74</v>
+        <v>62</v>
       </c>
       <c r="E243">
         <v>2023</v>
@@ -30785,7 +30785,7 @@
         <v>49</v>
       </c>
       <c r="D244" t="s">
-        <v>84</v>
+        <v>53</v>
       </c>
       <c r="E244">
         <v>1997</v>
@@ -31262,7 +31262,7 @@
         <v>49</v>
       </c>
       <c r="D253" t="s">
-        <v>75</v>
+        <v>63</v>
       </c>
       <c r="E253">
         <v>2008</v>
@@ -31527,7 +31527,7 @@
         <v>49</v>
       </c>
       <c r="D258" t="s">
-        <v>74</v>
+        <v>62</v>
       </c>
       <c r="E258">
         <v>2015</v>
@@ -31633,7 +31633,7 @@
         <v>49</v>
       </c>
       <c r="D260" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="E260">
         <v>2004</v>
@@ -31898,7 +31898,7 @@
         <v>49</v>
       </c>
       <c r="D265" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="E265">
         <v>2024</v>
@@ -32004,7 +32004,7 @@
         <v>49</v>
       </c>
       <c r="D267" t="s">
-        <v>78</v>
+        <v>55</v>
       </c>
       <c r="E267">
         <v>2023</v>
@@ -32216,7 +32216,7 @@
         <v>49</v>
       </c>
       <c r="D271" t="s">
-        <v>52</v>
+        <v>85</v>
       </c>
       <c r="E271">
         <v>1975</v>
@@ -32269,7 +32269,7 @@
         <v>49</v>
       </c>
       <c r="D272" t="s">
-        <v>52</v>
+        <v>85</v>
       </c>
       <c r="E272">
         <v>1975</v>
@@ -32322,7 +32322,7 @@
         <v>49</v>
       </c>
       <c r="D273" t="s">
-        <v>52</v>
+        <v>85</v>
       </c>
       <c r="E273">
         <v>1975</v>
@@ -32375,7 +32375,7 @@
         <v>49</v>
       </c>
       <c r="D274" t="s">
-        <v>55</v>
+        <v>79</v>
       </c>
       <c r="E274">
         <v>2015</v>
@@ -32428,7 +32428,7 @@
         <v>49</v>
       </c>
       <c r="D275" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E275">
         <v>1967</v>
@@ -32481,7 +32481,7 @@
         <v>49</v>
       </c>
       <c r="D276" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E276">
         <v>1971</v>
@@ -32534,7 +32534,7 @@
         <v>49</v>
       </c>
       <c r="D277" t="s">
-        <v>83</v>
+        <v>52</v>
       </c>
       <c r="E277">
         <v>1970</v>
@@ -32587,7 +32587,7 @@
         <v>49</v>
       </c>
       <c r="D278" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E278">
         <v>1978</v>
@@ -32640,7 +32640,7 @@
         <v>49</v>
       </c>
       <c r="D279" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E279">
         <v>1981</v>
@@ -32693,7 +32693,7 @@
         <v>49</v>
       </c>
       <c r="D280" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E280">
         <v>1987</v>
@@ -33117,7 +33117,7 @@
         <v>293</v>
       </c>
       <c r="D288" t="s">
-        <v>77</v>
+        <v>64</v>
       </c>
       <c r="E288">
         <v>1991</v>
@@ -33170,7 +33170,7 @@
         <v>293</v>
       </c>
       <c r="D289" t="s">
-        <v>77</v>
+        <v>64</v>
       </c>
       <c r="E289">
         <v>1991</v>
@@ -34230,13 +34230,13 @@
         <v>308</v>
       </c>
       <c r="D309" t="s">
-        <v>309</v>
+        <v>239</v>
       </c>
       <c r="E309">
         <v>2022</v>
       </c>
       <c r="F309">
-        <v>0.13036387865841995</v>
+        <v>0.22871669814448767</v>
       </c>
       <c r="G309">
         <v>1</v>
@@ -34283,13 +34283,13 @@
         <v>308</v>
       </c>
       <c r="D310" t="s">
-        <v>310</v>
+        <v>193</v>
       </c>
       <c r="E310">
         <v>2022</v>
       </c>
       <c r="F310">
-        <v>1.0883760118599757</v>
+        <v>0.61052976624370348</v>
       </c>
       <c r="G310">
         <v>1</v>
@@ -34336,25 +34336,25 @@
         <v>308</v>
       </c>
       <c r="D311" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="E311">
         <v>2022</v>
       </c>
       <c r="F311">
-        <v>0.15541601192373908</v>
+        <v>0.57944656385895543</v>
       </c>
       <c r="G311">
         <v>1</v>
       </c>
       <c r="H311">
-        <v>3162.5000000000005</v>
+        <v>2750</v>
       </c>
       <c r="I311">
-        <v>60.500000000000014</v>
+        <v>55.000000000000007</v>
       </c>
       <c r="J311">
-        <v>2.3100000000000005</v>
+        <v>2.1</v>
       </c>
       <c r="K311">
         <v>100</v>
@@ -34389,25 +34389,25 @@
         <v>308</v>
       </c>
       <c r="D312" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="E312">
         <v>2022</v>
       </c>
       <c r="F312">
-        <v>6.3558189950902247E-2</v>
+        <v>1.0883760118599757</v>
       </c>
       <c r="G312">
         <v>1</v>
       </c>
       <c r="H312">
-        <v>3162.5000000000005</v>
+        <v>2750</v>
       </c>
       <c r="I312">
-        <v>60.500000000000014</v>
+        <v>55.000000000000007</v>
       </c>
       <c r="J312">
-        <v>2.3100000000000005</v>
+        <v>2.1</v>
       </c>
       <c r="K312">
         <v>100</v>
@@ -34442,13 +34442,13 @@
         <v>308</v>
       </c>
       <c r="D313" t="s">
-        <v>204</v>
+        <v>311</v>
       </c>
       <c r="E313">
         <v>2022</v>
       </c>
       <c r="F313">
-        <v>7.8403898552572848E-2</v>
+        <v>6.0310691194286808E-2</v>
       </c>
       <c r="G313">
         <v>1</v>
@@ -34495,13 +34495,13 @@
         <v>308</v>
       </c>
       <c r="D314" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E314">
         <v>2022</v>
       </c>
       <c r="F314">
-        <v>6.0310691194286808E-2</v>
+        <v>5.8918906012880183E-2</v>
       </c>
       <c r="G314">
         <v>1</v>
@@ -34510,7 +34510,7 @@
         <v>3162.5000000000005</v>
       </c>
       <c r="I314">
-        <v>60.500000000000014</v>
+        <v>60.500000000000021</v>
       </c>
       <c r="J314">
         <v>2.3100000000000005</v>
@@ -34548,25 +34548,25 @@
         <v>308</v>
       </c>
       <c r="D315" t="s">
-        <v>193</v>
+        <v>313</v>
       </c>
       <c r="E315">
         <v>2022</v>
       </c>
       <c r="F315">
-        <v>0.61052976624370348</v>
+        <v>0.15541601192373908</v>
       </c>
       <c r="G315">
         <v>1</v>
       </c>
       <c r="H315">
-        <v>2750</v>
+        <v>3162.5000000000005</v>
       </c>
       <c r="I315">
-        <v>55.000000000000007</v>
+        <v>60.500000000000014</v>
       </c>
       <c r="J315">
-        <v>2.1</v>
+        <v>2.3100000000000005</v>
       </c>
       <c r="K315">
         <v>100</v>
@@ -34601,13 +34601,13 @@
         <v>308</v>
       </c>
       <c r="D316" t="s">
-        <v>314</v>
+        <v>204</v>
       </c>
       <c r="E316">
         <v>2022</v>
       </c>
       <c r="F316">
-        <v>0.1577356538927501</v>
+        <v>7.8403898552572848E-2</v>
       </c>
       <c r="G316">
         <v>1</v>
@@ -34654,13 +34654,13 @@
         <v>308</v>
       </c>
       <c r="D317" t="s">
-        <v>99</v>
+        <v>314</v>
       </c>
       <c r="E317">
         <v>2022</v>
       </c>
       <c r="F317">
-        <v>0.29181095970158766</v>
+        <v>0.19299421182171778</v>
       </c>
       <c r="G317">
         <v>1</v>
@@ -34760,25 +34760,25 @@
         <v>308</v>
       </c>
       <c r="D319" t="s">
-        <v>316</v>
+        <v>15</v>
       </c>
       <c r="E319">
         <v>2022</v>
       </c>
       <c r="F319">
-        <v>0.35629700644009438</v>
+        <v>0.11134281451252948</v>
       </c>
       <c r="G319">
         <v>1</v>
       </c>
       <c r="H319">
-        <v>2750</v>
+        <v>3162.5000000000005</v>
       </c>
       <c r="I319">
-        <v>55</v>
+        <v>60.500000000000014</v>
       </c>
       <c r="J319">
-        <v>2.1</v>
+        <v>2.3100000000000005</v>
       </c>
       <c r="K319">
         <v>100</v>
@@ -34813,13 +34813,13 @@
         <v>308</v>
       </c>
       <c r="D320" t="s">
-        <v>75</v>
+        <v>21</v>
       </c>
       <c r="E320">
         <v>2022</v>
       </c>
       <c r="F320">
-        <v>5.4743550468660328E-2</v>
+        <v>8.7682466428616976E-2</v>
       </c>
       <c r="G320">
         <v>1</v>
@@ -34828,7 +34828,7 @@
         <v>3162.5000000000005</v>
       </c>
       <c r="I320">
-        <v>60.500000000000014</v>
+        <v>60.500000000000007</v>
       </c>
       <c r="J320">
         <v>2.3100000000000005</v>
@@ -34866,13 +34866,13 @@
         <v>308</v>
       </c>
       <c r="D321" t="s">
-        <v>239</v>
+        <v>316</v>
       </c>
       <c r="E321">
         <v>2022</v>
       </c>
       <c r="F321">
-        <v>0.22871669814448767</v>
+        <v>5.1032123318242681E-2</v>
       </c>
       <c r="G321">
         <v>1</v>
@@ -34881,7 +34881,7 @@
         <v>3162.5000000000005</v>
       </c>
       <c r="I321">
-        <v>60.500000000000014</v>
+        <v>60.500000000000021</v>
       </c>
       <c r="J321">
         <v>2.3100000000000005</v>
@@ -34925,7 +34925,7 @@
         <v>2022</v>
       </c>
       <c r="F322">
-        <v>4.1753555442198553E-2</v>
+        <v>4.4073197411209589E-2</v>
       </c>
       <c r="G322">
         <v>1</v>
@@ -34972,13 +34972,13 @@
         <v>308</v>
       </c>
       <c r="D323" t="s">
-        <v>59</v>
+        <v>318</v>
       </c>
       <c r="E323">
         <v>2022</v>
       </c>
       <c r="F323">
-        <v>0.23196419690110309</v>
+        <v>0.1577356538927501</v>
       </c>
       <c r="G323">
         <v>1</v>
@@ -35025,13 +35025,13 @@
         <v>308</v>
       </c>
       <c r="D324" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="E324">
         <v>2022</v>
       </c>
       <c r="F324">
-        <v>0.56367299846968055</v>
+        <v>0.35629700644009438</v>
       </c>
       <c r="G324">
         <v>1</v>
@@ -35040,7 +35040,7 @@
         <v>2750</v>
       </c>
       <c r="I324">
-        <v>55.000000000000007</v>
+        <v>55</v>
       </c>
       <c r="J324">
         <v>2.1</v>
@@ -35078,13 +35078,13 @@
         <v>308</v>
       </c>
       <c r="D325" t="s">
-        <v>18</v>
+        <v>320</v>
       </c>
       <c r="E325">
         <v>2022</v>
       </c>
       <c r="F325">
-        <v>0.11134281451252948</v>
+        <v>6.3558189950902247E-2</v>
       </c>
       <c r="G325">
         <v>1</v>
@@ -35131,7 +35131,7 @@
         <v>308</v>
       </c>
       <c r="D326" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="E326">
         <v>2022</v>
@@ -35184,13 +35184,13 @@
         <v>308</v>
       </c>
       <c r="D327" t="s">
-        <v>320</v>
+        <v>63</v>
       </c>
       <c r="E327">
         <v>2022</v>
       </c>
       <c r="F327">
-        <v>0.19299421182171778</v>
+        <v>5.4743550468660328E-2</v>
       </c>
       <c r="G327">
         <v>1</v>
@@ -35237,7 +35237,7 @@
         <v>308</v>
       </c>
       <c r="D328" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="E328">
         <v>2022</v>
@@ -35290,7 +35290,7 @@
         <v>308</v>
       </c>
       <c r="D329" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="E329">
         <v>2022</v>
@@ -35343,7 +35343,7 @@
         <v>308</v>
       </c>
       <c r="D330" t="s">
-        <v>64</v>
+        <v>80</v>
       </c>
       <c r="E330">
         <v>2022</v>
@@ -35396,7 +35396,7 @@
         <v>308</v>
       </c>
       <c r="D331" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="E331">
         <v>2022</v>
@@ -35449,13 +35449,13 @@
         <v>308</v>
       </c>
       <c r="D332" t="s">
-        <v>324</v>
+        <v>83</v>
       </c>
       <c r="E332">
         <v>2022</v>
       </c>
       <c r="F332">
-        <v>0.20320063648536632</v>
+        <v>0.23196419690110309</v>
       </c>
       <c r="G332">
         <v>1</v>
@@ -35508,7 +35508,7 @@
         <v>2022</v>
       </c>
       <c r="F333">
-        <v>4.4073197411209589E-2</v>
+        <v>4.1753555442198553E-2</v>
       </c>
       <c r="G333">
         <v>1</v>
@@ -35561,19 +35561,19 @@
         <v>2022</v>
       </c>
       <c r="F334">
-        <v>0.57944656385895543</v>
+        <v>0.13036387865841995</v>
       </c>
       <c r="G334">
         <v>1</v>
       </c>
       <c r="H334">
-        <v>2750</v>
+        <v>3162.5000000000005</v>
       </c>
       <c r="I334">
-        <v>55.000000000000007</v>
+        <v>60.500000000000014</v>
       </c>
       <c r="J334">
-        <v>2.1</v>
+        <v>2.3100000000000005</v>
       </c>
       <c r="K334">
         <v>100</v>
@@ -35714,13 +35714,13 @@
         <v>308</v>
       </c>
       <c r="D337" t="s">
-        <v>327</v>
+        <v>99</v>
       </c>
       <c r="E337">
         <v>2022</v>
       </c>
       <c r="F337">
-        <v>5.8918906012880183E-2</v>
+        <v>0.29181095970158766</v>
       </c>
       <c r="G337">
         <v>1</v>
@@ -35729,7 +35729,7 @@
         <v>3162.5000000000005</v>
       </c>
       <c r="I337">
-        <v>60.500000000000021</v>
+        <v>60.500000000000014</v>
       </c>
       <c r="J337">
         <v>2.3100000000000005</v>
@@ -35767,7 +35767,7 @@
         <v>308</v>
       </c>
       <c r="D338" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="E338">
         <v>2022</v>
@@ -35820,25 +35820,25 @@
         <v>308</v>
       </c>
       <c r="D339" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="E339">
         <v>2022</v>
       </c>
       <c r="F339">
-        <v>5.1032123318242681E-2</v>
+        <v>0.56367299846968055</v>
       </c>
       <c r="G339">
         <v>1</v>
       </c>
       <c r="H339">
-        <v>3162.5000000000005</v>
+        <v>2750</v>
       </c>
       <c r="I339">
-        <v>60.500000000000021</v>
+        <v>55.000000000000007</v>
       </c>
       <c r="J339">
-        <v>2.3100000000000005</v>
+        <v>2.1</v>
       </c>
       <c r="K339">
         <v>100</v>
@@ -35873,13 +35873,13 @@
         <v>308</v>
       </c>
       <c r="D340" t="s">
-        <v>14</v>
+        <v>329</v>
       </c>
       <c r="E340">
         <v>2022</v>
       </c>
       <c r="F340">
-        <v>8.7682466428616976E-2</v>
+        <v>0.20320063648536632</v>
       </c>
       <c r="G340">
         <v>1</v>
@@ -35888,7 +35888,7 @@
         <v>3162.5000000000005</v>
       </c>
       <c r="I340">
-        <v>60.500000000000007</v>
+        <v>60.500000000000014</v>
       </c>
       <c r="J340">
         <v>2.3100000000000005</v>
@@ -35979,7 +35979,7 @@
         <v>308</v>
       </c>
       <c r="D342" t="s">
-        <v>325</v>
+        <v>317</v>
       </c>
       <c r="E342">
         <v>1959</v>
@@ -36085,7 +36085,7 @@
         <v>308</v>
       </c>
       <c r="D344" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="E344">
         <v>1973</v>
@@ -36244,7 +36244,7 @@
         <v>308</v>
       </c>
       <c r="D347" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="E347">
         <v>2015</v>
@@ -36297,7 +36297,7 @@
         <v>308</v>
       </c>
       <c r="D348" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="E348">
         <v>1931</v>
@@ -36350,7 +36350,7 @@
         <v>308</v>
       </c>
       <c r="D349" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="E349">
         <v>1949</v>
@@ -36403,7 +36403,7 @@
         <v>308</v>
       </c>
       <c r="D350" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="E350">
         <v>1951</v>
@@ -36509,7 +36509,7 @@
         <v>308</v>
       </c>
       <c r="D352" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="E352">
         <v>1958</v>
@@ -36562,7 +36562,7 @@
         <v>308</v>
       </c>
       <c r="D353" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="E353">
         <v>1967</v>
@@ -36615,7 +36615,7 @@
         <v>308</v>
       </c>
       <c r="D354" t="s">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="E354">
         <v>1968</v>
@@ -36668,7 +36668,7 @@
         <v>308</v>
       </c>
       <c r="D355" t="s">
-        <v>318</v>
+        <v>328</v>
       </c>
       <c r="E355">
         <v>1929</v>
@@ -36721,7 +36721,7 @@
         <v>308</v>
       </c>
       <c r="D356" t="s">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="E356">
         <v>1949</v>
@@ -36827,7 +36827,7 @@
         <v>308</v>
       </c>
       <c r="D358" t="s">
-        <v>75</v>
+        <v>63</v>
       </c>
       <c r="E358">
         <v>1952</v>
@@ -36880,7 +36880,7 @@
         <v>308</v>
       </c>
       <c r="D359" t="s">
-        <v>318</v>
+        <v>328</v>
       </c>
       <c r="E359">
         <v>1913</v>
@@ -36933,7 +36933,7 @@
         <v>308</v>
       </c>
       <c r="D360" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="E360">
         <v>1924</v>
@@ -37039,7 +37039,7 @@
         <v>308</v>
       </c>
       <c r="D362" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="E362">
         <v>1971</v>
@@ -37145,7 +37145,7 @@
         <v>308</v>
       </c>
       <c r="D364" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="E364">
         <v>1927</v>
@@ -37357,7 +37357,7 @@
         <v>308</v>
       </c>
       <c r="D368" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="E368">
         <v>1920</v>
@@ -37463,7 +37463,7 @@
         <v>308</v>
       </c>
       <c r="D370" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="E370">
         <v>1950</v>
@@ -37516,7 +37516,7 @@
         <v>308</v>
       </c>
       <c r="D371" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="E371">
         <v>1954</v>
@@ -37622,7 +37622,7 @@
         <v>308</v>
       </c>
       <c r="D373" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="E373">
         <v>1971</v>
@@ -37675,7 +37675,7 @@
         <v>308</v>
       </c>
       <c r="D374" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="E374">
         <v>1959</v>
@@ -38099,7 +38099,7 @@
         <v>308</v>
       </c>
       <c r="D382" t="s">
-        <v>67</v>
+        <v>78</v>
       </c>
       <c r="E382">
         <v>2022</v>
@@ -38311,7 +38311,7 @@
         <v>308</v>
       </c>
       <c r="D386" t="s">
-        <v>74</v>
+        <v>62</v>
       </c>
       <c r="E386">
         <v>2022</v>
@@ -38417,7 +38417,7 @@
         <v>383</v>
       </c>
       <c r="D388" t="s">
-        <v>59</v>
+        <v>83</v>
       </c>
       <c r="E388">
         <v>1989</v>
@@ -38470,7 +38470,7 @@
         <v>383</v>
       </c>
       <c r="D389" t="s">
-        <v>309</v>
+        <v>326</v>
       </c>
       <c r="E389">
         <v>1975</v>
@@ -38523,7 +38523,7 @@
         <v>383</v>
       </c>
       <c r="D390" t="s">
-        <v>64</v>
+        <v>80</v>
       </c>
       <c r="E390">
         <v>1966</v>
@@ -38629,7 +38629,7 @@
         <v>383</v>
       </c>
       <c r="D392" t="s">
-        <v>326</v>
+        <v>309</v>
       </c>
       <c r="E392">
         <v>2015</v>
@@ -38682,7 +38682,7 @@
         <v>383</v>
       </c>
       <c r="D393" t="s">
-        <v>326</v>
+        <v>309</v>
       </c>
       <c r="E393">
         <v>1982</v>
@@ -38735,7 +38735,7 @@
         <v>383</v>
       </c>
       <c r="D394" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="E394">
         <v>2015</v>
@@ -38788,7 +38788,7 @@
         <v>383</v>
       </c>
       <c r="D395" t="s">
-        <v>312</v>
+        <v>320</v>
       </c>
       <c r="E395">
         <v>2015</v>
@@ -38841,7 +38841,7 @@
         <v>383</v>
       </c>
       <c r="D396" t="s">
-        <v>74</v>
+        <v>62</v>
       </c>
       <c r="E396">
         <v>1961</v>
@@ -38947,7 +38947,7 @@
         <v>383</v>
       </c>
       <c r="D398" t="s">
-        <v>64</v>
+        <v>80</v>
       </c>
       <c r="E398">
         <v>1991</v>
@@ -39106,7 +39106,7 @@
         <v>383</v>
       </c>
       <c r="D401" t="s">
-        <v>318</v>
+        <v>328</v>
       </c>
       <c r="E401">
         <v>1971</v>
@@ -39159,7 +39159,7 @@
         <v>383</v>
       </c>
       <c r="D402" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="E402">
         <v>1973</v>
@@ -39318,7 +39318,7 @@
         <v>383</v>
       </c>
       <c r="D405" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E405">
         <v>1978</v>
@@ -39371,7 +39371,7 @@
         <v>383</v>
       </c>
       <c r="D406" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="E406">
         <v>1923</v>
@@ -39424,7 +39424,7 @@
         <v>308</v>
       </c>
       <c r="D407" t="s">
-        <v>327</v>
+        <v>312</v>
       </c>
       <c r="E407">
         <v>1959</v>
@@ -39583,7 +39583,7 @@
         <v>308</v>
       </c>
       <c r="D410" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="E410">
         <v>1953</v>
@@ -39742,7 +39742,7 @@
         <v>308</v>
       </c>
       <c r="D413" t="s">
-        <v>317</v>
+        <v>325</v>
       </c>
       <c r="E413">
         <v>1962</v>
@@ -39795,7 +39795,7 @@
         <v>308</v>
       </c>
       <c r="D414" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="E414">
         <v>2015</v>
@@ -39848,7 +39848,7 @@
         <v>308</v>
       </c>
       <c r="D415" t="s">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="E415">
         <v>1927</v>
@@ -39901,7 +39901,7 @@
         <v>308</v>
       </c>
       <c r="D416" t="s">
-        <v>329</v>
+        <v>316</v>
       </c>
       <c r="E416">
         <v>1954</v>
@@ -40007,7 +40007,7 @@
         <v>308</v>
       </c>
       <c r="D418" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="E418">
         <v>1956</v>
@@ -40060,7 +40060,7 @@
         <v>308</v>
       </c>
       <c r="D419" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="E419">
         <v>1956</v>
@@ -40166,7 +40166,7 @@
         <v>308</v>
       </c>
       <c r="D421" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="E421">
         <v>1960</v>
@@ -40272,7 +40272,7 @@
         <v>308</v>
       </c>
       <c r="D423" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="E423">
         <v>2015</v>
@@ -40378,7 +40378,7 @@
         <v>308</v>
       </c>
       <c r="D425" t="s">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="E425">
         <v>2015</v>
@@ -40431,7 +40431,7 @@
         <v>308</v>
       </c>
       <c r="D426" t="s">
-        <v>326</v>
+        <v>309</v>
       </c>
       <c r="E426">
         <v>2015</v>
@@ -40537,7 +40537,7 @@
         <v>308</v>
       </c>
       <c r="D428" t="s">
-        <v>67</v>
+        <v>78</v>
       </c>
       <c r="E428">
         <v>1955</v>
@@ -40590,7 +40590,7 @@
         <v>308</v>
       </c>
       <c r="D429" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="E429">
         <v>2015</v>
@@ -40696,7 +40696,7 @@
         <v>308</v>
       </c>
       <c r="D431" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="E431">
         <v>1932</v>
@@ -40855,7 +40855,7 @@
         <v>308</v>
       </c>
       <c r="D434" t="s">
-        <v>318</v>
+        <v>328</v>
       </c>
       <c r="E434">
         <v>1924</v>
@@ -40961,7 +40961,7 @@
         <v>308</v>
       </c>
       <c r="D436" t="s">
-        <v>318</v>
+        <v>328</v>
       </c>
       <c r="E436">
         <v>2002</v>
@@ -41120,7 +41120,7 @@
         <v>308</v>
       </c>
       <c r="D439" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="E439">
         <v>2015</v>
@@ -41173,7 +41173,7 @@
         <v>308</v>
       </c>
       <c r="D440" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="E440">
         <v>1914</v>
@@ -41279,7 +41279,7 @@
         <v>308</v>
       </c>
       <c r="D442" t="s">
-        <v>75</v>
+        <v>63</v>
       </c>
       <c r="E442">
         <v>1958</v>
@@ -41332,7 +41332,7 @@
         <v>439</v>
       </c>
       <c r="D443" t="s">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="E443">
         <v>1992</v>
@@ -41544,7 +41544,7 @@
         <v>439</v>
       </c>
       <c r="D447" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E447">
         <v>2005</v>
@@ -41809,7 +41809,7 @@
         <v>439</v>
       </c>
       <c r="D452" t="s">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="E452">
         <v>1985</v>
@@ -42067,7 +42067,7 @@
         <v>33</v>
       </c>
       <c r="L458">
-        <v>0.21124146529555185</v>
+        <v>0.21124146529555179</v>
       </c>
     </row>
     <row r="459" spans="2:20" x14ac:dyDescent="0.45">
@@ -42102,7 +42102,7 @@
         <v>33</v>
       </c>
       <c r="L459">
-        <v>0.21124146529555185</v>
+        <v>0.21124146529555179</v>
       </c>
     </row>
     <row r="460" spans="2:20" x14ac:dyDescent="0.45">
@@ -42137,7 +42137,7 @@
         <v>33</v>
       </c>
       <c r="L460">
-        <v>0.21124146529555185</v>
+        <v>0.21124146529555179</v>
       </c>
     </row>
     <row r="461" spans="2:20" x14ac:dyDescent="0.45">
@@ -44808,7 +44808,7 @@
         <v>510</v>
       </c>
       <c r="D537" t="s">
-        <v>52</v>
+        <v>85</v>
       </c>
       <c r="E537">
         <v>2022</v>
@@ -44843,7 +44843,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="L538">
-        <v>0.20228807173042845</v>
+        <v>0.2022880717304284</v>
       </c>
     </row>
     <row r="539" spans="2:12" x14ac:dyDescent="0.45">
@@ -44866,7 +44866,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="L539">
-        <v>0.20228807173042845</v>
+        <v>0.2022880717304284</v>
       </c>
     </row>
     <row r="540" spans="2:12" x14ac:dyDescent="0.45">
@@ -44889,7 +44889,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="L540">
-        <v>0.20228807173042845</v>
+        <v>0.2022880717304284</v>
       </c>
     </row>
     <row r="541" spans="2:12" x14ac:dyDescent="0.45">

--- a/VerveStacks_ITA_grids/vt_vervestacks_ITA_v1.xlsx
+++ b/VerveStacks_ITA_grids/vt_vervestacks_ITA_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{61CC0EA6-F78B-49D9-9FAF-B2EA0424AF33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9F73EAAA-FE79-49E3-A711-F2F9897927A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{B802FF8B-77F1-4651-A8F1-26C528872C0D}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{E0B7694D-DB59-4098-A227-472B6444F75D}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="2" r:id="rId1"/>
@@ -81,30 +81,30 @@
     <t>bioenergy</t>
   </si>
   <si>
+    <t>e_w108020416-380</t>
+  </si>
+  <si>
     <t>e_w34157795-380</t>
   </si>
   <si>
     <t>e_w144005863-380</t>
   </si>
   <si>
+    <t>e_w109756016-380</t>
+  </si>
+  <si>
+    <t>e_w84696559-380</t>
+  </si>
+  <si>
+    <t>e_w58440884-380</t>
+  </si>
+  <si>
     <t>e_w98902899-380</t>
   </si>
   <si>
     <t>e_w81938081-380</t>
   </si>
   <si>
-    <t>e_w84696559-380</t>
-  </si>
-  <si>
-    <t>e_w58440884-380</t>
-  </si>
-  <si>
-    <t>e_w109756016-380</t>
-  </si>
-  <si>
-    <t>e_w108020416-380</t>
-  </si>
-  <si>
     <t>ep_bioenergy_G100000200236</t>
   </si>
   <si>
@@ -144,15 +144,15 @@
     <t>e_w409439916-380</t>
   </si>
   <si>
+    <t>e_w303915533-380</t>
+  </si>
+  <si>
+    <t>e_w82767145-380</t>
+  </si>
+  <si>
     <t>e_w418902800-380</t>
   </si>
   <si>
-    <t>e_w303915533-380</t>
-  </si>
-  <si>
-    <t>e_w82767145-380</t>
-  </si>
-  <si>
     <t>ep_coal_subcritical_G100000102764</t>
   </si>
   <si>
@@ -189,120 +189,120 @@
     <t>gas</t>
   </si>
   <si>
+    <t>e_w110330925-380</t>
+  </si>
+  <si>
+    <t>e_w162828577-380</t>
+  </si>
+  <si>
+    <t>e_w98900549-380</t>
+  </si>
+  <si>
+    <t>e_w82084019-380</t>
+  </si>
+  <si>
+    <t>e_w107438024-380</t>
+  </si>
+  <si>
+    <t>e_w82078641-380</t>
+  </si>
+  <si>
+    <t>e_w61157826-380</t>
+  </si>
+  <si>
+    <t>e_w1137611914-380</t>
+  </si>
+  <si>
+    <t>e_w338753171-380</t>
+  </si>
+  <si>
+    <t>e_w162960205-380</t>
+  </si>
+  <si>
+    <t>e_w181125039-380</t>
+  </si>
+  <si>
     <t>e_w133601335-380</t>
   </si>
   <si>
+    <t>e_w103381531-380</t>
+  </si>
+  <si>
+    <t>e_w411026199-380</t>
+  </si>
+  <si>
+    <t>e_w432729521-380</t>
+  </si>
+  <si>
+    <t>e_w172302572-380</t>
+  </si>
+  <si>
+    <t>e_w109993642-380</t>
+  </si>
+  <si>
+    <t>e_w103653592-380</t>
+  </si>
+  <si>
+    <t>e_w339104227-380</t>
+  </si>
+  <si>
+    <t>e_w59462715-380</t>
+  </si>
+  <si>
+    <t>e_w421827453-380</t>
+  </si>
+  <si>
+    <t>e_w149997403-380</t>
+  </si>
+  <si>
+    <t>e_w100407576-380</t>
+  </si>
+  <si>
+    <t>e_w416989699-380</t>
+  </si>
+  <si>
+    <t>e_w199675964-380</t>
+  </si>
+  <si>
+    <t>e_w414663585-380</t>
+  </si>
+  <si>
+    <t>e_w255011550-380</t>
+  </si>
+  <si>
     <t>e_w105581403-380</t>
   </si>
   <si>
-    <t>e_w255011550-380</t>
-  </si>
-  <si>
-    <t>e_w414663585-380</t>
-  </si>
-  <si>
-    <t>e_w107438024-380</t>
-  </si>
-  <si>
-    <t>e_w411026199-380</t>
-  </si>
-  <si>
     <t>e_w158739183-380</t>
   </si>
   <si>
+    <t>e_w99826025-380</t>
+  </si>
+  <si>
+    <t>e_w145665799-380</t>
+  </si>
+  <si>
+    <t>e_w60725875-380</t>
+  </si>
+  <si>
+    <t>e_w116797658-380</t>
+  </si>
+  <si>
+    <t>e_w419423704-380</t>
+  </si>
+  <si>
+    <t>e_w98421779-380</t>
+  </si>
+  <si>
+    <t>e_w105757794-380</t>
+  </si>
+  <si>
     <t>e_w103974940-380</t>
   </si>
   <si>
-    <t>e_w60725875-380</t>
-  </si>
-  <si>
-    <t>e_w145665799-380</t>
-  </si>
-  <si>
-    <t>e_w339104227-380</t>
-  </si>
-  <si>
-    <t>e_w82078641-380</t>
-  </si>
-  <si>
-    <t>e_w61157826-380</t>
-  </si>
-  <si>
-    <t>e_w1137611914-380</t>
-  </si>
-  <si>
-    <t>e_w416989699-380</t>
-  </si>
-  <si>
-    <t>e_w432729521-380</t>
-  </si>
-  <si>
-    <t>e_w172302572-380</t>
-  </si>
-  <si>
-    <t>e_w59462715-380</t>
-  </si>
-  <si>
-    <t>e_w421827453-380</t>
-  </si>
-  <si>
-    <t>e_w149997403-380</t>
-  </si>
-  <si>
-    <t>e_w100407576-380</t>
-  </si>
-  <si>
-    <t>e_w109993642-380</t>
-  </si>
-  <si>
-    <t>e_w103653592-380</t>
-  </si>
-  <si>
-    <t>e_w99826025-380</t>
-  </si>
-  <si>
-    <t>e_w82084019-380</t>
-  </si>
-  <si>
-    <t>e_w98900549-380</t>
-  </si>
-  <si>
-    <t>e_w162828577-380</t>
-  </si>
-  <si>
     <t>e_w132450233-380</t>
   </si>
   <si>
-    <t>e_w110330925-380</t>
-  </si>
-  <si>
-    <t>e_w116797658-380</t>
-  </si>
-  <si>
-    <t>e_w419423704-380</t>
-  </si>
-  <si>
-    <t>e_w98421779-380</t>
-  </si>
-  <si>
-    <t>e_w162960205-380</t>
-  </si>
-  <si>
-    <t>e_w338753171-380</t>
-  </si>
-  <si>
-    <t>e_w199675964-380</t>
-  </si>
-  <si>
-    <t>e_w103381531-380</t>
-  </si>
-  <si>
-    <t>e_w105757794-380</t>
-  </si>
-  <si>
-    <t>e_w181125039-380</t>
-  </si>
-  <si>
     <t>ep_gas_combined_cycle_G100000400339</t>
   </si>
   <si>
@@ -966,69 +966,69 @@
     <t>hydro</t>
   </si>
   <si>
+    <t>e_IT72-400</t>
+  </si>
+  <si>
+    <t>e_w64200868-380</t>
+  </si>
+  <si>
+    <t>e_IT53-380</t>
+  </si>
+  <si>
+    <t>e_IT93-380</t>
+  </si>
+  <si>
+    <t>e_w491424937-380</t>
+  </si>
+  <si>
+    <t>e_w75602396-380</t>
+  </si>
+  <si>
+    <t>e_IT21-380</t>
+  </si>
+  <si>
+    <t>e_w1100665914-380</t>
+  </si>
+  <si>
+    <t>e_w82083756-380</t>
+  </si>
+  <si>
+    <t>e_IT71-400</t>
+  </si>
+  <si>
+    <t>e_IT10-380</t>
+  </si>
+  <si>
+    <t>e_IT72-380</t>
+  </si>
+  <si>
+    <t>e_w61626687-380</t>
+  </si>
+  <si>
+    <t>e_IT71-380</t>
+  </si>
+  <si>
+    <t>e_w114931087-380</t>
+  </si>
+  <si>
+    <t>e_IT31-380</t>
+  </si>
+  <si>
     <t>e_w104359058-380</t>
   </si>
   <si>
-    <t>e_w64200868-380</t>
-  </si>
-  <si>
-    <t>e_IT71-400</t>
-  </si>
-  <si>
-    <t>e_IT71-380</t>
+    <t>e_w116517585-380</t>
   </si>
   <si>
     <t>e_IT36-380</t>
   </si>
   <si>
-    <t>e_w1100665914-380</t>
-  </si>
-  <si>
-    <t>e_IT93-380</t>
-  </si>
-  <si>
-    <t>e_w61626687-380</t>
-  </si>
-  <si>
-    <t>e_IT31-380</t>
+    <t>e_IT7-380</t>
   </si>
   <si>
     <t>e_w72466334-380</t>
   </si>
   <si>
-    <t>e_w82083756-380</t>
-  </si>
-  <si>
-    <t>e_IT53-380</t>
-  </si>
-  <si>
-    <t>e_IT7-380</t>
-  </si>
-  <si>
-    <t>e_w75602396-380</t>
-  </si>
-  <si>
-    <t>e_w491424937-380</t>
-  </si>
-  <si>
-    <t>e_IT72-400</t>
-  </si>
-  <si>
-    <t>e_w116517585-380</t>
-  </si>
-  <si>
-    <t>e_w114931087-380</t>
-  </si>
-  <si>
-    <t>e_IT72-380</t>
-  </si>
-  <si>
-    <t>e_IT21-380</t>
-  </si>
-  <si>
-    <t>e_IT10-380</t>
-  </si>
-  <si>
     <t>ep_hydro_dam_G100000602220</t>
   </si>
   <si>
@@ -1578,12 +1578,12 @@
     <t>windon</t>
   </si>
   <si>
+    <t>elc_won_008</t>
+  </si>
+  <si>
     <t>elc_won_007</t>
   </si>
   <si>
-    <t>elc_won_008</t>
-  </si>
-  <si>
     <t>ep_windon_wind_007</t>
   </si>
   <si>
@@ -1680,42 +1680,42 @@
     <t>ele</t>
   </si>
   <si>
+    <t>Aggregated Plant - EMBER Gap - way/108020416-380_Missing Bioenergy Capacity</t>
+  </si>
+  <si>
+    <t>GW</t>
+  </si>
+  <si>
+    <t>TWh</t>
+  </si>
+  <si>
+    <t>daynite</t>
+  </si>
+  <si>
+    <t>yes</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/34157795-380_Missing Bioenergy Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/58440884-380_Missing Bioenergy Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/98902899-380_Missing Bioenergy Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/109756016-380_Missing Bioenergy Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/144005863-380_Missing Bioenergy Capacity</t>
+  </si>
+  <si>
     <t>Aggregated Plant - EMBER Gap - way/81938081-380_Missing Bioenergy Capacity</t>
   </si>
   <si>
-    <t>GW</t>
-  </si>
-  <si>
-    <t>TWh</t>
-  </si>
-  <si>
-    <t>daynite</t>
-  </si>
-  <si>
-    <t>yes</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/98902899-380_Missing Bioenergy Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/144005863-380_Missing Bioenergy Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/109756016-380_Missing Bioenergy Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/108020416-380_Missing Bioenergy Capacity</t>
-  </si>
-  <si>
     <t>Aggregated Plant - EMBER Gap - way/84696559-380_Missing Bioenergy Capacity</t>
   </si>
   <si>
-    <t>Aggregated Plant - EMBER Gap - way/58440884-380_Missing Bioenergy Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/34157795-380_Missing Bioenergy Capacity</t>
-  </si>
-  <si>
     <t>Acerra power station_1</t>
   </si>
   <si>
@@ -1737,15 +1737,15 @@
     <t>Aggregated Plant</t>
   </si>
   <si>
+    <t>Aggregated Plant - EMBER Gap - way/409439916-380_Missing Coal Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/303915533-380_Missing Coal Capacity</t>
+  </si>
+  <si>
     <t>Aggregated Plant - EMBER Gap - way/82767145-380_Missing Coal Capacity</t>
   </si>
   <si>
-    <t>Aggregated Plant - EMBER Gap - way/303915533-380_Missing Coal Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/409439916-380_Missing Coal Capacity</t>
-  </si>
-  <si>
     <t>Aggregated Plant - EMBER Gap - way/418902800-380_Missing Coal Capacity</t>
   </si>
   <si>
@@ -1779,55 +1779,106 @@
     <t>Torrevaldaliga Nord power station_Unit 3</t>
   </si>
   <si>
+    <t>Aggregated Plant - EMBER Gap - way/162828577-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/107438024-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/116797658-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/339104227-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/419423704-380_Missing Gas Capacity</t>
+  </si>
+  <si>
     <t>Aggregated Plant - EMBER Gap - way/414663585-380_Missing Gas Capacity</t>
   </si>
   <si>
-    <t>Aggregated Plant - EMBER Gap - way/419423704-380_Missing Gas Capacity</t>
-  </si>
-  <si>
     <t>Aggregated Plant - EMBER Gap - way/61157826-380_Missing Gas Capacity</t>
   </si>
   <si>
+    <t>Aggregated Plant - EMBER Gap - way/59462715-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/172302572-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/255011550-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/105757794-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/149997403-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/133601335-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/162960205-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/145665799-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/158739183-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/1137611914-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/60725875-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/181125039-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/432729521-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/199675964-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/100407576-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/109993642-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/98900549-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/338753171-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/103381531-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/411026199-380_Missing Gas Capacity</t>
+  </si>
+  <si>
     <t>Aggregated Plant - EMBER Gap - way/98421779-380_Missing Gas Capacity</t>
   </si>
   <si>
+    <t>Aggregated Plant - EMBER Gap - way/105581403-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/109756016-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/82084019-380_Missing Gas Capacity</t>
+  </si>
+  <si>
     <t>Aggregated Plant - EMBER Gap - way/110330925-380_Missing Gas Capacity</t>
   </si>
   <si>
-    <t>Aggregated Plant - EMBER Gap - way/82084019-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/109756016-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/411026199-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/105581403-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/107438024-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/116797658-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/339104227-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/103381531-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/1137611914-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/145665799-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/158739183-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/60725875-380_Missing Gas Capacity</t>
+    <t>Aggregated Plant - EMBER Gap - way/103974940-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/82078641-380_Missing Gas Capacity</t>
   </si>
   <si>
     <t>Aggregated Plant - EMBER Gap - way/421827453-380_Missing Gas Capacity</t>
@@ -1836,69 +1887,18 @@
     <t>Aggregated Plant - EMBER Gap - way/99826025-380_Missing Gas Capacity</t>
   </si>
   <si>
-    <t>Aggregated Plant - EMBER Gap - way/181125039-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/199675964-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/432729521-380_Missing Gas Capacity</t>
+    <t>Aggregated Plant - EMBER Gap - way/132450233-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/416989699-380_Missing Gas Capacity</t>
   </si>
   <si>
     <t>Aggregated Plant - EMBER Gap - way/103653592-380_Missing Gas Capacity</t>
   </si>
   <si>
-    <t>Aggregated Plant - EMBER Gap - way/109993642-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/416989699-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/100407576-380_Missing Gas Capacity</t>
-  </si>
-  <si>
     <t>Aggregated Plant - EMBER Gap - way/82767145-380_Missing Gas Capacity</t>
   </si>
   <si>
-    <t>Aggregated Plant - EMBER Gap - way/59462715-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/172302572-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/105757794-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/255011550-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/338753171-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/162828577-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/98900549-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/82078641-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/103974940-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/133601335-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/162960205-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/149997403-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/132450233-380_Missing Gas Capacity</t>
-  </si>
-  <si>
     <t>Altomonte power station_1</t>
   </si>
   <si>
@@ -2211,102 +2211,102 @@
     <t>Valle Secolo geothermal power plant_2</t>
   </si>
   <si>
+    <t>Aggregated Plant - IRENA Gap - way/64200868-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/61712456-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - IT30-500_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - IT7-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/339703159-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - IT53-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - IT72-400_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/109588422-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/1137611914-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
     <t>Aggregated Plant - IRENA Gap - IT71-380_Missing Hydro Capacity</t>
   </si>
   <si>
     <t>Aggregated Plant - IRENA Gap - way/108020416-380_Missing Hydro Capacity</t>
   </si>
   <si>
+    <t>Aggregated Plant - IRENA Gap - way/338753171-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - IT93-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - IT10-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - IT72-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/1100665914-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - IT21-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
     <t>Aggregated Plant - IRENA Gap - way/59462263-380_Missing Hydro Capacity</t>
   </si>
   <si>
-    <t>Aggregated Plant - IRENA Gap - way/1100665914-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - IT72-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/1137611914-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/109588422-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - IT72-400_Missing Hydro Capacity</t>
+    <t>Aggregated Plant - IRENA Gap - way/144005863-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/114931087-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - IT31-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/61626687-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/82083756-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/491424937-380_Missing Hydro Capacity</t>
   </si>
   <si>
     <t>Aggregated Plant - IRENA Gap - way/419423704-380_Missing Hydro Capacity</t>
   </si>
   <si>
+    <t>Aggregated Plant - IRENA Gap - way/104359058-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
     <t>Aggregated Plant - IRENA Gap - way/72466334-380_Missing Hydro Capacity</t>
   </si>
   <si>
-    <t>Aggregated Plant - IRENA Gap - way/104359058-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/491424937-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/82083756-380_Missing Hydro Capacity</t>
+    <t>Aggregated Plant - IRENA Gap - way/96190189-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/116517585-380_Missing Hydro Capacity</t>
   </si>
   <si>
     <t>Aggregated Plant - IRENA Gap - IT36-380_Missing Hydro Capacity</t>
   </si>
   <si>
+    <t>Aggregated Plant - IRENA Gap - IT71-400_Missing Hydro Capacity</t>
+  </si>
+  <si>
     <t>Aggregated Plant - IRENA Gap - way/75602396-380_Missing Hydro Capacity</t>
   </si>
   <si>
-    <t>Aggregated Plant - IRENA Gap - IT71-400_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/339703159-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/61712456-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - IT53-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - IT30-500_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - IT7-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/144005863-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - IT21-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/64200868-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/338753171-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - IT10-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - IT93-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/61626687-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - IT31-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/114931087-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/116517585-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/96190189-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
     <t>Baschi hydroelectric plant_</t>
   </si>
   <si>
@@ -2601,16 +2601,19 @@
     <t>San Filippo del Mela power station_1</t>
   </si>
   <si>
+    <t>Aggregated Plant - IRENA Gap - ITA_30_Missing Solar Capacity</t>
+  </si>
+  <si>
+    <t>annual</t>
+  </si>
+  <si>
     <t>Aggregated Plant - IRENA Gap - ITA_42_Missing Solar Capacity</t>
   </si>
   <si>
-    <t>annual</t>
-  </si>
-  <si>
     <t>Aggregated Plant - IRENA Gap - ITA_68_Missing Solar Capacity</t>
   </si>
   <si>
-    <t>Aggregated Plant - IRENA Gap - ITA_30_Missing Solar Capacity</t>
+    <t>Aggregated Plant - IRENA Gap - ITA_96_Missing Onshore wind energy Capacity</t>
   </si>
   <si>
     <t>Aggregated Plant - IRENA Gap - ITA_22_Missing Onshore wind energy Capacity</t>
@@ -2619,9 +2622,6 @@
     <t>Aggregated Plant - IRENA Gap - ITA_73_Missing Onshore wind energy Capacity</t>
   </si>
   <si>
-    <t>Aggregated Plant - IRENA Gap - ITA_96_Missing Onshore wind energy Capacity</t>
-  </si>
-  <si>
     <t>AF</t>
   </si>
   <si>
@@ -3216,12 +3216,12 @@
     <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/418902800-380_Missing Coal Capacity</t>
   </si>
   <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/409439916-380_Missing Coal Capacity</t>
+  </si>
+  <si>
     <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/82767145-380_Missing Coal Capacity</t>
   </si>
   <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/409439916-380_Missing Coal Capacity</t>
-  </si>
-  <si>
     <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/303915533-380_Missing Coal Capacity</t>
   </si>
   <si>
@@ -3513,124 +3513,124 @@
     <t>ccs retrofit of -- Aggregated Plant</t>
   </si>
   <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/116797658-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/414663585-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/149997403-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/162960205-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/432729521-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/105757794-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/99826025-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/416989699-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/107438024-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/98900549-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/98421779-380_Missing Gas Capacity</t>
+  </si>
+  <si>
     <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/145665799-380_Missing Gas Capacity</t>
   </si>
   <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/103974940-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/60725875-380_Missing Gas Capacity</t>
+  </si>
+  <si>
     <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/82084019-380_Missing Gas Capacity</t>
   </si>
   <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/421827453-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/339104227-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/133601335-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/158739183-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/255011550-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/181125039-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/419423704-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/1137611914-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/199675964-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/82078641-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/103653592-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/103381531-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/411026199-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/109756016-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/338753171-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/100407576-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/82767145-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/172302572-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/162828577-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/132450233-380_Missing Gas Capacity</t>
+  </si>
+  <si>
     <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/110330925-380_Missing Gas Capacity</t>
   </si>
   <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/338753171-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/414663585-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/116797658-380_Missing Gas Capacity</t>
-  </si>
-  <si>
     <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/61157826-380_Missing Gas Capacity</t>
   </si>
   <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/109756016-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/411026199-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/82767145-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/172302572-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/99826025-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/416989699-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/162828577-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/105757794-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/103381531-380_Missing Gas Capacity</t>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/59462715-380_Missing Gas Capacity</t>
   </si>
   <si>
     <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/109993642-380_Missing Gas Capacity</t>
   </si>
   <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/59462715-380_Missing Gas Capacity</t>
-  </si>
-  <si>
     <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/105581403-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/181125039-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/255011550-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/98421779-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/107438024-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/60725875-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/1137611914-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/199675964-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/103653592-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/82078641-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/103974940-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/339104227-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/158739183-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/133601335-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/100407576-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/132450233-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/432729521-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/162960205-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/149997403-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/421827453-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/419423704-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/98900549-380_Missing Gas Capacity</t>
   </si>
   <si>
     <t>ccs retrofit of -- Tavazzano power station_CCGT8, timepoint 1</t>
@@ -4034,7 +4034,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D0D3EA3A-814F-4FD4-A2FC-ACA8492B52CF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7F7ECB1-BA13-48F3-B812-A77D275962E3}">
   <dimension ref="B9:T278"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -4222,7 +4222,7 @@
         <v>33</v>
       </c>
       <c r="D13" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E13">
         <v>0.12764790000000001</v>
@@ -4278,7 +4278,7 @@
         <v>33</v>
       </c>
       <c r="D14" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E14">
         <v>8.7830160000000032E-2</v>
@@ -4558,7 +4558,7 @@
         <v>33</v>
       </c>
       <c r="D19" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E19">
         <v>0.260522535</v>
@@ -4614,7 +4614,7 @@
         <v>33</v>
       </c>
       <c r="D20" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E20">
         <v>0.260522535</v>
@@ -4670,7 +4670,7 @@
         <v>33</v>
       </c>
       <c r="D21" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E21">
         <v>0.260522535</v>
@@ -4726,7 +4726,7 @@
         <v>33</v>
       </c>
       <c r="D22" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E22">
         <v>0.28056272999999998</v>
@@ -4782,7 +4782,7 @@
         <v>33</v>
       </c>
       <c r="D23" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E23">
         <v>0.28056272999999998</v>
@@ -4838,7 +4838,7 @@
         <v>33</v>
       </c>
       <c r="D24" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E24">
         <v>0.28056272999999998</v>
@@ -4894,7 +4894,7 @@
         <v>49</v>
       </c>
       <c r="D25" t="s">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="E25">
         <v>0.41750406250000005</v>
@@ -4950,7 +4950,7 @@
         <v>49</v>
       </c>
       <c r="D26" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E26">
         <v>0.44431624999999997</v>
@@ -5006,7 +5006,7 @@
         <v>49</v>
       </c>
       <c r="D27" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E27">
         <v>0.38303124999999993</v>
@@ -5062,7 +5062,7 @@
         <v>49</v>
       </c>
       <c r="D28" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="E28">
         <v>0.44431624999999997</v>
@@ -5118,7 +5118,7 @@
         <v>49</v>
       </c>
       <c r="D29" t="s">
-        <v>59</v>
+        <v>80</v>
       </c>
       <c r="E29">
         <v>0.41750406249999999</v>
@@ -5174,7 +5174,7 @@
         <v>49</v>
       </c>
       <c r="D30" t="s">
-        <v>59</v>
+        <v>80</v>
       </c>
       <c r="E30">
         <v>0.41750406249999999</v>
@@ -5230,7 +5230,7 @@
         <v>49</v>
       </c>
       <c r="D31" t="s">
-        <v>59</v>
+        <v>80</v>
       </c>
       <c r="E31">
         <v>0.41750406249999999</v>
@@ -5342,7 +5342,7 @@
         <v>49</v>
       </c>
       <c r="D33" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="E33">
         <v>0.41750406249999999</v>
@@ -5510,7 +5510,7 @@
         <v>49</v>
       </c>
       <c r="D36" t="s">
-        <v>51</v>
+        <v>77</v>
       </c>
       <c r="E36">
         <v>0.41750406249999999</v>
@@ -5566,7 +5566,7 @@
         <v>49</v>
       </c>
       <c r="D37" t="s">
-        <v>51</v>
+        <v>77</v>
       </c>
       <c r="E37">
         <v>0.41750406249999999</v>
@@ -5622,7 +5622,7 @@
         <v>49</v>
       </c>
       <c r="D38" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="E38">
         <v>0.41750406249999999</v>
@@ -5678,7 +5678,7 @@
         <v>49</v>
       </c>
       <c r="D39" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="E39">
         <v>0.41750406249999999</v>
@@ -5734,7 +5734,7 @@
         <v>49</v>
       </c>
       <c r="D40" t="s">
-        <v>75</v>
+        <v>52</v>
       </c>
       <c r="E40">
         <v>0.3983525</v>
@@ -5790,7 +5790,7 @@
         <v>49</v>
       </c>
       <c r="D41" t="s">
-        <v>75</v>
+        <v>52</v>
       </c>
       <c r="E41">
         <v>0.41750406249999999</v>
@@ -5846,7 +5846,7 @@
         <v>49</v>
       </c>
       <c r="D42" t="s">
-        <v>75</v>
+        <v>52</v>
       </c>
       <c r="E42">
         <v>0.41750406249999999</v>
@@ -5902,7 +5902,7 @@
         <v>49</v>
       </c>
       <c r="D43" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="E43">
         <v>0.41750406249999999</v>
@@ -5958,7 +5958,7 @@
         <v>49</v>
       </c>
       <c r="D44" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="E44">
         <v>0.41750406249999999</v>
@@ -6238,7 +6238,7 @@
         <v>49</v>
       </c>
       <c r="D49" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E49">
         <v>0.40218281250000004</v>
@@ -6294,7 +6294,7 @@
         <v>49</v>
       </c>
       <c r="D50" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E50">
         <v>0.40218281250000004</v>
@@ -6350,7 +6350,7 @@
         <v>49</v>
       </c>
       <c r="D51" t="s">
-        <v>57</v>
+        <v>86</v>
       </c>
       <c r="E51">
         <v>0.41750406249999999</v>
@@ -6406,7 +6406,7 @@
         <v>49</v>
       </c>
       <c r="D52" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E52">
         <v>0.45963749999999998</v>
@@ -6462,7 +6462,7 @@
         <v>49</v>
       </c>
       <c r="D53" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E53">
         <v>0.41750406249999999</v>
@@ -6574,7 +6574,7 @@
         <v>49</v>
       </c>
       <c r="D55" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E55">
         <v>0.41750406249999999</v>
@@ -6630,7 +6630,7 @@
         <v>49</v>
       </c>
       <c r="D56" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="E56">
         <v>0.41750406249999999</v>
@@ -6686,7 +6686,7 @@
         <v>49</v>
       </c>
       <c r="D57" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="E57">
         <v>0.41750406249999999</v>
@@ -6742,7 +6742,7 @@
         <v>49</v>
       </c>
       <c r="D58" t="s">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="E58">
         <v>0.40218281249999999</v>
@@ -6798,7 +6798,7 @@
         <v>49</v>
       </c>
       <c r="D59" t="s">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="E59">
         <v>0.40218281249999999</v>
@@ -6854,7 +6854,7 @@
         <v>49</v>
       </c>
       <c r="D60" t="s">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="E60">
         <v>0.38303124999999993</v>
@@ -6910,7 +6910,7 @@
         <v>49</v>
       </c>
       <c r="D61" t="s">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="E61">
         <v>0.38303124999999993</v>
@@ -7022,7 +7022,7 @@
         <v>49</v>
       </c>
       <c r="D63" t="s">
-        <v>83</v>
+        <v>58</v>
       </c>
       <c r="E63">
         <v>0.41750406249999999</v>
@@ -7078,7 +7078,7 @@
         <v>49</v>
       </c>
       <c r="D64" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="E64">
         <v>0.41750406249999999</v>
@@ -7134,7 +7134,7 @@
         <v>49</v>
       </c>
       <c r="D65" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="E65">
         <v>0.41750406249999999</v>
@@ -7190,7 +7190,7 @@
         <v>49</v>
       </c>
       <c r="D66" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E66">
         <v>0.41750406249999999</v>
@@ -7358,7 +7358,7 @@
         <v>49</v>
       </c>
       <c r="D69" t="s">
-        <v>56</v>
+        <v>78</v>
       </c>
       <c r="E69">
         <v>0.41750406249999999</v>
@@ -7414,7 +7414,7 @@
         <v>49</v>
       </c>
       <c r="D70" t="s">
-        <v>56</v>
+        <v>78</v>
       </c>
       <c r="E70">
         <v>0.41750406249999999</v>
@@ -7470,7 +7470,7 @@
         <v>49</v>
       </c>
       <c r="D71" t="s">
-        <v>83</v>
+        <v>58</v>
       </c>
       <c r="E71">
         <v>0.41750406249999999</v>
@@ -7526,7 +7526,7 @@
         <v>49</v>
       </c>
       <c r="D72" t="s">
-        <v>83</v>
+        <v>58</v>
       </c>
       <c r="E72">
         <v>0.41750406249999999</v>
@@ -7582,7 +7582,7 @@
         <v>49</v>
       </c>
       <c r="D73" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="E73">
         <v>0.41750406249999999</v>
@@ -7638,7 +7638,7 @@
         <v>49</v>
       </c>
       <c r="D74" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="E74">
         <v>0.41750406249999999</v>
@@ -7694,7 +7694,7 @@
         <v>49</v>
       </c>
       <c r="D75" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="E75">
         <v>0.42899500000000002</v>
@@ -7750,7 +7750,7 @@
         <v>49</v>
       </c>
       <c r="D76" t="s">
-        <v>87</v>
+        <v>60</v>
       </c>
       <c r="E76">
         <v>0.41750406249999999</v>
@@ -7806,7 +7806,7 @@
         <v>49</v>
       </c>
       <c r="D77" t="s">
-        <v>87</v>
+        <v>60</v>
       </c>
       <c r="E77">
         <v>0.41750406249999999</v>
@@ -7974,7 +7974,7 @@
         <v>49</v>
       </c>
       <c r="D80" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E80">
         <v>0.41750406249999999</v>
@@ -8030,7 +8030,7 @@
         <v>49</v>
       </c>
       <c r="D81" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E81">
         <v>0.41750406249999999</v>
@@ -8086,7 +8086,7 @@
         <v>49</v>
       </c>
       <c r="D82" t="s">
-        <v>74</v>
+        <v>53</v>
       </c>
       <c r="E82">
         <v>0.41750406249999999</v>
@@ -8142,7 +8142,7 @@
         <v>49</v>
       </c>
       <c r="D83" t="s">
-        <v>74</v>
+        <v>53</v>
       </c>
       <c r="E83">
         <v>0.41750406249999999</v>
@@ -8198,7 +8198,7 @@
         <v>49</v>
       </c>
       <c r="D84" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="E84">
         <v>0.41750406249999999</v>
@@ -8254,7 +8254,7 @@
         <v>49</v>
       </c>
       <c r="D85" t="s">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="E85">
         <v>0.41750406249999999</v>
@@ -8310,7 +8310,7 @@
         <v>49</v>
       </c>
       <c r="D86" t="s">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="E86">
         <v>0.41750406249999999</v>
@@ -8366,7 +8366,7 @@
         <v>49</v>
       </c>
       <c r="D87" t="s">
-        <v>82</v>
+        <v>59</v>
       </c>
       <c r="E87">
         <v>0.41750406249999999</v>
@@ -8422,7 +8422,7 @@
         <v>49</v>
       </c>
       <c r="D88" t="s">
-        <v>82</v>
+        <v>59</v>
       </c>
       <c r="E88">
         <v>0.41750406249999999</v>
@@ -8478,7 +8478,7 @@
         <v>49</v>
       </c>
       <c r="D89" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="E89">
         <v>0.44431624999999997</v>
@@ -8534,7 +8534,7 @@
         <v>49</v>
       </c>
       <c r="D90" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="E90">
         <v>0.41750406249999999</v>
@@ -8590,7 +8590,7 @@
         <v>49</v>
       </c>
       <c r="D91" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="E91">
         <v>0.41750406249999999</v>
@@ -8646,7 +8646,7 @@
         <v>49</v>
       </c>
       <c r="D92" t="s">
-        <v>57</v>
+        <v>86</v>
       </c>
       <c r="E92">
         <v>0.44431624999999997</v>
@@ -8702,7 +8702,7 @@
         <v>49</v>
       </c>
       <c r="D93" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E93">
         <v>0.41750406249999999</v>
@@ -8758,7 +8758,7 @@
         <v>49</v>
       </c>
       <c r="D94" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E94">
         <v>0.41750406249999999</v>
@@ -8814,7 +8814,7 @@
         <v>49</v>
       </c>
       <c r="D95" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="E95">
         <v>0.41750406249999999</v>
@@ -8870,7 +8870,7 @@
         <v>49</v>
       </c>
       <c r="D96" t="s">
-        <v>76</v>
+        <v>51</v>
       </c>
       <c r="E96">
         <v>0.41750406249999999</v>
@@ -8926,7 +8926,7 @@
         <v>49</v>
       </c>
       <c r="D97" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="E97">
         <v>0.41750406249999999</v>
@@ -9038,7 +9038,7 @@
         <v>49</v>
       </c>
       <c r="D99" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="E99">
         <v>0.45963749999999998</v>
@@ -9094,7 +9094,7 @@
         <v>49</v>
       </c>
       <c r="D100" t="s">
-        <v>58</v>
+        <v>81</v>
       </c>
       <c r="E100">
         <v>0.45963749999999998</v>
@@ -9150,7 +9150,7 @@
         <v>49</v>
       </c>
       <c r="D101" t="s">
-        <v>76</v>
+        <v>51</v>
       </c>
       <c r="E101">
         <v>0.45963749999999998</v>
@@ -9206,7 +9206,7 @@
         <v>49</v>
       </c>
       <c r="D102" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E102">
         <v>0.41750406249999999</v>
@@ -9262,7 +9262,7 @@
         <v>49</v>
       </c>
       <c r="D103" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E103">
         <v>0.41750406249999999</v>
@@ -9318,7 +9318,7 @@
         <v>49</v>
       </c>
       <c r="D104" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="E104">
         <v>0.41750406249999999</v>
@@ -9374,7 +9374,7 @@
         <v>49</v>
       </c>
       <c r="D105" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="E105">
         <v>0.41750406249999999</v>
@@ -9430,7 +9430,7 @@
         <v>49</v>
       </c>
       <c r="D106" t="s">
-        <v>83</v>
+        <v>58</v>
       </c>
       <c r="E106">
         <v>0.38303124999999993</v>
@@ -9486,7 +9486,7 @@
         <v>49</v>
       </c>
       <c r="D107" t="s">
-        <v>83</v>
+        <v>58</v>
       </c>
       <c r="E107">
         <v>0.38303124999999993</v>
@@ -9542,7 +9542,7 @@
         <v>49</v>
       </c>
       <c r="D108" t="s">
-        <v>85</v>
+        <v>62</v>
       </c>
       <c r="E108">
         <v>0.4021828125000001</v>
@@ -9654,7 +9654,7 @@
         <v>49</v>
       </c>
       <c r="D110" t="s">
-        <v>52</v>
+        <v>76</v>
       </c>
       <c r="E110">
         <v>0.41750406249999999</v>
@@ -9710,7 +9710,7 @@
         <v>49</v>
       </c>
       <c r="D111" t="s">
-        <v>75</v>
+        <v>52</v>
       </c>
       <c r="E111">
         <v>0.3983525</v>
@@ -9822,7 +9822,7 @@
         <v>49</v>
       </c>
       <c r="D113" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="E113">
         <v>0.41750406249999999</v>
@@ -10270,7 +10270,7 @@
         <v>49</v>
       </c>
       <c r="D121" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E121">
         <v>0.45963749999999998</v>
@@ -10438,7 +10438,7 @@
         <v>49</v>
       </c>
       <c r="D124" t="s">
-        <v>37</v>
+        <v>75</v>
       </c>
       <c r="E124">
         <v>0.45963749999999998</v>
@@ -10494,7 +10494,7 @@
         <v>49</v>
       </c>
       <c r="D125" t="s">
-        <v>75</v>
+        <v>17</v>
       </c>
       <c r="E125">
         <v>0.45963749999999998</v>
@@ -10718,7 +10718,7 @@
         <v>49</v>
       </c>
       <c r="D129" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E129">
         <v>0.45963749999999998</v>
@@ -10774,7 +10774,7 @@
         <v>49</v>
       </c>
       <c r="D130" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E130">
         <v>0.45963749999999998</v>
@@ -10830,7 +10830,7 @@
         <v>49</v>
       </c>
       <c r="D131" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E131">
         <v>0.45963749999999998</v>
@@ -10886,7 +10886,7 @@
         <v>49</v>
       </c>
       <c r="D132" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E132">
         <v>0.45963749999999998</v>
@@ -10942,7 +10942,7 @@
         <v>49</v>
       </c>
       <c r="D133" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E133">
         <v>0.45963749999999998</v>
@@ -10998,7 +10998,7 @@
         <v>49</v>
       </c>
       <c r="D134" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E134">
         <v>0.45963749999999998</v>
@@ -11110,7 +11110,7 @@
         <v>49</v>
       </c>
       <c r="D136" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E136">
         <v>0.45963749999999998</v>
@@ -11166,7 +11166,7 @@
         <v>49</v>
       </c>
       <c r="D137" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E137">
         <v>0.45963749999999998</v>
@@ -11222,7 +11222,7 @@
         <v>49</v>
       </c>
       <c r="D138" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E138">
         <v>0.45963749999999998</v>
@@ -11278,7 +11278,7 @@
         <v>49</v>
       </c>
       <c r="D139" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E139">
         <v>0.45963749999999998</v>
@@ -11334,7 +11334,7 @@
         <v>49</v>
       </c>
       <c r="D140" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E140">
         <v>0.45963749999999998</v>
@@ -11390,7 +11390,7 @@
         <v>49</v>
       </c>
       <c r="D141" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E141">
         <v>0.45963749999999998</v>
@@ -11446,7 +11446,7 @@
         <v>49</v>
       </c>
       <c r="D142" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E142">
         <v>0.45963749999999998</v>
@@ -11502,7 +11502,7 @@
         <v>49</v>
       </c>
       <c r="D143" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E143">
         <v>0.45963749999999998</v>
@@ -11558,7 +11558,7 @@
         <v>49</v>
       </c>
       <c r="D144" t="s">
-        <v>20</v>
+        <v>72</v>
       </c>
       <c r="E144">
         <v>0.45963749999999998</v>
@@ -11726,7 +11726,7 @@
         <v>49</v>
       </c>
       <c r="D147" t="s">
-        <v>52</v>
+        <v>36</v>
       </c>
       <c r="E147">
         <v>0.45963749999999998</v>
@@ -11782,7 +11782,7 @@
         <v>49</v>
       </c>
       <c r="D148" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E148">
         <v>0.45963749999999998</v>
@@ -11838,7 +11838,7 @@
         <v>49</v>
       </c>
       <c r="D149" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E149">
         <v>0.45963749999999998</v>
@@ -11894,7 +11894,7 @@
         <v>49</v>
       </c>
       <c r="D150" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E150">
         <v>0.45963749999999998</v>
@@ -11950,7 +11950,7 @@
         <v>49</v>
       </c>
       <c r="D151" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E151">
         <v>0.45963749999999998</v>
@@ -12230,7 +12230,7 @@
         <v>49</v>
       </c>
       <c r="D156" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E156">
         <v>0.45963749999999998</v>
@@ -12678,7 +12678,7 @@
         <v>49</v>
       </c>
       <c r="D164" t="s">
-        <v>85</v>
+        <v>62</v>
       </c>
       <c r="E164">
         <v>0.41367375000000001</v>
@@ -13518,7 +13518,7 @@
         <v>49</v>
       </c>
       <c r="D179" t="s">
-        <v>76</v>
+        <v>51</v>
       </c>
       <c r="E179">
         <v>0.39835250000000011</v>
@@ -13574,7 +13574,7 @@
         <v>49</v>
       </c>
       <c r="D180" t="s">
-        <v>76</v>
+        <v>51</v>
       </c>
       <c r="E180">
         <v>0.39835250000000011</v>
@@ -13798,7 +13798,7 @@
         <v>49</v>
       </c>
       <c r="D184" t="s">
-        <v>83</v>
+        <v>58</v>
       </c>
       <c r="E184">
         <v>0.41367375000000001</v>
@@ -13854,7 +13854,7 @@
         <v>49</v>
       </c>
       <c r="D185" t="s">
-        <v>83</v>
+        <v>58</v>
       </c>
       <c r="E185">
         <v>0.41367375000000001</v>
@@ -14806,7 +14806,7 @@
         <v>49</v>
       </c>
       <c r="D202" t="s">
-        <v>58</v>
+        <v>81</v>
       </c>
       <c r="E202">
         <v>0.3983525</v>
@@ -15534,7 +15534,7 @@
         <v>49</v>
       </c>
       <c r="D215" t="s">
-        <v>74</v>
+        <v>53</v>
       </c>
       <c r="E215">
         <v>0.38303124999999993</v>
@@ -15702,7 +15702,7 @@
         <v>49</v>
       </c>
       <c r="D218" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E218">
         <v>0.42899499999999996</v>
@@ -15758,7 +15758,7 @@
         <v>49</v>
       </c>
       <c r="D219" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E219">
         <v>0.42899499999999996</v>
@@ -15926,7 +15926,7 @@
         <v>49</v>
       </c>
       <c r="D222" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="E222">
         <v>0.38303124999999993</v>
@@ -15982,7 +15982,7 @@
         <v>49</v>
       </c>
       <c r="D223" t="s">
-        <v>82</v>
+        <v>59</v>
       </c>
       <c r="E223">
         <v>0.25280062500000006</v>
@@ -16038,7 +16038,7 @@
         <v>49</v>
       </c>
       <c r="D224" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="E224">
         <v>0.24514000000000002</v>
@@ -16094,7 +16094,7 @@
         <v>49</v>
       </c>
       <c r="D225" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="E225">
         <v>0.24514000000000002</v>
@@ -16150,7 +16150,7 @@
         <v>49</v>
       </c>
       <c r="D226" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="E226">
         <v>0.21066718750000002</v>
@@ -16654,7 +16654,7 @@
         <v>49</v>
       </c>
       <c r="D235" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="E235">
         <v>0.21449750000000001</v>
@@ -16934,7 +16934,7 @@
         <v>49</v>
       </c>
       <c r="D240" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="E240">
         <v>0.23747937499999999</v>
@@ -17046,7 +17046,7 @@
         <v>49</v>
       </c>
       <c r="D242" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="E242">
         <v>0.21449750000000001</v>
@@ -17242,7 +17242,7 @@
         <v>49</v>
       </c>
       <c r="D247" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="E247">
         <v>0.27578249999999999</v>
@@ -17312,7 +17312,7 @@
         <v>49</v>
       </c>
       <c r="D249" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="E249">
         <v>0.27578249999999999</v>
@@ -17452,7 +17452,7 @@
         <v>49</v>
       </c>
       <c r="D253" t="s">
-        <v>85</v>
+        <v>62</v>
       </c>
       <c r="E253">
         <v>0.23747937499999999</v>
@@ -17487,7 +17487,7 @@
         <v>49</v>
       </c>
       <c r="D254" t="s">
-        <v>85</v>
+        <v>62</v>
       </c>
       <c r="E254">
         <v>0.23747937499999999</v>
@@ -17522,7 +17522,7 @@
         <v>49</v>
       </c>
       <c r="D255" t="s">
-        <v>85</v>
+        <v>62</v>
       </c>
       <c r="E255">
         <v>0.23747937499999999</v>
@@ -17557,7 +17557,7 @@
         <v>49</v>
       </c>
       <c r="D256" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="E256">
         <v>0.26429156249999997</v>
@@ -17592,7 +17592,7 @@
         <v>49</v>
       </c>
       <c r="D257" t="s">
-        <v>59</v>
+        <v>80</v>
       </c>
       <c r="E257">
         <v>0.23747937499999999</v>
@@ -17627,7 +17627,7 @@
         <v>49</v>
       </c>
       <c r="D258" t="s">
-        <v>59</v>
+        <v>80</v>
       </c>
       <c r="E258">
         <v>0.23747937499999999</v>
@@ -17662,7 +17662,7 @@
         <v>49</v>
       </c>
       <c r="D259" t="s">
-        <v>52</v>
+        <v>76</v>
       </c>
       <c r="E259">
         <v>0.22215812499999998</v>
@@ -17837,7 +17837,7 @@
         <v>439</v>
       </c>
       <c r="D264" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E264">
         <v>0.35238875000000003</v>
@@ -17942,7 +17942,7 @@
         <v>439</v>
       </c>
       <c r="D267" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E267">
         <v>0.19534593749999996</v>
@@ -18152,7 +18152,7 @@
         <v>439</v>
       </c>
       <c r="D273" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E273">
         <v>0.23747937499999999</v>
@@ -18360,7 +18360,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CAC2B88A-405C-446E-81B2-C0420EDDE10C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2B3BF5C1-DBAE-455B-8010-7F7314D67A27}">
   <dimension ref="B9:T641"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -18442,19 +18442,19 @@
         <v>2022</v>
       </c>
       <c r="F11">
-        <v>0.35800000000000004</v>
+        <v>0.24877966101694915</v>
       </c>
       <c r="G11">
-        <v>0.306425</v>
+        <v>0.28891500000000003</v>
       </c>
       <c r="H11">
-        <v>3850.0000000000009</v>
+        <v>4427.5</v>
       </c>
       <c r="I11">
-        <v>143</v>
+        <v>157.30000000000001</v>
       </c>
       <c r="J11">
-        <v>8.4</v>
+        <v>9.240000000000002</v>
       </c>
       <c r="K11">
         <v>50</v>
@@ -18495,19 +18495,19 @@
         <v>2022</v>
       </c>
       <c r="F12">
-        <v>0.22450847457627116</v>
+        <v>0.35800000000000004</v>
       </c>
       <c r="G12">
-        <v>0.28891500000000003</v>
+        <v>0.306425</v>
       </c>
       <c r="H12">
-        <v>4427.5</v>
+        <v>3850.0000000000009</v>
       </c>
       <c r="I12">
-        <v>157.30000000000001</v>
+        <v>143</v>
       </c>
       <c r="J12">
-        <v>9.240000000000002</v>
+        <v>8.4</v>
       </c>
       <c r="K12">
         <v>50</v>
@@ -18548,19 +18548,19 @@
         <v>2022</v>
       </c>
       <c r="F13">
-        <v>0.39440677966101695</v>
+        <v>0.22450847457627116</v>
       </c>
       <c r="G13">
-        <v>0.306425</v>
+        <v>0.28891500000000003</v>
       </c>
       <c r="H13">
-        <v>3850.0000000000005</v>
+        <v>4427.5</v>
       </c>
       <c r="I13">
-        <v>143</v>
+        <v>157.30000000000001</v>
       </c>
       <c r="J13">
-        <v>8.4</v>
+        <v>9.240000000000002</v>
       </c>
       <c r="K13">
         <v>50</v>
@@ -18601,19 +18601,19 @@
         <v>2022</v>
       </c>
       <c r="F14">
-        <v>0.49149152542372881</v>
+        <v>0.27911864406779663</v>
       </c>
       <c r="G14">
-        <v>0.306425</v>
+        <v>0.28891500000000003</v>
       </c>
       <c r="H14">
-        <v>3850.0000000000005</v>
+        <v>4427.5</v>
       </c>
       <c r="I14">
-        <v>143</v>
+        <v>157.30000000000001</v>
       </c>
       <c r="J14">
-        <v>8.4</v>
+        <v>9.240000000000002</v>
       </c>
       <c r="K14">
         <v>50</v>
@@ -18760,19 +18760,19 @@
         <v>2022</v>
       </c>
       <c r="F17">
-        <v>0.27911864406779663</v>
+        <v>0.39440677966101695</v>
       </c>
       <c r="G17">
-        <v>0.28891500000000003</v>
+        <v>0.306425</v>
       </c>
       <c r="H17">
-        <v>4427.5</v>
+        <v>3850.0000000000005</v>
       </c>
       <c r="I17">
-        <v>157.30000000000001</v>
+        <v>143</v>
       </c>
       <c r="J17">
-        <v>9.240000000000002</v>
+        <v>8.4</v>
       </c>
       <c r="K17">
         <v>50</v>
@@ -18813,19 +18813,19 @@
         <v>2022</v>
       </c>
       <c r="F18">
-        <v>0.24877966101694915</v>
+        <v>0.49149152542372881</v>
       </c>
       <c r="G18">
-        <v>0.28891500000000003</v>
+        <v>0.306425</v>
       </c>
       <c r="H18">
-        <v>4427.5</v>
+        <v>3850.0000000000005</v>
       </c>
       <c r="I18">
-        <v>157.30000000000001</v>
+        <v>143</v>
       </c>
       <c r="J18">
-        <v>9.240000000000002</v>
+        <v>8.4</v>
       </c>
       <c r="K18">
         <v>50</v>
@@ -18966,7 +18966,7 @@
         <v>13</v>
       </c>
       <c r="D21" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E21">
         <v>2008</v>
@@ -19019,7 +19019,7 @@
         <v>13</v>
       </c>
       <c r="D22" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E22">
         <v>2001</v>
@@ -19072,7 +19072,7 @@
         <v>13</v>
       </c>
       <c r="D23" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E23">
         <v>2013</v>
@@ -19125,7 +19125,7 @@
         <v>13</v>
       </c>
       <c r="D24" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="E24">
         <v>1965</v>
@@ -19178,7 +19178,7 @@
         <v>13</v>
       </c>
       <c r="D25" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E25">
         <v>2003</v>
@@ -19231,7 +19231,7 @@
         <v>13</v>
       </c>
       <c r="D26" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E26">
         <v>2009</v>
@@ -19284,7 +19284,7 @@
         <v>13</v>
       </c>
       <c r="D27" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E27">
         <v>2018</v>
@@ -19449,19 +19449,19 @@
         <v>2022</v>
       </c>
       <c r="F30">
-        <v>0.61803468208092449</v>
+        <v>0.18416184971098257</v>
       </c>
       <c r="G30">
-        <v>0.31518000000000002</v>
+        <v>0.29766999999999999</v>
       </c>
       <c r="H30">
-        <v>2200</v>
+        <v>2530</v>
       </c>
       <c r="I30">
-        <v>66</v>
+        <v>72.600000000000009</v>
       </c>
       <c r="J30">
-        <v>5.25</v>
+        <v>5.7750000000000004</v>
       </c>
       <c r="K30">
         <v>50</v>
@@ -19502,19 +19502,19 @@
         <v>2022</v>
       </c>
       <c r="F31">
-        <v>0.18416184971098257</v>
+        <v>0.61803468208092449</v>
       </c>
       <c r="G31">
-        <v>0.29766999999999999</v>
+        <v>0.31518000000000002</v>
       </c>
       <c r="H31">
-        <v>2530</v>
+        <v>2200</v>
       </c>
       <c r="I31">
-        <v>72.600000000000009</v>
+        <v>66</v>
       </c>
       <c r="J31">
-        <v>5.7750000000000004</v>
+        <v>5.25</v>
       </c>
       <c r="K31">
         <v>50</v>
@@ -19708,7 +19708,7 @@
         <v>33</v>
       </c>
       <c r="D35" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E35">
         <v>2005</v>
@@ -19761,7 +19761,7 @@
         <v>33</v>
       </c>
       <c r="D36" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E36">
         <v>1986</v>
@@ -19814,7 +19814,7 @@
         <v>33</v>
       </c>
       <c r="D37" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E37">
         <v>1991</v>
@@ -19867,7 +19867,7 @@
         <v>33</v>
       </c>
       <c r="D38" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E38">
         <v>1992</v>
@@ -19920,7 +19920,7 @@
         <v>33</v>
       </c>
       <c r="D39" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E39">
         <v>1993</v>
@@ -19973,7 +19973,7 @@
         <v>33</v>
       </c>
       <c r="D40" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E40">
         <v>2009</v>
@@ -20026,7 +20026,7 @@
         <v>33</v>
       </c>
       <c r="D41" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E41">
         <v>2010</v>
@@ -20079,7 +20079,7 @@
         <v>33</v>
       </c>
       <c r="D42" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E42">
         <v>2010</v>
@@ -20138,7 +20138,7 @@
         <v>2022</v>
       </c>
       <c r="F43">
-        <v>0.23280454489112914</v>
+        <v>0.19676367392472002</v>
       </c>
       <c r="G43">
         <v>0.50778999999999996</v>
@@ -20150,7 +20150,7 @@
         <v>36.300000000000004</v>
       </c>
       <c r="J43">
-        <v>3.4650000000000007</v>
+        <v>3.4650000000000003</v>
       </c>
       <c r="K43">
         <v>50</v>
@@ -20191,19 +20191,19 @@
         <v>2022</v>
       </c>
       <c r="F44">
-        <v>0.27347228442755023</v>
+        <v>0.3567559186877659</v>
       </c>
       <c r="G44">
-        <v>0.50778999999999996</v>
+        <v>0.52529999999999999</v>
       </c>
       <c r="H44">
-        <v>1265</v>
+        <v>1100</v>
       </c>
       <c r="I44">
-        <v>36.300000000000004</v>
+        <v>33</v>
       </c>
       <c r="J44">
-        <v>3.4650000000000003</v>
+        <v>3.1500000000000004</v>
       </c>
       <c r="K44">
         <v>50</v>
@@ -20238,13 +20238,13 @@
         <v>49</v>
       </c>
       <c r="D45" t="s">
-        <v>52</v>
+        <v>36</v>
       </c>
       <c r="E45">
         <v>2022</v>
       </c>
       <c r="F45">
-        <v>0.1548783373961905</v>
+        <v>0.27761211420071885</v>
       </c>
       <c r="G45">
         <v>0.50778999999999996</v>
@@ -20256,7 +20256,7 @@
         <v>36.300000000000004</v>
       </c>
       <c r="J45">
-        <v>3.4649999999999999</v>
+        <v>3.4650000000000003</v>
       </c>
       <c r="K45">
         <v>50</v>
@@ -20291,25 +20291,25 @@
         <v>49</v>
       </c>
       <c r="D46" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E46">
         <v>2022</v>
       </c>
       <c r="F46">
-        <v>0.22793415692269547</v>
+        <v>0.30829555840185086</v>
       </c>
       <c r="G46">
-        <v>0.50778999999999996</v>
+        <v>0.52529999999999999</v>
       </c>
       <c r="H46">
-        <v>1265</v>
+        <v>1100</v>
       </c>
       <c r="I46">
-        <v>36.300000000000004</v>
+        <v>33</v>
       </c>
       <c r="J46">
-        <v>3.4650000000000003</v>
+        <v>3.1500000000000004</v>
       </c>
       <c r="K46">
         <v>50</v>
@@ -20344,25 +20344,25 @@
         <v>49</v>
       </c>
       <c r="D47" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E47">
         <v>2022</v>
       </c>
       <c r="F47">
-        <v>0.37112356319464518</v>
+        <v>0.29344087509812827</v>
       </c>
       <c r="G47">
-        <v>0.52529999999999999</v>
+        <v>0.50778999999999996</v>
       </c>
       <c r="H47">
-        <v>1100</v>
+        <v>1265</v>
       </c>
       <c r="I47">
-        <v>33</v>
+        <v>36.300000000000004</v>
       </c>
       <c r="J47">
-        <v>3.1500000000000004</v>
+        <v>3.4650000000000003</v>
       </c>
       <c r="K47">
         <v>50</v>
@@ -20397,25 +20397,25 @@
         <v>49</v>
       </c>
       <c r="D48" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E48">
         <v>2022</v>
       </c>
       <c r="F48">
-        <v>0.20557907614758497</v>
+        <v>0.37112356319464518</v>
       </c>
       <c r="G48">
-        <v>0.50778999999999996</v>
+        <v>0.52529999999999999</v>
       </c>
       <c r="H48">
-        <v>1265</v>
+        <v>1100</v>
       </c>
       <c r="I48">
-        <v>36.300000000000004</v>
+        <v>33</v>
       </c>
       <c r="J48">
-        <v>3.4650000000000003</v>
+        <v>3.1500000000000004</v>
       </c>
       <c r="K48">
         <v>50</v>
@@ -20450,13 +20450,13 @@
         <v>49</v>
       </c>
       <c r="D49" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E49">
         <v>2022</v>
       </c>
       <c r="F49">
-        <v>0.17484692806676855</v>
+        <v>0.28443065735652601</v>
       </c>
       <c r="G49">
         <v>0.50778999999999996</v>
@@ -20503,25 +20503,25 @@
         <v>49</v>
       </c>
       <c r="D50" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E50">
         <v>2022</v>
       </c>
       <c r="F50">
-        <v>0.18872753377680451</v>
+        <v>0.39839773581787374</v>
       </c>
       <c r="G50">
-        <v>0.50778999999999996</v>
+        <v>0.52529999999999999</v>
       </c>
       <c r="H50">
-        <v>1265</v>
+        <v>1100</v>
       </c>
       <c r="I50">
-        <v>36.300000000000004</v>
+        <v>33</v>
       </c>
       <c r="J50">
-        <v>3.4650000000000007</v>
+        <v>3.1500000000000004</v>
       </c>
       <c r="K50">
         <v>50</v>
@@ -20556,13 +20556,13 @@
         <v>49</v>
       </c>
       <c r="D51" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E51">
         <v>2022</v>
       </c>
       <c r="F51">
-        <v>0.23864901045324952</v>
+        <v>0.21283595422055113</v>
       </c>
       <c r="G51">
         <v>0.50778999999999996</v>
@@ -20609,13 +20609,13 @@
         <v>49</v>
       </c>
       <c r="D52" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E52">
         <v>2022</v>
       </c>
       <c r="F52">
-        <v>0.31243538817501959</v>
+        <v>0.45732943023592104</v>
       </c>
       <c r="G52">
         <v>0.52529999999999999</v>
@@ -20662,25 +20662,25 @@
         <v>49</v>
       </c>
       <c r="D53" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E53">
         <v>2022</v>
       </c>
       <c r="F53">
-        <v>0.19481551873734657</v>
+        <v>0.49339465314217229</v>
       </c>
       <c r="G53">
-        <v>0.50778999999999996</v>
+        <v>0.52529999999999999</v>
       </c>
       <c r="H53">
-        <v>1265</v>
+        <v>1100</v>
       </c>
       <c r="I53">
-        <v>36.300000000000004</v>
+        <v>33</v>
       </c>
       <c r="J53">
-        <v>3.4650000000000003</v>
+        <v>3.1500000000000004</v>
       </c>
       <c r="K53">
         <v>50</v>
@@ -20715,13 +20715,13 @@
         <v>49</v>
       </c>
       <c r="D54" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E54">
         <v>2022</v>
       </c>
       <c r="F54">
-        <v>0.28443065735652601</v>
+        <v>0.18556178159732259</v>
       </c>
       <c r="G54">
         <v>0.50778999999999996</v>
@@ -20768,25 +20768,25 @@
         <v>49</v>
       </c>
       <c r="D55" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E55">
         <v>2022</v>
       </c>
       <c r="F55">
-        <v>0.39839773581787374</v>
+        <v>0.23280454489112914</v>
       </c>
       <c r="G55">
-        <v>0.52529999999999999</v>
+        <v>0.50778999999999996</v>
       </c>
       <c r="H55">
-        <v>1100</v>
+        <v>1265</v>
       </c>
       <c r="I55">
-        <v>33</v>
+        <v>36.300000000000004</v>
       </c>
       <c r="J55">
-        <v>3.1500000000000004</v>
+        <v>3.4650000000000007</v>
       </c>
       <c r="K55">
         <v>50</v>
@@ -20821,13 +20821,13 @@
         <v>49</v>
       </c>
       <c r="D56" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E56">
         <v>2022</v>
       </c>
       <c r="F56">
-        <v>0.21283595422055113</v>
+        <v>0.26604494277568891</v>
       </c>
       <c r="G56">
         <v>0.50778999999999996</v>
@@ -20874,13 +20874,13 @@
         <v>49</v>
       </c>
       <c r="D57" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E57">
         <v>2022</v>
       </c>
       <c r="F57">
-        <v>0.26543614427963469</v>
+        <v>0.20557907614758497</v>
       </c>
       <c r="G57">
         <v>0.50778999999999996</v>
@@ -20927,7 +20927,7 @@
         <v>49</v>
       </c>
       <c r="D58" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E58">
         <v>2022</v>
@@ -20980,7 +20980,7 @@
         <v>49</v>
       </c>
       <c r="D59" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E59">
         <v>2022</v>
@@ -21033,13 +21033,13 @@
         <v>49</v>
       </c>
       <c r="D60" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E60">
         <v>2022</v>
       </c>
       <c r="F60">
-        <v>0.21113131843159935</v>
+        <v>0.18702289798785268</v>
       </c>
       <c r="G60">
         <v>0.50778999999999996</v>
@@ -21086,13 +21086,13 @@
         <v>49</v>
       </c>
       <c r="D61" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E61">
         <v>2022</v>
       </c>
       <c r="F61">
-        <v>0.19627663512787666</v>
+        <v>0.19481551873734657</v>
       </c>
       <c r="G61">
         <v>0.50778999999999996</v>
@@ -21104,7 +21104,7 @@
         <v>36.300000000000004</v>
       </c>
       <c r="J61">
-        <v>3.4649999999999999</v>
+        <v>3.4650000000000003</v>
       </c>
       <c r="K61">
         <v>50</v>
@@ -21139,13 +21139,13 @@
         <v>49</v>
       </c>
       <c r="D62" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E62">
         <v>2022</v>
       </c>
       <c r="F62">
-        <v>0.18824049497996109</v>
+        <v>0.19481551873734657</v>
       </c>
       <c r="G62">
         <v>0.50778999999999996</v>
@@ -21192,25 +21192,25 @@
         <v>49</v>
       </c>
       <c r="D63" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E63">
         <v>2022</v>
       </c>
       <c r="F63">
-        <v>0.43468212618270452</v>
+        <v>0.21113131843159935</v>
       </c>
       <c r="G63">
-        <v>0.52529999999999999</v>
+        <v>0.50778999999999996</v>
       </c>
       <c r="H63">
-        <v>1100</v>
+        <v>1265</v>
       </c>
       <c r="I63">
-        <v>33</v>
+        <v>36.300000000000004</v>
       </c>
       <c r="J63">
-        <v>3.1500000000000004</v>
+        <v>3.4650000000000003</v>
       </c>
       <c r="K63">
         <v>50</v>
@@ -21245,13 +21245,13 @@
         <v>49</v>
       </c>
       <c r="D64" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E64">
         <v>2022</v>
       </c>
       <c r="F64">
-        <v>0.18702289798785268</v>
+        <v>0.19627663512787666</v>
       </c>
       <c r="G64">
         <v>0.50778999999999996</v>
@@ -21263,7 +21263,7 @@
         <v>36.300000000000004</v>
       </c>
       <c r="J64">
-        <v>3.4650000000000003</v>
+        <v>3.4649999999999999</v>
       </c>
       <c r="K64">
         <v>50</v>
@@ -21298,13 +21298,13 @@
         <v>49</v>
       </c>
       <c r="D65" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E65">
         <v>2022</v>
       </c>
       <c r="F65">
-        <v>0.19481551873734657</v>
+        <v>0.18824049497996109</v>
       </c>
       <c r="G65">
         <v>0.50778999999999996</v>
@@ -21351,25 +21351,25 @@
         <v>49</v>
       </c>
       <c r="D66" t="s">
-        <v>20</v>
+        <v>72</v>
       </c>
       <c r="E66">
         <v>2022</v>
       </c>
       <c r="F66">
-        <v>0.19822479031525012</v>
+        <v>0.43468212618270452</v>
       </c>
       <c r="G66">
-        <v>0.50778999999999996</v>
+        <v>0.52529999999999999</v>
       </c>
       <c r="H66">
-        <v>1265</v>
+        <v>1100</v>
       </c>
       <c r="I66">
-        <v>36.300000000000004</v>
+        <v>33</v>
       </c>
       <c r="J66">
-        <v>3.4650000000000003</v>
+        <v>3.1500000000000004</v>
       </c>
       <c r="K66">
         <v>50</v>
@@ -21410,7 +21410,7 @@
         <v>2022</v>
       </c>
       <c r="F67">
-        <v>0.20212110068999706</v>
+        <v>0.26543614427963469</v>
       </c>
       <c r="G67">
         <v>0.50778999999999996</v>
@@ -21463,7 +21463,7 @@
         <v>2022</v>
       </c>
       <c r="F68">
-        <v>0.29344087509812827</v>
+        <v>0.21551466760318963</v>
       </c>
       <c r="G68">
         <v>0.50778999999999996</v>
@@ -21510,25 +21510,25 @@
         <v>49</v>
       </c>
       <c r="D69" t="s">
-        <v>75</v>
+        <v>17</v>
       </c>
       <c r="E69">
         <v>2022</v>
       </c>
       <c r="F69">
-        <v>0.30829555840185086</v>
+        <v>0.19822479031525012</v>
       </c>
       <c r="G69">
-        <v>0.52529999999999999</v>
+        <v>0.50778999999999996</v>
       </c>
       <c r="H69">
-        <v>1100</v>
+        <v>1265</v>
       </c>
       <c r="I69">
-        <v>33</v>
+        <v>36.300000000000004</v>
       </c>
       <c r="J69">
-        <v>3.1500000000000004</v>
+        <v>3.4650000000000003</v>
       </c>
       <c r="K69">
         <v>50</v>
@@ -21563,13 +21563,13 @@
         <v>49</v>
       </c>
       <c r="D70" t="s">
-        <v>37</v>
+        <v>75</v>
       </c>
       <c r="E70">
         <v>2022</v>
       </c>
       <c r="F70">
-        <v>0.27761211420071885</v>
+        <v>0.22793415692269547</v>
       </c>
       <c r="G70">
         <v>0.50778999999999996</v>
@@ -21622,19 +21622,19 @@
         <v>2022</v>
       </c>
       <c r="F71">
-        <v>0.3567559186877659</v>
+        <v>0.1548783373961905</v>
       </c>
       <c r="G71">
-        <v>0.52529999999999999</v>
+        <v>0.50778999999999996</v>
       </c>
       <c r="H71">
-        <v>1100</v>
+        <v>1265</v>
       </c>
       <c r="I71">
-        <v>33</v>
+        <v>36.300000000000004</v>
       </c>
       <c r="J71">
-        <v>3.1500000000000004</v>
+        <v>3.4649999999999999</v>
       </c>
       <c r="K71">
         <v>50</v>
@@ -21675,7 +21675,7 @@
         <v>2022</v>
       </c>
       <c r="F72">
-        <v>0.18507474280047922</v>
+        <v>0.27347228442755023</v>
       </c>
       <c r="G72">
         <v>0.50778999999999996</v>
@@ -21687,7 +21687,7 @@
         <v>36.300000000000004</v>
       </c>
       <c r="J72">
-        <v>3.4649999999999999</v>
+        <v>3.4650000000000003</v>
       </c>
       <c r="K72">
         <v>50</v>
@@ -21728,7 +21728,7 @@
         <v>2022</v>
       </c>
       <c r="F73">
-        <v>0.19676367392472002</v>
+        <v>0.17484692806676855</v>
       </c>
       <c r="G73">
         <v>0.50778999999999996</v>
@@ -21781,7 +21781,7 @@
         <v>2022</v>
       </c>
       <c r="F74">
-        <v>0.20236462008841874</v>
+        <v>0.20212110068999706</v>
       </c>
       <c r="G74">
         <v>0.50778999999999996</v>
@@ -21834,19 +21834,19 @@
         <v>2022</v>
       </c>
       <c r="F75">
-        <v>0.18629233979258764</v>
+        <v>0.31243538817501959</v>
       </c>
       <c r="G75">
-        <v>0.50778999999999996</v>
+        <v>0.52529999999999999</v>
       </c>
       <c r="H75">
-        <v>1265</v>
+        <v>1100</v>
       </c>
       <c r="I75">
-        <v>36.300000000000004</v>
+        <v>33</v>
       </c>
       <c r="J75">
-        <v>3.4650000000000003</v>
+        <v>3.1500000000000004</v>
       </c>
       <c r="K75">
         <v>50</v>
@@ -21887,7 +21887,7 @@
         <v>2022</v>
       </c>
       <c r="F76">
-        <v>0.20820908565053911</v>
+        <v>0.23864901045324952</v>
       </c>
       <c r="G76">
         <v>0.50778999999999996</v>
@@ -21899,7 +21899,7 @@
         <v>36.300000000000004</v>
       </c>
       <c r="J76">
-        <v>3.4650000000000007</v>
+        <v>3.4650000000000003</v>
       </c>
       <c r="K76">
         <v>50</v>
@@ -21940,19 +21940,19 @@
         <v>2022</v>
       </c>
       <c r="F77">
-        <v>0.49339465314217229</v>
+        <v>0.20236462008841874</v>
       </c>
       <c r="G77">
-        <v>0.52529999999999999</v>
+        <v>0.50778999999999996</v>
       </c>
       <c r="H77">
-        <v>1100</v>
+        <v>1265</v>
       </c>
       <c r="I77">
-        <v>33</v>
+        <v>36.300000000000004</v>
       </c>
       <c r="J77">
-        <v>3.1500000000000004</v>
+        <v>3.4650000000000003</v>
       </c>
       <c r="K77">
         <v>50</v>
@@ -21993,19 +21993,19 @@
         <v>2022</v>
       </c>
       <c r="F78">
-        <v>0.45732943023592104</v>
+        <v>0.18629233979258764</v>
       </c>
       <c r="G78">
-        <v>0.52529999999999999</v>
+        <v>0.50778999999999996</v>
       </c>
       <c r="H78">
-        <v>1100</v>
+        <v>1265</v>
       </c>
       <c r="I78">
-        <v>33</v>
+        <v>36.300000000000004</v>
       </c>
       <c r="J78">
-        <v>3.1500000000000004</v>
+        <v>3.4650000000000003</v>
       </c>
       <c r="K78">
         <v>50</v>
@@ -22046,7 +22046,7 @@
         <v>2022</v>
       </c>
       <c r="F79">
-        <v>0.21551466760318963</v>
+        <v>0.20820908565053911</v>
       </c>
       <c r="G79">
         <v>0.50778999999999996</v>
@@ -22058,7 +22058,7 @@
         <v>36.300000000000004</v>
       </c>
       <c r="J79">
-        <v>3.4650000000000003</v>
+        <v>3.4650000000000007</v>
       </c>
       <c r="K79">
         <v>50</v>
@@ -22099,7 +22099,7 @@
         <v>2022</v>
       </c>
       <c r="F80">
-        <v>0.26604494277568891</v>
+        <v>0.16608022972358796</v>
       </c>
       <c r="G80">
         <v>0.50778999999999996</v>
@@ -22152,7 +22152,7 @@
         <v>2022</v>
       </c>
       <c r="F81">
-        <v>0.16608022972358796</v>
+        <v>0.18872753377680451</v>
       </c>
       <c r="G81">
         <v>0.50778999999999996</v>
@@ -22164,7 +22164,7 @@
         <v>36.300000000000004</v>
       </c>
       <c r="J81">
-        <v>3.4650000000000003</v>
+        <v>3.4650000000000007</v>
       </c>
       <c r="K81">
         <v>50</v>
@@ -22205,7 +22205,7 @@
         <v>2022</v>
       </c>
       <c r="F82">
-        <v>0.18556178159732259</v>
+        <v>0.18507474280047922</v>
       </c>
       <c r="G82">
         <v>0.50778999999999996</v>
@@ -22217,7 +22217,7 @@
         <v>36.300000000000004</v>
       </c>
       <c r="J82">
-        <v>3.4650000000000003</v>
+        <v>3.4649999999999999</v>
       </c>
       <c r="K82">
         <v>50</v>
@@ -22252,7 +22252,7 @@
         <v>49</v>
       </c>
       <c r="D83" t="s">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="E83">
         <v>2006</v>
@@ -22305,7 +22305,7 @@
         <v>49</v>
       </c>
       <c r="D84" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E84">
         <v>2012</v>
@@ -22358,7 +22358,7 @@
         <v>49</v>
       </c>
       <c r="D85" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E85">
         <v>1993</v>
@@ -22411,7 +22411,7 @@
         <v>49</v>
       </c>
       <c r="D86" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="E86">
         <v>2011</v>
@@ -22464,7 +22464,7 @@
         <v>49</v>
       </c>
       <c r="D87" t="s">
-        <v>59</v>
+        <v>80</v>
       </c>
       <c r="E87">
         <v>2005</v>
@@ -22517,7 +22517,7 @@
         <v>49</v>
       </c>
       <c r="D88" t="s">
-        <v>59</v>
+        <v>80</v>
       </c>
       <c r="E88">
         <v>2006</v>
@@ -22570,7 +22570,7 @@
         <v>49</v>
       </c>
       <c r="D89" t="s">
-        <v>59</v>
+        <v>80</v>
       </c>
       <c r="E89">
         <v>2006</v>
@@ -22676,7 +22676,7 @@
         <v>49</v>
       </c>
       <c r="D91" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="E91">
         <v>2003</v>
@@ -22835,7 +22835,7 @@
         <v>49</v>
       </c>
       <c r="D94" t="s">
-        <v>51</v>
+        <v>77</v>
       </c>
       <c r="E94">
         <v>2004</v>
@@ -22888,7 +22888,7 @@
         <v>49</v>
       </c>
       <c r="D95" t="s">
-        <v>51</v>
+        <v>77</v>
       </c>
       <c r="E95">
         <v>2005</v>
@@ -22941,7 +22941,7 @@
         <v>49</v>
       </c>
       <c r="D96" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="E96">
         <v>2005</v>
@@ -22994,7 +22994,7 @@
         <v>49</v>
       </c>
       <c r="D97" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="E97">
         <v>2005</v>
@@ -23047,7 +23047,7 @@
         <v>49</v>
       </c>
       <c r="D98" t="s">
-        <v>75</v>
+        <v>52</v>
       </c>
       <c r="E98">
         <v>2004</v>
@@ -23100,7 +23100,7 @@
         <v>49</v>
       </c>
       <c r="D99" t="s">
-        <v>75</v>
+        <v>52</v>
       </c>
       <c r="E99">
         <v>2004</v>
@@ -23153,7 +23153,7 @@
         <v>49</v>
       </c>
       <c r="D100" t="s">
-        <v>75</v>
+        <v>52</v>
       </c>
       <c r="E100">
         <v>2004</v>
@@ -23206,7 +23206,7 @@
         <v>49</v>
       </c>
       <c r="D101" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="E101">
         <v>2008</v>
@@ -23259,7 +23259,7 @@
         <v>49</v>
       </c>
       <c r="D102" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="E102">
         <v>2008</v>
@@ -23524,7 +23524,7 @@
         <v>49</v>
       </c>
       <c r="D107" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E107">
         <v>2000</v>
@@ -23577,7 +23577,7 @@
         <v>49</v>
       </c>
       <c r="D108" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E108">
         <v>2000</v>
@@ -23630,7 +23630,7 @@
         <v>49</v>
       </c>
       <c r="D109" t="s">
-        <v>57</v>
+        <v>86</v>
       </c>
       <c r="E109">
         <v>2007</v>
@@ -23683,7 +23683,7 @@
         <v>49</v>
       </c>
       <c r="D110" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E110">
         <v>2023</v>
@@ -23736,7 +23736,7 @@
         <v>49</v>
       </c>
       <c r="D111" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E111">
         <v>2001</v>
@@ -23842,7 +23842,7 @@
         <v>49</v>
       </c>
       <c r="D113" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E113">
         <v>2010</v>
@@ -23895,7 +23895,7 @@
         <v>49</v>
       </c>
       <c r="D114" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="E114">
         <v>2005</v>
@@ -23948,7 +23948,7 @@
         <v>49</v>
       </c>
       <c r="D115" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="E115">
         <v>2009</v>
@@ -24001,7 +24001,7 @@
         <v>49</v>
       </c>
       <c r="D116" t="s">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="E116">
         <v>1997</v>
@@ -24054,7 +24054,7 @@
         <v>49</v>
       </c>
       <c r="D117" t="s">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="E117">
         <v>1997</v>
@@ -24107,7 +24107,7 @@
         <v>49</v>
       </c>
       <c r="D118" t="s">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="E118">
         <v>1998</v>
@@ -24160,7 +24160,7 @@
         <v>49</v>
       </c>
       <c r="D119" t="s">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="E119">
         <v>1999</v>
@@ -24266,7 +24266,7 @@
         <v>49</v>
       </c>
       <c r="D121" t="s">
-        <v>83</v>
+        <v>58</v>
       </c>
       <c r="E121">
         <v>2010</v>
@@ -24319,7 +24319,7 @@
         <v>49</v>
       </c>
       <c r="D122" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="E122">
         <v>2003</v>
@@ -24372,7 +24372,7 @@
         <v>49</v>
       </c>
       <c r="D123" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="E123">
         <v>2003</v>
@@ -24425,7 +24425,7 @@
         <v>49</v>
       </c>
       <c r="D124" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E124">
         <v>2006</v>
@@ -24584,7 +24584,7 @@
         <v>49</v>
       </c>
       <c r="D127" t="s">
-        <v>56</v>
+        <v>78</v>
       </c>
       <c r="E127">
         <v>2002</v>
@@ -24637,7 +24637,7 @@
         <v>49</v>
       </c>
       <c r="D128" t="s">
-        <v>56</v>
+        <v>78</v>
       </c>
       <c r="E128">
         <v>2002</v>
@@ -24690,7 +24690,7 @@
         <v>49</v>
       </c>
       <c r="D129" t="s">
-        <v>83</v>
+        <v>58</v>
       </c>
       <c r="E129">
         <v>2010</v>
@@ -24743,7 +24743,7 @@
         <v>49</v>
       </c>
       <c r="D130" t="s">
-        <v>83</v>
+        <v>58</v>
       </c>
       <c r="E130">
         <v>2010</v>
@@ -24796,7 +24796,7 @@
         <v>49</v>
       </c>
       <c r="D131" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="E131">
         <v>2008</v>
@@ -24849,7 +24849,7 @@
         <v>49</v>
       </c>
       <c r="D132" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="E132">
         <v>2008</v>
@@ -24902,7 +24902,7 @@
         <v>49</v>
       </c>
       <c r="D133" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="E133">
         <v>2018</v>
@@ -24955,7 +24955,7 @@
         <v>49</v>
       </c>
       <c r="D134" t="s">
-        <v>87</v>
+        <v>60</v>
       </c>
       <c r="E134">
         <v>2006</v>
@@ -25008,7 +25008,7 @@
         <v>49</v>
       </c>
       <c r="D135" t="s">
-        <v>87</v>
+        <v>60</v>
       </c>
       <c r="E135">
         <v>2007</v>
@@ -25167,7 +25167,7 @@
         <v>49</v>
       </c>
       <c r="D138" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E138">
         <v>2010</v>
@@ -25220,7 +25220,7 @@
         <v>49</v>
       </c>
       <c r="D139" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E139">
         <v>2010</v>
@@ -25273,7 +25273,7 @@
         <v>49</v>
       </c>
       <c r="D140" t="s">
-        <v>74</v>
+        <v>53</v>
       </c>
       <c r="E140">
         <v>2004</v>
@@ -25326,7 +25326,7 @@
         <v>49</v>
       </c>
       <c r="D141" t="s">
-        <v>74</v>
+        <v>53</v>
       </c>
       <c r="E141">
         <v>2004</v>
@@ -25379,7 +25379,7 @@
         <v>49</v>
       </c>
       <c r="D142" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="E142">
         <v>2008</v>
@@ -25432,7 +25432,7 @@
         <v>49</v>
       </c>
       <c r="D143" t="s">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="E143">
         <v>2007</v>
@@ -25485,7 +25485,7 @@
         <v>49</v>
       </c>
       <c r="D144" t="s">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="E144">
         <v>2007</v>
@@ -25538,7 +25538,7 @@
         <v>49</v>
       </c>
       <c r="D145" t="s">
-        <v>82</v>
+        <v>59</v>
       </c>
       <c r="E145">
         <v>2005</v>
@@ -25591,7 +25591,7 @@
         <v>49</v>
       </c>
       <c r="D146" t="s">
-        <v>82</v>
+        <v>59</v>
       </c>
       <c r="E146">
         <v>2005</v>
@@ -25644,7 +25644,7 @@
         <v>49</v>
       </c>
       <c r="D147" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="E147">
         <v>2015</v>
@@ -25697,7 +25697,7 @@
         <v>49</v>
       </c>
       <c r="D148" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="E148">
         <v>2004</v>
@@ -25750,7 +25750,7 @@
         <v>49</v>
       </c>
       <c r="D149" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="E149">
         <v>2006</v>
@@ -25803,7 +25803,7 @@
         <v>49</v>
       </c>
       <c r="D150" t="s">
-        <v>57</v>
+        <v>86</v>
       </c>
       <c r="E150">
         <v>2011</v>
@@ -25856,7 +25856,7 @@
         <v>49</v>
       </c>
       <c r="D151" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E151">
         <v>2004</v>
@@ -25909,7 +25909,7 @@
         <v>49</v>
       </c>
       <c r="D152" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E152">
         <v>2005</v>
@@ -25962,7 +25962,7 @@
         <v>49</v>
       </c>
       <c r="D153" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="E153">
         <v>2006</v>
@@ -26015,7 +26015,7 @@
         <v>49</v>
       </c>
       <c r="D154" t="s">
-        <v>76</v>
+        <v>51</v>
       </c>
       <c r="E154">
         <v>2008</v>
@@ -26068,7 +26068,7 @@
         <v>49</v>
       </c>
       <c r="D155" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="E155">
         <v>2007</v>
@@ -26174,7 +26174,7 @@
         <v>49</v>
       </c>
       <c r="D157" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="E157">
         <v>2023</v>
@@ -26227,7 +26227,7 @@
         <v>49</v>
       </c>
       <c r="D158" t="s">
-        <v>58</v>
+        <v>81</v>
       </c>
       <c r="E158">
         <v>2026</v>
@@ -26280,7 +26280,7 @@
         <v>49</v>
       </c>
       <c r="D159" t="s">
-        <v>76</v>
+        <v>51</v>
       </c>
       <c r="E159">
         <v>2022</v>
@@ -26333,7 +26333,7 @@
         <v>49</v>
       </c>
       <c r="D160" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E160">
         <v>2003</v>
@@ -26386,7 +26386,7 @@
         <v>49</v>
       </c>
       <c r="D161" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E161">
         <v>2003</v>
@@ -26439,7 +26439,7 @@
         <v>49</v>
       </c>
       <c r="D162" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="E162">
         <v>2003</v>
@@ -26492,7 +26492,7 @@
         <v>49</v>
       </c>
       <c r="D163" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="E163">
         <v>2008</v>
@@ -26545,7 +26545,7 @@
         <v>49</v>
       </c>
       <c r="D164" t="s">
-        <v>83</v>
+        <v>58</v>
       </c>
       <c r="E164">
         <v>1999</v>
@@ -26598,7 +26598,7 @@
         <v>49</v>
       </c>
       <c r="D165" t="s">
-        <v>83</v>
+        <v>58</v>
       </c>
       <c r="E165">
         <v>1999</v>
@@ -26651,7 +26651,7 @@
         <v>49</v>
       </c>
       <c r="D166" t="s">
-        <v>85</v>
+        <v>62</v>
       </c>
       <c r="E166">
         <v>1997</v>
@@ -26757,7 +26757,7 @@
         <v>49</v>
       </c>
       <c r="D168" t="s">
-        <v>52</v>
+        <v>76</v>
       </c>
       <c r="E168">
         <v>2001</v>
@@ -26810,7 +26810,7 @@
         <v>49</v>
       </c>
       <c r="D169" t="s">
-        <v>75</v>
+        <v>52</v>
       </c>
       <c r="E169">
         <v>2006</v>
@@ -26916,7 +26916,7 @@
         <v>49</v>
       </c>
       <c r="D171" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="E171">
         <v>2007</v>
@@ -27499,7 +27499,7 @@
         <v>49</v>
       </c>
       <c r="D182" t="s">
-        <v>85</v>
+        <v>62</v>
       </c>
       <c r="E182">
         <v>2015</v>
@@ -28294,7 +28294,7 @@
         <v>49</v>
       </c>
       <c r="D197" t="s">
-        <v>76</v>
+        <v>51</v>
       </c>
       <c r="E197">
         <v>2004</v>
@@ -28347,7 +28347,7 @@
         <v>49</v>
       </c>
       <c r="D198" t="s">
-        <v>76</v>
+        <v>51</v>
       </c>
       <c r="E198">
         <v>2008</v>
@@ -28559,7 +28559,7 @@
         <v>49</v>
       </c>
       <c r="D202" t="s">
-        <v>83</v>
+        <v>58</v>
       </c>
       <c r="E202">
         <v>2005</v>
@@ -28612,7 +28612,7 @@
         <v>49</v>
       </c>
       <c r="D203" t="s">
-        <v>83</v>
+        <v>58</v>
       </c>
       <c r="E203">
         <v>2015</v>
@@ -29513,7 +29513,7 @@
         <v>49</v>
       </c>
       <c r="D220" t="s">
-        <v>58</v>
+        <v>81</v>
       </c>
       <c r="E220">
         <v>2009</v>
@@ -30202,7 +30202,7 @@
         <v>49</v>
       </c>
       <c r="D233" t="s">
-        <v>74</v>
+        <v>53</v>
       </c>
       <c r="E233">
         <v>1994</v>
@@ -30361,7 +30361,7 @@
         <v>49</v>
       </c>
       <c r="D236" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E236">
         <v>1990</v>
@@ -30414,7 +30414,7 @@
         <v>49</v>
       </c>
       <c r="D237" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E237">
         <v>2022</v>
@@ -30573,7 +30573,7 @@
         <v>49</v>
       </c>
       <c r="D240" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="E240">
         <v>2006</v>
@@ -30626,7 +30626,7 @@
         <v>49</v>
       </c>
       <c r="D241" t="s">
-        <v>82</v>
+        <v>59</v>
       </c>
       <c r="E241">
         <v>2024</v>
@@ -30679,7 +30679,7 @@
         <v>49</v>
       </c>
       <c r="D242" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="E242">
         <v>2023</v>
@@ -30732,7 +30732,7 @@
         <v>49</v>
       </c>
       <c r="D243" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="E243">
         <v>2023</v>
@@ -30785,7 +30785,7 @@
         <v>49</v>
       </c>
       <c r="D244" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="E244">
         <v>1997</v>
@@ -31262,7 +31262,7 @@
         <v>49</v>
       </c>
       <c r="D253" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="E253">
         <v>2008</v>
@@ -31527,7 +31527,7 @@
         <v>49</v>
       </c>
       <c r="D258" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="E258">
         <v>2015</v>
@@ -31633,7 +31633,7 @@
         <v>49</v>
       </c>
       <c r="D260" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="E260">
         <v>2004</v>
@@ -31898,7 +31898,7 @@
         <v>49</v>
       </c>
       <c r="D265" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="E265">
         <v>2024</v>
@@ -32004,7 +32004,7 @@
         <v>49</v>
       </c>
       <c r="D267" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="E267">
         <v>2023</v>
@@ -32216,7 +32216,7 @@
         <v>49</v>
       </c>
       <c r="D271" t="s">
-        <v>85</v>
+        <v>62</v>
       </c>
       <c r="E271">
         <v>1975</v>
@@ -32269,7 +32269,7 @@
         <v>49</v>
       </c>
       <c r="D272" t="s">
-        <v>85</v>
+        <v>62</v>
       </c>
       <c r="E272">
         <v>1975</v>
@@ -32322,7 +32322,7 @@
         <v>49</v>
       </c>
       <c r="D273" t="s">
-        <v>85</v>
+        <v>62</v>
       </c>
       <c r="E273">
         <v>1975</v>
@@ -32375,7 +32375,7 @@
         <v>49</v>
       </c>
       <c r="D274" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="E274">
         <v>2015</v>
@@ -32428,7 +32428,7 @@
         <v>49</v>
       </c>
       <c r="D275" t="s">
-        <v>59</v>
+        <v>80</v>
       </c>
       <c r="E275">
         <v>1967</v>
@@ -32481,7 +32481,7 @@
         <v>49</v>
       </c>
       <c r="D276" t="s">
-        <v>59</v>
+        <v>80</v>
       </c>
       <c r="E276">
         <v>1971</v>
@@ -32534,7 +32534,7 @@
         <v>49</v>
       </c>
       <c r="D277" t="s">
-        <v>52</v>
+        <v>76</v>
       </c>
       <c r="E277">
         <v>1970</v>
@@ -33117,7 +33117,7 @@
         <v>293</v>
       </c>
       <c r="D288" t="s">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="E288">
         <v>1991</v>
@@ -33170,7 +33170,7 @@
         <v>293</v>
       </c>
       <c r="D289" t="s">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="E289">
         <v>1991</v>
@@ -34230,25 +34230,25 @@
         <v>308</v>
       </c>
       <c r="D309" t="s">
-        <v>239</v>
+        <v>309</v>
       </c>
       <c r="E309">
         <v>2022</v>
       </c>
       <c r="F309">
-        <v>0.22871669814448767</v>
+        <v>4.4073197411209589E-2</v>
       </c>
       <c r="G309">
         <v>1</v>
       </c>
       <c r="H309">
-        <v>3162.5000000000005</v>
+        <v>3712.5000000000005</v>
       </c>
       <c r="I309">
-        <v>60.500000000000014</v>
+        <v>71.5</v>
       </c>
       <c r="J309">
-        <v>2.3100000000000005</v>
+        <v>2.52</v>
       </c>
       <c r="K309">
         <v>100</v>
@@ -34283,13 +34283,13 @@
         <v>308</v>
       </c>
       <c r="D310" t="s">
-        <v>193</v>
+        <v>310</v>
       </c>
       <c r="E310">
         <v>2022</v>
       </c>
       <c r="F310">
-        <v>0.61052976624370348</v>
+        <v>1.0883760118599757</v>
       </c>
       <c r="G310">
         <v>1</v>
@@ -34336,25 +34336,25 @@
         <v>308</v>
       </c>
       <c r="D311" t="s">
-        <v>309</v>
+        <v>57</v>
       </c>
       <c r="E311">
         <v>2022</v>
       </c>
       <c r="F311">
-        <v>0.57944656385895543</v>
+        <v>5.4743550468660328E-2</v>
       </c>
       <c r="G311">
         <v>1</v>
       </c>
       <c r="H311">
-        <v>2750</v>
+        <v>3162.5000000000005</v>
       </c>
       <c r="I311">
-        <v>55.000000000000007</v>
+        <v>60.500000000000014</v>
       </c>
       <c r="J311">
-        <v>2.1</v>
+        <v>2.3100000000000005</v>
       </c>
       <c r="K311">
         <v>100</v>
@@ -34389,25 +34389,25 @@
         <v>308</v>
       </c>
       <c r="D312" t="s">
-        <v>310</v>
+        <v>239</v>
       </c>
       <c r="E312">
         <v>2022</v>
       </c>
       <c r="F312">
-        <v>1.0883760118599757</v>
+        <v>0.22871669814448767</v>
       </c>
       <c r="G312">
         <v>1</v>
       </c>
       <c r="H312">
-        <v>2750</v>
+        <v>3162.5000000000005</v>
       </c>
       <c r="I312">
-        <v>55.000000000000007</v>
+        <v>60.500000000000014</v>
       </c>
       <c r="J312">
-        <v>2.1</v>
+        <v>2.3100000000000005</v>
       </c>
       <c r="K312">
         <v>100</v>
@@ -34448,7 +34448,7 @@
         <v>2022</v>
       </c>
       <c r="F313">
-        <v>6.0310691194286808E-2</v>
+        <v>6.3558189950902247E-2</v>
       </c>
       <c r="G313">
         <v>1</v>
@@ -34495,13 +34495,13 @@
         <v>308</v>
       </c>
       <c r="D314" t="s">
-        <v>312</v>
+        <v>204</v>
       </c>
       <c r="E314">
         <v>2022</v>
       </c>
       <c r="F314">
-        <v>5.8918906012880183E-2</v>
+        <v>7.8403898552572848E-2</v>
       </c>
       <c r="G314">
         <v>1</v>
@@ -34510,7 +34510,7 @@
         <v>3162.5000000000005</v>
       </c>
       <c r="I314">
-        <v>60.500000000000021</v>
+        <v>60.500000000000014</v>
       </c>
       <c r="J314">
         <v>2.3100000000000005</v>
@@ -34548,13 +34548,13 @@
         <v>308</v>
       </c>
       <c r="D315" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E315">
         <v>2022</v>
       </c>
       <c r="F315">
-        <v>0.15541601192373908</v>
+        <v>6.9589259070330922E-2</v>
       </c>
       <c r="G315">
         <v>1</v>
@@ -34563,7 +34563,7 @@
         <v>3162.5000000000005</v>
       </c>
       <c r="I315">
-        <v>60.500000000000014</v>
+        <v>60.500000000000007</v>
       </c>
       <c r="J315">
         <v>2.3100000000000005</v>
@@ -34601,13 +34601,13 @@
         <v>308</v>
       </c>
       <c r="D316" t="s">
-        <v>204</v>
+        <v>313</v>
       </c>
       <c r="E316">
         <v>2022</v>
       </c>
       <c r="F316">
-        <v>7.8403898552572848E-2</v>
+        <v>0.10670353057450742</v>
       </c>
       <c r="G316">
         <v>1</v>
@@ -34660,19 +34660,19 @@
         <v>2022</v>
       </c>
       <c r="F317">
-        <v>0.19299421182171778</v>
+        <v>4.3145340623605172E-2</v>
       </c>
       <c r="G317">
         <v>1</v>
       </c>
       <c r="H317">
-        <v>3162.5000000000005</v>
+        <v>3712.5000000000005</v>
       </c>
       <c r="I317">
-        <v>60.500000000000014</v>
+        <v>71.5</v>
       </c>
       <c r="J317">
-        <v>2.3100000000000005</v>
+        <v>2.52</v>
       </c>
       <c r="K317">
         <v>100</v>
@@ -34707,13 +34707,13 @@
         <v>308</v>
       </c>
       <c r="D318" t="s">
-        <v>315</v>
+        <v>291</v>
       </c>
       <c r="E318">
         <v>2022</v>
       </c>
       <c r="F318">
-        <v>6.9589259070330922E-2</v>
+        <v>0.13082780705222213</v>
       </c>
       <c r="G318">
         <v>1</v>
@@ -34722,7 +34722,7 @@
         <v>3162.5000000000005</v>
       </c>
       <c r="I318">
-        <v>60.500000000000007</v>
+        <v>60.500000000000014</v>
       </c>
       <c r="J318">
         <v>2.3100000000000005</v>
@@ -34760,25 +34760,25 @@
         <v>308</v>
       </c>
       <c r="D319" t="s">
-        <v>15</v>
+        <v>315</v>
       </c>
       <c r="E319">
         <v>2022</v>
       </c>
       <c r="F319">
-        <v>0.11134281451252948</v>
+        <v>0.56367299846968055</v>
       </c>
       <c r="G319">
         <v>1</v>
       </c>
       <c r="H319">
-        <v>3162.5000000000005</v>
+        <v>2750</v>
       </c>
       <c r="I319">
-        <v>60.500000000000014</v>
+        <v>55.000000000000007</v>
       </c>
       <c r="J319">
-        <v>2.3100000000000005</v>
+        <v>2.1</v>
       </c>
       <c r="K319">
         <v>100</v>
@@ -34813,13 +34813,13 @@
         <v>308</v>
       </c>
       <c r="D320" t="s">
-        <v>21</v>
+        <v>316</v>
       </c>
       <c r="E320">
         <v>2022</v>
       </c>
       <c r="F320">
-        <v>8.7682466428616976E-2</v>
+        <v>0.19299421182171778</v>
       </c>
       <c r="G320">
         <v>1</v>
@@ -34828,7 +34828,7 @@
         <v>3162.5000000000005</v>
       </c>
       <c r="I320">
-        <v>60.500000000000007</v>
+        <v>60.500000000000014</v>
       </c>
       <c r="J320">
         <v>2.3100000000000005</v>
@@ -34866,25 +34866,25 @@
         <v>308</v>
       </c>
       <c r="D321" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="E321">
         <v>2022</v>
       </c>
       <c r="F321">
-        <v>5.1032123318242681E-2</v>
+        <v>0.35629700644009438</v>
       </c>
       <c r="G321">
         <v>1</v>
       </c>
       <c r="H321">
-        <v>3162.5000000000005</v>
+        <v>2750</v>
       </c>
       <c r="I321">
-        <v>60.500000000000021</v>
+        <v>55</v>
       </c>
       <c r="J321">
-        <v>2.3100000000000005</v>
+        <v>2.1</v>
       </c>
       <c r="K321">
         <v>100</v>
@@ -34919,25 +34919,25 @@
         <v>308</v>
       </c>
       <c r="D322" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="E322">
         <v>2022</v>
       </c>
       <c r="F322">
-        <v>4.4073197411209589E-2</v>
+        <v>6.0310691194286808E-2</v>
       </c>
       <c r="G322">
         <v>1</v>
       </c>
       <c r="H322">
-        <v>3712.5000000000005</v>
+        <v>3162.5000000000005</v>
       </c>
       <c r="I322">
-        <v>71.5</v>
+        <v>60.500000000000014</v>
       </c>
       <c r="J322">
-        <v>2.52</v>
+        <v>2.3100000000000005</v>
       </c>
       <c r="K322">
         <v>100</v>
@@ -34972,25 +34972,25 @@
         <v>308</v>
       </c>
       <c r="D323" t="s">
-        <v>318</v>
+        <v>193</v>
       </c>
       <c r="E323">
         <v>2022</v>
       </c>
       <c r="F323">
-        <v>0.1577356538927501</v>
+        <v>0.61052976624370348</v>
       </c>
       <c r="G323">
         <v>1</v>
       </c>
       <c r="H323">
-        <v>3162.5000000000005</v>
+        <v>2750</v>
       </c>
       <c r="I323">
-        <v>60.500000000000014</v>
+        <v>55.000000000000007</v>
       </c>
       <c r="J323">
-        <v>2.3100000000000005</v>
+        <v>2.1</v>
       </c>
       <c r="K323">
         <v>100</v>
@@ -35031,19 +35031,19 @@
         <v>2022</v>
       </c>
       <c r="F324">
-        <v>0.35629700644009438</v>
+        <v>0.20320063648536632</v>
       </c>
       <c r="G324">
         <v>1</v>
       </c>
       <c r="H324">
-        <v>2750</v>
+        <v>3162.5000000000005</v>
       </c>
       <c r="I324">
-        <v>55</v>
+        <v>60.500000000000014</v>
       </c>
       <c r="J324">
-        <v>2.1</v>
+        <v>2.3100000000000005</v>
       </c>
       <c r="K324">
         <v>100</v>
@@ -35078,25 +35078,25 @@
         <v>308</v>
       </c>
       <c r="D325" t="s">
-        <v>320</v>
+        <v>83</v>
       </c>
       <c r="E325">
         <v>2022</v>
       </c>
       <c r="F325">
-        <v>6.3558189950902247E-2</v>
+        <v>0.50939337639482241</v>
       </c>
       <c r="G325">
         <v>1</v>
       </c>
       <c r="H325">
-        <v>3162.5000000000005</v>
+        <v>2750</v>
       </c>
       <c r="I325">
-        <v>60.500000000000014</v>
+        <v>55.000000000000007</v>
       </c>
       <c r="J325">
-        <v>2.3100000000000005</v>
+        <v>2.1</v>
       </c>
       <c r="K325">
         <v>100</v>
@@ -35131,25 +35131,25 @@
         <v>308</v>
       </c>
       <c r="D326" t="s">
-        <v>321</v>
+        <v>58</v>
       </c>
       <c r="E326">
         <v>2022</v>
       </c>
       <c r="F326">
-        <v>0.54140443556717466</v>
+        <v>0.23196419690110309</v>
       </c>
       <c r="G326">
         <v>1</v>
       </c>
       <c r="H326">
-        <v>2750</v>
+        <v>3162.5000000000005</v>
       </c>
       <c r="I326">
-        <v>55.000000000000007</v>
+        <v>60.500000000000014</v>
       </c>
       <c r="J326">
-        <v>2.1</v>
+        <v>2.3100000000000005</v>
       </c>
       <c r="K326">
         <v>100</v>
@@ -35184,13 +35184,13 @@
         <v>308</v>
       </c>
       <c r="D327" t="s">
-        <v>63</v>
+        <v>320</v>
       </c>
       <c r="E327">
         <v>2022</v>
       </c>
       <c r="F327">
-        <v>5.4743550468660328E-2</v>
+        <v>0.10067246145507874</v>
       </c>
       <c r="G327">
         <v>1</v>
@@ -35237,25 +35237,25 @@
         <v>308</v>
       </c>
       <c r="D328" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="E328">
         <v>2022</v>
       </c>
       <c r="F328">
-        <v>4.3145340623605172E-2</v>
+        <v>5.1032123318242681E-2</v>
       </c>
       <c r="G328">
         <v>1</v>
       </c>
       <c r="H328">
-        <v>3712.5000000000005</v>
+        <v>3162.5000000000005</v>
       </c>
       <c r="I328">
-        <v>71.5</v>
+        <v>60.500000000000021</v>
       </c>
       <c r="J328">
-        <v>2.52</v>
+        <v>2.3100000000000005</v>
       </c>
       <c r="K328">
         <v>100</v>
@@ -35290,13 +35290,13 @@
         <v>308</v>
       </c>
       <c r="D329" t="s">
-        <v>323</v>
+        <v>14</v>
       </c>
       <c r="E329">
         <v>2022</v>
       </c>
       <c r="F329">
-        <v>0.10670353057450742</v>
+        <v>8.7682466428616976E-2</v>
       </c>
       <c r="G329">
         <v>1</v>
@@ -35305,7 +35305,7 @@
         <v>3162.5000000000005</v>
       </c>
       <c r="I329">
-        <v>60.500000000000014</v>
+        <v>60.500000000000007</v>
       </c>
       <c r="J329">
         <v>2.3100000000000005</v>
@@ -35343,25 +35343,25 @@
         <v>308</v>
       </c>
       <c r="D330" t="s">
-        <v>80</v>
+        <v>322</v>
       </c>
       <c r="E330">
         <v>2022</v>
       </c>
       <c r="F330">
-        <v>0.50939337639482241</v>
+        <v>5.8918906012880183E-2</v>
       </c>
       <c r="G330">
         <v>1</v>
       </c>
       <c r="H330">
-        <v>2750</v>
+        <v>3162.5000000000005</v>
       </c>
       <c r="I330">
-        <v>55.000000000000007</v>
+        <v>60.500000000000021</v>
       </c>
       <c r="J330">
-        <v>2.1</v>
+        <v>2.3100000000000005</v>
       </c>
       <c r="K330">
         <v>100</v>
@@ -35396,13 +35396,13 @@
         <v>308</v>
       </c>
       <c r="D331" t="s">
-        <v>324</v>
+        <v>151</v>
       </c>
       <c r="E331">
         <v>2022</v>
       </c>
       <c r="F331">
-        <v>4.4073197411209589E-2</v>
+        <v>4.5464982592616207E-2</v>
       </c>
       <c r="G331">
         <v>1</v>
@@ -35449,13 +35449,13 @@
         <v>308</v>
       </c>
       <c r="D332" t="s">
-        <v>83</v>
+        <v>323</v>
       </c>
       <c r="E332">
         <v>2022</v>
       </c>
       <c r="F332">
-        <v>0.23196419690110309</v>
+        <v>0.13036387865841995</v>
       </c>
       <c r="G332">
         <v>1</v>
@@ -35502,13 +35502,13 @@
         <v>308</v>
       </c>
       <c r="D333" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="E333">
         <v>2022</v>
       </c>
       <c r="F333">
-        <v>4.1753555442198553E-2</v>
+        <v>4.4073197411209589E-2</v>
       </c>
       <c r="G333">
         <v>1</v>
@@ -35555,25 +35555,25 @@
         <v>308</v>
       </c>
       <c r="D334" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="E334">
         <v>2022</v>
       </c>
       <c r="F334">
-        <v>0.13036387865841995</v>
+        <v>0.57944656385895543</v>
       </c>
       <c r="G334">
         <v>1</v>
       </c>
       <c r="H334">
-        <v>3162.5000000000005</v>
+        <v>2750</v>
       </c>
       <c r="I334">
-        <v>60.500000000000014</v>
+        <v>55.000000000000007</v>
       </c>
       <c r="J334">
-        <v>2.3100000000000005</v>
+        <v>2.1</v>
       </c>
       <c r="K334">
         <v>100</v>
@@ -35608,13 +35608,13 @@
         <v>308</v>
       </c>
       <c r="D335" t="s">
-        <v>151</v>
+        <v>326</v>
       </c>
       <c r="E335">
         <v>2022</v>
       </c>
       <c r="F335">
-        <v>4.5464982592616207E-2</v>
+        <v>4.1753555442198553E-2</v>
       </c>
       <c r="G335">
         <v>1</v>
@@ -35661,13 +35661,13 @@
         <v>308</v>
       </c>
       <c r="D336" t="s">
-        <v>291</v>
+        <v>327</v>
       </c>
       <c r="E336">
         <v>2022</v>
       </c>
       <c r="F336">
-        <v>0.13082780705222213</v>
+        <v>0.15541601192373908</v>
       </c>
       <c r="G336">
         <v>1</v>
@@ -35714,13 +35714,13 @@
         <v>308</v>
       </c>
       <c r="D337" t="s">
-        <v>99</v>
+        <v>16</v>
       </c>
       <c r="E337">
         <v>2022</v>
       </c>
       <c r="F337">
-        <v>0.29181095970158766</v>
+        <v>0.11134281451252948</v>
       </c>
       <c r="G337">
         <v>1</v>
@@ -35767,25 +35767,25 @@
         <v>308</v>
       </c>
       <c r="D338" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="E338">
         <v>2022</v>
       </c>
       <c r="F338">
-        <v>0.10067246145507874</v>
+        <v>0.54140443556717466</v>
       </c>
       <c r="G338">
         <v>1</v>
       </c>
       <c r="H338">
-        <v>3162.5000000000005</v>
+        <v>2750</v>
       </c>
       <c r="I338">
-        <v>60.500000000000014</v>
+        <v>55.000000000000007</v>
       </c>
       <c r="J338">
-        <v>2.3100000000000005</v>
+        <v>2.1</v>
       </c>
       <c r="K338">
         <v>100</v>
@@ -35820,25 +35820,25 @@
         <v>308</v>
       </c>
       <c r="D339" t="s">
-        <v>328</v>
+        <v>99</v>
       </c>
       <c r="E339">
         <v>2022</v>
       </c>
       <c r="F339">
-        <v>0.56367299846968055</v>
+        <v>0.29181095970158766</v>
       </c>
       <c r="G339">
         <v>1</v>
       </c>
       <c r="H339">
-        <v>2750</v>
+        <v>3162.5000000000005</v>
       </c>
       <c r="I339">
-        <v>55.000000000000007</v>
+        <v>60.500000000000014</v>
       </c>
       <c r="J339">
-        <v>2.1</v>
+        <v>2.3100000000000005</v>
       </c>
       <c r="K339">
         <v>100</v>
@@ -35879,7 +35879,7 @@
         <v>2022</v>
       </c>
       <c r="F340">
-        <v>0.20320063648536632</v>
+        <v>0.1577356538927501</v>
       </c>
       <c r="G340">
         <v>1</v>
@@ -35979,7 +35979,7 @@
         <v>308</v>
       </c>
       <c r="D342" t="s">
-        <v>317</v>
+        <v>324</v>
       </c>
       <c r="E342">
         <v>1959</v>
@@ -36085,7 +36085,7 @@
         <v>308</v>
       </c>
       <c r="D344" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="E344">
         <v>1973</v>
@@ -36244,7 +36244,7 @@
         <v>308</v>
       </c>
       <c r="D347" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="E347">
         <v>2015</v>
@@ -36297,7 +36297,7 @@
         <v>308</v>
       </c>
       <c r="D348" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="E348">
         <v>1931</v>
@@ -36350,7 +36350,7 @@
         <v>308</v>
       </c>
       <c r="D349" t="s">
-        <v>321</v>
+        <v>328</v>
       </c>
       <c r="E349">
         <v>1949</v>
@@ -36403,7 +36403,7 @@
         <v>308</v>
       </c>
       <c r="D350" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="E350">
         <v>1951</v>
@@ -36509,7 +36509,7 @@
         <v>308</v>
       </c>
       <c r="D352" t="s">
-        <v>311</v>
+        <v>318</v>
       </c>
       <c r="E352">
         <v>1958</v>
@@ -36562,7 +36562,7 @@
         <v>308</v>
       </c>
       <c r="D353" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
       <c r="E353">
         <v>1967</v>
@@ -36615,7 +36615,7 @@
         <v>308</v>
       </c>
       <c r="D354" t="s">
-        <v>329</v>
+        <v>319</v>
       </c>
       <c r="E354">
         <v>1968</v>
@@ -36668,7 +36668,7 @@
         <v>308</v>
       </c>
       <c r="D355" t="s">
-        <v>328</v>
+        <v>315</v>
       </c>
       <c r="E355">
         <v>1929</v>
@@ -36721,7 +36721,7 @@
         <v>308</v>
       </c>
       <c r="D356" t="s">
-        <v>329</v>
+        <v>319</v>
       </c>
       <c r="E356">
         <v>1949</v>
@@ -36827,7 +36827,7 @@
         <v>308</v>
       </c>
       <c r="D358" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="E358">
         <v>1952</v>
@@ -36880,7 +36880,7 @@
         <v>308</v>
       </c>
       <c r="D359" t="s">
-        <v>328</v>
+        <v>315</v>
       </c>
       <c r="E359">
         <v>1913</v>
@@ -36933,7 +36933,7 @@
         <v>308</v>
       </c>
       <c r="D360" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="E360">
         <v>1924</v>
@@ -37039,7 +37039,7 @@
         <v>308</v>
       </c>
       <c r="D362" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="E362">
         <v>1971</v>
@@ -37145,7 +37145,7 @@
         <v>308</v>
       </c>
       <c r="D364" t="s">
-        <v>322</v>
+        <v>314</v>
       </c>
       <c r="E364">
         <v>1927</v>
@@ -37357,7 +37357,7 @@
         <v>308</v>
       </c>
       <c r="D368" t="s">
-        <v>324</v>
+        <v>309</v>
       </c>
       <c r="E368">
         <v>1920</v>
@@ -37463,7 +37463,7 @@
         <v>308</v>
       </c>
       <c r="D370" t="s">
-        <v>318</v>
+        <v>329</v>
       </c>
       <c r="E370">
         <v>1950</v>
@@ -37516,7 +37516,7 @@
         <v>308</v>
       </c>
       <c r="D371" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="E371">
         <v>1954</v>
@@ -37622,7 +37622,7 @@
         <v>308</v>
       </c>
       <c r="D373" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="E373">
         <v>1971</v>
@@ -37675,7 +37675,7 @@
         <v>308</v>
       </c>
       <c r="D374" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="E374">
         <v>1959</v>
@@ -38099,7 +38099,7 @@
         <v>308</v>
       </c>
       <c r="D382" t="s">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="E382">
         <v>2022</v>
@@ -38311,7 +38311,7 @@
         <v>308</v>
       </c>
       <c r="D386" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="E386">
         <v>2022</v>
@@ -38417,7 +38417,7 @@
         <v>383</v>
       </c>
       <c r="D388" t="s">
-        <v>83</v>
+        <v>58</v>
       </c>
       <c r="E388">
         <v>1989</v>
@@ -38470,7 +38470,7 @@
         <v>383</v>
       </c>
       <c r="D389" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="E389">
         <v>1975</v>
@@ -38523,7 +38523,7 @@
         <v>383</v>
       </c>
       <c r="D390" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="E390">
         <v>1966</v>
@@ -38629,7 +38629,7 @@
         <v>383</v>
       </c>
       <c r="D392" t="s">
-        <v>309</v>
+        <v>325</v>
       </c>
       <c r="E392">
         <v>2015</v>
@@ -38682,7 +38682,7 @@
         <v>383</v>
       </c>
       <c r="D393" t="s">
-        <v>309</v>
+        <v>325</v>
       </c>
       <c r="E393">
         <v>1982</v>
@@ -38735,7 +38735,7 @@
         <v>383</v>
       </c>
       <c r="D394" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="E394">
         <v>2015</v>
@@ -38788,7 +38788,7 @@
         <v>383</v>
       </c>
       <c r="D395" t="s">
-        <v>320</v>
+        <v>311</v>
       </c>
       <c r="E395">
         <v>2015</v>
@@ -38841,7 +38841,7 @@
         <v>383</v>
       </c>
       <c r="D396" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="E396">
         <v>1961</v>
@@ -38894,7 +38894,7 @@
         <v>383</v>
       </c>
       <c r="D397" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="E397">
         <v>2005</v>
@@ -38947,7 +38947,7 @@
         <v>383</v>
       </c>
       <c r="D398" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="E398">
         <v>1991</v>
@@ -39106,7 +39106,7 @@
         <v>383</v>
       </c>
       <c r="D401" t="s">
-        <v>328</v>
+        <v>315</v>
       </c>
       <c r="E401">
         <v>1971</v>
@@ -39159,7 +39159,7 @@
         <v>383</v>
       </c>
       <c r="D402" t="s">
-        <v>318</v>
+        <v>329</v>
       </c>
       <c r="E402">
         <v>1973</v>
@@ -39318,7 +39318,7 @@
         <v>383</v>
       </c>
       <c r="D405" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E405">
         <v>1978</v>
@@ -39371,7 +39371,7 @@
         <v>383</v>
       </c>
       <c r="D406" t="s">
-        <v>321</v>
+        <v>328</v>
       </c>
       <c r="E406">
         <v>1923</v>
@@ -39424,7 +39424,7 @@
         <v>308</v>
       </c>
       <c r="D407" t="s">
-        <v>312</v>
+        <v>322</v>
       </c>
       <c r="E407">
         <v>1959</v>
@@ -39583,7 +39583,7 @@
         <v>308</v>
       </c>
       <c r="D410" t="s">
-        <v>313</v>
+        <v>327</v>
       </c>
       <c r="E410">
         <v>1953</v>
@@ -39742,7 +39742,7 @@
         <v>308</v>
       </c>
       <c r="D413" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="E413">
         <v>1962</v>
@@ -39795,7 +39795,7 @@
         <v>308</v>
       </c>
       <c r="D414" t="s">
-        <v>321</v>
+        <v>328</v>
       </c>
       <c r="E414">
         <v>2015</v>
@@ -39848,7 +39848,7 @@
         <v>308</v>
       </c>
       <c r="D415" t="s">
-        <v>329</v>
+        <v>319</v>
       </c>
       <c r="E415">
         <v>1927</v>
@@ -39901,7 +39901,7 @@
         <v>308</v>
       </c>
       <c r="D416" t="s">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="E416">
         <v>1954</v>
@@ -40007,7 +40007,7 @@
         <v>308</v>
       </c>
       <c r="D418" t="s">
-        <v>321</v>
+        <v>328</v>
       </c>
       <c r="E418">
         <v>1956</v>
@@ -40060,7 +40060,7 @@
         <v>308</v>
       </c>
       <c r="D419" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="E419">
         <v>1956</v>
@@ -40166,7 +40166,7 @@
         <v>308</v>
       </c>
       <c r="D421" t="s">
-        <v>321</v>
+        <v>328</v>
       </c>
       <c r="E421">
         <v>1960</v>
@@ -40272,7 +40272,7 @@
         <v>308</v>
       </c>
       <c r="D423" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="E423">
         <v>2015</v>
@@ -40378,7 +40378,7 @@
         <v>308</v>
       </c>
       <c r="D425" t="s">
-        <v>329</v>
+        <v>319</v>
       </c>
       <c r="E425">
         <v>2015</v>
@@ -40431,7 +40431,7 @@
         <v>308</v>
       </c>
       <c r="D426" t="s">
-        <v>309</v>
+        <v>325</v>
       </c>
       <c r="E426">
         <v>2015</v>
@@ -40537,7 +40537,7 @@
         <v>308</v>
       </c>
       <c r="D428" t="s">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="E428">
         <v>1955</v>
@@ -40590,7 +40590,7 @@
         <v>308</v>
       </c>
       <c r="D429" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="E429">
         <v>2015</v>
@@ -40696,7 +40696,7 @@
         <v>308</v>
       </c>
       <c r="D431" t="s">
-        <v>322</v>
+        <v>314</v>
       </c>
       <c r="E431">
         <v>1932</v>
@@ -40855,7 +40855,7 @@
         <v>308</v>
       </c>
       <c r="D434" t="s">
-        <v>328</v>
+        <v>315</v>
       </c>
       <c r="E434">
         <v>1924</v>
@@ -40961,7 +40961,7 @@
         <v>308</v>
       </c>
       <c r="D436" t="s">
-        <v>328</v>
+        <v>315</v>
       </c>
       <c r="E436">
         <v>2002</v>
@@ -41120,7 +41120,7 @@
         <v>308</v>
       </c>
       <c r="D439" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="E439">
         <v>2015</v>
@@ -41173,7 +41173,7 @@
         <v>308</v>
       </c>
       <c r="D440" t="s">
-        <v>324</v>
+        <v>309</v>
       </c>
       <c r="E440">
         <v>1914</v>
@@ -41279,7 +41279,7 @@
         <v>308</v>
       </c>
       <c r="D442" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="E442">
         <v>1958</v>
@@ -41332,7 +41332,7 @@
         <v>439</v>
       </c>
       <c r="D443" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E443">
         <v>1992</v>
@@ -41491,7 +41491,7 @@
         <v>439</v>
       </c>
       <c r="D446" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E446">
         <v>1992</v>
@@ -41809,7 +41809,7 @@
         <v>439</v>
       </c>
       <c r="D452" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E452">
         <v>1985</v>
@@ -42067,7 +42067,7 @@
         <v>33</v>
       </c>
       <c r="L458">
-        <v>0.21124146529555179</v>
+        <v>0.21124146529555185</v>
       </c>
     </row>
     <row r="459" spans="2:20" x14ac:dyDescent="0.45">
@@ -42102,7 +42102,7 @@
         <v>33</v>
       </c>
       <c r="L459">
-        <v>0.21124146529555179</v>
+        <v>0.21124146529555185</v>
       </c>
     </row>
     <row r="460" spans="2:20" x14ac:dyDescent="0.45">
@@ -42137,7 +42137,7 @@
         <v>33</v>
       </c>
       <c r="L460">
-        <v>0.21124146529555179</v>
+        <v>0.21124146529555185</v>
       </c>
     </row>
     <row r="461" spans="2:20" x14ac:dyDescent="0.45">
@@ -44808,7 +44808,7 @@
         <v>510</v>
       </c>
       <c r="D537" t="s">
-        <v>85</v>
+        <v>62</v>
       </c>
       <c r="E537">
         <v>2022</v>
@@ -44837,13 +44837,13 @@
         <v>2022</v>
       </c>
       <c r="F538">
-        <v>0.6793056475905862</v>
+        <v>0.69928302455480262</v>
       </c>
       <c r="G538">
         <v>0.33123000000000002</v>
       </c>
       <c r="L538">
-        <v>0.2022880717304284</v>
+        <v>0.20228807173042843</v>
       </c>
     </row>
     <row r="539" spans="2:12" x14ac:dyDescent="0.45">
@@ -44860,13 +44860,13 @@
         <v>2022</v>
       </c>
       <c r="F539">
-        <v>0.69928302455480262</v>
+        <v>0.6793056475905862</v>
       </c>
       <c r="G539">
         <v>0.33123000000000002</v>
       </c>
       <c r="L539">
-        <v>0.2022880717304284</v>
+        <v>0.20228807173042843</v>
       </c>
     </row>
     <row r="540" spans="2:12" x14ac:dyDescent="0.45">
@@ -44877,7 +44877,7 @@
         <v>512</v>
       </c>
       <c r="D540" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="E540">
         <v>2022</v>
@@ -44889,7 +44889,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="L540">
-        <v>0.2022880717304284</v>
+        <v>0.20228807173042843</v>
       </c>
     </row>
     <row r="541" spans="2:12" x14ac:dyDescent="0.45">
@@ -44900,7 +44900,7 @@
         <v>512</v>
       </c>
       <c r="D541" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="E541">
         <v>2002</v>
@@ -44923,7 +44923,7 @@
         <v>512</v>
       </c>
       <c r="D542" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="E542">
         <v>2003</v>
@@ -44946,7 +44946,7 @@
         <v>512</v>
       </c>
       <c r="D543" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="E543">
         <v>2004</v>
@@ -44969,7 +44969,7 @@
         <v>512</v>
       </c>
       <c r="D544" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="E544">
         <v>2005</v>
@@ -44992,7 +44992,7 @@
         <v>512</v>
       </c>
       <c r="D545" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="E545">
         <v>2007</v>
@@ -45015,7 +45015,7 @@
         <v>512</v>
       </c>
       <c r="D546" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="E546">
         <v>2008</v>
@@ -45038,7 +45038,7 @@
         <v>512</v>
       </c>
       <c r="D547" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="E547">
         <v>2009</v>
@@ -45061,7 +45061,7 @@
         <v>512</v>
       </c>
       <c r="D548" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="E548">
         <v>2010</v>
@@ -45084,7 +45084,7 @@
         <v>512</v>
       </c>
       <c r="D549" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="E549">
         <v>2011</v>
@@ -45107,7 +45107,7 @@
         <v>512</v>
       </c>
       <c r="D550" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="E550">
         <v>2012</v>
@@ -45130,7 +45130,7 @@
         <v>512</v>
       </c>
       <c r="D551" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="E551">
         <v>2015</v>
@@ -45153,7 +45153,7 @@
         <v>512</v>
       </c>
       <c r="D552" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="E552">
         <v>2018</v>
@@ -45176,7 +45176,7 @@
         <v>512</v>
       </c>
       <c r="D553" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="E553">
         <v>2019</v>
@@ -45199,7 +45199,7 @@
         <v>512</v>
       </c>
       <c r="D554" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="E554">
         <v>2023</v>
@@ -45222,7 +45222,7 @@
         <v>512</v>
       </c>
       <c r="D555" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="E555">
         <v>2005</v>
@@ -45245,7 +45245,7 @@
         <v>512</v>
       </c>
       <c r="D556" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="E556">
         <v>2006</v>
@@ -45268,7 +45268,7 @@
         <v>512</v>
       </c>
       <c r="D557" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="E557">
         <v>2007</v>
@@ -45291,7 +45291,7 @@
         <v>512</v>
       </c>
       <c r="D558" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="E558">
         <v>2008</v>
@@ -45314,7 +45314,7 @@
         <v>512</v>
       </c>
       <c r="D559" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="E559">
         <v>2009</v>
@@ -45337,7 +45337,7 @@
         <v>512</v>
       </c>
       <c r="D560" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="E560">
         <v>2010</v>
@@ -45360,7 +45360,7 @@
         <v>512</v>
       </c>
       <c r="D561" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="E561">
         <v>2011</v>
@@ -45383,7 +45383,7 @@
         <v>512</v>
       </c>
       <c r="D562" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="E562">
         <v>2012</v>
@@ -45406,7 +45406,7 @@
         <v>512</v>
       </c>
       <c r="D563" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="E563">
         <v>2015</v>
@@ -45429,7 +45429,7 @@
         <v>512</v>
       </c>
       <c r="D564" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="E564">
         <v>2016</v>
@@ -45452,7 +45452,7 @@
         <v>512</v>
       </c>
       <c r="D565" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="E565">
         <v>2018</v>
@@ -45475,7 +45475,7 @@
         <v>512</v>
       </c>
       <c r="D566" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="E566">
         <v>2019</v>
@@ -45498,7 +45498,7 @@
         <v>512</v>
       </c>
       <c r="D567" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="E567">
         <v>2021</v>
@@ -45521,7 +45521,7 @@
         <v>512</v>
       </c>
       <c r="D568" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="E568">
         <v>2022</v>
@@ -45544,7 +45544,7 @@
         <v>512</v>
       </c>
       <c r="D569" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="E569">
         <v>2023</v>
@@ -45567,7 +45567,7 @@
         <v>512</v>
       </c>
       <c r="D570" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="E570">
         <v>2024</v>

--- a/VerveStacks_ITA_grids/vt_vervestacks_ITA_v1.xlsx
+++ b/VerveStacks_ITA_grids/vt_vervestacks_ITA_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9F73EAAA-FE79-49E3-A711-F2F9897927A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B3D63866-60A5-426F-AF4A-B565F8AE6526}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{E0B7694D-DB59-4098-A227-472B6444F75D}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{6D5BE3F6-1C53-4943-B41A-75691FFCE422}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="2" r:id="rId1"/>
@@ -81,27 +81,27 @@
     <t>bioenergy</t>
   </si>
   <si>
+    <t>e_w84696559-380</t>
+  </si>
+  <si>
+    <t>e_w34157795-380</t>
+  </si>
+  <si>
     <t>e_w108020416-380</t>
   </si>
   <si>
-    <t>e_w34157795-380</t>
+    <t>e_w98902899-380</t>
+  </si>
+  <si>
+    <t>e_w109756016-380</t>
   </si>
   <si>
     <t>e_w144005863-380</t>
   </si>
   <si>
-    <t>e_w109756016-380</t>
-  </si>
-  <si>
-    <t>e_w84696559-380</t>
-  </si>
-  <si>
     <t>e_w58440884-380</t>
   </si>
   <si>
-    <t>e_w98902899-380</t>
-  </si>
-  <si>
     <t>e_w81938081-380</t>
   </si>
   <si>
@@ -141,18 +141,18 @@
     <t>coal</t>
   </si>
   <si>
+    <t>e_w82767145-380</t>
+  </si>
+  <si>
+    <t>e_w418902800-380</t>
+  </si>
+  <si>
+    <t>e_w303915533-380</t>
+  </si>
+  <si>
     <t>e_w409439916-380</t>
   </si>
   <si>
-    <t>e_w303915533-380</t>
-  </si>
-  <si>
-    <t>e_w82767145-380</t>
-  </si>
-  <si>
-    <t>e_w418902800-380</t>
-  </si>
-  <si>
     <t>ep_coal_subcritical_G100000102764</t>
   </si>
   <si>
@@ -189,120 +189,120 @@
     <t>gas</t>
   </si>
   <si>
+    <t>e_w338753171-380</t>
+  </si>
+  <si>
+    <t>e_w255011550-380</t>
+  </si>
+  <si>
+    <t>e_w414663585-380</t>
+  </si>
+  <si>
+    <t>e_w199675964-380</t>
+  </si>
+  <si>
+    <t>e_w103381531-380</t>
+  </si>
+  <si>
+    <t>e_w133601335-380</t>
+  </si>
+  <si>
+    <t>e_w59462715-380</t>
+  </si>
+  <si>
+    <t>e_w421827453-380</t>
+  </si>
+  <si>
+    <t>e_w149997403-380</t>
+  </si>
+  <si>
+    <t>e_w100407576-380</t>
+  </si>
+  <si>
+    <t>e_w60725875-380</t>
+  </si>
+  <si>
+    <t>e_w145665799-380</t>
+  </si>
+  <si>
+    <t>e_w82078641-380</t>
+  </si>
+  <si>
+    <t>e_w61157826-380</t>
+  </si>
+  <si>
+    <t>e_w181125039-380</t>
+  </si>
+  <si>
+    <t>e_w1137611914-380</t>
+  </si>
+  <si>
+    <t>e_w82084019-380</t>
+  </si>
+  <si>
+    <t>e_w432729521-380</t>
+  </si>
+  <si>
+    <t>e_w172302572-380</t>
+  </si>
+  <si>
+    <t>e_w99826025-380</t>
+  </si>
+  <si>
+    <t>e_w416989699-380</t>
+  </si>
+  <si>
+    <t>e_w411026199-380</t>
+  </si>
+  <si>
+    <t>e_w107438024-380</t>
+  </si>
+  <si>
+    <t>e_w339104227-380</t>
+  </si>
+  <si>
+    <t>e_w116797658-380</t>
+  </si>
+  <si>
+    <t>e_w98900549-380</t>
+  </si>
+  <si>
+    <t>e_w162828577-380</t>
+  </si>
+  <si>
+    <t>e_w132450233-380</t>
+  </si>
+  <si>
     <t>e_w110330925-380</t>
   </si>
   <si>
-    <t>e_w162828577-380</t>
-  </si>
-  <si>
-    <t>e_w98900549-380</t>
-  </si>
-  <si>
-    <t>e_w82084019-380</t>
-  </si>
-  <si>
-    <t>e_w107438024-380</t>
-  </si>
-  <si>
-    <t>e_w82078641-380</t>
-  </si>
-  <si>
-    <t>e_w61157826-380</t>
-  </si>
-  <si>
-    <t>e_w1137611914-380</t>
-  </si>
-  <si>
-    <t>e_w338753171-380</t>
+    <t>e_w105757794-380</t>
+  </si>
+  <si>
+    <t>e_w419423704-380</t>
+  </si>
+  <si>
+    <t>e_w98421779-380</t>
+  </si>
+  <si>
+    <t>e_w103974940-380</t>
+  </si>
+  <si>
+    <t>e_w158739183-380</t>
+  </si>
+  <si>
+    <t>e_w103653592-380</t>
   </si>
   <si>
     <t>e_w162960205-380</t>
   </si>
   <si>
-    <t>e_w181125039-380</t>
-  </si>
-  <si>
-    <t>e_w133601335-380</t>
-  </si>
-  <si>
-    <t>e_w103381531-380</t>
-  </si>
-  <si>
-    <t>e_w411026199-380</t>
-  </si>
-  <si>
-    <t>e_w432729521-380</t>
-  </si>
-  <si>
-    <t>e_w172302572-380</t>
-  </si>
-  <si>
     <t>e_w109993642-380</t>
   </si>
   <si>
-    <t>e_w103653592-380</t>
-  </si>
-  <si>
-    <t>e_w339104227-380</t>
-  </si>
-  <si>
-    <t>e_w59462715-380</t>
-  </si>
-  <si>
-    <t>e_w421827453-380</t>
-  </si>
-  <si>
-    <t>e_w149997403-380</t>
-  </si>
-  <si>
-    <t>e_w100407576-380</t>
-  </si>
-  <si>
-    <t>e_w416989699-380</t>
-  </si>
-  <si>
-    <t>e_w199675964-380</t>
-  </si>
-  <si>
-    <t>e_w414663585-380</t>
-  </si>
-  <si>
-    <t>e_w255011550-380</t>
-  </si>
-  <si>
     <t>e_w105581403-380</t>
   </si>
   <si>
-    <t>e_w158739183-380</t>
-  </si>
-  <si>
-    <t>e_w99826025-380</t>
-  </si>
-  <si>
-    <t>e_w145665799-380</t>
-  </si>
-  <si>
-    <t>e_w60725875-380</t>
-  </si>
-  <si>
-    <t>e_w116797658-380</t>
-  </si>
-  <si>
-    <t>e_w419423704-380</t>
-  </si>
-  <si>
-    <t>e_w98421779-380</t>
-  </si>
-  <si>
-    <t>e_w105757794-380</t>
-  </si>
-  <si>
-    <t>e_w103974940-380</t>
-  </si>
-  <si>
-    <t>e_w132450233-380</t>
-  </si>
-  <si>
     <t>ep_gas_combined_cycle_G100000400339</t>
   </si>
   <si>
@@ -966,69 +966,69 @@
     <t>hydro</t>
   </si>
   <si>
+    <t>e_w82083756-380</t>
+  </si>
+  <si>
+    <t>e_w114931087-380</t>
+  </si>
+  <si>
+    <t>e_IT71-400</t>
+  </si>
+  <si>
+    <t>e_IT31-380</t>
+  </si>
+  <si>
+    <t>e_w64200868-380</t>
+  </si>
+  <si>
+    <t>e_IT7-380</t>
+  </si>
+  <si>
     <t>e_IT72-400</t>
   </si>
   <si>
-    <t>e_w64200868-380</t>
+    <t>e_w1100665914-380</t>
+  </si>
+  <si>
+    <t>e_IT21-380</t>
+  </si>
+  <si>
+    <t>e_w75602396-380</t>
+  </si>
+  <si>
+    <t>e_w104359058-380</t>
+  </si>
+  <si>
+    <t>e_IT71-380</t>
+  </si>
+  <si>
+    <t>e_w491424937-380</t>
+  </si>
+  <si>
+    <t>e_IT93-380</t>
+  </si>
+  <si>
+    <t>e_IT72-380</t>
+  </si>
+  <si>
+    <t>e_w72466334-380</t>
+  </si>
+  <si>
+    <t>e_w61626687-380</t>
+  </si>
+  <si>
+    <t>e_IT36-380</t>
+  </si>
+  <si>
+    <t>e_IT10-380</t>
+  </si>
+  <si>
+    <t>e_w116517585-380</t>
   </si>
   <si>
     <t>e_IT53-380</t>
   </si>
   <si>
-    <t>e_IT93-380</t>
-  </si>
-  <si>
-    <t>e_w491424937-380</t>
-  </si>
-  <si>
-    <t>e_w75602396-380</t>
-  </si>
-  <si>
-    <t>e_IT21-380</t>
-  </si>
-  <si>
-    <t>e_w1100665914-380</t>
-  </si>
-  <si>
-    <t>e_w82083756-380</t>
-  </si>
-  <si>
-    <t>e_IT71-400</t>
-  </si>
-  <si>
-    <t>e_IT10-380</t>
-  </si>
-  <si>
-    <t>e_IT72-380</t>
-  </si>
-  <si>
-    <t>e_w61626687-380</t>
-  </si>
-  <si>
-    <t>e_IT71-380</t>
-  </si>
-  <si>
-    <t>e_w114931087-380</t>
-  </si>
-  <si>
-    <t>e_IT31-380</t>
-  </si>
-  <si>
-    <t>e_w104359058-380</t>
-  </si>
-  <si>
-    <t>e_w116517585-380</t>
-  </si>
-  <si>
-    <t>e_IT36-380</t>
-  </si>
-  <si>
-    <t>e_IT7-380</t>
-  </si>
-  <si>
-    <t>e_w72466334-380</t>
-  </si>
-  <si>
     <t>ep_hydro_dam_G100000602220</t>
   </si>
   <si>
@@ -1578,12 +1578,12 @@
     <t>windon</t>
   </si>
   <si>
+    <t>elc_won_007</t>
+  </si>
+  <si>
     <t>elc_won_008</t>
   </si>
   <si>
-    <t>elc_won_007</t>
-  </si>
-  <si>
     <t>ep_windon_wind_007</t>
   </si>
   <si>
@@ -1680,42 +1680,42 @@
     <t>ele</t>
   </si>
   <si>
+    <t>Aggregated Plant - EMBER Gap - way/34157795-380_Missing Bioenergy Capacity</t>
+  </si>
+  <si>
+    <t>GW</t>
+  </si>
+  <si>
+    <t>TWh</t>
+  </si>
+  <si>
+    <t>daynite</t>
+  </si>
+  <si>
+    <t>yes</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/58440884-380_Missing Bioenergy Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/84696559-380_Missing Bioenergy Capacity</t>
+  </si>
+  <si>
     <t>Aggregated Plant - EMBER Gap - way/108020416-380_Missing Bioenergy Capacity</t>
   </si>
   <si>
-    <t>GW</t>
-  </si>
-  <si>
-    <t>TWh</t>
-  </si>
-  <si>
-    <t>daynite</t>
-  </si>
-  <si>
-    <t>yes</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/34157795-380_Missing Bioenergy Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/58440884-380_Missing Bioenergy Capacity</t>
+    <t>Aggregated Plant - EMBER Gap - way/144005863-380_Missing Bioenergy Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/81938081-380_Missing Bioenergy Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/109756016-380_Missing Bioenergy Capacity</t>
   </si>
   <si>
     <t>Aggregated Plant - EMBER Gap - way/98902899-380_Missing Bioenergy Capacity</t>
   </si>
   <si>
-    <t>Aggregated Plant - EMBER Gap - way/109756016-380_Missing Bioenergy Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/144005863-380_Missing Bioenergy Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/81938081-380_Missing Bioenergy Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/84696559-380_Missing Bioenergy Capacity</t>
-  </si>
-  <si>
     <t>Acerra power station_1</t>
   </si>
   <si>
@@ -1740,15 +1740,15 @@
     <t>Aggregated Plant - EMBER Gap - way/409439916-380_Missing Coal Capacity</t>
   </si>
   <si>
+    <t>Aggregated Plant - EMBER Gap - way/82767145-380_Missing Coal Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/418902800-380_Missing Coal Capacity</t>
+  </si>
+  <si>
     <t>Aggregated Plant - EMBER Gap - way/303915533-380_Missing Coal Capacity</t>
   </si>
   <si>
-    <t>Aggregated Plant - EMBER Gap - way/82767145-380_Missing Coal Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/418902800-380_Missing Coal Capacity</t>
-  </si>
-  <si>
     <t>Fiume Santo power station_Unit 3</t>
   </si>
   <si>
@@ -1779,126 +1779,126 @@
     <t>Torrevaldaliga Nord power station_Unit 3</t>
   </si>
   <si>
+    <t>Aggregated Plant - EMBER Gap - way/132450233-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/199675964-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/181125039-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/432729521-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/109993642-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/82767145-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/411026199-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/100407576-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/416989699-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/103653592-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/105581403-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/98421779-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/109756016-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/110330925-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/82084019-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/338753171-380_Missing Gas Capacity</t>
+  </si>
+  <si>
     <t>Aggregated Plant - EMBER Gap - way/162828577-380_Missing Gas Capacity</t>
   </si>
   <si>
+    <t>Aggregated Plant - EMBER Gap - way/98900549-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/116797658-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/339104227-380_Missing Gas Capacity</t>
+  </si>
+  <si>
     <t>Aggregated Plant - EMBER Gap - way/107438024-380_Missing Gas Capacity</t>
   </si>
   <si>
-    <t>Aggregated Plant - EMBER Gap - way/116797658-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/339104227-380_Missing Gas Capacity</t>
+    <t>Aggregated Plant - EMBER Gap - way/172302572-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/59462715-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/105757794-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/255011550-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/158739183-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/1137611914-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/145665799-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/414663585-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/61157826-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/149997403-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/133601335-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/162960205-380_Missing Gas Capacity</t>
   </si>
   <si>
     <t>Aggregated Plant - EMBER Gap - way/419423704-380_Missing Gas Capacity</t>
   </si>
   <si>
-    <t>Aggregated Plant - EMBER Gap - way/414663585-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/61157826-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/59462715-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/172302572-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/255011550-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/105757794-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/149997403-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/133601335-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/162960205-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/145665799-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/158739183-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/1137611914-380_Missing Gas Capacity</t>
+    <t>Aggregated Plant - EMBER Gap - way/103381531-380_Missing Gas Capacity</t>
   </si>
   <si>
     <t>Aggregated Plant - EMBER Gap - way/60725875-380_Missing Gas Capacity</t>
   </si>
   <si>
-    <t>Aggregated Plant - EMBER Gap - way/181125039-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/432729521-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/199675964-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/100407576-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/109993642-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/98900549-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/338753171-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/103381531-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/411026199-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/98421779-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/105581403-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/109756016-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/82084019-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/110330925-380_Missing Gas Capacity</t>
+    <t>Aggregated Plant - EMBER Gap - way/421827453-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/99826025-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/82078641-380_Missing Gas Capacity</t>
   </si>
   <si>
     <t>Aggregated Plant - EMBER Gap - way/103974940-380_Missing Gas Capacity</t>
   </si>
   <si>
-    <t>Aggregated Plant - EMBER Gap - way/82078641-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/421827453-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/99826025-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/132450233-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/416989699-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/103653592-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/82767145-380_Missing Gas Capacity</t>
-  </si>
-  <si>
     <t>Altomonte power station_1</t>
   </si>
   <si>
@@ -2211,91 +2211,94 @@
     <t>Valle Secolo geothermal power plant_2</t>
   </si>
   <si>
+    <t>Aggregated Plant - IRENA Gap - way/96190189-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/116517585-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/61712456-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/108020416-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - IT71-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - IT7-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/339703159-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - IT30-500_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - IT53-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
     <t>Aggregated Plant - IRENA Gap - way/64200868-380_Missing Hydro Capacity</t>
   </si>
   <si>
-    <t>Aggregated Plant - IRENA Gap - way/61712456-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - IT30-500_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - IT7-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/339703159-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - IT53-380_Missing Hydro Capacity</t>
+    <t>Aggregated Plant - IRENA Gap - way/59462263-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/1100665914-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - IT72-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/144005863-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - IT21-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/72466334-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/82083756-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/104359058-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/419423704-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/491424937-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - IT31-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/61626687-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/114931087-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - IT93-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/1137611914-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/109588422-380_Missing Hydro Capacity</t>
   </si>
   <si>
     <t>Aggregated Plant - IRENA Gap - IT72-400_Missing Hydro Capacity</t>
   </si>
   <si>
-    <t>Aggregated Plant - IRENA Gap - way/109588422-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/1137611914-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - IT71-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/108020416-380_Missing Hydro Capacity</t>
+    <t>Aggregated Plant - IRENA Gap - IT10-380_Missing Hydro Capacity</t>
   </si>
   <si>
     <t>Aggregated Plant - IRENA Gap - way/338753171-380_Missing Hydro Capacity</t>
   </si>
   <si>
-    <t>Aggregated Plant - IRENA Gap - IT93-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - IT10-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - IT72-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/1100665914-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - IT21-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/59462263-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/144005863-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/114931087-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - IT31-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/61626687-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/82083756-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/491424937-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/419423704-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/104359058-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/72466334-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/96190189-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/116517585-380_Missing Hydro Capacity</t>
+    <t>Aggregated Plant - IRENA Gap - way/75602396-380_Missing Hydro Capacity</t>
   </si>
   <si>
     <t>Aggregated Plant - IRENA Gap - IT36-380_Missing Hydro Capacity</t>
@@ -2304,9 +2307,6 @@
     <t>Aggregated Plant - IRENA Gap - IT71-400_Missing Hydro Capacity</t>
   </si>
   <si>
-    <t>Aggregated Plant - IRENA Gap - way/75602396-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
     <t>Baschi hydroelectric plant_</t>
   </si>
   <si>
@@ -2613,15 +2613,15 @@
     <t>Aggregated Plant - IRENA Gap - ITA_68_Missing Solar Capacity</t>
   </si>
   <si>
+    <t>Aggregated Plant - IRENA Gap - ITA_73_Missing Onshore wind energy Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - ITA_22_Missing Onshore wind energy Capacity</t>
+  </si>
+  <si>
     <t>Aggregated Plant - IRENA Gap - ITA_96_Missing Onshore wind energy Capacity</t>
   </si>
   <si>
-    <t>Aggregated Plant - IRENA Gap - ITA_22_Missing Onshore wind energy Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - ITA_73_Missing Onshore wind energy Capacity</t>
-  </si>
-  <si>
     <t>AF</t>
   </si>
   <si>
@@ -3219,12 +3219,12 @@
     <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/409439916-380_Missing Coal Capacity</t>
   </si>
   <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/303915533-380_Missing Coal Capacity</t>
+  </si>
+  <si>
     <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/82767145-380_Missing Coal Capacity</t>
   </si>
   <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/303915533-380_Missing Coal Capacity</t>
-  </si>
-  <si>
     <t>ccs retrofit of -- Brindisi Sud power station_Unit 1</t>
   </si>
   <si>
@@ -3519,118 +3519,118 @@
     <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/414663585-380_Missing Gas Capacity</t>
   </si>
   <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/411026199-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/109756016-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/103381531-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/103974940-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/199675964-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/103653592-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/1137611914-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/416989699-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/105757794-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/99826025-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/82078641-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/132450233-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/100407576-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/60725875-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/339104227-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/158739183-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/133601335-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/61157826-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/98421779-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/172302572-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/162828577-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/82767145-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/82084019-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/421827453-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/181125039-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/105581403-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/255011550-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/145665799-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/432729521-380_Missing Gas Capacity</t>
+  </si>
+  <si>
     <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/149997403-380_Missing Gas Capacity</t>
   </si>
   <si>
     <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/162960205-380_Missing Gas Capacity</t>
   </si>
   <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/432729521-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/105757794-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/99826025-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/416989699-380_Missing Gas Capacity</t>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/419423704-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/98900549-380_Missing Gas Capacity</t>
   </si>
   <si>
     <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/107438024-380_Missing Gas Capacity</t>
   </si>
   <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/98900549-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/98421779-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/145665799-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/103974940-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/60725875-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/82084019-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/421827453-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/339104227-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/133601335-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/158739183-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/255011550-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/181125039-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/419423704-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/1137611914-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/199675964-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/82078641-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/103653592-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/103381531-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/411026199-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/109756016-380_Missing Gas Capacity</t>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/110330925-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/109993642-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/59462715-380_Missing Gas Capacity</t>
   </si>
   <si>
     <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/338753171-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/100407576-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/82767145-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/172302572-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/162828577-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/132450233-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/110330925-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/61157826-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/59462715-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/109993642-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/105581403-380_Missing Gas Capacity</t>
   </si>
   <si>
     <t>ccs retrofit of -- Tavazzano power station_CCGT8, timepoint 1</t>
@@ -4034,7 +4034,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7F7ECB1-BA13-48F3-B812-A77D275962E3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1E9FAD3B-001F-4E84-9C9B-4DE6E6F44DB6}">
   <dimension ref="B9:T278"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -4110,7 +4110,7 @@
         <v>33</v>
       </c>
       <c r="D11" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="E11">
         <v>0.12764790000000001</v>
@@ -4166,7 +4166,7 @@
         <v>33</v>
       </c>
       <c r="D12" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="E12">
         <v>0.12764790000000001</v>
@@ -4222,7 +4222,7 @@
         <v>33</v>
       </c>
       <c r="D13" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E13">
         <v>0.12764790000000001</v>
@@ -4278,7 +4278,7 @@
         <v>33</v>
       </c>
       <c r="D14" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E14">
         <v>8.7830160000000032E-2</v>
@@ -4558,7 +4558,7 @@
         <v>33</v>
       </c>
       <c r="D19" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E19">
         <v>0.260522535</v>
@@ -4614,7 +4614,7 @@
         <v>33</v>
       </c>
       <c r="D20" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E20">
         <v>0.260522535</v>
@@ -4670,7 +4670,7 @@
         <v>33</v>
       </c>
       <c r="D21" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E21">
         <v>0.260522535</v>
@@ -4726,7 +4726,7 @@
         <v>33</v>
       </c>
       <c r="D22" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E22">
         <v>0.28056272999999998</v>
@@ -4782,7 +4782,7 @@
         <v>33</v>
       </c>
       <c r="D23" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E23">
         <v>0.28056272999999998</v>
@@ -4838,7 +4838,7 @@
         <v>33</v>
       </c>
       <c r="D24" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E24">
         <v>0.28056272999999998</v>
@@ -4894,7 +4894,7 @@
         <v>49</v>
       </c>
       <c r="D25" t="s">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="E25">
         <v>0.41750406250000005</v>
@@ -4950,7 +4950,7 @@
         <v>49</v>
       </c>
       <c r="D26" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="E26">
         <v>0.44431624999999997</v>
@@ -5006,7 +5006,7 @@
         <v>49</v>
       </c>
       <c r="D27" t="s">
-        <v>72</v>
+        <v>59</v>
       </c>
       <c r="E27">
         <v>0.38303124999999993</v>
@@ -5062,7 +5062,7 @@
         <v>49</v>
       </c>
       <c r="D28" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="E28">
         <v>0.44431624999999997</v>
@@ -5118,7 +5118,7 @@
         <v>49</v>
       </c>
       <c r="D29" t="s">
-        <v>80</v>
+        <v>61</v>
       </c>
       <c r="E29">
         <v>0.41750406249999999</v>
@@ -5174,7 +5174,7 @@
         <v>49</v>
       </c>
       <c r="D30" t="s">
-        <v>80</v>
+        <v>61</v>
       </c>
       <c r="E30">
         <v>0.41750406249999999</v>
@@ -5230,7 +5230,7 @@
         <v>49</v>
       </c>
       <c r="D31" t="s">
-        <v>80</v>
+        <v>61</v>
       </c>
       <c r="E31">
         <v>0.41750406249999999</v>
@@ -5342,7 +5342,7 @@
         <v>49</v>
       </c>
       <c r="D33" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="E33">
         <v>0.41750406249999999</v>
@@ -5510,7 +5510,7 @@
         <v>49</v>
       </c>
       <c r="D36" t="s">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="E36">
         <v>0.41750406249999999</v>
@@ -5566,7 +5566,7 @@
         <v>49</v>
       </c>
       <c r="D37" t="s">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="E37">
         <v>0.41750406249999999</v>
@@ -5622,7 +5622,7 @@
         <v>49</v>
       </c>
       <c r="D38" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="E38">
         <v>0.41750406249999999</v>
@@ -5678,7 +5678,7 @@
         <v>49</v>
       </c>
       <c r="D39" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="E39">
         <v>0.41750406249999999</v>
@@ -5734,7 +5734,7 @@
         <v>49</v>
       </c>
       <c r="D40" t="s">
-        <v>52</v>
+        <v>75</v>
       </c>
       <c r="E40">
         <v>0.3983525</v>
@@ -5790,7 +5790,7 @@
         <v>49</v>
       </c>
       <c r="D41" t="s">
-        <v>52</v>
+        <v>75</v>
       </c>
       <c r="E41">
         <v>0.41750406249999999</v>
@@ -5846,7 +5846,7 @@
         <v>49</v>
       </c>
       <c r="D42" t="s">
-        <v>52</v>
+        <v>75</v>
       </c>
       <c r="E42">
         <v>0.41750406249999999</v>
@@ -5902,7 +5902,7 @@
         <v>49</v>
       </c>
       <c r="D43" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="E43">
         <v>0.41750406249999999</v>
@@ -5958,7 +5958,7 @@
         <v>49</v>
       </c>
       <c r="D44" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="E44">
         <v>0.41750406249999999</v>
@@ -6014,7 +6014,7 @@
         <v>49</v>
       </c>
       <c r="D45" t="s">
-        <v>54</v>
+        <v>72</v>
       </c>
       <c r="E45">
         <v>0.41750406249999999</v>
@@ -6070,7 +6070,7 @@
         <v>49</v>
       </c>
       <c r="D46" t="s">
-        <v>54</v>
+        <v>72</v>
       </c>
       <c r="E46">
         <v>0.41750406249999999</v>
@@ -6126,7 +6126,7 @@
         <v>49</v>
       </c>
       <c r="D47" t="s">
-        <v>54</v>
+        <v>72</v>
       </c>
       <c r="E47">
         <v>0.41750406249999999</v>
@@ -6182,7 +6182,7 @@
         <v>49</v>
       </c>
       <c r="D48" t="s">
-        <v>54</v>
+        <v>72</v>
       </c>
       <c r="E48">
         <v>0.41750406249999999</v>
@@ -6238,7 +6238,7 @@
         <v>49</v>
       </c>
       <c r="D49" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="E49">
         <v>0.40218281250000004</v>
@@ -6294,7 +6294,7 @@
         <v>49</v>
       </c>
       <c r="D50" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="E50">
         <v>0.40218281250000004</v>
@@ -6350,7 +6350,7 @@
         <v>49</v>
       </c>
       <c r="D51" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="E51">
         <v>0.41750406249999999</v>
@@ -6406,7 +6406,7 @@
         <v>49</v>
       </c>
       <c r="D52" t="s">
-        <v>72</v>
+        <v>59</v>
       </c>
       <c r="E52">
         <v>0.45963749999999998</v>
@@ -6462,7 +6462,7 @@
         <v>49</v>
       </c>
       <c r="D53" t="s">
-        <v>72</v>
+        <v>59</v>
       </c>
       <c r="E53">
         <v>0.41750406249999999</v>
@@ -6574,7 +6574,7 @@
         <v>49</v>
       </c>
       <c r="D55" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="E55">
         <v>0.41750406249999999</v>
@@ -6630,7 +6630,7 @@
         <v>49</v>
       </c>
       <c r="D56" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="E56">
         <v>0.41750406249999999</v>
@@ -6686,7 +6686,7 @@
         <v>49</v>
       </c>
       <c r="D57" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="E57">
         <v>0.41750406249999999</v>
@@ -6742,7 +6742,7 @@
         <v>49</v>
       </c>
       <c r="D58" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="E58">
         <v>0.40218281249999999</v>
@@ -6798,7 +6798,7 @@
         <v>49</v>
       </c>
       <c r="D59" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="E59">
         <v>0.40218281249999999</v>
@@ -6854,7 +6854,7 @@
         <v>49</v>
       </c>
       <c r="D60" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="E60">
         <v>0.38303124999999993</v>
@@ -6910,7 +6910,7 @@
         <v>49</v>
       </c>
       <c r="D61" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="E61">
         <v>0.38303124999999993</v>
@@ -7022,7 +7022,7 @@
         <v>49</v>
       </c>
       <c r="D63" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="E63">
         <v>0.41750406249999999</v>
@@ -7078,7 +7078,7 @@
         <v>49</v>
       </c>
       <c r="D64" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="E64">
         <v>0.41750406249999999</v>
@@ -7134,7 +7134,7 @@
         <v>49</v>
       </c>
       <c r="D65" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="E65">
         <v>0.41750406249999999</v>
@@ -7190,7 +7190,7 @@
         <v>49</v>
       </c>
       <c r="D66" t="s">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="E66">
         <v>0.41750406249999999</v>
@@ -7358,7 +7358,7 @@
         <v>49</v>
       </c>
       <c r="D69" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="E69">
         <v>0.41750406249999999</v>
@@ -7414,7 +7414,7 @@
         <v>49</v>
       </c>
       <c r="D70" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="E70">
         <v>0.41750406249999999</v>
@@ -7470,7 +7470,7 @@
         <v>49</v>
       </c>
       <c r="D71" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="E71">
         <v>0.41750406249999999</v>
@@ -7526,7 +7526,7 @@
         <v>49</v>
       </c>
       <c r="D72" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="E72">
         <v>0.41750406249999999</v>
@@ -7582,7 +7582,7 @@
         <v>49</v>
       </c>
       <c r="D73" t="s">
-        <v>66</v>
+        <v>86</v>
       </c>
       <c r="E73">
         <v>0.41750406249999999</v>
@@ -7638,7 +7638,7 @@
         <v>49</v>
       </c>
       <c r="D74" t="s">
-        <v>66</v>
+        <v>86</v>
       </c>
       <c r="E74">
         <v>0.41750406249999999</v>
@@ -7694,7 +7694,7 @@
         <v>49</v>
       </c>
       <c r="D75" t="s">
-        <v>75</v>
+        <v>52</v>
       </c>
       <c r="E75">
         <v>0.42899500000000002</v>
@@ -7750,7 +7750,7 @@
         <v>49</v>
       </c>
       <c r="D76" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="E76">
         <v>0.41750406249999999</v>
@@ -7806,7 +7806,7 @@
         <v>49</v>
       </c>
       <c r="D77" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="E77">
         <v>0.41750406249999999</v>
@@ -7974,7 +7974,7 @@
         <v>49</v>
       </c>
       <c r="D80" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E80">
         <v>0.41750406249999999</v>
@@ -8030,7 +8030,7 @@
         <v>49</v>
       </c>
       <c r="D81" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E81">
         <v>0.41750406249999999</v>
@@ -8086,7 +8086,7 @@
         <v>49</v>
       </c>
       <c r="D82" t="s">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="E82">
         <v>0.41750406249999999</v>
@@ -8142,7 +8142,7 @@
         <v>49</v>
       </c>
       <c r="D83" t="s">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="E83">
         <v>0.41750406249999999</v>
@@ -8198,7 +8198,7 @@
         <v>49</v>
       </c>
       <c r="D84" t="s">
-        <v>74</v>
+        <v>53</v>
       </c>
       <c r="E84">
         <v>0.41750406249999999</v>
@@ -8254,7 +8254,7 @@
         <v>49</v>
       </c>
       <c r="D85" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="E85">
         <v>0.41750406249999999</v>
@@ -8310,7 +8310,7 @@
         <v>49</v>
       </c>
       <c r="D86" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="E86">
         <v>0.41750406249999999</v>
@@ -8366,7 +8366,7 @@
         <v>49</v>
       </c>
       <c r="D87" t="s">
-        <v>59</v>
+        <v>85</v>
       </c>
       <c r="E87">
         <v>0.41750406249999999</v>
@@ -8422,7 +8422,7 @@
         <v>49</v>
       </c>
       <c r="D88" t="s">
-        <v>59</v>
+        <v>85</v>
       </c>
       <c r="E88">
         <v>0.41750406249999999</v>
@@ -8478,7 +8478,7 @@
         <v>49</v>
       </c>
       <c r="D89" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="E89">
         <v>0.44431624999999997</v>
@@ -8534,7 +8534,7 @@
         <v>49</v>
       </c>
       <c r="D90" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="E90">
         <v>0.41750406249999999</v>
@@ -8590,7 +8590,7 @@
         <v>49</v>
       </c>
       <c r="D91" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="E91">
         <v>0.41750406249999999</v>
@@ -8646,7 +8646,7 @@
         <v>49</v>
       </c>
       <c r="D92" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="E92">
         <v>0.44431624999999997</v>
@@ -8702,7 +8702,7 @@
         <v>49</v>
       </c>
       <c r="D93" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E93">
         <v>0.41750406249999999</v>
@@ -8758,7 +8758,7 @@
         <v>49</v>
       </c>
       <c r="D94" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E94">
         <v>0.41750406249999999</v>
@@ -8814,7 +8814,7 @@
         <v>49</v>
       </c>
       <c r="D95" t="s">
-        <v>69</v>
+        <v>56</v>
       </c>
       <c r="E95">
         <v>0.41750406249999999</v>
@@ -8870,7 +8870,7 @@
         <v>49</v>
       </c>
       <c r="D96" t="s">
-        <v>51</v>
+        <v>76</v>
       </c>
       <c r="E96">
         <v>0.41750406249999999</v>
@@ -8926,7 +8926,7 @@
         <v>49</v>
       </c>
       <c r="D97" t="s">
-        <v>67</v>
+        <v>84</v>
       </c>
       <c r="E97">
         <v>0.41750406249999999</v>
@@ -9038,7 +9038,7 @@
         <v>49</v>
       </c>
       <c r="D99" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="E99">
         <v>0.45963749999999998</v>
@@ -9094,7 +9094,7 @@
         <v>49</v>
       </c>
       <c r="D100" t="s">
-        <v>81</v>
+        <v>60</v>
       </c>
       <c r="E100">
         <v>0.45963749999999998</v>
@@ -9150,7 +9150,7 @@
         <v>49</v>
       </c>
       <c r="D101" t="s">
-        <v>51</v>
+        <v>76</v>
       </c>
       <c r="E101">
         <v>0.45963749999999998</v>
@@ -9206,7 +9206,7 @@
         <v>49</v>
       </c>
       <c r="D102" t="s">
-        <v>71</v>
+        <v>58</v>
       </c>
       <c r="E102">
         <v>0.41750406249999999</v>
@@ -9262,7 +9262,7 @@
         <v>49</v>
       </c>
       <c r="D103" t="s">
-        <v>71</v>
+        <v>58</v>
       </c>
       <c r="E103">
         <v>0.41750406249999999</v>
@@ -9318,7 +9318,7 @@
         <v>49</v>
       </c>
       <c r="D104" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="E104">
         <v>0.41750406249999999</v>
@@ -9374,7 +9374,7 @@
         <v>49</v>
       </c>
       <c r="D105" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="E105">
         <v>0.41750406249999999</v>
@@ -9430,7 +9430,7 @@
         <v>49</v>
       </c>
       <c r="D106" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="E106">
         <v>0.38303124999999993</v>
@@ -9486,7 +9486,7 @@
         <v>49</v>
       </c>
       <c r="D107" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="E107">
         <v>0.38303124999999993</v>
@@ -9542,7 +9542,7 @@
         <v>49</v>
       </c>
       <c r="D108" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="E108">
         <v>0.4021828125000001</v>
@@ -9654,7 +9654,7 @@
         <v>49</v>
       </c>
       <c r="D110" t="s">
-        <v>76</v>
+        <v>51</v>
       </c>
       <c r="E110">
         <v>0.41750406249999999</v>
@@ -9710,7 +9710,7 @@
         <v>49</v>
       </c>
       <c r="D111" t="s">
-        <v>52</v>
+        <v>75</v>
       </c>
       <c r="E111">
         <v>0.3983525</v>
@@ -9822,7 +9822,7 @@
         <v>49</v>
       </c>
       <c r="D113" t="s">
-        <v>75</v>
+        <v>52</v>
       </c>
       <c r="E113">
         <v>0.41750406249999999</v>
@@ -10270,7 +10270,7 @@
         <v>49</v>
       </c>
       <c r="D121" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E121">
         <v>0.45963749999999998</v>
@@ -10326,7 +10326,7 @@
         <v>49</v>
       </c>
       <c r="D122" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E122">
         <v>0.45963749999999998</v>
@@ -10382,7 +10382,7 @@
         <v>49</v>
       </c>
       <c r="D123" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E123">
         <v>0.45963749999999998</v>
@@ -10438,7 +10438,7 @@
         <v>49</v>
       </c>
       <c r="D124" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E124">
         <v>0.45963749999999998</v>
@@ -10494,7 +10494,7 @@
         <v>49</v>
       </c>
       <c r="D125" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="E125">
         <v>0.45963749999999998</v>
@@ -10718,7 +10718,7 @@
         <v>49</v>
       </c>
       <c r="D129" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E129">
         <v>0.45963749999999998</v>
@@ -10774,7 +10774,7 @@
         <v>49</v>
       </c>
       <c r="D130" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E130">
         <v>0.45963749999999998</v>
@@ -10830,7 +10830,7 @@
         <v>49</v>
       </c>
       <c r="D131" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E131">
         <v>0.45963749999999998</v>
@@ -10886,7 +10886,7 @@
         <v>49</v>
       </c>
       <c r="D132" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E132">
         <v>0.45963749999999998</v>
@@ -10942,7 +10942,7 @@
         <v>49</v>
       </c>
       <c r="D133" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E133">
         <v>0.45963749999999998</v>
@@ -10998,7 +10998,7 @@
         <v>49</v>
       </c>
       <c r="D134" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E134">
         <v>0.45963749999999998</v>
@@ -11054,7 +11054,7 @@
         <v>49</v>
       </c>
       <c r="D135" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E135">
         <v>0.45963749999999998</v>
@@ -11110,7 +11110,7 @@
         <v>49</v>
       </c>
       <c r="D136" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E136">
         <v>0.45963749999999998</v>
@@ -11166,7 +11166,7 @@
         <v>49</v>
       </c>
       <c r="D137" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E137">
         <v>0.45963749999999998</v>
@@ -11222,7 +11222,7 @@
         <v>49</v>
       </c>
       <c r="D138" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E138">
         <v>0.45963749999999998</v>
@@ -11278,7 +11278,7 @@
         <v>49</v>
       </c>
       <c r="D139" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E139">
         <v>0.45963749999999998</v>
@@ -11334,7 +11334,7 @@
         <v>49</v>
       </c>
       <c r="D140" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E140">
         <v>0.45963749999999998</v>
@@ -11390,7 +11390,7 @@
         <v>49</v>
       </c>
       <c r="D141" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E141">
         <v>0.45963749999999998</v>
@@ -11446,7 +11446,7 @@
         <v>49</v>
       </c>
       <c r="D142" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E142">
         <v>0.45963749999999998</v>
@@ -11502,7 +11502,7 @@
         <v>49</v>
       </c>
       <c r="D143" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E143">
         <v>0.45963749999999998</v>
@@ -11558,7 +11558,7 @@
         <v>49</v>
       </c>
       <c r="D144" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E144">
         <v>0.45963749999999998</v>
@@ -11670,7 +11670,7 @@
         <v>49</v>
       </c>
       <c r="D146" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E146">
         <v>0.45963749999999998</v>
@@ -11726,7 +11726,7 @@
         <v>49</v>
       </c>
       <c r="D147" t="s">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="E147">
         <v>0.45963749999999998</v>
@@ -11782,7 +11782,7 @@
         <v>49</v>
       </c>
       <c r="D148" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E148">
         <v>0.45963749999999998</v>
@@ -11838,7 +11838,7 @@
         <v>49</v>
       </c>
       <c r="D149" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E149">
         <v>0.45963749999999998</v>
@@ -11894,7 +11894,7 @@
         <v>49</v>
       </c>
       <c r="D150" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E150">
         <v>0.45963749999999998</v>
@@ -11950,7 +11950,7 @@
         <v>49</v>
       </c>
       <c r="D151" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E151">
         <v>0.45963749999999998</v>
@@ -12006,7 +12006,7 @@
         <v>49</v>
       </c>
       <c r="D152" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E152">
         <v>0.45963749999999998</v>
@@ -12062,7 +12062,7 @@
         <v>49</v>
       </c>
       <c r="D153" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E153">
         <v>0.45963749999999998</v>
@@ -12118,7 +12118,7 @@
         <v>49</v>
       </c>
       <c r="D154" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E154">
         <v>0.45963749999999998</v>
@@ -12174,7 +12174,7 @@
         <v>49</v>
       </c>
       <c r="D155" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E155">
         <v>0.45963749999999998</v>
@@ -12230,7 +12230,7 @@
         <v>49</v>
       </c>
       <c r="D156" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E156">
         <v>0.45963749999999998</v>
@@ -12286,7 +12286,7 @@
         <v>49</v>
       </c>
       <c r="D157" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E157">
         <v>0.45963749999999998</v>
@@ -12342,7 +12342,7 @@
         <v>49</v>
       </c>
       <c r="D158" t="s">
-        <v>83</v>
+        <v>18</v>
       </c>
       <c r="E158">
         <v>0.45963749999999998</v>
@@ -12678,7 +12678,7 @@
         <v>49</v>
       </c>
       <c r="D164" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="E164">
         <v>0.41367375000000001</v>
@@ -13518,7 +13518,7 @@
         <v>49</v>
       </c>
       <c r="D179" t="s">
-        <v>51</v>
+        <v>76</v>
       </c>
       <c r="E179">
         <v>0.39835250000000011</v>
@@ -13574,7 +13574,7 @@
         <v>49</v>
       </c>
       <c r="D180" t="s">
-        <v>51</v>
+        <v>76</v>
       </c>
       <c r="E180">
         <v>0.39835250000000011</v>
@@ -13798,7 +13798,7 @@
         <v>49</v>
       </c>
       <c r="D184" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="E184">
         <v>0.41367375000000001</v>
@@ -13854,7 +13854,7 @@
         <v>49</v>
       </c>
       <c r="D185" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="E185">
         <v>0.41367375000000001</v>
@@ -14582,7 +14582,7 @@
         <v>49</v>
       </c>
       <c r="D198" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E198">
         <v>0.42899500000000002</v>
@@ -14806,7 +14806,7 @@
         <v>49</v>
       </c>
       <c r="D202" t="s">
-        <v>81</v>
+        <v>60</v>
       </c>
       <c r="E202">
         <v>0.3983525</v>
@@ -15534,7 +15534,7 @@
         <v>49</v>
       </c>
       <c r="D215" t="s">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="E215">
         <v>0.38303124999999993</v>
@@ -15702,7 +15702,7 @@
         <v>49</v>
       </c>
       <c r="D218" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E218">
         <v>0.42899499999999996</v>
@@ -15758,7 +15758,7 @@
         <v>49</v>
       </c>
       <c r="D219" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E219">
         <v>0.42899499999999996</v>
@@ -15926,7 +15926,7 @@
         <v>49</v>
       </c>
       <c r="D222" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="E222">
         <v>0.38303124999999993</v>
@@ -15982,7 +15982,7 @@
         <v>49</v>
       </c>
       <c r="D223" t="s">
-        <v>59</v>
+        <v>85</v>
       </c>
       <c r="E223">
         <v>0.25280062500000006</v>
@@ -16038,7 +16038,7 @@
         <v>49</v>
       </c>
       <c r="D224" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="E224">
         <v>0.24514000000000002</v>
@@ -16094,7 +16094,7 @@
         <v>49</v>
       </c>
       <c r="D225" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="E225">
         <v>0.24514000000000002</v>
@@ -16150,7 +16150,7 @@
         <v>49</v>
       </c>
       <c r="D226" t="s">
-        <v>75</v>
+        <v>52</v>
       </c>
       <c r="E226">
         <v>0.21066718750000002</v>
@@ -16654,7 +16654,7 @@
         <v>49</v>
       </c>
       <c r="D235" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="E235">
         <v>0.21449750000000001</v>
@@ -16934,7 +16934,7 @@
         <v>49</v>
       </c>
       <c r="D240" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="E240">
         <v>0.23747937499999999</v>
@@ -17046,7 +17046,7 @@
         <v>49</v>
       </c>
       <c r="D242" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="E242">
         <v>0.21449750000000001</v>
@@ -17242,7 +17242,7 @@
         <v>49</v>
       </c>
       <c r="D247" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="E247">
         <v>0.27578249999999999</v>
@@ -17312,7 +17312,7 @@
         <v>49</v>
       </c>
       <c r="D249" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="E249">
         <v>0.27578249999999999</v>
@@ -17452,7 +17452,7 @@
         <v>49</v>
       </c>
       <c r="D253" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="E253">
         <v>0.23747937499999999</v>
@@ -17487,7 +17487,7 @@
         <v>49</v>
       </c>
       <c r="D254" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="E254">
         <v>0.23747937499999999</v>
@@ -17522,7 +17522,7 @@
         <v>49</v>
       </c>
       <c r="D255" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="E255">
         <v>0.23747937499999999</v>
@@ -17557,7 +17557,7 @@
         <v>49</v>
       </c>
       <c r="D256" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="E256">
         <v>0.26429156249999997</v>
@@ -17592,7 +17592,7 @@
         <v>49</v>
       </c>
       <c r="D257" t="s">
-        <v>80</v>
+        <v>61</v>
       </c>
       <c r="E257">
         <v>0.23747937499999999</v>
@@ -17627,7 +17627,7 @@
         <v>49</v>
       </c>
       <c r="D258" t="s">
-        <v>80</v>
+        <v>61</v>
       </c>
       <c r="E258">
         <v>0.23747937499999999</v>
@@ -17662,7 +17662,7 @@
         <v>49</v>
       </c>
       <c r="D259" t="s">
-        <v>76</v>
+        <v>51</v>
       </c>
       <c r="E259">
         <v>0.22215812499999998</v>
@@ -17697,7 +17697,7 @@
         <v>49</v>
       </c>
       <c r="D260" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E260">
         <v>0.24514000000000002</v>
@@ -17732,7 +17732,7 @@
         <v>49</v>
       </c>
       <c r="D261" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E261">
         <v>0.24514000000000002</v>
@@ -17767,7 +17767,7 @@
         <v>49</v>
       </c>
       <c r="D262" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E262">
         <v>0.24514000000000002</v>
@@ -17837,7 +17837,7 @@
         <v>439</v>
       </c>
       <c r="D264" t="s">
-        <v>72</v>
+        <v>59</v>
       </c>
       <c r="E264">
         <v>0.35238875000000003</v>
@@ -17942,7 +17942,7 @@
         <v>439</v>
       </c>
       <c r="D267" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E267">
         <v>0.19534593749999996</v>
@@ -17977,7 +17977,7 @@
         <v>439</v>
       </c>
       <c r="D268" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="E268">
         <v>0.206836875</v>
@@ -18152,7 +18152,7 @@
         <v>439</v>
       </c>
       <c r="D273" t="s">
-        <v>72</v>
+        <v>59</v>
       </c>
       <c r="E273">
         <v>0.23747937499999999</v>
@@ -18360,7 +18360,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2B3BF5C1-DBAE-455B-8010-7F7314D67A27}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{20BDA0FA-69BB-4662-9915-EF4201268817}">
   <dimension ref="B9:T641"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -18442,19 +18442,19 @@
         <v>2022</v>
       </c>
       <c r="F11">
-        <v>0.24877966101694915</v>
+        <v>1.0679322033898306</v>
       </c>
       <c r="G11">
-        <v>0.28891500000000003</v>
+        <v>0.306425</v>
       </c>
       <c r="H11">
-        <v>4427.5</v>
+        <v>3850.0000000000005</v>
       </c>
       <c r="I11">
-        <v>157.30000000000001</v>
+        <v>143</v>
       </c>
       <c r="J11">
-        <v>9.240000000000002</v>
+        <v>8.4</v>
       </c>
       <c r="K11">
         <v>50</v>
@@ -18548,7 +18548,7 @@
         <v>2022</v>
       </c>
       <c r="F13">
-        <v>0.22450847457627116</v>
+        <v>0.24877966101694915</v>
       </c>
       <c r="G13">
         <v>0.28891500000000003</v>
@@ -18601,19 +18601,19 @@
         <v>2022</v>
       </c>
       <c r="F14">
-        <v>0.27911864406779663</v>
+        <v>0.39440677966101695</v>
       </c>
       <c r="G14">
-        <v>0.28891500000000003</v>
+        <v>0.306425</v>
       </c>
       <c r="H14">
-        <v>4427.5</v>
+        <v>3850.0000000000005</v>
       </c>
       <c r="I14">
-        <v>157.30000000000001</v>
+        <v>143</v>
       </c>
       <c r="J14">
-        <v>9.240000000000002</v>
+        <v>8.4</v>
       </c>
       <c r="K14">
         <v>50</v>
@@ -18654,19 +18654,19 @@
         <v>2022</v>
       </c>
       <c r="F15">
-        <v>1.0679322033898306</v>
+        <v>0.27911864406779663</v>
       </c>
       <c r="G15">
-        <v>0.306425</v>
+        <v>0.28891500000000003</v>
       </c>
       <c r="H15">
-        <v>3850.0000000000005</v>
+        <v>4427.5</v>
       </c>
       <c r="I15">
-        <v>143</v>
+        <v>157.30000000000001</v>
       </c>
       <c r="J15">
-        <v>8.4</v>
+        <v>9.240000000000002</v>
       </c>
       <c r="K15">
         <v>50</v>
@@ -18707,19 +18707,19 @@
         <v>2022</v>
       </c>
       <c r="F16">
-        <v>0.51576271186440681</v>
+        <v>0.22450847457627116</v>
       </c>
       <c r="G16">
-        <v>0.306425</v>
+        <v>0.28891500000000003</v>
       </c>
       <c r="H16">
-        <v>3850.0000000000005</v>
+        <v>4427.5</v>
       </c>
       <c r="I16">
-        <v>143</v>
+        <v>157.30000000000001</v>
       </c>
       <c r="J16">
-        <v>8.4</v>
+        <v>9.240000000000002</v>
       </c>
       <c r="K16">
         <v>50</v>
@@ -18760,7 +18760,7 @@
         <v>2022</v>
       </c>
       <c r="F17">
-        <v>0.39440677966101695</v>
+        <v>0.51576271186440681</v>
       </c>
       <c r="G17">
         <v>0.306425</v>
@@ -18860,7 +18860,7 @@
         <v>13</v>
       </c>
       <c r="D19" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E19">
         <v>2008</v>
@@ -18913,7 +18913,7 @@
         <v>13</v>
       </c>
       <c r="D20" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E20">
         <v>1998</v>
@@ -19072,7 +19072,7 @@
         <v>13</v>
       </c>
       <c r="D23" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E23">
         <v>2013</v>
@@ -19125,7 +19125,7 @@
         <v>13</v>
       </c>
       <c r="D24" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E24">
         <v>1965</v>
@@ -19178,7 +19178,7 @@
         <v>13</v>
       </c>
       <c r="D25" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E25">
         <v>2003</v>
@@ -19231,7 +19231,7 @@
         <v>13</v>
       </c>
       <c r="D26" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E26">
         <v>2009</v>
@@ -19337,7 +19337,7 @@
         <v>13</v>
       </c>
       <c r="D28" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E28">
         <v>2009</v>
@@ -19396,19 +19396,19 @@
         <v>2022</v>
       </c>
       <c r="F29">
-        <v>0.1997687861271675</v>
+        <v>0.61803468208092449</v>
       </c>
       <c r="G29">
-        <v>0.29766999999999999</v>
+        <v>0.31518000000000002</v>
       </c>
       <c r="H29">
-        <v>2530</v>
+        <v>2200</v>
       </c>
       <c r="I29">
-        <v>72.600000000000009</v>
+        <v>66</v>
       </c>
       <c r="J29">
-        <v>5.7750000000000004</v>
+        <v>5.25</v>
       </c>
       <c r="K29">
         <v>50</v>
@@ -19449,19 +19449,19 @@
         <v>2022</v>
       </c>
       <c r="F30">
-        <v>0.18416184971098257</v>
+        <v>0.61803468208092449</v>
       </c>
       <c r="G30">
-        <v>0.29766999999999999</v>
+        <v>0.31518000000000002</v>
       </c>
       <c r="H30">
-        <v>2530</v>
+        <v>2200</v>
       </c>
       <c r="I30">
-        <v>72.600000000000009</v>
+        <v>66</v>
       </c>
       <c r="J30">
-        <v>5.7750000000000004</v>
+        <v>5.25</v>
       </c>
       <c r="K30">
         <v>50</v>
@@ -19502,19 +19502,19 @@
         <v>2022</v>
       </c>
       <c r="F31">
-        <v>0.61803468208092449</v>
+        <v>0.18416184971098257</v>
       </c>
       <c r="G31">
-        <v>0.31518000000000002</v>
+        <v>0.29766999999999999</v>
       </c>
       <c r="H31">
-        <v>2200</v>
+        <v>2530</v>
       </c>
       <c r="I31">
-        <v>66</v>
+        <v>72.600000000000009</v>
       </c>
       <c r="J31">
-        <v>5.25</v>
+        <v>5.7750000000000004</v>
       </c>
       <c r="K31">
         <v>50</v>
@@ -19555,19 +19555,19 @@
         <v>2022</v>
       </c>
       <c r="F32">
-        <v>0.61803468208092449</v>
+        <v>0.1997687861271675</v>
       </c>
       <c r="G32">
-        <v>0.31518000000000002</v>
+        <v>0.29766999999999999</v>
       </c>
       <c r="H32">
-        <v>2200</v>
+        <v>2530</v>
       </c>
       <c r="I32">
-        <v>66</v>
+        <v>72.600000000000009</v>
       </c>
       <c r="J32">
-        <v>5.25</v>
+        <v>5.7750000000000004</v>
       </c>
       <c r="K32">
         <v>50</v>
@@ -19602,7 +19602,7 @@
         <v>33</v>
       </c>
       <c r="D33" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="E33">
         <v>1992</v>
@@ -19655,7 +19655,7 @@
         <v>33</v>
       </c>
       <c r="D34" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="E34">
         <v>1993</v>
@@ -19708,7 +19708,7 @@
         <v>33</v>
       </c>
       <c r="D35" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E35">
         <v>2005</v>
@@ -19761,7 +19761,7 @@
         <v>33</v>
       </c>
       <c r="D36" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E36">
         <v>1986</v>
@@ -19814,7 +19814,7 @@
         <v>33</v>
       </c>
       <c r="D37" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E37">
         <v>1991</v>
@@ -19867,7 +19867,7 @@
         <v>33</v>
       </c>
       <c r="D38" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E38">
         <v>1992</v>
@@ -19920,7 +19920,7 @@
         <v>33</v>
       </c>
       <c r="D39" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E39">
         <v>1993</v>
@@ -19973,7 +19973,7 @@
         <v>33</v>
       </c>
       <c r="D40" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E40">
         <v>2009</v>
@@ -20026,7 +20026,7 @@
         <v>33</v>
       </c>
       <c r="D41" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E41">
         <v>2010</v>
@@ -20079,7 +20079,7 @@
         <v>33</v>
       </c>
       <c r="D42" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E42">
         <v>2010</v>
@@ -20138,19 +20138,19 @@
         <v>2022</v>
       </c>
       <c r="F43">
-        <v>0.19676367392472002</v>
+        <v>0.45732943023592104</v>
       </c>
       <c r="G43">
-        <v>0.50778999999999996</v>
+        <v>0.52529999999999999</v>
       </c>
       <c r="H43">
-        <v>1265</v>
+        <v>1100</v>
       </c>
       <c r="I43">
-        <v>36.300000000000004</v>
+        <v>33</v>
       </c>
       <c r="J43">
-        <v>3.4650000000000003</v>
+        <v>3.1500000000000004</v>
       </c>
       <c r="K43">
         <v>50</v>
@@ -20191,19 +20191,19 @@
         <v>2022</v>
       </c>
       <c r="F44">
-        <v>0.3567559186877659</v>
+        <v>0.1548783373961905</v>
       </c>
       <c r="G44">
-        <v>0.52529999999999999</v>
+        <v>0.50778999999999996</v>
       </c>
       <c r="H44">
-        <v>1100</v>
+        <v>1265</v>
       </c>
       <c r="I44">
-        <v>33</v>
+        <v>36.300000000000004</v>
       </c>
       <c r="J44">
-        <v>3.1500000000000004</v>
+        <v>3.4649999999999999</v>
       </c>
       <c r="K44">
         <v>50</v>
@@ -20238,13 +20238,13 @@
         <v>49</v>
       </c>
       <c r="D45" t="s">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="E45">
         <v>2022</v>
       </c>
       <c r="F45">
-        <v>0.27761211420071885</v>
+        <v>0.22793415692269547</v>
       </c>
       <c r="G45">
         <v>0.50778999999999996</v>
@@ -20291,25 +20291,25 @@
         <v>49</v>
       </c>
       <c r="D46" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E46">
         <v>2022</v>
       </c>
       <c r="F46">
-        <v>0.30829555840185086</v>
+        <v>0.21551466760318963</v>
       </c>
       <c r="G46">
-        <v>0.52529999999999999</v>
+        <v>0.50778999999999996</v>
       </c>
       <c r="H46">
-        <v>1100</v>
+        <v>1265</v>
       </c>
       <c r="I46">
-        <v>33</v>
+        <v>36.300000000000004</v>
       </c>
       <c r="J46">
-        <v>3.1500000000000004</v>
+        <v>3.4650000000000003</v>
       </c>
       <c r="K46">
         <v>50</v>
@@ -20344,13 +20344,13 @@
         <v>49</v>
       </c>
       <c r="D47" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E47">
         <v>2022</v>
       </c>
       <c r="F47">
-        <v>0.29344087509812827</v>
+        <v>0.26604494277568891</v>
       </c>
       <c r="G47">
         <v>0.50778999999999996</v>
@@ -20397,25 +20397,25 @@
         <v>49</v>
       </c>
       <c r="D48" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E48">
         <v>2022</v>
       </c>
       <c r="F48">
-        <v>0.37112356319464518</v>
+        <v>0.23280454489112914</v>
       </c>
       <c r="G48">
-        <v>0.52529999999999999</v>
+        <v>0.50778999999999996</v>
       </c>
       <c r="H48">
-        <v>1100</v>
+        <v>1265</v>
       </c>
       <c r="I48">
-        <v>33</v>
+        <v>36.300000000000004</v>
       </c>
       <c r="J48">
-        <v>3.1500000000000004</v>
+        <v>3.4650000000000007</v>
       </c>
       <c r="K48">
         <v>50</v>
@@ -20450,13 +20450,13 @@
         <v>49</v>
       </c>
       <c r="D49" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E49">
         <v>2022</v>
       </c>
       <c r="F49">
-        <v>0.28443065735652601</v>
+        <v>0.21113131843159935</v>
       </c>
       <c r="G49">
         <v>0.50778999999999996</v>
@@ -20503,25 +20503,25 @@
         <v>49</v>
       </c>
       <c r="D50" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E50">
         <v>2022</v>
       </c>
       <c r="F50">
-        <v>0.39839773581787374</v>
+        <v>0.19627663512787666</v>
       </c>
       <c r="G50">
-        <v>0.52529999999999999</v>
+        <v>0.50778999999999996</v>
       </c>
       <c r="H50">
-        <v>1100</v>
+        <v>1265</v>
       </c>
       <c r="I50">
-        <v>33</v>
+        <v>36.300000000000004</v>
       </c>
       <c r="J50">
-        <v>3.1500000000000004</v>
+        <v>3.4649999999999999</v>
       </c>
       <c r="K50">
         <v>50</v>
@@ -20556,13 +20556,13 @@
         <v>49</v>
       </c>
       <c r="D51" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E51">
         <v>2022</v>
       </c>
       <c r="F51">
-        <v>0.21283595422055113</v>
+        <v>0.18824049497996109</v>
       </c>
       <c r="G51">
         <v>0.50778999999999996</v>
@@ -20609,13 +20609,13 @@
         <v>49</v>
       </c>
       <c r="D52" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E52">
         <v>2022</v>
       </c>
       <c r="F52">
-        <v>0.45732943023592104</v>
+        <v>0.43468212618270452</v>
       </c>
       <c r="G52">
         <v>0.52529999999999999</v>
@@ -20662,25 +20662,25 @@
         <v>49</v>
       </c>
       <c r="D53" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E53">
         <v>2022</v>
       </c>
       <c r="F53">
-        <v>0.49339465314217229</v>
+        <v>0.23864901045324952</v>
       </c>
       <c r="G53">
-        <v>0.52529999999999999</v>
+        <v>0.50778999999999996</v>
       </c>
       <c r="H53">
-        <v>1100</v>
+        <v>1265</v>
       </c>
       <c r="I53">
-        <v>33</v>
+        <v>36.300000000000004</v>
       </c>
       <c r="J53">
-        <v>3.1500000000000004</v>
+        <v>3.4650000000000003</v>
       </c>
       <c r="K53">
         <v>50</v>
@@ -20715,25 +20715,25 @@
         <v>49</v>
       </c>
       <c r="D54" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E54">
         <v>2022</v>
       </c>
       <c r="F54">
-        <v>0.18556178159732259</v>
+        <v>0.31243538817501959</v>
       </c>
       <c r="G54">
-        <v>0.50778999999999996</v>
+        <v>0.52529999999999999</v>
       </c>
       <c r="H54">
-        <v>1265</v>
+        <v>1100</v>
       </c>
       <c r="I54">
-        <v>36.300000000000004</v>
+        <v>33</v>
       </c>
       <c r="J54">
-        <v>3.4650000000000003</v>
+        <v>3.1500000000000004</v>
       </c>
       <c r="K54">
         <v>50</v>
@@ -20768,13 +20768,13 @@
         <v>49</v>
       </c>
       <c r="D55" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E55">
         <v>2022</v>
       </c>
       <c r="F55">
-        <v>0.23280454489112914</v>
+        <v>0.28443065735652601</v>
       </c>
       <c r="G55">
         <v>0.50778999999999996</v>
@@ -20786,7 +20786,7 @@
         <v>36.300000000000004</v>
       </c>
       <c r="J55">
-        <v>3.4650000000000007</v>
+        <v>3.4650000000000003</v>
       </c>
       <c r="K55">
         <v>50</v>
@@ -20821,25 +20821,25 @@
         <v>49</v>
       </c>
       <c r="D56" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E56">
         <v>2022</v>
       </c>
       <c r="F56">
-        <v>0.26604494277568891</v>
+        <v>0.39839773581787374</v>
       </c>
       <c r="G56">
-        <v>0.50778999999999996</v>
+        <v>0.52529999999999999</v>
       </c>
       <c r="H56">
-        <v>1265</v>
+        <v>1100</v>
       </c>
       <c r="I56">
-        <v>36.300000000000004</v>
+        <v>33</v>
       </c>
       <c r="J56">
-        <v>3.4650000000000003</v>
+        <v>3.1500000000000004</v>
       </c>
       <c r="K56">
         <v>50</v>
@@ -20874,13 +20874,13 @@
         <v>49</v>
       </c>
       <c r="D57" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E57">
         <v>2022</v>
       </c>
       <c r="F57">
-        <v>0.20557907614758497</v>
+        <v>0.18556178159732259</v>
       </c>
       <c r="G57">
         <v>0.50778999999999996</v>
@@ -20927,13 +20927,13 @@
         <v>49</v>
       </c>
       <c r="D58" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E58">
         <v>2022</v>
       </c>
       <c r="F58">
-        <v>0.19481551873734657</v>
+        <v>0.21283595422055113</v>
       </c>
       <c r="G58">
         <v>0.50778999999999996</v>
@@ -20980,13 +20980,13 @@
         <v>49</v>
       </c>
       <c r="D59" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E59">
         <v>2022</v>
       </c>
       <c r="F59">
-        <v>0.19481551873734657</v>
+        <v>0.29344087509812827</v>
       </c>
       <c r="G59">
         <v>0.50778999999999996</v>
@@ -21033,13 +21033,13 @@
         <v>49</v>
       </c>
       <c r="D60" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E60">
         <v>2022</v>
       </c>
       <c r="F60">
-        <v>0.18702289798785268</v>
+        <v>0.19481551873734657</v>
       </c>
       <c r="G60">
         <v>0.50778999999999996</v>
@@ -21086,7 +21086,7 @@
         <v>49</v>
       </c>
       <c r="D61" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E61">
         <v>2022</v>
@@ -21139,13 +21139,13 @@
         <v>49</v>
       </c>
       <c r="D62" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E62">
         <v>2022</v>
       </c>
       <c r="F62">
-        <v>0.19481551873734657</v>
+        <v>0.20212110068999706</v>
       </c>
       <c r="G62">
         <v>0.50778999999999996</v>
@@ -21192,13 +21192,13 @@
         <v>49</v>
       </c>
       <c r="D63" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E63">
         <v>2022</v>
       </c>
       <c r="F63">
-        <v>0.21113131843159935</v>
+        <v>0.26543614427963469</v>
       </c>
       <c r="G63">
         <v>0.50778999999999996</v>
@@ -21245,13 +21245,13 @@
         <v>49</v>
       </c>
       <c r="D64" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E64">
         <v>2022</v>
       </c>
       <c r="F64">
-        <v>0.19627663512787666</v>
+        <v>0.20557907614758497</v>
       </c>
       <c r="G64">
         <v>0.50778999999999996</v>
@@ -21263,7 +21263,7 @@
         <v>36.300000000000004</v>
       </c>
       <c r="J64">
-        <v>3.4649999999999999</v>
+        <v>3.4650000000000003</v>
       </c>
       <c r="K64">
         <v>50</v>
@@ -21298,25 +21298,25 @@
         <v>49</v>
       </c>
       <c r="D65" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E65">
         <v>2022</v>
       </c>
       <c r="F65">
-        <v>0.18824049497996109</v>
+        <v>0.37112356319464518</v>
       </c>
       <c r="G65">
-        <v>0.50778999999999996</v>
+        <v>0.52529999999999999</v>
       </c>
       <c r="H65">
-        <v>1265</v>
+        <v>1100</v>
       </c>
       <c r="I65">
-        <v>36.300000000000004</v>
+        <v>33</v>
       </c>
       <c r="J65">
-        <v>3.4650000000000003</v>
+        <v>3.1500000000000004</v>
       </c>
       <c r="K65">
         <v>50</v>
@@ -21351,25 +21351,25 @@
         <v>49</v>
       </c>
       <c r="D66" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E66">
         <v>2022</v>
       </c>
       <c r="F66">
-        <v>0.43468212618270452</v>
+        <v>0.19481551873734657</v>
       </c>
       <c r="G66">
-        <v>0.52529999999999999</v>
+        <v>0.50778999999999996</v>
       </c>
       <c r="H66">
-        <v>1100</v>
+        <v>1265</v>
       </c>
       <c r="I66">
-        <v>33</v>
+        <v>36.300000000000004</v>
       </c>
       <c r="J66">
-        <v>3.1500000000000004</v>
+        <v>3.4650000000000003</v>
       </c>
       <c r="K66">
         <v>50</v>
@@ -21404,13 +21404,13 @@
         <v>49</v>
       </c>
       <c r="D67" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E67">
         <v>2022</v>
       </c>
       <c r="F67">
-        <v>0.26543614427963469</v>
+        <v>0.20236462008841874</v>
       </c>
       <c r="G67">
         <v>0.50778999999999996</v>
@@ -21457,25 +21457,25 @@
         <v>49</v>
       </c>
       <c r="D68" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E68">
         <v>2022</v>
       </c>
       <c r="F68">
-        <v>0.21551466760318963</v>
+        <v>0.30829555840185086</v>
       </c>
       <c r="G68">
-        <v>0.50778999999999996</v>
+        <v>0.52529999999999999</v>
       </c>
       <c r="H68">
-        <v>1265</v>
+        <v>1100</v>
       </c>
       <c r="I68">
-        <v>36.300000000000004</v>
+        <v>33</v>
       </c>
       <c r="J68">
-        <v>3.4650000000000003</v>
+        <v>3.1500000000000004</v>
       </c>
       <c r="K68">
         <v>50</v>
@@ -21510,13 +21510,13 @@
         <v>49</v>
       </c>
       <c r="D69" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="E69">
         <v>2022</v>
       </c>
       <c r="F69">
-        <v>0.19822479031525012</v>
+        <v>0.27761211420071885</v>
       </c>
       <c r="G69">
         <v>0.50778999999999996</v>
@@ -21563,25 +21563,25 @@
         <v>49</v>
       </c>
       <c r="D70" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E70">
         <v>2022</v>
       </c>
       <c r="F70">
-        <v>0.22793415692269547</v>
+        <v>0.3567559186877659</v>
       </c>
       <c r="G70">
-        <v>0.50778999999999996</v>
+        <v>0.52529999999999999</v>
       </c>
       <c r="H70">
-        <v>1265</v>
+        <v>1100</v>
       </c>
       <c r="I70">
-        <v>36.300000000000004</v>
+        <v>33</v>
       </c>
       <c r="J70">
-        <v>3.4650000000000003</v>
+        <v>3.1500000000000004</v>
       </c>
       <c r="K70">
         <v>50</v>
@@ -21616,13 +21616,13 @@
         <v>49</v>
       </c>
       <c r="D71" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E71">
         <v>2022</v>
       </c>
       <c r="F71">
-        <v>0.1548783373961905</v>
+        <v>0.18507474280047922</v>
       </c>
       <c r="G71">
         <v>0.50778999999999996</v>
@@ -21669,13 +21669,13 @@
         <v>49</v>
       </c>
       <c r="D72" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E72">
         <v>2022</v>
       </c>
       <c r="F72">
-        <v>0.27347228442755023</v>
+        <v>0.19676367392472002</v>
       </c>
       <c r="G72">
         <v>0.50778999999999996</v>
@@ -21722,13 +21722,13 @@
         <v>49</v>
       </c>
       <c r="D73" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E73">
         <v>2022</v>
       </c>
       <c r="F73">
-        <v>0.17484692806676855</v>
+        <v>0.16608022972358796</v>
       </c>
       <c r="G73">
         <v>0.50778999999999996</v>
@@ -21775,13 +21775,13 @@
         <v>49</v>
       </c>
       <c r="D74" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E74">
         <v>2022</v>
       </c>
       <c r="F74">
-        <v>0.20212110068999706</v>
+        <v>0.18629233979258764</v>
       </c>
       <c r="G74">
         <v>0.50778999999999996</v>
@@ -21828,25 +21828,25 @@
         <v>49</v>
       </c>
       <c r="D75" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E75">
         <v>2022</v>
       </c>
       <c r="F75">
-        <v>0.31243538817501959</v>
+        <v>0.20820908565053911</v>
       </c>
       <c r="G75">
-        <v>0.52529999999999999</v>
+        <v>0.50778999999999996</v>
       </c>
       <c r="H75">
-        <v>1100</v>
+        <v>1265</v>
       </c>
       <c r="I75">
-        <v>33</v>
+        <v>36.300000000000004</v>
       </c>
       <c r="J75">
-        <v>3.1500000000000004</v>
+        <v>3.4650000000000007</v>
       </c>
       <c r="K75">
         <v>50</v>
@@ -21881,13 +21881,13 @@
         <v>49</v>
       </c>
       <c r="D76" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E76">
         <v>2022</v>
       </c>
       <c r="F76">
-        <v>0.23864901045324952</v>
+        <v>0.18872753377680451</v>
       </c>
       <c r="G76">
         <v>0.50778999999999996</v>
@@ -21899,7 +21899,7 @@
         <v>36.300000000000004</v>
       </c>
       <c r="J76">
-        <v>3.4650000000000003</v>
+        <v>3.4650000000000007</v>
       </c>
       <c r="K76">
         <v>50</v>
@@ -21934,13 +21934,13 @@
         <v>49</v>
       </c>
       <c r="D77" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E77">
         <v>2022</v>
       </c>
       <c r="F77">
-        <v>0.20236462008841874</v>
+        <v>0.17484692806676855</v>
       </c>
       <c r="G77">
         <v>0.50778999999999996</v>
@@ -21987,13 +21987,13 @@
         <v>49</v>
       </c>
       <c r="D78" t="s">
-        <v>83</v>
+        <v>18</v>
       </c>
       <c r="E78">
         <v>2022</v>
       </c>
       <c r="F78">
-        <v>0.18629233979258764</v>
+        <v>0.19822479031525012</v>
       </c>
       <c r="G78">
         <v>0.50778999999999996</v>
@@ -22046,7 +22046,7 @@
         <v>2022</v>
       </c>
       <c r="F79">
-        <v>0.20820908565053911</v>
+        <v>0.19481551873734657</v>
       </c>
       <c r="G79">
         <v>0.50778999999999996</v>
@@ -22058,7 +22058,7 @@
         <v>36.300000000000004</v>
       </c>
       <c r="J79">
-        <v>3.4650000000000007</v>
+        <v>3.4650000000000003</v>
       </c>
       <c r="K79">
         <v>50</v>
@@ -22099,19 +22099,19 @@
         <v>2022</v>
       </c>
       <c r="F80">
-        <v>0.16608022972358796</v>
+        <v>0.49339465314217229</v>
       </c>
       <c r="G80">
-        <v>0.50778999999999996</v>
+        <v>0.52529999999999999</v>
       </c>
       <c r="H80">
-        <v>1265</v>
+        <v>1100</v>
       </c>
       <c r="I80">
-        <v>36.300000000000004</v>
+        <v>33</v>
       </c>
       <c r="J80">
-        <v>3.4650000000000003</v>
+        <v>3.1500000000000004</v>
       </c>
       <c r="K80">
         <v>50</v>
@@ -22152,7 +22152,7 @@
         <v>2022</v>
       </c>
       <c r="F81">
-        <v>0.18872753377680451</v>
+        <v>0.18702289798785268</v>
       </c>
       <c r="G81">
         <v>0.50778999999999996</v>
@@ -22164,7 +22164,7 @@
         <v>36.300000000000004</v>
       </c>
       <c r="J81">
-        <v>3.4650000000000007</v>
+        <v>3.4650000000000003</v>
       </c>
       <c r="K81">
         <v>50</v>
@@ -22205,7 +22205,7 @@
         <v>2022</v>
       </c>
       <c r="F82">
-        <v>0.18507474280047922</v>
+        <v>0.27347228442755023</v>
       </c>
       <c r="G82">
         <v>0.50778999999999996</v>
@@ -22217,7 +22217,7 @@
         <v>36.300000000000004</v>
       </c>
       <c r="J82">
-        <v>3.4649999999999999</v>
+        <v>3.4650000000000003</v>
       </c>
       <c r="K82">
         <v>50</v>
@@ -22252,7 +22252,7 @@
         <v>49</v>
       </c>
       <c r="D83" t="s">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="E83">
         <v>2006</v>
@@ -22305,7 +22305,7 @@
         <v>49</v>
       </c>
       <c r="D84" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="E84">
         <v>2012</v>
@@ -22358,7 +22358,7 @@
         <v>49</v>
       </c>
       <c r="D85" t="s">
-        <v>72</v>
+        <v>59</v>
       </c>
       <c r="E85">
         <v>1993</v>
@@ -22411,7 +22411,7 @@
         <v>49</v>
       </c>
       <c r="D86" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="E86">
         <v>2011</v>
@@ -22464,7 +22464,7 @@
         <v>49</v>
       </c>
       <c r="D87" t="s">
-        <v>80</v>
+        <v>61</v>
       </c>
       <c r="E87">
         <v>2005</v>
@@ -22517,7 +22517,7 @@
         <v>49</v>
       </c>
       <c r="D88" t="s">
-        <v>80</v>
+        <v>61</v>
       </c>
       <c r="E88">
         <v>2006</v>
@@ -22570,7 +22570,7 @@
         <v>49</v>
       </c>
       <c r="D89" t="s">
-        <v>80</v>
+        <v>61</v>
       </c>
       <c r="E89">
         <v>2006</v>
@@ -22676,7 +22676,7 @@
         <v>49</v>
       </c>
       <c r="D91" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="E91">
         <v>2003</v>
@@ -22835,7 +22835,7 @@
         <v>49</v>
       </c>
       <c r="D94" t="s">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="E94">
         <v>2004</v>
@@ -22888,7 +22888,7 @@
         <v>49</v>
       </c>
       <c r="D95" t="s">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="E95">
         <v>2005</v>
@@ -22941,7 +22941,7 @@
         <v>49</v>
       </c>
       <c r="D96" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="E96">
         <v>2005</v>
@@ -22994,7 +22994,7 @@
         <v>49</v>
       </c>
       <c r="D97" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="E97">
         <v>2005</v>
@@ -23047,7 +23047,7 @@
         <v>49</v>
       </c>
       <c r="D98" t="s">
-        <v>52</v>
+        <v>75</v>
       </c>
       <c r="E98">
         <v>2004</v>
@@ -23100,7 +23100,7 @@
         <v>49</v>
       </c>
       <c r="D99" t="s">
-        <v>52</v>
+        <v>75</v>
       </c>
       <c r="E99">
         <v>2004</v>
@@ -23153,7 +23153,7 @@
         <v>49</v>
       </c>
       <c r="D100" t="s">
-        <v>52</v>
+        <v>75</v>
       </c>
       <c r="E100">
         <v>2004</v>
@@ -23206,7 +23206,7 @@
         <v>49</v>
       </c>
       <c r="D101" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="E101">
         <v>2008</v>
@@ -23259,7 +23259,7 @@
         <v>49</v>
       </c>
       <c r="D102" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="E102">
         <v>2008</v>
@@ -23312,7 +23312,7 @@
         <v>49</v>
       </c>
       <c r="D103" t="s">
-        <v>54</v>
+        <v>72</v>
       </c>
       <c r="E103">
         <v>2002</v>
@@ -23365,7 +23365,7 @@
         <v>49</v>
       </c>
       <c r="D104" t="s">
-        <v>54</v>
+        <v>72</v>
       </c>
       <c r="E104">
         <v>2002</v>
@@ -23418,7 +23418,7 @@
         <v>49</v>
       </c>
       <c r="D105" t="s">
-        <v>54</v>
+        <v>72</v>
       </c>
       <c r="E105">
         <v>2003</v>
@@ -23471,7 +23471,7 @@
         <v>49</v>
       </c>
       <c r="D106" t="s">
-        <v>54</v>
+        <v>72</v>
       </c>
       <c r="E106">
         <v>2003</v>
@@ -23524,7 +23524,7 @@
         <v>49</v>
       </c>
       <c r="D107" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="E107">
         <v>2000</v>
@@ -23577,7 +23577,7 @@
         <v>49</v>
       </c>
       <c r="D108" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="E108">
         <v>2000</v>
@@ -23630,7 +23630,7 @@
         <v>49</v>
       </c>
       <c r="D109" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="E109">
         <v>2007</v>
@@ -23683,7 +23683,7 @@
         <v>49</v>
       </c>
       <c r="D110" t="s">
-        <v>72</v>
+        <v>59</v>
       </c>
       <c r="E110">
         <v>2023</v>
@@ -23736,7 +23736,7 @@
         <v>49</v>
       </c>
       <c r="D111" t="s">
-        <v>72</v>
+        <v>59</v>
       </c>
       <c r="E111">
         <v>2001</v>
@@ -23842,7 +23842,7 @@
         <v>49</v>
       </c>
       <c r="D113" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="E113">
         <v>2010</v>
@@ -23895,7 +23895,7 @@
         <v>49</v>
       </c>
       <c r="D114" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="E114">
         <v>2005</v>
@@ -23948,7 +23948,7 @@
         <v>49</v>
       </c>
       <c r="D115" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="E115">
         <v>2009</v>
@@ -24001,7 +24001,7 @@
         <v>49</v>
       </c>
       <c r="D116" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="E116">
         <v>1997</v>
@@ -24054,7 +24054,7 @@
         <v>49</v>
       </c>
       <c r="D117" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="E117">
         <v>1997</v>
@@ -24107,7 +24107,7 @@
         <v>49</v>
       </c>
       <c r="D118" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="E118">
         <v>1998</v>
@@ -24160,7 +24160,7 @@
         <v>49</v>
       </c>
       <c r="D119" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="E119">
         <v>1999</v>
@@ -24266,7 +24266,7 @@
         <v>49</v>
       </c>
       <c r="D121" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="E121">
         <v>2010</v>
@@ -24319,7 +24319,7 @@
         <v>49</v>
       </c>
       <c r="D122" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="E122">
         <v>2003</v>
@@ -24372,7 +24372,7 @@
         <v>49</v>
       </c>
       <c r="D123" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="E123">
         <v>2003</v>
@@ -24425,7 +24425,7 @@
         <v>49</v>
       </c>
       <c r="D124" t="s">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="E124">
         <v>2006</v>
@@ -24584,7 +24584,7 @@
         <v>49</v>
       </c>
       <c r="D127" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="E127">
         <v>2002</v>
@@ -24637,7 +24637,7 @@
         <v>49</v>
       </c>
       <c r="D128" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="E128">
         <v>2002</v>
@@ -24690,7 +24690,7 @@
         <v>49</v>
       </c>
       <c r="D129" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="E129">
         <v>2010</v>
@@ -24743,7 +24743,7 @@
         <v>49</v>
       </c>
       <c r="D130" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="E130">
         <v>2010</v>
@@ -24796,7 +24796,7 @@
         <v>49</v>
       </c>
       <c r="D131" t="s">
-        <v>66</v>
+        <v>86</v>
       </c>
       <c r="E131">
         <v>2008</v>
@@ -24849,7 +24849,7 @@
         <v>49</v>
       </c>
       <c r="D132" t="s">
-        <v>66</v>
+        <v>86</v>
       </c>
       <c r="E132">
         <v>2008</v>
@@ -24902,7 +24902,7 @@
         <v>49</v>
       </c>
       <c r="D133" t="s">
-        <v>75</v>
+        <v>52</v>
       </c>
       <c r="E133">
         <v>2018</v>
@@ -24955,7 +24955,7 @@
         <v>49</v>
       </c>
       <c r="D134" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="E134">
         <v>2006</v>
@@ -25008,7 +25008,7 @@
         <v>49</v>
       </c>
       <c r="D135" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="E135">
         <v>2007</v>
@@ -25167,7 +25167,7 @@
         <v>49</v>
       </c>
       <c r="D138" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E138">
         <v>2010</v>
@@ -25220,7 +25220,7 @@
         <v>49</v>
       </c>
       <c r="D139" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E139">
         <v>2010</v>
@@ -25273,7 +25273,7 @@
         <v>49</v>
       </c>
       <c r="D140" t="s">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="E140">
         <v>2004</v>
@@ -25326,7 +25326,7 @@
         <v>49</v>
       </c>
       <c r="D141" t="s">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="E141">
         <v>2004</v>
@@ -25379,7 +25379,7 @@
         <v>49</v>
       </c>
       <c r="D142" t="s">
-        <v>74</v>
+        <v>53</v>
       </c>
       <c r="E142">
         <v>2008</v>
@@ -25432,7 +25432,7 @@
         <v>49</v>
       </c>
       <c r="D143" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="E143">
         <v>2007</v>
@@ -25485,7 +25485,7 @@
         <v>49</v>
       </c>
       <c r="D144" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="E144">
         <v>2007</v>
@@ -25538,7 +25538,7 @@
         <v>49</v>
       </c>
       <c r="D145" t="s">
-        <v>59</v>
+        <v>85</v>
       </c>
       <c r="E145">
         <v>2005</v>
@@ -25591,7 +25591,7 @@
         <v>49</v>
       </c>
       <c r="D146" t="s">
-        <v>59</v>
+        <v>85</v>
       </c>
       <c r="E146">
         <v>2005</v>
@@ -25644,7 +25644,7 @@
         <v>49</v>
       </c>
       <c r="D147" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="E147">
         <v>2015</v>
@@ -25697,7 +25697,7 @@
         <v>49</v>
       </c>
       <c r="D148" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="E148">
         <v>2004</v>
@@ -25750,7 +25750,7 @@
         <v>49</v>
       </c>
       <c r="D149" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="E149">
         <v>2006</v>
@@ -25803,7 +25803,7 @@
         <v>49</v>
       </c>
       <c r="D150" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="E150">
         <v>2011</v>
@@ -25856,7 +25856,7 @@
         <v>49</v>
       </c>
       <c r="D151" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E151">
         <v>2004</v>
@@ -25909,7 +25909,7 @@
         <v>49</v>
       </c>
       <c r="D152" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E152">
         <v>2005</v>
@@ -25962,7 +25962,7 @@
         <v>49</v>
       </c>
       <c r="D153" t="s">
-        <v>69</v>
+        <v>56</v>
       </c>
       <c r="E153">
         <v>2006</v>
@@ -26015,7 +26015,7 @@
         <v>49</v>
       </c>
       <c r="D154" t="s">
-        <v>51</v>
+        <v>76</v>
       </c>
       <c r="E154">
         <v>2008</v>
@@ -26068,7 +26068,7 @@
         <v>49</v>
       </c>
       <c r="D155" t="s">
-        <v>67</v>
+        <v>84</v>
       </c>
       <c r="E155">
         <v>2007</v>
@@ -26174,7 +26174,7 @@
         <v>49</v>
       </c>
       <c r="D157" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="E157">
         <v>2023</v>
@@ -26227,7 +26227,7 @@
         <v>49</v>
       </c>
       <c r="D158" t="s">
-        <v>81</v>
+        <v>60</v>
       </c>
       <c r="E158">
         <v>2026</v>
@@ -26280,7 +26280,7 @@
         <v>49</v>
       </c>
       <c r="D159" t="s">
-        <v>51</v>
+        <v>76</v>
       </c>
       <c r="E159">
         <v>2022</v>
@@ -26333,7 +26333,7 @@
         <v>49</v>
       </c>
       <c r="D160" t="s">
-        <v>71</v>
+        <v>58</v>
       </c>
       <c r="E160">
         <v>2003</v>
@@ -26386,7 +26386,7 @@
         <v>49</v>
       </c>
       <c r="D161" t="s">
-        <v>71</v>
+        <v>58</v>
       </c>
       <c r="E161">
         <v>2003</v>
@@ -26439,7 +26439,7 @@
         <v>49</v>
       </c>
       <c r="D162" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="E162">
         <v>2003</v>
@@ -26492,7 +26492,7 @@
         <v>49</v>
       </c>
       <c r="D163" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="E163">
         <v>2008</v>
@@ -26545,7 +26545,7 @@
         <v>49</v>
       </c>
       <c r="D164" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="E164">
         <v>1999</v>
@@ -26598,7 +26598,7 @@
         <v>49</v>
       </c>
       <c r="D165" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="E165">
         <v>1999</v>
@@ -26651,7 +26651,7 @@
         <v>49</v>
       </c>
       <c r="D166" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="E166">
         <v>1997</v>
@@ -26757,7 +26757,7 @@
         <v>49</v>
       </c>
       <c r="D168" t="s">
-        <v>76</v>
+        <v>51</v>
       </c>
       <c r="E168">
         <v>2001</v>
@@ -26810,7 +26810,7 @@
         <v>49</v>
       </c>
       <c r="D169" t="s">
-        <v>52</v>
+        <v>75</v>
       </c>
       <c r="E169">
         <v>2006</v>
@@ -26916,7 +26916,7 @@
         <v>49</v>
       </c>
       <c r="D171" t="s">
-        <v>75</v>
+        <v>52</v>
       </c>
       <c r="E171">
         <v>2007</v>
@@ -27499,7 +27499,7 @@
         <v>49</v>
       </c>
       <c r="D182" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="E182">
         <v>2015</v>
@@ -28294,7 +28294,7 @@
         <v>49</v>
       </c>
       <c r="D197" t="s">
-        <v>51</v>
+        <v>76</v>
       </c>
       <c r="E197">
         <v>2004</v>
@@ -28347,7 +28347,7 @@
         <v>49</v>
       </c>
       <c r="D198" t="s">
-        <v>51</v>
+        <v>76</v>
       </c>
       <c r="E198">
         <v>2008</v>
@@ -28559,7 +28559,7 @@
         <v>49</v>
       </c>
       <c r="D202" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="E202">
         <v>2005</v>
@@ -28612,7 +28612,7 @@
         <v>49</v>
       </c>
       <c r="D203" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="E203">
         <v>2015</v>
@@ -29301,7 +29301,7 @@
         <v>49</v>
       </c>
       <c r="D216" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E216">
         <v>2022</v>
@@ -29513,7 +29513,7 @@
         <v>49</v>
       </c>
       <c r="D220" t="s">
-        <v>81</v>
+        <v>60</v>
       </c>
       <c r="E220">
         <v>2009</v>
@@ -30202,7 +30202,7 @@
         <v>49</v>
       </c>
       <c r="D233" t="s">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="E233">
         <v>1994</v>
@@ -30361,7 +30361,7 @@
         <v>49</v>
       </c>
       <c r="D236" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E236">
         <v>1990</v>
@@ -30414,7 +30414,7 @@
         <v>49</v>
       </c>
       <c r="D237" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E237">
         <v>2022</v>
@@ -30573,7 +30573,7 @@
         <v>49</v>
       </c>
       <c r="D240" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="E240">
         <v>2006</v>
@@ -30626,7 +30626,7 @@
         <v>49</v>
       </c>
       <c r="D241" t="s">
-        <v>59</v>
+        <v>85</v>
       </c>
       <c r="E241">
         <v>2024</v>
@@ -30679,7 +30679,7 @@
         <v>49</v>
       </c>
       <c r="D242" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="E242">
         <v>2023</v>
@@ -30732,7 +30732,7 @@
         <v>49</v>
       </c>
       <c r="D243" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="E243">
         <v>2023</v>
@@ -30785,7 +30785,7 @@
         <v>49</v>
       </c>
       <c r="D244" t="s">
-        <v>75</v>
+        <v>52</v>
       </c>
       <c r="E244">
         <v>1997</v>
@@ -31262,7 +31262,7 @@
         <v>49</v>
       </c>
       <c r="D253" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="E253">
         <v>2008</v>
@@ -31527,7 +31527,7 @@
         <v>49</v>
       </c>
       <c r="D258" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="E258">
         <v>2015</v>
@@ -31633,7 +31633,7 @@
         <v>49</v>
       </c>
       <c r="D260" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="E260">
         <v>2004</v>
@@ -31898,7 +31898,7 @@
         <v>49</v>
       </c>
       <c r="D265" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="E265">
         <v>2024</v>
@@ -32004,7 +32004,7 @@
         <v>49</v>
       </c>
       <c r="D267" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="E267">
         <v>2023</v>
@@ -32216,7 +32216,7 @@
         <v>49</v>
       </c>
       <c r="D271" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="E271">
         <v>1975</v>
@@ -32269,7 +32269,7 @@
         <v>49</v>
       </c>
       <c r="D272" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="E272">
         <v>1975</v>
@@ -32322,7 +32322,7 @@
         <v>49</v>
       </c>
       <c r="D273" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="E273">
         <v>1975</v>
@@ -32375,7 +32375,7 @@
         <v>49</v>
       </c>
       <c r="D274" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="E274">
         <v>2015</v>
@@ -32428,7 +32428,7 @@
         <v>49</v>
       </c>
       <c r="D275" t="s">
-        <v>80</v>
+        <v>61</v>
       </c>
       <c r="E275">
         <v>1967</v>
@@ -32481,7 +32481,7 @@
         <v>49</v>
       </c>
       <c r="D276" t="s">
-        <v>80</v>
+        <v>61</v>
       </c>
       <c r="E276">
         <v>1971</v>
@@ -32534,7 +32534,7 @@
         <v>49</v>
       </c>
       <c r="D277" t="s">
-        <v>76</v>
+        <v>51</v>
       </c>
       <c r="E277">
         <v>1970</v>
@@ -32587,7 +32587,7 @@
         <v>49</v>
       </c>
       <c r="D278" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E278">
         <v>1978</v>
@@ -32640,7 +32640,7 @@
         <v>49</v>
       </c>
       <c r="D279" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E279">
         <v>1981</v>
@@ -32693,7 +32693,7 @@
         <v>49</v>
       </c>
       <c r="D280" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E280">
         <v>1987</v>
@@ -33117,7 +33117,7 @@
         <v>293</v>
       </c>
       <c r="D288" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="E288">
         <v>1991</v>
@@ -33170,7 +33170,7 @@
         <v>293</v>
       </c>
       <c r="D289" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="E289">
         <v>1991</v>
@@ -34230,25 +34230,25 @@
         <v>308</v>
       </c>
       <c r="D309" t="s">
-        <v>309</v>
+        <v>239</v>
       </c>
       <c r="E309">
         <v>2022</v>
       </c>
       <c r="F309">
-        <v>4.4073197411209589E-2</v>
+        <v>0.22871669814448767</v>
       </c>
       <c r="G309">
         <v>1</v>
       </c>
       <c r="H309">
-        <v>3712.5000000000005</v>
+        <v>3162.5000000000005</v>
       </c>
       <c r="I309">
-        <v>71.5</v>
+        <v>60.500000000000014</v>
       </c>
       <c r="J309">
-        <v>2.52</v>
+        <v>2.3100000000000005</v>
       </c>
       <c r="K309">
         <v>100</v>
@@ -34283,25 +34283,25 @@
         <v>308</v>
       </c>
       <c r="D310" t="s">
-        <v>310</v>
+        <v>99</v>
       </c>
       <c r="E310">
         <v>2022</v>
       </c>
       <c r="F310">
-        <v>1.0883760118599757</v>
+        <v>0.29181095970158766</v>
       </c>
       <c r="G310">
         <v>1</v>
       </c>
       <c r="H310">
-        <v>2750</v>
+        <v>3162.5000000000005</v>
       </c>
       <c r="I310">
-        <v>55.000000000000007</v>
+        <v>60.500000000000014</v>
       </c>
       <c r="J310">
-        <v>2.1</v>
+        <v>2.3100000000000005</v>
       </c>
       <c r="K310">
         <v>100</v>
@@ -34336,25 +34336,25 @@
         <v>308</v>
       </c>
       <c r="D311" t="s">
-        <v>57</v>
+        <v>309</v>
       </c>
       <c r="E311">
         <v>2022</v>
       </c>
       <c r="F311">
-        <v>5.4743550468660328E-2</v>
+        <v>0.35629700644009438</v>
       </c>
       <c r="G311">
         <v>1</v>
       </c>
       <c r="H311">
-        <v>3162.5000000000005</v>
+        <v>2750</v>
       </c>
       <c r="I311">
-        <v>60.500000000000014</v>
+        <v>55</v>
       </c>
       <c r="J311">
-        <v>2.3100000000000005</v>
+        <v>2.1</v>
       </c>
       <c r="K311">
         <v>100</v>
@@ -34389,13 +34389,13 @@
         <v>308</v>
       </c>
       <c r="D312" t="s">
-        <v>239</v>
+        <v>310</v>
       </c>
       <c r="E312">
         <v>2022</v>
       </c>
       <c r="F312">
-        <v>0.22871669814448767</v>
+        <v>0.13036387865841995</v>
       </c>
       <c r="G312">
         <v>1</v>
@@ -34448,7 +34448,7 @@
         <v>2022</v>
       </c>
       <c r="F313">
-        <v>6.3558189950902247E-2</v>
+        <v>6.0310691194286808E-2</v>
       </c>
       <c r="G313">
         <v>1</v>
@@ -34495,25 +34495,25 @@
         <v>308</v>
       </c>
       <c r="D314" t="s">
-        <v>204</v>
+        <v>151</v>
       </c>
       <c r="E314">
         <v>2022</v>
       </c>
       <c r="F314">
-        <v>7.8403898552572848E-2</v>
+        <v>4.5464982592616207E-2</v>
       </c>
       <c r="G314">
         <v>1</v>
       </c>
       <c r="H314">
-        <v>3162.5000000000005</v>
+        <v>3712.5000000000005</v>
       </c>
       <c r="I314">
-        <v>60.500000000000014</v>
+        <v>71.5</v>
       </c>
       <c r="J314">
-        <v>2.3100000000000005</v>
+        <v>2.52</v>
       </c>
       <c r="K314">
         <v>100</v>
@@ -34554,19 +34554,19 @@
         <v>2022</v>
       </c>
       <c r="F315">
-        <v>6.9589259070330922E-2</v>
+        <v>4.4073197411209589E-2</v>
       </c>
       <c r="G315">
         <v>1</v>
       </c>
       <c r="H315">
-        <v>3162.5000000000005</v>
+        <v>3712.5000000000005</v>
       </c>
       <c r="I315">
-        <v>60.500000000000007</v>
+        <v>71.5</v>
       </c>
       <c r="J315">
-        <v>2.3100000000000005</v>
+        <v>2.52</v>
       </c>
       <c r="K315">
         <v>100</v>
@@ -34607,19 +34607,19 @@
         <v>2022</v>
       </c>
       <c r="F316">
-        <v>0.10670353057450742</v>
+        <v>1.0883760118599757</v>
       </c>
       <c r="G316">
         <v>1</v>
       </c>
       <c r="H316">
-        <v>3162.5000000000005</v>
+        <v>2750</v>
       </c>
       <c r="I316">
-        <v>60.500000000000014</v>
+        <v>55.000000000000007</v>
       </c>
       <c r="J316">
-        <v>2.3100000000000005</v>
+        <v>2.1</v>
       </c>
       <c r="K316">
         <v>100</v>
@@ -34660,19 +34660,19 @@
         <v>2022</v>
       </c>
       <c r="F317">
-        <v>4.3145340623605172E-2</v>
+        <v>0.54140443556717466</v>
       </c>
       <c r="G317">
         <v>1</v>
       </c>
       <c r="H317">
-        <v>3712.5000000000005</v>
+        <v>2750</v>
       </c>
       <c r="I317">
-        <v>71.5</v>
+        <v>55.000000000000007</v>
       </c>
       <c r="J317">
-        <v>2.52</v>
+        <v>2.1</v>
       </c>
       <c r="K317">
         <v>100</v>
@@ -34707,25 +34707,25 @@
         <v>308</v>
       </c>
       <c r="D318" t="s">
-        <v>291</v>
+        <v>315</v>
       </c>
       <c r="E318">
         <v>2022</v>
       </c>
       <c r="F318">
-        <v>0.13082780705222213</v>
+        <v>4.4073197411209589E-2</v>
       </c>
       <c r="G318">
         <v>1</v>
       </c>
       <c r="H318">
-        <v>3162.5000000000005</v>
+        <v>3712.5000000000005</v>
       </c>
       <c r="I318">
-        <v>60.500000000000014</v>
+        <v>71.5</v>
       </c>
       <c r="J318">
-        <v>2.3100000000000005</v>
+        <v>2.52</v>
       </c>
       <c r="K318">
         <v>100</v>
@@ -34760,25 +34760,25 @@
         <v>308</v>
       </c>
       <c r="D319" t="s">
-        <v>315</v>
+        <v>50</v>
       </c>
       <c r="E319">
         <v>2022</v>
       </c>
       <c r="F319">
-        <v>0.56367299846968055</v>
+        <v>0.23196419690110309</v>
       </c>
       <c r="G319">
         <v>1</v>
       </c>
       <c r="H319">
-        <v>2750</v>
+        <v>3162.5000000000005</v>
       </c>
       <c r="I319">
-        <v>55.000000000000007</v>
+        <v>60.500000000000014</v>
       </c>
       <c r="J319">
-        <v>2.1</v>
+        <v>2.3100000000000005</v>
       </c>
       <c r="K319">
         <v>100</v>
@@ -34813,13 +34813,13 @@
         <v>308</v>
       </c>
       <c r="D320" t="s">
-        <v>316</v>
+        <v>291</v>
       </c>
       <c r="E320">
         <v>2022</v>
       </c>
       <c r="F320">
-        <v>0.19299421182171778</v>
+        <v>0.13082780705222213</v>
       </c>
       <c r="G320">
         <v>1</v>
@@ -34866,25 +34866,25 @@
         <v>308</v>
       </c>
       <c r="D321" t="s">
-        <v>317</v>
+        <v>204</v>
       </c>
       <c r="E321">
         <v>2022</v>
       </c>
       <c r="F321">
-        <v>0.35629700644009438</v>
+        <v>7.8403898552572848E-2</v>
       </c>
       <c r="G321">
         <v>1</v>
       </c>
       <c r="H321">
-        <v>2750</v>
+        <v>3162.5000000000005</v>
       </c>
       <c r="I321">
-        <v>55</v>
+        <v>60.500000000000014</v>
       </c>
       <c r="J321">
-        <v>2.1</v>
+        <v>2.3100000000000005</v>
       </c>
       <c r="K321">
         <v>100</v>
@@ -34919,13 +34919,13 @@
         <v>308</v>
       </c>
       <c r="D322" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="E322">
         <v>2022</v>
       </c>
       <c r="F322">
-        <v>6.0310691194286808E-2</v>
+        <v>0.19299421182171778</v>
       </c>
       <c r="G322">
         <v>1</v>
@@ -34972,13 +34972,13 @@
         <v>308</v>
       </c>
       <c r="D323" t="s">
-        <v>193</v>
+        <v>317</v>
       </c>
       <c r="E323">
         <v>2022</v>
       </c>
       <c r="F323">
-        <v>0.61052976624370348</v>
+        <v>0.56367299846968055</v>
       </c>
       <c r="G323">
         <v>1</v>
@@ -35025,25 +35025,25 @@
         <v>308</v>
       </c>
       <c r="D324" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="E324">
         <v>2022</v>
       </c>
       <c r="F324">
-        <v>0.20320063648536632</v>
+        <v>4.3145340623605172E-2</v>
       </c>
       <c r="G324">
         <v>1</v>
       </c>
       <c r="H324">
-        <v>3162.5000000000005</v>
+        <v>3712.5000000000005</v>
       </c>
       <c r="I324">
-        <v>60.500000000000014</v>
+        <v>71.5</v>
       </c>
       <c r="J324">
-        <v>2.3100000000000005</v>
+        <v>2.52</v>
       </c>
       <c r="K324">
         <v>100</v>
@@ -35078,13 +35078,13 @@
         <v>308</v>
       </c>
       <c r="D325" t="s">
-        <v>83</v>
+        <v>319</v>
       </c>
       <c r="E325">
         <v>2022</v>
       </c>
       <c r="F325">
-        <v>0.50939337639482241</v>
+        <v>0.57944656385895543</v>
       </c>
       <c r="G325">
         <v>1</v>
@@ -35131,13 +35131,13 @@
         <v>308</v>
       </c>
       <c r="D326" t="s">
-        <v>58</v>
+        <v>320</v>
       </c>
       <c r="E326">
         <v>2022</v>
       </c>
       <c r="F326">
-        <v>0.23196419690110309</v>
+        <v>5.8918906012880183E-2</v>
       </c>
       <c r="G326">
         <v>1</v>
@@ -35146,7 +35146,7 @@
         <v>3162.5000000000005</v>
       </c>
       <c r="I326">
-        <v>60.500000000000014</v>
+        <v>60.500000000000021</v>
       </c>
       <c r="J326">
         <v>2.3100000000000005</v>
@@ -35184,13 +35184,13 @@
         <v>308</v>
       </c>
       <c r="D327" t="s">
-        <v>320</v>
+        <v>65</v>
       </c>
       <c r="E327">
         <v>2022</v>
       </c>
       <c r="F327">
-        <v>0.10067246145507874</v>
+        <v>5.4743550468660328E-2</v>
       </c>
       <c r="G327">
         <v>1</v>
@@ -35243,7 +35243,7 @@
         <v>2022</v>
       </c>
       <c r="F328">
-        <v>5.1032123318242681E-2</v>
+        <v>0.10670353057450742</v>
       </c>
       <c r="G328">
         <v>1</v>
@@ -35252,7 +35252,7 @@
         <v>3162.5000000000005</v>
       </c>
       <c r="I328">
-        <v>60.500000000000021</v>
+        <v>60.500000000000014</v>
       </c>
       <c r="J328">
         <v>2.3100000000000005</v>
@@ -35290,25 +35290,25 @@
         <v>308</v>
       </c>
       <c r="D329" t="s">
-        <v>14</v>
+        <v>80</v>
       </c>
       <c r="E329">
         <v>2022</v>
       </c>
       <c r="F329">
-        <v>8.7682466428616976E-2</v>
+        <v>0.50939337639482241</v>
       </c>
       <c r="G329">
         <v>1</v>
       </c>
       <c r="H329">
-        <v>3162.5000000000005</v>
+        <v>2750</v>
       </c>
       <c r="I329">
-        <v>60.500000000000007</v>
+        <v>55.000000000000007</v>
       </c>
       <c r="J329">
-        <v>2.3100000000000005</v>
+        <v>2.1</v>
       </c>
       <c r="K329">
         <v>100</v>
@@ -35349,7 +35349,7 @@
         <v>2022</v>
       </c>
       <c r="F330">
-        <v>5.8918906012880183E-2</v>
+        <v>6.9589259070330922E-2</v>
       </c>
       <c r="G330">
         <v>1</v>
@@ -35358,7 +35358,7 @@
         <v>3162.5000000000005</v>
       </c>
       <c r="I330">
-        <v>60.500000000000021</v>
+        <v>60.500000000000007</v>
       </c>
       <c r="J330">
         <v>2.3100000000000005</v>
@@ -35396,25 +35396,25 @@
         <v>308</v>
       </c>
       <c r="D331" t="s">
-        <v>151</v>
+        <v>323</v>
       </c>
       <c r="E331">
         <v>2022</v>
       </c>
       <c r="F331">
-        <v>4.5464982592616207E-2</v>
+        <v>0.10067246145507874</v>
       </c>
       <c r="G331">
         <v>1</v>
       </c>
       <c r="H331">
-        <v>3712.5000000000005</v>
+        <v>3162.5000000000005</v>
       </c>
       <c r="I331">
-        <v>71.5</v>
+        <v>60.500000000000014</v>
       </c>
       <c r="J331">
-        <v>2.52</v>
+        <v>2.3100000000000005</v>
       </c>
       <c r="K331">
         <v>100</v>
@@ -35449,25 +35449,25 @@
         <v>308</v>
       </c>
       <c r="D332" t="s">
-        <v>323</v>
+        <v>193</v>
       </c>
       <c r="E332">
         <v>2022</v>
       </c>
       <c r="F332">
-        <v>0.13036387865841995</v>
+        <v>0.61052976624370348</v>
       </c>
       <c r="G332">
         <v>1</v>
       </c>
       <c r="H332">
-        <v>3162.5000000000005</v>
+        <v>2750</v>
       </c>
       <c r="I332">
-        <v>60.500000000000014</v>
+        <v>55.000000000000007</v>
       </c>
       <c r="J332">
-        <v>2.3100000000000005</v>
+        <v>2.1</v>
       </c>
       <c r="K332">
         <v>100</v>
@@ -35502,25 +35502,25 @@
         <v>308</v>
       </c>
       <c r="D333" t="s">
-        <v>324</v>
+        <v>19</v>
       </c>
       <c r="E333">
         <v>2022</v>
       </c>
       <c r="F333">
-        <v>4.4073197411209589E-2</v>
+        <v>0.11134281451252948</v>
       </c>
       <c r="G333">
         <v>1</v>
       </c>
       <c r="H333">
-        <v>3712.5000000000005</v>
+        <v>3162.5000000000005</v>
       </c>
       <c r="I333">
-        <v>71.5</v>
+        <v>60.500000000000014</v>
       </c>
       <c r="J333">
-        <v>2.52</v>
+        <v>2.3100000000000005</v>
       </c>
       <c r="K333">
         <v>100</v>
@@ -35555,25 +35555,25 @@
         <v>308</v>
       </c>
       <c r="D334" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="E334">
         <v>2022</v>
       </c>
       <c r="F334">
-        <v>0.57944656385895543</v>
+        <v>0.1577356538927501</v>
       </c>
       <c r="G334">
         <v>1</v>
       </c>
       <c r="H334">
-        <v>2750</v>
+        <v>3162.5000000000005</v>
       </c>
       <c r="I334">
-        <v>55.000000000000007</v>
+        <v>60.500000000000014</v>
       </c>
       <c r="J334">
-        <v>2.1</v>
+        <v>2.3100000000000005</v>
       </c>
       <c r="K334">
         <v>100</v>
@@ -35608,25 +35608,25 @@
         <v>308</v>
       </c>
       <c r="D335" t="s">
-        <v>326</v>
+        <v>16</v>
       </c>
       <c r="E335">
         <v>2022</v>
       </c>
       <c r="F335">
-        <v>4.1753555442198553E-2</v>
+        <v>8.7682466428616976E-2</v>
       </c>
       <c r="G335">
         <v>1</v>
       </c>
       <c r="H335">
-        <v>3712.5000000000005</v>
+        <v>3162.5000000000005</v>
       </c>
       <c r="I335">
-        <v>71.5</v>
+        <v>60.500000000000007</v>
       </c>
       <c r="J335">
-        <v>2.52</v>
+        <v>2.3100000000000005</v>
       </c>
       <c r="K335">
         <v>100</v>
@@ -35661,13 +35661,13 @@
         <v>308</v>
       </c>
       <c r="D336" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="E336">
         <v>2022</v>
       </c>
       <c r="F336">
-        <v>0.15541601192373908</v>
+        <v>5.1032123318242681E-2</v>
       </c>
       <c r="G336">
         <v>1</v>
@@ -35676,7 +35676,7 @@
         <v>3162.5000000000005</v>
       </c>
       <c r="I336">
-        <v>60.500000000000014</v>
+        <v>60.500000000000021</v>
       </c>
       <c r="J336">
         <v>2.3100000000000005</v>
@@ -35714,13 +35714,13 @@
         <v>308</v>
       </c>
       <c r="D337" t="s">
-        <v>16</v>
+        <v>326</v>
       </c>
       <c r="E337">
         <v>2022</v>
       </c>
       <c r="F337">
-        <v>0.11134281451252948</v>
+        <v>0.15541601192373908</v>
       </c>
       <c r="G337">
         <v>1</v>
@@ -35767,25 +35767,25 @@
         <v>308</v>
       </c>
       <c r="D338" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="E338">
         <v>2022</v>
       </c>
       <c r="F338">
-        <v>0.54140443556717466</v>
+        <v>0.20320063648536632</v>
       </c>
       <c r="G338">
         <v>1</v>
       </c>
       <c r="H338">
-        <v>2750</v>
+        <v>3162.5000000000005</v>
       </c>
       <c r="I338">
-        <v>55.000000000000007</v>
+        <v>60.500000000000014</v>
       </c>
       <c r="J338">
-        <v>2.1</v>
+        <v>2.3100000000000005</v>
       </c>
       <c r="K338">
         <v>100</v>
@@ -35820,25 +35820,25 @@
         <v>308</v>
       </c>
       <c r="D339" t="s">
-        <v>99</v>
+        <v>328</v>
       </c>
       <c r="E339">
         <v>2022</v>
       </c>
       <c r="F339">
-        <v>0.29181095970158766</v>
+        <v>4.1753555442198553E-2</v>
       </c>
       <c r="G339">
         <v>1</v>
       </c>
       <c r="H339">
-        <v>3162.5000000000005</v>
+        <v>3712.5000000000005</v>
       </c>
       <c r="I339">
-        <v>60.500000000000014</v>
+        <v>71.5</v>
       </c>
       <c r="J339">
-        <v>2.3100000000000005</v>
+        <v>2.52</v>
       </c>
       <c r="K339">
         <v>100</v>
@@ -35879,7 +35879,7 @@
         <v>2022</v>
       </c>
       <c r="F340">
-        <v>0.1577356538927501</v>
+        <v>6.3558189950902247E-2</v>
       </c>
       <c r="G340">
         <v>1</v>
@@ -35979,7 +35979,7 @@
         <v>308</v>
       </c>
       <c r="D342" t="s">
-        <v>324</v>
+        <v>312</v>
       </c>
       <c r="E342">
         <v>1959</v>
@@ -36085,7 +36085,7 @@
         <v>308</v>
       </c>
       <c r="D344" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E344">
         <v>1973</v>
@@ -36191,7 +36191,7 @@
         <v>308</v>
       </c>
       <c r="D346" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="E346">
         <v>1963</v>
@@ -36297,7 +36297,7 @@
         <v>308</v>
       </c>
       <c r="D348" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="E348">
         <v>1931</v>
@@ -36350,7 +36350,7 @@
         <v>308</v>
       </c>
       <c r="D349" t="s">
-        <v>328</v>
+        <v>314</v>
       </c>
       <c r="E349">
         <v>1949</v>
@@ -36403,7 +36403,7 @@
         <v>308</v>
       </c>
       <c r="D350" t="s">
-        <v>317</v>
+        <v>309</v>
       </c>
       <c r="E350">
         <v>1951</v>
@@ -36509,7 +36509,7 @@
         <v>308</v>
       </c>
       <c r="D352" t="s">
-        <v>318</v>
+        <v>311</v>
       </c>
       <c r="E352">
         <v>1958</v>
@@ -36562,7 +36562,7 @@
         <v>308</v>
       </c>
       <c r="D353" t="s">
-        <v>313</v>
+        <v>321</v>
       </c>
       <c r="E353">
         <v>1967</v>
@@ -36615,7 +36615,7 @@
         <v>308</v>
       </c>
       <c r="D354" t="s">
-        <v>319</v>
+        <v>327</v>
       </c>
       <c r="E354">
         <v>1968</v>
@@ -36668,7 +36668,7 @@
         <v>308</v>
       </c>
       <c r="D355" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="E355">
         <v>1929</v>
@@ -36721,7 +36721,7 @@
         <v>308</v>
       </c>
       <c r="D356" t="s">
-        <v>319</v>
+        <v>327</v>
       </c>
       <c r="E356">
         <v>1949</v>
@@ -36827,7 +36827,7 @@
         <v>308</v>
       </c>
       <c r="D358" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="E358">
         <v>1952</v>
@@ -36880,7 +36880,7 @@
         <v>308</v>
       </c>
       <c r="D359" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="E359">
         <v>1913</v>
@@ -36933,7 +36933,7 @@
         <v>308</v>
       </c>
       <c r="D360" t="s">
-        <v>317</v>
+        <v>309</v>
       </c>
       <c r="E360">
         <v>1924</v>
@@ -37039,7 +37039,7 @@
         <v>308</v>
       </c>
       <c r="D362" t="s">
-        <v>317</v>
+        <v>309</v>
       </c>
       <c r="E362">
         <v>1971</v>
@@ -37145,7 +37145,7 @@
         <v>308</v>
       </c>
       <c r="D364" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="E364">
         <v>1927</v>
@@ -37198,7 +37198,7 @@
         <v>308</v>
       </c>
       <c r="D365" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="E365">
         <v>1928</v>
@@ -37304,7 +37304,7 @@
         <v>308</v>
       </c>
       <c r="D367" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="E367">
         <v>1938</v>
@@ -37357,7 +37357,7 @@
         <v>308</v>
       </c>
       <c r="D368" t="s">
-        <v>309</v>
+        <v>315</v>
       </c>
       <c r="E368">
         <v>1920</v>
@@ -37410,7 +37410,7 @@
         <v>308</v>
       </c>
       <c r="D369" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="E369">
         <v>1947</v>
@@ -37463,7 +37463,7 @@
         <v>308</v>
       </c>
       <c r="D370" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="E370">
         <v>1950</v>
@@ -37516,7 +37516,7 @@
         <v>308</v>
       </c>
       <c r="D371" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E371">
         <v>1954</v>
@@ -37622,7 +37622,7 @@
         <v>308</v>
       </c>
       <c r="D373" t="s">
-        <v>317</v>
+        <v>309</v>
       </c>
       <c r="E373">
         <v>1971</v>
@@ -37675,7 +37675,7 @@
         <v>308</v>
       </c>
       <c r="D374" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="E374">
         <v>1959</v>
@@ -37781,7 +37781,7 @@
         <v>308</v>
       </c>
       <c r="D376" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="E376">
         <v>1955</v>
@@ -37834,7 +37834,7 @@
         <v>308</v>
       </c>
       <c r="D377" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="E377">
         <v>1959</v>
@@ -37887,7 +37887,7 @@
         <v>308</v>
       </c>
       <c r="D378" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="E378">
         <v>1954</v>
@@ -38099,7 +38099,7 @@
         <v>308</v>
       </c>
       <c r="D382" t="s">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="E382">
         <v>2022</v>
@@ -38311,7 +38311,7 @@
         <v>308</v>
       </c>
       <c r="D386" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="E386">
         <v>2022</v>
@@ -38417,7 +38417,7 @@
         <v>383</v>
       </c>
       <c r="D388" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="E388">
         <v>1989</v>
@@ -38470,7 +38470,7 @@
         <v>383</v>
       </c>
       <c r="D389" t="s">
-        <v>323</v>
+        <v>310</v>
       </c>
       <c r="E389">
         <v>1975</v>
@@ -38523,7 +38523,7 @@
         <v>383</v>
       </c>
       <c r="D390" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="E390">
         <v>1966</v>
@@ -38576,7 +38576,7 @@
         <v>383</v>
       </c>
       <c r="D391" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="E391">
         <v>2015</v>
@@ -38629,7 +38629,7 @@
         <v>383</v>
       </c>
       <c r="D392" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
       <c r="E392">
         <v>2015</v>
@@ -38682,7 +38682,7 @@
         <v>383</v>
       </c>
       <c r="D393" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
       <c r="E393">
         <v>1982</v>
@@ -38735,7 +38735,7 @@
         <v>383</v>
       </c>
       <c r="D394" t="s">
-        <v>317</v>
+        <v>309</v>
       </c>
       <c r="E394">
         <v>2015</v>
@@ -38788,7 +38788,7 @@
         <v>383</v>
       </c>
       <c r="D395" t="s">
-        <v>311</v>
+        <v>329</v>
       </c>
       <c r="E395">
         <v>2015</v>
@@ -38841,7 +38841,7 @@
         <v>383</v>
       </c>
       <c r="D396" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="E396">
         <v>1961</v>
@@ -38894,7 +38894,7 @@
         <v>383</v>
       </c>
       <c r="D397" t="s">
-        <v>312</v>
+        <v>322</v>
       </c>
       <c r="E397">
         <v>2005</v>
@@ -38947,7 +38947,7 @@
         <v>383</v>
       </c>
       <c r="D398" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="E398">
         <v>1991</v>
@@ -39106,7 +39106,7 @@
         <v>383</v>
       </c>
       <c r="D401" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="E401">
         <v>1971</v>
@@ -39159,7 +39159,7 @@
         <v>383</v>
       </c>
       <c r="D402" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="E402">
         <v>1973</v>
@@ -39318,7 +39318,7 @@
         <v>383</v>
       </c>
       <c r="D405" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E405">
         <v>1978</v>
@@ -39371,7 +39371,7 @@
         <v>383</v>
       </c>
       <c r="D406" t="s">
-        <v>328</v>
+        <v>314</v>
       </c>
       <c r="E406">
         <v>1923</v>
@@ -39424,7 +39424,7 @@
         <v>308</v>
       </c>
       <c r="D407" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="E407">
         <v>1959</v>
@@ -39530,7 +39530,7 @@
         <v>308</v>
       </c>
       <c r="D409" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="E409">
         <v>1949</v>
@@ -39583,7 +39583,7 @@
         <v>308</v>
       </c>
       <c r="D410" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="E410">
         <v>1953</v>
@@ -39689,7 +39689,7 @@
         <v>308</v>
       </c>
       <c r="D412" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="E412">
         <v>1960</v>
@@ -39742,7 +39742,7 @@
         <v>308</v>
       </c>
       <c r="D413" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="E413">
         <v>1962</v>
@@ -39795,7 +39795,7 @@
         <v>308</v>
       </c>
       <c r="D414" t="s">
-        <v>328</v>
+        <v>314</v>
       </c>
       <c r="E414">
         <v>2015</v>
@@ -39848,7 +39848,7 @@
         <v>308</v>
       </c>
       <c r="D415" t="s">
-        <v>319</v>
+        <v>327</v>
       </c>
       <c r="E415">
         <v>1927</v>
@@ -39901,7 +39901,7 @@
         <v>308</v>
       </c>
       <c r="D416" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="E416">
         <v>1954</v>
@@ -40007,7 +40007,7 @@
         <v>308</v>
       </c>
       <c r="D418" t="s">
-        <v>328</v>
+        <v>314</v>
       </c>
       <c r="E418">
         <v>1956</v>
@@ -40060,7 +40060,7 @@
         <v>308</v>
       </c>
       <c r="D419" t="s">
-        <v>317</v>
+        <v>309</v>
       </c>
       <c r="E419">
         <v>1956</v>
@@ -40166,7 +40166,7 @@
         <v>308</v>
       </c>
       <c r="D421" t="s">
-        <v>328</v>
+        <v>314</v>
       </c>
       <c r="E421">
         <v>1960</v>
@@ -40378,7 +40378,7 @@
         <v>308</v>
       </c>
       <c r="D425" t="s">
-        <v>319</v>
+        <v>327</v>
       </c>
       <c r="E425">
         <v>2015</v>
@@ -40431,7 +40431,7 @@
         <v>308</v>
       </c>
       <c r="D426" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
       <c r="E426">
         <v>2015</v>
@@ -40537,7 +40537,7 @@
         <v>308</v>
       </c>
       <c r="D428" t="s">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="E428">
         <v>1955</v>
@@ -40590,7 +40590,7 @@
         <v>308</v>
       </c>
       <c r="D429" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E429">
         <v>2015</v>
@@ -40696,7 +40696,7 @@
         <v>308</v>
       </c>
       <c r="D431" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="E431">
         <v>1932</v>
@@ -40855,7 +40855,7 @@
         <v>308</v>
       </c>
       <c r="D434" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="E434">
         <v>1924</v>
@@ -40961,7 +40961,7 @@
         <v>308</v>
       </c>
       <c r="D436" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="E436">
         <v>2002</v>
@@ -41067,7 +41067,7 @@
         <v>308</v>
       </c>
       <c r="D438" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="E438">
         <v>1948</v>
@@ -41173,7 +41173,7 @@
         <v>308</v>
       </c>
       <c r="D440" t="s">
-        <v>309</v>
+        <v>315</v>
       </c>
       <c r="E440">
         <v>1914</v>
@@ -41279,7 +41279,7 @@
         <v>308</v>
       </c>
       <c r="D442" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="E442">
         <v>1958</v>
@@ -41332,7 +41332,7 @@
         <v>439</v>
       </c>
       <c r="D443" t="s">
-        <v>72</v>
+        <v>59</v>
       </c>
       <c r="E443">
         <v>1992</v>
@@ -41491,7 +41491,7 @@
         <v>439</v>
       </c>
       <c r="D446" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E446">
         <v>1992</v>
@@ -41544,7 +41544,7 @@
         <v>439</v>
       </c>
       <c r="D447" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="E447">
         <v>2005</v>
@@ -41809,7 +41809,7 @@
         <v>439</v>
       </c>
       <c r="D452" t="s">
-        <v>72</v>
+        <v>59</v>
       </c>
       <c r="E452">
         <v>1985</v>
@@ -44808,7 +44808,7 @@
         <v>510</v>
       </c>
       <c r="D537" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="E537">
         <v>2022</v>
@@ -44837,13 +44837,13 @@
         <v>2022</v>
       </c>
       <c r="F538">
-        <v>0.69928302455480262</v>
+        <v>0.6793056475905862</v>
       </c>
       <c r="G538">
         <v>0.33123000000000002</v>
       </c>
       <c r="L538">
-        <v>0.20228807173042843</v>
+        <v>0.20228807173042845</v>
       </c>
     </row>
     <row r="539" spans="2:12" x14ac:dyDescent="0.45">
@@ -44860,13 +44860,13 @@
         <v>2022</v>
       </c>
       <c r="F539">
-        <v>0.6793056475905862</v>
+        <v>0.69928302455480262</v>
       </c>
       <c r="G539">
         <v>0.33123000000000002</v>
       </c>
       <c r="L539">
-        <v>0.20228807173042843</v>
+        <v>0.20228807173042845</v>
       </c>
     </row>
     <row r="540" spans="2:12" x14ac:dyDescent="0.45">
@@ -44877,7 +44877,7 @@
         <v>512</v>
       </c>
       <c r="D540" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="E540">
         <v>2022</v>
@@ -44889,7 +44889,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="L540">
-        <v>0.20228807173042843</v>
+        <v>0.20228807173042845</v>
       </c>
     </row>
     <row r="541" spans="2:12" x14ac:dyDescent="0.45">
@@ -44900,7 +44900,7 @@
         <v>512</v>
       </c>
       <c r="D541" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="E541">
         <v>2002</v>
@@ -44923,7 +44923,7 @@
         <v>512</v>
       </c>
       <c r="D542" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="E542">
         <v>2003</v>
@@ -44946,7 +44946,7 @@
         <v>512</v>
       </c>
       <c r="D543" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="E543">
         <v>2004</v>
@@ -44969,7 +44969,7 @@
         <v>512</v>
       </c>
       <c r="D544" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="E544">
         <v>2005</v>
@@ -44992,7 +44992,7 @@
         <v>512</v>
       </c>
       <c r="D545" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="E545">
         <v>2007</v>
@@ -45015,7 +45015,7 @@
         <v>512</v>
       </c>
       <c r="D546" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="E546">
         <v>2008</v>
@@ -45038,7 +45038,7 @@
         <v>512</v>
       </c>
       <c r="D547" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="E547">
         <v>2009</v>
@@ -45061,7 +45061,7 @@
         <v>512</v>
       </c>
       <c r="D548" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="E548">
         <v>2010</v>
@@ -45084,7 +45084,7 @@
         <v>512</v>
       </c>
       <c r="D549" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="E549">
         <v>2011</v>
@@ -45107,7 +45107,7 @@
         <v>512</v>
       </c>
       <c r="D550" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="E550">
         <v>2012</v>
@@ -45130,7 +45130,7 @@
         <v>512</v>
       </c>
       <c r="D551" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="E551">
         <v>2015</v>
@@ -45153,7 +45153,7 @@
         <v>512</v>
       </c>
       <c r="D552" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="E552">
         <v>2018</v>
@@ -45176,7 +45176,7 @@
         <v>512</v>
       </c>
       <c r="D553" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="E553">
         <v>2019</v>
@@ -45199,7 +45199,7 @@
         <v>512</v>
       </c>
       <c r="D554" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="E554">
         <v>2023</v>
@@ -45222,7 +45222,7 @@
         <v>512</v>
       </c>
       <c r="D555" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="E555">
         <v>2005</v>
@@ -45245,7 +45245,7 @@
         <v>512</v>
       </c>
       <c r="D556" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="E556">
         <v>2006</v>
@@ -45268,7 +45268,7 @@
         <v>512</v>
       </c>
       <c r="D557" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="E557">
         <v>2007</v>
@@ -45291,7 +45291,7 @@
         <v>512</v>
       </c>
       <c r="D558" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="E558">
         <v>2008</v>
@@ -45314,7 +45314,7 @@
         <v>512</v>
       </c>
       <c r="D559" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="E559">
         <v>2009</v>
@@ -45337,7 +45337,7 @@
         <v>512</v>
       </c>
       <c r="D560" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="E560">
         <v>2010</v>
@@ -45360,7 +45360,7 @@
         <v>512</v>
       </c>
       <c r="D561" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="E561">
         <v>2011</v>
@@ -45383,7 +45383,7 @@
         <v>512</v>
       </c>
       <c r="D562" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="E562">
         <v>2012</v>
@@ -45406,7 +45406,7 @@
         <v>512</v>
       </c>
       <c r="D563" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="E563">
         <v>2015</v>
@@ -45429,7 +45429,7 @@
         <v>512</v>
       </c>
       <c r="D564" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="E564">
         <v>2016</v>
@@ -45452,7 +45452,7 @@
         <v>512</v>
       </c>
       <c r="D565" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="E565">
         <v>2018</v>
@@ -45475,7 +45475,7 @@
         <v>512</v>
       </c>
       <c r="D566" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="E566">
         <v>2019</v>
@@ -45498,7 +45498,7 @@
         <v>512</v>
       </c>
       <c r="D567" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="E567">
         <v>2021</v>
@@ -45521,7 +45521,7 @@
         <v>512</v>
       </c>
       <c r="D568" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="E568">
         <v>2022</v>
@@ -45544,7 +45544,7 @@
         <v>512</v>
       </c>
       <c r="D569" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="E569">
         <v>2023</v>
@@ -45567,7 +45567,7 @@
         <v>512</v>
       </c>
       <c r="D570" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="E570">
         <v>2024</v>

--- a/VerveStacks_ITA_grids/vt_vervestacks_ITA_v1.xlsx
+++ b/VerveStacks_ITA_grids/vt_vervestacks_ITA_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B3D63866-60A5-426F-AF4A-B565F8AE6526}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{007722E8-91FA-4A2A-A7BD-161776BB6693}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{6D5BE3F6-1C53-4943-B41A-75691FFCE422}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{62776835-E1D9-48B3-BD86-C522629F2C80}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="2" r:id="rId1"/>
@@ -81,30 +81,30 @@
     <t>bioenergy</t>
   </si>
   <si>
+    <t>e_w81938081-380</t>
+  </si>
+  <si>
+    <t>e_w109756016-380</t>
+  </si>
+  <si>
     <t>e_w84696559-380</t>
   </si>
   <si>
+    <t>e_w108020416-380</t>
+  </si>
+  <si>
+    <t>e_w98902899-380</t>
+  </si>
+  <si>
+    <t>e_w144005863-380</t>
+  </si>
+  <si>
     <t>e_w34157795-380</t>
   </si>
   <si>
-    <t>e_w108020416-380</t>
-  </si>
-  <si>
-    <t>e_w98902899-380</t>
-  </si>
-  <si>
-    <t>e_w109756016-380</t>
-  </si>
-  <si>
-    <t>e_w144005863-380</t>
-  </si>
-  <si>
     <t>e_w58440884-380</t>
   </si>
   <si>
-    <t>e_w81938081-380</t>
-  </si>
-  <si>
     <t>ep_bioenergy_G100000200236</t>
   </si>
   <si>
@@ -141,6 +141,9 @@
     <t>coal</t>
   </si>
   <si>
+    <t>e_w409439916-380</t>
+  </si>
+  <si>
     <t>e_w82767145-380</t>
   </si>
   <si>
@@ -150,9 +153,6 @@
     <t>e_w303915533-380</t>
   </si>
   <si>
-    <t>e_w409439916-380</t>
-  </si>
-  <si>
     <t>ep_coal_subcritical_G100000102764</t>
   </si>
   <si>
@@ -189,120 +189,120 @@
     <t>gas</t>
   </si>
   <si>
+    <t>e_w149997403-380</t>
+  </si>
+  <si>
+    <t>e_w59462715-380</t>
+  </si>
+  <si>
+    <t>e_w1137611914-380</t>
+  </si>
+  <si>
+    <t>e_w61157826-380</t>
+  </si>
+  <si>
+    <t>e_w82078641-380</t>
+  </si>
+  <si>
+    <t>e_w162960205-380</t>
+  </si>
+  <si>
+    <t>e_w98421779-380</t>
+  </si>
+  <si>
+    <t>e_w419423704-380</t>
+  </si>
+  <si>
+    <t>e_w116797658-380</t>
+  </si>
+  <si>
+    <t>e_w199675964-380</t>
+  </si>
+  <si>
+    <t>e_w181125039-380</t>
+  </si>
+  <si>
+    <t>e_w133601335-380</t>
+  </si>
+  <si>
+    <t>e_w103381531-380</t>
+  </si>
+  <si>
+    <t>e_w414663585-380</t>
+  </si>
+  <si>
     <t>e_w338753171-380</t>
   </si>
   <si>
     <t>e_w255011550-380</t>
   </si>
   <si>
-    <t>e_w414663585-380</t>
-  </si>
-  <si>
-    <t>e_w199675964-380</t>
-  </si>
-  <si>
-    <t>e_w103381531-380</t>
-  </si>
-  <si>
-    <t>e_w133601335-380</t>
-  </si>
-  <si>
-    <t>e_w59462715-380</t>
+    <t>e_w105581403-380</t>
+  </si>
+  <si>
+    <t>e_w60725875-380</t>
+  </si>
+  <si>
+    <t>e_w145665799-380</t>
+  </si>
+  <si>
+    <t>e_w98900549-380</t>
+  </si>
+  <si>
+    <t>e_w162828577-380</t>
+  </si>
+  <si>
+    <t>e_w132450233-380</t>
+  </si>
+  <si>
+    <t>e_w110330925-380</t>
+  </si>
+  <si>
+    <t>e_w339104227-380</t>
+  </si>
+  <si>
+    <t>e_w105757794-380</t>
+  </si>
+  <si>
+    <t>e_w432729521-380</t>
+  </si>
+  <si>
+    <t>e_w172302572-380</t>
+  </si>
+  <si>
+    <t>e_w158739183-380</t>
+  </si>
+  <si>
+    <t>e_w103974940-380</t>
+  </si>
+  <si>
+    <t>e_w82084019-380</t>
+  </si>
+  <si>
+    <t>e_w103653592-380</t>
+  </si>
+  <si>
+    <t>e_w109993642-380</t>
+  </si>
+  <si>
+    <t>e_w107438024-380</t>
+  </si>
+  <si>
+    <t>e_w411026199-380</t>
+  </si>
+  <si>
+    <t>e_w416989699-380</t>
+  </si>
+  <si>
+    <t>e_w100407576-380</t>
+  </si>
+  <si>
+    <t>e_w99826025-380</t>
   </si>
   <si>
     <t>e_w421827453-380</t>
   </si>
   <si>
-    <t>e_w149997403-380</t>
-  </si>
-  <si>
-    <t>e_w100407576-380</t>
-  </si>
-  <si>
-    <t>e_w60725875-380</t>
-  </si>
-  <si>
-    <t>e_w145665799-380</t>
-  </si>
-  <si>
-    <t>e_w82078641-380</t>
-  </si>
-  <si>
-    <t>e_w61157826-380</t>
-  </si>
-  <si>
-    <t>e_w181125039-380</t>
-  </si>
-  <si>
-    <t>e_w1137611914-380</t>
-  </si>
-  <si>
-    <t>e_w82084019-380</t>
-  </si>
-  <si>
-    <t>e_w432729521-380</t>
-  </si>
-  <si>
-    <t>e_w172302572-380</t>
-  </si>
-  <si>
-    <t>e_w99826025-380</t>
-  </si>
-  <si>
-    <t>e_w416989699-380</t>
-  </si>
-  <si>
-    <t>e_w411026199-380</t>
-  </si>
-  <si>
-    <t>e_w107438024-380</t>
-  </si>
-  <si>
-    <t>e_w339104227-380</t>
-  </si>
-  <si>
-    <t>e_w116797658-380</t>
-  </si>
-  <si>
-    <t>e_w98900549-380</t>
-  </si>
-  <si>
-    <t>e_w162828577-380</t>
-  </si>
-  <si>
-    <t>e_w132450233-380</t>
-  </si>
-  <si>
-    <t>e_w110330925-380</t>
-  </si>
-  <si>
-    <t>e_w105757794-380</t>
-  </si>
-  <si>
-    <t>e_w419423704-380</t>
-  </si>
-  <si>
-    <t>e_w98421779-380</t>
-  </si>
-  <si>
-    <t>e_w103974940-380</t>
-  </si>
-  <si>
-    <t>e_w158739183-380</t>
-  </si>
-  <si>
-    <t>e_w103653592-380</t>
-  </si>
-  <si>
-    <t>e_w162960205-380</t>
-  </si>
-  <si>
-    <t>e_w109993642-380</t>
-  </si>
-  <si>
-    <t>e_w105581403-380</t>
-  </si>
-  <si>
     <t>ep_gas_combined_cycle_G100000400339</t>
   </si>
   <si>
@@ -966,69 +966,69 @@
     <t>hydro</t>
   </si>
   <si>
+    <t>e_w491424937-380</t>
+  </si>
+  <si>
+    <t>e_IT72-380</t>
+  </si>
+  <si>
+    <t>e_w61626687-380</t>
+  </si>
+  <si>
+    <t>e_IT36-380</t>
+  </si>
+  <si>
+    <t>e_w114931087-380</t>
+  </si>
+  <si>
+    <t>e_IT31-380</t>
+  </si>
+  <si>
+    <t>e_w75602396-380</t>
+  </si>
+  <si>
+    <t>e_IT53-380</t>
+  </si>
+  <si>
+    <t>e_w116517585-380</t>
+  </si>
+  <si>
     <t>e_w82083756-380</t>
   </si>
   <si>
-    <t>e_w114931087-380</t>
-  </si>
-  <si>
     <t>e_IT71-400</t>
   </si>
   <si>
-    <t>e_IT31-380</t>
+    <t>e_w1100665914-380</t>
+  </si>
+  <si>
+    <t>e_w72466334-380</t>
+  </si>
+  <si>
+    <t>e_IT10-380</t>
+  </si>
+  <si>
+    <t>e_IT21-380</t>
   </si>
   <si>
     <t>e_w64200868-380</t>
   </si>
   <si>
+    <t>e_w104359058-380</t>
+  </si>
+  <si>
+    <t>e_IT72-400</t>
+  </si>
+  <si>
+    <t>e_IT93-380</t>
+  </si>
+  <si>
+    <t>e_IT71-380</t>
+  </si>
+  <si>
     <t>e_IT7-380</t>
   </si>
   <si>
-    <t>e_IT72-400</t>
-  </si>
-  <si>
-    <t>e_w1100665914-380</t>
-  </si>
-  <si>
-    <t>e_IT21-380</t>
-  </si>
-  <si>
-    <t>e_w75602396-380</t>
-  </si>
-  <si>
-    <t>e_w104359058-380</t>
-  </si>
-  <si>
-    <t>e_IT71-380</t>
-  </si>
-  <si>
-    <t>e_w491424937-380</t>
-  </si>
-  <si>
-    <t>e_IT93-380</t>
-  </si>
-  <si>
-    <t>e_IT72-380</t>
-  </si>
-  <si>
-    <t>e_w72466334-380</t>
-  </si>
-  <si>
-    <t>e_w61626687-380</t>
-  </si>
-  <si>
-    <t>e_IT36-380</t>
-  </si>
-  <si>
-    <t>e_IT10-380</t>
-  </si>
-  <si>
-    <t>e_w116517585-380</t>
-  </si>
-  <si>
-    <t>e_IT53-380</t>
-  </si>
-  <si>
     <t>ep_hydro_dam_G100000602220</t>
   </si>
   <si>
@@ -1407,12 +1407,12 @@
     <t>solar</t>
   </si>
   <si>
+    <t>elc_spv_007</t>
+  </si>
+  <si>
     <t>elc_spv_001</t>
   </si>
   <si>
-    <t>elc_spv_007</t>
-  </si>
-  <si>
     <t>ep_solar_pv_001</t>
   </si>
   <si>
@@ -1680,42 +1680,42 @@
     <t>ele</t>
   </si>
   <si>
+    <t>Aggregated Plant - EMBER Gap - way/109756016-380_Missing Bioenergy Capacity</t>
+  </si>
+  <si>
+    <t>GW</t>
+  </si>
+  <si>
+    <t>TWh</t>
+  </si>
+  <si>
+    <t>daynite</t>
+  </si>
+  <si>
+    <t>yes</t>
+  </si>
+  <si>
     <t>Aggregated Plant - EMBER Gap - way/34157795-380_Missing Bioenergy Capacity</t>
   </si>
   <si>
-    <t>GW</t>
-  </si>
-  <si>
-    <t>TWh</t>
-  </si>
-  <si>
-    <t>daynite</t>
-  </si>
-  <si>
-    <t>yes</t>
-  </si>
-  <si>
     <t>Aggregated Plant - EMBER Gap - way/58440884-380_Missing Bioenergy Capacity</t>
   </si>
   <si>
+    <t>Aggregated Plant - EMBER Gap - way/98902899-380_Missing Bioenergy Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/144005863-380_Missing Bioenergy Capacity</t>
+  </si>
+  <si>
     <t>Aggregated Plant - EMBER Gap - way/84696559-380_Missing Bioenergy Capacity</t>
   </si>
   <si>
     <t>Aggregated Plant - EMBER Gap - way/108020416-380_Missing Bioenergy Capacity</t>
   </si>
   <si>
-    <t>Aggregated Plant - EMBER Gap - way/144005863-380_Missing Bioenergy Capacity</t>
-  </si>
-  <si>
     <t>Aggregated Plant - EMBER Gap - way/81938081-380_Missing Bioenergy Capacity</t>
   </si>
   <si>
-    <t>Aggregated Plant - EMBER Gap - way/109756016-380_Missing Bioenergy Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/98902899-380_Missing Bioenergy Capacity</t>
-  </si>
-  <si>
     <t>Acerra power station_1</t>
   </si>
   <si>
@@ -1737,18 +1737,18 @@
     <t>Aggregated Plant</t>
   </si>
   <si>
+    <t>Aggregated Plant - EMBER Gap - way/303915533-380_Missing Coal Capacity</t>
+  </si>
+  <si>
     <t>Aggregated Plant - EMBER Gap - way/409439916-380_Missing Coal Capacity</t>
   </si>
   <si>
+    <t>Aggregated Plant - EMBER Gap - way/418902800-380_Missing Coal Capacity</t>
+  </si>
+  <si>
     <t>Aggregated Plant - EMBER Gap - way/82767145-380_Missing Coal Capacity</t>
   </si>
   <si>
-    <t>Aggregated Plant - EMBER Gap - way/418902800-380_Missing Coal Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/303915533-380_Missing Coal Capacity</t>
-  </si>
-  <si>
     <t>Fiume Santo power station_Unit 3</t>
   </si>
   <si>
@@ -1779,51 +1779,96 @@
     <t>Torrevaldaliga Nord power station_Unit 3</t>
   </si>
   <si>
+    <t>Aggregated Plant - EMBER Gap - way/432729521-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/82084019-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/98421779-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/105581403-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/110330925-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/199675964-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/181125039-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/109756016-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/411026199-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/103381531-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/59462715-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/105757794-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/255011550-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/172302572-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/419423704-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/414663585-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/61157826-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/103974940-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/82078641-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/421827453-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/99826025-380_Missing Gas Capacity</t>
+  </si>
+  <si>
     <t>Aggregated Plant - EMBER Gap - way/132450233-380_Missing Gas Capacity</t>
   </si>
   <si>
-    <t>Aggregated Plant - EMBER Gap - way/199675964-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/181125039-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/432729521-380_Missing Gas Capacity</t>
+    <t>Aggregated Plant - EMBER Gap - way/1137611914-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/158739183-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/145665799-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/103653592-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/82767145-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/100407576-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/416989699-380_Missing Gas Capacity</t>
   </si>
   <si>
     <t>Aggregated Plant - EMBER Gap - way/109993642-380_Missing Gas Capacity</t>
   </si>
   <si>
-    <t>Aggregated Plant - EMBER Gap - way/82767145-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/411026199-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/100407576-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/416989699-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/103653592-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/105581403-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/98421779-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/109756016-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/110330925-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/82084019-380_Missing Gas Capacity</t>
-  </si>
-  <si>
     <t>Aggregated Plant - EMBER Gap - way/338753171-380_Missing Gas Capacity</t>
   </si>
   <si>
@@ -1833,72 +1878,27 @@
     <t>Aggregated Plant - EMBER Gap - way/98900549-380_Missing Gas Capacity</t>
   </si>
   <si>
+    <t>Aggregated Plant - EMBER Gap - way/149997403-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/162960205-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/133601335-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/60725875-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/339104227-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/107438024-380_Missing Gas Capacity</t>
+  </si>
+  <si>
     <t>Aggregated Plant - EMBER Gap - way/116797658-380_Missing Gas Capacity</t>
   </si>
   <si>
-    <t>Aggregated Plant - EMBER Gap - way/339104227-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/107438024-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/172302572-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/59462715-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/105757794-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/255011550-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/158739183-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/1137611914-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/145665799-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/414663585-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/61157826-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/149997403-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/133601335-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/162960205-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/419423704-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/103381531-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/60725875-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/421827453-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/99826025-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/82078641-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/103974940-380_Missing Gas Capacity</t>
-  </si>
-  <si>
     <t>Altomonte power station_1</t>
   </si>
   <si>
@@ -2211,102 +2211,102 @@
     <t>Valle Secolo geothermal power plant_2</t>
   </si>
   <si>
+    <t>Aggregated Plant - IRENA Gap - IT71-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/108020416-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - IT72-400_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/1137611914-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/109588422-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/144005863-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - IT21-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - IT71-400_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - IT36-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/116517585-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - IT93-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/338753171-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - IT10-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
     <t>Aggregated Plant - IRENA Gap - way/96190189-380_Missing Hydro Capacity</t>
   </si>
   <si>
-    <t>Aggregated Plant - IRENA Gap - way/116517585-380_Missing Hydro Capacity</t>
+    <t>Aggregated Plant - IRENA Gap - way/419423704-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/82083756-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/72466334-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/491424937-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/104359058-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/64200868-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - IT7-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/339703159-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/75602396-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - IT30-500_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - IT53-380_Missing Hydro Capacity</t>
   </si>
   <si>
     <t>Aggregated Plant - IRENA Gap - way/61712456-380_Missing Hydro Capacity</t>
   </si>
   <si>
-    <t>Aggregated Plant - IRENA Gap - way/108020416-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - IT71-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - IT7-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/339703159-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - IT30-500_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - IT53-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/64200868-380_Missing Hydro Capacity</t>
+    <t>Aggregated Plant - IRENA Gap - IT72-380_Missing Hydro Capacity</t>
   </si>
   <si>
     <t>Aggregated Plant - IRENA Gap - way/59462263-380_Missing Hydro Capacity</t>
   </si>
   <si>
+    <t>Aggregated Plant - IRENA Gap - way/61626687-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/114931087-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - IT31-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
     <t>Aggregated Plant - IRENA Gap - way/1100665914-380_Missing Hydro Capacity</t>
   </si>
   <si>
-    <t>Aggregated Plant - IRENA Gap - IT72-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/144005863-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - IT21-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/72466334-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/82083756-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/104359058-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/419423704-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/491424937-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - IT31-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/61626687-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/114931087-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - IT93-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/1137611914-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/109588422-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - IT72-400_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - IT10-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/338753171-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/75602396-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - IT36-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - IT71-400_Missing Hydro Capacity</t>
-  </si>
-  <si>
     <t>Baschi hydroelectric plant_</t>
   </si>
   <si>
@@ -2601,27 +2601,27 @@
     <t>San Filippo del Mela power station_1</t>
   </si>
   <si>
+    <t>Aggregated Plant - IRENA Gap - ITA_68_Missing Solar Capacity</t>
+  </si>
+  <si>
+    <t>annual</t>
+  </si>
+  <si>
     <t>Aggregated Plant - IRENA Gap - ITA_30_Missing Solar Capacity</t>
   </si>
   <si>
-    <t>annual</t>
-  </si>
-  <si>
     <t>Aggregated Plant - IRENA Gap - ITA_42_Missing Solar Capacity</t>
   </si>
   <si>
-    <t>Aggregated Plant - IRENA Gap - ITA_68_Missing Solar Capacity</t>
+    <t>Aggregated Plant - IRENA Gap - ITA_96_Missing Onshore wind energy Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - ITA_22_Missing Onshore wind energy Capacity</t>
   </si>
   <si>
     <t>Aggregated Plant - IRENA Gap - ITA_73_Missing Onshore wind energy Capacity</t>
   </si>
   <si>
-    <t>Aggregated Plant - IRENA Gap - ITA_22_Missing Onshore wind energy Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - ITA_96_Missing Onshore wind energy Capacity</t>
-  </si>
-  <si>
     <t>AF</t>
   </si>
   <si>
@@ -3213,18 +3213,18 @@
     <t>ccs retrofit of -- Sulcis power station_Unit 3</t>
   </si>
   <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/82767145-380_Missing Coal Capacity</t>
+  </si>
+  <si>
     <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/418902800-380_Missing Coal Capacity</t>
   </si>
   <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/303915533-380_Missing Coal Capacity</t>
+  </si>
+  <si>
     <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/409439916-380_Missing Coal Capacity</t>
   </si>
   <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/303915533-380_Missing Coal Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/82767145-380_Missing Coal Capacity</t>
-  </si>
-  <si>
     <t>ccs retrofit of -- Brindisi Sud power station_Unit 1</t>
   </si>
   <si>
@@ -3513,124 +3513,124 @@
     <t>ccs retrofit of -- Aggregated Plant</t>
   </si>
   <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/158739183-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/133601335-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/339104227-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/419423704-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/149997403-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/162960205-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/432729521-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/82084019-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/421827453-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/60725875-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/414663585-380_Missing Gas Capacity</t>
+  </si>
+  <si>
     <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/116797658-380_Missing Gas Capacity</t>
   </si>
   <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/414663585-380_Missing Gas Capacity</t>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/199675964-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/82767145-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/162828577-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/105581403-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/181125039-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/172302572-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/255011550-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/82078641-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/103653592-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/1137611914-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/105757794-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/110330925-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/103974940-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/132450233-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/100407576-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/145665799-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/59462715-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/109993642-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/338753171-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/98421779-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/98900549-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/107438024-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/61157826-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/109756016-380_Missing Gas Capacity</t>
   </si>
   <si>
     <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/411026199-380_Missing Gas Capacity</t>
   </si>
   <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/109756016-380_Missing Gas Capacity</t>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/99826025-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/416989699-380_Missing Gas Capacity</t>
   </si>
   <si>
     <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/103381531-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/103974940-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/199675964-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/103653592-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/1137611914-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/416989699-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/105757794-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/99826025-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/82078641-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/132450233-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/100407576-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/60725875-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/339104227-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/158739183-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/133601335-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/61157826-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/98421779-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/172302572-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/162828577-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/82767145-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/82084019-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/421827453-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/181125039-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/105581403-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/255011550-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/145665799-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/432729521-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/149997403-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/162960205-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/419423704-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/98900549-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/107438024-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/110330925-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/109993642-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/59462715-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/338753171-380_Missing Gas Capacity</t>
   </si>
   <si>
     <t>ccs retrofit of -- Tavazzano power station_CCGT8, timepoint 1</t>
@@ -4034,7 +4034,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1E9FAD3B-001F-4E84-9C9B-4DE6E6F44DB6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2B15C41F-02A3-4213-AA41-67CCBC1D998B}">
   <dimension ref="B9:T278"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -4110,7 +4110,7 @@
         <v>33</v>
       </c>
       <c r="D11" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E11">
         <v>0.12764790000000001</v>
@@ -4166,7 +4166,7 @@
         <v>33</v>
       </c>
       <c r="D12" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E12">
         <v>0.12764790000000001</v>
@@ -4222,7 +4222,7 @@
         <v>33</v>
       </c>
       <c r="D13" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E13">
         <v>0.12764790000000001</v>
@@ -4278,7 +4278,7 @@
         <v>33</v>
       </c>
       <c r="D14" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E14">
         <v>8.7830160000000032E-2</v>
@@ -4558,7 +4558,7 @@
         <v>33</v>
       </c>
       <c r="D19" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E19">
         <v>0.260522535</v>
@@ -4614,7 +4614,7 @@
         <v>33</v>
       </c>
       <c r="D20" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E20">
         <v>0.260522535</v>
@@ -4670,7 +4670,7 @@
         <v>33</v>
       </c>
       <c r="D21" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E21">
         <v>0.260522535</v>
@@ -4726,7 +4726,7 @@
         <v>33</v>
       </c>
       <c r="D22" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E22">
         <v>0.28056272999999998</v>
@@ -4782,7 +4782,7 @@
         <v>33</v>
       </c>
       <c r="D23" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E23">
         <v>0.28056272999999998</v>
@@ -4838,7 +4838,7 @@
         <v>33</v>
       </c>
       <c r="D24" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E24">
         <v>0.28056272999999998</v>
@@ -4894,7 +4894,7 @@
         <v>49</v>
       </c>
       <c r="D25" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="E25">
         <v>0.41750406250000005</v>
@@ -4950,7 +4950,7 @@
         <v>49</v>
       </c>
       <c r="D26" t="s">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="E26">
         <v>0.44431624999999997</v>
@@ -5006,7 +5006,7 @@
         <v>49</v>
       </c>
       <c r="D27" t="s">
-        <v>59</v>
+        <v>85</v>
       </c>
       <c r="E27">
         <v>0.38303124999999993</v>
@@ -5118,7 +5118,7 @@
         <v>49</v>
       </c>
       <c r="D29" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="E29">
         <v>0.41750406249999999</v>
@@ -5174,7 +5174,7 @@
         <v>49</v>
       </c>
       <c r="D30" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="E30">
         <v>0.41750406249999999</v>
@@ -5230,7 +5230,7 @@
         <v>49</v>
       </c>
       <c r="D31" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="E31">
         <v>0.41750406249999999</v>
@@ -5342,7 +5342,7 @@
         <v>49</v>
       </c>
       <c r="D33" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="E33">
         <v>0.41750406249999999</v>
@@ -5510,7 +5510,7 @@
         <v>49</v>
       </c>
       <c r="D36" t="s">
-        <v>87</v>
+        <v>66</v>
       </c>
       <c r="E36">
         <v>0.41750406249999999</v>
@@ -5566,7 +5566,7 @@
         <v>49</v>
       </c>
       <c r="D37" t="s">
-        <v>87</v>
+        <v>66</v>
       </c>
       <c r="E37">
         <v>0.41750406249999999</v>
@@ -5622,7 +5622,7 @@
         <v>49</v>
       </c>
       <c r="D38" t="s">
-        <v>74</v>
+        <v>58</v>
       </c>
       <c r="E38">
         <v>0.41750406249999999</v>
@@ -5678,7 +5678,7 @@
         <v>49</v>
       </c>
       <c r="D39" t="s">
-        <v>74</v>
+        <v>58</v>
       </c>
       <c r="E39">
         <v>0.41750406249999999</v>
@@ -5734,7 +5734,7 @@
         <v>49</v>
       </c>
       <c r="D40" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="E40">
         <v>0.3983525</v>
@@ -5790,7 +5790,7 @@
         <v>49</v>
       </c>
       <c r="D41" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="E41">
         <v>0.41750406249999999</v>
@@ -5846,7 +5846,7 @@
         <v>49</v>
       </c>
       <c r="D42" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="E42">
         <v>0.41750406249999999</v>
@@ -5902,7 +5902,7 @@
         <v>49</v>
       </c>
       <c r="D43" t="s">
-        <v>65</v>
+        <v>52</v>
       </c>
       <c r="E43">
         <v>0.41750406249999999</v>
@@ -5958,7 +5958,7 @@
         <v>49</v>
       </c>
       <c r="D44" t="s">
-        <v>65</v>
+        <v>52</v>
       </c>
       <c r="E44">
         <v>0.41750406249999999</v>
@@ -6014,7 +6014,7 @@
         <v>49</v>
       </c>
       <c r="D45" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="E45">
         <v>0.41750406249999999</v>
@@ -6070,7 +6070,7 @@
         <v>49</v>
       </c>
       <c r="D46" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="E46">
         <v>0.41750406249999999</v>
@@ -6126,7 +6126,7 @@
         <v>49</v>
       </c>
       <c r="D47" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="E47">
         <v>0.41750406249999999</v>
@@ -6182,7 +6182,7 @@
         <v>49</v>
       </c>
       <c r="D48" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="E48">
         <v>0.41750406249999999</v>
@@ -6238,7 +6238,7 @@
         <v>49</v>
       </c>
       <c r="D49" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="E49">
         <v>0.40218281250000004</v>
@@ -6294,7 +6294,7 @@
         <v>49</v>
       </c>
       <c r="D50" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="E50">
         <v>0.40218281250000004</v>
@@ -6350,7 +6350,7 @@
         <v>49</v>
       </c>
       <c r="D51" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="E51">
         <v>0.41750406249999999</v>
@@ -6406,7 +6406,7 @@
         <v>49</v>
       </c>
       <c r="D52" t="s">
-        <v>59</v>
+        <v>85</v>
       </c>
       <c r="E52">
         <v>0.45963749999999998</v>
@@ -6462,7 +6462,7 @@
         <v>49</v>
       </c>
       <c r="D53" t="s">
-        <v>59</v>
+        <v>85</v>
       </c>
       <c r="E53">
         <v>0.41750406249999999</v>
@@ -6574,7 +6574,7 @@
         <v>49</v>
       </c>
       <c r="D55" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="E55">
         <v>0.41750406249999999</v>
@@ -6630,7 +6630,7 @@
         <v>49</v>
       </c>
       <c r="D56" t="s">
-        <v>69</v>
+        <v>86</v>
       </c>
       <c r="E56">
         <v>0.41750406249999999</v>
@@ -6686,7 +6686,7 @@
         <v>49</v>
       </c>
       <c r="D57" t="s">
-        <v>69</v>
+        <v>86</v>
       </c>
       <c r="E57">
         <v>0.41750406249999999</v>
@@ -6742,7 +6742,7 @@
         <v>49</v>
       </c>
       <c r="D58" t="s">
-        <v>70</v>
+        <v>84</v>
       </c>
       <c r="E58">
         <v>0.40218281249999999</v>
@@ -6798,7 +6798,7 @@
         <v>49</v>
       </c>
       <c r="D59" t="s">
-        <v>70</v>
+        <v>84</v>
       </c>
       <c r="E59">
         <v>0.40218281249999999</v>
@@ -6854,7 +6854,7 @@
         <v>49</v>
       </c>
       <c r="D60" t="s">
-        <v>70</v>
+        <v>84</v>
       </c>
       <c r="E60">
         <v>0.38303124999999993</v>
@@ -6910,7 +6910,7 @@
         <v>49</v>
       </c>
       <c r="D61" t="s">
-        <v>70</v>
+        <v>84</v>
       </c>
       <c r="E61">
         <v>0.38303124999999993</v>
@@ -7022,7 +7022,7 @@
         <v>49</v>
       </c>
       <c r="D63" t="s">
-        <v>50</v>
+        <v>64</v>
       </c>
       <c r="E63">
         <v>0.41750406249999999</v>
@@ -7078,7 +7078,7 @@
         <v>49</v>
       </c>
       <c r="D64" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="E64">
         <v>0.41750406249999999</v>
@@ -7134,7 +7134,7 @@
         <v>49</v>
       </c>
       <c r="D65" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="E65">
         <v>0.41750406249999999</v>
@@ -7190,7 +7190,7 @@
         <v>49</v>
       </c>
       <c r="D66" t="s">
-        <v>57</v>
+        <v>87</v>
       </c>
       <c r="E66">
         <v>0.41750406249999999</v>
@@ -7358,7 +7358,7 @@
         <v>49</v>
       </c>
       <c r="D69" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="E69">
         <v>0.41750406249999999</v>
@@ -7414,7 +7414,7 @@
         <v>49</v>
       </c>
       <c r="D70" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="E70">
         <v>0.41750406249999999</v>
@@ -7470,7 +7470,7 @@
         <v>49</v>
       </c>
       <c r="D71" t="s">
-        <v>50</v>
+        <v>64</v>
       </c>
       <c r="E71">
         <v>0.41750406249999999</v>
@@ -7526,7 +7526,7 @@
         <v>49</v>
       </c>
       <c r="D72" t="s">
-        <v>50</v>
+        <v>64</v>
       </c>
       <c r="E72">
         <v>0.41750406249999999</v>
@@ -7582,7 +7582,7 @@
         <v>49</v>
       </c>
       <c r="D73" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="E73">
         <v>0.41750406249999999</v>
@@ -7638,7 +7638,7 @@
         <v>49</v>
       </c>
       <c r="D74" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="E74">
         <v>0.41750406249999999</v>
@@ -7694,7 +7694,7 @@
         <v>49</v>
       </c>
       <c r="D75" t="s">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="E75">
         <v>0.42899500000000002</v>
@@ -7750,7 +7750,7 @@
         <v>49</v>
       </c>
       <c r="D76" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="E76">
         <v>0.41750406249999999</v>
@@ -7806,7 +7806,7 @@
         <v>49</v>
       </c>
       <c r="D77" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="E77">
         <v>0.41750406249999999</v>
@@ -7974,7 +7974,7 @@
         <v>49</v>
       </c>
       <c r="D80" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E80">
         <v>0.41750406249999999</v>
@@ -8030,7 +8030,7 @@
         <v>49</v>
       </c>
       <c r="D81" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E81">
         <v>0.41750406249999999</v>
@@ -8086,7 +8086,7 @@
         <v>49</v>
       </c>
       <c r="D82" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="E82">
         <v>0.41750406249999999</v>
@@ -8142,7 +8142,7 @@
         <v>49</v>
       </c>
       <c r="D83" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="E83">
         <v>0.41750406249999999</v>
@@ -8198,7 +8198,7 @@
         <v>49</v>
       </c>
       <c r="D84" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="E84">
         <v>0.41750406249999999</v>
@@ -8254,7 +8254,7 @@
         <v>49</v>
       </c>
       <c r="D85" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="E85">
         <v>0.41750406249999999</v>
@@ -8310,7 +8310,7 @@
         <v>49</v>
       </c>
       <c r="D86" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="E86">
         <v>0.41750406249999999</v>
@@ -8366,7 +8366,7 @@
         <v>49</v>
       </c>
       <c r="D87" t="s">
-        <v>85</v>
+        <v>55</v>
       </c>
       <c r="E87">
         <v>0.41750406249999999</v>
@@ -8422,7 +8422,7 @@
         <v>49</v>
       </c>
       <c r="D88" t="s">
-        <v>85</v>
+        <v>55</v>
       </c>
       <c r="E88">
         <v>0.41750406249999999</v>
@@ -8478,7 +8478,7 @@
         <v>49</v>
       </c>
       <c r="D89" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="E89">
         <v>0.44431624999999997</v>
@@ -8534,7 +8534,7 @@
         <v>49</v>
       </c>
       <c r="D90" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="E90">
         <v>0.41750406249999999</v>
@@ -8590,7 +8590,7 @@
         <v>49</v>
       </c>
       <c r="D91" t="s">
-        <v>71</v>
+        <v>83</v>
       </c>
       <c r="E91">
         <v>0.41750406249999999</v>
@@ -8646,7 +8646,7 @@
         <v>49</v>
       </c>
       <c r="D92" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="E92">
         <v>0.44431624999999997</v>
@@ -8702,7 +8702,7 @@
         <v>49</v>
       </c>
       <c r="D93" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E93">
         <v>0.41750406249999999</v>
@@ -8758,7 +8758,7 @@
         <v>49</v>
       </c>
       <c r="D94" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E94">
         <v>0.41750406249999999</v>
@@ -8814,7 +8814,7 @@
         <v>49</v>
       </c>
       <c r="D95" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="E95">
         <v>0.41750406249999999</v>
@@ -8870,7 +8870,7 @@
         <v>49</v>
       </c>
       <c r="D96" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="E96">
         <v>0.41750406249999999</v>
@@ -8926,7 +8926,7 @@
         <v>49</v>
       </c>
       <c r="D97" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="E97">
         <v>0.41750406249999999</v>
@@ -9038,7 +9038,7 @@
         <v>49</v>
       </c>
       <c r="D99" t="s">
-        <v>80</v>
+        <v>57</v>
       </c>
       <c r="E99">
         <v>0.45963749999999998</v>
@@ -9094,7 +9094,7 @@
         <v>49</v>
       </c>
       <c r="D100" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="E100">
         <v>0.45963749999999998</v>
@@ -9150,7 +9150,7 @@
         <v>49</v>
       </c>
       <c r="D101" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="E101">
         <v>0.45963749999999998</v>
@@ -9206,7 +9206,7 @@
         <v>49</v>
       </c>
       <c r="D102" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="E102">
         <v>0.41750406249999999</v>
@@ -9262,7 +9262,7 @@
         <v>49</v>
       </c>
       <c r="D103" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="E103">
         <v>0.41750406249999999</v>
@@ -9318,7 +9318,7 @@
         <v>49</v>
       </c>
       <c r="D104" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="E104">
         <v>0.41750406249999999</v>
@@ -9374,7 +9374,7 @@
         <v>49</v>
       </c>
       <c r="D105" t="s">
-        <v>81</v>
+        <v>56</v>
       </c>
       <c r="E105">
         <v>0.41750406249999999</v>
@@ -9430,7 +9430,7 @@
         <v>49</v>
       </c>
       <c r="D106" t="s">
-        <v>50</v>
+        <v>64</v>
       </c>
       <c r="E106">
         <v>0.38303124999999993</v>
@@ -9486,7 +9486,7 @@
         <v>49</v>
       </c>
       <c r="D107" t="s">
-        <v>50</v>
+        <v>64</v>
       </c>
       <c r="E107">
         <v>0.38303124999999993</v>
@@ -9542,7 +9542,7 @@
         <v>49</v>
       </c>
       <c r="D108" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="E108">
         <v>0.4021828125000001</v>
@@ -9654,7 +9654,7 @@
         <v>49</v>
       </c>
       <c r="D110" t="s">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="E110">
         <v>0.41750406249999999</v>
@@ -9710,7 +9710,7 @@
         <v>49</v>
       </c>
       <c r="D111" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="E111">
         <v>0.3983525</v>
@@ -9822,7 +9822,7 @@
         <v>49</v>
       </c>
       <c r="D113" t="s">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="E113">
         <v>0.41750406249999999</v>
@@ -10494,7 +10494,7 @@
         <v>49</v>
       </c>
       <c r="D125" t="s">
-        <v>34</v>
+        <v>75</v>
       </c>
       <c r="E125">
         <v>0.45963749999999998</v>
@@ -10718,7 +10718,7 @@
         <v>49</v>
       </c>
       <c r="D129" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E129">
         <v>0.45963749999999998</v>
@@ -11446,7 +11446,7 @@
         <v>49</v>
       </c>
       <c r="D142" t="s">
-        <v>70</v>
+        <v>35</v>
       </c>
       <c r="E142">
         <v>0.45963749999999998</v>
@@ -11502,7 +11502,7 @@
         <v>49</v>
       </c>
       <c r="D143" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E143">
         <v>0.45963749999999998</v>
@@ -11558,7 +11558,7 @@
         <v>49</v>
       </c>
       <c r="D144" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E144">
         <v>0.45963749999999998</v>
@@ -12006,7 +12006,7 @@
         <v>49</v>
       </c>
       <c r="D152" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E152">
         <v>0.45963749999999998</v>
@@ -12062,7 +12062,7 @@
         <v>49</v>
       </c>
       <c r="D153" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E153">
         <v>0.45963749999999998</v>
@@ -12174,7 +12174,7 @@
         <v>49</v>
       </c>
       <c r="D155" t="s">
-        <v>82</v>
+        <v>15</v>
       </c>
       <c r="E155">
         <v>0.45963749999999998</v>
@@ -12286,7 +12286,7 @@
         <v>49</v>
       </c>
       <c r="D157" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E157">
         <v>0.45963749999999998</v>
@@ -12342,7 +12342,7 @@
         <v>49</v>
       </c>
       <c r="D158" t="s">
-        <v>18</v>
+        <v>83</v>
       </c>
       <c r="E158">
         <v>0.45963749999999998</v>
@@ -12678,7 +12678,7 @@
         <v>49</v>
       </c>
       <c r="D164" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="E164">
         <v>0.41367375000000001</v>
@@ -13518,7 +13518,7 @@
         <v>49</v>
       </c>
       <c r="D179" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="E179">
         <v>0.39835250000000011</v>
@@ -13574,7 +13574,7 @@
         <v>49</v>
       </c>
       <c r="D180" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="E180">
         <v>0.39835250000000011</v>
@@ -13798,7 +13798,7 @@
         <v>49</v>
       </c>
       <c r="D184" t="s">
-        <v>50</v>
+        <v>64</v>
       </c>
       <c r="E184">
         <v>0.41367375000000001</v>
@@ -13854,7 +13854,7 @@
         <v>49</v>
       </c>
       <c r="D185" t="s">
-        <v>50</v>
+        <v>64</v>
       </c>
       <c r="E185">
         <v>0.41367375000000001</v>
@@ -14582,7 +14582,7 @@
         <v>49</v>
       </c>
       <c r="D198" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E198">
         <v>0.42899500000000002</v>
@@ -14806,7 +14806,7 @@
         <v>49</v>
       </c>
       <c r="D202" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="E202">
         <v>0.3983525</v>
@@ -15534,7 +15534,7 @@
         <v>49</v>
       </c>
       <c r="D215" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="E215">
         <v>0.38303124999999993</v>
@@ -15702,7 +15702,7 @@
         <v>49</v>
       </c>
       <c r="D218" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E218">
         <v>0.42899499999999996</v>
@@ -15758,7 +15758,7 @@
         <v>49</v>
       </c>
       <c r="D219" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E219">
         <v>0.42899499999999996</v>
@@ -15926,7 +15926,7 @@
         <v>49</v>
       </c>
       <c r="D222" t="s">
-        <v>69</v>
+        <v>86</v>
       </c>
       <c r="E222">
         <v>0.38303124999999993</v>
@@ -15982,7 +15982,7 @@
         <v>49</v>
       </c>
       <c r="D223" t="s">
-        <v>85</v>
+        <v>55</v>
       </c>
       <c r="E223">
         <v>0.25280062500000006</v>
@@ -16038,7 +16038,7 @@
         <v>49</v>
       </c>
       <c r="D224" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="E224">
         <v>0.24514000000000002</v>
@@ -16094,7 +16094,7 @@
         <v>49</v>
       </c>
       <c r="D225" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="E225">
         <v>0.24514000000000002</v>
@@ -16150,7 +16150,7 @@
         <v>49</v>
       </c>
       <c r="D226" t="s">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="E226">
         <v>0.21066718750000002</v>
@@ -16654,7 +16654,7 @@
         <v>49</v>
       </c>
       <c r="D235" t="s">
-        <v>65</v>
+        <v>52</v>
       </c>
       <c r="E235">
         <v>0.21449750000000001</v>
@@ -16934,7 +16934,7 @@
         <v>49</v>
       </c>
       <c r="D240" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="E240">
         <v>0.23747937499999999</v>
@@ -17046,7 +17046,7 @@
         <v>49</v>
       </c>
       <c r="D242" t="s">
-        <v>81</v>
+        <v>56</v>
       </c>
       <c r="E242">
         <v>0.21449750000000001</v>
@@ -17242,7 +17242,7 @@
         <v>49</v>
       </c>
       <c r="D247" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="E247">
         <v>0.27578249999999999</v>
@@ -17312,7 +17312,7 @@
         <v>49</v>
       </c>
       <c r="D249" t="s">
-        <v>71</v>
+        <v>83</v>
       </c>
       <c r="E249">
         <v>0.27578249999999999</v>
@@ -17452,7 +17452,7 @@
         <v>49</v>
       </c>
       <c r="D253" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="E253">
         <v>0.23747937499999999</v>
@@ -17487,7 +17487,7 @@
         <v>49</v>
       </c>
       <c r="D254" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="E254">
         <v>0.23747937499999999</v>
@@ -17522,7 +17522,7 @@
         <v>49</v>
       </c>
       <c r="D255" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="E255">
         <v>0.23747937499999999</v>
@@ -17557,7 +17557,7 @@
         <v>49</v>
       </c>
       <c r="D256" t="s">
-        <v>74</v>
+        <v>58</v>
       </c>
       <c r="E256">
         <v>0.26429156249999997</v>
@@ -17592,7 +17592,7 @@
         <v>49</v>
       </c>
       <c r="D257" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="E257">
         <v>0.23747937499999999</v>
@@ -17627,7 +17627,7 @@
         <v>49</v>
       </c>
       <c r="D258" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="E258">
         <v>0.23747937499999999</v>
@@ -17662,7 +17662,7 @@
         <v>49</v>
       </c>
       <c r="D259" t="s">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="E259">
         <v>0.22215812499999998</v>
@@ -17697,7 +17697,7 @@
         <v>49</v>
       </c>
       <c r="D260" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E260">
         <v>0.24514000000000002</v>
@@ -17732,7 +17732,7 @@
         <v>49</v>
       </c>
       <c r="D261" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E261">
         <v>0.24514000000000002</v>
@@ -17767,7 +17767,7 @@
         <v>49</v>
       </c>
       <c r="D262" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E262">
         <v>0.24514000000000002</v>
@@ -17837,7 +17837,7 @@
         <v>439</v>
       </c>
       <c r="D264" t="s">
-        <v>59</v>
+        <v>85</v>
       </c>
       <c r="E264">
         <v>0.35238875000000003</v>
@@ -17942,7 +17942,7 @@
         <v>439</v>
       </c>
       <c r="D267" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E267">
         <v>0.19534593749999996</v>
@@ -17977,7 +17977,7 @@
         <v>439</v>
       </c>
       <c r="D268" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E268">
         <v>0.206836875</v>
@@ -18152,7 +18152,7 @@
         <v>439</v>
       </c>
       <c r="D273" t="s">
-        <v>59</v>
+        <v>85</v>
       </c>
       <c r="E273">
         <v>0.23747937499999999</v>
@@ -18360,7 +18360,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{20BDA0FA-69BB-4662-9915-EF4201268817}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{74DE5F44-6A85-477C-82A8-5BB69CFD26D0}">
   <dimension ref="B9:T641"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -18442,7 +18442,7 @@
         <v>2022</v>
       </c>
       <c r="F11">
-        <v>1.0679322033898306</v>
+        <v>0.49149152542372881</v>
       </c>
       <c r="G11">
         <v>0.306425</v>
@@ -18495,19 +18495,19 @@
         <v>2022</v>
       </c>
       <c r="F12">
-        <v>0.35800000000000004</v>
+        <v>0.27911864406779663</v>
       </c>
       <c r="G12">
-        <v>0.306425</v>
+        <v>0.28891500000000003</v>
       </c>
       <c r="H12">
-        <v>3850.0000000000009</v>
+        <v>4427.5</v>
       </c>
       <c r="I12">
-        <v>143</v>
+        <v>157.30000000000001</v>
       </c>
       <c r="J12">
-        <v>8.4</v>
+        <v>9.240000000000002</v>
       </c>
       <c r="K12">
         <v>50</v>
@@ -18548,19 +18548,19 @@
         <v>2022</v>
       </c>
       <c r="F13">
-        <v>0.24877966101694915</v>
+        <v>1.0679322033898306</v>
       </c>
       <c r="G13">
-        <v>0.28891500000000003</v>
+        <v>0.306425</v>
       </c>
       <c r="H13">
-        <v>4427.5</v>
+        <v>3850.0000000000005</v>
       </c>
       <c r="I13">
-        <v>157.30000000000001</v>
+        <v>143</v>
       </c>
       <c r="J13">
-        <v>9.240000000000002</v>
+        <v>8.4</v>
       </c>
       <c r="K13">
         <v>50</v>
@@ -18601,19 +18601,19 @@
         <v>2022</v>
       </c>
       <c r="F14">
-        <v>0.39440677966101695</v>
+        <v>0.24877966101694915</v>
       </c>
       <c r="G14">
-        <v>0.306425</v>
+        <v>0.28891500000000003</v>
       </c>
       <c r="H14">
-        <v>3850.0000000000005</v>
+        <v>4427.5</v>
       </c>
       <c r="I14">
-        <v>143</v>
+        <v>157.30000000000001</v>
       </c>
       <c r="J14">
-        <v>8.4</v>
+        <v>9.240000000000002</v>
       </c>
       <c r="K14">
         <v>50</v>
@@ -18654,19 +18654,19 @@
         <v>2022</v>
       </c>
       <c r="F15">
-        <v>0.27911864406779663</v>
+        <v>0.39440677966101695</v>
       </c>
       <c r="G15">
-        <v>0.28891500000000003</v>
+        <v>0.306425</v>
       </c>
       <c r="H15">
-        <v>4427.5</v>
+        <v>3850.0000000000005</v>
       </c>
       <c r="I15">
-        <v>157.30000000000001</v>
+        <v>143</v>
       </c>
       <c r="J15">
-        <v>9.240000000000002</v>
+        <v>8.4</v>
       </c>
       <c r="K15">
         <v>50</v>
@@ -18760,13 +18760,13 @@
         <v>2022</v>
       </c>
       <c r="F17">
-        <v>0.51576271186440681</v>
+        <v>0.35800000000000004</v>
       </c>
       <c r="G17">
         <v>0.306425</v>
       </c>
       <c r="H17">
-        <v>3850.0000000000005</v>
+        <v>3850.0000000000009</v>
       </c>
       <c r="I17">
         <v>143</v>
@@ -18813,7 +18813,7 @@
         <v>2022</v>
       </c>
       <c r="F18">
-        <v>0.49149152542372881</v>
+        <v>0.51576271186440681</v>
       </c>
       <c r="G18">
         <v>0.306425</v>
@@ -18860,7 +18860,7 @@
         <v>13</v>
       </c>
       <c r="D19" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E19">
         <v>2008</v>
@@ -18913,7 +18913,7 @@
         <v>13</v>
       </c>
       <c r="D20" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E20">
         <v>1998</v>
@@ -18966,7 +18966,7 @@
         <v>13</v>
       </c>
       <c r="D21" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="E21">
         <v>2008</v>
@@ -19019,7 +19019,7 @@
         <v>13</v>
       </c>
       <c r="D22" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E22">
         <v>2001</v>
@@ -19072,7 +19072,7 @@
         <v>13</v>
       </c>
       <c r="D23" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E23">
         <v>2013</v>
@@ -19125,7 +19125,7 @@
         <v>13</v>
       </c>
       <c r="D24" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E24">
         <v>1965</v>
@@ -19178,7 +19178,7 @@
         <v>13</v>
       </c>
       <c r="D25" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E25">
         <v>2003</v>
@@ -19284,7 +19284,7 @@
         <v>13</v>
       </c>
       <c r="D27" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="E27">
         <v>2018</v>
@@ -19337,7 +19337,7 @@
         <v>13</v>
       </c>
       <c r="D28" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E28">
         <v>2009</v>
@@ -19396,19 +19396,19 @@
         <v>2022</v>
       </c>
       <c r="F29">
-        <v>0.61803468208092449</v>
+        <v>0.1997687861271675</v>
       </c>
       <c r="G29">
-        <v>0.31518000000000002</v>
+        <v>0.29766999999999999</v>
       </c>
       <c r="H29">
-        <v>2200</v>
+        <v>2530</v>
       </c>
       <c r="I29">
-        <v>66</v>
+        <v>72.600000000000009</v>
       </c>
       <c r="J29">
-        <v>5.25</v>
+        <v>5.7750000000000004</v>
       </c>
       <c r="K29">
         <v>50</v>
@@ -19502,19 +19502,19 @@
         <v>2022</v>
       </c>
       <c r="F31">
-        <v>0.18416184971098257</v>
+        <v>0.61803468208092449</v>
       </c>
       <c r="G31">
-        <v>0.29766999999999999</v>
+        <v>0.31518000000000002</v>
       </c>
       <c r="H31">
-        <v>2530</v>
+        <v>2200</v>
       </c>
       <c r="I31">
-        <v>72.600000000000009</v>
+        <v>66</v>
       </c>
       <c r="J31">
-        <v>5.7750000000000004</v>
+        <v>5.25</v>
       </c>
       <c r="K31">
         <v>50</v>
@@ -19555,7 +19555,7 @@
         <v>2022</v>
       </c>
       <c r="F32">
-        <v>0.1997687861271675</v>
+        <v>0.18416184971098257</v>
       </c>
       <c r="G32">
         <v>0.29766999999999999</v>
@@ -19602,7 +19602,7 @@
         <v>33</v>
       </c>
       <c r="D33" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E33">
         <v>1992</v>
@@ -19655,7 +19655,7 @@
         <v>33</v>
       </c>
       <c r="D34" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E34">
         <v>1993</v>
@@ -19708,7 +19708,7 @@
         <v>33</v>
       </c>
       <c r="D35" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E35">
         <v>2005</v>
@@ -19761,7 +19761,7 @@
         <v>33</v>
       </c>
       <c r="D36" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E36">
         <v>1986</v>
@@ -19814,7 +19814,7 @@
         <v>33</v>
       </c>
       <c r="D37" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E37">
         <v>1991</v>
@@ -19867,7 +19867,7 @@
         <v>33</v>
       </c>
       <c r="D38" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E38">
         <v>1992</v>
@@ -19920,7 +19920,7 @@
         <v>33</v>
       </c>
       <c r="D39" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E39">
         <v>1993</v>
@@ -19973,7 +19973,7 @@
         <v>33</v>
       </c>
       <c r="D40" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E40">
         <v>2009</v>
@@ -20026,7 +20026,7 @@
         <v>33</v>
       </c>
       <c r="D41" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E41">
         <v>2010</v>
@@ -20079,7 +20079,7 @@
         <v>33</v>
       </c>
       <c r="D42" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E42">
         <v>2010</v>
@@ -20138,19 +20138,19 @@
         <v>2022</v>
       </c>
       <c r="F43">
-        <v>0.45732943023592104</v>
+        <v>0.18824049497996109</v>
       </c>
       <c r="G43">
-        <v>0.52529999999999999</v>
+        <v>0.50778999999999996</v>
       </c>
       <c r="H43">
-        <v>1100</v>
+        <v>1265</v>
       </c>
       <c r="I43">
-        <v>33</v>
+        <v>36.300000000000004</v>
       </c>
       <c r="J43">
-        <v>3.1500000000000004</v>
+        <v>3.4650000000000003</v>
       </c>
       <c r="K43">
         <v>50</v>
@@ -20191,7 +20191,7 @@
         <v>2022</v>
       </c>
       <c r="F44">
-        <v>0.1548783373961905</v>
+        <v>0.21113131843159935</v>
       </c>
       <c r="G44">
         <v>0.50778999999999996</v>
@@ -20203,7 +20203,7 @@
         <v>36.300000000000004</v>
       </c>
       <c r="J44">
-        <v>3.4649999999999999</v>
+        <v>3.4650000000000003</v>
       </c>
       <c r="K44">
         <v>50</v>
@@ -20244,7 +20244,7 @@
         <v>2022</v>
       </c>
       <c r="F45">
-        <v>0.22793415692269547</v>
+        <v>0.21283595422055113</v>
       </c>
       <c r="G45">
         <v>0.50778999999999996</v>
@@ -20297,19 +20297,19 @@
         <v>2022</v>
       </c>
       <c r="F46">
-        <v>0.21551466760318963</v>
+        <v>0.39839773581787374</v>
       </c>
       <c r="G46">
-        <v>0.50778999999999996</v>
+        <v>0.52529999999999999</v>
       </c>
       <c r="H46">
-        <v>1265</v>
+        <v>1100</v>
       </c>
       <c r="I46">
-        <v>36.300000000000004</v>
+        <v>33</v>
       </c>
       <c r="J46">
-        <v>3.4650000000000003</v>
+        <v>3.1500000000000004</v>
       </c>
       <c r="K46">
         <v>50</v>
@@ -20350,7 +20350,7 @@
         <v>2022</v>
       </c>
       <c r="F47">
-        <v>0.26604494277568891</v>
+        <v>0.28443065735652601</v>
       </c>
       <c r="G47">
         <v>0.50778999999999996</v>
@@ -20403,19 +20403,19 @@
         <v>2022</v>
       </c>
       <c r="F48">
-        <v>0.23280454489112914</v>
+        <v>0.49339465314217229</v>
       </c>
       <c r="G48">
-        <v>0.50778999999999996</v>
+        <v>0.52529999999999999</v>
       </c>
       <c r="H48">
-        <v>1265</v>
+        <v>1100</v>
       </c>
       <c r="I48">
-        <v>36.300000000000004</v>
+        <v>33</v>
       </c>
       <c r="J48">
-        <v>3.4650000000000007</v>
+        <v>3.1500000000000004</v>
       </c>
       <c r="K48">
         <v>50</v>
@@ -20456,7 +20456,7 @@
         <v>2022</v>
       </c>
       <c r="F49">
-        <v>0.21113131843159935</v>
+        <v>0.20820908565053911</v>
       </c>
       <c r="G49">
         <v>0.50778999999999996</v>
@@ -20468,7 +20468,7 @@
         <v>36.300000000000004</v>
       </c>
       <c r="J49">
-        <v>3.4650000000000003</v>
+        <v>3.4650000000000007</v>
       </c>
       <c r="K49">
         <v>50</v>
@@ -20509,7 +20509,7 @@
         <v>2022</v>
       </c>
       <c r="F50">
-        <v>0.19627663512787666</v>
+        <v>0.18629233979258764</v>
       </c>
       <c r="G50">
         <v>0.50778999999999996</v>
@@ -20521,7 +20521,7 @@
         <v>36.300000000000004</v>
       </c>
       <c r="J50">
-        <v>3.4649999999999999</v>
+        <v>3.4650000000000003</v>
       </c>
       <c r="K50">
         <v>50</v>
@@ -20562,7 +20562,7 @@
         <v>2022</v>
       </c>
       <c r="F51">
-        <v>0.18824049497996109</v>
+        <v>0.20236462008841874</v>
       </c>
       <c r="G51">
         <v>0.50778999999999996</v>
@@ -20615,19 +20615,19 @@
         <v>2022</v>
       </c>
       <c r="F52">
-        <v>0.43468212618270452</v>
+        <v>0.21551466760318963</v>
       </c>
       <c r="G52">
-        <v>0.52529999999999999</v>
+        <v>0.50778999999999996</v>
       </c>
       <c r="H52">
-        <v>1100</v>
+        <v>1265</v>
       </c>
       <c r="I52">
-        <v>33</v>
+        <v>36.300000000000004</v>
       </c>
       <c r="J52">
-        <v>3.1500000000000004</v>
+        <v>3.4650000000000003</v>
       </c>
       <c r="K52">
         <v>50</v>
@@ -20668,7 +20668,7 @@
         <v>2022</v>
       </c>
       <c r="F53">
-        <v>0.23864901045324952</v>
+        <v>0.18556178159732259</v>
       </c>
       <c r="G53">
         <v>0.50778999999999996</v>
@@ -20721,19 +20721,19 @@
         <v>2022</v>
       </c>
       <c r="F54">
-        <v>0.31243538817501959</v>
+        <v>0.23280454489112914</v>
       </c>
       <c r="G54">
-        <v>0.52529999999999999</v>
+        <v>0.50778999999999996</v>
       </c>
       <c r="H54">
-        <v>1100</v>
+        <v>1265</v>
       </c>
       <c r="I54">
-        <v>33</v>
+        <v>36.300000000000004</v>
       </c>
       <c r="J54">
-        <v>3.1500000000000004</v>
+        <v>3.4650000000000007</v>
       </c>
       <c r="K54">
         <v>50</v>
@@ -20774,7 +20774,7 @@
         <v>2022</v>
       </c>
       <c r="F55">
-        <v>0.28443065735652601</v>
+        <v>0.26604494277568891</v>
       </c>
       <c r="G55">
         <v>0.50778999999999996</v>
@@ -20827,19 +20827,19 @@
         <v>2022</v>
       </c>
       <c r="F56">
-        <v>0.39839773581787374</v>
+        <v>0.22793415692269547</v>
       </c>
       <c r="G56">
-        <v>0.52529999999999999</v>
+        <v>0.50778999999999996</v>
       </c>
       <c r="H56">
-        <v>1100</v>
+        <v>1265</v>
       </c>
       <c r="I56">
-        <v>33</v>
+        <v>36.300000000000004</v>
       </c>
       <c r="J56">
-        <v>3.1500000000000004</v>
+        <v>3.4650000000000003</v>
       </c>
       <c r="K56">
         <v>50</v>
@@ -20880,19 +20880,19 @@
         <v>2022</v>
       </c>
       <c r="F57">
-        <v>0.18556178159732259</v>
+        <v>0.45732943023592104</v>
       </c>
       <c r="G57">
-        <v>0.50778999999999996</v>
+        <v>0.52529999999999999</v>
       </c>
       <c r="H57">
-        <v>1265</v>
+        <v>1100</v>
       </c>
       <c r="I57">
-        <v>36.300000000000004</v>
+        <v>33</v>
       </c>
       <c r="J57">
-        <v>3.4650000000000003</v>
+        <v>3.1500000000000004</v>
       </c>
       <c r="K57">
         <v>50</v>
@@ -20933,7 +20933,7 @@
         <v>2022</v>
       </c>
       <c r="F58">
-        <v>0.21283595422055113</v>
+        <v>0.1548783373961905</v>
       </c>
       <c r="G58">
         <v>0.50778999999999996</v>
@@ -20945,7 +20945,7 @@
         <v>36.300000000000004</v>
       </c>
       <c r="J58">
-        <v>3.4650000000000003</v>
+        <v>3.4649999999999999</v>
       </c>
       <c r="K58">
         <v>50</v>
@@ -20986,7 +20986,7 @@
         <v>2022</v>
       </c>
       <c r="F59">
-        <v>0.29344087509812827</v>
+        <v>0.27347228442755023</v>
       </c>
       <c r="G59">
         <v>0.50778999999999996</v>
@@ -21039,7 +21039,7 @@
         <v>2022</v>
       </c>
       <c r="F60">
-        <v>0.19481551873734657</v>
+        <v>0.23864901045324952</v>
       </c>
       <c r="G60">
         <v>0.50778999999999996</v>
@@ -21092,19 +21092,19 @@
         <v>2022</v>
       </c>
       <c r="F61">
-        <v>0.19481551873734657</v>
+        <v>0.31243538817501959</v>
       </c>
       <c r="G61">
-        <v>0.50778999999999996</v>
+        <v>0.52529999999999999</v>
       </c>
       <c r="H61">
-        <v>1265</v>
+        <v>1100</v>
       </c>
       <c r="I61">
-        <v>36.300000000000004</v>
+        <v>33</v>
       </c>
       <c r="J61">
-        <v>3.4650000000000003</v>
+        <v>3.1500000000000004</v>
       </c>
       <c r="K61">
         <v>50</v>
@@ -21145,19 +21145,19 @@
         <v>2022</v>
       </c>
       <c r="F62">
-        <v>0.20212110068999706</v>
+        <v>0.30829555840185086</v>
       </c>
       <c r="G62">
-        <v>0.50778999999999996</v>
+        <v>0.52529999999999999</v>
       </c>
       <c r="H62">
-        <v>1265</v>
+        <v>1100</v>
       </c>
       <c r="I62">
-        <v>36.300000000000004</v>
+        <v>33</v>
       </c>
       <c r="J62">
-        <v>3.4650000000000003</v>
+        <v>3.1500000000000004</v>
       </c>
       <c r="K62">
         <v>50</v>
@@ -21192,13 +21192,13 @@
         <v>49</v>
       </c>
       <c r="D63" t="s">
-        <v>70</v>
+        <v>35</v>
       </c>
       <c r="E63">
         <v>2022</v>
       </c>
       <c r="F63">
-        <v>0.26543614427963469</v>
+        <v>0.27761211420071885</v>
       </c>
       <c r="G63">
         <v>0.50778999999999996</v>
@@ -21245,25 +21245,25 @@
         <v>49</v>
       </c>
       <c r="D64" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E64">
         <v>2022</v>
       </c>
       <c r="F64">
-        <v>0.20557907614758497</v>
+        <v>0.3567559186877659</v>
       </c>
       <c r="G64">
-        <v>0.50778999999999996</v>
+        <v>0.52529999999999999</v>
       </c>
       <c r="H64">
-        <v>1265</v>
+        <v>1100</v>
       </c>
       <c r="I64">
-        <v>36.300000000000004</v>
+        <v>33</v>
       </c>
       <c r="J64">
-        <v>3.4650000000000003</v>
+        <v>3.1500000000000004</v>
       </c>
       <c r="K64">
         <v>50</v>
@@ -21298,25 +21298,25 @@
         <v>49</v>
       </c>
       <c r="D65" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E65">
         <v>2022</v>
       </c>
       <c r="F65">
-        <v>0.37112356319464518</v>
+        <v>0.18507474280047922</v>
       </c>
       <c r="G65">
-        <v>0.52529999999999999</v>
+        <v>0.50778999999999996</v>
       </c>
       <c r="H65">
-        <v>1100</v>
+        <v>1265</v>
       </c>
       <c r="I65">
-        <v>33</v>
+        <v>36.300000000000004</v>
       </c>
       <c r="J65">
-        <v>3.1500000000000004</v>
+        <v>3.4649999999999999</v>
       </c>
       <c r="K65">
         <v>50</v>
@@ -21351,13 +21351,13 @@
         <v>49</v>
       </c>
       <c r="D66" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E66">
         <v>2022</v>
       </c>
       <c r="F66">
-        <v>0.19481551873734657</v>
+        <v>0.19676367392472002</v>
       </c>
       <c r="G66">
         <v>0.50778999999999996</v>
@@ -21404,13 +21404,13 @@
         <v>49</v>
       </c>
       <c r="D67" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E67">
         <v>2022</v>
       </c>
       <c r="F67">
-        <v>0.20236462008841874</v>
+        <v>0.19481551873734657</v>
       </c>
       <c r="G67">
         <v>0.50778999999999996</v>
@@ -21457,25 +21457,25 @@
         <v>49</v>
       </c>
       <c r="D68" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E68">
         <v>2022</v>
       </c>
       <c r="F68">
-        <v>0.30829555840185086</v>
+        <v>0.16608022972358796</v>
       </c>
       <c r="G68">
-        <v>0.52529999999999999</v>
+        <v>0.50778999999999996</v>
       </c>
       <c r="H68">
-        <v>1100</v>
+        <v>1265</v>
       </c>
       <c r="I68">
-        <v>33</v>
+        <v>36.300000000000004</v>
       </c>
       <c r="J68">
-        <v>3.1500000000000004</v>
+        <v>3.4650000000000003</v>
       </c>
       <c r="K68">
         <v>50</v>
@@ -21510,13 +21510,13 @@
         <v>49</v>
       </c>
       <c r="D69" t="s">
-        <v>34</v>
+        <v>75</v>
       </c>
       <c r="E69">
         <v>2022</v>
       </c>
       <c r="F69">
-        <v>0.27761211420071885</v>
+        <v>0.19481551873734657</v>
       </c>
       <c r="G69">
         <v>0.50778999999999996</v>
@@ -21569,19 +21569,19 @@
         <v>2022</v>
       </c>
       <c r="F70">
-        <v>0.3567559186877659</v>
+        <v>0.19481551873734657</v>
       </c>
       <c r="G70">
-        <v>0.52529999999999999</v>
+        <v>0.50778999999999996</v>
       </c>
       <c r="H70">
-        <v>1100</v>
+        <v>1265</v>
       </c>
       <c r="I70">
-        <v>33</v>
+        <v>36.300000000000004</v>
       </c>
       <c r="J70">
-        <v>3.1500000000000004</v>
+        <v>3.4650000000000003</v>
       </c>
       <c r="K70">
         <v>50</v>
@@ -21622,7 +21622,7 @@
         <v>2022</v>
       </c>
       <c r="F71">
-        <v>0.18507474280047922</v>
+        <v>0.17484692806676855</v>
       </c>
       <c r="G71">
         <v>0.50778999999999996</v>
@@ -21634,7 +21634,7 @@
         <v>36.300000000000004</v>
       </c>
       <c r="J71">
-        <v>3.4649999999999999</v>
+        <v>3.4650000000000003</v>
       </c>
       <c r="K71">
         <v>50</v>
@@ -21675,7 +21675,7 @@
         <v>2022</v>
       </c>
       <c r="F72">
-        <v>0.19676367392472002</v>
+        <v>0.18872753377680451</v>
       </c>
       <c r="G72">
         <v>0.50778999999999996</v>
@@ -21687,7 +21687,7 @@
         <v>36.300000000000004</v>
       </c>
       <c r="J72">
-        <v>3.4650000000000003</v>
+        <v>3.4650000000000007</v>
       </c>
       <c r="K72">
         <v>50</v>
@@ -21728,7 +21728,7 @@
         <v>2022</v>
       </c>
       <c r="F73">
-        <v>0.16608022972358796</v>
+        <v>0.29344087509812827</v>
       </c>
       <c r="G73">
         <v>0.50778999999999996</v>
@@ -21781,7 +21781,7 @@
         <v>2022</v>
       </c>
       <c r="F74">
-        <v>0.18629233979258764</v>
+        <v>0.19481551873734657</v>
       </c>
       <c r="G74">
         <v>0.50778999999999996</v>
@@ -21834,7 +21834,7 @@
         <v>2022</v>
       </c>
       <c r="F75">
-        <v>0.20820908565053911</v>
+        <v>0.18702289798785268</v>
       </c>
       <c r="G75">
         <v>0.50778999999999996</v>
@@ -21846,7 +21846,7 @@
         <v>36.300000000000004</v>
       </c>
       <c r="J75">
-        <v>3.4650000000000007</v>
+        <v>3.4650000000000003</v>
       </c>
       <c r="K75">
         <v>50</v>
@@ -21881,13 +21881,13 @@
         <v>49</v>
       </c>
       <c r="D76" t="s">
-        <v>82</v>
+        <v>15</v>
       </c>
       <c r="E76">
         <v>2022</v>
       </c>
       <c r="F76">
-        <v>0.18872753377680451</v>
+        <v>0.19822479031525012</v>
       </c>
       <c r="G76">
         <v>0.50778999999999996</v>
@@ -21899,7 +21899,7 @@
         <v>36.300000000000004</v>
       </c>
       <c r="J76">
-        <v>3.4650000000000007</v>
+        <v>3.4650000000000003</v>
       </c>
       <c r="K76">
         <v>50</v>
@@ -21934,25 +21934,25 @@
         <v>49</v>
       </c>
       <c r="D77" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E77">
         <v>2022</v>
       </c>
       <c r="F77">
-        <v>0.17484692806676855</v>
+        <v>0.37112356319464518</v>
       </c>
       <c r="G77">
-        <v>0.50778999999999996</v>
+        <v>0.52529999999999999</v>
       </c>
       <c r="H77">
-        <v>1265</v>
+        <v>1100</v>
       </c>
       <c r="I77">
-        <v>36.300000000000004</v>
+        <v>33</v>
       </c>
       <c r="J77">
-        <v>3.4650000000000003</v>
+        <v>3.1500000000000004</v>
       </c>
       <c r="K77">
         <v>50</v>
@@ -21987,13 +21987,13 @@
         <v>49</v>
       </c>
       <c r="D78" t="s">
-        <v>18</v>
+        <v>83</v>
       </c>
       <c r="E78">
         <v>2022</v>
       </c>
       <c r="F78">
-        <v>0.19822479031525012</v>
+        <v>0.20557907614758497</v>
       </c>
       <c r="G78">
         <v>0.50778999999999996</v>
@@ -22046,7 +22046,7 @@
         <v>2022</v>
       </c>
       <c r="F79">
-        <v>0.19481551873734657</v>
+        <v>0.26543614427963469</v>
       </c>
       <c r="G79">
         <v>0.50778999999999996</v>
@@ -22099,7 +22099,7 @@
         <v>2022</v>
       </c>
       <c r="F80">
-        <v>0.49339465314217229</v>
+        <v>0.43468212618270452</v>
       </c>
       <c r="G80">
         <v>0.52529999999999999</v>
@@ -22152,7 +22152,7 @@
         <v>2022</v>
       </c>
       <c r="F81">
-        <v>0.18702289798785268</v>
+        <v>0.20212110068999706</v>
       </c>
       <c r="G81">
         <v>0.50778999999999996</v>
@@ -22205,7 +22205,7 @@
         <v>2022</v>
       </c>
       <c r="F82">
-        <v>0.27347228442755023</v>
+        <v>0.19627663512787666</v>
       </c>
       <c r="G82">
         <v>0.50778999999999996</v>
@@ -22217,7 +22217,7 @@
         <v>36.300000000000004</v>
       </c>
       <c r="J82">
-        <v>3.4650000000000003</v>
+        <v>3.4649999999999999</v>
       </c>
       <c r="K82">
         <v>50</v>
@@ -22252,7 +22252,7 @@
         <v>49</v>
       </c>
       <c r="D83" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="E83">
         <v>2006</v>
@@ -22305,7 +22305,7 @@
         <v>49</v>
       </c>
       <c r="D84" t="s">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="E84">
         <v>2012</v>
@@ -22358,7 +22358,7 @@
         <v>49</v>
       </c>
       <c r="D85" t="s">
-        <v>59</v>
+        <v>85</v>
       </c>
       <c r="E85">
         <v>1993</v>
@@ -22464,7 +22464,7 @@
         <v>49</v>
       </c>
       <c r="D87" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="E87">
         <v>2005</v>
@@ -22517,7 +22517,7 @@
         <v>49</v>
       </c>
       <c r="D88" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="E88">
         <v>2006</v>
@@ -22570,7 +22570,7 @@
         <v>49</v>
       </c>
       <c r="D89" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="E89">
         <v>2006</v>
@@ -22676,7 +22676,7 @@
         <v>49</v>
       </c>
       <c r="D91" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="E91">
         <v>2003</v>
@@ -22835,7 +22835,7 @@
         <v>49</v>
       </c>
       <c r="D94" t="s">
-        <v>87</v>
+        <v>66</v>
       </c>
       <c r="E94">
         <v>2004</v>
@@ -22888,7 +22888,7 @@
         <v>49</v>
       </c>
       <c r="D95" t="s">
-        <v>87</v>
+        <v>66</v>
       </c>
       <c r="E95">
         <v>2005</v>
@@ -22941,7 +22941,7 @@
         <v>49</v>
       </c>
       <c r="D96" t="s">
-        <v>74</v>
+        <v>58</v>
       </c>
       <c r="E96">
         <v>2005</v>
@@ -22994,7 +22994,7 @@
         <v>49</v>
       </c>
       <c r="D97" t="s">
-        <v>74</v>
+        <v>58</v>
       </c>
       <c r="E97">
         <v>2005</v>
@@ -23047,7 +23047,7 @@
         <v>49</v>
       </c>
       <c r="D98" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="E98">
         <v>2004</v>
@@ -23100,7 +23100,7 @@
         <v>49</v>
       </c>
       <c r="D99" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="E99">
         <v>2004</v>
@@ -23153,7 +23153,7 @@
         <v>49</v>
       </c>
       <c r="D100" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="E100">
         <v>2004</v>
@@ -23206,7 +23206,7 @@
         <v>49</v>
       </c>
       <c r="D101" t="s">
-        <v>65</v>
+        <v>52</v>
       </c>
       <c r="E101">
         <v>2008</v>
@@ -23259,7 +23259,7 @@
         <v>49</v>
       </c>
       <c r="D102" t="s">
-        <v>65</v>
+        <v>52</v>
       </c>
       <c r="E102">
         <v>2008</v>
@@ -23312,7 +23312,7 @@
         <v>49</v>
       </c>
       <c r="D103" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="E103">
         <v>2002</v>
@@ -23365,7 +23365,7 @@
         <v>49</v>
       </c>
       <c r="D104" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="E104">
         <v>2002</v>
@@ -23418,7 +23418,7 @@
         <v>49</v>
       </c>
       <c r="D105" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="E105">
         <v>2003</v>
@@ -23471,7 +23471,7 @@
         <v>49</v>
       </c>
       <c r="D106" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="E106">
         <v>2003</v>
@@ -23524,7 +23524,7 @@
         <v>49</v>
       </c>
       <c r="D107" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="E107">
         <v>2000</v>
@@ -23577,7 +23577,7 @@
         <v>49</v>
       </c>
       <c r="D108" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="E108">
         <v>2000</v>
@@ -23630,7 +23630,7 @@
         <v>49</v>
       </c>
       <c r="D109" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="E109">
         <v>2007</v>
@@ -23683,7 +23683,7 @@
         <v>49</v>
       </c>
       <c r="D110" t="s">
-        <v>59</v>
+        <v>85</v>
       </c>
       <c r="E110">
         <v>2023</v>
@@ -23736,7 +23736,7 @@
         <v>49</v>
       </c>
       <c r="D111" t="s">
-        <v>59</v>
+        <v>85</v>
       </c>
       <c r="E111">
         <v>2001</v>
@@ -23842,7 +23842,7 @@
         <v>49</v>
       </c>
       <c r="D113" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="E113">
         <v>2010</v>
@@ -23895,7 +23895,7 @@
         <v>49</v>
       </c>
       <c r="D114" t="s">
-        <v>69</v>
+        <v>86</v>
       </c>
       <c r="E114">
         <v>2005</v>
@@ -23948,7 +23948,7 @@
         <v>49</v>
       </c>
       <c r="D115" t="s">
-        <v>69</v>
+        <v>86</v>
       </c>
       <c r="E115">
         <v>2009</v>
@@ -24001,7 +24001,7 @@
         <v>49</v>
       </c>
       <c r="D116" t="s">
-        <v>70</v>
+        <v>84</v>
       </c>
       <c r="E116">
         <v>1997</v>
@@ -24054,7 +24054,7 @@
         <v>49</v>
       </c>
       <c r="D117" t="s">
-        <v>70</v>
+        <v>84</v>
       </c>
       <c r="E117">
         <v>1997</v>
@@ -24107,7 +24107,7 @@
         <v>49</v>
       </c>
       <c r="D118" t="s">
-        <v>70</v>
+        <v>84</v>
       </c>
       <c r="E118">
         <v>1998</v>
@@ -24160,7 +24160,7 @@
         <v>49</v>
       </c>
       <c r="D119" t="s">
-        <v>70</v>
+        <v>84</v>
       </c>
       <c r="E119">
         <v>1999</v>
@@ -24266,7 +24266,7 @@
         <v>49</v>
       </c>
       <c r="D121" t="s">
-        <v>50</v>
+        <v>64</v>
       </c>
       <c r="E121">
         <v>2010</v>
@@ -24319,7 +24319,7 @@
         <v>49</v>
       </c>
       <c r="D122" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="E122">
         <v>2003</v>
@@ -24372,7 +24372,7 @@
         <v>49</v>
       </c>
       <c r="D123" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="E123">
         <v>2003</v>
@@ -24425,7 +24425,7 @@
         <v>49</v>
       </c>
       <c r="D124" t="s">
-        <v>57</v>
+        <v>87</v>
       </c>
       <c r="E124">
         <v>2006</v>
@@ -24584,7 +24584,7 @@
         <v>49</v>
       </c>
       <c r="D127" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="E127">
         <v>2002</v>
@@ -24637,7 +24637,7 @@
         <v>49</v>
       </c>
       <c r="D128" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="E128">
         <v>2002</v>
@@ -24690,7 +24690,7 @@
         <v>49</v>
       </c>
       <c r="D129" t="s">
-        <v>50</v>
+        <v>64</v>
       </c>
       <c r="E129">
         <v>2010</v>
@@ -24743,7 +24743,7 @@
         <v>49</v>
       </c>
       <c r="D130" t="s">
-        <v>50</v>
+        <v>64</v>
       </c>
       <c r="E130">
         <v>2010</v>
@@ -24796,7 +24796,7 @@
         <v>49</v>
       </c>
       <c r="D131" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="E131">
         <v>2008</v>
@@ -24849,7 +24849,7 @@
         <v>49</v>
       </c>
       <c r="D132" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="E132">
         <v>2008</v>
@@ -24902,7 +24902,7 @@
         <v>49</v>
       </c>
       <c r="D133" t="s">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="E133">
         <v>2018</v>
@@ -24955,7 +24955,7 @@
         <v>49</v>
       </c>
       <c r="D134" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="E134">
         <v>2006</v>
@@ -25008,7 +25008,7 @@
         <v>49</v>
       </c>
       <c r="D135" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="E135">
         <v>2007</v>
@@ -25167,7 +25167,7 @@
         <v>49</v>
       </c>
       <c r="D138" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E138">
         <v>2010</v>
@@ -25220,7 +25220,7 @@
         <v>49</v>
       </c>
       <c r="D139" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E139">
         <v>2010</v>
@@ -25273,7 +25273,7 @@
         <v>49</v>
       </c>
       <c r="D140" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="E140">
         <v>2004</v>
@@ -25326,7 +25326,7 @@
         <v>49</v>
       </c>
       <c r="D141" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="E141">
         <v>2004</v>
@@ -25379,7 +25379,7 @@
         <v>49</v>
       </c>
       <c r="D142" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="E142">
         <v>2008</v>
@@ -25432,7 +25432,7 @@
         <v>49</v>
       </c>
       <c r="D143" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="E143">
         <v>2007</v>
@@ -25485,7 +25485,7 @@
         <v>49</v>
       </c>
       <c r="D144" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="E144">
         <v>2007</v>
@@ -25538,7 +25538,7 @@
         <v>49</v>
       </c>
       <c r="D145" t="s">
-        <v>85</v>
+        <v>55</v>
       </c>
       <c r="E145">
         <v>2005</v>
@@ -25591,7 +25591,7 @@
         <v>49</v>
       </c>
       <c r="D146" t="s">
-        <v>85</v>
+        <v>55</v>
       </c>
       <c r="E146">
         <v>2005</v>
@@ -25644,7 +25644,7 @@
         <v>49</v>
       </c>
       <c r="D147" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="E147">
         <v>2015</v>
@@ -25697,7 +25697,7 @@
         <v>49</v>
       </c>
       <c r="D148" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="E148">
         <v>2004</v>
@@ -25750,7 +25750,7 @@
         <v>49</v>
       </c>
       <c r="D149" t="s">
-        <v>71</v>
+        <v>83</v>
       </c>
       <c r="E149">
         <v>2006</v>
@@ -25803,7 +25803,7 @@
         <v>49</v>
       </c>
       <c r="D150" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="E150">
         <v>2011</v>
@@ -25856,7 +25856,7 @@
         <v>49</v>
       </c>
       <c r="D151" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E151">
         <v>2004</v>
@@ -25909,7 +25909,7 @@
         <v>49</v>
       </c>
       <c r="D152" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E152">
         <v>2005</v>
@@ -25962,7 +25962,7 @@
         <v>49</v>
       </c>
       <c r="D153" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="E153">
         <v>2006</v>
@@ -26015,7 +26015,7 @@
         <v>49</v>
       </c>
       <c r="D154" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="E154">
         <v>2008</v>
@@ -26068,7 +26068,7 @@
         <v>49</v>
       </c>
       <c r="D155" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="E155">
         <v>2007</v>
@@ -26174,7 +26174,7 @@
         <v>49</v>
       </c>
       <c r="D157" t="s">
-        <v>80</v>
+        <v>57</v>
       </c>
       <c r="E157">
         <v>2023</v>
@@ -26227,7 +26227,7 @@
         <v>49</v>
       </c>
       <c r="D158" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="E158">
         <v>2026</v>
@@ -26280,7 +26280,7 @@
         <v>49</v>
       </c>
       <c r="D159" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="E159">
         <v>2022</v>
@@ -26333,7 +26333,7 @@
         <v>49</v>
       </c>
       <c r="D160" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="E160">
         <v>2003</v>
@@ -26386,7 +26386,7 @@
         <v>49</v>
       </c>
       <c r="D161" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="E161">
         <v>2003</v>
@@ -26439,7 +26439,7 @@
         <v>49</v>
       </c>
       <c r="D162" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="E162">
         <v>2003</v>
@@ -26492,7 +26492,7 @@
         <v>49</v>
       </c>
       <c r="D163" t="s">
-        <v>81</v>
+        <v>56</v>
       </c>
       <c r="E163">
         <v>2008</v>
@@ -26545,7 +26545,7 @@
         <v>49</v>
       </c>
       <c r="D164" t="s">
-        <v>50</v>
+        <v>64</v>
       </c>
       <c r="E164">
         <v>1999</v>
@@ -26598,7 +26598,7 @@
         <v>49</v>
       </c>
       <c r="D165" t="s">
-        <v>50</v>
+        <v>64</v>
       </c>
       <c r="E165">
         <v>1999</v>
@@ -26651,7 +26651,7 @@
         <v>49</v>
       </c>
       <c r="D166" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="E166">
         <v>1997</v>
@@ -26757,7 +26757,7 @@
         <v>49</v>
       </c>
       <c r="D168" t="s">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="E168">
         <v>2001</v>
@@ -26810,7 +26810,7 @@
         <v>49</v>
       </c>
       <c r="D169" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="E169">
         <v>2006</v>
@@ -26916,7 +26916,7 @@
         <v>49</v>
       </c>
       <c r="D171" t="s">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="E171">
         <v>2007</v>
@@ -27499,7 +27499,7 @@
         <v>49</v>
       </c>
       <c r="D182" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="E182">
         <v>2015</v>
@@ -28294,7 +28294,7 @@
         <v>49</v>
       </c>
       <c r="D197" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="E197">
         <v>2004</v>
@@ -28347,7 +28347,7 @@
         <v>49</v>
       </c>
       <c r="D198" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="E198">
         <v>2008</v>
@@ -28559,7 +28559,7 @@
         <v>49</v>
       </c>
       <c r="D202" t="s">
-        <v>50</v>
+        <v>64</v>
       </c>
       <c r="E202">
         <v>2005</v>
@@ -28612,7 +28612,7 @@
         <v>49</v>
       </c>
       <c r="D203" t="s">
-        <v>50</v>
+        <v>64</v>
       </c>
       <c r="E203">
         <v>2015</v>
@@ -29301,7 +29301,7 @@
         <v>49</v>
       </c>
       <c r="D216" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E216">
         <v>2022</v>
@@ -29513,7 +29513,7 @@
         <v>49</v>
       </c>
       <c r="D220" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="E220">
         <v>2009</v>
@@ -30202,7 +30202,7 @@
         <v>49</v>
       </c>
       <c r="D233" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="E233">
         <v>1994</v>
@@ -30361,7 +30361,7 @@
         <v>49</v>
       </c>
       <c r="D236" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E236">
         <v>1990</v>
@@ -30414,7 +30414,7 @@
         <v>49</v>
       </c>
       <c r="D237" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E237">
         <v>2022</v>
@@ -30573,7 +30573,7 @@
         <v>49</v>
       </c>
       <c r="D240" t="s">
-        <v>69</v>
+        <v>86</v>
       </c>
       <c r="E240">
         <v>2006</v>
@@ -30626,7 +30626,7 @@
         <v>49</v>
       </c>
       <c r="D241" t="s">
-        <v>85</v>
+        <v>55</v>
       </c>
       <c r="E241">
         <v>2024</v>
@@ -30679,7 +30679,7 @@
         <v>49</v>
       </c>
       <c r="D242" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="E242">
         <v>2023</v>
@@ -30732,7 +30732,7 @@
         <v>49</v>
       </c>
       <c r="D243" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="E243">
         <v>2023</v>
@@ -30785,7 +30785,7 @@
         <v>49</v>
       </c>
       <c r="D244" t="s">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="E244">
         <v>1997</v>
@@ -31262,7 +31262,7 @@
         <v>49</v>
       </c>
       <c r="D253" t="s">
-        <v>65</v>
+        <v>52</v>
       </c>
       <c r="E253">
         <v>2008</v>
@@ -31527,7 +31527,7 @@
         <v>49</v>
       </c>
       <c r="D258" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="E258">
         <v>2015</v>
@@ -31633,7 +31633,7 @@
         <v>49</v>
       </c>
       <c r="D260" t="s">
-        <v>81</v>
+        <v>56</v>
       </c>
       <c r="E260">
         <v>2004</v>
@@ -31898,7 +31898,7 @@
         <v>49</v>
       </c>
       <c r="D265" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="E265">
         <v>2024</v>
@@ -32004,7 +32004,7 @@
         <v>49</v>
       </c>
       <c r="D267" t="s">
-        <v>71</v>
+        <v>83</v>
       </c>
       <c r="E267">
         <v>2023</v>
@@ -32216,7 +32216,7 @@
         <v>49</v>
       </c>
       <c r="D271" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="E271">
         <v>1975</v>
@@ -32269,7 +32269,7 @@
         <v>49</v>
       </c>
       <c r="D272" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="E272">
         <v>1975</v>
@@ -32322,7 +32322,7 @@
         <v>49</v>
       </c>
       <c r="D273" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="E273">
         <v>1975</v>
@@ -32375,7 +32375,7 @@
         <v>49</v>
       </c>
       <c r="D274" t="s">
-        <v>74</v>
+        <v>58</v>
       </c>
       <c r="E274">
         <v>2015</v>
@@ -32428,7 +32428,7 @@
         <v>49</v>
       </c>
       <c r="D275" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="E275">
         <v>1967</v>
@@ -32481,7 +32481,7 @@
         <v>49</v>
       </c>
       <c r="D276" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="E276">
         <v>1971</v>
@@ -32534,7 +32534,7 @@
         <v>49</v>
       </c>
       <c r="D277" t="s">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="E277">
         <v>1970</v>
@@ -32587,7 +32587,7 @@
         <v>49</v>
       </c>
       <c r="D278" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E278">
         <v>1978</v>
@@ -32640,7 +32640,7 @@
         <v>49</v>
       </c>
       <c r="D279" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E279">
         <v>1981</v>
@@ -32693,7 +32693,7 @@
         <v>49</v>
       </c>
       <c r="D280" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E280">
         <v>1987</v>
@@ -33117,7 +33117,7 @@
         <v>293</v>
       </c>
       <c r="D288" t="s">
-        <v>70</v>
+        <v>84</v>
       </c>
       <c r="E288">
         <v>1991</v>
@@ -33170,7 +33170,7 @@
         <v>293</v>
       </c>
       <c r="D289" t="s">
-        <v>70</v>
+        <v>84</v>
       </c>
       <c r="E289">
         <v>1991</v>
@@ -34230,25 +34230,25 @@
         <v>308</v>
       </c>
       <c r="D309" t="s">
-        <v>239</v>
+        <v>193</v>
       </c>
       <c r="E309">
         <v>2022</v>
       </c>
       <c r="F309">
-        <v>0.22871669814448767</v>
+        <v>0.61052976624370348</v>
       </c>
       <c r="G309">
         <v>1</v>
       </c>
       <c r="H309">
-        <v>3162.5000000000005</v>
+        <v>2750</v>
       </c>
       <c r="I309">
-        <v>60.500000000000014</v>
+        <v>55.000000000000007</v>
       </c>
       <c r="J309">
-        <v>2.3100000000000005</v>
+        <v>2.1</v>
       </c>
       <c r="K309">
         <v>100</v>
@@ -34283,13 +34283,13 @@
         <v>308</v>
       </c>
       <c r="D310" t="s">
-        <v>99</v>
+        <v>309</v>
       </c>
       <c r="E310">
         <v>2022</v>
       </c>
       <c r="F310">
-        <v>0.29181095970158766</v>
+        <v>0.10670353057450742</v>
       </c>
       <c r="G310">
         <v>1</v>
@@ -34336,25 +34336,25 @@
         <v>308</v>
       </c>
       <c r="D311" t="s">
-        <v>309</v>
+        <v>64</v>
       </c>
       <c r="E311">
         <v>2022</v>
       </c>
       <c r="F311">
-        <v>0.35629700644009438</v>
+        <v>0.23196419690110309</v>
       </c>
       <c r="G311">
         <v>1</v>
       </c>
       <c r="H311">
-        <v>2750</v>
+        <v>3162.5000000000005</v>
       </c>
       <c r="I311">
-        <v>55</v>
+        <v>60.500000000000014</v>
       </c>
       <c r="J311">
-        <v>2.1</v>
+        <v>2.3100000000000005</v>
       </c>
       <c r="K311">
         <v>100</v>
@@ -34395,7 +34395,7 @@
         <v>2022</v>
       </c>
       <c r="F312">
-        <v>0.13036387865841995</v>
+        <v>0.10067246145507874</v>
       </c>
       <c r="G312">
         <v>1</v>
@@ -34448,7 +34448,7 @@
         <v>2022</v>
       </c>
       <c r="F313">
-        <v>6.0310691194286808E-2</v>
+        <v>5.1032123318242681E-2</v>
       </c>
       <c r="G313">
         <v>1</v>
@@ -34457,7 +34457,7 @@
         <v>3162.5000000000005</v>
       </c>
       <c r="I313">
-        <v>60.500000000000014</v>
+        <v>60.500000000000021</v>
       </c>
       <c r="J313">
         <v>2.3100000000000005</v>
@@ -34495,25 +34495,25 @@
         <v>308</v>
       </c>
       <c r="D314" t="s">
-        <v>151</v>
+        <v>312</v>
       </c>
       <c r="E314">
         <v>2022</v>
       </c>
       <c r="F314">
-        <v>4.5464982592616207E-2</v>
+        <v>0.15541601192373908</v>
       </c>
       <c r="G314">
         <v>1</v>
       </c>
       <c r="H314">
-        <v>3712.5000000000005</v>
+        <v>3162.5000000000005</v>
       </c>
       <c r="I314">
-        <v>71.5</v>
+        <v>60.500000000000014</v>
       </c>
       <c r="J314">
-        <v>2.52</v>
+        <v>2.3100000000000005</v>
       </c>
       <c r="K314">
         <v>100</v>
@@ -34548,25 +34548,25 @@
         <v>308</v>
       </c>
       <c r="D315" t="s">
-        <v>312</v>
+        <v>19</v>
       </c>
       <c r="E315">
         <v>2022</v>
       </c>
       <c r="F315">
-        <v>4.4073197411209589E-2</v>
+        <v>0.11134281451252948</v>
       </c>
       <c r="G315">
         <v>1</v>
       </c>
       <c r="H315">
-        <v>3712.5000000000005</v>
+        <v>3162.5000000000005</v>
       </c>
       <c r="I315">
-        <v>71.5</v>
+        <v>60.500000000000014</v>
       </c>
       <c r="J315">
-        <v>2.52</v>
+        <v>2.3100000000000005</v>
       </c>
       <c r="K315">
         <v>100</v>
@@ -34601,25 +34601,25 @@
         <v>308</v>
       </c>
       <c r="D316" t="s">
-        <v>313</v>
+        <v>99</v>
       </c>
       <c r="E316">
         <v>2022</v>
       </c>
       <c r="F316">
-        <v>1.0883760118599757</v>
+        <v>0.29181095970158766</v>
       </c>
       <c r="G316">
         <v>1</v>
       </c>
       <c r="H316">
-        <v>2750</v>
+        <v>3162.5000000000005</v>
       </c>
       <c r="I316">
-        <v>55.000000000000007</v>
+        <v>60.500000000000014</v>
       </c>
       <c r="J316">
-        <v>2.1</v>
+        <v>2.3100000000000005</v>
       </c>
       <c r="K316">
         <v>100</v>
@@ -34654,25 +34654,25 @@
         <v>308</v>
       </c>
       <c r="D317" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="E317">
         <v>2022</v>
       </c>
       <c r="F317">
-        <v>0.54140443556717466</v>
+        <v>0.13036387865841995</v>
       </c>
       <c r="G317">
         <v>1</v>
       </c>
       <c r="H317">
-        <v>2750</v>
+        <v>3162.5000000000005</v>
       </c>
       <c r="I317">
-        <v>55.000000000000007</v>
+        <v>60.500000000000014</v>
       </c>
       <c r="J317">
-        <v>2.1</v>
+        <v>2.3100000000000005</v>
       </c>
       <c r="K317">
         <v>100</v>
@@ -34707,7 +34707,7 @@
         <v>308</v>
       </c>
       <c r="D318" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="E318">
         <v>2022</v>
@@ -34760,25 +34760,25 @@
         <v>308</v>
       </c>
       <c r="D319" t="s">
-        <v>50</v>
+        <v>315</v>
       </c>
       <c r="E319">
         <v>2022</v>
       </c>
       <c r="F319">
-        <v>0.23196419690110309</v>
+        <v>4.3145340623605172E-2</v>
       </c>
       <c r="G319">
         <v>1</v>
       </c>
       <c r="H319">
-        <v>3162.5000000000005</v>
+        <v>3712.5000000000005</v>
       </c>
       <c r="I319">
-        <v>60.500000000000014</v>
+        <v>71.5</v>
       </c>
       <c r="J319">
-        <v>2.3100000000000005</v>
+        <v>2.52</v>
       </c>
       <c r="K319">
         <v>100</v>
@@ -34813,13 +34813,13 @@
         <v>308</v>
       </c>
       <c r="D320" t="s">
-        <v>291</v>
+        <v>316</v>
       </c>
       <c r="E320">
         <v>2022</v>
       </c>
       <c r="F320">
-        <v>0.13082780705222213</v>
+        <v>6.3558189950902247E-2</v>
       </c>
       <c r="G320">
         <v>1</v>
@@ -34866,25 +34866,25 @@
         <v>308</v>
       </c>
       <c r="D321" t="s">
-        <v>204</v>
+        <v>317</v>
       </c>
       <c r="E321">
         <v>2022</v>
       </c>
       <c r="F321">
-        <v>7.8403898552572848E-2</v>
+        <v>4.1753555442198553E-2</v>
       </c>
       <c r="G321">
         <v>1</v>
       </c>
       <c r="H321">
-        <v>3162.5000000000005</v>
+        <v>3712.5000000000005</v>
       </c>
       <c r="I321">
-        <v>60.500000000000014</v>
+        <v>71.5</v>
       </c>
       <c r="J321">
-        <v>2.3100000000000005</v>
+        <v>2.52</v>
       </c>
       <c r="K321">
         <v>100</v>
@@ -34919,25 +34919,25 @@
         <v>308</v>
       </c>
       <c r="D322" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="E322">
         <v>2022</v>
       </c>
       <c r="F322">
-        <v>0.19299421182171778</v>
+        <v>0.35629700644009438</v>
       </c>
       <c r="G322">
         <v>1</v>
       </c>
       <c r="H322">
-        <v>3162.5000000000005</v>
+        <v>2750</v>
       </c>
       <c r="I322">
-        <v>60.500000000000014</v>
+        <v>55</v>
       </c>
       <c r="J322">
-        <v>2.3100000000000005</v>
+        <v>2.1</v>
       </c>
       <c r="K322">
         <v>100</v>
@@ -34972,25 +34972,25 @@
         <v>308</v>
       </c>
       <c r="D323" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="E323">
         <v>2022</v>
       </c>
       <c r="F323">
-        <v>0.56367299846968055</v>
+        <v>6.0310691194286808E-2</v>
       </c>
       <c r="G323">
         <v>1</v>
       </c>
       <c r="H323">
-        <v>2750</v>
+        <v>3162.5000000000005</v>
       </c>
       <c r="I323">
-        <v>55.000000000000007</v>
+        <v>60.500000000000014</v>
       </c>
       <c r="J323">
-        <v>2.1</v>
+        <v>2.3100000000000005</v>
       </c>
       <c r="K323">
         <v>100</v>
@@ -35025,25 +35025,25 @@
         <v>308</v>
       </c>
       <c r="D324" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="E324">
         <v>2022</v>
       </c>
       <c r="F324">
-        <v>4.3145340623605172E-2</v>
+        <v>0.19299421182171778</v>
       </c>
       <c r="G324">
         <v>1</v>
       </c>
       <c r="H324">
-        <v>3712.5000000000005</v>
+        <v>3162.5000000000005</v>
       </c>
       <c r="I324">
-        <v>71.5</v>
+        <v>60.500000000000014</v>
       </c>
       <c r="J324">
-        <v>2.52</v>
+        <v>2.3100000000000005</v>
       </c>
       <c r="K324">
         <v>100</v>
@@ -35078,25 +35078,25 @@
         <v>308</v>
       </c>
       <c r="D325" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="E325">
         <v>2022</v>
       </c>
       <c r="F325">
-        <v>0.57944656385895543</v>
+        <v>0.1577356538927501</v>
       </c>
       <c r="G325">
         <v>1</v>
       </c>
       <c r="H325">
-        <v>2750</v>
+        <v>3162.5000000000005</v>
       </c>
       <c r="I325">
-        <v>55.000000000000007</v>
+        <v>60.500000000000014</v>
       </c>
       <c r="J325">
-        <v>2.1</v>
+        <v>2.3100000000000005</v>
       </c>
       <c r="K325">
         <v>100</v>
@@ -35131,13 +35131,13 @@
         <v>308</v>
       </c>
       <c r="D326" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="E326">
         <v>2022</v>
       </c>
       <c r="F326">
-        <v>5.8918906012880183E-2</v>
+        <v>0.20320063648536632</v>
       </c>
       <c r="G326">
         <v>1</v>
@@ -35146,7 +35146,7 @@
         <v>3162.5000000000005</v>
       </c>
       <c r="I326">
-        <v>60.500000000000021</v>
+        <v>60.500000000000014</v>
       </c>
       <c r="J326">
         <v>2.3100000000000005</v>
@@ -35184,25 +35184,25 @@
         <v>308</v>
       </c>
       <c r="D327" t="s">
-        <v>65</v>
+        <v>323</v>
       </c>
       <c r="E327">
         <v>2022</v>
       </c>
       <c r="F327">
-        <v>5.4743550468660328E-2</v>
+        <v>0.56367299846968055</v>
       </c>
       <c r="G327">
         <v>1</v>
       </c>
       <c r="H327">
-        <v>3162.5000000000005</v>
+        <v>2750</v>
       </c>
       <c r="I327">
-        <v>60.500000000000014</v>
+        <v>55.000000000000007</v>
       </c>
       <c r="J327">
-        <v>2.3100000000000005</v>
+        <v>2.1</v>
       </c>
       <c r="K327">
         <v>100</v>
@@ -35237,13 +35237,13 @@
         <v>308</v>
       </c>
       <c r="D328" t="s">
-        <v>321</v>
+        <v>204</v>
       </c>
       <c r="E328">
         <v>2022</v>
       </c>
       <c r="F328">
-        <v>0.10670353057450742</v>
+        <v>7.8403898552572848E-2</v>
       </c>
       <c r="G328">
         <v>1</v>
@@ -35290,13 +35290,13 @@
         <v>308</v>
       </c>
       <c r="D329" t="s">
-        <v>80</v>
+        <v>324</v>
       </c>
       <c r="E329">
         <v>2022</v>
       </c>
       <c r="F329">
-        <v>0.50939337639482241</v>
+        <v>1.0883760118599757</v>
       </c>
       <c r="G329">
         <v>1</v>
@@ -35343,25 +35343,25 @@
         <v>308</v>
       </c>
       <c r="D330" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="E330">
         <v>2022</v>
       </c>
       <c r="F330">
-        <v>6.9589259070330922E-2</v>
+        <v>0.57944656385895543</v>
       </c>
       <c r="G330">
         <v>1</v>
       </c>
       <c r="H330">
-        <v>3162.5000000000005</v>
+        <v>2750</v>
       </c>
       <c r="I330">
-        <v>60.500000000000007</v>
+        <v>55.000000000000007</v>
       </c>
       <c r="J330">
-        <v>2.3100000000000005</v>
+        <v>2.1</v>
       </c>
       <c r="K330">
         <v>100</v>
@@ -35396,13 +35396,13 @@
         <v>308</v>
       </c>
       <c r="D331" t="s">
-        <v>323</v>
+        <v>291</v>
       </c>
       <c r="E331">
         <v>2022</v>
       </c>
       <c r="F331">
-        <v>0.10067246145507874</v>
+        <v>0.13082780705222213</v>
       </c>
       <c r="G331">
         <v>1</v>
@@ -35449,25 +35449,25 @@
         <v>308</v>
       </c>
       <c r="D332" t="s">
-        <v>193</v>
+        <v>326</v>
       </c>
       <c r="E332">
         <v>2022</v>
       </c>
       <c r="F332">
-        <v>0.61052976624370348</v>
+        <v>4.4073197411209589E-2</v>
       </c>
       <c r="G332">
         <v>1</v>
       </c>
       <c r="H332">
-        <v>2750</v>
+        <v>3712.5000000000005</v>
       </c>
       <c r="I332">
-        <v>55.000000000000007</v>
+        <v>71.5</v>
       </c>
       <c r="J332">
-        <v>2.1</v>
+        <v>2.52</v>
       </c>
       <c r="K332">
         <v>100</v>
@@ -35502,13 +35502,13 @@
         <v>308</v>
       </c>
       <c r="D333" t="s">
-        <v>19</v>
+        <v>327</v>
       </c>
       <c r="E333">
         <v>2022</v>
       </c>
       <c r="F333">
-        <v>0.11134281451252948</v>
+        <v>6.9589259070330922E-2</v>
       </c>
       <c r="G333">
         <v>1</v>
@@ -35517,7 +35517,7 @@
         <v>3162.5000000000005</v>
       </c>
       <c r="I333">
-        <v>60.500000000000014</v>
+        <v>60.500000000000007</v>
       </c>
       <c r="J333">
         <v>2.3100000000000005</v>
@@ -35555,25 +35555,25 @@
         <v>308</v>
       </c>
       <c r="D334" t="s">
-        <v>324</v>
+        <v>57</v>
       </c>
       <c r="E334">
         <v>2022</v>
       </c>
       <c r="F334">
-        <v>0.1577356538927501</v>
+        <v>0.50939337639482241</v>
       </c>
       <c r="G334">
         <v>1</v>
       </c>
       <c r="H334">
-        <v>3162.5000000000005</v>
+        <v>2750</v>
       </c>
       <c r="I334">
-        <v>60.500000000000014</v>
+        <v>55.000000000000007</v>
       </c>
       <c r="J334">
-        <v>2.3100000000000005</v>
+        <v>2.1</v>
       </c>
       <c r="K334">
         <v>100</v>
@@ -35608,13 +35608,13 @@
         <v>308</v>
       </c>
       <c r="D335" t="s">
-        <v>16</v>
+        <v>328</v>
       </c>
       <c r="E335">
         <v>2022</v>
       </c>
       <c r="F335">
-        <v>8.7682466428616976E-2</v>
+        <v>5.8918906012880183E-2</v>
       </c>
       <c r="G335">
         <v>1</v>
@@ -35623,7 +35623,7 @@
         <v>3162.5000000000005</v>
       </c>
       <c r="I335">
-        <v>60.500000000000007</v>
+        <v>60.500000000000021</v>
       </c>
       <c r="J335">
         <v>2.3100000000000005</v>
@@ -35661,13 +35661,13 @@
         <v>308</v>
       </c>
       <c r="D336" t="s">
-        <v>325</v>
+        <v>17</v>
       </c>
       <c r="E336">
         <v>2022</v>
       </c>
       <c r="F336">
-        <v>5.1032123318242681E-2</v>
+        <v>8.7682466428616976E-2</v>
       </c>
       <c r="G336">
         <v>1</v>
@@ -35676,7 +35676,7 @@
         <v>3162.5000000000005</v>
       </c>
       <c r="I336">
-        <v>60.500000000000021</v>
+        <v>60.500000000000007</v>
       </c>
       <c r="J336">
         <v>2.3100000000000005</v>
@@ -35714,13 +35714,13 @@
         <v>308</v>
       </c>
       <c r="D337" t="s">
-        <v>326</v>
+        <v>52</v>
       </c>
       <c r="E337">
         <v>2022</v>
       </c>
       <c r="F337">
-        <v>0.15541601192373908</v>
+        <v>5.4743550468660328E-2</v>
       </c>
       <c r="G337">
         <v>1</v>
@@ -35767,25 +35767,25 @@
         <v>308</v>
       </c>
       <c r="D338" t="s">
-        <v>327</v>
+        <v>151</v>
       </c>
       <c r="E338">
         <v>2022</v>
       </c>
       <c r="F338">
-        <v>0.20320063648536632</v>
+        <v>4.5464982592616207E-2</v>
       </c>
       <c r="G338">
         <v>1</v>
       </c>
       <c r="H338">
-        <v>3162.5000000000005</v>
+        <v>3712.5000000000005</v>
       </c>
       <c r="I338">
-        <v>60.500000000000014</v>
+        <v>71.5</v>
       </c>
       <c r="J338">
-        <v>2.3100000000000005</v>
+        <v>2.52</v>
       </c>
       <c r="K338">
         <v>100</v>
@@ -35820,25 +35820,25 @@
         <v>308</v>
       </c>
       <c r="D339" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="E339">
         <v>2022</v>
       </c>
       <c r="F339">
-        <v>4.1753555442198553E-2</v>
+        <v>0.54140443556717466</v>
       </c>
       <c r="G339">
         <v>1</v>
       </c>
       <c r="H339">
-        <v>3712.5000000000005</v>
+        <v>2750</v>
       </c>
       <c r="I339">
-        <v>71.5</v>
+        <v>55.000000000000007</v>
       </c>
       <c r="J339">
-        <v>2.52</v>
+        <v>2.1</v>
       </c>
       <c r="K339">
         <v>100</v>
@@ -35873,13 +35873,13 @@
         <v>308</v>
       </c>
       <c r="D340" t="s">
-        <v>329</v>
+        <v>239</v>
       </c>
       <c r="E340">
         <v>2022</v>
       </c>
       <c r="F340">
-        <v>6.3558189950902247E-2</v>
+        <v>0.22871669814448767</v>
       </c>
       <c r="G340">
         <v>1</v>
@@ -35979,7 +35979,7 @@
         <v>308</v>
       </c>
       <c r="D342" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="E342">
         <v>1959</v>
@@ -36085,7 +36085,7 @@
         <v>308</v>
       </c>
       <c r="D344" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E344">
         <v>1973</v>
@@ -36191,7 +36191,7 @@
         <v>308</v>
       </c>
       <c r="D346" t="s">
-        <v>313</v>
+        <v>324</v>
       </c>
       <c r="E346">
         <v>1963</v>
@@ -36244,7 +36244,7 @@
         <v>308</v>
       </c>
       <c r="D347" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="E347">
         <v>2015</v>
@@ -36297,7 +36297,7 @@
         <v>308</v>
       </c>
       <c r="D348" t="s">
-        <v>323</v>
+        <v>310</v>
       </c>
       <c r="E348">
         <v>1931</v>
@@ -36350,7 +36350,7 @@
         <v>308</v>
       </c>
       <c r="D349" t="s">
-        <v>314</v>
+        <v>329</v>
       </c>
       <c r="E349">
         <v>1949</v>
@@ -36403,7 +36403,7 @@
         <v>308</v>
       </c>
       <c r="D350" t="s">
-        <v>309</v>
+        <v>318</v>
       </c>
       <c r="E350">
         <v>1951</v>
@@ -36509,7 +36509,7 @@
         <v>308</v>
       </c>
       <c r="D352" t="s">
-        <v>311</v>
+        <v>319</v>
       </c>
       <c r="E352">
         <v>1958</v>
@@ -36562,7 +36562,7 @@
         <v>308</v>
       </c>
       <c r="D353" t="s">
-        <v>321</v>
+        <v>309</v>
       </c>
       <c r="E353">
         <v>1967</v>
@@ -36615,7 +36615,7 @@
         <v>308</v>
       </c>
       <c r="D354" t="s">
-        <v>327</v>
+        <v>322</v>
       </c>
       <c r="E354">
         <v>1968</v>
@@ -36668,7 +36668,7 @@
         <v>308</v>
       </c>
       <c r="D355" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="E355">
         <v>1929</v>
@@ -36721,7 +36721,7 @@
         <v>308</v>
       </c>
       <c r="D356" t="s">
-        <v>327</v>
+        <v>322</v>
       </c>
       <c r="E356">
         <v>1949</v>
@@ -36827,7 +36827,7 @@
         <v>308</v>
       </c>
       <c r="D358" t="s">
-        <v>65</v>
+        <v>52</v>
       </c>
       <c r="E358">
         <v>1952</v>
@@ -36880,7 +36880,7 @@
         <v>308</v>
       </c>
       <c r="D359" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="E359">
         <v>1913</v>
@@ -36933,7 +36933,7 @@
         <v>308</v>
       </c>
       <c r="D360" t="s">
-        <v>309</v>
+        <v>318</v>
       </c>
       <c r="E360">
         <v>1924</v>
@@ -37039,7 +37039,7 @@
         <v>308</v>
       </c>
       <c r="D362" t="s">
-        <v>309</v>
+        <v>318</v>
       </c>
       <c r="E362">
         <v>1971</v>
@@ -37145,7 +37145,7 @@
         <v>308</v>
       </c>
       <c r="D364" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="E364">
         <v>1927</v>
@@ -37198,7 +37198,7 @@
         <v>308</v>
       </c>
       <c r="D365" t="s">
-        <v>313</v>
+        <v>324</v>
       </c>
       <c r="E365">
         <v>1928</v>
@@ -37304,7 +37304,7 @@
         <v>308</v>
       </c>
       <c r="D367" t="s">
-        <v>313</v>
+        <v>324</v>
       </c>
       <c r="E367">
         <v>1938</v>
@@ -37357,7 +37357,7 @@
         <v>308</v>
       </c>
       <c r="D368" t="s">
-        <v>315</v>
+        <v>326</v>
       </c>
       <c r="E368">
         <v>1920</v>
@@ -37410,7 +37410,7 @@
         <v>308</v>
       </c>
       <c r="D369" t="s">
-        <v>313</v>
+        <v>324</v>
       </c>
       <c r="E369">
         <v>1947</v>
@@ -37463,7 +37463,7 @@
         <v>308</v>
       </c>
       <c r="D370" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="E370">
         <v>1950</v>
@@ -37516,7 +37516,7 @@
         <v>308</v>
       </c>
       <c r="D371" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E371">
         <v>1954</v>
@@ -37622,7 +37622,7 @@
         <v>308</v>
       </c>
       <c r="D373" t="s">
-        <v>309</v>
+        <v>318</v>
       </c>
       <c r="E373">
         <v>1971</v>
@@ -37675,7 +37675,7 @@
         <v>308</v>
       </c>
       <c r="D374" t="s">
-        <v>323</v>
+        <v>310</v>
       </c>
       <c r="E374">
         <v>1959</v>
@@ -37781,7 +37781,7 @@
         <v>308</v>
       </c>
       <c r="D376" t="s">
-        <v>313</v>
+        <v>324</v>
       </c>
       <c r="E376">
         <v>1955</v>
@@ -37834,7 +37834,7 @@
         <v>308</v>
       </c>
       <c r="D377" t="s">
-        <v>313</v>
+        <v>324</v>
       </c>
       <c r="E377">
         <v>1959</v>
@@ -37887,7 +37887,7 @@
         <v>308</v>
       </c>
       <c r="D378" t="s">
-        <v>313</v>
+        <v>324</v>
       </c>
       <c r="E378">
         <v>1954</v>
@@ -38099,7 +38099,7 @@
         <v>308</v>
       </c>
       <c r="D382" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="E382">
         <v>2022</v>
@@ -38311,7 +38311,7 @@
         <v>308</v>
       </c>
       <c r="D386" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="E386">
         <v>2022</v>
@@ -38417,7 +38417,7 @@
         <v>383</v>
       </c>
       <c r="D388" t="s">
-        <v>50</v>
+        <v>64</v>
       </c>
       <c r="E388">
         <v>1989</v>
@@ -38470,7 +38470,7 @@
         <v>383</v>
       </c>
       <c r="D389" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="E389">
         <v>1975</v>
@@ -38523,7 +38523,7 @@
         <v>383</v>
       </c>
       <c r="D390" t="s">
-        <v>80</v>
+        <v>57</v>
       </c>
       <c r="E390">
         <v>1966</v>
@@ -38576,7 +38576,7 @@
         <v>383</v>
       </c>
       <c r="D391" t="s">
-        <v>313</v>
+        <v>324</v>
       </c>
       <c r="E391">
         <v>2015</v>
@@ -38629,7 +38629,7 @@
         <v>383</v>
       </c>
       <c r="D392" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="E392">
         <v>2015</v>
@@ -38682,7 +38682,7 @@
         <v>383</v>
       </c>
       <c r="D393" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="E393">
         <v>1982</v>
@@ -38735,7 +38735,7 @@
         <v>383</v>
       </c>
       <c r="D394" t="s">
-        <v>309</v>
+        <v>318</v>
       </c>
       <c r="E394">
         <v>2015</v>
@@ -38788,7 +38788,7 @@
         <v>383</v>
       </c>
       <c r="D395" t="s">
-        <v>329</v>
+        <v>316</v>
       </c>
       <c r="E395">
         <v>2015</v>
@@ -38841,7 +38841,7 @@
         <v>383</v>
       </c>
       <c r="D396" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="E396">
         <v>1961</v>
@@ -38894,7 +38894,7 @@
         <v>383</v>
       </c>
       <c r="D397" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="E397">
         <v>2005</v>
@@ -38947,7 +38947,7 @@
         <v>383</v>
       </c>
       <c r="D398" t="s">
-        <v>80</v>
+        <v>57</v>
       </c>
       <c r="E398">
         <v>1991</v>
@@ -39106,7 +39106,7 @@
         <v>383</v>
       </c>
       <c r="D401" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="E401">
         <v>1971</v>
@@ -39159,7 +39159,7 @@
         <v>383</v>
       </c>
       <c r="D402" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="E402">
         <v>1973</v>
@@ -39371,7 +39371,7 @@
         <v>383</v>
       </c>
       <c r="D406" t="s">
-        <v>314</v>
+        <v>329</v>
       </c>
       <c r="E406">
         <v>1923</v>
@@ -39424,7 +39424,7 @@
         <v>308</v>
       </c>
       <c r="D407" t="s">
-        <v>320</v>
+        <v>328</v>
       </c>
       <c r="E407">
         <v>1959</v>
@@ -39530,7 +39530,7 @@
         <v>308</v>
       </c>
       <c r="D409" t="s">
-        <v>313</v>
+        <v>324</v>
       </c>
       <c r="E409">
         <v>1949</v>
@@ -39583,7 +39583,7 @@
         <v>308</v>
       </c>
       <c r="D410" t="s">
-        <v>326</v>
+        <v>312</v>
       </c>
       <c r="E410">
         <v>1953</v>
@@ -39689,7 +39689,7 @@
         <v>308</v>
       </c>
       <c r="D412" t="s">
-        <v>313</v>
+        <v>324</v>
       </c>
       <c r="E412">
         <v>1960</v>
@@ -39742,7 +39742,7 @@
         <v>308</v>
       </c>
       <c r="D413" t="s">
-        <v>328</v>
+        <v>317</v>
       </c>
       <c r="E413">
         <v>1962</v>
@@ -39795,7 +39795,7 @@
         <v>308</v>
       </c>
       <c r="D414" t="s">
-        <v>314</v>
+        <v>329</v>
       </c>
       <c r="E414">
         <v>2015</v>
@@ -39848,7 +39848,7 @@
         <v>308</v>
       </c>
       <c r="D415" t="s">
-        <v>327</v>
+        <v>322</v>
       </c>
       <c r="E415">
         <v>1927</v>
@@ -39901,7 +39901,7 @@
         <v>308</v>
       </c>
       <c r="D416" t="s">
-        <v>325</v>
+        <v>311</v>
       </c>
       <c r="E416">
         <v>1954</v>
@@ -40007,7 +40007,7 @@
         <v>308</v>
       </c>
       <c r="D418" t="s">
-        <v>314</v>
+        <v>329</v>
       </c>
       <c r="E418">
         <v>1956</v>
@@ -40060,7 +40060,7 @@
         <v>308</v>
       </c>
       <c r="D419" t="s">
-        <v>309</v>
+        <v>318</v>
       </c>
       <c r="E419">
         <v>1956</v>
@@ -40166,7 +40166,7 @@
         <v>308</v>
       </c>
       <c r="D421" t="s">
-        <v>314</v>
+        <v>329</v>
       </c>
       <c r="E421">
         <v>1960</v>
@@ -40272,7 +40272,7 @@
         <v>308</v>
       </c>
       <c r="D423" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="E423">
         <v>2015</v>
@@ -40378,7 +40378,7 @@
         <v>308</v>
       </c>
       <c r="D425" t="s">
-        <v>327</v>
+        <v>322</v>
       </c>
       <c r="E425">
         <v>2015</v>
@@ -40431,7 +40431,7 @@
         <v>308</v>
       </c>
       <c r="D426" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="E426">
         <v>2015</v>
@@ -40537,7 +40537,7 @@
         <v>308</v>
       </c>
       <c r="D428" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="E428">
         <v>1955</v>
@@ -40590,7 +40590,7 @@
         <v>308</v>
       </c>
       <c r="D429" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E429">
         <v>2015</v>
@@ -40696,7 +40696,7 @@
         <v>308</v>
       </c>
       <c r="D431" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="E431">
         <v>1932</v>
@@ -40855,7 +40855,7 @@
         <v>308</v>
       </c>
       <c r="D434" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="E434">
         <v>1924</v>
@@ -40961,7 +40961,7 @@
         <v>308</v>
       </c>
       <c r="D436" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="E436">
         <v>2002</v>
@@ -41067,7 +41067,7 @@
         <v>308</v>
       </c>
       <c r="D438" t="s">
-        <v>313</v>
+        <v>324</v>
       </c>
       <c r="E438">
         <v>1948</v>
@@ -41120,7 +41120,7 @@
         <v>308</v>
       </c>
       <c r="D439" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="E439">
         <v>2015</v>
@@ -41173,7 +41173,7 @@
         <v>308</v>
       </c>
       <c r="D440" t="s">
-        <v>315</v>
+        <v>326</v>
       </c>
       <c r="E440">
         <v>1914</v>
@@ -41279,7 +41279,7 @@
         <v>308</v>
       </c>
       <c r="D442" t="s">
-        <v>65</v>
+        <v>52</v>
       </c>
       <c r="E442">
         <v>1958</v>
@@ -41332,7 +41332,7 @@
         <v>439</v>
       </c>
       <c r="D443" t="s">
-        <v>59</v>
+        <v>85</v>
       </c>
       <c r="E443">
         <v>1992</v>
@@ -41491,7 +41491,7 @@
         <v>439</v>
       </c>
       <c r="D446" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E446">
         <v>1992</v>
@@ -41544,7 +41544,7 @@
         <v>439</v>
       </c>
       <c r="D447" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E447">
         <v>2005</v>
@@ -41809,7 +41809,7 @@
         <v>439</v>
       </c>
       <c r="D452" t="s">
-        <v>59</v>
+        <v>85</v>
       </c>
       <c r="E452">
         <v>1985</v>
@@ -42049,7 +42049,7 @@
         <v>2022</v>
       </c>
       <c r="F458">
-        <v>6.6457416582336482</v>
+        <v>6.6307854518247753</v>
       </c>
       <c r="G458">
         <v>1</v>
@@ -42078,13 +42078,13 @@
         <v>455</v>
       </c>
       <c r="D459" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="E459">
         <v>2022</v>
       </c>
       <c r="F459">
-        <v>6.6039408899415779</v>
+        <v>6.6457416582336482</v>
       </c>
       <c r="G459">
         <v>1</v>
@@ -42119,7 +42119,7 @@
         <v>2022</v>
       </c>
       <c r="F460">
-        <v>6.6307854518247753</v>
+        <v>6.6039408899415779</v>
       </c>
       <c r="G460">
         <v>1</v>
@@ -42148,7 +42148,7 @@
         <v>455</v>
       </c>
       <c r="D461" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="E461">
         <v>2010</v>
@@ -42183,7 +42183,7 @@
         <v>455</v>
       </c>
       <c r="D462" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="E462">
         <v>2015</v>
@@ -42393,7 +42393,7 @@
         <v>455</v>
       </c>
       <c r="D468" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="E468">
         <v>2015</v>
@@ -44808,7 +44808,7 @@
         <v>510</v>
       </c>
       <c r="D537" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="E537">
         <v>2022</v>
@@ -44843,7 +44843,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="L538">
-        <v>0.20228807173042845</v>
+        <v>0.20228807173042843</v>
       </c>
     </row>
     <row r="539" spans="2:12" x14ac:dyDescent="0.45">
@@ -44860,13 +44860,13 @@
         <v>2022</v>
       </c>
       <c r="F539">
-        <v>0.69928302455480262</v>
+        <v>0.67351932785461166</v>
       </c>
       <c r="G539">
         <v>0.33123000000000002</v>
       </c>
       <c r="L539">
-        <v>0.20228807173042845</v>
+        <v>0.20228807173042843</v>
       </c>
     </row>
     <row r="540" spans="2:12" x14ac:dyDescent="0.45">
@@ -44883,13 +44883,13 @@
         <v>2022</v>
       </c>
       <c r="F540">
-        <v>0.67351932785461166</v>
+        <v>0.69928302455480262</v>
       </c>
       <c r="G540">
         <v>0.33123000000000002</v>
       </c>
       <c r="L540">
-        <v>0.20228807173042845</v>
+        <v>0.20228807173042843</v>
       </c>
     </row>
     <row r="541" spans="2:12" x14ac:dyDescent="0.45">

--- a/VerveStacks_ITA_grids/vt_vervestacks_ITA_v1.xlsx
+++ b/VerveStacks_ITA_grids/vt_vervestacks_ITA_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{02B19417-E4A7-4123-BF7F-758C579AD96C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{6CE3DD1D-3CD3-43CD-8E25-C533BA75AB08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1837" yWindow="1837" windowWidth="21600" windowHeight="12683" xr2:uid="{4D9415D1-E851-435D-A17A-231ED5E047FA}"/>
+    <workbookView xWindow="2573" yWindow="2573" windowWidth="21600" windowHeight="12682" xr2:uid="{D9BF9E88-4B90-411A-AE6D-578E4113968C}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="2" r:id="rId1"/>
@@ -81,30 +81,30 @@
     <t>bioenergy</t>
   </si>
   <si>
+    <t>e_w84696559-380</t>
+  </si>
+  <si>
+    <t>e_w81938081-380</t>
+  </si>
+  <si>
+    <t>e_w109756016-380</t>
+  </si>
+  <si>
+    <t>e_w98902899-380</t>
+  </si>
+  <si>
+    <t>e_w34157795-380</t>
+  </si>
+  <si>
+    <t>e_w108020416-380</t>
+  </si>
+  <si>
     <t>e_w144005863-380</t>
   </si>
   <si>
-    <t>e_w109756016-380</t>
-  </si>
-  <si>
-    <t>e_w81938081-380</t>
-  </si>
-  <si>
-    <t>e_w84696559-380</t>
-  </si>
-  <si>
-    <t>e_w34157795-380</t>
-  </si>
-  <si>
-    <t>e_w108020416-380</t>
-  </si>
-  <si>
     <t>e_w58440884-380</t>
   </si>
   <si>
-    <t>e_w98902899-380</t>
-  </si>
-  <si>
     <t>ep_bioenergy_G100000200236</t>
   </si>
   <si>
@@ -141,18 +141,18 @@
     <t>coal</t>
   </si>
   <si>
+    <t>e_w82767145-380</t>
+  </si>
+  <si>
     <t>e_w409439916-380</t>
   </si>
   <si>
+    <t>e_w303915533-380</t>
+  </si>
+  <si>
     <t>e_w418902800-380</t>
   </si>
   <si>
-    <t>e_w303915533-380</t>
-  </si>
-  <si>
-    <t>e_w82767145-380</t>
-  </si>
-  <si>
     <t>ep_coal_subcritical_G100000102764</t>
   </si>
   <si>
@@ -189,120 +189,120 @@
     <t>gas</t>
   </si>
   <si>
+    <t>e_w411026199-380</t>
+  </si>
+  <si>
+    <t>e_w99826025-380</t>
+  </si>
+  <si>
+    <t>e_w103653592-380</t>
+  </si>
+  <si>
+    <t>e_w109993642-380</t>
+  </si>
+  <si>
+    <t>e_w100407576-380</t>
+  </si>
+  <si>
+    <t>e_w149997403-380</t>
+  </si>
+  <si>
+    <t>e_w432729521-380</t>
+  </si>
+  <si>
+    <t>e_w172302572-380</t>
+  </si>
+  <si>
+    <t>e_w338753171-380</t>
+  </si>
+  <si>
+    <t>e_w162960205-380</t>
+  </si>
+  <si>
+    <t>e_w158739183-380</t>
+  </si>
+  <si>
+    <t>e_w103974940-380</t>
+  </si>
+  <si>
+    <t>e_w414663585-380</t>
+  </si>
+  <si>
+    <t>e_w255011550-380</t>
+  </si>
+  <si>
+    <t>e_w421827453-380</t>
+  </si>
+  <si>
+    <t>e_w105581403-380</t>
+  </si>
+  <si>
+    <t>e_w339104227-380</t>
+  </si>
+  <si>
+    <t>e_w82078641-380</t>
+  </si>
+  <si>
+    <t>e_w61157826-380</t>
+  </si>
+  <si>
+    <t>e_w1137611914-380</t>
+  </si>
+  <si>
+    <t>e_w181125039-380</t>
+  </si>
+  <si>
     <t>e_w133601335-380</t>
   </si>
   <si>
+    <t>e_w103381531-380</t>
+  </si>
+  <si>
+    <t>e_w199675964-380</t>
+  </si>
+  <si>
+    <t>e_w59462715-380</t>
+  </si>
+  <si>
+    <t>e_w82084019-380</t>
+  </si>
+  <si>
+    <t>e_w60725875-380</t>
+  </si>
+  <si>
+    <t>e_w145665799-380</t>
+  </si>
+  <si>
+    <t>e_w98421779-380</t>
+  </si>
+  <si>
+    <t>e_w419423704-380</t>
+  </si>
+  <si>
+    <t>e_w116797658-380</t>
+  </si>
+  <si>
+    <t>e_w105757794-380</t>
+  </si>
+  <si>
+    <t>e_w110330925-380</t>
+  </si>
+  <si>
+    <t>e_w132450233-380</t>
+  </si>
+  <si>
+    <t>e_w162828577-380</t>
+  </si>
+  <si>
     <t>e_w107438024-380</t>
   </si>
   <si>
-    <t>e_w411026199-380</t>
+    <t>e_w98900549-380</t>
   </si>
   <si>
     <t>e_w416989699-380</t>
   </si>
   <si>
-    <t>e_w99826025-380</t>
-  </si>
-  <si>
-    <t>e_w339104227-380</t>
-  </si>
-  <si>
-    <t>e_w82078641-380</t>
-  </si>
-  <si>
-    <t>e_w61157826-380</t>
-  </si>
-  <si>
-    <t>e_w1137611914-380</t>
-  </si>
-  <si>
-    <t>e_w432729521-380</t>
-  </si>
-  <si>
-    <t>e_w172302572-380</t>
-  </si>
-  <si>
-    <t>e_w338753171-380</t>
-  </si>
-  <si>
-    <t>e_w162960205-380</t>
-  </si>
-  <si>
-    <t>e_w158739183-380</t>
-  </si>
-  <si>
-    <t>e_w105757794-380</t>
-  </si>
-  <si>
-    <t>e_w103974940-380</t>
-  </si>
-  <si>
-    <t>e_w59462715-380</t>
-  </si>
-  <si>
-    <t>e_w421827453-380</t>
-  </si>
-  <si>
-    <t>e_w149997403-380</t>
-  </si>
-  <si>
-    <t>e_w100407576-380</t>
-  </si>
-  <si>
-    <t>e_w98421779-380</t>
-  </si>
-  <si>
-    <t>e_w419423704-380</t>
-  </si>
-  <si>
-    <t>e_w116797658-380</t>
-  </si>
-  <si>
-    <t>e_w109993642-380</t>
-  </si>
-  <si>
-    <t>e_w110330925-380</t>
-  </si>
-  <si>
-    <t>e_w103653592-380</t>
-  </si>
-  <si>
-    <t>e_w82084019-380</t>
-  </si>
-  <si>
-    <t>e_w414663585-380</t>
-  </si>
-  <si>
-    <t>e_w255011550-380</t>
-  </si>
-  <si>
-    <t>e_w105581403-380</t>
-  </si>
-  <si>
-    <t>e_w132450233-380</t>
-  </si>
-  <si>
-    <t>e_w162828577-380</t>
-  </si>
-  <si>
-    <t>e_w98900549-380</t>
-  </si>
-  <si>
-    <t>e_w145665799-380</t>
-  </si>
-  <si>
-    <t>e_w60725875-380</t>
-  </si>
-  <si>
-    <t>e_w103381531-380</t>
-  </si>
-  <si>
-    <t>e_w199675964-380</t>
-  </si>
-  <si>
-    <t>e_w181125039-380</t>
-  </si>
-  <si>
     <t>ep_gas_combined_cycle_G100000400339</t>
   </si>
   <si>
@@ -966,69 +966,69 @@
     <t>hydro</t>
   </si>
   <si>
+    <t>e_w64200868-380</t>
+  </si>
+  <si>
+    <t>e_w491424937-380</t>
+  </si>
+  <si>
+    <t>e_w75602396-380</t>
+  </si>
+  <si>
+    <t>e_IT72-380</t>
+  </si>
+  <si>
+    <t>e_w114931087-380</t>
+  </si>
+  <si>
+    <t>e_w1100665914-380</t>
+  </si>
+  <si>
+    <t>e_IT7-380</t>
+  </si>
+  <si>
+    <t>e_IT72-400</t>
+  </si>
+  <si>
+    <t>e_IT93-380</t>
+  </si>
+  <si>
+    <t>e_w61626687-380</t>
+  </si>
+  <si>
+    <t>e_w72466334-380</t>
+  </si>
+  <si>
+    <t>e_IT71-380</t>
+  </si>
+  <si>
+    <t>e_w82083756-380</t>
+  </si>
+  <si>
+    <t>e_w116517585-380</t>
+  </si>
+  <si>
+    <t>e_IT31-380</t>
+  </si>
+  <si>
+    <t>e_w104359058-380</t>
+  </si>
+  <si>
+    <t>e_IT53-380</t>
+  </si>
+  <si>
+    <t>e_IT71-400</t>
+  </si>
+  <si>
     <t>e_IT21-380</t>
   </si>
   <si>
-    <t>e_w114931087-380</t>
-  </si>
-  <si>
-    <t>e_w104359058-380</t>
-  </si>
-  <si>
-    <t>e_w64200868-380</t>
+    <t>e_IT10-380</t>
   </si>
   <si>
     <t>e_IT36-380</t>
   </si>
   <si>
-    <t>e_IT72-400</t>
-  </si>
-  <si>
-    <t>e_IT93-380</t>
-  </si>
-  <si>
-    <t>e_w82083756-380</t>
-  </si>
-  <si>
-    <t>e_w116517585-380</t>
-  </si>
-  <si>
-    <t>e_w491424937-380</t>
-  </si>
-  <si>
-    <t>e_w75602396-380</t>
-  </si>
-  <si>
-    <t>e_IT31-380</t>
-  </si>
-  <si>
-    <t>e_IT10-380</t>
-  </si>
-  <si>
-    <t>e_IT72-380</t>
-  </si>
-  <si>
-    <t>e_IT53-380</t>
-  </si>
-  <si>
-    <t>e_w61626687-380</t>
-  </si>
-  <si>
-    <t>e_IT71-380</t>
-  </si>
-  <si>
-    <t>e_w1100665914-380</t>
-  </si>
-  <si>
-    <t>e_IT71-400</t>
-  </si>
-  <si>
-    <t>e_w72466334-380</t>
-  </si>
-  <si>
-    <t>e_IT7-380</t>
-  </si>
-  <si>
     <t>ep_hydro_dam_G100000602220</t>
   </si>
   <si>
@@ -1407,12 +1407,12 @@
     <t>solar</t>
   </si>
   <si>
+    <t>elc_spv_002</t>
+  </si>
+  <si>
     <t>elc_spv_007</t>
   </si>
   <si>
-    <t>elc_spv_002</t>
-  </si>
-  <si>
     <t>ep_solar_pv_001</t>
   </si>
   <si>
@@ -1554,13 +1554,13 @@
     <t>ep_solar_pv_380</t>
   </si>
   <si>
-    <t>ep_solar_thermal_012</t>
-  </si>
-  <si>
-    <t>ep_solar_thermal_013</t>
-  </si>
-  <si>
-    <t>ep_solar_thermal_014</t>
+    <t>ep_solar_thermal_018</t>
+  </si>
+  <si>
+    <t>ep_solar_thermal_019</t>
+  </si>
+  <si>
+    <t>ep_solar_thermal_022</t>
   </si>
   <si>
     <t>ep_windoff_wind_380</t>
@@ -1698,42 +1698,42 @@
     <t>ele</t>
   </si>
   <si>
+    <t>Aggregated Plant - EMBER Gap - way/58440884-380_Missing Bioenergy Capacity</t>
+  </si>
+  <si>
+    <t>GW</t>
+  </si>
+  <si>
+    <t>TWh</t>
+  </si>
+  <si>
+    <t>daynite</t>
+  </si>
+  <si>
+    <t>yes</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/34157795-380_Missing Bioenergy Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/144005863-380_Missing Bioenergy Capacity</t>
+  </si>
+  <si>
     <t>Aggregated Plant - EMBER Gap - way/109756016-380_Missing Bioenergy Capacity</t>
   </si>
   <si>
-    <t>GW</t>
-  </si>
-  <si>
-    <t>TWh</t>
-  </si>
-  <si>
-    <t>daynite</t>
-  </si>
-  <si>
-    <t>yes</t>
-  </si>
-  <si>
     <t>Aggregated Plant - EMBER Gap - way/98902899-380_Missing Bioenergy Capacity</t>
   </si>
   <si>
-    <t>Aggregated Plant - EMBER Gap - way/144005863-380_Missing Bioenergy Capacity</t>
+    <t>Aggregated Plant - EMBER Gap - way/108020416-380_Missing Bioenergy Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/84696559-380_Missing Bioenergy Capacity</t>
   </si>
   <si>
     <t>Aggregated Plant - EMBER Gap - way/81938081-380_Missing Bioenergy Capacity</t>
   </si>
   <si>
-    <t>Aggregated Plant - EMBER Gap - way/108020416-380_Missing Bioenergy Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/84696559-380_Missing Bioenergy Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/34157795-380_Missing Bioenergy Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/58440884-380_Missing Bioenergy Capacity</t>
-  </si>
-  <si>
     <t>Acerra power station_1</t>
   </si>
   <si>
@@ -1755,18 +1755,18 @@
     <t>Aggregated Plant</t>
   </si>
   <si>
+    <t>Aggregated Plant - EMBER Gap - way/82767145-380_Missing Coal Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/409439916-380_Missing Coal Capacity</t>
+  </si>
+  <si>
     <t>Aggregated Plant - EMBER Gap - way/303915533-380_Missing Coal Capacity</t>
   </si>
   <si>
-    <t>Aggregated Plant - EMBER Gap - way/82767145-380_Missing Coal Capacity</t>
-  </si>
-  <si>
     <t>Aggregated Plant - EMBER Gap - way/418902800-380_Missing Coal Capacity</t>
   </si>
   <si>
-    <t>Aggregated Plant - EMBER Gap - way/409439916-380_Missing Coal Capacity</t>
-  </si>
-  <si>
     <t>Fiume Santo power station_Unit 3</t>
   </si>
   <si>
@@ -1797,126 +1797,126 @@
     <t>Torrevaldaliga Nord power station_Unit 3</t>
   </si>
   <si>
+    <t>Aggregated Plant - EMBER Gap - way/107438024-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/116797658-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/339104227-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/162828577-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/98900549-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/199675964-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/181125039-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/432729521-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/109993642-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/82767145-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/103381531-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/60725875-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/82078641-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/103974940-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/416989699-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/103653592-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/100407576-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/145665799-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/1137611914-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/158739183-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/149997403-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/133601335-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/338753171-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/255011550-380_Missing Gas Capacity</t>
+  </si>
+  <si>
     <t>Aggregated Plant - EMBER Gap - way/172302572-380_Missing Gas Capacity</t>
   </si>
   <si>
+    <t>Aggregated Plant - EMBER Gap - way/105757794-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/59462715-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/414663585-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/61157826-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/419423704-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/132450233-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/421827453-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/99826025-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/110330925-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/98421779-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/82084019-380_Missing Gas Capacity</t>
+  </si>
+  <si>
     <t>Aggregated Plant - EMBER Gap - way/105581403-380_Missing Gas Capacity</t>
   </si>
   <si>
+    <t>Aggregated Plant - EMBER Gap - way/109756016-380_Missing Gas Capacity</t>
+  </si>
+  <si>
     <t>Aggregated Plant - EMBER Gap - way/411026199-380_Missing Gas Capacity</t>
   </si>
   <si>
-    <t>Aggregated Plant - EMBER Gap - way/60725875-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/109756016-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/82084019-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/116797658-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/339104227-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/98421779-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/107438024-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/99826025-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/110330925-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/421827453-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/105757794-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/255011550-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/59462715-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/109993642-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/82767145-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/158739183-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/132450233-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/1137611914-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/145665799-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/103974940-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/82078641-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/133601335-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/149997403-380_Missing Gas Capacity</t>
-  </si>
-  <si>
     <t>Aggregated Plant - EMBER Gap - way/162960205-380_Missing Gas Capacity</t>
   </si>
   <si>
-    <t>Aggregated Plant - EMBER Gap - way/416989699-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/103653592-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/100407576-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/162828577-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/338753171-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/98900549-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/61157826-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/419423704-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/414663585-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/181125039-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/199675964-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/432729521-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/103381531-380_Missing Gas Capacity</t>
-  </si>
-  <si>
     <t>Altomonte power station_1</t>
   </si>
   <si>
@@ -2229,102 +2229,102 @@
     <t>Valle Secolo geothermal power plant_2</t>
   </si>
   <si>
+    <t>Aggregated Plant - IRENA Gap - IT72-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
     <t>Aggregated Plant - IRENA Gap - way/1100665914-380_Missing Hydro Capacity</t>
   </si>
   <si>
+    <t>Aggregated Plant - IRENA Gap - way/59462263-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - IT30-500_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - IT7-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/339703159-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/61712456-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - IT53-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/75602396-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/109588422-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - IT72-400_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/1137611914-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/104359058-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/338753171-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - IT93-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - IT10-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/419423704-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/491424937-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/72466334-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/82083756-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/114931087-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - IT31-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/64200868-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/144005863-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/116517585-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/96190189-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - IT21-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - IT36-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - IT71-400_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - IT71-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
     <t>Aggregated Plant - IRENA Gap - way/108020416-380_Missing Hydro Capacity</t>
   </si>
   <si>
-    <t>Aggregated Plant - IRENA Gap - IT71-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/75602396-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - IT21-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/144005863-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - IT36-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - IT71-400_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/59462263-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - IT72-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - IT7-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - IT30-500_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/61712456-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - IT53-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/339703159-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/419423704-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/82083756-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/72466334-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/104359058-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/491424937-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/116517585-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/96190189-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/338753171-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - IT93-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - IT10-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - IT31-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/114931087-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
     <t>Aggregated Plant - IRENA Gap - way/61626687-380_Missing Hydro Capacity</t>
   </si>
   <si>
-    <t>Aggregated Plant - IRENA Gap - way/64200868-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - IT72-400_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/1137611914-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/109588422-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
     <t>Baschi hydroelectric plant_</t>
   </si>
   <si>
@@ -2619,27 +2619,27 @@
     <t>San Filippo del Mela power station_1</t>
   </si>
   <si>
+    <t>Aggregated Plant - IRENA Gap - ITA_42_Missing Solar Capacity</t>
+  </si>
+  <si>
+    <t>annual</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - ITA_30_Missing Solar Capacity</t>
+  </si>
+  <si>
     <t>Aggregated Plant - IRENA Gap - ITA_68_Missing Solar Capacity</t>
   </si>
   <si>
-    <t>annual</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - ITA_42_Missing Solar Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - ITA_30_Missing Solar Capacity</t>
+    <t>Aggregated Plant - IRENA Gap - ITA_96_Missing Onshore wind energy Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - ITA_73_Missing Onshore wind energy Capacity</t>
   </si>
   <si>
     <t>Aggregated Plant - IRENA Gap - ITA_22_Missing Onshore wind energy Capacity</t>
   </si>
   <si>
-    <t>Aggregated Plant - IRENA Gap - ITA_96_Missing Onshore wind energy Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - ITA_73_Missing Onshore wind energy Capacity</t>
-  </si>
-  <si>
     <t>AF</t>
   </si>
   <si>
@@ -3231,12 +3231,12 @@
     <t>ccs retrofit of -- Sulcis power station_Unit 3</t>
   </si>
   <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/418902800-380_Missing Coal Capacity</t>
+  </si>
+  <si>
     <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/409439916-380_Missing Coal Capacity</t>
   </si>
   <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/418902800-380_Missing Coal Capacity</t>
-  </si>
-  <si>
     <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/82767145-380_Missing Coal Capacity</t>
   </si>
   <si>
@@ -3531,124 +3531,124 @@
     <t>ccs retrofit of -- Aggregated Plant</t>
   </si>
   <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/145665799-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/339104227-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/158739183-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/133601335-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/181125039-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/416989699-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/162828577-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/82767145-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/105757794-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/99826025-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/103974940-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/199675964-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/82078641-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/103653592-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/1137611914-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/172302572-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/255011550-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/105581403-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/103381531-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/109756016-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/411026199-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/107438024-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/98900549-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/116797658-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/338753171-380_Missing Gas Capacity</t>
+  </si>
+  <si>
     <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/110330925-380_Missing Gas Capacity</t>
   </si>
   <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/338753171-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/339104227-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/158739183-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/133601335-380_Missing Gas Capacity</t>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/414663585-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/60725875-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/421827453-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/82084019-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/100407576-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/149997403-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/132450233-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/419423704-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/162960205-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/432729521-380_Missing Gas Capacity</t>
   </si>
   <si>
     <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/61157826-380_Missing Gas Capacity</t>
   </si>
   <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/1137611914-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/132450233-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/100407576-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/162828577-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/82767145-380_Missing Gas Capacity</t>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/109993642-380_Missing Gas Capacity</t>
   </si>
   <si>
     <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/59462715-380_Missing Gas Capacity</t>
   </si>
   <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/109993642-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/103974940-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/172302572-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/411026199-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/109756016-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/103381531-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/99826025-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/105757794-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/416989699-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/60725875-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/82084019-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/421827453-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/145665799-380_Missing Gas Capacity</t>
-  </si>
-  <si>
     <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/98421779-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/98900549-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/162960205-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/419423704-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/432729521-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/149997403-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/116797658-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/414663585-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/107438024-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/82078641-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/103653592-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/199675964-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/105581403-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/255011550-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/181125039-380_Missing Gas Capacity</t>
   </si>
   <si>
     <t>ccs retrofit of -- Tavazzano power station_CCGT8, timepoint 1</t>
@@ -4052,7 +4052,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{12AE61B0-6BFF-4435-8F4C-1C882796FFA7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F04A458-1947-47EC-9E68-C8F9B7C9FF47}">
   <dimension ref="B9:T278"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -4128,7 +4128,7 @@
         <v>33</v>
       </c>
       <c r="D11" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E11">
         <v>0.12764790000000001</v>
@@ -4184,7 +4184,7 @@
         <v>33</v>
       </c>
       <c r="D12" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E12">
         <v>0.12764790000000001</v>
@@ -4576,7 +4576,7 @@
         <v>33</v>
       </c>
       <c r="D19" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E19">
         <v>0.260522535</v>
@@ -4632,7 +4632,7 @@
         <v>33</v>
       </c>
       <c r="D20" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E20">
         <v>0.260522535</v>
@@ -4688,7 +4688,7 @@
         <v>33</v>
       </c>
       <c r="D21" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E21">
         <v>0.260522535</v>
@@ -4744,7 +4744,7 @@
         <v>33</v>
       </c>
       <c r="D22" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E22">
         <v>0.28056272999999998</v>
@@ -4800,7 +4800,7 @@
         <v>33</v>
       </c>
       <c r="D23" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E23">
         <v>0.28056272999999998</v>
@@ -4856,7 +4856,7 @@
         <v>33</v>
       </c>
       <c r="D24" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E24">
         <v>0.28056272999999998</v>
@@ -4912,7 +4912,7 @@
         <v>49</v>
       </c>
       <c r="D25" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="E25">
         <v>0.41750406250000005</v>
@@ -4968,7 +4968,7 @@
         <v>49</v>
       </c>
       <c r="D26" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="E26">
         <v>0.44431624999999997</v>
@@ -5024,7 +5024,7 @@
         <v>49</v>
       </c>
       <c r="D27" t="s">
-        <v>69</v>
+        <v>54</v>
       </c>
       <c r="E27">
         <v>0.38303124999999993</v>
@@ -5080,7 +5080,7 @@
         <v>49</v>
       </c>
       <c r="D28" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="E28">
         <v>0.44431624999999997</v>
@@ -5136,7 +5136,7 @@
         <v>49</v>
       </c>
       <c r="D29" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="E29">
         <v>0.41750406249999999</v>
@@ -5192,7 +5192,7 @@
         <v>49</v>
       </c>
       <c r="D30" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="E30">
         <v>0.41750406249999999</v>
@@ -5248,7 +5248,7 @@
         <v>49</v>
       </c>
       <c r="D31" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="E31">
         <v>0.41750406249999999</v>
@@ -5360,7 +5360,7 @@
         <v>49</v>
       </c>
       <c r="D33" t="s">
-        <v>50</v>
+        <v>71</v>
       </c>
       <c r="E33">
         <v>0.41750406249999999</v>
@@ -5528,7 +5528,7 @@
         <v>49</v>
       </c>
       <c r="D36" t="s">
-        <v>79</v>
+        <v>65</v>
       </c>
       <c r="E36">
         <v>0.41750406249999999</v>
@@ -5584,7 +5584,7 @@
         <v>49</v>
       </c>
       <c r="D37" t="s">
-        <v>79</v>
+        <v>65</v>
       </c>
       <c r="E37">
         <v>0.41750406249999999</v>
@@ -5640,7 +5640,7 @@
         <v>49</v>
       </c>
       <c r="D38" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="E38">
         <v>0.41750406249999999</v>
@@ -5696,7 +5696,7 @@
         <v>49</v>
       </c>
       <c r="D39" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="E39">
         <v>0.41750406249999999</v>
@@ -5752,7 +5752,7 @@
         <v>49</v>
       </c>
       <c r="D40" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="E40">
         <v>0.3983525</v>
@@ -5808,7 +5808,7 @@
         <v>49</v>
       </c>
       <c r="D41" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="E41">
         <v>0.41750406249999999</v>
@@ -5864,7 +5864,7 @@
         <v>49</v>
       </c>
       <c r="D42" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="E42">
         <v>0.41750406249999999</v>
@@ -5920,7 +5920,7 @@
         <v>49</v>
       </c>
       <c r="D43" t="s">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="E43">
         <v>0.41750406249999999</v>
@@ -5976,7 +5976,7 @@
         <v>49</v>
       </c>
       <c r="D44" t="s">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="E44">
         <v>0.41750406249999999</v>
@@ -6032,7 +6032,7 @@
         <v>49</v>
       </c>
       <c r="D45" t="s">
-        <v>51</v>
+        <v>85</v>
       </c>
       <c r="E45">
         <v>0.41750406249999999</v>
@@ -6088,7 +6088,7 @@
         <v>49</v>
       </c>
       <c r="D46" t="s">
-        <v>51</v>
+        <v>85</v>
       </c>
       <c r="E46">
         <v>0.41750406249999999</v>
@@ -6144,7 +6144,7 @@
         <v>49</v>
       </c>
       <c r="D47" t="s">
-        <v>51</v>
+        <v>85</v>
       </c>
       <c r="E47">
         <v>0.41750406249999999</v>
@@ -6200,7 +6200,7 @@
         <v>49</v>
       </c>
       <c r="D48" t="s">
-        <v>51</v>
+        <v>85</v>
       </c>
       <c r="E48">
         <v>0.41750406249999999</v>
@@ -6256,7 +6256,7 @@
         <v>49</v>
       </c>
       <c r="D49" t="s">
-        <v>64</v>
+        <v>81</v>
       </c>
       <c r="E49">
         <v>0.40218281250000004</v>
@@ -6312,7 +6312,7 @@
         <v>49</v>
       </c>
       <c r="D50" t="s">
-        <v>64</v>
+        <v>81</v>
       </c>
       <c r="E50">
         <v>0.40218281250000004</v>
@@ -6368,7 +6368,7 @@
         <v>49</v>
       </c>
       <c r="D51" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="E51">
         <v>0.41750406249999999</v>
@@ -6424,7 +6424,7 @@
         <v>49</v>
       </c>
       <c r="D52" t="s">
-        <v>69</v>
+        <v>54</v>
       </c>
       <c r="E52">
         <v>0.45963749999999998</v>
@@ -6480,7 +6480,7 @@
         <v>49</v>
       </c>
       <c r="D53" t="s">
-        <v>69</v>
+        <v>54</v>
       </c>
       <c r="E53">
         <v>0.41750406249999999</v>
@@ -6592,7 +6592,7 @@
         <v>49</v>
       </c>
       <c r="D55" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="E55">
         <v>0.41750406249999999</v>
@@ -6648,7 +6648,7 @@
         <v>49</v>
       </c>
       <c r="D56" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E56">
         <v>0.41750406249999999</v>
@@ -6704,7 +6704,7 @@
         <v>49</v>
       </c>
       <c r="D57" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E57">
         <v>0.41750406249999999</v>
@@ -6760,7 +6760,7 @@
         <v>49</v>
       </c>
       <c r="D58" t="s">
-        <v>53</v>
+        <v>87</v>
       </c>
       <c r="E58">
         <v>0.40218281249999999</v>
@@ -6816,7 +6816,7 @@
         <v>49</v>
       </c>
       <c r="D59" t="s">
-        <v>53</v>
+        <v>87</v>
       </c>
       <c r="E59">
         <v>0.40218281249999999</v>
@@ -6872,7 +6872,7 @@
         <v>49</v>
       </c>
       <c r="D60" t="s">
-        <v>53</v>
+        <v>87</v>
       </c>
       <c r="E60">
         <v>0.38303124999999993</v>
@@ -6928,7 +6928,7 @@
         <v>49</v>
       </c>
       <c r="D61" t="s">
-        <v>53</v>
+        <v>87</v>
       </c>
       <c r="E61">
         <v>0.38303124999999993</v>
@@ -7040,7 +7040,7 @@
         <v>49</v>
       </c>
       <c r="D63" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="E63">
         <v>0.41750406249999999</v>
@@ -7096,7 +7096,7 @@
         <v>49</v>
       </c>
       <c r="D64" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="E64">
         <v>0.41750406249999999</v>
@@ -7152,7 +7152,7 @@
         <v>49</v>
       </c>
       <c r="D65" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="E65">
         <v>0.41750406249999999</v>
@@ -7208,7 +7208,7 @@
         <v>49</v>
       </c>
       <c r="D66" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="E66">
         <v>0.41750406249999999</v>
@@ -7376,7 +7376,7 @@
         <v>49</v>
       </c>
       <c r="D69" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="E69">
         <v>0.41750406249999999</v>
@@ -7432,7 +7432,7 @@
         <v>49</v>
       </c>
       <c r="D70" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="E70">
         <v>0.41750406249999999</v>
@@ -7488,7 +7488,7 @@
         <v>49</v>
       </c>
       <c r="D71" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="E71">
         <v>0.41750406249999999</v>
@@ -7544,7 +7544,7 @@
         <v>49</v>
       </c>
       <c r="D72" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="E72">
         <v>0.41750406249999999</v>
@@ -7600,7 +7600,7 @@
         <v>49</v>
       </c>
       <c r="D73" t="s">
-        <v>73</v>
+        <v>53</v>
       </c>
       <c r="E73">
         <v>0.41750406249999999</v>
@@ -7656,7 +7656,7 @@
         <v>49</v>
       </c>
       <c r="D74" t="s">
-        <v>73</v>
+        <v>53</v>
       </c>
       <c r="E74">
         <v>0.41750406249999999</v>
@@ -7712,7 +7712,7 @@
         <v>49</v>
       </c>
       <c r="D75" t="s">
-        <v>77</v>
+        <v>62</v>
       </c>
       <c r="E75">
         <v>0.42899500000000002</v>
@@ -7768,7 +7768,7 @@
         <v>49</v>
       </c>
       <c r="D76" t="s">
-        <v>87</v>
+        <v>70</v>
       </c>
       <c r="E76">
         <v>0.41750406249999999</v>
@@ -7824,7 +7824,7 @@
         <v>49</v>
       </c>
       <c r="D77" t="s">
-        <v>87</v>
+        <v>70</v>
       </c>
       <c r="E77">
         <v>0.41750406249999999</v>
@@ -7992,7 +7992,7 @@
         <v>49</v>
       </c>
       <c r="D80" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E80">
         <v>0.41750406249999999</v>
@@ -8048,7 +8048,7 @@
         <v>49</v>
       </c>
       <c r="D81" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E81">
         <v>0.41750406249999999</v>
@@ -8104,7 +8104,7 @@
         <v>49</v>
       </c>
       <c r="D82" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E82">
         <v>0.41750406249999999</v>
@@ -8160,7 +8160,7 @@
         <v>49</v>
       </c>
       <c r="D83" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E83">
         <v>0.41750406249999999</v>
@@ -8216,7 +8216,7 @@
         <v>49</v>
       </c>
       <c r="D84" t="s">
-        <v>86</v>
+        <v>73</v>
       </c>
       <c r="E84">
         <v>0.41750406249999999</v>
@@ -8272,7 +8272,7 @@
         <v>49</v>
       </c>
       <c r="D85" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="E85">
         <v>0.41750406249999999</v>
@@ -8328,7 +8328,7 @@
         <v>49</v>
       </c>
       <c r="D86" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="E86">
         <v>0.41750406249999999</v>
@@ -8384,7 +8384,7 @@
         <v>49</v>
       </c>
       <c r="D87" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="E87">
         <v>0.41750406249999999</v>
@@ -8440,7 +8440,7 @@
         <v>49</v>
       </c>
       <c r="D88" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="E88">
         <v>0.41750406249999999</v>
@@ -8496,7 +8496,7 @@
         <v>49</v>
       </c>
       <c r="D89" t="s">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="E89">
         <v>0.44431624999999997</v>
@@ -8552,7 +8552,7 @@
         <v>49</v>
       </c>
       <c r="D90" t="s">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="E90">
         <v>0.41750406249999999</v>
@@ -8608,7 +8608,7 @@
         <v>49</v>
       </c>
       <c r="D91" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E91">
         <v>0.41750406249999999</v>
@@ -8664,7 +8664,7 @@
         <v>49</v>
       </c>
       <c r="D92" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="E92">
         <v>0.44431624999999997</v>
@@ -8720,7 +8720,7 @@
         <v>49</v>
       </c>
       <c r="D93" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E93">
         <v>0.41750406249999999</v>
@@ -8776,7 +8776,7 @@
         <v>49</v>
       </c>
       <c r="D94" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E94">
         <v>0.41750406249999999</v>
@@ -8832,7 +8832,7 @@
         <v>49</v>
       </c>
       <c r="D95" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="E95">
         <v>0.41750406249999999</v>
@@ -8888,7 +8888,7 @@
         <v>49</v>
       </c>
       <c r="D96" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="E96">
         <v>0.41750406249999999</v>
@@ -8944,7 +8944,7 @@
         <v>49</v>
       </c>
       <c r="D97" t="s">
-        <v>75</v>
+        <v>52</v>
       </c>
       <c r="E97">
         <v>0.41750406249999999</v>
@@ -9056,7 +9056,7 @@
         <v>49</v>
       </c>
       <c r="D99" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="E99">
         <v>0.45963749999999998</v>
@@ -9112,7 +9112,7 @@
         <v>49</v>
       </c>
       <c r="D100" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="E100">
         <v>0.45963749999999998</v>
@@ -9168,7 +9168,7 @@
         <v>49</v>
       </c>
       <c r="D101" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="E101">
         <v>0.45963749999999998</v>
@@ -9224,7 +9224,7 @@
         <v>49</v>
       </c>
       <c r="D102" t="s">
-        <v>68</v>
+        <v>55</v>
       </c>
       <c r="E102">
         <v>0.41750406249999999</v>
@@ -9280,7 +9280,7 @@
         <v>49</v>
       </c>
       <c r="D103" t="s">
-        <v>68</v>
+        <v>55</v>
       </c>
       <c r="E103">
         <v>0.41750406249999999</v>
@@ -9336,7 +9336,7 @@
         <v>49</v>
       </c>
       <c r="D104" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="E104">
         <v>0.41750406249999999</v>
@@ -9392,7 +9392,7 @@
         <v>49</v>
       </c>
       <c r="D105" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="E105">
         <v>0.41750406249999999</v>
@@ -9448,7 +9448,7 @@
         <v>49</v>
       </c>
       <c r="D106" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="E106">
         <v>0.38303124999999993</v>
@@ -9504,7 +9504,7 @@
         <v>49</v>
       </c>
       <c r="D107" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="E107">
         <v>0.38303124999999993</v>
@@ -9560,7 +9560,7 @@
         <v>49</v>
       </c>
       <c r="D108" t="s">
-        <v>85</v>
+        <v>72</v>
       </c>
       <c r="E108">
         <v>0.4021828125000001</v>
@@ -9672,7 +9672,7 @@
         <v>49</v>
       </c>
       <c r="D110" t="s">
-        <v>78</v>
+        <v>63</v>
       </c>
       <c r="E110">
         <v>0.41750406249999999</v>
@@ -9728,7 +9728,7 @@
         <v>49</v>
       </c>
       <c r="D111" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="E111">
         <v>0.3983525</v>
@@ -9840,7 +9840,7 @@
         <v>49</v>
       </c>
       <c r="D113" t="s">
-        <v>77</v>
+        <v>62</v>
       </c>
       <c r="E113">
         <v>0.41750406249999999</v>
@@ -10344,7 +10344,7 @@
         <v>49</v>
       </c>
       <c r="D122" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E122">
         <v>0.45963749999999998</v>
@@ -10400,7 +10400,7 @@
         <v>49</v>
       </c>
       <c r="D123" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E123">
         <v>0.45963749999999998</v>
@@ -10456,7 +10456,7 @@
         <v>49</v>
       </c>
       <c r="D124" t="s">
-        <v>15</v>
+        <v>77</v>
       </c>
       <c r="E124">
         <v>0.45963749999999998</v>
@@ -11072,7 +11072,7 @@
         <v>49</v>
       </c>
       <c r="D135" t="s">
-        <v>80</v>
+        <v>16</v>
       </c>
       <c r="E135">
         <v>0.45963749999999998</v>
@@ -11688,7 +11688,7 @@
         <v>49</v>
       </c>
       <c r="D146" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E146">
         <v>0.45963749999999998</v>
@@ -12192,7 +12192,7 @@
         <v>49</v>
       </c>
       <c r="D155" t="s">
-        <v>37</v>
+        <v>82</v>
       </c>
       <c r="E155">
         <v>0.45963749999999998</v>
@@ -12304,7 +12304,7 @@
         <v>49</v>
       </c>
       <c r="D157" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E157">
         <v>0.45963749999999998</v>
@@ -12360,7 +12360,7 @@
         <v>49</v>
       </c>
       <c r="D158" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E158">
         <v>0.45963749999999998</v>
@@ -12416,7 +12416,7 @@
         <v>49</v>
       </c>
       <c r="D159" t="s">
-        <v>84</v>
+        <v>34</v>
       </c>
       <c r="E159">
         <v>0.45963749999999998</v>
@@ -12696,7 +12696,7 @@
         <v>49</v>
       </c>
       <c r="D164" t="s">
-        <v>85</v>
+        <v>72</v>
       </c>
       <c r="E164">
         <v>0.41367375000000001</v>
@@ -13536,7 +13536,7 @@
         <v>49</v>
       </c>
       <c r="D179" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="E179">
         <v>0.39835250000000011</v>
@@ -13592,7 +13592,7 @@
         <v>49</v>
       </c>
       <c r="D180" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="E180">
         <v>0.39835250000000011</v>
@@ -13816,7 +13816,7 @@
         <v>49</v>
       </c>
       <c r="D184" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="E184">
         <v>0.41367375000000001</v>
@@ -13872,7 +13872,7 @@
         <v>49</v>
       </c>
       <c r="D185" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="E185">
         <v>0.41367375000000001</v>
@@ -14600,7 +14600,7 @@
         <v>49</v>
       </c>
       <c r="D198" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E198">
         <v>0.42899500000000002</v>
@@ -14824,7 +14824,7 @@
         <v>49</v>
       </c>
       <c r="D202" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="E202">
         <v>0.3983525</v>
@@ -15552,7 +15552,7 @@
         <v>49</v>
       </c>
       <c r="D215" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E215">
         <v>0.38303124999999993</v>
@@ -15720,7 +15720,7 @@
         <v>49</v>
       </c>
       <c r="D218" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="E218">
         <v>0.42899499999999996</v>
@@ -15776,7 +15776,7 @@
         <v>49</v>
       </c>
       <c r="D219" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="E219">
         <v>0.42899499999999996</v>
@@ -15944,7 +15944,7 @@
         <v>49</v>
       </c>
       <c r="D222" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E222">
         <v>0.38303124999999993</v>
@@ -16000,7 +16000,7 @@
         <v>49</v>
       </c>
       <c r="D223" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="E223">
         <v>0.25280062500000006</v>
@@ -16056,7 +16056,7 @@
         <v>49</v>
       </c>
       <c r="D224" t="s">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="E224">
         <v>0.24514000000000002</v>
@@ -16112,7 +16112,7 @@
         <v>49</v>
       </c>
       <c r="D225" t="s">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="E225">
         <v>0.24514000000000002</v>
@@ -16168,7 +16168,7 @@
         <v>49</v>
       </c>
       <c r="D226" t="s">
-        <v>77</v>
+        <v>62</v>
       </c>
       <c r="E226">
         <v>0.21066718750000002</v>
@@ -16672,7 +16672,7 @@
         <v>49</v>
       </c>
       <c r="D235" t="s">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="E235">
         <v>0.21449750000000001</v>
@@ -16952,7 +16952,7 @@
         <v>49</v>
       </c>
       <c r="D240" t="s">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="E240">
         <v>0.23747937499999999</v>
@@ -17064,7 +17064,7 @@
         <v>49</v>
       </c>
       <c r="D242" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="E242">
         <v>0.21449750000000001</v>
@@ -17260,7 +17260,7 @@
         <v>49</v>
       </c>
       <c r="D247" t="s">
-        <v>50</v>
+        <v>71</v>
       </c>
       <c r="E247">
         <v>0.27578249999999999</v>
@@ -17330,7 +17330,7 @@
         <v>49</v>
       </c>
       <c r="D249" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E249">
         <v>0.27578249999999999</v>
@@ -17470,7 +17470,7 @@
         <v>49</v>
       </c>
       <c r="D253" t="s">
-        <v>85</v>
+        <v>72</v>
       </c>
       <c r="E253">
         <v>0.23747937499999999</v>
@@ -17505,7 +17505,7 @@
         <v>49</v>
       </c>
       <c r="D254" t="s">
-        <v>85</v>
+        <v>72</v>
       </c>
       <c r="E254">
         <v>0.23747937499999999</v>
@@ -17540,7 +17540,7 @@
         <v>49</v>
       </c>
       <c r="D255" t="s">
-        <v>85</v>
+        <v>72</v>
       </c>
       <c r="E255">
         <v>0.23747937499999999</v>
@@ -17575,7 +17575,7 @@
         <v>49</v>
       </c>
       <c r="D256" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="E256">
         <v>0.26429156249999997</v>
@@ -17610,7 +17610,7 @@
         <v>49</v>
       </c>
       <c r="D257" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="E257">
         <v>0.23747937499999999</v>
@@ -17645,7 +17645,7 @@
         <v>49</v>
       </c>
       <c r="D258" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="E258">
         <v>0.23747937499999999</v>
@@ -17680,7 +17680,7 @@
         <v>49</v>
       </c>
       <c r="D259" t="s">
-        <v>78</v>
+        <v>63</v>
       </c>
       <c r="E259">
         <v>0.22215812499999998</v>
@@ -17715,7 +17715,7 @@
         <v>49</v>
       </c>
       <c r="D260" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E260">
         <v>0.24514000000000002</v>
@@ -17750,7 +17750,7 @@
         <v>49</v>
       </c>
       <c r="D261" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E261">
         <v>0.24514000000000002</v>
@@ -17785,7 +17785,7 @@
         <v>49</v>
       </c>
       <c r="D262" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E262">
         <v>0.24514000000000002</v>
@@ -17855,7 +17855,7 @@
         <v>439</v>
       </c>
       <c r="D264" t="s">
-        <v>69</v>
+        <v>54</v>
       </c>
       <c r="E264">
         <v>0.35238875000000003</v>
@@ -17995,7 +17995,7 @@
         <v>439</v>
       </c>
       <c r="D268" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E268">
         <v>0.206836875</v>
@@ -18170,7 +18170,7 @@
         <v>439</v>
       </c>
       <c r="D273" t="s">
-        <v>69</v>
+        <v>54</v>
       </c>
       <c r="E273">
         <v>0.23747937499999999</v>
@@ -18378,7 +18378,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5FFA0BA0-7383-4C33-BB64-FBC13B8D60AD}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3CBAE07D-F4BC-460B-B273-31EFE364FCF9}">
   <dimension ref="B9:T672"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -18460,19 +18460,19 @@
         <v>2022</v>
       </c>
       <c r="F11">
-        <v>0.22450847457627116</v>
+        <v>1.0679322033898306</v>
       </c>
       <c r="G11">
-        <v>0.28891500000000003</v>
+        <v>0.306425</v>
       </c>
       <c r="H11">
-        <v>4427.5</v>
+        <v>3850.0000000000005</v>
       </c>
       <c r="I11">
-        <v>157.30000000000001</v>
+        <v>143</v>
       </c>
       <c r="J11">
-        <v>9.240000000000002</v>
+        <v>8.4</v>
       </c>
       <c r="K11">
         <v>50</v>
@@ -18513,19 +18513,19 @@
         <v>2022</v>
       </c>
       <c r="F12">
-        <v>0.27911864406779663</v>
+        <v>0.49149152542372881</v>
       </c>
       <c r="G12">
-        <v>0.28891500000000003</v>
+        <v>0.306425</v>
       </c>
       <c r="H12">
-        <v>4427.5</v>
+        <v>3850.0000000000005</v>
       </c>
       <c r="I12">
-        <v>157.30000000000001</v>
+        <v>143</v>
       </c>
       <c r="J12">
-        <v>9.240000000000002</v>
+        <v>8.4</v>
       </c>
       <c r="K12">
         <v>50</v>
@@ -18566,19 +18566,19 @@
         <v>2022</v>
       </c>
       <c r="F13">
-        <v>0.49149152542372881</v>
+        <v>0.27911864406779663</v>
       </c>
       <c r="G13">
-        <v>0.306425</v>
+        <v>0.28891500000000003</v>
       </c>
       <c r="H13">
-        <v>3850.0000000000005</v>
+        <v>4427.5</v>
       </c>
       <c r="I13">
-        <v>143</v>
+        <v>157.30000000000001</v>
       </c>
       <c r="J13">
-        <v>8.4</v>
+        <v>9.240000000000002</v>
       </c>
       <c r="K13">
         <v>50</v>
@@ -18619,7 +18619,7 @@
         <v>2022</v>
       </c>
       <c r="F14">
-        <v>1.0679322033898306</v>
+        <v>0.39440677966101695</v>
       </c>
       <c r="G14">
         <v>0.306425</v>
@@ -18778,19 +18778,19 @@
         <v>2022</v>
       </c>
       <c r="F17">
-        <v>0.51576271186440681</v>
+        <v>0.22450847457627116</v>
       </c>
       <c r="G17">
-        <v>0.306425</v>
+        <v>0.28891500000000003</v>
       </c>
       <c r="H17">
-        <v>3850.0000000000005</v>
+        <v>4427.5</v>
       </c>
       <c r="I17">
-        <v>143</v>
+        <v>157.30000000000001</v>
       </c>
       <c r="J17">
-        <v>8.4</v>
+        <v>9.240000000000002</v>
       </c>
       <c r="K17">
         <v>50</v>
@@ -18831,7 +18831,7 @@
         <v>2022</v>
       </c>
       <c r="F18">
-        <v>0.39440677966101695</v>
+        <v>0.51576271186440681</v>
       </c>
       <c r="G18">
         <v>0.306425</v>
@@ -18878,7 +18878,7 @@
         <v>13</v>
       </c>
       <c r="D19" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E19">
         <v>2008</v>
@@ -18931,7 +18931,7 @@
         <v>13</v>
       </c>
       <c r="D20" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E20">
         <v>1998</v>
@@ -18984,7 +18984,7 @@
         <v>13</v>
       </c>
       <c r="D21" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E21">
         <v>2008</v>
@@ -19090,7 +19090,7 @@
         <v>13</v>
       </c>
       <c r="D23" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="E23">
         <v>2013</v>
@@ -19196,7 +19196,7 @@
         <v>13</v>
       </c>
       <c r="D25" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E25">
         <v>2003</v>
@@ -19249,7 +19249,7 @@
         <v>13</v>
       </c>
       <c r="D26" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="E26">
         <v>2009</v>
@@ -19302,7 +19302,7 @@
         <v>13</v>
       </c>
       <c r="D27" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E27">
         <v>2018</v>
@@ -19355,7 +19355,7 @@
         <v>13</v>
       </c>
       <c r="D28" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E28">
         <v>2009</v>
@@ -19414,19 +19414,19 @@
         <v>2022</v>
       </c>
       <c r="F29">
-        <v>0.1997687861271675</v>
+        <v>0.61803468208092449</v>
       </c>
       <c r="G29">
-        <v>0.29766999999999999</v>
+        <v>0.31518000000000002</v>
       </c>
       <c r="H29">
-        <v>2530</v>
+        <v>2200</v>
       </c>
       <c r="I29">
-        <v>72.600000000000009</v>
+        <v>66</v>
       </c>
       <c r="J29">
-        <v>5.7750000000000004</v>
+        <v>5.25</v>
       </c>
       <c r="K29">
         <v>50</v>
@@ -19467,19 +19467,19 @@
         <v>2022</v>
       </c>
       <c r="F30">
-        <v>0.61803468208092449</v>
+        <v>0.1997687861271675</v>
       </c>
       <c r="G30">
-        <v>0.31518000000000002</v>
+        <v>0.29766999999999999</v>
       </c>
       <c r="H30">
-        <v>2200</v>
+        <v>2530</v>
       </c>
       <c r="I30">
-        <v>66</v>
+        <v>72.600000000000009</v>
       </c>
       <c r="J30">
-        <v>5.25</v>
+        <v>5.7750000000000004</v>
       </c>
       <c r="K30">
         <v>50</v>
@@ -19620,7 +19620,7 @@
         <v>33</v>
       </c>
       <c r="D33" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E33">
         <v>1992</v>
@@ -19673,7 +19673,7 @@
         <v>33</v>
       </c>
       <c r="D34" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E34">
         <v>1993</v>
@@ -19832,7 +19832,7 @@
         <v>33</v>
       </c>
       <c r="D37" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E37">
         <v>1991</v>
@@ -19885,7 +19885,7 @@
         <v>33</v>
       </c>
       <c r="D38" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E38">
         <v>1992</v>
@@ -19938,7 +19938,7 @@
         <v>33</v>
       </c>
       <c r="D39" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E39">
         <v>1993</v>
@@ -19991,7 +19991,7 @@
         <v>33</v>
       </c>
       <c r="D40" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E40">
         <v>2009</v>
@@ -20044,7 +20044,7 @@
         <v>33</v>
       </c>
       <c r="D41" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E41">
         <v>2010</v>
@@ -20097,7 +20097,7 @@
         <v>33</v>
       </c>
       <c r="D42" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E42">
         <v>2010</v>
@@ -20156,7 +20156,7 @@
         <v>2022</v>
       </c>
       <c r="F43">
-        <v>0.23280454489112914</v>
+        <v>0.20557907614758497</v>
       </c>
       <c r="G43">
         <v>0.50778999999999996</v>
@@ -20168,7 +20168,7 @@
         <v>36.300000000000004</v>
       </c>
       <c r="J43">
-        <v>3.4650000000000007</v>
+        <v>3.4650000000000003</v>
       </c>
       <c r="K43">
         <v>50</v>
@@ -20209,19 +20209,19 @@
         <v>2022</v>
       </c>
       <c r="F44">
-        <v>0.37112356319464518</v>
+        <v>0.20212110068999706</v>
       </c>
       <c r="G44">
-        <v>0.52529999999999999</v>
+        <v>0.50778999999999996</v>
       </c>
       <c r="H44">
-        <v>1100</v>
+        <v>1265</v>
       </c>
       <c r="I44">
-        <v>33</v>
+        <v>36.300000000000004</v>
       </c>
       <c r="J44">
-        <v>3.1500000000000004</v>
+        <v>3.4650000000000003</v>
       </c>
       <c r="K44">
         <v>50</v>
@@ -20262,7 +20262,7 @@
         <v>2022</v>
       </c>
       <c r="F45">
-        <v>0.20557907614758497</v>
+        <v>0.19481551873734657</v>
       </c>
       <c r="G45">
         <v>0.50778999999999996</v>
@@ -20315,7 +20315,7 @@
         <v>2022</v>
       </c>
       <c r="F46">
-        <v>0.26543614427963469</v>
+        <v>0.18702289798785268</v>
       </c>
       <c r="G46">
         <v>0.50778999999999996</v>
@@ -20368,19 +20368,19 @@
         <v>2022</v>
       </c>
       <c r="F47">
-        <v>0.20212110068999706</v>
+        <v>0.43468212618270452</v>
       </c>
       <c r="G47">
-        <v>0.50778999999999996</v>
+        <v>0.52529999999999999</v>
       </c>
       <c r="H47">
-        <v>1265</v>
+        <v>1100</v>
       </c>
       <c r="I47">
-        <v>36.300000000000004</v>
+        <v>33</v>
       </c>
       <c r="J47">
-        <v>3.4650000000000003</v>
+        <v>3.1500000000000004</v>
       </c>
       <c r="K47">
         <v>50</v>
@@ -20421,7 +20421,7 @@
         <v>2022</v>
       </c>
       <c r="F48">
-        <v>0.19481551873734657</v>
+        <v>0.18824049497996109</v>
       </c>
       <c r="G48">
         <v>0.50778999999999996</v>
@@ -20474,7 +20474,7 @@
         <v>2022</v>
       </c>
       <c r="F49">
-        <v>0.28443065735652601</v>
+        <v>0.19481551873734657</v>
       </c>
       <c r="G49">
         <v>0.50778999999999996</v>
@@ -20527,19 +20527,19 @@
         <v>2022</v>
       </c>
       <c r="F50">
-        <v>0.39839773581787374</v>
+        <v>0.19481551873734657</v>
       </c>
       <c r="G50">
-        <v>0.52529999999999999</v>
+        <v>0.50778999999999996</v>
       </c>
       <c r="H50">
-        <v>1100</v>
+        <v>1265</v>
       </c>
       <c r="I50">
-        <v>33</v>
+        <v>36.300000000000004</v>
       </c>
       <c r="J50">
-        <v>3.1500000000000004</v>
+        <v>3.4650000000000003</v>
       </c>
       <c r="K50">
         <v>50</v>
@@ -20580,19 +20580,19 @@
         <v>2022</v>
       </c>
       <c r="F51">
-        <v>0.21283595422055113</v>
+        <v>0.45732943023592104</v>
       </c>
       <c r="G51">
-        <v>0.50778999999999996</v>
+        <v>0.52529999999999999</v>
       </c>
       <c r="H51">
-        <v>1265</v>
+        <v>1100</v>
       </c>
       <c r="I51">
-        <v>36.300000000000004</v>
+        <v>33</v>
       </c>
       <c r="J51">
-        <v>3.4650000000000003</v>
+        <v>3.1500000000000004</v>
       </c>
       <c r="K51">
         <v>50</v>
@@ -20633,19 +20633,19 @@
         <v>2022</v>
       </c>
       <c r="F52">
-        <v>0.19481551873734657</v>
+        <v>0.49339465314217229</v>
       </c>
       <c r="G52">
-        <v>0.50778999999999996</v>
+        <v>0.52529999999999999</v>
       </c>
       <c r="H52">
-        <v>1265</v>
+        <v>1100</v>
       </c>
       <c r="I52">
-        <v>36.300000000000004</v>
+        <v>33</v>
       </c>
       <c r="J52">
-        <v>3.4650000000000003</v>
+        <v>3.1500000000000004</v>
       </c>
       <c r="K52">
         <v>50</v>
@@ -20686,7 +20686,7 @@
         <v>2022</v>
       </c>
       <c r="F53">
-        <v>0.19481551873734657</v>
+        <v>0.17484692806676855</v>
       </c>
       <c r="G53">
         <v>0.50778999999999996</v>
@@ -20739,19 +20739,19 @@
         <v>2022</v>
       </c>
       <c r="F54">
-        <v>0.45732943023592104</v>
+        <v>0.18872753377680451</v>
       </c>
       <c r="G54">
-        <v>0.52529999999999999</v>
+        <v>0.50778999999999996</v>
       </c>
       <c r="H54">
-        <v>1100</v>
+        <v>1265</v>
       </c>
       <c r="I54">
-        <v>33</v>
+        <v>36.300000000000004</v>
       </c>
       <c r="J54">
-        <v>3.1500000000000004</v>
+        <v>3.4650000000000007</v>
       </c>
       <c r="K54">
         <v>50</v>
@@ -20792,19 +20792,19 @@
         <v>2022</v>
       </c>
       <c r="F55">
-        <v>0.49339465314217229</v>
+        <v>0.22793415692269547</v>
       </c>
       <c r="G55">
-        <v>0.52529999999999999</v>
+        <v>0.50778999999999996</v>
       </c>
       <c r="H55">
-        <v>1100</v>
+        <v>1265</v>
       </c>
       <c r="I55">
-        <v>33</v>
+        <v>36.300000000000004</v>
       </c>
       <c r="J55">
-        <v>3.1500000000000004</v>
+        <v>3.4650000000000003</v>
       </c>
       <c r="K55">
         <v>50</v>
@@ -20845,7 +20845,7 @@
         <v>2022</v>
       </c>
       <c r="F56">
-        <v>0.17484692806676855</v>
+        <v>0.1548783373961905</v>
       </c>
       <c r="G56">
         <v>0.50778999999999996</v>
@@ -20857,7 +20857,7 @@
         <v>36.300000000000004</v>
       </c>
       <c r="J56">
-        <v>3.4650000000000003</v>
+        <v>3.4649999999999999</v>
       </c>
       <c r="K56">
         <v>50</v>
@@ -20898,7 +20898,7 @@
         <v>2022</v>
       </c>
       <c r="F57">
-        <v>0.16608022972358796</v>
+        <v>0.19627663512787666</v>
       </c>
       <c r="G57">
         <v>0.50778999999999996</v>
@@ -20910,7 +20910,7 @@
         <v>36.300000000000004</v>
       </c>
       <c r="J57">
-        <v>3.4650000000000003</v>
+        <v>3.4649999999999999</v>
       </c>
       <c r="K57">
         <v>50</v>
@@ -20951,7 +20951,7 @@
         <v>2022</v>
       </c>
       <c r="F58">
-        <v>0.18872753377680451</v>
+        <v>0.27347228442755023</v>
       </c>
       <c r="G58">
         <v>0.50778999999999996</v>
@@ -20963,7 +20963,7 @@
         <v>36.300000000000004</v>
       </c>
       <c r="J58">
-        <v>3.4650000000000007</v>
+        <v>3.4650000000000003</v>
       </c>
       <c r="K58">
         <v>50</v>
@@ -21004,7 +21004,7 @@
         <v>2022</v>
       </c>
       <c r="F59">
-        <v>0.21113131843159935</v>
+        <v>0.19481551873734657</v>
       </c>
       <c r="G59">
         <v>0.50778999999999996</v>
@@ -21057,7 +21057,7 @@
         <v>2022</v>
       </c>
       <c r="F60">
-        <v>0.19627663512787666</v>
+        <v>0.28443065735652601</v>
       </c>
       <c r="G60">
         <v>0.50778999999999996</v>
@@ -21069,7 +21069,7 @@
         <v>36.300000000000004</v>
       </c>
       <c r="J60">
-        <v>3.4649999999999999</v>
+        <v>3.4650000000000003</v>
       </c>
       <c r="K60">
         <v>50</v>
@@ -21110,19 +21110,19 @@
         <v>2022</v>
       </c>
       <c r="F61">
-        <v>0.18824049497996109</v>
+        <v>0.39839773581787374</v>
       </c>
       <c r="G61">
-        <v>0.50778999999999996</v>
+        <v>0.52529999999999999</v>
       </c>
       <c r="H61">
-        <v>1265</v>
+        <v>1100</v>
       </c>
       <c r="I61">
-        <v>36.300000000000004</v>
+        <v>33</v>
       </c>
       <c r="J61">
-        <v>3.4650000000000003</v>
+        <v>3.1500000000000004</v>
       </c>
       <c r="K61">
         <v>50</v>
@@ -21163,19 +21163,19 @@
         <v>2022</v>
       </c>
       <c r="F62">
-        <v>0.43468212618270452</v>
+        <v>0.21283595422055113</v>
       </c>
       <c r="G62">
-        <v>0.52529999999999999</v>
+        <v>0.50778999999999996</v>
       </c>
       <c r="H62">
-        <v>1100</v>
+        <v>1265</v>
       </c>
       <c r="I62">
-        <v>33</v>
+        <v>36.300000000000004</v>
       </c>
       <c r="J62">
-        <v>3.1500000000000004</v>
+        <v>3.4650000000000003</v>
       </c>
       <c r="K62">
         <v>50</v>
@@ -21216,7 +21216,7 @@
         <v>2022</v>
       </c>
       <c r="F63">
-        <v>0.20820908565053911</v>
+        <v>0.18556178159732259</v>
       </c>
       <c r="G63">
         <v>0.50778999999999996</v>
@@ -21228,7 +21228,7 @@
         <v>36.300000000000004</v>
       </c>
       <c r="J63">
-        <v>3.4650000000000007</v>
+        <v>3.4650000000000003</v>
       </c>
       <c r="K63">
         <v>50</v>
@@ -21269,7 +21269,7 @@
         <v>2022</v>
       </c>
       <c r="F64">
-        <v>0.18629233979258764</v>
+        <v>0.23280454489112914</v>
       </c>
       <c r="G64">
         <v>0.50778999999999996</v>
@@ -21281,7 +21281,7 @@
         <v>36.300000000000004</v>
       </c>
       <c r="J64">
-        <v>3.4650000000000003</v>
+        <v>3.4650000000000007</v>
       </c>
       <c r="K64">
         <v>50</v>
@@ -21322,7 +21322,7 @@
         <v>2022</v>
       </c>
       <c r="F65">
-        <v>0.20236462008841874</v>
+        <v>0.26604494277568891</v>
       </c>
       <c r="G65">
         <v>0.50778999999999996</v>
@@ -21375,7 +21375,7 @@
         <v>2022</v>
       </c>
       <c r="F66">
-        <v>0.18702289798785268</v>
+        <v>0.21551466760318963</v>
       </c>
       <c r="G66">
         <v>0.50778999999999996</v>
@@ -21428,7 +21428,7 @@
         <v>2022</v>
       </c>
       <c r="F67">
-        <v>0.19676367392472002</v>
+        <v>0.21113131843159935</v>
       </c>
       <c r="G67">
         <v>0.50778999999999996</v>
@@ -21481,7 +21481,7 @@
         <v>2022</v>
       </c>
       <c r="F68">
-        <v>0.19481551873734657</v>
+        <v>0.29344087509812827</v>
       </c>
       <c r="G68">
         <v>0.50778999999999996</v>
@@ -21534,7 +21534,7 @@
         <v>2022</v>
       </c>
       <c r="F69">
-        <v>0.29344087509812827</v>
+        <v>0.23864901045324952</v>
       </c>
       <c r="G69">
         <v>0.50778999999999996</v>
@@ -21581,25 +21581,25 @@
         <v>49</v>
       </c>
       <c r="D70" t="s">
-        <v>15</v>
+        <v>77</v>
       </c>
       <c r="E70">
         <v>2022</v>
       </c>
       <c r="F70">
-        <v>0.19822479031525012</v>
+        <v>0.31243538817501959</v>
       </c>
       <c r="G70">
-        <v>0.50778999999999996</v>
+        <v>0.52529999999999999</v>
       </c>
       <c r="H70">
-        <v>1265</v>
+        <v>1100</v>
       </c>
       <c r="I70">
-        <v>36.300000000000004</v>
+        <v>33</v>
       </c>
       <c r="J70">
-        <v>3.4650000000000003</v>
+        <v>3.1500000000000004</v>
       </c>
       <c r="K70">
         <v>50</v>
@@ -21634,13 +21634,13 @@
         <v>49</v>
       </c>
       <c r="D71" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E71">
         <v>2022</v>
       </c>
       <c r="F71">
-        <v>0.22793415692269547</v>
+        <v>0.20820908565053911</v>
       </c>
       <c r="G71">
         <v>0.50778999999999996</v>
@@ -21652,7 +21652,7 @@
         <v>36.300000000000004</v>
       </c>
       <c r="J71">
-        <v>3.4650000000000003</v>
+        <v>3.4650000000000007</v>
       </c>
       <c r="K71">
         <v>50</v>
@@ -21687,13 +21687,13 @@
         <v>49</v>
       </c>
       <c r="D72" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E72">
         <v>2022</v>
       </c>
       <c r="F72">
-        <v>0.1548783373961905</v>
+        <v>0.18629233979258764</v>
       </c>
       <c r="G72">
         <v>0.50778999999999996</v>
@@ -21705,7 +21705,7 @@
         <v>36.300000000000004</v>
       </c>
       <c r="J72">
-        <v>3.4649999999999999</v>
+        <v>3.4650000000000003</v>
       </c>
       <c r="K72">
         <v>50</v>
@@ -21740,13 +21740,13 @@
         <v>49</v>
       </c>
       <c r="D73" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E73">
         <v>2022</v>
       </c>
       <c r="F73">
-        <v>0.27347228442755023</v>
+        <v>0.20236462008841874</v>
       </c>
       <c r="G73">
         <v>0.50778999999999996</v>
@@ -21793,13 +21793,13 @@
         <v>49</v>
       </c>
       <c r="D74" t="s">
-        <v>80</v>
+        <v>16</v>
       </c>
       <c r="E74">
         <v>2022</v>
       </c>
       <c r="F74">
-        <v>0.18507474280047922</v>
+        <v>0.19822479031525012</v>
       </c>
       <c r="G74">
         <v>0.50778999999999996</v>
@@ -21811,7 +21811,7 @@
         <v>36.300000000000004</v>
       </c>
       <c r="J74">
-        <v>3.4649999999999999</v>
+        <v>3.4650000000000003</v>
       </c>
       <c r="K74">
         <v>50</v>
@@ -21852,19 +21852,19 @@
         <v>2022</v>
       </c>
       <c r="F75">
-        <v>0.3567559186877659</v>
+        <v>0.16608022972358796</v>
       </c>
       <c r="G75">
-        <v>0.52529999999999999</v>
+        <v>0.50778999999999996</v>
       </c>
       <c r="H75">
-        <v>1100</v>
+        <v>1265</v>
       </c>
       <c r="I75">
-        <v>33</v>
+        <v>36.300000000000004</v>
       </c>
       <c r="J75">
-        <v>3.1500000000000004</v>
+        <v>3.4650000000000003</v>
       </c>
       <c r="K75">
         <v>50</v>
@@ -21899,13 +21899,13 @@
         <v>49</v>
       </c>
       <c r="D76" t="s">
-        <v>37</v>
+        <v>82</v>
       </c>
       <c r="E76">
         <v>2022</v>
       </c>
       <c r="F76">
-        <v>0.27761211420071885</v>
+        <v>0.19676367392472002</v>
       </c>
       <c r="G76">
         <v>0.50778999999999996</v>
@@ -21952,25 +21952,25 @@
         <v>49</v>
       </c>
       <c r="D77" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E77">
         <v>2022</v>
       </c>
       <c r="F77">
-        <v>0.30829555840185086</v>
+        <v>0.18507474280047922</v>
       </c>
       <c r="G77">
-        <v>0.52529999999999999</v>
+        <v>0.50778999999999996</v>
       </c>
       <c r="H77">
-        <v>1100</v>
+        <v>1265</v>
       </c>
       <c r="I77">
-        <v>33</v>
+        <v>36.300000000000004</v>
       </c>
       <c r="J77">
-        <v>3.1500000000000004</v>
+        <v>3.4649999999999999</v>
       </c>
       <c r="K77">
         <v>50</v>
@@ -22005,13 +22005,13 @@
         <v>49</v>
       </c>
       <c r="D78" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E78">
         <v>2022</v>
       </c>
       <c r="F78">
-        <v>0.31243538817501959</v>
+        <v>0.3567559186877659</v>
       </c>
       <c r="G78">
         <v>0.52529999999999999</v>
@@ -22058,13 +22058,13 @@
         <v>49</v>
       </c>
       <c r="D79" t="s">
-        <v>84</v>
+        <v>34</v>
       </c>
       <c r="E79">
         <v>2022</v>
       </c>
       <c r="F79">
-        <v>0.23864901045324952</v>
+        <v>0.27761211420071885</v>
       </c>
       <c r="G79">
         <v>0.50778999999999996</v>
@@ -22117,19 +22117,19 @@
         <v>2022</v>
       </c>
       <c r="F80">
-        <v>0.26604494277568891</v>
+        <v>0.37112356319464518</v>
       </c>
       <c r="G80">
-        <v>0.50778999999999996</v>
+        <v>0.52529999999999999</v>
       </c>
       <c r="H80">
-        <v>1265</v>
+        <v>1100</v>
       </c>
       <c r="I80">
-        <v>36.300000000000004</v>
+        <v>33</v>
       </c>
       <c r="J80">
-        <v>3.4650000000000003</v>
+        <v>3.1500000000000004</v>
       </c>
       <c r="K80">
         <v>50</v>
@@ -22170,19 +22170,19 @@
         <v>2022</v>
       </c>
       <c r="F81">
-        <v>0.21551466760318963</v>
+        <v>0.30829555840185086</v>
       </c>
       <c r="G81">
-        <v>0.50778999999999996</v>
+        <v>0.52529999999999999</v>
       </c>
       <c r="H81">
-        <v>1265</v>
+        <v>1100</v>
       </c>
       <c r="I81">
-        <v>36.300000000000004</v>
+        <v>33</v>
       </c>
       <c r="J81">
-        <v>3.4650000000000003</v>
+        <v>3.1500000000000004</v>
       </c>
       <c r="K81">
         <v>50</v>
@@ -22223,7 +22223,7 @@
         <v>2022</v>
       </c>
       <c r="F82">
-        <v>0.18556178159732259</v>
+        <v>0.26543614427963469</v>
       </c>
       <c r="G82">
         <v>0.50778999999999996</v>
@@ -22270,7 +22270,7 @@
         <v>49</v>
       </c>
       <c r="D83" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="E83">
         <v>2006</v>
@@ -22323,7 +22323,7 @@
         <v>49</v>
       </c>
       <c r="D84" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="E84">
         <v>2012</v>
@@ -22376,7 +22376,7 @@
         <v>49</v>
       </c>
       <c r="D85" t="s">
-        <v>69</v>
+        <v>54</v>
       </c>
       <c r="E85">
         <v>1993</v>
@@ -22429,7 +22429,7 @@
         <v>49</v>
       </c>
       <c r="D86" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="E86">
         <v>2011</v>
@@ -22482,7 +22482,7 @@
         <v>49</v>
       </c>
       <c r="D87" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="E87">
         <v>2005</v>
@@ -22535,7 +22535,7 @@
         <v>49</v>
       </c>
       <c r="D88" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="E88">
         <v>2006</v>
@@ -22588,7 +22588,7 @@
         <v>49</v>
       </c>
       <c r="D89" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="E89">
         <v>2006</v>
@@ -22694,7 +22694,7 @@
         <v>49</v>
       </c>
       <c r="D91" t="s">
-        <v>50</v>
+        <v>71</v>
       </c>
       <c r="E91">
         <v>2003</v>
@@ -22853,7 +22853,7 @@
         <v>49</v>
       </c>
       <c r="D94" t="s">
-        <v>79</v>
+        <v>65</v>
       </c>
       <c r="E94">
         <v>2004</v>
@@ -22906,7 +22906,7 @@
         <v>49</v>
       </c>
       <c r="D95" t="s">
-        <v>79</v>
+        <v>65</v>
       </c>
       <c r="E95">
         <v>2005</v>
@@ -22959,7 +22959,7 @@
         <v>49</v>
       </c>
       <c r="D96" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="E96">
         <v>2005</v>
@@ -23012,7 +23012,7 @@
         <v>49</v>
       </c>
       <c r="D97" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="E97">
         <v>2005</v>
@@ -23065,7 +23065,7 @@
         <v>49</v>
       </c>
       <c r="D98" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="E98">
         <v>2004</v>
@@ -23118,7 +23118,7 @@
         <v>49</v>
       </c>
       <c r="D99" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="E99">
         <v>2004</v>
@@ -23171,7 +23171,7 @@
         <v>49</v>
       </c>
       <c r="D100" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="E100">
         <v>2004</v>
@@ -23224,7 +23224,7 @@
         <v>49</v>
       </c>
       <c r="D101" t="s">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="E101">
         <v>2008</v>
@@ -23277,7 +23277,7 @@
         <v>49</v>
       </c>
       <c r="D102" t="s">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="E102">
         <v>2008</v>
@@ -23330,7 +23330,7 @@
         <v>49</v>
       </c>
       <c r="D103" t="s">
-        <v>51</v>
+        <v>85</v>
       </c>
       <c r="E103">
         <v>2002</v>
@@ -23383,7 +23383,7 @@
         <v>49</v>
       </c>
       <c r="D104" t="s">
-        <v>51</v>
+        <v>85</v>
       </c>
       <c r="E104">
         <v>2002</v>
@@ -23436,7 +23436,7 @@
         <v>49</v>
       </c>
       <c r="D105" t="s">
-        <v>51</v>
+        <v>85</v>
       </c>
       <c r="E105">
         <v>2003</v>
@@ -23489,7 +23489,7 @@
         <v>49</v>
       </c>
       <c r="D106" t="s">
-        <v>51</v>
+        <v>85</v>
       </c>
       <c r="E106">
         <v>2003</v>
@@ -23542,7 +23542,7 @@
         <v>49</v>
       </c>
       <c r="D107" t="s">
-        <v>64</v>
+        <v>81</v>
       </c>
       <c r="E107">
         <v>2000</v>
@@ -23595,7 +23595,7 @@
         <v>49</v>
       </c>
       <c r="D108" t="s">
-        <v>64</v>
+        <v>81</v>
       </c>
       <c r="E108">
         <v>2000</v>
@@ -23648,7 +23648,7 @@
         <v>49</v>
       </c>
       <c r="D109" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="E109">
         <v>2007</v>
@@ -23701,7 +23701,7 @@
         <v>49</v>
       </c>
       <c r="D110" t="s">
-        <v>69</v>
+        <v>54</v>
       </c>
       <c r="E110">
         <v>2023</v>
@@ -23754,7 +23754,7 @@
         <v>49</v>
       </c>
       <c r="D111" t="s">
-        <v>69</v>
+        <v>54</v>
       </c>
       <c r="E111">
         <v>2001</v>
@@ -23860,7 +23860,7 @@
         <v>49</v>
       </c>
       <c r="D113" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="E113">
         <v>2010</v>
@@ -23913,7 +23913,7 @@
         <v>49</v>
       </c>
       <c r="D114" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E114">
         <v>2005</v>
@@ -23966,7 +23966,7 @@
         <v>49</v>
       </c>
       <c r="D115" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E115">
         <v>2009</v>
@@ -24019,7 +24019,7 @@
         <v>49</v>
       </c>
       <c r="D116" t="s">
-        <v>53</v>
+        <v>87</v>
       </c>
       <c r="E116">
         <v>1997</v>
@@ -24072,7 +24072,7 @@
         <v>49</v>
       </c>
       <c r="D117" t="s">
-        <v>53</v>
+        <v>87</v>
       </c>
       <c r="E117">
         <v>1997</v>
@@ -24125,7 +24125,7 @@
         <v>49</v>
       </c>
       <c r="D118" t="s">
-        <v>53</v>
+        <v>87</v>
       </c>
       <c r="E118">
         <v>1998</v>
@@ -24178,7 +24178,7 @@
         <v>49</v>
       </c>
       <c r="D119" t="s">
-        <v>53</v>
+        <v>87</v>
       </c>
       <c r="E119">
         <v>1999</v>
@@ -24284,7 +24284,7 @@
         <v>49</v>
       </c>
       <c r="D121" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="E121">
         <v>2010</v>
@@ -24337,7 +24337,7 @@
         <v>49</v>
       </c>
       <c r="D122" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="E122">
         <v>2003</v>
@@ -24390,7 +24390,7 @@
         <v>49</v>
       </c>
       <c r="D123" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="E123">
         <v>2003</v>
@@ -24443,7 +24443,7 @@
         <v>49</v>
       </c>
       <c r="D124" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="E124">
         <v>2006</v>
@@ -24602,7 +24602,7 @@
         <v>49</v>
       </c>
       <c r="D127" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="E127">
         <v>2002</v>
@@ -24655,7 +24655,7 @@
         <v>49</v>
       </c>
       <c r="D128" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="E128">
         <v>2002</v>
@@ -24708,7 +24708,7 @@
         <v>49</v>
       </c>
       <c r="D129" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="E129">
         <v>2010</v>
@@ -24761,7 +24761,7 @@
         <v>49</v>
       </c>
       <c r="D130" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="E130">
         <v>2010</v>
@@ -24814,7 +24814,7 @@
         <v>49</v>
       </c>
       <c r="D131" t="s">
-        <v>73</v>
+        <v>53</v>
       </c>
       <c r="E131">
         <v>2008</v>
@@ -24867,7 +24867,7 @@
         <v>49</v>
       </c>
       <c r="D132" t="s">
-        <v>73</v>
+        <v>53</v>
       </c>
       <c r="E132">
         <v>2008</v>
@@ -24920,7 +24920,7 @@
         <v>49</v>
       </c>
       <c r="D133" t="s">
-        <v>77</v>
+        <v>62</v>
       </c>
       <c r="E133">
         <v>2018</v>
@@ -24973,7 +24973,7 @@
         <v>49</v>
       </c>
       <c r="D134" t="s">
-        <v>87</v>
+        <v>70</v>
       </c>
       <c r="E134">
         <v>2006</v>
@@ -25026,7 +25026,7 @@
         <v>49</v>
       </c>
       <c r="D135" t="s">
-        <v>87</v>
+        <v>70</v>
       </c>
       <c r="E135">
         <v>2007</v>
@@ -25185,7 +25185,7 @@
         <v>49</v>
       </c>
       <c r="D138" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E138">
         <v>2010</v>
@@ -25238,7 +25238,7 @@
         <v>49</v>
       </c>
       <c r="D139" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E139">
         <v>2010</v>
@@ -25291,7 +25291,7 @@
         <v>49</v>
       </c>
       <c r="D140" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E140">
         <v>2004</v>
@@ -25344,7 +25344,7 @@
         <v>49</v>
       </c>
       <c r="D141" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E141">
         <v>2004</v>
@@ -25397,7 +25397,7 @@
         <v>49</v>
       </c>
       <c r="D142" t="s">
-        <v>86</v>
+        <v>73</v>
       </c>
       <c r="E142">
         <v>2008</v>
@@ -25450,7 +25450,7 @@
         <v>49</v>
       </c>
       <c r="D143" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="E143">
         <v>2007</v>
@@ -25503,7 +25503,7 @@
         <v>49</v>
       </c>
       <c r="D144" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="E144">
         <v>2007</v>
@@ -25556,7 +25556,7 @@
         <v>49</v>
       </c>
       <c r="D145" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="E145">
         <v>2005</v>
@@ -25609,7 +25609,7 @@
         <v>49</v>
       </c>
       <c r="D146" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="E146">
         <v>2005</v>
@@ -25662,7 +25662,7 @@
         <v>49</v>
       </c>
       <c r="D147" t="s">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="E147">
         <v>2015</v>
@@ -25715,7 +25715,7 @@
         <v>49</v>
       </c>
       <c r="D148" t="s">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="E148">
         <v>2004</v>
@@ -25768,7 +25768,7 @@
         <v>49</v>
       </c>
       <c r="D149" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E149">
         <v>2006</v>
@@ -25821,7 +25821,7 @@
         <v>49</v>
       </c>
       <c r="D150" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="E150">
         <v>2011</v>
@@ -25874,7 +25874,7 @@
         <v>49</v>
       </c>
       <c r="D151" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E151">
         <v>2004</v>
@@ -25927,7 +25927,7 @@
         <v>49</v>
       </c>
       <c r="D152" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E152">
         <v>2005</v>
@@ -25980,7 +25980,7 @@
         <v>49</v>
       </c>
       <c r="D153" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="E153">
         <v>2006</v>
@@ -26033,7 +26033,7 @@
         <v>49</v>
       </c>
       <c r="D154" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="E154">
         <v>2008</v>
@@ -26086,7 +26086,7 @@
         <v>49</v>
       </c>
       <c r="D155" t="s">
-        <v>75</v>
+        <v>52</v>
       </c>
       <c r="E155">
         <v>2007</v>
@@ -26192,7 +26192,7 @@
         <v>49</v>
       </c>
       <c r="D157" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="E157">
         <v>2023</v>
@@ -26245,7 +26245,7 @@
         <v>49</v>
       </c>
       <c r="D158" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="E158">
         <v>2026</v>
@@ -26298,7 +26298,7 @@
         <v>49</v>
       </c>
       <c r="D159" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="E159">
         <v>2022</v>
@@ -26351,7 +26351,7 @@
         <v>49</v>
       </c>
       <c r="D160" t="s">
-        <v>68</v>
+        <v>55</v>
       </c>
       <c r="E160">
         <v>2003</v>
@@ -26404,7 +26404,7 @@
         <v>49</v>
       </c>
       <c r="D161" t="s">
-        <v>68</v>
+        <v>55</v>
       </c>
       <c r="E161">
         <v>2003</v>
@@ -26457,7 +26457,7 @@
         <v>49</v>
       </c>
       <c r="D162" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="E162">
         <v>2003</v>
@@ -26510,7 +26510,7 @@
         <v>49</v>
       </c>
       <c r="D163" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="E163">
         <v>2008</v>
@@ -26563,7 +26563,7 @@
         <v>49</v>
       </c>
       <c r="D164" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="E164">
         <v>1999</v>
@@ -26616,7 +26616,7 @@
         <v>49</v>
       </c>
       <c r="D165" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="E165">
         <v>1999</v>
@@ -26669,7 +26669,7 @@
         <v>49</v>
       </c>
       <c r="D166" t="s">
-        <v>85</v>
+        <v>72</v>
       </c>
       <c r="E166">
         <v>1997</v>
@@ -26775,7 +26775,7 @@
         <v>49</v>
       </c>
       <c r="D168" t="s">
-        <v>78</v>
+        <v>63</v>
       </c>
       <c r="E168">
         <v>2001</v>
@@ -26828,7 +26828,7 @@
         <v>49</v>
       </c>
       <c r="D169" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="E169">
         <v>2006</v>
@@ -26934,7 +26934,7 @@
         <v>49</v>
       </c>
       <c r="D171" t="s">
-        <v>77</v>
+        <v>62</v>
       </c>
       <c r="E171">
         <v>2007</v>
@@ -27517,7 +27517,7 @@
         <v>49</v>
       </c>
       <c r="D182" t="s">
-        <v>85</v>
+        <v>72</v>
       </c>
       <c r="E182">
         <v>2015</v>
@@ -28312,7 +28312,7 @@
         <v>49</v>
       </c>
       <c r="D197" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="E197">
         <v>2004</v>
@@ -28365,7 +28365,7 @@
         <v>49</v>
       </c>
       <c r="D198" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="E198">
         <v>2008</v>
@@ -28577,7 +28577,7 @@
         <v>49</v>
       </c>
       <c r="D202" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="E202">
         <v>2005</v>
@@ -28630,7 +28630,7 @@
         <v>49</v>
       </c>
       <c r="D203" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="E203">
         <v>2015</v>
@@ -29319,7 +29319,7 @@
         <v>49</v>
       </c>
       <c r="D216" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E216">
         <v>2022</v>
@@ -29531,7 +29531,7 @@
         <v>49</v>
       </c>
       <c r="D220" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="E220">
         <v>2009</v>
@@ -30220,7 +30220,7 @@
         <v>49</v>
       </c>
       <c r="D233" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E233">
         <v>1994</v>
@@ -30379,7 +30379,7 @@
         <v>49</v>
       </c>
       <c r="D236" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="E236">
         <v>1990</v>
@@ -30432,7 +30432,7 @@
         <v>49</v>
       </c>
       <c r="D237" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="E237">
         <v>2022</v>
@@ -30591,7 +30591,7 @@
         <v>49</v>
       </c>
       <c r="D240" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E240">
         <v>2006</v>
@@ -30644,7 +30644,7 @@
         <v>49</v>
       </c>
       <c r="D241" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="E241">
         <v>2024</v>
@@ -30697,7 +30697,7 @@
         <v>49</v>
       </c>
       <c r="D242" t="s">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="E242">
         <v>2023</v>
@@ -30750,7 +30750,7 @@
         <v>49</v>
       </c>
       <c r="D243" t="s">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="E243">
         <v>2023</v>
@@ -30803,7 +30803,7 @@
         <v>49</v>
       </c>
       <c r="D244" t="s">
-        <v>77</v>
+        <v>62</v>
       </c>
       <c r="E244">
         <v>1997</v>
@@ -31280,7 +31280,7 @@
         <v>49</v>
       </c>
       <c r="D253" t="s">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="E253">
         <v>2008</v>
@@ -31545,7 +31545,7 @@
         <v>49</v>
       </c>
       <c r="D258" t="s">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="E258">
         <v>2015</v>
@@ -31651,7 +31651,7 @@
         <v>49</v>
       </c>
       <c r="D260" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="E260">
         <v>2004</v>
@@ -31916,7 +31916,7 @@
         <v>49</v>
       </c>
       <c r="D265" t="s">
-        <v>50</v>
+        <v>71</v>
       </c>
       <c r="E265">
         <v>2024</v>
@@ -32022,7 +32022,7 @@
         <v>49</v>
       </c>
       <c r="D267" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E267">
         <v>2023</v>
@@ -32234,7 +32234,7 @@
         <v>49</v>
       </c>
       <c r="D271" t="s">
-        <v>85</v>
+        <v>72</v>
       </c>
       <c r="E271">
         <v>1975</v>
@@ -32287,7 +32287,7 @@
         <v>49</v>
       </c>
       <c r="D272" t="s">
-        <v>85</v>
+        <v>72</v>
       </c>
       <c r="E272">
         <v>1975</v>
@@ -32340,7 +32340,7 @@
         <v>49</v>
       </c>
       <c r="D273" t="s">
-        <v>85</v>
+        <v>72</v>
       </c>
       <c r="E273">
         <v>1975</v>
@@ -32393,7 +32393,7 @@
         <v>49</v>
       </c>
       <c r="D274" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="E274">
         <v>2015</v>
@@ -32446,7 +32446,7 @@
         <v>49</v>
       </c>
       <c r="D275" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="E275">
         <v>1967</v>
@@ -32499,7 +32499,7 @@
         <v>49</v>
       </c>
       <c r="D276" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="E276">
         <v>1971</v>
@@ -32552,7 +32552,7 @@
         <v>49</v>
       </c>
       <c r="D277" t="s">
-        <v>78</v>
+        <v>63</v>
       </c>
       <c r="E277">
         <v>1970</v>
@@ -32605,7 +32605,7 @@
         <v>49</v>
       </c>
       <c r="D278" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E278">
         <v>1978</v>
@@ -32658,7 +32658,7 @@
         <v>49</v>
       </c>
       <c r="D279" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E279">
         <v>1981</v>
@@ -32711,7 +32711,7 @@
         <v>49</v>
       </c>
       <c r="D280" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E280">
         <v>1987</v>
@@ -33135,7 +33135,7 @@
         <v>293</v>
       </c>
       <c r="D288" t="s">
-        <v>53</v>
+        <v>87</v>
       </c>
       <c r="E288">
         <v>1991</v>
@@ -33188,7 +33188,7 @@
         <v>293</v>
       </c>
       <c r="D289" t="s">
-        <v>53</v>
+        <v>87</v>
       </c>
       <c r="E289">
         <v>1991</v>
@@ -34248,25 +34248,25 @@
         <v>308</v>
       </c>
       <c r="D309" t="s">
-        <v>309</v>
+        <v>99</v>
       </c>
       <c r="E309">
         <v>2022</v>
       </c>
       <c r="F309">
-        <v>0.56367299846968055</v>
+        <v>0.29181095970158766</v>
       </c>
       <c r="G309">
         <v>1</v>
       </c>
       <c r="H309">
-        <v>2750</v>
+        <v>3162.5000000000005</v>
       </c>
       <c r="I309">
-        <v>55.000000000000007</v>
+        <v>60.500000000000014</v>
       </c>
       <c r="J309">
-        <v>2.1</v>
+        <v>2.3100000000000005</v>
       </c>
       <c r="K309">
         <v>100</v>
@@ -34301,25 +34301,25 @@
         <v>308</v>
       </c>
       <c r="D310" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="E310">
         <v>2022</v>
       </c>
       <c r="F310">
-        <v>0.13036387865841995</v>
+        <v>1.0883760118599757</v>
       </c>
       <c r="G310">
         <v>1</v>
       </c>
       <c r="H310">
-        <v>3162.5000000000005</v>
+        <v>2750</v>
       </c>
       <c r="I310">
-        <v>60.500000000000014</v>
+        <v>55.000000000000007</v>
       </c>
       <c r="J310">
-        <v>2.3100000000000005</v>
+        <v>2.1</v>
       </c>
       <c r="K310">
         <v>100</v>
@@ -34354,25 +34354,25 @@
         <v>308</v>
       </c>
       <c r="D311" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="E311">
         <v>2022</v>
       </c>
       <c r="F311">
-        <v>0.57944656385895543</v>
+        <v>0.10670353057450742</v>
       </c>
       <c r="G311">
         <v>1</v>
       </c>
       <c r="H311">
-        <v>2750</v>
+        <v>3162.5000000000005</v>
       </c>
       <c r="I311">
-        <v>55.000000000000007</v>
+        <v>60.500000000000014</v>
       </c>
       <c r="J311">
-        <v>2.1</v>
+        <v>2.3100000000000005</v>
       </c>
       <c r="K311">
         <v>100</v>
@@ -34407,25 +34407,25 @@
         <v>308</v>
       </c>
       <c r="D312" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="E312">
         <v>2022</v>
       </c>
       <c r="F312">
-        <v>1.0883760118599757</v>
+        <v>4.3145340623605172E-2</v>
       </c>
       <c r="G312">
         <v>1</v>
       </c>
       <c r="H312">
-        <v>2750</v>
+        <v>3712.5000000000005</v>
       </c>
       <c r="I312">
-        <v>55.000000000000007</v>
+        <v>71.5</v>
       </c>
       <c r="J312">
-        <v>2.1</v>
+        <v>2.52</v>
       </c>
       <c r="K312">
         <v>100</v>
@@ -34460,13 +34460,13 @@
         <v>308</v>
       </c>
       <c r="D313" t="s">
-        <v>313</v>
+        <v>20</v>
       </c>
       <c r="E313">
         <v>2022</v>
       </c>
       <c r="F313">
-        <v>0.15541601192373908</v>
+        <v>0.11134281451252948</v>
       </c>
       <c r="G313">
         <v>1</v>
@@ -34513,25 +34513,25 @@
         <v>308</v>
       </c>
       <c r="D314" t="s">
-        <v>71</v>
+        <v>312</v>
       </c>
       <c r="E314">
         <v>2022</v>
       </c>
       <c r="F314">
-        <v>0.50939337639482241</v>
+        <v>0.10067246145507874</v>
       </c>
       <c r="G314">
         <v>1</v>
       </c>
       <c r="H314">
-        <v>2750</v>
+        <v>3162.5000000000005</v>
       </c>
       <c r="I314">
-        <v>55.000000000000007</v>
+        <v>60.500000000000014</v>
       </c>
       <c r="J314">
-        <v>2.1</v>
+        <v>2.3100000000000005</v>
       </c>
       <c r="K314">
         <v>100</v>
@@ -34566,13 +34566,13 @@
         <v>308</v>
       </c>
       <c r="D315" t="s">
-        <v>61</v>
+        <v>313</v>
       </c>
       <c r="E315">
         <v>2022</v>
       </c>
       <c r="F315">
-        <v>0.23196419690110309</v>
+        <v>0.13036387865841995</v>
       </c>
       <c r="G315">
         <v>1</v>
@@ -34619,25 +34619,25 @@
         <v>308</v>
       </c>
       <c r="D316" t="s">
-        <v>314</v>
+        <v>204</v>
       </c>
       <c r="E316">
         <v>2022</v>
       </c>
       <c r="F316">
-        <v>4.4073197411209589E-2</v>
+        <v>7.8403898552572848E-2</v>
       </c>
       <c r="G316">
         <v>1</v>
       </c>
       <c r="H316">
-        <v>3712.5000000000005</v>
+        <v>3162.5000000000005</v>
       </c>
       <c r="I316">
-        <v>71.5</v>
+        <v>60.500000000000014</v>
       </c>
       <c r="J316">
-        <v>2.52</v>
+        <v>2.3100000000000005</v>
       </c>
       <c r="K316">
         <v>100</v>
@@ -34672,13 +34672,13 @@
         <v>308</v>
       </c>
       <c r="D317" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="E317">
         <v>2022</v>
       </c>
       <c r="F317">
-        <v>6.9589259070330922E-2</v>
+        <v>0.19299421182171778</v>
       </c>
       <c r="G317">
         <v>1</v>
@@ -34687,7 +34687,7 @@
         <v>3162.5000000000005</v>
       </c>
       <c r="I317">
-        <v>60.500000000000007</v>
+        <v>60.500000000000014</v>
       </c>
       <c r="J317">
         <v>2.3100000000000005</v>
@@ -34725,25 +34725,25 @@
         <v>308</v>
       </c>
       <c r="D318" t="s">
-        <v>316</v>
+        <v>239</v>
       </c>
       <c r="E318">
         <v>2022</v>
       </c>
       <c r="F318">
-        <v>0.35629700644009438</v>
+        <v>0.22871669814448767</v>
       </c>
       <c r="G318">
         <v>1</v>
       </c>
       <c r="H318">
-        <v>2750</v>
+        <v>3162.5000000000005</v>
       </c>
       <c r="I318">
-        <v>55</v>
+        <v>60.500000000000014</v>
       </c>
       <c r="J318">
-        <v>2.1</v>
+        <v>2.3100000000000005</v>
       </c>
       <c r="K318">
         <v>100</v>
@@ -34778,25 +34778,25 @@
         <v>308</v>
       </c>
       <c r="D319" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="E319">
         <v>2022</v>
       </c>
       <c r="F319">
-        <v>4.1753555442198553E-2</v>
+        <v>0.54140443556717466</v>
       </c>
       <c r="G319">
         <v>1</v>
       </c>
       <c r="H319">
-        <v>3712.5000000000005</v>
+        <v>2750</v>
       </c>
       <c r="I319">
-        <v>71.5</v>
+        <v>55.000000000000007</v>
       </c>
       <c r="J319">
-        <v>2.52</v>
+        <v>2.1</v>
       </c>
       <c r="K319">
         <v>100</v>
@@ -34831,25 +34831,25 @@
         <v>308</v>
       </c>
       <c r="D320" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="E320">
         <v>2022</v>
       </c>
       <c r="F320">
-        <v>0.10670353057450742</v>
+        <v>4.4073197411209589E-2</v>
       </c>
       <c r="G320">
         <v>1</v>
       </c>
       <c r="H320">
-        <v>3162.5000000000005</v>
+        <v>3712.5000000000005</v>
       </c>
       <c r="I320">
-        <v>60.500000000000014</v>
+        <v>71.5</v>
       </c>
       <c r="J320">
-        <v>2.3100000000000005</v>
+        <v>2.52</v>
       </c>
       <c r="K320">
         <v>100</v>
@@ -34884,25 +34884,25 @@
         <v>308</v>
       </c>
       <c r="D321" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="E321">
         <v>2022</v>
       </c>
       <c r="F321">
-        <v>4.3145340623605172E-2</v>
+        <v>6.9589259070330922E-2</v>
       </c>
       <c r="G321">
         <v>1</v>
       </c>
       <c r="H321">
-        <v>3712.5000000000005</v>
+        <v>3162.5000000000005</v>
       </c>
       <c r="I321">
-        <v>71.5</v>
+        <v>60.500000000000007</v>
       </c>
       <c r="J321">
-        <v>2.52</v>
+        <v>2.3100000000000005</v>
       </c>
       <c r="K321">
         <v>100</v>
@@ -34937,25 +34937,25 @@
         <v>308</v>
       </c>
       <c r="D322" t="s">
-        <v>320</v>
+        <v>79</v>
       </c>
       <c r="E322">
         <v>2022</v>
       </c>
       <c r="F322">
-        <v>4.4073197411209589E-2</v>
+        <v>0.50939337639482241</v>
       </c>
       <c r="G322">
         <v>1</v>
       </c>
       <c r="H322">
-        <v>3712.5000000000005</v>
+        <v>2750</v>
       </c>
       <c r="I322">
-        <v>71.5</v>
+        <v>55.000000000000007</v>
       </c>
       <c r="J322">
-        <v>2.52</v>
+        <v>2.1</v>
       </c>
       <c r="K322">
         <v>100</v>
@@ -34990,25 +34990,25 @@
         <v>308</v>
       </c>
       <c r="D323" t="s">
-        <v>193</v>
+        <v>151</v>
       </c>
       <c r="E323">
         <v>2022</v>
       </c>
       <c r="F323">
-        <v>0.61052976624370348</v>
+        <v>4.5464982592616207E-2</v>
       </c>
       <c r="G323">
         <v>1</v>
       </c>
       <c r="H323">
-        <v>2750</v>
+        <v>3712.5000000000005</v>
       </c>
       <c r="I323">
-        <v>55.000000000000007</v>
+        <v>71.5</v>
       </c>
       <c r="J323">
-        <v>2.1</v>
+        <v>2.52</v>
       </c>
       <c r="K323">
         <v>100</v>
@@ -35043,13 +35043,13 @@
         <v>308</v>
       </c>
       <c r="D324" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="E324">
         <v>2022</v>
       </c>
       <c r="F324">
-        <v>0.20320063648536632</v>
+        <v>5.1032123318242681E-2</v>
       </c>
       <c r="G324">
         <v>1</v>
@@ -35058,7 +35058,7 @@
         <v>3162.5000000000005</v>
       </c>
       <c r="I324">
-        <v>60.500000000000014</v>
+        <v>60.500000000000021</v>
       </c>
       <c r="J324">
         <v>2.3100000000000005</v>
@@ -35096,13 +35096,13 @@
         <v>308</v>
       </c>
       <c r="D325" t="s">
-        <v>322</v>
+        <v>58</v>
       </c>
       <c r="E325">
         <v>2022</v>
       </c>
       <c r="F325">
-        <v>0.10067246145507874</v>
+        <v>0.23196419690110309</v>
       </c>
       <c r="G325">
         <v>1</v>
@@ -35149,13 +35149,13 @@
         <v>308</v>
       </c>
       <c r="D326" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="E326">
         <v>2022</v>
       </c>
       <c r="F326">
-        <v>6.3558189950902247E-2</v>
+        <v>0.1577356538927501</v>
       </c>
       <c r="G326">
         <v>1</v>
@@ -35202,13 +35202,13 @@
         <v>308</v>
       </c>
       <c r="D327" t="s">
-        <v>324</v>
+        <v>19</v>
       </c>
       <c r="E327">
         <v>2022</v>
       </c>
       <c r="F327">
-        <v>5.1032123318242681E-2</v>
+        <v>8.7682466428616976E-2</v>
       </c>
       <c r="G327">
         <v>1</v>
@@ -35217,7 +35217,7 @@
         <v>3162.5000000000005</v>
       </c>
       <c r="I327">
-        <v>60.500000000000021</v>
+        <v>60.500000000000007</v>
       </c>
       <c r="J327">
         <v>2.3100000000000005</v>
@@ -35255,13 +35255,13 @@
         <v>308</v>
       </c>
       <c r="D328" t="s">
-        <v>19</v>
+        <v>320</v>
       </c>
       <c r="E328">
         <v>2022</v>
       </c>
       <c r="F328">
-        <v>8.7682466428616976E-2</v>
+        <v>5.8918906012880183E-2</v>
       </c>
       <c r="G328">
         <v>1</v>
@@ -35270,7 +35270,7 @@
         <v>3162.5000000000005</v>
       </c>
       <c r="I328">
-        <v>60.500000000000007</v>
+        <v>60.500000000000021</v>
       </c>
       <c r="J328">
         <v>2.3100000000000005</v>
@@ -35308,25 +35308,25 @@
         <v>308</v>
       </c>
       <c r="D329" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="E329">
         <v>2022</v>
       </c>
       <c r="F329">
-        <v>5.8918906012880183E-2</v>
+        <v>0.35629700644009438</v>
       </c>
       <c r="G329">
         <v>1</v>
       </c>
       <c r="H329">
-        <v>3162.5000000000005</v>
+        <v>2750</v>
       </c>
       <c r="I329">
-        <v>60.500000000000021</v>
+        <v>55</v>
       </c>
       <c r="J329">
-        <v>2.3100000000000005</v>
+        <v>2.1</v>
       </c>
       <c r="K329">
         <v>100</v>
@@ -35361,13 +35361,13 @@
         <v>308</v>
       </c>
       <c r="D330" t="s">
-        <v>326</v>
+        <v>69</v>
       </c>
       <c r="E330">
         <v>2022</v>
       </c>
       <c r="F330">
-        <v>0.19299421182171778</v>
+        <v>5.4743550468660328E-2</v>
       </c>
       <c r="G330">
         <v>1</v>
@@ -35414,25 +35414,25 @@
         <v>308</v>
       </c>
       <c r="D331" t="s">
-        <v>327</v>
+        <v>322</v>
       </c>
       <c r="E331">
         <v>2022</v>
       </c>
       <c r="F331">
-        <v>6.0310691194286808E-2</v>
+        <v>4.1753555442198553E-2</v>
       </c>
       <c r="G331">
         <v>1</v>
       </c>
       <c r="H331">
-        <v>3162.5000000000005</v>
+        <v>3712.5000000000005</v>
       </c>
       <c r="I331">
-        <v>60.500000000000014</v>
+        <v>71.5</v>
       </c>
       <c r="J331">
-        <v>2.3100000000000005</v>
+        <v>2.52</v>
       </c>
       <c r="K331">
         <v>100</v>
@@ -35467,25 +35467,25 @@
         <v>308</v>
       </c>
       <c r="D332" t="s">
-        <v>58</v>
+        <v>323</v>
       </c>
       <c r="E332">
         <v>2022</v>
       </c>
       <c r="F332">
-        <v>5.4743550468660328E-2</v>
+        <v>4.4073197411209589E-2</v>
       </c>
       <c r="G332">
         <v>1</v>
       </c>
       <c r="H332">
-        <v>3162.5000000000005</v>
+        <v>3712.5000000000005</v>
       </c>
       <c r="I332">
-        <v>60.500000000000014</v>
+        <v>71.5</v>
       </c>
       <c r="J332">
-        <v>2.3100000000000005</v>
+        <v>2.52</v>
       </c>
       <c r="K332">
         <v>100</v>
@@ -35520,25 +35520,25 @@
         <v>308</v>
       </c>
       <c r="D333" t="s">
-        <v>239</v>
+        <v>324</v>
       </c>
       <c r="E333">
         <v>2022</v>
       </c>
       <c r="F333">
-        <v>0.22871669814448767</v>
+        <v>0.57944656385895543</v>
       </c>
       <c r="G333">
         <v>1</v>
       </c>
       <c r="H333">
-        <v>3162.5000000000005</v>
+        <v>2750</v>
       </c>
       <c r="I333">
-        <v>60.500000000000014</v>
+        <v>55.000000000000007</v>
       </c>
       <c r="J333">
-        <v>2.3100000000000005</v>
+        <v>2.1</v>
       </c>
       <c r="K333">
         <v>100</v>
@@ -35573,25 +35573,25 @@
         <v>308</v>
       </c>
       <c r="D334" t="s">
-        <v>151</v>
+        <v>325</v>
       </c>
       <c r="E334">
         <v>2022</v>
       </c>
       <c r="F334">
-        <v>4.5464982592616207E-2</v>
+        <v>6.3558189950902247E-2</v>
       </c>
       <c r="G334">
         <v>1</v>
       </c>
       <c r="H334">
-        <v>3712.5000000000005</v>
+        <v>3162.5000000000005</v>
       </c>
       <c r="I334">
-        <v>71.5</v>
+        <v>60.500000000000014</v>
       </c>
       <c r="J334">
-        <v>2.52</v>
+        <v>2.3100000000000005</v>
       </c>
       <c r="K334">
         <v>100</v>
@@ -35626,25 +35626,25 @@
         <v>308</v>
       </c>
       <c r="D335" t="s">
-        <v>291</v>
+        <v>193</v>
       </c>
       <c r="E335">
         <v>2022</v>
       </c>
       <c r="F335">
-        <v>0.13082780705222213</v>
+        <v>0.61052976624370348</v>
       </c>
       <c r="G335">
         <v>1</v>
       </c>
       <c r="H335">
-        <v>3162.5000000000005</v>
+        <v>2750</v>
       </c>
       <c r="I335">
-        <v>60.500000000000014</v>
+        <v>55.000000000000007</v>
       </c>
       <c r="J335">
-        <v>2.3100000000000005</v>
+        <v>2.1</v>
       </c>
       <c r="K335">
         <v>100</v>
@@ -35679,13 +35679,13 @@
         <v>308</v>
       </c>
       <c r="D336" t="s">
-        <v>204</v>
+        <v>326</v>
       </c>
       <c r="E336">
         <v>2022</v>
       </c>
       <c r="F336">
-        <v>7.8403898552572848E-2</v>
+        <v>6.0310691194286808E-2</v>
       </c>
       <c r="G336">
         <v>1</v>
@@ -35732,13 +35732,13 @@
         <v>308</v>
       </c>
       <c r="D337" t="s">
-        <v>14</v>
+        <v>291</v>
       </c>
       <c r="E337">
         <v>2022</v>
       </c>
       <c r="F337">
-        <v>0.11134281451252948</v>
+        <v>0.13082780705222213</v>
       </c>
       <c r="G337">
         <v>1</v>
@@ -35785,25 +35785,25 @@
         <v>308</v>
       </c>
       <c r="D338" t="s">
-        <v>99</v>
+        <v>327</v>
       </c>
       <c r="E338">
         <v>2022</v>
       </c>
       <c r="F338">
-        <v>0.29181095970158766</v>
+        <v>0.56367299846968055</v>
       </c>
       <c r="G338">
         <v>1</v>
       </c>
       <c r="H338">
-        <v>3162.5000000000005</v>
+        <v>2750</v>
       </c>
       <c r="I338">
-        <v>60.500000000000014</v>
+        <v>55.000000000000007</v>
       </c>
       <c r="J338">
-        <v>2.3100000000000005</v>
+        <v>2.1</v>
       </c>
       <c r="K338">
         <v>100</v>
@@ -35844,7 +35844,7 @@
         <v>2022</v>
       </c>
       <c r="F339">
-        <v>0.1577356538927501</v>
+        <v>0.20320063648536632</v>
       </c>
       <c r="G339">
         <v>1</v>
@@ -35897,19 +35897,19 @@
         <v>2022</v>
       </c>
       <c r="F340">
-        <v>0.54140443556717466</v>
+        <v>0.15541601192373908</v>
       </c>
       <c r="G340">
         <v>1</v>
       </c>
       <c r="H340">
-        <v>2750</v>
+        <v>3162.5000000000005</v>
       </c>
       <c r="I340">
-        <v>55.000000000000007</v>
+        <v>60.500000000000014</v>
       </c>
       <c r="J340">
-        <v>2.1</v>
+        <v>2.3100000000000005</v>
       </c>
       <c r="K340">
         <v>100</v>
@@ -35997,7 +35997,7 @@
         <v>308</v>
       </c>
       <c r="D342" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="E342">
         <v>1959</v>
@@ -36209,7 +36209,7 @@
         <v>308</v>
       </c>
       <c r="D346" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="E346">
         <v>1963</v>
@@ -36262,7 +36262,7 @@
         <v>308</v>
       </c>
       <c r="D347" t="s">
-        <v>326</v>
+        <v>314</v>
       </c>
       <c r="E347">
         <v>2015</v>
@@ -36315,7 +36315,7 @@
         <v>308</v>
       </c>
       <c r="D348" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="E348">
         <v>1931</v>
@@ -36368,7 +36368,7 @@
         <v>308</v>
       </c>
       <c r="D349" t="s">
-        <v>329</v>
+        <v>315</v>
       </c>
       <c r="E349">
         <v>1949</v>
@@ -36421,7 +36421,7 @@
         <v>308</v>
       </c>
       <c r="D350" t="s">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="E350">
         <v>1951</v>
@@ -36527,7 +36527,7 @@
         <v>308</v>
       </c>
       <c r="D352" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="E352">
         <v>1958</v>
@@ -36580,7 +36580,7 @@
         <v>308</v>
       </c>
       <c r="D353" t="s">
-        <v>318</v>
+        <v>310</v>
       </c>
       <c r="E353">
         <v>1967</v>
@@ -36633,7 +36633,7 @@
         <v>308</v>
       </c>
       <c r="D354" t="s">
-        <v>321</v>
+        <v>328</v>
       </c>
       <c r="E354">
         <v>1968</v>
@@ -36686,7 +36686,7 @@
         <v>308</v>
       </c>
       <c r="D355" t="s">
-        <v>309</v>
+        <v>327</v>
       </c>
       <c r="E355">
         <v>1929</v>
@@ -36739,7 +36739,7 @@
         <v>308</v>
       </c>
       <c r="D356" t="s">
-        <v>321</v>
+        <v>328</v>
       </c>
       <c r="E356">
         <v>1949</v>
@@ -36845,7 +36845,7 @@
         <v>308</v>
       </c>
       <c r="D358" t="s">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="E358">
         <v>1952</v>
@@ -36898,7 +36898,7 @@
         <v>308</v>
       </c>
       <c r="D359" t="s">
-        <v>309</v>
+        <v>327</v>
       </c>
       <c r="E359">
         <v>1913</v>
@@ -36951,7 +36951,7 @@
         <v>308</v>
       </c>
       <c r="D360" t="s">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="E360">
         <v>1924</v>
@@ -37057,7 +37057,7 @@
         <v>308</v>
       </c>
       <c r="D362" t="s">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="E362">
         <v>1971</v>
@@ -37163,7 +37163,7 @@
         <v>308</v>
       </c>
       <c r="D364" t="s">
-        <v>319</v>
+        <v>311</v>
       </c>
       <c r="E364">
         <v>1927</v>
@@ -37216,7 +37216,7 @@
         <v>308</v>
       </c>
       <c r="D365" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="E365">
         <v>1928</v>
@@ -37322,7 +37322,7 @@
         <v>308</v>
       </c>
       <c r="D367" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="E367">
         <v>1938</v>
@@ -37375,7 +37375,7 @@
         <v>308</v>
       </c>
       <c r="D368" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="E368">
         <v>1920</v>
@@ -37428,7 +37428,7 @@
         <v>308</v>
       </c>
       <c r="D369" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="E369">
         <v>1947</v>
@@ -37481,7 +37481,7 @@
         <v>308</v>
       </c>
       <c r="D370" t="s">
-        <v>328</v>
+        <v>319</v>
       </c>
       <c r="E370">
         <v>1950</v>
@@ -37640,7 +37640,7 @@
         <v>308</v>
       </c>
       <c r="D373" t="s">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="E373">
         <v>1971</v>
@@ -37693,7 +37693,7 @@
         <v>308</v>
       </c>
       <c r="D374" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="E374">
         <v>1959</v>
@@ -37799,7 +37799,7 @@
         <v>308</v>
       </c>
       <c r="D376" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="E376">
         <v>1955</v>
@@ -37852,7 +37852,7 @@
         <v>308</v>
       </c>
       <c r="D377" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="E377">
         <v>1959</v>
@@ -37905,7 +37905,7 @@
         <v>308</v>
       </c>
       <c r="D378" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="E378">
         <v>1954</v>
@@ -38117,7 +38117,7 @@
         <v>308</v>
       </c>
       <c r="D382" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="E382">
         <v>2022</v>
@@ -38329,7 +38329,7 @@
         <v>308</v>
       </c>
       <c r="D386" t="s">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="E386">
         <v>2022</v>
@@ -38435,7 +38435,7 @@
         <v>383</v>
       </c>
       <c r="D388" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="E388">
         <v>1989</v>
@@ -38488,7 +38488,7 @@
         <v>383</v>
       </c>
       <c r="D389" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="E389">
         <v>1975</v>
@@ -38541,7 +38541,7 @@
         <v>383</v>
       </c>
       <c r="D390" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="E390">
         <v>1966</v>
@@ -38594,7 +38594,7 @@
         <v>383</v>
       </c>
       <c r="D391" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="E391">
         <v>2015</v>
@@ -38647,7 +38647,7 @@
         <v>383</v>
       </c>
       <c r="D392" t="s">
-        <v>311</v>
+        <v>324</v>
       </c>
       <c r="E392">
         <v>2015</v>
@@ -38700,7 +38700,7 @@
         <v>383</v>
       </c>
       <c r="D393" t="s">
-        <v>311</v>
+        <v>324</v>
       </c>
       <c r="E393">
         <v>1982</v>
@@ -38753,7 +38753,7 @@
         <v>383</v>
       </c>
       <c r="D394" t="s">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="E394">
         <v>2015</v>
@@ -38806,7 +38806,7 @@
         <v>383</v>
       </c>
       <c r="D395" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="E395">
         <v>2015</v>
@@ -38859,7 +38859,7 @@
         <v>383</v>
       </c>
       <c r="D396" t="s">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="E396">
         <v>1961</v>
@@ -38912,7 +38912,7 @@
         <v>383</v>
       </c>
       <c r="D397" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="E397">
         <v>2005</v>
@@ -38965,7 +38965,7 @@
         <v>383</v>
       </c>
       <c r="D398" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="E398">
         <v>1991</v>
@@ -39124,7 +39124,7 @@
         <v>383</v>
       </c>
       <c r="D401" t="s">
-        <v>309</v>
+        <v>327</v>
       </c>
       <c r="E401">
         <v>1971</v>
@@ -39177,7 +39177,7 @@
         <v>383</v>
       </c>
       <c r="D402" t="s">
-        <v>328</v>
+        <v>319</v>
       </c>
       <c r="E402">
         <v>1973</v>
@@ -39336,7 +39336,7 @@
         <v>383</v>
       </c>
       <c r="D405" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="E405">
         <v>1978</v>
@@ -39389,7 +39389,7 @@
         <v>383</v>
       </c>
       <c r="D406" t="s">
-        <v>329</v>
+        <v>315</v>
       </c>
       <c r="E406">
         <v>1923</v>
@@ -39442,7 +39442,7 @@
         <v>308</v>
       </c>
       <c r="D407" t="s">
-        <v>325</v>
+        <v>320</v>
       </c>
       <c r="E407">
         <v>1959</v>
@@ -39548,7 +39548,7 @@
         <v>308</v>
       </c>
       <c r="D409" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="E409">
         <v>1949</v>
@@ -39601,7 +39601,7 @@
         <v>308</v>
       </c>
       <c r="D410" t="s">
-        <v>313</v>
+        <v>329</v>
       </c>
       <c r="E410">
         <v>1953</v>
@@ -39707,7 +39707,7 @@
         <v>308</v>
       </c>
       <c r="D412" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="E412">
         <v>1960</v>
@@ -39760,7 +39760,7 @@
         <v>308</v>
       </c>
       <c r="D413" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="E413">
         <v>1962</v>
@@ -39813,7 +39813,7 @@
         <v>308</v>
       </c>
       <c r="D414" t="s">
-        <v>329</v>
+        <v>315</v>
       </c>
       <c r="E414">
         <v>2015</v>
@@ -39866,7 +39866,7 @@
         <v>308</v>
       </c>
       <c r="D415" t="s">
-        <v>321</v>
+        <v>328</v>
       </c>
       <c r="E415">
         <v>1927</v>
@@ -39919,7 +39919,7 @@
         <v>308</v>
       </c>
       <c r="D416" t="s">
-        <v>324</v>
+        <v>318</v>
       </c>
       <c r="E416">
         <v>1954</v>
@@ -40025,7 +40025,7 @@
         <v>308</v>
       </c>
       <c r="D418" t="s">
-        <v>329</v>
+        <v>315</v>
       </c>
       <c r="E418">
         <v>1956</v>
@@ -40078,7 +40078,7 @@
         <v>308</v>
       </c>
       <c r="D419" t="s">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="E419">
         <v>1956</v>
@@ -40184,7 +40184,7 @@
         <v>308</v>
       </c>
       <c r="D421" t="s">
-        <v>329</v>
+        <v>315</v>
       </c>
       <c r="E421">
         <v>1960</v>
@@ -40290,7 +40290,7 @@
         <v>308</v>
       </c>
       <c r="D423" t="s">
-        <v>326</v>
+        <v>314</v>
       </c>
       <c r="E423">
         <v>2015</v>
@@ -40396,7 +40396,7 @@
         <v>308</v>
       </c>
       <c r="D425" t="s">
-        <v>321</v>
+        <v>328</v>
       </c>
       <c r="E425">
         <v>2015</v>
@@ -40449,7 +40449,7 @@
         <v>308</v>
       </c>
       <c r="D426" t="s">
-        <v>311</v>
+        <v>324</v>
       </c>
       <c r="E426">
         <v>2015</v>
@@ -40555,7 +40555,7 @@
         <v>308</v>
       </c>
       <c r="D428" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="E428">
         <v>1955</v>
@@ -40714,7 +40714,7 @@
         <v>308</v>
       </c>
       <c r="D431" t="s">
-        <v>319</v>
+        <v>311</v>
       </c>
       <c r="E431">
         <v>1932</v>
@@ -40873,7 +40873,7 @@
         <v>308</v>
       </c>
       <c r="D434" t="s">
-        <v>309</v>
+        <v>327</v>
       </c>
       <c r="E434">
         <v>1924</v>
@@ -40979,7 +40979,7 @@
         <v>308</v>
       </c>
       <c r="D436" t="s">
-        <v>309</v>
+        <v>327</v>
       </c>
       <c r="E436">
         <v>2002</v>
@@ -41085,7 +41085,7 @@
         <v>308</v>
       </c>
       <c r="D438" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="E438">
         <v>1948</v>
@@ -41138,7 +41138,7 @@
         <v>308</v>
       </c>
       <c r="D439" t="s">
-        <v>326</v>
+        <v>314</v>
       </c>
       <c r="E439">
         <v>2015</v>
@@ -41191,7 +41191,7 @@
         <v>308</v>
       </c>
       <c r="D440" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="E440">
         <v>1914</v>
@@ -41297,7 +41297,7 @@
         <v>308</v>
       </c>
       <c r="D442" t="s">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="E442">
         <v>1958</v>
@@ -41350,7 +41350,7 @@
         <v>439</v>
       </c>
       <c r="D443" t="s">
-        <v>69</v>
+        <v>54</v>
       </c>
       <c r="E443">
         <v>1992</v>
@@ -41562,7 +41562,7 @@
         <v>439</v>
       </c>
       <c r="D447" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E447">
         <v>2005</v>
@@ -41827,7 +41827,7 @@
         <v>439</v>
       </c>
       <c r="D452" t="s">
-        <v>69</v>
+        <v>54</v>
       </c>
       <c r="E452">
         <v>1985</v>
@@ -42151,7 +42151,7 @@
         <v>2022</v>
       </c>
       <c r="F458">
-        <v>6.6039408899415779</v>
+        <v>6.6307854518247753</v>
       </c>
       <c r="G458">
         <v>1</v>
@@ -42169,7 +42169,7 @@
         <v>33</v>
       </c>
       <c r="L458">
-        <v>0.21137197268125332</v>
+        <v>0.21113006244706151</v>
       </c>
     </row>
     <row r="459" spans="2:20" x14ac:dyDescent="0.45">
@@ -42180,13 +42180,13 @@
         <v>455</v>
       </c>
       <c r="D459" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="E459">
         <v>2022</v>
       </c>
       <c r="F459">
-        <v>6.6457416582336482</v>
+        <v>6.6039408899415779</v>
       </c>
       <c r="G459">
         <v>1</v>
@@ -42204,7 +42204,7 @@
         <v>33</v>
       </c>
       <c r="L459">
-        <v>0.21137197268125332</v>
+        <v>0.21113006244706151</v>
       </c>
     </row>
     <row r="460" spans="2:20" x14ac:dyDescent="0.45">
@@ -42221,7 +42221,7 @@
         <v>2022</v>
       </c>
       <c r="F460">
-        <v>6.6307854518247753</v>
+        <v>6.6457416582336482</v>
       </c>
       <c r="G460">
         <v>1</v>
@@ -42239,7 +42239,7 @@
         <v>33</v>
       </c>
       <c r="L460">
-        <v>0.21137197268125332</v>
+        <v>0.21113006244706151</v>
       </c>
     </row>
     <row r="461" spans="2:20" x14ac:dyDescent="0.45">
@@ -42285,7 +42285,7 @@
         <v>455</v>
       </c>
       <c r="D462" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="E462">
         <v>2015</v>
@@ -42530,7 +42530,7 @@
         <v>455</v>
       </c>
       <c r="D469" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="E469">
         <v>2010</v>
@@ -42565,7 +42565,7 @@
         <v>455</v>
       </c>
       <c r="D470" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="E470">
         <v>2015</v>
@@ -42606,16 +42606,16 @@
         <v>2015</v>
       </c>
       <c r="F471">
-        <v>3.0300000000000004E-2</v>
+        <v>6.2500000000000014E-2</v>
       </c>
       <c r="G471">
         <v>1</v>
       </c>
       <c r="H471">
-        <v>1336.5</v>
+        <v>1336.4999999999998</v>
       </c>
       <c r="I471">
-        <v>21.449999999999996</v>
+        <v>21.45</v>
       </c>
       <c r="J471">
         <v>0</v>
@@ -42624,7 +42624,7 @@
         <v>40</v>
       </c>
       <c r="L471">
-        <v>0.21332519636224806</v>
+        <v>0.20286272583739912</v>
       </c>
     </row>
     <row r="472" spans="2:12" x14ac:dyDescent="0.45">
@@ -42641,7 +42641,7 @@
         <v>2015</v>
       </c>
       <c r="F472">
-        <v>3.2199999999999993E-2</v>
+        <v>9.1499999999999998E-2</v>
       </c>
       <c r="G472">
         <v>1</v>
@@ -42650,7 +42650,7 @@
         <v>1336.5000000000002</v>
       </c>
       <c r="I472">
-        <v>21.450000000000003</v>
+        <v>21.45</v>
       </c>
       <c r="J472">
         <v>0</v>
@@ -42659,7 +42659,7 @@
         <v>40</v>
       </c>
       <c r="L472">
-        <v>0.19301760605780519</v>
+        <v>0.1997952190987608</v>
       </c>
     </row>
     <row r="473" spans="2:12" x14ac:dyDescent="0.45">
@@ -42673,16 +42673,16 @@
         <v>475</v>
       </c>
       <c r="E473">
-        <v>2015</v>
+        <v>2009</v>
       </c>
       <c r="F473">
-        <v>0.20680000000000001</v>
+        <v>4.4999999999999998E-2</v>
       </c>
       <c r="G473">
         <v>1</v>
       </c>
       <c r="H473">
-        <v>1336.5000000000002</v>
+        <v>1336.5</v>
       </c>
       <c r="I473">
         <v>21.450000000000003</v>
@@ -42691,10 +42691,10 @@
         <v>0</v>
       </c>
       <c r="K473">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="L473">
-        <v>0.22101078675173377</v>
+        <v>0.2145221180349477</v>
       </c>
     </row>
     <row r="474" spans="2:12" x14ac:dyDescent="0.45">
@@ -42708,45 +42708,45 @@
         <v>475</v>
       </c>
       <c r="E474">
-        <v>2020</v>
+        <v>2010</v>
       </c>
       <c r="F474">
-        <v>8.5000000000000006E-2</v>
+        <v>6.0000000000000001E-3</v>
       </c>
       <c r="G474">
         <v>1</v>
       </c>
       <c r="H474">
-        <v>1210.7117647058824</v>
+        <v>1336.5</v>
       </c>
       <c r="I474">
-        <v>19.353529411764708</v>
+        <v>21.450000000000003</v>
       </c>
       <c r="J474">
         <v>0</v>
       </c>
       <c r="K474">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="L474">
-        <v>0.2198394615353855</v>
+        <v>0.2145221180349477</v>
       </c>
     </row>
     <row r="475" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B475" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="C475" t="s">
         <v>455</v>
       </c>
       <c r="D475" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="E475">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="F475">
-        <v>9.300000000000001E-3</v>
+        <v>0.1288</v>
       </c>
       <c r="G475">
         <v>1</v>
@@ -42755,33 +42755,33 @@
         <v>1336.5</v>
       </c>
       <c r="I475">
-        <v>21.450000000000003</v>
+        <v>21.45</v>
       </c>
       <c r="J475">
         <v>0</v>
       </c>
       <c r="K475">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="L475">
-        <v>0.22779083409784781</v>
+        <v>0.21411465223084331</v>
       </c>
     </row>
     <row r="476" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B476" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="C476" t="s">
         <v>455</v>
       </c>
       <c r="D476" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="E476">
-        <v>2010</v>
+        <v>2013</v>
       </c>
       <c r="F476">
-        <v>5.7999999999999996E-3</v>
+        <v>2.1399999999999999E-2</v>
       </c>
       <c r="G476">
         <v>1</v>
@@ -42796,27 +42796,27 @@
         <v>0</v>
       </c>
       <c r="K476">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="L476">
-        <v>0.22779083409784781</v>
+        <v>0.21067761626260839</v>
       </c>
     </row>
     <row r="477" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B477" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="C477" t="s">
         <v>455</v>
       </c>
       <c r="D477" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="E477">
-        <v>2012</v>
+        <v>2015</v>
       </c>
       <c r="F477">
-        <v>0.02</v>
+        <v>0.45100000000000018</v>
       </c>
       <c r="G477">
         <v>1</v>
@@ -42825,182 +42825,182 @@
         <v>1336.5</v>
       </c>
       <c r="I477">
-        <v>21.450000000000003</v>
+        <v>21.45</v>
       </c>
       <c r="J477">
         <v>0</v>
       </c>
       <c r="K477">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="L477">
-        <v>0.22779083409784778</v>
+        <v>0.21157230862003179</v>
       </c>
     </row>
     <row r="478" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B478" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="C478" t="s">
         <v>455</v>
       </c>
       <c r="D478" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="E478">
-        <v>2015</v>
+        <v>2023</v>
       </c>
       <c r="F478">
-        <v>7.3399999999999979E-2</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="G478">
         <v>1</v>
       </c>
       <c r="H478">
-        <v>1336.5</v>
+        <v>1138.5</v>
       </c>
       <c r="I478">
-        <v>21.450000000000017</v>
+        <v>18.150000000000002</v>
       </c>
       <c r="J478">
         <v>0</v>
       </c>
       <c r="K478">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="L478">
-        <v>0.22254285010939953</v>
+        <v>0.2138278512842284</v>
       </c>
     </row>
     <row r="479" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B479" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="C479" t="s">
         <v>455</v>
       </c>
       <c r="D479" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="E479">
-        <v>2018</v>
+        <v>2024</v>
       </c>
       <c r="F479">
-        <v>2.5999999999999999E-2</v>
+        <v>0.13500000000000001</v>
       </c>
       <c r="G479">
         <v>1</v>
       </c>
       <c r="H479">
-        <v>1336.5</v>
+        <v>1258.7666666666667</v>
       </c>
       <c r="I479">
-        <v>21.450000000000003</v>
+        <v>20.154444444444447</v>
       </c>
       <c r="J479">
         <v>0</v>
       </c>
       <c r="K479">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="L479">
-        <v>0.22779083409784781</v>
+        <v>0.2145221180349477</v>
       </c>
     </row>
     <row r="480" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B480" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="C480" t="s">
         <v>455</v>
       </c>
       <c r="D480" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="E480">
-        <v>2022</v>
+        <v>2025</v>
       </c>
       <c r="F480">
-        <v>5.0999999999999995E-3</v>
+        <v>0.32800000000000001</v>
       </c>
       <c r="G480">
         <v>1</v>
       </c>
       <c r="H480">
-        <v>1336.5</v>
+        <v>1165.6646341463415</v>
       </c>
       <c r="I480">
-        <v>21.450000000000003</v>
+        <v>18.602743902439027</v>
       </c>
       <c r="J480">
         <v>0</v>
       </c>
       <c r="K480">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="L480">
-        <v>0.22330548534716901</v>
+        <v>0.21232145889152684</v>
       </c>
     </row>
     <row r="481" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B481" t="s">
-        <v>478</v>
+        <v>474</v>
       </c>
       <c r="C481" t="s">
         <v>455</v>
       </c>
       <c r="D481" t="s">
-        <v>479</v>
+        <v>475</v>
       </c>
       <c r="E481">
-        <v>2011</v>
+        <v>2028</v>
       </c>
       <c r="F481">
-        <v>1.9299999999999998E-2</v>
+        <v>0.19800000000000001</v>
       </c>
       <c r="G481">
         <v>1</v>
       </c>
       <c r="H481">
-        <v>1336.5</v>
+        <v>1186.5</v>
       </c>
       <c r="I481">
-        <v>21.450000000000003</v>
+        <v>18.950000000000003</v>
       </c>
       <c r="J481">
         <v>0</v>
       </c>
       <c r="K481">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="L481">
-        <v>0.22897581092516034</v>
+        <v>0.21307859743256818</v>
       </c>
     </row>
     <row r="482" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B482" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="C482" t="s">
         <v>455</v>
       </c>
       <c r="D482" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="E482">
         <v>2015</v>
       </c>
       <c r="F482">
-        <v>0.15100000000000002</v>
+        <v>0.20560000000000006</v>
       </c>
       <c r="G482">
         <v>1</v>
       </c>
       <c r="H482">
-        <v>1249.9569536423842</v>
+        <v>1336.4999999999998</v>
       </c>
       <c r="I482">
-        <v>20.007615894039731</v>
+        <v>21.450000000000003</v>
       </c>
       <c r="J482">
         <v>0</v>
@@ -43009,7 +43009,7 @@
         <v>40</v>
       </c>
       <c r="L482">
-        <v>0.22929965432338417</v>
+        <v>0.19688949549367962</v>
       </c>
     </row>
     <row r="483" spans="2:12" x14ac:dyDescent="0.45">
@@ -43023,63 +43023,63 @@
         <v>479</v>
       </c>
       <c r="E483">
-        <v>2024</v>
+        <v>2011</v>
       </c>
       <c r="F483">
-        <v>5.0999999999999997E-2</v>
+        <v>1.0500000000000001E-2</v>
       </c>
       <c r="G483">
         <v>1</v>
       </c>
       <c r="H483">
-        <v>1138.5</v>
+        <v>1336.5</v>
       </c>
       <c r="I483">
-        <v>18.150000000000002</v>
+        <v>21.450000000000003</v>
       </c>
       <c r="J483">
         <v>0</v>
       </c>
       <c r="K483">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="L483">
-        <v>0.22897581092516031</v>
+        <v>0.19372001814840661</v>
       </c>
     </row>
     <row r="484" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B484" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="C484" t="s">
         <v>455</v>
       </c>
       <c r="D484" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="E484">
-        <v>2010</v>
+        <v>2015</v>
       </c>
       <c r="F484">
-        <v>7.6E-3</v>
+        <v>3.2699999999999993E-2</v>
       </c>
       <c r="G484">
         <v>1</v>
       </c>
       <c r="H484">
-        <v>1336.5</v>
+        <v>1336.5000000000002</v>
       </c>
       <c r="I484">
-        <v>21.450000000000003</v>
+        <v>21.450000000000006</v>
       </c>
       <c r="J484">
         <v>0</v>
       </c>
       <c r="K484">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="L484">
-        <v>0.22621581035120261</v>
+        <v>0.18489803177812383</v>
       </c>
     </row>
     <row r="485" spans="2:12" x14ac:dyDescent="0.45">
@@ -43093,28 +43093,28 @@
         <v>481</v>
       </c>
       <c r="E485">
-        <v>2011</v>
+        <v>2010</v>
       </c>
       <c r="F485">
-        <v>3.5700000000000003E-2</v>
+        <v>7.5999999999999998E-2</v>
       </c>
       <c r="G485">
         <v>1</v>
       </c>
       <c r="H485">
-        <v>1336.5</v>
+        <v>1154.1315789473683</v>
       </c>
       <c r="I485">
-        <v>21.450000000000003</v>
+        <v>18.410526315789479</v>
       </c>
       <c r="J485">
         <v>0</v>
       </c>
       <c r="K485">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="L485">
-        <v>0.23261826092713075</v>
+        <v>0.18367495595626879</v>
       </c>
     </row>
     <row r="486" spans="2:12" x14ac:dyDescent="0.45">
@@ -43128,10 +43128,10 @@
         <v>481</v>
       </c>
       <c r="E486">
-        <v>2012</v>
+        <v>2011</v>
       </c>
       <c r="F486">
-        <v>9.4999999999999998E-3</v>
+        <v>4.8000000000000001E-2</v>
       </c>
       <c r="G486">
         <v>1</v>
@@ -43146,10 +43146,10 @@
         <v>0</v>
       </c>
       <c r="K486">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="L486">
-        <v>0.23546267084801317</v>
+        <v>0.1830157785160744</v>
       </c>
     </row>
     <row r="487" spans="2:12" x14ac:dyDescent="0.45">
@@ -43163,28 +43163,28 @@
         <v>481</v>
       </c>
       <c r="E487">
-        <v>2013</v>
+        <v>2015</v>
       </c>
       <c r="F487">
-        <v>5.0000000000000001E-3</v>
+        <v>0.32480000000000003</v>
       </c>
       <c r="G487">
         <v>1</v>
       </c>
       <c r="H487">
-        <v>1336.5</v>
+        <v>1336.5000000000002</v>
       </c>
       <c r="I487">
-        <v>21.450000000000003</v>
+        <v>21.449999999999989</v>
       </c>
       <c r="J487">
         <v>0</v>
       </c>
       <c r="K487">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="L487">
-        <v>0.22990287162581269</v>
+        <v>0.18637364754073979</v>
       </c>
     </row>
     <row r="488" spans="2:12" x14ac:dyDescent="0.45">
@@ -43198,10 +43198,10 @@
         <v>481</v>
       </c>
       <c r="E488">
-        <v>2015</v>
+        <v>2023</v>
       </c>
       <c r="F488">
-        <v>0.28910000000000002</v>
+        <v>1.7000000000000001E-2</v>
       </c>
       <c r="G488">
         <v>1</v>
@@ -43210,33 +43210,33 @@
         <v>1336.5</v>
       </c>
       <c r="I488">
-        <v>21.45</v>
+        <v>21.450000000000003</v>
       </c>
       <c r="J488">
         <v>0</v>
       </c>
       <c r="K488">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="L488">
-        <v>0.23157936681277738</v>
+        <v>0.1830157785160744</v>
       </c>
     </row>
     <row r="489" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B489" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="C489" t="s">
         <v>455</v>
       </c>
       <c r="D489" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="E489">
-        <v>2016</v>
+        <v>2011</v>
       </c>
       <c r="F489">
-        <v>0.01</v>
+        <v>2.1499999999999998E-2</v>
       </c>
       <c r="G489">
         <v>1</v>
@@ -43251,33 +43251,33 @@
         <v>0</v>
       </c>
       <c r="K489">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="L489">
-        <v>0.22990287162581269</v>
+        <v>0.17348833543116779</v>
       </c>
     </row>
     <row r="490" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B490" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="C490" t="s">
         <v>455</v>
       </c>
       <c r="D490" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="E490">
-        <v>2022</v>
+        <v>2015</v>
       </c>
       <c r="F490">
-        <v>9.6999999999999986E-3</v>
+        <v>0.1004</v>
       </c>
       <c r="G490">
         <v>1</v>
       </c>
       <c r="H490">
-        <v>1336.5</v>
+        <v>1336.4999999999998</v>
       </c>
       <c r="I490">
         <v>21.450000000000003</v>
@@ -43286,27 +43286,27 @@
         <v>0</v>
       </c>
       <c r="K490">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="L490">
-        <v>0.23546267084801323</v>
+        <v>0.17324856438753491</v>
       </c>
     </row>
     <row r="491" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B491" t="s">
-        <v>480</v>
+        <v>484</v>
       </c>
       <c r="C491" t="s">
         <v>455</v>
       </c>
       <c r="D491" t="s">
-        <v>481</v>
+        <v>485</v>
       </c>
       <c r="E491">
-        <v>2023</v>
+        <v>2015</v>
       </c>
       <c r="F491">
-        <v>4.1000000000000002E-2</v>
+        <v>1.8200000000000001E-2</v>
       </c>
       <c r="G491">
         <v>1</v>
@@ -43315,39 +43315,39 @@
         <v>1336.5</v>
       </c>
       <c r="I491">
-        <v>21.450000000000003</v>
+        <v>21.450000000000006</v>
       </c>
       <c r="J491">
         <v>0</v>
       </c>
       <c r="K491">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="L491">
-        <v>0.22990287162581269</v>
+        <v>0.17579142700954378</v>
       </c>
     </row>
     <row r="492" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B492" t="s">
-        <v>480</v>
+        <v>486</v>
       </c>
       <c r="C492" t="s">
         <v>455</v>
       </c>
       <c r="D492" t="s">
-        <v>481</v>
+        <v>487</v>
       </c>
       <c r="E492">
-        <v>2025</v>
+        <v>2015</v>
       </c>
       <c r="F492">
-        <v>1.7999999999999999E-2</v>
+        <v>0.20680000000000001</v>
       </c>
       <c r="G492">
         <v>1</v>
       </c>
       <c r="H492">
-        <v>1336.5</v>
+        <v>1336.5000000000002</v>
       </c>
       <c r="I492">
         <v>21.450000000000003</v>
@@ -43356,132 +43356,132 @@
         <v>0</v>
       </c>
       <c r="K492">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="L492">
-        <v>0.22990287162581266</v>
+        <v>0.22101078675173377</v>
       </c>
     </row>
     <row r="493" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B493" t="s">
-        <v>480</v>
+        <v>486</v>
       </c>
       <c r="C493" t="s">
         <v>455</v>
       </c>
       <c r="D493" t="s">
-        <v>481</v>
+        <v>487</v>
       </c>
       <c r="E493">
-        <v>2026</v>
+        <v>2020</v>
       </c>
       <c r="F493">
-        <v>3.7999999999999999E-2</v>
+        <v>8.5000000000000006E-2</v>
       </c>
       <c r="G493">
         <v>1</v>
       </c>
       <c r="H493">
-        <v>1336.5</v>
+        <v>1210.7117647058824</v>
       </c>
       <c r="I493">
-        <v>21.450000000000003</v>
+        <v>19.353529411764708</v>
       </c>
       <c r="J493">
         <v>0</v>
       </c>
       <c r="K493">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="L493">
-        <v>0.22817316965907841</v>
+        <v>0.2198394615353855</v>
       </c>
     </row>
     <row r="494" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B494" t="s">
-        <v>480</v>
+        <v>488</v>
       </c>
       <c r="C494" t="s">
         <v>455</v>
       </c>
       <c r="D494" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="E494">
-        <v>2028</v>
+        <v>2009</v>
       </c>
       <c r="F494">
-        <v>9.3099999999999988E-2</v>
+        <v>9.300000000000001E-3</v>
       </c>
       <c r="G494">
         <v>1</v>
       </c>
       <c r="H494">
-        <v>1138.5</v>
+        <v>1336.5</v>
       </c>
       <c r="I494">
-        <v>18.150000000000002</v>
+        <v>21.450000000000003</v>
       </c>
       <c r="J494">
         <v>0</v>
       </c>
       <c r="K494">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="L494">
-        <v>0.22735641515094751</v>
+        <v>0.22779083409784781</v>
       </c>
     </row>
     <row r="495" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B495" t="s">
-        <v>482</v>
+        <v>488</v>
       </c>
       <c r="C495" t="s">
         <v>455</v>
       </c>
       <c r="D495" t="s">
-        <v>483</v>
+        <v>489</v>
       </c>
       <c r="E495">
-        <v>2015</v>
+        <v>2010</v>
       </c>
       <c r="F495">
-        <v>0.13950000000000004</v>
+        <v>5.7999999999999996E-3</v>
       </c>
       <c r="G495">
         <v>1</v>
       </c>
       <c r="H495">
-        <v>1336.4999999999998</v>
+        <v>1336.5</v>
       </c>
       <c r="I495">
-        <v>21.450000000000006</v>
+        <v>21.450000000000003</v>
       </c>
       <c r="J495">
         <v>0</v>
       </c>
       <c r="K495">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="L495">
-        <v>0.22263780528731941</v>
+        <v>0.22779083409784781</v>
       </c>
     </row>
     <row r="496" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B496" t="s">
-        <v>484</v>
+        <v>488</v>
       </c>
       <c r="C496" t="s">
         <v>455</v>
       </c>
       <c r="D496" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="E496">
-        <v>2009</v>
+        <v>2012</v>
       </c>
       <c r="F496">
-        <v>5.0000000000000001E-3</v>
+        <v>0.02</v>
       </c>
       <c r="G496">
         <v>1</v>
@@ -43496,27 +43496,27 @@
         <v>0</v>
       </c>
       <c r="K496">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="L496">
-        <v>0.2200335851180813</v>
+        <v>0.22779083409784778</v>
       </c>
     </row>
     <row r="497" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B497" t="s">
-        <v>484</v>
+        <v>488</v>
       </c>
       <c r="C497" t="s">
         <v>455</v>
       </c>
       <c r="D497" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="E497">
-        <v>2010</v>
+        <v>2015</v>
       </c>
       <c r="F497">
-        <v>5.7700000000000001E-2</v>
+        <v>7.3399999999999979E-2</v>
       </c>
       <c r="G497">
         <v>1</v>
@@ -43525,33 +43525,33 @@
         <v>1336.5</v>
       </c>
       <c r="I497">
-        <v>21.450000000000003</v>
+        <v>21.450000000000017</v>
       </c>
       <c r="J497">
         <v>0</v>
       </c>
       <c r="K497">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="L497">
-        <v>0.22037760483842214</v>
+        <v>0.22254285010939953</v>
       </c>
     </row>
     <row r="498" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B498" t="s">
-        <v>484</v>
+        <v>488</v>
       </c>
       <c r="C498" t="s">
         <v>455</v>
       </c>
       <c r="D498" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="E498">
-        <v>2011</v>
+        <v>2018</v>
       </c>
       <c r="F498">
-        <v>2.0799999999999999E-2</v>
+        <v>2.5999999999999999E-2</v>
       </c>
       <c r="G498">
         <v>1</v>
@@ -43566,27 +43566,27 @@
         <v>0</v>
       </c>
       <c r="K498">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="L498">
-        <v>0.22057989228923436</v>
+        <v>0.22779083409784781</v>
       </c>
     </row>
     <row r="499" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B499" t="s">
-        <v>484</v>
+        <v>488</v>
       </c>
       <c r="C499" t="s">
         <v>455</v>
       </c>
       <c r="D499" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="E499">
-        <v>2013</v>
+        <v>2022</v>
       </c>
       <c r="F499">
-        <v>9.1999999999999998E-3</v>
+        <v>5.0999999999999995E-3</v>
       </c>
       <c r="G499">
         <v>1</v>
@@ -43601,202 +43601,202 @@
         <v>0</v>
       </c>
       <c r="K499">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="L499">
-        <v>0.21997659078087359</v>
+        <v>0.22330548534716901</v>
       </c>
     </row>
     <row r="500" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B500" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
       <c r="C500" t="s">
         <v>455</v>
       </c>
       <c r="D500" t="s">
-        <v>485</v>
+        <v>491</v>
       </c>
       <c r="E500">
-        <v>2015</v>
+        <v>2011</v>
       </c>
       <c r="F500">
-        <v>0.25670000000000009</v>
+        <v>1.9299999999999998E-2</v>
       </c>
       <c r="G500">
         <v>1</v>
       </c>
       <c r="H500">
-        <v>1336.4999999999993</v>
+        <v>1336.5</v>
       </c>
       <c r="I500">
-        <v>21.45</v>
+        <v>21.450000000000003</v>
       </c>
       <c r="J500">
         <v>0</v>
       </c>
       <c r="K500">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="L500">
-        <v>0.22051250081948157</v>
+        <v>0.22897581092516034</v>
       </c>
     </row>
     <row r="501" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B501" t="s">
-        <v>486</v>
+        <v>490</v>
       </c>
       <c r="C501" t="s">
         <v>455</v>
       </c>
       <c r="D501" t="s">
-        <v>487</v>
+        <v>491</v>
       </c>
       <c r="E501">
-        <v>2011</v>
+        <v>2015</v>
       </c>
       <c r="F501">
-        <v>3.78E-2</v>
+        <v>0.15100000000000002</v>
       </c>
       <c r="G501">
         <v>1</v>
       </c>
       <c r="H501">
-        <v>1336.5</v>
+        <v>1249.9569536423842</v>
       </c>
       <c r="I501">
-        <v>21.450000000000006</v>
+        <v>20.007615894039731</v>
       </c>
       <c r="J501">
         <v>0</v>
       </c>
       <c r="K501">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="L501">
-        <v>0.21133391274598409</v>
+        <v>0.22929965432338417</v>
       </c>
     </row>
     <row r="502" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B502" t="s">
-        <v>486</v>
+        <v>490</v>
       </c>
       <c r="C502" t="s">
         <v>455</v>
       </c>
       <c r="D502" t="s">
-        <v>487</v>
+        <v>491</v>
       </c>
       <c r="E502">
-        <v>2012</v>
+        <v>2024</v>
       </c>
       <c r="F502">
-        <v>0.03</v>
+        <v>5.0999999999999997E-2</v>
       </c>
       <c r="G502">
         <v>1</v>
       </c>
       <c r="H502">
-        <v>1336.5</v>
+        <v>1138.5</v>
       </c>
       <c r="I502">
-        <v>21.450000000000003</v>
+        <v>18.150000000000002</v>
       </c>
       <c r="J502">
         <v>0</v>
       </c>
       <c r="K502">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="L502">
-        <v>0.21706938938321105</v>
+        <v>0.22897581092516031</v>
       </c>
     </row>
     <row r="503" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B503" t="s">
-        <v>486</v>
+        <v>492</v>
       </c>
       <c r="C503" t="s">
         <v>455</v>
       </c>
       <c r="D503" t="s">
-        <v>487</v>
+        <v>493</v>
       </c>
       <c r="E503">
-        <v>2015</v>
+        <v>2010</v>
       </c>
       <c r="F503">
-        <v>0.18669999999999995</v>
+        <v>7.6E-3</v>
       </c>
       <c r="G503">
         <v>1</v>
       </c>
       <c r="H503">
-        <v>1336.5000000000002</v>
+        <v>1336.5</v>
       </c>
       <c r="I503">
-        <v>21.45000000000001</v>
+        <v>21.450000000000003</v>
       </c>
       <c r="J503">
         <v>0</v>
       </c>
       <c r="K503">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="L503">
-        <v>0.21407140711623759</v>
+        <v>0.22621581035120261</v>
       </c>
     </row>
     <row r="504" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B504" t="s">
-        <v>486</v>
+        <v>492</v>
       </c>
       <c r="C504" t="s">
         <v>455</v>
       </c>
       <c r="D504" t="s">
-        <v>487</v>
+        <v>493</v>
       </c>
       <c r="E504">
-        <v>2020</v>
+        <v>2011</v>
       </c>
       <c r="F504">
-        <v>0.189</v>
+        <v>3.5700000000000003E-2</v>
       </c>
       <c r="G504">
         <v>1</v>
       </c>
       <c r="H504">
-        <v>1180.4047619047619</v>
+        <v>1336.5</v>
       </c>
       <c r="I504">
-        <v>18.848412698412702</v>
+        <v>21.450000000000003</v>
       </c>
       <c r="J504">
         <v>0</v>
       </c>
       <c r="K504">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="L504">
-        <v>0.21045830299807192</v>
+        <v>0.23261826092713075</v>
       </c>
     </row>
     <row r="505" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B505" t="s">
-        <v>486</v>
+        <v>492</v>
       </c>
       <c r="C505" t="s">
         <v>455</v>
       </c>
       <c r="D505" t="s">
-        <v>487</v>
+        <v>493</v>
       </c>
       <c r="E505">
-        <v>2021</v>
+        <v>2012</v>
       </c>
       <c r="F505">
-        <v>1.9E-2</v>
+        <v>9.4999999999999998E-3</v>
       </c>
       <c r="G505">
         <v>1</v>
@@ -43811,27 +43811,27 @@
         <v>0</v>
       </c>
       <c r="K505">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="L505">
-        <v>0.21831799184116799</v>
+        <v>0.23546267084801317</v>
       </c>
     </row>
     <row r="506" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B506" t="s">
-        <v>486</v>
+        <v>492</v>
       </c>
       <c r="C506" t="s">
         <v>455</v>
       </c>
       <c r="D506" t="s">
-        <v>487</v>
+        <v>493</v>
       </c>
       <c r="E506">
-        <v>2028</v>
+        <v>2013</v>
       </c>
       <c r="F506">
-        <v>3.5000000000000003E-2</v>
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="G506">
         <v>1</v>
@@ -43846,27 +43846,27 @@
         <v>0</v>
       </c>
       <c r="K506">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="L506">
-        <v>0.21892389070522661</v>
+        <v>0.22990287162581269</v>
       </c>
     </row>
     <row r="507" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B507" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="C507" t="s">
         <v>455</v>
       </c>
       <c r="D507" t="s">
-        <v>489</v>
+        <v>493</v>
       </c>
       <c r="E507">
-        <v>2011</v>
+        <v>2015</v>
       </c>
       <c r="F507">
-        <v>2.1499999999999998E-2</v>
+        <v>0.28910000000000002</v>
       </c>
       <c r="G507">
         <v>1</v>
@@ -43875,39 +43875,39 @@
         <v>1336.5</v>
       </c>
       <c r="I507">
-        <v>21.450000000000003</v>
+        <v>21.45</v>
       </c>
       <c r="J507">
         <v>0</v>
       </c>
       <c r="K507">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="L507">
-        <v>0.17348833543116779</v>
+        <v>0.23157936681277738</v>
       </c>
     </row>
     <row r="508" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B508" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="C508" t="s">
         <v>455</v>
       </c>
       <c r="D508" t="s">
-        <v>489</v>
+        <v>493</v>
       </c>
       <c r="E508">
-        <v>2015</v>
+        <v>2016</v>
       </c>
       <c r="F508">
-        <v>0.1004</v>
+        <v>0.01</v>
       </c>
       <c r="G508">
         <v>1</v>
       </c>
       <c r="H508">
-        <v>1336.4999999999998</v>
+        <v>1336.5</v>
       </c>
       <c r="I508">
         <v>21.450000000000003</v>
@@ -43916,27 +43916,27 @@
         <v>0</v>
       </c>
       <c r="K508">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="L508">
-        <v>0.17324856438753491</v>
+        <v>0.22990287162581269</v>
       </c>
     </row>
     <row r="509" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B509" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="C509" t="s">
         <v>455</v>
       </c>
       <c r="D509" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="E509">
-        <v>2015</v>
+        <v>2022</v>
       </c>
       <c r="F509">
-        <v>1.8200000000000001E-2</v>
+        <v>9.6999999999999986E-3</v>
       </c>
       <c r="G509">
         <v>1</v>
@@ -43945,16 +43945,16 @@
         <v>1336.5</v>
       </c>
       <c r="I509">
-        <v>21.450000000000006</v>
+        <v>21.450000000000003</v>
       </c>
       <c r="J509">
         <v>0</v>
       </c>
       <c r="K509">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="L509">
-        <v>0.17579142700954378</v>
+        <v>0.23546267084801323</v>
       </c>
     </row>
     <row r="510" spans="2:12" x14ac:dyDescent="0.45">
@@ -43968,45 +43968,45 @@
         <v>493</v>
       </c>
       <c r="E510">
-        <v>2015</v>
+        <v>2023</v>
       </c>
       <c r="F510">
-        <v>0.15690000000000001</v>
+        <v>4.1000000000000002E-2</v>
       </c>
       <c r="G510">
         <v>1</v>
       </c>
       <c r="H510">
-        <v>1336.4999999999998</v>
+        <v>1336.5</v>
       </c>
       <c r="I510">
-        <v>21.45</v>
+        <v>21.450000000000003</v>
       </c>
       <c r="J510">
         <v>0</v>
       </c>
       <c r="K510">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="L510">
-        <v>0.20418013528360995</v>
+        <v>0.22990287162581269</v>
       </c>
     </row>
     <row r="511" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B511" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="C511" t="s">
         <v>455</v>
       </c>
       <c r="D511" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="E511">
-        <v>2009</v>
+        <v>2025</v>
       </c>
       <c r="F511">
-        <v>4.4999999999999998E-2</v>
+        <v>1.7999999999999999E-2</v>
       </c>
       <c r="G511">
         <v>1</v>
@@ -44021,27 +44021,27 @@
         <v>0</v>
       </c>
       <c r="K511">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="L511">
-        <v>0.2145221180349477</v>
+        <v>0.22990287162581266</v>
       </c>
     </row>
     <row r="512" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B512" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="C512" t="s">
         <v>455</v>
       </c>
       <c r="D512" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="E512">
-        <v>2010</v>
+        <v>2026</v>
       </c>
       <c r="F512">
-        <v>6.0000000000000001E-3</v>
+        <v>3.7999999999999999E-2</v>
       </c>
       <c r="G512">
         <v>1</v>
@@ -44056,45 +44056,45 @@
         <v>0</v>
       </c>
       <c r="K512">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="L512">
-        <v>0.2145221180349477</v>
+        <v>0.22817316965907841</v>
       </c>
     </row>
     <row r="513" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B513" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="C513" t="s">
         <v>455</v>
       </c>
       <c r="D513" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="E513">
-        <v>2011</v>
+        <v>2028</v>
       </c>
       <c r="F513">
-        <v>0.10100000000000001</v>
+        <v>9.3099999999999988E-2</v>
       </c>
       <c r="G513">
         <v>1</v>
       </c>
       <c r="H513">
-        <v>1336.5</v>
+        <v>1138.5</v>
       </c>
       <c r="I513">
-        <v>21.450000000000003</v>
+        <v>18.150000000000002</v>
       </c>
       <c r="J513">
         <v>0</v>
       </c>
       <c r="K513">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="L513">
-        <v>0.21419359348149575</v>
+        <v>0.22735641515094751</v>
       </c>
     </row>
     <row r="514" spans="2:12" x14ac:dyDescent="0.45">
@@ -44111,16 +44111,16 @@
         <v>2015</v>
       </c>
       <c r="F514">
-        <v>0.31230000000000013</v>
+        <v>0.14520000000000005</v>
       </c>
       <c r="G514">
         <v>1</v>
       </c>
       <c r="H514">
-        <v>1336.4999999999998</v>
+        <v>1336.4999999999995</v>
       </c>
       <c r="I514">
-        <v>21.449999999999996</v>
+        <v>21.45</v>
       </c>
       <c r="J514">
         <v>0</v>
@@ -44129,112 +44129,112 @@
         <v>40</v>
       </c>
       <c r="L514">
-        <v>0.21057056744960562</v>
+        <v>0.20450924525813621</v>
       </c>
     </row>
     <row r="515" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B515" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="C515" t="s">
         <v>455</v>
       </c>
       <c r="D515" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="E515">
-        <v>2024</v>
+        <v>2011</v>
       </c>
       <c r="F515">
-        <v>0.13500000000000001</v>
+        <v>2.9000000000000001E-2</v>
       </c>
       <c r="G515">
         <v>1</v>
       </c>
       <c r="H515">
-        <v>1258.7666666666667</v>
+        <v>1336.5</v>
       </c>
       <c r="I515">
-        <v>20.154444444444447</v>
+        <v>21.450000000000003</v>
       </c>
       <c r="J515">
         <v>0</v>
       </c>
       <c r="K515">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="L515">
-        <v>0.2145221180349477</v>
+        <v>0.20597633247206518</v>
       </c>
     </row>
     <row r="516" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B516" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="C516" t="s">
         <v>455</v>
       </c>
       <c r="D516" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="E516">
-        <v>2025</v>
+        <v>2013</v>
       </c>
       <c r="F516">
-        <v>0.223</v>
+        <v>1.8499999999999999E-2</v>
       </c>
       <c r="G516">
         <v>1</v>
       </c>
       <c r="H516">
-        <v>1138.5</v>
+        <v>1336.5</v>
       </c>
       <c r="I516">
-        <v>18.150000000000002</v>
+        <v>21.450000000000003</v>
       </c>
       <c r="J516">
         <v>0</v>
       </c>
       <c r="K516">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="L516">
-        <v>0.21267365757673162</v>
+        <v>0.20718566246803799</v>
       </c>
     </row>
     <row r="517" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B517" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="C517" t="s">
         <v>455</v>
       </c>
       <c r="D517" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="E517">
-        <v>2028</v>
+        <v>2015</v>
       </c>
       <c r="F517">
-        <v>0.15</v>
+        <v>0.25029999999999991</v>
       </c>
       <c r="G517">
         <v>1</v>
       </c>
       <c r="H517">
-        <v>1138.5</v>
+        <v>1336.5000000000005</v>
       </c>
       <c r="I517">
-        <v>18.150000000000002</v>
+        <v>21.450000000000006</v>
       </c>
       <c r="J517">
         <v>0</v>
       </c>
       <c r="K517">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="L517">
-        <v>0.21452211803494767</v>
+        <v>0.20450812804745619</v>
       </c>
     </row>
     <row r="518" spans="2:12" x14ac:dyDescent="0.45">
@@ -44248,10 +44248,10 @@
         <v>497</v>
       </c>
       <c r="E518">
-        <v>2011</v>
+        <v>2028</v>
       </c>
       <c r="F518">
-        <v>5.6799999999999996E-2</v>
+        <v>2.4E-2</v>
       </c>
       <c r="G518">
         <v>1</v>
@@ -44266,167 +44266,167 @@
         <v>0</v>
       </c>
       <c r="K518">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="L518">
-        <v>0.20981915329914508</v>
+        <v>0.2001715484913954</v>
       </c>
     </row>
     <row r="519" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B519" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="C519" t="s">
         <v>455</v>
       </c>
       <c r="D519" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="E519">
-        <v>2013</v>
+        <v>2015</v>
       </c>
       <c r="F519">
-        <v>3.9899999999999998E-2</v>
+        <v>0.13950000000000004</v>
       </c>
       <c r="G519">
         <v>1</v>
       </c>
       <c r="H519">
-        <v>1336.5</v>
+        <v>1336.4999999999998</v>
       </c>
       <c r="I519">
-        <v>21.450000000000003</v>
+        <v>21.450000000000006</v>
       </c>
       <c r="J519">
         <v>0</v>
       </c>
       <c r="K519">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="L519">
-        <v>0.20905853994181761</v>
+        <v>0.22263780528731941</v>
       </c>
     </row>
     <row r="520" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B520" t="s">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="C520" t="s">
         <v>455</v>
       </c>
       <c r="D520" t="s">
-        <v>497</v>
+        <v>501</v>
       </c>
       <c r="E520">
-        <v>2015</v>
+        <v>2009</v>
       </c>
       <c r="F520">
-        <v>0.46879999999999988</v>
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="G520">
         <v>1</v>
       </c>
       <c r="H520">
-        <v>1336.5000000000002</v>
+        <v>1336.5</v>
       </c>
       <c r="I520">
-        <v>21.450000000000006</v>
+        <v>21.450000000000003</v>
       </c>
       <c r="J520">
         <v>0</v>
       </c>
       <c r="K520">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="L520">
-        <v>0.20645573625516284</v>
+        <v>0.2200335851180813</v>
       </c>
     </row>
     <row r="521" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B521" t="s">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="C521" t="s">
         <v>455</v>
       </c>
       <c r="D521" t="s">
-        <v>497</v>
+        <v>501</v>
       </c>
       <c r="E521">
-        <v>2023</v>
+        <v>2010</v>
       </c>
       <c r="F521">
-        <v>7.0000000000000007E-2</v>
+        <v>5.7700000000000001E-2</v>
       </c>
       <c r="G521">
         <v>1</v>
       </c>
       <c r="H521">
-        <v>1138.5</v>
+        <v>1336.5</v>
       </c>
       <c r="I521">
-        <v>18.150000000000002</v>
+        <v>21.450000000000003</v>
       </c>
       <c r="J521">
         <v>0</v>
       </c>
       <c r="K521">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="L521">
-        <v>0.2138278512842284</v>
+        <v>0.22037760483842214</v>
       </c>
     </row>
     <row r="522" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B522" t="s">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="C522" t="s">
         <v>455</v>
       </c>
       <c r="D522" t="s">
-        <v>497</v>
+        <v>501</v>
       </c>
       <c r="E522">
-        <v>2025</v>
+        <v>2011</v>
       </c>
       <c r="F522">
-        <v>0.105</v>
+        <v>2.0799999999999999E-2</v>
       </c>
       <c r="G522">
         <v>1</v>
       </c>
       <c r="H522">
-        <v>1223.3571428571429</v>
+        <v>1336.5</v>
       </c>
       <c r="I522">
-        <v>19.56428571428572</v>
+        <v>21.450000000000003</v>
       </c>
       <c r="J522">
         <v>0</v>
       </c>
       <c r="K522">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="L522">
-        <v>0.2115734559696158</v>
+        <v>0.22057989228923436</v>
       </c>
     </row>
     <row r="523" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B523" t="s">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="C523" t="s">
         <v>455</v>
       </c>
       <c r="D523" t="s">
-        <v>497</v>
+        <v>501</v>
       </c>
       <c r="E523">
-        <v>2028</v>
+        <v>2013</v>
       </c>
       <c r="F523">
-        <v>7.1999999999999995E-2</v>
+        <v>9.1999999999999998E-3</v>
       </c>
       <c r="G523">
         <v>1</v>
@@ -44441,62 +44441,62 @@
         <v>0</v>
       </c>
       <c r="K523">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="L523">
-        <v>0.20576891319722002</v>
+        <v>0.21997659078087359</v>
       </c>
     </row>
     <row r="524" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B524" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="C524" t="s">
         <v>455</v>
       </c>
       <c r="D524" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="E524">
-        <v>2010</v>
+        <v>2015</v>
       </c>
       <c r="F524">
-        <v>7.5999999999999998E-2</v>
+        <v>0.25670000000000009</v>
       </c>
       <c r="G524">
         <v>1</v>
       </c>
       <c r="H524">
-        <v>1154.1315789473683</v>
+        <v>1336.4999999999993</v>
       </c>
       <c r="I524">
-        <v>18.410526315789479</v>
+        <v>21.45</v>
       </c>
       <c r="J524">
         <v>0</v>
       </c>
       <c r="K524">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="L524">
-        <v>0.18367495595626879</v>
+        <v>0.22051250081948157</v>
       </c>
     </row>
     <row r="525" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B525" t="s">
-        <v>498</v>
+        <v>502</v>
       </c>
       <c r="C525" t="s">
         <v>455</v>
       </c>
       <c r="D525" t="s">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="E525">
         <v>2011</v>
       </c>
       <c r="F525">
-        <v>4.8000000000000001E-2</v>
+        <v>3.78E-2</v>
       </c>
       <c r="G525">
         <v>1</v>
@@ -44505,7 +44505,7 @@
         <v>1336.5</v>
       </c>
       <c r="I525">
-        <v>21.450000000000003</v>
+        <v>21.450000000000006</v>
       </c>
       <c r="J525">
         <v>0</v>
@@ -44514,112 +44514,112 @@
         <v>44</v>
       </c>
       <c r="L525">
-        <v>0.1830157785160744</v>
+        <v>0.21133391274598409</v>
       </c>
     </row>
     <row r="526" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B526" t="s">
-        <v>498</v>
+        <v>502</v>
       </c>
       <c r="C526" t="s">
         <v>455</v>
       </c>
       <c r="D526" t="s">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="E526">
-        <v>2015</v>
+        <v>2012</v>
       </c>
       <c r="F526">
-        <v>0.32480000000000003</v>
+        <v>0.03</v>
       </c>
       <c r="G526">
         <v>1</v>
       </c>
       <c r="H526">
-        <v>1336.5000000000002</v>
+        <v>1336.5</v>
       </c>
       <c r="I526">
-        <v>21.449999999999989</v>
+        <v>21.450000000000003</v>
       </c>
       <c r="J526">
         <v>0</v>
       </c>
       <c r="K526">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="L526">
-        <v>0.18637364754073979</v>
+        <v>0.21706938938321105</v>
       </c>
     </row>
     <row r="527" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B527" t="s">
-        <v>498</v>
+        <v>502</v>
       </c>
       <c r="C527" t="s">
         <v>455</v>
       </c>
       <c r="D527" t="s">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="E527">
-        <v>2023</v>
+        <v>2015</v>
       </c>
       <c r="F527">
-        <v>1.7000000000000001E-2</v>
+        <v>0.18669999999999995</v>
       </c>
       <c r="G527">
         <v>1</v>
       </c>
       <c r="H527">
-        <v>1336.5</v>
+        <v>1336.5000000000002</v>
       </c>
       <c r="I527">
-        <v>21.450000000000003</v>
+        <v>21.45000000000001</v>
       </c>
       <c r="J527">
         <v>0</v>
       </c>
       <c r="K527">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="L527">
-        <v>0.1830157785160744</v>
+        <v>0.21407140711623759</v>
       </c>
     </row>
     <row r="528" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B528" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="C528" t="s">
         <v>455</v>
       </c>
       <c r="D528" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="E528">
-        <v>2015</v>
+        <v>2020</v>
       </c>
       <c r="F528">
-        <v>0.20560000000000006</v>
+        <v>0.189</v>
       </c>
       <c r="G528">
         <v>1</v>
       </c>
       <c r="H528">
-        <v>1336.4999999999998</v>
+        <v>1180.4047619047619</v>
       </c>
       <c r="I528">
-        <v>21.450000000000003</v>
+        <v>18.848412698412702</v>
       </c>
       <c r="J528">
         <v>0</v>
       </c>
       <c r="K528">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="L528">
-        <v>0.19688949549367962</v>
+        <v>0.21045830299807192</v>
       </c>
     </row>
     <row r="529" spans="2:12" x14ac:dyDescent="0.45">
@@ -44633,10 +44633,10 @@
         <v>503</v>
       </c>
       <c r="E529">
-        <v>2011</v>
+        <v>2021</v>
       </c>
       <c r="F529">
-        <v>1.0500000000000001E-2</v>
+        <v>1.9E-2</v>
       </c>
       <c r="G529">
         <v>1</v>
@@ -44651,10 +44651,10 @@
         <v>0</v>
       </c>
       <c r="K529">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="L529">
-        <v>0.19372001814840661</v>
+        <v>0.21831799184116799</v>
       </c>
     </row>
     <row r="530" spans="2:12" x14ac:dyDescent="0.45">
@@ -44668,28 +44668,28 @@
         <v>503</v>
       </c>
       <c r="E530">
-        <v>2015</v>
+        <v>2028</v>
       </c>
       <c r="F530">
-        <v>3.2699999999999993E-2</v>
+        <v>3.5000000000000003E-2</v>
       </c>
       <c r="G530">
         <v>1</v>
       </c>
       <c r="H530">
-        <v>1336.5000000000002</v>
+        <v>1336.5</v>
       </c>
       <c r="I530">
-        <v>21.450000000000006</v>
+        <v>21.450000000000003</v>
       </c>
       <c r="J530">
         <v>0</v>
       </c>
       <c r="K530">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="L530">
-        <v>0.18489803177812383</v>
+        <v>0.21892389070522661</v>
       </c>
     </row>
     <row r="531" spans="2:12" x14ac:dyDescent="0.45">
@@ -44735,7 +44735,7 @@
         <v>455</v>
       </c>
       <c r="D532" t="s">
-        <v>479</v>
+        <v>491</v>
       </c>
       <c r="E532">
         <v>2021</v>
@@ -44770,7 +44770,7 @@
         <v>455</v>
       </c>
       <c r="D533" t="s">
-        <v>479</v>
+        <v>491</v>
       </c>
       <c r="E533">
         <v>2028</v>
@@ -44805,7 +44805,7 @@
         <v>455</v>
       </c>
       <c r="D534" t="s">
-        <v>481</v>
+        <v>493</v>
       </c>
       <c r="E534">
         <v>2010</v>
@@ -44840,7 +44840,7 @@
         <v>455</v>
       </c>
       <c r="D535" t="s">
-        <v>481</v>
+        <v>493</v>
       </c>
       <c r="E535">
         <v>2028</v>
@@ -44875,7 +44875,7 @@
         <v>455</v>
       </c>
       <c r="D536" t="s">
-        <v>483</v>
+        <v>499</v>
       </c>
       <c r="E536">
         <v>2014</v>
@@ -44910,7 +44910,7 @@
         <v>509</v>
       </c>
       <c r="D537" t="s">
-        <v>85</v>
+        <v>72</v>
       </c>
       <c r="E537">
         <v>2022</v>
@@ -44945,7 +44945,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="L538">
-        <v>0.20125442366090374</v>
+        <v>0.20125442366090371</v>
       </c>
     </row>
     <row r="539" spans="2:12" x14ac:dyDescent="0.45">
@@ -44968,7 +44968,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="L539">
-        <v>0.20125442366090374</v>
+        <v>0.20125442366090371</v>
       </c>
     </row>
     <row r="540" spans="2:12" x14ac:dyDescent="0.45">
@@ -44991,7 +44991,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="L540">
-        <v>0.20125442366090374</v>
+        <v>0.20125442366090371</v>
       </c>
     </row>
     <row r="541" spans="2:12" x14ac:dyDescent="0.45">
@@ -47808,7 +47808,7 @@
         <v>511</v>
       </c>
       <c r="D663" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="E663">
         <v>2007</v>
@@ -47854,7 +47854,7 @@
         <v>511</v>
       </c>
       <c r="D665" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="E665">
         <v>2008</v>
@@ -47923,19 +47923,19 @@
         <v>511</v>
       </c>
       <c r="D668" t="s">
-        <v>191</v>
+        <v>136</v>
       </c>
       <c r="E668">
         <v>2010</v>
       </c>
       <c r="F668">
-        <v>2.8000000000000001E-2</v>
+        <v>0.03</v>
       </c>
       <c r="G668">
         <v>0.33123000000000002</v>
       </c>
       <c r="L668">
-        <v>2.8502917756321404E-2</v>
+        <v>7.9332316389961105E-2</v>
       </c>
     </row>
     <row r="669" spans="2:12" x14ac:dyDescent="0.45">
@@ -47946,19 +47946,19 @@
         <v>511</v>
       </c>
       <c r="D669" t="s">
-        <v>136</v>
+        <v>191</v>
       </c>
       <c r="E669">
         <v>2010</v>
       </c>
       <c r="F669">
-        <v>0.03</v>
+        <v>2.8000000000000001E-2</v>
       </c>
       <c r="G669">
         <v>0.33123000000000002</v>
       </c>
       <c r="L669">
-        <v>7.9332316389961105E-2</v>
+        <v>2.8502917756321404E-2</v>
       </c>
     </row>
     <row r="670" spans="2:12" x14ac:dyDescent="0.45">
@@ -47969,19 +47969,19 @@
         <v>511</v>
       </c>
       <c r="D670" t="s">
-        <v>136</v>
+        <v>191</v>
       </c>
       <c r="E670">
         <v>2015</v>
       </c>
       <c r="F670">
-        <v>0.192</v>
+        <v>6.9000000000000006E-2</v>
       </c>
       <c r="G670">
         <v>0.33123000000000002</v>
       </c>
       <c r="L670">
-        <v>7.9332316389961105E-2</v>
+        <v>4.6017377963485463E-2</v>
       </c>
     </row>
     <row r="671" spans="2:12" x14ac:dyDescent="0.45">
@@ -47992,19 +47992,19 @@
         <v>511</v>
       </c>
       <c r="D671" t="s">
-        <v>191</v>
+        <v>136</v>
       </c>
       <c r="E671">
         <v>2015</v>
       </c>
       <c r="F671">
-        <v>6.9000000000000006E-2</v>
+        <v>0.192</v>
       </c>
       <c r="G671">
         <v>0.33123000000000002</v>
       </c>
       <c r="L671">
-        <v>4.6017377963485463E-2</v>
+        <v>7.9332316389961105E-2</v>
       </c>
     </row>
     <row r="672" spans="2:12" x14ac:dyDescent="0.45">

--- a/VerveStacks_ITA_grids/vt_vervestacks_ITA_v1.xlsx
+++ b/VerveStacks_ITA_grids/vt_vervestacks_ITA_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6CE3DD1D-3CD3-43CD-8E25-C533BA75AB08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{DE247823-14E8-4728-944B-F3C0F28B072D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2573" yWindow="2573" windowWidth="21600" windowHeight="12682" xr2:uid="{D9BF9E88-4B90-411A-AE6D-578E4113968C}"/>
+    <workbookView xWindow="4043" yWindow="4043" windowWidth="21599" windowHeight="12682" xr2:uid="{5648A1C3-C430-47DF-AA55-ABDF1DF7D4D1}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="2" r:id="rId1"/>
@@ -81,30 +81,30 @@
     <t>bioenergy</t>
   </si>
   <si>
+    <t>e_w98902899-380</t>
+  </si>
+  <si>
+    <t>e_w34157795-380</t>
+  </si>
+  <si>
+    <t>e_w109756016-380</t>
+  </si>
+  <si>
+    <t>e_w108020416-380</t>
+  </si>
+  <si>
+    <t>e_w58440884-380</t>
+  </si>
+  <si>
     <t>e_w84696559-380</t>
   </si>
   <si>
+    <t>e_w144005863-380</t>
+  </si>
+  <si>
     <t>e_w81938081-380</t>
   </si>
   <si>
-    <t>e_w109756016-380</t>
-  </si>
-  <si>
-    <t>e_w98902899-380</t>
-  </si>
-  <si>
-    <t>e_w34157795-380</t>
-  </si>
-  <si>
-    <t>e_w108020416-380</t>
-  </si>
-  <si>
-    <t>e_w144005863-380</t>
-  </si>
-  <si>
-    <t>e_w58440884-380</t>
-  </si>
-  <si>
     <t>ep_bioenergy_G100000200236</t>
   </si>
   <si>
@@ -141,18 +141,18 @@
     <t>coal</t>
   </si>
   <si>
+    <t>e_w418902800-380</t>
+  </si>
+  <si>
     <t>e_w82767145-380</t>
   </si>
   <si>
+    <t>e_w303915533-380</t>
+  </si>
+  <si>
     <t>e_w409439916-380</t>
   </si>
   <si>
-    <t>e_w303915533-380</t>
-  </si>
-  <si>
-    <t>e_w418902800-380</t>
-  </si>
-  <si>
     <t>ep_coal_subcritical_G100000102764</t>
   </si>
   <si>
@@ -189,120 +189,120 @@
     <t>gas</t>
   </si>
   <si>
+    <t>e_w255011550-380</t>
+  </si>
+  <si>
+    <t>e_w1137611914-380</t>
+  </si>
+  <si>
+    <t>e_w61157826-380</t>
+  </si>
+  <si>
+    <t>e_w82078641-380</t>
+  </si>
+  <si>
+    <t>e_w145665799-380</t>
+  </si>
+  <si>
+    <t>e_w60725875-380</t>
+  </si>
+  <si>
+    <t>e_w199675964-380</t>
+  </si>
+  <si>
+    <t>e_w339104227-380</t>
+  </si>
+  <si>
+    <t>e_w59462715-380</t>
+  </si>
+  <si>
+    <t>e_w421827453-380</t>
+  </si>
+  <si>
+    <t>e_w149997403-380</t>
+  </si>
+  <si>
+    <t>e_w100407576-380</t>
+  </si>
+  <si>
+    <t>e_w432729521-380</t>
+  </si>
+  <si>
+    <t>e_w172302572-380</t>
+  </si>
+  <si>
+    <t>e_w103653592-380</t>
+  </si>
+  <si>
+    <t>e_w338753171-380</t>
+  </si>
+  <si>
+    <t>e_w162960205-380</t>
+  </si>
+  <si>
+    <t>e_w82084019-380</t>
+  </si>
+  <si>
+    <t>e_w99826025-380</t>
+  </si>
+  <si>
+    <t>e_w416989699-380</t>
+  </si>
+  <si>
     <t>e_w411026199-380</t>
   </si>
   <si>
-    <t>e_w99826025-380</t>
-  </si>
-  <si>
-    <t>e_w103653592-380</t>
+    <t>e_w107438024-380</t>
+  </si>
+  <si>
+    <t>e_w158739183-380</t>
   </si>
   <si>
     <t>e_w109993642-380</t>
   </si>
   <si>
-    <t>e_w100407576-380</t>
-  </si>
-  <si>
-    <t>e_w149997403-380</t>
-  </si>
-  <si>
-    <t>e_w432729521-380</t>
-  </si>
-  <si>
-    <t>e_w172302572-380</t>
-  </si>
-  <si>
-    <t>e_w338753171-380</t>
-  </si>
-  <si>
-    <t>e_w162960205-380</t>
-  </si>
-  <si>
-    <t>e_w158739183-380</t>
-  </si>
-  <si>
     <t>e_w103974940-380</t>
   </si>
   <si>
+    <t>e_w181125039-380</t>
+  </si>
+  <si>
+    <t>e_w133601335-380</t>
+  </si>
+  <si>
+    <t>e_w103381531-380</t>
+  </si>
+  <si>
+    <t>e_w98900549-380</t>
+  </si>
+  <si>
+    <t>e_w116797658-380</t>
+  </si>
+  <si>
+    <t>e_w419423704-380</t>
+  </si>
+  <si>
+    <t>e_w98421779-380</t>
+  </si>
+  <si>
+    <t>e_w105757794-380</t>
+  </si>
+  <si>
+    <t>e_w110330925-380</t>
+  </si>
+  <si>
+    <t>e_w132450233-380</t>
+  </si>
+  <si>
+    <t>e_w105581403-380</t>
+  </si>
+  <si>
+    <t>e_w162828577-380</t>
+  </si>
+  <si>
     <t>e_w414663585-380</t>
   </si>
   <si>
-    <t>e_w255011550-380</t>
-  </si>
-  <si>
-    <t>e_w421827453-380</t>
-  </si>
-  <si>
-    <t>e_w105581403-380</t>
-  </si>
-  <si>
-    <t>e_w339104227-380</t>
-  </si>
-  <si>
-    <t>e_w82078641-380</t>
-  </si>
-  <si>
-    <t>e_w61157826-380</t>
-  </si>
-  <si>
-    <t>e_w1137611914-380</t>
-  </si>
-  <si>
-    <t>e_w181125039-380</t>
-  </si>
-  <si>
-    <t>e_w133601335-380</t>
-  </si>
-  <si>
-    <t>e_w103381531-380</t>
-  </si>
-  <si>
-    <t>e_w199675964-380</t>
-  </si>
-  <si>
-    <t>e_w59462715-380</t>
-  </si>
-  <si>
-    <t>e_w82084019-380</t>
-  </si>
-  <si>
-    <t>e_w60725875-380</t>
-  </si>
-  <si>
-    <t>e_w145665799-380</t>
-  </si>
-  <si>
-    <t>e_w98421779-380</t>
-  </si>
-  <si>
-    <t>e_w419423704-380</t>
-  </si>
-  <si>
-    <t>e_w116797658-380</t>
-  </si>
-  <si>
-    <t>e_w105757794-380</t>
-  </si>
-  <si>
-    <t>e_w110330925-380</t>
-  </si>
-  <si>
-    <t>e_w132450233-380</t>
-  </si>
-  <si>
-    <t>e_w162828577-380</t>
-  </si>
-  <si>
-    <t>e_w107438024-380</t>
-  </si>
-  <si>
-    <t>e_w98900549-380</t>
-  </si>
-  <si>
-    <t>e_w416989699-380</t>
-  </si>
-  <si>
     <t>ep_gas_combined_cycle_G100000400339</t>
   </si>
   <si>
@@ -966,69 +966,69 @@
     <t>hydro</t>
   </si>
   <si>
+    <t>e_IT72-400</t>
+  </si>
+  <si>
+    <t>e_w1100665914-380</t>
+  </si>
+  <si>
+    <t>e_IT10-380</t>
+  </si>
+  <si>
+    <t>e_IT93-380</t>
+  </si>
+  <si>
+    <t>e_w491424937-380</t>
+  </si>
+  <si>
+    <t>e_w75602396-380</t>
+  </si>
+  <si>
+    <t>e_w114931087-380</t>
+  </si>
+  <si>
+    <t>e_w82083756-380</t>
+  </si>
+  <si>
+    <t>e_w72466334-380</t>
+  </si>
+  <si>
+    <t>e_IT36-380</t>
+  </si>
+  <si>
     <t>e_w64200868-380</t>
   </si>
   <si>
-    <t>e_w491424937-380</t>
-  </si>
-  <si>
-    <t>e_w75602396-380</t>
-  </si>
-  <si>
     <t>e_IT72-380</t>
   </si>
   <si>
-    <t>e_w114931087-380</t>
-  </si>
-  <si>
-    <t>e_w1100665914-380</t>
+    <t>e_w104359058-380</t>
+  </si>
+  <si>
+    <t>e_IT31-380</t>
+  </si>
+  <si>
+    <t>e_IT21-380</t>
+  </si>
+  <si>
+    <t>e_w61626687-380</t>
   </si>
   <si>
     <t>e_IT7-380</t>
   </si>
   <si>
-    <t>e_IT72-400</t>
-  </si>
-  <si>
-    <t>e_IT93-380</t>
-  </si>
-  <si>
-    <t>e_w61626687-380</t>
-  </si>
-  <si>
-    <t>e_w72466334-380</t>
+    <t>e_IT53-380</t>
   </si>
   <si>
     <t>e_IT71-380</t>
   </si>
   <si>
-    <t>e_w82083756-380</t>
-  </si>
-  <si>
     <t>e_w116517585-380</t>
   </si>
   <si>
-    <t>e_IT31-380</t>
-  </si>
-  <si>
-    <t>e_w104359058-380</t>
-  </si>
-  <si>
-    <t>e_IT53-380</t>
-  </si>
-  <si>
     <t>e_IT71-400</t>
   </si>
   <si>
-    <t>e_IT21-380</t>
-  </si>
-  <si>
-    <t>e_IT10-380</t>
-  </si>
-  <si>
-    <t>e_IT36-380</t>
-  </si>
-  <si>
     <t>ep_hydro_dam_G100000602220</t>
   </si>
   <si>
@@ -1575,12 +1575,12 @@
     <t>windon</t>
   </si>
   <si>
+    <t>elc_won_016</t>
+  </si>
+  <si>
     <t>elc_won_015</t>
   </si>
   <si>
-    <t>elc_won_016</t>
-  </si>
-  <si>
     <t>ep_windon_wind_002</t>
   </si>
   <si>
@@ -1698,42 +1698,42 @@
     <t>ele</t>
   </si>
   <si>
+    <t>Aggregated Plant - EMBER Gap - way/81938081-380_Missing Bioenergy Capacity</t>
+  </si>
+  <si>
+    <t>GW</t>
+  </si>
+  <si>
+    <t>TWh</t>
+  </si>
+  <si>
+    <t>daynite</t>
+  </si>
+  <si>
+    <t>yes</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/34157795-380_Missing Bioenergy Capacity</t>
+  </si>
+  <si>
     <t>Aggregated Plant - EMBER Gap - way/58440884-380_Missing Bioenergy Capacity</t>
   </si>
   <si>
-    <t>GW</t>
-  </si>
-  <si>
-    <t>TWh</t>
-  </si>
-  <si>
-    <t>daynite</t>
-  </si>
-  <si>
-    <t>yes</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/34157795-380_Missing Bioenergy Capacity</t>
+    <t>Aggregated Plant - EMBER Gap - way/98902899-380_Missing Bioenergy Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/84696559-380_Missing Bioenergy Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/109756016-380_Missing Bioenergy Capacity</t>
   </si>
   <si>
     <t>Aggregated Plant - EMBER Gap - way/144005863-380_Missing Bioenergy Capacity</t>
   </si>
   <si>
-    <t>Aggregated Plant - EMBER Gap - way/109756016-380_Missing Bioenergy Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/98902899-380_Missing Bioenergy Capacity</t>
-  </si>
-  <si>
     <t>Aggregated Plant - EMBER Gap - way/108020416-380_Missing Bioenergy Capacity</t>
   </si>
   <si>
-    <t>Aggregated Plant - EMBER Gap - way/84696559-380_Missing Bioenergy Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/81938081-380_Missing Bioenergy Capacity</t>
-  </si>
-  <si>
     <t>Acerra power station_1</t>
   </si>
   <si>
@@ -1797,123 +1797,123 @@
     <t>Torrevaldaliga Nord power station_Unit 3</t>
   </si>
   <si>
+    <t>Aggregated Plant - EMBER Gap - way/116797658-380_Missing Gas Capacity</t>
+  </si>
+  <si>
     <t>Aggregated Plant - EMBER Gap - way/107438024-380_Missing Gas Capacity</t>
   </si>
   <si>
-    <t>Aggregated Plant - EMBER Gap - way/116797658-380_Missing Gas Capacity</t>
-  </si>
-  <si>
     <t>Aggregated Plant - EMBER Gap - way/339104227-380_Missing Gas Capacity</t>
   </si>
   <si>
+    <t>Aggregated Plant - EMBER Gap - way/110330925-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/411026199-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/82084019-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/109756016-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/98421779-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/105581403-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/172302572-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/59462715-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/105757794-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/255011550-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/181125039-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/432729521-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/199675964-380_Missing Gas Capacity</t>
+  </si>
+  <si>
     <t>Aggregated Plant - EMBER Gap - way/162828577-380_Missing Gas Capacity</t>
   </si>
   <si>
     <t>Aggregated Plant - EMBER Gap - way/98900549-380_Missing Gas Capacity</t>
   </si>
   <si>
-    <t>Aggregated Plant - EMBER Gap - way/199675964-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/181125039-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/432729521-380_Missing Gas Capacity</t>
+    <t>Aggregated Plant - EMBER Gap - way/338753171-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/103653592-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/416989699-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/100407576-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/60725875-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/1137611914-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/145665799-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/158739183-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/132450233-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/414663585-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/421827453-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/99826025-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/82767145-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/61157826-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/419423704-380_Missing Gas Capacity</t>
   </si>
   <si>
     <t>Aggregated Plant - EMBER Gap - way/109993642-380_Missing Gas Capacity</t>
   </si>
   <si>
-    <t>Aggregated Plant - EMBER Gap - way/82767145-380_Missing Gas Capacity</t>
+    <t>Aggregated Plant - EMBER Gap - way/82078641-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/103974940-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/149997403-380_Missing Gas Capacity</t>
   </si>
   <si>
     <t>Aggregated Plant - EMBER Gap - way/103381531-380_Missing Gas Capacity</t>
   </si>
   <si>
-    <t>Aggregated Plant - EMBER Gap - way/60725875-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/82078641-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/103974940-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/416989699-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/103653592-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/100407576-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/145665799-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/1137611914-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/158739183-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/149997403-380_Missing Gas Capacity</t>
-  </si>
-  <si>
     <t>Aggregated Plant - EMBER Gap - way/133601335-380_Missing Gas Capacity</t>
   </si>
   <si>
-    <t>Aggregated Plant - EMBER Gap - way/338753171-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/255011550-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/172302572-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/105757794-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/59462715-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/414663585-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/61157826-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/419423704-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/132450233-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/421827453-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/99826025-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/110330925-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/98421779-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/82084019-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/105581403-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/109756016-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/411026199-380_Missing Gas Capacity</t>
-  </si>
-  <si>
     <t>Aggregated Plant - EMBER Gap - way/162960205-380_Missing Gas Capacity</t>
   </si>
   <si>
@@ -2229,102 +2229,102 @@
     <t>Valle Secolo geothermal power plant_2</t>
   </si>
   <si>
+    <t>Aggregated Plant - IRENA Gap - way/1100665914-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
     <t>Aggregated Plant - IRENA Gap - IT72-380_Missing Hydro Capacity</t>
   </si>
   <si>
-    <t>Aggregated Plant - IRENA Gap - way/1100665914-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
     <t>Aggregated Plant - IRENA Gap - way/59462263-380_Missing Hydro Capacity</t>
   </si>
   <si>
+    <t>Aggregated Plant - IRENA Gap - IT71-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/108020416-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/144005863-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - IT21-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/64200868-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/75602396-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/82083756-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/491424937-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/72466334-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/419423704-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/104359058-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/96190189-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/116517585-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - IT71-400_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - IT36-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - IT53-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/114931087-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/61626687-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/338753171-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - IT93-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - IT10-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - IT31-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/61712456-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
     <t>Aggregated Plant - IRENA Gap - IT30-500_Missing Hydro Capacity</t>
   </si>
   <si>
     <t>Aggregated Plant - IRENA Gap - IT7-380_Missing Hydro Capacity</t>
   </si>
   <si>
+    <t>Aggregated Plant - IRENA Gap - way/1137611914-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - IT72-400_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/109588422-380_Missing Hydro Capacity</t>
+  </si>
+  <si>
     <t>Aggregated Plant - IRENA Gap - way/339703159-380_Missing Hydro Capacity</t>
   </si>
   <si>
-    <t>Aggregated Plant - IRENA Gap - way/61712456-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - IT53-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/75602396-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/109588422-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - IT72-400_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/1137611914-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/104359058-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/338753171-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - IT93-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - IT10-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/419423704-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/491424937-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/72466334-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/82083756-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/114931087-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - IT31-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/64200868-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/144005863-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/116517585-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/96190189-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - IT21-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - IT36-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - IT71-400_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - IT71-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/108020416-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/61626687-380_Missing Hydro Capacity</t>
-  </si>
-  <si>
     <t>Baschi hydroelectric plant_</t>
   </si>
   <si>
@@ -2625,21 +2625,21 @@
     <t>annual</t>
   </si>
   <si>
+    <t>Aggregated Plant - IRENA Gap - ITA_68_Missing Solar Capacity</t>
+  </si>
+  <si>
     <t>Aggregated Plant - IRENA Gap - ITA_30_Missing Solar Capacity</t>
   </si>
   <si>
-    <t>Aggregated Plant - IRENA Gap - ITA_68_Missing Solar Capacity</t>
+    <t>Aggregated Plant - IRENA Gap - ITA_73_Missing Onshore wind energy Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - ITA_22_Missing Onshore wind energy Capacity</t>
   </si>
   <si>
     <t>Aggregated Plant - IRENA Gap - ITA_96_Missing Onshore wind energy Capacity</t>
   </si>
   <si>
-    <t>Aggregated Plant - IRENA Gap - ITA_73_Missing Onshore wind energy Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - ITA_22_Missing Onshore wind energy Capacity</t>
-  </si>
-  <si>
     <t>AF</t>
   </si>
   <si>
@@ -3231,18 +3231,18 @@
     <t>ccs retrofit of -- Sulcis power station_Unit 3</t>
   </si>
   <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/409439916-380_Missing Coal Capacity</t>
+  </si>
+  <si>
     <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/418902800-380_Missing Coal Capacity</t>
   </si>
   <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/409439916-380_Missing Coal Capacity</t>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/303915533-380_Missing Coal Capacity</t>
   </si>
   <si>
     <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/82767145-380_Missing Coal Capacity</t>
   </si>
   <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/303915533-380_Missing Coal Capacity</t>
-  </si>
-  <si>
     <t>ccs retrofit of -- Brindisi Sud power station_Unit 1</t>
   </si>
   <si>
@@ -3531,124 +3531,124 @@
     <t>ccs retrofit of -- Aggregated Plant</t>
   </si>
   <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/105757794-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/172302572-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/162828577-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/416989699-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/59462715-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/109993642-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/110330925-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/100407576-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/132450233-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/116797658-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/338753171-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/414663585-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/82078641-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/98421779-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/98900549-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/419423704-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/149997403-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/162960205-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/103974940-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/199675964-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/103653592-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/1137611914-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/107438024-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/432729521-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/105581403-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/255011550-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/181125039-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/339104227-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/158739183-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/133601335-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/99826025-380_Missing Gas Capacity</t>
+  </si>
+  <si>
     <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/145665799-380_Missing Gas Capacity</t>
   </si>
   <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/339104227-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/158739183-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/133601335-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/181125039-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/416989699-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/162828577-380_Missing Gas Capacity</t>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/109756016-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/103381531-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/82084019-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/60725875-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/421827453-380_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/411026199-380_Missing Gas Capacity</t>
   </si>
   <si>
     <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/82767145-380_Missing Gas Capacity</t>
   </si>
   <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/105757794-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/99826025-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/103974940-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/199675964-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/82078641-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/103653592-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/1137611914-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/172302572-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/255011550-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/105581403-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/103381531-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/109756016-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/411026199-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/107438024-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/98900549-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/116797658-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/338753171-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/110330925-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/414663585-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/60725875-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/421827453-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/82084019-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/100407576-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/149997403-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/132450233-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/419423704-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/162960205-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/432729521-380_Missing Gas Capacity</t>
-  </si>
-  <si>
     <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/61157826-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/109993642-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/59462715-380_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/98421779-380_Missing Gas Capacity</t>
   </si>
   <si>
     <t>ccs retrofit of -- Tavazzano power station_CCGT8, timepoint 1</t>
@@ -4052,7 +4052,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F04A458-1947-47EC-9E68-C8F9B7C9FF47}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6072BCCD-A21F-4AF9-A2E5-13281056A04F}">
   <dimension ref="B9:T278"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -4128,7 +4128,7 @@
         <v>33</v>
       </c>
       <c r="D11" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E11">
         <v>0.12764790000000001</v>
@@ -4184,7 +4184,7 @@
         <v>33</v>
       </c>
       <c r="D12" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E12">
         <v>0.12764790000000001</v>
@@ -4576,7 +4576,7 @@
         <v>33</v>
       </c>
       <c r="D19" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E19">
         <v>0.260522535</v>
@@ -4632,7 +4632,7 @@
         <v>33</v>
       </c>
       <c r="D20" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E20">
         <v>0.260522535</v>
@@ -4688,7 +4688,7 @@
         <v>33</v>
       </c>
       <c r="D21" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E21">
         <v>0.260522535</v>
@@ -4744,7 +4744,7 @@
         <v>33</v>
       </c>
       <c r="D22" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E22">
         <v>0.28056272999999998</v>
@@ -4800,7 +4800,7 @@
         <v>33</v>
       </c>
       <c r="D23" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E23">
         <v>0.28056272999999998</v>
@@ -4856,7 +4856,7 @@
         <v>33</v>
       </c>
       <c r="D24" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E24">
         <v>0.28056272999999998</v>
@@ -4912,7 +4912,7 @@
         <v>49</v>
       </c>
       <c r="D25" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E25">
         <v>0.41750406250000005</v>
@@ -4968,7 +4968,7 @@
         <v>49</v>
       </c>
       <c r="D26" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="E26">
         <v>0.44431624999999997</v>
@@ -5024,7 +5024,7 @@
         <v>49</v>
       </c>
       <c r="D27" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="E27">
         <v>0.38303124999999993</v>
@@ -5080,7 +5080,7 @@
         <v>49</v>
       </c>
       <c r="D28" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="E28">
         <v>0.44431624999999997</v>
@@ -5136,7 +5136,7 @@
         <v>49</v>
       </c>
       <c r="D29" t="s">
-        <v>77</v>
+        <v>54</v>
       </c>
       <c r="E29">
         <v>0.41750406249999999</v>
@@ -5192,7 +5192,7 @@
         <v>49</v>
       </c>
       <c r="D30" t="s">
-        <v>77</v>
+        <v>54</v>
       </c>
       <c r="E30">
         <v>0.41750406249999999</v>
@@ -5248,7 +5248,7 @@
         <v>49</v>
       </c>
       <c r="D31" t="s">
-        <v>77</v>
+        <v>54</v>
       </c>
       <c r="E31">
         <v>0.41750406249999999</v>
@@ -5360,7 +5360,7 @@
         <v>49</v>
       </c>
       <c r="D33" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="E33">
         <v>0.41750406249999999</v>
@@ -5528,7 +5528,7 @@
         <v>49</v>
       </c>
       <c r="D36" t="s">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="E36">
         <v>0.41750406249999999</v>
@@ -5584,7 +5584,7 @@
         <v>49</v>
       </c>
       <c r="D37" t="s">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="E37">
         <v>0.41750406249999999</v>
@@ -5640,7 +5640,7 @@
         <v>49</v>
       </c>
       <c r="D38" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E38">
         <v>0.41750406249999999</v>
@@ -5696,7 +5696,7 @@
         <v>49</v>
       </c>
       <c r="D39" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E39">
         <v>0.41750406249999999</v>
@@ -5752,7 +5752,7 @@
         <v>49</v>
       </c>
       <c r="D40" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="E40">
         <v>0.3983525</v>
@@ -5808,7 +5808,7 @@
         <v>49</v>
       </c>
       <c r="D41" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="E41">
         <v>0.41750406249999999</v>
@@ -5864,7 +5864,7 @@
         <v>49</v>
       </c>
       <c r="D42" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="E42">
         <v>0.41750406249999999</v>
@@ -5920,7 +5920,7 @@
         <v>49</v>
       </c>
       <c r="D43" t="s">
-        <v>69</v>
+        <v>51</v>
       </c>
       <c r="E43">
         <v>0.41750406249999999</v>
@@ -5976,7 +5976,7 @@
         <v>49</v>
       </c>
       <c r="D44" t="s">
-        <v>69</v>
+        <v>51</v>
       </c>
       <c r="E44">
         <v>0.41750406249999999</v>
@@ -6032,7 +6032,7 @@
         <v>49</v>
       </c>
       <c r="D45" t="s">
-        <v>85</v>
+        <v>71</v>
       </c>
       <c r="E45">
         <v>0.41750406249999999</v>
@@ -6088,7 +6088,7 @@
         <v>49</v>
       </c>
       <c r="D46" t="s">
-        <v>85</v>
+        <v>71</v>
       </c>
       <c r="E46">
         <v>0.41750406249999999</v>
@@ -6144,7 +6144,7 @@
         <v>49</v>
       </c>
       <c r="D47" t="s">
-        <v>85</v>
+        <v>71</v>
       </c>
       <c r="E47">
         <v>0.41750406249999999</v>
@@ -6200,7 +6200,7 @@
         <v>49</v>
       </c>
       <c r="D48" t="s">
-        <v>85</v>
+        <v>71</v>
       </c>
       <c r="E48">
         <v>0.41750406249999999</v>
@@ -6256,7 +6256,7 @@
         <v>49</v>
       </c>
       <c r="D49" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E49">
         <v>0.40218281250000004</v>
@@ -6312,7 +6312,7 @@
         <v>49</v>
       </c>
       <c r="D50" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E50">
         <v>0.40218281250000004</v>
@@ -6368,7 +6368,7 @@
         <v>49</v>
       </c>
       <c r="D51" t="s">
-        <v>61</v>
+        <v>74</v>
       </c>
       <c r="E51">
         <v>0.41750406249999999</v>
@@ -6424,7 +6424,7 @@
         <v>49</v>
       </c>
       <c r="D52" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="E52">
         <v>0.45963749999999998</v>
@@ -6480,7 +6480,7 @@
         <v>49</v>
       </c>
       <c r="D53" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="E53">
         <v>0.41750406249999999</v>
@@ -6592,7 +6592,7 @@
         <v>49</v>
       </c>
       <c r="D55" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="E55">
         <v>0.41750406249999999</v>
@@ -6648,7 +6648,7 @@
         <v>49</v>
       </c>
       <c r="D56" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="E56">
         <v>0.41750406249999999</v>
@@ -6704,7 +6704,7 @@
         <v>49</v>
       </c>
       <c r="D57" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="E57">
         <v>0.41750406249999999</v>
@@ -6760,7 +6760,7 @@
         <v>49</v>
       </c>
       <c r="D58" t="s">
-        <v>87</v>
+        <v>69</v>
       </c>
       <c r="E58">
         <v>0.40218281249999999</v>
@@ -6816,7 +6816,7 @@
         <v>49</v>
       </c>
       <c r="D59" t="s">
-        <v>87</v>
+        <v>69</v>
       </c>
       <c r="E59">
         <v>0.40218281249999999</v>
@@ -6872,7 +6872,7 @@
         <v>49</v>
       </c>
       <c r="D60" t="s">
-        <v>87</v>
+        <v>69</v>
       </c>
       <c r="E60">
         <v>0.38303124999999993</v>
@@ -6928,7 +6928,7 @@
         <v>49</v>
       </c>
       <c r="D61" t="s">
-        <v>87</v>
+        <v>69</v>
       </c>
       <c r="E61">
         <v>0.38303124999999993</v>
@@ -7040,7 +7040,7 @@
         <v>49</v>
       </c>
       <c r="D63" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="E63">
         <v>0.41750406249999999</v>
@@ -7096,7 +7096,7 @@
         <v>49</v>
       </c>
       <c r="D64" t="s">
-        <v>67</v>
+        <v>53</v>
       </c>
       <c r="E64">
         <v>0.41750406249999999</v>
@@ -7152,7 +7152,7 @@
         <v>49</v>
       </c>
       <c r="D65" t="s">
-        <v>67</v>
+        <v>53</v>
       </c>
       <c r="E65">
         <v>0.41750406249999999</v>
@@ -7208,7 +7208,7 @@
         <v>49</v>
       </c>
       <c r="D66" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="E66">
         <v>0.41750406249999999</v>
@@ -7376,7 +7376,7 @@
         <v>49</v>
       </c>
       <c r="D69" t="s">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="E69">
         <v>0.41750406249999999</v>
@@ -7432,7 +7432,7 @@
         <v>49</v>
       </c>
       <c r="D70" t="s">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="E70">
         <v>0.41750406249999999</v>
@@ -7488,7 +7488,7 @@
         <v>49</v>
       </c>
       <c r="D71" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="E71">
         <v>0.41750406249999999</v>
@@ -7544,7 +7544,7 @@
         <v>49</v>
       </c>
       <c r="D72" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="E72">
         <v>0.41750406249999999</v>
@@ -7600,7 +7600,7 @@
         <v>49</v>
       </c>
       <c r="D73" t="s">
-        <v>53</v>
+        <v>73</v>
       </c>
       <c r="E73">
         <v>0.41750406249999999</v>
@@ -7656,7 +7656,7 @@
         <v>49</v>
       </c>
       <c r="D74" t="s">
-        <v>53</v>
+        <v>73</v>
       </c>
       <c r="E74">
         <v>0.41750406249999999</v>
@@ -7712,7 +7712,7 @@
         <v>49</v>
       </c>
       <c r="D75" t="s">
-        <v>62</v>
+        <v>87</v>
       </c>
       <c r="E75">
         <v>0.42899500000000002</v>
@@ -7768,7 +7768,7 @@
         <v>49</v>
       </c>
       <c r="D76" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="E76">
         <v>0.41750406249999999</v>
@@ -7824,7 +7824,7 @@
         <v>49</v>
       </c>
       <c r="D77" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="E77">
         <v>0.41750406249999999</v>
@@ -8104,7 +8104,7 @@
         <v>49</v>
       </c>
       <c r="D82" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="E82">
         <v>0.41750406249999999</v>
@@ -8160,7 +8160,7 @@
         <v>49</v>
       </c>
       <c r="D83" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="E83">
         <v>0.41750406249999999</v>
@@ -8216,7 +8216,7 @@
         <v>49</v>
       </c>
       <c r="D84" t="s">
-        <v>73</v>
+        <v>56</v>
       </c>
       <c r="E84">
         <v>0.41750406249999999</v>
@@ -8272,7 +8272,7 @@
         <v>49</v>
       </c>
       <c r="D85" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E85">
         <v>0.41750406249999999</v>
@@ -8328,7 +8328,7 @@
         <v>49</v>
       </c>
       <c r="D86" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E86">
         <v>0.41750406249999999</v>
@@ -8384,7 +8384,7 @@
         <v>49</v>
       </c>
       <c r="D87" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="E87">
         <v>0.41750406249999999</v>
@@ -8440,7 +8440,7 @@
         <v>49</v>
       </c>
       <c r="D88" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="E88">
         <v>0.41750406249999999</v>
@@ -8496,7 +8496,7 @@
         <v>49</v>
       </c>
       <c r="D89" t="s">
-        <v>68</v>
+        <v>52</v>
       </c>
       <c r="E89">
         <v>0.44431624999999997</v>
@@ -8552,7 +8552,7 @@
         <v>49</v>
       </c>
       <c r="D90" t="s">
-        <v>68</v>
+        <v>52</v>
       </c>
       <c r="E90">
         <v>0.41750406249999999</v>
@@ -8608,7 +8608,7 @@
         <v>49</v>
       </c>
       <c r="D91" t="s">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="E91">
         <v>0.41750406249999999</v>
@@ -8664,7 +8664,7 @@
         <v>49</v>
       </c>
       <c r="D92" t="s">
-        <v>61</v>
+        <v>74</v>
       </c>
       <c r="E92">
         <v>0.44431624999999997</v>
@@ -8720,7 +8720,7 @@
         <v>49</v>
       </c>
       <c r="D93" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E93">
         <v>0.41750406249999999</v>
@@ -8776,7 +8776,7 @@
         <v>49</v>
       </c>
       <c r="D94" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E94">
         <v>0.41750406249999999</v>
@@ -8832,7 +8832,7 @@
         <v>49</v>
       </c>
       <c r="D95" t="s">
-        <v>74</v>
+        <v>58</v>
       </c>
       <c r="E95">
         <v>0.41750406249999999</v>
@@ -8888,7 +8888,7 @@
         <v>49</v>
       </c>
       <c r="D96" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E96">
         <v>0.41750406249999999</v>
@@ -8944,7 +8944,7 @@
         <v>49</v>
       </c>
       <c r="D97" t="s">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="E97">
         <v>0.41750406249999999</v>
@@ -9056,7 +9056,7 @@
         <v>49</v>
       </c>
       <c r="D99" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E99">
         <v>0.45963749999999998</v>
@@ -9112,7 +9112,7 @@
         <v>49</v>
       </c>
       <c r="D100" t="s">
-        <v>76</v>
+        <v>55</v>
       </c>
       <c r="E100">
         <v>0.45963749999999998</v>
@@ -9168,7 +9168,7 @@
         <v>49</v>
       </c>
       <c r="D101" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E101">
         <v>0.45963749999999998</v>
@@ -9224,7 +9224,7 @@
         <v>49</v>
       </c>
       <c r="D102" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="E102">
         <v>0.41750406249999999</v>
@@ -9280,7 +9280,7 @@
         <v>49</v>
       </c>
       <c r="D103" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="E103">
         <v>0.41750406249999999</v>
@@ -9336,7 +9336,7 @@
         <v>49</v>
       </c>
       <c r="D104" t="s">
-        <v>67</v>
+        <v>53</v>
       </c>
       <c r="E104">
         <v>0.41750406249999999</v>
@@ -9392,7 +9392,7 @@
         <v>49</v>
       </c>
       <c r="D105" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="E105">
         <v>0.41750406249999999</v>
@@ -9448,7 +9448,7 @@
         <v>49</v>
       </c>
       <c r="D106" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="E106">
         <v>0.38303124999999993</v>
@@ -9504,7 +9504,7 @@
         <v>49</v>
       </c>
       <c r="D107" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="E107">
         <v>0.38303124999999993</v>
@@ -9560,7 +9560,7 @@
         <v>49</v>
       </c>
       <c r="D108" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="E108">
         <v>0.4021828125000001</v>
@@ -9672,7 +9672,7 @@
         <v>49</v>
       </c>
       <c r="D110" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
       <c r="E110">
         <v>0.41750406249999999</v>
@@ -9728,7 +9728,7 @@
         <v>49</v>
       </c>
       <c r="D111" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="E111">
         <v>0.3983525</v>
@@ -9840,7 +9840,7 @@
         <v>49</v>
       </c>
       <c r="D113" t="s">
-        <v>62</v>
+        <v>87</v>
       </c>
       <c r="E113">
         <v>0.41750406249999999</v>
@@ -10344,7 +10344,7 @@
         <v>49</v>
       </c>
       <c r="D122" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E122">
         <v>0.45963749999999998</v>
@@ -10400,7 +10400,7 @@
         <v>49</v>
       </c>
       <c r="D123" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E123">
         <v>0.45963749999999998</v>
@@ -10456,7 +10456,7 @@
         <v>49</v>
       </c>
       <c r="D124" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E124">
         <v>0.45963749999999998</v>
@@ -10512,7 +10512,7 @@
         <v>49</v>
       </c>
       <c r="D125" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E125">
         <v>0.45963749999999998</v>
@@ -10736,7 +10736,7 @@
         <v>49</v>
       </c>
       <c r="D129" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E129">
         <v>0.45963749999999998</v>
@@ -11072,7 +11072,7 @@
         <v>49</v>
       </c>
       <c r="D135" t="s">
-        <v>16</v>
+        <v>79</v>
       </c>
       <c r="E135">
         <v>0.45963749999999998</v>
@@ -11184,7 +11184,7 @@
         <v>49</v>
       </c>
       <c r="D137" t="s">
-        <v>65</v>
+        <v>16</v>
       </c>
       <c r="E137">
         <v>0.45963749999999998</v>
@@ -11240,7 +11240,7 @@
         <v>49</v>
       </c>
       <c r="D138" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E138">
         <v>0.45963749999999998</v>
@@ -11296,7 +11296,7 @@
         <v>49</v>
       </c>
       <c r="D139" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E139">
         <v>0.45963749999999998</v>
@@ -11352,7 +11352,7 @@
         <v>49</v>
       </c>
       <c r="D140" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E140">
         <v>0.45963749999999998</v>
@@ -11408,7 +11408,7 @@
         <v>49</v>
       </c>
       <c r="D141" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E141">
         <v>0.45963749999999998</v>
@@ -11464,7 +11464,7 @@
         <v>49</v>
       </c>
       <c r="D142" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E142">
         <v>0.45963749999999998</v>
@@ -11520,7 +11520,7 @@
         <v>49</v>
       </c>
       <c r="D143" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E143">
         <v>0.45963749999999998</v>
@@ -11576,7 +11576,7 @@
         <v>49</v>
       </c>
       <c r="D144" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E144">
         <v>0.45963749999999998</v>
@@ -11688,7 +11688,7 @@
         <v>49</v>
       </c>
       <c r="D146" t="s">
-        <v>80</v>
+        <v>35</v>
       </c>
       <c r="E146">
         <v>0.45963749999999998</v>
@@ -12024,7 +12024,7 @@
         <v>49</v>
       </c>
       <c r="D152" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E152">
         <v>0.45963749999999998</v>
@@ -12080,7 +12080,7 @@
         <v>49</v>
       </c>
       <c r="D153" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E153">
         <v>0.45963749999999998</v>
@@ -12136,7 +12136,7 @@
         <v>49</v>
       </c>
       <c r="D154" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E154">
         <v>0.45963749999999998</v>
@@ -12192,7 +12192,7 @@
         <v>49</v>
       </c>
       <c r="D155" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E155">
         <v>0.45963749999999998</v>
@@ -12304,7 +12304,7 @@
         <v>49</v>
       </c>
       <c r="D157" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E157">
         <v>0.45963749999999998</v>
@@ -12360,7 +12360,7 @@
         <v>49</v>
       </c>
       <c r="D158" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E158">
         <v>0.45963749999999998</v>
@@ -12416,7 +12416,7 @@
         <v>49</v>
       </c>
       <c r="D159" t="s">
-        <v>34</v>
+        <v>84</v>
       </c>
       <c r="E159">
         <v>0.45963749999999998</v>
@@ -12696,7 +12696,7 @@
         <v>49</v>
       </c>
       <c r="D164" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="E164">
         <v>0.41367375000000001</v>
@@ -13536,7 +13536,7 @@
         <v>49</v>
       </c>
       <c r="D179" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E179">
         <v>0.39835250000000011</v>
@@ -13592,7 +13592,7 @@
         <v>49</v>
       </c>
       <c r="D180" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E180">
         <v>0.39835250000000011</v>
@@ -13816,7 +13816,7 @@
         <v>49</v>
       </c>
       <c r="D184" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="E184">
         <v>0.41367375000000001</v>
@@ -13872,7 +13872,7 @@
         <v>49</v>
       </c>
       <c r="D185" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="E185">
         <v>0.41367375000000001</v>
@@ -14600,7 +14600,7 @@
         <v>49</v>
       </c>
       <c r="D198" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="E198">
         <v>0.42899500000000002</v>
@@ -14824,7 +14824,7 @@
         <v>49</v>
       </c>
       <c r="D202" t="s">
-        <v>76</v>
+        <v>55</v>
       </c>
       <c r="E202">
         <v>0.3983525</v>
@@ -15552,7 +15552,7 @@
         <v>49</v>
       </c>
       <c r="D215" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="E215">
         <v>0.38303124999999993</v>
@@ -15720,7 +15720,7 @@
         <v>49</v>
       </c>
       <c r="D218" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E218">
         <v>0.42899499999999996</v>
@@ -15776,7 +15776,7 @@
         <v>49</v>
       </c>
       <c r="D219" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E219">
         <v>0.42899499999999996</v>
@@ -15944,7 +15944,7 @@
         <v>49</v>
       </c>
       <c r="D222" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="E222">
         <v>0.38303124999999993</v>
@@ -16000,7 +16000,7 @@
         <v>49</v>
       </c>
       <c r="D223" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="E223">
         <v>0.25280062500000006</v>
@@ -16056,7 +16056,7 @@
         <v>49</v>
       </c>
       <c r="D224" t="s">
-        <v>68</v>
+        <v>52</v>
       </c>
       <c r="E224">
         <v>0.24514000000000002</v>
@@ -16112,7 +16112,7 @@
         <v>49</v>
       </c>
       <c r="D225" t="s">
-        <v>68</v>
+        <v>52</v>
       </c>
       <c r="E225">
         <v>0.24514000000000002</v>
@@ -16168,7 +16168,7 @@
         <v>49</v>
       </c>
       <c r="D226" t="s">
-        <v>62</v>
+        <v>87</v>
       </c>
       <c r="E226">
         <v>0.21066718750000002</v>
@@ -16672,7 +16672,7 @@
         <v>49</v>
       </c>
       <c r="D235" t="s">
-        <v>69</v>
+        <v>51</v>
       </c>
       <c r="E235">
         <v>0.21449750000000001</v>
@@ -16952,7 +16952,7 @@
         <v>49</v>
       </c>
       <c r="D240" t="s">
-        <v>68</v>
+        <v>52</v>
       </c>
       <c r="E240">
         <v>0.23747937499999999</v>
@@ -17064,7 +17064,7 @@
         <v>49</v>
       </c>
       <c r="D242" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="E242">
         <v>0.21449750000000001</v>
@@ -17260,7 +17260,7 @@
         <v>49</v>
       </c>
       <c r="D247" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="E247">
         <v>0.27578249999999999</v>
@@ -17330,7 +17330,7 @@
         <v>49</v>
       </c>
       <c r="D249" t="s">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="E249">
         <v>0.27578249999999999</v>
@@ -17470,7 +17470,7 @@
         <v>49</v>
       </c>
       <c r="D253" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="E253">
         <v>0.23747937499999999</v>
@@ -17505,7 +17505,7 @@
         <v>49</v>
       </c>
       <c r="D254" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="E254">
         <v>0.23747937499999999</v>
@@ -17540,7 +17540,7 @@
         <v>49</v>
       </c>
       <c r="D255" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="E255">
         <v>0.23747937499999999</v>
@@ -17575,7 +17575,7 @@
         <v>49</v>
       </c>
       <c r="D256" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E256">
         <v>0.26429156249999997</v>
@@ -17610,7 +17610,7 @@
         <v>49</v>
       </c>
       <c r="D257" t="s">
-        <v>77</v>
+        <v>54</v>
       </c>
       <c r="E257">
         <v>0.23747937499999999</v>
@@ -17645,7 +17645,7 @@
         <v>49</v>
       </c>
       <c r="D258" t="s">
-        <v>77</v>
+        <v>54</v>
       </c>
       <c r="E258">
         <v>0.23747937499999999</v>
@@ -17680,7 +17680,7 @@
         <v>49</v>
       </c>
       <c r="D259" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
       <c r="E259">
         <v>0.22215812499999998</v>
@@ -17715,7 +17715,7 @@
         <v>49</v>
       </c>
       <c r="D260" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="E260">
         <v>0.24514000000000002</v>
@@ -17750,7 +17750,7 @@
         <v>49</v>
       </c>
       <c r="D261" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="E261">
         <v>0.24514000000000002</v>
@@ -17785,7 +17785,7 @@
         <v>49</v>
       </c>
       <c r="D262" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="E262">
         <v>0.24514000000000002</v>
@@ -17855,7 +17855,7 @@
         <v>439</v>
       </c>
       <c r="D264" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="E264">
         <v>0.35238875000000003</v>
@@ -17995,7 +17995,7 @@
         <v>439</v>
       </c>
       <c r="D268" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E268">
         <v>0.206836875</v>
@@ -18170,7 +18170,7 @@
         <v>439</v>
       </c>
       <c r="D273" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="E273">
         <v>0.23747937499999999</v>
@@ -18378,7 +18378,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3CBAE07D-F4BC-460B-B273-31EFE364FCF9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BC078732-979A-4F34-9B86-66591310E0A7}">
   <dimension ref="B9:T672"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -18460,7 +18460,7 @@
         <v>2022</v>
       </c>
       <c r="F11">
-        <v>1.0679322033898306</v>
+        <v>0.39440677966101695</v>
       </c>
       <c r="G11">
         <v>0.306425</v>
@@ -18513,13 +18513,13 @@
         <v>2022</v>
       </c>
       <c r="F12">
-        <v>0.49149152542372881</v>
+        <v>0.35800000000000004</v>
       </c>
       <c r="G12">
         <v>0.306425</v>
       </c>
       <c r="H12">
-        <v>3850.0000000000005</v>
+        <v>3850.0000000000009</v>
       </c>
       <c r="I12">
         <v>143</v>
@@ -18619,19 +18619,19 @@
         <v>2022</v>
       </c>
       <c r="F14">
-        <v>0.39440677966101695</v>
+        <v>0.24877966101694915</v>
       </c>
       <c r="G14">
-        <v>0.306425</v>
+        <v>0.28891500000000003</v>
       </c>
       <c r="H14">
-        <v>3850.0000000000005</v>
+        <v>4427.5</v>
       </c>
       <c r="I14">
-        <v>143</v>
+        <v>157.30000000000001</v>
       </c>
       <c r="J14">
-        <v>8.4</v>
+        <v>9.240000000000002</v>
       </c>
       <c r="K14">
         <v>50</v>
@@ -18672,13 +18672,13 @@
         <v>2022</v>
       </c>
       <c r="F15">
-        <v>0.35800000000000004</v>
+        <v>0.51576271186440681</v>
       </c>
       <c r="G15">
         <v>0.306425</v>
       </c>
       <c r="H15">
-        <v>3850.0000000000009</v>
+        <v>3850.0000000000005</v>
       </c>
       <c r="I15">
         <v>143</v>
@@ -18725,19 +18725,19 @@
         <v>2022</v>
       </c>
       <c r="F16">
-        <v>0.24877966101694915</v>
+        <v>1.0679322033898306</v>
       </c>
       <c r="G16">
-        <v>0.28891500000000003</v>
+        <v>0.306425</v>
       </c>
       <c r="H16">
-        <v>4427.5</v>
+        <v>3850.0000000000005</v>
       </c>
       <c r="I16">
-        <v>157.30000000000001</v>
+        <v>143</v>
       </c>
       <c r="J16">
-        <v>9.240000000000002</v>
+        <v>8.4</v>
       </c>
       <c r="K16">
         <v>50</v>
@@ -18831,7 +18831,7 @@
         <v>2022</v>
       </c>
       <c r="F18">
-        <v>0.51576271186440681</v>
+        <v>0.49149152542372881</v>
       </c>
       <c r="G18">
         <v>0.306425</v>
@@ -18878,7 +18878,7 @@
         <v>13</v>
       </c>
       <c r="D19" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="E19">
         <v>2008</v>
@@ -18931,7 +18931,7 @@
         <v>13</v>
       </c>
       <c r="D20" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="E20">
         <v>1998</v>
@@ -18984,7 +18984,7 @@
         <v>13</v>
       </c>
       <c r="D21" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="E21">
         <v>2008</v>
@@ -19037,7 +19037,7 @@
         <v>13</v>
       </c>
       <c r="D22" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E22">
         <v>2001</v>
@@ -19090,7 +19090,7 @@
         <v>13</v>
       </c>
       <c r="D23" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E23">
         <v>2013</v>
@@ -19143,7 +19143,7 @@
         <v>13</v>
       </c>
       <c r="D24" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E24">
         <v>1965</v>
@@ -19302,7 +19302,7 @@
         <v>13</v>
       </c>
       <c r="D27" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="E27">
         <v>2018</v>
@@ -19355,7 +19355,7 @@
         <v>13</v>
       </c>
       <c r="D28" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="E28">
         <v>2009</v>
@@ -19467,19 +19467,19 @@
         <v>2022</v>
       </c>
       <c r="F30">
-        <v>0.1997687861271675</v>
+        <v>0.61803468208092449</v>
       </c>
       <c r="G30">
-        <v>0.29766999999999999</v>
+        <v>0.31518000000000002</v>
       </c>
       <c r="H30">
-        <v>2530</v>
+        <v>2200</v>
       </c>
       <c r="I30">
-        <v>72.600000000000009</v>
+        <v>66</v>
       </c>
       <c r="J30">
-        <v>5.7750000000000004</v>
+        <v>5.25</v>
       </c>
       <c r="K30">
         <v>50</v>
@@ -19573,19 +19573,19 @@
         <v>2022</v>
       </c>
       <c r="F32">
-        <v>0.61803468208092449</v>
+        <v>0.1997687861271675</v>
       </c>
       <c r="G32">
-        <v>0.31518000000000002</v>
+        <v>0.29766999999999999</v>
       </c>
       <c r="H32">
-        <v>2200</v>
+        <v>2530</v>
       </c>
       <c r="I32">
-        <v>66</v>
+        <v>72.600000000000009</v>
       </c>
       <c r="J32">
-        <v>5.25</v>
+        <v>5.7750000000000004</v>
       </c>
       <c r="K32">
         <v>50</v>
@@ -19620,7 +19620,7 @@
         <v>33</v>
       </c>
       <c r="D33" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E33">
         <v>1992</v>
@@ -19673,7 +19673,7 @@
         <v>33</v>
       </c>
       <c r="D34" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E34">
         <v>1993</v>
@@ -19832,7 +19832,7 @@
         <v>33</v>
       </c>
       <c r="D37" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E37">
         <v>1991</v>
@@ -19885,7 +19885,7 @@
         <v>33</v>
       </c>
       <c r="D38" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E38">
         <v>1992</v>
@@ -19938,7 +19938,7 @@
         <v>33</v>
       </c>
       <c r="D39" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E39">
         <v>1993</v>
@@ -19991,7 +19991,7 @@
         <v>33</v>
       </c>
       <c r="D40" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E40">
         <v>2009</v>
@@ -20044,7 +20044,7 @@
         <v>33</v>
       </c>
       <c r="D41" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E41">
         <v>2010</v>
@@ -20097,7 +20097,7 @@
         <v>33</v>
       </c>
       <c r="D42" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E42">
         <v>2010</v>
@@ -20156,7 +20156,7 @@
         <v>2022</v>
       </c>
       <c r="F43">
-        <v>0.20557907614758497</v>
+        <v>0.1548783373961905</v>
       </c>
       <c r="G43">
         <v>0.50778999999999996</v>
@@ -20168,7 +20168,7 @@
         <v>36.300000000000004</v>
       </c>
       <c r="J43">
-        <v>3.4650000000000003</v>
+        <v>3.4649999999999999</v>
       </c>
       <c r="K43">
         <v>50</v>
@@ -20209,7 +20209,7 @@
         <v>2022</v>
       </c>
       <c r="F44">
-        <v>0.20212110068999706</v>
+        <v>0.21283595422055113</v>
       </c>
       <c r="G44">
         <v>0.50778999999999996</v>
@@ -20262,19 +20262,19 @@
         <v>2022</v>
       </c>
       <c r="F45">
-        <v>0.19481551873734657</v>
+        <v>0.39839773581787374</v>
       </c>
       <c r="G45">
-        <v>0.50778999999999996</v>
+        <v>0.52529999999999999</v>
       </c>
       <c r="H45">
-        <v>1265</v>
+        <v>1100</